--- a/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
+++ b/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1331"/>
+  <dimension ref="A1:K1330"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -16132,13 +16132,13 @@
         <v>449</v>
       </c>
       <c r="B450" t="str">
-        <v>-</v>
+        <v>FG-400259</v>
       </c>
       <c r="C450" t="str">
-        <v>UPVC- BRASS ELBOW 90 (1/2)</v>
+        <v>UPVC BRASS ELBOW (1)</v>
       </c>
       <c r="D450" t="str">
-        <v>UPVC- BRASS ELBOW 90</v>
+        <v>UPVC BRASS ELBOW</v>
       </c>
       <c r="E450" t="str">
         <v>UPVC Pipes &amp; Fittings</v>
@@ -16147,19 +16147,19 @@
         <v>General</v>
       </c>
       <c r="G450" t="str">
-        <v>1/2</v>
+        <v>1</v>
       </c>
       <c r="H450" t="str">
         <v>BOX</v>
       </c>
-      <c r="I450" t="str">
-        <v>-</v>
+      <c r="I450">
+        <v>70</v>
       </c>
       <c r="J450" t="str">
         <v>Active</v>
       </c>
       <c r="K450" t="str">
-        <v>UPVC- BRASS ELBOW 90. Available sizes: 1/2, 3/4, 1.</v>
+        <v>UPVC BRASS ELBOW. Available sizes: 1/2, 3/4, 1.</v>
       </c>
     </row>
     <row r="451">
@@ -16167,13 +16167,13 @@
         <v>450</v>
       </c>
       <c r="B451" t="str">
-        <v>-</v>
+        <v>FG-400257</v>
       </c>
       <c r="C451" t="str">
-        <v>UPVC- BRASS ELBOW 90 (3/4)</v>
+        <v>UPVC BRASS ELBOW (1/2)</v>
       </c>
       <c r="D451" t="str">
-        <v>UPVC- BRASS ELBOW 90</v>
+        <v>UPVC BRASS ELBOW</v>
       </c>
       <c r="E451" t="str">
         <v>UPVC Pipes &amp; Fittings</v>
@@ -16182,19 +16182,19 @@
         <v>General</v>
       </c>
       <c r="G451" t="str">
-        <v>3/4</v>
+        <v>1/2</v>
       </c>
       <c r="H451" t="str">
         <v>BOX</v>
       </c>
-      <c r="I451" t="str">
-        <v>-</v>
+      <c r="I451">
+        <v>210</v>
       </c>
       <c r="J451" t="str">
         <v>Active</v>
       </c>
       <c r="K451" t="str">
-        <v>UPVC- BRASS ELBOW 90. Available sizes: 1/2, 3/4, 1.</v>
+        <v>UPVC BRASS ELBOW. Available sizes: 1/2, 3/4, 1.</v>
       </c>
     </row>
     <row r="452">
@@ -16202,13 +16202,13 @@
         <v>451</v>
       </c>
       <c r="B452" t="str">
-        <v>-</v>
+        <v>FG-400258</v>
       </c>
       <c r="C452" t="str">
-        <v>UPVC- BRASS ELBOW 90 (1)</v>
+        <v>UPVC BRASS ELBOW (3/4)</v>
       </c>
       <c r="D452" t="str">
-        <v>UPVC- BRASS ELBOW 90</v>
+        <v>UPVC BRASS ELBOW</v>
       </c>
       <c r="E452" t="str">
         <v>UPVC Pipes &amp; Fittings</v>
@@ -16217,19 +16217,19 @@
         <v>General</v>
       </c>
       <c r="G452" t="str">
-        <v>1</v>
+        <v>3/4</v>
       </c>
       <c r="H452" t="str">
         <v>BOX</v>
       </c>
-      <c r="I452" t="str">
-        <v>-</v>
+      <c r="I452">
+        <v>100</v>
       </c>
       <c r="J452" t="str">
         <v>Active</v>
       </c>
       <c r="K452" t="str">
-        <v>UPVC- BRASS ELBOW 90. Available sizes: 1/2, 3/4, 1.</v>
+        <v>UPVC BRASS ELBOW. Available sizes: 1/2, 3/4, 1.</v>
       </c>
     </row>
     <row r="453">
@@ -36187,13 +36187,13 @@
         <v>1022</v>
       </c>
       <c r="B1023" t="str">
-        <v>-</v>
+        <v>FG-400585</v>
       </c>
       <c r="C1023" t="str">
-        <v>REDUCER (LW) (50 X 40)</v>
+        <v>AGRI REDUCER (50X40MM)</v>
       </c>
       <c r="D1023" t="str">
-        <v>REDUCER (LW)</v>
+        <v>AGRI REDUCER</v>
       </c>
       <c r="E1023" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36202,19 +36202,19 @@
         <v>General</v>
       </c>
       <c r="G1023" t="str">
-        <v>50 X 40</v>
+        <v>50X40MM</v>
       </c>
       <c r="H1023" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1023" t="str">
-        <v>-</v>
+      <c r="I1023">
+        <v>300</v>
       </c>
       <c r="J1023" t="str">
         <v>Active</v>
       </c>
       <c r="K1023" t="str">
-        <v>REDUCER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
       </c>
     </row>
     <row r="1024">
@@ -36222,13 +36222,13 @@
         <v>1023</v>
       </c>
       <c r="B1024" t="str">
-        <v>-</v>
+        <v>FG-400584</v>
       </c>
       <c r="C1024" t="str">
-        <v>REDUCER (LW) (63 X 40)</v>
+        <v>AGRI REDUCER (63X40MM)</v>
       </c>
       <c r="D1024" t="str">
-        <v>REDUCER (LW)</v>
+        <v>AGRI REDUCER</v>
       </c>
       <c r="E1024" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36237,19 +36237,19 @@
         <v>General</v>
       </c>
       <c r="G1024" t="str">
-        <v>63 X 40</v>
+        <v>63X40MM</v>
       </c>
       <c r="H1024" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1024" t="str">
-        <v>-</v>
+      <c r="I1024">
+        <v>200</v>
       </c>
       <c r="J1024" t="str">
         <v>Active</v>
       </c>
       <c r="K1024" t="str">
-        <v>REDUCER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
       </c>
     </row>
     <row r="1025">
@@ -36257,13 +36257,13 @@
         <v>1024</v>
       </c>
       <c r="B1025" t="str">
-        <v>-</v>
+        <v>FG-400583</v>
       </c>
       <c r="C1025" t="str">
-        <v>REDUCER (LW) (63 X 50)</v>
+        <v>AGRI REDUCER (63X50MM)</v>
       </c>
       <c r="D1025" t="str">
-        <v>REDUCER (LW)</v>
+        <v>AGRI REDUCER</v>
       </c>
       <c r="E1025" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36272,19 +36272,19 @@
         <v>General</v>
       </c>
       <c r="G1025" t="str">
-        <v>63 X 50</v>
+        <v>63X50MM</v>
       </c>
       <c r="H1025" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1025" t="str">
-        <v>-</v>
+      <c r="I1025">
+        <v>150</v>
       </c>
       <c r="J1025" t="str">
         <v>Active</v>
       </c>
       <c r="K1025" t="str">
-        <v>REDUCER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
       </c>
     </row>
     <row r="1026">
@@ -36292,13 +36292,13 @@
         <v>1025</v>
       </c>
       <c r="B1026" t="str">
-        <v>-</v>
+        <v>FG-400582</v>
       </c>
       <c r="C1026" t="str">
-        <v>REDUCER (LW) (75 X 40)</v>
+        <v>AGRI REDUCER (75X40MM)</v>
       </c>
       <c r="D1026" t="str">
-        <v>REDUCER (LW)</v>
+        <v>AGRI REDUCER</v>
       </c>
       <c r="E1026" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36307,19 +36307,19 @@
         <v>General</v>
       </c>
       <c r="G1026" t="str">
-        <v>75 X 40</v>
+        <v>75X40MM</v>
       </c>
       <c r="H1026" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1026" t="str">
-        <v>-</v>
+      <c r="I1026">
+        <v>100</v>
       </c>
       <c r="J1026" t="str">
         <v>Active</v>
       </c>
       <c r="K1026" t="str">
-        <v>REDUCER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
       </c>
     </row>
     <row r="1027">
@@ -36327,13 +36327,13 @@
         <v>1026</v>
       </c>
       <c r="B1027" t="str">
-        <v>-</v>
+        <v>FG-400581</v>
       </c>
       <c r="C1027" t="str">
-        <v>REDUCER (LW) (75 X 63)</v>
+        <v>AGRI REDUCER (75X50MM)</v>
       </c>
       <c r="D1027" t="str">
-        <v>REDUCER (LW)</v>
+        <v>AGRI REDUCER</v>
       </c>
       <c r="E1027" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36342,19 +36342,19 @@
         <v>General</v>
       </c>
       <c r="G1027" t="str">
-        <v>75 X 63</v>
+        <v>75X50MM</v>
       </c>
       <c r="H1027" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1027" t="str">
-        <v>-</v>
+      <c r="I1027">
+        <v>120</v>
       </c>
       <c r="J1027" t="str">
         <v>Active</v>
       </c>
       <c r="K1027" t="str">
-        <v>REDUCER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
       </c>
     </row>
     <row r="1028">
@@ -36362,13 +36362,13 @@
         <v>1027</v>
       </c>
       <c r="B1028" t="str">
-        <v>-</v>
+        <v>FG-400580</v>
       </c>
       <c r="C1028" t="str">
-        <v>REDUCER (LW) (90 X 50)</v>
+        <v>AGRI REDUCER (75X63MM)</v>
       </c>
       <c r="D1028" t="str">
-        <v>REDUCER (LW)</v>
+        <v>AGRI REDUCER</v>
       </c>
       <c r="E1028" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36377,19 +36377,19 @@
         <v>General</v>
       </c>
       <c r="G1028" t="str">
-        <v>90 X 50</v>
+        <v>75X63MM</v>
       </c>
       <c r="H1028" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1028" t="str">
-        <v>-</v>
+      <c r="I1028">
+        <v>100</v>
       </c>
       <c r="J1028" t="str">
         <v>Active</v>
       </c>
       <c r="K1028" t="str">
-        <v>REDUCER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
       </c>
     </row>
     <row r="1029">
@@ -36397,13 +36397,13 @@
         <v>1028</v>
       </c>
       <c r="B1029" t="str">
-        <v>-</v>
+        <v>FG-400579</v>
       </c>
       <c r="C1029" t="str">
-        <v>REDUCER (LW) (90 X 63)</v>
+        <v>AGRI REDUCER (90X50MM)</v>
       </c>
       <c r="D1029" t="str">
-        <v>REDUCER (LW)</v>
+        <v>AGRI REDUCER</v>
       </c>
       <c r="E1029" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36412,19 +36412,19 @@
         <v>General</v>
       </c>
       <c r="G1029" t="str">
-        <v>90 X 63</v>
+        <v>90X50MM</v>
       </c>
       <c r="H1029" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1029" t="str">
-        <v>-</v>
+      <c r="I1029">
+        <v>80</v>
       </c>
       <c r="J1029" t="str">
         <v>Active</v>
       </c>
       <c r="K1029" t="str">
-        <v>REDUCER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
       </c>
     </row>
     <row r="1030">
@@ -36432,13 +36432,13 @@
         <v>1029</v>
       </c>
       <c r="B1030" t="str">
-        <v>-</v>
+        <v>FG-400578</v>
       </c>
       <c r="C1030" t="str">
-        <v>REDUCER (LW) (90 X 75)</v>
+        <v>AGRI REDUCER (90X63MM)</v>
       </c>
       <c r="D1030" t="str">
-        <v>REDUCER (LW)</v>
+        <v>AGRI REDUCER</v>
       </c>
       <c r="E1030" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36447,19 +36447,19 @@
         <v>General</v>
       </c>
       <c r="G1030" t="str">
-        <v>90 X 75</v>
+        <v>90X63MM</v>
       </c>
       <c r="H1030" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1030" t="str">
-        <v>-</v>
+      <c r="I1030">
+        <v>70</v>
       </c>
       <c r="J1030" t="str">
         <v>Active</v>
       </c>
       <c r="K1030" t="str">
-        <v>REDUCER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
       </c>
     </row>
     <row r="1031">
@@ -36467,13 +36467,13 @@
         <v>1030</v>
       </c>
       <c r="B1031" t="str">
-        <v>-</v>
+        <v>FG-400577</v>
       </c>
       <c r="C1031" t="str">
-        <v>REDUCER (LW) (110 X 63)</v>
+        <v>AGRI REDUCER (90X75MM)</v>
       </c>
       <c r="D1031" t="str">
-        <v>REDUCER (LW)</v>
+        <v>AGRI REDUCER</v>
       </c>
       <c r="E1031" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36482,19 +36482,19 @@
         <v>General</v>
       </c>
       <c r="G1031" t="str">
-        <v>110 X 63</v>
+        <v>90X75MM</v>
       </c>
       <c r="H1031" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1031" t="str">
-        <v>-</v>
+      <c r="I1031">
+        <v>60</v>
       </c>
       <c r="J1031" t="str">
         <v>Active</v>
       </c>
       <c r="K1031" t="str">
-        <v>REDUCER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
       </c>
     </row>
     <row r="1032">
@@ -36502,13 +36502,13 @@
         <v>1031</v>
       </c>
       <c r="B1032" t="str">
-        <v>-</v>
+        <v>FG-400576</v>
       </c>
       <c r="C1032" t="str">
-        <v>REDUCER (LW) (110 X 75)</v>
+        <v>AGRI REDUCER (110X63MM)</v>
       </c>
       <c r="D1032" t="str">
-        <v>REDUCER (LW)</v>
+        <v>AGRI REDUCER</v>
       </c>
       <c r="E1032" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36517,19 +36517,19 @@
         <v>General</v>
       </c>
       <c r="G1032" t="str">
-        <v>110 X 75</v>
+        <v>110X63MM</v>
       </c>
       <c r="H1032" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1032" t="str">
-        <v>-</v>
+      <c r="I1032">
+        <v>45</v>
       </c>
       <c r="J1032" t="str">
         <v>Active</v>
       </c>
       <c r="K1032" t="str">
-        <v>REDUCER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
       </c>
     </row>
     <row r="1033">
@@ -36537,13 +36537,13 @@
         <v>1032</v>
       </c>
       <c r="B1033" t="str">
-        <v>-</v>
+        <v>FG-400575</v>
       </c>
       <c r="C1033" t="str">
-        <v>REDUCER (LW) (110 X 90)</v>
+        <v>AGRI REDUCER (110X75MM)</v>
       </c>
       <c r="D1033" t="str">
-        <v>REDUCER (LW)</v>
+        <v>AGRI REDUCER</v>
       </c>
       <c r="E1033" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36552,19 +36552,19 @@
         <v>General</v>
       </c>
       <c r="G1033" t="str">
-        <v>110 X 90</v>
+        <v>110X75MM</v>
       </c>
       <c r="H1033" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1033" t="str">
-        <v>-</v>
+      <c r="I1033">
+        <v>45</v>
       </c>
       <c r="J1033" t="str">
         <v>Active</v>
       </c>
       <c r="K1033" t="str">
-        <v>REDUCER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
       </c>
     </row>
     <row r="1034">
@@ -36572,13 +36572,13 @@
         <v>1033</v>
       </c>
       <c r="B1034" t="str">
-        <v>-</v>
+        <v>FG-400574</v>
       </c>
       <c r="C1034" t="str">
-        <v>REDUCER (LW) (140 X 110)</v>
+        <v>AGRI REDUCER (110X90MM)</v>
       </c>
       <c r="D1034" t="str">
-        <v>REDUCER (LW)</v>
+        <v>AGRI REDUCER</v>
       </c>
       <c r="E1034" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36587,19 +36587,19 @@
         <v>General</v>
       </c>
       <c r="G1034" t="str">
-        <v>140 X 110</v>
+        <v>110X90MM</v>
       </c>
       <c r="H1034" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1034" t="str">
-        <v>-</v>
+      <c r="I1034">
+        <v>40</v>
       </c>
       <c r="J1034" t="str">
         <v>Active</v>
       </c>
       <c r="K1034" t="str">
-        <v>REDUCER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
       </c>
     </row>
     <row r="1035">
@@ -36610,10 +36610,10 @@
         <v>-</v>
       </c>
       <c r="C1035" t="str">
-        <v>REDUCER (LW) (160 X 110)</v>
+        <v>REDUCING BUSH (LW) (63 X 40)</v>
       </c>
       <c r="D1035" t="str">
-        <v>REDUCER (LW)</v>
+        <v>REDUCING BUSH (LW)</v>
       </c>
       <c r="E1035" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36622,7 +36622,7 @@
         <v>General</v>
       </c>
       <c r="G1035" t="str">
-        <v>160 X 110</v>
+        <v>63 X 40</v>
       </c>
       <c r="H1035" t="str">
         <v>BOX</v>
@@ -36634,7 +36634,7 @@
         <v>Active</v>
       </c>
       <c r="K1035" t="str">
-        <v>REDUCER (LW) for agriculture irrigation and piping systems.</v>
+        <v>REDUCING BUSH (LW) for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1036">
@@ -36645,10 +36645,10 @@
         <v>-</v>
       </c>
       <c r="C1036" t="str">
-        <v>REDUCER (LW) (160 X 140)</v>
+        <v>REDUCING BUSH (LW) (63 X 50)</v>
       </c>
       <c r="D1036" t="str">
-        <v>REDUCER (LW)</v>
+        <v>REDUCING BUSH (LW)</v>
       </c>
       <c r="E1036" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36657,7 +36657,7 @@
         <v>General</v>
       </c>
       <c r="G1036" t="str">
-        <v>160 X 140</v>
+        <v>63 X 50</v>
       </c>
       <c r="H1036" t="str">
         <v>BOX</v>
@@ -36669,7 +36669,7 @@
         <v>Active</v>
       </c>
       <c r="K1036" t="str">
-        <v>REDUCER (LW) for agriculture irrigation and piping systems.</v>
+        <v>REDUCING BUSH (LW) for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1037">
@@ -36680,7 +36680,7 @@
         <v>-</v>
       </c>
       <c r="C1037" t="str">
-        <v>REDUCING BUSH (LW) (63 X 40)</v>
+        <v>REDUCING BUSH (LW) (75 X 40)</v>
       </c>
       <c r="D1037" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36692,7 +36692,7 @@
         <v>General</v>
       </c>
       <c r="G1037" t="str">
-        <v>63 X 40</v>
+        <v>75 X 40</v>
       </c>
       <c r="H1037" t="str">
         <v>BOX</v>
@@ -36715,7 +36715,7 @@
         <v>-</v>
       </c>
       <c r="C1038" t="str">
-        <v>REDUCING BUSH (LW) (63 X 50)</v>
+        <v>REDUCING BUSH (LW) (75 X 63)</v>
       </c>
       <c r="D1038" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36727,7 +36727,7 @@
         <v>General</v>
       </c>
       <c r="G1038" t="str">
-        <v>63 X 50</v>
+        <v>75 X 63</v>
       </c>
       <c r="H1038" t="str">
         <v>BOX</v>
@@ -36750,7 +36750,7 @@
         <v>-</v>
       </c>
       <c r="C1039" t="str">
-        <v>REDUCING BUSH (LW) (75 X 40)</v>
+        <v>REDUCING BUSH (LW) (90 X 50)</v>
       </c>
       <c r="D1039" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36762,7 +36762,7 @@
         <v>General</v>
       </c>
       <c r="G1039" t="str">
-        <v>75 X 40</v>
+        <v>90 X 50</v>
       </c>
       <c r="H1039" t="str">
         <v>BOX</v>
@@ -36785,7 +36785,7 @@
         <v>-</v>
       </c>
       <c r="C1040" t="str">
-        <v>REDUCING BUSH (LW) (75 X 63)</v>
+        <v>REDUCING BUSH (LW) (90 X 63)</v>
       </c>
       <c r="D1040" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36797,7 +36797,7 @@
         <v>General</v>
       </c>
       <c r="G1040" t="str">
-        <v>75 X 63</v>
+        <v>90 X 63</v>
       </c>
       <c r="H1040" t="str">
         <v>BOX</v>
@@ -36820,7 +36820,7 @@
         <v>-</v>
       </c>
       <c r="C1041" t="str">
-        <v>REDUCING BUSH (LW) (90 X 50)</v>
+        <v>REDUCING BUSH (LW) (90 X 75)</v>
       </c>
       <c r="D1041" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36832,7 +36832,7 @@
         <v>General</v>
       </c>
       <c r="G1041" t="str">
-        <v>90 X 50</v>
+        <v>90 X 75</v>
       </c>
       <c r="H1041" t="str">
         <v>BOX</v>
@@ -36855,7 +36855,7 @@
         <v>-</v>
       </c>
       <c r="C1042" t="str">
-        <v>REDUCING BUSH (LW) (90 X 63)</v>
+        <v>REDUCING BUSH (LW) (110 X 63)</v>
       </c>
       <c r="D1042" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36867,7 +36867,7 @@
         <v>General</v>
       </c>
       <c r="G1042" t="str">
-        <v>90 X 63</v>
+        <v>110 X 63</v>
       </c>
       <c r="H1042" t="str">
         <v>BOX</v>
@@ -36890,7 +36890,7 @@
         <v>-</v>
       </c>
       <c r="C1043" t="str">
-        <v>REDUCING BUSH (LW) (90 X 75)</v>
+        <v>REDUCING BUSH (LW) (110 X 75)</v>
       </c>
       <c r="D1043" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36902,7 +36902,7 @@
         <v>General</v>
       </c>
       <c r="G1043" t="str">
-        <v>90 X 75</v>
+        <v>110 X 75</v>
       </c>
       <c r="H1043" t="str">
         <v>BOX</v>
@@ -36925,7 +36925,7 @@
         <v>-</v>
       </c>
       <c r="C1044" t="str">
-        <v>REDUCING BUSH (LW) (110 X 63)</v>
+        <v>REDUCING BUSH (LW) (110 X 90)</v>
       </c>
       <c r="D1044" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36937,7 +36937,7 @@
         <v>General</v>
       </c>
       <c r="G1044" t="str">
-        <v>110 X 63</v>
+        <v>110 X 90</v>
       </c>
       <c r="H1044" t="str">
         <v>BOX</v>
@@ -36957,13 +36957,13 @@
         <v>1044</v>
       </c>
       <c r="B1045" t="str">
-        <v>-</v>
+        <v>FG-400550</v>
       </c>
       <c r="C1045" t="str">
-        <v>REDUCING BUSH (LW) (110 X 75)</v>
+        <v>AGRI TEE (40MM)</v>
       </c>
       <c r="D1045" t="str">
-        <v>REDUCING BUSH (LW)</v>
+        <v>AGRI TEE</v>
       </c>
       <c r="E1045" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36972,19 +36972,19 @@
         <v>General</v>
       </c>
       <c r="G1045" t="str">
-        <v>110 X 75</v>
+        <v>40MM</v>
       </c>
       <c r="H1045" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1045" t="str">
-        <v>-</v>
+      <c r="I1045">
+        <v>150</v>
       </c>
       <c r="J1045" t="str">
         <v>Active</v>
       </c>
       <c r="K1045" t="str">
-        <v>REDUCING BUSH (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1046">
@@ -36992,13 +36992,13 @@
         <v>1045</v>
       </c>
       <c r="B1046" t="str">
-        <v>-</v>
+        <v>FG-400551</v>
       </c>
       <c r="C1046" t="str">
-        <v>REDUCING BUSH (LW) (110 X 90)</v>
+        <v>AGRI TEE (50MM)</v>
       </c>
       <c r="D1046" t="str">
-        <v>REDUCING BUSH (LW)</v>
+        <v>AGRI TEE</v>
       </c>
       <c r="E1046" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37007,19 +37007,19 @@
         <v>General</v>
       </c>
       <c r="G1046" t="str">
-        <v>110 X 90</v>
+        <v>50MM</v>
       </c>
       <c r="H1046" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1046" t="str">
-        <v>-</v>
+      <c r="I1046">
+        <v>100</v>
       </c>
       <c r="J1046" t="str">
         <v>Active</v>
       </c>
       <c r="K1046" t="str">
-        <v>REDUCING BUSH (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1047">
@@ -37027,13 +37027,13 @@
         <v>1046</v>
       </c>
       <c r="B1047" t="str">
-        <v>-</v>
+        <v>FG-400552</v>
       </c>
       <c r="C1047" t="str">
-        <v>TEE (LW) (40MM)</v>
+        <v>AGRI TEE (63MM)</v>
       </c>
       <c r="D1047" t="str">
-        <v>TEE (LW)</v>
+        <v>AGRI TEE</v>
       </c>
       <c r="E1047" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37042,19 +37042,19 @@
         <v>General</v>
       </c>
       <c r="G1047" t="str">
-        <v>40MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1047" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1047" t="str">
-        <v>-</v>
+      <c r="I1047">
+        <v>70</v>
       </c>
       <c r="J1047" t="str">
         <v>Active</v>
       </c>
       <c r="K1047" t="str">
-        <v>TEE (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1048">
@@ -37062,13 +37062,13 @@
         <v>1047</v>
       </c>
       <c r="B1048" t="str">
-        <v>-</v>
+        <v>FG-400553</v>
       </c>
       <c r="C1048" t="str">
-        <v>TEE (LW) (50MM)</v>
+        <v>AGRI TEE (75MM)</v>
       </c>
       <c r="D1048" t="str">
-        <v>TEE (LW)</v>
+        <v>AGRI TEE</v>
       </c>
       <c r="E1048" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37077,19 +37077,19 @@
         <v>General</v>
       </c>
       <c r="G1048" t="str">
-        <v>50MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1048" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1048" t="str">
-        <v>-</v>
+      <c r="I1048">
+        <v>40</v>
       </c>
       <c r="J1048" t="str">
         <v>Active</v>
       </c>
       <c r="K1048" t="str">
-        <v>TEE (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1049">
@@ -37097,13 +37097,13 @@
         <v>1048</v>
       </c>
       <c r="B1049" t="str">
-        <v>-</v>
+        <v>FG-400554</v>
       </c>
       <c r="C1049" t="str">
-        <v>TEE (LW) (63MM)</v>
+        <v>AGRI TEE (90MM)</v>
       </c>
       <c r="D1049" t="str">
-        <v>TEE (LW)</v>
+        <v>AGRI TEE</v>
       </c>
       <c r="E1049" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37112,19 +37112,19 @@
         <v>General</v>
       </c>
       <c r="G1049" t="str">
-        <v>63MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1049" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1049" t="str">
-        <v>-</v>
+      <c r="I1049">
+        <v>50</v>
       </c>
       <c r="J1049" t="str">
         <v>Active</v>
       </c>
       <c r="K1049" t="str">
-        <v>TEE (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1050">
@@ -37132,13 +37132,13 @@
         <v>1049</v>
       </c>
       <c r="B1050" t="str">
-        <v>-</v>
+        <v>FG-400586</v>
       </c>
       <c r="C1050" t="str">
-        <v>TEE (LW) (75MM)</v>
+        <v>AGRI TEE (110MM)</v>
       </c>
       <c r="D1050" t="str">
-        <v>TEE (LW)</v>
+        <v>AGRI TEE</v>
       </c>
       <c r="E1050" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37147,19 +37147,19 @@
         <v>General</v>
       </c>
       <c r="G1050" t="str">
-        <v>75MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1050" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1050" t="str">
-        <v>-</v>
+      <c r="I1050">
+        <v>25</v>
       </c>
       <c r="J1050" t="str">
         <v>Active</v>
       </c>
       <c r="K1050" t="str">
-        <v>TEE (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1051">
@@ -37167,13 +37167,13 @@
         <v>1050</v>
       </c>
       <c r="B1051" t="str">
-        <v>-</v>
+        <v>FG-400607</v>
       </c>
       <c r="C1051" t="str">
-        <v>TEE (LW) (90MM)</v>
+        <v>AGRI TEE (140MM)</v>
       </c>
       <c r="D1051" t="str">
-        <v>TEE (LW)</v>
+        <v>AGRI TEE</v>
       </c>
       <c r="E1051" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37182,19 +37182,19 @@
         <v>General</v>
       </c>
       <c r="G1051" t="str">
-        <v>90MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1051" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1051" t="str">
-        <v>-</v>
+      <c r="I1051">
+        <v>6</v>
       </c>
       <c r="J1051" t="str">
         <v>Active</v>
       </c>
       <c r="K1051" t="str">
-        <v>TEE (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1052">
@@ -37202,13 +37202,13 @@
         <v>1051</v>
       </c>
       <c r="B1052" t="str">
-        <v>-</v>
+        <v>FG-400608</v>
       </c>
       <c r="C1052" t="str">
-        <v>TEE (LW) (110MM)</v>
+        <v>AGRI TEE (160MM)</v>
       </c>
       <c r="D1052" t="str">
-        <v>TEE (LW)</v>
+        <v>AGRI TEE</v>
       </c>
       <c r="E1052" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37217,19 +37217,19 @@
         <v>General</v>
       </c>
       <c r="G1052" t="str">
-        <v>110MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1052" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1052" t="str">
-        <v>-</v>
+      <c r="I1052">
+        <v>9</v>
       </c>
       <c r="J1052" t="str">
         <v>Active</v>
       </c>
       <c r="K1052" t="str">
-        <v>TEE (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1053">
@@ -37240,10 +37240,10 @@
         <v>-</v>
       </c>
       <c r="C1053" t="str">
-        <v>TEE (LW) (140MM)</v>
+        <v>COUPLER (LW) (75MM)</v>
       </c>
       <c r="D1053" t="str">
-        <v>TEE (LW)</v>
+        <v>COUPLER (LW)</v>
       </c>
       <c r="E1053" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37252,7 +37252,7 @@
         <v>General</v>
       </c>
       <c r="G1053" t="str">
-        <v>140MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1053" t="str">
         <v>BOX</v>
@@ -37264,7 +37264,7 @@
         <v>Active</v>
       </c>
       <c r="K1053" t="str">
-        <v>TEE (LW) for agriculture irrigation and piping systems.</v>
+        <v>COUPLER (LW) for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1054">
@@ -37275,10 +37275,10 @@
         <v>-</v>
       </c>
       <c r="C1054" t="str">
-        <v>TEE (LW) (160MM)</v>
+        <v>COUPLER (LW) (90MM)</v>
       </c>
       <c r="D1054" t="str">
-        <v>TEE (LW)</v>
+        <v>COUPLER (LW)</v>
       </c>
       <c r="E1054" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37287,7 +37287,7 @@
         <v>General</v>
       </c>
       <c r="G1054" t="str">
-        <v>160MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1054" t="str">
         <v>BOX</v>
@@ -37299,7 +37299,7 @@
         <v>Active</v>
       </c>
       <c r="K1054" t="str">
-        <v>TEE (LW) for agriculture irrigation and piping systems.</v>
+        <v>COUPLER (LW) for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1055">
@@ -37310,7 +37310,7 @@
         <v>-</v>
       </c>
       <c r="C1055" t="str">
-        <v>COUPLER (LW) (75MM)</v>
+        <v>COUPLER (LW) (110MM)</v>
       </c>
       <c r="D1055" t="str">
         <v>COUPLER (LW)</v>
@@ -37322,7 +37322,7 @@
         <v>General</v>
       </c>
       <c r="G1055" t="str">
-        <v>75MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1055" t="str">
         <v>BOX</v>
@@ -37342,13 +37342,13 @@
         <v>1055</v>
       </c>
       <c r="B1056" t="str">
-        <v>-</v>
+        <v>FG-400561</v>
       </c>
       <c r="C1056" t="str">
-        <v>COUPLER (LW) (90MM)</v>
+        <v>AGRI FABRICATED COUPLER (40MM)</v>
       </c>
       <c r="D1056" t="str">
-        <v>COUPLER (LW)</v>
+        <v>AGRI FABRICATED COUPLER</v>
       </c>
       <c r="E1056" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37357,19 +37357,19 @@
         <v>General</v>
       </c>
       <c r="G1056" t="str">
-        <v>90MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1056" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1056" t="str">
-        <v>-</v>
+      <c r="I1056">
+        <v>300</v>
       </c>
       <c r="J1056" t="str">
         <v>Active</v>
       </c>
       <c r="K1056" t="str">
-        <v>COUPLER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI FABRICATED COUPLER for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1057">
@@ -37377,13 +37377,13 @@
         <v>1056</v>
       </c>
       <c r="B1057" t="str">
-        <v>-</v>
+        <v>FG-400562</v>
       </c>
       <c r="C1057" t="str">
-        <v>COUPLER (LW) (110MM)</v>
+        <v>AGRI FABRICATED COUPLER (50MM)</v>
       </c>
       <c r="D1057" t="str">
-        <v>COUPLER (LW)</v>
+        <v>AGRI FABRICATED COUPLER</v>
       </c>
       <c r="E1057" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37392,19 +37392,19 @@
         <v>General</v>
       </c>
       <c r="G1057" t="str">
-        <v>110MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1057" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1057" t="str">
-        <v>-</v>
+      <c r="I1057">
+        <v>200</v>
       </c>
       <c r="J1057" t="str">
         <v>Active</v>
       </c>
       <c r="K1057" t="str">
-        <v>COUPLER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI FABRICATED COUPLER for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1058">
@@ -37412,10 +37412,10 @@
         <v>1057</v>
       </c>
       <c r="B1058" t="str">
-        <v>FG-400561</v>
+        <v>FG-400563</v>
       </c>
       <c r="C1058" t="str">
-        <v>AGRI FABRICATED COUPLER (40MM)</v>
+        <v>AGRI FABRICATED COUPLER (63MM)</v>
       </c>
       <c r="D1058" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37427,13 +37427,13 @@
         <v>General</v>
       </c>
       <c r="G1058" t="str">
-        <v>40MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1058" t="str">
         <v>BOX</v>
       </c>
       <c r="I1058">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J1058" t="str">
         <v>Active</v>
@@ -37447,10 +37447,10 @@
         <v>1058</v>
       </c>
       <c r="B1059" t="str">
-        <v>FG-400562</v>
+        <v>FG-400564</v>
       </c>
       <c r="C1059" t="str">
-        <v>AGRI FABRICATED COUPLER (50MM)</v>
+        <v>AGRI FABRICATED COUPLER (75MM)</v>
       </c>
       <c r="D1059" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37462,13 +37462,13 @@
         <v>General</v>
       </c>
       <c r="G1059" t="str">
-        <v>50MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1059" t="str">
         <v>BOX</v>
       </c>
       <c r="I1059">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="J1059" t="str">
         <v>Active</v>
@@ -37482,10 +37482,10 @@
         <v>1059</v>
       </c>
       <c r="B1060" t="str">
-        <v>FG-400563</v>
+        <v>FG-400565</v>
       </c>
       <c r="C1060" t="str">
-        <v>AGRI FABRICATED COUPLER (63MM)</v>
+        <v>AGRI FABRICATED COUPLER (90MM)</v>
       </c>
       <c r="D1060" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37497,13 +37497,13 @@
         <v>General</v>
       </c>
       <c r="G1060" t="str">
-        <v>63MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1060" t="str">
         <v>BOX</v>
       </c>
       <c r="I1060">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="J1060" t="str">
         <v>Active</v>
@@ -37517,10 +37517,10 @@
         <v>1060</v>
       </c>
       <c r="B1061" t="str">
-        <v>FG-400564</v>
+        <v>FG-400566</v>
       </c>
       <c r="C1061" t="str">
-        <v>AGRI FABRICATED COUPLER (75MM)</v>
+        <v>AGRI FABRICATED COUPLER (110MM)</v>
       </c>
       <c r="D1061" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37532,13 +37532,13 @@
         <v>General</v>
       </c>
       <c r="G1061" t="str">
-        <v>75MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1061" t="str">
         <v>BOX</v>
       </c>
       <c r="I1061">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J1061" t="str">
         <v>Active</v>
@@ -37552,10 +37552,10 @@
         <v>1061</v>
       </c>
       <c r="B1062" t="str">
-        <v>FG-400565</v>
+        <v>FG-400587</v>
       </c>
       <c r="C1062" t="str">
-        <v>AGRI FABRICATED COUPLER (90MM)</v>
+        <v>AGRI FABRICATED COUPLER (140MM 4KG)</v>
       </c>
       <c r="D1062" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37567,13 +37567,13 @@
         <v>General</v>
       </c>
       <c r="G1062" t="str">
-        <v>90MM</v>
+        <v>140MM 4KG</v>
       </c>
       <c r="H1062" t="str">
         <v>BOX</v>
       </c>
       <c r="I1062">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="J1062" t="str">
         <v>Active</v>
@@ -37587,10 +37587,10 @@
         <v>1062</v>
       </c>
       <c r="B1063" t="str">
-        <v>FG-400566</v>
+        <v>FG-400568</v>
       </c>
       <c r="C1063" t="str">
-        <v>AGRI FABRICATED COUPLER (110MM)</v>
+        <v>AGRI FABRICATED COUPLER (160MM 4KG)</v>
       </c>
       <c r="D1063" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37602,13 +37602,13 @@
         <v>General</v>
       </c>
       <c r="G1063" t="str">
-        <v>110MM</v>
+        <v>160MM 4KG</v>
       </c>
       <c r="H1063" t="str">
         <v>BOX</v>
       </c>
       <c r="I1063">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J1063" t="str">
         <v>Active</v>
@@ -37622,13 +37622,13 @@
         <v>1063</v>
       </c>
       <c r="B1064" t="str">
-        <v>FG-400587</v>
+        <v>FG-400567</v>
       </c>
       <c r="C1064" t="str">
-        <v>AGRI FABRICATED COUPLER (140MM 4KG)</v>
+        <v>AGRI FABRICATED COUPLER 6KG (140MM)</v>
       </c>
       <c r="D1064" t="str">
-        <v>AGRI FABRICATED COUPLER</v>
+        <v>AGRI FABRICATED COUPLER 6KG</v>
       </c>
       <c r="E1064" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37637,7 +37637,7 @@
         <v>General</v>
       </c>
       <c r="G1064" t="str">
-        <v>140MM 4KG</v>
+        <v>140MM</v>
       </c>
       <c r="H1064" t="str">
         <v>BOX</v>
@@ -37649,7 +37649,7 @@
         <v>Active</v>
       </c>
       <c r="K1064" t="str">
-        <v>AGRI FABRICATED COUPLER for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
+        <v>AGRI FABRICATED COUPLER 6KG for agriculture irrigation and piping systems. Available sizes: 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1065">
@@ -37657,13 +37657,13 @@
         <v>1064</v>
       </c>
       <c r="B1065" t="str">
-        <v>FG-400568</v>
+        <v>FG-400569</v>
       </c>
       <c r="C1065" t="str">
-        <v>AGRI FABRICATED COUPLER (160MM 4KG)</v>
+        <v>AGRI FABRICATED COUPLER 6KG (160MM)</v>
       </c>
       <c r="D1065" t="str">
-        <v>AGRI FABRICATED COUPLER</v>
+        <v>AGRI FABRICATED COUPLER 6KG</v>
       </c>
       <c r="E1065" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37672,7 +37672,7 @@
         <v>General</v>
       </c>
       <c r="G1065" t="str">
-        <v>160MM 4KG</v>
+        <v>160MM</v>
       </c>
       <c r="H1065" t="str">
         <v>BOX</v>
@@ -37684,7 +37684,7 @@
         <v>Active</v>
       </c>
       <c r="K1065" t="str">
-        <v>AGRI FABRICATED COUPLER for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
+        <v>AGRI FABRICATED COUPLER 6KG for agriculture irrigation and piping systems. Available sizes: 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1066">
@@ -37692,13 +37692,13 @@
         <v>1065</v>
       </c>
       <c r="B1066" t="str">
-        <v>FG-400567</v>
+        <v>FG-400544</v>
       </c>
       <c r="C1066" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG (140MM)</v>
+        <v>AGRI ELBOW (40MM)</v>
       </c>
       <c r="D1066" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG</v>
+        <v>AGRI ELBOW</v>
       </c>
       <c r="E1066" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37707,19 +37707,19 @@
         <v>General</v>
       </c>
       <c r="G1066" t="str">
-        <v>140MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1066" t="str">
         <v>BOX</v>
       </c>
       <c r="I1066">
-        <v>25</v>
+        <v>250</v>
       </c>
       <c r="J1066" t="str">
         <v>Active</v>
       </c>
       <c r="K1066" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG for agriculture irrigation and piping systems. Available sizes: 140MM, 160MM.</v>
+        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1067">
@@ -37727,13 +37727,13 @@
         <v>1066</v>
       </c>
       <c r="B1067" t="str">
-        <v>FG-400569</v>
+        <v>FG-400545</v>
       </c>
       <c r="C1067" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG (160MM)</v>
+        <v>AGRI ELBOW (50MM)</v>
       </c>
       <c r="D1067" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG</v>
+        <v>AGRI ELBOW</v>
       </c>
       <c r="E1067" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37742,19 +37742,19 @@
         <v>General</v>
       </c>
       <c r="G1067" t="str">
-        <v>160MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1067" t="str">
         <v>BOX</v>
       </c>
       <c r="I1067">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="J1067" t="str">
         <v>Active</v>
       </c>
       <c r="K1067" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG for agriculture irrigation and piping systems. Available sizes: 140MM, 160MM.</v>
+        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1068">
@@ -37762,13 +37762,13 @@
         <v>1067</v>
       </c>
       <c r="B1068" t="str">
-        <v>-</v>
+        <v>FG-400546</v>
       </c>
       <c r="C1068" t="str">
-        <v>ELBOW 90 (LW) (40MM)</v>
+        <v>AGRI ELBOW (63MM)</v>
       </c>
       <c r="D1068" t="str">
-        <v>ELBOW 90 (LW)</v>
+        <v>AGRI ELBOW</v>
       </c>
       <c r="E1068" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37777,19 +37777,19 @@
         <v>General</v>
       </c>
       <c r="G1068" t="str">
-        <v>40MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1068" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1068" t="str">
-        <v>-</v>
+      <c r="I1068">
+        <v>100</v>
       </c>
       <c r="J1068" t="str">
         <v>Active</v>
       </c>
       <c r="K1068" t="str">
-        <v>ELBOW 90 (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1069">
@@ -37797,13 +37797,13 @@
         <v>1068</v>
       </c>
       <c r="B1069" t="str">
-        <v>-</v>
+        <v>FG-400547</v>
       </c>
       <c r="C1069" t="str">
-        <v>ELBOW 90 (LW) (50MM)</v>
+        <v>AGRI ELBOW (75MM)</v>
       </c>
       <c r="D1069" t="str">
-        <v>ELBOW 90 (LW)</v>
+        <v>AGRI ELBOW</v>
       </c>
       <c r="E1069" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37812,19 +37812,19 @@
         <v>General</v>
       </c>
       <c r="G1069" t="str">
-        <v>50MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1069" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1069" t="str">
-        <v>-</v>
+      <c r="I1069">
+        <v>50</v>
       </c>
       <c r="J1069" t="str">
         <v>Active</v>
       </c>
       <c r="K1069" t="str">
-        <v>ELBOW 90 (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1070">
@@ -37832,13 +37832,13 @@
         <v>1069</v>
       </c>
       <c r="B1070" t="str">
-        <v>-</v>
+        <v>FG-400548</v>
       </c>
       <c r="C1070" t="str">
-        <v>ELBOW 90 (LW) (63MM)</v>
+        <v>AGRI ELBOW (90MM)</v>
       </c>
       <c r="D1070" t="str">
-        <v>ELBOW 90 (LW)</v>
+        <v>AGRI ELBOW</v>
       </c>
       <c r="E1070" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37847,19 +37847,19 @@
         <v>General</v>
       </c>
       <c r="G1070" t="str">
-        <v>63MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1070" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1070" t="str">
-        <v>-</v>
+      <c r="I1070">
+        <v>35</v>
       </c>
       <c r="J1070" t="str">
         <v>Active</v>
       </c>
       <c r="K1070" t="str">
-        <v>ELBOW 90 (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1071">
@@ -37867,13 +37867,13 @@
         <v>1070</v>
       </c>
       <c r="B1071" t="str">
-        <v>-</v>
+        <v>FG-400549</v>
       </c>
       <c r="C1071" t="str">
-        <v>ELBOW 90 (LW) (75MM)</v>
+        <v>AGRI ELBOW (110MM)</v>
       </c>
       <c r="D1071" t="str">
-        <v>ELBOW 90 (LW)</v>
+        <v>AGRI ELBOW</v>
       </c>
       <c r="E1071" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37882,19 +37882,19 @@
         <v>General</v>
       </c>
       <c r="G1071" t="str">
-        <v>75MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1071" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1071" t="str">
-        <v>-</v>
+      <c r="I1071">
+        <v>50</v>
       </c>
       <c r="J1071" t="str">
         <v>Active</v>
       </c>
       <c r="K1071" t="str">
-        <v>ELBOW 90 (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1072">
@@ -37902,13 +37902,13 @@
         <v>1071</v>
       </c>
       <c r="B1072" t="str">
-        <v>-</v>
+        <v>FG-400595</v>
       </c>
       <c r="C1072" t="str">
-        <v>ELBOW 90 (LW) (90MM)</v>
+        <v>AGRI ELBOW (140MM)</v>
       </c>
       <c r="D1072" t="str">
-        <v>ELBOW 90 (LW)</v>
+        <v>AGRI ELBOW</v>
       </c>
       <c r="E1072" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37917,19 +37917,19 @@
         <v>General</v>
       </c>
       <c r="G1072" t="str">
-        <v>90MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1072" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1072" t="str">
-        <v>-</v>
+      <c r="I1072">
+        <v>8</v>
       </c>
       <c r="J1072" t="str">
         <v>Active</v>
       </c>
       <c r="K1072" t="str">
-        <v>ELBOW 90 (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1073">
@@ -37937,13 +37937,13 @@
         <v>1072</v>
       </c>
       <c r="B1073" t="str">
-        <v>-</v>
+        <v>FG-400596</v>
       </c>
       <c r="C1073" t="str">
-        <v>ELBOW 90 (LW) (110MM)</v>
+        <v>AGRI ELBOW (160MM)</v>
       </c>
       <c r="D1073" t="str">
-        <v>ELBOW 90 (LW)</v>
+        <v>AGRI ELBOW</v>
       </c>
       <c r="E1073" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37952,19 +37952,19 @@
         <v>General</v>
       </c>
       <c r="G1073" t="str">
-        <v>110MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1073" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1073" t="str">
-        <v>-</v>
+      <c r="I1073">
+        <v>12</v>
       </c>
       <c r="J1073" t="str">
         <v>Active</v>
       </c>
       <c r="K1073" t="str">
-        <v>ELBOW 90 (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1074">
@@ -37972,13 +37972,13 @@
         <v>1073</v>
       </c>
       <c r="B1074" t="str">
-        <v>-</v>
+        <v>FG-400555</v>
       </c>
       <c r="C1074" t="str">
-        <v>ELBOW 90 (LW) (140MM)</v>
+        <v>AGRI END CAP (40MM)</v>
       </c>
       <c r="D1074" t="str">
-        <v>ELBOW 90 (LW)</v>
+        <v>AGRI END CAP</v>
       </c>
       <c r="E1074" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37987,19 +37987,19 @@
         <v>General</v>
       </c>
       <c r="G1074" t="str">
-        <v>140MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1074" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1074" t="str">
-        <v>-</v>
+      <c r="I1074">
+        <v>800</v>
       </c>
       <c r="J1074" t="str">
         <v>Active</v>
       </c>
       <c r="K1074" t="str">
-        <v>ELBOW 90 (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1075">
@@ -38007,13 +38007,13 @@
         <v>1074</v>
       </c>
       <c r="B1075" t="str">
-        <v>-</v>
+        <v>FG-400556</v>
       </c>
       <c r="C1075" t="str">
-        <v>ELBOW 90 (LW) (160MM)</v>
+        <v>AGRI END CAP (50MM)</v>
       </c>
       <c r="D1075" t="str">
-        <v>ELBOW 90 (LW)</v>
+        <v>AGRI END CAP</v>
       </c>
       <c r="E1075" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -38022,19 +38022,19 @@
         <v>General</v>
       </c>
       <c r="G1075" t="str">
-        <v>160MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1075" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1075" t="str">
-        <v>-</v>
+      <c r="I1075">
+        <v>450</v>
       </c>
       <c r="J1075" t="str">
         <v>Active</v>
       </c>
       <c r="K1075" t="str">
-        <v>ELBOW 90 (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1076">
@@ -38042,13 +38042,13 @@
         <v>1075</v>
       </c>
       <c r="B1076" t="str">
-        <v>-</v>
+        <v>FG-400557</v>
       </c>
       <c r="C1076" t="str">
-        <v>END CAP (LW) (40MM)</v>
+        <v>AGRI END CAP (63MM)</v>
       </c>
       <c r="D1076" t="str">
-        <v>END CAP (LW)</v>
+        <v>AGRI END CAP</v>
       </c>
       <c r="E1076" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -38057,19 +38057,19 @@
         <v>General</v>
       </c>
       <c r="G1076" t="str">
-        <v>40MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1076" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1076" t="str">
-        <v>-</v>
+      <c r="I1076">
+        <v>300</v>
       </c>
       <c r="J1076" t="str">
         <v>Active</v>
       </c>
       <c r="K1076" t="str">
-        <v>END CAP (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1077">
@@ -38077,13 +38077,13 @@
         <v>1076</v>
       </c>
       <c r="B1077" t="str">
-        <v>-</v>
+        <v>FG-400558</v>
       </c>
       <c r="C1077" t="str">
-        <v>END CAP (LW) (50MM)</v>
+        <v>AGRI END CAP (75MM)</v>
       </c>
       <c r="D1077" t="str">
-        <v>END CAP (LW)</v>
+        <v>AGRI END CAP</v>
       </c>
       <c r="E1077" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -38092,19 +38092,19 @@
         <v>General</v>
       </c>
       <c r="G1077" t="str">
-        <v>50MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1077" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1077" t="str">
-        <v>-</v>
+      <c r="I1077">
+        <v>150</v>
       </c>
       <c r="J1077" t="str">
         <v>Active</v>
       </c>
       <c r="K1077" t="str">
-        <v>END CAP (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1078">
@@ -38112,13 +38112,13 @@
         <v>1077</v>
       </c>
       <c r="B1078" t="str">
-        <v>-</v>
+        <v>FG-400559</v>
       </c>
       <c r="C1078" t="str">
-        <v>END CAP (LW) (63MM)</v>
+        <v>AGRI END CAP (90MM)</v>
       </c>
       <c r="D1078" t="str">
-        <v>END CAP (LW)</v>
+        <v>AGRI END CAP</v>
       </c>
       <c r="E1078" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -38127,19 +38127,19 @@
         <v>General</v>
       </c>
       <c r="G1078" t="str">
-        <v>63MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1078" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1078" t="str">
-        <v>-</v>
+      <c r="I1078">
+        <v>100</v>
       </c>
       <c r="J1078" t="str">
         <v>Active</v>
       </c>
       <c r="K1078" t="str">
-        <v>END CAP (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1079">
@@ -38147,13 +38147,13 @@
         <v>1078</v>
       </c>
       <c r="B1079" t="str">
-        <v>-</v>
+        <v>FG-400560</v>
       </c>
       <c r="C1079" t="str">
-        <v>END CAP (LW) (75MM)</v>
+        <v>AGRI END CAP (110MM)</v>
       </c>
       <c r="D1079" t="str">
-        <v>END CAP (LW)</v>
+        <v>AGRI END CAP</v>
       </c>
       <c r="E1079" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -38162,19 +38162,19 @@
         <v>General</v>
       </c>
       <c r="G1079" t="str">
-        <v>75MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1079" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1079" t="str">
-        <v>-</v>
+      <c r="I1079">
+        <v>60</v>
       </c>
       <c r="J1079" t="str">
         <v>Active</v>
       </c>
       <c r="K1079" t="str">
-        <v>END CAP (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1080">
@@ -38182,13 +38182,13 @@
         <v>1079</v>
       </c>
       <c r="B1080" t="str">
-        <v>-</v>
+        <v>FG-400639</v>
       </c>
       <c r="C1080" t="str">
-        <v>END CAP (LW) (90MM)</v>
+        <v>AGRI END CAP (140MM 4KG)</v>
       </c>
       <c r="D1080" t="str">
-        <v>END CAP (LW)</v>
+        <v>AGRI END CAP</v>
       </c>
       <c r="E1080" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -38197,19 +38197,19 @@
         <v>General</v>
       </c>
       <c r="G1080" t="str">
-        <v>90MM</v>
+        <v>140MM 4KG</v>
       </c>
       <c r="H1080" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1080" t="str">
-        <v>-</v>
+      <c r="I1080">
+        <v>30</v>
       </c>
       <c r="J1080" t="str">
         <v>Active</v>
       </c>
       <c r="K1080" t="str">
-        <v>END CAP (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1081">
@@ -38217,13 +38217,13 @@
         <v>1080</v>
       </c>
       <c r="B1081" t="str">
-        <v>-</v>
+        <v>FG-400640</v>
       </c>
       <c r="C1081" t="str">
-        <v>END CAP (LW) (110MM)</v>
+        <v>AGRI END CAP (160MM 4KG)</v>
       </c>
       <c r="D1081" t="str">
-        <v>END CAP (LW)</v>
+        <v>AGRI END CAP</v>
       </c>
       <c r="E1081" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -38232,19 +38232,19 @@
         <v>General</v>
       </c>
       <c r="G1081" t="str">
-        <v>110MM</v>
+        <v>160MM 4KG</v>
       </c>
       <c r="H1081" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1081" t="str">
-        <v>-</v>
+      <c r="I1081">
+        <v>16</v>
       </c>
       <c r="J1081" t="str">
         <v>Active</v>
       </c>
       <c r="K1081" t="str">
-        <v>END CAP (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1082">
@@ -38252,13 +38252,13 @@
         <v>1081</v>
       </c>
       <c r="B1082" t="str">
-        <v>-</v>
+        <v>FG-400570</v>
       </c>
       <c r="C1082" t="str">
-        <v>END CAP (LW) (140MM)</v>
+        <v>AGRI LONG BEND (63MM)</v>
       </c>
       <c r="D1082" t="str">
-        <v>END CAP (LW)</v>
+        <v>AGRI LONG BEND</v>
       </c>
       <c r="E1082" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -38267,19 +38267,19 @@
         <v>General</v>
       </c>
       <c r="G1082" t="str">
-        <v>140MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1082" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1082" t="str">
-        <v>-</v>
+      <c r="I1082">
+        <v>50</v>
       </c>
       <c r="J1082" t="str">
         <v>Active</v>
       </c>
       <c r="K1082" t="str">
-        <v>END CAP (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI LONG BEND for agriculture irrigation and piping systems. Available sizes: 63MM, 75MM, 90MM, 110MM.</v>
       </c>
     </row>
     <row r="1083">
@@ -38287,13 +38287,13 @@
         <v>1082</v>
       </c>
       <c r="B1083" t="str">
-        <v>-</v>
+        <v>FG-400571</v>
       </c>
       <c r="C1083" t="str">
-        <v>END CAP (LW) (160MM)</v>
+        <v>AGRI LONG BEND (75MM)</v>
       </c>
       <c r="D1083" t="str">
-        <v>END CAP (LW)</v>
+        <v>AGRI LONG BEND</v>
       </c>
       <c r="E1083" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -38302,19 +38302,19 @@
         <v>General</v>
       </c>
       <c r="G1083" t="str">
-        <v>160MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1083" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1083" t="str">
-        <v>-</v>
+      <c r="I1083">
+        <v>40</v>
       </c>
       <c r="J1083" t="str">
         <v>Active</v>
       </c>
       <c r="K1083" t="str">
-        <v>END CAP (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI LONG BEND for agriculture irrigation and piping systems. Available sizes: 63MM, 75MM, 90MM, 110MM.</v>
       </c>
     </row>
     <row r="1084">
@@ -38322,13 +38322,13 @@
         <v>1083</v>
       </c>
       <c r="B1084" t="str">
-        <v>-</v>
+        <v>FG-400572</v>
       </c>
       <c r="C1084" t="str">
-        <v>LONG BEND (LW) (63MM)</v>
+        <v>AGRI LONG BEND (90MM)</v>
       </c>
       <c r="D1084" t="str">
-        <v>LONG BEND (LW)</v>
+        <v>AGRI LONG BEND</v>
       </c>
       <c r="E1084" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -38337,19 +38337,19 @@
         <v>General</v>
       </c>
       <c r="G1084" t="str">
-        <v>63MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1084" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1084" t="str">
-        <v>-</v>
+      <c r="I1084">
+        <v>20</v>
       </c>
       <c r="J1084" t="str">
         <v>Active</v>
       </c>
       <c r="K1084" t="str">
-        <v>LONG BEND (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI LONG BEND for agriculture irrigation and piping systems. Available sizes: 63MM, 75MM, 90MM, 110MM.</v>
       </c>
     </row>
     <row r="1085">
@@ -38357,13 +38357,13 @@
         <v>1084</v>
       </c>
       <c r="B1085" t="str">
-        <v>-</v>
+        <v>FG-400573</v>
       </c>
       <c r="C1085" t="str">
-        <v>LONG BEND (LW) (75MM)</v>
+        <v>AGRI LONG BEND (110MM)</v>
       </c>
       <c r="D1085" t="str">
-        <v>LONG BEND (LW)</v>
+        <v>AGRI LONG BEND</v>
       </c>
       <c r="E1085" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -38372,19 +38372,19 @@
         <v>General</v>
       </c>
       <c r="G1085" t="str">
-        <v>75MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1085" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1085" t="str">
-        <v>-</v>
+      <c r="I1085">
+        <v>10</v>
       </c>
       <c r="J1085" t="str">
         <v>Active</v>
       </c>
       <c r="K1085" t="str">
-        <v>LONG BEND (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI LONG BEND for agriculture irrigation and piping systems. Available sizes: 63MM, 75MM, 90MM, 110MM.</v>
       </c>
     </row>
     <row r="1086">
@@ -38392,25 +38392,25 @@
         <v>1085</v>
       </c>
       <c r="B1086" t="str">
-        <v>-</v>
+        <v>FG-401520</v>
       </c>
       <c r="C1086" t="str">
-        <v>LONG BEND (LW) (90MM)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1086" t="str">
-        <v>LONG BEND (LW)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR</v>
       </c>
       <c r="E1086" t="str">
-        <v>Agriculture Pipes &amp; Fittings</v>
+        <v>Sprinkler Pipes &amp; Fittings</v>
       </c>
       <c r="F1086" t="str">
         <v>General</v>
       </c>
       <c r="G1086" t="str">
-        <v>90MM</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1086" t="str">
-        <v>BOX</v>
+        <v>Nos</v>
       </c>
       <c r="I1086" t="str">
         <v>-</v>
@@ -38419,7 +38419,7 @@
         <v>Active</v>
       </c>
       <c r="K1086" t="str">
-        <v>LONG BEND (LW) for agriculture irrigation and piping systems.</v>
+        <v>SPRINKLER ISI PIPE 6 MTR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1087">
@@ -38427,25 +38427,25 @@
         <v>1086</v>
       </c>
       <c r="B1087" t="str">
-        <v>-</v>
+        <v>FG-401491</v>
       </c>
       <c r="C1087" t="str">
-        <v>LONG BEND (LW) (110MM)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (63MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1087" t="str">
-        <v>LONG BEND (LW)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR</v>
       </c>
       <c r="E1087" t="str">
-        <v>Agriculture Pipes &amp; Fittings</v>
+        <v>Sprinkler Pipes &amp; Fittings</v>
       </c>
       <c r="F1087" t="str">
         <v>General</v>
       </c>
       <c r="G1087" t="str">
-        <v>110MM</v>
+        <v>63MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1087" t="str">
-        <v>BOX</v>
+        <v>Nos</v>
       </c>
       <c r="I1087" t="str">
         <v>-</v>
@@ -38454,7 +38454,7 @@
         <v>Active</v>
       </c>
       <c r="K1087" t="str">
-        <v>LONG BEND (LW) for agriculture irrigation and piping systems.</v>
+        <v>SPRINKLER ISI PIPE 6 MTR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1088">
@@ -38462,10 +38462,10 @@
         <v>1087</v>
       </c>
       <c r="B1088" t="str">
-        <v>FG-401520</v>
+        <v>FG-401490</v>
       </c>
       <c r="C1088" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 2.5 KG)</v>
       </c>
       <c r="D1088" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38477,7 +38477,7 @@
         <v>General</v>
       </c>
       <c r="G1088" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM C TYPE 2.5 KG</v>
       </c>
       <c r="H1088" t="str">
         <v>Nos</v>
@@ -38497,10 +38497,10 @@
         <v>1088</v>
       </c>
       <c r="B1089" t="str">
-        <v>FG-401491</v>
+        <v>FG-401492</v>
       </c>
       <c r="C1089" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (63MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1089" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38512,7 +38512,7 @@
         <v>General</v>
       </c>
       <c r="G1089" t="str">
-        <v>63MM L TYPE 3.2 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1089" t="str">
         <v>Nos</v>
@@ -38532,10 +38532,10 @@
         <v>1089</v>
       </c>
       <c r="B1090" t="str">
-        <v>FG-401490</v>
+        <v>FG-401519</v>
       </c>
       <c r="C1090" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 2.5 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 2.5 KG)</v>
       </c>
       <c r="D1090" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38547,7 +38547,7 @@
         <v>General</v>
       </c>
       <c r="G1090" t="str">
-        <v>75MM C TYPE 2.5 KG</v>
+        <v>75MM L TYPE 2.5 KG</v>
       </c>
       <c r="H1090" t="str">
         <v>Nos</v>
@@ -38567,10 +38567,10 @@
         <v>1090</v>
       </c>
       <c r="B1091" t="str">
-        <v>FG-401492</v>
+        <v>FG-401521</v>
       </c>
       <c r="C1091" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1091" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38582,7 +38582,7 @@
         <v>General</v>
       </c>
       <c r="G1091" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1091" t="str">
         <v>Nos</v>
@@ -38602,13 +38602,13 @@
         <v>1091</v>
       </c>
       <c r="B1092" t="str">
-        <v>FG-401519</v>
+        <v>FG-401522</v>
       </c>
       <c r="C1092" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 2.5 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1092" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR</v>
+        <v>SPRINKLER NISI PIPE 6 MTR</v>
       </c>
       <c r="E1092" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38617,7 +38617,7 @@
         <v>General</v>
       </c>
       <c r="G1092" t="str">
-        <v>75MM L TYPE 2.5 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1092" t="str">
         <v>Nos</v>
@@ -38629,7 +38629,7 @@
         <v>Active</v>
       </c>
       <c r="K1092" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER NISI PIPE 6 MTR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1093">
@@ -38637,13 +38637,13 @@
         <v>1092</v>
       </c>
       <c r="B1093" t="str">
-        <v>FG-401521</v>
+        <v>FG-401523</v>
       </c>
       <c r="C1093" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1093" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR</v>
+        <v>SPRINKLER NISI PIPE 6 MTR</v>
       </c>
       <c r="E1093" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38652,7 +38652,7 @@
         <v>General</v>
       </c>
       <c r="G1093" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1093" t="str">
         <v>Nos</v>
@@ -38664,7 +38664,7 @@
         <v>Active</v>
       </c>
       <c r="K1093" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER NISI PIPE 6 MTR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1094">
@@ -38672,10 +38672,10 @@
         <v>1093</v>
       </c>
       <c r="B1094" t="str">
-        <v>FG-401522</v>
+        <v>FG-401866</v>
       </c>
       <c r="C1094" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (90MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1094" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38687,7 +38687,7 @@
         <v>General</v>
       </c>
       <c r="G1094" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>90MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1094" t="str">
         <v>Nos</v>
@@ -38707,10 +38707,10 @@
         <v>1094</v>
       </c>
       <c r="B1095" t="str">
-        <v>FG-401523</v>
+        <v>FG-401867</v>
       </c>
       <c r="C1095" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (90MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1095" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38722,7 +38722,7 @@
         <v>General</v>
       </c>
       <c r="G1095" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>90MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1095" t="str">
         <v>Nos</v>
@@ -38742,13 +38742,13 @@
         <v>1095</v>
       </c>
       <c r="B1096" t="str">
-        <v>FG-401866</v>
+        <v>FG-401498</v>
       </c>
       <c r="C1096" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (90MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1096" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR</v>
+        <v>SPRINKLER SET 6 MTR ISI</v>
       </c>
       <c r="E1096" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38757,7 +38757,7 @@
         <v>General</v>
       </c>
       <c r="G1096" t="str">
-        <v>90MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1096" t="str">
         <v>Nos</v>
@@ -38769,7 +38769,7 @@
         <v>Active</v>
       </c>
       <c r="K1096" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER SET 6 MTR ISI for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1097">
@@ -38777,13 +38777,13 @@
         <v>1096</v>
       </c>
       <c r="B1097" t="str">
-        <v>FG-401867</v>
+        <v>FG-401499</v>
       </c>
       <c r="C1097" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (90MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1097" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR</v>
+        <v>SPRINKLER SET 6 MTR ISI</v>
       </c>
       <c r="E1097" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38792,7 +38792,7 @@
         <v>General</v>
       </c>
       <c r="G1097" t="str">
-        <v>90MM L TYPE 3.2 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1097" t="str">
         <v>Nos</v>
@@ -38804,7 +38804,7 @@
         <v>Active</v>
       </c>
       <c r="K1097" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER SET 6 MTR ISI for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1098">
@@ -38812,10 +38812,10 @@
         <v>1097</v>
       </c>
       <c r="B1098" t="str">
-        <v>FG-401498</v>
+        <v>FG-401500</v>
       </c>
       <c r="C1098" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 2.5 KG)</v>
       </c>
       <c r="D1098" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38827,7 +38827,7 @@
         <v>General</v>
       </c>
       <c r="G1098" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>75MM C TYPE 2.5 KG</v>
       </c>
       <c r="H1098" t="str">
         <v>Nos</v>
@@ -38847,10 +38847,10 @@
         <v>1098</v>
       </c>
       <c r="B1099" t="str">
-        <v>FG-401499</v>
+        <v>FG-401524</v>
       </c>
       <c r="C1099" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 2.5 KG)</v>
       </c>
       <c r="D1099" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38862,7 +38862,7 @@
         <v>General</v>
       </c>
       <c r="G1099" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 2.5 KG</v>
       </c>
       <c r="H1099" t="str">
         <v>Nos</v>
@@ -38882,10 +38882,10 @@
         <v>1099</v>
       </c>
       <c r="B1100" t="str">
-        <v>FG-401500</v>
+        <v>FG-401501</v>
       </c>
       <c r="C1100" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 2.5 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1100" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38897,7 +38897,7 @@
         <v>General</v>
       </c>
       <c r="G1100" t="str">
-        <v>75MM C TYPE 2.5 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1100" t="str">
         <v>Nos</v>
@@ -38917,13 +38917,13 @@
         <v>1100</v>
       </c>
       <c r="B1101" t="str">
-        <v>FG-401524</v>
+        <v>FG-401495</v>
       </c>
       <c r="C1101" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 2.5 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1101" t="str">
-        <v>SPRINKLER SET 6 MTR ISI</v>
+        <v>SPRINKLER SET 6 MTR N-ISI</v>
       </c>
       <c r="E1101" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38932,7 +38932,7 @@
         <v>General</v>
       </c>
       <c r="G1101" t="str">
-        <v>75MM L TYPE 2.5 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1101" t="str">
         <v>Nos</v>
@@ -38944,7 +38944,7 @@
         <v>Active</v>
       </c>
       <c r="K1101" t="str">
-        <v>SPRINKLER SET 6 MTR ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER SET 6 MTR N-ISI for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1102">
@@ -38952,13 +38952,13 @@
         <v>1101</v>
       </c>
       <c r="B1102" t="str">
-        <v>FG-401501</v>
+        <v>FG-401496</v>
       </c>
       <c r="C1102" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1102" t="str">
-        <v>SPRINKLER SET 6 MTR ISI</v>
+        <v>SPRINKLER SET 6 MTR N-ISI</v>
       </c>
       <c r="E1102" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38967,7 +38967,7 @@
         <v>General</v>
       </c>
       <c r="G1102" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1102" t="str">
         <v>Nos</v>
@@ -38979,7 +38979,7 @@
         <v>Active</v>
       </c>
       <c r="K1102" t="str">
-        <v>SPRINKLER SET 6 MTR ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER SET 6 MTR N-ISI for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1103">
@@ -38987,10 +38987,10 @@
         <v>1102</v>
       </c>
       <c r="B1103" t="str">
-        <v>FG-401495</v>
+        <v>FG-401497</v>
       </c>
       <c r="C1103" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1103" t="str">
         <v>SPRINKLER SET 6 MTR N-ISI</v>
@@ -39002,7 +39002,7 @@
         <v>General</v>
       </c>
       <c r="G1103" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1103" t="str">
         <v>Nos</v>
@@ -39022,13 +39022,13 @@
         <v>1103</v>
       </c>
       <c r="B1104" t="str">
-        <v>FG-401496</v>
+        <v>FG-401503</v>
       </c>
       <c r="C1104" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER FITTINGS TEE (75MM, C TYPE)</v>
       </c>
       <c r="D1104" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI</v>
+        <v>SPRINKLER FITTINGS TEE</v>
       </c>
       <c r="E1104" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39037,7 +39037,7 @@
         <v>General</v>
       </c>
       <c r="G1104" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>75MM, C TYPE</v>
       </c>
       <c r="H1104" t="str">
         <v>Nos</v>
@@ -39049,7 +39049,7 @@
         <v>Active</v>
       </c>
       <c r="K1104" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS TEE for sprinkler irrigation systems. Available sizes: 75MM, C TYPE, 75MM, L TYPE, 63MM, C TYPE.</v>
       </c>
     </row>
     <row r="1105">
@@ -39057,13 +39057,13 @@
         <v>1104</v>
       </c>
       <c r="B1105" t="str">
-        <v>FG-401497</v>
+        <v>FG-401511</v>
       </c>
       <c r="C1105" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER FITTINGS TEE (75MM, L TYPE)</v>
       </c>
       <c r="D1105" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI</v>
+        <v>SPRINKLER FITTINGS TEE</v>
       </c>
       <c r="E1105" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39072,7 +39072,7 @@
         <v>General</v>
       </c>
       <c r="G1105" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM, L TYPE</v>
       </c>
       <c r="H1105" t="str">
         <v>Nos</v>
@@ -39084,7 +39084,7 @@
         <v>Active</v>
       </c>
       <c r="K1105" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS TEE for sprinkler irrigation systems. Available sizes: 75MM, C TYPE, 75MM, L TYPE, 63MM, C TYPE.</v>
       </c>
     </row>
     <row r="1106">
@@ -39092,13 +39092,13 @@
         <v>1105</v>
       </c>
       <c r="B1106" t="str">
-        <v>-</v>
+        <v>FG-401526</v>
       </c>
       <c r="C1106" t="str">
-        <v>SPRINKLER TEE ISI (63MM)</v>
+        <v>SPRINKLER FITTINGS TEE (63MM, C TYPE)</v>
       </c>
       <c r="D1106" t="str">
-        <v>SPRINKLER TEE ISI</v>
+        <v>SPRINKLER FITTINGS TEE</v>
       </c>
       <c r="E1106" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39107,7 +39107,7 @@
         <v>General</v>
       </c>
       <c r="G1106" t="str">
-        <v>63MM</v>
+        <v>63MM, C TYPE</v>
       </c>
       <c r="H1106" t="str">
         <v>Nos</v>
@@ -39119,7 +39119,7 @@
         <v>Active</v>
       </c>
       <c r="K1106" t="str">
-        <v>SPRINKLER TEE ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS TEE for sprinkler irrigation systems. Available sizes: 75MM, C TYPE, 75MM, L TYPE, 63MM, C TYPE.</v>
       </c>
     </row>
     <row r="1107">
@@ -39127,13 +39127,13 @@
         <v>1106</v>
       </c>
       <c r="B1107" t="str">
-        <v>-</v>
+        <v>FG-401504</v>
       </c>
       <c r="C1107" t="str">
-        <v>SPRINKLER TEE ISI (75MM)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (75MM C TYPE)</v>
       </c>
       <c r="D1107" t="str">
-        <v>SPRINKLER TEE ISI</v>
+        <v>SPRINKLER FITTINGS ADAPTOR</v>
       </c>
       <c r="E1107" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39142,7 +39142,7 @@
         <v>General</v>
       </c>
       <c r="G1107" t="str">
-        <v>75MM</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1107" t="str">
         <v>Nos</v>
@@ -39154,7 +39154,7 @@
         <v>Active</v>
       </c>
       <c r="K1107" t="str">
-        <v>SPRINKLER TEE ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS ADAPTOR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1108">
@@ -39162,10 +39162,10 @@
         <v>1107</v>
       </c>
       <c r="B1108" t="str">
-        <v>FG-401504</v>
+        <v>FG-401512</v>
       </c>
       <c r="C1108" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (75MM P TYPE)</v>
       </c>
       <c r="D1108" t="str">
         <v>SPRINKLER FITTINGS ADAPTOR</v>
@@ -39177,7 +39177,7 @@
         <v>General</v>
       </c>
       <c r="G1108" t="str">
-        <v>75MM C TYPE</v>
+        <v>75MM P TYPE</v>
       </c>
       <c r="H1108" t="str">
         <v>Nos</v>
@@ -39197,10 +39197,10 @@
         <v>1108</v>
       </c>
       <c r="B1109" t="str">
-        <v>FG-401512</v>
+        <v>FG-401527</v>
       </c>
       <c r="C1109" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (75MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (63MM C TYPE)</v>
       </c>
       <c r="D1109" t="str">
         <v>SPRINKLER FITTINGS ADAPTOR</v>
@@ -39212,7 +39212,7 @@
         <v>General</v>
       </c>
       <c r="G1109" t="str">
-        <v>75MM P TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1109" t="str">
         <v>Nos</v>
@@ -39232,13 +39232,13 @@
         <v>1109</v>
       </c>
       <c r="B1110" t="str">
-        <v>FG-401527</v>
+        <v>FG-401502</v>
       </c>
       <c r="C1110" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (75MM C TYPE)</v>
       </c>
       <c r="D1110" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR</v>
+        <v>SPRINKLER FITTINGS BEND</v>
       </c>
       <c r="E1110" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39247,7 +39247,7 @@
         <v>General</v>
       </c>
       <c r="G1110" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1110" t="str">
         <v>Nos</v>
@@ -39259,7 +39259,7 @@
         <v>Active</v>
       </c>
       <c r="K1110" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS BEND for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1111">
@@ -39267,10 +39267,10 @@
         <v>1110</v>
       </c>
       <c r="B1111" t="str">
-        <v>FG-401502</v>
+        <v>FG-401510</v>
       </c>
       <c r="C1111" t="str">
-        <v>SPRINKLER FITTINGS BEND (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (75MM L TYPE)</v>
       </c>
       <c r="D1111" t="str">
         <v>SPRINKLER FITTINGS BEND</v>
@@ -39282,7 +39282,7 @@
         <v>General</v>
       </c>
       <c r="G1111" t="str">
-        <v>75MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1111" t="str">
         <v>Nos</v>
@@ -39302,10 +39302,10 @@
         <v>1111</v>
       </c>
       <c r="B1112" t="str">
-        <v>FG-401510</v>
+        <v>FG-401525</v>
       </c>
       <c r="C1112" t="str">
-        <v>SPRINKLER FITTINGS BEND (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (63MM C TYPE)</v>
       </c>
       <c r="D1112" t="str">
         <v>SPRINKLER FITTINGS BEND</v>
@@ -39317,7 +39317,7 @@
         <v>General</v>
       </c>
       <c r="G1112" t="str">
-        <v>75MM L TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1112" t="str">
         <v>Nos</v>
@@ -39337,13 +39337,13 @@
         <v>1112</v>
       </c>
       <c r="B1113" t="str">
-        <v>FG-401525</v>
+        <v>FG-401514</v>
       </c>
       <c r="C1113" t="str">
-        <v>SPRINKLER FITTINGS BEND (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (75MM L TYPE)</v>
       </c>
       <c r="D1113" t="str">
-        <v>SPRINKLER FITTINGS BEND</v>
+        <v>SPRINKLER FITTINGS END CAP</v>
       </c>
       <c r="E1113" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39352,7 +39352,7 @@
         <v>General</v>
       </c>
       <c r="G1113" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1113" t="str">
         <v>Nos</v>
@@ -39364,7 +39364,7 @@
         <v>Active</v>
       </c>
       <c r="K1113" t="str">
-        <v>SPRINKLER FITTINGS BEND for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS END CAP for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1114">
@@ -39372,10 +39372,10 @@
         <v>1113</v>
       </c>
       <c r="B1114" t="str">
-        <v>FG-401514</v>
+        <v>FG-401506</v>
       </c>
       <c r="C1114" t="str">
-        <v>SPRINKLER FITTINGS END CAP (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (75MM C TYPE)</v>
       </c>
       <c r="D1114" t="str">
         <v>SPRINKLER FITTINGS END CAP</v>
@@ -39387,7 +39387,7 @@
         <v>General</v>
       </c>
       <c r="G1114" t="str">
-        <v>75MM L TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1114" t="str">
         <v>Nos</v>
@@ -39407,10 +39407,10 @@
         <v>1114</v>
       </c>
       <c r="B1115" t="str">
-        <v>FG-401506</v>
+        <v>FG-401529</v>
       </c>
       <c r="C1115" t="str">
-        <v>SPRINKLER FITTINGS END CAP (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (63MM C TYPE)</v>
       </c>
       <c r="D1115" t="str">
         <v>SPRINKLER FITTINGS END CAP</v>
@@ -39422,7 +39422,7 @@
         <v>General</v>
       </c>
       <c r="G1115" t="str">
-        <v>75MM C TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1115" t="str">
         <v>Nos</v>
@@ -39442,13 +39442,13 @@
         <v>1115</v>
       </c>
       <c r="B1116" t="str">
-        <v>FG-401529</v>
+        <v>FG-401517</v>
       </c>
       <c r="C1116" t="str">
-        <v>SPRINKLER FITTINGS END CAP (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (75MM P TYPE)</v>
       </c>
       <c r="D1116" t="str">
-        <v>SPRINKLER FITTINGS END CAP</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
       </c>
       <c r="E1116" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39457,7 +39457,7 @@
         <v>General</v>
       </c>
       <c r="G1116" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM P TYPE</v>
       </c>
       <c r="H1116" t="str">
         <v>Nos</v>
@@ -39469,7 +39469,7 @@
         <v>Active</v>
       </c>
       <c r="K1116" t="str">
-        <v>SPRINKLER FITTINGS END CAP for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1117">
@@ -39477,10 +39477,10 @@
         <v>1116</v>
       </c>
       <c r="B1117" t="str">
-        <v>FG-401517</v>
+        <v>FG-401518</v>
       </c>
       <c r="C1117" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (75MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (63MM P TYPE)</v>
       </c>
       <c r="D1117" t="str">
         <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
@@ -39492,7 +39492,7 @@
         <v>General</v>
       </c>
       <c r="G1117" t="str">
-        <v>75MM P TYPE</v>
+        <v>63MM P TYPE</v>
       </c>
       <c r="H1117" t="str">
         <v>Nos</v>
@@ -39512,13 +39512,13 @@
         <v>1117</v>
       </c>
       <c r="B1118" t="str">
-        <v>FG-401518</v>
+        <v>FG-401505</v>
       </c>
       <c r="C1118" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (63MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (75MM C TYPE)</v>
       </c>
       <c r="D1118" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
+        <v>SPRINKLER FITTINGS PCN</v>
       </c>
       <c r="E1118" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39527,7 +39527,7 @@
         <v>General</v>
       </c>
       <c r="G1118" t="str">
-        <v>63MM P TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1118" t="str">
         <v>Nos</v>
@@ -39539,7 +39539,7 @@
         <v>Active</v>
       </c>
       <c r="K1118" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS PCN for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1119">
@@ -39547,10 +39547,10 @@
         <v>1118</v>
       </c>
       <c r="B1119" t="str">
-        <v>FG-401505</v>
+        <v>FG-401513</v>
       </c>
       <c r="C1119" t="str">
-        <v>SPRINKLER FITTINGS PCN (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (75MM L TYPE)</v>
       </c>
       <c r="D1119" t="str">
         <v>SPRINKLER FITTINGS PCN</v>
@@ -39562,7 +39562,7 @@
         <v>General</v>
       </c>
       <c r="G1119" t="str">
-        <v>75MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1119" t="str">
         <v>Nos</v>
@@ -39582,10 +39582,10 @@
         <v>1119</v>
       </c>
       <c r="B1120" t="str">
-        <v>FG-401513</v>
+        <v>FG-401528</v>
       </c>
       <c r="C1120" t="str">
-        <v>SPRINKLER FITTINGS PCN (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (63MM C TYPE)</v>
       </c>
       <c r="D1120" t="str">
         <v>SPRINKLER FITTINGS PCN</v>
@@ -39597,7 +39597,7 @@
         <v>General</v>
       </c>
       <c r="G1120" t="str">
-        <v>75MM L TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1120" t="str">
         <v>Nos</v>
@@ -39617,13 +39617,13 @@
         <v>1120</v>
       </c>
       <c r="B1121" t="str">
-        <v>FG-401528</v>
+        <v>FG-401507</v>
       </c>
       <c r="C1121" t="str">
-        <v>SPRINKLER FITTINGS PCN (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL (20MM)</v>
       </c>
       <c r="D1121" t="str">
-        <v>SPRINKLER FITTINGS PCN</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL</v>
       </c>
       <c r="E1121" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39632,7 +39632,7 @@
         <v>General</v>
       </c>
       <c r="G1121" t="str">
-        <v>63MM C TYPE</v>
+        <v>20MM</v>
       </c>
       <c r="H1121" t="str">
         <v>Nos</v>
@@ -39644,7 +39644,7 @@
         <v>Active</v>
       </c>
       <c r="K1121" t="str">
-        <v>SPRINKLER FITTINGS PCN for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1122">
@@ -39652,13 +39652,13 @@
         <v>1121</v>
       </c>
       <c r="B1122" t="str">
-        <v>FG-401507</v>
+        <v>FG-401508</v>
       </c>
       <c r="C1122" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL (20MM)</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE (75MM C TYPE)</v>
       </c>
       <c r="D1122" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE</v>
       </c>
       <c r="E1122" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39667,7 +39667,7 @@
         <v>General</v>
       </c>
       <c r="G1122" t="str">
-        <v>20MM</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1122" t="str">
         <v>Nos</v>
@@ -39679,7 +39679,7 @@
         <v>Active</v>
       </c>
       <c r="K1122" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1123">
@@ -39687,10 +39687,10 @@
         <v>1122</v>
       </c>
       <c r="B1123" t="str">
-        <v>FG-401508</v>
+        <v>FG-401515</v>
       </c>
       <c r="C1123" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE (20MM L TYPE)</v>
       </c>
       <c r="D1123" t="str">
         <v>SPRINKLER FITTINGS GI RISER PIPE</v>
@@ -39702,7 +39702,7 @@
         <v>General</v>
       </c>
       <c r="G1123" t="str">
-        <v>75MM C TYPE</v>
+        <v>20MM L TYPE</v>
       </c>
       <c r="H1123" t="str">
         <v>Nos</v>
@@ -39722,25 +39722,25 @@
         <v>1123</v>
       </c>
       <c r="B1124" t="str">
-        <v>FG-401515</v>
+        <v>FG-401742</v>
       </c>
       <c r="C1124" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE (20MM L TYPE)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 1)</v>
       </c>
       <c r="D1124" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE</v>
+        <v>ROUND DRIPLINE 12MM ISI</v>
       </c>
       <c r="E1124" t="str">
-        <v>Sprinkler Pipes &amp; Fittings</v>
+        <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1124" t="str">
-        <v>General</v>
+        <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1124" t="str">
-        <v>20MM L TYPE</v>
+        <v>12-4-30 CLASS 1</v>
       </c>
       <c r="H1124" t="str">
-        <v>Nos</v>
+        <v>ROLL</v>
       </c>
       <c r="I1124" t="str">
         <v>-</v>
@@ -39749,7 +39749,7 @@
         <v>Active</v>
       </c>
       <c r="K1124" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE for sprinkler irrigation systems.</v>
+        <v>ROUND DRIPLINE 12MM ISI certified.</v>
       </c>
     </row>
     <row r="1125">
@@ -39757,10 +39757,10 @@
         <v>1124</v>
       </c>
       <c r="B1125" t="str">
-        <v>FG-401742</v>
+        <v>FG-401743</v>
       </c>
       <c r="C1125" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 1)</v>
       </c>
       <c r="D1125" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39772,7 +39772,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1125" t="str">
-        <v>12-4-30 CLASS 1</v>
+        <v>12-4-40 CLASS 1</v>
       </c>
       <c r="H1125" t="str">
         <v>ROLL</v>
@@ -39792,10 +39792,10 @@
         <v>1125</v>
       </c>
       <c r="B1126" t="str">
-        <v>FG-401743</v>
+        <v>FG-401744</v>
       </c>
       <c r="C1126" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 1)</v>
       </c>
       <c r="D1126" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39807,7 +39807,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1126" t="str">
-        <v>12-4-40 CLASS 1</v>
+        <v>12-4-50 CLASS 1</v>
       </c>
       <c r="H1126" t="str">
         <v>ROLL</v>
@@ -39827,10 +39827,10 @@
         <v>1126</v>
       </c>
       <c r="B1127" t="str">
-        <v>FG-401744</v>
+        <v>FG-401751</v>
       </c>
       <c r="C1127" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1127" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39842,7 +39842,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1127" t="str">
-        <v>12-4-50 CLASS 1</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1127" t="str">
         <v>ROLL</v>
@@ -39862,10 +39862,10 @@
         <v>1127</v>
       </c>
       <c r="B1128" t="str">
-        <v>FG-401751</v>
+        <v>FG-401752</v>
       </c>
       <c r="C1128" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1128" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39877,7 +39877,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1128" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1128" t="str">
         <v>ROLL</v>
@@ -39897,10 +39897,10 @@
         <v>1128</v>
       </c>
       <c r="B1129" t="str">
-        <v>FG-401752</v>
+        <v>FG-401753</v>
       </c>
       <c r="C1129" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1129" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39912,7 +39912,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1129" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1129" t="str">
         <v>ROLL</v>
@@ -39932,10 +39932,10 @@
         <v>1129</v>
       </c>
       <c r="B1130" t="str">
-        <v>FG-401753</v>
+        <v>FG-401754</v>
       </c>
       <c r="C1130" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1130" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39947,7 +39947,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1130" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1130" t="str">
         <v>ROLL</v>
@@ -39967,10 +39967,10 @@
         <v>1130</v>
       </c>
       <c r="B1131" t="str">
-        <v>FG-401754</v>
+        <v>FG-401755</v>
       </c>
       <c r="C1131" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1131" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39982,7 +39982,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1131" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1131" t="str">
         <v>ROLL</v>
@@ -40002,10 +40002,10 @@
         <v>1131</v>
       </c>
       <c r="B1132" t="str">
-        <v>FG-401755</v>
+        <v>FG-401756</v>
       </c>
       <c r="C1132" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1132" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -40017,7 +40017,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1132" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1132" t="str">
         <v>ROLL</v>
@@ -40037,13 +40037,13 @@
         <v>1132</v>
       </c>
       <c r="B1133" t="str">
-        <v>FG-401756</v>
+        <v>FG-401745</v>
       </c>
       <c r="C1133" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1133" t="str">
-        <v>ROUND DRIPLINE 12MM ISI</v>
+        <v>ROUND DRIPLINE 16MM ISI</v>
       </c>
       <c r="E1133" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40052,7 +40052,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1133" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1133" t="str">
         <v>ROLL</v>
@@ -40064,7 +40064,7 @@
         <v>Active</v>
       </c>
       <c r="K1133" t="str">
-        <v>ROUND DRIPLINE 12MM ISI certified.</v>
+        <v>ROUND DRIPLINE 16MM ISI certified.</v>
       </c>
     </row>
     <row r="1134">
@@ -40072,10 +40072,10 @@
         <v>1133</v>
       </c>
       <c r="B1134" t="str">
-        <v>FG-401745</v>
+        <v>FG-401746</v>
       </c>
       <c r="C1134" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1134" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40087,7 +40087,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1134" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1134" t="str">
         <v>ROLL</v>
@@ -40107,10 +40107,10 @@
         <v>1134</v>
       </c>
       <c r="B1135" t="str">
-        <v>FG-401746</v>
+        <v>FG-401747</v>
       </c>
       <c r="C1135" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1135" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40122,7 +40122,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1135" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1135" t="str">
         <v>ROLL</v>
@@ -40142,10 +40142,10 @@
         <v>1135</v>
       </c>
       <c r="B1136" t="str">
-        <v>FG-401747</v>
+        <v>FG-401757</v>
       </c>
       <c r="C1136" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1136" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40157,7 +40157,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1136" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1136" t="str">
         <v>ROLL</v>
@@ -40177,10 +40177,10 @@
         <v>1136</v>
       </c>
       <c r="B1137" t="str">
-        <v>FG-401757</v>
+        <v>FG-401758</v>
       </c>
       <c r="C1137" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1137" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40192,7 +40192,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1137" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1137" t="str">
         <v>ROLL</v>
@@ -40212,10 +40212,10 @@
         <v>1137</v>
       </c>
       <c r="B1138" t="str">
-        <v>FG-401758</v>
+        <v>FG-401759</v>
       </c>
       <c r="C1138" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1138" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40227,7 +40227,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1138" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1138" t="str">
         <v>ROLL</v>
@@ -40247,13 +40247,13 @@
         <v>1138</v>
       </c>
       <c r="B1139" t="str">
-        <v>FG-401759</v>
+        <v>-</v>
       </c>
       <c r="C1139" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-30 CLASS-1)</v>
       </c>
       <c r="D1139" t="str">
-        <v>ROUND DRIPLINE 16MM ISI</v>
+        <v>20MM ROUND INLINE PIPE ISI</v>
       </c>
       <c r="E1139" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40262,10 +40262,10 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1139" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>20-4-30 CLASS-1</v>
       </c>
       <c r="H1139" t="str">
-        <v>ROLL</v>
+        <v>MTR</v>
       </c>
       <c r="I1139" t="str">
         <v>-</v>
@@ -40274,7 +40274,7 @@
         <v>Active</v>
       </c>
       <c r="K1139" t="str">
-        <v>ROUND DRIPLINE 16MM ISI certified.</v>
+        <v>20mm Round Inline Drip Pipe ISI certified.</v>
       </c>
     </row>
     <row r="1140">
@@ -40285,7 +40285,7 @@
         <v>-</v>
       </c>
       <c r="C1140" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-30 CLASS-1)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-40 CLASS-1)</v>
       </c>
       <c r="D1140" t="str">
         <v>20MM ROUND INLINE PIPE ISI</v>
@@ -40297,7 +40297,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1140" t="str">
-        <v>20-4-30 CLASS-1</v>
+        <v>20-4-40 CLASS-1</v>
       </c>
       <c r="H1140" t="str">
         <v>MTR</v>
@@ -40320,7 +40320,7 @@
         <v>-</v>
       </c>
       <c r="C1141" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-40 CLASS-1)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-50 CLASS-1)</v>
       </c>
       <c r="D1141" t="str">
         <v>20MM ROUND INLINE PIPE ISI</v>
@@ -40332,7 +40332,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1141" t="str">
-        <v>20-4-40 CLASS-1</v>
+        <v>20-4-50 CLASS-1</v>
       </c>
       <c r="H1141" t="str">
         <v>MTR</v>
@@ -40352,25 +40352,25 @@
         <v>1141</v>
       </c>
       <c r="B1142" t="str">
-        <v>-</v>
+        <v>FG-401763</v>
       </c>
       <c r="C1142" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-50 CLASS-1)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1142" t="str">
-        <v>20MM ROUND INLINE PIPE ISI</v>
+        <v>FLAT DRIPLINE 12MM ISI</v>
       </c>
       <c r="E1142" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1142" t="str">
-        <v>ROUND DRIP ISI</v>
+        <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1142" t="str">
-        <v>20-4-50 CLASS-1</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1142" t="str">
-        <v>MTR</v>
+        <v>ROLL</v>
       </c>
       <c r="I1142" t="str">
         <v>-</v>
@@ -40379,7 +40379,7 @@
         <v>Active</v>
       </c>
       <c r="K1142" t="str">
-        <v>20mm Round Inline Drip Pipe ISI certified.</v>
+        <v>FLAT DRIPLINE 12MM ISI certified.</v>
       </c>
     </row>
     <row r="1143">
@@ -40387,10 +40387,10 @@
         <v>1142</v>
       </c>
       <c r="B1143" t="str">
-        <v>FG-401763</v>
+        <v>FG-401764</v>
       </c>
       <c r="C1143" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1143" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40402,7 +40402,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1143" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1143" t="str">
         <v>ROLL</v>
@@ -40422,10 +40422,10 @@
         <v>1143</v>
       </c>
       <c r="B1144" t="str">
-        <v>FG-401764</v>
+        <v>FG-401765</v>
       </c>
       <c r="C1144" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1144" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40437,7 +40437,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1144" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1144" t="str">
         <v>ROLL</v>
@@ -40457,10 +40457,10 @@
         <v>1144</v>
       </c>
       <c r="B1145" t="str">
-        <v>FG-401765</v>
+        <v>FG-401766</v>
       </c>
       <c r="C1145" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1145" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40472,7 +40472,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1145" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1145" t="str">
         <v>ROLL</v>
@@ -40492,10 +40492,10 @@
         <v>1145</v>
       </c>
       <c r="B1146" t="str">
-        <v>FG-401766</v>
+        <v>FG-401767</v>
       </c>
       <c r="C1146" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1146" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40507,7 +40507,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1146" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1146" t="str">
         <v>ROLL</v>
@@ -40527,10 +40527,10 @@
         <v>1146</v>
       </c>
       <c r="B1147" t="str">
-        <v>FG-401767</v>
+        <v>FG-401768</v>
       </c>
       <c r="C1147" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1147" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40542,7 +40542,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1147" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1147" t="str">
         <v>ROLL</v>
@@ -40562,13 +40562,13 @@
         <v>1147</v>
       </c>
       <c r="B1148" t="str">
-        <v>FG-401768</v>
+        <v>FG-401760</v>
       </c>
       <c r="C1148" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1148" t="str">
-        <v>FLAT DRIPLINE 12MM ISI</v>
+        <v>FLAT DRIPLINE 16MM ISI</v>
       </c>
       <c r="E1148" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40577,7 +40577,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1148" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1148" t="str">
         <v>ROLL</v>
@@ -40589,7 +40589,7 @@
         <v>Active</v>
       </c>
       <c r="K1148" t="str">
-        <v>FLAT DRIPLINE 12MM ISI certified.</v>
+        <v>FLAT DRIPLINE 16MM ISI certified.</v>
       </c>
     </row>
     <row r="1149">
@@ -40597,10 +40597,10 @@
         <v>1148</v>
       </c>
       <c r="B1149" t="str">
-        <v>FG-401760</v>
+        <v>FG-401761</v>
       </c>
       <c r="C1149" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1149" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40612,7 +40612,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1149" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1149" t="str">
         <v>ROLL</v>
@@ -40632,10 +40632,10 @@
         <v>1149</v>
       </c>
       <c r="B1150" t="str">
-        <v>FG-401761</v>
+        <v>FG-401762</v>
       </c>
       <c r="C1150" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1150" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40647,7 +40647,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1150" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1150" t="str">
         <v>ROLL</v>
@@ -40667,10 +40667,10 @@
         <v>1150</v>
       </c>
       <c r="B1151" t="str">
-        <v>FG-401762</v>
+        <v>FG-401769</v>
       </c>
       <c r="C1151" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1151" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40682,7 +40682,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1151" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1151" t="str">
         <v>ROLL</v>
@@ -40702,10 +40702,10 @@
         <v>1151</v>
       </c>
       <c r="B1152" t="str">
-        <v>FG-401769</v>
+        <v>FG-401770</v>
       </c>
       <c r="C1152" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1152" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40717,7 +40717,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1152" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1152" t="str">
         <v>ROLL</v>
@@ -40737,10 +40737,10 @@
         <v>1152</v>
       </c>
       <c r="B1153" t="str">
-        <v>FG-401770</v>
+        <v>FG-401779</v>
       </c>
       <c r="C1153" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1153" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40752,7 +40752,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1153" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1153" t="str">
         <v>ROLL</v>
@@ -40772,13 +40772,13 @@
         <v>1153</v>
       </c>
       <c r="B1154" t="str">
-        <v>FG-401779</v>
+        <v>FG-401771</v>
       </c>
       <c r="C1154" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-30 CLASS 1)</v>
       </c>
       <c r="D1154" t="str">
-        <v>FLAT DRIPLINE 16MM ISI</v>
+        <v>FLAT DRIPLINE 20MM ISI</v>
       </c>
       <c r="E1154" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40787,7 +40787,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1154" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>20-4-30 CLASS 1</v>
       </c>
       <c r="H1154" t="str">
         <v>ROLL</v>
@@ -40799,7 +40799,7 @@
         <v>Active</v>
       </c>
       <c r="K1154" t="str">
-        <v>FLAT DRIPLINE 16MM ISI certified.</v>
+        <v>FLAT DRIPLINE 20MM ISI certified.</v>
       </c>
     </row>
     <row r="1155">
@@ -40807,10 +40807,10 @@
         <v>1154</v>
       </c>
       <c r="B1155" t="str">
-        <v>FG-401771</v>
+        <v>FG-401772</v>
       </c>
       <c r="C1155" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-40 CLASS 1)</v>
       </c>
       <c r="D1155" t="str">
         <v>FLAT DRIPLINE 20MM ISI</v>
@@ -40822,7 +40822,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1155" t="str">
-        <v>20-4-30 CLASS 1</v>
+        <v>20-4-40 CLASS 1</v>
       </c>
       <c r="H1155" t="str">
         <v>ROLL</v>
@@ -40842,10 +40842,10 @@
         <v>1155</v>
       </c>
       <c r="B1156" t="str">
-        <v>FG-401772</v>
+        <v>FG-401773</v>
       </c>
       <c r="C1156" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-50 CLASS 1)</v>
       </c>
       <c r="D1156" t="str">
         <v>FLAT DRIPLINE 20MM ISI</v>
@@ -40857,7 +40857,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1156" t="str">
-        <v>20-4-40 CLASS 1</v>
+        <v>20-4-50 CLASS 1</v>
       </c>
       <c r="H1156" t="str">
         <v>ROLL</v>
@@ -40877,25 +40877,25 @@
         <v>1156</v>
       </c>
       <c r="B1157" t="str">
-        <v>FG-401773</v>
+        <v>-</v>
       </c>
       <c r="C1157" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-50 CLASS 1)</v>
+        <v>12MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1157" t="str">
-        <v>FLAT DRIPLINE 20MM ISI</v>
+        <v>12MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1157" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1157" t="str">
-        <v>FLAT DRIP ISI</v>
+        <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1157" t="str">
-        <v>20-4-50 CLASS 1</v>
+        <v>CLASS-2</v>
       </c>
       <c r="H1157" t="str">
-        <v>ROLL</v>
+        <v>MTR</v>
       </c>
       <c r="I1157" t="str">
         <v>-</v>
@@ -40904,7 +40904,7 @@
         <v>Active</v>
       </c>
       <c r="K1157" t="str">
-        <v>FLAT DRIPLINE 20MM ISI certified.</v>
+        <v>12mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1158">
@@ -40915,10 +40915,10 @@
         <v>-</v>
       </c>
       <c r="C1158" t="str">
-        <v>12MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>16MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1158" t="str">
-        <v>12MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>16MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1158" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40939,7 +40939,7 @@
         <v>Active</v>
       </c>
       <c r="K1158" t="str">
-        <v>12mm Plain Lateral Online Drip Pipe.</v>
+        <v>16mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1159">
@@ -40950,10 +40950,10 @@
         <v>-</v>
       </c>
       <c r="C1159" t="str">
-        <v>16MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>20MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1159" t="str">
-        <v>16MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>20MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1159" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40974,7 +40974,7 @@
         <v>Active</v>
       </c>
       <c r="K1159" t="str">
-        <v>16mm Plain Lateral Online Drip Pipe.</v>
+        <v>20mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1160">
@@ -40985,10 +40985,10 @@
         <v>-</v>
       </c>
       <c r="C1160" t="str">
-        <v>20MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-1)</v>
       </c>
       <c r="D1160" t="str">
-        <v>20MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1160" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40997,7 +40997,7 @@
         <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1160" t="str">
-        <v>CLASS-2</v>
+        <v>CLASS-1</v>
       </c>
       <c r="H1160" t="str">
         <v>MTR</v>
@@ -41009,7 +41009,7 @@
         <v>Active</v>
       </c>
       <c r="K1160" t="str">
-        <v>20mm Plain Lateral Online Drip Pipe.</v>
+        <v>32mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1161">
@@ -41020,7 +41020,7 @@
         <v>-</v>
       </c>
       <c r="C1161" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-1)</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1161" t="str">
         <v>32MM PLAIN LATERAL ONLINE PIPE</v>
@@ -41032,7 +41032,7 @@
         <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1161" t="str">
-        <v>CLASS-1</v>
+        <v>CLASS-2</v>
       </c>
       <c r="H1161" t="str">
         <v>MTR</v>
@@ -41052,22 +41052,22 @@
         <v>1161</v>
       </c>
       <c r="B1162" t="str">
-        <v>-</v>
+        <v>FG-401763</v>
       </c>
       <c r="C1162" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1162" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12</v>
       </c>
       <c r="E1162" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1162" t="str">
-        <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
+        <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1162" t="str">
-        <v>CLASS-2</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1162" t="str">
         <v>MTR</v>
@@ -41079,7 +41079,7 @@
         <v>Active</v>
       </c>
       <c r="K1162" t="str">
-        <v>32mm Plain Lateral Online Drip Pipe.</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12. Available sizes: 12-4-30 CLASS 2, 12-4-40 CLASS 2, 12-4-50 CLASS 2, 12-4-30 CLASS 3, 12-4-40 CLASS 3, 12-4-50 CLASS 3.</v>
       </c>
     </row>
     <row r="1163">
@@ -41087,10 +41087,10 @@
         <v>1162</v>
       </c>
       <c r="B1163" t="str">
-        <v>FG-401763</v>
+        <v>FG-401764</v>
       </c>
       <c r="C1163" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1163" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41102,7 +41102,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1163" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1163" t="str">
         <v>MTR</v>
@@ -41122,10 +41122,10 @@
         <v>1163</v>
       </c>
       <c r="B1164" t="str">
-        <v>FG-401764</v>
+        <v>FG-401765</v>
       </c>
       <c r="C1164" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1164" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41137,7 +41137,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1164" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1164" t="str">
         <v>MTR</v>
@@ -41157,10 +41157,10 @@
         <v>1164</v>
       </c>
       <c r="B1165" t="str">
-        <v>FG-401765</v>
+        <v>FG-401766</v>
       </c>
       <c r="C1165" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1165" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41172,7 +41172,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1165" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1165" t="str">
         <v>MTR</v>
@@ -41192,10 +41192,10 @@
         <v>1165</v>
       </c>
       <c r="B1166" t="str">
-        <v>FG-401766</v>
+        <v>FG-401767</v>
       </c>
       <c r="C1166" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1166" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41207,7 +41207,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1166" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1166" t="str">
         <v>MTR</v>
@@ -41227,10 +41227,10 @@
         <v>1166</v>
       </c>
       <c r="B1167" t="str">
-        <v>FG-401767</v>
+        <v>FG-401768</v>
       </c>
       <c r="C1167" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1167" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41242,7 +41242,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1167" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1167" t="str">
         <v>MTR</v>
@@ -41262,13 +41262,13 @@
         <v>1167</v>
       </c>
       <c r="B1168" t="str">
-        <v>FG-401768</v>
+        <v>FG-401760</v>
       </c>
       <c r="C1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16</v>
       </c>
       <c r="E1168" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -41277,7 +41277,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1168" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1168" t="str">
         <v>MTR</v>
@@ -41289,7 +41289,7 @@
         <v>Active</v>
       </c>
       <c r="K1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12. Available sizes: 12-4-30 CLASS 2, 12-4-40 CLASS 2, 12-4-50 CLASS 2, 12-4-30 CLASS 3, 12-4-40 CLASS 3, 12-4-50 CLASS 3.</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16. Available sizes: 16-4-30 CLASS 1, 16-4-40 CLASS 1, 16-4-50 CLASS 1, 16-4-30 CLASS 2, 16-4-40 CLASS 2, 16-4-50 CLASS 2.</v>
       </c>
     </row>
     <row r="1169">
@@ -41297,10 +41297,10 @@
         <v>1168</v>
       </c>
       <c r="B1169" t="str">
-        <v>FG-401760</v>
+        <v>FG-401761</v>
       </c>
       <c r="C1169" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1169" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41312,7 +41312,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1169" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1169" t="str">
         <v>MTR</v>
@@ -41332,10 +41332,10 @@
         <v>1169</v>
       </c>
       <c r="B1170" t="str">
-        <v>FG-401761</v>
+        <v>FG-401762</v>
       </c>
       <c r="C1170" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1170" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41347,7 +41347,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1170" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1170" t="str">
         <v>MTR</v>
@@ -41367,10 +41367,10 @@
         <v>1170</v>
       </c>
       <c r="B1171" t="str">
-        <v>FG-401762</v>
+        <v>FG-401769</v>
       </c>
       <c r="C1171" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1171" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41382,7 +41382,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1171" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1171" t="str">
         <v>MTR</v>
@@ -41402,10 +41402,10 @@
         <v>1171</v>
       </c>
       <c r="B1172" t="str">
-        <v>FG-401769</v>
+        <v>FG-401770</v>
       </c>
       <c r="C1172" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1172" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41417,7 +41417,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1172" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1172" t="str">
         <v>MTR</v>
@@ -41437,10 +41437,10 @@
         <v>1172</v>
       </c>
       <c r="B1173" t="str">
-        <v>FG-401770</v>
+        <v>FG-401779</v>
       </c>
       <c r="C1173" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1173" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41452,7 +41452,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1173" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1173" t="str">
         <v>MTR</v>
@@ -41472,13 +41472,13 @@
         <v>1173</v>
       </c>
       <c r="B1174" t="str">
-        <v>FG-401779</v>
+        <v>FG-401771</v>
       </c>
       <c r="C1174" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-30 CLASS 1)</v>
       </c>
       <c r="D1174" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20</v>
       </c>
       <c r="E1174" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -41487,7 +41487,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1174" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>20-4-30 CLASS 1</v>
       </c>
       <c r="H1174" t="str">
         <v>MTR</v>
@@ -41499,7 +41499,7 @@
         <v>Active</v>
       </c>
       <c r="K1174" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16. Available sizes: 16-4-30 CLASS 1, 16-4-40 CLASS 1, 16-4-50 CLASS 1, 16-4-30 CLASS 2, 16-4-40 CLASS 2, 16-4-50 CLASS 2.</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20. Available sizes: 20-4-30 CLASS 1, 20-4-40 CLASS 1, 20-4-50 CLASS 1.</v>
       </c>
     </row>
     <row r="1175">
@@ -41507,10 +41507,10 @@
         <v>1174</v>
       </c>
       <c r="B1175" t="str">
-        <v>FG-401771</v>
+        <v>FG-401772</v>
       </c>
       <c r="C1175" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-40 CLASS 1)</v>
       </c>
       <c r="D1175" t="str">
         <v>FLAT DRIPLINE ISI 400MTR 20</v>
@@ -41522,7 +41522,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1175" t="str">
-        <v>20-4-30 CLASS 1</v>
+        <v>20-4-40 CLASS 1</v>
       </c>
       <c r="H1175" t="str">
         <v>MTR</v>
@@ -41542,10 +41542,10 @@
         <v>1175</v>
       </c>
       <c r="B1176" t="str">
-        <v>FG-401772</v>
+        <v>FG-401773</v>
       </c>
       <c r="C1176" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-50 CLASS 1)</v>
       </c>
       <c r="D1176" t="str">
         <v>FLAT DRIPLINE ISI 400MTR 20</v>
@@ -41557,7 +41557,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1176" t="str">
-        <v>20-4-40 CLASS 1</v>
+        <v>20-4-50 CLASS 1</v>
       </c>
       <c r="H1176" t="str">
         <v>MTR</v>
@@ -41577,22 +41577,22 @@
         <v>1176</v>
       </c>
       <c r="B1177" t="str">
-        <v>FG-401773</v>
+        <v>FG-401066</v>
       </c>
       <c r="C1177" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-50 CLASS 1)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
       </c>
       <c r="D1177" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
       </c>
       <c r="E1177" t="str">
-        <v>DRIP IRRIGATION SYSTEM</v>
+        <v>UPVC CASING PIPES</v>
       </c>
       <c r="F1177" t="str">
-        <v>FLAT DRIP (PEPSI) - INLINE</v>
+        <v>General</v>
       </c>
       <c r="G1177" t="str">
-        <v>20-4-50 CLASS 1</v>
+        <v>35MM 1 1/4 Inch</v>
       </c>
       <c r="H1177" t="str">
         <v>MTR</v>
@@ -41604,7 +41604,7 @@
         <v>Active</v>
       </c>
       <c r="K1177" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20. Available sizes: 20-4-30 CLASS 1, 20-4-40 CLASS 1, 20-4-50 CLASS 1.</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 40MM 1 1/2 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1178">
@@ -41612,10 +41612,10 @@
         <v>1177</v>
       </c>
       <c r="B1178" t="str">
-        <v>FG-401066</v>
+        <v>FG-401067</v>
       </c>
       <c r="C1178" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (40MM 1 1/2 Inch)</v>
       </c>
       <c r="D1178" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41627,7 +41627,7 @@
         <v>General</v>
       </c>
       <c r="G1178" t="str">
-        <v>35MM 1 1/4 Inch</v>
+        <v>40MM 1 1/2 Inch</v>
       </c>
       <c r="H1178" t="str">
         <v>MTR</v>
@@ -41647,10 +41647,10 @@
         <v>1178</v>
       </c>
       <c r="B1179" t="str">
-        <v>FG-401067</v>
+        <v>FG-401068</v>
       </c>
       <c r="C1179" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (40MM 1 1/2 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (50MM 2 Inch)</v>
       </c>
       <c r="D1179" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41662,7 +41662,7 @@
         <v>General</v>
       </c>
       <c r="G1179" t="str">
-        <v>40MM 1 1/2 Inch</v>
+        <v>50MM 2 Inch</v>
       </c>
       <c r="H1179" t="str">
         <v>MTR</v>
@@ -41682,10 +41682,10 @@
         <v>1179</v>
       </c>
       <c r="B1180" t="str">
-        <v>FG-401068</v>
+        <v>FG-401069</v>
       </c>
       <c r="C1180" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (50MM 2 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (100MM 4 Inch)</v>
       </c>
       <c r="D1180" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41697,7 +41697,7 @@
         <v>General</v>
       </c>
       <c r="G1180" t="str">
-        <v>50MM 2 Inch</v>
+        <v>100MM 4 Inch</v>
       </c>
       <c r="H1180" t="str">
         <v>MTR</v>
@@ -41717,10 +41717,10 @@
         <v>1180</v>
       </c>
       <c r="B1181" t="str">
-        <v>FG-401069</v>
+        <v>FG-401070</v>
       </c>
       <c r="C1181" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (100MM 4 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1181" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41732,7 +41732,7 @@
         <v>General</v>
       </c>
       <c r="G1181" t="str">
-        <v>100MM 4 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1181" t="str">
         <v>MTR</v>
@@ -41752,10 +41752,10 @@
         <v>1181</v>
       </c>
       <c r="B1182" t="str">
-        <v>FG-401070</v>
+        <v>FG-401071</v>
       </c>
       <c r="C1182" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1182" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41767,7 +41767,7 @@
         <v>General</v>
       </c>
       <c r="G1182" t="str">
-        <v>125MM 5 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1182" t="str">
         <v>MTR</v>
@@ -41787,10 +41787,10 @@
         <v>1182</v>
       </c>
       <c r="B1183" t="str">
-        <v>FG-401071</v>
+        <v>FG-401072</v>
       </c>
       <c r="C1183" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1183" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41802,7 +41802,7 @@
         <v>General</v>
       </c>
       <c r="G1183" t="str">
-        <v>150MM 6 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1183" t="str">
         <v>MTR</v>
@@ -41822,10 +41822,10 @@
         <v>1183</v>
       </c>
       <c r="B1184" t="str">
-        <v>FG-401072</v>
+        <v>FG-401073</v>
       </c>
       <c r="C1184" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1184" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41837,7 +41837,7 @@
         <v>General</v>
       </c>
       <c r="G1184" t="str">
-        <v>175MM 7 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1184" t="str">
         <v>MTR</v>
@@ -41857,13 +41857,13 @@
         <v>1184</v>
       </c>
       <c r="B1185" t="str">
-        <v>FG-401073</v>
+        <v>FG-401074</v>
       </c>
       <c r="C1185" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1185" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
       </c>
       <c r="E1185" t="str">
         <v>UPVC CASING PIPES</v>
@@ -41872,7 +41872,7 @@
         <v>General</v>
       </c>
       <c r="G1185" t="str">
-        <v>200MM 8 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1185" t="str">
         <v>MTR</v>
@@ -41884,7 +41884,7 @@
         <v>Active</v>
       </c>
       <c r="K1185" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 40MM 1 1/2 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1186">
@@ -41892,10 +41892,10 @@
         <v>1185</v>
       </c>
       <c r="B1186" t="str">
-        <v>FG-401074</v>
+        <v>FG-401075</v>
       </c>
       <c r="C1186" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1186" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41907,7 +41907,7 @@
         <v>General</v>
       </c>
       <c r="G1186" t="str">
-        <v>125MM 5 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1186" t="str">
         <v>MTR</v>
@@ -41927,10 +41927,10 @@
         <v>1186</v>
       </c>
       <c r="B1187" t="str">
-        <v>FG-401075</v>
+        <v>FG-401076</v>
       </c>
       <c r="C1187" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1187" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41942,7 +41942,7 @@
         <v>General</v>
       </c>
       <c r="G1187" t="str">
-        <v>150MM 6 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1187" t="str">
         <v>MTR</v>
@@ -41962,10 +41962,10 @@
         <v>1187</v>
       </c>
       <c r="B1188" t="str">
-        <v>FG-401076</v>
+        <v>FG-401077</v>
       </c>
       <c r="C1188" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1188" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41977,7 +41977,7 @@
         <v>General</v>
       </c>
       <c r="G1188" t="str">
-        <v>175MM 7 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1188" t="str">
         <v>MTR</v>
@@ -41997,13 +41997,13 @@
         <v>1188</v>
       </c>
       <c r="B1189" t="str">
-        <v>FG-401077</v>
+        <v>FG-401149</v>
       </c>
       <c r="C1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M (140MM 5 Inch)</v>
       </c>
       <c r="D1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M</v>
       </c>
       <c r="E1189" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42012,7 +42012,7 @@
         <v>General</v>
       </c>
       <c r="G1189" t="str">
-        <v>200MM 8 Inch</v>
+        <v>140MM 5 Inch</v>
       </c>
       <c r="H1189" t="str">
         <v>MTR</v>
@@ -42024,7 +42024,7 @@
         <v>Active</v>
       </c>
       <c r="K1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M. Available sizes: 140MM 5 Inch.</v>
       </c>
     </row>
     <row r="1190">
@@ -42032,13 +42032,13 @@
         <v>1189</v>
       </c>
       <c r="B1190" t="str">
-        <v>FG-401149</v>
+        <v>FG-401150</v>
       </c>
       <c r="C1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M (140MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M (140MM 5 Inch)</v>
       </c>
       <c r="D1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M</v>
       </c>
       <c r="E1190" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42059,7 +42059,7 @@
         <v>Active</v>
       </c>
       <c r="K1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M. Available sizes: 140MM 5 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M. Available sizes: 140MM 5 Inch.</v>
       </c>
     </row>
     <row r="1191">
@@ -42067,13 +42067,13 @@
         <v>1190</v>
       </c>
       <c r="B1191" t="str">
-        <v>FG-401150</v>
+        <v>FG-401078</v>
       </c>
       <c r="C1191" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M (140MM 5 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1191" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
       </c>
       <c r="E1191" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42082,7 +42082,7 @@
         <v>General</v>
       </c>
       <c r="G1191" t="str">
-        <v>140MM 5 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1191" t="str">
         <v>MTR</v>
@@ -42094,7 +42094,7 @@
         <v>Active</v>
       </c>
       <c r="K1191" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M. Available sizes: 140MM 5 Inch.</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1192">
@@ -42102,10 +42102,10 @@
         <v>1191</v>
       </c>
       <c r="B1192" t="str">
-        <v>FG-401078</v>
+        <v>FG-401079</v>
       </c>
       <c r="C1192" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1192" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42117,7 +42117,7 @@
         <v>General</v>
       </c>
       <c r="G1192" t="str">
-        <v>125MM 5 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1192" t="str">
         <v>MTR</v>
@@ -42137,10 +42137,10 @@
         <v>1192</v>
       </c>
       <c r="B1193" t="str">
-        <v>FG-401079</v>
+        <v>FG-401080</v>
       </c>
       <c r="C1193" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1193" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42152,7 +42152,7 @@
         <v>General</v>
       </c>
       <c r="G1193" t="str">
-        <v>150MM 6 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1193" t="str">
         <v>MTR</v>
@@ -42172,10 +42172,10 @@
         <v>1193</v>
       </c>
       <c r="B1194" t="str">
-        <v>FG-401080</v>
+        <v>FG-401081</v>
       </c>
       <c r="C1194" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1194" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42187,7 +42187,7 @@
         <v>General</v>
       </c>
       <c r="G1194" t="str">
-        <v>175MM 7 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1194" t="str">
         <v>MTR</v>
@@ -42207,13 +42207,13 @@
         <v>1194</v>
       </c>
       <c r="B1195" t="str">
-        <v>FG-401081</v>
+        <v>FG-401119</v>
       </c>
       <c r="C1195" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
       </c>
       <c r="D1195" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
       </c>
       <c r="E1195" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42222,7 +42222,7 @@
         <v>General</v>
       </c>
       <c r="G1195" t="str">
-        <v>200MM 8 Inch</v>
+        <v>35MM 1 1/4 Inch</v>
       </c>
       <c r="H1195" t="str">
         <v>MTR</v>
@@ -42234,7 +42234,7 @@
         <v>Active</v>
       </c>
       <c r="K1195" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1196">
@@ -42242,10 +42242,10 @@
         <v>1195</v>
       </c>
       <c r="B1196" t="str">
-        <v>FG-401119</v>
+        <v>FG-401121</v>
       </c>
       <c r="C1196" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (50MM 2 Inch)</v>
       </c>
       <c r="D1196" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42257,7 +42257,7 @@
         <v>General</v>
       </c>
       <c r="G1196" t="str">
-        <v>35MM 1 1/4 Inch</v>
+        <v>50MM 2 Inch</v>
       </c>
       <c r="H1196" t="str">
         <v>MTR</v>
@@ -42277,10 +42277,10 @@
         <v>1196</v>
       </c>
       <c r="B1197" t="str">
-        <v>FG-401121</v>
+        <v>FG-401122</v>
       </c>
       <c r="C1197" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (50MM 2 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (100MM 4 Inch)</v>
       </c>
       <c r="D1197" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42292,7 +42292,7 @@
         <v>General</v>
       </c>
       <c r="G1197" t="str">
-        <v>50MM 2 Inch</v>
+        <v>100MM 4 Inch</v>
       </c>
       <c r="H1197" t="str">
         <v>MTR</v>
@@ -42312,10 +42312,10 @@
         <v>1197</v>
       </c>
       <c r="B1198" t="str">
-        <v>FG-401122</v>
+        <v>FG-401123</v>
       </c>
       <c r="C1198" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (100MM 4 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1198" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42327,7 +42327,7 @@
         <v>General</v>
       </c>
       <c r="G1198" t="str">
-        <v>100MM 4 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1198" t="str">
         <v>MTR</v>
@@ -42347,10 +42347,10 @@
         <v>1198</v>
       </c>
       <c r="B1199" t="str">
-        <v>FG-401123</v>
+        <v>FG-401124</v>
       </c>
       <c r="C1199" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1199" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42362,7 +42362,7 @@
         <v>General</v>
       </c>
       <c r="G1199" t="str">
-        <v>125MM 5 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1199" t="str">
         <v>MTR</v>
@@ -42382,10 +42382,10 @@
         <v>1199</v>
       </c>
       <c r="B1200" t="str">
-        <v>FG-401124</v>
+        <v>FG-401125</v>
       </c>
       <c r="C1200" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1200" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42397,7 +42397,7 @@
         <v>General</v>
       </c>
       <c r="G1200" t="str">
-        <v>150MM 6 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1200" t="str">
         <v>MTR</v>
@@ -42417,10 +42417,10 @@
         <v>1200</v>
       </c>
       <c r="B1201" t="str">
-        <v>FG-401125</v>
+        <v>FG-401126</v>
       </c>
       <c r="C1201" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1201" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42432,7 +42432,7 @@
         <v>General</v>
       </c>
       <c r="G1201" t="str">
-        <v>175MM 7 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1201" t="str">
         <v>MTR</v>
@@ -42452,22 +42452,22 @@
         <v>1201</v>
       </c>
       <c r="B1202" t="str">
-        <v>FG-401126</v>
+        <v>FG-401166</v>
       </c>
       <c r="C1202" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (200MM 8 Inch)</v>
+        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1202" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
+        <v>COLOUMN PIPE ECO V4</v>
       </c>
       <c r="E1202" t="str">
-        <v>UPVC CASING PIPES</v>
+        <v>UPVC COLUMN PIPES</v>
       </c>
       <c r="F1202" t="str">
         <v>General</v>
       </c>
       <c r="G1202" t="str">
-        <v>200MM 8 Inch</v>
+        <v>33MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1202" t="str">
         <v>MTR</v>
@@ -42479,7 +42479,7 @@
         <v>Active</v>
       </c>
       <c r="K1202" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>COLOUMN PIPE ECO V4 for submersible pump systems.</v>
       </c>
     </row>
     <row r="1203">
@@ -42487,10 +42487,10 @@
         <v>1202</v>
       </c>
       <c r="B1203" t="str">
-        <v>FG-401166</v>
+        <v>FG-401162</v>
       </c>
       <c r="C1203" t="str">
-        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG BELL END TYPE)</v>
       </c>
       <c r="D1203" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42502,7 +42502,7 @@
         <v>General</v>
       </c>
       <c r="G1203" t="str">
-        <v>33MM 12.5KG COUPLER TYPE</v>
+        <v>33MM 12.5KG BELL END TYPE</v>
       </c>
       <c r="H1203" t="str">
         <v>MTR</v>
@@ -42522,10 +42522,10 @@
         <v>1203</v>
       </c>
       <c r="B1204" t="str">
-        <v>FG-401162</v>
+        <v>FG-401165</v>
       </c>
       <c r="C1204" t="str">
-        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG BELL END TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 10KG COUPLER TYPE)</v>
       </c>
       <c r="D1204" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42537,7 +42537,7 @@
         <v>General</v>
       </c>
       <c r="G1204" t="str">
-        <v>33MM 12.5KG BELL END TYPE</v>
+        <v>42MM 10KG COUPLER TYPE</v>
       </c>
       <c r="H1204" t="str">
         <v>MTR</v>
@@ -42557,10 +42557,10 @@
         <v>1204</v>
       </c>
       <c r="B1205" t="str">
-        <v>FG-401165</v>
+        <v>FG-401167</v>
       </c>
       <c r="C1205" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 10KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1205" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42572,7 +42572,7 @@
         <v>General</v>
       </c>
       <c r="G1205" t="str">
-        <v>42MM 10KG COUPLER TYPE</v>
+        <v>42MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1205" t="str">
         <v>MTR</v>
@@ -42592,10 +42592,10 @@
         <v>1205</v>
       </c>
       <c r="B1206" t="str">
-        <v>FG-401167</v>
+        <v>FG-401163</v>
       </c>
       <c r="C1206" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG BELL END TYPE)</v>
       </c>
       <c r="D1206" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42607,7 +42607,7 @@
         <v>General</v>
       </c>
       <c r="G1206" t="str">
-        <v>42MM 12.5KG COUPLER TYPE</v>
+        <v>42MM 12.5KG BELL END TYPE</v>
       </c>
       <c r="H1206" t="str">
         <v>MTR</v>
@@ -42627,10 +42627,10 @@
         <v>1206</v>
       </c>
       <c r="B1207" t="str">
-        <v>FG-401163</v>
+        <v>FG-401164</v>
       </c>
       <c r="C1207" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG BELL END TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (48MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1207" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42642,7 +42642,7 @@
         <v>General</v>
       </c>
       <c r="G1207" t="str">
-        <v>42MM 12.5KG BELL END TYPE</v>
+        <v>48MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1207" t="str">
         <v>MTR</v>
@@ -42662,10 +42662,10 @@
         <v>1207</v>
       </c>
       <c r="B1208" t="str">
-        <v>FG-401164</v>
+        <v>FG-401168</v>
       </c>
       <c r="C1208" t="str">
-        <v>COLOUMN PIPE ECO V4 (48MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (60MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1208" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42677,7 +42677,7 @@
         <v>General</v>
       </c>
       <c r="G1208" t="str">
-        <v>48MM 12.5KG COUPLER TYPE</v>
+        <v>60MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1208" t="str">
         <v>MTR</v>
@@ -42697,13 +42697,13 @@
         <v>1208</v>
       </c>
       <c r="B1209" t="str">
-        <v>FG-401168</v>
+        <v>FG-401175</v>
       </c>
       <c r="C1209" t="str">
-        <v>COLOUMN PIPE ECO V4 (60MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (33MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1209" t="str">
-        <v>COLOUMN PIPE ECO V4</v>
+        <v>COLOUMN PIPE MEDIUM</v>
       </c>
       <c r="E1209" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -42712,7 +42712,7 @@
         <v>General</v>
       </c>
       <c r="G1209" t="str">
-        <v>60MM 12.5KG COUPLER TYPE</v>
+        <v>33MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1209" t="str">
         <v>MTR</v>
@@ -42724,7 +42724,7 @@
         <v>Active</v>
       </c>
       <c r="K1209" t="str">
-        <v>COLOUMN PIPE ECO V4 for submersible pump systems.</v>
+        <v>COLOUMN PIPE MEDIUM for submersible pump systems.</v>
       </c>
     </row>
     <row r="1210">
@@ -42732,10 +42732,10 @@
         <v>1209</v>
       </c>
       <c r="B1210" t="str">
-        <v>FG-401175</v>
+        <v>FG-401177</v>
       </c>
       <c r="C1210" t="str">
-        <v>COLOUMN PIPE MEDIUM (33MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (42MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1210" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42747,7 +42747,7 @@
         <v>General</v>
       </c>
       <c r="G1210" t="str">
-        <v>33MM 18KG COUPLER TYPE</v>
+        <v>42MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1210" t="str">
         <v>MTR</v>
@@ -42767,10 +42767,10 @@
         <v>1210</v>
       </c>
       <c r="B1211" t="str">
-        <v>FG-401177</v>
+        <v>FG-401176</v>
       </c>
       <c r="C1211" t="str">
-        <v>COLOUMN PIPE MEDIUM (42MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (48MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1211" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42782,7 +42782,7 @@
         <v>General</v>
       </c>
       <c r="G1211" t="str">
-        <v>42MM 18KG COUPLER TYPE</v>
+        <v>48MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1211" t="str">
         <v>MTR</v>
@@ -42802,10 +42802,10 @@
         <v>1211</v>
       </c>
       <c r="B1212" t="str">
-        <v>FG-401176</v>
+        <v>FG-401178</v>
       </c>
       <c r="C1212" t="str">
-        <v>COLOUMN PIPE MEDIUM (48MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (60MM 15KG COUPLER TYPE)</v>
       </c>
       <c r="D1212" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42817,7 +42817,7 @@
         <v>General</v>
       </c>
       <c r="G1212" t="str">
-        <v>48MM 18KG COUPLER TYPE</v>
+        <v>60MM 15KG COUPLER TYPE</v>
       </c>
       <c r="H1212" t="str">
         <v>MTR</v>
@@ -42837,10 +42837,10 @@
         <v>1212</v>
       </c>
       <c r="B1213" t="str">
-        <v>FG-401178</v>
+        <v>FG-401180</v>
       </c>
       <c r="C1213" t="str">
-        <v>COLOUMN PIPE MEDIUM (60MM 15KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (75MM 10KG COUPLER TYPE)</v>
       </c>
       <c r="D1213" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42852,7 +42852,7 @@
         <v>General</v>
       </c>
       <c r="G1213" t="str">
-        <v>60MM 15KG COUPLER TYPE</v>
+        <v>75MM 10KG COUPLER TYPE</v>
       </c>
       <c r="H1213" t="str">
         <v>MTR</v>
@@ -42872,13 +42872,13 @@
         <v>1213</v>
       </c>
       <c r="B1214" t="str">
-        <v>FG-401180</v>
+        <v>FG-401169</v>
       </c>
       <c r="C1214" t="str">
-        <v>COLOUMN PIPE MEDIUM (75MM 10KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (33MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1214" t="str">
-        <v>COLOUMN PIPE MEDIUM</v>
+        <v>COLOUMN PIPE STANDARD</v>
       </c>
       <c r="E1214" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -42887,7 +42887,7 @@
         <v>General</v>
       </c>
       <c r="G1214" t="str">
-        <v>75MM 10KG COUPLER TYPE</v>
+        <v>33MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1214" t="str">
         <v>MTR</v>
@@ -42899,7 +42899,7 @@
         <v>Active</v>
       </c>
       <c r="K1214" t="str">
-        <v>COLOUMN PIPE MEDIUM for submersible pump systems.</v>
+        <v>COLOUMN PIPE STANDARD for submersible pump systems.</v>
       </c>
     </row>
     <row r="1215">
@@ -42907,10 +42907,10 @@
         <v>1214</v>
       </c>
       <c r="B1215" t="str">
-        <v>FG-401169</v>
+        <v>FG-401171</v>
       </c>
       <c r="C1215" t="str">
-        <v>COLOUMN PIPE STANDARD (33MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (42MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1215" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42922,7 +42922,7 @@
         <v>General</v>
       </c>
       <c r="G1215" t="str">
-        <v>33MM 25KG COUPLER TYPE</v>
+        <v>42MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1215" t="str">
         <v>MTR</v>
@@ -42942,10 +42942,10 @@
         <v>1215</v>
       </c>
       <c r="B1216" t="str">
-        <v>FG-401171</v>
+        <v>FG-401170</v>
       </c>
       <c r="C1216" t="str">
-        <v>COLOUMN PIPE STANDARD (42MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (48MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1216" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42957,7 +42957,7 @@
         <v>General</v>
       </c>
       <c r="G1216" t="str">
-        <v>42MM 25KG COUPLER TYPE</v>
+        <v>48MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1216" t="str">
         <v>MTR</v>
@@ -42977,10 +42977,10 @@
         <v>1216</v>
       </c>
       <c r="B1217" t="str">
-        <v>FG-401170</v>
+        <v>FG-401172</v>
       </c>
       <c r="C1217" t="str">
-        <v>COLOUMN PIPE STANDARD (48MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (60MM 20KG COUPLER TYPE)</v>
       </c>
       <c r="D1217" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42992,7 +42992,7 @@
         <v>General</v>
       </c>
       <c r="G1217" t="str">
-        <v>48MM 25KG COUPLER TYPE</v>
+        <v>60MM 20KG COUPLER TYPE</v>
       </c>
       <c r="H1217" t="str">
         <v>MTR</v>
@@ -43012,10 +43012,10 @@
         <v>1217</v>
       </c>
       <c r="B1218" t="str">
-        <v>FG-401172</v>
+        <v>FG-401174</v>
       </c>
       <c r="C1218" t="str">
-        <v>COLOUMN PIPE STANDARD (60MM 20KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (75MM 20KG COUPLER TYPE)</v>
       </c>
       <c r="D1218" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -43027,7 +43027,7 @@
         <v>General</v>
       </c>
       <c r="G1218" t="str">
-        <v>60MM 20KG COUPLER TYPE</v>
+        <v>75MM 20KG COUPLER TYPE</v>
       </c>
       <c r="H1218" t="str">
         <v>MTR</v>
@@ -43047,13 +43047,13 @@
         <v>1218</v>
       </c>
       <c r="B1219" t="str">
-        <v>FG-401174</v>
+        <v>-</v>
       </c>
       <c r="C1219" t="str">
-        <v>COLOUMN PIPE STANDARD (75MM 20KG COUPLER TYPE)</v>
+        <v>3M STANDARD PLUS PIPE (60MM 25 COUPLER TYPE)</v>
       </c>
       <c r="D1219" t="str">
-        <v>COLOUMN PIPE STANDARD</v>
+        <v>3M STANDARD PLUS PIPE</v>
       </c>
       <c r="E1219" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43062,7 +43062,7 @@
         <v>General</v>
       </c>
       <c r="G1219" t="str">
-        <v>75MM 20KG COUPLER TYPE</v>
+        <v>60MM 25 COUPLER TYPE</v>
       </c>
       <c r="H1219" t="str">
         <v>MTR</v>
@@ -43074,7 +43074,7 @@
         <v>Active</v>
       </c>
       <c r="K1219" t="str">
-        <v>COLOUMN PIPE STANDARD for submersible pump systems.</v>
+        <v>3M Standard Plus UPVC Column Pipe for submersible pump systems.</v>
       </c>
     </row>
     <row r="1220">
@@ -43082,13 +43082,13 @@
         <v>1219</v>
       </c>
       <c r="B1220" t="str">
-        <v>-</v>
+        <v>FG-401182</v>
       </c>
       <c r="C1220" t="str">
-        <v>3M STANDARD PLUS PIPE (60MM 25 COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (42MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1220" t="str">
-        <v>3M STANDARD PLUS PIPE</v>
+        <v>COLOUMN PIPE HEAVY</v>
       </c>
       <c r="E1220" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43097,7 +43097,7 @@
         <v>General</v>
       </c>
       <c r="G1220" t="str">
-        <v>60MM 25 COUPLER TYPE</v>
+        <v>42MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1220" t="str">
         <v>MTR</v>
@@ -43109,7 +43109,7 @@
         <v>Active</v>
       </c>
       <c r="K1220" t="str">
-        <v>3M Standard Plus UPVC Column Pipe for submersible pump systems.</v>
+        <v>COLOUMN PIPE HEAVY for submersible pump systems.</v>
       </c>
     </row>
     <row r="1221">
@@ -43117,10 +43117,10 @@
         <v>1220</v>
       </c>
       <c r="B1221" t="str">
-        <v>FG-401182</v>
+        <v>FG-401181</v>
       </c>
       <c r="C1221" t="str">
-        <v>COLOUMN PIPE HEAVY (42MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (48MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1221" t="str">
         <v>COLOUMN PIPE HEAVY</v>
@@ -43132,7 +43132,7 @@
         <v>General</v>
       </c>
       <c r="G1221" t="str">
-        <v>42MM 30KG COUPLER TYPE</v>
+        <v>48MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1221" t="str">
         <v>MTR</v>
@@ -43152,10 +43152,10 @@
         <v>1221</v>
       </c>
       <c r="B1222" t="str">
-        <v>FG-401181</v>
+        <v>FG-401183</v>
       </c>
       <c r="C1222" t="str">
-        <v>COLOUMN PIPE HEAVY (48MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (60MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1222" t="str">
         <v>COLOUMN PIPE HEAVY</v>
@@ -43167,7 +43167,7 @@
         <v>General</v>
       </c>
       <c r="G1222" t="str">
-        <v>48MM 30KG COUPLER TYPE</v>
+        <v>60MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1222" t="str">
         <v>MTR</v>
@@ -43187,13 +43187,13 @@
         <v>1222</v>
       </c>
       <c r="B1223" t="str">
-        <v>FG-401183</v>
+        <v>FG-401179</v>
       </c>
       <c r="C1223" t="str">
-        <v>COLOUMN PIPE HEAVY (60MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM PLUS (60MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1223" t="str">
-        <v>COLOUMN PIPE HEAVY</v>
+        <v>COLOUMN PIPE MEDIUM PLUS</v>
       </c>
       <c r="E1223" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43202,7 +43202,7 @@
         <v>General</v>
       </c>
       <c r="G1223" t="str">
-        <v>60MM 30KG COUPLER TYPE</v>
+        <v>60MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1223" t="str">
         <v>MTR</v>
@@ -43214,7 +43214,7 @@
         <v>Active</v>
       </c>
       <c r="K1223" t="str">
-        <v>COLOUMN PIPE HEAVY for submersible pump systems.</v>
+        <v>COLOUMN PIPE MEDIUM PLUS for submersible pump systems.</v>
       </c>
     </row>
     <row r="1224">
@@ -43222,34 +43222,34 @@
         <v>1223</v>
       </c>
       <c r="B1224" t="str">
-        <v>FG-401179</v>
+        <v>FG-401569</v>
       </c>
       <c r="C1224" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS (60MM 18KG COUPLER TYPE)</v>
+        <v>CONSTRUCTION GHAMELA SHIVA (15 Inch)</v>
       </c>
       <c r="D1224" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS</v>
+        <v>CONSTRUCTION GHAMELA SHIVA</v>
       </c>
       <c r="E1224" t="str">
-        <v>UPVC COLUMN PIPES</v>
+        <v>HOUSEHOLD PRODUCTS</v>
       </c>
       <c r="F1224" t="str">
         <v>General</v>
       </c>
       <c r="G1224" t="str">
-        <v>60MM 18KG COUPLER TYPE</v>
+        <v>15 Inch</v>
       </c>
       <c r="H1224" t="str">
-        <v>MTR</v>
+        <v>BAGS</v>
       </c>
       <c r="I1224" t="str">
-        <v>-</v>
+        <v>75</v>
       </c>
       <c r="J1224" t="str">
         <v>Active</v>
       </c>
       <c r="K1224" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS for submersible pump systems.</v>
+        <v>CONSTRUCTION GHAMELA SHIVA high durability ghamela.</v>
       </c>
     </row>
     <row r="1225">
@@ -43257,13 +43257,13 @@
         <v>1224</v>
       </c>
       <c r="B1225" t="str">
-        <v>FG-401569</v>
+        <v>FG-401570</v>
       </c>
       <c r="C1225" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA (15 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA GOURI (15 Inch)</v>
       </c>
       <c r="D1225" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA</v>
+        <v>MULTIPURPOSE GHAMELA GOURI</v>
       </c>
       <c r="E1225" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43284,7 +43284,7 @@
         <v>Active</v>
       </c>
       <c r="K1225" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA GOURI high durability ghamela.</v>
       </c>
     </row>
     <row r="1226">
@@ -43292,13 +43292,13 @@
         <v>1225</v>
       </c>
       <c r="B1226" t="str">
-        <v>FG-401570</v>
+        <v>FG-401571</v>
       </c>
       <c r="C1226" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI (15 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA (16 Inch)</v>
       </c>
       <c r="D1226" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA</v>
       </c>
       <c r="E1226" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43307,19 +43307,19 @@
         <v>General</v>
       </c>
       <c r="G1226" t="str">
-        <v>15 Inch</v>
+        <v>16 Inch</v>
       </c>
       <c r="H1226" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1226" t="str">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="J1226" t="str">
         <v>Active</v>
       </c>
       <c r="K1226" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA high durability ghamela.</v>
       </c>
     </row>
     <row r="1227">
@@ -43327,13 +43327,13 @@
         <v>1226</v>
       </c>
       <c r="B1227" t="str">
-        <v>FG-401571</v>
+        <v>FG-401573</v>
       </c>
       <c r="C1227" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA (16 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV (18 Inch)</v>
       </c>
       <c r="D1227" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV</v>
       </c>
       <c r="E1227" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43342,19 +43342,19 @@
         <v>General</v>
       </c>
       <c r="G1227" t="str">
-        <v>16 Inch</v>
+        <v>18 Inch</v>
       </c>
       <c r="H1227" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1227" t="str">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J1227" t="str">
         <v>Active</v>
       </c>
       <c r="K1227" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV high durability ghamela.</v>
       </c>
     </row>
     <row r="1228">
@@ -43362,13 +43362,13 @@
         <v>1227</v>
       </c>
       <c r="B1228" t="str">
-        <v>FG-401573</v>
+        <v>FG-401574</v>
       </c>
       <c r="C1228" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV (18 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET (20 Inch)</v>
       </c>
       <c r="D1228" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET</v>
       </c>
       <c r="E1228" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43377,19 +43377,19 @@
         <v>General</v>
       </c>
       <c r="G1228" t="str">
-        <v>18 Inch</v>
+        <v>20 Inch</v>
       </c>
       <c r="H1228" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1228" t="str">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J1228" t="str">
         <v>Active</v>
       </c>
       <c r="K1228" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET high durability ghamela.</v>
       </c>
     </row>
     <row r="1229">
@@ -43397,13 +43397,13 @@
         <v>1228</v>
       </c>
       <c r="B1229" t="str">
-        <v>FG-401574</v>
+        <v>FG-401572</v>
       </c>
       <c r="C1229" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET (20 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI (17 Inch)</v>
       </c>
       <c r="D1229" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI</v>
       </c>
       <c r="E1229" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43412,19 +43412,19 @@
         <v>General</v>
       </c>
       <c r="G1229" t="str">
-        <v>20 Inch</v>
+        <v>17 Inch</v>
       </c>
       <c r="H1229" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1229" t="str">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J1229" t="str">
         <v>Active</v>
       </c>
       <c r="K1229" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI high durability ghamela.</v>
       </c>
     </row>
     <row r="1230">
@@ -43432,13 +43432,13 @@
         <v>1229</v>
       </c>
       <c r="B1230" t="str">
-        <v>FG-401572</v>
+        <v>FG-401575</v>
       </c>
       <c r="C1230" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI (17 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ (22 Inch)</v>
       </c>
       <c r="D1230" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ</v>
       </c>
       <c r="E1230" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43447,19 +43447,19 @@
         <v>General</v>
       </c>
       <c r="G1230" t="str">
-        <v>17 Inch</v>
+        <v>22 Inch</v>
       </c>
       <c r="H1230" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1230" t="str">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J1230" t="str">
         <v>Active</v>
       </c>
       <c r="K1230" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ high durability ghamela.</v>
       </c>
     </row>
     <row r="1231">
@@ -43467,13 +43467,13 @@
         <v>1230</v>
       </c>
       <c r="B1231" t="str">
-        <v>FG-401575</v>
+        <v>FG-401578</v>
       </c>
       <c r="C1231" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ (22 Inch)</v>
+        <v>AQUA PLAST GHAMELA 16 (16 Inch)</v>
       </c>
       <c r="D1231" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ</v>
+        <v>AQUA PLAST GHAMELA 16</v>
       </c>
       <c r="E1231" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43482,19 +43482,19 @@
         <v>General</v>
       </c>
       <c r="G1231" t="str">
-        <v>22 Inch</v>
+        <v>16 Inch</v>
       </c>
       <c r="H1231" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1231" t="str">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J1231" t="str">
         <v>Active</v>
       </c>
       <c r="K1231" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ high durability ghamela.</v>
+        <v>AQUA PLAST GHAMELA 16 high durability ghamela.</v>
       </c>
     </row>
     <row r="1232">
@@ -43502,13 +43502,13 @@
         <v>1231</v>
       </c>
       <c r="B1232" t="str">
-        <v>FG-401578</v>
+        <v>FG-401579</v>
       </c>
       <c r="C1232" t="str">
-        <v>AQUA PLAST GHAMELA 16 (16 Inch)</v>
+        <v>AQUA PLAST GHAMELA 17 (17 Inch)</v>
       </c>
       <c r="D1232" t="str">
-        <v>AQUA PLAST GHAMELA 16</v>
+        <v>AQUA PLAST GHAMELA 17</v>
       </c>
       <c r="E1232" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43517,7 +43517,7 @@
         <v>General</v>
       </c>
       <c r="G1232" t="str">
-        <v>16 Inch</v>
+        <v>17 Inch</v>
       </c>
       <c r="H1232" t="str">
         <v>BAGS</v>
@@ -43529,7 +43529,7 @@
         <v>Active</v>
       </c>
       <c r="K1232" t="str">
-        <v>AQUA PLAST GHAMELA 16 high durability ghamela.</v>
+        <v>AQUA PLAST GHAMELA 17 high durability ghamela.</v>
       </c>
     </row>
     <row r="1233">
@@ -43537,34 +43537,34 @@
         <v>1232</v>
       </c>
       <c r="B1233" t="str">
-        <v>FG-401579</v>
+        <v>FG-401364</v>
       </c>
       <c r="C1233" t="str">
-        <v>AQUA PLAST GHAMELA 17 (17 Inch)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1/2 15MM)</v>
       </c>
       <c r="D1233" t="str">
-        <v>AQUA PLAST GHAMELA 17</v>
+        <v>GAP-ORA FLOW GARDEN PIPE</v>
       </c>
       <c r="E1233" t="str">
-        <v>HOUSEHOLD PRODUCTS</v>
+        <v>Garden, Braided &amp; LDPE Pipes</v>
       </c>
       <c r="F1233" t="str">
         <v>General</v>
       </c>
       <c r="G1233" t="str">
-        <v>17 Inch</v>
+        <v>1/2 15MM</v>
       </c>
       <c r="H1233" t="str">
-        <v>BAGS</v>
+        <v>BDL</v>
       </c>
       <c r="I1233" t="str">
-        <v>60</v>
+        <v>-</v>
       </c>
       <c r="J1233" t="str">
         <v>Active</v>
       </c>
       <c r="K1233" t="str">
-        <v>AQUA PLAST GHAMELA 17 high durability ghamela.</v>
+        <v>GAP-ORA FLOW GARDEN PIPE. Available sizes: 1/2 15MM, 3/4 20MM, 1 25MM, 1 1/4 32MM.</v>
       </c>
     </row>
     <row r="1234">
@@ -43572,13 +43572,13 @@
         <v>1233</v>
       </c>
       <c r="B1234" t="str">
-        <v>-</v>
+        <v>FG-401365</v>
       </c>
       <c r="C1234" t="str">
-        <v>ORA FLOW - HEAVY DUTY PIPE (15MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (3/4 20MM)</v>
       </c>
       <c r="D1234" t="str">
-        <v>ORA FLOW - HEAVY DUTY PIPE</v>
+        <v>GAP-ORA FLOW GARDEN PIPE</v>
       </c>
       <c r="E1234" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43587,7 +43587,7 @@
         <v>General</v>
       </c>
       <c r="G1234" t="str">
-        <v>15MM</v>
+        <v>3/4 20MM</v>
       </c>
       <c r="H1234" t="str">
         <v>BDL</v>
@@ -43599,7 +43599,7 @@
         <v>Active</v>
       </c>
       <c r="K1234" t="str">
-        <v>Ora Flow Heavy Duty Garden Pipe.</v>
+        <v>GAP-ORA FLOW GARDEN PIPE. Available sizes: 1/2 15MM, 3/4 20MM, 1 25MM, 1 1/4 32MM.</v>
       </c>
     </row>
     <row r="1235">
@@ -43607,13 +43607,13 @@
         <v>1234</v>
       </c>
       <c r="B1235" t="str">
-        <v>-</v>
+        <v>FG-401366</v>
       </c>
       <c r="C1235" t="str">
-        <v>ORA FLOW - HEAVY DUTY PIPE (20MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1 25MM)</v>
       </c>
       <c r="D1235" t="str">
-        <v>ORA FLOW - HEAVY DUTY PIPE</v>
+        <v>GAP-ORA FLOW GARDEN PIPE</v>
       </c>
       <c r="E1235" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43622,7 +43622,7 @@
         <v>General</v>
       </c>
       <c r="G1235" t="str">
-        <v>20MM</v>
+        <v>1 25MM</v>
       </c>
       <c r="H1235" t="str">
         <v>BDL</v>
@@ -43634,7 +43634,7 @@
         <v>Active</v>
       </c>
       <c r="K1235" t="str">
-        <v>Ora Flow Heavy Duty Garden Pipe.</v>
+        <v>GAP-ORA FLOW GARDEN PIPE. Available sizes: 1/2 15MM, 3/4 20MM, 1 25MM, 1 1/4 32MM.</v>
       </c>
     </row>
     <row r="1236">
@@ -43642,13 +43642,13 @@
         <v>1235</v>
       </c>
       <c r="B1236" t="str">
-        <v>-</v>
+        <v>FG-401367</v>
       </c>
       <c r="C1236" t="str">
-        <v>ORA FLOW - HEAVY DUTY PIPE (25MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1 1/4 32MM)</v>
       </c>
       <c r="D1236" t="str">
-        <v>ORA FLOW - HEAVY DUTY PIPE</v>
+        <v>GAP-ORA FLOW GARDEN PIPE</v>
       </c>
       <c r="E1236" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43657,7 +43657,7 @@
         <v>General</v>
       </c>
       <c r="G1236" t="str">
-        <v>25MM</v>
+        <v>1 1/4 32MM</v>
       </c>
       <c r="H1236" t="str">
         <v>BDL</v>
@@ -43669,7 +43669,7 @@
         <v>Active</v>
       </c>
       <c r="K1236" t="str">
-        <v>Ora Flow Heavy Duty Garden Pipe.</v>
+        <v>GAP-ORA FLOW GARDEN PIPE. Available sizes: 1/2 15MM, 3/4 20MM, 1 25MM, 1 1/4 32MM.</v>
       </c>
     </row>
     <row r="1237">
@@ -43677,13 +43677,13 @@
         <v>1236</v>
       </c>
       <c r="B1237" t="str">
-        <v>-</v>
+        <v>FG-401370</v>
       </c>
       <c r="C1237" t="str">
-        <v>ORA FLOW - HEAVY DUTY PIPE (32MM)</v>
+        <v>GAP-ORA BRAIDED PIPE (15MM 1/2)</v>
       </c>
       <c r="D1237" t="str">
-        <v>ORA FLOW - HEAVY DUTY PIPE</v>
+        <v>GAP-ORA BRAIDED PIPE</v>
       </c>
       <c r="E1237" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43692,7 +43692,7 @@
         <v>General</v>
       </c>
       <c r="G1237" t="str">
-        <v>32MM</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1237" t="str">
         <v>BDL</v>
@@ -43704,7 +43704,7 @@
         <v>Active</v>
       </c>
       <c r="K1237" t="str">
-        <v>Ora Flow Heavy Duty Garden Pipe.</v>
+        <v>GAP-ORA BRAIDED PIPE.</v>
       </c>
     </row>
     <row r="1238">
@@ -43712,10 +43712,10 @@
         <v>1237</v>
       </c>
       <c r="B1238" t="str">
-        <v>FG-401370</v>
+        <v>FG-401371</v>
       </c>
       <c r="C1238" t="str">
-        <v>GAP-ORA BRAIDED PIPE (15MM 1/2)</v>
+        <v>GAP-ORA BRAIDED PIPE (20MM 3/4)</v>
       </c>
       <c r="D1238" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43727,7 +43727,7 @@
         <v>General</v>
       </c>
       <c r="G1238" t="str">
-        <v>15MM 1/2</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1238" t="str">
         <v>BDL</v>
@@ -43747,10 +43747,10 @@
         <v>1238</v>
       </c>
       <c r="B1239" t="str">
-        <v>FG-401371</v>
+        <v>FG-401372</v>
       </c>
       <c r="C1239" t="str">
-        <v>GAP-ORA BRAIDED PIPE (20MM 3/4)</v>
+        <v>GAP-ORA BRAIDED PIPE (25MM 1)</v>
       </c>
       <c r="D1239" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43762,7 +43762,7 @@
         <v>General</v>
       </c>
       <c r="G1239" t="str">
-        <v>20MM 3/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1239" t="str">
         <v>BDL</v>
@@ -43782,10 +43782,10 @@
         <v>1239</v>
       </c>
       <c r="B1240" t="str">
-        <v>FG-401372</v>
+        <v>FG-401373</v>
       </c>
       <c r="C1240" t="str">
-        <v>GAP-ORA BRAIDED PIPE (25MM 1)</v>
+        <v>GAP-ORA BRAIDED PIPE (32MM 1 1/4)</v>
       </c>
       <c r="D1240" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43797,7 +43797,7 @@
         <v>General</v>
       </c>
       <c r="G1240" t="str">
-        <v>25MM 1</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1240" t="str">
         <v>BDL</v>
@@ -43817,13 +43817,13 @@
         <v>1240</v>
       </c>
       <c r="B1241" t="str">
-        <v>FG-401373</v>
+        <v>FG-401355</v>
       </c>
       <c r="C1241" t="str">
-        <v>GAP-ORA BRAIDED PIPE (32MM 1 1/4)</v>
+        <v>GARDEN FOAM PIPES (15MM 1/2)</v>
       </c>
       <c r="D1241" t="str">
-        <v>GAP-ORA BRAIDED PIPE</v>
+        <v>GARDEN FOAM PIPES</v>
       </c>
       <c r="E1241" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43832,7 +43832,7 @@
         <v>General</v>
       </c>
       <c r="G1241" t="str">
-        <v>32MM 1 1/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1241" t="str">
         <v>BDL</v>
@@ -43844,7 +43844,7 @@
         <v>Active</v>
       </c>
       <c r="K1241" t="str">
-        <v>GAP-ORA BRAIDED PIPE.</v>
+        <v>GARDEN FOAM PIPES.</v>
       </c>
     </row>
     <row r="1242">
@@ -43852,10 +43852,10 @@
         <v>1241</v>
       </c>
       <c r="B1242" t="str">
-        <v>FG-401355</v>
+        <v>FG-401356</v>
       </c>
       <c r="C1242" t="str">
-        <v>GARDEN FOAM PIPES (15MM 1/2)</v>
+        <v>GARDEN FOAM PIPES (20MM 3/4)</v>
       </c>
       <c r="D1242" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43867,7 +43867,7 @@
         <v>General</v>
       </c>
       <c r="G1242" t="str">
-        <v>15MM 1/2</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1242" t="str">
         <v>BDL</v>
@@ -43887,10 +43887,10 @@
         <v>1242</v>
       </c>
       <c r="B1243" t="str">
-        <v>FG-401356</v>
+        <v>FG-401369</v>
       </c>
       <c r="C1243" t="str">
-        <v>GARDEN FOAM PIPES (20MM 3/4)</v>
+        <v>GARDEN FOAM PIPES (20MM 3/4 20MTR)</v>
       </c>
       <c r="D1243" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43902,7 +43902,7 @@
         <v>General</v>
       </c>
       <c r="G1243" t="str">
-        <v>20MM 3/4</v>
+        <v>20MM 3/4 20MTR</v>
       </c>
       <c r="H1243" t="str">
         <v>BDL</v>
@@ -43922,10 +43922,10 @@
         <v>1243</v>
       </c>
       <c r="B1244" t="str">
-        <v>FG-401369</v>
+        <v>FG-401357</v>
       </c>
       <c r="C1244" t="str">
-        <v>GARDEN FOAM PIPES (20MM 3/4 20MTR)</v>
+        <v>GARDEN FOAM PIPES (25MM 1)</v>
       </c>
       <c r="D1244" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43937,7 +43937,7 @@
         <v>General</v>
       </c>
       <c r="G1244" t="str">
-        <v>20MM 3/4 20MTR</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1244" t="str">
         <v>BDL</v>
@@ -43957,10 +43957,10 @@
         <v>1244</v>
       </c>
       <c r="B1245" t="str">
-        <v>FG-401357</v>
+        <v>FG-401358</v>
       </c>
       <c r="C1245" t="str">
-        <v>GARDEN FOAM PIPES (25MM 1)</v>
+        <v>GARDEN FOAM PIPES (32MM 1 1/4)</v>
       </c>
       <c r="D1245" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43972,7 +43972,7 @@
         <v>General</v>
       </c>
       <c r="G1245" t="str">
-        <v>25MM 1</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1245" t="str">
         <v>BDL</v>
@@ -43992,13 +43992,13 @@
         <v>1245</v>
       </c>
       <c r="B1246" t="str">
-        <v>FG-401358</v>
+        <v>FG-401344</v>
       </c>
       <c r="C1246" t="str">
-        <v>GARDEN FOAM PIPES (32MM 1 1/4)</v>
+        <v>BRAIDED PIPE (15MM 1/2)</v>
       </c>
       <c r="D1246" t="str">
-        <v>GARDEN FOAM PIPES</v>
+        <v>BRAIDED PIPE</v>
       </c>
       <c r="E1246" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44007,7 +44007,7 @@
         <v>General</v>
       </c>
       <c r="G1246" t="str">
-        <v>32MM 1 1/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1246" t="str">
         <v>BDL</v>
@@ -44019,7 +44019,7 @@
         <v>Active</v>
       </c>
       <c r="K1246" t="str">
-        <v>GARDEN FOAM PIPES.</v>
+        <v>Reinforced Braided Garden Pipe.</v>
       </c>
     </row>
     <row r="1247">
@@ -44027,10 +44027,10 @@
         <v>1246</v>
       </c>
       <c r="B1247" t="str">
-        <v>FG-401344</v>
+        <v>FG-401345</v>
       </c>
       <c r="C1247" t="str">
-        <v>BRAIDED PIPE (15MM 1/2)</v>
+        <v>BRAIDED PIPE (20MM 3/4)</v>
       </c>
       <c r="D1247" t="str">
         <v>BRAIDED PIPE</v>
@@ -44042,7 +44042,7 @@
         <v>General</v>
       </c>
       <c r="G1247" t="str">
-        <v>15MM 1/2</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1247" t="str">
         <v>BDL</v>
@@ -44062,10 +44062,10 @@
         <v>1247</v>
       </c>
       <c r="B1248" t="str">
-        <v>FG-401345</v>
+        <v>FG-401346</v>
       </c>
       <c r="C1248" t="str">
-        <v>BRAIDED PIPE (20MM 3/4)</v>
+        <v>BRAIDED PIPE (25MM 1)</v>
       </c>
       <c r="D1248" t="str">
         <v>BRAIDED PIPE</v>
@@ -44077,7 +44077,7 @@
         <v>General</v>
       </c>
       <c r="G1248" t="str">
-        <v>20MM 3/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1248" t="str">
         <v>BDL</v>
@@ -44097,10 +44097,10 @@
         <v>1248</v>
       </c>
       <c r="B1249" t="str">
-        <v>FG-401346</v>
+        <v>FG-401363</v>
       </c>
       <c r="C1249" t="str">
-        <v>BRAIDED PIPE (25MM 1)</v>
+        <v>BRAIDED PIPE (32MM 1 1/4)</v>
       </c>
       <c r="D1249" t="str">
         <v>BRAIDED PIPE</v>
@@ -44112,7 +44112,7 @@
         <v>General</v>
       </c>
       <c r="G1249" t="str">
-        <v>25MM 1</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1249" t="str">
         <v>BDL</v>
@@ -44132,13 +44132,13 @@
         <v>1249</v>
       </c>
       <c r="B1250" t="str">
-        <v>FG-401363</v>
+        <v>FG-401374</v>
       </c>
       <c r="C1250" t="str">
-        <v>BRAIDED PIPE (32MM 1 1/4)</v>
+        <v>LEVEL PIPE (6MM)</v>
       </c>
       <c r="D1250" t="str">
-        <v>BRAIDED PIPE</v>
+        <v>LEVEL PIPE</v>
       </c>
       <c r="E1250" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44147,7 +44147,7 @@
         <v>General</v>
       </c>
       <c r="G1250" t="str">
-        <v>32MM 1 1/4</v>
+        <v>6MM</v>
       </c>
       <c r="H1250" t="str">
         <v>BDL</v>
@@ -44159,7 +44159,7 @@
         <v>Active</v>
       </c>
       <c r="K1250" t="str">
-        <v>Reinforced Braided Garden Pipe.</v>
+        <v>Transparent Level Pipe for construction &amp; garden work.</v>
       </c>
     </row>
     <row r="1251">
@@ -44167,13 +44167,13 @@
         <v>1250</v>
       </c>
       <c r="B1251" t="str">
-        <v>FG-401374</v>
+        <v>FG-401340</v>
       </c>
       <c r="C1251" t="str">
-        <v>LEVEL PIPE (6MM)</v>
+        <v>GARDEN PIPES SUPER FLOW (15MM 1/2)</v>
       </c>
       <c r="D1251" t="str">
-        <v>LEVEL PIPE</v>
+        <v>GARDEN PIPES SUPER FLOW</v>
       </c>
       <c r="E1251" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44182,7 +44182,7 @@
         <v>General</v>
       </c>
       <c r="G1251" t="str">
-        <v>6MM</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1251" t="str">
         <v>BDL</v>
@@ -44194,7 +44194,7 @@
         <v>Active</v>
       </c>
       <c r="K1251" t="str">
-        <v>Transparent Level Pipe for construction &amp; garden work.</v>
+        <v>GARDEN PIPES SUPER FLOW.</v>
       </c>
     </row>
     <row r="1252">
@@ -44202,10 +44202,10 @@
         <v>1251</v>
       </c>
       <c r="B1252" t="str">
-        <v>FG-401340</v>
+        <v>FG-401341</v>
       </c>
       <c r="C1252" t="str">
-        <v>GARDEN PIPES SUPER FLOW (15MM 1/2)</v>
+        <v>GARDEN PIPES SUPER FLOW (20MM 3/4)</v>
       </c>
       <c r="D1252" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44217,7 +44217,7 @@
         <v>General</v>
       </c>
       <c r="G1252" t="str">
-        <v>15MM 1/2</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1252" t="str">
         <v>BDL</v>
@@ -44237,10 +44237,10 @@
         <v>1252</v>
       </c>
       <c r="B1253" t="str">
-        <v>FG-401341</v>
+        <v>FG-401652</v>
       </c>
       <c r="C1253" t="str">
-        <v>GARDEN PIPES SUPER FLOW (20MM 3/4)</v>
+        <v>GARDEN PIPES SUPER FLOW (20MM 3/4 15MTR)</v>
       </c>
       <c r="D1253" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44252,7 +44252,7 @@
         <v>General</v>
       </c>
       <c r="G1253" t="str">
-        <v>20MM 3/4</v>
+        <v>20MM 3/4 15MTR</v>
       </c>
       <c r="H1253" t="str">
         <v>BDL</v>
@@ -44272,10 +44272,10 @@
         <v>1253</v>
       </c>
       <c r="B1254" t="str">
-        <v>FG-401652</v>
+        <v>FG-401342</v>
       </c>
       <c r="C1254" t="str">
-        <v>GARDEN PIPES SUPER FLOW (20MM 3/4 15MTR)</v>
+        <v>GARDEN PIPES SUPER FLOW (25MM 1)</v>
       </c>
       <c r="D1254" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44287,7 +44287,7 @@
         <v>General</v>
       </c>
       <c r="G1254" t="str">
-        <v>20MM 3/4 15MTR</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1254" t="str">
         <v>BDL</v>
@@ -44307,10 +44307,10 @@
         <v>1254</v>
       </c>
       <c r="B1255" t="str">
-        <v>FG-401342</v>
+        <v>FG-401343</v>
       </c>
       <c r="C1255" t="str">
-        <v>GARDEN PIPES SUPER FLOW (25MM 1)</v>
+        <v>GARDEN PIPES SUPER FLOW (32MM 1 1/4)</v>
       </c>
       <c r="D1255" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44322,7 +44322,7 @@
         <v>General</v>
       </c>
       <c r="G1255" t="str">
-        <v>25MM 1</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1255" t="str">
         <v>BDL</v>
@@ -44342,10 +44342,10 @@
         <v>1255</v>
       </c>
       <c r="B1256" t="str">
-        <v>FG-401343</v>
+        <v>FG-401627</v>
       </c>
       <c r="C1256" t="str">
-        <v>GARDEN PIPES SUPER FLOW (32MM 1 1/4)</v>
+        <v>GARDEN PIPES SUPER FLOW (40MM 1 1/2)</v>
       </c>
       <c r="D1256" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44357,7 +44357,7 @@
         <v>General</v>
       </c>
       <c r="G1256" t="str">
-        <v>32MM 1 1/4</v>
+        <v>40MM 1 1/2</v>
       </c>
       <c r="H1256" t="str">
         <v>BDL</v>
@@ -44377,34 +44377,34 @@
         <v>1256</v>
       </c>
       <c r="B1257" t="str">
-        <v>FG-401627</v>
+        <v>FG-401552</v>
       </c>
       <c r="C1257" t="str">
-        <v>GARDEN PIPES SUPER FLOW (40MM 1 1/2)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2 inch)</v>
       </c>
       <c r="D1257" t="str">
-        <v>GARDEN PIPES SUPER FLOW</v>
+        <v>EDGE SERIES SHORT BODY TAP</v>
       </c>
       <c r="E1257" t="str">
-        <v>Garden, Braided &amp; LDPE Pipes</v>
+        <v>FAUCETS</v>
       </c>
       <c r="F1257" t="str">
         <v>General</v>
       </c>
       <c r="G1257" t="str">
-        <v>40MM 1 1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1257" t="str">
-        <v>BDL</v>
-      </c>
-      <c r="I1257" t="str">
-        <v>-</v>
+        <v>NOS</v>
+      </c>
+      <c r="I1257">
+        <v>20</v>
       </c>
       <c r="J1257" t="str">
         <v>Active</v>
       </c>
       <c r="K1257" t="str">
-        <v>GARDEN PIPES SUPER FLOW.</v>
+        <v>EDGE SERIES SHORT BODY TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1258">
@@ -44415,7 +44415,7 @@
         <v>FG-401552</v>
       </c>
       <c r="C1258" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2 inch)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2)</v>
       </c>
       <c r="D1258" t="str">
         <v>EDGE SERIES SHORT BODY TAP</v>
@@ -44427,7 +44427,7 @@
         <v>General</v>
       </c>
       <c r="G1258" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1258" t="str">
         <v>NOS</v>
@@ -44450,7 +44450,7 @@
         <v>FG-401552</v>
       </c>
       <c r="C1259" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2")</v>
       </c>
       <c r="D1259" t="str">
         <v>EDGE SERIES SHORT BODY TAP</v>
@@ -44462,7 +44462,7 @@
         <v>General</v>
       </c>
       <c r="G1259" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1259" t="str">
         <v>NOS</v>
@@ -44482,13 +44482,13 @@
         <v>1259</v>
       </c>
       <c r="B1260" t="str">
-        <v>FG-401552</v>
+        <v>FG-401551</v>
       </c>
       <c r="C1260" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2")</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2 inch)</v>
       </c>
       <c r="D1260" t="str">
-        <v>EDGE SERIES SHORT BODY TAP</v>
+        <v>EDGE SERIES LONG BODY TAP</v>
       </c>
       <c r="E1260" t="str">
         <v>FAUCETS</v>
@@ -44497,19 +44497,19 @@
         <v>General</v>
       </c>
       <c r="G1260" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1260" t="str">
         <v>NOS</v>
       </c>
       <c r="I1260">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J1260" t="str">
         <v>Active</v>
       </c>
       <c r="K1260" t="str">
-        <v>EDGE SERIES SHORT BODY TAP high quality faucet.</v>
+        <v>EDGE SERIES LONG BODY TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1261">
@@ -44520,7 +44520,7 @@
         <v>FG-401551</v>
       </c>
       <c r="C1261" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2 inch)</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2)</v>
       </c>
       <c r="D1261" t="str">
         <v>EDGE SERIES LONG BODY TAP</v>
@@ -44532,7 +44532,7 @@
         <v>General</v>
       </c>
       <c r="G1261" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1261" t="str">
         <v>NOS</v>
@@ -44555,7 +44555,7 @@
         <v>FG-401551</v>
       </c>
       <c r="C1262" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2)</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2")</v>
       </c>
       <c r="D1262" t="str">
         <v>EDGE SERIES LONG BODY TAP</v>
@@ -44567,7 +44567,7 @@
         <v>General</v>
       </c>
       <c r="G1262" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1262" t="str">
         <v>NOS</v>
@@ -44587,13 +44587,13 @@
         <v>1262</v>
       </c>
       <c r="B1263" t="str">
-        <v>FG-401551</v>
+        <v>FG-401549</v>
       </c>
       <c r="C1263" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2")</v>
+        <v>EDGE SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1263" t="str">
-        <v>EDGE SERIES LONG BODY TAP</v>
+        <v>EDGE SERIES SWAN NECK</v>
       </c>
       <c r="E1263" t="str">
         <v>FAUCETS</v>
@@ -44602,19 +44602,19 @@
         <v>General</v>
       </c>
       <c r="G1263" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1263" t="str">
         <v>NOS</v>
       </c>
       <c r="I1263">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J1263" t="str">
         <v>Active</v>
       </c>
       <c r="K1263" t="str">
-        <v>EDGE SERIES LONG BODY TAP high quality faucet.</v>
+        <v>EDGE SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1264">
@@ -44625,7 +44625,7 @@
         <v>FG-401549</v>
       </c>
       <c r="C1264" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2 inch)</v>
+        <v>EDGE SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1264" t="str">
         <v>EDGE SERIES SWAN NECK</v>
@@ -44637,7 +44637,7 @@
         <v>General</v>
       </c>
       <c r="G1264" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1264" t="str">
         <v>NOS</v>
@@ -44660,7 +44660,7 @@
         <v>FG-401549</v>
       </c>
       <c r="C1265" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2)</v>
+        <v>EDGE SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1265" t="str">
         <v>EDGE SERIES SWAN NECK</v>
@@ -44672,7 +44672,7 @@
         <v>General</v>
       </c>
       <c r="G1265" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1265" t="str">
         <v>NOS</v>
@@ -44692,13 +44692,13 @@
         <v>1265</v>
       </c>
       <c r="B1266" t="str">
-        <v>FG-401549</v>
+        <v>FG-401546</v>
       </c>
       <c r="C1266" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2")</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1266" t="str">
-        <v>EDGE SERIES SWAN NECK</v>
+        <v>EDGE SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1266" t="str">
         <v>FAUCETS</v>
@@ -44707,19 +44707,19 @@
         <v>General</v>
       </c>
       <c r="G1266" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1266" t="str">
         <v>NOS</v>
       </c>
       <c r="I1266">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="J1266" t="str">
         <v>Active</v>
       </c>
       <c r="K1266" t="str">
-        <v>EDGE SERIES SWAN NECK high quality faucet.</v>
+        <v>EDGE SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1267">
@@ -44730,7 +44730,7 @@
         <v>FG-401546</v>
       </c>
       <c r="C1267" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1267" t="str">
         <v>EDGE SERIES ANGULAR VALVE</v>
@@ -44742,7 +44742,7 @@
         <v>General</v>
       </c>
       <c r="G1267" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1267" t="str">
         <v>NOS</v>
@@ -44765,7 +44765,7 @@
         <v>FG-401546</v>
       </c>
       <c r="C1268" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2)</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1268" t="str">
         <v>EDGE SERIES ANGULAR VALVE</v>
@@ -44777,7 +44777,7 @@
         <v>General</v>
       </c>
       <c r="G1268" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1268" t="str">
         <v>NOS</v>
@@ -44797,13 +44797,13 @@
         <v>1268</v>
       </c>
       <c r="B1269" t="str">
-        <v>FG-401546</v>
+        <v>FG-401547</v>
       </c>
       <c r="C1269" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2")</v>
+        <v>EDGE SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1269" t="str">
-        <v>EDGE SERIES ANGULAR VALVE</v>
+        <v>EDGE SERIES PILLAR TAP</v>
       </c>
       <c r="E1269" t="str">
         <v>FAUCETS</v>
@@ -44812,19 +44812,19 @@
         <v>General</v>
       </c>
       <c r="G1269" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1269" t="str">
         <v>NOS</v>
       </c>
       <c r="I1269">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J1269" t="str">
         <v>Active</v>
       </c>
       <c r="K1269" t="str">
-        <v>EDGE SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>EDGE SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1270">
@@ -44835,7 +44835,7 @@
         <v>FG-401547</v>
       </c>
       <c r="C1270" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2 inch)</v>
+        <v>EDGE SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1270" t="str">
         <v>EDGE SERIES PILLAR TAP</v>
@@ -44847,7 +44847,7 @@
         <v>General</v>
       </c>
       <c r="G1270" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1270" t="str">
         <v>NOS</v>
@@ -44870,7 +44870,7 @@
         <v>FG-401547</v>
       </c>
       <c r="C1271" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2)</v>
+        <v>EDGE SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1271" t="str">
         <v>EDGE SERIES PILLAR TAP</v>
@@ -44882,7 +44882,7 @@
         <v>General</v>
       </c>
       <c r="G1271" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1271" t="str">
         <v>NOS</v>
@@ -44902,13 +44902,13 @@
         <v>1271</v>
       </c>
       <c r="B1272" t="str">
-        <v>FG-401547</v>
+        <v>FG-401550</v>
       </c>
       <c r="C1272" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2")</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2 inch)</v>
       </c>
       <c r="D1272" t="str">
-        <v>EDGE SERIES PILLAR TAP</v>
+        <v>EDGE SERIES 2 WAY BIB TAB</v>
       </c>
       <c r="E1272" t="str">
         <v>FAUCETS</v>
@@ -44917,19 +44917,19 @@
         <v>General</v>
       </c>
       <c r="G1272" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1272" t="str">
         <v>NOS</v>
       </c>
       <c r="I1272">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J1272" t="str">
         <v>Active</v>
       </c>
       <c r="K1272" t="str">
-        <v>EDGE SERIES PILLAR TAP high quality faucet.</v>
+        <v>EDGE SERIES 2 WAY BIB TAB high quality faucet.</v>
       </c>
     </row>
     <row r="1273">
@@ -44940,7 +44940,7 @@
         <v>FG-401550</v>
       </c>
       <c r="C1273" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2 inch)</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2)</v>
       </c>
       <c r="D1273" t="str">
         <v>EDGE SERIES 2 WAY BIB TAB</v>
@@ -44952,7 +44952,7 @@
         <v>General</v>
       </c>
       <c r="G1273" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1273" t="str">
         <v>NOS</v>
@@ -44975,7 +44975,7 @@
         <v>FG-401550</v>
       </c>
       <c r="C1274" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2)</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2")</v>
       </c>
       <c r="D1274" t="str">
         <v>EDGE SERIES 2 WAY BIB TAB</v>
@@ -44987,7 +44987,7 @@
         <v>General</v>
       </c>
       <c r="G1274" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1274" t="str">
         <v>NOS</v>
@@ -45007,13 +45007,13 @@
         <v>1274</v>
       </c>
       <c r="B1275" t="str">
-        <v>FG-401550</v>
+        <v>FG-401548</v>
       </c>
       <c r="C1275" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2")</v>
+        <v>EDGE SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1275" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB</v>
+        <v>EDGE SERIES SINK TAP</v>
       </c>
       <c r="E1275" t="str">
         <v>FAUCETS</v>
@@ -45022,19 +45022,19 @@
         <v>General</v>
       </c>
       <c r="G1275" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1275" t="str">
         <v>NOS</v>
       </c>
       <c r="I1275">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1275" t="str">
         <v>Active</v>
       </c>
       <c r="K1275" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB high quality faucet.</v>
+        <v>EDGE SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1276">
@@ -45045,7 +45045,7 @@
         <v>FG-401548</v>
       </c>
       <c r="C1276" t="str">
-        <v>EDGE SERIES SINK TAP (1/2 inch)</v>
+        <v>EDGE SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1276" t="str">
         <v>EDGE SERIES SINK TAP</v>
@@ -45057,7 +45057,7 @@
         <v>General</v>
       </c>
       <c r="G1276" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1276" t="str">
         <v>NOS</v>
@@ -45080,7 +45080,7 @@
         <v>FG-401548</v>
       </c>
       <c r="C1277" t="str">
-        <v>EDGE SERIES SINK TAP (1/2)</v>
+        <v>EDGE SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1277" t="str">
         <v>EDGE SERIES SINK TAP</v>
@@ -45092,7 +45092,7 @@
         <v>General</v>
       </c>
       <c r="G1277" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1277" t="str">
         <v>NOS</v>
@@ -45112,13 +45112,13 @@
         <v>1277</v>
       </c>
       <c r="B1278" t="str">
-        <v>FG-401548</v>
+        <v>FG-401568</v>
       </c>
       <c r="C1278" t="str">
-        <v>EDGE SERIES SINK TAP (1/2")</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1278" t="str">
-        <v>EDGE SERIES SINK TAP</v>
+        <v>SMART SERIES SHORT BODY BIB TAP</v>
       </c>
       <c r="E1278" t="str">
         <v>FAUCETS</v>
@@ -45127,19 +45127,19 @@
         <v>General</v>
       </c>
       <c r="G1278" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1278" t="str">
         <v>NOS</v>
       </c>
       <c r="I1278">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="J1278" t="str">
         <v>Active</v>
       </c>
       <c r="K1278" t="str">
-        <v>EDGE SERIES SINK TAP high quality faucet.</v>
+        <v>SMART SERIES SHORT BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1279">
@@ -45150,7 +45150,7 @@
         <v>FG-401568</v>
       </c>
       <c r="C1279" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1279" t="str">
         <v>SMART SERIES SHORT BODY BIB TAP</v>
@@ -45162,7 +45162,7 @@
         <v>General</v>
       </c>
       <c r="G1279" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1279" t="str">
         <v>NOS</v>
@@ -45185,7 +45185,7 @@
         <v>FG-401568</v>
       </c>
       <c r="C1280" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2)</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1280" t="str">
         <v>SMART SERIES SHORT BODY BIB TAP</v>
@@ -45197,7 +45197,7 @@
         <v>General</v>
       </c>
       <c r="G1280" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1280" t="str">
         <v>NOS</v>
@@ -45217,13 +45217,13 @@
         <v>1280</v>
       </c>
       <c r="B1281" t="str">
-        <v>FG-401568</v>
+        <v>FG-401567</v>
       </c>
       <c r="C1281" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2")</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1281" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP</v>
+        <v>SMART SERIES LONG BODY BIB TAP</v>
       </c>
       <c r="E1281" t="str">
         <v>FAUCETS</v>
@@ -45232,7 +45232,7 @@
         <v>General</v>
       </c>
       <c r="G1281" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1281" t="str">
         <v>NOS</v>
@@ -45244,7 +45244,7 @@
         <v>Active</v>
       </c>
       <c r="K1281" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP high quality faucet.</v>
+        <v>SMART SERIES LONG BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1282">
@@ -45255,7 +45255,7 @@
         <v>FG-401567</v>
       </c>
       <c r="C1282" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1282" t="str">
         <v>SMART SERIES LONG BODY BIB TAP</v>
@@ -45267,7 +45267,7 @@
         <v>General</v>
       </c>
       <c r="G1282" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1282" t="str">
         <v>NOS</v>
@@ -45290,7 +45290,7 @@
         <v>FG-401567</v>
       </c>
       <c r="C1283" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2)</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1283" t="str">
         <v>SMART SERIES LONG BODY BIB TAP</v>
@@ -45302,7 +45302,7 @@
         <v>General</v>
       </c>
       <c r="G1283" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1283" t="str">
         <v>NOS</v>
@@ -45322,13 +45322,13 @@
         <v>1283</v>
       </c>
       <c r="B1284" t="str">
-        <v>FG-401567</v>
+        <v>FG-401562</v>
       </c>
       <c r="C1284" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2")</v>
+        <v>SMART SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1284" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP</v>
+        <v>SMART SERIES PILLAR TAP</v>
       </c>
       <c r="E1284" t="str">
         <v>FAUCETS</v>
@@ -45337,19 +45337,19 @@
         <v>General</v>
       </c>
       <c r="G1284" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1284" t="str">
         <v>NOS</v>
       </c>
       <c r="I1284">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1284" t="str">
         <v>Active</v>
       </c>
       <c r="K1284" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP high quality faucet.</v>
+        <v>SMART SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1285">
@@ -45360,7 +45360,7 @@
         <v>FG-401562</v>
       </c>
       <c r="C1285" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2 inch)</v>
+        <v>SMART SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1285" t="str">
         <v>SMART SERIES PILLAR TAP</v>
@@ -45372,7 +45372,7 @@
         <v>General</v>
       </c>
       <c r="G1285" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1285" t="str">
         <v>NOS</v>
@@ -45395,7 +45395,7 @@
         <v>FG-401562</v>
       </c>
       <c r="C1286" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2)</v>
+        <v>SMART SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1286" t="str">
         <v>SMART SERIES PILLAR TAP</v>
@@ -45407,7 +45407,7 @@
         <v>General</v>
       </c>
       <c r="G1286" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1286" t="str">
         <v>NOS</v>
@@ -45427,13 +45427,13 @@
         <v>1286</v>
       </c>
       <c r="B1287" t="str">
-        <v>FG-401562</v>
+        <v>FG-401563</v>
       </c>
       <c r="C1287" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2")</v>
+        <v>SMART SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1287" t="str">
-        <v>SMART SERIES PILLAR TAP</v>
+        <v>SMART SERIES SINK TAP</v>
       </c>
       <c r="E1287" t="str">
         <v>FAUCETS</v>
@@ -45442,7 +45442,7 @@
         <v>General</v>
       </c>
       <c r="G1287" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1287" t="str">
         <v>NOS</v>
@@ -45454,7 +45454,7 @@
         <v>Active</v>
       </c>
       <c r="K1287" t="str">
-        <v>SMART SERIES PILLAR TAP high quality faucet.</v>
+        <v>SMART SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1288">
@@ -45465,7 +45465,7 @@
         <v>FG-401563</v>
       </c>
       <c r="C1288" t="str">
-        <v>SMART SERIES SINK TAP (1/2 inch)</v>
+        <v>SMART SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1288" t="str">
         <v>SMART SERIES SINK TAP</v>
@@ -45477,7 +45477,7 @@
         <v>General</v>
       </c>
       <c r="G1288" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1288" t="str">
         <v>NOS</v>
@@ -45500,7 +45500,7 @@
         <v>FG-401563</v>
       </c>
       <c r="C1289" t="str">
-        <v>SMART SERIES SINK TAP (1/2)</v>
+        <v>SMART SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1289" t="str">
         <v>SMART SERIES SINK TAP</v>
@@ -45512,7 +45512,7 @@
         <v>General</v>
       </c>
       <c r="G1289" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1289" t="str">
         <v>NOS</v>
@@ -45532,13 +45532,13 @@
         <v>1289</v>
       </c>
       <c r="B1290" t="str">
-        <v>FG-401563</v>
+        <v>FG-401564</v>
       </c>
       <c r="C1290" t="str">
-        <v>SMART SERIES SINK TAP (1/2")</v>
+        <v>SMART SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1290" t="str">
-        <v>SMART SERIES SINK TAP</v>
+        <v>SMART SERIES SWAN NECK</v>
       </c>
       <c r="E1290" t="str">
         <v>FAUCETS</v>
@@ -45547,7 +45547,7 @@
         <v>General</v>
       </c>
       <c r="G1290" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1290" t="str">
         <v>NOS</v>
@@ -45559,7 +45559,7 @@
         <v>Active</v>
       </c>
       <c r="K1290" t="str">
-        <v>SMART SERIES SINK TAP high quality faucet.</v>
+        <v>SMART SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1291">
@@ -45570,7 +45570,7 @@
         <v>FG-401564</v>
       </c>
       <c r="C1291" t="str">
-        <v>SMART SERIES SWAN NECK (1/2 inch)</v>
+        <v>SMART SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1291" t="str">
         <v>SMART SERIES SWAN NECK</v>
@@ -45582,7 +45582,7 @@
         <v>General</v>
       </c>
       <c r="G1291" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1291" t="str">
         <v>NOS</v>
@@ -45605,7 +45605,7 @@
         <v>FG-401564</v>
       </c>
       <c r="C1292" t="str">
-        <v>SMART SERIES SWAN NECK (1/2)</v>
+        <v>SMART SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1292" t="str">
         <v>SMART SERIES SWAN NECK</v>
@@ -45617,7 +45617,7 @@
         <v>General</v>
       </c>
       <c r="G1292" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1292" t="str">
         <v>NOS</v>
@@ -45637,13 +45637,13 @@
         <v>1292</v>
       </c>
       <c r="B1293" t="str">
-        <v>FG-401564</v>
+        <v>FG-401561</v>
       </c>
       <c r="C1293" t="str">
-        <v>SMART SERIES SWAN NECK (1/2")</v>
+        <v>SMART SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1293" t="str">
-        <v>SMART SERIES SWAN NECK</v>
+        <v>SMART SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1293" t="str">
         <v>FAUCETS</v>
@@ -45652,19 +45652,19 @@
         <v>General</v>
       </c>
       <c r="G1293" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1293" t="str">
         <v>NOS</v>
       </c>
       <c r="I1293">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1293" t="str">
         <v>Active</v>
       </c>
       <c r="K1293" t="str">
-        <v>SMART SERIES SWAN NECK high quality faucet.</v>
+        <v>SMART SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1294">
@@ -45672,13 +45672,13 @@
         <v>1293</v>
       </c>
       <c r="B1294" t="str">
-        <v>FG-401561</v>
+        <v>FG-401566</v>
       </c>
       <c r="C1294" t="str">
-        <v>SMART SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1294" t="str">
-        <v>SMART SERIES ANGULAR VALVE</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
       </c>
       <c r="E1294" t="str">
         <v>FAUCETS</v>
@@ -45693,13 +45693,13 @@
         <v>NOS</v>
       </c>
       <c r="I1294">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1294" t="str">
         <v>Active</v>
       </c>
       <c r="K1294" t="str">
-        <v>SMART SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1295">
@@ -45710,7 +45710,7 @@
         <v>FG-401566</v>
       </c>
       <c r="C1295" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1295" t="str">
         <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
@@ -45722,7 +45722,7 @@
         <v>General</v>
       </c>
       <c r="G1295" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1295" t="str">
         <v>NOS</v>
@@ -45745,7 +45745,7 @@
         <v>FG-401566</v>
       </c>
       <c r="C1296" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1296" t="str">
         <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
@@ -45757,7 +45757,7 @@
         <v>General</v>
       </c>
       <c r="G1296" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1296" t="str">
         <v>NOS</v>
@@ -45777,13 +45777,13 @@
         <v>1296</v>
       </c>
       <c r="B1297" t="str">
-        <v>FG-401566</v>
+        <v>FG-401565</v>
       </c>
       <c r="C1297" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2")</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1297" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
+        <v>SMART SERIES 2 WAY BIB TAP</v>
       </c>
       <c r="E1297" t="str">
         <v>FAUCETS</v>
@@ -45792,7 +45792,7 @@
         <v>General</v>
       </c>
       <c r="G1297" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1297" t="str">
         <v>NOS</v>
@@ -45804,7 +45804,7 @@
         <v>Active</v>
       </c>
       <c r="K1297" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
+        <v>SMART SERIES 2 WAY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1298">
@@ -45815,7 +45815,7 @@
         <v>FG-401565</v>
       </c>
       <c r="C1298" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2)</v>
       </c>
       <c r="D1298" t="str">
         <v>SMART SERIES 2 WAY BIB TAP</v>
@@ -45827,7 +45827,7 @@
         <v>General</v>
       </c>
       <c r="G1298" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1298" t="str">
         <v>NOS</v>
@@ -45850,7 +45850,7 @@
         <v>FG-401565</v>
       </c>
       <c r="C1299" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2)</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2")</v>
       </c>
       <c r="D1299" t="str">
         <v>SMART SERIES 2 WAY BIB TAP</v>
@@ -45862,7 +45862,7 @@
         <v>General</v>
       </c>
       <c r="G1299" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1299" t="str">
         <v>NOS</v>
@@ -45882,13 +45882,13 @@
         <v>1299</v>
       </c>
       <c r="B1300" t="str">
-        <v>FG-401565</v>
+        <v>FG-401560</v>
       </c>
       <c r="C1300" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1300" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP</v>
       </c>
       <c r="E1300" t="str">
         <v>FAUCETS</v>
@@ -45897,19 +45897,19 @@
         <v>General</v>
       </c>
       <c r="G1300" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1300" t="str">
         <v>NOS</v>
       </c>
       <c r="I1300">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1300" t="str">
         <v>Active</v>
       </c>
       <c r="K1300" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1301">
@@ -45920,7 +45920,7 @@
         <v>FG-401560</v>
       </c>
       <c r="C1301" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1301" t="str">
         <v>REGULAR SERIES SHORT BODY BIB TAP</v>
@@ -45932,7 +45932,7 @@
         <v>General</v>
       </c>
       <c r="G1301" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1301" t="str">
         <v>NOS</v>
@@ -45955,7 +45955,7 @@
         <v>FG-401560</v>
       </c>
       <c r="C1302" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1302" t="str">
         <v>REGULAR SERIES SHORT BODY BIB TAP</v>
@@ -45967,7 +45967,7 @@
         <v>General</v>
       </c>
       <c r="G1302" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1302" t="str">
         <v>NOS</v>
@@ -45987,13 +45987,13 @@
         <v>1302</v>
       </c>
       <c r="B1303" t="str">
-        <v>FG-401560</v>
+        <v>FG-401559</v>
       </c>
       <c r="C1303" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1303" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP</v>
       </c>
       <c r="E1303" t="str">
         <v>FAUCETS</v>
@@ -46002,7 +46002,7 @@
         <v>General</v>
       </c>
       <c r="G1303" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1303" t="str">
         <v>NOS</v>
@@ -46014,7 +46014,7 @@
         <v>Active</v>
       </c>
       <c r="K1303" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1304">
@@ -46025,7 +46025,7 @@
         <v>FG-401559</v>
       </c>
       <c r="C1304" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1304" t="str">
         <v>REGULAR SERIES LONG BODY BIB TAP</v>
@@ -46037,7 +46037,7 @@
         <v>General</v>
       </c>
       <c r="G1304" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1304" t="str">
         <v>NOS</v>
@@ -46060,7 +46060,7 @@
         <v>FG-401559</v>
       </c>
       <c r="C1305" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1305" t="str">
         <v>REGULAR SERIES LONG BODY BIB TAP</v>
@@ -46072,7 +46072,7 @@
         <v>General</v>
       </c>
       <c r="G1305" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1305" t="str">
         <v>NOS</v>
@@ -46092,13 +46092,13 @@
         <v>1305</v>
       </c>
       <c r="B1306" t="str">
-        <v>FG-401559</v>
+        <v>FG-401554</v>
       </c>
       <c r="C1306" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1306" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP</v>
+        <v>REGULAR SERIES PILLAR TAP</v>
       </c>
       <c r="E1306" t="str">
         <v>FAUCETS</v>
@@ -46107,19 +46107,19 @@
         <v>General</v>
       </c>
       <c r="G1306" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1306" t="str">
         <v>NOS</v>
       </c>
       <c r="I1306">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1306" t="str">
         <v>Active</v>
       </c>
       <c r="K1306" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1307">
@@ -46130,7 +46130,7 @@
         <v>FG-401554</v>
       </c>
       <c r="C1307" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2 inch)</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1307" t="str">
         <v>REGULAR SERIES PILLAR TAP</v>
@@ -46142,7 +46142,7 @@
         <v>General</v>
       </c>
       <c r="G1307" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1307" t="str">
         <v>NOS</v>
@@ -46165,7 +46165,7 @@
         <v>FG-401554</v>
       </c>
       <c r="C1308" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2)</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1308" t="str">
         <v>REGULAR SERIES PILLAR TAP</v>
@@ -46177,7 +46177,7 @@
         <v>General</v>
       </c>
       <c r="G1308" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1308" t="str">
         <v>NOS</v>
@@ -46197,13 +46197,13 @@
         <v>1308</v>
       </c>
       <c r="B1309" t="str">
-        <v>FG-401554</v>
+        <v>FG-401555</v>
       </c>
       <c r="C1309" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2")</v>
+        <v>REGULAR SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1309" t="str">
-        <v>REGULAR SERIES PILLAR TAP</v>
+        <v>REGULAR SERIES SINK TAP</v>
       </c>
       <c r="E1309" t="str">
         <v>FAUCETS</v>
@@ -46212,7 +46212,7 @@
         <v>General</v>
       </c>
       <c r="G1309" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1309" t="str">
         <v>NOS</v>
@@ -46224,7 +46224,7 @@
         <v>Active</v>
       </c>
       <c r="K1309" t="str">
-        <v>REGULAR SERIES PILLAR TAP high quality faucet.</v>
+        <v>REGULAR SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1310">
@@ -46235,7 +46235,7 @@
         <v>FG-401555</v>
       </c>
       <c r="C1310" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2 inch)</v>
+        <v>REGULAR SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1310" t="str">
         <v>REGULAR SERIES SINK TAP</v>
@@ -46247,7 +46247,7 @@
         <v>General</v>
       </c>
       <c r="G1310" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1310" t="str">
         <v>NOS</v>
@@ -46270,7 +46270,7 @@
         <v>FG-401555</v>
       </c>
       <c r="C1311" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2)</v>
+        <v>REGULAR SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1311" t="str">
         <v>REGULAR SERIES SINK TAP</v>
@@ -46282,7 +46282,7 @@
         <v>General</v>
       </c>
       <c r="G1311" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1311" t="str">
         <v>NOS</v>
@@ -46302,13 +46302,13 @@
         <v>1311</v>
       </c>
       <c r="B1312" t="str">
-        <v>FG-401555</v>
+        <v>FG-401556</v>
       </c>
       <c r="C1312" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2")</v>
+        <v>REGULAR SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1312" t="str">
-        <v>REGULAR SERIES SINK TAP</v>
+        <v>REGULAR SERIES SWAN NECK</v>
       </c>
       <c r="E1312" t="str">
         <v>FAUCETS</v>
@@ -46317,7 +46317,7 @@
         <v>General</v>
       </c>
       <c r="G1312" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1312" t="str">
         <v>NOS</v>
@@ -46329,7 +46329,7 @@
         <v>Active</v>
       </c>
       <c r="K1312" t="str">
-        <v>REGULAR SERIES SINK TAP high quality faucet.</v>
+        <v>REGULAR SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1313">
@@ -46340,7 +46340,7 @@
         <v>FG-401556</v>
       </c>
       <c r="C1313" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2 inch)</v>
+        <v>REGULAR SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1313" t="str">
         <v>REGULAR SERIES SWAN NECK</v>
@@ -46352,7 +46352,7 @@
         <v>General</v>
       </c>
       <c r="G1313" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1313" t="str">
         <v>NOS</v>
@@ -46375,7 +46375,7 @@
         <v>FG-401556</v>
       </c>
       <c r="C1314" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2)</v>
+        <v>REGULAR SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1314" t="str">
         <v>REGULAR SERIES SWAN NECK</v>
@@ -46387,7 +46387,7 @@
         <v>General</v>
       </c>
       <c r="G1314" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1314" t="str">
         <v>NOS</v>
@@ -46407,13 +46407,13 @@
         <v>1314</v>
       </c>
       <c r="B1315" t="str">
-        <v>FG-401556</v>
+        <v>FG-401553</v>
       </c>
       <c r="C1315" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2")</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1315" t="str">
-        <v>REGULAR SERIES SWAN NECK</v>
+        <v>REGULAR SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1315" t="str">
         <v>FAUCETS</v>
@@ -46422,19 +46422,19 @@
         <v>General</v>
       </c>
       <c r="G1315" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1315" t="str">
         <v>NOS</v>
       </c>
       <c r="I1315">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1315" t="str">
         <v>Active</v>
       </c>
       <c r="K1315" t="str">
-        <v>REGULAR SERIES SWAN NECK high quality faucet.</v>
+        <v>REGULAR SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1316">
@@ -46445,7 +46445,7 @@
         <v>FG-401553</v>
       </c>
       <c r="C1316" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1316" t="str">
         <v>REGULAR SERIES ANGULAR VALVE</v>
@@ -46457,7 +46457,7 @@
         <v>General</v>
       </c>
       <c r="G1316" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1316" t="str">
         <v>NOS</v>
@@ -46480,7 +46480,7 @@
         <v>FG-401553</v>
       </c>
       <c r="C1317" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2)</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1317" t="str">
         <v>REGULAR SERIES ANGULAR VALVE</v>
@@ -46492,7 +46492,7 @@
         <v>General</v>
       </c>
       <c r="G1317" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1317" t="str">
         <v>NOS</v>
@@ -46512,13 +46512,13 @@
         <v>1317</v>
       </c>
       <c r="B1318" t="str">
-        <v>FG-401553</v>
+        <v>FG-401558</v>
       </c>
       <c r="C1318" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2")</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1318" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
       </c>
       <c r="E1318" t="str">
         <v>FAUCETS</v>
@@ -46527,19 +46527,19 @@
         <v>General</v>
       </c>
       <c r="G1318" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1318" t="str">
         <v>NOS</v>
       </c>
       <c r="I1318">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1318" t="str">
         <v>Active</v>
       </c>
       <c r="K1318" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1319">
@@ -46550,7 +46550,7 @@
         <v>FG-401558</v>
       </c>
       <c r="C1319" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1319" t="str">
         <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
@@ -46562,7 +46562,7 @@
         <v>General</v>
       </c>
       <c r="G1319" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1319" t="str">
         <v>NOS</v>
@@ -46585,7 +46585,7 @@
         <v>FG-401558</v>
       </c>
       <c r="C1320" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2)</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1320" t="str">
         <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
@@ -46597,7 +46597,7 @@
         <v>General</v>
       </c>
       <c r="G1320" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1320" t="str">
         <v>NOS</v>
@@ -46617,13 +46617,13 @@
         <v>1320</v>
       </c>
       <c r="B1321" t="str">
-        <v>FG-401558</v>
+        <v>FG-401557</v>
       </c>
       <c r="C1321" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2")</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1321" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP</v>
       </c>
       <c r="E1321" t="str">
         <v>FAUCETS</v>
@@ -46632,7 +46632,7 @@
         <v>General</v>
       </c>
       <c r="G1321" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1321" t="str">
         <v>NOS</v>
@@ -46644,7 +46644,7 @@
         <v>Active</v>
       </c>
       <c r="K1321" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1322">
@@ -46655,7 +46655,7 @@
         <v>FG-401557</v>
       </c>
       <c r="C1322" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2)</v>
       </c>
       <c r="D1322" t="str">
         <v>REGULAR SERIES 2 WAY BIB TAP</v>
@@ -46667,7 +46667,7 @@
         <v>General</v>
       </c>
       <c r="G1322" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1322" t="str">
         <v>NOS</v>
@@ -46690,7 +46690,7 @@
         <v>FG-401557</v>
       </c>
       <c r="C1323" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2")</v>
       </c>
       <c r="D1323" t="str">
         <v>REGULAR SERIES 2 WAY BIB TAP</v>
@@ -46702,7 +46702,7 @@
         <v>General</v>
       </c>
       <c r="G1323" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1323" t="str">
         <v>NOS</v>
@@ -46722,34 +46722,34 @@
         <v>1323</v>
       </c>
       <c r="B1324" t="str">
-        <v>FG-401557</v>
+        <v>FG-400836</v>
       </c>
       <c r="C1324" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2")</v>
+        <v>SINGLE SIDE HANDLE FLUSH 8L (8L)</v>
       </c>
       <c r="D1324" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP</v>
+        <v>SINGLE SIDE HANDLE FLUSH 8L</v>
       </c>
       <c r="E1324" t="str">
-        <v>FAUCETS</v>
+        <v>Toilet Seat Cover &amp; Flushing Cistern</v>
       </c>
       <c r="F1324" t="str">
         <v>General</v>
       </c>
       <c r="G1324" t="str">
-        <v>1/2"</v>
+        <v>8L</v>
       </c>
       <c r="H1324" t="str">
         <v>NOS</v>
       </c>
       <c r="I1324">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J1324" t="str">
         <v>Active</v>
       </c>
       <c r="K1324" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP high quality faucet.</v>
+        <v>8 Litre Single Side Handle Flushing Cistern.</v>
       </c>
     </row>
     <row r="1325">
@@ -46757,13 +46757,13 @@
         <v>1324</v>
       </c>
       <c r="B1325" t="str">
-        <v>FG-400836</v>
+        <v>FG-400837</v>
       </c>
       <c r="C1325" t="str">
-        <v>SINGLE SIDE HANDLE FLUSH 8L (8L)</v>
+        <v>CENTER SINGLE PUSH FLUSH 8L (8L)</v>
       </c>
       <c r="D1325" t="str">
-        <v>SINGLE SIDE HANDLE FLUSH 8L</v>
+        <v>CENTER SINGLE PUSH FLUSH 8L</v>
       </c>
       <c r="E1325" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46784,7 +46784,7 @@
         <v>Active</v>
       </c>
       <c r="K1325" t="str">
-        <v>8 Litre Single Side Handle Flushing Cistern.</v>
+        <v>8 Litre Center Single Push Flushing Cistern.</v>
       </c>
     </row>
     <row r="1326">
@@ -46792,13 +46792,13 @@
         <v>1325</v>
       </c>
       <c r="B1326" t="str">
-        <v>FG-400837</v>
+        <v>FG-400838</v>
       </c>
       <c r="C1326" t="str">
-        <v>CENTER SINGLE PUSH FLUSH 8L (8L)</v>
+        <v>DUAL FLUSH 10L (10L)</v>
       </c>
       <c r="D1326" t="str">
-        <v>CENTER SINGLE PUSH FLUSH 8L</v>
+        <v>DUAL FLUSH 10L</v>
       </c>
       <c r="E1326" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46807,7 +46807,7 @@
         <v>General</v>
       </c>
       <c r="G1326" t="str">
-        <v>8L</v>
+        <v>10L</v>
       </c>
       <c r="H1326" t="str">
         <v>NOS</v>
@@ -46819,7 +46819,7 @@
         <v>Active</v>
       </c>
       <c r="K1326" t="str">
-        <v>8 Litre Center Single Push Flushing Cistern.</v>
+        <v>10 Litre Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1327">
@@ -46827,13 +46827,13 @@
         <v>1326</v>
       </c>
       <c r="B1327" t="str">
-        <v>FG-400838</v>
+        <v>FG-400835</v>
       </c>
       <c r="C1327" t="str">
-        <v>DUAL FLUSH 10L (10L)</v>
+        <v>EWC SEAT COVER (WITH JET) (Standard)</v>
       </c>
       <c r="D1327" t="str">
-        <v>DUAL FLUSH 10L</v>
+        <v>EWC SEAT COVER (WITH JET)</v>
       </c>
       <c r="E1327" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46842,19 +46842,19 @@
         <v>General</v>
       </c>
       <c r="G1327" t="str">
-        <v>10L</v>
+        <v>Standard</v>
       </c>
       <c r="H1327" t="str">
         <v>NOS</v>
       </c>
       <c r="I1327">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J1327" t="str">
         <v>Active</v>
       </c>
       <c r="K1327" t="str">
-        <v>10 Litre Dual Flush Cistern.</v>
+        <v>EWC Toilet Seat Cover with integrated jet spray.</v>
       </c>
     </row>
     <row r="1328">
@@ -46862,13 +46862,13 @@
         <v>1327</v>
       </c>
       <c r="B1328" t="str">
-        <v>FG-400835</v>
+        <v>FG-400840</v>
       </c>
       <c r="C1328" t="str">
-        <v>EWC SEAT COVER (WITH JET) (Standard)</v>
+        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L) (10L)</v>
       </c>
       <c r="D1328" t="str">
-        <v>EWC SEAT COVER (WITH JET)</v>
+        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L)</v>
       </c>
       <c r="E1328" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46877,19 +46877,19 @@
         <v>General</v>
       </c>
       <c r="G1328" t="str">
-        <v>Standard</v>
+        <v>10L</v>
       </c>
       <c r="H1328" t="str">
         <v>NOS</v>
       </c>
       <c r="I1328">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J1328" t="str">
         <v>Active</v>
       </c>
       <c r="K1328" t="str">
-        <v>EWC Toilet Seat Cover with integrated jet spray.</v>
+        <v>10 Litre Premium Dual Colour Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1329">
@@ -46897,13 +46897,13 @@
         <v>1328</v>
       </c>
       <c r="B1329" t="str">
-        <v>FG-400840</v>
+        <v>FG-400839</v>
       </c>
       <c r="C1329" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L) (10L)</v>
+        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L) (10L)</v>
       </c>
       <c r="D1329" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L)</v>
+        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L)</v>
       </c>
       <c r="E1329" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46924,7 +46924,7 @@
         <v>Active</v>
       </c>
       <c r="K1329" t="str">
-        <v>10 Litre Premium Dual Colour Dual Flush Cistern.</v>
+        <v>10 Litre Economy Dual Colour Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1330">
@@ -46932,13 +46932,13 @@
         <v>1329</v>
       </c>
       <c r="B1330" t="str">
-        <v>FG-400839</v>
+        <v>FG-400834</v>
       </c>
       <c r="C1330" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L) (10L)</v>
+        <v>EWC SEAT COVER (WITHOUT JET) (Standard)</v>
       </c>
       <c r="D1330" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L)</v>
+        <v>EWC SEAT COVER (WITHOUT JET)</v>
       </c>
       <c r="E1330" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46947,59 +46947,24 @@
         <v>General</v>
       </c>
       <c r="G1330" t="str">
-        <v>10L</v>
+        <v>Standard</v>
       </c>
       <c r="H1330" t="str">
         <v>NOS</v>
       </c>
       <c r="I1330">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J1330" t="str">
         <v>Active</v>
       </c>
       <c r="K1330" t="str">
-        <v>10 Litre Economy Dual Colour Dual Flush Cistern.</v>
-      </c>
-    </row>
-    <row r="1331">
-      <c r="A1331">
-        <v>1330</v>
-      </c>
-      <c r="B1331" t="str">
-        <v>FG-400834</v>
-      </c>
-      <c r="C1331" t="str">
-        <v>EWC SEAT COVER (WITHOUT JET) (Standard)</v>
-      </c>
-      <c r="D1331" t="str">
-        <v>EWC SEAT COVER (WITHOUT JET)</v>
-      </c>
-      <c r="E1331" t="str">
-        <v>Toilet Seat Cover &amp; Flushing Cistern</v>
-      </c>
-      <c r="F1331" t="str">
-        <v>General</v>
-      </c>
-      <c r="G1331" t="str">
-        <v>Standard</v>
-      </c>
-      <c r="H1331" t="str">
-        <v>NOS</v>
-      </c>
-      <c r="I1331">
-        <v>20</v>
-      </c>
-      <c r="J1331" t="str">
-        <v>Active</v>
-      </c>
-      <c r="K1331" t="str">
         <v>EWC Toilet Seat Cover without jet spray.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K1331"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K1330"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
+++ b/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
@@ -17220,10 +17220,10 @@
         <v>-</v>
       </c>
       <c r="C481" t="str">
-        <v>UPVC- END PLUG (1/2)</v>
+        <v>UPVC CIRCUIT PLUG</v>
       </c>
       <c r="D481" t="str">
-        <v>UPVC- END PLUG</v>
+        <v>UPVC CIRCUIT PLUG</v>
       </c>
       <c r="E481" t="str">
         <v>UPVC Pipes &amp; Fittings</v>
@@ -17232,7 +17232,7 @@
         <v>General</v>
       </c>
       <c r="G481" t="str">
-        <v>1/2</v>
+        <v>Standard</v>
       </c>
       <c r="H481" t="str">
         <v>BOX</v>
@@ -17244,7 +17244,7 @@
         <v>Active</v>
       </c>
       <c r="K481" t="str">
-        <v>UPVC- END PLUG. Available sizes: 1/2.</v>
+        <v>UPVC CIRCUIT PLUG.</v>
       </c>
     </row>
     <row r="482">

--- a/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
+++ b/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
@@ -17217,10 +17217,10 @@
         <v>480</v>
       </c>
       <c r="B481" t="str">
-        <v>-</v>
+        <v>FG-400402</v>
       </c>
       <c r="C481" t="str">
-        <v>UPVC CIRCUIT PLUG</v>
+        <v>UPVC CIRCUIT PLUG (1/2)</v>
       </c>
       <c r="D481" t="str">
         <v>UPVC CIRCUIT PLUG</v>
@@ -17232,19 +17232,19 @@
         <v>General</v>
       </c>
       <c r="G481" t="str">
-        <v>Standard</v>
+        <v>1/2</v>
       </c>
       <c r="H481" t="str">
         <v>BOX</v>
       </c>
-      <c r="I481" t="str">
-        <v>-</v>
+      <c r="I481">
+        <v>300</v>
       </c>
       <c r="J481" t="str">
         <v>Active</v>
       </c>
       <c r="K481" t="str">
-        <v>UPVC CIRCUIT PLUG.</v>
+        <v>UPVC CIRCUIT PLUG. Available sizes: 1/2.</v>
       </c>
     </row>
     <row r="482">

--- a/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
+++ b/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1331"/>
+  <dimension ref="A1:K1330"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -35665,10 +35665,10 @@
         <v>-</v>
       </c>
       <c r="C1008" t="str">
-        <v>PN10 - ELBOW ISI (25MM)</v>
+        <v>AGRI ELBOW 10KG</v>
       </c>
       <c r="D1008" t="str">
-        <v>PN10 - ELBOW ISI</v>
+        <v>AGRI ELBOW 10KG</v>
       </c>
       <c r="E1008" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35677,7 +35677,7 @@
         <v>General</v>
       </c>
       <c r="G1008" t="str">
-        <v>25MM</v>
+        <v>Standard</v>
       </c>
       <c r="H1008" t="str">
         <v>BOX</v>
@@ -35689,7 +35689,7 @@
         <v>Active</v>
       </c>
       <c r="K1008" t="str">
-        <v>PN10 - ELBOW ISI for agriculture irrigation and piping systems.</v>
+        <v>AGRI ELBOW 10KG.</v>
       </c>
     </row>
     <row r="1009">
@@ -35700,10 +35700,10 @@
         <v>-</v>
       </c>
       <c r="C1009" t="str">
-        <v>PN10 - ELBOW ISI (32MM)</v>
+        <v>PN10 - UNION ISI (25MM)</v>
       </c>
       <c r="D1009" t="str">
-        <v>PN10 - ELBOW ISI</v>
+        <v>PN10 - UNION ISI</v>
       </c>
       <c r="E1009" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35712,7 +35712,7 @@
         <v>General</v>
       </c>
       <c r="G1009" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1009" t="str">
         <v>BOX</v>
@@ -35724,7 +35724,7 @@
         <v>Active</v>
       </c>
       <c r="K1009" t="str">
-        <v>PN10 - ELBOW ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - UNION ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1010">
@@ -35735,7 +35735,7 @@
         <v>-</v>
       </c>
       <c r="C1010" t="str">
-        <v>PN10 - UNION ISI (25MM)</v>
+        <v>PN10 - UNION ISI (32MM)</v>
       </c>
       <c r="D1010" t="str">
         <v>PN10 - UNION ISI</v>
@@ -35747,7 +35747,7 @@
         <v>General</v>
       </c>
       <c r="G1010" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1010" t="str">
         <v>BOX</v>
@@ -35770,10 +35770,10 @@
         <v>-</v>
       </c>
       <c r="C1011" t="str">
-        <v>PN10 - UNION ISI (32MM)</v>
+        <v>PN10 - TEE ISI (25MM)</v>
       </c>
       <c r="D1011" t="str">
-        <v>PN10 - UNION ISI</v>
+        <v>PN10 - TEE ISI</v>
       </c>
       <c r="E1011" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35782,7 +35782,7 @@
         <v>General</v>
       </c>
       <c r="G1011" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1011" t="str">
         <v>BOX</v>
@@ -35794,7 +35794,7 @@
         <v>Active</v>
       </c>
       <c r="K1011" t="str">
-        <v>PN10 - UNION ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - TEE ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1012">
@@ -35805,7 +35805,7 @@
         <v>-</v>
       </c>
       <c r="C1012" t="str">
-        <v>PN10 - TEE ISI (25MM)</v>
+        <v>PN10 - TEE ISI (32MM)</v>
       </c>
       <c r="D1012" t="str">
         <v>PN10 - TEE ISI</v>
@@ -35817,7 +35817,7 @@
         <v>General</v>
       </c>
       <c r="G1012" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1012" t="str">
         <v>BOX</v>
@@ -35840,10 +35840,10 @@
         <v>-</v>
       </c>
       <c r="C1013" t="str">
-        <v>PN10 - TEE ISI (32MM)</v>
+        <v>PN10 - COUPLER ISI (25MM)</v>
       </c>
       <c r="D1013" t="str">
-        <v>PN10 - TEE ISI</v>
+        <v>PN10 - COUPLER ISI</v>
       </c>
       <c r="E1013" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35852,7 +35852,7 @@
         <v>General</v>
       </c>
       <c r="G1013" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1013" t="str">
         <v>BOX</v>
@@ -35864,7 +35864,7 @@
         <v>Active</v>
       </c>
       <c r="K1013" t="str">
-        <v>PN10 - TEE ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - COUPLER ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1014">
@@ -35875,7 +35875,7 @@
         <v>-</v>
       </c>
       <c r="C1014" t="str">
-        <v>PN10 - COUPLER ISI (25MM)</v>
+        <v>PN10 - COUPLER ISI (32MM)</v>
       </c>
       <c r="D1014" t="str">
         <v>PN10 - COUPLER ISI</v>
@@ -35887,7 +35887,7 @@
         <v>General</v>
       </c>
       <c r="G1014" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1014" t="str">
         <v>BOX</v>
@@ -35910,10 +35910,10 @@
         <v>-</v>
       </c>
       <c r="C1015" t="str">
-        <v>PN10 - COUPLER ISI (32MM)</v>
+        <v>PN10 - MTA ISI (25MM)</v>
       </c>
       <c r="D1015" t="str">
-        <v>PN10 - COUPLER ISI</v>
+        <v>PN10 - MTA ISI</v>
       </c>
       <c r="E1015" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35922,7 +35922,7 @@
         <v>General</v>
       </c>
       <c r="G1015" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1015" t="str">
         <v>BOX</v>
@@ -35934,7 +35934,7 @@
         <v>Active</v>
       </c>
       <c r="K1015" t="str">
-        <v>PN10 - COUPLER ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - MTA ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1016">
@@ -35945,7 +35945,7 @@
         <v>-</v>
       </c>
       <c r="C1016" t="str">
-        <v>PN10 - MTA ISI (25MM)</v>
+        <v>PN10 - MTA ISI (32MM)</v>
       </c>
       <c r="D1016" t="str">
         <v>PN10 - MTA ISI</v>
@@ -35957,7 +35957,7 @@
         <v>General</v>
       </c>
       <c r="G1016" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1016" t="str">
         <v>BOX</v>
@@ -35980,10 +35980,10 @@
         <v>-</v>
       </c>
       <c r="C1017" t="str">
-        <v>PN10 - MTA ISI (32MM)</v>
+        <v>PN10 - FTA ISI (25MM)</v>
       </c>
       <c r="D1017" t="str">
-        <v>PN10 - MTA ISI</v>
+        <v>PN10 - FTA ISI</v>
       </c>
       <c r="E1017" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35992,7 +35992,7 @@
         <v>General</v>
       </c>
       <c r="G1017" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1017" t="str">
         <v>BOX</v>
@@ -36004,7 +36004,7 @@
         <v>Active</v>
       </c>
       <c r="K1017" t="str">
-        <v>PN10 - MTA ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - FTA ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1018">
@@ -36015,7 +36015,7 @@
         <v>-</v>
       </c>
       <c r="C1018" t="str">
-        <v>PN10 - FTA ISI (25MM)</v>
+        <v>PN10 - FTA ISI (32MM)</v>
       </c>
       <c r="D1018" t="str">
         <v>PN10 - FTA ISI</v>
@@ -36027,7 +36027,7 @@
         <v>General</v>
       </c>
       <c r="G1018" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1018" t="str">
         <v>BOX</v>
@@ -36050,10 +36050,10 @@
         <v>-</v>
       </c>
       <c r="C1019" t="str">
-        <v>PN10 - FTA ISI (32MM)</v>
+        <v>PN10 - END CAP ISI (25MM)</v>
       </c>
       <c r="D1019" t="str">
-        <v>PN10 - FTA ISI</v>
+        <v>PN10 - END CAP ISI</v>
       </c>
       <c r="E1019" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36062,7 +36062,7 @@
         <v>General</v>
       </c>
       <c r="G1019" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1019" t="str">
         <v>BOX</v>
@@ -36074,7 +36074,7 @@
         <v>Active</v>
       </c>
       <c r="K1019" t="str">
-        <v>PN10 - FTA ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - END CAP ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1020">
@@ -36085,7 +36085,7 @@
         <v>-</v>
       </c>
       <c r="C1020" t="str">
-        <v>PN10 - END CAP ISI (25MM)</v>
+        <v>PN10 - END CAP ISI (32MM)</v>
       </c>
       <c r="D1020" t="str">
         <v>PN10 - END CAP ISI</v>
@@ -36097,7 +36097,7 @@
         <v>General</v>
       </c>
       <c r="G1020" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1020" t="str">
         <v>BOX</v>
@@ -36120,10 +36120,10 @@
         <v>-</v>
       </c>
       <c r="C1021" t="str">
-        <v>PN10 - END CAP ISI (32MM)</v>
+        <v>PN10 - REDUCING BUSH ISI (32 X 20)</v>
       </c>
       <c r="D1021" t="str">
-        <v>PN10 - END CAP ISI</v>
+        <v>PN10 - REDUCING BUSH ISI</v>
       </c>
       <c r="E1021" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36132,7 +36132,7 @@
         <v>General</v>
       </c>
       <c r="G1021" t="str">
-        <v>32MM</v>
+        <v>32 X 20</v>
       </c>
       <c r="H1021" t="str">
         <v>BOX</v>
@@ -36144,7 +36144,7 @@
         <v>Active</v>
       </c>
       <c r="K1021" t="str">
-        <v>PN10 - END CAP ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - REDUCING BUSH ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1022">
@@ -36155,7 +36155,7 @@
         <v>-</v>
       </c>
       <c r="C1022" t="str">
-        <v>PN10 - REDUCING BUSH ISI (32 X 20)</v>
+        <v>PN10 - REDUCING BUSH ISI (32 X 25)</v>
       </c>
       <c r="D1022" t="str">
         <v>PN10 - REDUCING BUSH ISI</v>
@@ -36167,7 +36167,7 @@
         <v>General</v>
       </c>
       <c r="G1022" t="str">
-        <v>32 X 20</v>
+        <v>32 X 25</v>
       </c>
       <c r="H1022" t="str">
         <v>BOX</v>
@@ -36187,13 +36187,13 @@
         <v>1022</v>
       </c>
       <c r="B1023" t="str">
-        <v>-</v>
+        <v>FG-400585</v>
       </c>
       <c r="C1023" t="str">
-        <v>PN10 - REDUCING BUSH ISI (32 X 25)</v>
+        <v>AGRI REDUCER (50X40MM)</v>
       </c>
       <c r="D1023" t="str">
-        <v>PN10 - REDUCING BUSH ISI</v>
+        <v>AGRI REDUCER</v>
       </c>
       <c r="E1023" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36202,19 +36202,19 @@
         <v>General</v>
       </c>
       <c r="G1023" t="str">
-        <v>32 X 25</v>
+        <v>50X40MM</v>
       </c>
       <c r="H1023" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1023" t="str">
-        <v>-</v>
+      <c r="I1023">
+        <v>300</v>
       </c>
       <c r="J1023" t="str">
         <v>Active</v>
       </c>
       <c r="K1023" t="str">
-        <v>PN10 - REDUCING BUSH ISI for agriculture irrigation and piping systems.</v>
+        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
       </c>
     </row>
     <row r="1024">
@@ -36222,10 +36222,10 @@
         <v>1023</v>
       </c>
       <c r="B1024" t="str">
-        <v>FG-400585</v>
+        <v>FG-400584</v>
       </c>
       <c r="C1024" t="str">
-        <v>AGRI REDUCER (50X40MM)</v>
+        <v>AGRI REDUCER (63X40MM)</v>
       </c>
       <c r="D1024" t="str">
         <v>AGRI REDUCER</v>
@@ -36237,13 +36237,13 @@
         <v>General</v>
       </c>
       <c r="G1024" t="str">
-        <v>50X40MM</v>
+        <v>63X40MM</v>
       </c>
       <c r="H1024" t="str">
         <v>BOX</v>
       </c>
       <c r="I1024">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J1024" t="str">
         <v>Active</v>
@@ -36257,10 +36257,10 @@
         <v>1024</v>
       </c>
       <c r="B1025" t="str">
-        <v>FG-400584</v>
+        <v>FG-400583</v>
       </c>
       <c r="C1025" t="str">
-        <v>AGRI REDUCER (63X40MM)</v>
+        <v>AGRI REDUCER (63X50MM)</v>
       </c>
       <c r="D1025" t="str">
         <v>AGRI REDUCER</v>
@@ -36272,13 +36272,13 @@
         <v>General</v>
       </c>
       <c r="G1025" t="str">
-        <v>63X40MM</v>
+        <v>63X50MM</v>
       </c>
       <c r="H1025" t="str">
         <v>BOX</v>
       </c>
       <c r="I1025">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="J1025" t="str">
         <v>Active</v>
@@ -36292,10 +36292,10 @@
         <v>1025</v>
       </c>
       <c r="B1026" t="str">
-        <v>FG-400583</v>
+        <v>FG-400582</v>
       </c>
       <c r="C1026" t="str">
-        <v>AGRI REDUCER (63X50MM)</v>
+        <v>AGRI REDUCER (75X40MM)</v>
       </c>
       <c r="D1026" t="str">
         <v>AGRI REDUCER</v>
@@ -36307,13 +36307,13 @@
         <v>General</v>
       </c>
       <c r="G1026" t="str">
-        <v>63X50MM</v>
+        <v>75X40MM</v>
       </c>
       <c r="H1026" t="str">
         <v>BOX</v>
       </c>
       <c r="I1026">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J1026" t="str">
         <v>Active</v>
@@ -36327,10 +36327,10 @@
         <v>1026</v>
       </c>
       <c r="B1027" t="str">
-        <v>FG-400582</v>
+        <v>FG-400581</v>
       </c>
       <c r="C1027" t="str">
-        <v>AGRI REDUCER (75X40MM)</v>
+        <v>AGRI REDUCER (75X50MM)</v>
       </c>
       <c r="D1027" t="str">
         <v>AGRI REDUCER</v>
@@ -36342,13 +36342,13 @@
         <v>General</v>
       </c>
       <c r="G1027" t="str">
-        <v>75X40MM</v>
+        <v>75X50MM</v>
       </c>
       <c r="H1027" t="str">
         <v>BOX</v>
       </c>
       <c r="I1027">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J1027" t="str">
         <v>Active</v>
@@ -36362,10 +36362,10 @@
         <v>1027</v>
       </c>
       <c r="B1028" t="str">
-        <v>FG-400581</v>
+        <v>FG-400580</v>
       </c>
       <c r="C1028" t="str">
-        <v>AGRI REDUCER (75X50MM)</v>
+        <v>AGRI REDUCER (75X63MM)</v>
       </c>
       <c r="D1028" t="str">
         <v>AGRI REDUCER</v>
@@ -36377,13 +36377,13 @@
         <v>General</v>
       </c>
       <c r="G1028" t="str">
-        <v>75X50MM</v>
+        <v>75X63MM</v>
       </c>
       <c r="H1028" t="str">
         <v>BOX</v>
       </c>
       <c r="I1028">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J1028" t="str">
         <v>Active</v>
@@ -36397,10 +36397,10 @@
         <v>1028</v>
       </c>
       <c r="B1029" t="str">
-        <v>FG-400580</v>
+        <v>FG-400579</v>
       </c>
       <c r="C1029" t="str">
-        <v>AGRI REDUCER (75X63MM)</v>
+        <v>AGRI REDUCER (90X50MM)</v>
       </c>
       <c r="D1029" t="str">
         <v>AGRI REDUCER</v>
@@ -36412,13 +36412,13 @@
         <v>General</v>
       </c>
       <c r="G1029" t="str">
-        <v>75X63MM</v>
+        <v>90X50MM</v>
       </c>
       <c r="H1029" t="str">
         <v>BOX</v>
       </c>
       <c r="I1029">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J1029" t="str">
         <v>Active</v>
@@ -36432,10 +36432,10 @@
         <v>1029</v>
       </c>
       <c r="B1030" t="str">
-        <v>FG-400579</v>
+        <v>FG-400578</v>
       </c>
       <c r="C1030" t="str">
-        <v>AGRI REDUCER (90X50MM)</v>
+        <v>AGRI REDUCER (90X63MM)</v>
       </c>
       <c r="D1030" t="str">
         <v>AGRI REDUCER</v>
@@ -36447,13 +36447,13 @@
         <v>General</v>
       </c>
       <c r="G1030" t="str">
-        <v>90X50MM</v>
+        <v>90X63MM</v>
       </c>
       <c r="H1030" t="str">
         <v>BOX</v>
       </c>
       <c r="I1030">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J1030" t="str">
         <v>Active</v>
@@ -36467,10 +36467,10 @@
         <v>1030</v>
       </c>
       <c r="B1031" t="str">
-        <v>FG-400578</v>
+        <v>FG-400577</v>
       </c>
       <c r="C1031" t="str">
-        <v>AGRI REDUCER (90X63MM)</v>
+        <v>AGRI REDUCER (90X75MM)</v>
       </c>
       <c r="D1031" t="str">
         <v>AGRI REDUCER</v>
@@ -36482,13 +36482,13 @@
         <v>General</v>
       </c>
       <c r="G1031" t="str">
-        <v>90X63MM</v>
+        <v>90X75MM</v>
       </c>
       <c r="H1031" t="str">
         <v>BOX</v>
       </c>
       <c r="I1031">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="J1031" t="str">
         <v>Active</v>
@@ -36502,10 +36502,10 @@
         <v>1031</v>
       </c>
       <c r="B1032" t="str">
-        <v>FG-400577</v>
+        <v>FG-400576</v>
       </c>
       <c r="C1032" t="str">
-        <v>AGRI REDUCER (90X75MM)</v>
+        <v>AGRI REDUCER (110X63MM)</v>
       </c>
       <c r="D1032" t="str">
         <v>AGRI REDUCER</v>
@@ -36517,13 +36517,13 @@
         <v>General</v>
       </c>
       <c r="G1032" t="str">
-        <v>90X75MM</v>
+        <v>110X63MM</v>
       </c>
       <c r="H1032" t="str">
         <v>BOX</v>
       </c>
       <c r="I1032">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J1032" t="str">
         <v>Active</v>
@@ -36537,10 +36537,10 @@
         <v>1032</v>
       </c>
       <c r="B1033" t="str">
-        <v>FG-400576</v>
+        <v>FG-400575</v>
       </c>
       <c r="C1033" t="str">
-        <v>AGRI REDUCER (110X63MM)</v>
+        <v>AGRI REDUCER (110X75MM)</v>
       </c>
       <c r="D1033" t="str">
         <v>AGRI REDUCER</v>
@@ -36552,7 +36552,7 @@
         <v>General</v>
       </c>
       <c r="G1033" t="str">
-        <v>110X63MM</v>
+        <v>110X75MM</v>
       </c>
       <c r="H1033" t="str">
         <v>BOX</v>
@@ -36572,10 +36572,10 @@
         <v>1033</v>
       </c>
       <c r="B1034" t="str">
-        <v>FG-400575</v>
+        <v>FG-400574</v>
       </c>
       <c r="C1034" t="str">
-        <v>AGRI REDUCER (110X75MM)</v>
+        <v>AGRI REDUCER (110X90MM)</v>
       </c>
       <c r="D1034" t="str">
         <v>AGRI REDUCER</v>
@@ -36587,13 +36587,13 @@
         <v>General</v>
       </c>
       <c r="G1034" t="str">
-        <v>110X75MM</v>
+        <v>110X90MM</v>
       </c>
       <c r="H1034" t="str">
         <v>BOX</v>
       </c>
       <c r="I1034">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J1034" t="str">
         <v>Active</v>
@@ -36607,13 +36607,13 @@
         <v>1034</v>
       </c>
       <c r="B1035" t="str">
-        <v>FG-400574</v>
+        <v>-</v>
       </c>
       <c r="C1035" t="str">
-        <v>AGRI REDUCER (110X90MM)</v>
+        <v>REDUCING BUSH (LW) (63 X 40)</v>
       </c>
       <c r="D1035" t="str">
-        <v>AGRI REDUCER</v>
+        <v>REDUCING BUSH (LW)</v>
       </c>
       <c r="E1035" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36622,19 +36622,19 @@
         <v>General</v>
       </c>
       <c r="G1035" t="str">
-        <v>110X90MM</v>
+        <v>63 X 40</v>
       </c>
       <c r="H1035" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1035">
-        <v>40</v>
+      <c r="I1035" t="str">
+        <v>-</v>
       </c>
       <c r="J1035" t="str">
         <v>Active</v>
       </c>
       <c r="K1035" t="str">
-        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
+        <v>REDUCING BUSH (LW) for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1036">
@@ -36645,7 +36645,7 @@
         <v>-</v>
       </c>
       <c r="C1036" t="str">
-        <v>REDUCING BUSH (LW) (63 X 40)</v>
+        <v>REDUCING BUSH (LW) (63 X 50)</v>
       </c>
       <c r="D1036" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36657,7 +36657,7 @@
         <v>General</v>
       </c>
       <c r="G1036" t="str">
-        <v>63 X 40</v>
+        <v>63 X 50</v>
       </c>
       <c r="H1036" t="str">
         <v>BOX</v>
@@ -36680,7 +36680,7 @@
         <v>-</v>
       </c>
       <c r="C1037" t="str">
-        <v>REDUCING BUSH (LW) (63 X 50)</v>
+        <v>REDUCING BUSH (LW) (75 X 40)</v>
       </c>
       <c r="D1037" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36692,7 +36692,7 @@
         <v>General</v>
       </c>
       <c r="G1037" t="str">
-        <v>63 X 50</v>
+        <v>75 X 40</v>
       </c>
       <c r="H1037" t="str">
         <v>BOX</v>
@@ -36715,7 +36715,7 @@
         <v>-</v>
       </c>
       <c r="C1038" t="str">
-        <v>REDUCING BUSH (LW) (75 X 40)</v>
+        <v>REDUCING BUSH (LW) (75 X 63)</v>
       </c>
       <c r="D1038" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36727,7 +36727,7 @@
         <v>General</v>
       </c>
       <c r="G1038" t="str">
-        <v>75 X 40</v>
+        <v>75 X 63</v>
       </c>
       <c r="H1038" t="str">
         <v>BOX</v>
@@ -36750,7 +36750,7 @@
         <v>-</v>
       </c>
       <c r="C1039" t="str">
-        <v>REDUCING BUSH (LW) (75 X 63)</v>
+        <v>REDUCING BUSH (LW) (90 X 50)</v>
       </c>
       <c r="D1039" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36762,7 +36762,7 @@
         <v>General</v>
       </c>
       <c r="G1039" t="str">
-        <v>75 X 63</v>
+        <v>90 X 50</v>
       </c>
       <c r="H1039" t="str">
         <v>BOX</v>
@@ -36785,7 +36785,7 @@
         <v>-</v>
       </c>
       <c r="C1040" t="str">
-        <v>REDUCING BUSH (LW) (90 X 50)</v>
+        <v>REDUCING BUSH (LW) (90 X 63)</v>
       </c>
       <c r="D1040" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36797,7 +36797,7 @@
         <v>General</v>
       </c>
       <c r="G1040" t="str">
-        <v>90 X 50</v>
+        <v>90 X 63</v>
       </c>
       <c r="H1040" t="str">
         <v>BOX</v>
@@ -36820,7 +36820,7 @@
         <v>-</v>
       </c>
       <c r="C1041" t="str">
-        <v>REDUCING BUSH (LW) (90 X 63)</v>
+        <v>REDUCING BUSH (LW) (90 X 75)</v>
       </c>
       <c r="D1041" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36832,7 +36832,7 @@
         <v>General</v>
       </c>
       <c r="G1041" t="str">
-        <v>90 X 63</v>
+        <v>90 X 75</v>
       </c>
       <c r="H1041" t="str">
         <v>BOX</v>
@@ -36855,7 +36855,7 @@
         <v>-</v>
       </c>
       <c r="C1042" t="str">
-        <v>REDUCING BUSH (LW) (90 X 75)</v>
+        <v>REDUCING BUSH (LW) (110 X 63)</v>
       </c>
       <c r="D1042" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36867,7 +36867,7 @@
         <v>General</v>
       </c>
       <c r="G1042" t="str">
-        <v>90 X 75</v>
+        <v>110 X 63</v>
       </c>
       <c r="H1042" t="str">
         <v>BOX</v>
@@ -36890,7 +36890,7 @@
         <v>-</v>
       </c>
       <c r="C1043" t="str">
-        <v>REDUCING BUSH (LW) (110 X 63)</v>
+        <v>REDUCING BUSH (LW) (110 X 75)</v>
       </c>
       <c r="D1043" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36902,7 +36902,7 @@
         <v>General</v>
       </c>
       <c r="G1043" t="str">
-        <v>110 X 63</v>
+        <v>110 X 75</v>
       </c>
       <c r="H1043" t="str">
         <v>BOX</v>
@@ -36925,7 +36925,7 @@
         <v>-</v>
       </c>
       <c r="C1044" t="str">
-        <v>REDUCING BUSH (LW) (110 X 75)</v>
+        <v>REDUCING BUSH (LW) (110 X 90)</v>
       </c>
       <c r="D1044" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36937,7 +36937,7 @@
         <v>General</v>
       </c>
       <c r="G1044" t="str">
-        <v>110 X 75</v>
+        <v>110 X 90</v>
       </c>
       <c r="H1044" t="str">
         <v>BOX</v>
@@ -36957,13 +36957,13 @@
         <v>1044</v>
       </c>
       <c r="B1045" t="str">
-        <v>-</v>
+        <v>FG-400550</v>
       </c>
       <c r="C1045" t="str">
-        <v>REDUCING BUSH (LW) (110 X 90)</v>
+        <v>AGRI TEE (40MM)</v>
       </c>
       <c r="D1045" t="str">
-        <v>REDUCING BUSH (LW)</v>
+        <v>AGRI TEE</v>
       </c>
       <c r="E1045" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36972,19 +36972,19 @@
         <v>General</v>
       </c>
       <c r="G1045" t="str">
-        <v>110 X 90</v>
+        <v>40MM</v>
       </c>
       <c r="H1045" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1045" t="str">
-        <v>-</v>
+      <c r="I1045">
+        <v>150</v>
       </c>
       <c r="J1045" t="str">
         <v>Active</v>
       </c>
       <c r="K1045" t="str">
-        <v>REDUCING BUSH (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1046">
@@ -36992,10 +36992,10 @@
         <v>1045</v>
       </c>
       <c r="B1046" t="str">
-        <v>FG-400550</v>
+        <v>FG-400551</v>
       </c>
       <c r="C1046" t="str">
-        <v>AGRI TEE (40MM)</v>
+        <v>AGRI TEE (50MM)</v>
       </c>
       <c r="D1046" t="str">
         <v>AGRI TEE</v>
@@ -37007,13 +37007,13 @@
         <v>General</v>
       </c>
       <c r="G1046" t="str">
-        <v>40MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1046" t="str">
         <v>BOX</v>
       </c>
       <c r="I1046">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J1046" t="str">
         <v>Active</v>
@@ -37027,10 +37027,10 @@
         <v>1046</v>
       </c>
       <c r="B1047" t="str">
-        <v>FG-400551</v>
+        <v>FG-400552</v>
       </c>
       <c r="C1047" t="str">
-        <v>AGRI TEE (50MM)</v>
+        <v>AGRI TEE (63MM)</v>
       </c>
       <c r="D1047" t="str">
         <v>AGRI TEE</v>
@@ -37042,13 +37042,13 @@
         <v>General</v>
       </c>
       <c r="G1047" t="str">
-        <v>50MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1047" t="str">
         <v>BOX</v>
       </c>
       <c r="I1047">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J1047" t="str">
         <v>Active</v>
@@ -37062,10 +37062,10 @@
         <v>1047</v>
       </c>
       <c r="B1048" t="str">
-        <v>FG-400552</v>
+        <v>FG-400553</v>
       </c>
       <c r="C1048" t="str">
-        <v>AGRI TEE (63MM)</v>
+        <v>AGRI TEE (75MM)</v>
       </c>
       <c r="D1048" t="str">
         <v>AGRI TEE</v>
@@ -37077,13 +37077,13 @@
         <v>General</v>
       </c>
       <c r="G1048" t="str">
-        <v>63MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1048" t="str">
         <v>BOX</v>
       </c>
       <c r="I1048">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="J1048" t="str">
         <v>Active</v>
@@ -37097,10 +37097,10 @@
         <v>1048</v>
       </c>
       <c r="B1049" t="str">
-        <v>FG-400553</v>
+        <v>FG-400554</v>
       </c>
       <c r="C1049" t="str">
-        <v>AGRI TEE (75MM)</v>
+        <v>AGRI TEE (90MM)</v>
       </c>
       <c r="D1049" t="str">
         <v>AGRI TEE</v>
@@ -37112,13 +37112,13 @@
         <v>General</v>
       </c>
       <c r="G1049" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1049" t="str">
         <v>BOX</v>
       </c>
       <c r="I1049">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J1049" t="str">
         <v>Active</v>
@@ -37132,10 +37132,10 @@
         <v>1049</v>
       </c>
       <c r="B1050" t="str">
-        <v>FG-400554</v>
+        <v>FG-400586</v>
       </c>
       <c r="C1050" t="str">
-        <v>AGRI TEE (90MM)</v>
+        <v>AGRI TEE (110MM)</v>
       </c>
       <c r="D1050" t="str">
         <v>AGRI TEE</v>
@@ -37147,13 +37147,13 @@
         <v>General</v>
       </c>
       <c r="G1050" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1050" t="str">
         <v>BOX</v>
       </c>
       <c r="I1050">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J1050" t="str">
         <v>Active</v>
@@ -37167,10 +37167,10 @@
         <v>1050</v>
       </c>
       <c r="B1051" t="str">
-        <v>FG-400586</v>
+        <v>FG-400607</v>
       </c>
       <c r="C1051" t="str">
-        <v>AGRI TEE (110MM)</v>
+        <v>AGRI TEE (140MM)</v>
       </c>
       <c r="D1051" t="str">
         <v>AGRI TEE</v>
@@ -37182,13 +37182,13 @@
         <v>General</v>
       </c>
       <c r="G1051" t="str">
-        <v>110MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1051" t="str">
         <v>BOX</v>
       </c>
       <c r="I1051">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="J1051" t="str">
         <v>Active</v>
@@ -37202,10 +37202,10 @@
         <v>1051</v>
       </c>
       <c r="B1052" t="str">
-        <v>FG-400607</v>
+        <v>FG-400608</v>
       </c>
       <c r="C1052" t="str">
-        <v>AGRI TEE (140MM)</v>
+        <v>AGRI TEE (160MM)</v>
       </c>
       <c r="D1052" t="str">
         <v>AGRI TEE</v>
@@ -37217,13 +37217,13 @@
         <v>General</v>
       </c>
       <c r="G1052" t="str">
-        <v>140MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1052" t="str">
         <v>BOX</v>
       </c>
       <c r="I1052">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J1052" t="str">
         <v>Active</v>
@@ -37237,13 +37237,13 @@
         <v>1052</v>
       </c>
       <c r="B1053" t="str">
-        <v>FG-400608</v>
+        <v>-</v>
       </c>
       <c r="C1053" t="str">
-        <v>AGRI TEE (160MM)</v>
+        <v>COUPLER (LW) (75MM)</v>
       </c>
       <c r="D1053" t="str">
-        <v>AGRI TEE</v>
+        <v>COUPLER (LW)</v>
       </c>
       <c r="E1053" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37252,19 +37252,19 @@
         <v>General</v>
       </c>
       <c r="G1053" t="str">
-        <v>160MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1053" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1053">
-        <v>9</v>
+      <c r="I1053" t="str">
+        <v>-</v>
       </c>
       <c r="J1053" t="str">
         <v>Active</v>
       </c>
       <c r="K1053" t="str">
-        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
+        <v>COUPLER (LW) for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1054">
@@ -37275,7 +37275,7 @@
         <v>-</v>
       </c>
       <c r="C1054" t="str">
-        <v>COUPLER (LW) (75MM)</v>
+        <v>COUPLER (LW) (90MM)</v>
       </c>
       <c r="D1054" t="str">
         <v>COUPLER (LW)</v>
@@ -37287,7 +37287,7 @@
         <v>General</v>
       </c>
       <c r="G1054" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1054" t="str">
         <v>BOX</v>
@@ -37310,7 +37310,7 @@
         <v>-</v>
       </c>
       <c r="C1055" t="str">
-        <v>COUPLER (LW) (90MM)</v>
+        <v>COUPLER (LW) (110MM)</v>
       </c>
       <c r="D1055" t="str">
         <v>COUPLER (LW)</v>
@@ -37322,7 +37322,7 @@
         <v>General</v>
       </c>
       <c r="G1055" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1055" t="str">
         <v>BOX</v>
@@ -37342,13 +37342,13 @@
         <v>1055</v>
       </c>
       <c r="B1056" t="str">
-        <v>-</v>
+        <v>FG-400561</v>
       </c>
       <c r="C1056" t="str">
-        <v>COUPLER (LW) (110MM)</v>
+        <v>AGRI FABRICATED COUPLER (40MM)</v>
       </c>
       <c r="D1056" t="str">
-        <v>COUPLER (LW)</v>
+        <v>AGRI FABRICATED COUPLER</v>
       </c>
       <c r="E1056" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37357,19 +37357,19 @@
         <v>General</v>
       </c>
       <c r="G1056" t="str">
-        <v>110MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1056" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1056" t="str">
-        <v>-</v>
+      <c r="I1056">
+        <v>300</v>
       </c>
       <c r="J1056" t="str">
         <v>Active</v>
       </c>
       <c r="K1056" t="str">
-        <v>COUPLER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI FABRICATED COUPLER for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1057">
@@ -37377,10 +37377,10 @@
         <v>1056</v>
       </c>
       <c r="B1057" t="str">
-        <v>FG-400561</v>
+        <v>FG-400562</v>
       </c>
       <c r="C1057" t="str">
-        <v>AGRI FABRICATED COUPLER (40MM)</v>
+        <v>AGRI FABRICATED COUPLER (50MM)</v>
       </c>
       <c r="D1057" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37392,13 +37392,13 @@
         <v>General</v>
       </c>
       <c r="G1057" t="str">
-        <v>40MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1057" t="str">
         <v>BOX</v>
       </c>
       <c r="I1057">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J1057" t="str">
         <v>Active</v>
@@ -37412,10 +37412,10 @@
         <v>1057</v>
       </c>
       <c r="B1058" t="str">
-        <v>FG-400562</v>
+        <v>FG-400563</v>
       </c>
       <c r="C1058" t="str">
-        <v>AGRI FABRICATED COUPLER (50MM)</v>
+        <v>AGRI FABRICATED COUPLER (63MM)</v>
       </c>
       <c r="D1058" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37427,7 +37427,7 @@
         <v>General</v>
       </c>
       <c r="G1058" t="str">
-        <v>50MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1058" t="str">
         <v>BOX</v>
@@ -37447,10 +37447,10 @@
         <v>1058</v>
       </c>
       <c r="B1059" t="str">
-        <v>FG-400563</v>
+        <v>FG-400564</v>
       </c>
       <c r="C1059" t="str">
-        <v>AGRI FABRICATED COUPLER (63MM)</v>
+        <v>AGRI FABRICATED COUPLER (75MM)</v>
       </c>
       <c r="D1059" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37462,13 +37462,13 @@
         <v>General</v>
       </c>
       <c r="G1059" t="str">
-        <v>63MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1059" t="str">
         <v>BOX</v>
       </c>
       <c r="I1059">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="J1059" t="str">
         <v>Active</v>
@@ -37482,10 +37482,10 @@
         <v>1059</v>
       </c>
       <c r="B1060" t="str">
-        <v>FG-400564</v>
+        <v>FG-400565</v>
       </c>
       <c r="C1060" t="str">
-        <v>AGRI FABRICATED COUPLER (75MM)</v>
+        <v>AGRI FABRICATED COUPLER (90MM)</v>
       </c>
       <c r="D1060" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37497,13 +37497,13 @@
         <v>General</v>
       </c>
       <c r="G1060" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1060" t="str">
         <v>BOX</v>
       </c>
       <c r="I1060">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="J1060" t="str">
         <v>Active</v>
@@ -37517,10 +37517,10 @@
         <v>1060</v>
       </c>
       <c r="B1061" t="str">
-        <v>FG-400565</v>
+        <v>FG-400566</v>
       </c>
       <c r="C1061" t="str">
-        <v>AGRI FABRICATED COUPLER (90MM)</v>
+        <v>AGRI FABRICATED COUPLER (110MM)</v>
       </c>
       <c r="D1061" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37532,13 +37532,13 @@
         <v>General</v>
       </c>
       <c r="G1061" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1061" t="str">
         <v>BOX</v>
       </c>
       <c r="I1061">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J1061" t="str">
         <v>Active</v>
@@ -37552,10 +37552,10 @@
         <v>1061</v>
       </c>
       <c r="B1062" t="str">
-        <v>FG-400566</v>
+        <v>FG-400587</v>
       </c>
       <c r="C1062" t="str">
-        <v>AGRI FABRICATED COUPLER (110MM)</v>
+        <v>AGRI FABRICATED COUPLER (140MM 4KG)</v>
       </c>
       <c r="D1062" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37567,13 +37567,13 @@
         <v>General</v>
       </c>
       <c r="G1062" t="str">
-        <v>110MM</v>
+        <v>140MM 4KG</v>
       </c>
       <c r="H1062" t="str">
         <v>BOX</v>
       </c>
       <c r="I1062">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J1062" t="str">
         <v>Active</v>
@@ -37587,10 +37587,10 @@
         <v>1062</v>
       </c>
       <c r="B1063" t="str">
-        <v>FG-400587</v>
+        <v>FG-400568</v>
       </c>
       <c r="C1063" t="str">
-        <v>AGRI FABRICATED COUPLER (140MM 4KG)</v>
+        <v>AGRI FABRICATED COUPLER (160MM 4KG)</v>
       </c>
       <c r="D1063" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37602,13 +37602,13 @@
         <v>General</v>
       </c>
       <c r="G1063" t="str">
-        <v>140MM 4KG</v>
+        <v>160MM 4KG</v>
       </c>
       <c r="H1063" t="str">
         <v>BOX</v>
       </c>
       <c r="I1063">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J1063" t="str">
         <v>Active</v>
@@ -37622,13 +37622,13 @@
         <v>1063</v>
       </c>
       <c r="B1064" t="str">
-        <v>FG-400568</v>
+        <v>FG-400567</v>
       </c>
       <c r="C1064" t="str">
-        <v>AGRI FABRICATED COUPLER (160MM 4KG)</v>
+        <v>AGRI FABRICATED COUPLER 6KG (140MM)</v>
       </c>
       <c r="D1064" t="str">
-        <v>AGRI FABRICATED COUPLER</v>
+        <v>AGRI FABRICATED COUPLER 6KG</v>
       </c>
       <c r="E1064" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37637,19 +37637,19 @@
         <v>General</v>
       </c>
       <c r="G1064" t="str">
-        <v>160MM 4KG</v>
+        <v>140MM</v>
       </c>
       <c r="H1064" t="str">
         <v>BOX</v>
       </c>
       <c r="I1064">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J1064" t="str">
         <v>Active</v>
       </c>
       <c r="K1064" t="str">
-        <v>AGRI FABRICATED COUPLER for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
+        <v>AGRI FABRICATED COUPLER 6KG for agriculture irrigation and piping systems. Available sizes: 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1065">
@@ -37657,10 +37657,10 @@
         <v>1064</v>
       </c>
       <c r="B1065" t="str">
-        <v>FG-400567</v>
+        <v>FG-400569</v>
       </c>
       <c r="C1065" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG (140MM)</v>
+        <v>AGRI FABRICATED COUPLER 6KG (160MM)</v>
       </c>
       <c r="D1065" t="str">
         <v>AGRI FABRICATED COUPLER 6KG</v>
@@ -37672,13 +37672,13 @@
         <v>General</v>
       </c>
       <c r="G1065" t="str">
-        <v>140MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1065" t="str">
         <v>BOX</v>
       </c>
       <c r="I1065">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J1065" t="str">
         <v>Active</v>
@@ -37692,13 +37692,13 @@
         <v>1065</v>
       </c>
       <c r="B1066" t="str">
-        <v>FG-400569</v>
+        <v>FG-400544</v>
       </c>
       <c r="C1066" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG (160MM)</v>
+        <v>AGRI ELBOW (40MM)</v>
       </c>
       <c r="D1066" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG</v>
+        <v>AGRI ELBOW</v>
       </c>
       <c r="E1066" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37707,19 +37707,19 @@
         <v>General</v>
       </c>
       <c r="G1066" t="str">
-        <v>160MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1066" t="str">
         <v>BOX</v>
       </c>
       <c r="I1066">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="J1066" t="str">
         <v>Active</v>
       </c>
       <c r="K1066" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG for agriculture irrigation and piping systems. Available sizes: 140MM, 160MM.</v>
+        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1067">
@@ -37727,10 +37727,10 @@
         <v>1066</v>
       </c>
       <c r="B1067" t="str">
-        <v>FG-400544</v>
+        <v>FG-400545</v>
       </c>
       <c r="C1067" t="str">
-        <v>AGRI ELBOW (40MM)</v>
+        <v>AGRI ELBOW (50MM)</v>
       </c>
       <c r="D1067" t="str">
         <v>AGRI ELBOW</v>
@@ -37742,13 +37742,13 @@
         <v>General</v>
       </c>
       <c r="G1067" t="str">
-        <v>40MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1067" t="str">
         <v>BOX</v>
       </c>
       <c r="I1067">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="J1067" t="str">
         <v>Active</v>
@@ -37762,10 +37762,10 @@
         <v>1067</v>
       </c>
       <c r="B1068" t="str">
-        <v>FG-400545</v>
+        <v>FG-400546</v>
       </c>
       <c r="C1068" t="str">
-        <v>AGRI ELBOW (50MM)</v>
+        <v>AGRI ELBOW (63MM)</v>
       </c>
       <c r="D1068" t="str">
         <v>AGRI ELBOW</v>
@@ -37777,13 +37777,13 @@
         <v>General</v>
       </c>
       <c r="G1068" t="str">
-        <v>50MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1068" t="str">
         <v>BOX</v>
       </c>
       <c r="I1068">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J1068" t="str">
         <v>Active</v>
@@ -37797,10 +37797,10 @@
         <v>1068</v>
       </c>
       <c r="B1069" t="str">
-        <v>FG-400546</v>
+        <v>FG-400547</v>
       </c>
       <c r="C1069" t="str">
-        <v>AGRI ELBOW (63MM)</v>
+        <v>AGRI ELBOW (75MM)</v>
       </c>
       <c r="D1069" t="str">
         <v>AGRI ELBOW</v>
@@ -37812,13 +37812,13 @@
         <v>General</v>
       </c>
       <c r="G1069" t="str">
-        <v>63MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1069" t="str">
         <v>BOX</v>
       </c>
       <c r="I1069">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J1069" t="str">
         <v>Active</v>
@@ -37832,10 +37832,10 @@
         <v>1069</v>
       </c>
       <c r="B1070" t="str">
-        <v>FG-400547</v>
+        <v>FG-400548</v>
       </c>
       <c r="C1070" t="str">
-        <v>AGRI ELBOW (75MM)</v>
+        <v>AGRI ELBOW (90MM)</v>
       </c>
       <c r="D1070" t="str">
         <v>AGRI ELBOW</v>
@@ -37847,13 +37847,13 @@
         <v>General</v>
       </c>
       <c r="G1070" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1070" t="str">
         <v>BOX</v>
       </c>
       <c r="I1070">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="J1070" t="str">
         <v>Active</v>
@@ -37867,10 +37867,10 @@
         <v>1070</v>
       </c>
       <c r="B1071" t="str">
-        <v>FG-400548</v>
+        <v>FG-400549</v>
       </c>
       <c r="C1071" t="str">
-        <v>AGRI ELBOW (90MM)</v>
+        <v>AGRI ELBOW (110MM)</v>
       </c>
       <c r="D1071" t="str">
         <v>AGRI ELBOW</v>
@@ -37882,13 +37882,13 @@
         <v>General</v>
       </c>
       <c r="G1071" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1071" t="str">
         <v>BOX</v>
       </c>
       <c r="I1071">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J1071" t="str">
         <v>Active</v>
@@ -37902,10 +37902,10 @@
         <v>1071</v>
       </c>
       <c r="B1072" t="str">
-        <v>FG-400549</v>
+        <v>FG-400595</v>
       </c>
       <c r="C1072" t="str">
-        <v>AGRI ELBOW (110MM)</v>
+        <v>AGRI ELBOW (140MM)</v>
       </c>
       <c r="D1072" t="str">
         <v>AGRI ELBOW</v>
@@ -37917,13 +37917,13 @@
         <v>General</v>
       </c>
       <c r="G1072" t="str">
-        <v>110MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1072" t="str">
         <v>BOX</v>
       </c>
       <c r="I1072">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="J1072" t="str">
         <v>Active</v>
@@ -37937,10 +37937,10 @@
         <v>1072</v>
       </c>
       <c r="B1073" t="str">
-        <v>FG-400595</v>
+        <v>FG-400596</v>
       </c>
       <c r="C1073" t="str">
-        <v>AGRI ELBOW (140MM)</v>
+        <v>AGRI ELBOW (160MM)</v>
       </c>
       <c r="D1073" t="str">
         <v>AGRI ELBOW</v>
@@ -37952,13 +37952,13 @@
         <v>General</v>
       </c>
       <c r="G1073" t="str">
-        <v>140MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1073" t="str">
         <v>BOX</v>
       </c>
       <c r="I1073">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J1073" t="str">
         <v>Active</v>
@@ -37972,13 +37972,13 @@
         <v>1073</v>
       </c>
       <c r="B1074" t="str">
-        <v>FG-400596</v>
+        <v>FG-400555</v>
       </c>
       <c r="C1074" t="str">
-        <v>AGRI ELBOW (160MM)</v>
+        <v>AGRI END CAP (40MM)</v>
       </c>
       <c r="D1074" t="str">
-        <v>AGRI ELBOW</v>
+        <v>AGRI END CAP</v>
       </c>
       <c r="E1074" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37987,19 +37987,19 @@
         <v>General</v>
       </c>
       <c r="G1074" t="str">
-        <v>160MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1074" t="str">
         <v>BOX</v>
       </c>
       <c r="I1074">
-        <v>12</v>
+        <v>800</v>
       </c>
       <c r="J1074" t="str">
         <v>Active</v>
       </c>
       <c r="K1074" t="str">
-        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
+        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1075">
@@ -38007,10 +38007,10 @@
         <v>1074</v>
       </c>
       <c r="B1075" t="str">
-        <v>FG-400555</v>
+        <v>FG-400556</v>
       </c>
       <c r="C1075" t="str">
-        <v>AGRI END CAP (40MM)</v>
+        <v>AGRI END CAP (50MM)</v>
       </c>
       <c r="D1075" t="str">
         <v>AGRI END CAP</v>
@@ -38022,13 +38022,13 @@
         <v>General</v>
       </c>
       <c r="G1075" t="str">
-        <v>40MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1075" t="str">
         <v>BOX</v>
       </c>
       <c r="I1075">
-        <v>800</v>
+        <v>450</v>
       </c>
       <c r="J1075" t="str">
         <v>Active</v>
@@ -38042,10 +38042,10 @@
         <v>1075</v>
       </c>
       <c r="B1076" t="str">
-        <v>FG-400556</v>
+        <v>FG-400557</v>
       </c>
       <c r="C1076" t="str">
-        <v>AGRI END CAP (50MM)</v>
+        <v>AGRI END CAP (63MM)</v>
       </c>
       <c r="D1076" t="str">
         <v>AGRI END CAP</v>
@@ -38057,13 +38057,13 @@
         <v>General</v>
       </c>
       <c r="G1076" t="str">
-        <v>50MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1076" t="str">
         <v>BOX</v>
       </c>
       <c r="I1076">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="J1076" t="str">
         <v>Active</v>
@@ -38077,10 +38077,10 @@
         <v>1076</v>
       </c>
       <c r="B1077" t="str">
-        <v>FG-400557</v>
+        <v>FG-400558</v>
       </c>
       <c r="C1077" t="str">
-        <v>AGRI END CAP (63MM)</v>
+        <v>AGRI END CAP (75MM)</v>
       </c>
       <c r="D1077" t="str">
         <v>AGRI END CAP</v>
@@ -38092,13 +38092,13 @@
         <v>General</v>
       </c>
       <c r="G1077" t="str">
-        <v>63MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1077" t="str">
         <v>BOX</v>
       </c>
       <c r="I1077">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="J1077" t="str">
         <v>Active</v>
@@ -38112,10 +38112,10 @@
         <v>1077</v>
       </c>
       <c r="B1078" t="str">
-        <v>FG-400558</v>
+        <v>FG-400559</v>
       </c>
       <c r="C1078" t="str">
-        <v>AGRI END CAP (75MM)</v>
+        <v>AGRI END CAP (90MM)</v>
       </c>
       <c r="D1078" t="str">
         <v>AGRI END CAP</v>
@@ -38127,13 +38127,13 @@
         <v>General</v>
       </c>
       <c r="G1078" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1078" t="str">
         <v>BOX</v>
       </c>
       <c r="I1078">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J1078" t="str">
         <v>Active</v>
@@ -38147,10 +38147,10 @@
         <v>1078</v>
       </c>
       <c r="B1079" t="str">
-        <v>FG-400559</v>
+        <v>FG-400560</v>
       </c>
       <c r="C1079" t="str">
-        <v>AGRI END CAP (90MM)</v>
+        <v>AGRI END CAP (110MM)</v>
       </c>
       <c r="D1079" t="str">
         <v>AGRI END CAP</v>
@@ -38162,13 +38162,13 @@
         <v>General</v>
       </c>
       <c r="G1079" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1079" t="str">
         <v>BOX</v>
       </c>
       <c r="I1079">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J1079" t="str">
         <v>Active</v>
@@ -38182,10 +38182,10 @@
         <v>1079</v>
       </c>
       <c r="B1080" t="str">
-        <v>FG-400560</v>
+        <v>FG-400639</v>
       </c>
       <c r="C1080" t="str">
-        <v>AGRI END CAP (110MM)</v>
+        <v>AGRI END CAP (140MM 4KG)</v>
       </c>
       <c r="D1080" t="str">
         <v>AGRI END CAP</v>
@@ -38197,13 +38197,13 @@
         <v>General</v>
       </c>
       <c r="G1080" t="str">
-        <v>110MM</v>
+        <v>140MM 4KG</v>
       </c>
       <c r="H1080" t="str">
         <v>BOX</v>
       </c>
       <c r="I1080">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J1080" t="str">
         <v>Active</v>
@@ -38217,10 +38217,10 @@
         <v>1080</v>
       </c>
       <c r="B1081" t="str">
-        <v>FG-400639</v>
+        <v>FG-400640</v>
       </c>
       <c r="C1081" t="str">
-        <v>AGRI END CAP (140MM 4KG)</v>
+        <v>AGRI END CAP (160MM 4KG)</v>
       </c>
       <c r="D1081" t="str">
         <v>AGRI END CAP</v>
@@ -38232,13 +38232,13 @@
         <v>General</v>
       </c>
       <c r="G1081" t="str">
-        <v>140MM 4KG</v>
+        <v>160MM 4KG</v>
       </c>
       <c r="H1081" t="str">
         <v>BOX</v>
       </c>
       <c r="I1081">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J1081" t="str">
         <v>Active</v>
@@ -38252,13 +38252,13 @@
         <v>1081</v>
       </c>
       <c r="B1082" t="str">
-        <v>FG-400640</v>
+        <v>FG-400570</v>
       </c>
       <c r="C1082" t="str">
-        <v>AGRI END CAP (160MM 4KG)</v>
+        <v>AGRI LONG BEND (63MM)</v>
       </c>
       <c r="D1082" t="str">
-        <v>AGRI END CAP</v>
+        <v>AGRI LONG BEND</v>
       </c>
       <c r="E1082" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -38267,19 +38267,19 @@
         <v>General</v>
       </c>
       <c r="G1082" t="str">
-        <v>160MM 4KG</v>
+        <v>63MM</v>
       </c>
       <c r="H1082" t="str">
         <v>BOX</v>
       </c>
       <c r="I1082">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="J1082" t="str">
         <v>Active</v>
       </c>
       <c r="K1082" t="str">
-        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
+        <v>AGRI LONG BEND for agriculture irrigation and piping systems. Available sizes: 63MM, 75MM, 90MM, 110MM.</v>
       </c>
     </row>
     <row r="1083">
@@ -38287,10 +38287,10 @@
         <v>1082</v>
       </c>
       <c r="B1083" t="str">
-        <v>FG-400570</v>
+        <v>FG-400571</v>
       </c>
       <c r="C1083" t="str">
-        <v>AGRI LONG BEND (63MM)</v>
+        <v>AGRI LONG BEND (75MM)</v>
       </c>
       <c r="D1083" t="str">
         <v>AGRI LONG BEND</v>
@@ -38302,13 +38302,13 @@
         <v>General</v>
       </c>
       <c r="G1083" t="str">
-        <v>63MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1083" t="str">
         <v>BOX</v>
       </c>
       <c r="I1083">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J1083" t="str">
         <v>Active</v>
@@ -38322,10 +38322,10 @@
         <v>1083</v>
       </c>
       <c r="B1084" t="str">
-        <v>FG-400571</v>
+        <v>FG-400572</v>
       </c>
       <c r="C1084" t="str">
-        <v>AGRI LONG BEND (75MM)</v>
+        <v>AGRI LONG BEND (90MM)</v>
       </c>
       <c r="D1084" t="str">
         <v>AGRI LONG BEND</v>
@@ -38337,13 +38337,13 @@
         <v>General</v>
       </c>
       <c r="G1084" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1084" t="str">
         <v>BOX</v>
       </c>
       <c r="I1084">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J1084" t="str">
         <v>Active</v>
@@ -38357,10 +38357,10 @@
         <v>1084</v>
       </c>
       <c r="B1085" t="str">
-        <v>FG-400572</v>
+        <v>FG-400573</v>
       </c>
       <c r="C1085" t="str">
-        <v>AGRI LONG BEND (90MM)</v>
+        <v>AGRI LONG BEND (110MM)</v>
       </c>
       <c r="D1085" t="str">
         <v>AGRI LONG BEND</v>
@@ -38372,13 +38372,13 @@
         <v>General</v>
       </c>
       <c r="G1085" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1085" t="str">
         <v>BOX</v>
       </c>
       <c r="I1085">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J1085" t="str">
         <v>Active</v>
@@ -38392,34 +38392,34 @@
         <v>1085</v>
       </c>
       <c r="B1086" t="str">
-        <v>FG-400573</v>
+        <v>FG-401520</v>
       </c>
       <c r="C1086" t="str">
-        <v>AGRI LONG BEND (110MM)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1086" t="str">
-        <v>AGRI LONG BEND</v>
+        <v>SPRINKLER ISI PIPE 6 MTR</v>
       </c>
       <c r="E1086" t="str">
-        <v>Agriculture Pipes &amp; Fittings</v>
+        <v>Sprinkler Pipes &amp; Fittings</v>
       </c>
       <c r="F1086" t="str">
         <v>General</v>
       </c>
       <c r="G1086" t="str">
-        <v>110MM</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1086" t="str">
-        <v>BOX</v>
-      </c>
-      <c r="I1086">
-        <v>10</v>
+        <v>Nos</v>
+      </c>
+      <c r="I1086" t="str">
+        <v>-</v>
       </c>
       <c r="J1086" t="str">
         <v>Active</v>
       </c>
       <c r="K1086" t="str">
-        <v>AGRI LONG BEND for agriculture irrigation and piping systems. Available sizes: 63MM, 75MM, 90MM, 110MM.</v>
+        <v>SPRINKLER ISI PIPE 6 MTR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1087">
@@ -38427,10 +38427,10 @@
         <v>1086</v>
       </c>
       <c r="B1087" t="str">
-        <v>FG-401520</v>
+        <v>FG-401491</v>
       </c>
       <c r="C1087" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (63MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1087" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38442,7 +38442,7 @@
         <v>General</v>
       </c>
       <c r="G1087" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>63MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1087" t="str">
         <v>Nos</v>
@@ -38462,10 +38462,10 @@
         <v>1087</v>
       </c>
       <c r="B1088" t="str">
-        <v>FG-401491</v>
+        <v>FG-401490</v>
       </c>
       <c r="C1088" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (63MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 2.5 KG)</v>
       </c>
       <c r="D1088" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38477,7 +38477,7 @@
         <v>General</v>
       </c>
       <c r="G1088" t="str">
-        <v>63MM L TYPE 3.2 KG</v>
+        <v>75MM C TYPE 2.5 KG</v>
       </c>
       <c r="H1088" t="str">
         <v>Nos</v>
@@ -38497,10 +38497,10 @@
         <v>1088</v>
       </c>
       <c r="B1089" t="str">
-        <v>FG-401490</v>
+        <v>FG-401492</v>
       </c>
       <c r="C1089" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 2.5 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1089" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38512,7 +38512,7 @@
         <v>General</v>
       </c>
       <c r="G1089" t="str">
-        <v>75MM C TYPE 2.5 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1089" t="str">
         <v>Nos</v>
@@ -38532,10 +38532,10 @@
         <v>1089</v>
       </c>
       <c r="B1090" t="str">
-        <v>FG-401492</v>
+        <v>FG-401519</v>
       </c>
       <c r="C1090" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 2.5 KG)</v>
       </c>
       <c r="D1090" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38547,7 +38547,7 @@
         <v>General</v>
       </c>
       <c r="G1090" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>75MM L TYPE 2.5 KG</v>
       </c>
       <c r="H1090" t="str">
         <v>Nos</v>
@@ -38567,10 +38567,10 @@
         <v>1090</v>
       </c>
       <c r="B1091" t="str">
-        <v>FG-401519</v>
+        <v>FG-401521</v>
       </c>
       <c r="C1091" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 2.5 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1091" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38582,7 +38582,7 @@
         <v>General</v>
       </c>
       <c r="G1091" t="str">
-        <v>75MM L TYPE 2.5 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1091" t="str">
         <v>Nos</v>
@@ -38602,13 +38602,13 @@
         <v>1091</v>
       </c>
       <c r="B1092" t="str">
-        <v>FG-401521</v>
+        <v>FG-401522</v>
       </c>
       <c r="C1092" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1092" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR</v>
+        <v>SPRINKLER NISI PIPE 6 MTR</v>
       </c>
       <c r="E1092" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38629,7 +38629,7 @@
         <v>Active</v>
       </c>
       <c r="K1092" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER NISI PIPE 6 MTR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1093">
@@ -38637,10 +38637,10 @@
         <v>1092</v>
       </c>
       <c r="B1093" t="str">
-        <v>FG-401522</v>
+        <v>FG-401523</v>
       </c>
       <c r="C1093" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1093" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38652,7 +38652,7 @@
         <v>General</v>
       </c>
       <c r="G1093" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1093" t="str">
         <v>Nos</v>
@@ -38672,10 +38672,10 @@
         <v>1093</v>
       </c>
       <c r="B1094" t="str">
-        <v>FG-401523</v>
+        <v>FG-401866</v>
       </c>
       <c r="C1094" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (90MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1094" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38687,7 +38687,7 @@
         <v>General</v>
       </c>
       <c r="G1094" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>90MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1094" t="str">
         <v>Nos</v>
@@ -38707,10 +38707,10 @@
         <v>1094</v>
       </c>
       <c r="B1095" t="str">
-        <v>FG-401866</v>
+        <v>FG-401867</v>
       </c>
       <c r="C1095" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (90MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (90MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1095" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38722,7 +38722,7 @@
         <v>General</v>
       </c>
       <c r="G1095" t="str">
-        <v>90MM C TYPE 3.2 KG</v>
+        <v>90MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1095" t="str">
         <v>Nos</v>
@@ -38742,13 +38742,13 @@
         <v>1095</v>
       </c>
       <c r="B1096" t="str">
-        <v>FG-401867</v>
+        <v>FG-401498</v>
       </c>
       <c r="C1096" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (90MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1096" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR</v>
+        <v>SPRINKLER SET 6 MTR ISI</v>
       </c>
       <c r="E1096" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38757,7 +38757,7 @@
         <v>General</v>
       </c>
       <c r="G1096" t="str">
-        <v>90MM L TYPE 3.2 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1096" t="str">
         <v>Nos</v>
@@ -38769,7 +38769,7 @@
         <v>Active</v>
       </c>
       <c r="K1096" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER SET 6 MTR ISI for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1097">
@@ -38777,10 +38777,10 @@
         <v>1096</v>
       </c>
       <c r="B1097" t="str">
-        <v>FG-401498</v>
+        <v>FG-401499</v>
       </c>
       <c r="C1097" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1097" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38792,7 +38792,7 @@
         <v>General</v>
       </c>
       <c r="G1097" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1097" t="str">
         <v>Nos</v>
@@ -38812,10 +38812,10 @@
         <v>1097</v>
       </c>
       <c r="B1098" t="str">
-        <v>FG-401499</v>
+        <v>FG-401500</v>
       </c>
       <c r="C1098" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 2.5 KG)</v>
       </c>
       <c r="D1098" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38827,7 +38827,7 @@
         <v>General</v>
       </c>
       <c r="G1098" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>75MM C TYPE 2.5 KG</v>
       </c>
       <c r="H1098" t="str">
         <v>Nos</v>
@@ -38847,10 +38847,10 @@
         <v>1098</v>
       </c>
       <c r="B1099" t="str">
-        <v>FG-401500</v>
+        <v>FG-401524</v>
       </c>
       <c r="C1099" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 2.5 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 2.5 KG)</v>
       </c>
       <c r="D1099" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38862,7 +38862,7 @@
         <v>General</v>
       </c>
       <c r="G1099" t="str">
-        <v>75MM C TYPE 2.5 KG</v>
+        <v>75MM L TYPE 2.5 KG</v>
       </c>
       <c r="H1099" t="str">
         <v>Nos</v>
@@ -38882,10 +38882,10 @@
         <v>1099</v>
       </c>
       <c r="B1100" t="str">
-        <v>FG-401524</v>
+        <v>FG-401501</v>
       </c>
       <c r="C1100" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 2.5 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1100" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38897,7 +38897,7 @@
         <v>General</v>
       </c>
       <c r="G1100" t="str">
-        <v>75MM L TYPE 2.5 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1100" t="str">
         <v>Nos</v>
@@ -38917,13 +38917,13 @@
         <v>1100</v>
       </c>
       <c r="B1101" t="str">
-        <v>FG-401501</v>
+        <v>FG-401495</v>
       </c>
       <c r="C1101" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1101" t="str">
-        <v>SPRINKLER SET 6 MTR ISI</v>
+        <v>SPRINKLER SET 6 MTR N-ISI</v>
       </c>
       <c r="E1101" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38932,7 +38932,7 @@
         <v>General</v>
       </c>
       <c r="G1101" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1101" t="str">
         <v>Nos</v>
@@ -38944,7 +38944,7 @@
         <v>Active</v>
       </c>
       <c r="K1101" t="str">
-        <v>SPRINKLER SET 6 MTR ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER SET 6 MTR N-ISI for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1102">
@@ -38952,10 +38952,10 @@
         <v>1101</v>
       </c>
       <c r="B1102" t="str">
-        <v>FG-401495</v>
+        <v>FG-401496</v>
       </c>
       <c r="C1102" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1102" t="str">
         <v>SPRINKLER SET 6 MTR N-ISI</v>
@@ -38967,7 +38967,7 @@
         <v>General</v>
       </c>
       <c r="G1102" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1102" t="str">
         <v>Nos</v>
@@ -38987,10 +38987,10 @@
         <v>1102</v>
       </c>
       <c r="B1103" t="str">
-        <v>FG-401496</v>
+        <v>FG-401497</v>
       </c>
       <c r="C1103" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1103" t="str">
         <v>SPRINKLER SET 6 MTR N-ISI</v>
@@ -39002,7 +39002,7 @@
         <v>General</v>
       </c>
       <c r="G1103" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1103" t="str">
         <v>Nos</v>
@@ -39022,13 +39022,13 @@
         <v>1103</v>
       </c>
       <c r="B1104" t="str">
-        <v>FG-401497</v>
+        <v>FG-401503</v>
       </c>
       <c r="C1104" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER FITTINGS TEE (75MM, C TYPE)</v>
       </c>
       <c r="D1104" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI</v>
+        <v>SPRINKLER FITTINGS TEE</v>
       </c>
       <c r="E1104" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39037,7 +39037,7 @@
         <v>General</v>
       </c>
       <c r="G1104" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM, C TYPE</v>
       </c>
       <c r="H1104" t="str">
         <v>Nos</v>
@@ -39049,7 +39049,7 @@
         <v>Active</v>
       </c>
       <c r="K1104" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS TEE for sprinkler irrigation systems. Available sizes: 75MM, C TYPE, 75MM, L TYPE, 63MM, C TYPE.</v>
       </c>
     </row>
     <row r="1105">
@@ -39057,10 +39057,10 @@
         <v>1104</v>
       </c>
       <c r="B1105" t="str">
-        <v>FG-401503</v>
+        <v>FG-401511</v>
       </c>
       <c r="C1105" t="str">
-        <v>SPRINKLER FITTINGS TEE (75MM, C TYPE)</v>
+        <v>SPRINKLER FITTINGS TEE (75MM, L TYPE)</v>
       </c>
       <c r="D1105" t="str">
         <v>SPRINKLER FITTINGS TEE</v>
@@ -39072,7 +39072,7 @@
         <v>General</v>
       </c>
       <c r="G1105" t="str">
-        <v>75MM, C TYPE</v>
+        <v>75MM, L TYPE</v>
       </c>
       <c r="H1105" t="str">
         <v>Nos</v>
@@ -39092,10 +39092,10 @@
         <v>1105</v>
       </c>
       <c r="B1106" t="str">
-        <v>FG-401511</v>
+        <v>FG-401526</v>
       </c>
       <c r="C1106" t="str">
-        <v>SPRINKLER FITTINGS TEE (75MM, L TYPE)</v>
+        <v>SPRINKLER FITTINGS TEE (63MM, C TYPE)</v>
       </c>
       <c r="D1106" t="str">
         <v>SPRINKLER FITTINGS TEE</v>
@@ -39107,7 +39107,7 @@
         <v>General</v>
       </c>
       <c r="G1106" t="str">
-        <v>75MM, L TYPE</v>
+        <v>63MM, C TYPE</v>
       </c>
       <c r="H1106" t="str">
         <v>Nos</v>
@@ -39127,13 +39127,13 @@
         <v>1106</v>
       </c>
       <c r="B1107" t="str">
-        <v>FG-401526</v>
+        <v>FG-401504</v>
       </c>
       <c r="C1107" t="str">
-        <v>SPRINKLER FITTINGS TEE (63MM, C TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (75MM C TYPE)</v>
       </c>
       <c r="D1107" t="str">
-        <v>SPRINKLER FITTINGS TEE</v>
+        <v>SPRINKLER FITTINGS ADAPTOR</v>
       </c>
       <c r="E1107" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39142,7 +39142,7 @@
         <v>General</v>
       </c>
       <c r="G1107" t="str">
-        <v>63MM, C TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1107" t="str">
         <v>Nos</v>
@@ -39154,7 +39154,7 @@
         <v>Active</v>
       </c>
       <c r="K1107" t="str">
-        <v>SPRINKLER FITTINGS TEE for sprinkler irrigation systems. Available sizes: 75MM, C TYPE, 75MM, L TYPE, 63MM, C TYPE.</v>
+        <v>SPRINKLER FITTINGS ADAPTOR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1108">
@@ -39162,10 +39162,10 @@
         <v>1107</v>
       </c>
       <c r="B1108" t="str">
-        <v>FG-401504</v>
+        <v>FG-401512</v>
       </c>
       <c r="C1108" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (75MM P TYPE)</v>
       </c>
       <c r="D1108" t="str">
         <v>SPRINKLER FITTINGS ADAPTOR</v>
@@ -39177,7 +39177,7 @@
         <v>General</v>
       </c>
       <c r="G1108" t="str">
-        <v>75MM C TYPE</v>
+        <v>75MM P TYPE</v>
       </c>
       <c r="H1108" t="str">
         <v>Nos</v>
@@ -39197,10 +39197,10 @@
         <v>1108</v>
       </c>
       <c r="B1109" t="str">
-        <v>FG-401512</v>
+        <v>FG-401527</v>
       </c>
       <c r="C1109" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (75MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (63MM C TYPE)</v>
       </c>
       <c r="D1109" t="str">
         <v>SPRINKLER FITTINGS ADAPTOR</v>
@@ -39212,7 +39212,7 @@
         <v>General</v>
       </c>
       <c r="G1109" t="str">
-        <v>75MM P TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1109" t="str">
         <v>Nos</v>
@@ -39232,13 +39232,13 @@
         <v>1109</v>
       </c>
       <c r="B1110" t="str">
-        <v>FG-401527</v>
+        <v>FG-401502</v>
       </c>
       <c r="C1110" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (75MM C TYPE)</v>
       </c>
       <c r="D1110" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR</v>
+        <v>SPRINKLER FITTINGS BEND</v>
       </c>
       <c r="E1110" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39247,7 +39247,7 @@
         <v>General</v>
       </c>
       <c r="G1110" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1110" t="str">
         <v>Nos</v>
@@ -39259,7 +39259,7 @@
         <v>Active</v>
       </c>
       <c r="K1110" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS BEND for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1111">
@@ -39267,10 +39267,10 @@
         <v>1110</v>
       </c>
       <c r="B1111" t="str">
-        <v>FG-401502</v>
+        <v>FG-401510</v>
       </c>
       <c r="C1111" t="str">
-        <v>SPRINKLER FITTINGS BEND (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (75MM L TYPE)</v>
       </c>
       <c r="D1111" t="str">
         <v>SPRINKLER FITTINGS BEND</v>
@@ -39282,7 +39282,7 @@
         <v>General</v>
       </c>
       <c r="G1111" t="str">
-        <v>75MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1111" t="str">
         <v>Nos</v>
@@ -39302,10 +39302,10 @@
         <v>1111</v>
       </c>
       <c r="B1112" t="str">
-        <v>FG-401510</v>
+        <v>FG-401525</v>
       </c>
       <c r="C1112" t="str">
-        <v>SPRINKLER FITTINGS BEND (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (63MM C TYPE)</v>
       </c>
       <c r="D1112" t="str">
         <v>SPRINKLER FITTINGS BEND</v>
@@ -39317,7 +39317,7 @@
         <v>General</v>
       </c>
       <c r="G1112" t="str">
-        <v>75MM L TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1112" t="str">
         <v>Nos</v>
@@ -39337,13 +39337,13 @@
         <v>1112</v>
       </c>
       <c r="B1113" t="str">
-        <v>FG-401525</v>
+        <v>FG-401514</v>
       </c>
       <c r="C1113" t="str">
-        <v>SPRINKLER FITTINGS BEND (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (75MM L TYPE)</v>
       </c>
       <c r="D1113" t="str">
-        <v>SPRINKLER FITTINGS BEND</v>
+        <v>SPRINKLER FITTINGS END CAP</v>
       </c>
       <c r="E1113" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39352,7 +39352,7 @@
         <v>General</v>
       </c>
       <c r="G1113" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1113" t="str">
         <v>Nos</v>
@@ -39364,7 +39364,7 @@
         <v>Active</v>
       </c>
       <c r="K1113" t="str">
-        <v>SPRINKLER FITTINGS BEND for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS END CAP for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1114">
@@ -39372,10 +39372,10 @@
         <v>1113</v>
       </c>
       <c r="B1114" t="str">
-        <v>FG-401514</v>
+        <v>FG-401506</v>
       </c>
       <c r="C1114" t="str">
-        <v>SPRINKLER FITTINGS END CAP (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (75MM C TYPE)</v>
       </c>
       <c r="D1114" t="str">
         <v>SPRINKLER FITTINGS END CAP</v>
@@ -39387,7 +39387,7 @@
         <v>General</v>
       </c>
       <c r="G1114" t="str">
-        <v>75MM L TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1114" t="str">
         <v>Nos</v>
@@ -39407,10 +39407,10 @@
         <v>1114</v>
       </c>
       <c r="B1115" t="str">
-        <v>FG-401506</v>
+        <v>FG-401529</v>
       </c>
       <c r="C1115" t="str">
-        <v>SPRINKLER FITTINGS END CAP (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (63MM C TYPE)</v>
       </c>
       <c r="D1115" t="str">
         <v>SPRINKLER FITTINGS END CAP</v>
@@ -39422,7 +39422,7 @@
         <v>General</v>
       </c>
       <c r="G1115" t="str">
-        <v>75MM C TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1115" t="str">
         <v>Nos</v>
@@ -39442,13 +39442,13 @@
         <v>1115</v>
       </c>
       <c r="B1116" t="str">
-        <v>FG-401529</v>
+        <v>FG-401517</v>
       </c>
       <c r="C1116" t="str">
-        <v>SPRINKLER FITTINGS END CAP (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (75MM P TYPE)</v>
       </c>
       <c r="D1116" t="str">
-        <v>SPRINKLER FITTINGS END CAP</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
       </c>
       <c r="E1116" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39457,7 +39457,7 @@
         <v>General</v>
       </c>
       <c r="G1116" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM P TYPE</v>
       </c>
       <c r="H1116" t="str">
         <v>Nos</v>
@@ -39469,7 +39469,7 @@
         <v>Active</v>
       </c>
       <c r="K1116" t="str">
-        <v>SPRINKLER FITTINGS END CAP for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1117">
@@ -39477,10 +39477,10 @@
         <v>1116</v>
       </c>
       <c r="B1117" t="str">
-        <v>FG-401517</v>
+        <v>FG-401518</v>
       </c>
       <c r="C1117" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (75MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (63MM P TYPE)</v>
       </c>
       <c r="D1117" t="str">
         <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
@@ -39492,7 +39492,7 @@
         <v>General</v>
       </c>
       <c r="G1117" t="str">
-        <v>75MM P TYPE</v>
+        <v>63MM P TYPE</v>
       </c>
       <c r="H1117" t="str">
         <v>Nos</v>
@@ -39512,13 +39512,13 @@
         <v>1117</v>
       </c>
       <c r="B1118" t="str">
-        <v>FG-401518</v>
+        <v>FG-401505</v>
       </c>
       <c r="C1118" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (63MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (75MM C TYPE)</v>
       </c>
       <c r="D1118" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
+        <v>SPRINKLER FITTINGS PCN</v>
       </c>
       <c r="E1118" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39527,7 +39527,7 @@
         <v>General</v>
       </c>
       <c r="G1118" t="str">
-        <v>63MM P TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1118" t="str">
         <v>Nos</v>
@@ -39539,7 +39539,7 @@
         <v>Active</v>
       </c>
       <c r="K1118" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS PCN for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1119">
@@ -39547,10 +39547,10 @@
         <v>1118</v>
       </c>
       <c r="B1119" t="str">
-        <v>FG-401505</v>
+        <v>FG-401513</v>
       </c>
       <c r="C1119" t="str">
-        <v>SPRINKLER FITTINGS PCN (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (75MM L TYPE)</v>
       </c>
       <c r="D1119" t="str">
         <v>SPRINKLER FITTINGS PCN</v>
@@ -39562,7 +39562,7 @@
         <v>General</v>
       </c>
       <c r="G1119" t="str">
-        <v>75MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1119" t="str">
         <v>Nos</v>
@@ -39582,10 +39582,10 @@
         <v>1119</v>
       </c>
       <c r="B1120" t="str">
-        <v>FG-401513</v>
+        <v>FG-401528</v>
       </c>
       <c r="C1120" t="str">
-        <v>SPRINKLER FITTINGS PCN (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (63MM C TYPE)</v>
       </c>
       <c r="D1120" t="str">
         <v>SPRINKLER FITTINGS PCN</v>
@@ -39597,7 +39597,7 @@
         <v>General</v>
       </c>
       <c r="G1120" t="str">
-        <v>75MM L TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1120" t="str">
         <v>Nos</v>
@@ -39617,13 +39617,13 @@
         <v>1120</v>
       </c>
       <c r="B1121" t="str">
-        <v>FG-401528</v>
+        <v>FG-401507</v>
       </c>
       <c r="C1121" t="str">
-        <v>SPRINKLER FITTINGS PCN (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL (20MM)</v>
       </c>
       <c r="D1121" t="str">
-        <v>SPRINKLER FITTINGS PCN</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL</v>
       </c>
       <c r="E1121" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39632,7 +39632,7 @@
         <v>General</v>
       </c>
       <c r="G1121" t="str">
-        <v>63MM C TYPE</v>
+        <v>20MM</v>
       </c>
       <c r="H1121" t="str">
         <v>Nos</v>
@@ -39644,7 +39644,7 @@
         <v>Active</v>
       </c>
       <c r="K1121" t="str">
-        <v>SPRINKLER FITTINGS PCN for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1122">
@@ -39652,13 +39652,13 @@
         <v>1121</v>
       </c>
       <c r="B1122" t="str">
-        <v>FG-401507</v>
+        <v>FG-401508</v>
       </c>
       <c r="C1122" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL (20MM)</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE (75MM C TYPE)</v>
       </c>
       <c r="D1122" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE</v>
       </c>
       <c r="E1122" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39667,7 +39667,7 @@
         <v>General</v>
       </c>
       <c r="G1122" t="str">
-        <v>20MM</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1122" t="str">
         <v>Nos</v>
@@ -39679,7 +39679,7 @@
         <v>Active</v>
       </c>
       <c r="K1122" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1123">
@@ -39687,10 +39687,10 @@
         <v>1122</v>
       </c>
       <c r="B1123" t="str">
-        <v>FG-401508</v>
+        <v>FG-401515</v>
       </c>
       <c r="C1123" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE (20MM L TYPE)</v>
       </c>
       <c r="D1123" t="str">
         <v>SPRINKLER FITTINGS GI RISER PIPE</v>
@@ -39702,7 +39702,7 @@
         <v>General</v>
       </c>
       <c r="G1123" t="str">
-        <v>75MM C TYPE</v>
+        <v>20MM L TYPE</v>
       </c>
       <c r="H1123" t="str">
         <v>Nos</v>
@@ -39722,25 +39722,25 @@
         <v>1123</v>
       </c>
       <c r="B1124" t="str">
-        <v>FG-401515</v>
+        <v>FG-401742</v>
       </c>
       <c r="C1124" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE (20MM L TYPE)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 1)</v>
       </c>
       <c r="D1124" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE</v>
+        <v>ROUND DRIPLINE 12MM ISI</v>
       </c>
       <c r="E1124" t="str">
-        <v>Sprinkler Pipes &amp; Fittings</v>
+        <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1124" t="str">
-        <v>General</v>
+        <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1124" t="str">
-        <v>20MM L TYPE</v>
+        <v>12-4-30 CLASS 1</v>
       </c>
       <c r="H1124" t="str">
-        <v>Nos</v>
+        <v>ROLL</v>
       </c>
       <c r="I1124" t="str">
         <v>-</v>
@@ -39749,7 +39749,7 @@
         <v>Active</v>
       </c>
       <c r="K1124" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE for sprinkler irrigation systems.</v>
+        <v>ROUND DRIPLINE 12MM ISI certified.</v>
       </c>
     </row>
     <row r="1125">
@@ -39757,10 +39757,10 @@
         <v>1124</v>
       </c>
       <c r="B1125" t="str">
-        <v>FG-401742</v>
+        <v>FG-401743</v>
       </c>
       <c r="C1125" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 1)</v>
       </c>
       <c r="D1125" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39772,7 +39772,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1125" t="str">
-        <v>12-4-30 CLASS 1</v>
+        <v>12-4-40 CLASS 1</v>
       </c>
       <c r="H1125" t="str">
         <v>ROLL</v>
@@ -39792,10 +39792,10 @@
         <v>1125</v>
       </c>
       <c r="B1126" t="str">
-        <v>FG-401743</v>
+        <v>FG-401744</v>
       </c>
       <c r="C1126" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 1)</v>
       </c>
       <c r="D1126" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39807,7 +39807,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1126" t="str">
-        <v>12-4-40 CLASS 1</v>
+        <v>12-4-50 CLASS 1</v>
       </c>
       <c r="H1126" t="str">
         <v>ROLL</v>
@@ -39827,10 +39827,10 @@
         <v>1126</v>
       </c>
       <c r="B1127" t="str">
-        <v>FG-401744</v>
+        <v>FG-401751</v>
       </c>
       <c r="C1127" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1127" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39842,7 +39842,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1127" t="str">
-        <v>12-4-50 CLASS 1</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1127" t="str">
         <v>ROLL</v>
@@ -39862,10 +39862,10 @@
         <v>1127</v>
       </c>
       <c r="B1128" t="str">
-        <v>FG-401751</v>
+        <v>FG-401752</v>
       </c>
       <c r="C1128" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1128" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39877,7 +39877,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1128" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1128" t="str">
         <v>ROLL</v>
@@ -39897,10 +39897,10 @@
         <v>1128</v>
       </c>
       <c r="B1129" t="str">
-        <v>FG-401752</v>
+        <v>FG-401753</v>
       </c>
       <c r="C1129" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1129" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39912,7 +39912,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1129" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1129" t="str">
         <v>ROLL</v>
@@ -39932,10 +39932,10 @@
         <v>1129</v>
       </c>
       <c r="B1130" t="str">
-        <v>FG-401753</v>
+        <v>FG-401754</v>
       </c>
       <c r="C1130" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1130" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39947,7 +39947,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1130" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1130" t="str">
         <v>ROLL</v>
@@ -39967,10 +39967,10 @@
         <v>1130</v>
       </c>
       <c r="B1131" t="str">
-        <v>FG-401754</v>
+        <v>FG-401755</v>
       </c>
       <c r="C1131" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1131" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39982,7 +39982,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1131" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1131" t="str">
         <v>ROLL</v>
@@ -40002,10 +40002,10 @@
         <v>1131</v>
       </c>
       <c r="B1132" t="str">
-        <v>FG-401755</v>
+        <v>FG-401756</v>
       </c>
       <c r="C1132" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1132" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -40017,7 +40017,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1132" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1132" t="str">
         <v>ROLL</v>
@@ -40037,13 +40037,13 @@
         <v>1132</v>
       </c>
       <c r="B1133" t="str">
-        <v>FG-401756</v>
+        <v>FG-401745</v>
       </c>
       <c r="C1133" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1133" t="str">
-        <v>ROUND DRIPLINE 12MM ISI</v>
+        <v>ROUND DRIPLINE 16MM ISI</v>
       </c>
       <c r="E1133" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40052,7 +40052,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1133" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1133" t="str">
         <v>ROLL</v>
@@ -40064,7 +40064,7 @@
         <v>Active</v>
       </c>
       <c r="K1133" t="str">
-        <v>ROUND DRIPLINE 12MM ISI certified.</v>
+        <v>ROUND DRIPLINE 16MM ISI certified.</v>
       </c>
     </row>
     <row r="1134">
@@ -40072,10 +40072,10 @@
         <v>1133</v>
       </c>
       <c r="B1134" t="str">
-        <v>FG-401745</v>
+        <v>FG-401746</v>
       </c>
       <c r="C1134" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1134" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40087,7 +40087,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1134" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1134" t="str">
         <v>ROLL</v>
@@ -40107,10 +40107,10 @@
         <v>1134</v>
       </c>
       <c r="B1135" t="str">
-        <v>FG-401746</v>
+        <v>FG-401747</v>
       </c>
       <c r="C1135" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1135" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40122,7 +40122,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1135" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1135" t="str">
         <v>ROLL</v>
@@ -40142,10 +40142,10 @@
         <v>1135</v>
       </c>
       <c r="B1136" t="str">
-        <v>FG-401747</v>
+        <v>FG-401757</v>
       </c>
       <c r="C1136" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1136" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40157,7 +40157,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1136" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1136" t="str">
         <v>ROLL</v>
@@ -40177,10 +40177,10 @@
         <v>1136</v>
       </c>
       <c r="B1137" t="str">
-        <v>FG-401757</v>
+        <v>FG-401758</v>
       </c>
       <c r="C1137" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1137" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40192,7 +40192,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1137" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1137" t="str">
         <v>ROLL</v>
@@ -40212,10 +40212,10 @@
         <v>1137</v>
       </c>
       <c r="B1138" t="str">
-        <v>FG-401758</v>
+        <v>FG-401759</v>
       </c>
       <c r="C1138" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1138" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40227,7 +40227,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1138" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1138" t="str">
         <v>ROLL</v>
@@ -40247,13 +40247,13 @@
         <v>1138</v>
       </c>
       <c r="B1139" t="str">
-        <v>FG-401759</v>
+        <v>-</v>
       </c>
       <c r="C1139" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-30 CLASS-1)</v>
       </c>
       <c r="D1139" t="str">
-        <v>ROUND DRIPLINE 16MM ISI</v>
+        <v>20MM ROUND INLINE PIPE ISI</v>
       </c>
       <c r="E1139" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40262,10 +40262,10 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1139" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>20-4-30 CLASS-1</v>
       </c>
       <c r="H1139" t="str">
-        <v>ROLL</v>
+        <v>MTR</v>
       </c>
       <c r="I1139" t="str">
         <v>-</v>
@@ -40274,7 +40274,7 @@
         <v>Active</v>
       </c>
       <c r="K1139" t="str">
-        <v>ROUND DRIPLINE 16MM ISI certified.</v>
+        <v>20mm Round Inline Drip Pipe ISI certified.</v>
       </c>
     </row>
     <row r="1140">
@@ -40285,7 +40285,7 @@
         <v>-</v>
       </c>
       <c r="C1140" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-30 CLASS-1)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-40 CLASS-1)</v>
       </c>
       <c r="D1140" t="str">
         <v>20MM ROUND INLINE PIPE ISI</v>
@@ -40297,7 +40297,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1140" t="str">
-        <v>20-4-30 CLASS-1</v>
+        <v>20-4-40 CLASS-1</v>
       </c>
       <c r="H1140" t="str">
         <v>MTR</v>
@@ -40320,7 +40320,7 @@
         <v>-</v>
       </c>
       <c r="C1141" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-40 CLASS-1)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-50 CLASS-1)</v>
       </c>
       <c r="D1141" t="str">
         <v>20MM ROUND INLINE PIPE ISI</v>
@@ -40332,7 +40332,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1141" t="str">
-        <v>20-4-40 CLASS-1</v>
+        <v>20-4-50 CLASS-1</v>
       </c>
       <c r="H1141" t="str">
         <v>MTR</v>
@@ -40352,25 +40352,25 @@
         <v>1141</v>
       </c>
       <c r="B1142" t="str">
-        <v>-</v>
+        <v>FG-401763</v>
       </c>
       <c r="C1142" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-50 CLASS-1)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1142" t="str">
-        <v>20MM ROUND INLINE PIPE ISI</v>
+        <v>FLAT DRIPLINE 12MM ISI</v>
       </c>
       <c r="E1142" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1142" t="str">
-        <v>ROUND DRIP ISI</v>
+        <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1142" t="str">
-        <v>20-4-50 CLASS-1</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1142" t="str">
-        <v>MTR</v>
+        <v>ROLL</v>
       </c>
       <c r="I1142" t="str">
         <v>-</v>
@@ -40379,7 +40379,7 @@
         <v>Active</v>
       </c>
       <c r="K1142" t="str">
-        <v>20mm Round Inline Drip Pipe ISI certified.</v>
+        <v>FLAT DRIPLINE 12MM ISI certified.</v>
       </c>
     </row>
     <row r="1143">
@@ -40387,10 +40387,10 @@
         <v>1142</v>
       </c>
       <c r="B1143" t="str">
-        <v>FG-401763</v>
+        <v>FG-401764</v>
       </c>
       <c r="C1143" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1143" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40402,7 +40402,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1143" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1143" t="str">
         <v>ROLL</v>
@@ -40422,10 +40422,10 @@
         <v>1143</v>
       </c>
       <c r="B1144" t="str">
-        <v>FG-401764</v>
+        <v>FG-401765</v>
       </c>
       <c r="C1144" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1144" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40437,7 +40437,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1144" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1144" t="str">
         <v>ROLL</v>
@@ -40457,10 +40457,10 @@
         <v>1144</v>
       </c>
       <c r="B1145" t="str">
-        <v>FG-401765</v>
+        <v>FG-401766</v>
       </c>
       <c r="C1145" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1145" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40472,7 +40472,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1145" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1145" t="str">
         <v>ROLL</v>
@@ -40492,10 +40492,10 @@
         <v>1145</v>
       </c>
       <c r="B1146" t="str">
-        <v>FG-401766</v>
+        <v>FG-401767</v>
       </c>
       <c r="C1146" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1146" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40507,7 +40507,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1146" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1146" t="str">
         <v>ROLL</v>
@@ -40527,10 +40527,10 @@
         <v>1146</v>
       </c>
       <c r="B1147" t="str">
-        <v>FG-401767</v>
+        <v>FG-401768</v>
       </c>
       <c r="C1147" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1147" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40542,7 +40542,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1147" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1147" t="str">
         <v>ROLL</v>
@@ -40562,13 +40562,13 @@
         <v>1147</v>
       </c>
       <c r="B1148" t="str">
-        <v>FG-401768</v>
+        <v>FG-401760</v>
       </c>
       <c r="C1148" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1148" t="str">
-        <v>FLAT DRIPLINE 12MM ISI</v>
+        <v>FLAT DRIPLINE 16MM ISI</v>
       </c>
       <c r="E1148" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40577,7 +40577,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1148" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1148" t="str">
         <v>ROLL</v>
@@ -40589,7 +40589,7 @@
         <v>Active</v>
       </c>
       <c r="K1148" t="str">
-        <v>FLAT DRIPLINE 12MM ISI certified.</v>
+        <v>FLAT DRIPLINE 16MM ISI certified.</v>
       </c>
     </row>
     <row r="1149">
@@ -40597,10 +40597,10 @@
         <v>1148</v>
       </c>
       <c r="B1149" t="str">
-        <v>FG-401760</v>
+        <v>FG-401761</v>
       </c>
       <c r="C1149" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1149" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40612,7 +40612,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1149" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1149" t="str">
         <v>ROLL</v>
@@ -40632,10 +40632,10 @@
         <v>1149</v>
       </c>
       <c r="B1150" t="str">
-        <v>FG-401761</v>
+        <v>FG-401762</v>
       </c>
       <c r="C1150" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1150" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40647,7 +40647,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1150" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1150" t="str">
         <v>ROLL</v>
@@ -40667,10 +40667,10 @@
         <v>1150</v>
       </c>
       <c r="B1151" t="str">
-        <v>FG-401762</v>
+        <v>FG-401769</v>
       </c>
       <c r="C1151" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1151" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40682,7 +40682,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1151" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1151" t="str">
         <v>ROLL</v>
@@ -40702,10 +40702,10 @@
         <v>1151</v>
       </c>
       <c r="B1152" t="str">
-        <v>FG-401769</v>
+        <v>FG-401770</v>
       </c>
       <c r="C1152" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1152" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40717,7 +40717,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1152" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1152" t="str">
         <v>ROLL</v>
@@ -40737,10 +40737,10 @@
         <v>1152</v>
       </c>
       <c r="B1153" t="str">
-        <v>FG-401770</v>
+        <v>FG-401779</v>
       </c>
       <c r="C1153" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1153" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40752,7 +40752,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1153" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1153" t="str">
         <v>ROLL</v>
@@ -40772,13 +40772,13 @@
         <v>1153</v>
       </c>
       <c r="B1154" t="str">
-        <v>FG-401779</v>
+        <v>FG-401771</v>
       </c>
       <c r="C1154" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-30 CLASS 1)</v>
       </c>
       <c r="D1154" t="str">
-        <v>FLAT DRIPLINE 16MM ISI</v>
+        <v>FLAT DRIPLINE 20MM ISI</v>
       </c>
       <c r="E1154" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40787,7 +40787,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1154" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>20-4-30 CLASS 1</v>
       </c>
       <c r="H1154" t="str">
         <v>ROLL</v>
@@ -40799,7 +40799,7 @@
         <v>Active</v>
       </c>
       <c r="K1154" t="str">
-        <v>FLAT DRIPLINE 16MM ISI certified.</v>
+        <v>FLAT DRIPLINE 20MM ISI certified.</v>
       </c>
     </row>
     <row r="1155">
@@ -40807,10 +40807,10 @@
         <v>1154</v>
       </c>
       <c r="B1155" t="str">
-        <v>FG-401771</v>
+        <v>FG-401772</v>
       </c>
       <c r="C1155" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-40 CLASS 1)</v>
       </c>
       <c r="D1155" t="str">
         <v>FLAT DRIPLINE 20MM ISI</v>
@@ -40822,7 +40822,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1155" t="str">
-        <v>20-4-30 CLASS 1</v>
+        <v>20-4-40 CLASS 1</v>
       </c>
       <c r="H1155" t="str">
         <v>ROLL</v>
@@ -40842,10 +40842,10 @@
         <v>1155</v>
       </c>
       <c r="B1156" t="str">
-        <v>FG-401772</v>
+        <v>FG-401773</v>
       </c>
       <c r="C1156" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-50 CLASS 1)</v>
       </c>
       <c r="D1156" t="str">
         <v>FLAT DRIPLINE 20MM ISI</v>
@@ -40857,7 +40857,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1156" t="str">
-        <v>20-4-40 CLASS 1</v>
+        <v>20-4-50 CLASS 1</v>
       </c>
       <c r="H1156" t="str">
         <v>ROLL</v>
@@ -40877,25 +40877,25 @@
         <v>1156</v>
       </c>
       <c r="B1157" t="str">
-        <v>FG-401773</v>
+        <v>-</v>
       </c>
       <c r="C1157" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-50 CLASS 1)</v>
+        <v>12MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1157" t="str">
-        <v>FLAT DRIPLINE 20MM ISI</v>
+        <v>12MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1157" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1157" t="str">
-        <v>FLAT DRIP ISI</v>
+        <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1157" t="str">
-        <v>20-4-50 CLASS 1</v>
+        <v>CLASS-2</v>
       </c>
       <c r="H1157" t="str">
-        <v>ROLL</v>
+        <v>MTR</v>
       </c>
       <c r="I1157" t="str">
         <v>-</v>
@@ -40904,7 +40904,7 @@
         <v>Active</v>
       </c>
       <c r="K1157" t="str">
-        <v>FLAT DRIPLINE 20MM ISI certified.</v>
+        <v>12mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1158">
@@ -40915,10 +40915,10 @@
         <v>-</v>
       </c>
       <c r="C1158" t="str">
-        <v>12MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>16MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1158" t="str">
-        <v>12MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>16MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1158" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40939,7 +40939,7 @@
         <v>Active</v>
       </c>
       <c r="K1158" t="str">
-        <v>12mm Plain Lateral Online Drip Pipe.</v>
+        <v>16mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1159">
@@ -40950,10 +40950,10 @@
         <v>-</v>
       </c>
       <c r="C1159" t="str">
-        <v>16MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>20MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1159" t="str">
-        <v>16MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>20MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1159" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40974,7 +40974,7 @@
         <v>Active</v>
       </c>
       <c r="K1159" t="str">
-        <v>16mm Plain Lateral Online Drip Pipe.</v>
+        <v>20mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1160">
@@ -40985,10 +40985,10 @@
         <v>-</v>
       </c>
       <c r="C1160" t="str">
-        <v>20MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-1)</v>
       </c>
       <c r="D1160" t="str">
-        <v>20MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1160" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40997,7 +40997,7 @@
         <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1160" t="str">
-        <v>CLASS-2</v>
+        <v>CLASS-1</v>
       </c>
       <c r="H1160" t="str">
         <v>MTR</v>
@@ -41009,7 +41009,7 @@
         <v>Active</v>
       </c>
       <c r="K1160" t="str">
-        <v>20mm Plain Lateral Online Drip Pipe.</v>
+        <v>32mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1161">
@@ -41020,7 +41020,7 @@
         <v>-</v>
       </c>
       <c r="C1161" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-1)</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1161" t="str">
         <v>32MM PLAIN LATERAL ONLINE PIPE</v>
@@ -41032,7 +41032,7 @@
         <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1161" t="str">
-        <v>CLASS-1</v>
+        <v>CLASS-2</v>
       </c>
       <c r="H1161" t="str">
         <v>MTR</v>
@@ -41052,22 +41052,22 @@
         <v>1161</v>
       </c>
       <c r="B1162" t="str">
-        <v>-</v>
+        <v>FG-401763</v>
       </c>
       <c r="C1162" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1162" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12</v>
       </c>
       <c r="E1162" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1162" t="str">
-        <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
+        <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1162" t="str">
-        <v>CLASS-2</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1162" t="str">
         <v>MTR</v>
@@ -41079,7 +41079,7 @@
         <v>Active</v>
       </c>
       <c r="K1162" t="str">
-        <v>32mm Plain Lateral Online Drip Pipe.</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12. Available sizes: 12-4-30 CLASS 2, 12-4-40 CLASS 2, 12-4-50 CLASS 2, 12-4-30 CLASS 3, 12-4-40 CLASS 3, 12-4-50 CLASS 3.</v>
       </c>
     </row>
     <row r="1163">
@@ -41087,10 +41087,10 @@
         <v>1162</v>
       </c>
       <c r="B1163" t="str">
-        <v>FG-401763</v>
+        <v>FG-401764</v>
       </c>
       <c r="C1163" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1163" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41102,7 +41102,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1163" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1163" t="str">
         <v>MTR</v>
@@ -41122,10 +41122,10 @@
         <v>1163</v>
       </c>
       <c r="B1164" t="str">
-        <v>FG-401764</v>
+        <v>FG-401765</v>
       </c>
       <c r="C1164" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1164" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41137,7 +41137,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1164" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1164" t="str">
         <v>MTR</v>
@@ -41157,10 +41157,10 @@
         <v>1164</v>
       </c>
       <c r="B1165" t="str">
-        <v>FG-401765</v>
+        <v>FG-401766</v>
       </c>
       <c r="C1165" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1165" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41172,7 +41172,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1165" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1165" t="str">
         <v>MTR</v>
@@ -41192,10 +41192,10 @@
         <v>1165</v>
       </c>
       <c r="B1166" t="str">
-        <v>FG-401766</v>
+        <v>FG-401767</v>
       </c>
       <c r="C1166" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1166" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41207,7 +41207,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1166" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1166" t="str">
         <v>MTR</v>
@@ -41227,10 +41227,10 @@
         <v>1166</v>
       </c>
       <c r="B1167" t="str">
-        <v>FG-401767</v>
+        <v>FG-401768</v>
       </c>
       <c r="C1167" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1167" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41242,7 +41242,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1167" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1167" t="str">
         <v>MTR</v>
@@ -41262,13 +41262,13 @@
         <v>1167</v>
       </c>
       <c r="B1168" t="str">
-        <v>FG-401768</v>
+        <v>FG-401760</v>
       </c>
       <c r="C1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16</v>
       </c>
       <c r="E1168" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -41277,7 +41277,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1168" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1168" t="str">
         <v>MTR</v>
@@ -41289,7 +41289,7 @@
         <v>Active</v>
       </c>
       <c r="K1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12. Available sizes: 12-4-30 CLASS 2, 12-4-40 CLASS 2, 12-4-50 CLASS 2, 12-4-30 CLASS 3, 12-4-40 CLASS 3, 12-4-50 CLASS 3.</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16. Available sizes: 16-4-30 CLASS 1, 16-4-40 CLASS 1, 16-4-50 CLASS 1, 16-4-30 CLASS 2, 16-4-40 CLASS 2, 16-4-50 CLASS 2.</v>
       </c>
     </row>
     <row r="1169">
@@ -41297,10 +41297,10 @@
         <v>1168</v>
       </c>
       <c r="B1169" t="str">
-        <v>FG-401760</v>
+        <v>FG-401761</v>
       </c>
       <c r="C1169" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1169" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41312,7 +41312,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1169" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1169" t="str">
         <v>MTR</v>
@@ -41332,10 +41332,10 @@
         <v>1169</v>
       </c>
       <c r="B1170" t="str">
-        <v>FG-401761</v>
+        <v>FG-401762</v>
       </c>
       <c r="C1170" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1170" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41347,7 +41347,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1170" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1170" t="str">
         <v>MTR</v>
@@ -41367,10 +41367,10 @@
         <v>1170</v>
       </c>
       <c r="B1171" t="str">
-        <v>FG-401762</v>
+        <v>FG-401769</v>
       </c>
       <c r="C1171" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1171" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41382,7 +41382,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1171" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1171" t="str">
         <v>MTR</v>
@@ -41402,10 +41402,10 @@
         <v>1171</v>
       </c>
       <c r="B1172" t="str">
-        <v>FG-401769</v>
+        <v>FG-401770</v>
       </c>
       <c r="C1172" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1172" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41417,7 +41417,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1172" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1172" t="str">
         <v>MTR</v>
@@ -41437,10 +41437,10 @@
         <v>1172</v>
       </c>
       <c r="B1173" t="str">
-        <v>FG-401770</v>
+        <v>FG-401779</v>
       </c>
       <c r="C1173" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1173" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41452,7 +41452,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1173" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1173" t="str">
         <v>MTR</v>
@@ -41472,13 +41472,13 @@
         <v>1173</v>
       </c>
       <c r="B1174" t="str">
-        <v>FG-401779</v>
+        <v>FG-401771</v>
       </c>
       <c r="C1174" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-30 CLASS 1)</v>
       </c>
       <c r="D1174" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20</v>
       </c>
       <c r="E1174" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -41487,7 +41487,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1174" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>20-4-30 CLASS 1</v>
       </c>
       <c r="H1174" t="str">
         <v>MTR</v>
@@ -41499,7 +41499,7 @@
         <v>Active</v>
       </c>
       <c r="K1174" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16. Available sizes: 16-4-30 CLASS 1, 16-4-40 CLASS 1, 16-4-50 CLASS 1, 16-4-30 CLASS 2, 16-4-40 CLASS 2, 16-4-50 CLASS 2.</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20. Available sizes: 20-4-30 CLASS 1, 20-4-40 CLASS 1, 20-4-50 CLASS 1.</v>
       </c>
     </row>
     <row r="1175">
@@ -41507,10 +41507,10 @@
         <v>1174</v>
       </c>
       <c r="B1175" t="str">
-        <v>FG-401771</v>
+        <v>FG-401772</v>
       </c>
       <c r="C1175" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-40 CLASS 1)</v>
       </c>
       <c r="D1175" t="str">
         <v>FLAT DRIPLINE ISI 400MTR 20</v>
@@ -41522,7 +41522,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1175" t="str">
-        <v>20-4-30 CLASS 1</v>
+        <v>20-4-40 CLASS 1</v>
       </c>
       <c r="H1175" t="str">
         <v>MTR</v>
@@ -41542,10 +41542,10 @@
         <v>1175</v>
       </c>
       <c r="B1176" t="str">
-        <v>FG-401772</v>
+        <v>FG-401773</v>
       </c>
       <c r="C1176" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-50 CLASS 1)</v>
       </c>
       <c r="D1176" t="str">
         <v>FLAT DRIPLINE ISI 400MTR 20</v>
@@ -41557,7 +41557,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1176" t="str">
-        <v>20-4-40 CLASS 1</v>
+        <v>20-4-50 CLASS 1</v>
       </c>
       <c r="H1176" t="str">
         <v>MTR</v>
@@ -41577,22 +41577,22 @@
         <v>1176</v>
       </c>
       <c r="B1177" t="str">
-        <v>FG-401773</v>
+        <v>FG-401066</v>
       </c>
       <c r="C1177" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-50 CLASS 1)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
       </c>
       <c r="D1177" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
       </c>
       <c r="E1177" t="str">
-        <v>DRIP IRRIGATION SYSTEM</v>
+        <v>UPVC CASING PIPES</v>
       </c>
       <c r="F1177" t="str">
-        <v>FLAT DRIP (PEPSI) - INLINE</v>
+        <v>General</v>
       </c>
       <c r="G1177" t="str">
-        <v>20-4-50 CLASS 1</v>
+        <v>35MM 1 1/4 Inch</v>
       </c>
       <c r="H1177" t="str">
         <v>MTR</v>
@@ -41604,7 +41604,7 @@
         <v>Active</v>
       </c>
       <c r="K1177" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20. Available sizes: 20-4-30 CLASS 1, 20-4-40 CLASS 1, 20-4-50 CLASS 1.</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 40MM 1 1/2 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1178">
@@ -41612,10 +41612,10 @@
         <v>1177</v>
       </c>
       <c r="B1178" t="str">
-        <v>FG-401066</v>
+        <v>FG-401067</v>
       </c>
       <c r="C1178" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (40MM 1 1/2 Inch)</v>
       </c>
       <c r="D1178" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41627,7 +41627,7 @@
         <v>General</v>
       </c>
       <c r="G1178" t="str">
-        <v>35MM 1 1/4 Inch</v>
+        <v>40MM 1 1/2 Inch</v>
       </c>
       <c r="H1178" t="str">
         <v>MTR</v>
@@ -41647,10 +41647,10 @@
         <v>1178</v>
       </c>
       <c r="B1179" t="str">
-        <v>FG-401067</v>
+        <v>FG-401068</v>
       </c>
       <c r="C1179" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (40MM 1 1/2 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (50MM 2 Inch)</v>
       </c>
       <c r="D1179" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41662,7 +41662,7 @@
         <v>General</v>
       </c>
       <c r="G1179" t="str">
-        <v>40MM 1 1/2 Inch</v>
+        <v>50MM 2 Inch</v>
       </c>
       <c r="H1179" t="str">
         <v>MTR</v>
@@ -41682,10 +41682,10 @@
         <v>1179</v>
       </c>
       <c r="B1180" t="str">
-        <v>FG-401068</v>
+        <v>FG-401069</v>
       </c>
       <c r="C1180" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (50MM 2 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (100MM 4 Inch)</v>
       </c>
       <c r="D1180" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41697,7 +41697,7 @@
         <v>General</v>
       </c>
       <c r="G1180" t="str">
-        <v>50MM 2 Inch</v>
+        <v>100MM 4 Inch</v>
       </c>
       <c r="H1180" t="str">
         <v>MTR</v>
@@ -41717,10 +41717,10 @@
         <v>1180</v>
       </c>
       <c r="B1181" t="str">
-        <v>FG-401069</v>
+        <v>FG-401070</v>
       </c>
       <c r="C1181" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (100MM 4 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1181" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41732,7 +41732,7 @@
         <v>General</v>
       </c>
       <c r="G1181" t="str">
-        <v>100MM 4 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1181" t="str">
         <v>MTR</v>
@@ -41752,10 +41752,10 @@
         <v>1181</v>
       </c>
       <c r="B1182" t="str">
-        <v>FG-401070</v>
+        <v>FG-401071</v>
       </c>
       <c r="C1182" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1182" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41767,7 +41767,7 @@
         <v>General</v>
       </c>
       <c r="G1182" t="str">
-        <v>125MM 5 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1182" t="str">
         <v>MTR</v>
@@ -41787,10 +41787,10 @@
         <v>1182</v>
       </c>
       <c r="B1183" t="str">
-        <v>FG-401071</v>
+        <v>FG-401072</v>
       </c>
       <c r="C1183" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1183" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41802,7 +41802,7 @@
         <v>General</v>
       </c>
       <c r="G1183" t="str">
-        <v>150MM 6 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1183" t="str">
         <v>MTR</v>
@@ -41822,10 +41822,10 @@
         <v>1183</v>
       </c>
       <c r="B1184" t="str">
-        <v>FG-401072</v>
+        <v>FG-401073</v>
       </c>
       <c r="C1184" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1184" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41837,7 +41837,7 @@
         <v>General</v>
       </c>
       <c r="G1184" t="str">
-        <v>175MM 7 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1184" t="str">
         <v>MTR</v>
@@ -41857,13 +41857,13 @@
         <v>1184</v>
       </c>
       <c r="B1185" t="str">
-        <v>FG-401073</v>
+        <v>FG-401074</v>
       </c>
       <c r="C1185" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1185" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
       </c>
       <c r="E1185" t="str">
         <v>UPVC CASING PIPES</v>
@@ -41872,7 +41872,7 @@
         <v>General</v>
       </c>
       <c r="G1185" t="str">
-        <v>200MM 8 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1185" t="str">
         <v>MTR</v>
@@ -41884,7 +41884,7 @@
         <v>Active</v>
       </c>
       <c r="K1185" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 40MM 1 1/2 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1186">
@@ -41892,10 +41892,10 @@
         <v>1185</v>
       </c>
       <c r="B1186" t="str">
-        <v>FG-401074</v>
+        <v>FG-401075</v>
       </c>
       <c r="C1186" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1186" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41907,7 +41907,7 @@
         <v>General</v>
       </c>
       <c r="G1186" t="str">
-        <v>125MM 5 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1186" t="str">
         <v>MTR</v>
@@ -41927,10 +41927,10 @@
         <v>1186</v>
       </c>
       <c r="B1187" t="str">
-        <v>FG-401075</v>
+        <v>FG-401076</v>
       </c>
       <c r="C1187" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1187" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41942,7 +41942,7 @@
         <v>General</v>
       </c>
       <c r="G1187" t="str">
-        <v>150MM 6 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1187" t="str">
         <v>MTR</v>
@@ -41962,10 +41962,10 @@
         <v>1187</v>
       </c>
       <c r="B1188" t="str">
-        <v>FG-401076</v>
+        <v>FG-401077</v>
       </c>
       <c r="C1188" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1188" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41977,7 +41977,7 @@
         <v>General</v>
       </c>
       <c r="G1188" t="str">
-        <v>175MM 7 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1188" t="str">
         <v>MTR</v>
@@ -41997,13 +41997,13 @@
         <v>1188</v>
       </c>
       <c r="B1189" t="str">
-        <v>FG-401077</v>
+        <v>FG-401149</v>
       </c>
       <c r="C1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M (140MM 5 Inch)</v>
       </c>
       <c r="D1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M</v>
       </c>
       <c r="E1189" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42012,7 +42012,7 @@
         <v>General</v>
       </c>
       <c r="G1189" t="str">
-        <v>200MM 8 Inch</v>
+        <v>140MM 5 Inch</v>
       </c>
       <c r="H1189" t="str">
         <v>MTR</v>
@@ -42024,7 +42024,7 @@
         <v>Active</v>
       </c>
       <c r="K1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M. Available sizes: 140MM 5 Inch.</v>
       </c>
     </row>
     <row r="1190">
@@ -42032,13 +42032,13 @@
         <v>1189</v>
       </c>
       <c r="B1190" t="str">
-        <v>FG-401149</v>
+        <v>FG-401150</v>
       </c>
       <c r="C1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M (140MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M (140MM 5 Inch)</v>
       </c>
       <c r="D1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M</v>
       </c>
       <c r="E1190" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42059,7 +42059,7 @@
         <v>Active</v>
       </c>
       <c r="K1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M. Available sizes: 140MM 5 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M. Available sizes: 140MM 5 Inch.</v>
       </c>
     </row>
     <row r="1191">
@@ -42067,13 +42067,13 @@
         <v>1190</v>
       </c>
       <c r="B1191" t="str">
-        <v>FG-401150</v>
+        <v>FG-401078</v>
       </c>
       <c r="C1191" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M (140MM 5 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1191" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
       </c>
       <c r="E1191" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42082,7 +42082,7 @@
         <v>General</v>
       </c>
       <c r="G1191" t="str">
-        <v>140MM 5 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1191" t="str">
         <v>MTR</v>
@@ -42094,7 +42094,7 @@
         <v>Active</v>
       </c>
       <c r="K1191" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M. Available sizes: 140MM 5 Inch.</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1192">
@@ -42102,10 +42102,10 @@
         <v>1191</v>
       </c>
       <c r="B1192" t="str">
-        <v>FG-401078</v>
+        <v>FG-401079</v>
       </c>
       <c r="C1192" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1192" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42117,7 +42117,7 @@
         <v>General</v>
       </c>
       <c r="G1192" t="str">
-        <v>125MM 5 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1192" t="str">
         <v>MTR</v>
@@ -42137,10 +42137,10 @@
         <v>1192</v>
       </c>
       <c r="B1193" t="str">
-        <v>FG-401079</v>
+        <v>FG-401080</v>
       </c>
       <c r="C1193" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1193" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42152,7 +42152,7 @@
         <v>General</v>
       </c>
       <c r="G1193" t="str">
-        <v>150MM 6 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1193" t="str">
         <v>MTR</v>
@@ -42172,10 +42172,10 @@
         <v>1193</v>
       </c>
       <c r="B1194" t="str">
-        <v>FG-401080</v>
+        <v>FG-401081</v>
       </c>
       <c r="C1194" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1194" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42187,7 +42187,7 @@
         <v>General</v>
       </c>
       <c r="G1194" t="str">
-        <v>175MM 7 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1194" t="str">
         <v>MTR</v>
@@ -42207,13 +42207,13 @@
         <v>1194</v>
       </c>
       <c r="B1195" t="str">
-        <v>FG-401081</v>
+        <v>FG-401119</v>
       </c>
       <c r="C1195" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
       </c>
       <c r="D1195" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
       </c>
       <c r="E1195" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42222,7 +42222,7 @@
         <v>General</v>
       </c>
       <c r="G1195" t="str">
-        <v>200MM 8 Inch</v>
+        <v>35MM 1 1/4 Inch</v>
       </c>
       <c r="H1195" t="str">
         <v>MTR</v>
@@ -42234,7 +42234,7 @@
         <v>Active</v>
       </c>
       <c r="K1195" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1196">
@@ -42242,10 +42242,10 @@
         <v>1195</v>
       </c>
       <c r="B1196" t="str">
-        <v>FG-401119</v>
+        <v>FG-401121</v>
       </c>
       <c r="C1196" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (50MM 2 Inch)</v>
       </c>
       <c r="D1196" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42257,7 +42257,7 @@
         <v>General</v>
       </c>
       <c r="G1196" t="str">
-        <v>35MM 1 1/4 Inch</v>
+        <v>50MM 2 Inch</v>
       </c>
       <c r="H1196" t="str">
         <v>MTR</v>
@@ -42277,10 +42277,10 @@
         <v>1196</v>
       </c>
       <c r="B1197" t="str">
-        <v>FG-401121</v>
+        <v>FG-401122</v>
       </c>
       <c r="C1197" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (50MM 2 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (100MM 4 Inch)</v>
       </c>
       <c r="D1197" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42292,7 +42292,7 @@
         <v>General</v>
       </c>
       <c r="G1197" t="str">
-        <v>50MM 2 Inch</v>
+        <v>100MM 4 Inch</v>
       </c>
       <c r="H1197" t="str">
         <v>MTR</v>
@@ -42312,10 +42312,10 @@
         <v>1197</v>
       </c>
       <c r="B1198" t="str">
-        <v>FG-401122</v>
+        <v>FG-401123</v>
       </c>
       <c r="C1198" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (100MM 4 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1198" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42327,7 +42327,7 @@
         <v>General</v>
       </c>
       <c r="G1198" t="str">
-        <v>100MM 4 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1198" t="str">
         <v>MTR</v>
@@ -42347,10 +42347,10 @@
         <v>1198</v>
       </c>
       <c r="B1199" t="str">
-        <v>FG-401123</v>
+        <v>FG-401124</v>
       </c>
       <c r="C1199" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1199" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42362,7 +42362,7 @@
         <v>General</v>
       </c>
       <c r="G1199" t="str">
-        <v>125MM 5 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1199" t="str">
         <v>MTR</v>
@@ -42382,10 +42382,10 @@
         <v>1199</v>
       </c>
       <c r="B1200" t="str">
-        <v>FG-401124</v>
+        <v>FG-401125</v>
       </c>
       <c r="C1200" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1200" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42397,7 +42397,7 @@
         <v>General</v>
       </c>
       <c r="G1200" t="str">
-        <v>150MM 6 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1200" t="str">
         <v>MTR</v>
@@ -42417,10 +42417,10 @@
         <v>1200</v>
       </c>
       <c r="B1201" t="str">
-        <v>FG-401125</v>
+        <v>FG-401126</v>
       </c>
       <c r="C1201" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1201" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42432,7 +42432,7 @@
         <v>General</v>
       </c>
       <c r="G1201" t="str">
-        <v>175MM 7 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1201" t="str">
         <v>MTR</v>
@@ -42452,22 +42452,22 @@
         <v>1201</v>
       </c>
       <c r="B1202" t="str">
-        <v>FG-401126</v>
+        <v>FG-401166</v>
       </c>
       <c r="C1202" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (200MM 8 Inch)</v>
+        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1202" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
+        <v>COLOUMN PIPE ECO V4</v>
       </c>
       <c r="E1202" t="str">
-        <v>UPVC CASING PIPES</v>
+        <v>UPVC COLUMN PIPES</v>
       </c>
       <c r="F1202" t="str">
         <v>General</v>
       </c>
       <c r="G1202" t="str">
-        <v>200MM 8 Inch</v>
+        <v>33MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1202" t="str">
         <v>MTR</v>
@@ -42479,7 +42479,7 @@
         <v>Active</v>
       </c>
       <c r="K1202" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>COLOUMN PIPE ECO V4 for submersible pump systems.</v>
       </c>
     </row>
     <row r="1203">
@@ -42487,10 +42487,10 @@
         <v>1202</v>
       </c>
       <c r="B1203" t="str">
-        <v>FG-401166</v>
+        <v>FG-401162</v>
       </c>
       <c r="C1203" t="str">
-        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG BELL END TYPE)</v>
       </c>
       <c r="D1203" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42502,7 +42502,7 @@
         <v>General</v>
       </c>
       <c r="G1203" t="str">
-        <v>33MM 12.5KG COUPLER TYPE</v>
+        <v>33MM 12.5KG BELL END TYPE</v>
       </c>
       <c r="H1203" t="str">
         <v>MTR</v>
@@ -42522,10 +42522,10 @@
         <v>1203</v>
       </c>
       <c r="B1204" t="str">
-        <v>FG-401162</v>
+        <v>FG-401165</v>
       </c>
       <c r="C1204" t="str">
-        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG BELL END TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 10KG COUPLER TYPE)</v>
       </c>
       <c r="D1204" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42537,7 +42537,7 @@
         <v>General</v>
       </c>
       <c r="G1204" t="str">
-        <v>33MM 12.5KG BELL END TYPE</v>
+        <v>42MM 10KG COUPLER TYPE</v>
       </c>
       <c r="H1204" t="str">
         <v>MTR</v>
@@ -42557,10 +42557,10 @@
         <v>1204</v>
       </c>
       <c r="B1205" t="str">
-        <v>FG-401165</v>
+        <v>FG-401167</v>
       </c>
       <c r="C1205" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 10KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1205" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42572,7 +42572,7 @@
         <v>General</v>
       </c>
       <c r="G1205" t="str">
-        <v>42MM 10KG COUPLER TYPE</v>
+        <v>42MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1205" t="str">
         <v>MTR</v>
@@ -42592,10 +42592,10 @@
         <v>1205</v>
       </c>
       <c r="B1206" t="str">
-        <v>FG-401167</v>
+        <v>FG-401163</v>
       </c>
       <c r="C1206" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG BELL END TYPE)</v>
       </c>
       <c r="D1206" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42607,7 +42607,7 @@
         <v>General</v>
       </c>
       <c r="G1206" t="str">
-        <v>42MM 12.5KG COUPLER TYPE</v>
+        <v>42MM 12.5KG BELL END TYPE</v>
       </c>
       <c r="H1206" t="str">
         <v>MTR</v>
@@ -42627,10 +42627,10 @@
         <v>1206</v>
       </c>
       <c r="B1207" t="str">
-        <v>FG-401163</v>
+        <v>FG-401164</v>
       </c>
       <c r="C1207" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG BELL END TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (48MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1207" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42642,7 +42642,7 @@
         <v>General</v>
       </c>
       <c r="G1207" t="str">
-        <v>42MM 12.5KG BELL END TYPE</v>
+        <v>48MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1207" t="str">
         <v>MTR</v>
@@ -42662,10 +42662,10 @@
         <v>1207</v>
       </c>
       <c r="B1208" t="str">
-        <v>FG-401164</v>
+        <v>FG-401168</v>
       </c>
       <c r="C1208" t="str">
-        <v>COLOUMN PIPE ECO V4 (48MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (60MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1208" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42677,7 +42677,7 @@
         <v>General</v>
       </c>
       <c r="G1208" t="str">
-        <v>48MM 12.5KG COUPLER TYPE</v>
+        <v>60MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1208" t="str">
         <v>MTR</v>
@@ -42697,13 +42697,13 @@
         <v>1208</v>
       </c>
       <c r="B1209" t="str">
-        <v>FG-401168</v>
+        <v>FG-401175</v>
       </c>
       <c r="C1209" t="str">
-        <v>COLOUMN PIPE ECO V4 (60MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (33MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1209" t="str">
-        <v>COLOUMN PIPE ECO V4</v>
+        <v>COLOUMN PIPE MEDIUM</v>
       </c>
       <c r="E1209" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -42712,7 +42712,7 @@
         <v>General</v>
       </c>
       <c r="G1209" t="str">
-        <v>60MM 12.5KG COUPLER TYPE</v>
+        <v>33MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1209" t="str">
         <v>MTR</v>
@@ -42724,7 +42724,7 @@
         <v>Active</v>
       </c>
       <c r="K1209" t="str">
-        <v>COLOUMN PIPE ECO V4 for submersible pump systems.</v>
+        <v>COLOUMN PIPE MEDIUM for submersible pump systems.</v>
       </c>
     </row>
     <row r="1210">
@@ -42732,10 +42732,10 @@
         <v>1209</v>
       </c>
       <c r="B1210" t="str">
-        <v>FG-401175</v>
+        <v>FG-401177</v>
       </c>
       <c r="C1210" t="str">
-        <v>COLOUMN PIPE MEDIUM (33MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (42MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1210" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42747,7 +42747,7 @@
         <v>General</v>
       </c>
       <c r="G1210" t="str">
-        <v>33MM 18KG COUPLER TYPE</v>
+        <v>42MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1210" t="str">
         <v>MTR</v>
@@ -42767,10 +42767,10 @@
         <v>1210</v>
       </c>
       <c r="B1211" t="str">
-        <v>FG-401177</v>
+        <v>FG-401176</v>
       </c>
       <c r="C1211" t="str">
-        <v>COLOUMN PIPE MEDIUM (42MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (48MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1211" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42782,7 +42782,7 @@
         <v>General</v>
       </c>
       <c r="G1211" t="str">
-        <v>42MM 18KG COUPLER TYPE</v>
+        <v>48MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1211" t="str">
         <v>MTR</v>
@@ -42802,10 +42802,10 @@
         <v>1211</v>
       </c>
       <c r="B1212" t="str">
-        <v>FG-401176</v>
+        <v>FG-401178</v>
       </c>
       <c r="C1212" t="str">
-        <v>COLOUMN PIPE MEDIUM (48MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (60MM 15KG COUPLER TYPE)</v>
       </c>
       <c r="D1212" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42817,7 +42817,7 @@
         <v>General</v>
       </c>
       <c r="G1212" t="str">
-        <v>48MM 18KG COUPLER TYPE</v>
+        <v>60MM 15KG COUPLER TYPE</v>
       </c>
       <c r="H1212" t="str">
         <v>MTR</v>
@@ -42837,10 +42837,10 @@
         <v>1212</v>
       </c>
       <c r="B1213" t="str">
-        <v>FG-401178</v>
+        <v>FG-401180</v>
       </c>
       <c r="C1213" t="str">
-        <v>COLOUMN PIPE MEDIUM (60MM 15KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (75MM 10KG COUPLER TYPE)</v>
       </c>
       <c r="D1213" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42852,7 +42852,7 @@
         <v>General</v>
       </c>
       <c r="G1213" t="str">
-        <v>60MM 15KG COUPLER TYPE</v>
+        <v>75MM 10KG COUPLER TYPE</v>
       </c>
       <c r="H1213" t="str">
         <v>MTR</v>
@@ -42872,13 +42872,13 @@
         <v>1213</v>
       </c>
       <c r="B1214" t="str">
-        <v>FG-401180</v>
+        <v>FG-401169</v>
       </c>
       <c r="C1214" t="str">
-        <v>COLOUMN PIPE MEDIUM (75MM 10KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (33MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1214" t="str">
-        <v>COLOUMN PIPE MEDIUM</v>
+        <v>COLOUMN PIPE STANDARD</v>
       </c>
       <c r="E1214" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -42887,7 +42887,7 @@
         <v>General</v>
       </c>
       <c r="G1214" t="str">
-        <v>75MM 10KG COUPLER TYPE</v>
+        <v>33MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1214" t="str">
         <v>MTR</v>
@@ -42899,7 +42899,7 @@
         <v>Active</v>
       </c>
       <c r="K1214" t="str">
-        <v>COLOUMN PIPE MEDIUM for submersible pump systems.</v>
+        <v>COLOUMN PIPE STANDARD for submersible pump systems.</v>
       </c>
     </row>
     <row r="1215">
@@ -42907,10 +42907,10 @@
         <v>1214</v>
       </c>
       <c r="B1215" t="str">
-        <v>FG-401169</v>
+        <v>FG-401171</v>
       </c>
       <c r="C1215" t="str">
-        <v>COLOUMN PIPE STANDARD (33MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (42MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1215" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42922,7 +42922,7 @@
         <v>General</v>
       </c>
       <c r="G1215" t="str">
-        <v>33MM 25KG COUPLER TYPE</v>
+        <v>42MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1215" t="str">
         <v>MTR</v>
@@ -42942,10 +42942,10 @@
         <v>1215</v>
       </c>
       <c r="B1216" t="str">
-        <v>FG-401171</v>
+        <v>FG-401170</v>
       </c>
       <c r="C1216" t="str">
-        <v>COLOUMN PIPE STANDARD (42MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (48MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1216" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42957,7 +42957,7 @@
         <v>General</v>
       </c>
       <c r="G1216" t="str">
-        <v>42MM 25KG COUPLER TYPE</v>
+        <v>48MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1216" t="str">
         <v>MTR</v>
@@ -42977,10 +42977,10 @@
         <v>1216</v>
       </c>
       <c r="B1217" t="str">
-        <v>FG-401170</v>
+        <v>FG-401172</v>
       </c>
       <c r="C1217" t="str">
-        <v>COLOUMN PIPE STANDARD (48MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (60MM 20KG COUPLER TYPE)</v>
       </c>
       <c r="D1217" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42992,7 +42992,7 @@
         <v>General</v>
       </c>
       <c r="G1217" t="str">
-        <v>48MM 25KG COUPLER TYPE</v>
+        <v>60MM 20KG COUPLER TYPE</v>
       </c>
       <c r="H1217" t="str">
         <v>MTR</v>
@@ -43012,10 +43012,10 @@
         <v>1217</v>
       </c>
       <c r="B1218" t="str">
-        <v>FG-401172</v>
+        <v>FG-401174</v>
       </c>
       <c r="C1218" t="str">
-        <v>COLOUMN PIPE STANDARD (60MM 20KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (75MM 20KG COUPLER TYPE)</v>
       </c>
       <c r="D1218" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -43027,7 +43027,7 @@
         <v>General</v>
       </c>
       <c r="G1218" t="str">
-        <v>60MM 20KG COUPLER TYPE</v>
+        <v>75MM 20KG COUPLER TYPE</v>
       </c>
       <c r="H1218" t="str">
         <v>MTR</v>
@@ -43047,13 +43047,13 @@
         <v>1218</v>
       </c>
       <c r="B1219" t="str">
-        <v>FG-401174</v>
+        <v>-</v>
       </c>
       <c r="C1219" t="str">
-        <v>COLOUMN PIPE STANDARD (75MM 20KG COUPLER TYPE)</v>
+        <v>3M STANDARD PLUS PIPE (60MM 25 COUPLER TYPE)</v>
       </c>
       <c r="D1219" t="str">
-        <v>COLOUMN PIPE STANDARD</v>
+        <v>3M STANDARD PLUS PIPE</v>
       </c>
       <c r="E1219" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43062,7 +43062,7 @@
         <v>General</v>
       </c>
       <c r="G1219" t="str">
-        <v>75MM 20KG COUPLER TYPE</v>
+        <v>60MM 25 COUPLER TYPE</v>
       </c>
       <c r="H1219" t="str">
         <v>MTR</v>
@@ -43074,7 +43074,7 @@
         <v>Active</v>
       </c>
       <c r="K1219" t="str">
-        <v>COLOUMN PIPE STANDARD for submersible pump systems.</v>
+        <v>3M Standard Plus UPVC Column Pipe for submersible pump systems.</v>
       </c>
     </row>
     <row r="1220">
@@ -43082,13 +43082,13 @@
         <v>1219</v>
       </c>
       <c r="B1220" t="str">
-        <v>-</v>
+        <v>FG-401182</v>
       </c>
       <c r="C1220" t="str">
-        <v>3M STANDARD PLUS PIPE (60MM 25 COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (42MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1220" t="str">
-        <v>3M STANDARD PLUS PIPE</v>
+        <v>COLOUMN PIPE HEAVY</v>
       </c>
       <c r="E1220" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43097,7 +43097,7 @@
         <v>General</v>
       </c>
       <c r="G1220" t="str">
-        <v>60MM 25 COUPLER TYPE</v>
+        <v>42MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1220" t="str">
         <v>MTR</v>
@@ -43109,7 +43109,7 @@
         <v>Active</v>
       </c>
       <c r="K1220" t="str">
-        <v>3M Standard Plus UPVC Column Pipe for submersible pump systems.</v>
+        <v>COLOUMN PIPE HEAVY for submersible pump systems.</v>
       </c>
     </row>
     <row r="1221">
@@ -43117,10 +43117,10 @@
         <v>1220</v>
       </c>
       <c r="B1221" t="str">
-        <v>FG-401182</v>
+        <v>FG-401181</v>
       </c>
       <c r="C1221" t="str">
-        <v>COLOUMN PIPE HEAVY (42MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (48MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1221" t="str">
         <v>COLOUMN PIPE HEAVY</v>
@@ -43132,7 +43132,7 @@
         <v>General</v>
       </c>
       <c r="G1221" t="str">
-        <v>42MM 30KG COUPLER TYPE</v>
+        <v>48MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1221" t="str">
         <v>MTR</v>
@@ -43152,10 +43152,10 @@
         <v>1221</v>
       </c>
       <c r="B1222" t="str">
-        <v>FG-401181</v>
+        <v>FG-401183</v>
       </c>
       <c r="C1222" t="str">
-        <v>COLOUMN PIPE HEAVY (48MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (60MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1222" t="str">
         <v>COLOUMN PIPE HEAVY</v>
@@ -43167,7 +43167,7 @@
         <v>General</v>
       </c>
       <c r="G1222" t="str">
-        <v>48MM 30KG COUPLER TYPE</v>
+        <v>60MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1222" t="str">
         <v>MTR</v>
@@ -43187,13 +43187,13 @@
         <v>1222</v>
       </c>
       <c r="B1223" t="str">
-        <v>FG-401183</v>
+        <v>FG-401179</v>
       </c>
       <c r="C1223" t="str">
-        <v>COLOUMN PIPE HEAVY (60MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM PLUS (60MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1223" t="str">
-        <v>COLOUMN PIPE HEAVY</v>
+        <v>COLOUMN PIPE MEDIUM PLUS</v>
       </c>
       <c r="E1223" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43202,7 +43202,7 @@
         <v>General</v>
       </c>
       <c r="G1223" t="str">
-        <v>60MM 30KG COUPLER TYPE</v>
+        <v>60MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1223" t="str">
         <v>MTR</v>
@@ -43214,7 +43214,7 @@
         <v>Active</v>
       </c>
       <c r="K1223" t="str">
-        <v>COLOUMN PIPE HEAVY for submersible pump systems.</v>
+        <v>COLOUMN PIPE MEDIUM PLUS for submersible pump systems.</v>
       </c>
     </row>
     <row r="1224">
@@ -43222,34 +43222,34 @@
         <v>1223</v>
       </c>
       <c r="B1224" t="str">
-        <v>FG-401179</v>
+        <v>FG-401569</v>
       </c>
       <c r="C1224" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS (60MM 18KG COUPLER TYPE)</v>
+        <v>CONSTRUCTION GHAMELA SHIVA (15 Inch)</v>
       </c>
       <c r="D1224" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS</v>
+        <v>CONSTRUCTION GHAMELA SHIVA</v>
       </c>
       <c r="E1224" t="str">
-        <v>UPVC COLUMN PIPES</v>
+        <v>HOUSEHOLD PRODUCTS</v>
       </c>
       <c r="F1224" t="str">
         <v>General</v>
       </c>
       <c r="G1224" t="str">
-        <v>60MM 18KG COUPLER TYPE</v>
+        <v>15 Inch</v>
       </c>
       <c r="H1224" t="str">
-        <v>MTR</v>
+        <v>BAGS</v>
       </c>
       <c r="I1224" t="str">
-        <v>-</v>
+        <v>75</v>
       </c>
       <c r="J1224" t="str">
         <v>Active</v>
       </c>
       <c r="K1224" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS for submersible pump systems.</v>
+        <v>CONSTRUCTION GHAMELA SHIVA high durability ghamela.</v>
       </c>
     </row>
     <row r="1225">
@@ -43257,13 +43257,13 @@
         <v>1224</v>
       </c>
       <c r="B1225" t="str">
-        <v>FG-401569</v>
+        <v>FG-401570</v>
       </c>
       <c r="C1225" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA (15 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA GOURI (15 Inch)</v>
       </c>
       <c r="D1225" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA</v>
+        <v>MULTIPURPOSE GHAMELA GOURI</v>
       </c>
       <c r="E1225" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43284,7 +43284,7 @@
         <v>Active</v>
       </c>
       <c r="K1225" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA GOURI high durability ghamela.</v>
       </c>
     </row>
     <row r="1226">
@@ -43292,13 +43292,13 @@
         <v>1225</v>
       </c>
       <c r="B1226" t="str">
-        <v>FG-401570</v>
+        <v>FG-401571</v>
       </c>
       <c r="C1226" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI (15 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA (16 Inch)</v>
       </c>
       <c r="D1226" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA</v>
       </c>
       <c r="E1226" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43307,19 +43307,19 @@
         <v>General</v>
       </c>
       <c r="G1226" t="str">
-        <v>15 Inch</v>
+        <v>16 Inch</v>
       </c>
       <c r="H1226" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1226" t="str">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="J1226" t="str">
         <v>Active</v>
       </c>
       <c r="K1226" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA high durability ghamela.</v>
       </c>
     </row>
     <row r="1227">
@@ -43327,13 +43327,13 @@
         <v>1226</v>
       </c>
       <c r="B1227" t="str">
-        <v>FG-401571</v>
+        <v>FG-401573</v>
       </c>
       <c r="C1227" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA (16 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV (18 Inch)</v>
       </c>
       <c r="D1227" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV</v>
       </c>
       <c r="E1227" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43342,19 +43342,19 @@
         <v>General</v>
       </c>
       <c r="G1227" t="str">
-        <v>16 Inch</v>
+        <v>18 Inch</v>
       </c>
       <c r="H1227" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1227" t="str">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J1227" t="str">
         <v>Active</v>
       </c>
       <c r="K1227" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV high durability ghamela.</v>
       </c>
     </row>
     <row r="1228">
@@ -43362,13 +43362,13 @@
         <v>1227</v>
       </c>
       <c r="B1228" t="str">
-        <v>FG-401573</v>
+        <v>FG-401574</v>
       </c>
       <c r="C1228" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV (18 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET (20 Inch)</v>
       </c>
       <c r="D1228" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET</v>
       </c>
       <c r="E1228" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43377,19 +43377,19 @@
         <v>General</v>
       </c>
       <c r="G1228" t="str">
-        <v>18 Inch</v>
+        <v>20 Inch</v>
       </c>
       <c r="H1228" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1228" t="str">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J1228" t="str">
         <v>Active</v>
       </c>
       <c r="K1228" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET high durability ghamela.</v>
       </c>
     </row>
     <row r="1229">
@@ -43397,13 +43397,13 @@
         <v>1228</v>
       </c>
       <c r="B1229" t="str">
-        <v>FG-401574</v>
+        <v>FG-401572</v>
       </c>
       <c r="C1229" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET (20 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI (17 Inch)</v>
       </c>
       <c r="D1229" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI</v>
       </c>
       <c r="E1229" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43412,19 +43412,19 @@
         <v>General</v>
       </c>
       <c r="G1229" t="str">
-        <v>20 Inch</v>
+        <v>17 Inch</v>
       </c>
       <c r="H1229" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1229" t="str">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J1229" t="str">
         <v>Active</v>
       </c>
       <c r="K1229" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI high durability ghamela.</v>
       </c>
     </row>
     <row r="1230">
@@ -43432,13 +43432,13 @@
         <v>1229</v>
       </c>
       <c r="B1230" t="str">
-        <v>FG-401572</v>
+        <v>FG-401575</v>
       </c>
       <c r="C1230" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI (17 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ (22 Inch)</v>
       </c>
       <c r="D1230" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ</v>
       </c>
       <c r="E1230" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43447,19 +43447,19 @@
         <v>General</v>
       </c>
       <c r="G1230" t="str">
-        <v>17 Inch</v>
+        <v>22 Inch</v>
       </c>
       <c r="H1230" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1230" t="str">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J1230" t="str">
         <v>Active</v>
       </c>
       <c r="K1230" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ high durability ghamela.</v>
       </c>
     </row>
     <row r="1231">
@@ -43467,13 +43467,13 @@
         <v>1230</v>
       </c>
       <c r="B1231" t="str">
-        <v>FG-401575</v>
+        <v>FG-401578</v>
       </c>
       <c r="C1231" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ (22 Inch)</v>
+        <v>AQUA PLAST GHAMELA 16 (16 Inch)</v>
       </c>
       <c r="D1231" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ</v>
+        <v>AQUA PLAST GHAMELA 16</v>
       </c>
       <c r="E1231" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43482,19 +43482,19 @@
         <v>General</v>
       </c>
       <c r="G1231" t="str">
-        <v>22 Inch</v>
+        <v>16 Inch</v>
       </c>
       <c r="H1231" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1231" t="str">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J1231" t="str">
         <v>Active</v>
       </c>
       <c r="K1231" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ high durability ghamela.</v>
+        <v>AQUA PLAST GHAMELA 16 high durability ghamela.</v>
       </c>
     </row>
     <row r="1232">
@@ -43502,13 +43502,13 @@
         <v>1231</v>
       </c>
       <c r="B1232" t="str">
-        <v>FG-401578</v>
+        <v>FG-401579</v>
       </c>
       <c r="C1232" t="str">
-        <v>AQUA PLAST GHAMELA 16 (16 Inch)</v>
+        <v>AQUA PLAST GHAMELA 17 (17 Inch)</v>
       </c>
       <c r="D1232" t="str">
-        <v>AQUA PLAST GHAMELA 16</v>
+        <v>AQUA PLAST GHAMELA 17</v>
       </c>
       <c r="E1232" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43517,7 +43517,7 @@
         <v>General</v>
       </c>
       <c r="G1232" t="str">
-        <v>16 Inch</v>
+        <v>17 Inch</v>
       </c>
       <c r="H1232" t="str">
         <v>BAGS</v>
@@ -43529,7 +43529,7 @@
         <v>Active</v>
       </c>
       <c r="K1232" t="str">
-        <v>AQUA PLAST GHAMELA 16 high durability ghamela.</v>
+        <v>AQUA PLAST GHAMELA 17 high durability ghamela.</v>
       </c>
     </row>
     <row r="1233">
@@ -43537,34 +43537,34 @@
         <v>1232</v>
       </c>
       <c r="B1233" t="str">
-        <v>FG-401579</v>
+        <v>FG-401364</v>
       </c>
       <c r="C1233" t="str">
-        <v>AQUA PLAST GHAMELA 17 (17 Inch)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1/2 15MM)</v>
       </c>
       <c r="D1233" t="str">
-        <v>AQUA PLAST GHAMELA 17</v>
+        <v>GAP-ORA FLOW GARDEN PIPE</v>
       </c>
       <c r="E1233" t="str">
-        <v>HOUSEHOLD PRODUCTS</v>
+        <v>Garden, Braided &amp; LDPE Pipes</v>
       </c>
       <c r="F1233" t="str">
         <v>General</v>
       </c>
       <c r="G1233" t="str">
-        <v>17 Inch</v>
+        <v>1/2 15MM</v>
       </c>
       <c r="H1233" t="str">
-        <v>BAGS</v>
+        <v>BDL</v>
       </c>
       <c r="I1233" t="str">
-        <v>60</v>
+        <v>-</v>
       </c>
       <c r="J1233" t="str">
         <v>Active</v>
       </c>
       <c r="K1233" t="str">
-        <v>AQUA PLAST GHAMELA 17 high durability ghamela.</v>
+        <v>GAP-ORA FLOW GARDEN PIPE. Available sizes: 1/2 15MM, 3/4 20MM, 1 25MM, 1 1/4 32MM.</v>
       </c>
     </row>
     <row r="1234">
@@ -43572,10 +43572,10 @@
         <v>1233</v>
       </c>
       <c r="B1234" t="str">
-        <v>FG-401364</v>
+        <v>FG-401365</v>
       </c>
       <c r="C1234" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1/2 15MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (3/4 20MM)</v>
       </c>
       <c r="D1234" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43587,7 +43587,7 @@
         <v>General</v>
       </c>
       <c r="G1234" t="str">
-        <v>1/2 15MM</v>
+        <v>3/4 20MM</v>
       </c>
       <c r="H1234" t="str">
         <v>BDL</v>
@@ -43607,10 +43607,10 @@
         <v>1234</v>
       </c>
       <c r="B1235" t="str">
-        <v>FG-401365</v>
+        <v>FG-401366</v>
       </c>
       <c r="C1235" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (3/4 20MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1 25MM)</v>
       </c>
       <c r="D1235" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43622,7 +43622,7 @@
         <v>General</v>
       </c>
       <c r="G1235" t="str">
-        <v>3/4 20MM</v>
+        <v>1 25MM</v>
       </c>
       <c r="H1235" t="str">
         <v>BDL</v>
@@ -43642,10 +43642,10 @@
         <v>1235</v>
       </c>
       <c r="B1236" t="str">
-        <v>FG-401366</v>
+        <v>FG-401367</v>
       </c>
       <c r="C1236" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1 25MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1 1/4 32MM)</v>
       </c>
       <c r="D1236" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43657,7 +43657,7 @@
         <v>General</v>
       </c>
       <c r="G1236" t="str">
-        <v>1 25MM</v>
+        <v>1 1/4 32MM</v>
       </c>
       <c r="H1236" t="str">
         <v>BDL</v>
@@ -43677,13 +43677,13 @@
         <v>1236</v>
       </c>
       <c r="B1237" t="str">
-        <v>FG-401367</v>
+        <v>FG-401370</v>
       </c>
       <c r="C1237" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1 1/4 32MM)</v>
+        <v>GAP-ORA BRAIDED PIPE (15MM 1/2)</v>
       </c>
       <c r="D1237" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE</v>
+        <v>GAP-ORA BRAIDED PIPE</v>
       </c>
       <c r="E1237" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43692,7 +43692,7 @@
         <v>General</v>
       </c>
       <c r="G1237" t="str">
-        <v>1 1/4 32MM</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1237" t="str">
         <v>BDL</v>
@@ -43704,7 +43704,7 @@
         <v>Active</v>
       </c>
       <c r="K1237" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE. Available sizes: 1/2 15MM, 3/4 20MM, 1 25MM, 1 1/4 32MM.</v>
+        <v>GAP-ORA BRAIDED PIPE.</v>
       </c>
     </row>
     <row r="1238">
@@ -43712,10 +43712,10 @@
         <v>1237</v>
       </c>
       <c r="B1238" t="str">
-        <v>FG-401370</v>
+        <v>FG-401371</v>
       </c>
       <c r="C1238" t="str">
-        <v>GAP-ORA BRAIDED PIPE (15MM 1/2)</v>
+        <v>GAP-ORA BRAIDED PIPE (20MM 3/4)</v>
       </c>
       <c r="D1238" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43727,7 +43727,7 @@
         <v>General</v>
       </c>
       <c r="G1238" t="str">
-        <v>15MM 1/2</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1238" t="str">
         <v>BDL</v>
@@ -43747,10 +43747,10 @@
         <v>1238</v>
       </c>
       <c r="B1239" t="str">
-        <v>FG-401371</v>
+        <v>FG-401372</v>
       </c>
       <c r="C1239" t="str">
-        <v>GAP-ORA BRAIDED PIPE (20MM 3/4)</v>
+        <v>GAP-ORA BRAIDED PIPE (25MM 1)</v>
       </c>
       <c r="D1239" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43762,7 +43762,7 @@
         <v>General</v>
       </c>
       <c r="G1239" t="str">
-        <v>20MM 3/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1239" t="str">
         <v>BDL</v>
@@ -43782,10 +43782,10 @@
         <v>1239</v>
       </c>
       <c r="B1240" t="str">
-        <v>FG-401372</v>
+        <v>FG-401373</v>
       </c>
       <c r="C1240" t="str">
-        <v>GAP-ORA BRAIDED PIPE (25MM 1)</v>
+        <v>GAP-ORA BRAIDED PIPE (32MM 1 1/4)</v>
       </c>
       <c r="D1240" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43797,7 +43797,7 @@
         <v>General</v>
       </c>
       <c r="G1240" t="str">
-        <v>25MM 1</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1240" t="str">
         <v>BDL</v>
@@ -43817,13 +43817,13 @@
         <v>1240</v>
       </c>
       <c r="B1241" t="str">
-        <v>FG-401373</v>
+        <v>FG-401355</v>
       </c>
       <c r="C1241" t="str">
-        <v>GAP-ORA BRAIDED PIPE (32MM 1 1/4)</v>
+        <v>GARDEN FOAM PIPES (15MM 1/2)</v>
       </c>
       <c r="D1241" t="str">
-        <v>GAP-ORA BRAIDED PIPE</v>
+        <v>GARDEN FOAM PIPES</v>
       </c>
       <c r="E1241" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43832,7 +43832,7 @@
         <v>General</v>
       </c>
       <c r="G1241" t="str">
-        <v>32MM 1 1/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1241" t="str">
         <v>BDL</v>
@@ -43844,7 +43844,7 @@
         <v>Active</v>
       </c>
       <c r="K1241" t="str">
-        <v>GAP-ORA BRAIDED PIPE.</v>
+        <v>GARDEN FOAM PIPES.</v>
       </c>
     </row>
     <row r="1242">
@@ -43852,10 +43852,10 @@
         <v>1241</v>
       </c>
       <c r="B1242" t="str">
-        <v>FG-401355</v>
+        <v>FG-401356</v>
       </c>
       <c r="C1242" t="str">
-        <v>GARDEN FOAM PIPES (15MM 1/2)</v>
+        <v>GARDEN FOAM PIPES (20MM 3/4)</v>
       </c>
       <c r="D1242" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43867,7 +43867,7 @@
         <v>General</v>
       </c>
       <c r="G1242" t="str">
-        <v>15MM 1/2</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1242" t="str">
         <v>BDL</v>
@@ -43887,10 +43887,10 @@
         <v>1242</v>
       </c>
       <c r="B1243" t="str">
-        <v>FG-401356</v>
+        <v>FG-401369</v>
       </c>
       <c r="C1243" t="str">
-        <v>GARDEN FOAM PIPES (20MM 3/4)</v>
+        <v>GARDEN FOAM PIPES (20MM 3/4 20MTR)</v>
       </c>
       <c r="D1243" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43902,7 +43902,7 @@
         <v>General</v>
       </c>
       <c r="G1243" t="str">
-        <v>20MM 3/4</v>
+        <v>20MM 3/4 20MTR</v>
       </c>
       <c r="H1243" t="str">
         <v>BDL</v>
@@ -43922,10 +43922,10 @@
         <v>1243</v>
       </c>
       <c r="B1244" t="str">
-        <v>FG-401369</v>
+        <v>FG-401357</v>
       </c>
       <c r="C1244" t="str">
-        <v>GARDEN FOAM PIPES (20MM 3/4 20MTR)</v>
+        <v>GARDEN FOAM PIPES (25MM 1)</v>
       </c>
       <c r="D1244" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43937,7 +43937,7 @@
         <v>General</v>
       </c>
       <c r="G1244" t="str">
-        <v>20MM 3/4 20MTR</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1244" t="str">
         <v>BDL</v>
@@ -43957,10 +43957,10 @@
         <v>1244</v>
       </c>
       <c r="B1245" t="str">
-        <v>FG-401357</v>
+        <v>FG-401358</v>
       </c>
       <c r="C1245" t="str">
-        <v>GARDEN FOAM PIPES (25MM 1)</v>
+        <v>GARDEN FOAM PIPES (32MM 1 1/4)</v>
       </c>
       <c r="D1245" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43972,7 +43972,7 @@
         <v>General</v>
       </c>
       <c r="G1245" t="str">
-        <v>25MM 1</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1245" t="str">
         <v>BDL</v>
@@ -43992,13 +43992,13 @@
         <v>1245</v>
       </c>
       <c r="B1246" t="str">
-        <v>FG-401358</v>
+        <v>FG-401344</v>
       </c>
       <c r="C1246" t="str">
-        <v>GARDEN FOAM PIPES (32MM 1 1/4)</v>
+        <v>BRAIDED PIPE (15MM 1/2)</v>
       </c>
       <c r="D1246" t="str">
-        <v>GARDEN FOAM PIPES</v>
+        <v>BRAIDED PIPE</v>
       </c>
       <c r="E1246" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44007,7 +44007,7 @@
         <v>General</v>
       </c>
       <c r="G1246" t="str">
-        <v>32MM 1 1/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1246" t="str">
         <v>BDL</v>
@@ -44019,7 +44019,7 @@
         <v>Active</v>
       </c>
       <c r="K1246" t="str">
-        <v>GARDEN FOAM PIPES.</v>
+        <v>Reinforced Braided Garden Pipe.</v>
       </c>
     </row>
     <row r="1247">
@@ -44027,10 +44027,10 @@
         <v>1246</v>
       </c>
       <c r="B1247" t="str">
-        <v>FG-401344</v>
+        <v>FG-401345</v>
       </c>
       <c r="C1247" t="str">
-        <v>BRAIDED PIPE (15MM 1/2)</v>
+        <v>BRAIDED PIPE (20MM 3/4)</v>
       </c>
       <c r="D1247" t="str">
         <v>BRAIDED PIPE</v>
@@ -44042,7 +44042,7 @@
         <v>General</v>
       </c>
       <c r="G1247" t="str">
-        <v>15MM 1/2</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1247" t="str">
         <v>BDL</v>
@@ -44062,10 +44062,10 @@
         <v>1247</v>
       </c>
       <c r="B1248" t="str">
-        <v>FG-401345</v>
+        <v>FG-401346</v>
       </c>
       <c r="C1248" t="str">
-        <v>BRAIDED PIPE (20MM 3/4)</v>
+        <v>BRAIDED PIPE (25MM 1)</v>
       </c>
       <c r="D1248" t="str">
         <v>BRAIDED PIPE</v>
@@ -44077,7 +44077,7 @@
         <v>General</v>
       </c>
       <c r="G1248" t="str">
-        <v>20MM 3/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1248" t="str">
         <v>BDL</v>
@@ -44097,10 +44097,10 @@
         <v>1248</v>
       </c>
       <c r="B1249" t="str">
-        <v>FG-401346</v>
+        <v>FG-401363</v>
       </c>
       <c r="C1249" t="str">
-        <v>BRAIDED PIPE (25MM 1)</v>
+        <v>BRAIDED PIPE (32MM 1 1/4)</v>
       </c>
       <c r="D1249" t="str">
         <v>BRAIDED PIPE</v>
@@ -44112,7 +44112,7 @@
         <v>General</v>
       </c>
       <c r="G1249" t="str">
-        <v>25MM 1</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1249" t="str">
         <v>BDL</v>
@@ -44132,13 +44132,13 @@
         <v>1249</v>
       </c>
       <c r="B1250" t="str">
-        <v>FG-401363</v>
+        <v>FG-401374</v>
       </c>
       <c r="C1250" t="str">
-        <v>BRAIDED PIPE (32MM 1 1/4)</v>
+        <v>LEVEL PIPE (6MM)</v>
       </c>
       <c r="D1250" t="str">
-        <v>BRAIDED PIPE</v>
+        <v>LEVEL PIPE</v>
       </c>
       <c r="E1250" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44147,7 +44147,7 @@
         <v>General</v>
       </c>
       <c r="G1250" t="str">
-        <v>32MM 1 1/4</v>
+        <v>6MM</v>
       </c>
       <c r="H1250" t="str">
         <v>BDL</v>
@@ -44159,7 +44159,7 @@
         <v>Active</v>
       </c>
       <c r="K1250" t="str">
-        <v>Reinforced Braided Garden Pipe.</v>
+        <v>Transparent Level Pipe for construction &amp; garden work.</v>
       </c>
     </row>
     <row r="1251">
@@ -44167,13 +44167,13 @@
         <v>1250</v>
       </c>
       <c r="B1251" t="str">
-        <v>FG-401374</v>
+        <v>FG-401340</v>
       </c>
       <c r="C1251" t="str">
-        <v>LEVEL PIPE (6MM)</v>
+        <v>GARDEN PIPES SUPER FLOW (15MM 1/2)</v>
       </c>
       <c r="D1251" t="str">
-        <v>LEVEL PIPE</v>
+        <v>GARDEN PIPES SUPER FLOW</v>
       </c>
       <c r="E1251" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44182,7 +44182,7 @@
         <v>General</v>
       </c>
       <c r="G1251" t="str">
-        <v>6MM</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1251" t="str">
         <v>BDL</v>
@@ -44194,7 +44194,7 @@
         <v>Active</v>
       </c>
       <c r="K1251" t="str">
-        <v>Transparent Level Pipe for construction &amp; garden work.</v>
+        <v>GARDEN PIPES SUPER FLOW.</v>
       </c>
     </row>
     <row r="1252">
@@ -44202,10 +44202,10 @@
         <v>1251</v>
       </c>
       <c r="B1252" t="str">
-        <v>FG-401340</v>
+        <v>FG-401341</v>
       </c>
       <c r="C1252" t="str">
-        <v>GARDEN PIPES SUPER FLOW (15MM 1/2)</v>
+        <v>GARDEN PIPES SUPER FLOW (20MM 3/4)</v>
       </c>
       <c r="D1252" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44217,7 +44217,7 @@
         <v>General</v>
       </c>
       <c r="G1252" t="str">
-        <v>15MM 1/2</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1252" t="str">
         <v>BDL</v>
@@ -44237,10 +44237,10 @@
         <v>1252</v>
       </c>
       <c r="B1253" t="str">
-        <v>FG-401341</v>
+        <v>FG-401652</v>
       </c>
       <c r="C1253" t="str">
-        <v>GARDEN PIPES SUPER FLOW (20MM 3/4)</v>
+        <v>GARDEN PIPES SUPER FLOW (20MM 3/4 15MTR)</v>
       </c>
       <c r="D1253" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44252,7 +44252,7 @@
         <v>General</v>
       </c>
       <c r="G1253" t="str">
-        <v>20MM 3/4</v>
+        <v>20MM 3/4 15MTR</v>
       </c>
       <c r="H1253" t="str">
         <v>BDL</v>
@@ -44272,10 +44272,10 @@
         <v>1253</v>
       </c>
       <c r="B1254" t="str">
-        <v>FG-401652</v>
+        <v>FG-401342</v>
       </c>
       <c r="C1254" t="str">
-        <v>GARDEN PIPES SUPER FLOW (20MM 3/4 15MTR)</v>
+        <v>GARDEN PIPES SUPER FLOW (25MM 1)</v>
       </c>
       <c r="D1254" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44287,7 +44287,7 @@
         <v>General</v>
       </c>
       <c r="G1254" t="str">
-        <v>20MM 3/4 15MTR</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1254" t="str">
         <v>BDL</v>
@@ -44307,10 +44307,10 @@
         <v>1254</v>
       </c>
       <c r="B1255" t="str">
-        <v>FG-401342</v>
+        <v>FG-401343</v>
       </c>
       <c r="C1255" t="str">
-        <v>GARDEN PIPES SUPER FLOW (25MM 1)</v>
+        <v>GARDEN PIPES SUPER FLOW (32MM 1 1/4)</v>
       </c>
       <c r="D1255" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44322,7 +44322,7 @@
         <v>General</v>
       </c>
       <c r="G1255" t="str">
-        <v>25MM 1</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1255" t="str">
         <v>BDL</v>
@@ -44342,10 +44342,10 @@
         <v>1255</v>
       </c>
       <c r="B1256" t="str">
-        <v>FG-401343</v>
+        <v>FG-401627</v>
       </c>
       <c r="C1256" t="str">
-        <v>GARDEN PIPES SUPER FLOW (32MM 1 1/4)</v>
+        <v>GARDEN PIPES SUPER FLOW (40MM 1 1/2)</v>
       </c>
       <c r="D1256" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44357,7 +44357,7 @@
         <v>General</v>
       </c>
       <c r="G1256" t="str">
-        <v>32MM 1 1/4</v>
+        <v>40MM 1 1/2</v>
       </c>
       <c r="H1256" t="str">
         <v>BDL</v>
@@ -44377,34 +44377,34 @@
         <v>1256</v>
       </c>
       <c r="B1257" t="str">
-        <v>FG-401627</v>
+        <v>FG-401552</v>
       </c>
       <c r="C1257" t="str">
-        <v>GARDEN PIPES SUPER FLOW (40MM 1 1/2)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2 inch)</v>
       </c>
       <c r="D1257" t="str">
-        <v>GARDEN PIPES SUPER FLOW</v>
+        <v>EDGE SERIES SHORT BODY TAP</v>
       </c>
       <c r="E1257" t="str">
-        <v>Garden, Braided &amp; LDPE Pipes</v>
+        <v>FAUCETS</v>
       </c>
       <c r="F1257" t="str">
         <v>General</v>
       </c>
       <c r="G1257" t="str">
-        <v>40MM 1 1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1257" t="str">
-        <v>BDL</v>
-      </c>
-      <c r="I1257" t="str">
-        <v>-</v>
+        <v>NOS</v>
+      </c>
+      <c r="I1257">
+        <v>20</v>
       </c>
       <c r="J1257" t="str">
         <v>Active</v>
       </c>
       <c r="K1257" t="str">
-        <v>GARDEN PIPES SUPER FLOW.</v>
+        <v>EDGE SERIES SHORT BODY TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1258">
@@ -44415,7 +44415,7 @@
         <v>FG-401552</v>
       </c>
       <c r="C1258" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2 inch)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2)</v>
       </c>
       <c r="D1258" t="str">
         <v>EDGE SERIES SHORT BODY TAP</v>
@@ -44427,7 +44427,7 @@
         <v>General</v>
       </c>
       <c r="G1258" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1258" t="str">
         <v>NOS</v>
@@ -44450,7 +44450,7 @@
         <v>FG-401552</v>
       </c>
       <c r="C1259" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2")</v>
       </c>
       <c r="D1259" t="str">
         <v>EDGE SERIES SHORT BODY TAP</v>
@@ -44462,7 +44462,7 @@
         <v>General</v>
       </c>
       <c r="G1259" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1259" t="str">
         <v>NOS</v>
@@ -44482,13 +44482,13 @@
         <v>1259</v>
       </c>
       <c r="B1260" t="str">
-        <v>FG-401552</v>
+        <v>FG-401551</v>
       </c>
       <c r="C1260" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2")</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2 inch)</v>
       </c>
       <c r="D1260" t="str">
-        <v>EDGE SERIES SHORT BODY TAP</v>
+        <v>EDGE SERIES LONG BODY TAP</v>
       </c>
       <c r="E1260" t="str">
         <v>FAUCETS</v>
@@ -44497,19 +44497,19 @@
         <v>General</v>
       </c>
       <c r="G1260" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1260" t="str">
         <v>NOS</v>
       </c>
       <c r="I1260">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J1260" t="str">
         <v>Active</v>
       </c>
       <c r="K1260" t="str">
-        <v>EDGE SERIES SHORT BODY TAP high quality faucet.</v>
+        <v>EDGE SERIES LONG BODY TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1261">
@@ -44520,7 +44520,7 @@
         <v>FG-401551</v>
       </c>
       <c r="C1261" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2 inch)</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2)</v>
       </c>
       <c r="D1261" t="str">
         <v>EDGE SERIES LONG BODY TAP</v>
@@ -44532,7 +44532,7 @@
         <v>General</v>
       </c>
       <c r="G1261" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1261" t="str">
         <v>NOS</v>
@@ -44555,7 +44555,7 @@
         <v>FG-401551</v>
       </c>
       <c r="C1262" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2)</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2")</v>
       </c>
       <c r="D1262" t="str">
         <v>EDGE SERIES LONG BODY TAP</v>
@@ -44567,7 +44567,7 @@
         <v>General</v>
       </c>
       <c r="G1262" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1262" t="str">
         <v>NOS</v>
@@ -44587,13 +44587,13 @@
         <v>1262</v>
       </c>
       <c r="B1263" t="str">
-        <v>FG-401551</v>
+        <v>FG-401549</v>
       </c>
       <c r="C1263" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2")</v>
+        <v>EDGE SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1263" t="str">
-        <v>EDGE SERIES LONG BODY TAP</v>
+        <v>EDGE SERIES SWAN NECK</v>
       </c>
       <c r="E1263" t="str">
         <v>FAUCETS</v>
@@ -44602,19 +44602,19 @@
         <v>General</v>
       </c>
       <c r="G1263" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1263" t="str">
         <v>NOS</v>
       </c>
       <c r="I1263">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J1263" t="str">
         <v>Active</v>
       </c>
       <c r="K1263" t="str">
-        <v>EDGE SERIES LONG BODY TAP high quality faucet.</v>
+        <v>EDGE SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1264">
@@ -44625,7 +44625,7 @@
         <v>FG-401549</v>
       </c>
       <c r="C1264" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2 inch)</v>
+        <v>EDGE SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1264" t="str">
         <v>EDGE SERIES SWAN NECK</v>
@@ -44637,7 +44637,7 @@
         <v>General</v>
       </c>
       <c r="G1264" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1264" t="str">
         <v>NOS</v>
@@ -44660,7 +44660,7 @@
         <v>FG-401549</v>
       </c>
       <c r="C1265" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2)</v>
+        <v>EDGE SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1265" t="str">
         <v>EDGE SERIES SWAN NECK</v>
@@ -44672,7 +44672,7 @@
         <v>General</v>
       </c>
       <c r="G1265" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1265" t="str">
         <v>NOS</v>
@@ -44692,13 +44692,13 @@
         <v>1265</v>
       </c>
       <c r="B1266" t="str">
-        <v>FG-401549</v>
+        <v>FG-401546</v>
       </c>
       <c r="C1266" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2")</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1266" t="str">
-        <v>EDGE SERIES SWAN NECK</v>
+        <v>EDGE SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1266" t="str">
         <v>FAUCETS</v>
@@ -44707,19 +44707,19 @@
         <v>General</v>
       </c>
       <c r="G1266" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1266" t="str">
         <v>NOS</v>
       </c>
       <c r="I1266">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="J1266" t="str">
         <v>Active</v>
       </c>
       <c r="K1266" t="str">
-        <v>EDGE SERIES SWAN NECK high quality faucet.</v>
+        <v>EDGE SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1267">
@@ -44730,7 +44730,7 @@
         <v>FG-401546</v>
       </c>
       <c r="C1267" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1267" t="str">
         <v>EDGE SERIES ANGULAR VALVE</v>
@@ -44742,7 +44742,7 @@
         <v>General</v>
       </c>
       <c r="G1267" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1267" t="str">
         <v>NOS</v>
@@ -44765,7 +44765,7 @@
         <v>FG-401546</v>
       </c>
       <c r="C1268" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2)</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1268" t="str">
         <v>EDGE SERIES ANGULAR VALVE</v>
@@ -44777,7 +44777,7 @@
         <v>General</v>
       </c>
       <c r="G1268" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1268" t="str">
         <v>NOS</v>
@@ -44797,13 +44797,13 @@
         <v>1268</v>
       </c>
       <c r="B1269" t="str">
-        <v>FG-401546</v>
+        <v>FG-401547</v>
       </c>
       <c r="C1269" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2")</v>
+        <v>EDGE SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1269" t="str">
-        <v>EDGE SERIES ANGULAR VALVE</v>
+        <v>EDGE SERIES PILLAR TAP</v>
       </c>
       <c r="E1269" t="str">
         <v>FAUCETS</v>
@@ -44812,19 +44812,19 @@
         <v>General</v>
       </c>
       <c r="G1269" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1269" t="str">
         <v>NOS</v>
       </c>
       <c r="I1269">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J1269" t="str">
         <v>Active</v>
       </c>
       <c r="K1269" t="str">
-        <v>EDGE SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>EDGE SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1270">
@@ -44835,7 +44835,7 @@
         <v>FG-401547</v>
       </c>
       <c r="C1270" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2 inch)</v>
+        <v>EDGE SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1270" t="str">
         <v>EDGE SERIES PILLAR TAP</v>
@@ -44847,7 +44847,7 @@
         <v>General</v>
       </c>
       <c r="G1270" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1270" t="str">
         <v>NOS</v>
@@ -44870,7 +44870,7 @@
         <v>FG-401547</v>
       </c>
       <c r="C1271" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2)</v>
+        <v>EDGE SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1271" t="str">
         <v>EDGE SERIES PILLAR TAP</v>
@@ -44882,7 +44882,7 @@
         <v>General</v>
       </c>
       <c r="G1271" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1271" t="str">
         <v>NOS</v>
@@ -44902,13 +44902,13 @@
         <v>1271</v>
       </c>
       <c r="B1272" t="str">
-        <v>FG-401547</v>
+        <v>FG-401550</v>
       </c>
       <c r="C1272" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2")</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2 inch)</v>
       </c>
       <c r="D1272" t="str">
-        <v>EDGE SERIES PILLAR TAP</v>
+        <v>EDGE SERIES 2 WAY BIB TAB</v>
       </c>
       <c r="E1272" t="str">
         <v>FAUCETS</v>
@@ -44917,19 +44917,19 @@
         <v>General</v>
       </c>
       <c r="G1272" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1272" t="str">
         <v>NOS</v>
       </c>
       <c r="I1272">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J1272" t="str">
         <v>Active</v>
       </c>
       <c r="K1272" t="str">
-        <v>EDGE SERIES PILLAR TAP high quality faucet.</v>
+        <v>EDGE SERIES 2 WAY BIB TAB high quality faucet.</v>
       </c>
     </row>
     <row r="1273">
@@ -44940,7 +44940,7 @@
         <v>FG-401550</v>
       </c>
       <c r="C1273" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2 inch)</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2)</v>
       </c>
       <c r="D1273" t="str">
         <v>EDGE SERIES 2 WAY BIB TAB</v>
@@ -44952,7 +44952,7 @@
         <v>General</v>
       </c>
       <c r="G1273" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1273" t="str">
         <v>NOS</v>
@@ -44975,7 +44975,7 @@
         <v>FG-401550</v>
       </c>
       <c r="C1274" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2)</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2")</v>
       </c>
       <c r="D1274" t="str">
         <v>EDGE SERIES 2 WAY BIB TAB</v>
@@ -44987,7 +44987,7 @@
         <v>General</v>
       </c>
       <c r="G1274" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1274" t="str">
         <v>NOS</v>
@@ -45007,13 +45007,13 @@
         <v>1274</v>
       </c>
       <c r="B1275" t="str">
-        <v>FG-401550</v>
+        <v>FG-401548</v>
       </c>
       <c r="C1275" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2")</v>
+        <v>EDGE SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1275" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB</v>
+        <v>EDGE SERIES SINK TAP</v>
       </c>
       <c r="E1275" t="str">
         <v>FAUCETS</v>
@@ -45022,19 +45022,19 @@
         <v>General</v>
       </c>
       <c r="G1275" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1275" t="str">
         <v>NOS</v>
       </c>
       <c r="I1275">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1275" t="str">
         <v>Active</v>
       </c>
       <c r="K1275" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB high quality faucet.</v>
+        <v>EDGE SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1276">
@@ -45045,7 +45045,7 @@
         <v>FG-401548</v>
       </c>
       <c r="C1276" t="str">
-        <v>EDGE SERIES SINK TAP (1/2 inch)</v>
+        <v>EDGE SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1276" t="str">
         <v>EDGE SERIES SINK TAP</v>
@@ -45057,7 +45057,7 @@
         <v>General</v>
       </c>
       <c r="G1276" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1276" t="str">
         <v>NOS</v>
@@ -45080,7 +45080,7 @@
         <v>FG-401548</v>
       </c>
       <c r="C1277" t="str">
-        <v>EDGE SERIES SINK TAP (1/2)</v>
+        <v>EDGE SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1277" t="str">
         <v>EDGE SERIES SINK TAP</v>
@@ -45092,7 +45092,7 @@
         <v>General</v>
       </c>
       <c r="G1277" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1277" t="str">
         <v>NOS</v>
@@ -45112,13 +45112,13 @@
         <v>1277</v>
       </c>
       <c r="B1278" t="str">
-        <v>FG-401548</v>
+        <v>FG-401568</v>
       </c>
       <c r="C1278" t="str">
-        <v>EDGE SERIES SINK TAP (1/2")</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1278" t="str">
-        <v>EDGE SERIES SINK TAP</v>
+        <v>SMART SERIES SHORT BODY BIB TAP</v>
       </c>
       <c r="E1278" t="str">
         <v>FAUCETS</v>
@@ -45127,19 +45127,19 @@
         <v>General</v>
       </c>
       <c r="G1278" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1278" t="str">
         <v>NOS</v>
       </c>
       <c r="I1278">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="J1278" t="str">
         <v>Active</v>
       </c>
       <c r="K1278" t="str">
-        <v>EDGE SERIES SINK TAP high quality faucet.</v>
+        <v>SMART SERIES SHORT BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1279">
@@ -45150,7 +45150,7 @@
         <v>FG-401568</v>
       </c>
       <c r="C1279" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1279" t="str">
         <v>SMART SERIES SHORT BODY BIB TAP</v>
@@ -45162,7 +45162,7 @@
         <v>General</v>
       </c>
       <c r="G1279" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1279" t="str">
         <v>NOS</v>
@@ -45185,7 +45185,7 @@
         <v>FG-401568</v>
       </c>
       <c r="C1280" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2)</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1280" t="str">
         <v>SMART SERIES SHORT BODY BIB TAP</v>
@@ -45197,7 +45197,7 @@
         <v>General</v>
       </c>
       <c r="G1280" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1280" t="str">
         <v>NOS</v>
@@ -45217,13 +45217,13 @@
         <v>1280</v>
       </c>
       <c r="B1281" t="str">
-        <v>FG-401568</v>
+        <v>FG-401567</v>
       </c>
       <c r="C1281" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2")</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1281" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP</v>
+        <v>SMART SERIES LONG BODY BIB TAP</v>
       </c>
       <c r="E1281" t="str">
         <v>FAUCETS</v>
@@ -45232,7 +45232,7 @@
         <v>General</v>
       </c>
       <c r="G1281" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1281" t="str">
         <v>NOS</v>
@@ -45244,7 +45244,7 @@
         <v>Active</v>
       </c>
       <c r="K1281" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP high quality faucet.</v>
+        <v>SMART SERIES LONG BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1282">
@@ -45255,7 +45255,7 @@
         <v>FG-401567</v>
       </c>
       <c r="C1282" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1282" t="str">
         <v>SMART SERIES LONG BODY BIB TAP</v>
@@ -45267,7 +45267,7 @@
         <v>General</v>
       </c>
       <c r="G1282" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1282" t="str">
         <v>NOS</v>
@@ -45290,7 +45290,7 @@
         <v>FG-401567</v>
       </c>
       <c r="C1283" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2)</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1283" t="str">
         <v>SMART SERIES LONG BODY BIB TAP</v>
@@ -45302,7 +45302,7 @@
         <v>General</v>
       </c>
       <c r="G1283" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1283" t="str">
         <v>NOS</v>
@@ -45322,13 +45322,13 @@
         <v>1283</v>
       </c>
       <c r="B1284" t="str">
-        <v>FG-401567</v>
+        <v>FG-401562</v>
       </c>
       <c r="C1284" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2")</v>
+        <v>SMART SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1284" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP</v>
+        <v>SMART SERIES PILLAR TAP</v>
       </c>
       <c r="E1284" t="str">
         <v>FAUCETS</v>
@@ -45337,19 +45337,19 @@
         <v>General</v>
       </c>
       <c r="G1284" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1284" t="str">
         <v>NOS</v>
       </c>
       <c r="I1284">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1284" t="str">
         <v>Active</v>
       </c>
       <c r="K1284" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP high quality faucet.</v>
+        <v>SMART SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1285">
@@ -45360,7 +45360,7 @@
         <v>FG-401562</v>
       </c>
       <c r="C1285" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2 inch)</v>
+        <v>SMART SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1285" t="str">
         <v>SMART SERIES PILLAR TAP</v>
@@ -45372,7 +45372,7 @@
         <v>General</v>
       </c>
       <c r="G1285" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1285" t="str">
         <v>NOS</v>
@@ -45395,7 +45395,7 @@
         <v>FG-401562</v>
       </c>
       <c r="C1286" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2)</v>
+        <v>SMART SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1286" t="str">
         <v>SMART SERIES PILLAR TAP</v>
@@ -45407,7 +45407,7 @@
         <v>General</v>
       </c>
       <c r="G1286" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1286" t="str">
         <v>NOS</v>
@@ -45427,13 +45427,13 @@
         <v>1286</v>
       </c>
       <c r="B1287" t="str">
-        <v>FG-401562</v>
+        <v>FG-401563</v>
       </c>
       <c r="C1287" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2")</v>
+        <v>SMART SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1287" t="str">
-        <v>SMART SERIES PILLAR TAP</v>
+        <v>SMART SERIES SINK TAP</v>
       </c>
       <c r="E1287" t="str">
         <v>FAUCETS</v>
@@ -45442,7 +45442,7 @@
         <v>General</v>
       </c>
       <c r="G1287" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1287" t="str">
         <v>NOS</v>
@@ -45454,7 +45454,7 @@
         <v>Active</v>
       </c>
       <c r="K1287" t="str">
-        <v>SMART SERIES PILLAR TAP high quality faucet.</v>
+        <v>SMART SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1288">
@@ -45465,7 +45465,7 @@
         <v>FG-401563</v>
       </c>
       <c r="C1288" t="str">
-        <v>SMART SERIES SINK TAP (1/2 inch)</v>
+        <v>SMART SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1288" t="str">
         <v>SMART SERIES SINK TAP</v>
@@ -45477,7 +45477,7 @@
         <v>General</v>
       </c>
       <c r="G1288" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1288" t="str">
         <v>NOS</v>
@@ -45500,7 +45500,7 @@
         <v>FG-401563</v>
       </c>
       <c r="C1289" t="str">
-        <v>SMART SERIES SINK TAP (1/2)</v>
+        <v>SMART SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1289" t="str">
         <v>SMART SERIES SINK TAP</v>
@@ -45512,7 +45512,7 @@
         <v>General</v>
       </c>
       <c r="G1289" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1289" t="str">
         <v>NOS</v>
@@ -45532,13 +45532,13 @@
         <v>1289</v>
       </c>
       <c r="B1290" t="str">
-        <v>FG-401563</v>
+        <v>FG-401564</v>
       </c>
       <c r="C1290" t="str">
-        <v>SMART SERIES SINK TAP (1/2")</v>
+        <v>SMART SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1290" t="str">
-        <v>SMART SERIES SINK TAP</v>
+        <v>SMART SERIES SWAN NECK</v>
       </c>
       <c r="E1290" t="str">
         <v>FAUCETS</v>
@@ -45547,7 +45547,7 @@
         <v>General</v>
       </c>
       <c r="G1290" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1290" t="str">
         <v>NOS</v>
@@ -45559,7 +45559,7 @@
         <v>Active</v>
       </c>
       <c r="K1290" t="str">
-        <v>SMART SERIES SINK TAP high quality faucet.</v>
+        <v>SMART SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1291">
@@ -45570,7 +45570,7 @@
         <v>FG-401564</v>
       </c>
       <c r="C1291" t="str">
-        <v>SMART SERIES SWAN NECK (1/2 inch)</v>
+        <v>SMART SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1291" t="str">
         <v>SMART SERIES SWAN NECK</v>
@@ -45582,7 +45582,7 @@
         <v>General</v>
       </c>
       <c r="G1291" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1291" t="str">
         <v>NOS</v>
@@ -45605,7 +45605,7 @@
         <v>FG-401564</v>
       </c>
       <c r="C1292" t="str">
-        <v>SMART SERIES SWAN NECK (1/2)</v>
+        <v>SMART SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1292" t="str">
         <v>SMART SERIES SWAN NECK</v>
@@ -45617,7 +45617,7 @@
         <v>General</v>
       </c>
       <c r="G1292" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1292" t="str">
         <v>NOS</v>
@@ -45637,13 +45637,13 @@
         <v>1292</v>
       </c>
       <c r="B1293" t="str">
-        <v>FG-401564</v>
+        <v>FG-401561</v>
       </c>
       <c r="C1293" t="str">
-        <v>SMART SERIES SWAN NECK (1/2")</v>
+        <v>SMART SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1293" t="str">
-        <v>SMART SERIES SWAN NECK</v>
+        <v>SMART SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1293" t="str">
         <v>FAUCETS</v>
@@ -45652,19 +45652,19 @@
         <v>General</v>
       </c>
       <c r="G1293" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1293" t="str">
         <v>NOS</v>
       </c>
       <c r="I1293">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1293" t="str">
         <v>Active</v>
       </c>
       <c r="K1293" t="str">
-        <v>SMART SERIES SWAN NECK high quality faucet.</v>
+        <v>SMART SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1294">
@@ -45672,13 +45672,13 @@
         <v>1293</v>
       </c>
       <c r="B1294" t="str">
-        <v>FG-401561</v>
+        <v>FG-401566</v>
       </c>
       <c r="C1294" t="str">
-        <v>SMART SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1294" t="str">
-        <v>SMART SERIES ANGULAR VALVE</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
       </c>
       <c r="E1294" t="str">
         <v>FAUCETS</v>
@@ -45693,13 +45693,13 @@
         <v>NOS</v>
       </c>
       <c r="I1294">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1294" t="str">
         <v>Active</v>
       </c>
       <c r="K1294" t="str">
-        <v>SMART SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1295">
@@ -45710,7 +45710,7 @@
         <v>FG-401566</v>
       </c>
       <c r="C1295" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1295" t="str">
         <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
@@ -45722,7 +45722,7 @@
         <v>General</v>
       </c>
       <c r="G1295" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1295" t="str">
         <v>NOS</v>
@@ -45745,7 +45745,7 @@
         <v>FG-401566</v>
       </c>
       <c r="C1296" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1296" t="str">
         <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
@@ -45757,7 +45757,7 @@
         <v>General</v>
       </c>
       <c r="G1296" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1296" t="str">
         <v>NOS</v>
@@ -45777,13 +45777,13 @@
         <v>1296</v>
       </c>
       <c r="B1297" t="str">
-        <v>FG-401566</v>
+        <v>FG-401565</v>
       </c>
       <c r="C1297" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2")</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1297" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
+        <v>SMART SERIES 2 WAY BIB TAP</v>
       </c>
       <c r="E1297" t="str">
         <v>FAUCETS</v>
@@ -45792,7 +45792,7 @@
         <v>General</v>
       </c>
       <c r="G1297" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1297" t="str">
         <v>NOS</v>
@@ -45804,7 +45804,7 @@
         <v>Active</v>
       </c>
       <c r="K1297" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
+        <v>SMART SERIES 2 WAY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1298">
@@ -45815,7 +45815,7 @@
         <v>FG-401565</v>
       </c>
       <c r="C1298" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2)</v>
       </c>
       <c r="D1298" t="str">
         <v>SMART SERIES 2 WAY BIB TAP</v>
@@ -45827,7 +45827,7 @@
         <v>General</v>
       </c>
       <c r="G1298" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1298" t="str">
         <v>NOS</v>
@@ -45850,7 +45850,7 @@
         <v>FG-401565</v>
       </c>
       <c r="C1299" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2)</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2")</v>
       </c>
       <c r="D1299" t="str">
         <v>SMART SERIES 2 WAY BIB TAP</v>
@@ -45862,7 +45862,7 @@
         <v>General</v>
       </c>
       <c r="G1299" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1299" t="str">
         <v>NOS</v>
@@ -45882,13 +45882,13 @@
         <v>1299</v>
       </c>
       <c r="B1300" t="str">
-        <v>FG-401565</v>
+        <v>FG-401560</v>
       </c>
       <c r="C1300" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1300" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP</v>
       </c>
       <c r="E1300" t="str">
         <v>FAUCETS</v>
@@ -45897,19 +45897,19 @@
         <v>General</v>
       </c>
       <c r="G1300" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1300" t="str">
         <v>NOS</v>
       </c>
       <c r="I1300">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1300" t="str">
         <v>Active</v>
       </c>
       <c r="K1300" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1301">
@@ -45920,7 +45920,7 @@
         <v>FG-401560</v>
       </c>
       <c r="C1301" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1301" t="str">
         <v>REGULAR SERIES SHORT BODY BIB TAP</v>
@@ -45932,7 +45932,7 @@
         <v>General</v>
       </c>
       <c r="G1301" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1301" t="str">
         <v>NOS</v>
@@ -45955,7 +45955,7 @@
         <v>FG-401560</v>
       </c>
       <c r="C1302" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1302" t="str">
         <v>REGULAR SERIES SHORT BODY BIB TAP</v>
@@ -45967,7 +45967,7 @@
         <v>General</v>
       </c>
       <c r="G1302" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1302" t="str">
         <v>NOS</v>
@@ -45987,13 +45987,13 @@
         <v>1302</v>
       </c>
       <c r="B1303" t="str">
-        <v>FG-401560</v>
+        <v>FG-401559</v>
       </c>
       <c r="C1303" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1303" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP</v>
       </c>
       <c r="E1303" t="str">
         <v>FAUCETS</v>
@@ -46002,7 +46002,7 @@
         <v>General</v>
       </c>
       <c r="G1303" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1303" t="str">
         <v>NOS</v>
@@ -46014,7 +46014,7 @@
         <v>Active</v>
       </c>
       <c r="K1303" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1304">
@@ -46025,7 +46025,7 @@
         <v>FG-401559</v>
       </c>
       <c r="C1304" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1304" t="str">
         <v>REGULAR SERIES LONG BODY BIB TAP</v>
@@ -46037,7 +46037,7 @@
         <v>General</v>
       </c>
       <c r="G1304" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1304" t="str">
         <v>NOS</v>
@@ -46060,7 +46060,7 @@
         <v>FG-401559</v>
       </c>
       <c r="C1305" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1305" t="str">
         <v>REGULAR SERIES LONG BODY BIB TAP</v>
@@ -46072,7 +46072,7 @@
         <v>General</v>
       </c>
       <c r="G1305" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1305" t="str">
         <v>NOS</v>
@@ -46092,13 +46092,13 @@
         <v>1305</v>
       </c>
       <c r="B1306" t="str">
-        <v>FG-401559</v>
+        <v>FG-401554</v>
       </c>
       <c r="C1306" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1306" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP</v>
+        <v>REGULAR SERIES PILLAR TAP</v>
       </c>
       <c r="E1306" t="str">
         <v>FAUCETS</v>
@@ -46107,19 +46107,19 @@
         <v>General</v>
       </c>
       <c r="G1306" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1306" t="str">
         <v>NOS</v>
       </c>
       <c r="I1306">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1306" t="str">
         <v>Active</v>
       </c>
       <c r="K1306" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1307">
@@ -46130,7 +46130,7 @@
         <v>FG-401554</v>
       </c>
       <c r="C1307" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2 inch)</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1307" t="str">
         <v>REGULAR SERIES PILLAR TAP</v>
@@ -46142,7 +46142,7 @@
         <v>General</v>
       </c>
       <c r="G1307" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1307" t="str">
         <v>NOS</v>
@@ -46165,7 +46165,7 @@
         <v>FG-401554</v>
       </c>
       <c r="C1308" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2)</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1308" t="str">
         <v>REGULAR SERIES PILLAR TAP</v>
@@ -46177,7 +46177,7 @@
         <v>General</v>
       </c>
       <c r="G1308" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1308" t="str">
         <v>NOS</v>
@@ -46197,13 +46197,13 @@
         <v>1308</v>
       </c>
       <c r="B1309" t="str">
-        <v>FG-401554</v>
+        <v>FG-401555</v>
       </c>
       <c r="C1309" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2")</v>
+        <v>REGULAR SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1309" t="str">
-        <v>REGULAR SERIES PILLAR TAP</v>
+        <v>REGULAR SERIES SINK TAP</v>
       </c>
       <c r="E1309" t="str">
         <v>FAUCETS</v>
@@ -46212,7 +46212,7 @@
         <v>General</v>
       </c>
       <c r="G1309" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1309" t="str">
         <v>NOS</v>
@@ -46224,7 +46224,7 @@
         <v>Active</v>
       </c>
       <c r="K1309" t="str">
-        <v>REGULAR SERIES PILLAR TAP high quality faucet.</v>
+        <v>REGULAR SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1310">
@@ -46235,7 +46235,7 @@
         <v>FG-401555</v>
       </c>
       <c r="C1310" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2 inch)</v>
+        <v>REGULAR SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1310" t="str">
         <v>REGULAR SERIES SINK TAP</v>
@@ -46247,7 +46247,7 @@
         <v>General</v>
       </c>
       <c r="G1310" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1310" t="str">
         <v>NOS</v>
@@ -46270,7 +46270,7 @@
         <v>FG-401555</v>
       </c>
       <c r="C1311" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2)</v>
+        <v>REGULAR SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1311" t="str">
         <v>REGULAR SERIES SINK TAP</v>
@@ -46282,7 +46282,7 @@
         <v>General</v>
       </c>
       <c r="G1311" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1311" t="str">
         <v>NOS</v>
@@ -46302,13 +46302,13 @@
         <v>1311</v>
       </c>
       <c r="B1312" t="str">
-        <v>FG-401555</v>
+        <v>FG-401556</v>
       </c>
       <c r="C1312" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2")</v>
+        <v>REGULAR SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1312" t="str">
-        <v>REGULAR SERIES SINK TAP</v>
+        <v>REGULAR SERIES SWAN NECK</v>
       </c>
       <c r="E1312" t="str">
         <v>FAUCETS</v>
@@ -46317,7 +46317,7 @@
         <v>General</v>
       </c>
       <c r="G1312" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1312" t="str">
         <v>NOS</v>
@@ -46329,7 +46329,7 @@
         <v>Active</v>
       </c>
       <c r="K1312" t="str">
-        <v>REGULAR SERIES SINK TAP high quality faucet.</v>
+        <v>REGULAR SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1313">
@@ -46340,7 +46340,7 @@
         <v>FG-401556</v>
       </c>
       <c r="C1313" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2 inch)</v>
+        <v>REGULAR SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1313" t="str">
         <v>REGULAR SERIES SWAN NECK</v>
@@ -46352,7 +46352,7 @@
         <v>General</v>
       </c>
       <c r="G1313" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1313" t="str">
         <v>NOS</v>
@@ -46375,7 +46375,7 @@
         <v>FG-401556</v>
       </c>
       <c r="C1314" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2)</v>
+        <v>REGULAR SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1314" t="str">
         <v>REGULAR SERIES SWAN NECK</v>
@@ -46387,7 +46387,7 @@
         <v>General</v>
       </c>
       <c r="G1314" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1314" t="str">
         <v>NOS</v>
@@ -46407,13 +46407,13 @@
         <v>1314</v>
       </c>
       <c r="B1315" t="str">
-        <v>FG-401556</v>
+        <v>FG-401553</v>
       </c>
       <c r="C1315" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2")</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1315" t="str">
-        <v>REGULAR SERIES SWAN NECK</v>
+        <v>REGULAR SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1315" t="str">
         <v>FAUCETS</v>
@@ -46422,19 +46422,19 @@
         <v>General</v>
       </c>
       <c r="G1315" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1315" t="str">
         <v>NOS</v>
       </c>
       <c r="I1315">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1315" t="str">
         <v>Active</v>
       </c>
       <c r="K1315" t="str">
-        <v>REGULAR SERIES SWAN NECK high quality faucet.</v>
+        <v>REGULAR SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1316">
@@ -46445,7 +46445,7 @@
         <v>FG-401553</v>
       </c>
       <c r="C1316" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1316" t="str">
         <v>REGULAR SERIES ANGULAR VALVE</v>
@@ -46457,7 +46457,7 @@
         <v>General</v>
       </c>
       <c r="G1316" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1316" t="str">
         <v>NOS</v>
@@ -46480,7 +46480,7 @@
         <v>FG-401553</v>
       </c>
       <c r="C1317" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2)</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1317" t="str">
         <v>REGULAR SERIES ANGULAR VALVE</v>
@@ -46492,7 +46492,7 @@
         <v>General</v>
       </c>
       <c r="G1317" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1317" t="str">
         <v>NOS</v>
@@ -46512,13 +46512,13 @@
         <v>1317</v>
       </c>
       <c r="B1318" t="str">
-        <v>FG-401553</v>
+        <v>FG-401558</v>
       </c>
       <c r="C1318" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2")</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1318" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
       </c>
       <c r="E1318" t="str">
         <v>FAUCETS</v>
@@ -46527,19 +46527,19 @@
         <v>General</v>
       </c>
       <c r="G1318" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1318" t="str">
         <v>NOS</v>
       </c>
       <c r="I1318">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1318" t="str">
         <v>Active</v>
       </c>
       <c r="K1318" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1319">
@@ -46550,7 +46550,7 @@
         <v>FG-401558</v>
       </c>
       <c r="C1319" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1319" t="str">
         <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
@@ -46562,7 +46562,7 @@
         <v>General</v>
       </c>
       <c r="G1319" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1319" t="str">
         <v>NOS</v>
@@ -46585,7 +46585,7 @@
         <v>FG-401558</v>
       </c>
       <c r="C1320" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2)</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1320" t="str">
         <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
@@ -46597,7 +46597,7 @@
         <v>General</v>
       </c>
       <c r="G1320" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1320" t="str">
         <v>NOS</v>
@@ -46617,13 +46617,13 @@
         <v>1320</v>
       </c>
       <c r="B1321" t="str">
-        <v>FG-401558</v>
+        <v>FG-401557</v>
       </c>
       <c r="C1321" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2")</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1321" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP</v>
       </c>
       <c r="E1321" t="str">
         <v>FAUCETS</v>
@@ -46632,7 +46632,7 @@
         <v>General</v>
       </c>
       <c r="G1321" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1321" t="str">
         <v>NOS</v>
@@ -46644,7 +46644,7 @@
         <v>Active</v>
       </c>
       <c r="K1321" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1322">
@@ -46655,7 +46655,7 @@
         <v>FG-401557</v>
       </c>
       <c r="C1322" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2)</v>
       </c>
       <c r="D1322" t="str">
         <v>REGULAR SERIES 2 WAY BIB TAP</v>
@@ -46667,7 +46667,7 @@
         <v>General</v>
       </c>
       <c r="G1322" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1322" t="str">
         <v>NOS</v>
@@ -46690,7 +46690,7 @@
         <v>FG-401557</v>
       </c>
       <c r="C1323" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2")</v>
       </c>
       <c r="D1323" t="str">
         <v>REGULAR SERIES 2 WAY BIB TAP</v>
@@ -46702,7 +46702,7 @@
         <v>General</v>
       </c>
       <c r="G1323" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1323" t="str">
         <v>NOS</v>
@@ -46722,34 +46722,34 @@
         <v>1323</v>
       </c>
       <c r="B1324" t="str">
-        <v>FG-401557</v>
+        <v>FG-400836</v>
       </c>
       <c r="C1324" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2")</v>
+        <v>SINGLE SIDE HANDLE FLUSH 8L (8L)</v>
       </c>
       <c r="D1324" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP</v>
+        <v>SINGLE SIDE HANDLE FLUSH 8L</v>
       </c>
       <c r="E1324" t="str">
-        <v>FAUCETS</v>
+        <v>Toilet Seat Cover &amp; Flushing Cistern</v>
       </c>
       <c r="F1324" t="str">
         <v>General</v>
       </c>
       <c r="G1324" t="str">
-        <v>1/2"</v>
+        <v>8L</v>
       </c>
       <c r="H1324" t="str">
         <v>NOS</v>
       </c>
       <c r="I1324">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J1324" t="str">
         <v>Active</v>
       </c>
       <c r="K1324" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP high quality faucet.</v>
+        <v>8 Litre Single Side Handle Flushing Cistern.</v>
       </c>
     </row>
     <row r="1325">
@@ -46757,13 +46757,13 @@
         <v>1324</v>
       </c>
       <c r="B1325" t="str">
-        <v>FG-400836</v>
+        <v>FG-400837</v>
       </c>
       <c r="C1325" t="str">
-        <v>SINGLE SIDE HANDLE FLUSH 8L (8L)</v>
+        <v>CENTER SINGLE PUSH FLUSH 8L (8L)</v>
       </c>
       <c r="D1325" t="str">
-        <v>SINGLE SIDE HANDLE FLUSH 8L</v>
+        <v>CENTER SINGLE PUSH FLUSH 8L</v>
       </c>
       <c r="E1325" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46784,7 +46784,7 @@
         <v>Active</v>
       </c>
       <c r="K1325" t="str">
-        <v>8 Litre Single Side Handle Flushing Cistern.</v>
+        <v>8 Litre Center Single Push Flushing Cistern.</v>
       </c>
     </row>
     <row r="1326">
@@ -46792,13 +46792,13 @@
         <v>1325</v>
       </c>
       <c r="B1326" t="str">
-        <v>FG-400837</v>
+        <v>FG-400838</v>
       </c>
       <c r="C1326" t="str">
-        <v>CENTER SINGLE PUSH FLUSH 8L (8L)</v>
+        <v>DUAL FLUSH 10L (10L)</v>
       </c>
       <c r="D1326" t="str">
-        <v>CENTER SINGLE PUSH FLUSH 8L</v>
+        <v>DUAL FLUSH 10L</v>
       </c>
       <c r="E1326" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46807,7 +46807,7 @@
         <v>General</v>
       </c>
       <c r="G1326" t="str">
-        <v>8L</v>
+        <v>10L</v>
       </c>
       <c r="H1326" t="str">
         <v>NOS</v>
@@ -46819,7 +46819,7 @@
         <v>Active</v>
       </c>
       <c r="K1326" t="str">
-        <v>8 Litre Center Single Push Flushing Cistern.</v>
+        <v>10 Litre Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1327">
@@ -46827,13 +46827,13 @@
         <v>1326</v>
       </c>
       <c r="B1327" t="str">
-        <v>FG-400838</v>
+        <v>FG-400835</v>
       </c>
       <c r="C1327" t="str">
-        <v>DUAL FLUSH 10L (10L)</v>
+        <v>EWC SEAT COVER (WITH JET) (Standard)</v>
       </c>
       <c r="D1327" t="str">
-        <v>DUAL FLUSH 10L</v>
+        <v>EWC SEAT COVER (WITH JET)</v>
       </c>
       <c r="E1327" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46842,19 +46842,19 @@
         <v>General</v>
       </c>
       <c r="G1327" t="str">
-        <v>10L</v>
+        <v>Standard</v>
       </c>
       <c r="H1327" t="str">
         <v>NOS</v>
       </c>
       <c r="I1327">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J1327" t="str">
         <v>Active</v>
       </c>
       <c r="K1327" t="str">
-        <v>10 Litre Dual Flush Cistern.</v>
+        <v>EWC Toilet Seat Cover with integrated jet spray.</v>
       </c>
     </row>
     <row r="1328">
@@ -46862,13 +46862,13 @@
         <v>1327</v>
       </c>
       <c r="B1328" t="str">
-        <v>FG-400835</v>
+        <v>FG-400840</v>
       </c>
       <c r="C1328" t="str">
-        <v>EWC SEAT COVER (WITH JET) (Standard)</v>
+        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L) (10L)</v>
       </c>
       <c r="D1328" t="str">
-        <v>EWC SEAT COVER (WITH JET)</v>
+        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L)</v>
       </c>
       <c r="E1328" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46877,19 +46877,19 @@
         <v>General</v>
       </c>
       <c r="G1328" t="str">
-        <v>Standard</v>
+        <v>10L</v>
       </c>
       <c r="H1328" t="str">
         <v>NOS</v>
       </c>
       <c r="I1328">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J1328" t="str">
         <v>Active</v>
       </c>
       <c r="K1328" t="str">
-        <v>EWC Toilet Seat Cover with integrated jet spray.</v>
+        <v>10 Litre Premium Dual Colour Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1329">
@@ -46897,13 +46897,13 @@
         <v>1328</v>
       </c>
       <c r="B1329" t="str">
-        <v>FG-400840</v>
+        <v>FG-400839</v>
       </c>
       <c r="C1329" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L) (10L)</v>
+        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L) (10L)</v>
       </c>
       <c r="D1329" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L)</v>
+        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L)</v>
       </c>
       <c r="E1329" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46924,7 +46924,7 @@
         <v>Active</v>
       </c>
       <c r="K1329" t="str">
-        <v>10 Litre Premium Dual Colour Dual Flush Cistern.</v>
+        <v>10 Litre Economy Dual Colour Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1330">
@@ -46932,13 +46932,13 @@
         <v>1329</v>
       </c>
       <c r="B1330" t="str">
-        <v>FG-400839</v>
+        <v>FG-400834</v>
       </c>
       <c r="C1330" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L) (10L)</v>
+        <v>EWC SEAT COVER (WITHOUT JET) (Standard)</v>
       </c>
       <c r="D1330" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L)</v>
+        <v>EWC SEAT COVER (WITHOUT JET)</v>
       </c>
       <c r="E1330" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46947,59 +46947,24 @@
         <v>General</v>
       </c>
       <c r="G1330" t="str">
-        <v>10L</v>
+        <v>Standard</v>
       </c>
       <c r="H1330" t="str">
         <v>NOS</v>
       </c>
       <c r="I1330">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J1330" t="str">
         <v>Active</v>
       </c>
       <c r="K1330" t="str">
-        <v>10 Litre Economy Dual Colour Dual Flush Cistern.</v>
-      </c>
-    </row>
-    <row r="1331">
-      <c r="A1331">
-        <v>1330</v>
-      </c>
-      <c r="B1331" t="str">
-        <v>FG-400834</v>
-      </c>
-      <c r="C1331" t="str">
-        <v>EWC SEAT COVER (WITHOUT JET) (Standard)</v>
-      </c>
-      <c r="D1331" t="str">
-        <v>EWC SEAT COVER (WITHOUT JET)</v>
-      </c>
-      <c r="E1331" t="str">
-        <v>Toilet Seat Cover &amp; Flushing Cistern</v>
-      </c>
-      <c r="F1331" t="str">
-        <v>General</v>
-      </c>
-      <c r="G1331" t="str">
-        <v>Standard</v>
-      </c>
-      <c r="H1331" t="str">
-        <v>NOS</v>
-      </c>
-      <c r="I1331">
-        <v>20</v>
-      </c>
-      <c r="J1331" t="str">
-        <v>Active</v>
-      </c>
-      <c r="K1331" t="str">
         <v>EWC Toilet Seat Cover without jet spray.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K1331"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K1330"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
+++ b/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1330"/>
+  <dimension ref="A1:K1331"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -35662,10 +35662,10 @@
         <v>1007</v>
       </c>
       <c r="B1008" t="str">
-        <v>-</v>
+        <v>FG-400665</v>
       </c>
       <c r="C1008" t="str">
-        <v>AGRI ELBOW 10KG</v>
+        <v>AGRI ELBOW 10KG (25MM)</v>
       </c>
       <c r="D1008" t="str">
         <v>AGRI ELBOW 10KG</v>
@@ -35677,19 +35677,19 @@
         <v>General</v>
       </c>
       <c r="G1008" t="str">
-        <v>Standard</v>
+        <v>25MM</v>
       </c>
       <c r="H1008" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1008" t="str">
-        <v>-</v>
+      <c r="I1008">
+        <v>300</v>
       </c>
       <c r="J1008" t="str">
         <v>Active</v>
       </c>
       <c r="K1008" t="str">
-        <v>AGRI ELBOW 10KG.</v>
+        <v>AGRI ELBOW 10KG. Available sizes: 25MM, 32MM.</v>
       </c>
     </row>
     <row r="1009">
@@ -35697,13 +35697,13 @@
         <v>1008</v>
       </c>
       <c r="B1009" t="str">
-        <v>-</v>
+        <v>FG-400666</v>
       </c>
       <c r="C1009" t="str">
-        <v>PN10 - UNION ISI (25MM)</v>
+        <v>AGRI ELBOW 10KG (32MM)</v>
       </c>
       <c r="D1009" t="str">
-        <v>PN10 - UNION ISI</v>
+        <v>AGRI ELBOW 10KG</v>
       </c>
       <c r="E1009" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35712,19 +35712,19 @@
         <v>General</v>
       </c>
       <c r="G1009" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1009" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1009" t="str">
-        <v>-</v>
+      <c r="I1009">
+        <v>150</v>
       </c>
       <c r="J1009" t="str">
         <v>Active</v>
       </c>
       <c r="K1009" t="str">
-        <v>PN10 - UNION ISI for agriculture irrigation and piping systems.</v>
+        <v>AGRI ELBOW 10KG. Available sizes: 25MM, 32MM.</v>
       </c>
     </row>
     <row r="1010">
@@ -35735,7 +35735,7 @@
         <v>-</v>
       </c>
       <c r="C1010" t="str">
-        <v>PN10 - UNION ISI (32MM)</v>
+        <v>PN10 - UNION ISI (25MM)</v>
       </c>
       <c r="D1010" t="str">
         <v>PN10 - UNION ISI</v>
@@ -35747,7 +35747,7 @@
         <v>General</v>
       </c>
       <c r="G1010" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1010" t="str">
         <v>BOX</v>
@@ -35770,10 +35770,10 @@
         <v>-</v>
       </c>
       <c r="C1011" t="str">
-        <v>PN10 - TEE ISI (25MM)</v>
+        <v>PN10 - UNION ISI (32MM)</v>
       </c>
       <c r="D1011" t="str">
-        <v>PN10 - TEE ISI</v>
+        <v>PN10 - UNION ISI</v>
       </c>
       <c r="E1011" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35782,7 +35782,7 @@
         <v>General</v>
       </c>
       <c r="G1011" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1011" t="str">
         <v>BOX</v>
@@ -35794,7 +35794,7 @@
         <v>Active</v>
       </c>
       <c r="K1011" t="str">
-        <v>PN10 - TEE ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - UNION ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1012">
@@ -35805,7 +35805,7 @@
         <v>-</v>
       </c>
       <c r="C1012" t="str">
-        <v>PN10 - TEE ISI (32MM)</v>
+        <v>PN10 - TEE ISI (25MM)</v>
       </c>
       <c r="D1012" t="str">
         <v>PN10 - TEE ISI</v>
@@ -35817,7 +35817,7 @@
         <v>General</v>
       </c>
       <c r="G1012" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1012" t="str">
         <v>BOX</v>
@@ -35840,10 +35840,10 @@
         <v>-</v>
       </c>
       <c r="C1013" t="str">
-        <v>PN10 - COUPLER ISI (25MM)</v>
+        <v>PN10 - TEE ISI (32MM)</v>
       </c>
       <c r="D1013" t="str">
-        <v>PN10 - COUPLER ISI</v>
+        <v>PN10 - TEE ISI</v>
       </c>
       <c r="E1013" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35852,7 +35852,7 @@
         <v>General</v>
       </c>
       <c r="G1013" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1013" t="str">
         <v>BOX</v>
@@ -35864,7 +35864,7 @@
         <v>Active</v>
       </c>
       <c r="K1013" t="str">
-        <v>PN10 - COUPLER ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - TEE ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1014">
@@ -35875,7 +35875,7 @@
         <v>-</v>
       </c>
       <c r="C1014" t="str">
-        <v>PN10 - COUPLER ISI (32MM)</v>
+        <v>PN10 - COUPLER ISI (25MM)</v>
       </c>
       <c r="D1014" t="str">
         <v>PN10 - COUPLER ISI</v>
@@ -35887,7 +35887,7 @@
         <v>General</v>
       </c>
       <c r="G1014" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1014" t="str">
         <v>BOX</v>
@@ -35910,10 +35910,10 @@
         <v>-</v>
       </c>
       <c r="C1015" t="str">
-        <v>PN10 - MTA ISI (25MM)</v>
+        <v>PN10 - COUPLER ISI (32MM)</v>
       </c>
       <c r="D1015" t="str">
-        <v>PN10 - MTA ISI</v>
+        <v>PN10 - COUPLER ISI</v>
       </c>
       <c r="E1015" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35922,7 +35922,7 @@
         <v>General</v>
       </c>
       <c r="G1015" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1015" t="str">
         <v>BOX</v>
@@ -35934,7 +35934,7 @@
         <v>Active</v>
       </c>
       <c r="K1015" t="str">
-        <v>PN10 - MTA ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - COUPLER ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1016">
@@ -35945,7 +35945,7 @@
         <v>-</v>
       </c>
       <c r="C1016" t="str">
-        <v>PN10 - MTA ISI (32MM)</v>
+        <v>PN10 - MTA ISI (25MM)</v>
       </c>
       <c r="D1016" t="str">
         <v>PN10 - MTA ISI</v>
@@ -35957,7 +35957,7 @@
         <v>General</v>
       </c>
       <c r="G1016" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1016" t="str">
         <v>BOX</v>
@@ -35980,10 +35980,10 @@
         <v>-</v>
       </c>
       <c r="C1017" t="str">
-        <v>PN10 - FTA ISI (25MM)</v>
+        <v>PN10 - MTA ISI (32MM)</v>
       </c>
       <c r="D1017" t="str">
-        <v>PN10 - FTA ISI</v>
+        <v>PN10 - MTA ISI</v>
       </c>
       <c r="E1017" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35992,7 +35992,7 @@
         <v>General</v>
       </c>
       <c r="G1017" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1017" t="str">
         <v>BOX</v>
@@ -36004,7 +36004,7 @@
         <v>Active</v>
       </c>
       <c r="K1017" t="str">
-        <v>PN10 - FTA ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - MTA ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1018">
@@ -36015,7 +36015,7 @@
         <v>-</v>
       </c>
       <c r="C1018" t="str">
-        <v>PN10 - FTA ISI (32MM)</v>
+        <v>PN10 - FTA ISI (25MM)</v>
       </c>
       <c r="D1018" t="str">
         <v>PN10 - FTA ISI</v>
@@ -36027,7 +36027,7 @@
         <v>General</v>
       </c>
       <c r="G1018" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1018" t="str">
         <v>BOX</v>
@@ -36050,10 +36050,10 @@
         <v>-</v>
       </c>
       <c r="C1019" t="str">
-        <v>PN10 - END CAP ISI (25MM)</v>
+        <v>PN10 - FTA ISI (32MM)</v>
       </c>
       <c r="D1019" t="str">
-        <v>PN10 - END CAP ISI</v>
+        <v>PN10 - FTA ISI</v>
       </c>
       <c r="E1019" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36062,7 +36062,7 @@
         <v>General</v>
       </c>
       <c r="G1019" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1019" t="str">
         <v>BOX</v>
@@ -36074,7 +36074,7 @@
         <v>Active</v>
       </c>
       <c r="K1019" t="str">
-        <v>PN10 - END CAP ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - FTA ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1020">
@@ -36085,7 +36085,7 @@
         <v>-</v>
       </c>
       <c r="C1020" t="str">
-        <v>PN10 - END CAP ISI (32MM)</v>
+        <v>PN10 - END CAP ISI (25MM)</v>
       </c>
       <c r="D1020" t="str">
         <v>PN10 - END CAP ISI</v>
@@ -36097,7 +36097,7 @@
         <v>General</v>
       </c>
       <c r="G1020" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1020" t="str">
         <v>BOX</v>
@@ -36120,10 +36120,10 @@
         <v>-</v>
       </c>
       <c r="C1021" t="str">
-        <v>PN10 - REDUCING BUSH ISI (32 X 20)</v>
+        <v>PN10 - END CAP ISI (32MM)</v>
       </c>
       <c r="D1021" t="str">
-        <v>PN10 - REDUCING BUSH ISI</v>
+        <v>PN10 - END CAP ISI</v>
       </c>
       <c r="E1021" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36132,7 +36132,7 @@
         <v>General</v>
       </c>
       <c r="G1021" t="str">
-        <v>32 X 20</v>
+        <v>32MM</v>
       </c>
       <c r="H1021" t="str">
         <v>BOX</v>
@@ -36144,7 +36144,7 @@
         <v>Active</v>
       </c>
       <c r="K1021" t="str">
-        <v>PN10 - REDUCING BUSH ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - END CAP ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1022">
@@ -36155,7 +36155,7 @@
         <v>-</v>
       </c>
       <c r="C1022" t="str">
-        <v>PN10 - REDUCING BUSH ISI (32 X 25)</v>
+        <v>PN10 - REDUCING BUSH ISI (32 X 20)</v>
       </c>
       <c r="D1022" t="str">
         <v>PN10 - REDUCING BUSH ISI</v>
@@ -36167,7 +36167,7 @@
         <v>General</v>
       </c>
       <c r="G1022" t="str">
-        <v>32 X 25</v>
+        <v>32 X 20</v>
       </c>
       <c r="H1022" t="str">
         <v>BOX</v>
@@ -36187,13 +36187,13 @@
         <v>1022</v>
       </c>
       <c r="B1023" t="str">
-        <v>FG-400585</v>
+        <v>-</v>
       </c>
       <c r="C1023" t="str">
-        <v>AGRI REDUCER (50X40MM)</v>
+        <v>PN10 - REDUCING BUSH ISI (32 X 25)</v>
       </c>
       <c r="D1023" t="str">
-        <v>AGRI REDUCER</v>
+        <v>PN10 - REDUCING BUSH ISI</v>
       </c>
       <c r="E1023" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36202,19 +36202,19 @@
         <v>General</v>
       </c>
       <c r="G1023" t="str">
-        <v>50X40MM</v>
+        <v>32 X 25</v>
       </c>
       <c r="H1023" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1023">
-        <v>300</v>
+      <c r="I1023" t="str">
+        <v>-</v>
       </c>
       <c r="J1023" t="str">
         <v>Active</v>
       </c>
       <c r="K1023" t="str">
-        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
+        <v>PN10 - REDUCING BUSH ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1024">
@@ -36222,10 +36222,10 @@
         <v>1023</v>
       </c>
       <c r="B1024" t="str">
-        <v>FG-400584</v>
+        <v>FG-400585</v>
       </c>
       <c r="C1024" t="str">
-        <v>AGRI REDUCER (63X40MM)</v>
+        <v>AGRI REDUCER (50X40MM)</v>
       </c>
       <c r="D1024" t="str">
         <v>AGRI REDUCER</v>
@@ -36237,13 +36237,13 @@
         <v>General</v>
       </c>
       <c r="G1024" t="str">
-        <v>63X40MM</v>
+        <v>50X40MM</v>
       </c>
       <c r="H1024" t="str">
         <v>BOX</v>
       </c>
       <c r="I1024">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J1024" t="str">
         <v>Active</v>
@@ -36257,10 +36257,10 @@
         <v>1024</v>
       </c>
       <c r="B1025" t="str">
-        <v>FG-400583</v>
+        <v>FG-400584</v>
       </c>
       <c r="C1025" t="str">
-        <v>AGRI REDUCER (63X50MM)</v>
+        <v>AGRI REDUCER (63X40MM)</v>
       </c>
       <c r="D1025" t="str">
         <v>AGRI REDUCER</v>
@@ -36272,13 +36272,13 @@
         <v>General</v>
       </c>
       <c r="G1025" t="str">
-        <v>63X50MM</v>
+        <v>63X40MM</v>
       </c>
       <c r="H1025" t="str">
         <v>BOX</v>
       </c>
       <c r="I1025">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="J1025" t="str">
         <v>Active</v>
@@ -36292,10 +36292,10 @@
         <v>1025</v>
       </c>
       <c r="B1026" t="str">
-        <v>FG-400582</v>
+        <v>FG-400583</v>
       </c>
       <c r="C1026" t="str">
-        <v>AGRI REDUCER (75X40MM)</v>
+        <v>AGRI REDUCER (63X50MM)</v>
       </c>
       <c r="D1026" t="str">
         <v>AGRI REDUCER</v>
@@ -36307,13 +36307,13 @@
         <v>General</v>
       </c>
       <c r="G1026" t="str">
-        <v>75X40MM</v>
+        <v>63X50MM</v>
       </c>
       <c r="H1026" t="str">
         <v>BOX</v>
       </c>
       <c r="I1026">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J1026" t="str">
         <v>Active</v>
@@ -36327,10 +36327,10 @@
         <v>1026</v>
       </c>
       <c r="B1027" t="str">
-        <v>FG-400581</v>
+        <v>FG-400582</v>
       </c>
       <c r="C1027" t="str">
-        <v>AGRI REDUCER (75X50MM)</v>
+        <v>AGRI REDUCER (75X40MM)</v>
       </c>
       <c r="D1027" t="str">
         <v>AGRI REDUCER</v>
@@ -36342,13 +36342,13 @@
         <v>General</v>
       </c>
       <c r="G1027" t="str">
-        <v>75X50MM</v>
+        <v>75X40MM</v>
       </c>
       <c r="H1027" t="str">
         <v>BOX</v>
       </c>
       <c r="I1027">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J1027" t="str">
         <v>Active</v>
@@ -36362,10 +36362,10 @@
         <v>1027</v>
       </c>
       <c r="B1028" t="str">
-        <v>FG-400580</v>
+        <v>FG-400581</v>
       </c>
       <c r="C1028" t="str">
-        <v>AGRI REDUCER (75X63MM)</v>
+        <v>AGRI REDUCER (75X50MM)</v>
       </c>
       <c r="D1028" t="str">
         <v>AGRI REDUCER</v>
@@ -36377,13 +36377,13 @@
         <v>General</v>
       </c>
       <c r="G1028" t="str">
-        <v>75X63MM</v>
+        <v>75X50MM</v>
       </c>
       <c r="H1028" t="str">
         <v>BOX</v>
       </c>
       <c r="I1028">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J1028" t="str">
         <v>Active</v>
@@ -36397,10 +36397,10 @@
         <v>1028</v>
       </c>
       <c r="B1029" t="str">
-        <v>FG-400579</v>
+        <v>FG-400580</v>
       </c>
       <c r="C1029" t="str">
-        <v>AGRI REDUCER (90X50MM)</v>
+        <v>AGRI REDUCER (75X63MM)</v>
       </c>
       <c r="D1029" t="str">
         <v>AGRI REDUCER</v>
@@ -36412,13 +36412,13 @@
         <v>General</v>
       </c>
       <c r="G1029" t="str">
-        <v>90X50MM</v>
+        <v>75X63MM</v>
       </c>
       <c r="H1029" t="str">
         <v>BOX</v>
       </c>
       <c r="I1029">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J1029" t="str">
         <v>Active</v>
@@ -36432,10 +36432,10 @@
         <v>1029</v>
       </c>
       <c r="B1030" t="str">
-        <v>FG-400578</v>
+        <v>FG-400579</v>
       </c>
       <c r="C1030" t="str">
-        <v>AGRI REDUCER (90X63MM)</v>
+        <v>AGRI REDUCER (90X50MM)</v>
       </c>
       <c r="D1030" t="str">
         <v>AGRI REDUCER</v>
@@ -36447,13 +36447,13 @@
         <v>General</v>
       </c>
       <c r="G1030" t="str">
-        <v>90X63MM</v>
+        <v>90X50MM</v>
       </c>
       <c r="H1030" t="str">
         <v>BOX</v>
       </c>
       <c r="I1030">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J1030" t="str">
         <v>Active</v>
@@ -36467,10 +36467,10 @@
         <v>1030</v>
       </c>
       <c r="B1031" t="str">
-        <v>FG-400577</v>
+        <v>FG-400578</v>
       </c>
       <c r="C1031" t="str">
-        <v>AGRI REDUCER (90X75MM)</v>
+        <v>AGRI REDUCER (90X63MM)</v>
       </c>
       <c r="D1031" t="str">
         <v>AGRI REDUCER</v>
@@ -36482,13 +36482,13 @@
         <v>General</v>
       </c>
       <c r="G1031" t="str">
-        <v>90X75MM</v>
+        <v>90X63MM</v>
       </c>
       <c r="H1031" t="str">
         <v>BOX</v>
       </c>
       <c r="I1031">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J1031" t="str">
         <v>Active</v>
@@ -36502,10 +36502,10 @@
         <v>1031</v>
       </c>
       <c r="B1032" t="str">
-        <v>FG-400576</v>
+        <v>FG-400577</v>
       </c>
       <c r="C1032" t="str">
-        <v>AGRI REDUCER (110X63MM)</v>
+        <v>AGRI REDUCER (90X75MM)</v>
       </c>
       <c r="D1032" t="str">
         <v>AGRI REDUCER</v>
@@ -36517,13 +36517,13 @@
         <v>General</v>
       </c>
       <c r="G1032" t="str">
-        <v>110X63MM</v>
+        <v>90X75MM</v>
       </c>
       <c r="H1032" t="str">
         <v>BOX</v>
       </c>
       <c r="I1032">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J1032" t="str">
         <v>Active</v>
@@ -36537,10 +36537,10 @@
         <v>1032</v>
       </c>
       <c r="B1033" t="str">
-        <v>FG-400575</v>
+        <v>FG-400576</v>
       </c>
       <c r="C1033" t="str">
-        <v>AGRI REDUCER (110X75MM)</v>
+        <v>AGRI REDUCER (110X63MM)</v>
       </c>
       <c r="D1033" t="str">
         <v>AGRI REDUCER</v>
@@ -36552,7 +36552,7 @@
         <v>General</v>
       </c>
       <c r="G1033" t="str">
-        <v>110X75MM</v>
+        <v>110X63MM</v>
       </c>
       <c r="H1033" t="str">
         <v>BOX</v>
@@ -36572,10 +36572,10 @@
         <v>1033</v>
       </c>
       <c r="B1034" t="str">
-        <v>FG-400574</v>
+        <v>FG-400575</v>
       </c>
       <c r="C1034" t="str">
-        <v>AGRI REDUCER (110X90MM)</v>
+        <v>AGRI REDUCER (110X75MM)</v>
       </c>
       <c r="D1034" t="str">
         <v>AGRI REDUCER</v>
@@ -36587,13 +36587,13 @@
         <v>General</v>
       </c>
       <c r="G1034" t="str">
-        <v>110X90MM</v>
+        <v>110X75MM</v>
       </c>
       <c r="H1034" t="str">
         <v>BOX</v>
       </c>
       <c r="I1034">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J1034" t="str">
         <v>Active</v>
@@ -36607,13 +36607,13 @@
         <v>1034</v>
       </c>
       <c r="B1035" t="str">
-        <v>-</v>
+        <v>FG-400574</v>
       </c>
       <c r="C1035" t="str">
-        <v>REDUCING BUSH (LW) (63 X 40)</v>
+        <v>AGRI REDUCER (110X90MM)</v>
       </c>
       <c r="D1035" t="str">
-        <v>REDUCING BUSH (LW)</v>
+        <v>AGRI REDUCER</v>
       </c>
       <c r="E1035" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36622,19 +36622,19 @@
         <v>General</v>
       </c>
       <c r="G1035" t="str">
-        <v>63 X 40</v>
+        <v>110X90MM</v>
       </c>
       <c r="H1035" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1035" t="str">
-        <v>-</v>
+      <c r="I1035">
+        <v>40</v>
       </c>
       <c r="J1035" t="str">
         <v>Active</v>
       </c>
       <c r="K1035" t="str">
-        <v>REDUCING BUSH (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
       </c>
     </row>
     <row r="1036">
@@ -36645,7 +36645,7 @@
         <v>-</v>
       </c>
       <c r="C1036" t="str">
-        <v>REDUCING BUSH (LW) (63 X 50)</v>
+        <v>REDUCING BUSH (LW) (63 X 40)</v>
       </c>
       <c r="D1036" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36657,7 +36657,7 @@
         <v>General</v>
       </c>
       <c r="G1036" t="str">
-        <v>63 X 50</v>
+        <v>63 X 40</v>
       </c>
       <c r="H1036" t="str">
         <v>BOX</v>
@@ -36680,7 +36680,7 @@
         <v>-</v>
       </c>
       <c r="C1037" t="str">
-        <v>REDUCING BUSH (LW) (75 X 40)</v>
+        <v>REDUCING BUSH (LW) (63 X 50)</v>
       </c>
       <c r="D1037" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36692,7 +36692,7 @@
         <v>General</v>
       </c>
       <c r="G1037" t="str">
-        <v>75 X 40</v>
+        <v>63 X 50</v>
       </c>
       <c r="H1037" t="str">
         <v>BOX</v>
@@ -36715,7 +36715,7 @@
         <v>-</v>
       </c>
       <c r="C1038" t="str">
-        <v>REDUCING BUSH (LW) (75 X 63)</v>
+        <v>REDUCING BUSH (LW) (75 X 40)</v>
       </c>
       <c r="D1038" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36727,7 +36727,7 @@
         <v>General</v>
       </c>
       <c r="G1038" t="str">
-        <v>75 X 63</v>
+        <v>75 X 40</v>
       </c>
       <c r="H1038" t="str">
         <v>BOX</v>
@@ -36750,7 +36750,7 @@
         <v>-</v>
       </c>
       <c r="C1039" t="str">
-        <v>REDUCING BUSH (LW) (90 X 50)</v>
+        <v>REDUCING BUSH (LW) (75 X 63)</v>
       </c>
       <c r="D1039" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36762,7 +36762,7 @@
         <v>General</v>
       </c>
       <c r="G1039" t="str">
-        <v>90 X 50</v>
+        <v>75 X 63</v>
       </c>
       <c r="H1039" t="str">
         <v>BOX</v>
@@ -36785,7 +36785,7 @@
         <v>-</v>
       </c>
       <c r="C1040" t="str">
-        <v>REDUCING BUSH (LW) (90 X 63)</v>
+        <v>REDUCING BUSH (LW) (90 X 50)</v>
       </c>
       <c r="D1040" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36797,7 +36797,7 @@
         <v>General</v>
       </c>
       <c r="G1040" t="str">
-        <v>90 X 63</v>
+        <v>90 X 50</v>
       </c>
       <c r="H1040" t="str">
         <v>BOX</v>
@@ -36820,7 +36820,7 @@
         <v>-</v>
       </c>
       <c r="C1041" t="str">
-        <v>REDUCING BUSH (LW) (90 X 75)</v>
+        <v>REDUCING BUSH (LW) (90 X 63)</v>
       </c>
       <c r="D1041" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36832,7 +36832,7 @@
         <v>General</v>
       </c>
       <c r="G1041" t="str">
-        <v>90 X 75</v>
+        <v>90 X 63</v>
       </c>
       <c r="H1041" t="str">
         <v>BOX</v>
@@ -36855,7 +36855,7 @@
         <v>-</v>
       </c>
       <c r="C1042" t="str">
-        <v>REDUCING BUSH (LW) (110 X 63)</v>
+        <v>REDUCING BUSH (LW) (90 X 75)</v>
       </c>
       <c r="D1042" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36867,7 +36867,7 @@
         <v>General</v>
       </c>
       <c r="G1042" t="str">
-        <v>110 X 63</v>
+        <v>90 X 75</v>
       </c>
       <c r="H1042" t="str">
         <v>BOX</v>
@@ -36890,7 +36890,7 @@
         <v>-</v>
       </c>
       <c r="C1043" t="str">
-        <v>REDUCING BUSH (LW) (110 X 75)</v>
+        <v>REDUCING BUSH (LW) (110 X 63)</v>
       </c>
       <c r="D1043" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36902,7 +36902,7 @@
         <v>General</v>
       </c>
       <c r="G1043" t="str">
-        <v>110 X 75</v>
+        <v>110 X 63</v>
       </c>
       <c r="H1043" t="str">
         <v>BOX</v>
@@ -36925,7 +36925,7 @@
         <v>-</v>
       </c>
       <c r="C1044" t="str">
-        <v>REDUCING BUSH (LW) (110 X 90)</v>
+        <v>REDUCING BUSH (LW) (110 X 75)</v>
       </c>
       <c r="D1044" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36937,7 +36937,7 @@
         <v>General</v>
       </c>
       <c r="G1044" t="str">
-        <v>110 X 90</v>
+        <v>110 X 75</v>
       </c>
       <c r="H1044" t="str">
         <v>BOX</v>
@@ -36957,13 +36957,13 @@
         <v>1044</v>
       </c>
       <c r="B1045" t="str">
-        <v>FG-400550</v>
+        <v>-</v>
       </c>
       <c r="C1045" t="str">
-        <v>AGRI TEE (40MM)</v>
+        <v>REDUCING BUSH (LW) (110 X 90)</v>
       </c>
       <c r="D1045" t="str">
-        <v>AGRI TEE</v>
+        <v>REDUCING BUSH (LW)</v>
       </c>
       <c r="E1045" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36972,19 +36972,19 @@
         <v>General</v>
       </c>
       <c r="G1045" t="str">
-        <v>40MM</v>
+        <v>110 X 90</v>
       </c>
       <c r="H1045" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1045">
-        <v>150</v>
+      <c r="I1045" t="str">
+        <v>-</v>
       </c>
       <c r="J1045" t="str">
         <v>Active</v>
       </c>
       <c r="K1045" t="str">
-        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
+        <v>REDUCING BUSH (LW) for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1046">
@@ -36992,10 +36992,10 @@
         <v>1045</v>
       </c>
       <c r="B1046" t="str">
-        <v>FG-400551</v>
+        <v>FG-400550</v>
       </c>
       <c r="C1046" t="str">
-        <v>AGRI TEE (50MM)</v>
+        <v>AGRI TEE (40MM)</v>
       </c>
       <c r="D1046" t="str">
         <v>AGRI TEE</v>
@@ -37007,13 +37007,13 @@
         <v>General</v>
       </c>
       <c r="G1046" t="str">
-        <v>50MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1046" t="str">
         <v>BOX</v>
       </c>
       <c r="I1046">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J1046" t="str">
         <v>Active</v>
@@ -37027,10 +37027,10 @@
         <v>1046</v>
       </c>
       <c r="B1047" t="str">
-        <v>FG-400552</v>
+        <v>FG-400551</v>
       </c>
       <c r="C1047" t="str">
-        <v>AGRI TEE (63MM)</v>
+        <v>AGRI TEE (50MM)</v>
       </c>
       <c r="D1047" t="str">
         <v>AGRI TEE</v>
@@ -37042,13 +37042,13 @@
         <v>General</v>
       </c>
       <c r="G1047" t="str">
-        <v>63MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1047" t="str">
         <v>BOX</v>
       </c>
       <c r="I1047">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="J1047" t="str">
         <v>Active</v>
@@ -37062,10 +37062,10 @@
         <v>1047</v>
       </c>
       <c r="B1048" t="str">
-        <v>FG-400553</v>
+        <v>FG-400552</v>
       </c>
       <c r="C1048" t="str">
-        <v>AGRI TEE (75MM)</v>
+        <v>AGRI TEE (63MM)</v>
       </c>
       <c r="D1048" t="str">
         <v>AGRI TEE</v>
@@ -37077,13 +37077,13 @@
         <v>General</v>
       </c>
       <c r="G1048" t="str">
-        <v>75MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1048" t="str">
         <v>BOX</v>
       </c>
       <c r="I1048">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="J1048" t="str">
         <v>Active</v>
@@ -37097,10 +37097,10 @@
         <v>1048</v>
       </c>
       <c r="B1049" t="str">
-        <v>FG-400554</v>
+        <v>FG-400553</v>
       </c>
       <c r="C1049" t="str">
-        <v>AGRI TEE (90MM)</v>
+        <v>AGRI TEE (75MM)</v>
       </c>
       <c r="D1049" t="str">
         <v>AGRI TEE</v>
@@ -37112,13 +37112,13 @@
         <v>General</v>
       </c>
       <c r="G1049" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1049" t="str">
         <v>BOX</v>
       </c>
       <c r="I1049">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J1049" t="str">
         <v>Active</v>
@@ -37132,10 +37132,10 @@
         <v>1049</v>
       </c>
       <c r="B1050" t="str">
-        <v>FG-400586</v>
+        <v>FG-400554</v>
       </c>
       <c r="C1050" t="str">
-        <v>AGRI TEE (110MM)</v>
+        <v>AGRI TEE (90MM)</v>
       </c>
       <c r="D1050" t="str">
         <v>AGRI TEE</v>
@@ -37147,13 +37147,13 @@
         <v>General</v>
       </c>
       <c r="G1050" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1050" t="str">
         <v>BOX</v>
       </c>
       <c r="I1050">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J1050" t="str">
         <v>Active</v>
@@ -37167,10 +37167,10 @@
         <v>1050</v>
       </c>
       <c r="B1051" t="str">
-        <v>FG-400607</v>
+        <v>FG-400586</v>
       </c>
       <c r="C1051" t="str">
-        <v>AGRI TEE (140MM)</v>
+        <v>AGRI TEE (110MM)</v>
       </c>
       <c r="D1051" t="str">
         <v>AGRI TEE</v>
@@ -37182,13 +37182,13 @@
         <v>General</v>
       </c>
       <c r="G1051" t="str">
-        <v>140MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1051" t="str">
         <v>BOX</v>
       </c>
       <c r="I1051">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="J1051" t="str">
         <v>Active</v>
@@ -37202,10 +37202,10 @@
         <v>1051</v>
       </c>
       <c r="B1052" t="str">
-        <v>FG-400608</v>
+        <v>FG-400607</v>
       </c>
       <c r="C1052" t="str">
-        <v>AGRI TEE (160MM)</v>
+        <v>AGRI TEE (140MM)</v>
       </c>
       <c r="D1052" t="str">
         <v>AGRI TEE</v>
@@ -37217,13 +37217,13 @@
         <v>General</v>
       </c>
       <c r="G1052" t="str">
-        <v>160MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1052" t="str">
         <v>BOX</v>
       </c>
       <c r="I1052">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J1052" t="str">
         <v>Active</v>
@@ -37237,13 +37237,13 @@
         <v>1052</v>
       </c>
       <c r="B1053" t="str">
-        <v>-</v>
+        <v>FG-400608</v>
       </c>
       <c r="C1053" t="str">
-        <v>COUPLER (LW) (75MM)</v>
+        <v>AGRI TEE (160MM)</v>
       </c>
       <c r="D1053" t="str">
-        <v>COUPLER (LW)</v>
+        <v>AGRI TEE</v>
       </c>
       <c r="E1053" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37252,19 +37252,19 @@
         <v>General</v>
       </c>
       <c r="G1053" t="str">
-        <v>75MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1053" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1053" t="str">
-        <v>-</v>
+      <c r="I1053">
+        <v>9</v>
       </c>
       <c r="J1053" t="str">
         <v>Active</v>
       </c>
       <c r="K1053" t="str">
-        <v>COUPLER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1054">
@@ -37275,7 +37275,7 @@
         <v>-</v>
       </c>
       <c r="C1054" t="str">
-        <v>COUPLER (LW) (90MM)</v>
+        <v>COUPLER (LW) (75MM)</v>
       </c>
       <c r="D1054" t="str">
         <v>COUPLER (LW)</v>
@@ -37287,7 +37287,7 @@
         <v>General</v>
       </c>
       <c r="G1054" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1054" t="str">
         <v>BOX</v>
@@ -37310,7 +37310,7 @@
         <v>-</v>
       </c>
       <c r="C1055" t="str">
-        <v>COUPLER (LW) (110MM)</v>
+        <v>COUPLER (LW) (90MM)</v>
       </c>
       <c r="D1055" t="str">
         <v>COUPLER (LW)</v>
@@ -37322,7 +37322,7 @@
         <v>General</v>
       </c>
       <c r="G1055" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1055" t="str">
         <v>BOX</v>
@@ -37342,13 +37342,13 @@
         <v>1055</v>
       </c>
       <c r="B1056" t="str">
-        <v>FG-400561</v>
+        <v>-</v>
       </c>
       <c r="C1056" t="str">
-        <v>AGRI FABRICATED COUPLER (40MM)</v>
+        <v>COUPLER (LW) (110MM)</v>
       </c>
       <c r="D1056" t="str">
-        <v>AGRI FABRICATED COUPLER</v>
+        <v>COUPLER (LW)</v>
       </c>
       <c r="E1056" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37357,19 +37357,19 @@
         <v>General</v>
       </c>
       <c r="G1056" t="str">
-        <v>40MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1056" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1056">
-        <v>300</v>
+      <c r="I1056" t="str">
+        <v>-</v>
       </c>
       <c r="J1056" t="str">
         <v>Active</v>
       </c>
       <c r="K1056" t="str">
-        <v>AGRI FABRICATED COUPLER for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
+        <v>COUPLER (LW) for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1057">
@@ -37377,10 +37377,10 @@
         <v>1056</v>
       </c>
       <c r="B1057" t="str">
-        <v>FG-400562</v>
+        <v>FG-400561</v>
       </c>
       <c r="C1057" t="str">
-        <v>AGRI FABRICATED COUPLER (50MM)</v>
+        <v>AGRI FABRICATED COUPLER (40MM)</v>
       </c>
       <c r="D1057" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37392,13 +37392,13 @@
         <v>General</v>
       </c>
       <c r="G1057" t="str">
-        <v>50MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1057" t="str">
         <v>BOX</v>
       </c>
       <c r="I1057">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J1057" t="str">
         <v>Active</v>
@@ -37412,10 +37412,10 @@
         <v>1057</v>
       </c>
       <c r="B1058" t="str">
-        <v>FG-400563</v>
+        <v>FG-400562</v>
       </c>
       <c r="C1058" t="str">
-        <v>AGRI FABRICATED COUPLER (63MM)</v>
+        <v>AGRI FABRICATED COUPLER (50MM)</v>
       </c>
       <c r="D1058" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37427,7 +37427,7 @@
         <v>General</v>
       </c>
       <c r="G1058" t="str">
-        <v>63MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1058" t="str">
         <v>BOX</v>
@@ -37447,10 +37447,10 @@
         <v>1058</v>
       </c>
       <c r="B1059" t="str">
-        <v>FG-400564</v>
+        <v>FG-400563</v>
       </c>
       <c r="C1059" t="str">
-        <v>AGRI FABRICATED COUPLER (75MM)</v>
+        <v>AGRI FABRICATED COUPLER (63MM)</v>
       </c>
       <c r="D1059" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37462,13 +37462,13 @@
         <v>General</v>
       </c>
       <c r="G1059" t="str">
-        <v>75MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1059" t="str">
         <v>BOX</v>
       </c>
       <c r="I1059">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="J1059" t="str">
         <v>Active</v>
@@ -37482,10 +37482,10 @@
         <v>1059</v>
       </c>
       <c r="B1060" t="str">
-        <v>FG-400565</v>
+        <v>FG-400564</v>
       </c>
       <c r="C1060" t="str">
-        <v>AGRI FABRICATED COUPLER (90MM)</v>
+        <v>AGRI FABRICATED COUPLER (75MM)</v>
       </c>
       <c r="D1060" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37497,13 +37497,13 @@
         <v>General</v>
       </c>
       <c r="G1060" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1060" t="str">
         <v>BOX</v>
       </c>
       <c r="I1060">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="J1060" t="str">
         <v>Active</v>
@@ -37517,10 +37517,10 @@
         <v>1060</v>
       </c>
       <c r="B1061" t="str">
-        <v>FG-400566</v>
+        <v>FG-400565</v>
       </c>
       <c r="C1061" t="str">
-        <v>AGRI FABRICATED COUPLER (110MM)</v>
+        <v>AGRI FABRICATED COUPLER (90MM)</v>
       </c>
       <c r="D1061" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37532,13 +37532,13 @@
         <v>General</v>
       </c>
       <c r="G1061" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1061" t="str">
         <v>BOX</v>
       </c>
       <c r="I1061">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J1061" t="str">
         <v>Active</v>
@@ -37552,10 +37552,10 @@
         <v>1061</v>
       </c>
       <c r="B1062" t="str">
-        <v>FG-400587</v>
+        <v>FG-400566</v>
       </c>
       <c r="C1062" t="str">
-        <v>AGRI FABRICATED COUPLER (140MM 4KG)</v>
+        <v>AGRI FABRICATED COUPLER (110MM)</v>
       </c>
       <c r="D1062" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37567,13 +37567,13 @@
         <v>General</v>
       </c>
       <c r="G1062" t="str">
-        <v>140MM 4KG</v>
+        <v>110MM</v>
       </c>
       <c r="H1062" t="str">
         <v>BOX</v>
       </c>
       <c r="I1062">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J1062" t="str">
         <v>Active</v>
@@ -37587,10 +37587,10 @@
         <v>1062</v>
       </c>
       <c r="B1063" t="str">
-        <v>FG-400568</v>
+        <v>FG-400587</v>
       </c>
       <c r="C1063" t="str">
-        <v>AGRI FABRICATED COUPLER (160MM 4KG)</v>
+        <v>AGRI FABRICATED COUPLER (140MM 4KG)</v>
       </c>
       <c r="D1063" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37602,13 +37602,13 @@
         <v>General</v>
       </c>
       <c r="G1063" t="str">
-        <v>160MM 4KG</v>
+        <v>140MM 4KG</v>
       </c>
       <c r="H1063" t="str">
         <v>BOX</v>
       </c>
       <c r="I1063">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J1063" t="str">
         <v>Active</v>
@@ -37622,13 +37622,13 @@
         <v>1063</v>
       </c>
       <c r="B1064" t="str">
-        <v>FG-400567</v>
+        <v>FG-400568</v>
       </c>
       <c r="C1064" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG (140MM)</v>
+        <v>AGRI FABRICATED COUPLER (160MM 4KG)</v>
       </c>
       <c r="D1064" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG</v>
+        <v>AGRI FABRICATED COUPLER</v>
       </c>
       <c r="E1064" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37637,19 +37637,19 @@
         <v>General</v>
       </c>
       <c r="G1064" t="str">
-        <v>140MM</v>
+        <v>160MM 4KG</v>
       </c>
       <c r="H1064" t="str">
         <v>BOX</v>
       </c>
       <c r="I1064">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J1064" t="str">
         <v>Active</v>
       </c>
       <c r="K1064" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG for agriculture irrigation and piping systems. Available sizes: 140MM, 160MM.</v>
+        <v>AGRI FABRICATED COUPLER for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1065">
@@ -37657,10 +37657,10 @@
         <v>1064</v>
       </c>
       <c r="B1065" t="str">
-        <v>FG-400569</v>
+        <v>FG-400567</v>
       </c>
       <c r="C1065" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG (160MM)</v>
+        <v>AGRI FABRICATED COUPLER 6KG (140MM)</v>
       </c>
       <c r="D1065" t="str">
         <v>AGRI FABRICATED COUPLER 6KG</v>
@@ -37672,13 +37672,13 @@
         <v>General</v>
       </c>
       <c r="G1065" t="str">
-        <v>160MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1065" t="str">
         <v>BOX</v>
       </c>
       <c r="I1065">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J1065" t="str">
         <v>Active</v>
@@ -37692,13 +37692,13 @@
         <v>1065</v>
       </c>
       <c r="B1066" t="str">
-        <v>FG-400544</v>
+        <v>FG-400569</v>
       </c>
       <c r="C1066" t="str">
-        <v>AGRI ELBOW (40MM)</v>
+        <v>AGRI FABRICATED COUPLER 6KG (160MM)</v>
       </c>
       <c r="D1066" t="str">
-        <v>AGRI ELBOW</v>
+        <v>AGRI FABRICATED COUPLER 6KG</v>
       </c>
       <c r="E1066" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37707,19 +37707,19 @@
         <v>General</v>
       </c>
       <c r="G1066" t="str">
-        <v>40MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1066" t="str">
         <v>BOX</v>
       </c>
       <c r="I1066">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="J1066" t="str">
         <v>Active</v>
       </c>
       <c r="K1066" t="str">
-        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
+        <v>AGRI FABRICATED COUPLER 6KG for agriculture irrigation and piping systems. Available sizes: 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1067">
@@ -37727,10 +37727,10 @@
         <v>1066</v>
       </c>
       <c r="B1067" t="str">
-        <v>FG-400545</v>
+        <v>FG-400544</v>
       </c>
       <c r="C1067" t="str">
-        <v>AGRI ELBOW (50MM)</v>
+        <v>AGRI ELBOW (40MM)</v>
       </c>
       <c r="D1067" t="str">
         <v>AGRI ELBOW</v>
@@ -37742,13 +37742,13 @@
         <v>General</v>
       </c>
       <c r="G1067" t="str">
-        <v>50MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1067" t="str">
         <v>BOX</v>
       </c>
       <c r="I1067">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="J1067" t="str">
         <v>Active</v>
@@ -37762,10 +37762,10 @@
         <v>1067</v>
       </c>
       <c r="B1068" t="str">
-        <v>FG-400546</v>
+        <v>FG-400545</v>
       </c>
       <c r="C1068" t="str">
-        <v>AGRI ELBOW (63MM)</v>
+        <v>AGRI ELBOW (50MM)</v>
       </c>
       <c r="D1068" t="str">
         <v>AGRI ELBOW</v>
@@ -37777,13 +37777,13 @@
         <v>General</v>
       </c>
       <c r="G1068" t="str">
-        <v>63MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1068" t="str">
         <v>BOX</v>
       </c>
       <c r="I1068">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J1068" t="str">
         <v>Active</v>
@@ -37797,10 +37797,10 @@
         <v>1068</v>
       </c>
       <c r="B1069" t="str">
-        <v>FG-400547</v>
+        <v>FG-400546</v>
       </c>
       <c r="C1069" t="str">
-        <v>AGRI ELBOW (75MM)</v>
+        <v>AGRI ELBOW (63MM)</v>
       </c>
       <c r="D1069" t="str">
         <v>AGRI ELBOW</v>
@@ -37812,13 +37812,13 @@
         <v>General</v>
       </c>
       <c r="G1069" t="str">
-        <v>75MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1069" t="str">
         <v>BOX</v>
       </c>
       <c r="I1069">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J1069" t="str">
         <v>Active</v>
@@ -37832,10 +37832,10 @@
         <v>1069</v>
       </c>
       <c r="B1070" t="str">
-        <v>FG-400548</v>
+        <v>FG-400547</v>
       </c>
       <c r="C1070" t="str">
-        <v>AGRI ELBOW (90MM)</v>
+        <v>AGRI ELBOW (75MM)</v>
       </c>
       <c r="D1070" t="str">
         <v>AGRI ELBOW</v>
@@ -37847,13 +37847,13 @@
         <v>General</v>
       </c>
       <c r="G1070" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1070" t="str">
         <v>BOX</v>
       </c>
       <c r="I1070">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J1070" t="str">
         <v>Active</v>
@@ -37867,10 +37867,10 @@
         <v>1070</v>
       </c>
       <c r="B1071" t="str">
-        <v>FG-400549</v>
+        <v>FG-400548</v>
       </c>
       <c r="C1071" t="str">
-        <v>AGRI ELBOW (110MM)</v>
+        <v>AGRI ELBOW (90MM)</v>
       </c>
       <c r="D1071" t="str">
         <v>AGRI ELBOW</v>
@@ -37882,13 +37882,13 @@
         <v>General</v>
       </c>
       <c r="G1071" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1071" t="str">
         <v>BOX</v>
       </c>
       <c r="I1071">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="J1071" t="str">
         <v>Active</v>
@@ -37902,10 +37902,10 @@
         <v>1071</v>
       </c>
       <c r="B1072" t="str">
-        <v>FG-400595</v>
+        <v>FG-400549</v>
       </c>
       <c r="C1072" t="str">
-        <v>AGRI ELBOW (140MM)</v>
+        <v>AGRI ELBOW (110MM)</v>
       </c>
       <c r="D1072" t="str">
         <v>AGRI ELBOW</v>
@@ -37917,13 +37917,13 @@
         <v>General</v>
       </c>
       <c r="G1072" t="str">
-        <v>140MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1072" t="str">
         <v>BOX</v>
       </c>
       <c r="I1072">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="J1072" t="str">
         <v>Active</v>
@@ -37937,10 +37937,10 @@
         <v>1072</v>
       </c>
       <c r="B1073" t="str">
-        <v>FG-400596</v>
+        <v>FG-400595</v>
       </c>
       <c r="C1073" t="str">
-        <v>AGRI ELBOW (160MM)</v>
+        <v>AGRI ELBOW (140MM)</v>
       </c>
       <c r="D1073" t="str">
         <v>AGRI ELBOW</v>
@@ -37952,13 +37952,13 @@
         <v>General</v>
       </c>
       <c r="G1073" t="str">
-        <v>160MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1073" t="str">
         <v>BOX</v>
       </c>
       <c r="I1073">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J1073" t="str">
         <v>Active</v>
@@ -37972,13 +37972,13 @@
         <v>1073</v>
       </c>
       <c r="B1074" t="str">
-        <v>FG-400555</v>
+        <v>FG-400596</v>
       </c>
       <c r="C1074" t="str">
-        <v>AGRI END CAP (40MM)</v>
+        <v>AGRI ELBOW (160MM)</v>
       </c>
       <c r="D1074" t="str">
-        <v>AGRI END CAP</v>
+        <v>AGRI ELBOW</v>
       </c>
       <c r="E1074" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37987,19 +37987,19 @@
         <v>General</v>
       </c>
       <c r="G1074" t="str">
-        <v>40MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1074" t="str">
         <v>BOX</v>
       </c>
       <c r="I1074">
-        <v>800</v>
+        <v>12</v>
       </c>
       <c r="J1074" t="str">
         <v>Active</v>
       </c>
       <c r="K1074" t="str">
-        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
+        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1075">
@@ -38007,10 +38007,10 @@
         <v>1074</v>
       </c>
       <c r="B1075" t="str">
-        <v>FG-400556</v>
+        <v>FG-400555</v>
       </c>
       <c r="C1075" t="str">
-        <v>AGRI END CAP (50MM)</v>
+        <v>AGRI END CAP (40MM)</v>
       </c>
       <c r="D1075" t="str">
         <v>AGRI END CAP</v>
@@ -38022,13 +38022,13 @@
         <v>General</v>
       </c>
       <c r="G1075" t="str">
-        <v>50MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1075" t="str">
         <v>BOX</v>
       </c>
       <c r="I1075">
-        <v>450</v>
+        <v>800</v>
       </c>
       <c r="J1075" t="str">
         <v>Active</v>
@@ -38042,10 +38042,10 @@
         <v>1075</v>
       </c>
       <c r="B1076" t="str">
-        <v>FG-400557</v>
+        <v>FG-400556</v>
       </c>
       <c r="C1076" t="str">
-        <v>AGRI END CAP (63MM)</v>
+        <v>AGRI END CAP (50MM)</v>
       </c>
       <c r="D1076" t="str">
         <v>AGRI END CAP</v>
@@ -38057,13 +38057,13 @@
         <v>General</v>
       </c>
       <c r="G1076" t="str">
-        <v>63MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1076" t="str">
         <v>BOX</v>
       </c>
       <c r="I1076">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="J1076" t="str">
         <v>Active</v>
@@ -38077,10 +38077,10 @@
         <v>1076</v>
       </c>
       <c r="B1077" t="str">
-        <v>FG-400558</v>
+        <v>FG-400557</v>
       </c>
       <c r="C1077" t="str">
-        <v>AGRI END CAP (75MM)</v>
+        <v>AGRI END CAP (63MM)</v>
       </c>
       <c r="D1077" t="str">
         <v>AGRI END CAP</v>
@@ -38092,13 +38092,13 @@
         <v>General</v>
       </c>
       <c r="G1077" t="str">
-        <v>75MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1077" t="str">
         <v>BOX</v>
       </c>
       <c r="I1077">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="J1077" t="str">
         <v>Active</v>
@@ -38112,10 +38112,10 @@
         <v>1077</v>
       </c>
       <c r="B1078" t="str">
-        <v>FG-400559</v>
+        <v>FG-400558</v>
       </c>
       <c r="C1078" t="str">
-        <v>AGRI END CAP (90MM)</v>
+        <v>AGRI END CAP (75MM)</v>
       </c>
       <c r="D1078" t="str">
         <v>AGRI END CAP</v>
@@ -38127,13 +38127,13 @@
         <v>General</v>
       </c>
       <c r="G1078" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1078" t="str">
         <v>BOX</v>
       </c>
       <c r="I1078">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J1078" t="str">
         <v>Active</v>
@@ -38147,10 +38147,10 @@
         <v>1078</v>
       </c>
       <c r="B1079" t="str">
-        <v>FG-400560</v>
+        <v>FG-400559</v>
       </c>
       <c r="C1079" t="str">
-        <v>AGRI END CAP (110MM)</v>
+        <v>AGRI END CAP (90MM)</v>
       </c>
       <c r="D1079" t="str">
         <v>AGRI END CAP</v>
@@ -38162,13 +38162,13 @@
         <v>General</v>
       </c>
       <c r="G1079" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1079" t="str">
         <v>BOX</v>
       </c>
       <c r="I1079">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J1079" t="str">
         <v>Active</v>
@@ -38182,10 +38182,10 @@
         <v>1079</v>
       </c>
       <c r="B1080" t="str">
-        <v>FG-400639</v>
+        <v>FG-400560</v>
       </c>
       <c r="C1080" t="str">
-        <v>AGRI END CAP (140MM 4KG)</v>
+        <v>AGRI END CAP (110MM)</v>
       </c>
       <c r="D1080" t="str">
         <v>AGRI END CAP</v>
@@ -38197,13 +38197,13 @@
         <v>General</v>
       </c>
       <c r="G1080" t="str">
-        <v>140MM 4KG</v>
+        <v>110MM</v>
       </c>
       <c r="H1080" t="str">
         <v>BOX</v>
       </c>
       <c r="I1080">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J1080" t="str">
         <v>Active</v>
@@ -38217,10 +38217,10 @@
         <v>1080</v>
       </c>
       <c r="B1081" t="str">
-        <v>FG-400640</v>
+        <v>FG-400639</v>
       </c>
       <c r="C1081" t="str">
-        <v>AGRI END CAP (160MM 4KG)</v>
+        <v>AGRI END CAP (140MM 4KG)</v>
       </c>
       <c r="D1081" t="str">
         <v>AGRI END CAP</v>
@@ -38232,13 +38232,13 @@
         <v>General</v>
       </c>
       <c r="G1081" t="str">
-        <v>160MM 4KG</v>
+        <v>140MM 4KG</v>
       </c>
       <c r="H1081" t="str">
         <v>BOX</v>
       </c>
       <c r="I1081">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J1081" t="str">
         <v>Active</v>
@@ -38252,13 +38252,13 @@
         <v>1081</v>
       </c>
       <c r="B1082" t="str">
-        <v>FG-400570</v>
+        <v>FG-400640</v>
       </c>
       <c r="C1082" t="str">
-        <v>AGRI LONG BEND (63MM)</v>
+        <v>AGRI END CAP (160MM 4KG)</v>
       </c>
       <c r="D1082" t="str">
-        <v>AGRI LONG BEND</v>
+        <v>AGRI END CAP</v>
       </c>
       <c r="E1082" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -38267,19 +38267,19 @@
         <v>General</v>
       </c>
       <c r="G1082" t="str">
-        <v>63MM</v>
+        <v>160MM 4KG</v>
       </c>
       <c r="H1082" t="str">
         <v>BOX</v>
       </c>
       <c r="I1082">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="J1082" t="str">
         <v>Active</v>
       </c>
       <c r="K1082" t="str">
-        <v>AGRI LONG BEND for agriculture irrigation and piping systems. Available sizes: 63MM, 75MM, 90MM, 110MM.</v>
+        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1083">
@@ -38287,10 +38287,10 @@
         <v>1082</v>
       </c>
       <c r="B1083" t="str">
-        <v>FG-400571</v>
+        <v>FG-400570</v>
       </c>
       <c r="C1083" t="str">
-        <v>AGRI LONG BEND (75MM)</v>
+        <v>AGRI LONG BEND (63MM)</v>
       </c>
       <c r="D1083" t="str">
         <v>AGRI LONG BEND</v>
@@ -38302,13 +38302,13 @@
         <v>General</v>
       </c>
       <c r="G1083" t="str">
-        <v>75MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1083" t="str">
         <v>BOX</v>
       </c>
       <c r="I1083">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J1083" t="str">
         <v>Active</v>
@@ -38322,10 +38322,10 @@
         <v>1083</v>
       </c>
       <c r="B1084" t="str">
-        <v>FG-400572</v>
+        <v>FG-400571</v>
       </c>
       <c r="C1084" t="str">
-        <v>AGRI LONG BEND (90MM)</v>
+        <v>AGRI LONG BEND (75MM)</v>
       </c>
       <c r="D1084" t="str">
         <v>AGRI LONG BEND</v>
@@ -38337,13 +38337,13 @@
         <v>General</v>
       </c>
       <c r="G1084" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1084" t="str">
         <v>BOX</v>
       </c>
       <c r="I1084">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J1084" t="str">
         <v>Active</v>
@@ -38357,10 +38357,10 @@
         <v>1084</v>
       </c>
       <c r="B1085" t="str">
-        <v>FG-400573</v>
+        <v>FG-400572</v>
       </c>
       <c r="C1085" t="str">
-        <v>AGRI LONG BEND (110MM)</v>
+        <v>AGRI LONG BEND (90MM)</v>
       </c>
       <c r="D1085" t="str">
         <v>AGRI LONG BEND</v>
@@ -38372,13 +38372,13 @@
         <v>General</v>
       </c>
       <c r="G1085" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1085" t="str">
         <v>BOX</v>
       </c>
       <c r="I1085">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J1085" t="str">
         <v>Active</v>
@@ -38392,34 +38392,34 @@
         <v>1085</v>
       </c>
       <c r="B1086" t="str">
-        <v>FG-401520</v>
+        <v>FG-400573</v>
       </c>
       <c r="C1086" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
+        <v>AGRI LONG BEND (110MM)</v>
       </c>
       <c r="D1086" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR</v>
+        <v>AGRI LONG BEND</v>
       </c>
       <c r="E1086" t="str">
-        <v>Sprinkler Pipes &amp; Fittings</v>
+        <v>Agriculture Pipes &amp; Fittings</v>
       </c>
       <c r="F1086" t="str">
         <v>General</v>
       </c>
       <c r="G1086" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>110MM</v>
       </c>
       <c r="H1086" t="str">
-        <v>Nos</v>
-      </c>
-      <c r="I1086" t="str">
-        <v>-</v>
+        <v>BOX</v>
+      </c>
+      <c r="I1086">
+        <v>10</v>
       </c>
       <c r="J1086" t="str">
         <v>Active</v>
       </c>
       <c r="K1086" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR for sprinkler irrigation systems.</v>
+        <v>AGRI LONG BEND for agriculture irrigation and piping systems. Available sizes: 63MM, 75MM, 90MM, 110MM.</v>
       </c>
     </row>
     <row r="1087">
@@ -38427,10 +38427,10 @@
         <v>1086</v>
       </c>
       <c r="B1087" t="str">
-        <v>FG-401491</v>
+        <v>FG-401520</v>
       </c>
       <c r="C1087" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (63MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1087" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38442,7 +38442,7 @@
         <v>General</v>
       </c>
       <c r="G1087" t="str">
-        <v>63MM L TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1087" t="str">
         <v>Nos</v>
@@ -38462,10 +38462,10 @@
         <v>1087</v>
       </c>
       <c r="B1088" t="str">
-        <v>FG-401490</v>
+        <v>FG-401491</v>
       </c>
       <c r="C1088" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 2.5 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (63MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1088" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38477,7 +38477,7 @@
         <v>General</v>
       </c>
       <c r="G1088" t="str">
-        <v>75MM C TYPE 2.5 KG</v>
+        <v>63MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1088" t="str">
         <v>Nos</v>
@@ -38497,10 +38497,10 @@
         <v>1088</v>
       </c>
       <c r="B1089" t="str">
-        <v>FG-401492</v>
+        <v>FG-401490</v>
       </c>
       <c r="C1089" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 2.5 KG)</v>
       </c>
       <c r="D1089" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38512,7 +38512,7 @@
         <v>General</v>
       </c>
       <c r="G1089" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>75MM C TYPE 2.5 KG</v>
       </c>
       <c r="H1089" t="str">
         <v>Nos</v>
@@ -38532,10 +38532,10 @@
         <v>1089</v>
       </c>
       <c r="B1090" t="str">
-        <v>FG-401519</v>
+        <v>FG-401492</v>
       </c>
       <c r="C1090" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 2.5 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1090" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38547,7 +38547,7 @@
         <v>General</v>
       </c>
       <c r="G1090" t="str">
-        <v>75MM L TYPE 2.5 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1090" t="str">
         <v>Nos</v>
@@ -38567,10 +38567,10 @@
         <v>1090</v>
       </c>
       <c r="B1091" t="str">
-        <v>FG-401521</v>
+        <v>FG-401519</v>
       </c>
       <c r="C1091" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 2.5 KG)</v>
       </c>
       <c r="D1091" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38582,7 +38582,7 @@
         <v>General</v>
       </c>
       <c r="G1091" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 2.5 KG</v>
       </c>
       <c r="H1091" t="str">
         <v>Nos</v>
@@ -38602,13 +38602,13 @@
         <v>1091</v>
       </c>
       <c r="B1092" t="str">
-        <v>FG-401522</v>
+        <v>FG-401521</v>
       </c>
       <c r="C1092" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1092" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR</v>
+        <v>SPRINKLER ISI PIPE 6 MTR</v>
       </c>
       <c r="E1092" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38629,7 +38629,7 @@
         <v>Active</v>
       </c>
       <c r="K1092" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER ISI PIPE 6 MTR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1093">
@@ -38637,10 +38637,10 @@
         <v>1092</v>
       </c>
       <c r="B1093" t="str">
-        <v>FG-401523</v>
+        <v>FG-401522</v>
       </c>
       <c r="C1093" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1093" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38652,7 +38652,7 @@
         <v>General</v>
       </c>
       <c r="G1093" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1093" t="str">
         <v>Nos</v>
@@ -38672,10 +38672,10 @@
         <v>1093</v>
       </c>
       <c r="B1094" t="str">
-        <v>FG-401866</v>
+        <v>FG-401523</v>
       </c>
       <c r="C1094" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (90MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1094" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38687,7 +38687,7 @@
         <v>General</v>
       </c>
       <c r="G1094" t="str">
-        <v>90MM C TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1094" t="str">
         <v>Nos</v>
@@ -38707,10 +38707,10 @@
         <v>1094</v>
       </c>
       <c r="B1095" t="str">
-        <v>FG-401867</v>
+        <v>FG-401866</v>
       </c>
       <c r="C1095" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (90MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (90MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1095" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38722,7 +38722,7 @@
         <v>General</v>
       </c>
       <c r="G1095" t="str">
-        <v>90MM L TYPE 3.2 KG</v>
+        <v>90MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1095" t="str">
         <v>Nos</v>
@@ -38742,13 +38742,13 @@
         <v>1095</v>
       </c>
       <c r="B1096" t="str">
-        <v>FG-401498</v>
+        <v>FG-401867</v>
       </c>
       <c r="C1096" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (90MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1096" t="str">
-        <v>SPRINKLER SET 6 MTR ISI</v>
+        <v>SPRINKLER NISI PIPE 6 MTR</v>
       </c>
       <c r="E1096" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38757,7 +38757,7 @@
         <v>General</v>
       </c>
       <c r="G1096" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>90MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1096" t="str">
         <v>Nos</v>
@@ -38769,7 +38769,7 @@
         <v>Active</v>
       </c>
       <c r="K1096" t="str">
-        <v>SPRINKLER SET 6 MTR ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER NISI PIPE 6 MTR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1097">
@@ -38777,10 +38777,10 @@
         <v>1096</v>
       </c>
       <c r="B1097" t="str">
-        <v>FG-401499</v>
+        <v>FG-401498</v>
       </c>
       <c r="C1097" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1097" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38792,7 +38792,7 @@
         <v>General</v>
       </c>
       <c r="G1097" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1097" t="str">
         <v>Nos</v>
@@ -38812,10 +38812,10 @@
         <v>1097</v>
       </c>
       <c r="B1098" t="str">
-        <v>FG-401500</v>
+        <v>FG-401499</v>
       </c>
       <c r="C1098" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 2.5 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1098" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38827,7 +38827,7 @@
         <v>General</v>
       </c>
       <c r="G1098" t="str">
-        <v>75MM C TYPE 2.5 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1098" t="str">
         <v>Nos</v>
@@ -38847,10 +38847,10 @@
         <v>1098</v>
       </c>
       <c r="B1099" t="str">
-        <v>FG-401524</v>
+        <v>FG-401500</v>
       </c>
       <c r="C1099" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 2.5 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 2.5 KG)</v>
       </c>
       <c r="D1099" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38862,7 +38862,7 @@
         <v>General</v>
       </c>
       <c r="G1099" t="str">
-        <v>75MM L TYPE 2.5 KG</v>
+        <v>75MM C TYPE 2.5 KG</v>
       </c>
       <c r="H1099" t="str">
         <v>Nos</v>
@@ -38882,10 +38882,10 @@
         <v>1099</v>
       </c>
       <c r="B1100" t="str">
-        <v>FG-401501</v>
+        <v>FG-401524</v>
       </c>
       <c r="C1100" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 2.5 KG)</v>
       </c>
       <c r="D1100" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38897,7 +38897,7 @@
         <v>General</v>
       </c>
       <c r="G1100" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 2.5 KG</v>
       </c>
       <c r="H1100" t="str">
         <v>Nos</v>
@@ -38917,13 +38917,13 @@
         <v>1100</v>
       </c>
       <c r="B1101" t="str">
-        <v>FG-401495</v>
+        <v>FG-401501</v>
       </c>
       <c r="C1101" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1101" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI</v>
+        <v>SPRINKLER SET 6 MTR ISI</v>
       </c>
       <c r="E1101" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38932,7 +38932,7 @@
         <v>General</v>
       </c>
       <c r="G1101" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1101" t="str">
         <v>Nos</v>
@@ -38944,7 +38944,7 @@
         <v>Active</v>
       </c>
       <c r="K1101" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER SET 6 MTR ISI for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1102">
@@ -38952,10 +38952,10 @@
         <v>1101</v>
       </c>
       <c r="B1102" t="str">
-        <v>FG-401496</v>
+        <v>FG-401495</v>
       </c>
       <c r="C1102" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1102" t="str">
         <v>SPRINKLER SET 6 MTR N-ISI</v>
@@ -38967,7 +38967,7 @@
         <v>General</v>
       </c>
       <c r="G1102" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1102" t="str">
         <v>Nos</v>
@@ -38987,10 +38987,10 @@
         <v>1102</v>
       </c>
       <c r="B1103" t="str">
-        <v>FG-401497</v>
+        <v>FG-401496</v>
       </c>
       <c r="C1103" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1103" t="str">
         <v>SPRINKLER SET 6 MTR N-ISI</v>
@@ -39002,7 +39002,7 @@
         <v>General</v>
       </c>
       <c r="G1103" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1103" t="str">
         <v>Nos</v>
@@ -39022,13 +39022,13 @@
         <v>1103</v>
       </c>
       <c r="B1104" t="str">
-        <v>FG-401503</v>
+        <v>FG-401497</v>
       </c>
       <c r="C1104" t="str">
-        <v>SPRINKLER FITTINGS TEE (75MM, C TYPE)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1104" t="str">
-        <v>SPRINKLER FITTINGS TEE</v>
+        <v>SPRINKLER SET 6 MTR N-ISI</v>
       </c>
       <c r="E1104" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39037,7 +39037,7 @@
         <v>General</v>
       </c>
       <c r="G1104" t="str">
-        <v>75MM, C TYPE</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1104" t="str">
         <v>Nos</v>
@@ -39049,7 +39049,7 @@
         <v>Active</v>
       </c>
       <c r="K1104" t="str">
-        <v>SPRINKLER FITTINGS TEE for sprinkler irrigation systems. Available sizes: 75MM, C TYPE, 75MM, L TYPE, 63MM, C TYPE.</v>
+        <v>SPRINKLER SET 6 MTR N-ISI for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1105">
@@ -39057,10 +39057,10 @@
         <v>1104</v>
       </c>
       <c r="B1105" t="str">
-        <v>FG-401511</v>
+        <v>FG-401503</v>
       </c>
       <c r="C1105" t="str">
-        <v>SPRINKLER FITTINGS TEE (75MM, L TYPE)</v>
+        <v>SPRINKLER FITTINGS TEE (75MM, C TYPE)</v>
       </c>
       <c r="D1105" t="str">
         <v>SPRINKLER FITTINGS TEE</v>
@@ -39072,7 +39072,7 @@
         <v>General</v>
       </c>
       <c r="G1105" t="str">
-        <v>75MM, L TYPE</v>
+        <v>75MM, C TYPE</v>
       </c>
       <c r="H1105" t="str">
         <v>Nos</v>
@@ -39092,10 +39092,10 @@
         <v>1105</v>
       </c>
       <c r="B1106" t="str">
-        <v>FG-401526</v>
+        <v>FG-401511</v>
       </c>
       <c r="C1106" t="str">
-        <v>SPRINKLER FITTINGS TEE (63MM, C TYPE)</v>
+        <v>SPRINKLER FITTINGS TEE (75MM, L TYPE)</v>
       </c>
       <c r="D1106" t="str">
         <v>SPRINKLER FITTINGS TEE</v>
@@ -39107,7 +39107,7 @@
         <v>General</v>
       </c>
       <c r="G1106" t="str">
-        <v>63MM, C TYPE</v>
+        <v>75MM, L TYPE</v>
       </c>
       <c r="H1106" t="str">
         <v>Nos</v>
@@ -39127,13 +39127,13 @@
         <v>1106</v>
       </c>
       <c r="B1107" t="str">
-        <v>FG-401504</v>
+        <v>FG-401526</v>
       </c>
       <c r="C1107" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS TEE (63MM, C TYPE)</v>
       </c>
       <c r="D1107" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR</v>
+        <v>SPRINKLER FITTINGS TEE</v>
       </c>
       <c r="E1107" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39142,7 +39142,7 @@
         <v>General</v>
       </c>
       <c r="G1107" t="str">
-        <v>75MM C TYPE</v>
+        <v>63MM, C TYPE</v>
       </c>
       <c r="H1107" t="str">
         <v>Nos</v>
@@ -39154,7 +39154,7 @@
         <v>Active</v>
       </c>
       <c r="K1107" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS TEE for sprinkler irrigation systems. Available sizes: 75MM, C TYPE, 75MM, L TYPE, 63MM, C TYPE.</v>
       </c>
     </row>
     <row r="1108">
@@ -39162,10 +39162,10 @@
         <v>1107</v>
       </c>
       <c r="B1108" t="str">
-        <v>FG-401512</v>
+        <v>FG-401504</v>
       </c>
       <c r="C1108" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (75MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (75MM C TYPE)</v>
       </c>
       <c r="D1108" t="str">
         <v>SPRINKLER FITTINGS ADAPTOR</v>
@@ -39177,7 +39177,7 @@
         <v>General</v>
       </c>
       <c r="G1108" t="str">
-        <v>75MM P TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1108" t="str">
         <v>Nos</v>
@@ -39197,10 +39197,10 @@
         <v>1108</v>
       </c>
       <c r="B1109" t="str">
-        <v>FG-401527</v>
+        <v>FG-401512</v>
       </c>
       <c r="C1109" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (75MM P TYPE)</v>
       </c>
       <c r="D1109" t="str">
         <v>SPRINKLER FITTINGS ADAPTOR</v>
@@ -39212,7 +39212,7 @@
         <v>General</v>
       </c>
       <c r="G1109" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM P TYPE</v>
       </c>
       <c r="H1109" t="str">
         <v>Nos</v>
@@ -39232,13 +39232,13 @@
         <v>1109</v>
       </c>
       <c r="B1110" t="str">
-        <v>FG-401502</v>
+        <v>FG-401527</v>
       </c>
       <c r="C1110" t="str">
-        <v>SPRINKLER FITTINGS BEND (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (63MM C TYPE)</v>
       </c>
       <c r="D1110" t="str">
-        <v>SPRINKLER FITTINGS BEND</v>
+        <v>SPRINKLER FITTINGS ADAPTOR</v>
       </c>
       <c r="E1110" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39247,7 +39247,7 @@
         <v>General</v>
       </c>
       <c r="G1110" t="str">
-        <v>75MM C TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1110" t="str">
         <v>Nos</v>
@@ -39259,7 +39259,7 @@
         <v>Active</v>
       </c>
       <c r="K1110" t="str">
-        <v>SPRINKLER FITTINGS BEND for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS ADAPTOR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1111">
@@ -39267,10 +39267,10 @@
         <v>1110</v>
       </c>
       <c r="B1111" t="str">
-        <v>FG-401510</v>
+        <v>FG-401502</v>
       </c>
       <c r="C1111" t="str">
-        <v>SPRINKLER FITTINGS BEND (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (75MM C TYPE)</v>
       </c>
       <c r="D1111" t="str">
         <v>SPRINKLER FITTINGS BEND</v>
@@ -39282,7 +39282,7 @@
         <v>General</v>
       </c>
       <c r="G1111" t="str">
-        <v>75MM L TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1111" t="str">
         <v>Nos</v>
@@ -39302,10 +39302,10 @@
         <v>1111</v>
       </c>
       <c r="B1112" t="str">
-        <v>FG-401525</v>
+        <v>FG-401510</v>
       </c>
       <c r="C1112" t="str">
-        <v>SPRINKLER FITTINGS BEND (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (75MM L TYPE)</v>
       </c>
       <c r="D1112" t="str">
         <v>SPRINKLER FITTINGS BEND</v>
@@ -39317,7 +39317,7 @@
         <v>General</v>
       </c>
       <c r="G1112" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1112" t="str">
         <v>Nos</v>
@@ -39337,13 +39337,13 @@
         <v>1112</v>
       </c>
       <c r="B1113" t="str">
-        <v>FG-401514</v>
+        <v>FG-401525</v>
       </c>
       <c r="C1113" t="str">
-        <v>SPRINKLER FITTINGS END CAP (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (63MM C TYPE)</v>
       </c>
       <c r="D1113" t="str">
-        <v>SPRINKLER FITTINGS END CAP</v>
+        <v>SPRINKLER FITTINGS BEND</v>
       </c>
       <c r="E1113" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39352,7 +39352,7 @@
         <v>General</v>
       </c>
       <c r="G1113" t="str">
-        <v>75MM L TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1113" t="str">
         <v>Nos</v>
@@ -39364,7 +39364,7 @@
         <v>Active</v>
       </c>
       <c r="K1113" t="str">
-        <v>SPRINKLER FITTINGS END CAP for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS BEND for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1114">
@@ -39372,10 +39372,10 @@
         <v>1113</v>
       </c>
       <c r="B1114" t="str">
-        <v>FG-401506</v>
+        <v>FG-401514</v>
       </c>
       <c r="C1114" t="str">
-        <v>SPRINKLER FITTINGS END CAP (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (75MM L TYPE)</v>
       </c>
       <c r="D1114" t="str">
         <v>SPRINKLER FITTINGS END CAP</v>
@@ -39387,7 +39387,7 @@
         <v>General</v>
       </c>
       <c r="G1114" t="str">
-        <v>75MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1114" t="str">
         <v>Nos</v>
@@ -39407,10 +39407,10 @@
         <v>1114</v>
       </c>
       <c r="B1115" t="str">
-        <v>FG-401529</v>
+        <v>FG-401506</v>
       </c>
       <c r="C1115" t="str">
-        <v>SPRINKLER FITTINGS END CAP (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (75MM C TYPE)</v>
       </c>
       <c r="D1115" t="str">
         <v>SPRINKLER FITTINGS END CAP</v>
@@ -39422,7 +39422,7 @@
         <v>General</v>
       </c>
       <c r="G1115" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1115" t="str">
         <v>Nos</v>
@@ -39442,13 +39442,13 @@
         <v>1115</v>
       </c>
       <c r="B1116" t="str">
-        <v>FG-401517</v>
+        <v>FG-401529</v>
       </c>
       <c r="C1116" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (75MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (63MM C TYPE)</v>
       </c>
       <c r="D1116" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
+        <v>SPRINKLER FITTINGS END CAP</v>
       </c>
       <c r="E1116" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39457,7 +39457,7 @@
         <v>General</v>
       </c>
       <c r="G1116" t="str">
-        <v>75MM P TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1116" t="str">
         <v>Nos</v>
@@ -39469,7 +39469,7 @@
         <v>Active</v>
       </c>
       <c r="K1116" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS END CAP for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1117">
@@ -39477,10 +39477,10 @@
         <v>1116</v>
       </c>
       <c r="B1117" t="str">
-        <v>FG-401518</v>
+        <v>FG-401517</v>
       </c>
       <c r="C1117" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (63MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (75MM P TYPE)</v>
       </c>
       <c r="D1117" t="str">
         <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
@@ -39492,7 +39492,7 @@
         <v>General</v>
       </c>
       <c r="G1117" t="str">
-        <v>63MM P TYPE</v>
+        <v>75MM P TYPE</v>
       </c>
       <c r="H1117" t="str">
         <v>Nos</v>
@@ -39512,13 +39512,13 @@
         <v>1117</v>
       </c>
       <c r="B1118" t="str">
-        <v>FG-401505</v>
+        <v>FG-401518</v>
       </c>
       <c r="C1118" t="str">
-        <v>SPRINKLER FITTINGS PCN (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (63MM P TYPE)</v>
       </c>
       <c r="D1118" t="str">
-        <v>SPRINKLER FITTINGS PCN</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
       </c>
       <c r="E1118" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39527,7 +39527,7 @@
         <v>General</v>
       </c>
       <c r="G1118" t="str">
-        <v>75MM C TYPE</v>
+        <v>63MM P TYPE</v>
       </c>
       <c r="H1118" t="str">
         <v>Nos</v>
@@ -39539,7 +39539,7 @@
         <v>Active</v>
       </c>
       <c r="K1118" t="str">
-        <v>SPRINKLER FITTINGS PCN for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1119">
@@ -39547,10 +39547,10 @@
         <v>1118</v>
       </c>
       <c r="B1119" t="str">
-        <v>FG-401513</v>
+        <v>FG-401505</v>
       </c>
       <c r="C1119" t="str">
-        <v>SPRINKLER FITTINGS PCN (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (75MM C TYPE)</v>
       </c>
       <c r="D1119" t="str">
         <v>SPRINKLER FITTINGS PCN</v>
@@ -39562,7 +39562,7 @@
         <v>General</v>
       </c>
       <c r="G1119" t="str">
-        <v>75MM L TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1119" t="str">
         <v>Nos</v>
@@ -39582,10 +39582,10 @@
         <v>1119</v>
       </c>
       <c r="B1120" t="str">
-        <v>FG-401528</v>
+        <v>FG-401513</v>
       </c>
       <c r="C1120" t="str">
-        <v>SPRINKLER FITTINGS PCN (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (75MM L TYPE)</v>
       </c>
       <c r="D1120" t="str">
         <v>SPRINKLER FITTINGS PCN</v>
@@ -39597,7 +39597,7 @@
         <v>General</v>
       </c>
       <c r="G1120" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1120" t="str">
         <v>Nos</v>
@@ -39617,13 +39617,13 @@
         <v>1120</v>
       </c>
       <c r="B1121" t="str">
-        <v>FG-401507</v>
+        <v>FG-401528</v>
       </c>
       <c r="C1121" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL (20MM)</v>
+        <v>SPRINKLER FITTINGS PCN (63MM C TYPE)</v>
       </c>
       <c r="D1121" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL</v>
+        <v>SPRINKLER FITTINGS PCN</v>
       </c>
       <c r="E1121" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39632,7 +39632,7 @@
         <v>General</v>
       </c>
       <c r="G1121" t="str">
-        <v>20MM</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1121" t="str">
         <v>Nos</v>
@@ -39644,7 +39644,7 @@
         <v>Active</v>
       </c>
       <c r="K1121" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS PCN for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1122">
@@ -39652,13 +39652,13 @@
         <v>1121</v>
       </c>
       <c r="B1122" t="str">
-        <v>FG-401508</v>
+        <v>FG-401507</v>
       </c>
       <c r="C1122" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL (20MM)</v>
       </c>
       <c r="D1122" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL</v>
       </c>
       <c r="E1122" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39667,7 +39667,7 @@
         <v>General</v>
       </c>
       <c r="G1122" t="str">
-        <v>75MM C TYPE</v>
+        <v>20MM</v>
       </c>
       <c r="H1122" t="str">
         <v>Nos</v>
@@ -39679,7 +39679,7 @@
         <v>Active</v>
       </c>
       <c r="K1122" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1123">
@@ -39687,10 +39687,10 @@
         <v>1122</v>
       </c>
       <c r="B1123" t="str">
-        <v>FG-401515</v>
+        <v>FG-401508</v>
       </c>
       <c r="C1123" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE (20MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE (75MM C TYPE)</v>
       </c>
       <c r="D1123" t="str">
         <v>SPRINKLER FITTINGS GI RISER PIPE</v>
@@ -39702,7 +39702,7 @@
         <v>General</v>
       </c>
       <c r="G1123" t="str">
-        <v>20MM L TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1123" t="str">
         <v>Nos</v>
@@ -39722,25 +39722,25 @@
         <v>1123</v>
       </c>
       <c r="B1124" t="str">
-        <v>FG-401742</v>
+        <v>FG-401515</v>
       </c>
       <c r="C1124" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 1)</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE (20MM L TYPE)</v>
       </c>
       <c r="D1124" t="str">
-        <v>ROUND DRIPLINE 12MM ISI</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE</v>
       </c>
       <c r="E1124" t="str">
-        <v>DRIP IRRIGATION SYSTEM</v>
+        <v>Sprinkler Pipes &amp; Fittings</v>
       </c>
       <c r="F1124" t="str">
-        <v>ROUND DRIP ISI</v>
+        <v>General</v>
       </c>
       <c r="G1124" t="str">
-        <v>12-4-30 CLASS 1</v>
+        <v>20MM L TYPE</v>
       </c>
       <c r="H1124" t="str">
-        <v>ROLL</v>
+        <v>Nos</v>
       </c>
       <c r="I1124" t="str">
         <v>-</v>
@@ -39749,7 +39749,7 @@
         <v>Active</v>
       </c>
       <c r="K1124" t="str">
-        <v>ROUND DRIPLINE 12MM ISI certified.</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1125">
@@ -39757,10 +39757,10 @@
         <v>1124</v>
       </c>
       <c r="B1125" t="str">
-        <v>FG-401743</v>
+        <v>FG-401742</v>
       </c>
       <c r="C1125" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 1)</v>
       </c>
       <c r="D1125" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39772,7 +39772,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1125" t="str">
-        <v>12-4-40 CLASS 1</v>
+        <v>12-4-30 CLASS 1</v>
       </c>
       <c r="H1125" t="str">
         <v>ROLL</v>
@@ -39792,10 +39792,10 @@
         <v>1125</v>
       </c>
       <c r="B1126" t="str">
-        <v>FG-401744</v>
+        <v>FG-401743</v>
       </c>
       <c r="C1126" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 1)</v>
       </c>
       <c r="D1126" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39807,7 +39807,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1126" t="str">
-        <v>12-4-50 CLASS 1</v>
+        <v>12-4-40 CLASS 1</v>
       </c>
       <c r="H1126" t="str">
         <v>ROLL</v>
@@ -39827,10 +39827,10 @@
         <v>1126</v>
       </c>
       <c r="B1127" t="str">
-        <v>FG-401751</v>
+        <v>FG-401744</v>
       </c>
       <c r="C1127" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 1)</v>
       </c>
       <c r="D1127" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39842,7 +39842,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1127" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-50 CLASS 1</v>
       </c>
       <c r="H1127" t="str">
         <v>ROLL</v>
@@ -39862,10 +39862,10 @@
         <v>1127</v>
       </c>
       <c r="B1128" t="str">
-        <v>FG-401752</v>
+        <v>FG-401751</v>
       </c>
       <c r="C1128" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1128" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39877,7 +39877,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1128" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1128" t="str">
         <v>ROLL</v>
@@ -39897,10 +39897,10 @@
         <v>1128</v>
       </c>
       <c r="B1129" t="str">
-        <v>FG-401753</v>
+        <v>FG-401752</v>
       </c>
       <c r="C1129" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1129" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39912,7 +39912,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1129" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1129" t="str">
         <v>ROLL</v>
@@ -39932,10 +39932,10 @@
         <v>1129</v>
       </c>
       <c r="B1130" t="str">
-        <v>FG-401754</v>
+        <v>FG-401753</v>
       </c>
       <c r="C1130" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1130" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39947,7 +39947,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1130" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1130" t="str">
         <v>ROLL</v>
@@ -39967,10 +39967,10 @@
         <v>1130</v>
       </c>
       <c r="B1131" t="str">
-        <v>FG-401755</v>
+        <v>FG-401754</v>
       </c>
       <c r="C1131" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1131" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39982,7 +39982,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1131" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1131" t="str">
         <v>ROLL</v>
@@ -40002,10 +40002,10 @@
         <v>1131</v>
       </c>
       <c r="B1132" t="str">
-        <v>FG-401756</v>
+        <v>FG-401755</v>
       </c>
       <c r="C1132" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1132" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -40017,7 +40017,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1132" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1132" t="str">
         <v>ROLL</v>
@@ -40037,13 +40037,13 @@
         <v>1132</v>
       </c>
       <c r="B1133" t="str">
-        <v>FG-401745</v>
+        <v>FG-401756</v>
       </c>
       <c r="C1133" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1133" t="str">
-        <v>ROUND DRIPLINE 16MM ISI</v>
+        <v>ROUND DRIPLINE 12MM ISI</v>
       </c>
       <c r="E1133" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40052,7 +40052,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1133" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1133" t="str">
         <v>ROLL</v>
@@ -40064,7 +40064,7 @@
         <v>Active</v>
       </c>
       <c r="K1133" t="str">
-        <v>ROUND DRIPLINE 16MM ISI certified.</v>
+        <v>ROUND DRIPLINE 12MM ISI certified.</v>
       </c>
     </row>
     <row r="1134">
@@ -40072,10 +40072,10 @@
         <v>1133</v>
       </c>
       <c r="B1134" t="str">
-        <v>FG-401746</v>
+        <v>FG-401745</v>
       </c>
       <c r="C1134" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1134" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40087,7 +40087,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1134" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1134" t="str">
         <v>ROLL</v>
@@ -40107,10 +40107,10 @@
         <v>1134</v>
       </c>
       <c r="B1135" t="str">
-        <v>FG-401747</v>
+        <v>FG-401746</v>
       </c>
       <c r="C1135" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1135" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40122,7 +40122,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1135" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1135" t="str">
         <v>ROLL</v>
@@ -40142,10 +40142,10 @@
         <v>1135</v>
       </c>
       <c r="B1136" t="str">
-        <v>FG-401757</v>
+        <v>FG-401747</v>
       </c>
       <c r="C1136" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1136" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40157,7 +40157,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1136" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1136" t="str">
         <v>ROLL</v>
@@ -40177,10 +40177,10 @@
         <v>1136</v>
       </c>
       <c r="B1137" t="str">
-        <v>FG-401758</v>
+        <v>FG-401757</v>
       </c>
       <c r="C1137" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1137" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40192,7 +40192,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1137" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1137" t="str">
         <v>ROLL</v>
@@ -40212,10 +40212,10 @@
         <v>1137</v>
       </c>
       <c r="B1138" t="str">
-        <v>FG-401759</v>
+        <v>FG-401758</v>
       </c>
       <c r="C1138" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1138" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40227,7 +40227,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1138" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1138" t="str">
         <v>ROLL</v>
@@ -40247,13 +40247,13 @@
         <v>1138</v>
       </c>
       <c r="B1139" t="str">
-        <v>-</v>
+        <v>FG-401759</v>
       </c>
       <c r="C1139" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-30 CLASS-1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1139" t="str">
-        <v>20MM ROUND INLINE PIPE ISI</v>
+        <v>ROUND DRIPLINE 16MM ISI</v>
       </c>
       <c r="E1139" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40262,10 +40262,10 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1139" t="str">
-        <v>20-4-30 CLASS-1</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1139" t="str">
-        <v>MTR</v>
+        <v>ROLL</v>
       </c>
       <c r="I1139" t="str">
         <v>-</v>
@@ -40274,7 +40274,7 @@
         <v>Active</v>
       </c>
       <c r="K1139" t="str">
-        <v>20mm Round Inline Drip Pipe ISI certified.</v>
+        <v>ROUND DRIPLINE 16MM ISI certified.</v>
       </c>
     </row>
     <row r="1140">
@@ -40285,7 +40285,7 @@
         <v>-</v>
       </c>
       <c r="C1140" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-40 CLASS-1)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-30 CLASS-1)</v>
       </c>
       <c r="D1140" t="str">
         <v>20MM ROUND INLINE PIPE ISI</v>
@@ -40297,7 +40297,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1140" t="str">
-        <v>20-4-40 CLASS-1</v>
+        <v>20-4-30 CLASS-1</v>
       </c>
       <c r="H1140" t="str">
         <v>MTR</v>
@@ -40320,7 +40320,7 @@
         <v>-</v>
       </c>
       <c r="C1141" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-50 CLASS-1)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-40 CLASS-1)</v>
       </c>
       <c r="D1141" t="str">
         <v>20MM ROUND INLINE PIPE ISI</v>
@@ -40332,7 +40332,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1141" t="str">
-        <v>20-4-50 CLASS-1</v>
+        <v>20-4-40 CLASS-1</v>
       </c>
       <c r="H1141" t="str">
         <v>MTR</v>
@@ -40352,25 +40352,25 @@
         <v>1141</v>
       </c>
       <c r="B1142" t="str">
-        <v>FG-401763</v>
+        <v>-</v>
       </c>
       <c r="C1142" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-50 CLASS-1)</v>
       </c>
       <c r="D1142" t="str">
-        <v>FLAT DRIPLINE 12MM ISI</v>
+        <v>20MM ROUND INLINE PIPE ISI</v>
       </c>
       <c r="E1142" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1142" t="str">
-        <v>FLAT DRIP ISI</v>
+        <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1142" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>20-4-50 CLASS-1</v>
       </c>
       <c r="H1142" t="str">
-        <v>ROLL</v>
+        <v>MTR</v>
       </c>
       <c r="I1142" t="str">
         <v>-</v>
@@ -40379,7 +40379,7 @@
         <v>Active</v>
       </c>
       <c r="K1142" t="str">
-        <v>FLAT DRIPLINE 12MM ISI certified.</v>
+        <v>20mm Round Inline Drip Pipe ISI certified.</v>
       </c>
     </row>
     <row r="1143">
@@ -40387,10 +40387,10 @@
         <v>1142</v>
       </c>
       <c r="B1143" t="str">
-        <v>FG-401764</v>
+        <v>FG-401763</v>
       </c>
       <c r="C1143" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1143" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40402,7 +40402,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1143" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1143" t="str">
         <v>ROLL</v>
@@ -40422,10 +40422,10 @@
         <v>1143</v>
       </c>
       <c r="B1144" t="str">
-        <v>FG-401765</v>
+        <v>FG-401764</v>
       </c>
       <c r="C1144" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1144" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40437,7 +40437,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1144" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1144" t="str">
         <v>ROLL</v>
@@ -40457,10 +40457,10 @@
         <v>1144</v>
       </c>
       <c r="B1145" t="str">
-        <v>FG-401766</v>
+        <v>FG-401765</v>
       </c>
       <c r="C1145" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1145" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40472,7 +40472,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1145" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1145" t="str">
         <v>ROLL</v>
@@ -40492,10 +40492,10 @@
         <v>1145</v>
       </c>
       <c r="B1146" t="str">
-        <v>FG-401767</v>
+        <v>FG-401766</v>
       </c>
       <c r="C1146" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1146" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40507,7 +40507,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1146" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1146" t="str">
         <v>ROLL</v>
@@ -40527,10 +40527,10 @@
         <v>1146</v>
       </c>
       <c r="B1147" t="str">
-        <v>FG-401768</v>
+        <v>FG-401767</v>
       </c>
       <c r="C1147" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1147" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40542,7 +40542,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1147" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1147" t="str">
         <v>ROLL</v>
@@ -40562,13 +40562,13 @@
         <v>1147</v>
       </c>
       <c r="B1148" t="str">
-        <v>FG-401760</v>
+        <v>FG-401768</v>
       </c>
       <c r="C1148" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1148" t="str">
-        <v>FLAT DRIPLINE 16MM ISI</v>
+        <v>FLAT DRIPLINE 12MM ISI</v>
       </c>
       <c r="E1148" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40577,7 +40577,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1148" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1148" t="str">
         <v>ROLL</v>
@@ -40589,7 +40589,7 @@
         <v>Active</v>
       </c>
       <c r="K1148" t="str">
-        <v>FLAT DRIPLINE 16MM ISI certified.</v>
+        <v>FLAT DRIPLINE 12MM ISI certified.</v>
       </c>
     </row>
     <row r="1149">
@@ -40597,10 +40597,10 @@
         <v>1148</v>
       </c>
       <c r="B1149" t="str">
-        <v>FG-401761</v>
+        <v>FG-401760</v>
       </c>
       <c r="C1149" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1149" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40612,7 +40612,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1149" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1149" t="str">
         <v>ROLL</v>
@@ -40632,10 +40632,10 @@
         <v>1149</v>
       </c>
       <c r="B1150" t="str">
-        <v>FG-401762</v>
+        <v>FG-401761</v>
       </c>
       <c r="C1150" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1150" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40647,7 +40647,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1150" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1150" t="str">
         <v>ROLL</v>
@@ -40667,10 +40667,10 @@
         <v>1150</v>
       </c>
       <c r="B1151" t="str">
-        <v>FG-401769</v>
+        <v>FG-401762</v>
       </c>
       <c r="C1151" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1151" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40682,7 +40682,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1151" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1151" t="str">
         <v>ROLL</v>
@@ -40702,10 +40702,10 @@
         <v>1151</v>
       </c>
       <c r="B1152" t="str">
-        <v>FG-401770</v>
+        <v>FG-401769</v>
       </c>
       <c r="C1152" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1152" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40717,7 +40717,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1152" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1152" t="str">
         <v>ROLL</v>
@@ -40737,10 +40737,10 @@
         <v>1152</v>
       </c>
       <c r="B1153" t="str">
-        <v>FG-401779</v>
+        <v>FG-401770</v>
       </c>
       <c r="C1153" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1153" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40752,7 +40752,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1153" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1153" t="str">
         <v>ROLL</v>
@@ -40772,13 +40772,13 @@
         <v>1153</v>
       </c>
       <c r="B1154" t="str">
-        <v>FG-401771</v>
+        <v>FG-401779</v>
       </c>
       <c r="C1154" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1154" t="str">
-        <v>FLAT DRIPLINE 20MM ISI</v>
+        <v>FLAT DRIPLINE 16MM ISI</v>
       </c>
       <c r="E1154" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40787,7 +40787,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1154" t="str">
-        <v>20-4-30 CLASS 1</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1154" t="str">
         <v>ROLL</v>
@@ -40799,7 +40799,7 @@
         <v>Active</v>
       </c>
       <c r="K1154" t="str">
-        <v>FLAT DRIPLINE 20MM ISI certified.</v>
+        <v>FLAT DRIPLINE 16MM ISI certified.</v>
       </c>
     </row>
     <row r="1155">
@@ -40807,10 +40807,10 @@
         <v>1154</v>
       </c>
       <c r="B1155" t="str">
-        <v>FG-401772</v>
+        <v>FG-401771</v>
       </c>
       <c r="C1155" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-30 CLASS 1)</v>
       </c>
       <c r="D1155" t="str">
         <v>FLAT DRIPLINE 20MM ISI</v>
@@ -40822,7 +40822,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1155" t="str">
-        <v>20-4-40 CLASS 1</v>
+        <v>20-4-30 CLASS 1</v>
       </c>
       <c r="H1155" t="str">
         <v>ROLL</v>
@@ -40842,10 +40842,10 @@
         <v>1155</v>
       </c>
       <c r="B1156" t="str">
-        <v>FG-401773</v>
+        <v>FG-401772</v>
       </c>
       <c r="C1156" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-40 CLASS 1)</v>
       </c>
       <c r="D1156" t="str">
         <v>FLAT DRIPLINE 20MM ISI</v>
@@ -40857,7 +40857,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1156" t="str">
-        <v>20-4-50 CLASS 1</v>
+        <v>20-4-40 CLASS 1</v>
       </c>
       <c r="H1156" t="str">
         <v>ROLL</v>
@@ -40877,25 +40877,25 @@
         <v>1156</v>
       </c>
       <c r="B1157" t="str">
-        <v>-</v>
+        <v>FG-401773</v>
       </c>
       <c r="C1157" t="str">
-        <v>12MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-50 CLASS 1)</v>
       </c>
       <c r="D1157" t="str">
-        <v>12MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>FLAT DRIPLINE 20MM ISI</v>
       </c>
       <c r="E1157" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1157" t="str">
-        <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
+        <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1157" t="str">
-        <v>CLASS-2</v>
+        <v>20-4-50 CLASS 1</v>
       </c>
       <c r="H1157" t="str">
-        <v>MTR</v>
+        <v>ROLL</v>
       </c>
       <c r="I1157" t="str">
         <v>-</v>
@@ -40904,7 +40904,7 @@
         <v>Active</v>
       </c>
       <c r="K1157" t="str">
-        <v>12mm Plain Lateral Online Drip Pipe.</v>
+        <v>FLAT DRIPLINE 20MM ISI certified.</v>
       </c>
     </row>
     <row r="1158">
@@ -40915,10 +40915,10 @@
         <v>-</v>
       </c>
       <c r="C1158" t="str">
-        <v>16MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>12MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1158" t="str">
-        <v>16MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>12MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1158" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40939,7 +40939,7 @@
         <v>Active</v>
       </c>
       <c r="K1158" t="str">
-        <v>16mm Plain Lateral Online Drip Pipe.</v>
+        <v>12mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1159">
@@ -40950,10 +40950,10 @@
         <v>-</v>
       </c>
       <c r="C1159" t="str">
-        <v>20MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>16MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1159" t="str">
-        <v>20MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>16MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1159" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40974,7 +40974,7 @@
         <v>Active</v>
       </c>
       <c r="K1159" t="str">
-        <v>20mm Plain Lateral Online Drip Pipe.</v>
+        <v>16mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1160">
@@ -40985,10 +40985,10 @@
         <v>-</v>
       </c>
       <c r="C1160" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-1)</v>
+        <v>20MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1160" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>20MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1160" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40997,7 +40997,7 @@
         <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1160" t="str">
-        <v>CLASS-1</v>
+        <v>CLASS-2</v>
       </c>
       <c r="H1160" t="str">
         <v>MTR</v>
@@ -41009,7 +41009,7 @@
         <v>Active</v>
       </c>
       <c r="K1160" t="str">
-        <v>32mm Plain Lateral Online Drip Pipe.</v>
+        <v>20mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1161">
@@ -41020,7 +41020,7 @@
         <v>-</v>
       </c>
       <c r="C1161" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-1)</v>
       </c>
       <c r="D1161" t="str">
         <v>32MM PLAIN LATERAL ONLINE PIPE</v>
@@ -41032,7 +41032,7 @@
         <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1161" t="str">
-        <v>CLASS-2</v>
+        <v>CLASS-1</v>
       </c>
       <c r="H1161" t="str">
         <v>MTR</v>
@@ -41052,22 +41052,22 @@
         <v>1161</v>
       </c>
       <c r="B1162" t="str">
-        <v>FG-401763</v>
+        <v>-</v>
       </c>
       <c r="C1162" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 2)</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1162" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1162" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1162" t="str">
-        <v>FLAT DRIP (PEPSI) - INLINE</v>
+        <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1162" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>CLASS-2</v>
       </c>
       <c r="H1162" t="str">
         <v>MTR</v>
@@ -41079,7 +41079,7 @@
         <v>Active</v>
       </c>
       <c r="K1162" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12. Available sizes: 12-4-30 CLASS 2, 12-4-40 CLASS 2, 12-4-50 CLASS 2, 12-4-30 CLASS 3, 12-4-40 CLASS 3, 12-4-50 CLASS 3.</v>
+        <v>32mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1163">
@@ -41087,10 +41087,10 @@
         <v>1162</v>
       </c>
       <c r="B1163" t="str">
-        <v>FG-401764</v>
+        <v>FG-401763</v>
       </c>
       <c r="C1163" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1163" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41102,7 +41102,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1163" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1163" t="str">
         <v>MTR</v>
@@ -41122,10 +41122,10 @@
         <v>1163</v>
       </c>
       <c r="B1164" t="str">
-        <v>FG-401765</v>
+        <v>FG-401764</v>
       </c>
       <c r="C1164" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1164" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41137,7 +41137,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1164" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1164" t="str">
         <v>MTR</v>
@@ -41157,10 +41157,10 @@
         <v>1164</v>
       </c>
       <c r="B1165" t="str">
-        <v>FG-401766</v>
+        <v>FG-401765</v>
       </c>
       <c r="C1165" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1165" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41172,7 +41172,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1165" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1165" t="str">
         <v>MTR</v>
@@ -41192,10 +41192,10 @@
         <v>1165</v>
       </c>
       <c r="B1166" t="str">
-        <v>FG-401767</v>
+        <v>FG-401766</v>
       </c>
       <c r="C1166" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1166" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41207,7 +41207,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1166" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1166" t="str">
         <v>MTR</v>
@@ -41227,10 +41227,10 @@
         <v>1166</v>
       </c>
       <c r="B1167" t="str">
-        <v>FG-401768</v>
+        <v>FG-401767</v>
       </c>
       <c r="C1167" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1167" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41242,7 +41242,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1167" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1167" t="str">
         <v>MTR</v>
@@ -41262,13 +41262,13 @@
         <v>1167</v>
       </c>
       <c r="B1168" t="str">
-        <v>FG-401760</v>
+        <v>FG-401768</v>
       </c>
       <c r="C1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12</v>
       </c>
       <c r="E1168" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -41277,7 +41277,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1168" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1168" t="str">
         <v>MTR</v>
@@ -41289,7 +41289,7 @@
         <v>Active</v>
       </c>
       <c r="K1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16. Available sizes: 16-4-30 CLASS 1, 16-4-40 CLASS 1, 16-4-50 CLASS 1, 16-4-30 CLASS 2, 16-4-40 CLASS 2, 16-4-50 CLASS 2.</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12. Available sizes: 12-4-30 CLASS 2, 12-4-40 CLASS 2, 12-4-50 CLASS 2, 12-4-30 CLASS 3, 12-4-40 CLASS 3, 12-4-50 CLASS 3.</v>
       </c>
     </row>
     <row r="1169">
@@ -41297,10 +41297,10 @@
         <v>1168</v>
       </c>
       <c r="B1169" t="str">
-        <v>FG-401761</v>
+        <v>FG-401760</v>
       </c>
       <c r="C1169" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1169" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41312,7 +41312,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1169" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1169" t="str">
         <v>MTR</v>
@@ -41332,10 +41332,10 @@
         <v>1169</v>
       </c>
       <c r="B1170" t="str">
-        <v>FG-401762</v>
+        <v>FG-401761</v>
       </c>
       <c r="C1170" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1170" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41347,7 +41347,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1170" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1170" t="str">
         <v>MTR</v>
@@ -41367,10 +41367,10 @@
         <v>1170</v>
       </c>
       <c r="B1171" t="str">
-        <v>FG-401769</v>
+        <v>FG-401762</v>
       </c>
       <c r="C1171" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1171" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41382,7 +41382,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1171" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1171" t="str">
         <v>MTR</v>
@@ -41402,10 +41402,10 @@
         <v>1171</v>
       </c>
       <c r="B1172" t="str">
-        <v>FG-401770</v>
+        <v>FG-401769</v>
       </c>
       <c r="C1172" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1172" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41417,7 +41417,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1172" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1172" t="str">
         <v>MTR</v>
@@ -41437,10 +41437,10 @@
         <v>1172</v>
       </c>
       <c r="B1173" t="str">
-        <v>FG-401779</v>
+        <v>FG-401770</v>
       </c>
       <c r="C1173" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1173" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41452,7 +41452,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1173" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1173" t="str">
         <v>MTR</v>
@@ -41472,13 +41472,13 @@
         <v>1173</v>
       </c>
       <c r="B1174" t="str">
-        <v>FG-401771</v>
+        <v>FG-401779</v>
       </c>
       <c r="C1174" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1174" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16</v>
       </c>
       <c r="E1174" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -41487,7 +41487,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1174" t="str">
-        <v>20-4-30 CLASS 1</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1174" t="str">
         <v>MTR</v>
@@ -41499,7 +41499,7 @@
         <v>Active</v>
       </c>
       <c r="K1174" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20. Available sizes: 20-4-30 CLASS 1, 20-4-40 CLASS 1, 20-4-50 CLASS 1.</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16. Available sizes: 16-4-30 CLASS 1, 16-4-40 CLASS 1, 16-4-50 CLASS 1, 16-4-30 CLASS 2, 16-4-40 CLASS 2, 16-4-50 CLASS 2.</v>
       </c>
     </row>
     <row r="1175">
@@ -41507,10 +41507,10 @@
         <v>1174</v>
       </c>
       <c r="B1175" t="str">
-        <v>FG-401772</v>
+        <v>FG-401771</v>
       </c>
       <c r="C1175" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-30 CLASS 1)</v>
       </c>
       <c r="D1175" t="str">
         <v>FLAT DRIPLINE ISI 400MTR 20</v>
@@ -41522,7 +41522,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1175" t="str">
-        <v>20-4-40 CLASS 1</v>
+        <v>20-4-30 CLASS 1</v>
       </c>
       <c r="H1175" t="str">
         <v>MTR</v>
@@ -41542,10 +41542,10 @@
         <v>1175</v>
       </c>
       <c r="B1176" t="str">
-        <v>FG-401773</v>
+        <v>FG-401772</v>
       </c>
       <c r="C1176" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-40 CLASS 1)</v>
       </c>
       <c r="D1176" t="str">
         <v>FLAT DRIPLINE ISI 400MTR 20</v>
@@ -41557,7 +41557,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1176" t="str">
-        <v>20-4-50 CLASS 1</v>
+        <v>20-4-40 CLASS 1</v>
       </c>
       <c r="H1176" t="str">
         <v>MTR</v>
@@ -41577,22 +41577,22 @@
         <v>1176</v>
       </c>
       <c r="B1177" t="str">
-        <v>FG-401066</v>
+        <v>FG-401773</v>
       </c>
       <c r="C1177" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-50 CLASS 1)</v>
       </c>
       <c r="D1177" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20</v>
       </c>
       <c r="E1177" t="str">
-        <v>UPVC CASING PIPES</v>
+        <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1177" t="str">
-        <v>General</v>
+        <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1177" t="str">
-        <v>35MM 1 1/4 Inch</v>
+        <v>20-4-50 CLASS 1</v>
       </c>
       <c r="H1177" t="str">
         <v>MTR</v>
@@ -41604,7 +41604,7 @@
         <v>Active</v>
       </c>
       <c r="K1177" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 40MM 1 1/2 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20. Available sizes: 20-4-30 CLASS 1, 20-4-40 CLASS 1, 20-4-50 CLASS 1.</v>
       </c>
     </row>
     <row r="1178">
@@ -41612,10 +41612,10 @@
         <v>1177</v>
       </c>
       <c r="B1178" t="str">
-        <v>FG-401067</v>
+        <v>FG-401066</v>
       </c>
       <c r="C1178" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (40MM 1 1/2 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
       </c>
       <c r="D1178" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41627,7 +41627,7 @@
         <v>General</v>
       </c>
       <c r="G1178" t="str">
-        <v>40MM 1 1/2 Inch</v>
+        <v>35MM 1 1/4 Inch</v>
       </c>
       <c r="H1178" t="str">
         <v>MTR</v>
@@ -41647,10 +41647,10 @@
         <v>1178</v>
       </c>
       <c r="B1179" t="str">
-        <v>FG-401068</v>
+        <v>FG-401067</v>
       </c>
       <c r="C1179" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (50MM 2 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (40MM 1 1/2 Inch)</v>
       </c>
       <c r="D1179" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41662,7 +41662,7 @@
         <v>General</v>
       </c>
       <c r="G1179" t="str">
-        <v>50MM 2 Inch</v>
+        <v>40MM 1 1/2 Inch</v>
       </c>
       <c r="H1179" t="str">
         <v>MTR</v>
@@ -41682,10 +41682,10 @@
         <v>1179</v>
       </c>
       <c r="B1180" t="str">
-        <v>FG-401069</v>
+        <v>FG-401068</v>
       </c>
       <c r="C1180" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (100MM 4 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (50MM 2 Inch)</v>
       </c>
       <c r="D1180" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41697,7 +41697,7 @@
         <v>General</v>
       </c>
       <c r="G1180" t="str">
-        <v>100MM 4 Inch</v>
+        <v>50MM 2 Inch</v>
       </c>
       <c r="H1180" t="str">
         <v>MTR</v>
@@ -41717,10 +41717,10 @@
         <v>1180</v>
       </c>
       <c r="B1181" t="str">
-        <v>FG-401070</v>
+        <v>FG-401069</v>
       </c>
       <c r="C1181" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (100MM 4 Inch)</v>
       </c>
       <c r="D1181" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41732,7 +41732,7 @@
         <v>General</v>
       </c>
       <c r="G1181" t="str">
-        <v>125MM 5 Inch</v>
+        <v>100MM 4 Inch</v>
       </c>
       <c r="H1181" t="str">
         <v>MTR</v>
@@ -41752,10 +41752,10 @@
         <v>1181</v>
       </c>
       <c r="B1182" t="str">
-        <v>FG-401071</v>
+        <v>FG-401070</v>
       </c>
       <c r="C1182" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1182" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41767,7 +41767,7 @@
         <v>General</v>
       </c>
       <c r="G1182" t="str">
-        <v>150MM 6 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1182" t="str">
         <v>MTR</v>
@@ -41787,10 +41787,10 @@
         <v>1182</v>
       </c>
       <c r="B1183" t="str">
-        <v>FG-401072</v>
+        <v>FG-401071</v>
       </c>
       <c r="C1183" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1183" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41802,7 +41802,7 @@
         <v>General</v>
       </c>
       <c r="G1183" t="str">
-        <v>175MM 7 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1183" t="str">
         <v>MTR</v>
@@ -41822,10 +41822,10 @@
         <v>1183</v>
       </c>
       <c r="B1184" t="str">
-        <v>FG-401073</v>
+        <v>FG-401072</v>
       </c>
       <c r="C1184" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1184" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41837,7 +41837,7 @@
         <v>General</v>
       </c>
       <c r="G1184" t="str">
-        <v>200MM 8 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1184" t="str">
         <v>MTR</v>
@@ -41857,13 +41857,13 @@
         <v>1184</v>
       </c>
       <c r="B1185" t="str">
-        <v>FG-401074</v>
+        <v>FG-401073</v>
       </c>
       <c r="C1185" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1185" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
       </c>
       <c r="E1185" t="str">
         <v>UPVC CASING PIPES</v>
@@ -41872,7 +41872,7 @@
         <v>General</v>
       </c>
       <c r="G1185" t="str">
-        <v>125MM 5 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1185" t="str">
         <v>MTR</v>
@@ -41884,7 +41884,7 @@
         <v>Active</v>
       </c>
       <c r="K1185" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 40MM 1 1/2 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1186">
@@ -41892,10 +41892,10 @@
         <v>1185</v>
       </c>
       <c r="B1186" t="str">
-        <v>FG-401075</v>
+        <v>FG-401074</v>
       </c>
       <c r="C1186" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1186" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41907,7 +41907,7 @@
         <v>General</v>
       </c>
       <c r="G1186" t="str">
-        <v>150MM 6 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1186" t="str">
         <v>MTR</v>
@@ -41927,10 +41927,10 @@
         <v>1186</v>
       </c>
       <c r="B1187" t="str">
-        <v>FG-401076</v>
+        <v>FG-401075</v>
       </c>
       <c r="C1187" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1187" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41942,7 +41942,7 @@
         <v>General</v>
       </c>
       <c r="G1187" t="str">
-        <v>175MM 7 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1187" t="str">
         <v>MTR</v>
@@ -41962,10 +41962,10 @@
         <v>1187</v>
       </c>
       <c r="B1188" t="str">
-        <v>FG-401077</v>
+        <v>FG-401076</v>
       </c>
       <c r="C1188" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1188" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41977,7 +41977,7 @@
         <v>General</v>
       </c>
       <c r="G1188" t="str">
-        <v>200MM 8 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1188" t="str">
         <v>MTR</v>
@@ -41997,13 +41997,13 @@
         <v>1188</v>
       </c>
       <c r="B1189" t="str">
-        <v>FG-401149</v>
+        <v>FG-401077</v>
       </c>
       <c r="C1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M (140MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
       </c>
       <c r="E1189" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42012,7 +42012,7 @@
         <v>General</v>
       </c>
       <c r="G1189" t="str">
-        <v>140MM 5 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1189" t="str">
         <v>MTR</v>
@@ -42024,7 +42024,7 @@
         <v>Active</v>
       </c>
       <c r="K1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M. Available sizes: 140MM 5 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1190">
@@ -42032,13 +42032,13 @@
         <v>1189</v>
       </c>
       <c r="B1190" t="str">
-        <v>FG-401150</v>
+        <v>FG-401149</v>
       </c>
       <c r="C1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M (140MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M (140MM 5 Inch)</v>
       </c>
       <c r="D1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M</v>
       </c>
       <c r="E1190" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42059,7 +42059,7 @@
         <v>Active</v>
       </c>
       <c r="K1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M. Available sizes: 140MM 5 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M. Available sizes: 140MM 5 Inch.</v>
       </c>
     </row>
     <row r="1191">
@@ -42067,13 +42067,13 @@
         <v>1190</v>
       </c>
       <c r="B1191" t="str">
-        <v>FG-401078</v>
+        <v>FG-401150</v>
       </c>
       <c r="C1191" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M (140MM 5 Inch)</v>
       </c>
       <c r="D1191" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M</v>
       </c>
       <c r="E1191" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42082,7 +42082,7 @@
         <v>General</v>
       </c>
       <c r="G1191" t="str">
-        <v>125MM 5 Inch</v>
+        <v>140MM 5 Inch</v>
       </c>
       <c r="H1191" t="str">
         <v>MTR</v>
@@ -42094,7 +42094,7 @@
         <v>Active</v>
       </c>
       <c r="K1191" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M. Available sizes: 140MM 5 Inch.</v>
       </c>
     </row>
     <row r="1192">
@@ -42102,10 +42102,10 @@
         <v>1191</v>
       </c>
       <c r="B1192" t="str">
-        <v>FG-401079</v>
+        <v>FG-401078</v>
       </c>
       <c r="C1192" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1192" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42117,7 +42117,7 @@
         <v>General</v>
       </c>
       <c r="G1192" t="str">
-        <v>150MM 6 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1192" t="str">
         <v>MTR</v>
@@ -42137,10 +42137,10 @@
         <v>1192</v>
       </c>
       <c r="B1193" t="str">
-        <v>FG-401080</v>
+        <v>FG-401079</v>
       </c>
       <c r="C1193" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1193" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42152,7 +42152,7 @@
         <v>General</v>
       </c>
       <c r="G1193" t="str">
-        <v>175MM 7 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1193" t="str">
         <v>MTR</v>
@@ -42172,10 +42172,10 @@
         <v>1193</v>
       </c>
       <c r="B1194" t="str">
-        <v>FG-401081</v>
+        <v>FG-401080</v>
       </c>
       <c r="C1194" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1194" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42187,7 +42187,7 @@
         <v>General</v>
       </c>
       <c r="G1194" t="str">
-        <v>200MM 8 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1194" t="str">
         <v>MTR</v>
@@ -42207,13 +42207,13 @@
         <v>1194</v>
       </c>
       <c r="B1195" t="str">
-        <v>FG-401119</v>
+        <v>FG-401081</v>
       </c>
       <c r="C1195" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1195" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
       </c>
       <c r="E1195" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42222,7 +42222,7 @@
         <v>General</v>
       </c>
       <c r="G1195" t="str">
-        <v>35MM 1 1/4 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1195" t="str">
         <v>MTR</v>
@@ -42234,7 +42234,7 @@
         <v>Active</v>
       </c>
       <c r="K1195" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1196">
@@ -42242,10 +42242,10 @@
         <v>1195</v>
       </c>
       <c r="B1196" t="str">
-        <v>FG-401121</v>
+        <v>FG-401119</v>
       </c>
       <c r="C1196" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (50MM 2 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
       </c>
       <c r="D1196" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42257,7 +42257,7 @@
         <v>General</v>
       </c>
       <c r="G1196" t="str">
-        <v>50MM 2 Inch</v>
+        <v>35MM 1 1/4 Inch</v>
       </c>
       <c r="H1196" t="str">
         <v>MTR</v>
@@ -42277,10 +42277,10 @@
         <v>1196</v>
       </c>
       <c r="B1197" t="str">
-        <v>FG-401122</v>
+        <v>FG-401121</v>
       </c>
       <c r="C1197" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (100MM 4 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (50MM 2 Inch)</v>
       </c>
       <c r="D1197" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42292,7 +42292,7 @@
         <v>General</v>
       </c>
       <c r="G1197" t="str">
-        <v>100MM 4 Inch</v>
+        <v>50MM 2 Inch</v>
       </c>
       <c r="H1197" t="str">
         <v>MTR</v>
@@ -42312,10 +42312,10 @@
         <v>1197</v>
       </c>
       <c r="B1198" t="str">
-        <v>FG-401123</v>
+        <v>FG-401122</v>
       </c>
       <c r="C1198" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (100MM 4 Inch)</v>
       </c>
       <c r="D1198" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42327,7 +42327,7 @@
         <v>General</v>
       </c>
       <c r="G1198" t="str">
-        <v>125MM 5 Inch</v>
+        <v>100MM 4 Inch</v>
       </c>
       <c r="H1198" t="str">
         <v>MTR</v>
@@ -42347,10 +42347,10 @@
         <v>1198</v>
       </c>
       <c r="B1199" t="str">
-        <v>FG-401124</v>
+        <v>FG-401123</v>
       </c>
       <c r="C1199" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1199" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42362,7 +42362,7 @@
         <v>General</v>
       </c>
       <c r="G1199" t="str">
-        <v>150MM 6 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1199" t="str">
         <v>MTR</v>
@@ -42382,10 +42382,10 @@
         <v>1199</v>
       </c>
       <c r="B1200" t="str">
-        <v>FG-401125</v>
+        <v>FG-401124</v>
       </c>
       <c r="C1200" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1200" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42397,7 +42397,7 @@
         <v>General</v>
       </c>
       <c r="G1200" t="str">
-        <v>175MM 7 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1200" t="str">
         <v>MTR</v>
@@ -42417,10 +42417,10 @@
         <v>1200</v>
       </c>
       <c r="B1201" t="str">
-        <v>FG-401126</v>
+        <v>FG-401125</v>
       </c>
       <c r="C1201" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1201" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42432,7 +42432,7 @@
         <v>General</v>
       </c>
       <c r="G1201" t="str">
-        <v>200MM 8 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1201" t="str">
         <v>MTR</v>
@@ -42452,22 +42452,22 @@
         <v>1201</v>
       </c>
       <c r="B1202" t="str">
-        <v>FG-401166</v>
+        <v>FG-401126</v>
       </c>
       <c r="C1202" t="str">
-        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG COUPLER TYPE)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1202" t="str">
-        <v>COLOUMN PIPE ECO V4</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
       </c>
       <c r="E1202" t="str">
-        <v>UPVC COLUMN PIPES</v>
+        <v>UPVC CASING PIPES</v>
       </c>
       <c r="F1202" t="str">
         <v>General</v>
       </c>
       <c r="G1202" t="str">
-        <v>33MM 12.5KG COUPLER TYPE</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1202" t="str">
         <v>MTR</v>
@@ -42479,7 +42479,7 @@
         <v>Active</v>
       </c>
       <c r="K1202" t="str">
-        <v>COLOUMN PIPE ECO V4 for submersible pump systems.</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1203">
@@ -42487,10 +42487,10 @@
         <v>1202</v>
       </c>
       <c r="B1203" t="str">
-        <v>FG-401162</v>
+        <v>FG-401166</v>
       </c>
       <c r="C1203" t="str">
-        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG BELL END TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1203" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42502,7 +42502,7 @@
         <v>General</v>
       </c>
       <c r="G1203" t="str">
-        <v>33MM 12.5KG BELL END TYPE</v>
+        <v>33MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1203" t="str">
         <v>MTR</v>
@@ -42522,10 +42522,10 @@
         <v>1203</v>
       </c>
       <c r="B1204" t="str">
-        <v>FG-401165</v>
+        <v>FG-401162</v>
       </c>
       <c r="C1204" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 10KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG BELL END TYPE)</v>
       </c>
       <c r="D1204" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42537,7 +42537,7 @@
         <v>General</v>
       </c>
       <c r="G1204" t="str">
-        <v>42MM 10KG COUPLER TYPE</v>
+        <v>33MM 12.5KG BELL END TYPE</v>
       </c>
       <c r="H1204" t="str">
         <v>MTR</v>
@@ -42557,10 +42557,10 @@
         <v>1204</v>
       </c>
       <c r="B1205" t="str">
-        <v>FG-401167</v>
+        <v>FG-401165</v>
       </c>
       <c r="C1205" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 10KG COUPLER TYPE)</v>
       </c>
       <c r="D1205" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42572,7 +42572,7 @@
         <v>General</v>
       </c>
       <c r="G1205" t="str">
-        <v>42MM 12.5KG COUPLER TYPE</v>
+        <v>42MM 10KG COUPLER TYPE</v>
       </c>
       <c r="H1205" t="str">
         <v>MTR</v>
@@ -42592,10 +42592,10 @@
         <v>1205</v>
       </c>
       <c r="B1206" t="str">
-        <v>FG-401163</v>
+        <v>FG-401167</v>
       </c>
       <c r="C1206" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG BELL END TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1206" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42607,7 +42607,7 @@
         <v>General</v>
       </c>
       <c r="G1206" t="str">
-        <v>42MM 12.5KG BELL END TYPE</v>
+        <v>42MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1206" t="str">
         <v>MTR</v>
@@ -42627,10 +42627,10 @@
         <v>1206</v>
       </c>
       <c r="B1207" t="str">
-        <v>FG-401164</v>
+        <v>FG-401163</v>
       </c>
       <c r="C1207" t="str">
-        <v>COLOUMN PIPE ECO V4 (48MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG BELL END TYPE)</v>
       </c>
       <c r="D1207" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42642,7 +42642,7 @@
         <v>General</v>
       </c>
       <c r="G1207" t="str">
-        <v>48MM 12.5KG COUPLER TYPE</v>
+        <v>42MM 12.5KG BELL END TYPE</v>
       </c>
       <c r="H1207" t="str">
         <v>MTR</v>
@@ -42662,10 +42662,10 @@
         <v>1207</v>
       </c>
       <c r="B1208" t="str">
-        <v>FG-401168</v>
+        <v>FG-401164</v>
       </c>
       <c r="C1208" t="str">
-        <v>COLOUMN PIPE ECO V4 (60MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (48MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1208" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42677,7 +42677,7 @@
         <v>General</v>
       </c>
       <c r="G1208" t="str">
-        <v>60MM 12.5KG COUPLER TYPE</v>
+        <v>48MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1208" t="str">
         <v>MTR</v>
@@ -42697,13 +42697,13 @@
         <v>1208</v>
       </c>
       <c r="B1209" t="str">
-        <v>FG-401175</v>
+        <v>FG-401168</v>
       </c>
       <c r="C1209" t="str">
-        <v>COLOUMN PIPE MEDIUM (33MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (60MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1209" t="str">
-        <v>COLOUMN PIPE MEDIUM</v>
+        <v>COLOUMN PIPE ECO V4</v>
       </c>
       <c r="E1209" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -42712,7 +42712,7 @@
         <v>General</v>
       </c>
       <c r="G1209" t="str">
-        <v>33MM 18KG COUPLER TYPE</v>
+        <v>60MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1209" t="str">
         <v>MTR</v>
@@ -42724,7 +42724,7 @@
         <v>Active</v>
       </c>
       <c r="K1209" t="str">
-        <v>COLOUMN PIPE MEDIUM for submersible pump systems.</v>
+        <v>COLOUMN PIPE ECO V4 for submersible pump systems.</v>
       </c>
     </row>
     <row r="1210">
@@ -42732,10 +42732,10 @@
         <v>1209</v>
       </c>
       <c r="B1210" t="str">
-        <v>FG-401177</v>
+        <v>FG-401175</v>
       </c>
       <c r="C1210" t="str">
-        <v>COLOUMN PIPE MEDIUM (42MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (33MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1210" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42747,7 +42747,7 @@
         <v>General</v>
       </c>
       <c r="G1210" t="str">
-        <v>42MM 18KG COUPLER TYPE</v>
+        <v>33MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1210" t="str">
         <v>MTR</v>
@@ -42767,10 +42767,10 @@
         <v>1210</v>
       </c>
       <c r="B1211" t="str">
-        <v>FG-401176</v>
+        <v>FG-401177</v>
       </c>
       <c r="C1211" t="str">
-        <v>COLOUMN PIPE MEDIUM (48MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (42MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1211" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42782,7 +42782,7 @@
         <v>General</v>
       </c>
       <c r="G1211" t="str">
-        <v>48MM 18KG COUPLER TYPE</v>
+        <v>42MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1211" t="str">
         <v>MTR</v>
@@ -42802,10 +42802,10 @@
         <v>1211</v>
       </c>
       <c r="B1212" t="str">
-        <v>FG-401178</v>
+        <v>FG-401176</v>
       </c>
       <c r="C1212" t="str">
-        <v>COLOUMN PIPE MEDIUM (60MM 15KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (48MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1212" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42817,7 +42817,7 @@
         <v>General</v>
       </c>
       <c r="G1212" t="str">
-        <v>60MM 15KG COUPLER TYPE</v>
+        <v>48MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1212" t="str">
         <v>MTR</v>
@@ -42837,10 +42837,10 @@
         <v>1212</v>
       </c>
       <c r="B1213" t="str">
-        <v>FG-401180</v>
+        <v>FG-401178</v>
       </c>
       <c r="C1213" t="str">
-        <v>COLOUMN PIPE MEDIUM (75MM 10KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (60MM 15KG COUPLER TYPE)</v>
       </c>
       <c r="D1213" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42852,7 +42852,7 @@
         <v>General</v>
       </c>
       <c r="G1213" t="str">
-        <v>75MM 10KG COUPLER TYPE</v>
+        <v>60MM 15KG COUPLER TYPE</v>
       </c>
       <c r="H1213" t="str">
         <v>MTR</v>
@@ -42872,13 +42872,13 @@
         <v>1213</v>
       </c>
       <c r="B1214" t="str">
-        <v>FG-401169</v>
+        <v>FG-401180</v>
       </c>
       <c r="C1214" t="str">
-        <v>COLOUMN PIPE STANDARD (33MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (75MM 10KG COUPLER TYPE)</v>
       </c>
       <c r="D1214" t="str">
-        <v>COLOUMN PIPE STANDARD</v>
+        <v>COLOUMN PIPE MEDIUM</v>
       </c>
       <c r="E1214" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -42887,7 +42887,7 @@
         <v>General</v>
       </c>
       <c r="G1214" t="str">
-        <v>33MM 25KG COUPLER TYPE</v>
+        <v>75MM 10KG COUPLER TYPE</v>
       </c>
       <c r="H1214" t="str">
         <v>MTR</v>
@@ -42899,7 +42899,7 @@
         <v>Active</v>
       </c>
       <c r="K1214" t="str">
-        <v>COLOUMN PIPE STANDARD for submersible pump systems.</v>
+        <v>COLOUMN PIPE MEDIUM for submersible pump systems.</v>
       </c>
     </row>
     <row r="1215">
@@ -42907,10 +42907,10 @@
         <v>1214</v>
       </c>
       <c r="B1215" t="str">
-        <v>FG-401171</v>
+        <v>FG-401169</v>
       </c>
       <c r="C1215" t="str">
-        <v>COLOUMN PIPE STANDARD (42MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (33MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1215" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42922,7 +42922,7 @@
         <v>General</v>
       </c>
       <c r="G1215" t="str">
-        <v>42MM 25KG COUPLER TYPE</v>
+        <v>33MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1215" t="str">
         <v>MTR</v>
@@ -42942,10 +42942,10 @@
         <v>1215</v>
       </c>
       <c r="B1216" t="str">
-        <v>FG-401170</v>
+        <v>FG-401171</v>
       </c>
       <c r="C1216" t="str">
-        <v>COLOUMN PIPE STANDARD (48MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (42MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1216" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42957,7 +42957,7 @@
         <v>General</v>
       </c>
       <c r="G1216" t="str">
-        <v>48MM 25KG COUPLER TYPE</v>
+        <v>42MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1216" t="str">
         <v>MTR</v>
@@ -42977,10 +42977,10 @@
         <v>1216</v>
       </c>
       <c r="B1217" t="str">
-        <v>FG-401172</v>
+        <v>FG-401170</v>
       </c>
       <c r="C1217" t="str">
-        <v>COLOUMN PIPE STANDARD (60MM 20KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (48MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1217" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42992,7 +42992,7 @@
         <v>General</v>
       </c>
       <c r="G1217" t="str">
-        <v>60MM 20KG COUPLER TYPE</v>
+        <v>48MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1217" t="str">
         <v>MTR</v>
@@ -43012,10 +43012,10 @@
         <v>1217</v>
       </c>
       <c r="B1218" t="str">
-        <v>FG-401174</v>
+        <v>FG-401172</v>
       </c>
       <c r="C1218" t="str">
-        <v>COLOUMN PIPE STANDARD (75MM 20KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (60MM 20KG COUPLER TYPE)</v>
       </c>
       <c r="D1218" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -43027,7 +43027,7 @@
         <v>General</v>
       </c>
       <c r="G1218" t="str">
-        <v>75MM 20KG COUPLER TYPE</v>
+        <v>60MM 20KG COUPLER TYPE</v>
       </c>
       <c r="H1218" t="str">
         <v>MTR</v>
@@ -43047,13 +43047,13 @@
         <v>1218</v>
       </c>
       <c r="B1219" t="str">
-        <v>-</v>
+        <v>FG-401174</v>
       </c>
       <c r="C1219" t="str">
-        <v>3M STANDARD PLUS PIPE (60MM 25 COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (75MM 20KG COUPLER TYPE)</v>
       </c>
       <c r="D1219" t="str">
-        <v>3M STANDARD PLUS PIPE</v>
+        <v>COLOUMN PIPE STANDARD</v>
       </c>
       <c r="E1219" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43062,7 +43062,7 @@
         <v>General</v>
       </c>
       <c r="G1219" t="str">
-        <v>60MM 25 COUPLER TYPE</v>
+        <v>75MM 20KG COUPLER TYPE</v>
       </c>
       <c r="H1219" t="str">
         <v>MTR</v>
@@ -43074,7 +43074,7 @@
         <v>Active</v>
       </c>
       <c r="K1219" t="str">
-        <v>3M Standard Plus UPVC Column Pipe for submersible pump systems.</v>
+        <v>COLOUMN PIPE STANDARD for submersible pump systems.</v>
       </c>
     </row>
     <row r="1220">
@@ -43082,13 +43082,13 @@
         <v>1219</v>
       </c>
       <c r="B1220" t="str">
-        <v>FG-401182</v>
+        <v>-</v>
       </c>
       <c r="C1220" t="str">
-        <v>COLOUMN PIPE HEAVY (42MM 30KG COUPLER TYPE)</v>
+        <v>3M STANDARD PLUS PIPE (60MM 25 COUPLER TYPE)</v>
       </c>
       <c r="D1220" t="str">
-        <v>COLOUMN PIPE HEAVY</v>
+        <v>3M STANDARD PLUS PIPE</v>
       </c>
       <c r="E1220" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43097,7 +43097,7 @@
         <v>General</v>
       </c>
       <c r="G1220" t="str">
-        <v>42MM 30KG COUPLER TYPE</v>
+        <v>60MM 25 COUPLER TYPE</v>
       </c>
       <c r="H1220" t="str">
         <v>MTR</v>
@@ -43109,7 +43109,7 @@
         <v>Active</v>
       </c>
       <c r="K1220" t="str">
-        <v>COLOUMN PIPE HEAVY for submersible pump systems.</v>
+        <v>3M Standard Plus UPVC Column Pipe for submersible pump systems.</v>
       </c>
     </row>
     <row r="1221">
@@ -43117,10 +43117,10 @@
         <v>1220</v>
       </c>
       <c r="B1221" t="str">
-        <v>FG-401181</v>
+        <v>FG-401182</v>
       </c>
       <c r="C1221" t="str">
-        <v>COLOUMN PIPE HEAVY (48MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (42MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1221" t="str">
         <v>COLOUMN PIPE HEAVY</v>
@@ -43132,7 +43132,7 @@
         <v>General</v>
       </c>
       <c r="G1221" t="str">
-        <v>48MM 30KG COUPLER TYPE</v>
+        <v>42MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1221" t="str">
         <v>MTR</v>
@@ -43152,10 +43152,10 @@
         <v>1221</v>
       </c>
       <c r="B1222" t="str">
-        <v>FG-401183</v>
+        <v>FG-401181</v>
       </c>
       <c r="C1222" t="str">
-        <v>COLOUMN PIPE HEAVY (60MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (48MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1222" t="str">
         <v>COLOUMN PIPE HEAVY</v>
@@ -43167,7 +43167,7 @@
         <v>General</v>
       </c>
       <c r="G1222" t="str">
-        <v>60MM 30KG COUPLER TYPE</v>
+        <v>48MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1222" t="str">
         <v>MTR</v>
@@ -43187,13 +43187,13 @@
         <v>1222</v>
       </c>
       <c r="B1223" t="str">
-        <v>FG-401179</v>
+        <v>FG-401183</v>
       </c>
       <c r="C1223" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS (60MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (60MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1223" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS</v>
+        <v>COLOUMN PIPE HEAVY</v>
       </c>
       <c r="E1223" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43202,7 +43202,7 @@
         <v>General</v>
       </c>
       <c r="G1223" t="str">
-        <v>60MM 18KG COUPLER TYPE</v>
+        <v>60MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1223" t="str">
         <v>MTR</v>
@@ -43214,7 +43214,7 @@
         <v>Active</v>
       </c>
       <c r="K1223" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS for submersible pump systems.</v>
+        <v>COLOUMN PIPE HEAVY for submersible pump systems.</v>
       </c>
     </row>
     <row r="1224">
@@ -43222,34 +43222,34 @@
         <v>1223</v>
       </c>
       <c r="B1224" t="str">
-        <v>FG-401569</v>
+        <v>FG-401179</v>
       </c>
       <c r="C1224" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA (15 Inch)</v>
+        <v>COLOUMN PIPE MEDIUM PLUS (60MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1224" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA</v>
+        <v>COLOUMN PIPE MEDIUM PLUS</v>
       </c>
       <c r="E1224" t="str">
-        <v>HOUSEHOLD PRODUCTS</v>
+        <v>UPVC COLUMN PIPES</v>
       </c>
       <c r="F1224" t="str">
         <v>General</v>
       </c>
       <c r="G1224" t="str">
-        <v>15 Inch</v>
+        <v>60MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1224" t="str">
-        <v>BAGS</v>
+        <v>MTR</v>
       </c>
       <c r="I1224" t="str">
-        <v>75</v>
+        <v>-</v>
       </c>
       <c r="J1224" t="str">
         <v>Active</v>
       </c>
       <c r="K1224" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA high durability ghamela.</v>
+        <v>COLOUMN PIPE MEDIUM PLUS for submersible pump systems.</v>
       </c>
     </row>
     <row r="1225">
@@ -43257,13 +43257,13 @@
         <v>1224</v>
       </c>
       <c r="B1225" t="str">
-        <v>FG-401570</v>
+        <v>FG-401569</v>
       </c>
       <c r="C1225" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI (15 Inch)</v>
+        <v>CONSTRUCTION GHAMELA SHIVA (15 Inch)</v>
       </c>
       <c r="D1225" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI</v>
+        <v>CONSTRUCTION GHAMELA SHIVA</v>
       </c>
       <c r="E1225" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43284,7 +43284,7 @@
         <v>Active</v>
       </c>
       <c r="K1225" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI high durability ghamela.</v>
+        <v>CONSTRUCTION GHAMELA SHIVA high durability ghamela.</v>
       </c>
     </row>
     <row r="1226">
@@ -43292,13 +43292,13 @@
         <v>1225</v>
       </c>
       <c r="B1226" t="str">
-        <v>FG-401571</v>
+        <v>FG-401570</v>
       </c>
       <c r="C1226" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA (16 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA GOURI (15 Inch)</v>
       </c>
       <c r="D1226" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA</v>
+        <v>MULTIPURPOSE GHAMELA GOURI</v>
       </c>
       <c r="E1226" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43307,19 +43307,19 @@
         <v>General</v>
       </c>
       <c r="G1226" t="str">
-        <v>16 Inch</v>
+        <v>15 Inch</v>
       </c>
       <c r="H1226" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1226" t="str">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="J1226" t="str">
         <v>Active</v>
       </c>
       <c r="K1226" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA GOURI high durability ghamela.</v>
       </c>
     </row>
     <row r="1227">
@@ -43327,13 +43327,13 @@
         <v>1226</v>
       </c>
       <c r="B1227" t="str">
-        <v>FG-401573</v>
+        <v>FG-401571</v>
       </c>
       <c r="C1227" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV (18 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA (16 Inch)</v>
       </c>
       <c r="D1227" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA</v>
       </c>
       <c r="E1227" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43342,19 +43342,19 @@
         <v>General</v>
       </c>
       <c r="G1227" t="str">
-        <v>18 Inch</v>
+        <v>16 Inch</v>
       </c>
       <c r="H1227" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1227" t="str">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J1227" t="str">
         <v>Active</v>
       </c>
       <c r="K1227" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA high durability ghamela.</v>
       </c>
     </row>
     <row r="1228">
@@ -43362,13 +43362,13 @@
         <v>1227</v>
       </c>
       <c r="B1228" t="str">
-        <v>FG-401574</v>
+        <v>FG-401573</v>
       </c>
       <c r="C1228" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET (20 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV (18 Inch)</v>
       </c>
       <c r="D1228" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV</v>
       </c>
       <c r="E1228" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43377,19 +43377,19 @@
         <v>General</v>
       </c>
       <c r="G1228" t="str">
-        <v>20 Inch</v>
+        <v>18 Inch</v>
       </c>
       <c r="H1228" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1228" t="str">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J1228" t="str">
         <v>Active</v>
       </c>
       <c r="K1228" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV high durability ghamela.</v>
       </c>
     </row>
     <row r="1229">
@@ -43397,13 +43397,13 @@
         <v>1228</v>
       </c>
       <c r="B1229" t="str">
-        <v>FG-401572</v>
+        <v>FG-401574</v>
       </c>
       <c r="C1229" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI (17 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET (20 Inch)</v>
       </c>
       <c r="D1229" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET</v>
       </c>
       <c r="E1229" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43412,19 +43412,19 @@
         <v>General</v>
       </c>
       <c r="G1229" t="str">
-        <v>17 Inch</v>
+        <v>20 Inch</v>
       </c>
       <c r="H1229" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1229" t="str">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J1229" t="str">
         <v>Active</v>
       </c>
       <c r="K1229" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET high durability ghamela.</v>
       </c>
     </row>
     <row r="1230">
@@ -43432,13 +43432,13 @@
         <v>1229</v>
       </c>
       <c r="B1230" t="str">
-        <v>FG-401575</v>
+        <v>FG-401572</v>
       </c>
       <c r="C1230" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ (22 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI (17 Inch)</v>
       </c>
       <c r="D1230" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI</v>
       </c>
       <c r="E1230" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43447,19 +43447,19 @@
         <v>General</v>
       </c>
       <c r="G1230" t="str">
-        <v>22 Inch</v>
+        <v>17 Inch</v>
       </c>
       <c r="H1230" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1230" t="str">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J1230" t="str">
         <v>Active</v>
       </c>
       <c r="K1230" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI high durability ghamela.</v>
       </c>
     </row>
     <row r="1231">
@@ -43467,13 +43467,13 @@
         <v>1230</v>
       </c>
       <c r="B1231" t="str">
-        <v>FG-401578</v>
+        <v>FG-401575</v>
       </c>
       <c r="C1231" t="str">
-        <v>AQUA PLAST GHAMELA 16 (16 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ (22 Inch)</v>
       </c>
       <c r="D1231" t="str">
-        <v>AQUA PLAST GHAMELA 16</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ</v>
       </c>
       <c r="E1231" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43482,19 +43482,19 @@
         <v>General</v>
       </c>
       <c r="G1231" t="str">
-        <v>16 Inch</v>
+        <v>22 Inch</v>
       </c>
       <c r="H1231" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1231" t="str">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J1231" t="str">
         <v>Active</v>
       </c>
       <c r="K1231" t="str">
-        <v>AQUA PLAST GHAMELA 16 high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ high durability ghamela.</v>
       </c>
     </row>
     <row r="1232">
@@ -43502,13 +43502,13 @@
         <v>1231</v>
       </c>
       <c r="B1232" t="str">
-        <v>FG-401579</v>
+        <v>FG-401578</v>
       </c>
       <c r="C1232" t="str">
-        <v>AQUA PLAST GHAMELA 17 (17 Inch)</v>
+        <v>AQUA PLAST GHAMELA 16 (16 Inch)</v>
       </c>
       <c r="D1232" t="str">
-        <v>AQUA PLAST GHAMELA 17</v>
+        <v>AQUA PLAST GHAMELA 16</v>
       </c>
       <c r="E1232" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43517,7 +43517,7 @@
         <v>General</v>
       </c>
       <c r="G1232" t="str">
-        <v>17 Inch</v>
+        <v>16 Inch</v>
       </c>
       <c r="H1232" t="str">
         <v>BAGS</v>
@@ -43529,7 +43529,7 @@
         <v>Active</v>
       </c>
       <c r="K1232" t="str">
-        <v>AQUA PLAST GHAMELA 17 high durability ghamela.</v>
+        <v>AQUA PLAST GHAMELA 16 high durability ghamela.</v>
       </c>
     </row>
     <row r="1233">
@@ -43537,34 +43537,34 @@
         <v>1232</v>
       </c>
       <c r="B1233" t="str">
-        <v>FG-401364</v>
+        <v>FG-401579</v>
       </c>
       <c r="C1233" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1/2 15MM)</v>
+        <v>AQUA PLAST GHAMELA 17 (17 Inch)</v>
       </c>
       <c r="D1233" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE</v>
+        <v>AQUA PLAST GHAMELA 17</v>
       </c>
       <c r="E1233" t="str">
-        <v>Garden, Braided &amp; LDPE Pipes</v>
+        <v>HOUSEHOLD PRODUCTS</v>
       </c>
       <c r="F1233" t="str">
         <v>General</v>
       </c>
       <c r="G1233" t="str">
-        <v>1/2 15MM</v>
+        <v>17 Inch</v>
       </c>
       <c r="H1233" t="str">
-        <v>BDL</v>
+        <v>BAGS</v>
       </c>
       <c r="I1233" t="str">
-        <v>-</v>
+        <v>60</v>
       </c>
       <c r="J1233" t="str">
         <v>Active</v>
       </c>
       <c r="K1233" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE. Available sizes: 1/2 15MM, 3/4 20MM, 1 25MM, 1 1/4 32MM.</v>
+        <v>AQUA PLAST GHAMELA 17 high durability ghamela.</v>
       </c>
     </row>
     <row r="1234">
@@ -43572,10 +43572,10 @@
         <v>1233</v>
       </c>
       <c r="B1234" t="str">
-        <v>FG-401365</v>
+        <v>FG-401364</v>
       </c>
       <c r="C1234" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (3/4 20MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1/2 15MM)</v>
       </c>
       <c r="D1234" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43587,7 +43587,7 @@
         <v>General</v>
       </c>
       <c r="G1234" t="str">
-        <v>3/4 20MM</v>
+        <v>1/2 15MM</v>
       </c>
       <c r="H1234" t="str">
         <v>BDL</v>
@@ -43607,10 +43607,10 @@
         <v>1234</v>
       </c>
       <c r="B1235" t="str">
-        <v>FG-401366</v>
+        <v>FG-401365</v>
       </c>
       <c r="C1235" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1 25MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (3/4 20MM)</v>
       </c>
       <c r="D1235" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43622,7 +43622,7 @@
         <v>General</v>
       </c>
       <c r="G1235" t="str">
-        <v>1 25MM</v>
+        <v>3/4 20MM</v>
       </c>
       <c r="H1235" t="str">
         <v>BDL</v>
@@ -43642,10 +43642,10 @@
         <v>1235</v>
       </c>
       <c r="B1236" t="str">
-        <v>FG-401367</v>
+        <v>FG-401366</v>
       </c>
       <c r="C1236" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1 1/4 32MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1 25MM)</v>
       </c>
       <c r="D1236" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43657,7 +43657,7 @@
         <v>General</v>
       </c>
       <c r="G1236" t="str">
-        <v>1 1/4 32MM</v>
+        <v>1 25MM</v>
       </c>
       <c r="H1236" t="str">
         <v>BDL</v>
@@ -43677,13 +43677,13 @@
         <v>1236</v>
       </c>
       <c r="B1237" t="str">
-        <v>FG-401370</v>
+        <v>FG-401367</v>
       </c>
       <c r="C1237" t="str">
-        <v>GAP-ORA BRAIDED PIPE (15MM 1/2)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1 1/4 32MM)</v>
       </c>
       <c r="D1237" t="str">
-        <v>GAP-ORA BRAIDED PIPE</v>
+        <v>GAP-ORA FLOW GARDEN PIPE</v>
       </c>
       <c r="E1237" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43692,7 +43692,7 @@
         <v>General</v>
       </c>
       <c r="G1237" t="str">
-        <v>15MM 1/2</v>
+        <v>1 1/4 32MM</v>
       </c>
       <c r="H1237" t="str">
         <v>BDL</v>
@@ -43704,7 +43704,7 @@
         <v>Active</v>
       </c>
       <c r="K1237" t="str">
-        <v>GAP-ORA BRAIDED PIPE.</v>
+        <v>GAP-ORA FLOW GARDEN PIPE. Available sizes: 1/2 15MM, 3/4 20MM, 1 25MM, 1 1/4 32MM.</v>
       </c>
     </row>
     <row r="1238">
@@ -43712,10 +43712,10 @@
         <v>1237</v>
       </c>
       <c r="B1238" t="str">
-        <v>FG-401371</v>
+        <v>FG-401370</v>
       </c>
       <c r="C1238" t="str">
-        <v>GAP-ORA BRAIDED PIPE (20MM 3/4)</v>
+        <v>GAP-ORA BRAIDED PIPE (15MM 1/2)</v>
       </c>
       <c r="D1238" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43727,7 +43727,7 @@
         <v>General</v>
       </c>
       <c r="G1238" t="str">
-        <v>20MM 3/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1238" t="str">
         <v>BDL</v>
@@ -43747,10 +43747,10 @@
         <v>1238</v>
       </c>
       <c r="B1239" t="str">
-        <v>FG-401372</v>
+        <v>FG-401371</v>
       </c>
       <c r="C1239" t="str">
-        <v>GAP-ORA BRAIDED PIPE (25MM 1)</v>
+        <v>GAP-ORA BRAIDED PIPE (20MM 3/4)</v>
       </c>
       <c r="D1239" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43762,7 +43762,7 @@
         <v>General</v>
       </c>
       <c r="G1239" t="str">
-        <v>25MM 1</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1239" t="str">
         <v>BDL</v>
@@ -43782,10 +43782,10 @@
         <v>1239</v>
       </c>
       <c r="B1240" t="str">
-        <v>FG-401373</v>
+        <v>FG-401372</v>
       </c>
       <c r="C1240" t="str">
-        <v>GAP-ORA BRAIDED PIPE (32MM 1 1/4)</v>
+        <v>GAP-ORA BRAIDED PIPE (25MM 1)</v>
       </c>
       <c r="D1240" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43797,7 +43797,7 @@
         <v>General</v>
       </c>
       <c r="G1240" t="str">
-        <v>32MM 1 1/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1240" t="str">
         <v>BDL</v>
@@ -43817,13 +43817,13 @@
         <v>1240</v>
       </c>
       <c r="B1241" t="str">
-        <v>FG-401355</v>
+        <v>FG-401373</v>
       </c>
       <c r="C1241" t="str">
-        <v>GARDEN FOAM PIPES (15MM 1/2)</v>
+        <v>GAP-ORA BRAIDED PIPE (32MM 1 1/4)</v>
       </c>
       <c r="D1241" t="str">
-        <v>GARDEN FOAM PIPES</v>
+        <v>GAP-ORA BRAIDED PIPE</v>
       </c>
       <c r="E1241" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43832,7 +43832,7 @@
         <v>General</v>
       </c>
       <c r="G1241" t="str">
-        <v>15MM 1/2</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1241" t="str">
         <v>BDL</v>
@@ -43844,7 +43844,7 @@
         <v>Active</v>
       </c>
       <c r="K1241" t="str">
-        <v>GARDEN FOAM PIPES.</v>
+        <v>GAP-ORA BRAIDED PIPE.</v>
       </c>
     </row>
     <row r="1242">
@@ -43852,10 +43852,10 @@
         <v>1241</v>
       </c>
       <c r="B1242" t="str">
-        <v>FG-401356</v>
+        <v>FG-401355</v>
       </c>
       <c r="C1242" t="str">
-        <v>GARDEN FOAM PIPES (20MM 3/4)</v>
+        <v>GARDEN FOAM PIPES (15MM 1/2)</v>
       </c>
       <c r="D1242" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43867,7 +43867,7 @@
         <v>General</v>
       </c>
       <c r="G1242" t="str">
-        <v>20MM 3/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1242" t="str">
         <v>BDL</v>
@@ -43887,10 +43887,10 @@
         <v>1242</v>
       </c>
       <c r="B1243" t="str">
-        <v>FG-401369</v>
+        <v>FG-401356</v>
       </c>
       <c r="C1243" t="str">
-        <v>GARDEN FOAM PIPES (20MM 3/4 20MTR)</v>
+        <v>GARDEN FOAM PIPES (20MM 3/4)</v>
       </c>
       <c r="D1243" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43902,7 +43902,7 @@
         <v>General</v>
       </c>
       <c r="G1243" t="str">
-        <v>20MM 3/4 20MTR</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1243" t="str">
         <v>BDL</v>
@@ -43922,10 +43922,10 @@
         <v>1243</v>
       </c>
       <c r="B1244" t="str">
-        <v>FG-401357</v>
+        <v>FG-401369</v>
       </c>
       <c r="C1244" t="str">
-        <v>GARDEN FOAM PIPES (25MM 1)</v>
+        <v>GARDEN FOAM PIPES (20MM 3/4 20MTR)</v>
       </c>
       <c r="D1244" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43937,7 +43937,7 @@
         <v>General</v>
       </c>
       <c r="G1244" t="str">
-        <v>25MM 1</v>
+        <v>20MM 3/4 20MTR</v>
       </c>
       <c r="H1244" t="str">
         <v>BDL</v>
@@ -43957,10 +43957,10 @@
         <v>1244</v>
       </c>
       <c r="B1245" t="str">
-        <v>FG-401358</v>
+        <v>FG-401357</v>
       </c>
       <c r="C1245" t="str">
-        <v>GARDEN FOAM PIPES (32MM 1 1/4)</v>
+        <v>GARDEN FOAM PIPES (25MM 1)</v>
       </c>
       <c r="D1245" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43972,7 +43972,7 @@
         <v>General</v>
       </c>
       <c r="G1245" t="str">
-        <v>32MM 1 1/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1245" t="str">
         <v>BDL</v>
@@ -43992,13 +43992,13 @@
         <v>1245</v>
       </c>
       <c r="B1246" t="str">
-        <v>FG-401344</v>
+        <v>FG-401358</v>
       </c>
       <c r="C1246" t="str">
-        <v>BRAIDED PIPE (15MM 1/2)</v>
+        <v>GARDEN FOAM PIPES (32MM 1 1/4)</v>
       </c>
       <c r="D1246" t="str">
-        <v>BRAIDED PIPE</v>
+        <v>GARDEN FOAM PIPES</v>
       </c>
       <c r="E1246" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44007,7 +44007,7 @@
         <v>General</v>
       </c>
       <c r="G1246" t="str">
-        <v>15MM 1/2</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1246" t="str">
         <v>BDL</v>
@@ -44019,7 +44019,7 @@
         <v>Active</v>
       </c>
       <c r="K1246" t="str">
-        <v>Reinforced Braided Garden Pipe.</v>
+        <v>GARDEN FOAM PIPES.</v>
       </c>
     </row>
     <row r="1247">
@@ -44027,10 +44027,10 @@
         <v>1246</v>
       </c>
       <c r="B1247" t="str">
-        <v>FG-401345</v>
+        <v>FG-401344</v>
       </c>
       <c r="C1247" t="str">
-        <v>BRAIDED PIPE (20MM 3/4)</v>
+        <v>BRAIDED PIPE (15MM 1/2)</v>
       </c>
       <c r="D1247" t="str">
         <v>BRAIDED PIPE</v>
@@ -44042,7 +44042,7 @@
         <v>General</v>
       </c>
       <c r="G1247" t="str">
-        <v>20MM 3/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1247" t="str">
         <v>BDL</v>
@@ -44062,10 +44062,10 @@
         <v>1247</v>
       </c>
       <c r="B1248" t="str">
-        <v>FG-401346</v>
+        <v>FG-401345</v>
       </c>
       <c r="C1248" t="str">
-        <v>BRAIDED PIPE (25MM 1)</v>
+        <v>BRAIDED PIPE (20MM 3/4)</v>
       </c>
       <c r="D1248" t="str">
         <v>BRAIDED PIPE</v>
@@ -44077,7 +44077,7 @@
         <v>General</v>
       </c>
       <c r="G1248" t="str">
-        <v>25MM 1</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1248" t="str">
         <v>BDL</v>
@@ -44097,10 +44097,10 @@
         <v>1248</v>
       </c>
       <c r="B1249" t="str">
-        <v>FG-401363</v>
+        <v>FG-401346</v>
       </c>
       <c r="C1249" t="str">
-        <v>BRAIDED PIPE (32MM 1 1/4)</v>
+        <v>BRAIDED PIPE (25MM 1)</v>
       </c>
       <c r="D1249" t="str">
         <v>BRAIDED PIPE</v>
@@ -44112,7 +44112,7 @@
         <v>General</v>
       </c>
       <c r="G1249" t="str">
-        <v>32MM 1 1/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1249" t="str">
         <v>BDL</v>
@@ -44132,13 +44132,13 @@
         <v>1249</v>
       </c>
       <c r="B1250" t="str">
-        <v>FG-401374</v>
+        <v>FG-401363</v>
       </c>
       <c r="C1250" t="str">
-        <v>LEVEL PIPE (6MM)</v>
+        <v>BRAIDED PIPE (32MM 1 1/4)</v>
       </c>
       <c r="D1250" t="str">
-        <v>LEVEL PIPE</v>
+        <v>BRAIDED PIPE</v>
       </c>
       <c r="E1250" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44147,7 +44147,7 @@
         <v>General</v>
       </c>
       <c r="G1250" t="str">
-        <v>6MM</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1250" t="str">
         <v>BDL</v>
@@ -44159,7 +44159,7 @@
         <v>Active</v>
       </c>
       <c r="K1250" t="str">
-        <v>Transparent Level Pipe for construction &amp; garden work.</v>
+        <v>Reinforced Braided Garden Pipe.</v>
       </c>
     </row>
     <row r="1251">
@@ -44167,13 +44167,13 @@
         <v>1250</v>
       </c>
       <c r="B1251" t="str">
-        <v>FG-401340</v>
+        <v>FG-401374</v>
       </c>
       <c r="C1251" t="str">
-        <v>GARDEN PIPES SUPER FLOW (15MM 1/2)</v>
+        <v>LEVEL PIPE (6MM)</v>
       </c>
       <c r="D1251" t="str">
-        <v>GARDEN PIPES SUPER FLOW</v>
+        <v>LEVEL PIPE</v>
       </c>
       <c r="E1251" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44182,7 +44182,7 @@
         <v>General</v>
       </c>
       <c r="G1251" t="str">
-        <v>15MM 1/2</v>
+        <v>6MM</v>
       </c>
       <c r="H1251" t="str">
         <v>BDL</v>
@@ -44194,7 +44194,7 @@
         <v>Active</v>
       </c>
       <c r="K1251" t="str">
-        <v>GARDEN PIPES SUPER FLOW.</v>
+        <v>Transparent Level Pipe for construction &amp; garden work.</v>
       </c>
     </row>
     <row r="1252">
@@ -44202,10 +44202,10 @@
         <v>1251</v>
       </c>
       <c r="B1252" t="str">
-        <v>FG-401341</v>
+        <v>FG-401340</v>
       </c>
       <c r="C1252" t="str">
-        <v>GARDEN PIPES SUPER FLOW (20MM 3/4)</v>
+        <v>GARDEN PIPES SUPER FLOW (15MM 1/2)</v>
       </c>
       <c r="D1252" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44217,7 +44217,7 @@
         <v>General</v>
       </c>
       <c r="G1252" t="str">
-        <v>20MM 3/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1252" t="str">
         <v>BDL</v>
@@ -44237,10 +44237,10 @@
         <v>1252</v>
       </c>
       <c r="B1253" t="str">
-        <v>FG-401652</v>
+        <v>FG-401341</v>
       </c>
       <c r="C1253" t="str">
-        <v>GARDEN PIPES SUPER FLOW (20MM 3/4 15MTR)</v>
+        <v>GARDEN PIPES SUPER FLOW (20MM 3/4)</v>
       </c>
       <c r="D1253" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44252,7 +44252,7 @@
         <v>General</v>
       </c>
       <c r="G1253" t="str">
-        <v>20MM 3/4 15MTR</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1253" t="str">
         <v>BDL</v>
@@ -44272,10 +44272,10 @@
         <v>1253</v>
       </c>
       <c r="B1254" t="str">
-        <v>FG-401342</v>
+        <v>FG-401652</v>
       </c>
       <c r="C1254" t="str">
-        <v>GARDEN PIPES SUPER FLOW (25MM 1)</v>
+        <v>GARDEN PIPES SUPER FLOW (20MM 3/4 15MTR)</v>
       </c>
       <c r="D1254" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44287,7 +44287,7 @@
         <v>General</v>
       </c>
       <c r="G1254" t="str">
-        <v>25MM 1</v>
+        <v>20MM 3/4 15MTR</v>
       </c>
       <c r="H1254" t="str">
         <v>BDL</v>
@@ -44307,10 +44307,10 @@
         <v>1254</v>
       </c>
       <c r="B1255" t="str">
-        <v>FG-401343</v>
+        <v>FG-401342</v>
       </c>
       <c r="C1255" t="str">
-        <v>GARDEN PIPES SUPER FLOW (32MM 1 1/4)</v>
+        <v>GARDEN PIPES SUPER FLOW (25MM 1)</v>
       </c>
       <c r="D1255" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44322,7 +44322,7 @@
         <v>General</v>
       </c>
       <c r="G1255" t="str">
-        <v>32MM 1 1/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1255" t="str">
         <v>BDL</v>
@@ -44342,10 +44342,10 @@
         <v>1255</v>
       </c>
       <c r="B1256" t="str">
-        <v>FG-401627</v>
+        <v>FG-401343</v>
       </c>
       <c r="C1256" t="str">
-        <v>GARDEN PIPES SUPER FLOW (40MM 1 1/2)</v>
+        <v>GARDEN PIPES SUPER FLOW (32MM 1 1/4)</v>
       </c>
       <c r="D1256" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44357,7 +44357,7 @@
         <v>General</v>
       </c>
       <c r="G1256" t="str">
-        <v>40MM 1 1/2</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1256" t="str">
         <v>BDL</v>
@@ -44377,34 +44377,34 @@
         <v>1256</v>
       </c>
       <c r="B1257" t="str">
-        <v>FG-401552</v>
+        <v>FG-401627</v>
       </c>
       <c r="C1257" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2 inch)</v>
+        <v>GARDEN PIPES SUPER FLOW (40MM 1 1/2)</v>
       </c>
       <c r="D1257" t="str">
-        <v>EDGE SERIES SHORT BODY TAP</v>
+        <v>GARDEN PIPES SUPER FLOW</v>
       </c>
       <c r="E1257" t="str">
-        <v>FAUCETS</v>
+        <v>Garden, Braided &amp; LDPE Pipes</v>
       </c>
       <c r="F1257" t="str">
         <v>General</v>
       </c>
       <c r="G1257" t="str">
-        <v>1/2 inch</v>
+        <v>40MM 1 1/2</v>
       </c>
       <c r="H1257" t="str">
-        <v>NOS</v>
-      </c>
-      <c r="I1257">
-        <v>20</v>
+        <v>BDL</v>
+      </c>
+      <c r="I1257" t="str">
+        <v>-</v>
       </c>
       <c r="J1257" t="str">
         <v>Active</v>
       </c>
       <c r="K1257" t="str">
-        <v>EDGE SERIES SHORT BODY TAP high quality faucet.</v>
+        <v>GARDEN PIPES SUPER FLOW.</v>
       </c>
     </row>
     <row r="1258">
@@ -44415,7 +44415,7 @@
         <v>FG-401552</v>
       </c>
       <c r="C1258" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2 inch)</v>
       </c>
       <c r="D1258" t="str">
         <v>EDGE SERIES SHORT BODY TAP</v>
@@ -44427,7 +44427,7 @@
         <v>General</v>
       </c>
       <c r="G1258" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1258" t="str">
         <v>NOS</v>
@@ -44450,7 +44450,7 @@
         <v>FG-401552</v>
       </c>
       <c r="C1259" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2")</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2)</v>
       </c>
       <c r="D1259" t="str">
         <v>EDGE SERIES SHORT BODY TAP</v>
@@ -44462,7 +44462,7 @@
         <v>General</v>
       </c>
       <c r="G1259" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1259" t="str">
         <v>NOS</v>
@@ -44482,13 +44482,13 @@
         <v>1259</v>
       </c>
       <c r="B1260" t="str">
-        <v>FG-401551</v>
+        <v>FG-401552</v>
       </c>
       <c r="C1260" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2 inch)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2")</v>
       </c>
       <c r="D1260" t="str">
-        <v>EDGE SERIES LONG BODY TAP</v>
+        <v>EDGE SERIES SHORT BODY TAP</v>
       </c>
       <c r="E1260" t="str">
         <v>FAUCETS</v>
@@ -44497,19 +44497,19 @@
         <v>General</v>
       </c>
       <c r="G1260" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1260" t="str">
         <v>NOS</v>
       </c>
       <c r="I1260">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J1260" t="str">
         <v>Active</v>
       </c>
       <c r="K1260" t="str">
-        <v>EDGE SERIES LONG BODY TAP high quality faucet.</v>
+        <v>EDGE SERIES SHORT BODY TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1261">
@@ -44520,7 +44520,7 @@
         <v>FG-401551</v>
       </c>
       <c r="C1261" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2)</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2 inch)</v>
       </c>
       <c r="D1261" t="str">
         <v>EDGE SERIES LONG BODY TAP</v>
@@ -44532,7 +44532,7 @@
         <v>General</v>
       </c>
       <c r="G1261" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1261" t="str">
         <v>NOS</v>
@@ -44555,7 +44555,7 @@
         <v>FG-401551</v>
       </c>
       <c r="C1262" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2")</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2)</v>
       </c>
       <c r="D1262" t="str">
         <v>EDGE SERIES LONG BODY TAP</v>
@@ -44567,7 +44567,7 @@
         <v>General</v>
       </c>
       <c r="G1262" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1262" t="str">
         <v>NOS</v>
@@ -44587,13 +44587,13 @@
         <v>1262</v>
       </c>
       <c r="B1263" t="str">
-        <v>FG-401549</v>
+        <v>FG-401551</v>
       </c>
       <c r="C1263" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2 inch)</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2")</v>
       </c>
       <c r="D1263" t="str">
-        <v>EDGE SERIES SWAN NECK</v>
+        <v>EDGE SERIES LONG BODY TAP</v>
       </c>
       <c r="E1263" t="str">
         <v>FAUCETS</v>
@@ -44602,19 +44602,19 @@
         <v>General</v>
       </c>
       <c r="G1263" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1263" t="str">
         <v>NOS</v>
       </c>
       <c r="I1263">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J1263" t="str">
         <v>Active</v>
       </c>
       <c r="K1263" t="str">
-        <v>EDGE SERIES SWAN NECK high quality faucet.</v>
+        <v>EDGE SERIES LONG BODY TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1264">
@@ -44625,7 +44625,7 @@
         <v>FG-401549</v>
       </c>
       <c r="C1264" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2)</v>
+        <v>EDGE SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1264" t="str">
         <v>EDGE SERIES SWAN NECK</v>
@@ -44637,7 +44637,7 @@
         <v>General</v>
       </c>
       <c r="G1264" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1264" t="str">
         <v>NOS</v>
@@ -44660,7 +44660,7 @@
         <v>FG-401549</v>
       </c>
       <c r="C1265" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2")</v>
+        <v>EDGE SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1265" t="str">
         <v>EDGE SERIES SWAN NECK</v>
@@ -44672,7 +44672,7 @@
         <v>General</v>
       </c>
       <c r="G1265" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1265" t="str">
         <v>NOS</v>
@@ -44692,13 +44692,13 @@
         <v>1265</v>
       </c>
       <c r="B1266" t="str">
-        <v>FG-401546</v>
+        <v>FG-401549</v>
       </c>
       <c r="C1266" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>EDGE SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1266" t="str">
-        <v>EDGE SERIES ANGULAR VALVE</v>
+        <v>EDGE SERIES SWAN NECK</v>
       </c>
       <c r="E1266" t="str">
         <v>FAUCETS</v>
@@ -44707,19 +44707,19 @@
         <v>General</v>
       </c>
       <c r="G1266" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1266" t="str">
         <v>NOS</v>
       </c>
       <c r="I1266">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J1266" t="str">
         <v>Active</v>
       </c>
       <c r="K1266" t="str">
-        <v>EDGE SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>EDGE SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1267">
@@ -44730,7 +44730,7 @@
         <v>FG-401546</v>
       </c>
       <c r="C1267" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2)</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1267" t="str">
         <v>EDGE SERIES ANGULAR VALVE</v>
@@ -44742,7 +44742,7 @@
         <v>General</v>
       </c>
       <c r="G1267" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1267" t="str">
         <v>NOS</v>
@@ -44765,7 +44765,7 @@
         <v>FG-401546</v>
       </c>
       <c r="C1268" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2")</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1268" t="str">
         <v>EDGE SERIES ANGULAR VALVE</v>
@@ -44777,7 +44777,7 @@
         <v>General</v>
       </c>
       <c r="G1268" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1268" t="str">
         <v>NOS</v>
@@ -44797,13 +44797,13 @@
         <v>1268</v>
       </c>
       <c r="B1269" t="str">
-        <v>FG-401547</v>
+        <v>FG-401546</v>
       </c>
       <c r="C1269" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2 inch)</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1269" t="str">
-        <v>EDGE SERIES PILLAR TAP</v>
+        <v>EDGE SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1269" t="str">
         <v>FAUCETS</v>
@@ -44812,19 +44812,19 @@
         <v>General</v>
       </c>
       <c r="G1269" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1269" t="str">
         <v>NOS</v>
       </c>
       <c r="I1269">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J1269" t="str">
         <v>Active</v>
       </c>
       <c r="K1269" t="str">
-        <v>EDGE SERIES PILLAR TAP high quality faucet.</v>
+        <v>EDGE SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1270">
@@ -44835,7 +44835,7 @@
         <v>FG-401547</v>
       </c>
       <c r="C1270" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2)</v>
+        <v>EDGE SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1270" t="str">
         <v>EDGE SERIES PILLAR TAP</v>
@@ -44847,7 +44847,7 @@
         <v>General</v>
       </c>
       <c r="G1270" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1270" t="str">
         <v>NOS</v>
@@ -44870,7 +44870,7 @@
         <v>FG-401547</v>
       </c>
       <c r="C1271" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2")</v>
+        <v>EDGE SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1271" t="str">
         <v>EDGE SERIES PILLAR TAP</v>
@@ -44882,7 +44882,7 @@
         <v>General</v>
       </c>
       <c r="G1271" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1271" t="str">
         <v>NOS</v>
@@ -44902,13 +44902,13 @@
         <v>1271</v>
       </c>
       <c r="B1272" t="str">
-        <v>FG-401550</v>
+        <v>FG-401547</v>
       </c>
       <c r="C1272" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2 inch)</v>
+        <v>EDGE SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1272" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB</v>
+        <v>EDGE SERIES PILLAR TAP</v>
       </c>
       <c r="E1272" t="str">
         <v>FAUCETS</v>
@@ -44917,19 +44917,19 @@
         <v>General</v>
       </c>
       <c r="G1272" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1272" t="str">
         <v>NOS</v>
       </c>
       <c r="I1272">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J1272" t="str">
         <v>Active</v>
       </c>
       <c r="K1272" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB high quality faucet.</v>
+        <v>EDGE SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1273">
@@ -44940,7 +44940,7 @@
         <v>FG-401550</v>
       </c>
       <c r="C1273" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2)</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2 inch)</v>
       </c>
       <c r="D1273" t="str">
         <v>EDGE SERIES 2 WAY BIB TAB</v>
@@ -44952,7 +44952,7 @@
         <v>General</v>
       </c>
       <c r="G1273" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1273" t="str">
         <v>NOS</v>
@@ -44975,7 +44975,7 @@
         <v>FG-401550</v>
       </c>
       <c r="C1274" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2")</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2)</v>
       </c>
       <c r="D1274" t="str">
         <v>EDGE SERIES 2 WAY BIB TAB</v>
@@ -44987,7 +44987,7 @@
         <v>General</v>
       </c>
       <c r="G1274" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1274" t="str">
         <v>NOS</v>
@@ -45007,13 +45007,13 @@
         <v>1274</v>
       </c>
       <c r="B1275" t="str">
-        <v>FG-401548</v>
+        <v>FG-401550</v>
       </c>
       <c r="C1275" t="str">
-        <v>EDGE SERIES SINK TAP (1/2 inch)</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2")</v>
       </c>
       <c r="D1275" t="str">
-        <v>EDGE SERIES SINK TAP</v>
+        <v>EDGE SERIES 2 WAY BIB TAB</v>
       </c>
       <c r="E1275" t="str">
         <v>FAUCETS</v>
@@ -45022,19 +45022,19 @@
         <v>General</v>
       </c>
       <c r="G1275" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1275" t="str">
         <v>NOS</v>
       </c>
       <c r="I1275">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J1275" t="str">
         <v>Active</v>
       </c>
       <c r="K1275" t="str">
-        <v>EDGE SERIES SINK TAP high quality faucet.</v>
+        <v>EDGE SERIES 2 WAY BIB TAB high quality faucet.</v>
       </c>
     </row>
     <row r="1276">
@@ -45045,7 +45045,7 @@
         <v>FG-401548</v>
       </c>
       <c r="C1276" t="str">
-        <v>EDGE SERIES SINK TAP (1/2)</v>
+        <v>EDGE SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1276" t="str">
         <v>EDGE SERIES SINK TAP</v>
@@ -45057,7 +45057,7 @@
         <v>General</v>
       </c>
       <c r="G1276" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1276" t="str">
         <v>NOS</v>
@@ -45080,7 +45080,7 @@
         <v>FG-401548</v>
       </c>
       <c r="C1277" t="str">
-        <v>EDGE SERIES SINK TAP (1/2")</v>
+        <v>EDGE SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1277" t="str">
         <v>EDGE SERIES SINK TAP</v>
@@ -45092,7 +45092,7 @@
         <v>General</v>
       </c>
       <c r="G1277" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1277" t="str">
         <v>NOS</v>
@@ -45112,13 +45112,13 @@
         <v>1277</v>
       </c>
       <c r="B1278" t="str">
-        <v>FG-401568</v>
+        <v>FG-401548</v>
       </c>
       <c r="C1278" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2 inch)</v>
+        <v>EDGE SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1278" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP</v>
+        <v>EDGE SERIES SINK TAP</v>
       </c>
       <c r="E1278" t="str">
         <v>FAUCETS</v>
@@ -45127,19 +45127,19 @@
         <v>General</v>
       </c>
       <c r="G1278" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1278" t="str">
         <v>NOS</v>
       </c>
       <c r="I1278">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="J1278" t="str">
         <v>Active</v>
       </c>
       <c r="K1278" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP high quality faucet.</v>
+        <v>EDGE SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1279">
@@ -45150,7 +45150,7 @@
         <v>FG-401568</v>
       </c>
       <c r="C1279" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2)</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1279" t="str">
         <v>SMART SERIES SHORT BODY BIB TAP</v>
@@ -45162,7 +45162,7 @@
         <v>General</v>
       </c>
       <c r="G1279" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1279" t="str">
         <v>NOS</v>
@@ -45185,7 +45185,7 @@
         <v>FG-401568</v>
       </c>
       <c r="C1280" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2")</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1280" t="str">
         <v>SMART SERIES SHORT BODY BIB TAP</v>
@@ -45197,7 +45197,7 @@
         <v>General</v>
       </c>
       <c r="G1280" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1280" t="str">
         <v>NOS</v>
@@ -45217,13 +45217,13 @@
         <v>1280</v>
       </c>
       <c r="B1281" t="str">
-        <v>FG-401567</v>
+        <v>FG-401568</v>
       </c>
       <c r="C1281" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1281" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP</v>
+        <v>SMART SERIES SHORT BODY BIB TAP</v>
       </c>
       <c r="E1281" t="str">
         <v>FAUCETS</v>
@@ -45232,7 +45232,7 @@
         <v>General</v>
       </c>
       <c r="G1281" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1281" t="str">
         <v>NOS</v>
@@ -45244,7 +45244,7 @@
         <v>Active</v>
       </c>
       <c r="K1281" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP high quality faucet.</v>
+        <v>SMART SERIES SHORT BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1282">
@@ -45255,7 +45255,7 @@
         <v>FG-401567</v>
       </c>
       <c r="C1282" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2)</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1282" t="str">
         <v>SMART SERIES LONG BODY BIB TAP</v>
@@ -45267,7 +45267,7 @@
         <v>General</v>
       </c>
       <c r="G1282" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1282" t="str">
         <v>NOS</v>
@@ -45290,7 +45290,7 @@
         <v>FG-401567</v>
       </c>
       <c r="C1283" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2")</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1283" t="str">
         <v>SMART SERIES LONG BODY BIB TAP</v>
@@ -45302,7 +45302,7 @@
         <v>General</v>
       </c>
       <c r="G1283" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1283" t="str">
         <v>NOS</v>
@@ -45322,13 +45322,13 @@
         <v>1283</v>
       </c>
       <c r="B1284" t="str">
-        <v>FG-401562</v>
+        <v>FG-401567</v>
       </c>
       <c r="C1284" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2 inch)</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1284" t="str">
-        <v>SMART SERIES PILLAR TAP</v>
+        <v>SMART SERIES LONG BODY BIB TAP</v>
       </c>
       <c r="E1284" t="str">
         <v>FAUCETS</v>
@@ -45337,19 +45337,19 @@
         <v>General</v>
       </c>
       <c r="G1284" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1284" t="str">
         <v>NOS</v>
       </c>
       <c r="I1284">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1284" t="str">
         <v>Active</v>
       </c>
       <c r="K1284" t="str">
-        <v>SMART SERIES PILLAR TAP high quality faucet.</v>
+        <v>SMART SERIES LONG BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1285">
@@ -45360,7 +45360,7 @@
         <v>FG-401562</v>
       </c>
       <c r="C1285" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2)</v>
+        <v>SMART SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1285" t="str">
         <v>SMART SERIES PILLAR TAP</v>
@@ -45372,7 +45372,7 @@
         <v>General</v>
       </c>
       <c r="G1285" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1285" t="str">
         <v>NOS</v>
@@ -45395,7 +45395,7 @@
         <v>FG-401562</v>
       </c>
       <c r="C1286" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2")</v>
+        <v>SMART SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1286" t="str">
         <v>SMART SERIES PILLAR TAP</v>
@@ -45407,7 +45407,7 @@
         <v>General</v>
       </c>
       <c r="G1286" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1286" t="str">
         <v>NOS</v>
@@ -45427,13 +45427,13 @@
         <v>1286</v>
       </c>
       <c r="B1287" t="str">
-        <v>FG-401563</v>
+        <v>FG-401562</v>
       </c>
       <c r="C1287" t="str">
-        <v>SMART SERIES SINK TAP (1/2 inch)</v>
+        <v>SMART SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1287" t="str">
-        <v>SMART SERIES SINK TAP</v>
+        <v>SMART SERIES PILLAR TAP</v>
       </c>
       <c r="E1287" t="str">
         <v>FAUCETS</v>
@@ -45442,7 +45442,7 @@
         <v>General</v>
       </c>
       <c r="G1287" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1287" t="str">
         <v>NOS</v>
@@ -45454,7 +45454,7 @@
         <v>Active</v>
       </c>
       <c r="K1287" t="str">
-        <v>SMART SERIES SINK TAP high quality faucet.</v>
+        <v>SMART SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1288">
@@ -45465,7 +45465,7 @@
         <v>FG-401563</v>
       </c>
       <c r="C1288" t="str">
-        <v>SMART SERIES SINK TAP (1/2)</v>
+        <v>SMART SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1288" t="str">
         <v>SMART SERIES SINK TAP</v>
@@ -45477,7 +45477,7 @@
         <v>General</v>
       </c>
       <c r="G1288" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1288" t="str">
         <v>NOS</v>
@@ -45500,7 +45500,7 @@
         <v>FG-401563</v>
       </c>
       <c r="C1289" t="str">
-        <v>SMART SERIES SINK TAP (1/2")</v>
+        <v>SMART SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1289" t="str">
         <v>SMART SERIES SINK TAP</v>
@@ -45512,7 +45512,7 @@
         <v>General</v>
       </c>
       <c r="G1289" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1289" t="str">
         <v>NOS</v>
@@ -45532,13 +45532,13 @@
         <v>1289</v>
       </c>
       <c r="B1290" t="str">
-        <v>FG-401564</v>
+        <v>FG-401563</v>
       </c>
       <c r="C1290" t="str">
-        <v>SMART SERIES SWAN NECK (1/2 inch)</v>
+        <v>SMART SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1290" t="str">
-        <v>SMART SERIES SWAN NECK</v>
+        <v>SMART SERIES SINK TAP</v>
       </c>
       <c r="E1290" t="str">
         <v>FAUCETS</v>
@@ -45547,7 +45547,7 @@
         <v>General</v>
       </c>
       <c r="G1290" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1290" t="str">
         <v>NOS</v>
@@ -45559,7 +45559,7 @@
         <v>Active</v>
       </c>
       <c r="K1290" t="str">
-        <v>SMART SERIES SWAN NECK high quality faucet.</v>
+        <v>SMART SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1291">
@@ -45570,7 +45570,7 @@
         <v>FG-401564</v>
       </c>
       <c r="C1291" t="str">
-        <v>SMART SERIES SWAN NECK (1/2)</v>
+        <v>SMART SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1291" t="str">
         <v>SMART SERIES SWAN NECK</v>
@@ -45582,7 +45582,7 @@
         <v>General</v>
       </c>
       <c r="G1291" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1291" t="str">
         <v>NOS</v>
@@ -45605,7 +45605,7 @@
         <v>FG-401564</v>
       </c>
       <c r="C1292" t="str">
-        <v>SMART SERIES SWAN NECK (1/2")</v>
+        <v>SMART SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1292" t="str">
         <v>SMART SERIES SWAN NECK</v>
@@ -45617,7 +45617,7 @@
         <v>General</v>
       </c>
       <c r="G1292" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1292" t="str">
         <v>NOS</v>
@@ -45637,13 +45637,13 @@
         <v>1292</v>
       </c>
       <c r="B1293" t="str">
-        <v>FG-401561</v>
+        <v>FG-401564</v>
       </c>
       <c r="C1293" t="str">
-        <v>SMART SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>SMART SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1293" t="str">
-        <v>SMART SERIES ANGULAR VALVE</v>
+        <v>SMART SERIES SWAN NECK</v>
       </c>
       <c r="E1293" t="str">
         <v>FAUCETS</v>
@@ -45652,19 +45652,19 @@
         <v>General</v>
       </c>
       <c r="G1293" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1293" t="str">
         <v>NOS</v>
       </c>
       <c r="I1293">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1293" t="str">
         <v>Active</v>
       </c>
       <c r="K1293" t="str">
-        <v>SMART SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>SMART SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1294">
@@ -45672,13 +45672,13 @@
         <v>1293</v>
       </c>
       <c r="B1294" t="str">
-        <v>FG-401566</v>
+        <v>FG-401561</v>
       </c>
       <c r="C1294" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
+        <v>SMART SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1294" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
+        <v>SMART SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1294" t="str">
         <v>FAUCETS</v>
@@ -45693,13 +45693,13 @@
         <v>NOS</v>
       </c>
       <c r="I1294">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1294" t="str">
         <v>Active</v>
       </c>
       <c r="K1294" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
+        <v>SMART SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1295">
@@ -45710,7 +45710,7 @@
         <v>FG-401566</v>
       </c>
       <c r="C1295" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1295" t="str">
         <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
@@ -45722,7 +45722,7 @@
         <v>General</v>
       </c>
       <c r="G1295" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1295" t="str">
         <v>NOS</v>
@@ -45745,7 +45745,7 @@
         <v>FG-401566</v>
       </c>
       <c r="C1296" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2")</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1296" t="str">
         <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
@@ -45757,7 +45757,7 @@
         <v>General</v>
       </c>
       <c r="G1296" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1296" t="str">
         <v>NOS</v>
@@ -45777,13 +45777,13 @@
         <v>1296</v>
       </c>
       <c r="B1297" t="str">
-        <v>FG-401565</v>
+        <v>FG-401566</v>
       </c>
       <c r="C1297" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1297" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
       </c>
       <c r="E1297" t="str">
         <v>FAUCETS</v>
@@ -45792,7 +45792,7 @@
         <v>General</v>
       </c>
       <c r="G1297" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1297" t="str">
         <v>NOS</v>
@@ -45804,7 +45804,7 @@
         <v>Active</v>
       </c>
       <c r="K1297" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP high quality faucet.</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1298">
@@ -45815,7 +45815,7 @@
         <v>FG-401565</v>
       </c>
       <c r="C1298" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2)</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1298" t="str">
         <v>SMART SERIES 2 WAY BIB TAP</v>
@@ -45827,7 +45827,7 @@
         <v>General</v>
       </c>
       <c r="G1298" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1298" t="str">
         <v>NOS</v>
@@ -45850,7 +45850,7 @@
         <v>FG-401565</v>
       </c>
       <c r="C1299" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2")</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2)</v>
       </c>
       <c r="D1299" t="str">
         <v>SMART SERIES 2 WAY BIB TAP</v>
@@ -45862,7 +45862,7 @@
         <v>General</v>
       </c>
       <c r="G1299" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1299" t="str">
         <v>NOS</v>
@@ -45882,13 +45882,13 @@
         <v>1299</v>
       </c>
       <c r="B1300" t="str">
-        <v>FG-401560</v>
+        <v>FG-401565</v>
       </c>
       <c r="C1300" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2")</v>
       </c>
       <c r="D1300" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP</v>
+        <v>SMART SERIES 2 WAY BIB TAP</v>
       </c>
       <c r="E1300" t="str">
         <v>FAUCETS</v>
@@ -45897,19 +45897,19 @@
         <v>General</v>
       </c>
       <c r="G1300" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1300" t="str">
         <v>NOS</v>
       </c>
       <c r="I1300">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1300" t="str">
         <v>Active</v>
       </c>
       <c r="K1300" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP high quality faucet.</v>
+        <v>SMART SERIES 2 WAY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1301">
@@ -45920,7 +45920,7 @@
         <v>FG-401560</v>
       </c>
       <c r="C1301" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1301" t="str">
         <v>REGULAR SERIES SHORT BODY BIB TAP</v>
@@ -45932,7 +45932,7 @@
         <v>General</v>
       </c>
       <c r="G1301" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1301" t="str">
         <v>NOS</v>
@@ -45955,7 +45955,7 @@
         <v>FG-401560</v>
       </c>
       <c r="C1302" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1302" t="str">
         <v>REGULAR SERIES SHORT BODY BIB TAP</v>
@@ -45967,7 +45967,7 @@
         <v>General</v>
       </c>
       <c r="G1302" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1302" t="str">
         <v>NOS</v>
@@ -45987,13 +45987,13 @@
         <v>1302</v>
       </c>
       <c r="B1303" t="str">
-        <v>FG-401559</v>
+        <v>FG-401560</v>
       </c>
       <c r="C1303" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1303" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP</v>
       </c>
       <c r="E1303" t="str">
         <v>FAUCETS</v>
@@ -46002,7 +46002,7 @@
         <v>General</v>
       </c>
       <c r="G1303" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1303" t="str">
         <v>NOS</v>
@@ -46014,7 +46014,7 @@
         <v>Active</v>
       </c>
       <c r="K1303" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1304">
@@ -46025,7 +46025,7 @@
         <v>FG-401559</v>
       </c>
       <c r="C1304" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1304" t="str">
         <v>REGULAR SERIES LONG BODY BIB TAP</v>
@@ -46037,7 +46037,7 @@
         <v>General</v>
       </c>
       <c r="G1304" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1304" t="str">
         <v>NOS</v>
@@ -46060,7 +46060,7 @@
         <v>FG-401559</v>
       </c>
       <c r="C1305" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1305" t="str">
         <v>REGULAR SERIES LONG BODY BIB TAP</v>
@@ -46072,7 +46072,7 @@
         <v>General</v>
       </c>
       <c r="G1305" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1305" t="str">
         <v>NOS</v>
@@ -46092,13 +46092,13 @@
         <v>1305</v>
       </c>
       <c r="B1306" t="str">
-        <v>FG-401554</v>
+        <v>FG-401559</v>
       </c>
       <c r="C1306" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2 inch)</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1306" t="str">
-        <v>REGULAR SERIES PILLAR TAP</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP</v>
       </c>
       <c r="E1306" t="str">
         <v>FAUCETS</v>
@@ -46107,19 +46107,19 @@
         <v>General</v>
       </c>
       <c r="G1306" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1306" t="str">
         <v>NOS</v>
       </c>
       <c r="I1306">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1306" t="str">
         <v>Active</v>
       </c>
       <c r="K1306" t="str">
-        <v>REGULAR SERIES PILLAR TAP high quality faucet.</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1307">
@@ -46130,7 +46130,7 @@
         <v>FG-401554</v>
       </c>
       <c r="C1307" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2)</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1307" t="str">
         <v>REGULAR SERIES PILLAR TAP</v>
@@ -46142,7 +46142,7 @@
         <v>General</v>
       </c>
       <c r="G1307" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1307" t="str">
         <v>NOS</v>
@@ -46165,7 +46165,7 @@
         <v>FG-401554</v>
       </c>
       <c r="C1308" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2")</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1308" t="str">
         <v>REGULAR SERIES PILLAR TAP</v>
@@ -46177,7 +46177,7 @@
         <v>General</v>
       </c>
       <c r="G1308" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1308" t="str">
         <v>NOS</v>
@@ -46197,13 +46197,13 @@
         <v>1308</v>
       </c>
       <c r="B1309" t="str">
-        <v>FG-401555</v>
+        <v>FG-401554</v>
       </c>
       <c r="C1309" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2 inch)</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1309" t="str">
-        <v>REGULAR SERIES SINK TAP</v>
+        <v>REGULAR SERIES PILLAR TAP</v>
       </c>
       <c r="E1309" t="str">
         <v>FAUCETS</v>
@@ -46212,7 +46212,7 @@
         <v>General</v>
       </c>
       <c r="G1309" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1309" t="str">
         <v>NOS</v>
@@ -46224,7 +46224,7 @@
         <v>Active</v>
       </c>
       <c r="K1309" t="str">
-        <v>REGULAR SERIES SINK TAP high quality faucet.</v>
+        <v>REGULAR SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1310">
@@ -46235,7 +46235,7 @@
         <v>FG-401555</v>
       </c>
       <c r="C1310" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2)</v>
+        <v>REGULAR SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1310" t="str">
         <v>REGULAR SERIES SINK TAP</v>
@@ -46247,7 +46247,7 @@
         <v>General</v>
       </c>
       <c r="G1310" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1310" t="str">
         <v>NOS</v>
@@ -46270,7 +46270,7 @@
         <v>FG-401555</v>
       </c>
       <c r="C1311" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2")</v>
+        <v>REGULAR SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1311" t="str">
         <v>REGULAR SERIES SINK TAP</v>
@@ -46282,7 +46282,7 @@
         <v>General</v>
       </c>
       <c r="G1311" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1311" t="str">
         <v>NOS</v>
@@ -46302,13 +46302,13 @@
         <v>1311</v>
       </c>
       <c r="B1312" t="str">
-        <v>FG-401556</v>
+        <v>FG-401555</v>
       </c>
       <c r="C1312" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2 inch)</v>
+        <v>REGULAR SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1312" t="str">
-        <v>REGULAR SERIES SWAN NECK</v>
+        <v>REGULAR SERIES SINK TAP</v>
       </c>
       <c r="E1312" t="str">
         <v>FAUCETS</v>
@@ -46317,7 +46317,7 @@
         <v>General</v>
       </c>
       <c r="G1312" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1312" t="str">
         <v>NOS</v>
@@ -46329,7 +46329,7 @@
         <v>Active</v>
       </c>
       <c r="K1312" t="str">
-        <v>REGULAR SERIES SWAN NECK high quality faucet.</v>
+        <v>REGULAR SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1313">
@@ -46340,7 +46340,7 @@
         <v>FG-401556</v>
       </c>
       <c r="C1313" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2)</v>
+        <v>REGULAR SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1313" t="str">
         <v>REGULAR SERIES SWAN NECK</v>
@@ -46352,7 +46352,7 @@
         <v>General</v>
       </c>
       <c r="G1313" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1313" t="str">
         <v>NOS</v>
@@ -46375,7 +46375,7 @@
         <v>FG-401556</v>
       </c>
       <c r="C1314" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2")</v>
+        <v>REGULAR SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1314" t="str">
         <v>REGULAR SERIES SWAN NECK</v>
@@ -46387,7 +46387,7 @@
         <v>General</v>
       </c>
       <c r="G1314" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1314" t="str">
         <v>NOS</v>
@@ -46407,13 +46407,13 @@
         <v>1314</v>
       </c>
       <c r="B1315" t="str">
-        <v>FG-401553</v>
+        <v>FG-401556</v>
       </c>
       <c r="C1315" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>REGULAR SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1315" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE</v>
+        <v>REGULAR SERIES SWAN NECK</v>
       </c>
       <c r="E1315" t="str">
         <v>FAUCETS</v>
@@ -46422,19 +46422,19 @@
         <v>General</v>
       </c>
       <c r="G1315" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1315" t="str">
         <v>NOS</v>
       </c>
       <c r="I1315">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1315" t="str">
         <v>Active</v>
       </c>
       <c r="K1315" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>REGULAR SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1316">
@@ -46445,7 +46445,7 @@
         <v>FG-401553</v>
       </c>
       <c r="C1316" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2)</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1316" t="str">
         <v>REGULAR SERIES ANGULAR VALVE</v>
@@ -46457,7 +46457,7 @@
         <v>General</v>
       </c>
       <c r="G1316" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1316" t="str">
         <v>NOS</v>
@@ -46480,7 +46480,7 @@
         <v>FG-401553</v>
       </c>
       <c r="C1317" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2")</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1317" t="str">
         <v>REGULAR SERIES ANGULAR VALVE</v>
@@ -46492,7 +46492,7 @@
         <v>General</v>
       </c>
       <c r="G1317" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1317" t="str">
         <v>NOS</v>
@@ -46512,13 +46512,13 @@
         <v>1317</v>
       </c>
       <c r="B1318" t="str">
-        <v>FG-401558</v>
+        <v>FG-401553</v>
       </c>
       <c r="C1318" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1318" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
+        <v>REGULAR SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1318" t="str">
         <v>FAUCETS</v>
@@ -46527,19 +46527,19 @@
         <v>General</v>
       </c>
       <c r="G1318" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1318" t="str">
         <v>NOS</v>
       </c>
       <c r="I1318">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1318" t="str">
         <v>Active</v>
       </c>
       <c r="K1318" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
+        <v>REGULAR SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1319">
@@ -46550,7 +46550,7 @@
         <v>FG-401558</v>
       </c>
       <c r="C1319" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2)</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1319" t="str">
         <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
@@ -46562,7 +46562,7 @@
         <v>General</v>
       </c>
       <c r="G1319" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1319" t="str">
         <v>NOS</v>
@@ -46585,7 +46585,7 @@
         <v>FG-401558</v>
       </c>
       <c r="C1320" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2")</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1320" t="str">
         <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
@@ -46597,7 +46597,7 @@
         <v>General</v>
       </c>
       <c r="G1320" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1320" t="str">
         <v>NOS</v>
@@ -46617,13 +46617,13 @@
         <v>1320</v>
       </c>
       <c r="B1321" t="str">
-        <v>FG-401557</v>
+        <v>FG-401558</v>
       </c>
       <c r="C1321" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1321" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
       </c>
       <c r="E1321" t="str">
         <v>FAUCETS</v>
@@ -46632,7 +46632,7 @@
         <v>General</v>
       </c>
       <c r="G1321" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1321" t="str">
         <v>NOS</v>
@@ -46644,7 +46644,7 @@
         <v>Active</v>
       </c>
       <c r="K1321" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1322">
@@ -46655,7 +46655,7 @@
         <v>FG-401557</v>
       </c>
       <c r="C1322" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1322" t="str">
         <v>REGULAR SERIES 2 WAY BIB TAP</v>
@@ -46667,7 +46667,7 @@
         <v>General</v>
       </c>
       <c r="G1322" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1322" t="str">
         <v>NOS</v>
@@ -46690,7 +46690,7 @@
         <v>FG-401557</v>
       </c>
       <c r="C1323" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2)</v>
       </c>
       <c r="D1323" t="str">
         <v>REGULAR SERIES 2 WAY BIB TAP</v>
@@ -46702,7 +46702,7 @@
         <v>General</v>
       </c>
       <c r="G1323" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1323" t="str">
         <v>NOS</v>
@@ -46722,34 +46722,34 @@
         <v>1323</v>
       </c>
       <c r="B1324" t="str">
-        <v>FG-400836</v>
+        <v>FG-401557</v>
       </c>
       <c r="C1324" t="str">
-        <v>SINGLE SIDE HANDLE FLUSH 8L (8L)</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2")</v>
       </c>
       <c r="D1324" t="str">
-        <v>SINGLE SIDE HANDLE FLUSH 8L</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP</v>
       </c>
       <c r="E1324" t="str">
-        <v>Toilet Seat Cover &amp; Flushing Cistern</v>
+        <v>FAUCETS</v>
       </c>
       <c r="F1324" t="str">
         <v>General</v>
       </c>
       <c r="G1324" t="str">
-        <v>8L</v>
+        <v>1/2"</v>
       </c>
       <c r="H1324" t="str">
         <v>NOS</v>
       </c>
       <c r="I1324">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="J1324" t="str">
         <v>Active</v>
       </c>
       <c r="K1324" t="str">
-        <v>8 Litre Single Side Handle Flushing Cistern.</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1325">
@@ -46757,13 +46757,13 @@
         <v>1324</v>
       </c>
       <c r="B1325" t="str">
-        <v>FG-400837</v>
+        <v>FG-400836</v>
       </c>
       <c r="C1325" t="str">
-        <v>CENTER SINGLE PUSH FLUSH 8L (8L)</v>
+        <v>SINGLE SIDE HANDLE FLUSH 8L (8L)</v>
       </c>
       <c r="D1325" t="str">
-        <v>CENTER SINGLE PUSH FLUSH 8L</v>
+        <v>SINGLE SIDE HANDLE FLUSH 8L</v>
       </c>
       <c r="E1325" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46784,7 +46784,7 @@
         <v>Active</v>
       </c>
       <c r="K1325" t="str">
-        <v>8 Litre Center Single Push Flushing Cistern.</v>
+        <v>8 Litre Single Side Handle Flushing Cistern.</v>
       </c>
     </row>
     <row r="1326">
@@ -46792,13 +46792,13 @@
         <v>1325</v>
       </c>
       <c r="B1326" t="str">
-        <v>FG-400838</v>
+        <v>FG-400837</v>
       </c>
       <c r="C1326" t="str">
-        <v>DUAL FLUSH 10L (10L)</v>
+        <v>CENTER SINGLE PUSH FLUSH 8L (8L)</v>
       </c>
       <c r="D1326" t="str">
-        <v>DUAL FLUSH 10L</v>
+        <v>CENTER SINGLE PUSH FLUSH 8L</v>
       </c>
       <c r="E1326" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46807,7 +46807,7 @@
         <v>General</v>
       </c>
       <c r="G1326" t="str">
-        <v>10L</v>
+        <v>8L</v>
       </c>
       <c r="H1326" t="str">
         <v>NOS</v>
@@ -46819,7 +46819,7 @@
         <v>Active</v>
       </c>
       <c r="K1326" t="str">
-        <v>10 Litre Dual Flush Cistern.</v>
+        <v>8 Litre Center Single Push Flushing Cistern.</v>
       </c>
     </row>
     <row r="1327">
@@ -46827,13 +46827,13 @@
         <v>1326</v>
       </c>
       <c r="B1327" t="str">
-        <v>FG-400835</v>
+        <v>FG-400838</v>
       </c>
       <c r="C1327" t="str">
-        <v>EWC SEAT COVER (WITH JET) (Standard)</v>
+        <v>DUAL FLUSH 10L (10L)</v>
       </c>
       <c r="D1327" t="str">
-        <v>EWC SEAT COVER (WITH JET)</v>
+        <v>DUAL FLUSH 10L</v>
       </c>
       <c r="E1327" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46842,19 +46842,19 @@
         <v>General</v>
       </c>
       <c r="G1327" t="str">
-        <v>Standard</v>
+        <v>10L</v>
       </c>
       <c r="H1327" t="str">
         <v>NOS</v>
       </c>
       <c r="I1327">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J1327" t="str">
         <v>Active</v>
       </c>
       <c r="K1327" t="str">
-        <v>EWC Toilet Seat Cover with integrated jet spray.</v>
+        <v>10 Litre Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1328">
@@ -46862,13 +46862,13 @@
         <v>1327</v>
       </c>
       <c r="B1328" t="str">
-        <v>FG-400840</v>
+        <v>FG-400835</v>
       </c>
       <c r="C1328" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L) (10L)</v>
+        <v>EWC SEAT COVER (WITH JET) (Standard)</v>
       </c>
       <c r="D1328" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L)</v>
+        <v>EWC SEAT COVER (WITH JET)</v>
       </c>
       <c r="E1328" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46877,19 +46877,19 @@
         <v>General</v>
       </c>
       <c r="G1328" t="str">
-        <v>10L</v>
+        <v>Standard</v>
       </c>
       <c r="H1328" t="str">
         <v>NOS</v>
       </c>
       <c r="I1328">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J1328" t="str">
         <v>Active</v>
       </c>
       <c r="K1328" t="str">
-        <v>10 Litre Premium Dual Colour Dual Flush Cistern.</v>
+        <v>EWC Toilet Seat Cover with integrated jet spray.</v>
       </c>
     </row>
     <row r="1329">
@@ -46897,13 +46897,13 @@
         <v>1328</v>
       </c>
       <c r="B1329" t="str">
-        <v>FG-400839</v>
+        <v>FG-400840</v>
       </c>
       <c r="C1329" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L) (10L)</v>
+        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L) (10L)</v>
       </c>
       <c r="D1329" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L)</v>
+        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L)</v>
       </c>
       <c r="E1329" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46924,7 +46924,7 @@
         <v>Active</v>
       </c>
       <c r="K1329" t="str">
-        <v>10 Litre Economy Dual Colour Dual Flush Cistern.</v>
+        <v>10 Litre Premium Dual Colour Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1330">
@@ -46932,13 +46932,13 @@
         <v>1329</v>
       </c>
       <c r="B1330" t="str">
-        <v>FG-400834</v>
+        <v>FG-400839</v>
       </c>
       <c r="C1330" t="str">
-        <v>EWC SEAT COVER (WITHOUT JET) (Standard)</v>
+        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L) (10L)</v>
       </c>
       <c r="D1330" t="str">
-        <v>EWC SEAT COVER (WITHOUT JET)</v>
+        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L)</v>
       </c>
       <c r="E1330" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46947,24 +46947,59 @@
         <v>General</v>
       </c>
       <c r="G1330" t="str">
-        <v>Standard</v>
+        <v>10L</v>
       </c>
       <c r="H1330" t="str">
         <v>NOS</v>
       </c>
       <c r="I1330">
+        <v>10</v>
+      </c>
+      <c r="J1330" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K1330" t="str">
+        <v>10 Litre Economy Dual Colour Dual Flush Cistern.</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331">
+        <v>1330</v>
+      </c>
+      <c r="B1331" t="str">
+        <v>FG-400834</v>
+      </c>
+      <c r="C1331" t="str">
+        <v>EWC SEAT COVER (WITHOUT JET) (Standard)</v>
+      </c>
+      <c r="D1331" t="str">
+        <v>EWC SEAT COVER (WITHOUT JET)</v>
+      </c>
+      <c r="E1331" t="str">
+        <v>Toilet Seat Cover &amp; Flushing Cistern</v>
+      </c>
+      <c r="F1331" t="str">
+        <v>General</v>
+      </c>
+      <c r="G1331" t="str">
+        <v>Standard</v>
+      </c>
+      <c r="H1331" t="str">
+        <v>NOS</v>
+      </c>
+      <c r="I1331">
         <v>20</v>
       </c>
-      <c r="J1330" t="str">
-        <v>Active</v>
-      </c>
-      <c r="K1330" t="str">
+      <c r="J1331" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K1331" t="str">
         <v>EWC Toilet Seat Cover without jet spray.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K1330"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K1331"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
+++ b/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1331"/>
+  <dimension ref="A1:K1330"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -35735,10 +35735,10 @@
         <v>-</v>
       </c>
       <c r="C1010" t="str">
-        <v>PN10 - UNION ISI (25MM)</v>
+        <v>AGRI UNION 10KG</v>
       </c>
       <c r="D1010" t="str">
-        <v>PN10 - UNION ISI</v>
+        <v>AGRI UNION 10KG</v>
       </c>
       <c r="E1010" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35747,7 +35747,7 @@
         <v>General</v>
       </c>
       <c r="G1010" t="str">
-        <v>25MM</v>
+        <v>Standard</v>
       </c>
       <c r="H1010" t="str">
         <v>BOX</v>
@@ -35759,7 +35759,7 @@
         <v>Active</v>
       </c>
       <c r="K1010" t="str">
-        <v>PN10 - UNION ISI for agriculture irrigation and piping systems.</v>
+        <v>AGRI UNION 10KG.</v>
       </c>
     </row>
     <row r="1011">
@@ -35770,10 +35770,10 @@
         <v>-</v>
       </c>
       <c r="C1011" t="str">
-        <v>PN10 - UNION ISI (32MM)</v>
+        <v>PN10 - TEE ISI (25MM)</v>
       </c>
       <c r="D1011" t="str">
-        <v>PN10 - UNION ISI</v>
+        <v>PN10 - TEE ISI</v>
       </c>
       <c r="E1011" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35782,7 +35782,7 @@
         <v>General</v>
       </c>
       <c r="G1011" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1011" t="str">
         <v>BOX</v>
@@ -35794,7 +35794,7 @@
         <v>Active</v>
       </c>
       <c r="K1011" t="str">
-        <v>PN10 - UNION ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - TEE ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1012">
@@ -35805,7 +35805,7 @@
         <v>-</v>
       </c>
       <c r="C1012" t="str">
-        <v>PN10 - TEE ISI (25MM)</v>
+        <v>PN10 - TEE ISI (32MM)</v>
       </c>
       <c r="D1012" t="str">
         <v>PN10 - TEE ISI</v>
@@ -35817,7 +35817,7 @@
         <v>General</v>
       </c>
       <c r="G1012" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1012" t="str">
         <v>BOX</v>
@@ -35840,10 +35840,10 @@
         <v>-</v>
       </c>
       <c r="C1013" t="str">
-        <v>PN10 - TEE ISI (32MM)</v>
+        <v>PN10 - COUPLER ISI (25MM)</v>
       </c>
       <c r="D1013" t="str">
-        <v>PN10 - TEE ISI</v>
+        <v>PN10 - COUPLER ISI</v>
       </c>
       <c r="E1013" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35852,7 +35852,7 @@
         <v>General</v>
       </c>
       <c r="G1013" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1013" t="str">
         <v>BOX</v>
@@ -35864,7 +35864,7 @@
         <v>Active</v>
       </c>
       <c r="K1013" t="str">
-        <v>PN10 - TEE ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - COUPLER ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1014">
@@ -35875,7 +35875,7 @@
         <v>-</v>
       </c>
       <c r="C1014" t="str">
-        <v>PN10 - COUPLER ISI (25MM)</v>
+        <v>PN10 - COUPLER ISI (32MM)</v>
       </c>
       <c r="D1014" t="str">
         <v>PN10 - COUPLER ISI</v>
@@ -35887,7 +35887,7 @@
         <v>General</v>
       </c>
       <c r="G1014" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1014" t="str">
         <v>BOX</v>
@@ -35910,10 +35910,10 @@
         <v>-</v>
       </c>
       <c r="C1015" t="str">
-        <v>PN10 - COUPLER ISI (32MM)</v>
+        <v>PN10 - MTA ISI (25MM)</v>
       </c>
       <c r="D1015" t="str">
-        <v>PN10 - COUPLER ISI</v>
+        <v>PN10 - MTA ISI</v>
       </c>
       <c r="E1015" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35922,7 +35922,7 @@
         <v>General</v>
       </c>
       <c r="G1015" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1015" t="str">
         <v>BOX</v>
@@ -35934,7 +35934,7 @@
         <v>Active</v>
       </c>
       <c r="K1015" t="str">
-        <v>PN10 - COUPLER ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - MTA ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1016">
@@ -35945,7 +35945,7 @@
         <v>-</v>
       </c>
       <c r="C1016" t="str">
-        <v>PN10 - MTA ISI (25MM)</v>
+        <v>PN10 - MTA ISI (32MM)</v>
       </c>
       <c r="D1016" t="str">
         <v>PN10 - MTA ISI</v>
@@ -35957,7 +35957,7 @@
         <v>General</v>
       </c>
       <c r="G1016" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1016" t="str">
         <v>BOX</v>
@@ -35980,10 +35980,10 @@
         <v>-</v>
       </c>
       <c r="C1017" t="str">
-        <v>PN10 - MTA ISI (32MM)</v>
+        <v>PN10 - FTA ISI (25MM)</v>
       </c>
       <c r="D1017" t="str">
-        <v>PN10 - MTA ISI</v>
+        <v>PN10 - FTA ISI</v>
       </c>
       <c r="E1017" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35992,7 +35992,7 @@
         <v>General</v>
       </c>
       <c r="G1017" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1017" t="str">
         <v>BOX</v>
@@ -36004,7 +36004,7 @@
         <v>Active</v>
       </c>
       <c r="K1017" t="str">
-        <v>PN10 - MTA ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - FTA ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1018">
@@ -36015,7 +36015,7 @@
         <v>-</v>
       </c>
       <c r="C1018" t="str">
-        <v>PN10 - FTA ISI (25MM)</v>
+        <v>PN10 - FTA ISI (32MM)</v>
       </c>
       <c r="D1018" t="str">
         <v>PN10 - FTA ISI</v>
@@ -36027,7 +36027,7 @@
         <v>General</v>
       </c>
       <c r="G1018" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1018" t="str">
         <v>BOX</v>
@@ -36050,10 +36050,10 @@
         <v>-</v>
       </c>
       <c r="C1019" t="str">
-        <v>PN10 - FTA ISI (32MM)</v>
+        <v>PN10 - END CAP ISI (25MM)</v>
       </c>
       <c r="D1019" t="str">
-        <v>PN10 - FTA ISI</v>
+        <v>PN10 - END CAP ISI</v>
       </c>
       <c r="E1019" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36062,7 +36062,7 @@
         <v>General</v>
       </c>
       <c r="G1019" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1019" t="str">
         <v>BOX</v>
@@ -36074,7 +36074,7 @@
         <v>Active</v>
       </c>
       <c r="K1019" t="str">
-        <v>PN10 - FTA ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - END CAP ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1020">
@@ -36085,7 +36085,7 @@
         <v>-</v>
       </c>
       <c r="C1020" t="str">
-        <v>PN10 - END CAP ISI (25MM)</v>
+        <v>PN10 - END CAP ISI (32MM)</v>
       </c>
       <c r="D1020" t="str">
         <v>PN10 - END CAP ISI</v>
@@ -36097,7 +36097,7 @@
         <v>General</v>
       </c>
       <c r="G1020" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1020" t="str">
         <v>BOX</v>
@@ -36120,10 +36120,10 @@
         <v>-</v>
       </c>
       <c r="C1021" t="str">
-        <v>PN10 - END CAP ISI (32MM)</v>
+        <v>PN10 - REDUCING BUSH ISI (32 X 20)</v>
       </c>
       <c r="D1021" t="str">
-        <v>PN10 - END CAP ISI</v>
+        <v>PN10 - REDUCING BUSH ISI</v>
       </c>
       <c r="E1021" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36132,7 +36132,7 @@
         <v>General</v>
       </c>
       <c r="G1021" t="str">
-        <v>32MM</v>
+        <v>32 X 20</v>
       </c>
       <c r="H1021" t="str">
         <v>BOX</v>
@@ -36144,7 +36144,7 @@
         <v>Active</v>
       </c>
       <c r="K1021" t="str">
-        <v>PN10 - END CAP ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - REDUCING BUSH ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1022">
@@ -36155,7 +36155,7 @@
         <v>-</v>
       </c>
       <c r="C1022" t="str">
-        <v>PN10 - REDUCING BUSH ISI (32 X 20)</v>
+        <v>PN10 - REDUCING BUSH ISI (32 X 25)</v>
       </c>
       <c r="D1022" t="str">
         <v>PN10 - REDUCING BUSH ISI</v>
@@ -36167,7 +36167,7 @@
         <v>General</v>
       </c>
       <c r="G1022" t="str">
-        <v>32 X 20</v>
+        <v>32 X 25</v>
       </c>
       <c r="H1022" t="str">
         <v>BOX</v>
@@ -36187,13 +36187,13 @@
         <v>1022</v>
       </c>
       <c r="B1023" t="str">
-        <v>-</v>
+        <v>FG-400585</v>
       </c>
       <c r="C1023" t="str">
-        <v>PN10 - REDUCING BUSH ISI (32 X 25)</v>
+        <v>AGRI REDUCER (50X40MM)</v>
       </c>
       <c r="D1023" t="str">
-        <v>PN10 - REDUCING BUSH ISI</v>
+        <v>AGRI REDUCER</v>
       </c>
       <c r="E1023" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36202,19 +36202,19 @@
         <v>General</v>
       </c>
       <c r="G1023" t="str">
-        <v>32 X 25</v>
+        <v>50X40MM</v>
       </c>
       <c r="H1023" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1023" t="str">
-        <v>-</v>
+      <c r="I1023">
+        <v>300</v>
       </c>
       <c r="J1023" t="str">
         <v>Active</v>
       </c>
       <c r="K1023" t="str">
-        <v>PN10 - REDUCING BUSH ISI for agriculture irrigation and piping systems.</v>
+        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
       </c>
     </row>
     <row r="1024">
@@ -36222,10 +36222,10 @@
         <v>1023</v>
       </c>
       <c r="B1024" t="str">
-        <v>FG-400585</v>
+        <v>FG-400584</v>
       </c>
       <c r="C1024" t="str">
-        <v>AGRI REDUCER (50X40MM)</v>
+        <v>AGRI REDUCER (63X40MM)</v>
       </c>
       <c r="D1024" t="str">
         <v>AGRI REDUCER</v>
@@ -36237,13 +36237,13 @@
         <v>General</v>
       </c>
       <c r="G1024" t="str">
-        <v>50X40MM</v>
+        <v>63X40MM</v>
       </c>
       <c r="H1024" t="str">
         <v>BOX</v>
       </c>
       <c r="I1024">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J1024" t="str">
         <v>Active</v>
@@ -36257,10 +36257,10 @@
         <v>1024</v>
       </c>
       <c r="B1025" t="str">
-        <v>FG-400584</v>
+        <v>FG-400583</v>
       </c>
       <c r="C1025" t="str">
-        <v>AGRI REDUCER (63X40MM)</v>
+        <v>AGRI REDUCER (63X50MM)</v>
       </c>
       <c r="D1025" t="str">
         <v>AGRI REDUCER</v>
@@ -36272,13 +36272,13 @@
         <v>General</v>
       </c>
       <c r="G1025" t="str">
-        <v>63X40MM</v>
+        <v>63X50MM</v>
       </c>
       <c r="H1025" t="str">
         <v>BOX</v>
       </c>
       <c r="I1025">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="J1025" t="str">
         <v>Active</v>
@@ -36292,10 +36292,10 @@
         <v>1025</v>
       </c>
       <c r="B1026" t="str">
-        <v>FG-400583</v>
+        <v>FG-400582</v>
       </c>
       <c r="C1026" t="str">
-        <v>AGRI REDUCER (63X50MM)</v>
+        <v>AGRI REDUCER (75X40MM)</v>
       </c>
       <c r="D1026" t="str">
         <v>AGRI REDUCER</v>
@@ -36307,13 +36307,13 @@
         <v>General</v>
       </c>
       <c r="G1026" t="str">
-        <v>63X50MM</v>
+        <v>75X40MM</v>
       </c>
       <c r="H1026" t="str">
         <v>BOX</v>
       </c>
       <c r="I1026">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J1026" t="str">
         <v>Active</v>
@@ -36327,10 +36327,10 @@
         <v>1026</v>
       </c>
       <c r="B1027" t="str">
-        <v>FG-400582</v>
+        <v>FG-400581</v>
       </c>
       <c r="C1027" t="str">
-        <v>AGRI REDUCER (75X40MM)</v>
+        <v>AGRI REDUCER (75X50MM)</v>
       </c>
       <c r="D1027" t="str">
         <v>AGRI REDUCER</v>
@@ -36342,13 +36342,13 @@
         <v>General</v>
       </c>
       <c r="G1027" t="str">
-        <v>75X40MM</v>
+        <v>75X50MM</v>
       </c>
       <c r="H1027" t="str">
         <v>BOX</v>
       </c>
       <c r="I1027">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J1027" t="str">
         <v>Active</v>
@@ -36362,10 +36362,10 @@
         <v>1027</v>
       </c>
       <c r="B1028" t="str">
-        <v>FG-400581</v>
+        <v>FG-400580</v>
       </c>
       <c r="C1028" t="str">
-        <v>AGRI REDUCER (75X50MM)</v>
+        <v>AGRI REDUCER (75X63MM)</v>
       </c>
       <c r="D1028" t="str">
         <v>AGRI REDUCER</v>
@@ -36377,13 +36377,13 @@
         <v>General</v>
       </c>
       <c r="G1028" t="str">
-        <v>75X50MM</v>
+        <v>75X63MM</v>
       </c>
       <c r="H1028" t="str">
         <v>BOX</v>
       </c>
       <c r="I1028">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J1028" t="str">
         <v>Active</v>
@@ -36397,10 +36397,10 @@
         <v>1028</v>
       </c>
       <c r="B1029" t="str">
-        <v>FG-400580</v>
+        <v>FG-400579</v>
       </c>
       <c r="C1029" t="str">
-        <v>AGRI REDUCER (75X63MM)</v>
+        <v>AGRI REDUCER (90X50MM)</v>
       </c>
       <c r="D1029" t="str">
         <v>AGRI REDUCER</v>
@@ -36412,13 +36412,13 @@
         <v>General</v>
       </c>
       <c r="G1029" t="str">
-        <v>75X63MM</v>
+        <v>90X50MM</v>
       </c>
       <c r="H1029" t="str">
         <v>BOX</v>
       </c>
       <c r="I1029">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J1029" t="str">
         <v>Active</v>
@@ -36432,10 +36432,10 @@
         <v>1029</v>
       </c>
       <c r="B1030" t="str">
-        <v>FG-400579</v>
+        <v>FG-400578</v>
       </c>
       <c r="C1030" t="str">
-        <v>AGRI REDUCER (90X50MM)</v>
+        <v>AGRI REDUCER (90X63MM)</v>
       </c>
       <c r="D1030" t="str">
         <v>AGRI REDUCER</v>
@@ -36447,13 +36447,13 @@
         <v>General</v>
       </c>
       <c r="G1030" t="str">
-        <v>90X50MM</v>
+        <v>90X63MM</v>
       </c>
       <c r="H1030" t="str">
         <v>BOX</v>
       </c>
       <c r="I1030">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J1030" t="str">
         <v>Active</v>
@@ -36467,10 +36467,10 @@
         <v>1030</v>
       </c>
       <c r="B1031" t="str">
-        <v>FG-400578</v>
+        <v>FG-400577</v>
       </c>
       <c r="C1031" t="str">
-        <v>AGRI REDUCER (90X63MM)</v>
+        <v>AGRI REDUCER (90X75MM)</v>
       </c>
       <c r="D1031" t="str">
         <v>AGRI REDUCER</v>
@@ -36482,13 +36482,13 @@
         <v>General</v>
       </c>
       <c r="G1031" t="str">
-        <v>90X63MM</v>
+        <v>90X75MM</v>
       </c>
       <c r="H1031" t="str">
         <v>BOX</v>
       </c>
       <c r="I1031">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="J1031" t="str">
         <v>Active</v>
@@ -36502,10 +36502,10 @@
         <v>1031</v>
       </c>
       <c r="B1032" t="str">
-        <v>FG-400577</v>
+        <v>FG-400576</v>
       </c>
       <c r="C1032" t="str">
-        <v>AGRI REDUCER (90X75MM)</v>
+        <v>AGRI REDUCER (110X63MM)</v>
       </c>
       <c r="D1032" t="str">
         <v>AGRI REDUCER</v>
@@ -36517,13 +36517,13 @@
         <v>General</v>
       </c>
       <c r="G1032" t="str">
-        <v>90X75MM</v>
+        <v>110X63MM</v>
       </c>
       <c r="H1032" t="str">
         <v>BOX</v>
       </c>
       <c r="I1032">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J1032" t="str">
         <v>Active</v>
@@ -36537,10 +36537,10 @@
         <v>1032</v>
       </c>
       <c r="B1033" t="str">
-        <v>FG-400576</v>
+        <v>FG-400575</v>
       </c>
       <c r="C1033" t="str">
-        <v>AGRI REDUCER (110X63MM)</v>
+        <v>AGRI REDUCER (110X75MM)</v>
       </c>
       <c r="D1033" t="str">
         <v>AGRI REDUCER</v>
@@ -36552,7 +36552,7 @@
         <v>General</v>
       </c>
       <c r="G1033" t="str">
-        <v>110X63MM</v>
+        <v>110X75MM</v>
       </c>
       <c r="H1033" t="str">
         <v>BOX</v>
@@ -36572,10 +36572,10 @@
         <v>1033</v>
       </c>
       <c r="B1034" t="str">
-        <v>FG-400575</v>
+        <v>FG-400574</v>
       </c>
       <c r="C1034" t="str">
-        <v>AGRI REDUCER (110X75MM)</v>
+        <v>AGRI REDUCER (110X90MM)</v>
       </c>
       <c r="D1034" t="str">
         <v>AGRI REDUCER</v>
@@ -36587,13 +36587,13 @@
         <v>General</v>
       </c>
       <c r="G1034" t="str">
-        <v>110X75MM</v>
+        <v>110X90MM</v>
       </c>
       <c r="H1034" t="str">
         <v>BOX</v>
       </c>
       <c r="I1034">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J1034" t="str">
         <v>Active</v>
@@ -36607,13 +36607,13 @@
         <v>1034</v>
       </c>
       <c r="B1035" t="str">
-        <v>FG-400574</v>
+        <v>-</v>
       </c>
       <c r="C1035" t="str">
-        <v>AGRI REDUCER (110X90MM)</v>
+        <v>REDUCING BUSH (LW) (63 X 40)</v>
       </c>
       <c r="D1035" t="str">
-        <v>AGRI REDUCER</v>
+        <v>REDUCING BUSH (LW)</v>
       </c>
       <c r="E1035" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36622,19 +36622,19 @@
         <v>General</v>
       </c>
       <c r="G1035" t="str">
-        <v>110X90MM</v>
+        <v>63 X 40</v>
       </c>
       <c r="H1035" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1035">
-        <v>40</v>
+      <c r="I1035" t="str">
+        <v>-</v>
       </c>
       <c r="J1035" t="str">
         <v>Active</v>
       </c>
       <c r="K1035" t="str">
-        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
+        <v>REDUCING BUSH (LW) for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1036">
@@ -36645,7 +36645,7 @@
         <v>-</v>
       </c>
       <c r="C1036" t="str">
-        <v>REDUCING BUSH (LW) (63 X 40)</v>
+        <v>REDUCING BUSH (LW) (63 X 50)</v>
       </c>
       <c r="D1036" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36657,7 +36657,7 @@
         <v>General</v>
       </c>
       <c r="G1036" t="str">
-        <v>63 X 40</v>
+        <v>63 X 50</v>
       </c>
       <c r="H1036" t="str">
         <v>BOX</v>
@@ -36680,7 +36680,7 @@
         <v>-</v>
       </c>
       <c r="C1037" t="str">
-        <v>REDUCING BUSH (LW) (63 X 50)</v>
+        <v>REDUCING BUSH (LW) (75 X 40)</v>
       </c>
       <c r="D1037" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36692,7 +36692,7 @@
         <v>General</v>
       </c>
       <c r="G1037" t="str">
-        <v>63 X 50</v>
+        <v>75 X 40</v>
       </c>
       <c r="H1037" t="str">
         <v>BOX</v>
@@ -36715,7 +36715,7 @@
         <v>-</v>
       </c>
       <c r="C1038" t="str">
-        <v>REDUCING BUSH (LW) (75 X 40)</v>
+        <v>REDUCING BUSH (LW) (75 X 63)</v>
       </c>
       <c r="D1038" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36727,7 +36727,7 @@
         <v>General</v>
       </c>
       <c r="G1038" t="str">
-        <v>75 X 40</v>
+        <v>75 X 63</v>
       </c>
       <c r="H1038" t="str">
         <v>BOX</v>
@@ -36750,7 +36750,7 @@
         <v>-</v>
       </c>
       <c r="C1039" t="str">
-        <v>REDUCING BUSH (LW) (75 X 63)</v>
+        <v>REDUCING BUSH (LW) (90 X 50)</v>
       </c>
       <c r="D1039" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36762,7 +36762,7 @@
         <v>General</v>
       </c>
       <c r="G1039" t="str">
-        <v>75 X 63</v>
+        <v>90 X 50</v>
       </c>
       <c r="H1039" t="str">
         <v>BOX</v>
@@ -36785,7 +36785,7 @@
         <v>-</v>
       </c>
       <c r="C1040" t="str">
-        <v>REDUCING BUSH (LW) (90 X 50)</v>
+        <v>REDUCING BUSH (LW) (90 X 63)</v>
       </c>
       <c r="D1040" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36797,7 +36797,7 @@
         <v>General</v>
       </c>
       <c r="G1040" t="str">
-        <v>90 X 50</v>
+        <v>90 X 63</v>
       </c>
       <c r="H1040" t="str">
         <v>BOX</v>
@@ -36820,7 +36820,7 @@
         <v>-</v>
       </c>
       <c r="C1041" t="str">
-        <v>REDUCING BUSH (LW) (90 X 63)</v>
+        <v>REDUCING BUSH (LW) (90 X 75)</v>
       </c>
       <c r="D1041" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36832,7 +36832,7 @@
         <v>General</v>
       </c>
       <c r="G1041" t="str">
-        <v>90 X 63</v>
+        <v>90 X 75</v>
       </c>
       <c r="H1041" t="str">
         <v>BOX</v>
@@ -36855,7 +36855,7 @@
         <v>-</v>
       </c>
       <c r="C1042" t="str">
-        <v>REDUCING BUSH (LW) (90 X 75)</v>
+        <v>REDUCING BUSH (LW) (110 X 63)</v>
       </c>
       <c r="D1042" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36867,7 +36867,7 @@
         <v>General</v>
       </c>
       <c r="G1042" t="str">
-        <v>90 X 75</v>
+        <v>110 X 63</v>
       </c>
       <c r="H1042" t="str">
         <v>BOX</v>
@@ -36890,7 +36890,7 @@
         <v>-</v>
       </c>
       <c r="C1043" t="str">
-        <v>REDUCING BUSH (LW) (110 X 63)</v>
+        <v>REDUCING BUSH (LW) (110 X 75)</v>
       </c>
       <c r="D1043" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36902,7 +36902,7 @@
         <v>General</v>
       </c>
       <c r="G1043" t="str">
-        <v>110 X 63</v>
+        <v>110 X 75</v>
       </c>
       <c r="H1043" t="str">
         <v>BOX</v>
@@ -36925,7 +36925,7 @@
         <v>-</v>
       </c>
       <c r="C1044" t="str">
-        <v>REDUCING BUSH (LW) (110 X 75)</v>
+        <v>REDUCING BUSH (LW) (110 X 90)</v>
       </c>
       <c r="D1044" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36937,7 +36937,7 @@
         <v>General</v>
       </c>
       <c r="G1044" t="str">
-        <v>110 X 75</v>
+        <v>110 X 90</v>
       </c>
       <c r="H1044" t="str">
         <v>BOX</v>
@@ -36957,13 +36957,13 @@
         <v>1044</v>
       </c>
       <c r="B1045" t="str">
-        <v>-</v>
+        <v>FG-400550</v>
       </c>
       <c r="C1045" t="str">
-        <v>REDUCING BUSH (LW) (110 X 90)</v>
+        <v>AGRI TEE (40MM)</v>
       </c>
       <c r="D1045" t="str">
-        <v>REDUCING BUSH (LW)</v>
+        <v>AGRI TEE</v>
       </c>
       <c r="E1045" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36972,19 +36972,19 @@
         <v>General</v>
       </c>
       <c r="G1045" t="str">
-        <v>110 X 90</v>
+        <v>40MM</v>
       </c>
       <c r="H1045" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1045" t="str">
-        <v>-</v>
+      <c r="I1045">
+        <v>150</v>
       </c>
       <c r="J1045" t="str">
         <v>Active</v>
       </c>
       <c r="K1045" t="str">
-        <v>REDUCING BUSH (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1046">
@@ -36992,10 +36992,10 @@
         <v>1045</v>
       </c>
       <c r="B1046" t="str">
-        <v>FG-400550</v>
+        <v>FG-400551</v>
       </c>
       <c r="C1046" t="str">
-        <v>AGRI TEE (40MM)</v>
+        <v>AGRI TEE (50MM)</v>
       </c>
       <c r="D1046" t="str">
         <v>AGRI TEE</v>
@@ -37007,13 +37007,13 @@
         <v>General</v>
       </c>
       <c r="G1046" t="str">
-        <v>40MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1046" t="str">
         <v>BOX</v>
       </c>
       <c r="I1046">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J1046" t="str">
         <v>Active</v>
@@ -37027,10 +37027,10 @@
         <v>1046</v>
       </c>
       <c r="B1047" t="str">
-        <v>FG-400551</v>
+        <v>FG-400552</v>
       </c>
       <c r="C1047" t="str">
-        <v>AGRI TEE (50MM)</v>
+        <v>AGRI TEE (63MM)</v>
       </c>
       <c r="D1047" t="str">
         <v>AGRI TEE</v>
@@ -37042,13 +37042,13 @@
         <v>General</v>
       </c>
       <c r="G1047" t="str">
-        <v>50MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1047" t="str">
         <v>BOX</v>
       </c>
       <c r="I1047">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J1047" t="str">
         <v>Active</v>
@@ -37062,10 +37062,10 @@
         <v>1047</v>
       </c>
       <c r="B1048" t="str">
-        <v>FG-400552</v>
+        <v>FG-400553</v>
       </c>
       <c r="C1048" t="str">
-        <v>AGRI TEE (63MM)</v>
+        <v>AGRI TEE (75MM)</v>
       </c>
       <c r="D1048" t="str">
         <v>AGRI TEE</v>
@@ -37077,13 +37077,13 @@
         <v>General</v>
       </c>
       <c r="G1048" t="str">
-        <v>63MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1048" t="str">
         <v>BOX</v>
       </c>
       <c r="I1048">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="J1048" t="str">
         <v>Active</v>
@@ -37097,10 +37097,10 @@
         <v>1048</v>
       </c>
       <c r="B1049" t="str">
-        <v>FG-400553</v>
+        <v>FG-400554</v>
       </c>
       <c r="C1049" t="str">
-        <v>AGRI TEE (75MM)</v>
+        <v>AGRI TEE (90MM)</v>
       </c>
       <c r="D1049" t="str">
         <v>AGRI TEE</v>
@@ -37112,13 +37112,13 @@
         <v>General</v>
       </c>
       <c r="G1049" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1049" t="str">
         <v>BOX</v>
       </c>
       <c r="I1049">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J1049" t="str">
         <v>Active</v>
@@ -37132,10 +37132,10 @@
         <v>1049</v>
       </c>
       <c r="B1050" t="str">
-        <v>FG-400554</v>
+        <v>FG-400586</v>
       </c>
       <c r="C1050" t="str">
-        <v>AGRI TEE (90MM)</v>
+        <v>AGRI TEE (110MM)</v>
       </c>
       <c r="D1050" t="str">
         <v>AGRI TEE</v>
@@ -37147,13 +37147,13 @@
         <v>General</v>
       </c>
       <c r="G1050" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1050" t="str">
         <v>BOX</v>
       </c>
       <c r="I1050">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J1050" t="str">
         <v>Active</v>
@@ -37167,10 +37167,10 @@
         <v>1050</v>
       </c>
       <c r="B1051" t="str">
-        <v>FG-400586</v>
+        <v>FG-400607</v>
       </c>
       <c r="C1051" t="str">
-        <v>AGRI TEE (110MM)</v>
+        <v>AGRI TEE (140MM)</v>
       </c>
       <c r="D1051" t="str">
         <v>AGRI TEE</v>
@@ -37182,13 +37182,13 @@
         <v>General</v>
       </c>
       <c r="G1051" t="str">
-        <v>110MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1051" t="str">
         <v>BOX</v>
       </c>
       <c r="I1051">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="J1051" t="str">
         <v>Active</v>
@@ -37202,10 +37202,10 @@
         <v>1051</v>
       </c>
       <c r="B1052" t="str">
-        <v>FG-400607</v>
+        <v>FG-400608</v>
       </c>
       <c r="C1052" t="str">
-        <v>AGRI TEE (140MM)</v>
+        <v>AGRI TEE (160MM)</v>
       </c>
       <c r="D1052" t="str">
         <v>AGRI TEE</v>
@@ -37217,13 +37217,13 @@
         <v>General</v>
       </c>
       <c r="G1052" t="str">
-        <v>140MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1052" t="str">
         <v>BOX</v>
       </c>
       <c r="I1052">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J1052" t="str">
         <v>Active</v>
@@ -37237,13 +37237,13 @@
         <v>1052</v>
       </c>
       <c r="B1053" t="str">
-        <v>FG-400608</v>
+        <v>-</v>
       </c>
       <c r="C1053" t="str">
-        <v>AGRI TEE (160MM)</v>
+        <v>COUPLER (LW) (75MM)</v>
       </c>
       <c r="D1053" t="str">
-        <v>AGRI TEE</v>
+        <v>COUPLER (LW)</v>
       </c>
       <c r="E1053" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37252,19 +37252,19 @@
         <v>General</v>
       </c>
       <c r="G1053" t="str">
-        <v>160MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1053" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1053">
-        <v>9</v>
+      <c r="I1053" t="str">
+        <v>-</v>
       </c>
       <c r="J1053" t="str">
         <v>Active</v>
       </c>
       <c r="K1053" t="str">
-        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
+        <v>COUPLER (LW) for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1054">
@@ -37275,7 +37275,7 @@
         <v>-</v>
       </c>
       <c r="C1054" t="str">
-        <v>COUPLER (LW) (75MM)</v>
+        <v>COUPLER (LW) (90MM)</v>
       </c>
       <c r="D1054" t="str">
         <v>COUPLER (LW)</v>
@@ -37287,7 +37287,7 @@
         <v>General</v>
       </c>
       <c r="G1054" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1054" t="str">
         <v>BOX</v>
@@ -37310,7 +37310,7 @@
         <v>-</v>
       </c>
       <c r="C1055" t="str">
-        <v>COUPLER (LW) (90MM)</v>
+        <v>COUPLER (LW) (110MM)</v>
       </c>
       <c r="D1055" t="str">
         <v>COUPLER (LW)</v>
@@ -37322,7 +37322,7 @@
         <v>General</v>
       </c>
       <c r="G1055" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1055" t="str">
         <v>BOX</v>
@@ -37342,13 +37342,13 @@
         <v>1055</v>
       </c>
       <c r="B1056" t="str">
-        <v>-</v>
+        <v>FG-400561</v>
       </c>
       <c r="C1056" t="str">
-        <v>COUPLER (LW) (110MM)</v>
+        <v>AGRI FABRICATED COUPLER (40MM)</v>
       </c>
       <c r="D1056" t="str">
-        <v>COUPLER (LW)</v>
+        <v>AGRI FABRICATED COUPLER</v>
       </c>
       <c r="E1056" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37357,19 +37357,19 @@
         <v>General</v>
       </c>
       <c r="G1056" t="str">
-        <v>110MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1056" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1056" t="str">
-        <v>-</v>
+      <c r="I1056">
+        <v>300</v>
       </c>
       <c r="J1056" t="str">
         <v>Active</v>
       </c>
       <c r="K1056" t="str">
-        <v>COUPLER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI FABRICATED COUPLER for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1057">
@@ -37377,10 +37377,10 @@
         <v>1056</v>
       </c>
       <c r="B1057" t="str">
-        <v>FG-400561</v>
+        <v>FG-400562</v>
       </c>
       <c r="C1057" t="str">
-        <v>AGRI FABRICATED COUPLER (40MM)</v>
+        <v>AGRI FABRICATED COUPLER (50MM)</v>
       </c>
       <c r="D1057" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37392,13 +37392,13 @@
         <v>General</v>
       </c>
       <c r="G1057" t="str">
-        <v>40MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1057" t="str">
         <v>BOX</v>
       </c>
       <c r="I1057">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J1057" t="str">
         <v>Active</v>
@@ -37412,10 +37412,10 @@
         <v>1057</v>
       </c>
       <c r="B1058" t="str">
-        <v>FG-400562</v>
+        <v>FG-400563</v>
       </c>
       <c r="C1058" t="str">
-        <v>AGRI FABRICATED COUPLER (50MM)</v>
+        <v>AGRI FABRICATED COUPLER (63MM)</v>
       </c>
       <c r="D1058" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37427,7 +37427,7 @@
         <v>General</v>
       </c>
       <c r="G1058" t="str">
-        <v>50MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1058" t="str">
         <v>BOX</v>
@@ -37447,10 +37447,10 @@
         <v>1058</v>
       </c>
       <c r="B1059" t="str">
-        <v>FG-400563</v>
+        <v>FG-400564</v>
       </c>
       <c r="C1059" t="str">
-        <v>AGRI FABRICATED COUPLER (63MM)</v>
+        <v>AGRI FABRICATED COUPLER (75MM)</v>
       </c>
       <c r="D1059" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37462,13 +37462,13 @@
         <v>General</v>
       </c>
       <c r="G1059" t="str">
-        <v>63MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1059" t="str">
         <v>BOX</v>
       </c>
       <c r="I1059">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="J1059" t="str">
         <v>Active</v>
@@ -37482,10 +37482,10 @@
         <v>1059</v>
       </c>
       <c r="B1060" t="str">
-        <v>FG-400564</v>
+        <v>FG-400565</v>
       </c>
       <c r="C1060" t="str">
-        <v>AGRI FABRICATED COUPLER (75MM)</v>
+        <v>AGRI FABRICATED COUPLER (90MM)</v>
       </c>
       <c r="D1060" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37497,13 +37497,13 @@
         <v>General</v>
       </c>
       <c r="G1060" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1060" t="str">
         <v>BOX</v>
       </c>
       <c r="I1060">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="J1060" t="str">
         <v>Active</v>
@@ -37517,10 +37517,10 @@
         <v>1060</v>
       </c>
       <c r="B1061" t="str">
-        <v>FG-400565</v>
+        <v>FG-400566</v>
       </c>
       <c r="C1061" t="str">
-        <v>AGRI FABRICATED COUPLER (90MM)</v>
+        <v>AGRI FABRICATED COUPLER (110MM)</v>
       </c>
       <c r="D1061" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37532,13 +37532,13 @@
         <v>General</v>
       </c>
       <c r="G1061" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1061" t="str">
         <v>BOX</v>
       </c>
       <c r="I1061">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J1061" t="str">
         <v>Active</v>
@@ -37552,10 +37552,10 @@
         <v>1061</v>
       </c>
       <c r="B1062" t="str">
-        <v>FG-400566</v>
+        <v>FG-400587</v>
       </c>
       <c r="C1062" t="str">
-        <v>AGRI FABRICATED COUPLER (110MM)</v>
+        <v>AGRI FABRICATED COUPLER (140MM 4KG)</v>
       </c>
       <c r="D1062" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37567,13 +37567,13 @@
         <v>General</v>
       </c>
       <c r="G1062" t="str">
-        <v>110MM</v>
+        <v>140MM 4KG</v>
       </c>
       <c r="H1062" t="str">
         <v>BOX</v>
       </c>
       <c r="I1062">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J1062" t="str">
         <v>Active</v>
@@ -37587,10 +37587,10 @@
         <v>1062</v>
       </c>
       <c r="B1063" t="str">
-        <v>FG-400587</v>
+        <v>FG-400568</v>
       </c>
       <c r="C1063" t="str">
-        <v>AGRI FABRICATED COUPLER (140MM 4KG)</v>
+        <v>AGRI FABRICATED COUPLER (160MM 4KG)</v>
       </c>
       <c r="D1063" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37602,13 +37602,13 @@
         <v>General</v>
       </c>
       <c r="G1063" t="str">
-        <v>140MM 4KG</v>
+        <v>160MM 4KG</v>
       </c>
       <c r="H1063" t="str">
         <v>BOX</v>
       </c>
       <c r="I1063">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J1063" t="str">
         <v>Active</v>
@@ -37622,13 +37622,13 @@
         <v>1063</v>
       </c>
       <c r="B1064" t="str">
-        <v>FG-400568</v>
+        <v>FG-400567</v>
       </c>
       <c r="C1064" t="str">
-        <v>AGRI FABRICATED COUPLER (160MM 4KG)</v>
+        <v>AGRI FABRICATED COUPLER 6KG (140MM)</v>
       </c>
       <c r="D1064" t="str">
-        <v>AGRI FABRICATED COUPLER</v>
+        <v>AGRI FABRICATED COUPLER 6KG</v>
       </c>
       <c r="E1064" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37637,19 +37637,19 @@
         <v>General</v>
       </c>
       <c r="G1064" t="str">
-        <v>160MM 4KG</v>
+        <v>140MM</v>
       </c>
       <c r="H1064" t="str">
         <v>BOX</v>
       </c>
       <c r="I1064">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J1064" t="str">
         <v>Active</v>
       </c>
       <c r="K1064" t="str">
-        <v>AGRI FABRICATED COUPLER for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
+        <v>AGRI FABRICATED COUPLER 6KG for agriculture irrigation and piping systems. Available sizes: 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1065">
@@ -37657,10 +37657,10 @@
         <v>1064</v>
       </c>
       <c r="B1065" t="str">
-        <v>FG-400567</v>
+        <v>FG-400569</v>
       </c>
       <c r="C1065" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG (140MM)</v>
+        <v>AGRI FABRICATED COUPLER 6KG (160MM)</v>
       </c>
       <c r="D1065" t="str">
         <v>AGRI FABRICATED COUPLER 6KG</v>
@@ -37672,13 +37672,13 @@
         <v>General</v>
       </c>
       <c r="G1065" t="str">
-        <v>140MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1065" t="str">
         <v>BOX</v>
       </c>
       <c r="I1065">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J1065" t="str">
         <v>Active</v>
@@ -37692,13 +37692,13 @@
         <v>1065</v>
       </c>
       <c r="B1066" t="str">
-        <v>FG-400569</v>
+        <v>FG-400544</v>
       </c>
       <c r="C1066" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG (160MM)</v>
+        <v>AGRI ELBOW (40MM)</v>
       </c>
       <c r="D1066" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG</v>
+        <v>AGRI ELBOW</v>
       </c>
       <c r="E1066" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37707,19 +37707,19 @@
         <v>General</v>
       </c>
       <c r="G1066" t="str">
-        <v>160MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1066" t="str">
         <v>BOX</v>
       </c>
       <c r="I1066">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="J1066" t="str">
         <v>Active</v>
       </c>
       <c r="K1066" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG for agriculture irrigation and piping systems. Available sizes: 140MM, 160MM.</v>
+        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1067">
@@ -37727,10 +37727,10 @@
         <v>1066</v>
       </c>
       <c r="B1067" t="str">
-        <v>FG-400544</v>
+        <v>FG-400545</v>
       </c>
       <c r="C1067" t="str">
-        <v>AGRI ELBOW (40MM)</v>
+        <v>AGRI ELBOW (50MM)</v>
       </c>
       <c r="D1067" t="str">
         <v>AGRI ELBOW</v>
@@ -37742,13 +37742,13 @@
         <v>General</v>
       </c>
       <c r="G1067" t="str">
-        <v>40MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1067" t="str">
         <v>BOX</v>
       </c>
       <c r="I1067">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="J1067" t="str">
         <v>Active</v>
@@ -37762,10 +37762,10 @@
         <v>1067</v>
       </c>
       <c r="B1068" t="str">
-        <v>FG-400545</v>
+        <v>FG-400546</v>
       </c>
       <c r="C1068" t="str">
-        <v>AGRI ELBOW (50MM)</v>
+        <v>AGRI ELBOW (63MM)</v>
       </c>
       <c r="D1068" t="str">
         <v>AGRI ELBOW</v>
@@ -37777,13 +37777,13 @@
         <v>General</v>
       </c>
       <c r="G1068" t="str">
-        <v>50MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1068" t="str">
         <v>BOX</v>
       </c>
       <c r="I1068">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J1068" t="str">
         <v>Active</v>
@@ -37797,10 +37797,10 @@
         <v>1068</v>
       </c>
       <c r="B1069" t="str">
-        <v>FG-400546</v>
+        <v>FG-400547</v>
       </c>
       <c r="C1069" t="str">
-        <v>AGRI ELBOW (63MM)</v>
+        <v>AGRI ELBOW (75MM)</v>
       </c>
       <c r="D1069" t="str">
         <v>AGRI ELBOW</v>
@@ -37812,13 +37812,13 @@
         <v>General</v>
       </c>
       <c r="G1069" t="str">
-        <v>63MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1069" t="str">
         <v>BOX</v>
       </c>
       <c r="I1069">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J1069" t="str">
         <v>Active</v>
@@ -37832,10 +37832,10 @@
         <v>1069</v>
       </c>
       <c r="B1070" t="str">
-        <v>FG-400547</v>
+        <v>FG-400548</v>
       </c>
       <c r="C1070" t="str">
-        <v>AGRI ELBOW (75MM)</v>
+        <v>AGRI ELBOW (90MM)</v>
       </c>
       <c r="D1070" t="str">
         <v>AGRI ELBOW</v>
@@ -37847,13 +37847,13 @@
         <v>General</v>
       </c>
       <c r="G1070" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1070" t="str">
         <v>BOX</v>
       </c>
       <c r="I1070">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="J1070" t="str">
         <v>Active</v>
@@ -37867,10 +37867,10 @@
         <v>1070</v>
       </c>
       <c r="B1071" t="str">
-        <v>FG-400548</v>
+        <v>FG-400549</v>
       </c>
       <c r="C1071" t="str">
-        <v>AGRI ELBOW (90MM)</v>
+        <v>AGRI ELBOW (110MM)</v>
       </c>
       <c r="D1071" t="str">
         <v>AGRI ELBOW</v>
@@ -37882,13 +37882,13 @@
         <v>General</v>
       </c>
       <c r="G1071" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1071" t="str">
         <v>BOX</v>
       </c>
       <c r="I1071">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J1071" t="str">
         <v>Active</v>
@@ -37902,10 +37902,10 @@
         <v>1071</v>
       </c>
       <c r="B1072" t="str">
-        <v>FG-400549</v>
+        <v>FG-400595</v>
       </c>
       <c r="C1072" t="str">
-        <v>AGRI ELBOW (110MM)</v>
+        <v>AGRI ELBOW (140MM)</v>
       </c>
       <c r="D1072" t="str">
         <v>AGRI ELBOW</v>
@@ -37917,13 +37917,13 @@
         <v>General</v>
       </c>
       <c r="G1072" t="str">
-        <v>110MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1072" t="str">
         <v>BOX</v>
       </c>
       <c r="I1072">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="J1072" t="str">
         <v>Active</v>
@@ -37937,10 +37937,10 @@
         <v>1072</v>
       </c>
       <c r="B1073" t="str">
-        <v>FG-400595</v>
+        <v>FG-400596</v>
       </c>
       <c r="C1073" t="str">
-        <v>AGRI ELBOW (140MM)</v>
+        <v>AGRI ELBOW (160MM)</v>
       </c>
       <c r="D1073" t="str">
         <v>AGRI ELBOW</v>
@@ -37952,13 +37952,13 @@
         <v>General</v>
       </c>
       <c r="G1073" t="str">
-        <v>140MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1073" t="str">
         <v>BOX</v>
       </c>
       <c r="I1073">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J1073" t="str">
         <v>Active</v>
@@ -37972,13 +37972,13 @@
         <v>1073</v>
       </c>
       <c r="B1074" t="str">
-        <v>FG-400596</v>
+        <v>FG-400555</v>
       </c>
       <c r="C1074" t="str">
-        <v>AGRI ELBOW (160MM)</v>
+        <v>AGRI END CAP (40MM)</v>
       </c>
       <c r="D1074" t="str">
-        <v>AGRI ELBOW</v>
+        <v>AGRI END CAP</v>
       </c>
       <c r="E1074" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37987,19 +37987,19 @@
         <v>General</v>
       </c>
       <c r="G1074" t="str">
-        <v>160MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1074" t="str">
         <v>BOX</v>
       </c>
       <c r="I1074">
-        <v>12</v>
+        <v>800</v>
       </c>
       <c r="J1074" t="str">
         <v>Active</v>
       </c>
       <c r="K1074" t="str">
-        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
+        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1075">
@@ -38007,10 +38007,10 @@
         <v>1074</v>
       </c>
       <c r="B1075" t="str">
-        <v>FG-400555</v>
+        <v>FG-400556</v>
       </c>
       <c r="C1075" t="str">
-        <v>AGRI END CAP (40MM)</v>
+        <v>AGRI END CAP (50MM)</v>
       </c>
       <c r="D1075" t="str">
         <v>AGRI END CAP</v>
@@ -38022,13 +38022,13 @@
         <v>General</v>
       </c>
       <c r="G1075" t="str">
-        <v>40MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1075" t="str">
         <v>BOX</v>
       </c>
       <c r="I1075">
-        <v>800</v>
+        <v>450</v>
       </c>
       <c r="J1075" t="str">
         <v>Active</v>
@@ -38042,10 +38042,10 @@
         <v>1075</v>
       </c>
       <c r="B1076" t="str">
-        <v>FG-400556</v>
+        <v>FG-400557</v>
       </c>
       <c r="C1076" t="str">
-        <v>AGRI END CAP (50MM)</v>
+        <v>AGRI END CAP (63MM)</v>
       </c>
       <c r="D1076" t="str">
         <v>AGRI END CAP</v>
@@ -38057,13 +38057,13 @@
         <v>General</v>
       </c>
       <c r="G1076" t="str">
-        <v>50MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1076" t="str">
         <v>BOX</v>
       </c>
       <c r="I1076">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="J1076" t="str">
         <v>Active</v>
@@ -38077,10 +38077,10 @@
         <v>1076</v>
       </c>
       <c r="B1077" t="str">
-        <v>FG-400557</v>
+        <v>FG-400558</v>
       </c>
       <c r="C1077" t="str">
-        <v>AGRI END CAP (63MM)</v>
+        <v>AGRI END CAP (75MM)</v>
       </c>
       <c r="D1077" t="str">
         <v>AGRI END CAP</v>
@@ -38092,13 +38092,13 @@
         <v>General</v>
       </c>
       <c r="G1077" t="str">
-        <v>63MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1077" t="str">
         <v>BOX</v>
       </c>
       <c r="I1077">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="J1077" t="str">
         <v>Active</v>
@@ -38112,10 +38112,10 @@
         <v>1077</v>
       </c>
       <c r="B1078" t="str">
-        <v>FG-400558</v>
+        <v>FG-400559</v>
       </c>
       <c r="C1078" t="str">
-        <v>AGRI END CAP (75MM)</v>
+        <v>AGRI END CAP (90MM)</v>
       </c>
       <c r="D1078" t="str">
         <v>AGRI END CAP</v>
@@ -38127,13 +38127,13 @@
         <v>General</v>
       </c>
       <c r="G1078" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1078" t="str">
         <v>BOX</v>
       </c>
       <c r="I1078">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J1078" t="str">
         <v>Active</v>
@@ -38147,10 +38147,10 @@
         <v>1078</v>
       </c>
       <c r="B1079" t="str">
-        <v>FG-400559</v>
+        <v>FG-400560</v>
       </c>
       <c r="C1079" t="str">
-        <v>AGRI END CAP (90MM)</v>
+        <v>AGRI END CAP (110MM)</v>
       </c>
       <c r="D1079" t="str">
         <v>AGRI END CAP</v>
@@ -38162,13 +38162,13 @@
         <v>General</v>
       </c>
       <c r="G1079" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1079" t="str">
         <v>BOX</v>
       </c>
       <c r="I1079">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J1079" t="str">
         <v>Active</v>
@@ -38182,10 +38182,10 @@
         <v>1079</v>
       </c>
       <c r="B1080" t="str">
-        <v>FG-400560</v>
+        <v>FG-400639</v>
       </c>
       <c r="C1080" t="str">
-        <v>AGRI END CAP (110MM)</v>
+        <v>AGRI END CAP (140MM 4KG)</v>
       </c>
       <c r="D1080" t="str">
         <v>AGRI END CAP</v>
@@ -38197,13 +38197,13 @@
         <v>General</v>
       </c>
       <c r="G1080" t="str">
-        <v>110MM</v>
+        <v>140MM 4KG</v>
       </c>
       <c r="H1080" t="str">
         <v>BOX</v>
       </c>
       <c r="I1080">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J1080" t="str">
         <v>Active</v>
@@ -38217,10 +38217,10 @@
         <v>1080</v>
       </c>
       <c r="B1081" t="str">
-        <v>FG-400639</v>
+        <v>FG-400640</v>
       </c>
       <c r="C1081" t="str">
-        <v>AGRI END CAP (140MM 4KG)</v>
+        <v>AGRI END CAP (160MM 4KG)</v>
       </c>
       <c r="D1081" t="str">
         <v>AGRI END CAP</v>
@@ -38232,13 +38232,13 @@
         <v>General</v>
       </c>
       <c r="G1081" t="str">
-        <v>140MM 4KG</v>
+        <v>160MM 4KG</v>
       </c>
       <c r="H1081" t="str">
         <v>BOX</v>
       </c>
       <c r="I1081">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J1081" t="str">
         <v>Active</v>
@@ -38252,13 +38252,13 @@
         <v>1081</v>
       </c>
       <c r="B1082" t="str">
-        <v>FG-400640</v>
+        <v>FG-400570</v>
       </c>
       <c r="C1082" t="str">
-        <v>AGRI END CAP (160MM 4KG)</v>
+        <v>AGRI LONG BEND (63MM)</v>
       </c>
       <c r="D1082" t="str">
-        <v>AGRI END CAP</v>
+        <v>AGRI LONG BEND</v>
       </c>
       <c r="E1082" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -38267,19 +38267,19 @@
         <v>General</v>
       </c>
       <c r="G1082" t="str">
-        <v>160MM 4KG</v>
+        <v>63MM</v>
       </c>
       <c r="H1082" t="str">
         <v>BOX</v>
       </c>
       <c r="I1082">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="J1082" t="str">
         <v>Active</v>
       </c>
       <c r="K1082" t="str">
-        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
+        <v>AGRI LONG BEND for agriculture irrigation and piping systems. Available sizes: 63MM, 75MM, 90MM, 110MM.</v>
       </c>
     </row>
     <row r="1083">
@@ -38287,10 +38287,10 @@
         <v>1082</v>
       </c>
       <c r="B1083" t="str">
-        <v>FG-400570</v>
+        <v>FG-400571</v>
       </c>
       <c r="C1083" t="str">
-        <v>AGRI LONG BEND (63MM)</v>
+        <v>AGRI LONG BEND (75MM)</v>
       </c>
       <c r="D1083" t="str">
         <v>AGRI LONG BEND</v>
@@ -38302,13 +38302,13 @@
         <v>General</v>
       </c>
       <c r="G1083" t="str">
-        <v>63MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1083" t="str">
         <v>BOX</v>
       </c>
       <c r="I1083">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J1083" t="str">
         <v>Active</v>
@@ -38322,10 +38322,10 @@
         <v>1083</v>
       </c>
       <c r="B1084" t="str">
-        <v>FG-400571</v>
+        <v>FG-400572</v>
       </c>
       <c r="C1084" t="str">
-        <v>AGRI LONG BEND (75MM)</v>
+        <v>AGRI LONG BEND (90MM)</v>
       </c>
       <c r="D1084" t="str">
         <v>AGRI LONG BEND</v>
@@ -38337,13 +38337,13 @@
         <v>General</v>
       </c>
       <c r="G1084" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1084" t="str">
         <v>BOX</v>
       </c>
       <c r="I1084">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J1084" t="str">
         <v>Active</v>
@@ -38357,10 +38357,10 @@
         <v>1084</v>
       </c>
       <c r="B1085" t="str">
-        <v>FG-400572</v>
+        <v>FG-400573</v>
       </c>
       <c r="C1085" t="str">
-        <v>AGRI LONG BEND (90MM)</v>
+        <v>AGRI LONG BEND (110MM)</v>
       </c>
       <c r="D1085" t="str">
         <v>AGRI LONG BEND</v>
@@ -38372,13 +38372,13 @@
         <v>General</v>
       </c>
       <c r="G1085" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1085" t="str">
         <v>BOX</v>
       </c>
       <c r="I1085">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J1085" t="str">
         <v>Active</v>
@@ -38392,34 +38392,34 @@
         <v>1085</v>
       </c>
       <c r="B1086" t="str">
-        <v>FG-400573</v>
+        <v>FG-401520</v>
       </c>
       <c r="C1086" t="str">
-        <v>AGRI LONG BEND (110MM)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1086" t="str">
-        <v>AGRI LONG BEND</v>
+        <v>SPRINKLER ISI PIPE 6 MTR</v>
       </c>
       <c r="E1086" t="str">
-        <v>Agriculture Pipes &amp; Fittings</v>
+        <v>Sprinkler Pipes &amp; Fittings</v>
       </c>
       <c r="F1086" t="str">
         <v>General</v>
       </c>
       <c r="G1086" t="str">
-        <v>110MM</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1086" t="str">
-        <v>BOX</v>
-      </c>
-      <c r="I1086">
-        <v>10</v>
+        <v>Nos</v>
+      </c>
+      <c r="I1086" t="str">
+        <v>-</v>
       </c>
       <c r="J1086" t="str">
         <v>Active</v>
       </c>
       <c r="K1086" t="str">
-        <v>AGRI LONG BEND for agriculture irrigation and piping systems. Available sizes: 63MM, 75MM, 90MM, 110MM.</v>
+        <v>SPRINKLER ISI PIPE 6 MTR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1087">
@@ -38427,10 +38427,10 @@
         <v>1086</v>
       </c>
       <c r="B1087" t="str">
-        <v>FG-401520</v>
+        <v>FG-401491</v>
       </c>
       <c r="C1087" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (63MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1087" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38442,7 +38442,7 @@
         <v>General</v>
       </c>
       <c r="G1087" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>63MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1087" t="str">
         <v>Nos</v>
@@ -38462,10 +38462,10 @@
         <v>1087</v>
       </c>
       <c r="B1088" t="str">
-        <v>FG-401491</v>
+        <v>FG-401490</v>
       </c>
       <c r="C1088" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (63MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 2.5 KG)</v>
       </c>
       <c r="D1088" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38477,7 +38477,7 @@
         <v>General</v>
       </c>
       <c r="G1088" t="str">
-        <v>63MM L TYPE 3.2 KG</v>
+        <v>75MM C TYPE 2.5 KG</v>
       </c>
       <c r="H1088" t="str">
         <v>Nos</v>
@@ -38497,10 +38497,10 @@
         <v>1088</v>
       </c>
       <c r="B1089" t="str">
-        <v>FG-401490</v>
+        <v>FG-401492</v>
       </c>
       <c r="C1089" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 2.5 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1089" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38512,7 +38512,7 @@
         <v>General</v>
       </c>
       <c r="G1089" t="str">
-        <v>75MM C TYPE 2.5 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1089" t="str">
         <v>Nos</v>
@@ -38532,10 +38532,10 @@
         <v>1089</v>
       </c>
       <c r="B1090" t="str">
-        <v>FG-401492</v>
+        <v>FG-401519</v>
       </c>
       <c r="C1090" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 2.5 KG)</v>
       </c>
       <c r="D1090" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38547,7 +38547,7 @@
         <v>General</v>
       </c>
       <c r="G1090" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>75MM L TYPE 2.5 KG</v>
       </c>
       <c r="H1090" t="str">
         <v>Nos</v>
@@ -38567,10 +38567,10 @@
         <v>1090</v>
       </c>
       <c r="B1091" t="str">
-        <v>FG-401519</v>
+        <v>FG-401521</v>
       </c>
       <c r="C1091" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 2.5 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1091" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38582,7 +38582,7 @@
         <v>General</v>
       </c>
       <c r="G1091" t="str">
-        <v>75MM L TYPE 2.5 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1091" t="str">
         <v>Nos</v>
@@ -38602,13 +38602,13 @@
         <v>1091</v>
       </c>
       <c r="B1092" t="str">
-        <v>FG-401521</v>
+        <v>FG-401522</v>
       </c>
       <c r="C1092" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1092" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR</v>
+        <v>SPRINKLER NISI PIPE 6 MTR</v>
       </c>
       <c r="E1092" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38629,7 +38629,7 @@
         <v>Active</v>
       </c>
       <c r="K1092" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER NISI PIPE 6 MTR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1093">
@@ -38637,10 +38637,10 @@
         <v>1092</v>
       </c>
       <c r="B1093" t="str">
-        <v>FG-401522</v>
+        <v>FG-401523</v>
       </c>
       <c r="C1093" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1093" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38652,7 +38652,7 @@
         <v>General</v>
       </c>
       <c r="G1093" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1093" t="str">
         <v>Nos</v>
@@ -38672,10 +38672,10 @@
         <v>1093</v>
       </c>
       <c r="B1094" t="str">
-        <v>FG-401523</v>
+        <v>FG-401866</v>
       </c>
       <c r="C1094" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (90MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1094" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38687,7 +38687,7 @@
         <v>General</v>
       </c>
       <c r="G1094" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>90MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1094" t="str">
         <v>Nos</v>
@@ -38707,10 +38707,10 @@
         <v>1094</v>
       </c>
       <c r="B1095" t="str">
-        <v>FG-401866</v>
+        <v>FG-401867</v>
       </c>
       <c r="C1095" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (90MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (90MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1095" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38722,7 +38722,7 @@
         <v>General</v>
       </c>
       <c r="G1095" t="str">
-        <v>90MM C TYPE 3.2 KG</v>
+        <v>90MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1095" t="str">
         <v>Nos</v>
@@ -38742,13 +38742,13 @@
         <v>1095</v>
       </c>
       <c r="B1096" t="str">
-        <v>FG-401867</v>
+        <v>FG-401498</v>
       </c>
       <c r="C1096" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (90MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1096" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR</v>
+        <v>SPRINKLER SET 6 MTR ISI</v>
       </c>
       <c r="E1096" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38757,7 +38757,7 @@
         <v>General</v>
       </c>
       <c r="G1096" t="str">
-        <v>90MM L TYPE 3.2 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1096" t="str">
         <v>Nos</v>
@@ -38769,7 +38769,7 @@
         <v>Active</v>
       </c>
       <c r="K1096" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER SET 6 MTR ISI for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1097">
@@ -38777,10 +38777,10 @@
         <v>1096</v>
       </c>
       <c r="B1097" t="str">
-        <v>FG-401498</v>
+        <v>FG-401499</v>
       </c>
       <c r="C1097" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1097" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38792,7 +38792,7 @@
         <v>General</v>
       </c>
       <c r="G1097" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1097" t="str">
         <v>Nos</v>
@@ -38812,10 +38812,10 @@
         <v>1097</v>
       </c>
       <c r="B1098" t="str">
-        <v>FG-401499</v>
+        <v>FG-401500</v>
       </c>
       <c r="C1098" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 2.5 KG)</v>
       </c>
       <c r="D1098" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38827,7 +38827,7 @@
         <v>General</v>
       </c>
       <c r="G1098" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>75MM C TYPE 2.5 KG</v>
       </c>
       <c r="H1098" t="str">
         <v>Nos</v>
@@ -38847,10 +38847,10 @@
         <v>1098</v>
       </c>
       <c r="B1099" t="str">
-        <v>FG-401500</v>
+        <v>FG-401524</v>
       </c>
       <c r="C1099" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 2.5 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 2.5 KG)</v>
       </c>
       <c r="D1099" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38862,7 +38862,7 @@
         <v>General</v>
       </c>
       <c r="G1099" t="str">
-        <v>75MM C TYPE 2.5 KG</v>
+        <v>75MM L TYPE 2.5 KG</v>
       </c>
       <c r="H1099" t="str">
         <v>Nos</v>
@@ -38882,10 +38882,10 @@
         <v>1099</v>
       </c>
       <c r="B1100" t="str">
-        <v>FG-401524</v>
+        <v>FG-401501</v>
       </c>
       <c r="C1100" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 2.5 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1100" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38897,7 +38897,7 @@
         <v>General</v>
       </c>
       <c r="G1100" t="str">
-        <v>75MM L TYPE 2.5 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1100" t="str">
         <v>Nos</v>
@@ -38917,13 +38917,13 @@
         <v>1100</v>
       </c>
       <c r="B1101" t="str">
-        <v>FG-401501</v>
+        <v>FG-401495</v>
       </c>
       <c r="C1101" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1101" t="str">
-        <v>SPRINKLER SET 6 MTR ISI</v>
+        <v>SPRINKLER SET 6 MTR N-ISI</v>
       </c>
       <c r="E1101" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38932,7 +38932,7 @@
         <v>General</v>
       </c>
       <c r="G1101" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1101" t="str">
         <v>Nos</v>
@@ -38944,7 +38944,7 @@
         <v>Active</v>
       </c>
       <c r="K1101" t="str">
-        <v>SPRINKLER SET 6 MTR ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER SET 6 MTR N-ISI for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1102">
@@ -38952,10 +38952,10 @@
         <v>1101</v>
       </c>
       <c r="B1102" t="str">
-        <v>FG-401495</v>
+        <v>FG-401496</v>
       </c>
       <c r="C1102" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1102" t="str">
         <v>SPRINKLER SET 6 MTR N-ISI</v>
@@ -38967,7 +38967,7 @@
         <v>General</v>
       </c>
       <c r="G1102" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1102" t="str">
         <v>Nos</v>
@@ -38987,10 +38987,10 @@
         <v>1102</v>
       </c>
       <c r="B1103" t="str">
-        <v>FG-401496</v>
+        <v>FG-401497</v>
       </c>
       <c r="C1103" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1103" t="str">
         <v>SPRINKLER SET 6 MTR N-ISI</v>
@@ -39002,7 +39002,7 @@
         <v>General</v>
       </c>
       <c r="G1103" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1103" t="str">
         <v>Nos</v>
@@ -39022,13 +39022,13 @@
         <v>1103</v>
       </c>
       <c r="B1104" t="str">
-        <v>FG-401497</v>
+        <v>FG-401503</v>
       </c>
       <c r="C1104" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER FITTINGS TEE (75MM, C TYPE)</v>
       </c>
       <c r="D1104" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI</v>
+        <v>SPRINKLER FITTINGS TEE</v>
       </c>
       <c r="E1104" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39037,7 +39037,7 @@
         <v>General</v>
       </c>
       <c r="G1104" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM, C TYPE</v>
       </c>
       <c r="H1104" t="str">
         <v>Nos</v>
@@ -39049,7 +39049,7 @@
         <v>Active</v>
       </c>
       <c r="K1104" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS TEE for sprinkler irrigation systems. Available sizes: 75MM, C TYPE, 75MM, L TYPE, 63MM, C TYPE.</v>
       </c>
     </row>
     <row r="1105">
@@ -39057,10 +39057,10 @@
         <v>1104</v>
       </c>
       <c r="B1105" t="str">
-        <v>FG-401503</v>
+        <v>FG-401511</v>
       </c>
       <c r="C1105" t="str">
-        <v>SPRINKLER FITTINGS TEE (75MM, C TYPE)</v>
+        <v>SPRINKLER FITTINGS TEE (75MM, L TYPE)</v>
       </c>
       <c r="D1105" t="str">
         <v>SPRINKLER FITTINGS TEE</v>
@@ -39072,7 +39072,7 @@
         <v>General</v>
       </c>
       <c r="G1105" t="str">
-        <v>75MM, C TYPE</v>
+        <v>75MM, L TYPE</v>
       </c>
       <c r="H1105" t="str">
         <v>Nos</v>
@@ -39092,10 +39092,10 @@
         <v>1105</v>
       </c>
       <c r="B1106" t="str">
-        <v>FG-401511</v>
+        <v>FG-401526</v>
       </c>
       <c r="C1106" t="str">
-        <v>SPRINKLER FITTINGS TEE (75MM, L TYPE)</v>
+        <v>SPRINKLER FITTINGS TEE (63MM, C TYPE)</v>
       </c>
       <c r="D1106" t="str">
         <v>SPRINKLER FITTINGS TEE</v>
@@ -39107,7 +39107,7 @@
         <v>General</v>
       </c>
       <c r="G1106" t="str">
-        <v>75MM, L TYPE</v>
+        <v>63MM, C TYPE</v>
       </c>
       <c r="H1106" t="str">
         <v>Nos</v>
@@ -39127,13 +39127,13 @@
         <v>1106</v>
       </c>
       <c r="B1107" t="str">
-        <v>FG-401526</v>
+        <v>FG-401504</v>
       </c>
       <c r="C1107" t="str">
-        <v>SPRINKLER FITTINGS TEE (63MM, C TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (75MM C TYPE)</v>
       </c>
       <c r="D1107" t="str">
-        <v>SPRINKLER FITTINGS TEE</v>
+        <v>SPRINKLER FITTINGS ADAPTOR</v>
       </c>
       <c r="E1107" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39142,7 +39142,7 @@
         <v>General</v>
       </c>
       <c r="G1107" t="str">
-        <v>63MM, C TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1107" t="str">
         <v>Nos</v>
@@ -39154,7 +39154,7 @@
         <v>Active</v>
       </c>
       <c r="K1107" t="str">
-        <v>SPRINKLER FITTINGS TEE for sprinkler irrigation systems. Available sizes: 75MM, C TYPE, 75MM, L TYPE, 63MM, C TYPE.</v>
+        <v>SPRINKLER FITTINGS ADAPTOR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1108">
@@ -39162,10 +39162,10 @@
         <v>1107</v>
       </c>
       <c r="B1108" t="str">
-        <v>FG-401504</v>
+        <v>FG-401512</v>
       </c>
       <c r="C1108" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (75MM P TYPE)</v>
       </c>
       <c r="D1108" t="str">
         <v>SPRINKLER FITTINGS ADAPTOR</v>
@@ -39177,7 +39177,7 @@
         <v>General</v>
       </c>
       <c r="G1108" t="str">
-        <v>75MM C TYPE</v>
+        <v>75MM P TYPE</v>
       </c>
       <c r="H1108" t="str">
         <v>Nos</v>
@@ -39197,10 +39197,10 @@
         <v>1108</v>
       </c>
       <c r="B1109" t="str">
-        <v>FG-401512</v>
+        <v>FG-401527</v>
       </c>
       <c r="C1109" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (75MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (63MM C TYPE)</v>
       </c>
       <c r="D1109" t="str">
         <v>SPRINKLER FITTINGS ADAPTOR</v>
@@ -39212,7 +39212,7 @@
         <v>General</v>
       </c>
       <c r="G1109" t="str">
-        <v>75MM P TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1109" t="str">
         <v>Nos</v>
@@ -39232,13 +39232,13 @@
         <v>1109</v>
       </c>
       <c r="B1110" t="str">
-        <v>FG-401527</v>
+        <v>FG-401502</v>
       </c>
       <c r="C1110" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (75MM C TYPE)</v>
       </c>
       <c r="D1110" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR</v>
+        <v>SPRINKLER FITTINGS BEND</v>
       </c>
       <c r="E1110" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39247,7 +39247,7 @@
         <v>General</v>
       </c>
       <c r="G1110" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1110" t="str">
         <v>Nos</v>
@@ -39259,7 +39259,7 @@
         <v>Active</v>
       </c>
       <c r="K1110" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS BEND for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1111">
@@ -39267,10 +39267,10 @@
         <v>1110</v>
       </c>
       <c r="B1111" t="str">
-        <v>FG-401502</v>
+        <v>FG-401510</v>
       </c>
       <c r="C1111" t="str">
-        <v>SPRINKLER FITTINGS BEND (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (75MM L TYPE)</v>
       </c>
       <c r="D1111" t="str">
         <v>SPRINKLER FITTINGS BEND</v>
@@ -39282,7 +39282,7 @@
         <v>General</v>
       </c>
       <c r="G1111" t="str">
-        <v>75MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1111" t="str">
         <v>Nos</v>
@@ -39302,10 +39302,10 @@
         <v>1111</v>
       </c>
       <c r="B1112" t="str">
-        <v>FG-401510</v>
+        <v>FG-401525</v>
       </c>
       <c r="C1112" t="str">
-        <v>SPRINKLER FITTINGS BEND (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (63MM C TYPE)</v>
       </c>
       <c r="D1112" t="str">
         <v>SPRINKLER FITTINGS BEND</v>
@@ -39317,7 +39317,7 @@
         <v>General</v>
       </c>
       <c r="G1112" t="str">
-        <v>75MM L TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1112" t="str">
         <v>Nos</v>
@@ -39337,13 +39337,13 @@
         <v>1112</v>
       </c>
       <c r="B1113" t="str">
-        <v>FG-401525</v>
+        <v>FG-401514</v>
       </c>
       <c r="C1113" t="str">
-        <v>SPRINKLER FITTINGS BEND (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (75MM L TYPE)</v>
       </c>
       <c r="D1113" t="str">
-        <v>SPRINKLER FITTINGS BEND</v>
+        <v>SPRINKLER FITTINGS END CAP</v>
       </c>
       <c r="E1113" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39352,7 +39352,7 @@
         <v>General</v>
       </c>
       <c r="G1113" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1113" t="str">
         <v>Nos</v>
@@ -39364,7 +39364,7 @@
         <v>Active</v>
       </c>
       <c r="K1113" t="str">
-        <v>SPRINKLER FITTINGS BEND for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS END CAP for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1114">
@@ -39372,10 +39372,10 @@
         <v>1113</v>
       </c>
       <c r="B1114" t="str">
-        <v>FG-401514</v>
+        <v>FG-401506</v>
       </c>
       <c r="C1114" t="str">
-        <v>SPRINKLER FITTINGS END CAP (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (75MM C TYPE)</v>
       </c>
       <c r="D1114" t="str">
         <v>SPRINKLER FITTINGS END CAP</v>
@@ -39387,7 +39387,7 @@
         <v>General</v>
       </c>
       <c r="G1114" t="str">
-        <v>75MM L TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1114" t="str">
         <v>Nos</v>
@@ -39407,10 +39407,10 @@
         <v>1114</v>
       </c>
       <c r="B1115" t="str">
-        <v>FG-401506</v>
+        <v>FG-401529</v>
       </c>
       <c r="C1115" t="str">
-        <v>SPRINKLER FITTINGS END CAP (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (63MM C TYPE)</v>
       </c>
       <c r="D1115" t="str">
         <v>SPRINKLER FITTINGS END CAP</v>
@@ -39422,7 +39422,7 @@
         <v>General</v>
       </c>
       <c r="G1115" t="str">
-        <v>75MM C TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1115" t="str">
         <v>Nos</v>
@@ -39442,13 +39442,13 @@
         <v>1115</v>
       </c>
       <c r="B1116" t="str">
-        <v>FG-401529</v>
+        <v>FG-401517</v>
       </c>
       <c r="C1116" t="str">
-        <v>SPRINKLER FITTINGS END CAP (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (75MM P TYPE)</v>
       </c>
       <c r="D1116" t="str">
-        <v>SPRINKLER FITTINGS END CAP</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
       </c>
       <c r="E1116" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39457,7 +39457,7 @@
         <v>General</v>
       </c>
       <c r="G1116" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM P TYPE</v>
       </c>
       <c r="H1116" t="str">
         <v>Nos</v>
@@ -39469,7 +39469,7 @@
         <v>Active</v>
       </c>
       <c r="K1116" t="str">
-        <v>SPRINKLER FITTINGS END CAP for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1117">
@@ -39477,10 +39477,10 @@
         <v>1116</v>
       </c>
       <c r="B1117" t="str">
-        <v>FG-401517</v>
+        <v>FG-401518</v>
       </c>
       <c r="C1117" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (75MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (63MM P TYPE)</v>
       </c>
       <c r="D1117" t="str">
         <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
@@ -39492,7 +39492,7 @@
         <v>General</v>
       </c>
       <c r="G1117" t="str">
-        <v>75MM P TYPE</v>
+        <v>63MM P TYPE</v>
       </c>
       <c r="H1117" t="str">
         <v>Nos</v>
@@ -39512,13 +39512,13 @@
         <v>1117</v>
       </c>
       <c r="B1118" t="str">
-        <v>FG-401518</v>
+        <v>FG-401505</v>
       </c>
       <c r="C1118" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (63MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (75MM C TYPE)</v>
       </c>
       <c r="D1118" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
+        <v>SPRINKLER FITTINGS PCN</v>
       </c>
       <c r="E1118" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39527,7 +39527,7 @@
         <v>General</v>
       </c>
       <c r="G1118" t="str">
-        <v>63MM P TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1118" t="str">
         <v>Nos</v>
@@ -39539,7 +39539,7 @@
         <v>Active</v>
       </c>
       <c r="K1118" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS PCN for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1119">
@@ -39547,10 +39547,10 @@
         <v>1118</v>
       </c>
       <c r="B1119" t="str">
-        <v>FG-401505</v>
+        <v>FG-401513</v>
       </c>
       <c r="C1119" t="str">
-        <v>SPRINKLER FITTINGS PCN (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (75MM L TYPE)</v>
       </c>
       <c r="D1119" t="str">
         <v>SPRINKLER FITTINGS PCN</v>
@@ -39562,7 +39562,7 @@
         <v>General</v>
       </c>
       <c r="G1119" t="str">
-        <v>75MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1119" t="str">
         <v>Nos</v>
@@ -39582,10 +39582,10 @@
         <v>1119</v>
       </c>
       <c r="B1120" t="str">
-        <v>FG-401513</v>
+        <v>FG-401528</v>
       </c>
       <c r="C1120" t="str">
-        <v>SPRINKLER FITTINGS PCN (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (63MM C TYPE)</v>
       </c>
       <c r="D1120" t="str">
         <v>SPRINKLER FITTINGS PCN</v>
@@ -39597,7 +39597,7 @@
         <v>General</v>
       </c>
       <c r="G1120" t="str">
-        <v>75MM L TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1120" t="str">
         <v>Nos</v>
@@ -39617,13 +39617,13 @@
         <v>1120</v>
       </c>
       <c r="B1121" t="str">
-        <v>FG-401528</v>
+        <v>FG-401507</v>
       </c>
       <c r="C1121" t="str">
-        <v>SPRINKLER FITTINGS PCN (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL (20MM)</v>
       </c>
       <c r="D1121" t="str">
-        <v>SPRINKLER FITTINGS PCN</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL</v>
       </c>
       <c r="E1121" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39632,7 +39632,7 @@
         <v>General</v>
       </c>
       <c r="G1121" t="str">
-        <v>63MM C TYPE</v>
+        <v>20MM</v>
       </c>
       <c r="H1121" t="str">
         <v>Nos</v>
@@ -39644,7 +39644,7 @@
         <v>Active</v>
       </c>
       <c r="K1121" t="str">
-        <v>SPRINKLER FITTINGS PCN for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1122">
@@ -39652,13 +39652,13 @@
         <v>1121</v>
       </c>
       <c r="B1122" t="str">
-        <v>FG-401507</v>
+        <v>FG-401508</v>
       </c>
       <c r="C1122" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL (20MM)</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE (75MM C TYPE)</v>
       </c>
       <c r="D1122" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE</v>
       </c>
       <c r="E1122" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39667,7 +39667,7 @@
         <v>General</v>
       </c>
       <c r="G1122" t="str">
-        <v>20MM</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1122" t="str">
         <v>Nos</v>
@@ -39679,7 +39679,7 @@
         <v>Active</v>
       </c>
       <c r="K1122" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1123">
@@ -39687,10 +39687,10 @@
         <v>1122</v>
       </c>
       <c r="B1123" t="str">
-        <v>FG-401508</v>
+        <v>FG-401515</v>
       </c>
       <c r="C1123" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE (20MM L TYPE)</v>
       </c>
       <c r="D1123" t="str">
         <v>SPRINKLER FITTINGS GI RISER PIPE</v>
@@ -39702,7 +39702,7 @@
         <v>General</v>
       </c>
       <c r="G1123" t="str">
-        <v>75MM C TYPE</v>
+        <v>20MM L TYPE</v>
       </c>
       <c r="H1123" t="str">
         <v>Nos</v>
@@ -39722,25 +39722,25 @@
         <v>1123</v>
       </c>
       <c r="B1124" t="str">
-        <v>FG-401515</v>
+        <v>FG-401742</v>
       </c>
       <c r="C1124" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE (20MM L TYPE)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 1)</v>
       </c>
       <c r="D1124" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE</v>
+        <v>ROUND DRIPLINE 12MM ISI</v>
       </c>
       <c r="E1124" t="str">
-        <v>Sprinkler Pipes &amp; Fittings</v>
+        <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1124" t="str">
-        <v>General</v>
+        <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1124" t="str">
-        <v>20MM L TYPE</v>
+        <v>12-4-30 CLASS 1</v>
       </c>
       <c r="H1124" t="str">
-        <v>Nos</v>
+        <v>ROLL</v>
       </c>
       <c r="I1124" t="str">
         <v>-</v>
@@ -39749,7 +39749,7 @@
         <v>Active</v>
       </c>
       <c r="K1124" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE for sprinkler irrigation systems.</v>
+        <v>ROUND DRIPLINE 12MM ISI certified.</v>
       </c>
     </row>
     <row r="1125">
@@ -39757,10 +39757,10 @@
         <v>1124</v>
       </c>
       <c r="B1125" t="str">
-        <v>FG-401742</v>
+        <v>FG-401743</v>
       </c>
       <c r="C1125" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 1)</v>
       </c>
       <c r="D1125" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39772,7 +39772,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1125" t="str">
-        <v>12-4-30 CLASS 1</v>
+        <v>12-4-40 CLASS 1</v>
       </c>
       <c r="H1125" t="str">
         <v>ROLL</v>
@@ -39792,10 +39792,10 @@
         <v>1125</v>
       </c>
       <c r="B1126" t="str">
-        <v>FG-401743</v>
+        <v>FG-401744</v>
       </c>
       <c r="C1126" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 1)</v>
       </c>
       <c r="D1126" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39807,7 +39807,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1126" t="str">
-        <v>12-4-40 CLASS 1</v>
+        <v>12-4-50 CLASS 1</v>
       </c>
       <c r="H1126" t="str">
         <v>ROLL</v>
@@ -39827,10 +39827,10 @@
         <v>1126</v>
       </c>
       <c r="B1127" t="str">
-        <v>FG-401744</v>
+        <v>FG-401751</v>
       </c>
       <c r="C1127" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1127" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39842,7 +39842,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1127" t="str">
-        <v>12-4-50 CLASS 1</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1127" t="str">
         <v>ROLL</v>
@@ -39862,10 +39862,10 @@
         <v>1127</v>
       </c>
       <c r="B1128" t="str">
-        <v>FG-401751</v>
+        <v>FG-401752</v>
       </c>
       <c r="C1128" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1128" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39877,7 +39877,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1128" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1128" t="str">
         <v>ROLL</v>
@@ -39897,10 +39897,10 @@
         <v>1128</v>
       </c>
       <c r="B1129" t="str">
-        <v>FG-401752</v>
+        <v>FG-401753</v>
       </c>
       <c r="C1129" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1129" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39912,7 +39912,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1129" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1129" t="str">
         <v>ROLL</v>
@@ -39932,10 +39932,10 @@
         <v>1129</v>
       </c>
       <c r="B1130" t="str">
-        <v>FG-401753</v>
+        <v>FG-401754</v>
       </c>
       <c r="C1130" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1130" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39947,7 +39947,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1130" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1130" t="str">
         <v>ROLL</v>
@@ -39967,10 +39967,10 @@
         <v>1130</v>
       </c>
       <c r="B1131" t="str">
-        <v>FG-401754</v>
+        <v>FG-401755</v>
       </c>
       <c r="C1131" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1131" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39982,7 +39982,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1131" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1131" t="str">
         <v>ROLL</v>
@@ -40002,10 +40002,10 @@
         <v>1131</v>
       </c>
       <c r="B1132" t="str">
-        <v>FG-401755</v>
+        <v>FG-401756</v>
       </c>
       <c r="C1132" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1132" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -40017,7 +40017,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1132" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1132" t="str">
         <v>ROLL</v>
@@ -40037,13 +40037,13 @@
         <v>1132</v>
       </c>
       <c r="B1133" t="str">
-        <v>FG-401756</v>
+        <v>FG-401745</v>
       </c>
       <c r="C1133" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1133" t="str">
-        <v>ROUND DRIPLINE 12MM ISI</v>
+        <v>ROUND DRIPLINE 16MM ISI</v>
       </c>
       <c r="E1133" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40052,7 +40052,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1133" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1133" t="str">
         <v>ROLL</v>
@@ -40064,7 +40064,7 @@
         <v>Active</v>
       </c>
       <c r="K1133" t="str">
-        <v>ROUND DRIPLINE 12MM ISI certified.</v>
+        <v>ROUND DRIPLINE 16MM ISI certified.</v>
       </c>
     </row>
     <row r="1134">
@@ -40072,10 +40072,10 @@
         <v>1133</v>
       </c>
       <c r="B1134" t="str">
-        <v>FG-401745</v>
+        <v>FG-401746</v>
       </c>
       <c r="C1134" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1134" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40087,7 +40087,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1134" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1134" t="str">
         <v>ROLL</v>
@@ -40107,10 +40107,10 @@
         <v>1134</v>
       </c>
       <c r="B1135" t="str">
-        <v>FG-401746</v>
+        <v>FG-401747</v>
       </c>
       <c r="C1135" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1135" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40122,7 +40122,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1135" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1135" t="str">
         <v>ROLL</v>
@@ -40142,10 +40142,10 @@
         <v>1135</v>
       </c>
       <c r="B1136" t="str">
-        <v>FG-401747</v>
+        <v>FG-401757</v>
       </c>
       <c r="C1136" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1136" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40157,7 +40157,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1136" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1136" t="str">
         <v>ROLL</v>
@@ -40177,10 +40177,10 @@
         <v>1136</v>
       </c>
       <c r="B1137" t="str">
-        <v>FG-401757</v>
+        <v>FG-401758</v>
       </c>
       <c r="C1137" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1137" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40192,7 +40192,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1137" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1137" t="str">
         <v>ROLL</v>
@@ -40212,10 +40212,10 @@
         <v>1137</v>
       </c>
       <c r="B1138" t="str">
-        <v>FG-401758</v>
+        <v>FG-401759</v>
       </c>
       <c r="C1138" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1138" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40227,7 +40227,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1138" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1138" t="str">
         <v>ROLL</v>
@@ -40247,13 +40247,13 @@
         <v>1138</v>
       </c>
       <c r="B1139" t="str">
-        <v>FG-401759</v>
+        <v>-</v>
       </c>
       <c r="C1139" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-30 CLASS-1)</v>
       </c>
       <c r="D1139" t="str">
-        <v>ROUND DRIPLINE 16MM ISI</v>
+        <v>20MM ROUND INLINE PIPE ISI</v>
       </c>
       <c r="E1139" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40262,10 +40262,10 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1139" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>20-4-30 CLASS-1</v>
       </c>
       <c r="H1139" t="str">
-        <v>ROLL</v>
+        <v>MTR</v>
       </c>
       <c r="I1139" t="str">
         <v>-</v>
@@ -40274,7 +40274,7 @@
         <v>Active</v>
       </c>
       <c r="K1139" t="str">
-        <v>ROUND DRIPLINE 16MM ISI certified.</v>
+        <v>20mm Round Inline Drip Pipe ISI certified.</v>
       </c>
     </row>
     <row r="1140">
@@ -40285,7 +40285,7 @@
         <v>-</v>
       </c>
       <c r="C1140" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-30 CLASS-1)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-40 CLASS-1)</v>
       </c>
       <c r="D1140" t="str">
         <v>20MM ROUND INLINE PIPE ISI</v>
@@ -40297,7 +40297,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1140" t="str">
-        <v>20-4-30 CLASS-1</v>
+        <v>20-4-40 CLASS-1</v>
       </c>
       <c r="H1140" t="str">
         <v>MTR</v>
@@ -40320,7 +40320,7 @@
         <v>-</v>
       </c>
       <c r="C1141" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-40 CLASS-1)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-50 CLASS-1)</v>
       </c>
       <c r="D1141" t="str">
         <v>20MM ROUND INLINE PIPE ISI</v>
@@ -40332,7 +40332,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1141" t="str">
-        <v>20-4-40 CLASS-1</v>
+        <v>20-4-50 CLASS-1</v>
       </c>
       <c r="H1141" t="str">
         <v>MTR</v>
@@ -40352,25 +40352,25 @@
         <v>1141</v>
       </c>
       <c r="B1142" t="str">
-        <v>-</v>
+        <v>FG-401763</v>
       </c>
       <c r="C1142" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-50 CLASS-1)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1142" t="str">
-        <v>20MM ROUND INLINE PIPE ISI</v>
+        <v>FLAT DRIPLINE 12MM ISI</v>
       </c>
       <c r="E1142" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1142" t="str">
-        <v>ROUND DRIP ISI</v>
+        <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1142" t="str">
-        <v>20-4-50 CLASS-1</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1142" t="str">
-        <v>MTR</v>
+        <v>ROLL</v>
       </c>
       <c r="I1142" t="str">
         <v>-</v>
@@ -40379,7 +40379,7 @@
         <v>Active</v>
       </c>
       <c r="K1142" t="str">
-        <v>20mm Round Inline Drip Pipe ISI certified.</v>
+        <v>FLAT DRIPLINE 12MM ISI certified.</v>
       </c>
     </row>
     <row r="1143">
@@ -40387,10 +40387,10 @@
         <v>1142</v>
       </c>
       <c r="B1143" t="str">
-        <v>FG-401763</v>
+        <v>FG-401764</v>
       </c>
       <c r="C1143" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1143" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40402,7 +40402,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1143" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1143" t="str">
         <v>ROLL</v>
@@ -40422,10 +40422,10 @@
         <v>1143</v>
       </c>
       <c r="B1144" t="str">
-        <v>FG-401764</v>
+        <v>FG-401765</v>
       </c>
       <c r="C1144" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1144" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40437,7 +40437,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1144" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1144" t="str">
         <v>ROLL</v>
@@ -40457,10 +40457,10 @@
         <v>1144</v>
       </c>
       <c r="B1145" t="str">
-        <v>FG-401765</v>
+        <v>FG-401766</v>
       </c>
       <c r="C1145" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1145" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40472,7 +40472,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1145" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1145" t="str">
         <v>ROLL</v>
@@ -40492,10 +40492,10 @@
         <v>1145</v>
       </c>
       <c r="B1146" t="str">
-        <v>FG-401766</v>
+        <v>FG-401767</v>
       </c>
       <c r="C1146" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1146" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40507,7 +40507,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1146" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1146" t="str">
         <v>ROLL</v>
@@ -40527,10 +40527,10 @@
         <v>1146</v>
       </c>
       <c r="B1147" t="str">
-        <v>FG-401767</v>
+        <v>FG-401768</v>
       </c>
       <c r="C1147" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1147" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40542,7 +40542,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1147" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1147" t="str">
         <v>ROLL</v>
@@ -40562,13 +40562,13 @@
         <v>1147</v>
       </c>
       <c r="B1148" t="str">
-        <v>FG-401768</v>
+        <v>FG-401760</v>
       </c>
       <c r="C1148" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1148" t="str">
-        <v>FLAT DRIPLINE 12MM ISI</v>
+        <v>FLAT DRIPLINE 16MM ISI</v>
       </c>
       <c r="E1148" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40577,7 +40577,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1148" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1148" t="str">
         <v>ROLL</v>
@@ -40589,7 +40589,7 @@
         <v>Active</v>
       </c>
       <c r="K1148" t="str">
-        <v>FLAT DRIPLINE 12MM ISI certified.</v>
+        <v>FLAT DRIPLINE 16MM ISI certified.</v>
       </c>
     </row>
     <row r="1149">
@@ -40597,10 +40597,10 @@
         <v>1148</v>
       </c>
       <c r="B1149" t="str">
-        <v>FG-401760</v>
+        <v>FG-401761</v>
       </c>
       <c r="C1149" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1149" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40612,7 +40612,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1149" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1149" t="str">
         <v>ROLL</v>
@@ -40632,10 +40632,10 @@
         <v>1149</v>
       </c>
       <c r="B1150" t="str">
-        <v>FG-401761</v>
+        <v>FG-401762</v>
       </c>
       <c r="C1150" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1150" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40647,7 +40647,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1150" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1150" t="str">
         <v>ROLL</v>
@@ -40667,10 +40667,10 @@
         <v>1150</v>
       </c>
       <c r="B1151" t="str">
-        <v>FG-401762</v>
+        <v>FG-401769</v>
       </c>
       <c r="C1151" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1151" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40682,7 +40682,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1151" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1151" t="str">
         <v>ROLL</v>
@@ -40702,10 +40702,10 @@
         <v>1151</v>
       </c>
       <c r="B1152" t="str">
-        <v>FG-401769</v>
+        <v>FG-401770</v>
       </c>
       <c r="C1152" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1152" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40717,7 +40717,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1152" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1152" t="str">
         <v>ROLL</v>
@@ -40737,10 +40737,10 @@
         <v>1152</v>
       </c>
       <c r="B1153" t="str">
-        <v>FG-401770</v>
+        <v>FG-401779</v>
       </c>
       <c r="C1153" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1153" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40752,7 +40752,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1153" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1153" t="str">
         <v>ROLL</v>
@@ -40772,13 +40772,13 @@
         <v>1153</v>
       </c>
       <c r="B1154" t="str">
-        <v>FG-401779</v>
+        <v>FG-401771</v>
       </c>
       <c r="C1154" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-30 CLASS 1)</v>
       </c>
       <c r="D1154" t="str">
-        <v>FLAT DRIPLINE 16MM ISI</v>
+        <v>FLAT DRIPLINE 20MM ISI</v>
       </c>
       <c r="E1154" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40787,7 +40787,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1154" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>20-4-30 CLASS 1</v>
       </c>
       <c r="H1154" t="str">
         <v>ROLL</v>
@@ -40799,7 +40799,7 @@
         <v>Active</v>
       </c>
       <c r="K1154" t="str">
-        <v>FLAT DRIPLINE 16MM ISI certified.</v>
+        <v>FLAT DRIPLINE 20MM ISI certified.</v>
       </c>
     </row>
     <row r="1155">
@@ -40807,10 +40807,10 @@
         <v>1154</v>
       </c>
       <c r="B1155" t="str">
-        <v>FG-401771</v>
+        <v>FG-401772</v>
       </c>
       <c r="C1155" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-40 CLASS 1)</v>
       </c>
       <c r="D1155" t="str">
         <v>FLAT DRIPLINE 20MM ISI</v>
@@ -40822,7 +40822,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1155" t="str">
-        <v>20-4-30 CLASS 1</v>
+        <v>20-4-40 CLASS 1</v>
       </c>
       <c r="H1155" t="str">
         <v>ROLL</v>
@@ -40842,10 +40842,10 @@
         <v>1155</v>
       </c>
       <c r="B1156" t="str">
-        <v>FG-401772</v>
+        <v>FG-401773</v>
       </c>
       <c r="C1156" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-50 CLASS 1)</v>
       </c>
       <c r="D1156" t="str">
         <v>FLAT DRIPLINE 20MM ISI</v>
@@ -40857,7 +40857,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1156" t="str">
-        <v>20-4-40 CLASS 1</v>
+        <v>20-4-50 CLASS 1</v>
       </c>
       <c r="H1156" t="str">
         <v>ROLL</v>
@@ -40877,25 +40877,25 @@
         <v>1156</v>
       </c>
       <c r="B1157" t="str">
-        <v>FG-401773</v>
+        <v>-</v>
       </c>
       <c r="C1157" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-50 CLASS 1)</v>
+        <v>12MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1157" t="str">
-        <v>FLAT DRIPLINE 20MM ISI</v>
+        <v>12MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1157" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1157" t="str">
-        <v>FLAT DRIP ISI</v>
+        <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1157" t="str">
-        <v>20-4-50 CLASS 1</v>
+        <v>CLASS-2</v>
       </c>
       <c r="H1157" t="str">
-        <v>ROLL</v>
+        <v>MTR</v>
       </c>
       <c r="I1157" t="str">
         <v>-</v>
@@ -40904,7 +40904,7 @@
         <v>Active</v>
       </c>
       <c r="K1157" t="str">
-        <v>FLAT DRIPLINE 20MM ISI certified.</v>
+        <v>12mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1158">
@@ -40915,10 +40915,10 @@
         <v>-</v>
       </c>
       <c r="C1158" t="str">
-        <v>12MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>16MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1158" t="str">
-        <v>12MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>16MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1158" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40939,7 +40939,7 @@
         <v>Active</v>
       </c>
       <c r="K1158" t="str">
-        <v>12mm Plain Lateral Online Drip Pipe.</v>
+        <v>16mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1159">
@@ -40950,10 +40950,10 @@
         <v>-</v>
       </c>
       <c r="C1159" t="str">
-        <v>16MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>20MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1159" t="str">
-        <v>16MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>20MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1159" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40974,7 +40974,7 @@
         <v>Active</v>
       </c>
       <c r="K1159" t="str">
-        <v>16mm Plain Lateral Online Drip Pipe.</v>
+        <v>20mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1160">
@@ -40985,10 +40985,10 @@
         <v>-</v>
       </c>
       <c r="C1160" t="str">
-        <v>20MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-1)</v>
       </c>
       <c r="D1160" t="str">
-        <v>20MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1160" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40997,7 +40997,7 @@
         <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1160" t="str">
-        <v>CLASS-2</v>
+        <v>CLASS-1</v>
       </c>
       <c r="H1160" t="str">
         <v>MTR</v>
@@ -41009,7 +41009,7 @@
         <v>Active</v>
       </c>
       <c r="K1160" t="str">
-        <v>20mm Plain Lateral Online Drip Pipe.</v>
+        <v>32mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1161">
@@ -41020,7 +41020,7 @@
         <v>-</v>
       </c>
       <c r="C1161" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-1)</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1161" t="str">
         <v>32MM PLAIN LATERAL ONLINE PIPE</v>
@@ -41032,7 +41032,7 @@
         <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1161" t="str">
-        <v>CLASS-1</v>
+        <v>CLASS-2</v>
       </c>
       <c r="H1161" t="str">
         <v>MTR</v>
@@ -41052,22 +41052,22 @@
         <v>1161</v>
       </c>
       <c r="B1162" t="str">
-        <v>-</v>
+        <v>FG-401763</v>
       </c>
       <c r="C1162" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1162" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12</v>
       </c>
       <c r="E1162" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1162" t="str">
-        <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
+        <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1162" t="str">
-        <v>CLASS-2</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1162" t="str">
         <v>MTR</v>
@@ -41079,7 +41079,7 @@
         <v>Active</v>
       </c>
       <c r="K1162" t="str">
-        <v>32mm Plain Lateral Online Drip Pipe.</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12. Available sizes: 12-4-30 CLASS 2, 12-4-40 CLASS 2, 12-4-50 CLASS 2, 12-4-30 CLASS 3, 12-4-40 CLASS 3, 12-4-50 CLASS 3.</v>
       </c>
     </row>
     <row r="1163">
@@ -41087,10 +41087,10 @@
         <v>1162</v>
       </c>
       <c r="B1163" t="str">
-        <v>FG-401763</v>
+        <v>FG-401764</v>
       </c>
       <c r="C1163" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1163" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41102,7 +41102,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1163" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1163" t="str">
         <v>MTR</v>
@@ -41122,10 +41122,10 @@
         <v>1163</v>
       </c>
       <c r="B1164" t="str">
-        <v>FG-401764</v>
+        <v>FG-401765</v>
       </c>
       <c r="C1164" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1164" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41137,7 +41137,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1164" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1164" t="str">
         <v>MTR</v>
@@ -41157,10 +41157,10 @@
         <v>1164</v>
       </c>
       <c r="B1165" t="str">
-        <v>FG-401765</v>
+        <v>FG-401766</v>
       </c>
       <c r="C1165" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1165" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41172,7 +41172,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1165" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1165" t="str">
         <v>MTR</v>
@@ -41192,10 +41192,10 @@
         <v>1165</v>
       </c>
       <c r="B1166" t="str">
-        <v>FG-401766</v>
+        <v>FG-401767</v>
       </c>
       <c r="C1166" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1166" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41207,7 +41207,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1166" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1166" t="str">
         <v>MTR</v>
@@ -41227,10 +41227,10 @@
         <v>1166</v>
       </c>
       <c r="B1167" t="str">
-        <v>FG-401767</v>
+        <v>FG-401768</v>
       </c>
       <c r="C1167" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1167" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41242,7 +41242,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1167" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1167" t="str">
         <v>MTR</v>
@@ -41262,13 +41262,13 @@
         <v>1167</v>
       </c>
       <c r="B1168" t="str">
-        <v>FG-401768</v>
+        <v>FG-401760</v>
       </c>
       <c r="C1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16</v>
       </c>
       <c r="E1168" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -41277,7 +41277,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1168" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1168" t="str">
         <v>MTR</v>
@@ -41289,7 +41289,7 @@
         <v>Active</v>
       </c>
       <c r="K1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12. Available sizes: 12-4-30 CLASS 2, 12-4-40 CLASS 2, 12-4-50 CLASS 2, 12-4-30 CLASS 3, 12-4-40 CLASS 3, 12-4-50 CLASS 3.</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16. Available sizes: 16-4-30 CLASS 1, 16-4-40 CLASS 1, 16-4-50 CLASS 1, 16-4-30 CLASS 2, 16-4-40 CLASS 2, 16-4-50 CLASS 2.</v>
       </c>
     </row>
     <row r="1169">
@@ -41297,10 +41297,10 @@
         <v>1168</v>
       </c>
       <c r="B1169" t="str">
-        <v>FG-401760</v>
+        <v>FG-401761</v>
       </c>
       <c r="C1169" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1169" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41312,7 +41312,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1169" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1169" t="str">
         <v>MTR</v>
@@ -41332,10 +41332,10 @@
         <v>1169</v>
       </c>
       <c r="B1170" t="str">
-        <v>FG-401761</v>
+        <v>FG-401762</v>
       </c>
       <c r="C1170" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1170" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41347,7 +41347,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1170" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1170" t="str">
         <v>MTR</v>
@@ -41367,10 +41367,10 @@
         <v>1170</v>
       </c>
       <c r="B1171" t="str">
-        <v>FG-401762</v>
+        <v>FG-401769</v>
       </c>
       <c r="C1171" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1171" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41382,7 +41382,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1171" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1171" t="str">
         <v>MTR</v>
@@ -41402,10 +41402,10 @@
         <v>1171</v>
       </c>
       <c r="B1172" t="str">
-        <v>FG-401769</v>
+        <v>FG-401770</v>
       </c>
       <c r="C1172" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1172" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41417,7 +41417,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1172" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1172" t="str">
         <v>MTR</v>
@@ -41437,10 +41437,10 @@
         <v>1172</v>
       </c>
       <c r="B1173" t="str">
-        <v>FG-401770</v>
+        <v>FG-401779</v>
       </c>
       <c r="C1173" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1173" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41452,7 +41452,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1173" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1173" t="str">
         <v>MTR</v>
@@ -41472,13 +41472,13 @@
         <v>1173</v>
       </c>
       <c r="B1174" t="str">
-        <v>FG-401779</v>
+        <v>FG-401771</v>
       </c>
       <c r="C1174" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-30 CLASS 1)</v>
       </c>
       <c r="D1174" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20</v>
       </c>
       <c r="E1174" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -41487,7 +41487,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1174" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>20-4-30 CLASS 1</v>
       </c>
       <c r="H1174" t="str">
         <v>MTR</v>
@@ -41499,7 +41499,7 @@
         <v>Active</v>
       </c>
       <c r="K1174" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16. Available sizes: 16-4-30 CLASS 1, 16-4-40 CLASS 1, 16-4-50 CLASS 1, 16-4-30 CLASS 2, 16-4-40 CLASS 2, 16-4-50 CLASS 2.</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20. Available sizes: 20-4-30 CLASS 1, 20-4-40 CLASS 1, 20-4-50 CLASS 1.</v>
       </c>
     </row>
     <row r="1175">
@@ -41507,10 +41507,10 @@
         <v>1174</v>
       </c>
       <c r="B1175" t="str">
-        <v>FG-401771</v>
+        <v>FG-401772</v>
       </c>
       <c r="C1175" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-40 CLASS 1)</v>
       </c>
       <c r="D1175" t="str">
         <v>FLAT DRIPLINE ISI 400MTR 20</v>
@@ -41522,7 +41522,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1175" t="str">
-        <v>20-4-30 CLASS 1</v>
+        <v>20-4-40 CLASS 1</v>
       </c>
       <c r="H1175" t="str">
         <v>MTR</v>
@@ -41542,10 +41542,10 @@
         <v>1175</v>
       </c>
       <c r="B1176" t="str">
-        <v>FG-401772</v>
+        <v>FG-401773</v>
       </c>
       <c r="C1176" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-50 CLASS 1)</v>
       </c>
       <c r="D1176" t="str">
         <v>FLAT DRIPLINE ISI 400MTR 20</v>
@@ -41557,7 +41557,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1176" t="str">
-        <v>20-4-40 CLASS 1</v>
+        <v>20-4-50 CLASS 1</v>
       </c>
       <c r="H1176" t="str">
         <v>MTR</v>
@@ -41577,22 +41577,22 @@
         <v>1176</v>
       </c>
       <c r="B1177" t="str">
-        <v>FG-401773</v>
+        <v>FG-401066</v>
       </c>
       <c r="C1177" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-50 CLASS 1)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
       </c>
       <c r="D1177" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
       </c>
       <c r="E1177" t="str">
-        <v>DRIP IRRIGATION SYSTEM</v>
+        <v>UPVC CASING PIPES</v>
       </c>
       <c r="F1177" t="str">
-        <v>FLAT DRIP (PEPSI) - INLINE</v>
+        <v>General</v>
       </c>
       <c r="G1177" t="str">
-        <v>20-4-50 CLASS 1</v>
+        <v>35MM 1 1/4 Inch</v>
       </c>
       <c r="H1177" t="str">
         <v>MTR</v>
@@ -41604,7 +41604,7 @@
         <v>Active</v>
       </c>
       <c r="K1177" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20. Available sizes: 20-4-30 CLASS 1, 20-4-40 CLASS 1, 20-4-50 CLASS 1.</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 40MM 1 1/2 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1178">
@@ -41612,10 +41612,10 @@
         <v>1177</v>
       </c>
       <c r="B1178" t="str">
-        <v>FG-401066</v>
+        <v>FG-401067</v>
       </c>
       <c r="C1178" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (40MM 1 1/2 Inch)</v>
       </c>
       <c r="D1178" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41627,7 +41627,7 @@
         <v>General</v>
       </c>
       <c r="G1178" t="str">
-        <v>35MM 1 1/4 Inch</v>
+        <v>40MM 1 1/2 Inch</v>
       </c>
       <c r="H1178" t="str">
         <v>MTR</v>
@@ -41647,10 +41647,10 @@
         <v>1178</v>
       </c>
       <c r="B1179" t="str">
-        <v>FG-401067</v>
+        <v>FG-401068</v>
       </c>
       <c r="C1179" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (40MM 1 1/2 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (50MM 2 Inch)</v>
       </c>
       <c r="D1179" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41662,7 +41662,7 @@
         <v>General</v>
       </c>
       <c r="G1179" t="str">
-        <v>40MM 1 1/2 Inch</v>
+        <v>50MM 2 Inch</v>
       </c>
       <c r="H1179" t="str">
         <v>MTR</v>
@@ -41682,10 +41682,10 @@
         <v>1179</v>
       </c>
       <c r="B1180" t="str">
-        <v>FG-401068</v>
+        <v>FG-401069</v>
       </c>
       <c r="C1180" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (50MM 2 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (100MM 4 Inch)</v>
       </c>
       <c r="D1180" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41697,7 +41697,7 @@
         <v>General</v>
       </c>
       <c r="G1180" t="str">
-        <v>50MM 2 Inch</v>
+        <v>100MM 4 Inch</v>
       </c>
       <c r="H1180" t="str">
         <v>MTR</v>
@@ -41717,10 +41717,10 @@
         <v>1180</v>
       </c>
       <c r="B1181" t="str">
-        <v>FG-401069</v>
+        <v>FG-401070</v>
       </c>
       <c r="C1181" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (100MM 4 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1181" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41732,7 +41732,7 @@
         <v>General</v>
       </c>
       <c r="G1181" t="str">
-        <v>100MM 4 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1181" t="str">
         <v>MTR</v>
@@ -41752,10 +41752,10 @@
         <v>1181</v>
       </c>
       <c r="B1182" t="str">
-        <v>FG-401070</v>
+        <v>FG-401071</v>
       </c>
       <c r="C1182" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1182" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41767,7 +41767,7 @@
         <v>General</v>
       </c>
       <c r="G1182" t="str">
-        <v>125MM 5 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1182" t="str">
         <v>MTR</v>
@@ -41787,10 +41787,10 @@
         <v>1182</v>
       </c>
       <c r="B1183" t="str">
-        <v>FG-401071</v>
+        <v>FG-401072</v>
       </c>
       <c r="C1183" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1183" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41802,7 +41802,7 @@
         <v>General</v>
       </c>
       <c r="G1183" t="str">
-        <v>150MM 6 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1183" t="str">
         <v>MTR</v>
@@ -41822,10 +41822,10 @@
         <v>1183</v>
       </c>
       <c r="B1184" t="str">
-        <v>FG-401072</v>
+        <v>FG-401073</v>
       </c>
       <c r="C1184" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1184" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41837,7 +41837,7 @@
         <v>General</v>
       </c>
       <c r="G1184" t="str">
-        <v>175MM 7 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1184" t="str">
         <v>MTR</v>
@@ -41857,13 +41857,13 @@
         <v>1184</v>
       </c>
       <c r="B1185" t="str">
-        <v>FG-401073</v>
+        <v>FG-401074</v>
       </c>
       <c r="C1185" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1185" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
       </c>
       <c r="E1185" t="str">
         <v>UPVC CASING PIPES</v>
@@ -41872,7 +41872,7 @@
         <v>General</v>
       </c>
       <c r="G1185" t="str">
-        <v>200MM 8 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1185" t="str">
         <v>MTR</v>
@@ -41884,7 +41884,7 @@
         <v>Active</v>
       </c>
       <c r="K1185" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 40MM 1 1/2 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1186">
@@ -41892,10 +41892,10 @@
         <v>1185</v>
       </c>
       <c r="B1186" t="str">
-        <v>FG-401074</v>
+        <v>FG-401075</v>
       </c>
       <c r="C1186" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1186" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41907,7 +41907,7 @@
         <v>General</v>
       </c>
       <c r="G1186" t="str">
-        <v>125MM 5 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1186" t="str">
         <v>MTR</v>
@@ -41927,10 +41927,10 @@
         <v>1186</v>
       </c>
       <c r="B1187" t="str">
-        <v>FG-401075</v>
+        <v>FG-401076</v>
       </c>
       <c r="C1187" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1187" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41942,7 +41942,7 @@
         <v>General</v>
       </c>
       <c r="G1187" t="str">
-        <v>150MM 6 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1187" t="str">
         <v>MTR</v>
@@ -41962,10 +41962,10 @@
         <v>1187</v>
       </c>
       <c r="B1188" t="str">
-        <v>FG-401076</v>
+        <v>FG-401077</v>
       </c>
       <c r="C1188" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1188" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41977,7 +41977,7 @@
         <v>General</v>
       </c>
       <c r="G1188" t="str">
-        <v>175MM 7 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1188" t="str">
         <v>MTR</v>
@@ -41997,13 +41997,13 @@
         <v>1188</v>
       </c>
       <c r="B1189" t="str">
-        <v>FG-401077</v>
+        <v>FG-401149</v>
       </c>
       <c r="C1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M (140MM 5 Inch)</v>
       </c>
       <c r="D1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M</v>
       </c>
       <c r="E1189" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42012,7 +42012,7 @@
         <v>General</v>
       </c>
       <c r="G1189" t="str">
-        <v>200MM 8 Inch</v>
+        <v>140MM 5 Inch</v>
       </c>
       <c r="H1189" t="str">
         <v>MTR</v>
@@ -42024,7 +42024,7 @@
         <v>Active</v>
       </c>
       <c r="K1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M. Available sizes: 140MM 5 Inch.</v>
       </c>
     </row>
     <row r="1190">
@@ -42032,13 +42032,13 @@
         <v>1189</v>
       </c>
       <c r="B1190" t="str">
-        <v>FG-401149</v>
+        <v>FG-401150</v>
       </c>
       <c r="C1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M (140MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M (140MM 5 Inch)</v>
       </c>
       <c r="D1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M</v>
       </c>
       <c r="E1190" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42059,7 +42059,7 @@
         <v>Active</v>
       </c>
       <c r="K1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M. Available sizes: 140MM 5 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M. Available sizes: 140MM 5 Inch.</v>
       </c>
     </row>
     <row r="1191">
@@ -42067,13 +42067,13 @@
         <v>1190</v>
       </c>
       <c r="B1191" t="str">
-        <v>FG-401150</v>
+        <v>FG-401078</v>
       </c>
       <c r="C1191" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M (140MM 5 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1191" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
       </c>
       <c r="E1191" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42082,7 +42082,7 @@
         <v>General</v>
       </c>
       <c r="G1191" t="str">
-        <v>140MM 5 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1191" t="str">
         <v>MTR</v>
@@ -42094,7 +42094,7 @@
         <v>Active</v>
       </c>
       <c r="K1191" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M. Available sizes: 140MM 5 Inch.</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1192">
@@ -42102,10 +42102,10 @@
         <v>1191</v>
       </c>
       <c r="B1192" t="str">
-        <v>FG-401078</v>
+        <v>FG-401079</v>
       </c>
       <c r="C1192" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1192" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42117,7 +42117,7 @@
         <v>General</v>
       </c>
       <c r="G1192" t="str">
-        <v>125MM 5 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1192" t="str">
         <v>MTR</v>
@@ -42137,10 +42137,10 @@
         <v>1192</v>
       </c>
       <c r="B1193" t="str">
-        <v>FG-401079</v>
+        <v>FG-401080</v>
       </c>
       <c r="C1193" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1193" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42152,7 +42152,7 @@
         <v>General</v>
       </c>
       <c r="G1193" t="str">
-        <v>150MM 6 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1193" t="str">
         <v>MTR</v>
@@ -42172,10 +42172,10 @@
         <v>1193</v>
       </c>
       <c r="B1194" t="str">
-        <v>FG-401080</v>
+        <v>FG-401081</v>
       </c>
       <c r="C1194" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1194" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42187,7 +42187,7 @@
         <v>General</v>
       </c>
       <c r="G1194" t="str">
-        <v>175MM 7 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1194" t="str">
         <v>MTR</v>
@@ -42207,13 +42207,13 @@
         <v>1194</v>
       </c>
       <c r="B1195" t="str">
-        <v>FG-401081</v>
+        <v>FG-401119</v>
       </c>
       <c r="C1195" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
       </c>
       <c r="D1195" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
       </c>
       <c r="E1195" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42222,7 +42222,7 @@
         <v>General</v>
       </c>
       <c r="G1195" t="str">
-        <v>200MM 8 Inch</v>
+        <v>35MM 1 1/4 Inch</v>
       </c>
       <c r="H1195" t="str">
         <v>MTR</v>
@@ -42234,7 +42234,7 @@
         <v>Active</v>
       </c>
       <c r="K1195" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1196">
@@ -42242,10 +42242,10 @@
         <v>1195</v>
       </c>
       <c r="B1196" t="str">
-        <v>FG-401119</v>
+        <v>FG-401121</v>
       </c>
       <c r="C1196" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (50MM 2 Inch)</v>
       </c>
       <c r="D1196" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42257,7 +42257,7 @@
         <v>General</v>
       </c>
       <c r="G1196" t="str">
-        <v>35MM 1 1/4 Inch</v>
+        <v>50MM 2 Inch</v>
       </c>
       <c r="H1196" t="str">
         <v>MTR</v>
@@ -42277,10 +42277,10 @@
         <v>1196</v>
       </c>
       <c r="B1197" t="str">
-        <v>FG-401121</v>
+        <v>FG-401122</v>
       </c>
       <c r="C1197" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (50MM 2 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (100MM 4 Inch)</v>
       </c>
       <c r="D1197" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42292,7 +42292,7 @@
         <v>General</v>
       </c>
       <c r="G1197" t="str">
-        <v>50MM 2 Inch</v>
+        <v>100MM 4 Inch</v>
       </c>
       <c r="H1197" t="str">
         <v>MTR</v>
@@ -42312,10 +42312,10 @@
         <v>1197</v>
       </c>
       <c r="B1198" t="str">
-        <v>FG-401122</v>
+        <v>FG-401123</v>
       </c>
       <c r="C1198" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (100MM 4 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1198" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42327,7 +42327,7 @@
         <v>General</v>
       </c>
       <c r="G1198" t="str">
-        <v>100MM 4 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1198" t="str">
         <v>MTR</v>
@@ -42347,10 +42347,10 @@
         <v>1198</v>
       </c>
       <c r="B1199" t="str">
-        <v>FG-401123</v>
+        <v>FG-401124</v>
       </c>
       <c r="C1199" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1199" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42362,7 +42362,7 @@
         <v>General</v>
       </c>
       <c r="G1199" t="str">
-        <v>125MM 5 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1199" t="str">
         <v>MTR</v>
@@ -42382,10 +42382,10 @@
         <v>1199</v>
       </c>
       <c r="B1200" t="str">
-        <v>FG-401124</v>
+        <v>FG-401125</v>
       </c>
       <c r="C1200" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1200" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42397,7 +42397,7 @@
         <v>General</v>
       </c>
       <c r="G1200" t="str">
-        <v>150MM 6 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1200" t="str">
         <v>MTR</v>
@@ -42417,10 +42417,10 @@
         <v>1200</v>
       </c>
       <c r="B1201" t="str">
-        <v>FG-401125</v>
+        <v>FG-401126</v>
       </c>
       <c r="C1201" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1201" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42432,7 +42432,7 @@
         <v>General</v>
       </c>
       <c r="G1201" t="str">
-        <v>175MM 7 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1201" t="str">
         <v>MTR</v>
@@ -42452,22 +42452,22 @@
         <v>1201</v>
       </c>
       <c r="B1202" t="str">
-        <v>FG-401126</v>
+        <v>FG-401166</v>
       </c>
       <c r="C1202" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (200MM 8 Inch)</v>
+        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1202" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
+        <v>COLOUMN PIPE ECO V4</v>
       </c>
       <c r="E1202" t="str">
-        <v>UPVC CASING PIPES</v>
+        <v>UPVC COLUMN PIPES</v>
       </c>
       <c r="F1202" t="str">
         <v>General</v>
       </c>
       <c r="G1202" t="str">
-        <v>200MM 8 Inch</v>
+        <v>33MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1202" t="str">
         <v>MTR</v>
@@ -42479,7 +42479,7 @@
         <v>Active</v>
       </c>
       <c r="K1202" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>COLOUMN PIPE ECO V4 for submersible pump systems.</v>
       </c>
     </row>
     <row r="1203">
@@ -42487,10 +42487,10 @@
         <v>1202</v>
       </c>
       <c r="B1203" t="str">
-        <v>FG-401166</v>
+        <v>FG-401162</v>
       </c>
       <c r="C1203" t="str">
-        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG BELL END TYPE)</v>
       </c>
       <c r="D1203" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42502,7 +42502,7 @@
         <v>General</v>
       </c>
       <c r="G1203" t="str">
-        <v>33MM 12.5KG COUPLER TYPE</v>
+        <v>33MM 12.5KG BELL END TYPE</v>
       </c>
       <c r="H1203" t="str">
         <v>MTR</v>
@@ -42522,10 +42522,10 @@
         <v>1203</v>
       </c>
       <c r="B1204" t="str">
-        <v>FG-401162</v>
+        <v>FG-401165</v>
       </c>
       <c r="C1204" t="str">
-        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG BELL END TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 10KG COUPLER TYPE)</v>
       </c>
       <c r="D1204" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42537,7 +42537,7 @@
         <v>General</v>
       </c>
       <c r="G1204" t="str">
-        <v>33MM 12.5KG BELL END TYPE</v>
+        <v>42MM 10KG COUPLER TYPE</v>
       </c>
       <c r="H1204" t="str">
         <v>MTR</v>
@@ -42557,10 +42557,10 @@
         <v>1204</v>
       </c>
       <c r="B1205" t="str">
-        <v>FG-401165</v>
+        <v>FG-401167</v>
       </c>
       <c r="C1205" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 10KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1205" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42572,7 +42572,7 @@
         <v>General</v>
       </c>
       <c r="G1205" t="str">
-        <v>42MM 10KG COUPLER TYPE</v>
+        <v>42MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1205" t="str">
         <v>MTR</v>
@@ -42592,10 +42592,10 @@
         <v>1205</v>
       </c>
       <c r="B1206" t="str">
-        <v>FG-401167</v>
+        <v>FG-401163</v>
       </c>
       <c r="C1206" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG BELL END TYPE)</v>
       </c>
       <c r="D1206" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42607,7 +42607,7 @@
         <v>General</v>
       </c>
       <c r="G1206" t="str">
-        <v>42MM 12.5KG COUPLER TYPE</v>
+        <v>42MM 12.5KG BELL END TYPE</v>
       </c>
       <c r="H1206" t="str">
         <v>MTR</v>
@@ -42627,10 +42627,10 @@
         <v>1206</v>
       </c>
       <c r="B1207" t="str">
-        <v>FG-401163</v>
+        <v>FG-401164</v>
       </c>
       <c r="C1207" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG BELL END TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (48MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1207" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42642,7 +42642,7 @@
         <v>General</v>
       </c>
       <c r="G1207" t="str">
-        <v>42MM 12.5KG BELL END TYPE</v>
+        <v>48MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1207" t="str">
         <v>MTR</v>
@@ -42662,10 +42662,10 @@
         <v>1207</v>
       </c>
       <c r="B1208" t="str">
-        <v>FG-401164</v>
+        <v>FG-401168</v>
       </c>
       <c r="C1208" t="str">
-        <v>COLOUMN PIPE ECO V4 (48MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (60MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1208" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42677,7 +42677,7 @@
         <v>General</v>
       </c>
       <c r="G1208" t="str">
-        <v>48MM 12.5KG COUPLER TYPE</v>
+        <v>60MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1208" t="str">
         <v>MTR</v>
@@ -42697,13 +42697,13 @@
         <v>1208</v>
       </c>
       <c r="B1209" t="str">
-        <v>FG-401168</v>
+        <v>FG-401175</v>
       </c>
       <c r="C1209" t="str">
-        <v>COLOUMN PIPE ECO V4 (60MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (33MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1209" t="str">
-        <v>COLOUMN PIPE ECO V4</v>
+        <v>COLOUMN PIPE MEDIUM</v>
       </c>
       <c r="E1209" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -42712,7 +42712,7 @@
         <v>General</v>
       </c>
       <c r="G1209" t="str">
-        <v>60MM 12.5KG COUPLER TYPE</v>
+        <v>33MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1209" t="str">
         <v>MTR</v>
@@ -42724,7 +42724,7 @@
         <v>Active</v>
       </c>
       <c r="K1209" t="str">
-        <v>COLOUMN PIPE ECO V4 for submersible pump systems.</v>
+        <v>COLOUMN PIPE MEDIUM for submersible pump systems.</v>
       </c>
     </row>
     <row r="1210">
@@ -42732,10 +42732,10 @@
         <v>1209</v>
       </c>
       <c r="B1210" t="str">
-        <v>FG-401175</v>
+        <v>FG-401177</v>
       </c>
       <c r="C1210" t="str">
-        <v>COLOUMN PIPE MEDIUM (33MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (42MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1210" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42747,7 +42747,7 @@
         <v>General</v>
       </c>
       <c r="G1210" t="str">
-        <v>33MM 18KG COUPLER TYPE</v>
+        <v>42MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1210" t="str">
         <v>MTR</v>
@@ -42767,10 +42767,10 @@
         <v>1210</v>
       </c>
       <c r="B1211" t="str">
-        <v>FG-401177</v>
+        <v>FG-401176</v>
       </c>
       <c r="C1211" t="str">
-        <v>COLOUMN PIPE MEDIUM (42MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (48MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1211" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42782,7 +42782,7 @@
         <v>General</v>
       </c>
       <c r="G1211" t="str">
-        <v>42MM 18KG COUPLER TYPE</v>
+        <v>48MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1211" t="str">
         <v>MTR</v>
@@ -42802,10 +42802,10 @@
         <v>1211</v>
       </c>
       <c r="B1212" t="str">
-        <v>FG-401176</v>
+        <v>FG-401178</v>
       </c>
       <c r="C1212" t="str">
-        <v>COLOUMN PIPE MEDIUM (48MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (60MM 15KG COUPLER TYPE)</v>
       </c>
       <c r="D1212" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42817,7 +42817,7 @@
         <v>General</v>
       </c>
       <c r="G1212" t="str">
-        <v>48MM 18KG COUPLER TYPE</v>
+        <v>60MM 15KG COUPLER TYPE</v>
       </c>
       <c r="H1212" t="str">
         <v>MTR</v>
@@ -42837,10 +42837,10 @@
         <v>1212</v>
       </c>
       <c r="B1213" t="str">
-        <v>FG-401178</v>
+        <v>FG-401180</v>
       </c>
       <c r="C1213" t="str">
-        <v>COLOUMN PIPE MEDIUM (60MM 15KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (75MM 10KG COUPLER TYPE)</v>
       </c>
       <c r="D1213" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42852,7 +42852,7 @@
         <v>General</v>
       </c>
       <c r="G1213" t="str">
-        <v>60MM 15KG COUPLER TYPE</v>
+        <v>75MM 10KG COUPLER TYPE</v>
       </c>
       <c r="H1213" t="str">
         <v>MTR</v>
@@ -42872,13 +42872,13 @@
         <v>1213</v>
       </c>
       <c r="B1214" t="str">
-        <v>FG-401180</v>
+        <v>FG-401169</v>
       </c>
       <c r="C1214" t="str">
-        <v>COLOUMN PIPE MEDIUM (75MM 10KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (33MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1214" t="str">
-        <v>COLOUMN PIPE MEDIUM</v>
+        <v>COLOUMN PIPE STANDARD</v>
       </c>
       <c r="E1214" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -42887,7 +42887,7 @@
         <v>General</v>
       </c>
       <c r="G1214" t="str">
-        <v>75MM 10KG COUPLER TYPE</v>
+        <v>33MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1214" t="str">
         <v>MTR</v>
@@ -42899,7 +42899,7 @@
         <v>Active</v>
       </c>
       <c r="K1214" t="str">
-        <v>COLOUMN PIPE MEDIUM for submersible pump systems.</v>
+        <v>COLOUMN PIPE STANDARD for submersible pump systems.</v>
       </c>
     </row>
     <row r="1215">
@@ -42907,10 +42907,10 @@
         <v>1214</v>
       </c>
       <c r="B1215" t="str">
-        <v>FG-401169</v>
+        <v>FG-401171</v>
       </c>
       <c r="C1215" t="str">
-        <v>COLOUMN PIPE STANDARD (33MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (42MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1215" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42922,7 +42922,7 @@
         <v>General</v>
       </c>
       <c r="G1215" t="str">
-        <v>33MM 25KG COUPLER TYPE</v>
+        <v>42MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1215" t="str">
         <v>MTR</v>
@@ -42942,10 +42942,10 @@
         <v>1215</v>
       </c>
       <c r="B1216" t="str">
-        <v>FG-401171</v>
+        <v>FG-401170</v>
       </c>
       <c r="C1216" t="str">
-        <v>COLOUMN PIPE STANDARD (42MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (48MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1216" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42957,7 +42957,7 @@
         <v>General</v>
       </c>
       <c r="G1216" t="str">
-        <v>42MM 25KG COUPLER TYPE</v>
+        <v>48MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1216" t="str">
         <v>MTR</v>
@@ -42977,10 +42977,10 @@
         <v>1216</v>
       </c>
       <c r="B1217" t="str">
-        <v>FG-401170</v>
+        <v>FG-401172</v>
       </c>
       <c r="C1217" t="str">
-        <v>COLOUMN PIPE STANDARD (48MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (60MM 20KG COUPLER TYPE)</v>
       </c>
       <c r="D1217" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42992,7 +42992,7 @@
         <v>General</v>
       </c>
       <c r="G1217" t="str">
-        <v>48MM 25KG COUPLER TYPE</v>
+        <v>60MM 20KG COUPLER TYPE</v>
       </c>
       <c r="H1217" t="str">
         <v>MTR</v>
@@ -43012,10 +43012,10 @@
         <v>1217</v>
       </c>
       <c r="B1218" t="str">
-        <v>FG-401172</v>
+        <v>FG-401174</v>
       </c>
       <c r="C1218" t="str">
-        <v>COLOUMN PIPE STANDARD (60MM 20KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (75MM 20KG COUPLER TYPE)</v>
       </c>
       <c r="D1218" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -43027,7 +43027,7 @@
         <v>General</v>
       </c>
       <c r="G1218" t="str">
-        <v>60MM 20KG COUPLER TYPE</v>
+        <v>75MM 20KG COUPLER TYPE</v>
       </c>
       <c r="H1218" t="str">
         <v>MTR</v>
@@ -43047,13 +43047,13 @@
         <v>1218</v>
       </c>
       <c r="B1219" t="str">
-        <v>FG-401174</v>
+        <v>-</v>
       </c>
       <c r="C1219" t="str">
-        <v>COLOUMN PIPE STANDARD (75MM 20KG COUPLER TYPE)</v>
+        <v>3M STANDARD PLUS PIPE (60MM 25 COUPLER TYPE)</v>
       </c>
       <c r="D1219" t="str">
-        <v>COLOUMN PIPE STANDARD</v>
+        <v>3M STANDARD PLUS PIPE</v>
       </c>
       <c r="E1219" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43062,7 +43062,7 @@
         <v>General</v>
       </c>
       <c r="G1219" t="str">
-        <v>75MM 20KG COUPLER TYPE</v>
+        <v>60MM 25 COUPLER TYPE</v>
       </c>
       <c r="H1219" t="str">
         <v>MTR</v>
@@ -43074,7 +43074,7 @@
         <v>Active</v>
       </c>
       <c r="K1219" t="str">
-        <v>COLOUMN PIPE STANDARD for submersible pump systems.</v>
+        <v>3M Standard Plus UPVC Column Pipe for submersible pump systems.</v>
       </c>
     </row>
     <row r="1220">
@@ -43082,13 +43082,13 @@
         <v>1219</v>
       </c>
       <c r="B1220" t="str">
-        <v>-</v>
+        <v>FG-401182</v>
       </c>
       <c r="C1220" t="str">
-        <v>3M STANDARD PLUS PIPE (60MM 25 COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (42MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1220" t="str">
-        <v>3M STANDARD PLUS PIPE</v>
+        <v>COLOUMN PIPE HEAVY</v>
       </c>
       <c r="E1220" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43097,7 +43097,7 @@
         <v>General</v>
       </c>
       <c r="G1220" t="str">
-        <v>60MM 25 COUPLER TYPE</v>
+        <v>42MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1220" t="str">
         <v>MTR</v>
@@ -43109,7 +43109,7 @@
         <v>Active</v>
       </c>
       <c r="K1220" t="str">
-        <v>3M Standard Plus UPVC Column Pipe for submersible pump systems.</v>
+        <v>COLOUMN PIPE HEAVY for submersible pump systems.</v>
       </c>
     </row>
     <row r="1221">
@@ -43117,10 +43117,10 @@
         <v>1220</v>
       </c>
       <c r="B1221" t="str">
-        <v>FG-401182</v>
+        <v>FG-401181</v>
       </c>
       <c r="C1221" t="str">
-        <v>COLOUMN PIPE HEAVY (42MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (48MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1221" t="str">
         <v>COLOUMN PIPE HEAVY</v>
@@ -43132,7 +43132,7 @@
         <v>General</v>
       </c>
       <c r="G1221" t="str">
-        <v>42MM 30KG COUPLER TYPE</v>
+        <v>48MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1221" t="str">
         <v>MTR</v>
@@ -43152,10 +43152,10 @@
         <v>1221</v>
       </c>
       <c r="B1222" t="str">
-        <v>FG-401181</v>
+        <v>FG-401183</v>
       </c>
       <c r="C1222" t="str">
-        <v>COLOUMN PIPE HEAVY (48MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (60MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1222" t="str">
         <v>COLOUMN PIPE HEAVY</v>
@@ -43167,7 +43167,7 @@
         <v>General</v>
       </c>
       <c r="G1222" t="str">
-        <v>48MM 30KG COUPLER TYPE</v>
+        <v>60MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1222" t="str">
         <v>MTR</v>
@@ -43187,13 +43187,13 @@
         <v>1222</v>
       </c>
       <c r="B1223" t="str">
-        <v>FG-401183</v>
+        <v>FG-401179</v>
       </c>
       <c r="C1223" t="str">
-        <v>COLOUMN PIPE HEAVY (60MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM PLUS (60MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1223" t="str">
-        <v>COLOUMN PIPE HEAVY</v>
+        <v>COLOUMN PIPE MEDIUM PLUS</v>
       </c>
       <c r="E1223" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43202,7 +43202,7 @@
         <v>General</v>
       </c>
       <c r="G1223" t="str">
-        <v>60MM 30KG COUPLER TYPE</v>
+        <v>60MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1223" t="str">
         <v>MTR</v>
@@ -43214,7 +43214,7 @@
         <v>Active</v>
       </c>
       <c r="K1223" t="str">
-        <v>COLOUMN PIPE HEAVY for submersible pump systems.</v>
+        <v>COLOUMN PIPE MEDIUM PLUS for submersible pump systems.</v>
       </c>
     </row>
     <row r="1224">
@@ -43222,34 +43222,34 @@
         <v>1223</v>
       </c>
       <c r="B1224" t="str">
-        <v>FG-401179</v>
+        <v>FG-401569</v>
       </c>
       <c r="C1224" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS (60MM 18KG COUPLER TYPE)</v>
+        <v>CONSTRUCTION GHAMELA SHIVA (15 Inch)</v>
       </c>
       <c r="D1224" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS</v>
+        <v>CONSTRUCTION GHAMELA SHIVA</v>
       </c>
       <c r="E1224" t="str">
-        <v>UPVC COLUMN PIPES</v>
+        <v>HOUSEHOLD PRODUCTS</v>
       </c>
       <c r="F1224" t="str">
         <v>General</v>
       </c>
       <c r="G1224" t="str">
-        <v>60MM 18KG COUPLER TYPE</v>
+        <v>15 Inch</v>
       </c>
       <c r="H1224" t="str">
-        <v>MTR</v>
+        <v>BAGS</v>
       </c>
       <c r="I1224" t="str">
-        <v>-</v>
+        <v>75</v>
       </c>
       <c r="J1224" t="str">
         <v>Active</v>
       </c>
       <c r="K1224" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS for submersible pump systems.</v>
+        <v>CONSTRUCTION GHAMELA SHIVA high durability ghamela.</v>
       </c>
     </row>
     <row r="1225">
@@ -43257,13 +43257,13 @@
         <v>1224</v>
       </c>
       <c r="B1225" t="str">
-        <v>FG-401569</v>
+        <v>FG-401570</v>
       </c>
       <c r="C1225" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA (15 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA GOURI (15 Inch)</v>
       </c>
       <c r="D1225" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA</v>
+        <v>MULTIPURPOSE GHAMELA GOURI</v>
       </c>
       <c r="E1225" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43284,7 +43284,7 @@
         <v>Active</v>
       </c>
       <c r="K1225" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA GOURI high durability ghamela.</v>
       </c>
     </row>
     <row r="1226">
@@ -43292,13 +43292,13 @@
         <v>1225</v>
       </c>
       <c r="B1226" t="str">
-        <v>FG-401570</v>
+        <v>FG-401571</v>
       </c>
       <c r="C1226" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI (15 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA (16 Inch)</v>
       </c>
       <c r="D1226" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA</v>
       </c>
       <c r="E1226" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43307,19 +43307,19 @@
         <v>General</v>
       </c>
       <c r="G1226" t="str">
-        <v>15 Inch</v>
+        <v>16 Inch</v>
       </c>
       <c r="H1226" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1226" t="str">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="J1226" t="str">
         <v>Active</v>
       </c>
       <c r="K1226" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA high durability ghamela.</v>
       </c>
     </row>
     <row r="1227">
@@ -43327,13 +43327,13 @@
         <v>1226</v>
       </c>
       <c r="B1227" t="str">
-        <v>FG-401571</v>
+        <v>FG-401573</v>
       </c>
       <c r="C1227" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA (16 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV (18 Inch)</v>
       </c>
       <c r="D1227" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV</v>
       </c>
       <c r="E1227" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43342,19 +43342,19 @@
         <v>General</v>
       </c>
       <c r="G1227" t="str">
-        <v>16 Inch</v>
+        <v>18 Inch</v>
       </c>
       <c r="H1227" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1227" t="str">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J1227" t="str">
         <v>Active</v>
       </c>
       <c r="K1227" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV high durability ghamela.</v>
       </c>
     </row>
     <row r="1228">
@@ -43362,13 +43362,13 @@
         <v>1227</v>
       </c>
       <c r="B1228" t="str">
-        <v>FG-401573</v>
+        <v>FG-401574</v>
       </c>
       <c r="C1228" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV (18 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET (20 Inch)</v>
       </c>
       <c r="D1228" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET</v>
       </c>
       <c r="E1228" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43377,19 +43377,19 @@
         <v>General</v>
       </c>
       <c r="G1228" t="str">
-        <v>18 Inch</v>
+        <v>20 Inch</v>
       </c>
       <c r="H1228" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1228" t="str">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J1228" t="str">
         <v>Active</v>
       </c>
       <c r="K1228" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET high durability ghamela.</v>
       </c>
     </row>
     <row r="1229">
@@ -43397,13 +43397,13 @@
         <v>1228</v>
       </c>
       <c r="B1229" t="str">
-        <v>FG-401574</v>
+        <v>FG-401572</v>
       </c>
       <c r="C1229" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET (20 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI (17 Inch)</v>
       </c>
       <c r="D1229" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI</v>
       </c>
       <c r="E1229" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43412,19 +43412,19 @@
         <v>General</v>
       </c>
       <c r="G1229" t="str">
-        <v>20 Inch</v>
+        <v>17 Inch</v>
       </c>
       <c r="H1229" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1229" t="str">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J1229" t="str">
         <v>Active</v>
       </c>
       <c r="K1229" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI high durability ghamela.</v>
       </c>
     </row>
     <row r="1230">
@@ -43432,13 +43432,13 @@
         <v>1229</v>
       </c>
       <c r="B1230" t="str">
-        <v>FG-401572</v>
+        <v>FG-401575</v>
       </c>
       <c r="C1230" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI (17 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ (22 Inch)</v>
       </c>
       <c r="D1230" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ</v>
       </c>
       <c r="E1230" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43447,19 +43447,19 @@
         <v>General</v>
       </c>
       <c r="G1230" t="str">
-        <v>17 Inch</v>
+        <v>22 Inch</v>
       </c>
       <c r="H1230" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1230" t="str">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J1230" t="str">
         <v>Active</v>
       </c>
       <c r="K1230" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ high durability ghamela.</v>
       </c>
     </row>
     <row r="1231">
@@ -43467,13 +43467,13 @@
         <v>1230</v>
       </c>
       <c r="B1231" t="str">
-        <v>FG-401575</v>
+        <v>FG-401578</v>
       </c>
       <c r="C1231" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ (22 Inch)</v>
+        <v>AQUA PLAST GHAMELA 16 (16 Inch)</v>
       </c>
       <c r="D1231" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ</v>
+        <v>AQUA PLAST GHAMELA 16</v>
       </c>
       <c r="E1231" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43482,19 +43482,19 @@
         <v>General</v>
       </c>
       <c r="G1231" t="str">
-        <v>22 Inch</v>
+        <v>16 Inch</v>
       </c>
       <c r="H1231" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1231" t="str">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J1231" t="str">
         <v>Active</v>
       </c>
       <c r="K1231" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ high durability ghamela.</v>
+        <v>AQUA PLAST GHAMELA 16 high durability ghamela.</v>
       </c>
     </row>
     <row r="1232">
@@ -43502,13 +43502,13 @@
         <v>1231</v>
       </c>
       <c r="B1232" t="str">
-        <v>FG-401578</v>
+        <v>FG-401579</v>
       </c>
       <c r="C1232" t="str">
-        <v>AQUA PLAST GHAMELA 16 (16 Inch)</v>
+        <v>AQUA PLAST GHAMELA 17 (17 Inch)</v>
       </c>
       <c r="D1232" t="str">
-        <v>AQUA PLAST GHAMELA 16</v>
+        <v>AQUA PLAST GHAMELA 17</v>
       </c>
       <c r="E1232" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43517,7 +43517,7 @@
         <v>General</v>
       </c>
       <c r="G1232" t="str">
-        <v>16 Inch</v>
+        <v>17 Inch</v>
       </c>
       <c r="H1232" t="str">
         <v>BAGS</v>
@@ -43529,7 +43529,7 @@
         <v>Active</v>
       </c>
       <c r="K1232" t="str">
-        <v>AQUA PLAST GHAMELA 16 high durability ghamela.</v>
+        <v>AQUA PLAST GHAMELA 17 high durability ghamela.</v>
       </c>
     </row>
     <row r="1233">
@@ -43537,34 +43537,34 @@
         <v>1232</v>
       </c>
       <c r="B1233" t="str">
-        <v>FG-401579</v>
+        <v>FG-401364</v>
       </c>
       <c r="C1233" t="str">
-        <v>AQUA PLAST GHAMELA 17 (17 Inch)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1/2 15MM)</v>
       </c>
       <c r="D1233" t="str">
-        <v>AQUA PLAST GHAMELA 17</v>
+        <v>GAP-ORA FLOW GARDEN PIPE</v>
       </c>
       <c r="E1233" t="str">
-        <v>HOUSEHOLD PRODUCTS</v>
+        <v>Garden, Braided &amp; LDPE Pipes</v>
       </c>
       <c r="F1233" t="str">
         <v>General</v>
       </c>
       <c r="G1233" t="str">
-        <v>17 Inch</v>
+        <v>1/2 15MM</v>
       </c>
       <c r="H1233" t="str">
-        <v>BAGS</v>
+        <v>BDL</v>
       </c>
       <c r="I1233" t="str">
-        <v>60</v>
+        <v>-</v>
       </c>
       <c r="J1233" t="str">
         <v>Active</v>
       </c>
       <c r="K1233" t="str">
-        <v>AQUA PLAST GHAMELA 17 high durability ghamela.</v>
+        <v>GAP-ORA FLOW GARDEN PIPE. Available sizes: 1/2 15MM, 3/4 20MM, 1 25MM, 1 1/4 32MM.</v>
       </c>
     </row>
     <row r="1234">
@@ -43572,10 +43572,10 @@
         <v>1233</v>
       </c>
       <c r="B1234" t="str">
-        <v>FG-401364</v>
+        <v>FG-401365</v>
       </c>
       <c r="C1234" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1/2 15MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (3/4 20MM)</v>
       </c>
       <c r="D1234" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43587,7 +43587,7 @@
         <v>General</v>
       </c>
       <c r="G1234" t="str">
-        <v>1/2 15MM</v>
+        <v>3/4 20MM</v>
       </c>
       <c r="H1234" t="str">
         <v>BDL</v>
@@ -43607,10 +43607,10 @@
         <v>1234</v>
       </c>
       <c r="B1235" t="str">
-        <v>FG-401365</v>
+        <v>FG-401366</v>
       </c>
       <c r="C1235" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (3/4 20MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1 25MM)</v>
       </c>
       <c r="D1235" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43622,7 +43622,7 @@
         <v>General</v>
       </c>
       <c r="G1235" t="str">
-        <v>3/4 20MM</v>
+        <v>1 25MM</v>
       </c>
       <c r="H1235" t="str">
         <v>BDL</v>
@@ -43642,10 +43642,10 @@
         <v>1235</v>
       </c>
       <c r="B1236" t="str">
-        <v>FG-401366</v>
+        <v>FG-401367</v>
       </c>
       <c r="C1236" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1 25MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1 1/4 32MM)</v>
       </c>
       <c r="D1236" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43657,7 +43657,7 @@
         <v>General</v>
       </c>
       <c r="G1236" t="str">
-        <v>1 25MM</v>
+        <v>1 1/4 32MM</v>
       </c>
       <c r="H1236" t="str">
         <v>BDL</v>
@@ -43677,13 +43677,13 @@
         <v>1236</v>
       </c>
       <c r="B1237" t="str">
-        <v>FG-401367</v>
+        <v>FG-401370</v>
       </c>
       <c r="C1237" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1 1/4 32MM)</v>
+        <v>GAP-ORA BRAIDED PIPE (15MM 1/2)</v>
       </c>
       <c r="D1237" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE</v>
+        <v>GAP-ORA BRAIDED PIPE</v>
       </c>
       <c r="E1237" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43692,7 +43692,7 @@
         <v>General</v>
       </c>
       <c r="G1237" t="str">
-        <v>1 1/4 32MM</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1237" t="str">
         <v>BDL</v>
@@ -43704,7 +43704,7 @@
         <v>Active</v>
       </c>
       <c r="K1237" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE. Available sizes: 1/2 15MM, 3/4 20MM, 1 25MM, 1 1/4 32MM.</v>
+        <v>GAP-ORA BRAIDED PIPE.</v>
       </c>
     </row>
     <row r="1238">
@@ -43712,10 +43712,10 @@
         <v>1237</v>
       </c>
       <c r="B1238" t="str">
-        <v>FG-401370</v>
+        <v>FG-401371</v>
       </c>
       <c r="C1238" t="str">
-        <v>GAP-ORA BRAIDED PIPE (15MM 1/2)</v>
+        <v>GAP-ORA BRAIDED PIPE (20MM 3/4)</v>
       </c>
       <c r="D1238" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43727,7 +43727,7 @@
         <v>General</v>
       </c>
       <c r="G1238" t="str">
-        <v>15MM 1/2</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1238" t="str">
         <v>BDL</v>
@@ -43747,10 +43747,10 @@
         <v>1238</v>
       </c>
       <c r="B1239" t="str">
-        <v>FG-401371</v>
+        <v>FG-401372</v>
       </c>
       <c r="C1239" t="str">
-        <v>GAP-ORA BRAIDED PIPE (20MM 3/4)</v>
+        <v>GAP-ORA BRAIDED PIPE (25MM 1)</v>
       </c>
       <c r="D1239" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43762,7 +43762,7 @@
         <v>General</v>
       </c>
       <c r="G1239" t="str">
-        <v>20MM 3/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1239" t="str">
         <v>BDL</v>
@@ -43782,10 +43782,10 @@
         <v>1239</v>
       </c>
       <c r="B1240" t="str">
-        <v>FG-401372</v>
+        <v>FG-401373</v>
       </c>
       <c r="C1240" t="str">
-        <v>GAP-ORA BRAIDED PIPE (25MM 1)</v>
+        <v>GAP-ORA BRAIDED PIPE (32MM 1 1/4)</v>
       </c>
       <c r="D1240" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43797,7 +43797,7 @@
         <v>General</v>
       </c>
       <c r="G1240" t="str">
-        <v>25MM 1</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1240" t="str">
         <v>BDL</v>
@@ -43817,13 +43817,13 @@
         <v>1240</v>
       </c>
       <c r="B1241" t="str">
-        <v>FG-401373</v>
+        <v>FG-401355</v>
       </c>
       <c r="C1241" t="str">
-        <v>GAP-ORA BRAIDED PIPE (32MM 1 1/4)</v>
+        <v>GARDEN FOAM PIPES (15MM 1/2)</v>
       </c>
       <c r="D1241" t="str">
-        <v>GAP-ORA BRAIDED PIPE</v>
+        <v>GARDEN FOAM PIPES</v>
       </c>
       <c r="E1241" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43832,7 +43832,7 @@
         <v>General</v>
       </c>
       <c r="G1241" t="str">
-        <v>32MM 1 1/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1241" t="str">
         <v>BDL</v>
@@ -43844,7 +43844,7 @@
         <v>Active</v>
       </c>
       <c r="K1241" t="str">
-        <v>GAP-ORA BRAIDED PIPE.</v>
+        <v>GARDEN FOAM PIPES.</v>
       </c>
     </row>
     <row r="1242">
@@ -43852,10 +43852,10 @@
         <v>1241</v>
       </c>
       <c r="B1242" t="str">
-        <v>FG-401355</v>
+        <v>FG-401356</v>
       </c>
       <c r="C1242" t="str">
-        <v>GARDEN FOAM PIPES (15MM 1/2)</v>
+        <v>GARDEN FOAM PIPES (20MM 3/4)</v>
       </c>
       <c r="D1242" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43867,7 +43867,7 @@
         <v>General</v>
       </c>
       <c r="G1242" t="str">
-        <v>15MM 1/2</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1242" t="str">
         <v>BDL</v>
@@ -43887,10 +43887,10 @@
         <v>1242</v>
       </c>
       <c r="B1243" t="str">
-        <v>FG-401356</v>
+        <v>FG-401369</v>
       </c>
       <c r="C1243" t="str">
-        <v>GARDEN FOAM PIPES (20MM 3/4)</v>
+        <v>GARDEN FOAM PIPES (20MM 3/4 20MTR)</v>
       </c>
       <c r="D1243" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43902,7 +43902,7 @@
         <v>General</v>
       </c>
       <c r="G1243" t="str">
-        <v>20MM 3/4</v>
+        <v>20MM 3/4 20MTR</v>
       </c>
       <c r="H1243" t="str">
         <v>BDL</v>
@@ -43922,10 +43922,10 @@
         <v>1243</v>
       </c>
       <c r="B1244" t="str">
-        <v>FG-401369</v>
+        <v>FG-401357</v>
       </c>
       <c r="C1244" t="str">
-        <v>GARDEN FOAM PIPES (20MM 3/4 20MTR)</v>
+        <v>GARDEN FOAM PIPES (25MM 1)</v>
       </c>
       <c r="D1244" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43937,7 +43937,7 @@
         <v>General</v>
       </c>
       <c r="G1244" t="str">
-        <v>20MM 3/4 20MTR</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1244" t="str">
         <v>BDL</v>
@@ -43957,10 +43957,10 @@
         <v>1244</v>
       </c>
       <c r="B1245" t="str">
-        <v>FG-401357</v>
+        <v>FG-401358</v>
       </c>
       <c r="C1245" t="str">
-        <v>GARDEN FOAM PIPES (25MM 1)</v>
+        <v>GARDEN FOAM PIPES (32MM 1 1/4)</v>
       </c>
       <c r="D1245" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43972,7 +43972,7 @@
         <v>General</v>
       </c>
       <c r="G1245" t="str">
-        <v>25MM 1</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1245" t="str">
         <v>BDL</v>
@@ -43992,13 +43992,13 @@
         <v>1245</v>
       </c>
       <c r="B1246" t="str">
-        <v>FG-401358</v>
+        <v>FG-401344</v>
       </c>
       <c r="C1246" t="str">
-        <v>GARDEN FOAM PIPES (32MM 1 1/4)</v>
+        <v>BRAIDED PIPE (15MM 1/2)</v>
       </c>
       <c r="D1246" t="str">
-        <v>GARDEN FOAM PIPES</v>
+        <v>BRAIDED PIPE</v>
       </c>
       <c r="E1246" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44007,7 +44007,7 @@
         <v>General</v>
       </c>
       <c r="G1246" t="str">
-        <v>32MM 1 1/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1246" t="str">
         <v>BDL</v>
@@ -44019,7 +44019,7 @@
         <v>Active</v>
       </c>
       <c r="K1246" t="str">
-        <v>GARDEN FOAM PIPES.</v>
+        <v>Reinforced Braided Garden Pipe.</v>
       </c>
     </row>
     <row r="1247">
@@ -44027,10 +44027,10 @@
         <v>1246</v>
       </c>
       <c r="B1247" t="str">
-        <v>FG-401344</v>
+        <v>FG-401345</v>
       </c>
       <c r="C1247" t="str">
-        <v>BRAIDED PIPE (15MM 1/2)</v>
+        <v>BRAIDED PIPE (20MM 3/4)</v>
       </c>
       <c r="D1247" t="str">
         <v>BRAIDED PIPE</v>
@@ -44042,7 +44042,7 @@
         <v>General</v>
       </c>
       <c r="G1247" t="str">
-        <v>15MM 1/2</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1247" t="str">
         <v>BDL</v>
@@ -44062,10 +44062,10 @@
         <v>1247</v>
       </c>
       <c r="B1248" t="str">
-        <v>FG-401345</v>
+        <v>FG-401346</v>
       </c>
       <c r="C1248" t="str">
-        <v>BRAIDED PIPE (20MM 3/4)</v>
+        <v>BRAIDED PIPE (25MM 1)</v>
       </c>
       <c r="D1248" t="str">
         <v>BRAIDED PIPE</v>
@@ -44077,7 +44077,7 @@
         <v>General</v>
       </c>
       <c r="G1248" t="str">
-        <v>20MM 3/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1248" t="str">
         <v>BDL</v>
@@ -44097,10 +44097,10 @@
         <v>1248</v>
       </c>
       <c r="B1249" t="str">
-        <v>FG-401346</v>
+        <v>FG-401363</v>
       </c>
       <c r="C1249" t="str">
-        <v>BRAIDED PIPE (25MM 1)</v>
+        <v>BRAIDED PIPE (32MM 1 1/4)</v>
       </c>
       <c r="D1249" t="str">
         <v>BRAIDED PIPE</v>
@@ -44112,7 +44112,7 @@
         <v>General</v>
       </c>
       <c r="G1249" t="str">
-        <v>25MM 1</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1249" t="str">
         <v>BDL</v>
@@ -44132,13 +44132,13 @@
         <v>1249</v>
       </c>
       <c r="B1250" t="str">
-        <v>FG-401363</v>
+        <v>FG-401374</v>
       </c>
       <c r="C1250" t="str">
-        <v>BRAIDED PIPE (32MM 1 1/4)</v>
+        <v>LEVEL PIPE (6MM)</v>
       </c>
       <c r="D1250" t="str">
-        <v>BRAIDED PIPE</v>
+        <v>LEVEL PIPE</v>
       </c>
       <c r="E1250" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44147,7 +44147,7 @@
         <v>General</v>
       </c>
       <c r="G1250" t="str">
-        <v>32MM 1 1/4</v>
+        <v>6MM</v>
       </c>
       <c r="H1250" t="str">
         <v>BDL</v>
@@ -44159,7 +44159,7 @@
         <v>Active</v>
       </c>
       <c r="K1250" t="str">
-        <v>Reinforced Braided Garden Pipe.</v>
+        <v>Transparent Level Pipe for construction &amp; garden work.</v>
       </c>
     </row>
     <row r="1251">
@@ -44167,13 +44167,13 @@
         <v>1250</v>
       </c>
       <c r="B1251" t="str">
-        <v>FG-401374</v>
+        <v>FG-401340</v>
       </c>
       <c r="C1251" t="str">
-        <v>LEVEL PIPE (6MM)</v>
+        <v>GARDEN PIPES SUPER FLOW (15MM 1/2)</v>
       </c>
       <c r="D1251" t="str">
-        <v>LEVEL PIPE</v>
+        <v>GARDEN PIPES SUPER FLOW</v>
       </c>
       <c r="E1251" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44182,7 +44182,7 @@
         <v>General</v>
       </c>
       <c r="G1251" t="str">
-        <v>6MM</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1251" t="str">
         <v>BDL</v>
@@ -44194,7 +44194,7 @@
         <v>Active</v>
       </c>
       <c r="K1251" t="str">
-        <v>Transparent Level Pipe for construction &amp; garden work.</v>
+        <v>GARDEN PIPES SUPER FLOW.</v>
       </c>
     </row>
     <row r="1252">
@@ -44202,10 +44202,10 @@
         <v>1251</v>
       </c>
       <c r="B1252" t="str">
-        <v>FG-401340</v>
+        <v>FG-401341</v>
       </c>
       <c r="C1252" t="str">
-        <v>GARDEN PIPES SUPER FLOW (15MM 1/2)</v>
+        <v>GARDEN PIPES SUPER FLOW (20MM 3/4)</v>
       </c>
       <c r="D1252" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44217,7 +44217,7 @@
         <v>General</v>
       </c>
       <c r="G1252" t="str">
-        <v>15MM 1/2</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1252" t="str">
         <v>BDL</v>
@@ -44237,10 +44237,10 @@
         <v>1252</v>
       </c>
       <c r="B1253" t="str">
-        <v>FG-401341</v>
+        <v>FG-401652</v>
       </c>
       <c r="C1253" t="str">
-        <v>GARDEN PIPES SUPER FLOW (20MM 3/4)</v>
+        <v>GARDEN PIPES SUPER FLOW (20MM 3/4 15MTR)</v>
       </c>
       <c r="D1253" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44252,7 +44252,7 @@
         <v>General</v>
       </c>
       <c r="G1253" t="str">
-        <v>20MM 3/4</v>
+        <v>20MM 3/4 15MTR</v>
       </c>
       <c r="H1253" t="str">
         <v>BDL</v>
@@ -44272,10 +44272,10 @@
         <v>1253</v>
       </c>
       <c r="B1254" t="str">
-        <v>FG-401652</v>
+        <v>FG-401342</v>
       </c>
       <c r="C1254" t="str">
-        <v>GARDEN PIPES SUPER FLOW (20MM 3/4 15MTR)</v>
+        <v>GARDEN PIPES SUPER FLOW (25MM 1)</v>
       </c>
       <c r="D1254" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44287,7 +44287,7 @@
         <v>General</v>
       </c>
       <c r="G1254" t="str">
-        <v>20MM 3/4 15MTR</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1254" t="str">
         <v>BDL</v>
@@ -44307,10 +44307,10 @@
         <v>1254</v>
       </c>
       <c r="B1255" t="str">
-        <v>FG-401342</v>
+        <v>FG-401343</v>
       </c>
       <c r="C1255" t="str">
-        <v>GARDEN PIPES SUPER FLOW (25MM 1)</v>
+        <v>GARDEN PIPES SUPER FLOW (32MM 1 1/4)</v>
       </c>
       <c r="D1255" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44322,7 +44322,7 @@
         <v>General</v>
       </c>
       <c r="G1255" t="str">
-        <v>25MM 1</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1255" t="str">
         <v>BDL</v>
@@ -44342,10 +44342,10 @@
         <v>1255</v>
       </c>
       <c r="B1256" t="str">
-        <v>FG-401343</v>
+        <v>FG-401627</v>
       </c>
       <c r="C1256" t="str">
-        <v>GARDEN PIPES SUPER FLOW (32MM 1 1/4)</v>
+        <v>GARDEN PIPES SUPER FLOW (40MM 1 1/2)</v>
       </c>
       <c r="D1256" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44357,7 +44357,7 @@
         <v>General</v>
       </c>
       <c r="G1256" t="str">
-        <v>32MM 1 1/4</v>
+        <v>40MM 1 1/2</v>
       </c>
       <c r="H1256" t="str">
         <v>BDL</v>
@@ -44377,34 +44377,34 @@
         <v>1256</v>
       </c>
       <c r="B1257" t="str">
-        <v>FG-401627</v>
+        <v>FG-401552</v>
       </c>
       <c r="C1257" t="str">
-        <v>GARDEN PIPES SUPER FLOW (40MM 1 1/2)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2 inch)</v>
       </c>
       <c r="D1257" t="str">
-        <v>GARDEN PIPES SUPER FLOW</v>
+        <v>EDGE SERIES SHORT BODY TAP</v>
       </c>
       <c r="E1257" t="str">
-        <v>Garden, Braided &amp; LDPE Pipes</v>
+        <v>FAUCETS</v>
       </c>
       <c r="F1257" t="str">
         <v>General</v>
       </c>
       <c r="G1257" t="str">
-        <v>40MM 1 1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1257" t="str">
-        <v>BDL</v>
-      </c>
-      <c r="I1257" t="str">
-        <v>-</v>
+        <v>NOS</v>
+      </c>
+      <c r="I1257">
+        <v>20</v>
       </c>
       <c r="J1257" t="str">
         <v>Active</v>
       </c>
       <c r="K1257" t="str">
-        <v>GARDEN PIPES SUPER FLOW.</v>
+        <v>EDGE SERIES SHORT BODY TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1258">
@@ -44415,7 +44415,7 @@
         <v>FG-401552</v>
       </c>
       <c r="C1258" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2 inch)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2)</v>
       </c>
       <c r="D1258" t="str">
         <v>EDGE SERIES SHORT BODY TAP</v>
@@ -44427,7 +44427,7 @@
         <v>General</v>
       </c>
       <c r="G1258" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1258" t="str">
         <v>NOS</v>
@@ -44450,7 +44450,7 @@
         <v>FG-401552</v>
       </c>
       <c r="C1259" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2")</v>
       </c>
       <c r="D1259" t="str">
         <v>EDGE SERIES SHORT BODY TAP</v>
@@ -44462,7 +44462,7 @@
         <v>General</v>
       </c>
       <c r="G1259" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1259" t="str">
         <v>NOS</v>
@@ -44482,13 +44482,13 @@
         <v>1259</v>
       </c>
       <c r="B1260" t="str">
-        <v>FG-401552</v>
+        <v>FG-401551</v>
       </c>
       <c r="C1260" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2")</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2 inch)</v>
       </c>
       <c r="D1260" t="str">
-        <v>EDGE SERIES SHORT BODY TAP</v>
+        <v>EDGE SERIES LONG BODY TAP</v>
       </c>
       <c r="E1260" t="str">
         <v>FAUCETS</v>
@@ -44497,19 +44497,19 @@
         <v>General</v>
       </c>
       <c r="G1260" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1260" t="str">
         <v>NOS</v>
       </c>
       <c r="I1260">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J1260" t="str">
         <v>Active</v>
       </c>
       <c r="K1260" t="str">
-        <v>EDGE SERIES SHORT BODY TAP high quality faucet.</v>
+        <v>EDGE SERIES LONG BODY TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1261">
@@ -44520,7 +44520,7 @@
         <v>FG-401551</v>
       </c>
       <c r="C1261" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2 inch)</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2)</v>
       </c>
       <c r="D1261" t="str">
         <v>EDGE SERIES LONG BODY TAP</v>
@@ -44532,7 +44532,7 @@
         <v>General</v>
       </c>
       <c r="G1261" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1261" t="str">
         <v>NOS</v>
@@ -44555,7 +44555,7 @@
         <v>FG-401551</v>
       </c>
       <c r="C1262" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2)</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2")</v>
       </c>
       <c r="D1262" t="str">
         <v>EDGE SERIES LONG BODY TAP</v>
@@ -44567,7 +44567,7 @@
         <v>General</v>
       </c>
       <c r="G1262" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1262" t="str">
         <v>NOS</v>
@@ -44587,13 +44587,13 @@
         <v>1262</v>
       </c>
       <c r="B1263" t="str">
-        <v>FG-401551</v>
+        <v>FG-401549</v>
       </c>
       <c r="C1263" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2")</v>
+        <v>EDGE SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1263" t="str">
-        <v>EDGE SERIES LONG BODY TAP</v>
+        <v>EDGE SERIES SWAN NECK</v>
       </c>
       <c r="E1263" t="str">
         <v>FAUCETS</v>
@@ -44602,19 +44602,19 @@
         <v>General</v>
       </c>
       <c r="G1263" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1263" t="str">
         <v>NOS</v>
       </c>
       <c r="I1263">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J1263" t="str">
         <v>Active</v>
       </c>
       <c r="K1263" t="str">
-        <v>EDGE SERIES LONG BODY TAP high quality faucet.</v>
+        <v>EDGE SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1264">
@@ -44625,7 +44625,7 @@
         <v>FG-401549</v>
       </c>
       <c r="C1264" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2 inch)</v>
+        <v>EDGE SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1264" t="str">
         <v>EDGE SERIES SWAN NECK</v>
@@ -44637,7 +44637,7 @@
         <v>General</v>
       </c>
       <c r="G1264" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1264" t="str">
         <v>NOS</v>
@@ -44660,7 +44660,7 @@
         <v>FG-401549</v>
       </c>
       <c r="C1265" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2)</v>
+        <v>EDGE SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1265" t="str">
         <v>EDGE SERIES SWAN NECK</v>
@@ -44672,7 +44672,7 @@
         <v>General</v>
       </c>
       <c r="G1265" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1265" t="str">
         <v>NOS</v>
@@ -44692,13 +44692,13 @@
         <v>1265</v>
       </c>
       <c r="B1266" t="str">
-        <v>FG-401549</v>
+        <v>FG-401546</v>
       </c>
       <c r="C1266" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2")</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1266" t="str">
-        <v>EDGE SERIES SWAN NECK</v>
+        <v>EDGE SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1266" t="str">
         <v>FAUCETS</v>
@@ -44707,19 +44707,19 @@
         <v>General</v>
       </c>
       <c r="G1266" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1266" t="str">
         <v>NOS</v>
       </c>
       <c r="I1266">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="J1266" t="str">
         <v>Active</v>
       </c>
       <c r="K1266" t="str">
-        <v>EDGE SERIES SWAN NECK high quality faucet.</v>
+        <v>EDGE SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1267">
@@ -44730,7 +44730,7 @@
         <v>FG-401546</v>
       </c>
       <c r="C1267" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1267" t="str">
         <v>EDGE SERIES ANGULAR VALVE</v>
@@ -44742,7 +44742,7 @@
         <v>General</v>
       </c>
       <c r="G1267" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1267" t="str">
         <v>NOS</v>
@@ -44765,7 +44765,7 @@
         <v>FG-401546</v>
       </c>
       <c r="C1268" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2)</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1268" t="str">
         <v>EDGE SERIES ANGULAR VALVE</v>
@@ -44777,7 +44777,7 @@
         <v>General</v>
       </c>
       <c r="G1268" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1268" t="str">
         <v>NOS</v>
@@ -44797,13 +44797,13 @@
         <v>1268</v>
       </c>
       <c r="B1269" t="str">
-        <v>FG-401546</v>
+        <v>FG-401547</v>
       </c>
       <c r="C1269" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2")</v>
+        <v>EDGE SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1269" t="str">
-        <v>EDGE SERIES ANGULAR VALVE</v>
+        <v>EDGE SERIES PILLAR TAP</v>
       </c>
       <c r="E1269" t="str">
         <v>FAUCETS</v>
@@ -44812,19 +44812,19 @@
         <v>General</v>
       </c>
       <c r="G1269" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1269" t="str">
         <v>NOS</v>
       </c>
       <c r="I1269">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J1269" t="str">
         <v>Active</v>
       </c>
       <c r="K1269" t="str">
-        <v>EDGE SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>EDGE SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1270">
@@ -44835,7 +44835,7 @@
         <v>FG-401547</v>
       </c>
       <c r="C1270" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2 inch)</v>
+        <v>EDGE SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1270" t="str">
         <v>EDGE SERIES PILLAR TAP</v>
@@ -44847,7 +44847,7 @@
         <v>General</v>
       </c>
       <c r="G1270" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1270" t="str">
         <v>NOS</v>
@@ -44870,7 +44870,7 @@
         <v>FG-401547</v>
       </c>
       <c r="C1271" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2)</v>
+        <v>EDGE SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1271" t="str">
         <v>EDGE SERIES PILLAR TAP</v>
@@ -44882,7 +44882,7 @@
         <v>General</v>
       </c>
       <c r="G1271" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1271" t="str">
         <v>NOS</v>
@@ -44902,13 +44902,13 @@
         <v>1271</v>
       </c>
       <c r="B1272" t="str">
-        <v>FG-401547</v>
+        <v>FG-401550</v>
       </c>
       <c r="C1272" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2")</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2 inch)</v>
       </c>
       <c r="D1272" t="str">
-        <v>EDGE SERIES PILLAR TAP</v>
+        <v>EDGE SERIES 2 WAY BIB TAB</v>
       </c>
       <c r="E1272" t="str">
         <v>FAUCETS</v>
@@ -44917,19 +44917,19 @@
         <v>General</v>
       </c>
       <c r="G1272" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1272" t="str">
         <v>NOS</v>
       </c>
       <c r="I1272">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J1272" t="str">
         <v>Active</v>
       </c>
       <c r="K1272" t="str">
-        <v>EDGE SERIES PILLAR TAP high quality faucet.</v>
+        <v>EDGE SERIES 2 WAY BIB TAB high quality faucet.</v>
       </c>
     </row>
     <row r="1273">
@@ -44940,7 +44940,7 @@
         <v>FG-401550</v>
       </c>
       <c r="C1273" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2 inch)</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2)</v>
       </c>
       <c r="D1273" t="str">
         <v>EDGE SERIES 2 WAY BIB TAB</v>
@@ -44952,7 +44952,7 @@
         <v>General</v>
       </c>
       <c r="G1273" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1273" t="str">
         <v>NOS</v>
@@ -44975,7 +44975,7 @@
         <v>FG-401550</v>
       </c>
       <c r="C1274" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2)</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2")</v>
       </c>
       <c r="D1274" t="str">
         <v>EDGE SERIES 2 WAY BIB TAB</v>
@@ -44987,7 +44987,7 @@
         <v>General</v>
       </c>
       <c r="G1274" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1274" t="str">
         <v>NOS</v>
@@ -45007,13 +45007,13 @@
         <v>1274</v>
       </c>
       <c r="B1275" t="str">
-        <v>FG-401550</v>
+        <v>FG-401548</v>
       </c>
       <c r="C1275" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2")</v>
+        <v>EDGE SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1275" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB</v>
+        <v>EDGE SERIES SINK TAP</v>
       </c>
       <c r="E1275" t="str">
         <v>FAUCETS</v>
@@ -45022,19 +45022,19 @@
         <v>General</v>
       </c>
       <c r="G1275" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1275" t="str">
         <v>NOS</v>
       </c>
       <c r="I1275">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1275" t="str">
         <v>Active</v>
       </c>
       <c r="K1275" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB high quality faucet.</v>
+        <v>EDGE SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1276">
@@ -45045,7 +45045,7 @@
         <v>FG-401548</v>
       </c>
       <c r="C1276" t="str">
-        <v>EDGE SERIES SINK TAP (1/2 inch)</v>
+        <v>EDGE SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1276" t="str">
         <v>EDGE SERIES SINK TAP</v>
@@ -45057,7 +45057,7 @@
         <v>General</v>
       </c>
       <c r="G1276" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1276" t="str">
         <v>NOS</v>
@@ -45080,7 +45080,7 @@
         <v>FG-401548</v>
       </c>
       <c r="C1277" t="str">
-        <v>EDGE SERIES SINK TAP (1/2)</v>
+        <v>EDGE SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1277" t="str">
         <v>EDGE SERIES SINK TAP</v>
@@ -45092,7 +45092,7 @@
         <v>General</v>
       </c>
       <c r="G1277" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1277" t="str">
         <v>NOS</v>
@@ -45112,13 +45112,13 @@
         <v>1277</v>
       </c>
       <c r="B1278" t="str">
-        <v>FG-401548</v>
+        <v>FG-401568</v>
       </c>
       <c r="C1278" t="str">
-        <v>EDGE SERIES SINK TAP (1/2")</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1278" t="str">
-        <v>EDGE SERIES SINK TAP</v>
+        <v>SMART SERIES SHORT BODY BIB TAP</v>
       </c>
       <c r="E1278" t="str">
         <v>FAUCETS</v>
@@ -45127,19 +45127,19 @@
         <v>General</v>
       </c>
       <c r="G1278" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1278" t="str">
         <v>NOS</v>
       </c>
       <c r="I1278">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="J1278" t="str">
         <v>Active</v>
       </c>
       <c r="K1278" t="str">
-        <v>EDGE SERIES SINK TAP high quality faucet.</v>
+        <v>SMART SERIES SHORT BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1279">
@@ -45150,7 +45150,7 @@
         <v>FG-401568</v>
       </c>
       <c r="C1279" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1279" t="str">
         <v>SMART SERIES SHORT BODY BIB TAP</v>
@@ -45162,7 +45162,7 @@
         <v>General</v>
       </c>
       <c r="G1279" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1279" t="str">
         <v>NOS</v>
@@ -45185,7 +45185,7 @@
         <v>FG-401568</v>
       </c>
       <c r="C1280" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2)</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1280" t="str">
         <v>SMART SERIES SHORT BODY BIB TAP</v>
@@ -45197,7 +45197,7 @@
         <v>General</v>
       </c>
       <c r="G1280" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1280" t="str">
         <v>NOS</v>
@@ -45217,13 +45217,13 @@
         <v>1280</v>
       </c>
       <c r="B1281" t="str">
-        <v>FG-401568</v>
+        <v>FG-401567</v>
       </c>
       <c r="C1281" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2")</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1281" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP</v>
+        <v>SMART SERIES LONG BODY BIB TAP</v>
       </c>
       <c r="E1281" t="str">
         <v>FAUCETS</v>
@@ -45232,7 +45232,7 @@
         <v>General</v>
       </c>
       <c r="G1281" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1281" t="str">
         <v>NOS</v>
@@ -45244,7 +45244,7 @@
         <v>Active</v>
       </c>
       <c r="K1281" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP high quality faucet.</v>
+        <v>SMART SERIES LONG BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1282">
@@ -45255,7 +45255,7 @@
         <v>FG-401567</v>
       </c>
       <c r="C1282" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1282" t="str">
         <v>SMART SERIES LONG BODY BIB TAP</v>
@@ -45267,7 +45267,7 @@
         <v>General</v>
       </c>
       <c r="G1282" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1282" t="str">
         <v>NOS</v>
@@ -45290,7 +45290,7 @@
         <v>FG-401567</v>
       </c>
       <c r="C1283" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2)</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1283" t="str">
         <v>SMART SERIES LONG BODY BIB TAP</v>
@@ -45302,7 +45302,7 @@
         <v>General</v>
       </c>
       <c r="G1283" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1283" t="str">
         <v>NOS</v>
@@ -45322,13 +45322,13 @@
         <v>1283</v>
       </c>
       <c r="B1284" t="str">
-        <v>FG-401567</v>
+        <v>FG-401562</v>
       </c>
       <c r="C1284" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2")</v>
+        <v>SMART SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1284" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP</v>
+        <v>SMART SERIES PILLAR TAP</v>
       </c>
       <c r="E1284" t="str">
         <v>FAUCETS</v>
@@ -45337,19 +45337,19 @@
         <v>General</v>
       </c>
       <c r="G1284" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1284" t="str">
         <v>NOS</v>
       </c>
       <c r="I1284">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1284" t="str">
         <v>Active</v>
       </c>
       <c r="K1284" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP high quality faucet.</v>
+        <v>SMART SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1285">
@@ -45360,7 +45360,7 @@
         <v>FG-401562</v>
       </c>
       <c r="C1285" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2 inch)</v>
+        <v>SMART SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1285" t="str">
         <v>SMART SERIES PILLAR TAP</v>
@@ -45372,7 +45372,7 @@
         <v>General</v>
       </c>
       <c r="G1285" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1285" t="str">
         <v>NOS</v>
@@ -45395,7 +45395,7 @@
         <v>FG-401562</v>
       </c>
       <c r="C1286" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2)</v>
+        <v>SMART SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1286" t="str">
         <v>SMART SERIES PILLAR TAP</v>
@@ -45407,7 +45407,7 @@
         <v>General</v>
       </c>
       <c r="G1286" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1286" t="str">
         <v>NOS</v>
@@ -45427,13 +45427,13 @@
         <v>1286</v>
       </c>
       <c r="B1287" t="str">
-        <v>FG-401562</v>
+        <v>FG-401563</v>
       </c>
       <c r="C1287" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2")</v>
+        <v>SMART SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1287" t="str">
-        <v>SMART SERIES PILLAR TAP</v>
+        <v>SMART SERIES SINK TAP</v>
       </c>
       <c r="E1287" t="str">
         <v>FAUCETS</v>
@@ -45442,7 +45442,7 @@
         <v>General</v>
       </c>
       <c r="G1287" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1287" t="str">
         <v>NOS</v>
@@ -45454,7 +45454,7 @@
         <v>Active</v>
       </c>
       <c r="K1287" t="str">
-        <v>SMART SERIES PILLAR TAP high quality faucet.</v>
+        <v>SMART SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1288">
@@ -45465,7 +45465,7 @@
         <v>FG-401563</v>
       </c>
       <c r="C1288" t="str">
-        <v>SMART SERIES SINK TAP (1/2 inch)</v>
+        <v>SMART SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1288" t="str">
         <v>SMART SERIES SINK TAP</v>
@@ -45477,7 +45477,7 @@
         <v>General</v>
       </c>
       <c r="G1288" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1288" t="str">
         <v>NOS</v>
@@ -45500,7 +45500,7 @@
         <v>FG-401563</v>
       </c>
       <c r="C1289" t="str">
-        <v>SMART SERIES SINK TAP (1/2)</v>
+        <v>SMART SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1289" t="str">
         <v>SMART SERIES SINK TAP</v>
@@ -45512,7 +45512,7 @@
         <v>General</v>
       </c>
       <c r="G1289" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1289" t="str">
         <v>NOS</v>
@@ -45532,13 +45532,13 @@
         <v>1289</v>
       </c>
       <c r="B1290" t="str">
-        <v>FG-401563</v>
+        <v>FG-401564</v>
       </c>
       <c r="C1290" t="str">
-        <v>SMART SERIES SINK TAP (1/2")</v>
+        <v>SMART SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1290" t="str">
-        <v>SMART SERIES SINK TAP</v>
+        <v>SMART SERIES SWAN NECK</v>
       </c>
       <c r="E1290" t="str">
         <v>FAUCETS</v>
@@ -45547,7 +45547,7 @@
         <v>General</v>
       </c>
       <c r="G1290" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1290" t="str">
         <v>NOS</v>
@@ -45559,7 +45559,7 @@
         <v>Active</v>
       </c>
       <c r="K1290" t="str">
-        <v>SMART SERIES SINK TAP high quality faucet.</v>
+        <v>SMART SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1291">
@@ -45570,7 +45570,7 @@
         <v>FG-401564</v>
       </c>
       <c r="C1291" t="str">
-        <v>SMART SERIES SWAN NECK (1/2 inch)</v>
+        <v>SMART SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1291" t="str">
         <v>SMART SERIES SWAN NECK</v>
@@ -45582,7 +45582,7 @@
         <v>General</v>
       </c>
       <c r="G1291" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1291" t="str">
         <v>NOS</v>
@@ -45605,7 +45605,7 @@
         <v>FG-401564</v>
       </c>
       <c r="C1292" t="str">
-        <v>SMART SERIES SWAN NECK (1/2)</v>
+        <v>SMART SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1292" t="str">
         <v>SMART SERIES SWAN NECK</v>
@@ -45617,7 +45617,7 @@
         <v>General</v>
       </c>
       <c r="G1292" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1292" t="str">
         <v>NOS</v>
@@ -45637,13 +45637,13 @@
         <v>1292</v>
       </c>
       <c r="B1293" t="str">
-        <v>FG-401564</v>
+        <v>FG-401561</v>
       </c>
       <c r="C1293" t="str">
-        <v>SMART SERIES SWAN NECK (1/2")</v>
+        <v>SMART SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1293" t="str">
-        <v>SMART SERIES SWAN NECK</v>
+        <v>SMART SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1293" t="str">
         <v>FAUCETS</v>
@@ -45652,19 +45652,19 @@
         <v>General</v>
       </c>
       <c r="G1293" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1293" t="str">
         <v>NOS</v>
       </c>
       <c r="I1293">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1293" t="str">
         <v>Active</v>
       </c>
       <c r="K1293" t="str">
-        <v>SMART SERIES SWAN NECK high quality faucet.</v>
+        <v>SMART SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1294">
@@ -45672,13 +45672,13 @@
         <v>1293</v>
       </c>
       <c r="B1294" t="str">
-        <v>FG-401561</v>
+        <v>FG-401566</v>
       </c>
       <c r="C1294" t="str">
-        <v>SMART SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1294" t="str">
-        <v>SMART SERIES ANGULAR VALVE</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
       </c>
       <c r="E1294" t="str">
         <v>FAUCETS</v>
@@ -45693,13 +45693,13 @@
         <v>NOS</v>
       </c>
       <c r="I1294">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1294" t="str">
         <v>Active</v>
       </c>
       <c r="K1294" t="str">
-        <v>SMART SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1295">
@@ -45710,7 +45710,7 @@
         <v>FG-401566</v>
       </c>
       <c r="C1295" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1295" t="str">
         <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
@@ -45722,7 +45722,7 @@
         <v>General</v>
       </c>
       <c r="G1295" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1295" t="str">
         <v>NOS</v>
@@ -45745,7 +45745,7 @@
         <v>FG-401566</v>
       </c>
       <c r="C1296" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1296" t="str">
         <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
@@ -45757,7 +45757,7 @@
         <v>General</v>
       </c>
       <c r="G1296" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1296" t="str">
         <v>NOS</v>
@@ -45777,13 +45777,13 @@
         <v>1296</v>
       </c>
       <c r="B1297" t="str">
-        <v>FG-401566</v>
+        <v>FG-401565</v>
       </c>
       <c r="C1297" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2")</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1297" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
+        <v>SMART SERIES 2 WAY BIB TAP</v>
       </c>
       <c r="E1297" t="str">
         <v>FAUCETS</v>
@@ -45792,7 +45792,7 @@
         <v>General</v>
       </c>
       <c r="G1297" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1297" t="str">
         <v>NOS</v>
@@ -45804,7 +45804,7 @@
         <v>Active</v>
       </c>
       <c r="K1297" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
+        <v>SMART SERIES 2 WAY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1298">
@@ -45815,7 +45815,7 @@
         <v>FG-401565</v>
       </c>
       <c r="C1298" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2)</v>
       </c>
       <c r="D1298" t="str">
         <v>SMART SERIES 2 WAY BIB TAP</v>
@@ -45827,7 +45827,7 @@
         <v>General</v>
       </c>
       <c r="G1298" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1298" t="str">
         <v>NOS</v>
@@ -45850,7 +45850,7 @@
         <v>FG-401565</v>
       </c>
       <c r="C1299" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2)</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2")</v>
       </c>
       <c r="D1299" t="str">
         <v>SMART SERIES 2 WAY BIB TAP</v>
@@ -45862,7 +45862,7 @@
         <v>General</v>
       </c>
       <c r="G1299" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1299" t="str">
         <v>NOS</v>
@@ -45882,13 +45882,13 @@
         <v>1299</v>
       </c>
       <c r="B1300" t="str">
-        <v>FG-401565</v>
+        <v>FG-401560</v>
       </c>
       <c r="C1300" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1300" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP</v>
       </c>
       <c r="E1300" t="str">
         <v>FAUCETS</v>
@@ -45897,19 +45897,19 @@
         <v>General</v>
       </c>
       <c r="G1300" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1300" t="str">
         <v>NOS</v>
       </c>
       <c r="I1300">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1300" t="str">
         <v>Active</v>
       </c>
       <c r="K1300" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1301">
@@ -45920,7 +45920,7 @@
         <v>FG-401560</v>
       </c>
       <c r="C1301" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1301" t="str">
         <v>REGULAR SERIES SHORT BODY BIB TAP</v>
@@ -45932,7 +45932,7 @@
         <v>General</v>
       </c>
       <c r="G1301" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1301" t="str">
         <v>NOS</v>
@@ -45955,7 +45955,7 @@
         <v>FG-401560</v>
       </c>
       <c r="C1302" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1302" t="str">
         <v>REGULAR SERIES SHORT BODY BIB TAP</v>
@@ -45967,7 +45967,7 @@
         <v>General</v>
       </c>
       <c r="G1302" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1302" t="str">
         <v>NOS</v>
@@ -45987,13 +45987,13 @@
         <v>1302</v>
       </c>
       <c r="B1303" t="str">
-        <v>FG-401560</v>
+        <v>FG-401559</v>
       </c>
       <c r="C1303" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1303" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP</v>
       </c>
       <c r="E1303" t="str">
         <v>FAUCETS</v>
@@ -46002,7 +46002,7 @@
         <v>General</v>
       </c>
       <c r="G1303" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1303" t="str">
         <v>NOS</v>
@@ -46014,7 +46014,7 @@
         <v>Active</v>
       </c>
       <c r="K1303" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1304">
@@ -46025,7 +46025,7 @@
         <v>FG-401559</v>
       </c>
       <c r="C1304" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1304" t="str">
         <v>REGULAR SERIES LONG BODY BIB TAP</v>
@@ -46037,7 +46037,7 @@
         <v>General</v>
       </c>
       <c r="G1304" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1304" t="str">
         <v>NOS</v>
@@ -46060,7 +46060,7 @@
         <v>FG-401559</v>
       </c>
       <c r="C1305" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1305" t="str">
         <v>REGULAR SERIES LONG BODY BIB TAP</v>
@@ -46072,7 +46072,7 @@
         <v>General</v>
       </c>
       <c r="G1305" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1305" t="str">
         <v>NOS</v>
@@ -46092,13 +46092,13 @@
         <v>1305</v>
       </c>
       <c r="B1306" t="str">
-        <v>FG-401559</v>
+        <v>FG-401554</v>
       </c>
       <c r="C1306" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1306" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP</v>
+        <v>REGULAR SERIES PILLAR TAP</v>
       </c>
       <c r="E1306" t="str">
         <v>FAUCETS</v>
@@ -46107,19 +46107,19 @@
         <v>General</v>
       </c>
       <c r="G1306" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1306" t="str">
         <v>NOS</v>
       </c>
       <c r="I1306">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1306" t="str">
         <v>Active</v>
       </c>
       <c r="K1306" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1307">
@@ -46130,7 +46130,7 @@
         <v>FG-401554</v>
       </c>
       <c r="C1307" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2 inch)</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1307" t="str">
         <v>REGULAR SERIES PILLAR TAP</v>
@@ -46142,7 +46142,7 @@
         <v>General</v>
       </c>
       <c r="G1307" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1307" t="str">
         <v>NOS</v>
@@ -46165,7 +46165,7 @@
         <v>FG-401554</v>
       </c>
       <c r="C1308" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2)</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1308" t="str">
         <v>REGULAR SERIES PILLAR TAP</v>
@@ -46177,7 +46177,7 @@
         <v>General</v>
       </c>
       <c r="G1308" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1308" t="str">
         <v>NOS</v>
@@ -46197,13 +46197,13 @@
         <v>1308</v>
       </c>
       <c r="B1309" t="str">
-        <v>FG-401554</v>
+        <v>FG-401555</v>
       </c>
       <c r="C1309" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2")</v>
+        <v>REGULAR SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1309" t="str">
-        <v>REGULAR SERIES PILLAR TAP</v>
+        <v>REGULAR SERIES SINK TAP</v>
       </c>
       <c r="E1309" t="str">
         <v>FAUCETS</v>
@@ -46212,7 +46212,7 @@
         <v>General</v>
       </c>
       <c r="G1309" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1309" t="str">
         <v>NOS</v>
@@ -46224,7 +46224,7 @@
         <v>Active</v>
       </c>
       <c r="K1309" t="str">
-        <v>REGULAR SERIES PILLAR TAP high quality faucet.</v>
+        <v>REGULAR SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1310">
@@ -46235,7 +46235,7 @@
         <v>FG-401555</v>
       </c>
       <c r="C1310" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2 inch)</v>
+        <v>REGULAR SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1310" t="str">
         <v>REGULAR SERIES SINK TAP</v>
@@ -46247,7 +46247,7 @@
         <v>General</v>
       </c>
       <c r="G1310" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1310" t="str">
         <v>NOS</v>
@@ -46270,7 +46270,7 @@
         <v>FG-401555</v>
       </c>
       <c r="C1311" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2)</v>
+        <v>REGULAR SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1311" t="str">
         <v>REGULAR SERIES SINK TAP</v>
@@ -46282,7 +46282,7 @@
         <v>General</v>
       </c>
       <c r="G1311" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1311" t="str">
         <v>NOS</v>
@@ -46302,13 +46302,13 @@
         <v>1311</v>
       </c>
       <c r="B1312" t="str">
-        <v>FG-401555</v>
+        <v>FG-401556</v>
       </c>
       <c r="C1312" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2")</v>
+        <v>REGULAR SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1312" t="str">
-        <v>REGULAR SERIES SINK TAP</v>
+        <v>REGULAR SERIES SWAN NECK</v>
       </c>
       <c r="E1312" t="str">
         <v>FAUCETS</v>
@@ -46317,7 +46317,7 @@
         <v>General</v>
       </c>
       <c r="G1312" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1312" t="str">
         <v>NOS</v>
@@ -46329,7 +46329,7 @@
         <v>Active</v>
       </c>
       <c r="K1312" t="str">
-        <v>REGULAR SERIES SINK TAP high quality faucet.</v>
+        <v>REGULAR SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1313">
@@ -46340,7 +46340,7 @@
         <v>FG-401556</v>
       </c>
       <c r="C1313" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2 inch)</v>
+        <v>REGULAR SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1313" t="str">
         <v>REGULAR SERIES SWAN NECK</v>
@@ -46352,7 +46352,7 @@
         <v>General</v>
       </c>
       <c r="G1313" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1313" t="str">
         <v>NOS</v>
@@ -46375,7 +46375,7 @@
         <v>FG-401556</v>
       </c>
       <c r="C1314" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2)</v>
+        <v>REGULAR SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1314" t="str">
         <v>REGULAR SERIES SWAN NECK</v>
@@ -46387,7 +46387,7 @@
         <v>General</v>
       </c>
       <c r="G1314" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1314" t="str">
         <v>NOS</v>
@@ -46407,13 +46407,13 @@
         <v>1314</v>
       </c>
       <c r="B1315" t="str">
-        <v>FG-401556</v>
+        <v>FG-401553</v>
       </c>
       <c r="C1315" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2")</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1315" t="str">
-        <v>REGULAR SERIES SWAN NECK</v>
+        <v>REGULAR SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1315" t="str">
         <v>FAUCETS</v>
@@ -46422,19 +46422,19 @@
         <v>General</v>
       </c>
       <c r="G1315" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1315" t="str">
         <v>NOS</v>
       </c>
       <c r="I1315">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1315" t="str">
         <v>Active</v>
       </c>
       <c r="K1315" t="str">
-        <v>REGULAR SERIES SWAN NECK high quality faucet.</v>
+        <v>REGULAR SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1316">
@@ -46445,7 +46445,7 @@
         <v>FG-401553</v>
       </c>
       <c r="C1316" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1316" t="str">
         <v>REGULAR SERIES ANGULAR VALVE</v>
@@ -46457,7 +46457,7 @@
         <v>General</v>
       </c>
       <c r="G1316" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1316" t="str">
         <v>NOS</v>
@@ -46480,7 +46480,7 @@
         <v>FG-401553</v>
       </c>
       <c r="C1317" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2)</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1317" t="str">
         <v>REGULAR SERIES ANGULAR VALVE</v>
@@ -46492,7 +46492,7 @@
         <v>General</v>
       </c>
       <c r="G1317" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1317" t="str">
         <v>NOS</v>
@@ -46512,13 +46512,13 @@
         <v>1317</v>
       </c>
       <c r="B1318" t="str">
-        <v>FG-401553</v>
+        <v>FG-401558</v>
       </c>
       <c r="C1318" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2")</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1318" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
       </c>
       <c r="E1318" t="str">
         <v>FAUCETS</v>
@@ -46527,19 +46527,19 @@
         <v>General</v>
       </c>
       <c r="G1318" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1318" t="str">
         <v>NOS</v>
       </c>
       <c r="I1318">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1318" t="str">
         <v>Active</v>
       </c>
       <c r="K1318" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1319">
@@ -46550,7 +46550,7 @@
         <v>FG-401558</v>
       </c>
       <c r="C1319" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1319" t="str">
         <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
@@ -46562,7 +46562,7 @@
         <v>General</v>
       </c>
       <c r="G1319" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1319" t="str">
         <v>NOS</v>
@@ -46585,7 +46585,7 @@
         <v>FG-401558</v>
       </c>
       <c r="C1320" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2)</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1320" t="str">
         <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
@@ -46597,7 +46597,7 @@
         <v>General</v>
       </c>
       <c r="G1320" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1320" t="str">
         <v>NOS</v>
@@ -46617,13 +46617,13 @@
         <v>1320</v>
       </c>
       <c r="B1321" t="str">
-        <v>FG-401558</v>
+        <v>FG-401557</v>
       </c>
       <c r="C1321" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2")</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1321" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP</v>
       </c>
       <c r="E1321" t="str">
         <v>FAUCETS</v>
@@ -46632,7 +46632,7 @@
         <v>General</v>
       </c>
       <c r="G1321" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1321" t="str">
         <v>NOS</v>
@@ -46644,7 +46644,7 @@
         <v>Active</v>
       </c>
       <c r="K1321" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1322">
@@ -46655,7 +46655,7 @@
         <v>FG-401557</v>
       </c>
       <c r="C1322" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2)</v>
       </c>
       <c r="D1322" t="str">
         <v>REGULAR SERIES 2 WAY BIB TAP</v>
@@ -46667,7 +46667,7 @@
         <v>General</v>
       </c>
       <c r="G1322" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1322" t="str">
         <v>NOS</v>
@@ -46690,7 +46690,7 @@
         <v>FG-401557</v>
       </c>
       <c r="C1323" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2")</v>
       </c>
       <c r="D1323" t="str">
         <v>REGULAR SERIES 2 WAY BIB TAP</v>
@@ -46702,7 +46702,7 @@
         <v>General</v>
       </c>
       <c r="G1323" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1323" t="str">
         <v>NOS</v>
@@ -46722,34 +46722,34 @@
         <v>1323</v>
       </c>
       <c r="B1324" t="str">
-        <v>FG-401557</v>
+        <v>FG-400836</v>
       </c>
       <c r="C1324" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2")</v>
+        <v>SINGLE SIDE HANDLE FLUSH 8L (8L)</v>
       </c>
       <c r="D1324" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP</v>
+        <v>SINGLE SIDE HANDLE FLUSH 8L</v>
       </c>
       <c r="E1324" t="str">
-        <v>FAUCETS</v>
+        <v>Toilet Seat Cover &amp; Flushing Cistern</v>
       </c>
       <c r="F1324" t="str">
         <v>General</v>
       </c>
       <c r="G1324" t="str">
-        <v>1/2"</v>
+        <v>8L</v>
       </c>
       <c r="H1324" t="str">
         <v>NOS</v>
       </c>
       <c r="I1324">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J1324" t="str">
         <v>Active</v>
       </c>
       <c r="K1324" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP high quality faucet.</v>
+        <v>8 Litre Single Side Handle Flushing Cistern.</v>
       </c>
     </row>
     <row r="1325">
@@ -46757,13 +46757,13 @@
         <v>1324</v>
       </c>
       <c r="B1325" t="str">
-        <v>FG-400836</v>
+        <v>FG-400837</v>
       </c>
       <c r="C1325" t="str">
-        <v>SINGLE SIDE HANDLE FLUSH 8L (8L)</v>
+        <v>CENTER SINGLE PUSH FLUSH 8L (8L)</v>
       </c>
       <c r="D1325" t="str">
-        <v>SINGLE SIDE HANDLE FLUSH 8L</v>
+        <v>CENTER SINGLE PUSH FLUSH 8L</v>
       </c>
       <c r="E1325" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46784,7 +46784,7 @@
         <v>Active</v>
       </c>
       <c r="K1325" t="str">
-        <v>8 Litre Single Side Handle Flushing Cistern.</v>
+        <v>8 Litre Center Single Push Flushing Cistern.</v>
       </c>
     </row>
     <row r="1326">
@@ -46792,13 +46792,13 @@
         <v>1325</v>
       </c>
       <c r="B1326" t="str">
-        <v>FG-400837</v>
+        <v>FG-400838</v>
       </c>
       <c r="C1326" t="str">
-        <v>CENTER SINGLE PUSH FLUSH 8L (8L)</v>
+        <v>DUAL FLUSH 10L (10L)</v>
       </c>
       <c r="D1326" t="str">
-        <v>CENTER SINGLE PUSH FLUSH 8L</v>
+        <v>DUAL FLUSH 10L</v>
       </c>
       <c r="E1326" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46807,7 +46807,7 @@
         <v>General</v>
       </c>
       <c r="G1326" t="str">
-        <v>8L</v>
+        <v>10L</v>
       </c>
       <c r="H1326" t="str">
         <v>NOS</v>
@@ -46819,7 +46819,7 @@
         <v>Active</v>
       </c>
       <c r="K1326" t="str">
-        <v>8 Litre Center Single Push Flushing Cistern.</v>
+        <v>10 Litre Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1327">
@@ -46827,13 +46827,13 @@
         <v>1326</v>
       </c>
       <c r="B1327" t="str">
-        <v>FG-400838</v>
+        <v>FG-400835</v>
       </c>
       <c r="C1327" t="str">
-        <v>DUAL FLUSH 10L (10L)</v>
+        <v>EWC SEAT COVER (WITH JET) (Standard)</v>
       </c>
       <c r="D1327" t="str">
-        <v>DUAL FLUSH 10L</v>
+        <v>EWC SEAT COVER (WITH JET)</v>
       </c>
       <c r="E1327" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46842,19 +46842,19 @@
         <v>General</v>
       </c>
       <c r="G1327" t="str">
-        <v>10L</v>
+        <v>Standard</v>
       </c>
       <c r="H1327" t="str">
         <v>NOS</v>
       </c>
       <c r="I1327">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J1327" t="str">
         <v>Active</v>
       </c>
       <c r="K1327" t="str">
-        <v>10 Litre Dual Flush Cistern.</v>
+        <v>EWC Toilet Seat Cover with integrated jet spray.</v>
       </c>
     </row>
     <row r="1328">
@@ -46862,13 +46862,13 @@
         <v>1327</v>
       </c>
       <c r="B1328" t="str">
-        <v>FG-400835</v>
+        <v>FG-400840</v>
       </c>
       <c r="C1328" t="str">
-        <v>EWC SEAT COVER (WITH JET) (Standard)</v>
+        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L) (10L)</v>
       </c>
       <c r="D1328" t="str">
-        <v>EWC SEAT COVER (WITH JET)</v>
+        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L)</v>
       </c>
       <c r="E1328" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46877,19 +46877,19 @@
         <v>General</v>
       </c>
       <c r="G1328" t="str">
-        <v>Standard</v>
+        <v>10L</v>
       </c>
       <c r="H1328" t="str">
         <v>NOS</v>
       </c>
       <c r="I1328">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J1328" t="str">
         <v>Active</v>
       </c>
       <c r="K1328" t="str">
-        <v>EWC Toilet Seat Cover with integrated jet spray.</v>
+        <v>10 Litre Premium Dual Colour Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1329">
@@ -46897,13 +46897,13 @@
         <v>1328</v>
       </c>
       <c r="B1329" t="str">
-        <v>FG-400840</v>
+        <v>FG-400839</v>
       </c>
       <c r="C1329" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L) (10L)</v>
+        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L) (10L)</v>
       </c>
       <c r="D1329" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L)</v>
+        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L)</v>
       </c>
       <c r="E1329" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46924,7 +46924,7 @@
         <v>Active</v>
       </c>
       <c r="K1329" t="str">
-        <v>10 Litre Premium Dual Colour Dual Flush Cistern.</v>
+        <v>10 Litre Economy Dual Colour Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1330">
@@ -46932,13 +46932,13 @@
         <v>1329</v>
       </c>
       <c r="B1330" t="str">
-        <v>FG-400839</v>
+        <v>FG-400834</v>
       </c>
       <c r="C1330" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L) (10L)</v>
+        <v>EWC SEAT COVER (WITHOUT JET) (Standard)</v>
       </c>
       <c r="D1330" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L)</v>
+        <v>EWC SEAT COVER (WITHOUT JET)</v>
       </c>
       <c r="E1330" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46947,59 +46947,24 @@
         <v>General</v>
       </c>
       <c r="G1330" t="str">
-        <v>10L</v>
+        <v>Standard</v>
       </c>
       <c r="H1330" t="str">
         <v>NOS</v>
       </c>
       <c r="I1330">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J1330" t="str">
         <v>Active</v>
       </c>
       <c r="K1330" t="str">
-        <v>10 Litre Economy Dual Colour Dual Flush Cistern.</v>
-      </c>
-    </row>
-    <row r="1331">
-      <c r="A1331">
-        <v>1330</v>
-      </c>
-      <c r="B1331" t="str">
-        <v>FG-400834</v>
-      </c>
-      <c r="C1331" t="str">
-        <v>EWC SEAT COVER (WITHOUT JET) (Standard)</v>
-      </c>
-      <c r="D1331" t="str">
-        <v>EWC SEAT COVER (WITHOUT JET)</v>
-      </c>
-      <c r="E1331" t="str">
-        <v>Toilet Seat Cover &amp; Flushing Cistern</v>
-      </c>
-      <c r="F1331" t="str">
-        <v>General</v>
-      </c>
-      <c r="G1331" t="str">
-        <v>Standard</v>
-      </c>
-      <c r="H1331" t="str">
-        <v>NOS</v>
-      </c>
-      <c r="I1331">
-        <v>20</v>
-      </c>
-      <c r="J1331" t="str">
-        <v>Active</v>
-      </c>
-      <c r="K1331" t="str">
         <v>EWC Toilet Seat Cover without jet spray.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K1331"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K1330"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
+++ b/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1330"/>
+  <dimension ref="A1:K1331"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -35732,10 +35732,10 @@
         <v>1009</v>
       </c>
       <c r="B1010" t="str">
-        <v>-</v>
+        <v>FG-400679</v>
       </c>
       <c r="C1010" t="str">
-        <v>AGRI UNION 10KG</v>
+        <v>AGRI UNION 10KG (25MM)</v>
       </c>
       <c r="D1010" t="str">
         <v>AGRI UNION 10KG</v>
@@ -35747,19 +35747,19 @@
         <v>General</v>
       </c>
       <c r="G1010" t="str">
-        <v>Standard</v>
+        <v>25MM</v>
       </c>
       <c r="H1010" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1010" t="str">
-        <v>-</v>
+      <c r="I1010">
+        <v>180</v>
       </c>
       <c r="J1010" t="str">
         <v>Active</v>
       </c>
       <c r="K1010" t="str">
-        <v>AGRI UNION 10KG.</v>
+        <v>AGRI UNION 10KG. Available sizes: 25MM, 32MM.</v>
       </c>
     </row>
     <row r="1011">
@@ -35767,13 +35767,13 @@
         <v>1010</v>
       </c>
       <c r="B1011" t="str">
-        <v>-</v>
+        <v>FG-400680</v>
       </c>
       <c r="C1011" t="str">
-        <v>PN10 - TEE ISI (25MM)</v>
+        <v>AGRI UNION 10KG (32MM)</v>
       </c>
       <c r="D1011" t="str">
-        <v>PN10 - TEE ISI</v>
+        <v>AGRI UNION 10KG</v>
       </c>
       <c r="E1011" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35782,19 +35782,19 @@
         <v>General</v>
       </c>
       <c r="G1011" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1011" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1011" t="str">
-        <v>-</v>
+      <c r="I1011">
+        <v>100</v>
       </c>
       <c r="J1011" t="str">
         <v>Active</v>
       </c>
       <c r="K1011" t="str">
-        <v>PN10 - TEE ISI for agriculture irrigation and piping systems.</v>
+        <v>AGRI UNION 10KG. Available sizes: 25MM, 32MM.</v>
       </c>
     </row>
     <row r="1012">
@@ -35805,7 +35805,7 @@
         <v>-</v>
       </c>
       <c r="C1012" t="str">
-        <v>PN10 - TEE ISI (32MM)</v>
+        <v>PN10 - TEE ISI (25MM)</v>
       </c>
       <c r="D1012" t="str">
         <v>PN10 - TEE ISI</v>
@@ -35817,7 +35817,7 @@
         <v>General</v>
       </c>
       <c r="G1012" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1012" t="str">
         <v>BOX</v>
@@ -35840,10 +35840,10 @@
         <v>-</v>
       </c>
       <c r="C1013" t="str">
-        <v>PN10 - COUPLER ISI (25MM)</v>
+        <v>PN10 - TEE ISI (32MM)</v>
       </c>
       <c r="D1013" t="str">
-        <v>PN10 - COUPLER ISI</v>
+        <v>PN10 - TEE ISI</v>
       </c>
       <c r="E1013" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35852,7 +35852,7 @@
         <v>General</v>
       </c>
       <c r="G1013" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1013" t="str">
         <v>BOX</v>
@@ -35864,7 +35864,7 @@
         <v>Active</v>
       </c>
       <c r="K1013" t="str">
-        <v>PN10 - COUPLER ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - TEE ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1014">
@@ -35875,7 +35875,7 @@
         <v>-</v>
       </c>
       <c r="C1014" t="str">
-        <v>PN10 - COUPLER ISI (32MM)</v>
+        <v>PN10 - COUPLER ISI (25MM)</v>
       </c>
       <c r="D1014" t="str">
         <v>PN10 - COUPLER ISI</v>
@@ -35887,7 +35887,7 @@
         <v>General</v>
       </c>
       <c r="G1014" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1014" t="str">
         <v>BOX</v>
@@ -35910,10 +35910,10 @@
         <v>-</v>
       </c>
       <c r="C1015" t="str">
-        <v>PN10 - MTA ISI (25MM)</v>
+        <v>PN10 - COUPLER ISI (32MM)</v>
       </c>
       <c r="D1015" t="str">
-        <v>PN10 - MTA ISI</v>
+        <v>PN10 - COUPLER ISI</v>
       </c>
       <c r="E1015" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35922,7 +35922,7 @@
         <v>General</v>
       </c>
       <c r="G1015" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1015" t="str">
         <v>BOX</v>
@@ -35934,7 +35934,7 @@
         <v>Active</v>
       </c>
       <c r="K1015" t="str">
-        <v>PN10 - MTA ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - COUPLER ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1016">
@@ -35945,7 +35945,7 @@
         <v>-</v>
       </c>
       <c r="C1016" t="str">
-        <v>PN10 - MTA ISI (32MM)</v>
+        <v>PN10 - MTA ISI (25MM)</v>
       </c>
       <c r="D1016" t="str">
         <v>PN10 - MTA ISI</v>
@@ -35957,7 +35957,7 @@
         <v>General</v>
       </c>
       <c r="G1016" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1016" t="str">
         <v>BOX</v>
@@ -35980,10 +35980,10 @@
         <v>-</v>
       </c>
       <c r="C1017" t="str">
-        <v>PN10 - FTA ISI (25MM)</v>
+        <v>PN10 - MTA ISI (32MM)</v>
       </c>
       <c r="D1017" t="str">
-        <v>PN10 - FTA ISI</v>
+        <v>PN10 - MTA ISI</v>
       </c>
       <c r="E1017" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35992,7 +35992,7 @@
         <v>General</v>
       </c>
       <c r="G1017" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1017" t="str">
         <v>BOX</v>
@@ -36004,7 +36004,7 @@
         <v>Active</v>
       </c>
       <c r="K1017" t="str">
-        <v>PN10 - FTA ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - MTA ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1018">
@@ -36015,7 +36015,7 @@
         <v>-</v>
       </c>
       <c r="C1018" t="str">
-        <v>PN10 - FTA ISI (32MM)</v>
+        <v>PN10 - FTA ISI (25MM)</v>
       </c>
       <c r="D1018" t="str">
         <v>PN10 - FTA ISI</v>
@@ -36027,7 +36027,7 @@
         <v>General</v>
       </c>
       <c r="G1018" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1018" t="str">
         <v>BOX</v>
@@ -36050,10 +36050,10 @@
         <v>-</v>
       </c>
       <c r="C1019" t="str">
-        <v>PN10 - END CAP ISI (25MM)</v>
+        <v>PN10 - FTA ISI (32MM)</v>
       </c>
       <c r="D1019" t="str">
-        <v>PN10 - END CAP ISI</v>
+        <v>PN10 - FTA ISI</v>
       </c>
       <c r="E1019" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36062,7 +36062,7 @@
         <v>General</v>
       </c>
       <c r="G1019" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1019" t="str">
         <v>BOX</v>
@@ -36074,7 +36074,7 @@
         <v>Active</v>
       </c>
       <c r="K1019" t="str">
-        <v>PN10 - END CAP ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - FTA ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1020">
@@ -36085,7 +36085,7 @@
         <v>-</v>
       </c>
       <c r="C1020" t="str">
-        <v>PN10 - END CAP ISI (32MM)</v>
+        <v>PN10 - END CAP ISI (25MM)</v>
       </c>
       <c r="D1020" t="str">
         <v>PN10 - END CAP ISI</v>
@@ -36097,7 +36097,7 @@
         <v>General</v>
       </c>
       <c r="G1020" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1020" t="str">
         <v>BOX</v>
@@ -36120,10 +36120,10 @@
         <v>-</v>
       </c>
       <c r="C1021" t="str">
-        <v>PN10 - REDUCING BUSH ISI (32 X 20)</v>
+        <v>PN10 - END CAP ISI (32MM)</v>
       </c>
       <c r="D1021" t="str">
-        <v>PN10 - REDUCING BUSH ISI</v>
+        <v>PN10 - END CAP ISI</v>
       </c>
       <c r="E1021" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36132,7 +36132,7 @@
         <v>General</v>
       </c>
       <c r="G1021" t="str">
-        <v>32 X 20</v>
+        <v>32MM</v>
       </c>
       <c r="H1021" t="str">
         <v>BOX</v>
@@ -36144,7 +36144,7 @@
         <v>Active</v>
       </c>
       <c r="K1021" t="str">
-        <v>PN10 - REDUCING BUSH ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - END CAP ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1022">
@@ -36155,7 +36155,7 @@
         <v>-</v>
       </c>
       <c r="C1022" t="str">
-        <v>PN10 - REDUCING BUSH ISI (32 X 25)</v>
+        <v>PN10 - REDUCING BUSH ISI (32 X 20)</v>
       </c>
       <c r="D1022" t="str">
         <v>PN10 - REDUCING BUSH ISI</v>
@@ -36167,7 +36167,7 @@
         <v>General</v>
       </c>
       <c r="G1022" t="str">
-        <v>32 X 25</v>
+        <v>32 X 20</v>
       </c>
       <c r="H1022" t="str">
         <v>BOX</v>
@@ -36187,13 +36187,13 @@
         <v>1022</v>
       </c>
       <c r="B1023" t="str">
-        <v>FG-400585</v>
+        <v>-</v>
       </c>
       <c r="C1023" t="str">
-        <v>AGRI REDUCER (50X40MM)</v>
+        <v>PN10 - REDUCING BUSH ISI (32 X 25)</v>
       </c>
       <c r="D1023" t="str">
-        <v>AGRI REDUCER</v>
+        <v>PN10 - REDUCING BUSH ISI</v>
       </c>
       <c r="E1023" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36202,19 +36202,19 @@
         <v>General</v>
       </c>
       <c r="G1023" t="str">
-        <v>50X40MM</v>
+        <v>32 X 25</v>
       </c>
       <c r="H1023" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1023">
-        <v>300</v>
+      <c r="I1023" t="str">
+        <v>-</v>
       </c>
       <c r="J1023" t="str">
         <v>Active</v>
       </c>
       <c r="K1023" t="str">
-        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
+        <v>PN10 - REDUCING BUSH ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1024">
@@ -36222,10 +36222,10 @@
         <v>1023</v>
       </c>
       <c r="B1024" t="str">
-        <v>FG-400584</v>
+        <v>FG-400585</v>
       </c>
       <c r="C1024" t="str">
-        <v>AGRI REDUCER (63X40MM)</v>
+        <v>AGRI REDUCER (50X40MM)</v>
       </c>
       <c r="D1024" t="str">
         <v>AGRI REDUCER</v>
@@ -36237,13 +36237,13 @@
         <v>General</v>
       </c>
       <c r="G1024" t="str">
-        <v>63X40MM</v>
+        <v>50X40MM</v>
       </c>
       <c r="H1024" t="str">
         <v>BOX</v>
       </c>
       <c r="I1024">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J1024" t="str">
         <v>Active</v>
@@ -36257,10 +36257,10 @@
         <v>1024</v>
       </c>
       <c r="B1025" t="str">
-        <v>FG-400583</v>
+        <v>FG-400584</v>
       </c>
       <c r="C1025" t="str">
-        <v>AGRI REDUCER (63X50MM)</v>
+        <v>AGRI REDUCER (63X40MM)</v>
       </c>
       <c r="D1025" t="str">
         <v>AGRI REDUCER</v>
@@ -36272,13 +36272,13 @@
         <v>General</v>
       </c>
       <c r="G1025" t="str">
-        <v>63X50MM</v>
+        <v>63X40MM</v>
       </c>
       <c r="H1025" t="str">
         <v>BOX</v>
       </c>
       <c r="I1025">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="J1025" t="str">
         <v>Active</v>
@@ -36292,10 +36292,10 @@
         <v>1025</v>
       </c>
       <c r="B1026" t="str">
-        <v>FG-400582</v>
+        <v>FG-400583</v>
       </c>
       <c r="C1026" t="str">
-        <v>AGRI REDUCER (75X40MM)</v>
+        <v>AGRI REDUCER (63X50MM)</v>
       </c>
       <c r="D1026" t="str">
         <v>AGRI REDUCER</v>
@@ -36307,13 +36307,13 @@
         <v>General</v>
       </c>
       <c r="G1026" t="str">
-        <v>75X40MM</v>
+        <v>63X50MM</v>
       </c>
       <c r="H1026" t="str">
         <v>BOX</v>
       </c>
       <c r="I1026">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J1026" t="str">
         <v>Active</v>
@@ -36327,10 +36327,10 @@
         <v>1026</v>
       </c>
       <c r="B1027" t="str">
-        <v>FG-400581</v>
+        <v>FG-400582</v>
       </c>
       <c r="C1027" t="str">
-        <v>AGRI REDUCER (75X50MM)</v>
+        <v>AGRI REDUCER (75X40MM)</v>
       </c>
       <c r="D1027" t="str">
         <v>AGRI REDUCER</v>
@@ -36342,13 +36342,13 @@
         <v>General</v>
       </c>
       <c r="G1027" t="str">
-        <v>75X50MM</v>
+        <v>75X40MM</v>
       </c>
       <c r="H1027" t="str">
         <v>BOX</v>
       </c>
       <c r="I1027">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J1027" t="str">
         <v>Active</v>
@@ -36362,10 +36362,10 @@
         <v>1027</v>
       </c>
       <c r="B1028" t="str">
-        <v>FG-400580</v>
+        <v>FG-400581</v>
       </c>
       <c r="C1028" t="str">
-        <v>AGRI REDUCER (75X63MM)</v>
+        <v>AGRI REDUCER (75X50MM)</v>
       </c>
       <c r="D1028" t="str">
         <v>AGRI REDUCER</v>
@@ -36377,13 +36377,13 @@
         <v>General</v>
       </c>
       <c r="G1028" t="str">
-        <v>75X63MM</v>
+        <v>75X50MM</v>
       </c>
       <c r="H1028" t="str">
         <v>BOX</v>
       </c>
       <c r="I1028">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J1028" t="str">
         <v>Active</v>
@@ -36397,10 +36397,10 @@
         <v>1028</v>
       </c>
       <c r="B1029" t="str">
-        <v>FG-400579</v>
+        <v>FG-400580</v>
       </c>
       <c r="C1029" t="str">
-        <v>AGRI REDUCER (90X50MM)</v>
+        <v>AGRI REDUCER (75X63MM)</v>
       </c>
       <c r="D1029" t="str">
         <v>AGRI REDUCER</v>
@@ -36412,13 +36412,13 @@
         <v>General</v>
       </c>
       <c r="G1029" t="str">
-        <v>90X50MM</v>
+        <v>75X63MM</v>
       </c>
       <c r="H1029" t="str">
         <v>BOX</v>
       </c>
       <c r="I1029">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J1029" t="str">
         <v>Active</v>
@@ -36432,10 +36432,10 @@
         <v>1029</v>
       </c>
       <c r="B1030" t="str">
-        <v>FG-400578</v>
+        <v>FG-400579</v>
       </c>
       <c r="C1030" t="str">
-        <v>AGRI REDUCER (90X63MM)</v>
+        <v>AGRI REDUCER (90X50MM)</v>
       </c>
       <c r="D1030" t="str">
         <v>AGRI REDUCER</v>
@@ -36447,13 +36447,13 @@
         <v>General</v>
       </c>
       <c r="G1030" t="str">
-        <v>90X63MM</v>
+        <v>90X50MM</v>
       </c>
       <c r="H1030" t="str">
         <v>BOX</v>
       </c>
       <c r="I1030">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J1030" t="str">
         <v>Active</v>
@@ -36467,10 +36467,10 @@
         <v>1030</v>
       </c>
       <c r="B1031" t="str">
-        <v>FG-400577</v>
+        <v>FG-400578</v>
       </c>
       <c r="C1031" t="str">
-        <v>AGRI REDUCER (90X75MM)</v>
+        <v>AGRI REDUCER (90X63MM)</v>
       </c>
       <c r="D1031" t="str">
         <v>AGRI REDUCER</v>
@@ -36482,13 +36482,13 @@
         <v>General</v>
       </c>
       <c r="G1031" t="str">
-        <v>90X75MM</v>
+        <v>90X63MM</v>
       </c>
       <c r="H1031" t="str">
         <v>BOX</v>
       </c>
       <c r="I1031">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J1031" t="str">
         <v>Active</v>
@@ -36502,10 +36502,10 @@
         <v>1031</v>
       </c>
       <c r="B1032" t="str">
-        <v>FG-400576</v>
+        <v>FG-400577</v>
       </c>
       <c r="C1032" t="str">
-        <v>AGRI REDUCER (110X63MM)</v>
+        <v>AGRI REDUCER (90X75MM)</v>
       </c>
       <c r="D1032" t="str">
         <v>AGRI REDUCER</v>
@@ -36517,13 +36517,13 @@
         <v>General</v>
       </c>
       <c r="G1032" t="str">
-        <v>110X63MM</v>
+        <v>90X75MM</v>
       </c>
       <c r="H1032" t="str">
         <v>BOX</v>
       </c>
       <c r="I1032">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J1032" t="str">
         <v>Active</v>
@@ -36537,10 +36537,10 @@
         <v>1032</v>
       </c>
       <c r="B1033" t="str">
-        <v>FG-400575</v>
+        <v>FG-400576</v>
       </c>
       <c r="C1033" t="str">
-        <v>AGRI REDUCER (110X75MM)</v>
+        <v>AGRI REDUCER (110X63MM)</v>
       </c>
       <c r="D1033" t="str">
         <v>AGRI REDUCER</v>
@@ -36552,7 +36552,7 @@
         <v>General</v>
       </c>
       <c r="G1033" t="str">
-        <v>110X75MM</v>
+        <v>110X63MM</v>
       </c>
       <c r="H1033" t="str">
         <v>BOX</v>
@@ -36572,10 +36572,10 @@
         <v>1033</v>
       </c>
       <c r="B1034" t="str">
-        <v>FG-400574</v>
+        <v>FG-400575</v>
       </c>
       <c r="C1034" t="str">
-        <v>AGRI REDUCER (110X90MM)</v>
+        <v>AGRI REDUCER (110X75MM)</v>
       </c>
       <c r="D1034" t="str">
         <v>AGRI REDUCER</v>
@@ -36587,13 +36587,13 @@
         <v>General</v>
       </c>
       <c r="G1034" t="str">
-        <v>110X90MM</v>
+        <v>110X75MM</v>
       </c>
       <c r="H1034" t="str">
         <v>BOX</v>
       </c>
       <c r="I1034">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J1034" t="str">
         <v>Active</v>
@@ -36607,13 +36607,13 @@
         <v>1034</v>
       </c>
       <c r="B1035" t="str">
-        <v>-</v>
+        <v>FG-400574</v>
       </c>
       <c r="C1035" t="str">
-        <v>REDUCING BUSH (LW) (63 X 40)</v>
+        <v>AGRI REDUCER (110X90MM)</v>
       </c>
       <c r="D1035" t="str">
-        <v>REDUCING BUSH (LW)</v>
+        <v>AGRI REDUCER</v>
       </c>
       <c r="E1035" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36622,19 +36622,19 @@
         <v>General</v>
       </c>
       <c r="G1035" t="str">
-        <v>63 X 40</v>
+        <v>110X90MM</v>
       </c>
       <c r="H1035" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1035" t="str">
-        <v>-</v>
+      <c r="I1035">
+        <v>40</v>
       </c>
       <c r="J1035" t="str">
         <v>Active</v>
       </c>
       <c r="K1035" t="str">
-        <v>REDUCING BUSH (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
       </c>
     </row>
     <row r="1036">
@@ -36645,7 +36645,7 @@
         <v>-</v>
       </c>
       <c r="C1036" t="str">
-        <v>REDUCING BUSH (LW) (63 X 50)</v>
+        <v>REDUCING BUSH (LW) (63 X 40)</v>
       </c>
       <c r="D1036" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36657,7 +36657,7 @@
         <v>General</v>
       </c>
       <c r="G1036" t="str">
-        <v>63 X 50</v>
+        <v>63 X 40</v>
       </c>
       <c r="H1036" t="str">
         <v>BOX</v>
@@ -36680,7 +36680,7 @@
         <v>-</v>
       </c>
       <c r="C1037" t="str">
-        <v>REDUCING BUSH (LW) (75 X 40)</v>
+        <v>REDUCING BUSH (LW) (63 X 50)</v>
       </c>
       <c r="D1037" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36692,7 +36692,7 @@
         <v>General</v>
       </c>
       <c r="G1037" t="str">
-        <v>75 X 40</v>
+        <v>63 X 50</v>
       </c>
       <c r="H1037" t="str">
         <v>BOX</v>
@@ -36715,7 +36715,7 @@
         <v>-</v>
       </c>
       <c r="C1038" t="str">
-        <v>REDUCING BUSH (LW) (75 X 63)</v>
+        <v>REDUCING BUSH (LW) (75 X 40)</v>
       </c>
       <c r="D1038" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36727,7 +36727,7 @@
         <v>General</v>
       </c>
       <c r="G1038" t="str">
-        <v>75 X 63</v>
+        <v>75 X 40</v>
       </c>
       <c r="H1038" t="str">
         <v>BOX</v>
@@ -36750,7 +36750,7 @@
         <v>-</v>
       </c>
       <c r="C1039" t="str">
-        <v>REDUCING BUSH (LW) (90 X 50)</v>
+        <v>REDUCING BUSH (LW) (75 X 63)</v>
       </c>
       <c r="D1039" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36762,7 +36762,7 @@
         <v>General</v>
       </c>
       <c r="G1039" t="str">
-        <v>90 X 50</v>
+        <v>75 X 63</v>
       </c>
       <c r="H1039" t="str">
         <v>BOX</v>
@@ -36785,7 +36785,7 @@
         <v>-</v>
       </c>
       <c r="C1040" t="str">
-        <v>REDUCING BUSH (LW) (90 X 63)</v>
+        <v>REDUCING BUSH (LW) (90 X 50)</v>
       </c>
       <c r="D1040" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36797,7 +36797,7 @@
         <v>General</v>
       </c>
       <c r="G1040" t="str">
-        <v>90 X 63</v>
+        <v>90 X 50</v>
       </c>
       <c r="H1040" t="str">
         <v>BOX</v>
@@ -36820,7 +36820,7 @@
         <v>-</v>
       </c>
       <c r="C1041" t="str">
-        <v>REDUCING BUSH (LW) (90 X 75)</v>
+        <v>REDUCING BUSH (LW) (90 X 63)</v>
       </c>
       <c r="D1041" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36832,7 +36832,7 @@
         <v>General</v>
       </c>
       <c r="G1041" t="str">
-        <v>90 X 75</v>
+        <v>90 X 63</v>
       </c>
       <c r="H1041" t="str">
         <v>BOX</v>
@@ -36855,7 +36855,7 @@
         <v>-</v>
       </c>
       <c r="C1042" t="str">
-        <v>REDUCING BUSH (LW) (110 X 63)</v>
+        <v>REDUCING BUSH (LW) (90 X 75)</v>
       </c>
       <c r="D1042" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36867,7 +36867,7 @@
         <v>General</v>
       </c>
       <c r="G1042" t="str">
-        <v>110 X 63</v>
+        <v>90 X 75</v>
       </c>
       <c r="H1042" t="str">
         <v>BOX</v>
@@ -36890,7 +36890,7 @@
         <v>-</v>
       </c>
       <c r="C1043" t="str">
-        <v>REDUCING BUSH (LW) (110 X 75)</v>
+        <v>REDUCING BUSH (LW) (110 X 63)</v>
       </c>
       <c r="D1043" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36902,7 +36902,7 @@
         <v>General</v>
       </c>
       <c r="G1043" t="str">
-        <v>110 X 75</v>
+        <v>110 X 63</v>
       </c>
       <c r="H1043" t="str">
         <v>BOX</v>
@@ -36925,7 +36925,7 @@
         <v>-</v>
       </c>
       <c r="C1044" t="str">
-        <v>REDUCING BUSH (LW) (110 X 90)</v>
+        <v>REDUCING BUSH (LW) (110 X 75)</v>
       </c>
       <c r="D1044" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36937,7 +36937,7 @@
         <v>General</v>
       </c>
       <c r="G1044" t="str">
-        <v>110 X 90</v>
+        <v>110 X 75</v>
       </c>
       <c r="H1044" t="str">
         <v>BOX</v>
@@ -36957,13 +36957,13 @@
         <v>1044</v>
       </c>
       <c r="B1045" t="str">
-        <v>FG-400550</v>
+        <v>-</v>
       </c>
       <c r="C1045" t="str">
-        <v>AGRI TEE (40MM)</v>
+        <v>REDUCING BUSH (LW) (110 X 90)</v>
       </c>
       <c r="D1045" t="str">
-        <v>AGRI TEE</v>
+        <v>REDUCING BUSH (LW)</v>
       </c>
       <c r="E1045" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36972,19 +36972,19 @@
         <v>General</v>
       </c>
       <c r="G1045" t="str">
-        <v>40MM</v>
+        <v>110 X 90</v>
       </c>
       <c r="H1045" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1045">
-        <v>150</v>
+      <c r="I1045" t="str">
+        <v>-</v>
       </c>
       <c r="J1045" t="str">
         <v>Active</v>
       </c>
       <c r="K1045" t="str">
-        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
+        <v>REDUCING BUSH (LW) for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1046">
@@ -36992,10 +36992,10 @@
         <v>1045</v>
       </c>
       <c r="B1046" t="str">
-        <v>FG-400551</v>
+        <v>FG-400550</v>
       </c>
       <c r="C1046" t="str">
-        <v>AGRI TEE (50MM)</v>
+        <v>AGRI TEE (40MM)</v>
       </c>
       <c r="D1046" t="str">
         <v>AGRI TEE</v>
@@ -37007,13 +37007,13 @@
         <v>General</v>
       </c>
       <c r="G1046" t="str">
-        <v>50MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1046" t="str">
         <v>BOX</v>
       </c>
       <c r="I1046">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J1046" t="str">
         <v>Active</v>
@@ -37027,10 +37027,10 @@
         <v>1046</v>
       </c>
       <c r="B1047" t="str">
-        <v>FG-400552</v>
+        <v>FG-400551</v>
       </c>
       <c r="C1047" t="str">
-        <v>AGRI TEE (63MM)</v>
+        <v>AGRI TEE (50MM)</v>
       </c>
       <c r="D1047" t="str">
         <v>AGRI TEE</v>
@@ -37042,13 +37042,13 @@
         <v>General</v>
       </c>
       <c r="G1047" t="str">
-        <v>63MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1047" t="str">
         <v>BOX</v>
       </c>
       <c r="I1047">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="J1047" t="str">
         <v>Active</v>
@@ -37062,10 +37062,10 @@
         <v>1047</v>
       </c>
       <c r="B1048" t="str">
-        <v>FG-400553</v>
+        <v>FG-400552</v>
       </c>
       <c r="C1048" t="str">
-        <v>AGRI TEE (75MM)</v>
+        <v>AGRI TEE (63MM)</v>
       </c>
       <c r="D1048" t="str">
         <v>AGRI TEE</v>
@@ -37077,13 +37077,13 @@
         <v>General</v>
       </c>
       <c r="G1048" t="str">
-        <v>75MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1048" t="str">
         <v>BOX</v>
       </c>
       <c r="I1048">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="J1048" t="str">
         <v>Active</v>
@@ -37097,10 +37097,10 @@
         <v>1048</v>
       </c>
       <c r="B1049" t="str">
-        <v>FG-400554</v>
+        <v>FG-400553</v>
       </c>
       <c r="C1049" t="str">
-        <v>AGRI TEE (90MM)</v>
+        <v>AGRI TEE (75MM)</v>
       </c>
       <c r="D1049" t="str">
         <v>AGRI TEE</v>
@@ -37112,13 +37112,13 @@
         <v>General</v>
       </c>
       <c r="G1049" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1049" t="str">
         <v>BOX</v>
       </c>
       <c r="I1049">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J1049" t="str">
         <v>Active</v>
@@ -37132,10 +37132,10 @@
         <v>1049</v>
       </c>
       <c r="B1050" t="str">
-        <v>FG-400586</v>
+        <v>FG-400554</v>
       </c>
       <c r="C1050" t="str">
-        <v>AGRI TEE (110MM)</v>
+        <v>AGRI TEE (90MM)</v>
       </c>
       <c r="D1050" t="str">
         <v>AGRI TEE</v>
@@ -37147,13 +37147,13 @@
         <v>General</v>
       </c>
       <c r="G1050" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1050" t="str">
         <v>BOX</v>
       </c>
       <c r="I1050">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J1050" t="str">
         <v>Active</v>
@@ -37167,10 +37167,10 @@
         <v>1050</v>
       </c>
       <c r="B1051" t="str">
-        <v>FG-400607</v>
+        <v>FG-400586</v>
       </c>
       <c r="C1051" t="str">
-        <v>AGRI TEE (140MM)</v>
+        <v>AGRI TEE (110MM)</v>
       </c>
       <c r="D1051" t="str">
         <v>AGRI TEE</v>
@@ -37182,13 +37182,13 @@
         <v>General</v>
       </c>
       <c r="G1051" t="str">
-        <v>140MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1051" t="str">
         <v>BOX</v>
       </c>
       <c r="I1051">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="J1051" t="str">
         <v>Active</v>
@@ -37202,10 +37202,10 @@
         <v>1051</v>
       </c>
       <c r="B1052" t="str">
-        <v>FG-400608</v>
+        <v>FG-400607</v>
       </c>
       <c r="C1052" t="str">
-        <v>AGRI TEE (160MM)</v>
+        <v>AGRI TEE (140MM)</v>
       </c>
       <c r="D1052" t="str">
         <v>AGRI TEE</v>
@@ -37217,13 +37217,13 @@
         <v>General</v>
       </c>
       <c r="G1052" t="str">
-        <v>160MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1052" t="str">
         <v>BOX</v>
       </c>
       <c r="I1052">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J1052" t="str">
         <v>Active</v>
@@ -37237,13 +37237,13 @@
         <v>1052</v>
       </c>
       <c r="B1053" t="str">
-        <v>-</v>
+        <v>FG-400608</v>
       </c>
       <c r="C1053" t="str">
-        <v>COUPLER (LW) (75MM)</v>
+        <v>AGRI TEE (160MM)</v>
       </c>
       <c r="D1053" t="str">
-        <v>COUPLER (LW)</v>
+        <v>AGRI TEE</v>
       </c>
       <c r="E1053" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37252,19 +37252,19 @@
         <v>General</v>
       </c>
       <c r="G1053" t="str">
-        <v>75MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1053" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1053" t="str">
-        <v>-</v>
+      <c r="I1053">
+        <v>9</v>
       </c>
       <c r="J1053" t="str">
         <v>Active</v>
       </c>
       <c r="K1053" t="str">
-        <v>COUPLER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1054">
@@ -37275,7 +37275,7 @@
         <v>-</v>
       </c>
       <c r="C1054" t="str">
-        <v>COUPLER (LW) (90MM)</v>
+        <v>COUPLER (LW) (75MM)</v>
       </c>
       <c r="D1054" t="str">
         <v>COUPLER (LW)</v>
@@ -37287,7 +37287,7 @@
         <v>General</v>
       </c>
       <c r="G1054" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1054" t="str">
         <v>BOX</v>
@@ -37310,7 +37310,7 @@
         <v>-</v>
       </c>
       <c r="C1055" t="str">
-        <v>COUPLER (LW) (110MM)</v>
+        <v>COUPLER (LW) (90MM)</v>
       </c>
       <c r="D1055" t="str">
         <v>COUPLER (LW)</v>
@@ -37322,7 +37322,7 @@
         <v>General</v>
       </c>
       <c r="G1055" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1055" t="str">
         <v>BOX</v>
@@ -37342,13 +37342,13 @@
         <v>1055</v>
       </c>
       <c r="B1056" t="str">
-        <v>FG-400561</v>
+        <v>-</v>
       </c>
       <c r="C1056" t="str">
-        <v>AGRI FABRICATED COUPLER (40MM)</v>
+        <v>COUPLER (LW) (110MM)</v>
       </c>
       <c r="D1056" t="str">
-        <v>AGRI FABRICATED COUPLER</v>
+        <v>COUPLER (LW)</v>
       </c>
       <c r="E1056" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37357,19 +37357,19 @@
         <v>General</v>
       </c>
       <c r="G1056" t="str">
-        <v>40MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1056" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1056">
-        <v>300</v>
+      <c r="I1056" t="str">
+        <v>-</v>
       </c>
       <c r="J1056" t="str">
         <v>Active</v>
       </c>
       <c r="K1056" t="str">
-        <v>AGRI FABRICATED COUPLER for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
+        <v>COUPLER (LW) for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1057">
@@ -37377,10 +37377,10 @@
         <v>1056</v>
       </c>
       <c r="B1057" t="str">
-        <v>FG-400562</v>
+        <v>FG-400561</v>
       </c>
       <c r="C1057" t="str">
-        <v>AGRI FABRICATED COUPLER (50MM)</v>
+        <v>AGRI FABRICATED COUPLER (40MM)</v>
       </c>
       <c r="D1057" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37392,13 +37392,13 @@
         <v>General</v>
       </c>
       <c r="G1057" t="str">
-        <v>50MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1057" t="str">
         <v>BOX</v>
       </c>
       <c r="I1057">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J1057" t="str">
         <v>Active</v>
@@ -37412,10 +37412,10 @@
         <v>1057</v>
       </c>
       <c r="B1058" t="str">
-        <v>FG-400563</v>
+        <v>FG-400562</v>
       </c>
       <c r="C1058" t="str">
-        <v>AGRI FABRICATED COUPLER (63MM)</v>
+        <v>AGRI FABRICATED COUPLER (50MM)</v>
       </c>
       <c r="D1058" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37427,7 +37427,7 @@
         <v>General</v>
       </c>
       <c r="G1058" t="str">
-        <v>63MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1058" t="str">
         <v>BOX</v>
@@ -37447,10 +37447,10 @@
         <v>1058</v>
       </c>
       <c r="B1059" t="str">
-        <v>FG-400564</v>
+        <v>FG-400563</v>
       </c>
       <c r="C1059" t="str">
-        <v>AGRI FABRICATED COUPLER (75MM)</v>
+        <v>AGRI FABRICATED COUPLER (63MM)</v>
       </c>
       <c r="D1059" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37462,13 +37462,13 @@
         <v>General</v>
       </c>
       <c r="G1059" t="str">
-        <v>75MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1059" t="str">
         <v>BOX</v>
       </c>
       <c r="I1059">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="J1059" t="str">
         <v>Active</v>
@@ -37482,10 +37482,10 @@
         <v>1059</v>
       </c>
       <c r="B1060" t="str">
-        <v>FG-400565</v>
+        <v>FG-400564</v>
       </c>
       <c r="C1060" t="str">
-        <v>AGRI FABRICATED COUPLER (90MM)</v>
+        <v>AGRI FABRICATED COUPLER (75MM)</v>
       </c>
       <c r="D1060" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37497,13 +37497,13 @@
         <v>General</v>
       </c>
       <c r="G1060" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1060" t="str">
         <v>BOX</v>
       </c>
       <c r="I1060">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="J1060" t="str">
         <v>Active</v>
@@ -37517,10 +37517,10 @@
         <v>1060</v>
       </c>
       <c r="B1061" t="str">
-        <v>FG-400566</v>
+        <v>FG-400565</v>
       </c>
       <c r="C1061" t="str">
-        <v>AGRI FABRICATED COUPLER (110MM)</v>
+        <v>AGRI FABRICATED COUPLER (90MM)</v>
       </c>
       <c r="D1061" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37532,13 +37532,13 @@
         <v>General</v>
       </c>
       <c r="G1061" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1061" t="str">
         <v>BOX</v>
       </c>
       <c r="I1061">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J1061" t="str">
         <v>Active</v>
@@ -37552,10 +37552,10 @@
         <v>1061</v>
       </c>
       <c r="B1062" t="str">
-        <v>FG-400587</v>
+        <v>FG-400566</v>
       </c>
       <c r="C1062" t="str">
-        <v>AGRI FABRICATED COUPLER (140MM 4KG)</v>
+        <v>AGRI FABRICATED COUPLER (110MM)</v>
       </c>
       <c r="D1062" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37567,13 +37567,13 @@
         <v>General</v>
       </c>
       <c r="G1062" t="str">
-        <v>140MM 4KG</v>
+        <v>110MM</v>
       </c>
       <c r="H1062" t="str">
         <v>BOX</v>
       </c>
       <c r="I1062">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J1062" t="str">
         <v>Active</v>
@@ -37587,10 +37587,10 @@
         <v>1062</v>
       </c>
       <c r="B1063" t="str">
-        <v>FG-400568</v>
+        <v>FG-400587</v>
       </c>
       <c r="C1063" t="str">
-        <v>AGRI FABRICATED COUPLER (160MM 4KG)</v>
+        <v>AGRI FABRICATED COUPLER (140MM 4KG)</v>
       </c>
       <c r="D1063" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37602,13 +37602,13 @@
         <v>General</v>
       </c>
       <c r="G1063" t="str">
-        <v>160MM 4KG</v>
+        <v>140MM 4KG</v>
       </c>
       <c r="H1063" t="str">
         <v>BOX</v>
       </c>
       <c r="I1063">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J1063" t="str">
         <v>Active</v>
@@ -37622,13 +37622,13 @@
         <v>1063</v>
       </c>
       <c r="B1064" t="str">
-        <v>FG-400567</v>
+        <v>FG-400568</v>
       </c>
       <c r="C1064" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG (140MM)</v>
+        <v>AGRI FABRICATED COUPLER (160MM 4KG)</v>
       </c>
       <c r="D1064" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG</v>
+        <v>AGRI FABRICATED COUPLER</v>
       </c>
       <c r="E1064" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37637,19 +37637,19 @@
         <v>General</v>
       </c>
       <c r="G1064" t="str">
-        <v>140MM</v>
+        <v>160MM 4KG</v>
       </c>
       <c r="H1064" t="str">
         <v>BOX</v>
       </c>
       <c r="I1064">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J1064" t="str">
         <v>Active</v>
       </c>
       <c r="K1064" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG for agriculture irrigation and piping systems. Available sizes: 140MM, 160MM.</v>
+        <v>AGRI FABRICATED COUPLER for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1065">
@@ -37657,10 +37657,10 @@
         <v>1064</v>
       </c>
       <c r="B1065" t="str">
-        <v>FG-400569</v>
+        <v>FG-400567</v>
       </c>
       <c r="C1065" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG (160MM)</v>
+        <v>AGRI FABRICATED COUPLER 6KG (140MM)</v>
       </c>
       <c r="D1065" t="str">
         <v>AGRI FABRICATED COUPLER 6KG</v>
@@ -37672,13 +37672,13 @@
         <v>General</v>
       </c>
       <c r="G1065" t="str">
-        <v>160MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1065" t="str">
         <v>BOX</v>
       </c>
       <c r="I1065">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J1065" t="str">
         <v>Active</v>
@@ -37692,13 +37692,13 @@
         <v>1065</v>
       </c>
       <c r="B1066" t="str">
-        <v>FG-400544</v>
+        <v>FG-400569</v>
       </c>
       <c r="C1066" t="str">
-        <v>AGRI ELBOW (40MM)</v>
+        <v>AGRI FABRICATED COUPLER 6KG (160MM)</v>
       </c>
       <c r="D1066" t="str">
-        <v>AGRI ELBOW</v>
+        <v>AGRI FABRICATED COUPLER 6KG</v>
       </c>
       <c r="E1066" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37707,19 +37707,19 @@
         <v>General</v>
       </c>
       <c r="G1066" t="str">
-        <v>40MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1066" t="str">
         <v>BOX</v>
       </c>
       <c r="I1066">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="J1066" t="str">
         <v>Active</v>
       </c>
       <c r="K1066" t="str">
-        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
+        <v>AGRI FABRICATED COUPLER 6KG for agriculture irrigation and piping systems. Available sizes: 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1067">
@@ -37727,10 +37727,10 @@
         <v>1066</v>
       </c>
       <c r="B1067" t="str">
-        <v>FG-400545</v>
+        <v>FG-400544</v>
       </c>
       <c r="C1067" t="str">
-        <v>AGRI ELBOW (50MM)</v>
+        <v>AGRI ELBOW (40MM)</v>
       </c>
       <c r="D1067" t="str">
         <v>AGRI ELBOW</v>
@@ -37742,13 +37742,13 @@
         <v>General</v>
       </c>
       <c r="G1067" t="str">
-        <v>50MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1067" t="str">
         <v>BOX</v>
       </c>
       <c r="I1067">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="J1067" t="str">
         <v>Active</v>
@@ -37762,10 +37762,10 @@
         <v>1067</v>
       </c>
       <c r="B1068" t="str">
-        <v>FG-400546</v>
+        <v>FG-400545</v>
       </c>
       <c r="C1068" t="str">
-        <v>AGRI ELBOW (63MM)</v>
+        <v>AGRI ELBOW (50MM)</v>
       </c>
       <c r="D1068" t="str">
         <v>AGRI ELBOW</v>
@@ -37777,13 +37777,13 @@
         <v>General</v>
       </c>
       <c r="G1068" t="str">
-        <v>63MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1068" t="str">
         <v>BOX</v>
       </c>
       <c r="I1068">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J1068" t="str">
         <v>Active</v>
@@ -37797,10 +37797,10 @@
         <v>1068</v>
       </c>
       <c r="B1069" t="str">
-        <v>FG-400547</v>
+        <v>FG-400546</v>
       </c>
       <c r="C1069" t="str">
-        <v>AGRI ELBOW (75MM)</v>
+        <v>AGRI ELBOW (63MM)</v>
       </c>
       <c r="D1069" t="str">
         <v>AGRI ELBOW</v>
@@ -37812,13 +37812,13 @@
         <v>General</v>
       </c>
       <c r="G1069" t="str">
-        <v>75MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1069" t="str">
         <v>BOX</v>
       </c>
       <c r="I1069">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J1069" t="str">
         <v>Active</v>
@@ -37832,10 +37832,10 @@
         <v>1069</v>
       </c>
       <c r="B1070" t="str">
-        <v>FG-400548</v>
+        <v>FG-400547</v>
       </c>
       <c r="C1070" t="str">
-        <v>AGRI ELBOW (90MM)</v>
+        <v>AGRI ELBOW (75MM)</v>
       </c>
       <c r="D1070" t="str">
         <v>AGRI ELBOW</v>
@@ -37847,13 +37847,13 @@
         <v>General</v>
       </c>
       <c r="G1070" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1070" t="str">
         <v>BOX</v>
       </c>
       <c r="I1070">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J1070" t="str">
         <v>Active</v>
@@ -37867,10 +37867,10 @@
         <v>1070</v>
       </c>
       <c r="B1071" t="str">
-        <v>FG-400549</v>
+        <v>FG-400548</v>
       </c>
       <c r="C1071" t="str">
-        <v>AGRI ELBOW (110MM)</v>
+        <v>AGRI ELBOW (90MM)</v>
       </c>
       <c r="D1071" t="str">
         <v>AGRI ELBOW</v>
@@ -37882,13 +37882,13 @@
         <v>General</v>
       </c>
       <c r="G1071" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1071" t="str">
         <v>BOX</v>
       </c>
       <c r="I1071">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="J1071" t="str">
         <v>Active</v>
@@ -37902,10 +37902,10 @@
         <v>1071</v>
       </c>
       <c r="B1072" t="str">
-        <v>FG-400595</v>
+        <v>FG-400549</v>
       </c>
       <c r="C1072" t="str">
-        <v>AGRI ELBOW (140MM)</v>
+        <v>AGRI ELBOW (110MM)</v>
       </c>
       <c r="D1072" t="str">
         <v>AGRI ELBOW</v>
@@ -37917,13 +37917,13 @@
         <v>General</v>
       </c>
       <c r="G1072" t="str">
-        <v>140MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1072" t="str">
         <v>BOX</v>
       </c>
       <c r="I1072">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="J1072" t="str">
         <v>Active</v>
@@ -37937,10 +37937,10 @@
         <v>1072</v>
       </c>
       <c r="B1073" t="str">
-        <v>FG-400596</v>
+        <v>FG-400595</v>
       </c>
       <c r="C1073" t="str">
-        <v>AGRI ELBOW (160MM)</v>
+        <v>AGRI ELBOW (140MM)</v>
       </c>
       <c r="D1073" t="str">
         <v>AGRI ELBOW</v>
@@ -37952,13 +37952,13 @@
         <v>General</v>
       </c>
       <c r="G1073" t="str">
-        <v>160MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1073" t="str">
         <v>BOX</v>
       </c>
       <c r="I1073">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J1073" t="str">
         <v>Active</v>
@@ -37972,13 +37972,13 @@
         <v>1073</v>
       </c>
       <c r="B1074" t="str">
-        <v>FG-400555</v>
+        <v>FG-400596</v>
       </c>
       <c r="C1074" t="str">
-        <v>AGRI END CAP (40MM)</v>
+        <v>AGRI ELBOW (160MM)</v>
       </c>
       <c r="D1074" t="str">
-        <v>AGRI END CAP</v>
+        <v>AGRI ELBOW</v>
       </c>
       <c r="E1074" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37987,19 +37987,19 @@
         <v>General</v>
       </c>
       <c r="G1074" t="str">
-        <v>40MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1074" t="str">
         <v>BOX</v>
       </c>
       <c r="I1074">
-        <v>800</v>
+        <v>12</v>
       </c>
       <c r="J1074" t="str">
         <v>Active</v>
       </c>
       <c r="K1074" t="str">
-        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
+        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1075">
@@ -38007,10 +38007,10 @@
         <v>1074</v>
       </c>
       <c r="B1075" t="str">
-        <v>FG-400556</v>
+        <v>FG-400555</v>
       </c>
       <c r="C1075" t="str">
-        <v>AGRI END CAP (50MM)</v>
+        <v>AGRI END CAP (40MM)</v>
       </c>
       <c r="D1075" t="str">
         <v>AGRI END CAP</v>
@@ -38022,13 +38022,13 @@
         <v>General</v>
       </c>
       <c r="G1075" t="str">
-        <v>50MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1075" t="str">
         <v>BOX</v>
       </c>
       <c r="I1075">
-        <v>450</v>
+        <v>800</v>
       </c>
       <c r="J1075" t="str">
         <v>Active</v>
@@ -38042,10 +38042,10 @@
         <v>1075</v>
       </c>
       <c r="B1076" t="str">
-        <v>FG-400557</v>
+        <v>FG-400556</v>
       </c>
       <c r="C1076" t="str">
-        <v>AGRI END CAP (63MM)</v>
+        <v>AGRI END CAP (50MM)</v>
       </c>
       <c r="D1076" t="str">
         <v>AGRI END CAP</v>
@@ -38057,13 +38057,13 @@
         <v>General</v>
       </c>
       <c r="G1076" t="str">
-        <v>63MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1076" t="str">
         <v>BOX</v>
       </c>
       <c r="I1076">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="J1076" t="str">
         <v>Active</v>
@@ -38077,10 +38077,10 @@
         <v>1076</v>
       </c>
       <c r="B1077" t="str">
-        <v>FG-400558</v>
+        <v>FG-400557</v>
       </c>
       <c r="C1077" t="str">
-        <v>AGRI END CAP (75MM)</v>
+        <v>AGRI END CAP (63MM)</v>
       </c>
       <c r="D1077" t="str">
         <v>AGRI END CAP</v>
@@ -38092,13 +38092,13 @@
         <v>General</v>
       </c>
       <c r="G1077" t="str">
-        <v>75MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1077" t="str">
         <v>BOX</v>
       </c>
       <c r="I1077">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="J1077" t="str">
         <v>Active</v>
@@ -38112,10 +38112,10 @@
         <v>1077</v>
       </c>
       <c r="B1078" t="str">
-        <v>FG-400559</v>
+        <v>FG-400558</v>
       </c>
       <c r="C1078" t="str">
-        <v>AGRI END CAP (90MM)</v>
+        <v>AGRI END CAP (75MM)</v>
       </c>
       <c r="D1078" t="str">
         <v>AGRI END CAP</v>
@@ -38127,13 +38127,13 @@
         <v>General</v>
       </c>
       <c r="G1078" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1078" t="str">
         <v>BOX</v>
       </c>
       <c r="I1078">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J1078" t="str">
         <v>Active</v>
@@ -38147,10 +38147,10 @@
         <v>1078</v>
       </c>
       <c r="B1079" t="str">
-        <v>FG-400560</v>
+        <v>FG-400559</v>
       </c>
       <c r="C1079" t="str">
-        <v>AGRI END CAP (110MM)</v>
+        <v>AGRI END CAP (90MM)</v>
       </c>
       <c r="D1079" t="str">
         <v>AGRI END CAP</v>
@@ -38162,13 +38162,13 @@
         <v>General</v>
       </c>
       <c r="G1079" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1079" t="str">
         <v>BOX</v>
       </c>
       <c r="I1079">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J1079" t="str">
         <v>Active</v>
@@ -38182,10 +38182,10 @@
         <v>1079</v>
       </c>
       <c r="B1080" t="str">
-        <v>FG-400639</v>
+        <v>FG-400560</v>
       </c>
       <c r="C1080" t="str">
-        <v>AGRI END CAP (140MM 4KG)</v>
+        <v>AGRI END CAP (110MM)</v>
       </c>
       <c r="D1080" t="str">
         <v>AGRI END CAP</v>
@@ -38197,13 +38197,13 @@
         <v>General</v>
       </c>
       <c r="G1080" t="str">
-        <v>140MM 4KG</v>
+        <v>110MM</v>
       </c>
       <c r="H1080" t="str">
         <v>BOX</v>
       </c>
       <c r="I1080">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J1080" t="str">
         <v>Active</v>
@@ -38217,10 +38217,10 @@
         <v>1080</v>
       </c>
       <c r="B1081" t="str">
-        <v>FG-400640</v>
+        <v>FG-400639</v>
       </c>
       <c r="C1081" t="str">
-        <v>AGRI END CAP (160MM 4KG)</v>
+        <v>AGRI END CAP (140MM 4KG)</v>
       </c>
       <c r="D1081" t="str">
         <v>AGRI END CAP</v>
@@ -38232,13 +38232,13 @@
         <v>General</v>
       </c>
       <c r="G1081" t="str">
-        <v>160MM 4KG</v>
+        <v>140MM 4KG</v>
       </c>
       <c r="H1081" t="str">
         <v>BOX</v>
       </c>
       <c r="I1081">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J1081" t="str">
         <v>Active</v>
@@ -38252,13 +38252,13 @@
         <v>1081</v>
       </c>
       <c r="B1082" t="str">
-        <v>FG-400570</v>
+        <v>FG-400640</v>
       </c>
       <c r="C1082" t="str">
-        <v>AGRI LONG BEND (63MM)</v>
+        <v>AGRI END CAP (160MM 4KG)</v>
       </c>
       <c r="D1082" t="str">
-        <v>AGRI LONG BEND</v>
+        <v>AGRI END CAP</v>
       </c>
       <c r="E1082" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -38267,19 +38267,19 @@
         <v>General</v>
       </c>
       <c r="G1082" t="str">
-        <v>63MM</v>
+        <v>160MM 4KG</v>
       </c>
       <c r="H1082" t="str">
         <v>BOX</v>
       </c>
       <c r="I1082">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="J1082" t="str">
         <v>Active</v>
       </c>
       <c r="K1082" t="str">
-        <v>AGRI LONG BEND for agriculture irrigation and piping systems. Available sizes: 63MM, 75MM, 90MM, 110MM.</v>
+        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1083">
@@ -38287,10 +38287,10 @@
         <v>1082</v>
       </c>
       <c r="B1083" t="str">
-        <v>FG-400571</v>
+        <v>FG-400570</v>
       </c>
       <c r="C1083" t="str">
-        <v>AGRI LONG BEND (75MM)</v>
+        <v>AGRI LONG BEND (63MM)</v>
       </c>
       <c r="D1083" t="str">
         <v>AGRI LONG BEND</v>
@@ -38302,13 +38302,13 @@
         <v>General</v>
       </c>
       <c r="G1083" t="str">
-        <v>75MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1083" t="str">
         <v>BOX</v>
       </c>
       <c r="I1083">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J1083" t="str">
         <v>Active</v>
@@ -38322,10 +38322,10 @@
         <v>1083</v>
       </c>
       <c r="B1084" t="str">
-        <v>FG-400572</v>
+        <v>FG-400571</v>
       </c>
       <c r="C1084" t="str">
-        <v>AGRI LONG BEND (90MM)</v>
+        <v>AGRI LONG BEND (75MM)</v>
       </c>
       <c r="D1084" t="str">
         <v>AGRI LONG BEND</v>
@@ -38337,13 +38337,13 @@
         <v>General</v>
       </c>
       <c r="G1084" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1084" t="str">
         <v>BOX</v>
       </c>
       <c r="I1084">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J1084" t="str">
         <v>Active</v>
@@ -38357,10 +38357,10 @@
         <v>1084</v>
       </c>
       <c r="B1085" t="str">
-        <v>FG-400573</v>
+        <v>FG-400572</v>
       </c>
       <c r="C1085" t="str">
-        <v>AGRI LONG BEND (110MM)</v>
+        <v>AGRI LONG BEND (90MM)</v>
       </c>
       <c r="D1085" t="str">
         <v>AGRI LONG BEND</v>
@@ -38372,13 +38372,13 @@
         <v>General</v>
       </c>
       <c r="G1085" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1085" t="str">
         <v>BOX</v>
       </c>
       <c r="I1085">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J1085" t="str">
         <v>Active</v>
@@ -38392,34 +38392,34 @@
         <v>1085</v>
       </c>
       <c r="B1086" t="str">
-        <v>FG-401520</v>
+        <v>FG-400573</v>
       </c>
       <c r="C1086" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
+        <v>AGRI LONG BEND (110MM)</v>
       </c>
       <c r="D1086" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR</v>
+        <v>AGRI LONG BEND</v>
       </c>
       <c r="E1086" t="str">
-        <v>Sprinkler Pipes &amp; Fittings</v>
+        <v>Agriculture Pipes &amp; Fittings</v>
       </c>
       <c r="F1086" t="str">
         <v>General</v>
       </c>
       <c r="G1086" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>110MM</v>
       </c>
       <c r="H1086" t="str">
-        <v>Nos</v>
-      </c>
-      <c r="I1086" t="str">
-        <v>-</v>
+        <v>BOX</v>
+      </c>
+      <c r="I1086">
+        <v>10</v>
       </c>
       <c r="J1086" t="str">
         <v>Active</v>
       </c>
       <c r="K1086" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR for sprinkler irrigation systems.</v>
+        <v>AGRI LONG BEND for agriculture irrigation and piping systems. Available sizes: 63MM, 75MM, 90MM, 110MM.</v>
       </c>
     </row>
     <row r="1087">
@@ -38427,10 +38427,10 @@
         <v>1086</v>
       </c>
       <c r="B1087" t="str">
-        <v>FG-401491</v>
+        <v>FG-401520</v>
       </c>
       <c r="C1087" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (63MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1087" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38442,7 +38442,7 @@
         <v>General</v>
       </c>
       <c r="G1087" t="str">
-        <v>63MM L TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1087" t="str">
         <v>Nos</v>
@@ -38462,10 +38462,10 @@
         <v>1087</v>
       </c>
       <c r="B1088" t="str">
-        <v>FG-401490</v>
+        <v>FG-401491</v>
       </c>
       <c r="C1088" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 2.5 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (63MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1088" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38477,7 +38477,7 @@
         <v>General</v>
       </c>
       <c r="G1088" t="str">
-        <v>75MM C TYPE 2.5 KG</v>
+        <v>63MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1088" t="str">
         <v>Nos</v>
@@ -38497,10 +38497,10 @@
         <v>1088</v>
       </c>
       <c r="B1089" t="str">
-        <v>FG-401492</v>
+        <v>FG-401490</v>
       </c>
       <c r="C1089" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 2.5 KG)</v>
       </c>
       <c r="D1089" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38512,7 +38512,7 @@
         <v>General</v>
       </c>
       <c r="G1089" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>75MM C TYPE 2.5 KG</v>
       </c>
       <c r="H1089" t="str">
         <v>Nos</v>
@@ -38532,10 +38532,10 @@
         <v>1089</v>
       </c>
       <c r="B1090" t="str">
-        <v>FG-401519</v>
+        <v>FG-401492</v>
       </c>
       <c r="C1090" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 2.5 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1090" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38547,7 +38547,7 @@
         <v>General</v>
       </c>
       <c r="G1090" t="str">
-        <v>75MM L TYPE 2.5 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1090" t="str">
         <v>Nos</v>
@@ -38567,10 +38567,10 @@
         <v>1090</v>
       </c>
       <c r="B1091" t="str">
-        <v>FG-401521</v>
+        <v>FG-401519</v>
       </c>
       <c r="C1091" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 2.5 KG)</v>
       </c>
       <c r="D1091" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38582,7 +38582,7 @@
         <v>General</v>
       </c>
       <c r="G1091" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 2.5 KG</v>
       </c>
       <c r="H1091" t="str">
         <v>Nos</v>
@@ -38602,13 +38602,13 @@
         <v>1091</v>
       </c>
       <c r="B1092" t="str">
-        <v>FG-401522</v>
+        <v>FG-401521</v>
       </c>
       <c r="C1092" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1092" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR</v>
+        <v>SPRINKLER ISI PIPE 6 MTR</v>
       </c>
       <c r="E1092" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38629,7 +38629,7 @@
         <v>Active</v>
       </c>
       <c r="K1092" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER ISI PIPE 6 MTR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1093">
@@ -38637,10 +38637,10 @@
         <v>1092</v>
       </c>
       <c r="B1093" t="str">
-        <v>FG-401523</v>
+        <v>FG-401522</v>
       </c>
       <c r="C1093" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1093" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38652,7 +38652,7 @@
         <v>General</v>
       </c>
       <c r="G1093" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1093" t="str">
         <v>Nos</v>
@@ -38672,10 +38672,10 @@
         <v>1093</v>
       </c>
       <c r="B1094" t="str">
-        <v>FG-401866</v>
+        <v>FG-401523</v>
       </c>
       <c r="C1094" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (90MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1094" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38687,7 +38687,7 @@
         <v>General</v>
       </c>
       <c r="G1094" t="str">
-        <v>90MM C TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1094" t="str">
         <v>Nos</v>
@@ -38707,10 +38707,10 @@
         <v>1094</v>
       </c>
       <c r="B1095" t="str">
-        <v>FG-401867</v>
+        <v>FG-401866</v>
       </c>
       <c r="C1095" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (90MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (90MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1095" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38722,7 +38722,7 @@
         <v>General</v>
       </c>
       <c r="G1095" t="str">
-        <v>90MM L TYPE 3.2 KG</v>
+        <v>90MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1095" t="str">
         <v>Nos</v>
@@ -38742,13 +38742,13 @@
         <v>1095</v>
       </c>
       <c r="B1096" t="str">
-        <v>FG-401498</v>
+        <v>FG-401867</v>
       </c>
       <c r="C1096" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (90MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1096" t="str">
-        <v>SPRINKLER SET 6 MTR ISI</v>
+        <v>SPRINKLER NISI PIPE 6 MTR</v>
       </c>
       <c r="E1096" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38757,7 +38757,7 @@
         <v>General</v>
       </c>
       <c r="G1096" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>90MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1096" t="str">
         <v>Nos</v>
@@ -38769,7 +38769,7 @@
         <v>Active</v>
       </c>
       <c r="K1096" t="str">
-        <v>SPRINKLER SET 6 MTR ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER NISI PIPE 6 MTR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1097">
@@ -38777,10 +38777,10 @@
         <v>1096</v>
       </c>
       <c r="B1097" t="str">
-        <v>FG-401499</v>
+        <v>FG-401498</v>
       </c>
       <c r="C1097" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1097" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38792,7 +38792,7 @@
         <v>General</v>
       </c>
       <c r="G1097" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1097" t="str">
         <v>Nos</v>
@@ -38812,10 +38812,10 @@
         <v>1097</v>
       </c>
       <c r="B1098" t="str">
-        <v>FG-401500</v>
+        <v>FG-401499</v>
       </c>
       <c r="C1098" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 2.5 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1098" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38827,7 +38827,7 @@
         <v>General</v>
       </c>
       <c r="G1098" t="str">
-        <v>75MM C TYPE 2.5 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1098" t="str">
         <v>Nos</v>
@@ -38847,10 +38847,10 @@
         <v>1098</v>
       </c>
       <c r="B1099" t="str">
-        <v>FG-401524</v>
+        <v>FG-401500</v>
       </c>
       <c r="C1099" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 2.5 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 2.5 KG)</v>
       </c>
       <c r="D1099" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38862,7 +38862,7 @@
         <v>General</v>
       </c>
       <c r="G1099" t="str">
-        <v>75MM L TYPE 2.5 KG</v>
+        <v>75MM C TYPE 2.5 KG</v>
       </c>
       <c r="H1099" t="str">
         <v>Nos</v>
@@ -38882,10 +38882,10 @@
         <v>1099</v>
       </c>
       <c r="B1100" t="str">
-        <v>FG-401501</v>
+        <v>FG-401524</v>
       </c>
       <c r="C1100" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 2.5 KG)</v>
       </c>
       <c r="D1100" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38897,7 +38897,7 @@
         <v>General</v>
       </c>
       <c r="G1100" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 2.5 KG</v>
       </c>
       <c r="H1100" t="str">
         <v>Nos</v>
@@ -38917,13 +38917,13 @@
         <v>1100</v>
       </c>
       <c r="B1101" t="str">
-        <v>FG-401495</v>
+        <v>FG-401501</v>
       </c>
       <c r="C1101" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1101" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI</v>
+        <v>SPRINKLER SET 6 MTR ISI</v>
       </c>
       <c r="E1101" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38932,7 +38932,7 @@
         <v>General</v>
       </c>
       <c r="G1101" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1101" t="str">
         <v>Nos</v>
@@ -38944,7 +38944,7 @@
         <v>Active</v>
       </c>
       <c r="K1101" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER SET 6 MTR ISI for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1102">
@@ -38952,10 +38952,10 @@
         <v>1101</v>
       </c>
       <c r="B1102" t="str">
-        <v>FG-401496</v>
+        <v>FG-401495</v>
       </c>
       <c r="C1102" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1102" t="str">
         <v>SPRINKLER SET 6 MTR N-ISI</v>
@@ -38967,7 +38967,7 @@
         <v>General</v>
       </c>
       <c r="G1102" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1102" t="str">
         <v>Nos</v>
@@ -38987,10 +38987,10 @@
         <v>1102</v>
       </c>
       <c r="B1103" t="str">
-        <v>FG-401497</v>
+        <v>FG-401496</v>
       </c>
       <c r="C1103" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1103" t="str">
         <v>SPRINKLER SET 6 MTR N-ISI</v>
@@ -39002,7 +39002,7 @@
         <v>General</v>
       </c>
       <c r="G1103" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1103" t="str">
         <v>Nos</v>
@@ -39022,13 +39022,13 @@
         <v>1103</v>
       </c>
       <c r="B1104" t="str">
-        <v>FG-401503</v>
+        <v>FG-401497</v>
       </c>
       <c r="C1104" t="str">
-        <v>SPRINKLER FITTINGS TEE (75MM, C TYPE)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1104" t="str">
-        <v>SPRINKLER FITTINGS TEE</v>
+        <v>SPRINKLER SET 6 MTR N-ISI</v>
       </c>
       <c r="E1104" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39037,7 +39037,7 @@
         <v>General</v>
       </c>
       <c r="G1104" t="str">
-        <v>75MM, C TYPE</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1104" t="str">
         <v>Nos</v>
@@ -39049,7 +39049,7 @@
         <v>Active</v>
       </c>
       <c r="K1104" t="str">
-        <v>SPRINKLER FITTINGS TEE for sprinkler irrigation systems. Available sizes: 75MM, C TYPE, 75MM, L TYPE, 63MM, C TYPE.</v>
+        <v>SPRINKLER SET 6 MTR N-ISI for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1105">
@@ -39057,10 +39057,10 @@
         <v>1104</v>
       </c>
       <c r="B1105" t="str">
-        <v>FG-401511</v>
+        <v>FG-401503</v>
       </c>
       <c r="C1105" t="str">
-        <v>SPRINKLER FITTINGS TEE (75MM, L TYPE)</v>
+        <v>SPRINKLER FITTINGS TEE (75MM, C TYPE)</v>
       </c>
       <c r="D1105" t="str">
         <v>SPRINKLER FITTINGS TEE</v>
@@ -39072,7 +39072,7 @@
         <v>General</v>
       </c>
       <c r="G1105" t="str">
-        <v>75MM, L TYPE</v>
+        <v>75MM, C TYPE</v>
       </c>
       <c r="H1105" t="str">
         <v>Nos</v>
@@ -39092,10 +39092,10 @@
         <v>1105</v>
       </c>
       <c r="B1106" t="str">
-        <v>FG-401526</v>
+        <v>FG-401511</v>
       </c>
       <c r="C1106" t="str">
-        <v>SPRINKLER FITTINGS TEE (63MM, C TYPE)</v>
+        <v>SPRINKLER FITTINGS TEE (75MM, L TYPE)</v>
       </c>
       <c r="D1106" t="str">
         <v>SPRINKLER FITTINGS TEE</v>
@@ -39107,7 +39107,7 @@
         <v>General</v>
       </c>
       <c r="G1106" t="str">
-        <v>63MM, C TYPE</v>
+        <v>75MM, L TYPE</v>
       </c>
       <c r="H1106" t="str">
         <v>Nos</v>
@@ -39127,13 +39127,13 @@
         <v>1106</v>
       </c>
       <c r="B1107" t="str">
-        <v>FG-401504</v>
+        <v>FG-401526</v>
       </c>
       <c r="C1107" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS TEE (63MM, C TYPE)</v>
       </c>
       <c r="D1107" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR</v>
+        <v>SPRINKLER FITTINGS TEE</v>
       </c>
       <c r="E1107" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39142,7 +39142,7 @@
         <v>General</v>
       </c>
       <c r="G1107" t="str">
-        <v>75MM C TYPE</v>
+        <v>63MM, C TYPE</v>
       </c>
       <c r="H1107" t="str">
         <v>Nos</v>
@@ -39154,7 +39154,7 @@
         <v>Active</v>
       </c>
       <c r="K1107" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS TEE for sprinkler irrigation systems. Available sizes: 75MM, C TYPE, 75MM, L TYPE, 63MM, C TYPE.</v>
       </c>
     </row>
     <row r="1108">
@@ -39162,10 +39162,10 @@
         <v>1107</v>
       </c>
       <c r="B1108" t="str">
-        <v>FG-401512</v>
+        <v>FG-401504</v>
       </c>
       <c r="C1108" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (75MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (75MM C TYPE)</v>
       </c>
       <c r="D1108" t="str">
         <v>SPRINKLER FITTINGS ADAPTOR</v>
@@ -39177,7 +39177,7 @@
         <v>General</v>
       </c>
       <c r="G1108" t="str">
-        <v>75MM P TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1108" t="str">
         <v>Nos</v>
@@ -39197,10 +39197,10 @@
         <v>1108</v>
       </c>
       <c r="B1109" t="str">
-        <v>FG-401527</v>
+        <v>FG-401512</v>
       </c>
       <c r="C1109" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (75MM P TYPE)</v>
       </c>
       <c r="D1109" t="str">
         <v>SPRINKLER FITTINGS ADAPTOR</v>
@@ -39212,7 +39212,7 @@
         <v>General</v>
       </c>
       <c r="G1109" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM P TYPE</v>
       </c>
       <c r="H1109" t="str">
         <v>Nos</v>
@@ -39232,13 +39232,13 @@
         <v>1109</v>
       </c>
       <c r="B1110" t="str">
-        <v>FG-401502</v>
+        <v>FG-401527</v>
       </c>
       <c r="C1110" t="str">
-        <v>SPRINKLER FITTINGS BEND (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (63MM C TYPE)</v>
       </c>
       <c r="D1110" t="str">
-        <v>SPRINKLER FITTINGS BEND</v>
+        <v>SPRINKLER FITTINGS ADAPTOR</v>
       </c>
       <c r="E1110" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39247,7 +39247,7 @@
         <v>General</v>
       </c>
       <c r="G1110" t="str">
-        <v>75MM C TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1110" t="str">
         <v>Nos</v>
@@ -39259,7 +39259,7 @@
         <v>Active</v>
       </c>
       <c r="K1110" t="str">
-        <v>SPRINKLER FITTINGS BEND for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS ADAPTOR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1111">
@@ -39267,10 +39267,10 @@
         <v>1110</v>
       </c>
       <c r="B1111" t="str">
-        <v>FG-401510</v>
+        <v>FG-401502</v>
       </c>
       <c r="C1111" t="str">
-        <v>SPRINKLER FITTINGS BEND (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (75MM C TYPE)</v>
       </c>
       <c r="D1111" t="str">
         <v>SPRINKLER FITTINGS BEND</v>
@@ -39282,7 +39282,7 @@
         <v>General</v>
       </c>
       <c r="G1111" t="str">
-        <v>75MM L TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1111" t="str">
         <v>Nos</v>
@@ -39302,10 +39302,10 @@
         <v>1111</v>
       </c>
       <c r="B1112" t="str">
-        <v>FG-401525</v>
+        <v>FG-401510</v>
       </c>
       <c r="C1112" t="str">
-        <v>SPRINKLER FITTINGS BEND (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (75MM L TYPE)</v>
       </c>
       <c r="D1112" t="str">
         <v>SPRINKLER FITTINGS BEND</v>
@@ -39317,7 +39317,7 @@
         <v>General</v>
       </c>
       <c r="G1112" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1112" t="str">
         <v>Nos</v>
@@ -39337,13 +39337,13 @@
         <v>1112</v>
       </c>
       <c r="B1113" t="str">
-        <v>FG-401514</v>
+        <v>FG-401525</v>
       </c>
       <c r="C1113" t="str">
-        <v>SPRINKLER FITTINGS END CAP (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (63MM C TYPE)</v>
       </c>
       <c r="D1113" t="str">
-        <v>SPRINKLER FITTINGS END CAP</v>
+        <v>SPRINKLER FITTINGS BEND</v>
       </c>
       <c r="E1113" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39352,7 +39352,7 @@
         <v>General</v>
       </c>
       <c r="G1113" t="str">
-        <v>75MM L TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1113" t="str">
         <v>Nos</v>
@@ -39364,7 +39364,7 @@
         <v>Active</v>
       </c>
       <c r="K1113" t="str">
-        <v>SPRINKLER FITTINGS END CAP for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS BEND for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1114">
@@ -39372,10 +39372,10 @@
         <v>1113</v>
       </c>
       <c r="B1114" t="str">
-        <v>FG-401506</v>
+        <v>FG-401514</v>
       </c>
       <c r="C1114" t="str">
-        <v>SPRINKLER FITTINGS END CAP (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (75MM L TYPE)</v>
       </c>
       <c r="D1114" t="str">
         <v>SPRINKLER FITTINGS END CAP</v>
@@ -39387,7 +39387,7 @@
         <v>General</v>
       </c>
       <c r="G1114" t="str">
-        <v>75MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1114" t="str">
         <v>Nos</v>
@@ -39407,10 +39407,10 @@
         <v>1114</v>
       </c>
       <c r="B1115" t="str">
-        <v>FG-401529</v>
+        <v>FG-401506</v>
       </c>
       <c r="C1115" t="str">
-        <v>SPRINKLER FITTINGS END CAP (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (75MM C TYPE)</v>
       </c>
       <c r="D1115" t="str">
         <v>SPRINKLER FITTINGS END CAP</v>
@@ -39422,7 +39422,7 @@
         <v>General</v>
       </c>
       <c r="G1115" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1115" t="str">
         <v>Nos</v>
@@ -39442,13 +39442,13 @@
         <v>1115</v>
       </c>
       <c r="B1116" t="str">
-        <v>FG-401517</v>
+        <v>FG-401529</v>
       </c>
       <c r="C1116" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (75MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (63MM C TYPE)</v>
       </c>
       <c r="D1116" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
+        <v>SPRINKLER FITTINGS END CAP</v>
       </c>
       <c r="E1116" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39457,7 +39457,7 @@
         <v>General</v>
       </c>
       <c r="G1116" t="str">
-        <v>75MM P TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1116" t="str">
         <v>Nos</v>
@@ -39469,7 +39469,7 @@
         <v>Active</v>
       </c>
       <c r="K1116" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS END CAP for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1117">
@@ -39477,10 +39477,10 @@
         <v>1116</v>
       </c>
       <c r="B1117" t="str">
-        <v>FG-401518</v>
+        <v>FG-401517</v>
       </c>
       <c r="C1117" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (63MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (75MM P TYPE)</v>
       </c>
       <c r="D1117" t="str">
         <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
@@ -39492,7 +39492,7 @@
         <v>General</v>
       </c>
       <c r="G1117" t="str">
-        <v>63MM P TYPE</v>
+        <v>75MM P TYPE</v>
       </c>
       <c r="H1117" t="str">
         <v>Nos</v>
@@ -39512,13 +39512,13 @@
         <v>1117</v>
       </c>
       <c r="B1118" t="str">
-        <v>FG-401505</v>
+        <v>FG-401518</v>
       </c>
       <c r="C1118" t="str">
-        <v>SPRINKLER FITTINGS PCN (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (63MM P TYPE)</v>
       </c>
       <c r="D1118" t="str">
-        <v>SPRINKLER FITTINGS PCN</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
       </c>
       <c r="E1118" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39527,7 +39527,7 @@
         <v>General</v>
       </c>
       <c r="G1118" t="str">
-        <v>75MM C TYPE</v>
+        <v>63MM P TYPE</v>
       </c>
       <c r="H1118" t="str">
         <v>Nos</v>
@@ -39539,7 +39539,7 @@
         <v>Active</v>
       </c>
       <c r="K1118" t="str">
-        <v>SPRINKLER FITTINGS PCN for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1119">
@@ -39547,10 +39547,10 @@
         <v>1118</v>
       </c>
       <c r="B1119" t="str">
-        <v>FG-401513</v>
+        <v>FG-401505</v>
       </c>
       <c r="C1119" t="str">
-        <v>SPRINKLER FITTINGS PCN (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (75MM C TYPE)</v>
       </c>
       <c r="D1119" t="str">
         <v>SPRINKLER FITTINGS PCN</v>
@@ -39562,7 +39562,7 @@
         <v>General</v>
       </c>
       <c r="G1119" t="str">
-        <v>75MM L TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1119" t="str">
         <v>Nos</v>
@@ -39582,10 +39582,10 @@
         <v>1119</v>
       </c>
       <c r="B1120" t="str">
-        <v>FG-401528</v>
+        <v>FG-401513</v>
       </c>
       <c r="C1120" t="str">
-        <v>SPRINKLER FITTINGS PCN (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (75MM L TYPE)</v>
       </c>
       <c r="D1120" t="str">
         <v>SPRINKLER FITTINGS PCN</v>
@@ -39597,7 +39597,7 @@
         <v>General</v>
       </c>
       <c r="G1120" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1120" t="str">
         <v>Nos</v>
@@ -39617,13 +39617,13 @@
         <v>1120</v>
       </c>
       <c r="B1121" t="str">
-        <v>FG-401507</v>
+        <v>FG-401528</v>
       </c>
       <c r="C1121" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL (20MM)</v>
+        <v>SPRINKLER FITTINGS PCN (63MM C TYPE)</v>
       </c>
       <c r="D1121" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL</v>
+        <v>SPRINKLER FITTINGS PCN</v>
       </c>
       <c r="E1121" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39632,7 +39632,7 @@
         <v>General</v>
       </c>
       <c r="G1121" t="str">
-        <v>20MM</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1121" t="str">
         <v>Nos</v>
@@ -39644,7 +39644,7 @@
         <v>Active</v>
       </c>
       <c r="K1121" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS PCN for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1122">
@@ -39652,13 +39652,13 @@
         <v>1121</v>
       </c>
       <c r="B1122" t="str">
-        <v>FG-401508</v>
+        <v>FG-401507</v>
       </c>
       <c r="C1122" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL (20MM)</v>
       </c>
       <c r="D1122" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL</v>
       </c>
       <c r="E1122" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39667,7 +39667,7 @@
         <v>General</v>
       </c>
       <c r="G1122" t="str">
-        <v>75MM C TYPE</v>
+        <v>20MM</v>
       </c>
       <c r="H1122" t="str">
         <v>Nos</v>
@@ -39679,7 +39679,7 @@
         <v>Active</v>
       </c>
       <c r="K1122" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1123">
@@ -39687,10 +39687,10 @@
         <v>1122</v>
       </c>
       <c r="B1123" t="str">
-        <v>FG-401515</v>
+        <v>FG-401508</v>
       </c>
       <c r="C1123" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE (20MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE (75MM C TYPE)</v>
       </c>
       <c r="D1123" t="str">
         <v>SPRINKLER FITTINGS GI RISER PIPE</v>
@@ -39702,7 +39702,7 @@
         <v>General</v>
       </c>
       <c r="G1123" t="str">
-        <v>20MM L TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1123" t="str">
         <v>Nos</v>
@@ -39722,25 +39722,25 @@
         <v>1123</v>
       </c>
       <c r="B1124" t="str">
-        <v>FG-401742</v>
+        <v>FG-401515</v>
       </c>
       <c r="C1124" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 1)</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE (20MM L TYPE)</v>
       </c>
       <c r="D1124" t="str">
-        <v>ROUND DRIPLINE 12MM ISI</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE</v>
       </c>
       <c r="E1124" t="str">
-        <v>DRIP IRRIGATION SYSTEM</v>
+        <v>Sprinkler Pipes &amp; Fittings</v>
       </c>
       <c r="F1124" t="str">
-        <v>ROUND DRIP ISI</v>
+        <v>General</v>
       </c>
       <c r="G1124" t="str">
-        <v>12-4-30 CLASS 1</v>
+        <v>20MM L TYPE</v>
       </c>
       <c r="H1124" t="str">
-        <v>ROLL</v>
+        <v>Nos</v>
       </c>
       <c r="I1124" t="str">
         <v>-</v>
@@ -39749,7 +39749,7 @@
         <v>Active</v>
       </c>
       <c r="K1124" t="str">
-        <v>ROUND DRIPLINE 12MM ISI certified.</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1125">
@@ -39757,10 +39757,10 @@
         <v>1124</v>
       </c>
       <c r="B1125" t="str">
-        <v>FG-401743</v>
+        <v>FG-401742</v>
       </c>
       <c r="C1125" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 1)</v>
       </c>
       <c r="D1125" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39772,7 +39772,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1125" t="str">
-        <v>12-4-40 CLASS 1</v>
+        <v>12-4-30 CLASS 1</v>
       </c>
       <c r="H1125" t="str">
         <v>ROLL</v>
@@ -39792,10 +39792,10 @@
         <v>1125</v>
       </c>
       <c r="B1126" t="str">
-        <v>FG-401744</v>
+        <v>FG-401743</v>
       </c>
       <c r="C1126" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 1)</v>
       </c>
       <c r="D1126" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39807,7 +39807,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1126" t="str">
-        <v>12-4-50 CLASS 1</v>
+        <v>12-4-40 CLASS 1</v>
       </c>
       <c r="H1126" t="str">
         <v>ROLL</v>
@@ -39827,10 +39827,10 @@
         <v>1126</v>
       </c>
       <c r="B1127" t="str">
-        <v>FG-401751</v>
+        <v>FG-401744</v>
       </c>
       <c r="C1127" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 1)</v>
       </c>
       <c r="D1127" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39842,7 +39842,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1127" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-50 CLASS 1</v>
       </c>
       <c r="H1127" t="str">
         <v>ROLL</v>
@@ -39862,10 +39862,10 @@
         <v>1127</v>
       </c>
       <c r="B1128" t="str">
-        <v>FG-401752</v>
+        <v>FG-401751</v>
       </c>
       <c r="C1128" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1128" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39877,7 +39877,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1128" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1128" t="str">
         <v>ROLL</v>
@@ -39897,10 +39897,10 @@
         <v>1128</v>
       </c>
       <c r="B1129" t="str">
-        <v>FG-401753</v>
+        <v>FG-401752</v>
       </c>
       <c r="C1129" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1129" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39912,7 +39912,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1129" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1129" t="str">
         <v>ROLL</v>
@@ -39932,10 +39932,10 @@
         <v>1129</v>
       </c>
       <c r="B1130" t="str">
-        <v>FG-401754</v>
+        <v>FG-401753</v>
       </c>
       <c r="C1130" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1130" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39947,7 +39947,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1130" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1130" t="str">
         <v>ROLL</v>
@@ -39967,10 +39967,10 @@
         <v>1130</v>
       </c>
       <c r="B1131" t="str">
-        <v>FG-401755</v>
+        <v>FG-401754</v>
       </c>
       <c r="C1131" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1131" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39982,7 +39982,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1131" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1131" t="str">
         <v>ROLL</v>
@@ -40002,10 +40002,10 @@
         <v>1131</v>
       </c>
       <c r="B1132" t="str">
-        <v>FG-401756</v>
+        <v>FG-401755</v>
       </c>
       <c r="C1132" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1132" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -40017,7 +40017,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1132" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1132" t="str">
         <v>ROLL</v>
@@ -40037,13 +40037,13 @@
         <v>1132</v>
       </c>
       <c r="B1133" t="str">
-        <v>FG-401745</v>
+        <v>FG-401756</v>
       </c>
       <c r="C1133" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1133" t="str">
-        <v>ROUND DRIPLINE 16MM ISI</v>
+        <v>ROUND DRIPLINE 12MM ISI</v>
       </c>
       <c r="E1133" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40052,7 +40052,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1133" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1133" t="str">
         <v>ROLL</v>
@@ -40064,7 +40064,7 @@
         <v>Active</v>
       </c>
       <c r="K1133" t="str">
-        <v>ROUND DRIPLINE 16MM ISI certified.</v>
+        <v>ROUND DRIPLINE 12MM ISI certified.</v>
       </c>
     </row>
     <row r="1134">
@@ -40072,10 +40072,10 @@
         <v>1133</v>
       </c>
       <c r="B1134" t="str">
-        <v>FG-401746</v>
+        <v>FG-401745</v>
       </c>
       <c r="C1134" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1134" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40087,7 +40087,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1134" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1134" t="str">
         <v>ROLL</v>
@@ -40107,10 +40107,10 @@
         <v>1134</v>
       </c>
       <c r="B1135" t="str">
-        <v>FG-401747</v>
+        <v>FG-401746</v>
       </c>
       <c r="C1135" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1135" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40122,7 +40122,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1135" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1135" t="str">
         <v>ROLL</v>
@@ -40142,10 +40142,10 @@
         <v>1135</v>
       </c>
       <c r="B1136" t="str">
-        <v>FG-401757</v>
+        <v>FG-401747</v>
       </c>
       <c r="C1136" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1136" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40157,7 +40157,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1136" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1136" t="str">
         <v>ROLL</v>
@@ -40177,10 +40177,10 @@
         <v>1136</v>
       </c>
       <c r="B1137" t="str">
-        <v>FG-401758</v>
+        <v>FG-401757</v>
       </c>
       <c r="C1137" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1137" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40192,7 +40192,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1137" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1137" t="str">
         <v>ROLL</v>
@@ -40212,10 +40212,10 @@
         <v>1137</v>
       </c>
       <c r="B1138" t="str">
-        <v>FG-401759</v>
+        <v>FG-401758</v>
       </c>
       <c r="C1138" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1138" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40227,7 +40227,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1138" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1138" t="str">
         <v>ROLL</v>
@@ -40247,13 +40247,13 @@
         <v>1138</v>
       </c>
       <c r="B1139" t="str">
-        <v>-</v>
+        <v>FG-401759</v>
       </c>
       <c r="C1139" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-30 CLASS-1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1139" t="str">
-        <v>20MM ROUND INLINE PIPE ISI</v>
+        <v>ROUND DRIPLINE 16MM ISI</v>
       </c>
       <c r="E1139" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40262,10 +40262,10 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1139" t="str">
-        <v>20-4-30 CLASS-1</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1139" t="str">
-        <v>MTR</v>
+        <v>ROLL</v>
       </c>
       <c r="I1139" t="str">
         <v>-</v>
@@ -40274,7 +40274,7 @@
         <v>Active</v>
       </c>
       <c r="K1139" t="str">
-        <v>20mm Round Inline Drip Pipe ISI certified.</v>
+        <v>ROUND DRIPLINE 16MM ISI certified.</v>
       </c>
     </row>
     <row r="1140">
@@ -40285,7 +40285,7 @@
         <v>-</v>
       </c>
       <c r="C1140" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-40 CLASS-1)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-30 CLASS-1)</v>
       </c>
       <c r="D1140" t="str">
         <v>20MM ROUND INLINE PIPE ISI</v>
@@ -40297,7 +40297,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1140" t="str">
-        <v>20-4-40 CLASS-1</v>
+        <v>20-4-30 CLASS-1</v>
       </c>
       <c r="H1140" t="str">
         <v>MTR</v>
@@ -40320,7 +40320,7 @@
         <v>-</v>
       </c>
       <c r="C1141" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-50 CLASS-1)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-40 CLASS-1)</v>
       </c>
       <c r="D1141" t="str">
         <v>20MM ROUND INLINE PIPE ISI</v>
@@ -40332,7 +40332,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1141" t="str">
-        <v>20-4-50 CLASS-1</v>
+        <v>20-4-40 CLASS-1</v>
       </c>
       <c r="H1141" t="str">
         <v>MTR</v>
@@ -40352,25 +40352,25 @@
         <v>1141</v>
       </c>
       <c r="B1142" t="str">
-        <v>FG-401763</v>
+        <v>-</v>
       </c>
       <c r="C1142" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-50 CLASS-1)</v>
       </c>
       <c r="D1142" t="str">
-        <v>FLAT DRIPLINE 12MM ISI</v>
+        <v>20MM ROUND INLINE PIPE ISI</v>
       </c>
       <c r="E1142" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1142" t="str">
-        <v>FLAT DRIP ISI</v>
+        <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1142" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>20-4-50 CLASS-1</v>
       </c>
       <c r="H1142" t="str">
-        <v>ROLL</v>
+        <v>MTR</v>
       </c>
       <c r="I1142" t="str">
         <v>-</v>
@@ -40379,7 +40379,7 @@
         <v>Active</v>
       </c>
       <c r="K1142" t="str">
-        <v>FLAT DRIPLINE 12MM ISI certified.</v>
+        <v>20mm Round Inline Drip Pipe ISI certified.</v>
       </c>
     </row>
     <row r="1143">
@@ -40387,10 +40387,10 @@
         <v>1142</v>
       </c>
       <c r="B1143" t="str">
-        <v>FG-401764</v>
+        <v>FG-401763</v>
       </c>
       <c r="C1143" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1143" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40402,7 +40402,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1143" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1143" t="str">
         <v>ROLL</v>
@@ -40422,10 +40422,10 @@
         <v>1143</v>
       </c>
       <c r="B1144" t="str">
-        <v>FG-401765</v>
+        <v>FG-401764</v>
       </c>
       <c r="C1144" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1144" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40437,7 +40437,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1144" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1144" t="str">
         <v>ROLL</v>
@@ -40457,10 +40457,10 @@
         <v>1144</v>
       </c>
       <c r="B1145" t="str">
-        <v>FG-401766</v>
+        <v>FG-401765</v>
       </c>
       <c r="C1145" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1145" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40472,7 +40472,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1145" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1145" t="str">
         <v>ROLL</v>
@@ -40492,10 +40492,10 @@
         <v>1145</v>
       </c>
       <c r="B1146" t="str">
-        <v>FG-401767</v>
+        <v>FG-401766</v>
       </c>
       <c r="C1146" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1146" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40507,7 +40507,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1146" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1146" t="str">
         <v>ROLL</v>
@@ -40527,10 +40527,10 @@
         <v>1146</v>
       </c>
       <c r="B1147" t="str">
-        <v>FG-401768</v>
+        <v>FG-401767</v>
       </c>
       <c r="C1147" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1147" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40542,7 +40542,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1147" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1147" t="str">
         <v>ROLL</v>
@@ -40562,13 +40562,13 @@
         <v>1147</v>
       </c>
       <c r="B1148" t="str">
-        <v>FG-401760</v>
+        <v>FG-401768</v>
       </c>
       <c r="C1148" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1148" t="str">
-        <v>FLAT DRIPLINE 16MM ISI</v>
+        <v>FLAT DRIPLINE 12MM ISI</v>
       </c>
       <c r="E1148" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40577,7 +40577,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1148" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1148" t="str">
         <v>ROLL</v>
@@ -40589,7 +40589,7 @@
         <v>Active</v>
       </c>
       <c r="K1148" t="str">
-        <v>FLAT DRIPLINE 16MM ISI certified.</v>
+        <v>FLAT DRIPLINE 12MM ISI certified.</v>
       </c>
     </row>
     <row r="1149">
@@ -40597,10 +40597,10 @@
         <v>1148</v>
       </c>
       <c r="B1149" t="str">
-        <v>FG-401761</v>
+        <v>FG-401760</v>
       </c>
       <c r="C1149" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1149" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40612,7 +40612,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1149" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1149" t="str">
         <v>ROLL</v>
@@ -40632,10 +40632,10 @@
         <v>1149</v>
       </c>
       <c r="B1150" t="str">
-        <v>FG-401762</v>
+        <v>FG-401761</v>
       </c>
       <c r="C1150" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1150" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40647,7 +40647,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1150" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1150" t="str">
         <v>ROLL</v>
@@ -40667,10 +40667,10 @@
         <v>1150</v>
       </c>
       <c r="B1151" t="str">
-        <v>FG-401769</v>
+        <v>FG-401762</v>
       </c>
       <c r="C1151" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1151" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40682,7 +40682,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1151" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1151" t="str">
         <v>ROLL</v>
@@ -40702,10 +40702,10 @@
         <v>1151</v>
       </c>
       <c r="B1152" t="str">
-        <v>FG-401770</v>
+        <v>FG-401769</v>
       </c>
       <c r="C1152" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1152" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40717,7 +40717,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1152" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1152" t="str">
         <v>ROLL</v>
@@ -40737,10 +40737,10 @@
         <v>1152</v>
       </c>
       <c r="B1153" t="str">
-        <v>FG-401779</v>
+        <v>FG-401770</v>
       </c>
       <c r="C1153" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1153" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40752,7 +40752,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1153" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1153" t="str">
         <v>ROLL</v>
@@ -40772,13 +40772,13 @@
         <v>1153</v>
       </c>
       <c r="B1154" t="str">
-        <v>FG-401771</v>
+        <v>FG-401779</v>
       </c>
       <c r="C1154" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1154" t="str">
-        <v>FLAT DRIPLINE 20MM ISI</v>
+        <v>FLAT DRIPLINE 16MM ISI</v>
       </c>
       <c r="E1154" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40787,7 +40787,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1154" t="str">
-        <v>20-4-30 CLASS 1</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1154" t="str">
         <v>ROLL</v>
@@ -40799,7 +40799,7 @@
         <v>Active</v>
       </c>
       <c r="K1154" t="str">
-        <v>FLAT DRIPLINE 20MM ISI certified.</v>
+        <v>FLAT DRIPLINE 16MM ISI certified.</v>
       </c>
     </row>
     <row r="1155">
@@ -40807,10 +40807,10 @@
         <v>1154</v>
       </c>
       <c r="B1155" t="str">
-        <v>FG-401772</v>
+        <v>FG-401771</v>
       </c>
       <c r="C1155" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-30 CLASS 1)</v>
       </c>
       <c r="D1155" t="str">
         <v>FLAT DRIPLINE 20MM ISI</v>
@@ -40822,7 +40822,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1155" t="str">
-        <v>20-4-40 CLASS 1</v>
+        <v>20-4-30 CLASS 1</v>
       </c>
       <c r="H1155" t="str">
         <v>ROLL</v>
@@ -40842,10 +40842,10 @@
         <v>1155</v>
       </c>
       <c r="B1156" t="str">
-        <v>FG-401773</v>
+        <v>FG-401772</v>
       </c>
       <c r="C1156" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-40 CLASS 1)</v>
       </c>
       <c r="D1156" t="str">
         <v>FLAT DRIPLINE 20MM ISI</v>
@@ -40857,7 +40857,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1156" t="str">
-        <v>20-4-50 CLASS 1</v>
+        <v>20-4-40 CLASS 1</v>
       </c>
       <c r="H1156" t="str">
         <v>ROLL</v>
@@ -40877,25 +40877,25 @@
         <v>1156</v>
       </c>
       <c r="B1157" t="str">
-        <v>-</v>
+        <v>FG-401773</v>
       </c>
       <c r="C1157" t="str">
-        <v>12MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-50 CLASS 1)</v>
       </c>
       <c r="D1157" t="str">
-        <v>12MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>FLAT DRIPLINE 20MM ISI</v>
       </c>
       <c r="E1157" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1157" t="str">
-        <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
+        <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1157" t="str">
-        <v>CLASS-2</v>
+        <v>20-4-50 CLASS 1</v>
       </c>
       <c r="H1157" t="str">
-        <v>MTR</v>
+        <v>ROLL</v>
       </c>
       <c r="I1157" t="str">
         <v>-</v>
@@ -40904,7 +40904,7 @@
         <v>Active</v>
       </c>
       <c r="K1157" t="str">
-        <v>12mm Plain Lateral Online Drip Pipe.</v>
+        <v>FLAT DRIPLINE 20MM ISI certified.</v>
       </c>
     </row>
     <row r="1158">
@@ -40915,10 +40915,10 @@
         <v>-</v>
       </c>
       <c r="C1158" t="str">
-        <v>16MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>12MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1158" t="str">
-        <v>16MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>12MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1158" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40939,7 +40939,7 @@
         <v>Active</v>
       </c>
       <c r="K1158" t="str">
-        <v>16mm Plain Lateral Online Drip Pipe.</v>
+        <v>12mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1159">
@@ -40950,10 +40950,10 @@
         <v>-</v>
       </c>
       <c r="C1159" t="str">
-        <v>20MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>16MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1159" t="str">
-        <v>20MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>16MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1159" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40974,7 +40974,7 @@
         <v>Active</v>
       </c>
       <c r="K1159" t="str">
-        <v>20mm Plain Lateral Online Drip Pipe.</v>
+        <v>16mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1160">
@@ -40985,10 +40985,10 @@
         <v>-</v>
       </c>
       <c r="C1160" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-1)</v>
+        <v>20MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1160" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>20MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1160" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40997,7 +40997,7 @@
         <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1160" t="str">
-        <v>CLASS-1</v>
+        <v>CLASS-2</v>
       </c>
       <c r="H1160" t="str">
         <v>MTR</v>
@@ -41009,7 +41009,7 @@
         <v>Active</v>
       </c>
       <c r="K1160" t="str">
-        <v>32mm Plain Lateral Online Drip Pipe.</v>
+        <v>20mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1161">
@@ -41020,7 +41020,7 @@
         <v>-</v>
       </c>
       <c r="C1161" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-1)</v>
       </c>
       <c r="D1161" t="str">
         <v>32MM PLAIN LATERAL ONLINE PIPE</v>
@@ -41032,7 +41032,7 @@
         <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1161" t="str">
-        <v>CLASS-2</v>
+        <v>CLASS-1</v>
       </c>
       <c r="H1161" t="str">
         <v>MTR</v>
@@ -41052,22 +41052,22 @@
         <v>1161</v>
       </c>
       <c r="B1162" t="str">
-        <v>FG-401763</v>
+        <v>-</v>
       </c>
       <c r="C1162" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 2)</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1162" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1162" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1162" t="str">
-        <v>FLAT DRIP (PEPSI) - INLINE</v>
+        <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1162" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>CLASS-2</v>
       </c>
       <c r="H1162" t="str">
         <v>MTR</v>
@@ -41079,7 +41079,7 @@
         <v>Active</v>
       </c>
       <c r="K1162" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12. Available sizes: 12-4-30 CLASS 2, 12-4-40 CLASS 2, 12-4-50 CLASS 2, 12-4-30 CLASS 3, 12-4-40 CLASS 3, 12-4-50 CLASS 3.</v>
+        <v>32mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1163">
@@ -41087,10 +41087,10 @@
         <v>1162</v>
       </c>
       <c r="B1163" t="str">
-        <v>FG-401764</v>
+        <v>FG-401763</v>
       </c>
       <c r="C1163" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1163" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41102,7 +41102,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1163" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1163" t="str">
         <v>MTR</v>
@@ -41122,10 +41122,10 @@
         <v>1163</v>
       </c>
       <c r="B1164" t="str">
-        <v>FG-401765</v>
+        <v>FG-401764</v>
       </c>
       <c r="C1164" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1164" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41137,7 +41137,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1164" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1164" t="str">
         <v>MTR</v>
@@ -41157,10 +41157,10 @@
         <v>1164</v>
       </c>
       <c r="B1165" t="str">
-        <v>FG-401766</v>
+        <v>FG-401765</v>
       </c>
       <c r="C1165" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1165" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41172,7 +41172,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1165" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1165" t="str">
         <v>MTR</v>
@@ -41192,10 +41192,10 @@
         <v>1165</v>
       </c>
       <c r="B1166" t="str">
-        <v>FG-401767</v>
+        <v>FG-401766</v>
       </c>
       <c r="C1166" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1166" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41207,7 +41207,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1166" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1166" t="str">
         <v>MTR</v>
@@ -41227,10 +41227,10 @@
         <v>1166</v>
       </c>
       <c r="B1167" t="str">
-        <v>FG-401768</v>
+        <v>FG-401767</v>
       </c>
       <c r="C1167" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1167" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41242,7 +41242,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1167" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1167" t="str">
         <v>MTR</v>
@@ -41262,13 +41262,13 @@
         <v>1167</v>
       </c>
       <c r="B1168" t="str">
-        <v>FG-401760</v>
+        <v>FG-401768</v>
       </c>
       <c r="C1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12</v>
       </c>
       <c r="E1168" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -41277,7 +41277,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1168" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1168" t="str">
         <v>MTR</v>
@@ -41289,7 +41289,7 @@
         <v>Active</v>
       </c>
       <c r="K1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16. Available sizes: 16-4-30 CLASS 1, 16-4-40 CLASS 1, 16-4-50 CLASS 1, 16-4-30 CLASS 2, 16-4-40 CLASS 2, 16-4-50 CLASS 2.</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12. Available sizes: 12-4-30 CLASS 2, 12-4-40 CLASS 2, 12-4-50 CLASS 2, 12-4-30 CLASS 3, 12-4-40 CLASS 3, 12-4-50 CLASS 3.</v>
       </c>
     </row>
     <row r="1169">
@@ -41297,10 +41297,10 @@
         <v>1168</v>
       </c>
       <c r="B1169" t="str">
-        <v>FG-401761</v>
+        <v>FG-401760</v>
       </c>
       <c r="C1169" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1169" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41312,7 +41312,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1169" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1169" t="str">
         <v>MTR</v>
@@ -41332,10 +41332,10 @@
         <v>1169</v>
       </c>
       <c r="B1170" t="str">
-        <v>FG-401762</v>
+        <v>FG-401761</v>
       </c>
       <c r="C1170" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1170" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41347,7 +41347,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1170" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1170" t="str">
         <v>MTR</v>
@@ -41367,10 +41367,10 @@
         <v>1170</v>
       </c>
       <c r="B1171" t="str">
-        <v>FG-401769</v>
+        <v>FG-401762</v>
       </c>
       <c r="C1171" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1171" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41382,7 +41382,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1171" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1171" t="str">
         <v>MTR</v>
@@ -41402,10 +41402,10 @@
         <v>1171</v>
       </c>
       <c r="B1172" t="str">
-        <v>FG-401770</v>
+        <v>FG-401769</v>
       </c>
       <c r="C1172" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1172" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41417,7 +41417,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1172" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1172" t="str">
         <v>MTR</v>
@@ -41437,10 +41437,10 @@
         <v>1172</v>
       </c>
       <c r="B1173" t="str">
-        <v>FG-401779</v>
+        <v>FG-401770</v>
       </c>
       <c r="C1173" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1173" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41452,7 +41452,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1173" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1173" t="str">
         <v>MTR</v>
@@ -41472,13 +41472,13 @@
         <v>1173</v>
       </c>
       <c r="B1174" t="str">
-        <v>FG-401771</v>
+        <v>FG-401779</v>
       </c>
       <c r="C1174" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1174" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16</v>
       </c>
       <c r="E1174" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -41487,7 +41487,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1174" t="str">
-        <v>20-4-30 CLASS 1</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1174" t="str">
         <v>MTR</v>
@@ -41499,7 +41499,7 @@
         <v>Active</v>
       </c>
       <c r="K1174" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20. Available sizes: 20-4-30 CLASS 1, 20-4-40 CLASS 1, 20-4-50 CLASS 1.</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16. Available sizes: 16-4-30 CLASS 1, 16-4-40 CLASS 1, 16-4-50 CLASS 1, 16-4-30 CLASS 2, 16-4-40 CLASS 2, 16-4-50 CLASS 2.</v>
       </c>
     </row>
     <row r="1175">
@@ -41507,10 +41507,10 @@
         <v>1174</v>
       </c>
       <c r="B1175" t="str">
-        <v>FG-401772</v>
+        <v>FG-401771</v>
       </c>
       <c r="C1175" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-30 CLASS 1)</v>
       </c>
       <c r="D1175" t="str">
         <v>FLAT DRIPLINE ISI 400MTR 20</v>
@@ -41522,7 +41522,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1175" t="str">
-        <v>20-4-40 CLASS 1</v>
+        <v>20-4-30 CLASS 1</v>
       </c>
       <c r="H1175" t="str">
         <v>MTR</v>
@@ -41542,10 +41542,10 @@
         <v>1175</v>
       </c>
       <c r="B1176" t="str">
-        <v>FG-401773</v>
+        <v>FG-401772</v>
       </c>
       <c r="C1176" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-40 CLASS 1)</v>
       </c>
       <c r="D1176" t="str">
         <v>FLAT DRIPLINE ISI 400MTR 20</v>
@@ -41557,7 +41557,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1176" t="str">
-        <v>20-4-50 CLASS 1</v>
+        <v>20-4-40 CLASS 1</v>
       </c>
       <c r="H1176" t="str">
         <v>MTR</v>
@@ -41577,22 +41577,22 @@
         <v>1176</v>
       </c>
       <c r="B1177" t="str">
-        <v>FG-401066</v>
+        <v>FG-401773</v>
       </c>
       <c r="C1177" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-50 CLASS 1)</v>
       </c>
       <c r="D1177" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20</v>
       </c>
       <c r="E1177" t="str">
-        <v>UPVC CASING PIPES</v>
+        <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1177" t="str">
-        <v>General</v>
+        <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1177" t="str">
-        <v>35MM 1 1/4 Inch</v>
+        <v>20-4-50 CLASS 1</v>
       </c>
       <c r="H1177" t="str">
         <v>MTR</v>
@@ -41604,7 +41604,7 @@
         <v>Active</v>
       </c>
       <c r="K1177" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 40MM 1 1/2 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20. Available sizes: 20-4-30 CLASS 1, 20-4-40 CLASS 1, 20-4-50 CLASS 1.</v>
       </c>
     </row>
     <row r="1178">
@@ -41612,10 +41612,10 @@
         <v>1177</v>
       </c>
       <c r="B1178" t="str">
-        <v>FG-401067</v>
+        <v>FG-401066</v>
       </c>
       <c r="C1178" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (40MM 1 1/2 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
       </c>
       <c r="D1178" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41627,7 +41627,7 @@
         <v>General</v>
       </c>
       <c r="G1178" t="str">
-        <v>40MM 1 1/2 Inch</v>
+        <v>35MM 1 1/4 Inch</v>
       </c>
       <c r="H1178" t="str">
         <v>MTR</v>
@@ -41647,10 +41647,10 @@
         <v>1178</v>
       </c>
       <c r="B1179" t="str">
-        <v>FG-401068</v>
+        <v>FG-401067</v>
       </c>
       <c r="C1179" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (50MM 2 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (40MM 1 1/2 Inch)</v>
       </c>
       <c r="D1179" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41662,7 +41662,7 @@
         <v>General</v>
       </c>
       <c r="G1179" t="str">
-        <v>50MM 2 Inch</v>
+        <v>40MM 1 1/2 Inch</v>
       </c>
       <c r="H1179" t="str">
         <v>MTR</v>
@@ -41682,10 +41682,10 @@
         <v>1179</v>
       </c>
       <c r="B1180" t="str">
-        <v>FG-401069</v>
+        <v>FG-401068</v>
       </c>
       <c r="C1180" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (100MM 4 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (50MM 2 Inch)</v>
       </c>
       <c r="D1180" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41697,7 +41697,7 @@
         <v>General</v>
       </c>
       <c r="G1180" t="str">
-        <v>100MM 4 Inch</v>
+        <v>50MM 2 Inch</v>
       </c>
       <c r="H1180" t="str">
         <v>MTR</v>
@@ -41717,10 +41717,10 @@
         <v>1180</v>
       </c>
       <c r="B1181" t="str">
-        <v>FG-401070</v>
+        <v>FG-401069</v>
       </c>
       <c r="C1181" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (100MM 4 Inch)</v>
       </c>
       <c r="D1181" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41732,7 +41732,7 @@
         <v>General</v>
       </c>
       <c r="G1181" t="str">
-        <v>125MM 5 Inch</v>
+        <v>100MM 4 Inch</v>
       </c>
       <c r="H1181" t="str">
         <v>MTR</v>
@@ -41752,10 +41752,10 @@
         <v>1181</v>
       </c>
       <c r="B1182" t="str">
-        <v>FG-401071</v>
+        <v>FG-401070</v>
       </c>
       <c r="C1182" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1182" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41767,7 +41767,7 @@
         <v>General</v>
       </c>
       <c r="G1182" t="str">
-        <v>150MM 6 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1182" t="str">
         <v>MTR</v>
@@ -41787,10 +41787,10 @@
         <v>1182</v>
       </c>
       <c r="B1183" t="str">
-        <v>FG-401072</v>
+        <v>FG-401071</v>
       </c>
       <c r="C1183" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1183" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41802,7 +41802,7 @@
         <v>General</v>
       </c>
       <c r="G1183" t="str">
-        <v>175MM 7 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1183" t="str">
         <v>MTR</v>
@@ -41822,10 +41822,10 @@
         <v>1183</v>
       </c>
       <c r="B1184" t="str">
-        <v>FG-401073</v>
+        <v>FG-401072</v>
       </c>
       <c r="C1184" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1184" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41837,7 +41837,7 @@
         <v>General</v>
       </c>
       <c r="G1184" t="str">
-        <v>200MM 8 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1184" t="str">
         <v>MTR</v>
@@ -41857,13 +41857,13 @@
         <v>1184</v>
       </c>
       <c r="B1185" t="str">
-        <v>FG-401074</v>
+        <v>FG-401073</v>
       </c>
       <c r="C1185" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1185" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
       </c>
       <c r="E1185" t="str">
         <v>UPVC CASING PIPES</v>
@@ -41872,7 +41872,7 @@
         <v>General</v>
       </c>
       <c r="G1185" t="str">
-        <v>125MM 5 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1185" t="str">
         <v>MTR</v>
@@ -41884,7 +41884,7 @@
         <v>Active</v>
       </c>
       <c r="K1185" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 40MM 1 1/2 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1186">
@@ -41892,10 +41892,10 @@
         <v>1185</v>
       </c>
       <c r="B1186" t="str">
-        <v>FG-401075</v>
+        <v>FG-401074</v>
       </c>
       <c r="C1186" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1186" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41907,7 +41907,7 @@
         <v>General</v>
       </c>
       <c r="G1186" t="str">
-        <v>150MM 6 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1186" t="str">
         <v>MTR</v>
@@ -41927,10 +41927,10 @@
         <v>1186</v>
       </c>
       <c r="B1187" t="str">
-        <v>FG-401076</v>
+        <v>FG-401075</v>
       </c>
       <c r="C1187" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1187" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41942,7 +41942,7 @@
         <v>General</v>
       </c>
       <c r="G1187" t="str">
-        <v>175MM 7 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1187" t="str">
         <v>MTR</v>
@@ -41962,10 +41962,10 @@
         <v>1187</v>
       </c>
       <c r="B1188" t="str">
-        <v>FG-401077</v>
+        <v>FG-401076</v>
       </c>
       <c r="C1188" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1188" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41977,7 +41977,7 @@
         <v>General</v>
       </c>
       <c r="G1188" t="str">
-        <v>200MM 8 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1188" t="str">
         <v>MTR</v>
@@ -41997,13 +41997,13 @@
         <v>1188</v>
       </c>
       <c r="B1189" t="str">
-        <v>FG-401149</v>
+        <v>FG-401077</v>
       </c>
       <c r="C1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M (140MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
       </c>
       <c r="E1189" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42012,7 +42012,7 @@
         <v>General</v>
       </c>
       <c r="G1189" t="str">
-        <v>140MM 5 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1189" t="str">
         <v>MTR</v>
@@ -42024,7 +42024,7 @@
         <v>Active</v>
       </c>
       <c r="K1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M. Available sizes: 140MM 5 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1190">
@@ -42032,13 +42032,13 @@
         <v>1189</v>
       </c>
       <c r="B1190" t="str">
-        <v>FG-401150</v>
+        <v>FG-401149</v>
       </c>
       <c r="C1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M (140MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M (140MM 5 Inch)</v>
       </c>
       <c r="D1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M</v>
       </c>
       <c r="E1190" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42059,7 +42059,7 @@
         <v>Active</v>
       </c>
       <c r="K1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M. Available sizes: 140MM 5 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M. Available sizes: 140MM 5 Inch.</v>
       </c>
     </row>
     <row r="1191">
@@ -42067,13 +42067,13 @@
         <v>1190</v>
       </c>
       <c r="B1191" t="str">
-        <v>FG-401078</v>
+        <v>FG-401150</v>
       </c>
       <c r="C1191" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M (140MM 5 Inch)</v>
       </c>
       <c r="D1191" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M</v>
       </c>
       <c r="E1191" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42082,7 +42082,7 @@
         <v>General</v>
       </c>
       <c r="G1191" t="str">
-        <v>125MM 5 Inch</v>
+        <v>140MM 5 Inch</v>
       </c>
       <c r="H1191" t="str">
         <v>MTR</v>
@@ -42094,7 +42094,7 @@
         <v>Active</v>
       </c>
       <c r="K1191" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M. Available sizes: 140MM 5 Inch.</v>
       </c>
     </row>
     <row r="1192">
@@ -42102,10 +42102,10 @@
         <v>1191</v>
       </c>
       <c r="B1192" t="str">
-        <v>FG-401079</v>
+        <v>FG-401078</v>
       </c>
       <c r="C1192" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1192" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42117,7 +42117,7 @@
         <v>General</v>
       </c>
       <c r="G1192" t="str">
-        <v>150MM 6 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1192" t="str">
         <v>MTR</v>
@@ -42137,10 +42137,10 @@
         <v>1192</v>
       </c>
       <c r="B1193" t="str">
-        <v>FG-401080</v>
+        <v>FG-401079</v>
       </c>
       <c r="C1193" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1193" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42152,7 +42152,7 @@
         <v>General</v>
       </c>
       <c r="G1193" t="str">
-        <v>175MM 7 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1193" t="str">
         <v>MTR</v>
@@ -42172,10 +42172,10 @@
         <v>1193</v>
       </c>
       <c r="B1194" t="str">
-        <v>FG-401081</v>
+        <v>FG-401080</v>
       </c>
       <c r="C1194" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1194" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42187,7 +42187,7 @@
         <v>General</v>
       </c>
       <c r="G1194" t="str">
-        <v>200MM 8 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1194" t="str">
         <v>MTR</v>
@@ -42207,13 +42207,13 @@
         <v>1194</v>
       </c>
       <c r="B1195" t="str">
-        <v>FG-401119</v>
+        <v>FG-401081</v>
       </c>
       <c r="C1195" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1195" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
       </c>
       <c r="E1195" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42222,7 +42222,7 @@
         <v>General</v>
       </c>
       <c r="G1195" t="str">
-        <v>35MM 1 1/4 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1195" t="str">
         <v>MTR</v>
@@ -42234,7 +42234,7 @@
         <v>Active</v>
       </c>
       <c r="K1195" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1196">
@@ -42242,10 +42242,10 @@
         <v>1195</v>
       </c>
       <c r="B1196" t="str">
-        <v>FG-401121</v>
+        <v>FG-401119</v>
       </c>
       <c r="C1196" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (50MM 2 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
       </c>
       <c r="D1196" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42257,7 +42257,7 @@
         <v>General</v>
       </c>
       <c r="G1196" t="str">
-        <v>50MM 2 Inch</v>
+        <v>35MM 1 1/4 Inch</v>
       </c>
       <c r="H1196" t="str">
         <v>MTR</v>
@@ -42277,10 +42277,10 @@
         <v>1196</v>
       </c>
       <c r="B1197" t="str">
-        <v>FG-401122</v>
+        <v>FG-401121</v>
       </c>
       <c r="C1197" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (100MM 4 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (50MM 2 Inch)</v>
       </c>
       <c r="D1197" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42292,7 +42292,7 @@
         <v>General</v>
       </c>
       <c r="G1197" t="str">
-        <v>100MM 4 Inch</v>
+        <v>50MM 2 Inch</v>
       </c>
       <c r="H1197" t="str">
         <v>MTR</v>
@@ -42312,10 +42312,10 @@
         <v>1197</v>
       </c>
       <c r="B1198" t="str">
-        <v>FG-401123</v>
+        <v>FG-401122</v>
       </c>
       <c r="C1198" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (100MM 4 Inch)</v>
       </c>
       <c r="D1198" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42327,7 +42327,7 @@
         <v>General</v>
       </c>
       <c r="G1198" t="str">
-        <v>125MM 5 Inch</v>
+        <v>100MM 4 Inch</v>
       </c>
       <c r="H1198" t="str">
         <v>MTR</v>
@@ -42347,10 +42347,10 @@
         <v>1198</v>
       </c>
       <c r="B1199" t="str">
-        <v>FG-401124</v>
+        <v>FG-401123</v>
       </c>
       <c r="C1199" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1199" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42362,7 +42362,7 @@
         <v>General</v>
       </c>
       <c r="G1199" t="str">
-        <v>150MM 6 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1199" t="str">
         <v>MTR</v>
@@ -42382,10 +42382,10 @@
         <v>1199</v>
       </c>
       <c r="B1200" t="str">
-        <v>FG-401125</v>
+        <v>FG-401124</v>
       </c>
       <c r="C1200" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1200" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42397,7 +42397,7 @@
         <v>General</v>
       </c>
       <c r="G1200" t="str">
-        <v>175MM 7 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1200" t="str">
         <v>MTR</v>
@@ -42417,10 +42417,10 @@
         <v>1200</v>
       </c>
       <c r="B1201" t="str">
-        <v>FG-401126</v>
+        <v>FG-401125</v>
       </c>
       <c r="C1201" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1201" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42432,7 +42432,7 @@
         <v>General</v>
       </c>
       <c r="G1201" t="str">
-        <v>200MM 8 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1201" t="str">
         <v>MTR</v>
@@ -42452,22 +42452,22 @@
         <v>1201</v>
       </c>
       <c r="B1202" t="str">
-        <v>FG-401166</v>
+        <v>FG-401126</v>
       </c>
       <c r="C1202" t="str">
-        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG COUPLER TYPE)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1202" t="str">
-        <v>COLOUMN PIPE ECO V4</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
       </c>
       <c r="E1202" t="str">
-        <v>UPVC COLUMN PIPES</v>
+        <v>UPVC CASING PIPES</v>
       </c>
       <c r="F1202" t="str">
         <v>General</v>
       </c>
       <c r="G1202" t="str">
-        <v>33MM 12.5KG COUPLER TYPE</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1202" t="str">
         <v>MTR</v>
@@ -42479,7 +42479,7 @@
         <v>Active</v>
       </c>
       <c r="K1202" t="str">
-        <v>COLOUMN PIPE ECO V4 for submersible pump systems.</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1203">
@@ -42487,10 +42487,10 @@
         <v>1202</v>
       </c>
       <c r="B1203" t="str">
-        <v>FG-401162</v>
+        <v>FG-401166</v>
       </c>
       <c r="C1203" t="str">
-        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG BELL END TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1203" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42502,7 +42502,7 @@
         <v>General</v>
       </c>
       <c r="G1203" t="str">
-        <v>33MM 12.5KG BELL END TYPE</v>
+        <v>33MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1203" t="str">
         <v>MTR</v>
@@ -42522,10 +42522,10 @@
         <v>1203</v>
       </c>
       <c r="B1204" t="str">
-        <v>FG-401165</v>
+        <v>FG-401162</v>
       </c>
       <c r="C1204" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 10KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG BELL END TYPE)</v>
       </c>
       <c r="D1204" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42537,7 +42537,7 @@
         <v>General</v>
       </c>
       <c r="G1204" t="str">
-        <v>42MM 10KG COUPLER TYPE</v>
+        <v>33MM 12.5KG BELL END TYPE</v>
       </c>
       <c r="H1204" t="str">
         <v>MTR</v>
@@ -42557,10 +42557,10 @@
         <v>1204</v>
       </c>
       <c r="B1205" t="str">
-        <v>FG-401167</v>
+        <v>FG-401165</v>
       </c>
       <c r="C1205" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 10KG COUPLER TYPE)</v>
       </c>
       <c r="D1205" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42572,7 +42572,7 @@
         <v>General</v>
       </c>
       <c r="G1205" t="str">
-        <v>42MM 12.5KG COUPLER TYPE</v>
+        <v>42MM 10KG COUPLER TYPE</v>
       </c>
       <c r="H1205" t="str">
         <v>MTR</v>
@@ -42592,10 +42592,10 @@
         <v>1205</v>
       </c>
       <c r="B1206" t="str">
-        <v>FG-401163</v>
+        <v>FG-401167</v>
       </c>
       <c r="C1206" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG BELL END TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1206" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42607,7 +42607,7 @@
         <v>General</v>
       </c>
       <c r="G1206" t="str">
-        <v>42MM 12.5KG BELL END TYPE</v>
+        <v>42MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1206" t="str">
         <v>MTR</v>
@@ -42627,10 +42627,10 @@
         <v>1206</v>
       </c>
       <c r="B1207" t="str">
-        <v>FG-401164</v>
+        <v>FG-401163</v>
       </c>
       <c r="C1207" t="str">
-        <v>COLOUMN PIPE ECO V4 (48MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG BELL END TYPE)</v>
       </c>
       <c r="D1207" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42642,7 +42642,7 @@
         <v>General</v>
       </c>
       <c r="G1207" t="str">
-        <v>48MM 12.5KG COUPLER TYPE</v>
+        <v>42MM 12.5KG BELL END TYPE</v>
       </c>
       <c r="H1207" t="str">
         <v>MTR</v>
@@ -42662,10 +42662,10 @@
         <v>1207</v>
       </c>
       <c r="B1208" t="str">
-        <v>FG-401168</v>
+        <v>FG-401164</v>
       </c>
       <c r="C1208" t="str">
-        <v>COLOUMN PIPE ECO V4 (60MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (48MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1208" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42677,7 +42677,7 @@
         <v>General</v>
       </c>
       <c r="G1208" t="str">
-        <v>60MM 12.5KG COUPLER TYPE</v>
+        <v>48MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1208" t="str">
         <v>MTR</v>
@@ -42697,13 +42697,13 @@
         <v>1208</v>
       </c>
       <c r="B1209" t="str">
-        <v>FG-401175</v>
+        <v>FG-401168</v>
       </c>
       <c r="C1209" t="str">
-        <v>COLOUMN PIPE MEDIUM (33MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (60MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1209" t="str">
-        <v>COLOUMN PIPE MEDIUM</v>
+        <v>COLOUMN PIPE ECO V4</v>
       </c>
       <c r="E1209" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -42712,7 +42712,7 @@
         <v>General</v>
       </c>
       <c r="G1209" t="str">
-        <v>33MM 18KG COUPLER TYPE</v>
+        <v>60MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1209" t="str">
         <v>MTR</v>
@@ -42724,7 +42724,7 @@
         <v>Active</v>
       </c>
       <c r="K1209" t="str">
-        <v>COLOUMN PIPE MEDIUM for submersible pump systems.</v>
+        <v>COLOUMN PIPE ECO V4 for submersible pump systems.</v>
       </c>
     </row>
     <row r="1210">
@@ -42732,10 +42732,10 @@
         <v>1209</v>
       </c>
       <c r="B1210" t="str">
-        <v>FG-401177</v>
+        <v>FG-401175</v>
       </c>
       <c r="C1210" t="str">
-        <v>COLOUMN PIPE MEDIUM (42MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (33MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1210" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42747,7 +42747,7 @@
         <v>General</v>
       </c>
       <c r="G1210" t="str">
-        <v>42MM 18KG COUPLER TYPE</v>
+        <v>33MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1210" t="str">
         <v>MTR</v>
@@ -42767,10 +42767,10 @@
         <v>1210</v>
       </c>
       <c r="B1211" t="str">
-        <v>FG-401176</v>
+        <v>FG-401177</v>
       </c>
       <c r="C1211" t="str">
-        <v>COLOUMN PIPE MEDIUM (48MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (42MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1211" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42782,7 +42782,7 @@
         <v>General</v>
       </c>
       <c r="G1211" t="str">
-        <v>48MM 18KG COUPLER TYPE</v>
+        <v>42MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1211" t="str">
         <v>MTR</v>
@@ -42802,10 +42802,10 @@
         <v>1211</v>
       </c>
       <c r="B1212" t="str">
-        <v>FG-401178</v>
+        <v>FG-401176</v>
       </c>
       <c r="C1212" t="str">
-        <v>COLOUMN PIPE MEDIUM (60MM 15KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (48MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1212" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42817,7 +42817,7 @@
         <v>General</v>
       </c>
       <c r="G1212" t="str">
-        <v>60MM 15KG COUPLER TYPE</v>
+        <v>48MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1212" t="str">
         <v>MTR</v>
@@ -42837,10 +42837,10 @@
         <v>1212</v>
       </c>
       <c r="B1213" t="str">
-        <v>FG-401180</v>
+        <v>FG-401178</v>
       </c>
       <c r="C1213" t="str">
-        <v>COLOUMN PIPE MEDIUM (75MM 10KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (60MM 15KG COUPLER TYPE)</v>
       </c>
       <c r="D1213" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42852,7 +42852,7 @@
         <v>General</v>
       </c>
       <c r="G1213" t="str">
-        <v>75MM 10KG COUPLER TYPE</v>
+        <v>60MM 15KG COUPLER TYPE</v>
       </c>
       <c r="H1213" t="str">
         <v>MTR</v>
@@ -42872,13 +42872,13 @@
         <v>1213</v>
       </c>
       <c r="B1214" t="str">
-        <v>FG-401169</v>
+        <v>FG-401180</v>
       </c>
       <c r="C1214" t="str">
-        <v>COLOUMN PIPE STANDARD (33MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (75MM 10KG COUPLER TYPE)</v>
       </c>
       <c r="D1214" t="str">
-        <v>COLOUMN PIPE STANDARD</v>
+        <v>COLOUMN PIPE MEDIUM</v>
       </c>
       <c r="E1214" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -42887,7 +42887,7 @@
         <v>General</v>
       </c>
       <c r="G1214" t="str">
-        <v>33MM 25KG COUPLER TYPE</v>
+        <v>75MM 10KG COUPLER TYPE</v>
       </c>
       <c r="H1214" t="str">
         <v>MTR</v>
@@ -42899,7 +42899,7 @@
         <v>Active</v>
       </c>
       <c r="K1214" t="str">
-        <v>COLOUMN PIPE STANDARD for submersible pump systems.</v>
+        <v>COLOUMN PIPE MEDIUM for submersible pump systems.</v>
       </c>
     </row>
     <row r="1215">
@@ -42907,10 +42907,10 @@
         <v>1214</v>
       </c>
       <c r="B1215" t="str">
-        <v>FG-401171</v>
+        <v>FG-401169</v>
       </c>
       <c r="C1215" t="str">
-        <v>COLOUMN PIPE STANDARD (42MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (33MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1215" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42922,7 +42922,7 @@
         <v>General</v>
       </c>
       <c r="G1215" t="str">
-        <v>42MM 25KG COUPLER TYPE</v>
+        <v>33MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1215" t="str">
         <v>MTR</v>
@@ -42942,10 +42942,10 @@
         <v>1215</v>
       </c>
       <c r="B1216" t="str">
-        <v>FG-401170</v>
+        <v>FG-401171</v>
       </c>
       <c r="C1216" t="str">
-        <v>COLOUMN PIPE STANDARD (48MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (42MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1216" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42957,7 +42957,7 @@
         <v>General</v>
       </c>
       <c r="G1216" t="str">
-        <v>48MM 25KG COUPLER TYPE</v>
+        <v>42MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1216" t="str">
         <v>MTR</v>
@@ -42977,10 +42977,10 @@
         <v>1216</v>
       </c>
       <c r="B1217" t="str">
-        <v>FG-401172</v>
+        <v>FG-401170</v>
       </c>
       <c r="C1217" t="str">
-        <v>COLOUMN PIPE STANDARD (60MM 20KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (48MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1217" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42992,7 +42992,7 @@
         <v>General</v>
       </c>
       <c r="G1217" t="str">
-        <v>60MM 20KG COUPLER TYPE</v>
+        <v>48MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1217" t="str">
         <v>MTR</v>
@@ -43012,10 +43012,10 @@
         <v>1217</v>
       </c>
       <c r="B1218" t="str">
-        <v>FG-401174</v>
+        <v>FG-401172</v>
       </c>
       <c r="C1218" t="str">
-        <v>COLOUMN PIPE STANDARD (75MM 20KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (60MM 20KG COUPLER TYPE)</v>
       </c>
       <c r="D1218" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -43027,7 +43027,7 @@
         <v>General</v>
       </c>
       <c r="G1218" t="str">
-        <v>75MM 20KG COUPLER TYPE</v>
+        <v>60MM 20KG COUPLER TYPE</v>
       </c>
       <c r="H1218" t="str">
         <v>MTR</v>
@@ -43047,13 +43047,13 @@
         <v>1218</v>
       </c>
       <c r="B1219" t="str">
-        <v>-</v>
+        <v>FG-401174</v>
       </c>
       <c r="C1219" t="str">
-        <v>3M STANDARD PLUS PIPE (60MM 25 COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (75MM 20KG COUPLER TYPE)</v>
       </c>
       <c r="D1219" t="str">
-        <v>3M STANDARD PLUS PIPE</v>
+        <v>COLOUMN PIPE STANDARD</v>
       </c>
       <c r="E1219" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43062,7 +43062,7 @@
         <v>General</v>
       </c>
       <c r="G1219" t="str">
-        <v>60MM 25 COUPLER TYPE</v>
+        <v>75MM 20KG COUPLER TYPE</v>
       </c>
       <c r="H1219" t="str">
         <v>MTR</v>
@@ -43074,7 +43074,7 @@
         <v>Active</v>
       </c>
       <c r="K1219" t="str">
-        <v>3M Standard Plus UPVC Column Pipe for submersible pump systems.</v>
+        <v>COLOUMN PIPE STANDARD for submersible pump systems.</v>
       </c>
     </row>
     <row r="1220">
@@ -43082,13 +43082,13 @@
         <v>1219</v>
       </c>
       <c r="B1220" t="str">
-        <v>FG-401182</v>
+        <v>-</v>
       </c>
       <c r="C1220" t="str">
-        <v>COLOUMN PIPE HEAVY (42MM 30KG COUPLER TYPE)</v>
+        <v>3M STANDARD PLUS PIPE (60MM 25 COUPLER TYPE)</v>
       </c>
       <c r="D1220" t="str">
-        <v>COLOUMN PIPE HEAVY</v>
+        <v>3M STANDARD PLUS PIPE</v>
       </c>
       <c r="E1220" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43097,7 +43097,7 @@
         <v>General</v>
       </c>
       <c r="G1220" t="str">
-        <v>42MM 30KG COUPLER TYPE</v>
+        <v>60MM 25 COUPLER TYPE</v>
       </c>
       <c r="H1220" t="str">
         <v>MTR</v>
@@ -43109,7 +43109,7 @@
         <v>Active</v>
       </c>
       <c r="K1220" t="str">
-        <v>COLOUMN PIPE HEAVY for submersible pump systems.</v>
+        <v>3M Standard Plus UPVC Column Pipe for submersible pump systems.</v>
       </c>
     </row>
     <row r="1221">
@@ -43117,10 +43117,10 @@
         <v>1220</v>
       </c>
       <c r="B1221" t="str">
-        <v>FG-401181</v>
+        <v>FG-401182</v>
       </c>
       <c r="C1221" t="str">
-        <v>COLOUMN PIPE HEAVY (48MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (42MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1221" t="str">
         <v>COLOUMN PIPE HEAVY</v>
@@ -43132,7 +43132,7 @@
         <v>General</v>
       </c>
       <c r="G1221" t="str">
-        <v>48MM 30KG COUPLER TYPE</v>
+        <v>42MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1221" t="str">
         <v>MTR</v>
@@ -43152,10 +43152,10 @@
         <v>1221</v>
       </c>
       <c r="B1222" t="str">
-        <v>FG-401183</v>
+        <v>FG-401181</v>
       </c>
       <c r="C1222" t="str">
-        <v>COLOUMN PIPE HEAVY (60MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (48MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1222" t="str">
         <v>COLOUMN PIPE HEAVY</v>
@@ -43167,7 +43167,7 @@
         <v>General</v>
       </c>
       <c r="G1222" t="str">
-        <v>60MM 30KG COUPLER TYPE</v>
+        <v>48MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1222" t="str">
         <v>MTR</v>
@@ -43187,13 +43187,13 @@
         <v>1222</v>
       </c>
       <c r="B1223" t="str">
-        <v>FG-401179</v>
+        <v>FG-401183</v>
       </c>
       <c r="C1223" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS (60MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (60MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1223" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS</v>
+        <v>COLOUMN PIPE HEAVY</v>
       </c>
       <c r="E1223" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43202,7 +43202,7 @@
         <v>General</v>
       </c>
       <c r="G1223" t="str">
-        <v>60MM 18KG COUPLER TYPE</v>
+        <v>60MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1223" t="str">
         <v>MTR</v>
@@ -43214,7 +43214,7 @@
         <v>Active</v>
       </c>
       <c r="K1223" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS for submersible pump systems.</v>
+        <v>COLOUMN PIPE HEAVY for submersible pump systems.</v>
       </c>
     </row>
     <row r="1224">
@@ -43222,34 +43222,34 @@
         <v>1223</v>
       </c>
       <c r="B1224" t="str">
-        <v>FG-401569</v>
+        <v>FG-401179</v>
       </c>
       <c r="C1224" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA (15 Inch)</v>
+        <v>COLOUMN PIPE MEDIUM PLUS (60MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1224" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA</v>
+        <v>COLOUMN PIPE MEDIUM PLUS</v>
       </c>
       <c r="E1224" t="str">
-        <v>HOUSEHOLD PRODUCTS</v>
+        <v>UPVC COLUMN PIPES</v>
       </c>
       <c r="F1224" t="str">
         <v>General</v>
       </c>
       <c r="G1224" t="str">
-        <v>15 Inch</v>
+        <v>60MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1224" t="str">
-        <v>BAGS</v>
+        <v>MTR</v>
       </c>
       <c r="I1224" t="str">
-        <v>75</v>
+        <v>-</v>
       </c>
       <c r="J1224" t="str">
         <v>Active</v>
       </c>
       <c r="K1224" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA high durability ghamela.</v>
+        <v>COLOUMN PIPE MEDIUM PLUS for submersible pump systems.</v>
       </c>
     </row>
     <row r="1225">
@@ -43257,13 +43257,13 @@
         <v>1224</v>
       </c>
       <c r="B1225" t="str">
-        <v>FG-401570</v>
+        <v>FG-401569</v>
       </c>
       <c r="C1225" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI (15 Inch)</v>
+        <v>CONSTRUCTION GHAMELA SHIVA (15 Inch)</v>
       </c>
       <c r="D1225" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI</v>
+        <v>CONSTRUCTION GHAMELA SHIVA</v>
       </c>
       <c r="E1225" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43284,7 +43284,7 @@
         <v>Active</v>
       </c>
       <c r="K1225" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI high durability ghamela.</v>
+        <v>CONSTRUCTION GHAMELA SHIVA high durability ghamela.</v>
       </c>
     </row>
     <row r="1226">
@@ -43292,13 +43292,13 @@
         <v>1225</v>
       </c>
       <c r="B1226" t="str">
-        <v>FG-401571</v>
+        <v>FG-401570</v>
       </c>
       <c r="C1226" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA (16 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA GOURI (15 Inch)</v>
       </c>
       <c r="D1226" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA</v>
+        <v>MULTIPURPOSE GHAMELA GOURI</v>
       </c>
       <c r="E1226" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43307,19 +43307,19 @@
         <v>General</v>
       </c>
       <c r="G1226" t="str">
-        <v>16 Inch</v>
+        <v>15 Inch</v>
       </c>
       <c r="H1226" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1226" t="str">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="J1226" t="str">
         <v>Active</v>
       </c>
       <c r="K1226" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA GOURI high durability ghamela.</v>
       </c>
     </row>
     <row r="1227">
@@ -43327,13 +43327,13 @@
         <v>1226</v>
       </c>
       <c r="B1227" t="str">
-        <v>FG-401573</v>
+        <v>FG-401571</v>
       </c>
       <c r="C1227" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV (18 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA (16 Inch)</v>
       </c>
       <c r="D1227" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA</v>
       </c>
       <c r="E1227" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43342,19 +43342,19 @@
         <v>General</v>
       </c>
       <c r="G1227" t="str">
-        <v>18 Inch</v>
+        <v>16 Inch</v>
       </c>
       <c r="H1227" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1227" t="str">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J1227" t="str">
         <v>Active</v>
       </c>
       <c r="K1227" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA high durability ghamela.</v>
       </c>
     </row>
     <row r="1228">
@@ -43362,13 +43362,13 @@
         <v>1227</v>
       </c>
       <c r="B1228" t="str">
-        <v>FG-401574</v>
+        <v>FG-401573</v>
       </c>
       <c r="C1228" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET (20 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV (18 Inch)</v>
       </c>
       <c r="D1228" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV</v>
       </c>
       <c r="E1228" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43377,19 +43377,19 @@
         <v>General</v>
       </c>
       <c r="G1228" t="str">
-        <v>20 Inch</v>
+        <v>18 Inch</v>
       </c>
       <c r="H1228" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1228" t="str">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J1228" t="str">
         <v>Active</v>
       </c>
       <c r="K1228" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV high durability ghamela.</v>
       </c>
     </row>
     <row r="1229">
@@ -43397,13 +43397,13 @@
         <v>1228</v>
       </c>
       <c r="B1229" t="str">
-        <v>FG-401572</v>
+        <v>FG-401574</v>
       </c>
       <c r="C1229" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI (17 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET (20 Inch)</v>
       </c>
       <c r="D1229" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET</v>
       </c>
       <c r="E1229" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43412,19 +43412,19 @@
         <v>General</v>
       </c>
       <c r="G1229" t="str">
-        <v>17 Inch</v>
+        <v>20 Inch</v>
       </c>
       <c r="H1229" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1229" t="str">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J1229" t="str">
         <v>Active</v>
       </c>
       <c r="K1229" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET high durability ghamela.</v>
       </c>
     </row>
     <row r="1230">
@@ -43432,13 +43432,13 @@
         <v>1229</v>
       </c>
       <c r="B1230" t="str">
-        <v>FG-401575</v>
+        <v>FG-401572</v>
       </c>
       <c r="C1230" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ (22 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI (17 Inch)</v>
       </c>
       <c r="D1230" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI</v>
       </c>
       <c r="E1230" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43447,19 +43447,19 @@
         <v>General</v>
       </c>
       <c r="G1230" t="str">
-        <v>22 Inch</v>
+        <v>17 Inch</v>
       </c>
       <c r="H1230" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1230" t="str">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J1230" t="str">
         <v>Active</v>
       </c>
       <c r="K1230" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI high durability ghamela.</v>
       </c>
     </row>
     <row r="1231">
@@ -43467,13 +43467,13 @@
         <v>1230</v>
       </c>
       <c r="B1231" t="str">
-        <v>FG-401578</v>
+        <v>FG-401575</v>
       </c>
       <c r="C1231" t="str">
-        <v>AQUA PLAST GHAMELA 16 (16 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ (22 Inch)</v>
       </c>
       <c r="D1231" t="str">
-        <v>AQUA PLAST GHAMELA 16</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ</v>
       </c>
       <c r="E1231" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43482,19 +43482,19 @@
         <v>General</v>
       </c>
       <c r="G1231" t="str">
-        <v>16 Inch</v>
+        <v>22 Inch</v>
       </c>
       <c r="H1231" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1231" t="str">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J1231" t="str">
         <v>Active</v>
       </c>
       <c r="K1231" t="str">
-        <v>AQUA PLAST GHAMELA 16 high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ high durability ghamela.</v>
       </c>
     </row>
     <row r="1232">
@@ -43502,13 +43502,13 @@
         <v>1231</v>
       </c>
       <c r="B1232" t="str">
-        <v>FG-401579</v>
+        <v>FG-401578</v>
       </c>
       <c r="C1232" t="str">
-        <v>AQUA PLAST GHAMELA 17 (17 Inch)</v>
+        <v>AQUA PLAST GHAMELA 16 (16 Inch)</v>
       </c>
       <c r="D1232" t="str">
-        <v>AQUA PLAST GHAMELA 17</v>
+        <v>AQUA PLAST GHAMELA 16</v>
       </c>
       <c r="E1232" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43517,7 +43517,7 @@
         <v>General</v>
       </c>
       <c r="G1232" t="str">
-        <v>17 Inch</v>
+        <v>16 Inch</v>
       </c>
       <c r="H1232" t="str">
         <v>BAGS</v>
@@ -43529,7 +43529,7 @@
         <v>Active</v>
       </c>
       <c r="K1232" t="str">
-        <v>AQUA PLAST GHAMELA 17 high durability ghamela.</v>
+        <v>AQUA PLAST GHAMELA 16 high durability ghamela.</v>
       </c>
     </row>
     <row r="1233">
@@ -43537,34 +43537,34 @@
         <v>1232</v>
       </c>
       <c r="B1233" t="str">
-        <v>FG-401364</v>
+        <v>FG-401579</v>
       </c>
       <c r="C1233" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1/2 15MM)</v>
+        <v>AQUA PLAST GHAMELA 17 (17 Inch)</v>
       </c>
       <c r="D1233" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE</v>
+        <v>AQUA PLAST GHAMELA 17</v>
       </c>
       <c r="E1233" t="str">
-        <v>Garden, Braided &amp; LDPE Pipes</v>
+        <v>HOUSEHOLD PRODUCTS</v>
       </c>
       <c r="F1233" t="str">
         <v>General</v>
       </c>
       <c r="G1233" t="str">
-        <v>1/2 15MM</v>
+        <v>17 Inch</v>
       </c>
       <c r="H1233" t="str">
-        <v>BDL</v>
+        <v>BAGS</v>
       </c>
       <c r="I1233" t="str">
-        <v>-</v>
+        <v>60</v>
       </c>
       <c r="J1233" t="str">
         <v>Active</v>
       </c>
       <c r="K1233" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE. Available sizes: 1/2 15MM, 3/4 20MM, 1 25MM, 1 1/4 32MM.</v>
+        <v>AQUA PLAST GHAMELA 17 high durability ghamela.</v>
       </c>
     </row>
     <row r="1234">
@@ -43572,10 +43572,10 @@
         <v>1233</v>
       </c>
       <c r="B1234" t="str">
-        <v>FG-401365</v>
+        <v>FG-401364</v>
       </c>
       <c r="C1234" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (3/4 20MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1/2 15MM)</v>
       </c>
       <c r="D1234" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43587,7 +43587,7 @@
         <v>General</v>
       </c>
       <c r="G1234" t="str">
-        <v>3/4 20MM</v>
+        <v>1/2 15MM</v>
       </c>
       <c r="H1234" t="str">
         <v>BDL</v>
@@ -43607,10 +43607,10 @@
         <v>1234</v>
       </c>
       <c r="B1235" t="str">
-        <v>FG-401366</v>
+        <v>FG-401365</v>
       </c>
       <c r="C1235" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1 25MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (3/4 20MM)</v>
       </c>
       <c r="D1235" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43622,7 +43622,7 @@
         <v>General</v>
       </c>
       <c r="G1235" t="str">
-        <v>1 25MM</v>
+        <v>3/4 20MM</v>
       </c>
       <c r="H1235" t="str">
         <v>BDL</v>
@@ -43642,10 +43642,10 @@
         <v>1235</v>
       </c>
       <c r="B1236" t="str">
-        <v>FG-401367</v>
+        <v>FG-401366</v>
       </c>
       <c r="C1236" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1 1/4 32MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1 25MM)</v>
       </c>
       <c r="D1236" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43657,7 +43657,7 @@
         <v>General</v>
       </c>
       <c r="G1236" t="str">
-        <v>1 1/4 32MM</v>
+        <v>1 25MM</v>
       </c>
       <c r="H1236" t="str">
         <v>BDL</v>
@@ -43677,13 +43677,13 @@
         <v>1236</v>
       </c>
       <c r="B1237" t="str">
-        <v>FG-401370</v>
+        <v>FG-401367</v>
       </c>
       <c r="C1237" t="str">
-        <v>GAP-ORA BRAIDED PIPE (15MM 1/2)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1 1/4 32MM)</v>
       </c>
       <c r="D1237" t="str">
-        <v>GAP-ORA BRAIDED PIPE</v>
+        <v>GAP-ORA FLOW GARDEN PIPE</v>
       </c>
       <c r="E1237" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43692,7 +43692,7 @@
         <v>General</v>
       </c>
       <c r="G1237" t="str">
-        <v>15MM 1/2</v>
+        <v>1 1/4 32MM</v>
       </c>
       <c r="H1237" t="str">
         <v>BDL</v>
@@ -43704,7 +43704,7 @@
         <v>Active</v>
       </c>
       <c r="K1237" t="str">
-        <v>GAP-ORA BRAIDED PIPE.</v>
+        <v>GAP-ORA FLOW GARDEN PIPE. Available sizes: 1/2 15MM, 3/4 20MM, 1 25MM, 1 1/4 32MM.</v>
       </c>
     </row>
     <row r="1238">
@@ -43712,10 +43712,10 @@
         <v>1237</v>
       </c>
       <c r="B1238" t="str">
-        <v>FG-401371</v>
+        <v>FG-401370</v>
       </c>
       <c r="C1238" t="str">
-        <v>GAP-ORA BRAIDED PIPE (20MM 3/4)</v>
+        <v>GAP-ORA BRAIDED PIPE (15MM 1/2)</v>
       </c>
       <c r="D1238" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43727,7 +43727,7 @@
         <v>General</v>
       </c>
       <c r="G1238" t="str">
-        <v>20MM 3/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1238" t="str">
         <v>BDL</v>
@@ -43747,10 +43747,10 @@
         <v>1238</v>
       </c>
       <c r="B1239" t="str">
-        <v>FG-401372</v>
+        <v>FG-401371</v>
       </c>
       <c r="C1239" t="str">
-        <v>GAP-ORA BRAIDED PIPE (25MM 1)</v>
+        <v>GAP-ORA BRAIDED PIPE (20MM 3/4)</v>
       </c>
       <c r="D1239" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43762,7 +43762,7 @@
         <v>General</v>
       </c>
       <c r="G1239" t="str">
-        <v>25MM 1</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1239" t="str">
         <v>BDL</v>
@@ -43782,10 +43782,10 @@
         <v>1239</v>
       </c>
       <c r="B1240" t="str">
-        <v>FG-401373</v>
+        <v>FG-401372</v>
       </c>
       <c r="C1240" t="str">
-        <v>GAP-ORA BRAIDED PIPE (32MM 1 1/4)</v>
+        <v>GAP-ORA BRAIDED PIPE (25MM 1)</v>
       </c>
       <c r="D1240" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43797,7 +43797,7 @@
         <v>General</v>
       </c>
       <c r="G1240" t="str">
-        <v>32MM 1 1/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1240" t="str">
         <v>BDL</v>
@@ -43817,13 +43817,13 @@
         <v>1240</v>
       </c>
       <c r="B1241" t="str">
-        <v>FG-401355</v>
+        <v>FG-401373</v>
       </c>
       <c r="C1241" t="str">
-        <v>GARDEN FOAM PIPES (15MM 1/2)</v>
+        <v>GAP-ORA BRAIDED PIPE (32MM 1 1/4)</v>
       </c>
       <c r="D1241" t="str">
-        <v>GARDEN FOAM PIPES</v>
+        <v>GAP-ORA BRAIDED PIPE</v>
       </c>
       <c r="E1241" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43832,7 +43832,7 @@
         <v>General</v>
       </c>
       <c r="G1241" t="str">
-        <v>15MM 1/2</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1241" t="str">
         <v>BDL</v>
@@ -43844,7 +43844,7 @@
         <v>Active</v>
       </c>
       <c r="K1241" t="str">
-        <v>GARDEN FOAM PIPES.</v>
+        <v>GAP-ORA BRAIDED PIPE.</v>
       </c>
     </row>
     <row r="1242">
@@ -43852,10 +43852,10 @@
         <v>1241</v>
       </c>
       <c r="B1242" t="str">
-        <v>FG-401356</v>
+        <v>FG-401355</v>
       </c>
       <c r="C1242" t="str">
-        <v>GARDEN FOAM PIPES (20MM 3/4)</v>
+        <v>GARDEN FOAM PIPES (15MM 1/2)</v>
       </c>
       <c r="D1242" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43867,7 +43867,7 @@
         <v>General</v>
       </c>
       <c r="G1242" t="str">
-        <v>20MM 3/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1242" t="str">
         <v>BDL</v>
@@ -43887,10 +43887,10 @@
         <v>1242</v>
       </c>
       <c r="B1243" t="str">
-        <v>FG-401369</v>
+        <v>FG-401356</v>
       </c>
       <c r="C1243" t="str">
-        <v>GARDEN FOAM PIPES (20MM 3/4 20MTR)</v>
+        <v>GARDEN FOAM PIPES (20MM 3/4)</v>
       </c>
       <c r="D1243" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43902,7 +43902,7 @@
         <v>General</v>
       </c>
       <c r="G1243" t="str">
-        <v>20MM 3/4 20MTR</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1243" t="str">
         <v>BDL</v>
@@ -43922,10 +43922,10 @@
         <v>1243</v>
       </c>
       <c r="B1244" t="str">
-        <v>FG-401357</v>
+        <v>FG-401369</v>
       </c>
       <c r="C1244" t="str">
-        <v>GARDEN FOAM PIPES (25MM 1)</v>
+        <v>GARDEN FOAM PIPES (20MM 3/4 20MTR)</v>
       </c>
       <c r="D1244" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43937,7 +43937,7 @@
         <v>General</v>
       </c>
       <c r="G1244" t="str">
-        <v>25MM 1</v>
+        <v>20MM 3/4 20MTR</v>
       </c>
       <c r="H1244" t="str">
         <v>BDL</v>
@@ -43957,10 +43957,10 @@
         <v>1244</v>
       </c>
       <c r="B1245" t="str">
-        <v>FG-401358</v>
+        <v>FG-401357</v>
       </c>
       <c r="C1245" t="str">
-        <v>GARDEN FOAM PIPES (32MM 1 1/4)</v>
+        <v>GARDEN FOAM PIPES (25MM 1)</v>
       </c>
       <c r="D1245" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43972,7 +43972,7 @@
         <v>General</v>
       </c>
       <c r="G1245" t="str">
-        <v>32MM 1 1/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1245" t="str">
         <v>BDL</v>
@@ -43992,13 +43992,13 @@
         <v>1245</v>
       </c>
       <c r="B1246" t="str">
-        <v>FG-401344</v>
+        <v>FG-401358</v>
       </c>
       <c r="C1246" t="str">
-        <v>BRAIDED PIPE (15MM 1/2)</v>
+        <v>GARDEN FOAM PIPES (32MM 1 1/4)</v>
       </c>
       <c r="D1246" t="str">
-        <v>BRAIDED PIPE</v>
+        <v>GARDEN FOAM PIPES</v>
       </c>
       <c r="E1246" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44007,7 +44007,7 @@
         <v>General</v>
       </c>
       <c r="G1246" t="str">
-        <v>15MM 1/2</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1246" t="str">
         <v>BDL</v>
@@ -44019,7 +44019,7 @@
         <v>Active</v>
       </c>
       <c r="K1246" t="str">
-        <v>Reinforced Braided Garden Pipe.</v>
+        <v>GARDEN FOAM PIPES.</v>
       </c>
     </row>
     <row r="1247">
@@ -44027,10 +44027,10 @@
         <v>1246</v>
       </c>
       <c r="B1247" t="str">
-        <v>FG-401345</v>
+        <v>FG-401344</v>
       </c>
       <c r="C1247" t="str">
-        <v>BRAIDED PIPE (20MM 3/4)</v>
+        <v>BRAIDED PIPE (15MM 1/2)</v>
       </c>
       <c r="D1247" t="str">
         <v>BRAIDED PIPE</v>
@@ -44042,7 +44042,7 @@
         <v>General</v>
       </c>
       <c r="G1247" t="str">
-        <v>20MM 3/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1247" t="str">
         <v>BDL</v>
@@ -44062,10 +44062,10 @@
         <v>1247</v>
       </c>
       <c r="B1248" t="str">
-        <v>FG-401346</v>
+        <v>FG-401345</v>
       </c>
       <c r="C1248" t="str">
-        <v>BRAIDED PIPE (25MM 1)</v>
+        <v>BRAIDED PIPE (20MM 3/4)</v>
       </c>
       <c r="D1248" t="str">
         <v>BRAIDED PIPE</v>
@@ -44077,7 +44077,7 @@
         <v>General</v>
       </c>
       <c r="G1248" t="str">
-        <v>25MM 1</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1248" t="str">
         <v>BDL</v>
@@ -44097,10 +44097,10 @@
         <v>1248</v>
       </c>
       <c r="B1249" t="str">
-        <v>FG-401363</v>
+        <v>FG-401346</v>
       </c>
       <c r="C1249" t="str">
-        <v>BRAIDED PIPE (32MM 1 1/4)</v>
+        <v>BRAIDED PIPE (25MM 1)</v>
       </c>
       <c r="D1249" t="str">
         <v>BRAIDED PIPE</v>
@@ -44112,7 +44112,7 @@
         <v>General</v>
       </c>
       <c r="G1249" t="str">
-        <v>32MM 1 1/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1249" t="str">
         <v>BDL</v>
@@ -44132,13 +44132,13 @@
         <v>1249</v>
       </c>
       <c r="B1250" t="str">
-        <v>FG-401374</v>
+        <v>FG-401363</v>
       </c>
       <c r="C1250" t="str">
-        <v>LEVEL PIPE (6MM)</v>
+        <v>BRAIDED PIPE (32MM 1 1/4)</v>
       </c>
       <c r="D1250" t="str">
-        <v>LEVEL PIPE</v>
+        <v>BRAIDED PIPE</v>
       </c>
       <c r="E1250" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44147,7 +44147,7 @@
         <v>General</v>
       </c>
       <c r="G1250" t="str">
-        <v>6MM</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1250" t="str">
         <v>BDL</v>
@@ -44159,7 +44159,7 @@
         <v>Active</v>
       </c>
       <c r="K1250" t="str">
-        <v>Transparent Level Pipe for construction &amp; garden work.</v>
+        <v>Reinforced Braided Garden Pipe.</v>
       </c>
     </row>
     <row r="1251">
@@ -44167,13 +44167,13 @@
         <v>1250</v>
       </c>
       <c r="B1251" t="str">
-        <v>FG-401340</v>
+        <v>FG-401374</v>
       </c>
       <c r="C1251" t="str">
-        <v>GARDEN PIPES SUPER FLOW (15MM 1/2)</v>
+        <v>LEVEL PIPE (6MM)</v>
       </c>
       <c r="D1251" t="str">
-        <v>GARDEN PIPES SUPER FLOW</v>
+        <v>LEVEL PIPE</v>
       </c>
       <c r="E1251" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44182,7 +44182,7 @@
         <v>General</v>
       </c>
       <c r="G1251" t="str">
-        <v>15MM 1/2</v>
+        <v>6MM</v>
       </c>
       <c r="H1251" t="str">
         <v>BDL</v>
@@ -44194,7 +44194,7 @@
         <v>Active</v>
       </c>
       <c r="K1251" t="str">
-        <v>GARDEN PIPES SUPER FLOW.</v>
+        <v>Transparent Level Pipe for construction &amp; garden work.</v>
       </c>
     </row>
     <row r="1252">
@@ -44202,10 +44202,10 @@
         <v>1251</v>
       </c>
       <c r="B1252" t="str">
-        <v>FG-401341</v>
+        <v>FG-401340</v>
       </c>
       <c r="C1252" t="str">
-        <v>GARDEN PIPES SUPER FLOW (20MM 3/4)</v>
+        <v>GARDEN PIPES SUPER FLOW (15MM 1/2)</v>
       </c>
       <c r="D1252" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44217,7 +44217,7 @@
         <v>General</v>
       </c>
       <c r="G1252" t="str">
-        <v>20MM 3/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1252" t="str">
         <v>BDL</v>
@@ -44237,10 +44237,10 @@
         <v>1252</v>
       </c>
       <c r="B1253" t="str">
-        <v>FG-401652</v>
+        <v>FG-401341</v>
       </c>
       <c r="C1253" t="str">
-        <v>GARDEN PIPES SUPER FLOW (20MM 3/4 15MTR)</v>
+        <v>GARDEN PIPES SUPER FLOW (20MM 3/4)</v>
       </c>
       <c r="D1253" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44252,7 +44252,7 @@
         <v>General</v>
       </c>
       <c r="G1253" t="str">
-        <v>20MM 3/4 15MTR</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1253" t="str">
         <v>BDL</v>
@@ -44272,10 +44272,10 @@
         <v>1253</v>
       </c>
       <c r="B1254" t="str">
-        <v>FG-401342</v>
+        <v>FG-401652</v>
       </c>
       <c r="C1254" t="str">
-        <v>GARDEN PIPES SUPER FLOW (25MM 1)</v>
+        <v>GARDEN PIPES SUPER FLOW (20MM 3/4 15MTR)</v>
       </c>
       <c r="D1254" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44287,7 +44287,7 @@
         <v>General</v>
       </c>
       <c r="G1254" t="str">
-        <v>25MM 1</v>
+        <v>20MM 3/4 15MTR</v>
       </c>
       <c r="H1254" t="str">
         <v>BDL</v>
@@ -44307,10 +44307,10 @@
         <v>1254</v>
       </c>
       <c r="B1255" t="str">
-        <v>FG-401343</v>
+        <v>FG-401342</v>
       </c>
       <c r="C1255" t="str">
-        <v>GARDEN PIPES SUPER FLOW (32MM 1 1/4)</v>
+        <v>GARDEN PIPES SUPER FLOW (25MM 1)</v>
       </c>
       <c r="D1255" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44322,7 +44322,7 @@
         <v>General</v>
       </c>
       <c r="G1255" t="str">
-        <v>32MM 1 1/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1255" t="str">
         <v>BDL</v>
@@ -44342,10 +44342,10 @@
         <v>1255</v>
       </c>
       <c r="B1256" t="str">
-        <v>FG-401627</v>
+        <v>FG-401343</v>
       </c>
       <c r="C1256" t="str">
-        <v>GARDEN PIPES SUPER FLOW (40MM 1 1/2)</v>
+        <v>GARDEN PIPES SUPER FLOW (32MM 1 1/4)</v>
       </c>
       <c r="D1256" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44357,7 +44357,7 @@
         <v>General</v>
       </c>
       <c r="G1256" t="str">
-        <v>40MM 1 1/2</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1256" t="str">
         <v>BDL</v>
@@ -44377,34 +44377,34 @@
         <v>1256</v>
       </c>
       <c r="B1257" t="str">
-        <v>FG-401552</v>
+        <v>FG-401627</v>
       </c>
       <c r="C1257" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2 inch)</v>
+        <v>GARDEN PIPES SUPER FLOW (40MM 1 1/2)</v>
       </c>
       <c r="D1257" t="str">
-        <v>EDGE SERIES SHORT BODY TAP</v>
+        <v>GARDEN PIPES SUPER FLOW</v>
       </c>
       <c r="E1257" t="str">
-        <v>FAUCETS</v>
+        <v>Garden, Braided &amp; LDPE Pipes</v>
       </c>
       <c r="F1257" t="str">
         <v>General</v>
       </c>
       <c r="G1257" t="str">
-        <v>1/2 inch</v>
+        <v>40MM 1 1/2</v>
       </c>
       <c r="H1257" t="str">
-        <v>NOS</v>
-      </c>
-      <c r="I1257">
-        <v>20</v>
+        <v>BDL</v>
+      </c>
+      <c r="I1257" t="str">
+        <v>-</v>
       </c>
       <c r="J1257" t="str">
         <v>Active</v>
       </c>
       <c r="K1257" t="str">
-        <v>EDGE SERIES SHORT BODY TAP high quality faucet.</v>
+        <v>GARDEN PIPES SUPER FLOW.</v>
       </c>
     </row>
     <row r="1258">
@@ -44415,7 +44415,7 @@
         <v>FG-401552</v>
       </c>
       <c r="C1258" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2 inch)</v>
       </c>
       <c r="D1258" t="str">
         <v>EDGE SERIES SHORT BODY TAP</v>
@@ -44427,7 +44427,7 @@
         <v>General</v>
       </c>
       <c r="G1258" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1258" t="str">
         <v>NOS</v>
@@ -44450,7 +44450,7 @@
         <v>FG-401552</v>
       </c>
       <c r="C1259" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2")</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2)</v>
       </c>
       <c r="D1259" t="str">
         <v>EDGE SERIES SHORT BODY TAP</v>
@@ -44462,7 +44462,7 @@
         <v>General</v>
       </c>
       <c r="G1259" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1259" t="str">
         <v>NOS</v>
@@ -44482,13 +44482,13 @@
         <v>1259</v>
       </c>
       <c r="B1260" t="str">
-        <v>FG-401551</v>
+        <v>FG-401552</v>
       </c>
       <c r="C1260" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2 inch)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2")</v>
       </c>
       <c r="D1260" t="str">
-        <v>EDGE SERIES LONG BODY TAP</v>
+        <v>EDGE SERIES SHORT BODY TAP</v>
       </c>
       <c r="E1260" t="str">
         <v>FAUCETS</v>
@@ -44497,19 +44497,19 @@
         <v>General</v>
       </c>
       <c r="G1260" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1260" t="str">
         <v>NOS</v>
       </c>
       <c r="I1260">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J1260" t="str">
         <v>Active</v>
       </c>
       <c r="K1260" t="str">
-        <v>EDGE SERIES LONG BODY TAP high quality faucet.</v>
+        <v>EDGE SERIES SHORT BODY TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1261">
@@ -44520,7 +44520,7 @@
         <v>FG-401551</v>
       </c>
       <c r="C1261" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2)</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2 inch)</v>
       </c>
       <c r="D1261" t="str">
         <v>EDGE SERIES LONG BODY TAP</v>
@@ -44532,7 +44532,7 @@
         <v>General</v>
       </c>
       <c r="G1261" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1261" t="str">
         <v>NOS</v>
@@ -44555,7 +44555,7 @@
         <v>FG-401551</v>
       </c>
       <c r="C1262" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2")</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2)</v>
       </c>
       <c r="D1262" t="str">
         <v>EDGE SERIES LONG BODY TAP</v>
@@ -44567,7 +44567,7 @@
         <v>General</v>
       </c>
       <c r="G1262" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1262" t="str">
         <v>NOS</v>
@@ -44587,13 +44587,13 @@
         <v>1262</v>
       </c>
       <c r="B1263" t="str">
-        <v>FG-401549</v>
+        <v>FG-401551</v>
       </c>
       <c r="C1263" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2 inch)</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2")</v>
       </c>
       <c r="D1263" t="str">
-        <v>EDGE SERIES SWAN NECK</v>
+        <v>EDGE SERIES LONG BODY TAP</v>
       </c>
       <c r="E1263" t="str">
         <v>FAUCETS</v>
@@ -44602,19 +44602,19 @@
         <v>General</v>
       </c>
       <c r="G1263" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1263" t="str">
         <v>NOS</v>
       </c>
       <c r="I1263">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J1263" t="str">
         <v>Active</v>
       </c>
       <c r="K1263" t="str">
-        <v>EDGE SERIES SWAN NECK high quality faucet.</v>
+        <v>EDGE SERIES LONG BODY TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1264">
@@ -44625,7 +44625,7 @@
         <v>FG-401549</v>
       </c>
       <c r="C1264" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2)</v>
+        <v>EDGE SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1264" t="str">
         <v>EDGE SERIES SWAN NECK</v>
@@ -44637,7 +44637,7 @@
         <v>General</v>
       </c>
       <c r="G1264" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1264" t="str">
         <v>NOS</v>
@@ -44660,7 +44660,7 @@
         <v>FG-401549</v>
       </c>
       <c r="C1265" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2")</v>
+        <v>EDGE SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1265" t="str">
         <v>EDGE SERIES SWAN NECK</v>
@@ -44672,7 +44672,7 @@
         <v>General</v>
       </c>
       <c r="G1265" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1265" t="str">
         <v>NOS</v>
@@ -44692,13 +44692,13 @@
         <v>1265</v>
       </c>
       <c r="B1266" t="str">
-        <v>FG-401546</v>
+        <v>FG-401549</v>
       </c>
       <c r="C1266" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>EDGE SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1266" t="str">
-        <v>EDGE SERIES ANGULAR VALVE</v>
+        <v>EDGE SERIES SWAN NECK</v>
       </c>
       <c r="E1266" t="str">
         <v>FAUCETS</v>
@@ -44707,19 +44707,19 @@
         <v>General</v>
       </c>
       <c r="G1266" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1266" t="str">
         <v>NOS</v>
       </c>
       <c r="I1266">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J1266" t="str">
         <v>Active</v>
       </c>
       <c r="K1266" t="str">
-        <v>EDGE SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>EDGE SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1267">
@@ -44730,7 +44730,7 @@
         <v>FG-401546</v>
       </c>
       <c r="C1267" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2)</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1267" t="str">
         <v>EDGE SERIES ANGULAR VALVE</v>
@@ -44742,7 +44742,7 @@
         <v>General</v>
       </c>
       <c r="G1267" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1267" t="str">
         <v>NOS</v>
@@ -44765,7 +44765,7 @@
         <v>FG-401546</v>
       </c>
       <c r="C1268" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2")</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1268" t="str">
         <v>EDGE SERIES ANGULAR VALVE</v>
@@ -44777,7 +44777,7 @@
         <v>General</v>
       </c>
       <c r="G1268" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1268" t="str">
         <v>NOS</v>
@@ -44797,13 +44797,13 @@
         <v>1268</v>
       </c>
       <c r="B1269" t="str">
-        <v>FG-401547</v>
+        <v>FG-401546</v>
       </c>
       <c r="C1269" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2 inch)</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1269" t="str">
-        <v>EDGE SERIES PILLAR TAP</v>
+        <v>EDGE SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1269" t="str">
         <v>FAUCETS</v>
@@ -44812,19 +44812,19 @@
         <v>General</v>
       </c>
       <c r="G1269" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1269" t="str">
         <v>NOS</v>
       </c>
       <c r="I1269">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J1269" t="str">
         <v>Active</v>
       </c>
       <c r="K1269" t="str">
-        <v>EDGE SERIES PILLAR TAP high quality faucet.</v>
+        <v>EDGE SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1270">
@@ -44835,7 +44835,7 @@
         <v>FG-401547</v>
       </c>
       <c r="C1270" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2)</v>
+        <v>EDGE SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1270" t="str">
         <v>EDGE SERIES PILLAR TAP</v>
@@ -44847,7 +44847,7 @@
         <v>General</v>
       </c>
       <c r="G1270" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1270" t="str">
         <v>NOS</v>
@@ -44870,7 +44870,7 @@
         <v>FG-401547</v>
       </c>
       <c r="C1271" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2")</v>
+        <v>EDGE SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1271" t="str">
         <v>EDGE SERIES PILLAR TAP</v>
@@ -44882,7 +44882,7 @@
         <v>General</v>
       </c>
       <c r="G1271" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1271" t="str">
         <v>NOS</v>
@@ -44902,13 +44902,13 @@
         <v>1271</v>
       </c>
       <c r="B1272" t="str">
-        <v>FG-401550</v>
+        <v>FG-401547</v>
       </c>
       <c r="C1272" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2 inch)</v>
+        <v>EDGE SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1272" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB</v>
+        <v>EDGE SERIES PILLAR TAP</v>
       </c>
       <c r="E1272" t="str">
         <v>FAUCETS</v>
@@ -44917,19 +44917,19 @@
         <v>General</v>
       </c>
       <c r="G1272" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1272" t="str">
         <v>NOS</v>
       </c>
       <c r="I1272">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J1272" t="str">
         <v>Active</v>
       </c>
       <c r="K1272" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB high quality faucet.</v>
+        <v>EDGE SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1273">
@@ -44940,7 +44940,7 @@
         <v>FG-401550</v>
       </c>
       <c r="C1273" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2)</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2 inch)</v>
       </c>
       <c r="D1273" t="str">
         <v>EDGE SERIES 2 WAY BIB TAB</v>
@@ -44952,7 +44952,7 @@
         <v>General</v>
       </c>
       <c r="G1273" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1273" t="str">
         <v>NOS</v>
@@ -44975,7 +44975,7 @@
         <v>FG-401550</v>
       </c>
       <c r="C1274" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2")</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2)</v>
       </c>
       <c r="D1274" t="str">
         <v>EDGE SERIES 2 WAY BIB TAB</v>
@@ -44987,7 +44987,7 @@
         <v>General</v>
       </c>
       <c r="G1274" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1274" t="str">
         <v>NOS</v>
@@ -45007,13 +45007,13 @@
         <v>1274</v>
       </c>
       <c r="B1275" t="str">
-        <v>FG-401548</v>
+        <v>FG-401550</v>
       </c>
       <c r="C1275" t="str">
-        <v>EDGE SERIES SINK TAP (1/2 inch)</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2")</v>
       </c>
       <c r="D1275" t="str">
-        <v>EDGE SERIES SINK TAP</v>
+        <v>EDGE SERIES 2 WAY BIB TAB</v>
       </c>
       <c r="E1275" t="str">
         <v>FAUCETS</v>
@@ -45022,19 +45022,19 @@
         <v>General</v>
       </c>
       <c r="G1275" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1275" t="str">
         <v>NOS</v>
       </c>
       <c r="I1275">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J1275" t="str">
         <v>Active</v>
       </c>
       <c r="K1275" t="str">
-        <v>EDGE SERIES SINK TAP high quality faucet.</v>
+        <v>EDGE SERIES 2 WAY BIB TAB high quality faucet.</v>
       </c>
     </row>
     <row r="1276">
@@ -45045,7 +45045,7 @@
         <v>FG-401548</v>
       </c>
       <c r="C1276" t="str">
-        <v>EDGE SERIES SINK TAP (1/2)</v>
+        <v>EDGE SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1276" t="str">
         <v>EDGE SERIES SINK TAP</v>
@@ -45057,7 +45057,7 @@
         <v>General</v>
       </c>
       <c r="G1276" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1276" t="str">
         <v>NOS</v>
@@ -45080,7 +45080,7 @@
         <v>FG-401548</v>
       </c>
       <c r="C1277" t="str">
-        <v>EDGE SERIES SINK TAP (1/2")</v>
+        <v>EDGE SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1277" t="str">
         <v>EDGE SERIES SINK TAP</v>
@@ -45092,7 +45092,7 @@
         <v>General</v>
       </c>
       <c r="G1277" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1277" t="str">
         <v>NOS</v>
@@ -45112,13 +45112,13 @@
         <v>1277</v>
       </c>
       <c r="B1278" t="str">
-        <v>FG-401568</v>
+        <v>FG-401548</v>
       </c>
       <c r="C1278" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2 inch)</v>
+        <v>EDGE SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1278" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP</v>
+        <v>EDGE SERIES SINK TAP</v>
       </c>
       <c r="E1278" t="str">
         <v>FAUCETS</v>
@@ -45127,19 +45127,19 @@
         <v>General</v>
       </c>
       <c r="G1278" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1278" t="str">
         <v>NOS</v>
       </c>
       <c r="I1278">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="J1278" t="str">
         <v>Active</v>
       </c>
       <c r="K1278" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP high quality faucet.</v>
+        <v>EDGE SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1279">
@@ -45150,7 +45150,7 @@
         <v>FG-401568</v>
       </c>
       <c r="C1279" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2)</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1279" t="str">
         <v>SMART SERIES SHORT BODY BIB TAP</v>
@@ -45162,7 +45162,7 @@
         <v>General</v>
       </c>
       <c r="G1279" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1279" t="str">
         <v>NOS</v>
@@ -45185,7 +45185,7 @@
         <v>FG-401568</v>
       </c>
       <c r="C1280" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2")</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1280" t="str">
         <v>SMART SERIES SHORT BODY BIB TAP</v>
@@ -45197,7 +45197,7 @@
         <v>General</v>
       </c>
       <c r="G1280" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1280" t="str">
         <v>NOS</v>
@@ -45217,13 +45217,13 @@
         <v>1280</v>
       </c>
       <c r="B1281" t="str">
-        <v>FG-401567</v>
+        <v>FG-401568</v>
       </c>
       <c r="C1281" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1281" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP</v>
+        <v>SMART SERIES SHORT BODY BIB TAP</v>
       </c>
       <c r="E1281" t="str">
         <v>FAUCETS</v>
@@ -45232,7 +45232,7 @@
         <v>General</v>
       </c>
       <c r="G1281" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1281" t="str">
         <v>NOS</v>
@@ -45244,7 +45244,7 @@
         <v>Active</v>
       </c>
       <c r="K1281" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP high quality faucet.</v>
+        <v>SMART SERIES SHORT BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1282">
@@ -45255,7 +45255,7 @@
         <v>FG-401567</v>
       </c>
       <c r="C1282" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2)</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1282" t="str">
         <v>SMART SERIES LONG BODY BIB TAP</v>
@@ -45267,7 +45267,7 @@
         <v>General</v>
       </c>
       <c r="G1282" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1282" t="str">
         <v>NOS</v>
@@ -45290,7 +45290,7 @@
         <v>FG-401567</v>
       </c>
       <c r="C1283" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2")</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1283" t="str">
         <v>SMART SERIES LONG BODY BIB TAP</v>
@@ -45302,7 +45302,7 @@
         <v>General</v>
       </c>
       <c r="G1283" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1283" t="str">
         <v>NOS</v>
@@ -45322,13 +45322,13 @@
         <v>1283</v>
       </c>
       <c r="B1284" t="str">
-        <v>FG-401562</v>
+        <v>FG-401567</v>
       </c>
       <c r="C1284" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2 inch)</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1284" t="str">
-        <v>SMART SERIES PILLAR TAP</v>
+        <v>SMART SERIES LONG BODY BIB TAP</v>
       </c>
       <c r="E1284" t="str">
         <v>FAUCETS</v>
@@ -45337,19 +45337,19 @@
         <v>General</v>
       </c>
       <c r="G1284" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1284" t="str">
         <v>NOS</v>
       </c>
       <c r="I1284">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1284" t="str">
         <v>Active</v>
       </c>
       <c r="K1284" t="str">
-        <v>SMART SERIES PILLAR TAP high quality faucet.</v>
+        <v>SMART SERIES LONG BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1285">
@@ -45360,7 +45360,7 @@
         <v>FG-401562</v>
       </c>
       <c r="C1285" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2)</v>
+        <v>SMART SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1285" t="str">
         <v>SMART SERIES PILLAR TAP</v>
@@ -45372,7 +45372,7 @@
         <v>General</v>
       </c>
       <c r="G1285" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1285" t="str">
         <v>NOS</v>
@@ -45395,7 +45395,7 @@
         <v>FG-401562</v>
       </c>
       <c r="C1286" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2")</v>
+        <v>SMART SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1286" t="str">
         <v>SMART SERIES PILLAR TAP</v>
@@ -45407,7 +45407,7 @@
         <v>General</v>
       </c>
       <c r="G1286" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1286" t="str">
         <v>NOS</v>
@@ -45427,13 +45427,13 @@
         <v>1286</v>
       </c>
       <c r="B1287" t="str">
-        <v>FG-401563</v>
+        <v>FG-401562</v>
       </c>
       <c r="C1287" t="str">
-        <v>SMART SERIES SINK TAP (1/2 inch)</v>
+        <v>SMART SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1287" t="str">
-        <v>SMART SERIES SINK TAP</v>
+        <v>SMART SERIES PILLAR TAP</v>
       </c>
       <c r="E1287" t="str">
         <v>FAUCETS</v>
@@ -45442,7 +45442,7 @@
         <v>General</v>
       </c>
       <c r="G1287" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1287" t="str">
         <v>NOS</v>
@@ -45454,7 +45454,7 @@
         <v>Active</v>
       </c>
       <c r="K1287" t="str">
-        <v>SMART SERIES SINK TAP high quality faucet.</v>
+        <v>SMART SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1288">
@@ -45465,7 +45465,7 @@
         <v>FG-401563</v>
       </c>
       <c r="C1288" t="str">
-        <v>SMART SERIES SINK TAP (1/2)</v>
+        <v>SMART SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1288" t="str">
         <v>SMART SERIES SINK TAP</v>
@@ -45477,7 +45477,7 @@
         <v>General</v>
       </c>
       <c r="G1288" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1288" t="str">
         <v>NOS</v>
@@ -45500,7 +45500,7 @@
         <v>FG-401563</v>
       </c>
       <c r="C1289" t="str">
-        <v>SMART SERIES SINK TAP (1/2")</v>
+        <v>SMART SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1289" t="str">
         <v>SMART SERIES SINK TAP</v>
@@ -45512,7 +45512,7 @@
         <v>General</v>
       </c>
       <c r="G1289" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1289" t="str">
         <v>NOS</v>
@@ -45532,13 +45532,13 @@
         <v>1289</v>
       </c>
       <c r="B1290" t="str">
-        <v>FG-401564</v>
+        <v>FG-401563</v>
       </c>
       <c r="C1290" t="str">
-        <v>SMART SERIES SWAN NECK (1/2 inch)</v>
+        <v>SMART SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1290" t="str">
-        <v>SMART SERIES SWAN NECK</v>
+        <v>SMART SERIES SINK TAP</v>
       </c>
       <c r="E1290" t="str">
         <v>FAUCETS</v>
@@ -45547,7 +45547,7 @@
         <v>General</v>
       </c>
       <c r="G1290" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1290" t="str">
         <v>NOS</v>
@@ -45559,7 +45559,7 @@
         <v>Active</v>
       </c>
       <c r="K1290" t="str">
-        <v>SMART SERIES SWAN NECK high quality faucet.</v>
+        <v>SMART SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1291">
@@ -45570,7 +45570,7 @@
         <v>FG-401564</v>
       </c>
       <c r="C1291" t="str">
-        <v>SMART SERIES SWAN NECK (1/2)</v>
+        <v>SMART SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1291" t="str">
         <v>SMART SERIES SWAN NECK</v>
@@ -45582,7 +45582,7 @@
         <v>General</v>
       </c>
       <c r="G1291" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1291" t="str">
         <v>NOS</v>
@@ -45605,7 +45605,7 @@
         <v>FG-401564</v>
       </c>
       <c r="C1292" t="str">
-        <v>SMART SERIES SWAN NECK (1/2")</v>
+        <v>SMART SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1292" t="str">
         <v>SMART SERIES SWAN NECK</v>
@@ -45617,7 +45617,7 @@
         <v>General</v>
       </c>
       <c r="G1292" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1292" t="str">
         <v>NOS</v>
@@ -45637,13 +45637,13 @@
         <v>1292</v>
       </c>
       <c r="B1293" t="str">
-        <v>FG-401561</v>
+        <v>FG-401564</v>
       </c>
       <c r="C1293" t="str">
-        <v>SMART SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>SMART SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1293" t="str">
-        <v>SMART SERIES ANGULAR VALVE</v>
+        <v>SMART SERIES SWAN NECK</v>
       </c>
       <c r="E1293" t="str">
         <v>FAUCETS</v>
@@ -45652,19 +45652,19 @@
         <v>General</v>
       </c>
       <c r="G1293" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1293" t="str">
         <v>NOS</v>
       </c>
       <c r="I1293">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1293" t="str">
         <v>Active</v>
       </c>
       <c r="K1293" t="str">
-        <v>SMART SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>SMART SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1294">
@@ -45672,13 +45672,13 @@
         <v>1293</v>
       </c>
       <c r="B1294" t="str">
-        <v>FG-401566</v>
+        <v>FG-401561</v>
       </c>
       <c r="C1294" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
+        <v>SMART SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1294" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
+        <v>SMART SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1294" t="str">
         <v>FAUCETS</v>
@@ -45693,13 +45693,13 @@
         <v>NOS</v>
       </c>
       <c r="I1294">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1294" t="str">
         <v>Active</v>
       </c>
       <c r="K1294" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
+        <v>SMART SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1295">
@@ -45710,7 +45710,7 @@
         <v>FG-401566</v>
       </c>
       <c r="C1295" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1295" t="str">
         <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
@@ -45722,7 +45722,7 @@
         <v>General</v>
       </c>
       <c r="G1295" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1295" t="str">
         <v>NOS</v>
@@ -45745,7 +45745,7 @@
         <v>FG-401566</v>
       </c>
       <c r="C1296" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2")</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1296" t="str">
         <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
@@ -45757,7 +45757,7 @@
         <v>General</v>
       </c>
       <c r="G1296" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1296" t="str">
         <v>NOS</v>
@@ -45777,13 +45777,13 @@
         <v>1296</v>
       </c>
       <c r="B1297" t="str">
-        <v>FG-401565</v>
+        <v>FG-401566</v>
       </c>
       <c r="C1297" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1297" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
       </c>
       <c r="E1297" t="str">
         <v>FAUCETS</v>
@@ -45792,7 +45792,7 @@
         <v>General</v>
       </c>
       <c r="G1297" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1297" t="str">
         <v>NOS</v>
@@ -45804,7 +45804,7 @@
         <v>Active</v>
       </c>
       <c r="K1297" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP high quality faucet.</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1298">
@@ -45815,7 +45815,7 @@
         <v>FG-401565</v>
       </c>
       <c r="C1298" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2)</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1298" t="str">
         <v>SMART SERIES 2 WAY BIB TAP</v>
@@ -45827,7 +45827,7 @@
         <v>General</v>
       </c>
       <c r="G1298" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1298" t="str">
         <v>NOS</v>
@@ -45850,7 +45850,7 @@
         <v>FG-401565</v>
       </c>
       <c r="C1299" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2")</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2)</v>
       </c>
       <c r="D1299" t="str">
         <v>SMART SERIES 2 WAY BIB TAP</v>
@@ -45862,7 +45862,7 @@
         <v>General</v>
       </c>
       <c r="G1299" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1299" t="str">
         <v>NOS</v>
@@ -45882,13 +45882,13 @@
         <v>1299</v>
       </c>
       <c r="B1300" t="str">
-        <v>FG-401560</v>
+        <v>FG-401565</v>
       </c>
       <c r="C1300" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2")</v>
       </c>
       <c r="D1300" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP</v>
+        <v>SMART SERIES 2 WAY BIB TAP</v>
       </c>
       <c r="E1300" t="str">
         <v>FAUCETS</v>
@@ -45897,19 +45897,19 @@
         <v>General</v>
       </c>
       <c r="G1300" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1300" t="str">
         <v>NOS</v>
       </c>
       <c r="I1300">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1300" t="str">
         <v>Active</v>
       </c>
       <c r="K1300" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP high quality faucet.</v>
+        <v>SMART SERIES 2 WAY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1301">
@@ -45920,7 +45920,7 @@
         <v>FG-401560</v>
       </c>
       <c r="C1301" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1301" t="str">
         <v>REGULAR SERIES SHORT BODY BIB TAP</v>
@@ -45932,7 +45932,7 @@
         <v>General</v>
       </c>
       <c r="G1301" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1301" t="str">
         <v>NOS</v>
@@ -45955,7 +45955,7 @@
         <v>FG-401560</v>
       </c>
       <c r="C1302" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1302" t="str">
         <v>REGULAR SERIES SHORT BODY BIB TAP</v>
@@ -45967,7 +45967,7 @@
         <v>General</v>
       </c>
       <c r="G1302" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1302" t="str">
         <v>NOS</v>
@@ -45987,13 +45987,13 @@
         <v>1302</v>
       </c>
       <c r="B1303" t="str">
-        <v>FG-401559</v>
+        <v>FG-401560</v>
       </c>
       <c r="C1303" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1303" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP</v>
       </c>
       <c r="E1303" t="str">
         <v>FAUCETS</v>
@@ -46002,7 +46002,7 @@
         <v>General</v>
       </c>
       <c r="G1303" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1303" t="str">
         <v>NOS</v>
@@ -46014,7 +46014,7 @@
         <v>Active</v>
       </c>
       <c r="K1303" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1304">
@@ -46025,7 +46025,7 @@
         <v>FG-401559</v>
       </c>
       <c r="C1304" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1304" t="str">
         <v>REGULAR SERIES LONG BODY BIB TAP</v>
@@ -46037,7 +46037,7 @@
         <v>General</v>
       </c>
       <c r="G1304" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1304" t="str">
         <v>NOS</v>
@@ -46060,7 +46060,7 @@
         <v>FG-401559</v>
       </c>
       <c r="C1305" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1305" t="str">
         <v>REGULAR SERIES LONG BODY BIB TAP</v>
@@ -46072,7 +46072,7 @@
         <v>General</v>
       </c>
       <c r="G1305" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1305" t="str">
         <v>NOS</v>
@@ -46092,13 +46092,13 @@
         <v>1305</v>
       </c>
       <c r="B1306" t="str">
-        <v>FG-401554</v>
+        <v>FG-401559</v>
       </c>
       <c r="C1306" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2 inch)</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1306" t="str">
-        <v>REGULAR SERIES PILLAR TAP</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP</v>
       </c>
       <c r="E1306" t="str">
         <v>FAUCETS</v>
@@ -46107,19 +46107,19 @@
         <v>General</v>
       </c>
       <c r="G1306" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1306" t="str">
         <v>NOS</v>
       </c>
       <c r="I1306">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1306" t="str">
         <v>Active</v>
       </c>
       <c r="K1306" t="str">
-        <v>REGULAR SERIES PILLAR TAP high quality faucet.</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1307">
@@ -46130,7 +46130,7 @@
         <v>FG-401554</v>
       </c>
       <c r="C1307" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2)</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1307" t="str">
         <v>REGULAR SERIES PILLAR TAP</v>
@@ -46142,7 +46142,7 @@
         <v>General</v>
       </c>
       <c r="G1307" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1307" t="str">
         <v>NOS</v>
@@ -46165,7 +46165,7 @@
         <v>FG-401554</v>
       </c>
       <c r="C1308" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2")</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1308" t="str">
         <v>REGULAR SERIES PILLAR TAP</v>
@@ -46177,7 +46177,7 @@
         <v>General</v>
       </c>
       <c r="G1308" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1308" t="str">
         <v>NOS</v>
@@ -46197,13 +46197,13 @@
         <v>1308</v>
       </c>
       <c r="B1309" t="str">
-        <v>FG-401555</v>
+        <v>FG-401554</v>
       </c>
       <c r="C1309" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2 inch)</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1309" t="str">
-        <v>REGULAR SERIES SINK TAP</v>
+        <v>REGULAR SERIES PILLAR TAP</v>
       </c>
       <c r="E1309" t="str">
         <v>FAUCETS</v>
@@ -46212,7 +46212,7 @@
         <v>General</v>
       </c>
       <c r="G1309" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1309" t="str">
         <v>NOS</v>
@@ -46224,7 +46224,7 @@
         <v>Active</v>
       </c>
       <c r="K1309" t="str">
-        <v>REGULAR SERIES SINK TAP high quality faucet.</v>
+        <v>REGULAR SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1310">
@@ -46235,7 +46235,7 @@
         <v>FG-401555</v>
       </c>
       <c r="C1310" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2)</v>
+        <v>REGULAR SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1310" t="str">
         <v>REGULAR SERIES SINK TAP</v>
@@ -46247,7 +46247,7 @@
         <v>General</v>
       </c>
       <c r="G1310" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1310" t="str">
         <v>NOS</v>
@@ -46270,7 +46270,7 @@
         <v>FG-401555</v>
       </c>
       <c r="C1311" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2")</v>
+        <v>REGULAR SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1311" t="str">
         <v>REGULAR SERIES SINK TAP</v>
@@ -46282,7 +46282,7 @@
         <v>General</v>
       </c>
       <c r="G1311" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1311" t="str">
         <v>NOS</v>
@@ -46302,13 +46302,13 @@
         <v>1311</v>
       </c>
       <c r="B1312" t="str">
-        <v>FG-401556</v>
+        <v>FG-401555</v>
       </c>
       <c r="C1312" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2 inch)</v>
+        <v>REGULAR SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1312" t="str">
-        <v>REGULAR SERIES SWAN NECK</v>
+        <v>REGULAR SERIES SINK TAP</v>
       </c>
       <c r="E1312" t="str">
         <v>FAUCETS</v>
@@ -46317,7 +46317,7 @@
         <v>General</v>
       </c>
       <c r="G1312" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1312" t="str">
         <v>NOS</v>
@@ -46329,7 +46329,7 @@
         <v>Active</v>
       </c>
       <c r="K1312" t="str">
-        <v>REGULAR SERIES SWAN NECK high quality faucet.</v>
+        <v>REGULAR SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1313">
@@ -46340,7 +46340,7 @@
         <v>FG-401556</v>
       </c>
       <c r="C1313" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2)</v>
+        <v>REGULAR SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1313" t="str">
         <v>REGULAR SERIES SWAN NECK</v>
@@ -46352,7 +46352,7 @@
         <v>General</v>
       </c>
       <c r="G1313" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1313" t="str">
         <v>NOS</v>
@@ -46375,7 +46375,7 @@
         <v>FG-401556</v>
       </c>
       <c r="C1314" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2")</v>
+        <v>REGULAR SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1314" t="str">
         <v>REGULAR SERIES SWAN NECK</v>
@@ -46387,7 +46387,7 @@
         <v>General</v>
       </c>
       <c r="G1314" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1314" t="str">
         <v>NOS</v>
@@ -46407,13 +46407,13 @@
         <v>1314</v>
       </c>
       <c r="B1315" t="str">
-        <v>FG-401553</v>
+        <v>FG-401556</v>
       </c>
       <c r="C1315" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>REGULAR SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1315" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE</v>
+        <v>REGULAR SERIES SWAN NECK</v>
       </c>
       <c r="E1315" t="str">
         <v>FAUCETS</v>
@@ -46422,19 +46422,19 @@
         <v>General</v>
       </c>
       <c r="G1315" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1315" t="str">
         <v>NOS</v>
       </c>
       <c r="I1315">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1315" t="str">
         <v>Active</v>
       </c>
       <c r="K1315" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>REGULAR SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1316">
@@ -46445,7 +46445,7 @@
         <v>FG-401553</v>
       </c>
       <c r="C1316" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2)</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1316" t="str">
         <v>REGULAR SERIES ANGULAR VALVE</v>
@@ -46457,7 +46457,7 @@
         <v>General</v>
       </c>
       <c r="G1316" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1316" t="str">
         <v>NOS</v>
@@ -46480,7 +46480,7 @@
         <v>FG-401553</v>
       </c>
       <c r="C1317" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2")</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1317" t="str">
         <v>REGULAR SERIES ANGULAR VALVE</v>
@@ -46492,7 +46492,7 @@
         <v>General</v>
       </c>
       <c r="G1317" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1317" t="str">
         <v>NOS</v>
@@ -46512,13 +46512,13 @@
         <v>1317</v>
       </c>
       <c r="B1318" t="str">
-        <v>FG-401558</v>
+        <v>FG-401553</v>
       </c>
       <c r="C1318" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1318" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
+        <v>REGULAR SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1318" t="str">
         <v>FAUCETS</v>
@@ -46527,19 +46527,19 @@
         <v>General</v>
       </c>
       <c r="G1318" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1318" t="str">
         <v>NOS</v>
       </c>
       <c r="I1318">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1318" t="str">
         <v>Active</v>
       </c>
       <c r="K1318" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
+        <v>REGULAR SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1319">
@@ -46550,7 +46550,7 @@
         <v>FG-401558</v>
       </c>
       <c r="C1319" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2)</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1319" t="str">
         <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
@@ -46562,7 +46562,7 @@
         <v>General</v>
       </c>
       <c r="G1319" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1319" t="str">
         <v>NOS</v>
@@ -46585,7 +46585,7 @@
         <v>FG-401558</v>
       </c>
       <c r="C1320" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2")</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1320" t="str">
         <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
@@ -46597,7 +46597,7 @@
         <v>General</v>
       </c>
       <c r="G1320" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1320" t="str">
         <v>NOS</v>
@@ -46617,13 +46617,13 @@
         <v>1320</v>
       </c>
       <c r="B1321" t="str">
-        <v>FG-401557</v>
+        <v>FG-401558</v>
       </c>
       <c r="C1321" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1321" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
       </c>
       <c r="E1321" t="str">
         <v>FAUCETS</v>
@@ -46632,7 +46632,7 @@
         <v>General</v>
       </c>
       <c r="G1321" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1321" t="str">
         <v>NOS</v>
@@ -46644,7 +46644,7 @@
         <v>Active</v>
       </c>
       <c r="K1321" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1322">
@@ -46655,7 +46655,7 @@
         <v>FG-401557</v>
       </c>
       <c r="C1322" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1322" t="str">
         <v>REGULAR SERIES 2 WAY BIB TAP</v>
@@ -46667,7 +46667,7 @@
         <v>General</v>
       </c>
       <c r="G1322" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1322" t="str">
         <v>NOS</v>
@@ -46690,7 +46690,7 @@
         <v>FG-401557</v>
       </c>
       <c r="C1323" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2)</v>
       </c>
       <c r="D1323" t="str">
         <v>REGULAR SERIES 2 WAY BIB TAP</v>
@@ -46702,7 +46702,7 @@
         <v>General</v>
       </c>
       <c r="G1323" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1323" t="str">
         <v>NOS</v>
@@ -46722,34 +46722,34 @@
         <v>1323</v>
       </c>
       <c r="B1324" t="str">
-        <v>FG-400836</v>
+        <v>FG-401557</v>
       </c>
       <c r="C1324" t="str">
-        <v>SINGLE SIDE HANDLE FLUSH 8L (8L)</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2")</v>
       </c>
       <c r="D1324" t="str">
-        <v>SINGLE SIDE HANDLE FLUSH 8L</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP</v>
       </c>
       <c r="E1324" t="str">
-        <v>Toilet Seat Cover &amp; Flushing Cistern</v>
+        <v>FAUCETS</v>
       </c>
       <c r="F1324" t="str">
         <v>General</v>
       </c>
       <c r="G1324" t="str">
-        <v>8L</v>
+        <v>1/2"</v>
       </c>
       <c r="H1324" t="str">
         <v>NOS</v>
       </c>
       <c r="I1324">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="J1324" t="str">
         <v>Active</v>
       </c>
       <c r="K1324" t="str">
-        <v>8 Litre Single Side Handle Flushing Cistern.</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1325">
@@ -46757,13 +46757,13 @@
         <v>1324</v>
       </c>
       <c r="B1325" t="str">
-        <v>FG-400837</v>
+        <v>FG-400836</v>
       </c>
       <c r="C1325" t="str">
-        <v>CENTER SINGLE PUSH FLUSH 8L (8L)</v>
+        <v>SINGLE SIDE HANDLE FLUSH 8L (8L)</v>
       </c>
       <c r="D1325" t="str">
-        <v>CENTER SINGLE PUSH FLUSH 8L</v>
+        <v>SINGLE SIDE HANDLE FLUSH 8L</v>
       </c>
       <c r="E1325" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46784,7 +46784,7 @@
         <v>Active</v>
       </c>
       <c r="K1325" t="str">
-        <v>8 Litre Center Single Push Flushing Cistern.</v>
+        <v>8 Litre Single Side Handle Flushing Cistern.</v>
       </c>
     </row>
     <row r="1326">
@@ -46792,13 +46792,13 @@
         <v>1325</v>
       </c>
       <c r="B1326" t="str">
-        <v>FG-400838</v>
+        <v>FG-400837</v>
       </c>
       <c r="C1326" t="str">
-        <v>DUAL FLUSH 10L (10L)</v>
+        <v>CENTER SINGLE PUSH FLUSH 8L (8L)</v>
       </c>
       <c r="D1326" t="str">
-        <v>DUAL FLUSH 10L</v>
+        <v>CENTER SINGLE PUSH FLUSH 8L</v>
       </c>
       <c r="E1326" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46807,7 +46807,7 @@
         <v>General</v>
       </c>
       <c r="G1326" t="str">
-        <v>10L</v>
+        <v>8L</v>
       </c>
       <c r="H1326" t="str">
         <v>NOS</v>
@@ -46819,7 +46819,7 @@
         <v>Active</v>
       </c>
       <c r="K1326" t="str">
-        <v>10 Litre Dual Flush Cistern.</v>
+        <v>8 Litre Center Single Push Flushing Cistern.</v>
       </c>
     </row>
     <row r="1327">
@@ -46827,13 +46827,13 @@
         <v>1326</v>
       </c>
       <c r="B1327" t="str">
-        <v>FG-400835</v>
+        <v>FG-400838</v>
       </c>
       <c r="C1327" t="str">
-        <v>EWC SEAT COVER (WITH JET) (Standard)</v>
+        <v>DUAL FLUSH 10L (10L)</v>
       </c>
       <c r="D1327" t="str">
-        <v>EWC SEAT COVER (WITH JET)</v>
+        <v>DUAL FLUSH 10L</v>
       </c>
       <c r="E1327" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46842,19 +46842,19 @@
         <v>General</v>
       </c>
       <c r="G1327" t="str">
-        <v>Standard</v>
+        <v>10L</v>
       </c>
       <c r="H1327" t="str">
         <v>NOS</v>
       </c>
       <c r="I1327">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J1327" t="str">
         <v>Active</v>
       </c>
       <c r="K1327" t="str">
-        <v>EWC Toilet Seat Cover with integrated jet spray.</v>
+        <v>10 Litre Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1328">
@@ -46862,13 +46862,13 @@
         <v>1327</v>
       </c>
       <c r="B1328" t="str">
-        <v>FG-400840</v>
+        <v>FG-400835</v>
       </c>
       <c r="C1328" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L) (10L)</v>
+        <v>EWC SEAT COVER (WITH JET) (Standard)</v>
       </c>
       <c r="D1328" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L)</v>
+        <v>EWC SEAT COVER (WITH JET)</v>
       </c>
       <c r="E1328" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46877,19 +46877,19 @@
         <v>General</v>
       </c>
       <c r="G1328" t="str">
-        <v>10L</v>
+        <v>Standard</v>
       </c>
       <c r="H1328" t="str">
         <v>NOS</v>
       </c>
       <c r="I1328">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J1328" t="str">
         <v>Active</v>
       </c>
       <c r="K1328" t="str">
-        <v>10 Litre Premium Dual Colour Dual Flush Cistern.</v>
+        <v>EWC Toilet Seat Cover with integrated jet spray.</v>
       </c>
     </row>
     <row r="1329">
@@ -46897,13 +46897,13 @@
         <v>1328</v>
       </c>
       <c r="B1329" t="str">
-        <v>FG-400839</v>
+        <v>FG-400840</v>
       </c>
       <c r="C1329" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L) (10L)</v>
+        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L) (10L)</v>
       </c>
       <c r="D1329" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L)</v>
+        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L)</v>
       </c>
       <c r="E1329" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46924,7 +46924,7 @@
         <v>Active</v>
       </c>
       <c r="K1329" t="str">
-        <v>10 Litre Economy Dual Colour Dual Flush Cistern.</v>
+        <v>10 Litre Premium Dual Colour Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1330">
@@ -46932,13 +46932,13 @@
         <v>1329</v>
       </c>
       <c r="B1330" t="str">
-        <v>FG-400834</v>
+        <v>FG-400839</v>
       </c>
       <c r="C1330" t="str">
-        <v>EWC SEAT COVER (WITHOUT JET) (Standard)</v>
+        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L) (10L)</v>
       </c>
       <c r="D1330" t="str">
-        <v>EWC SEAT COVER (WITHOUT JET)</v>
+        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L)</v>
       </c>
       <c r="E1330" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46947,24 +46947,59 @@
         <v>General</v>
       </c>
       <c r="G1330" t="str">
-        <v>Standard</v>
+        <v>10L</v>
       </c>
       <c r="H1330" t="str">
         <v>NOS</v>
       </c>
       <c r="I1330">
+        <v>10</v>
+      </c>
+      <c r="J1330" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K1330" t="str">
+        <v>10 Litre Economy Dual Colour Dual Flush Cistern.</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331">
+        <v>1330</v>
+      </c>
+      <c r="B1331" t="str">
+        <v>FG-400834</v>
+      </c>
+      <c r="C1331" t="str">
+        <v>EWC SEAT COVER (WITHOUT JET) (Standard)</v>
+      </c>
+      <c r="D1331" t="str">
+        <v>EWC SEAT COVER (WITHOUT JET)</v>
+      </c>
+      <c r="E1331" t="str">
+        <v>Toilet Seat Cover &amp; Flushing Cistern</v>
+      </c>
+      <c r="F1331" t="str">
+        <v>General</v>
+      </c>
+      <c r="G1331" t="str">
+        <v>Standard</v>
+      </c>
+      <c r="H1331" t="str">
+        <v>NOS</v>
+      </c>
+      <c r="I1331">
         <v>20</v>
       </c>
-      <c r="J1330" t="str">
-        <v>Active</v>
-      </c>
-      <c r="K1330" t="str">
+      <c r="J1331" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K1331" t="str">
         <v>EWC Toilet Seat Cover without jet spray.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K1330"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K1331"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
+++ b/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1331"/>
+  <dimension ref="A1:K1330"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -35805,10 +35805,10 @@
         <v>-</v>
       </c>
       <c r="C1012" t="str">
-        <v>PN10 - TEE ISI (25MM)</v>
+        <v>AGRI TEE 10KG</v>
       </c>
       <c r="D1012" t="str">
-        <v>PN10 - TEE ISI</v>
+        <v>AGRI TEE 10KG</v>
       </c>
       <c r="E1012" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35817,7 +35817,7 @@
         <v>General</v>
       </c>
       <c r="G1012" t="str">
-        <v>25MM</v>
+        <v>Standard</v>
       </c>
       <c r="H1012" t="str">
         <v>BOX</v>
@@ -35829,7 +35829,7 @@
         <v>Active</v>
       </c>
       <c r="K1012" t="str">
-        <v>PN10 - TEE ISI for agriculture irrigation and piping systems.</v>
+        <v>AGRI TEE 10KG.</v>
       </c>
     </row>
     <row r="1013">
@@ -35840,10 +35840,10 @@
         <v>-</v>
       </c>
       <c r="C1013" t="str">
-        <v>PN10 - TEE ISI (32MM)</v>
+        <v>PN10 - COUPLER ISI (25MM)</v>
       </c>
       <c r="D1013" t="str">
-        <v>PN10 - TEE ISI</v>
+        <v>PN10 - COUPLER ISI</v>
       </c>
       <c r="E1013" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35852,7 +35852,7 @@
         <v>General</v>
       </c>
       <c r="G1013" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1013" t="str">
         <v>BOX</v>
@@ -35864,7 +35864,7 @@
         <v>Active</v>
       </c>
       <c r="K1013" t="str">
-        <v>PN10 - TEE ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - COUPLER ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1014">
@@ -35875,7 +35875,7 @@
         <v>-</v>
       </c>
       <c r="C1014" t="str">
-        <v>PN10 - COUPLER ISI (25MM)</v>
+        <v>PN10 - COUPLER ISI (32MM)</v>
       </c>
       <c r="D1014" t="str">
         <v>PN10 - COUPLER ISI</v>
@@ -35887,7 +35887,7 @@
         <v>General</v>
       </c>
       <c r="G1014" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1014" t="str">
         <v>BOX</v>
@@ -35910,10 +35910,10 @@
         <v>-</v>
       </c>
       <c r="C1015" t="str">
-        <v>PN10 - COUPLER ISI (32MM)</v>
+        <v>PN10 - MTA ISI (25MM)</v>
       </c>
       <c r="D1015" t="str">
-        <v>PN10 - COUPLER ISI</v>
+        <v>PN10 - MTA ISI</v>
       </c>
       <c r="E1015" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35922,7 +35922,7 @@
         <v>General</v>
       </c>
       <c r="G1015" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1015" t="str">
         <v>BOX</v>
@@ -35934,7 +35934,7 @@
         <v>Active</v>
       </c>
       <c r="K1015" t="str">
-        <v>PN10 - COUPLER ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - MTA ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1016">
@@ -35945,7 +35945,7 @@
         <v>-</v>
       </c>
       <c r="C1016" t="str">
-        <v>PN10 - MTA ISI (25MM)</v>
+        <v>PN10 - MTA ISI (32MM)</v>
       </c>
       <c r="D1016" t="str">
         <v>PN10 - MTA ISI</v>
@@ -35957,7 +35957,7 @@
         <v>General</v>
       </c>
       <c r="G1016" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1016" t="str">
         <v>BOX</v>
@@ -35980,10 +35980,10 @@
         <v>-</v>
       </c>
       <c r="C1017" t="str">
-        <v>PN10 - MTA ISI (32MM)</v>
+        <v>PN10 - FTA ISI (25MM)</v>
       </c>
       <c r="D1017" t="str">
-        <v>PN10 - MTA ISI</v>
+        <v>PN10 - FTA ISI</v>
       </c>
       <c r="E1017" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35992,7 +35992,7 @@
         <v>General</v>
       </c>
       <c r="G1017" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1017" t="str">
         <v>BOX</v>
@@ -36004,7 +36004,7 @@
         <v>Active</v>
       </c>
       <c r="K1017" t="str">
-        <v>PN10 - MTA ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - FTA ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1018">
@@ -36015,7 +36015,7 @@
         <v>-</v>
       </c>
       <c r="C1018" t="str">
-        <v>PN10 - FTA ISI (25MM)</v>
+        <v>PN10 - FTA ISI (32MM)</v>
       </c>
       <c r="D1018" t="str">
         <v>PN10 - FTA ISI</v>
@@ -36027,7 +36027,7 @@
         <v>General</v>
       </c>
       <c r="G1018" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1018" t="str">
         <v>BOX</v>
@@ -36050,10 +36050,10 @@
         <v>-</v>
       </c>
       <c r="C1019" t="str">
-        <v>PN10 - FTA ISI (32MM)</v>
+        <v>PN10 - END CAP ISI (25MM)</v>
       </c>
       <c r="D1019" t="str">
-        <v>PN10 - FTA ISI</v>
+        <v>PN10 - END CAP ISI</v>
       </c>
       <c r="E1019" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36062,7 +36062,7 @@
         <v>General</v>
       </c>
       <c r="G1019" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1019" t="str">
         <v>BOX</v>
@@ -36074,7 +36074,7 @@
         <v>Active</v>
       </c>
       <c r="K1019" t="str">
-        <v>PN10 - FTA ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - END CAP ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1020">
@@ -36085,7 +36085,7 @@
         <v>-</v>
       </c>
       <c r="C1020" t="str">
-        <v>PN10 - END CAP ISI (25MM)</v>
+        <v>PN10 - END CAP ISI (32MM)</v>
       </c>
       <c r="D1020" t="str">
         <v>PN10 - END CAP ISI</v>
@@ -36097,7 +36097,7 @@
         <v>General</v>
       </c>
       <c r="G1020" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1020" t="str">
         <v>BOX</v>
@@ -36120,10 +36120,10 @@
         <v>-</v>
       </c>
       <c r="C1021" t="str">
-        <v>PN10 - END CAP ISI (32MM)</v>
+        <v>PN10 - REDUCING BUSH ISI (32 X 20)</v>
       </c>
       <c r="D1021" t="str">
-        <v>PN10 - END CAP ISI</v>
+        <v>PN10 - REDUCING BUSH ISI</v>
       </c>
       <c r="E1021" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36132,7 +36132,7 @@
         <v>General</v>
       </c>
       <c r="G1021" t="str">
-        <v>32MM</v>
+        <v>32 X 20</v>
       </c>
       <c r="H1021" t="str">
         <v>BOX</v>
@@ -36144,7 +36144,7 @@
         <v>Active</v>
       </c>
       <c r="K1021" t="str">
-        <v>PN10 - END CAP ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - REDUCING BUSH ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1022">
@@ -36155,7 +36155,7 @@
         <v>-</v>
       </c>
       <c r="C1022" t="str">
-        <v>PN10 - REDUCING BUSH ISI (32 X 20)</v>
+        <v>PN10 - REDUCING BUSH ISI (32 X 25)</v>
       </c>
       <c r="D1022" t="str">
         <v>PN10 - REDUCING BUSH ISI</v>
@@ -36167,7 +36167,7 @@
         <v>General</v>
       </c>
       <c r="G1022" t="str">
-        <v>32 X 20</v>
+        <v>32 X 25</v>
       </c>
       <c r="H1022" t="str">
         <v>BOX</v>
@@ -36187,13 +36187,13 @@
         <v>1022</v>
       </c>
       <c r="B1023" t="str">
-        <v>-</v>
+        <v>FG-400585</v>
       </c>
       <c r="C1023" t="str">
-        <v>PN10 - REDUCING BUSH ISI (32 X 25)</v>
+        <v>AGRI REDUCER (50X40MM)</v>
       </c>
       <c r="D1023" t="str">
-        <v>PN10 - REDUCING BUSH ISI</v>
+        <v>AGRI REDUCER</v>
       </c>
       <c r="E1023" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36202,19 +36202,19 @@
         <v>General</v>
       </c>
       <c r="G1023" t="str">
-        <v>32 X 25</v>
+        <v>50X40MM</v>
       </c>
       <c r="H1023" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1023" t="str">
-        <v>-</v>
+      <c r="I1023">
+        <v>300</v>
       </c>
       <c r="J1023" t="str">
         <v>Active</v>
       </c>
       <c r="K1023" t="str">
-        <v>PN10 - REDUCING BUSH ISI for agriculture irrigation and piping systems.</v>
+        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
       </c>
     </row>
     <row r="1024">
@@ -36222,10 +36222,10 @@
         <v>1023</v>
       </c>
       <c r="B1024" t="str">
-        <v>FG-400585</v>
+        <v>FG-400584</v>
       </c>
       <c r="C1024" t="str">
-        <v>AGRI REDUCER (50X40MM)</v>
+        <v>AGRI REDUCER (63X40MM)</v>
       </c>
       <c r="D1024" t="str">
         <v>AGRI REDUCER</v>
@@ -36237,13 +36237,13 @@
         <v>General</v>
       </c>
       <c r="G1024" t="str">
-        <v>50X40MM</v>
+        <v>63X40MM</v>
       </c>
       <c r="H1024" t="str">
         <v>BOX</v>
       </c>
       <c r="I1024">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J1024" t="str">
         <v>Active</v>
@@ -36257,10 +36257,10 @@
         <v>1024</v>
       </c>
       <c r="B1025" t="str">
-        <v>FG-400584</v>
+        <v>FG-400583</v>
       </c>
       <c r="C1025" t="str">
-        <v>AGRI REDUCER (63X40MM)</v>
+        <v>AGRI REDUCER (63X50MM)</v>
       </c>
       <c r="D1025" t="str">
         <v>AGRI REDUCER</v>
@@ -36272,13 +36272,13 @@
         <v>General</v>
       </c>
       <c r="G1025" t="str">
-        <v>63X40MM</v>
+        <v>63X50MM</v>
       </c>
       <c r="H1025" t="str">
         <v>BOX</v>
       </c>
       <c r="I1025">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="J1025" t="str">
         <v>Active</v>
@@ -36292,10 +36292,10 @@
         <v>1025</v>
       </c>
       <c r="B1026" t="str">
-        <v>FG-400583</v>
+        <v>FG-400582</v>
       </c>
       <c r="C1026" t="str">
-        <v>AGRI REDUCER (63X50MM)</v>
+        <v>AGRI REDUCER (75X40MM)</v>
       </c>
       <c r="D1026" t="str">
         <v>AGRI REDUCER</v>
@@ -36307,13 +36307,13 @@
         <v>General</v>
       </c>
       <c r="G1026" t="str">
-        <v>63X50MM</v>
+        <v>75X40MM</v>
       </c>
       <c r="H1026" t="str">
         <v>BOX</v>
       </c>
       <c r="I1026">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J1026" t="str">
         <v>Active</v>
@@ -36327,10 +36327,10 @@
         <v>1026</v>
       </c>
       <c r="B1027" t="str">
-        <v>FG-400582</v>
+        <v>FG-400581</v>
       </c>
       <c r="C1027" t="str">
-        <v>AGRI REDUCER (75X40MM)</v>
+        <v>AGRI REDUCER (75X50MM)</v>
       </c>
       <c r="D1027" t="str">
         <v>AGRI REDUCER</v>
@@ -36342,13 +36342,13 @@
         <v>General</v>
       </c>
       <c r="G1027" t="str">
-        <v>75X40MM</v>
+        <v>75X50MM</v>
       </c>
       <c r="H1027" t="str">
         <v>BOX</v>
       </c>
       <c r="I1027">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J1027" t="str">
         <v>Active</v>
@@ -36362,10 +36362,10 @@
         <v>1027</v>
       </c>
       <c r="B1028" t="str">
-        <v>FG-400581</v>
+        <v>FG-400580</v>
       </c>
       <c r="C1028" t="str">
-        <v>AGRI REDUCER (75X50MM)</v>
+        <v>AGRI REDUCER (75X63MM)</v>
       </c>
       <c r="D1028" t="str">
         <v>AGRI REDUCER</v>
@@ -36377,13 +36377,13 @@
         <v>General</v>
       </c>
       <c r="G1028" t="str">
-        <v>75X50MM</v>
+        <v>75X63MM</v>
       </c>
       <c r="H1028" t="str">
         <v>BOX</v>
       </c>
       <c r="I1028">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J1028" t="str">
         <v>Active</v>
@@ -36397,10 +36397,10 @@
         <v>1028</v>
       </c>
       <c r="B1029" t="str">
-        <v>FG-400580</v>
+        <v>FG-400579</v>
       </c>
       <c r="C1029" t="str">
-        <v>AGRI REDUCER (75X63MM)</v>
+        <v>AGRI REDUCER (90X50MM)</v>
       </c>
       <c r="D1029" t="str">
         <v>AGRI REDUCER</v>
@@ -36412,13 +36412,13 @@
         <v>General</v>
       </c>
       <c r="G1029" t="str">
-        <v>75X63MM</v>
+        <v>90X50MM</v>
       </c>
       <c r="H1029" t="str">
         <v>BOX</v>
       </c>
       <c r="I1029">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J1029" t="str">
         <v>Active</v>
@@ -36432,10 +36432,10 @@
         <v>1029</v>
       </c>
       <c r="B1030" t="str">
-        <v>FG-400579</v>
+        <v>FG-400578</v>
       </c>
       <c r="C1030" t="str">
-        <v>AGRI REDUCER (90X50MM)</v>
+        <v>AGRI REDUCER (90X63MM)</v>
       </c>
       <c r="D1030" t="str">
         <v>AGRI REDUCER</v>
@@ -36447,13 +36447,13 @@
         <v>General</v>
       </c>
       <c r="G1030" t="str">
-        <v>90X50MM</v>
+        <v>90X63MM</v>
       </c>
       <c r="H1030" t="str">
         <v>BOX</v>
       </c>
       <c r="I1030">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J1030" t="str">
         <v>Active</v>
@@ -36467,10 +36467,10 @@
         <v>1030</v>
       </c>
       <c r="B1031" t="str">
-        <v>FG-400578</v>
+        <v>FG-400577</v>
       </c>
       <c r="C1031" t="str">
-        <v>AGRI REDUCER (90X63MM)</v>
+        <v>AGRI REDUCER (90X75MM)</v>
       </c>
       <c r="D1031" t="str">
         <v>AGRI REDUCER</v>
@@ -36482,13 +36482,13 @@
         <v>General</v>
       </c>
       <c r="G1031" t="str">
-        <v>90X63MM</v>
+        <v>90X75MM</v>
       </c>
       <c r="H1031" t="str">
         <v>BOX</v>
       </c>
       <c r="I1031">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="J1031" t="str">
         <v>Active</v>
@@ -36502,10 +36502,10 @@
         <v>1031</v>
       </c>
       <c r="B1032" t="str">
-        <v>FG-400577</v>
+        <v>FG-400576</v>
       </c>
       <c r="C1032" t="str">
-        <v>AGRI REDUCER (90X75MM)</v>
+        <v>AGRI REDUCER (110X63MM)</v>
       </c>
       <c r="D1032" t="str">
         <v>AGRI REDUCER</v>
@@ -36517,13 +36517,13 @@
         <v>General</v>
       </c>
       <c r="G1032" t="str">
-        <v>90X75MM</v>
+        <v>110X63MM</v>
       </c>
       <c r="H1032" t="str">
         <v>BOX</v>
       </c>
       <c r="I1032">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J1032" t="str">
         <v>Active</v>
@@ -36537,10 +36537,10 @@
         <v>1032</v>
       </c>
       <c r="B1033" t="str">
-        <v>FG-400576</v>
+        <v>FG-400575</v>
       </c>
       <c r="C1033" t="str">
-        <v>AGRI REDUCER (110X63MM)</v>
+        <v>AGRI REDUCER (110X75MM)</v>
       </c>
       <c r="D1033" t="str">
         <v>AGRI REDUCER</v>
@@ -36552,7 +36552,7 @@
         <v>General</v>
       </c>
       <c r="G1033" t="str">
-        <v>110X63MM</v>
+        <v>110X75MM</v>
       </c>
       <c r="H1033" t="str">
         <v>BOX</v>
@@ -36572,10 +36572,10 @@
         <v>1033</v>
       </c>
       <c r="B1034" t="str">
-        <v>FG-400575</v>
+        <v>FG-400574</v>
       </c>
       <c r="C1034" t="str">
-        <v>AGRI REDUCER (110X75MM)</v>
+        <v>AGRI REDUCER (110X90MM)</v>
       </c>
       <c r="D1034" t="str">
         <v>AGRI REDUCER</v>
@@ -36587,13 +36587,13 @@
         <v>General</v>
       </c>
       <c r="G1034" t="str">
-        <v>110X75MM</v>
+        <v>110X90MM</v>
       </c>
       <c r="H1034" t="str">
         <v>BOX</v>
       </c>
       <c r="I1034">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J1034" t="str">
         <v>Active</v>
@@ -36607,13 +36607,13 @@
         <v>1034</v>
       </c>
       <c r="B1035" t="str">
-        <v>FG-400574</v>
+        <v>-</v>
       </c>
       <c r="C1035" t="str">
-        <v>AGRI REDUCER (110X90MM)</v>
+        <v>REDUCING BUSH (LW) (63 X 40)</v>
       </c>
       <c r="D1035" t="str">
-        <v>AGRI REDUCER</v>
+        <v>REDUCING BUSH (LW)</v>
       </c>
       <c r="E1035" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36622,19 +36622,19 @@
         <v>General</v>
       </c>
       <c r="G1035" t="str">
-        <v>110X90MM</v>
+        <v>63 X 40</v>
       </c>
       <c r="H1035" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1035">
-        <v>40</v>
+      <c r="I1035" t="str">
+        <v>-</v>
       </c>
       <c r="J1035" t="str">
         <v>Active</v>
       </c>
       <c r="K1035" t="str">
-        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
+        <v>REDUCING BUSH (LW) for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1036">
@@ -36645,7 +36645,7 @@
         <v>-</v>
       </c>
       <c r="C1036" t="str">
-        <v>REDUCING BUSH (LW) (63 X 40)</v>
+        <v>REDUCING BUSH (LW) (63 X 50)</v>
       </c>
       <c r="D1036" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36657,7 +36657,7 @@
         <v>General</v>
       </c>
       <c r="G1036" t="str">
-        <v>63 X 40</v>
+        <v>63 X 50</v>
       </c>
       <c r="H1036" t="str">
         <v>BOX</v>
@@ -36680,7 +36680,7 @@
         <v>-</v>
       </c>
       <c r="C1037" t="str">
-        <v>REDUCING BUSH (LW) (63 X 50)</v>
+        <v>REDUCING BUSH (LW) (75 X 40)</v>
       </c>
       <c r="D1037" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36692,7 +36692,7 @@
         <v>General</v>
       </c>
       <c r="G1037" t="str">
-        <v>63 X 50</v>
+        <v>75 X 40</v>
       </c>
       <c r="H1037" t="str">
         <v>BOX</v>
@@ -36715,7 +36715,7 @@
         <v>-</v>
       </c>
       <c r="C1038" t="str">
-        <v>REDUCING BUSH (LW) (75 X 40)</v>
+        <v>REDUCING BUSH (LW) (75 X 63)</v>
       </c>
       <c r="D1038" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36727,7 +36727,7 @@
         <v>General</v>
       </c>
       <c r="G1038" t="str">
-        <v>75 X 40</v>
+        <v>75 X 63</v>
       </c>
       <c r="H1038" t="str">
         <v>BOX</v>
@@ -36750,7 +36750,7 @@
         <v>-</v>
       </c>
       <c r="C1039" t="str">
-        <v>REDUCING BUSH (LW) (75 X 63)</v>
+        <v>REDUCING BUSH (LW) (90 X 50)</v>
       </c>
       <c r="D1039" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36762,7 +36762,7 @@
         <v>General</v>
       </c>
       <c r="G1039" t="str">
-        <v>75 X 63</v>
+        <v>90 X 50</v>
       </c>
       <c r="H1039" t="str">
         <v>BOX</v>
@@ -36785,7 +36785,7 @@
         <v>-</v>
       </c>
       <c r="C1040" t="str">
-        <v>REDUCING BUSH (LW) (90 X 50)</v>
+        <v>REDUCING BUSH (LW) (90 X 63)</v>
       </c>
       <c r="D1040" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36797,7 +36797,7 @@
         <v>General</v>
       </c>
       <c r="G1040" t="str">
-        <v>90 X 50</v>
+        <v>90 X 63</v>
       </c>
       <c r="H1040" t="str">
         <v>BOX</v>
@@ -36820,7 +36820,7 @@
         <v>-</v>
       </c>
       <c r="C1041" t="str">
-        <v>REDUCING BUSH (LW) (90 X 63)</v>
+        <v>REDUCING BUSH (LW) (90 X 75)</v>
       </c>
       <c r="D1041" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36832,7 +36832,7 @@
         <v>General</v>
       </c>
       <c r="G1041" t="str">
-        <v>90 X 63</v>
+        <v>90 X 75</v>
       </c>
       <c r="H1041" t="str">
         <v>BOX</v>
@@ -36855,7 +36855,7 @@
         <v>-</v>
       </c>
       <c r="C1042" t="str">
-        <v>REDUCING BUSH (LW) (90 X 75)</v>
+        <v>REDUCING BUSH (LW) (110 X 63)</v>
       </c>
       <c r="D1042" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36867,7 +36867,7 @@
         <v>General</v>
       </c>
       <c r="G1042" t="str">
-        <v>90 X 75</v>
+        <v>110 X 63</v>
       </c>
       <c r="H1042" t="str">
         <v>BOX</v>
@@ -36890,7 +36890,7 @@
         <v>-</v>
       </c>
       <c r="C1043" t="str">
-        <v>REDUCING BUSH (LW) (110 X 63)</v>
+        <v>REDUCING BUSH (LW) (110 X 75)</v>
       </c>
       <c r="D1043" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36902,7 +36902,7 @@
         <v>General</v>
       </c>
       <c r="G1043" t="str">
-        <v>110 X 63</v>
+        <v>110 X 75</v>
       </c>
       <c r="H1043" t="str">
         <v>BOX</v>
@@ -36925,7 +36925,7 @@
         <v>-</v>
       </c>
       <c r="C1044" t="str">
-        <v>REDUCING BUSH (LW) (110 X 75)</v>
+        <v>REDUCING BUSH (LW) (110 X 90)</v>
       </c>
       <c r="D1044" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36937,7 +36937,7 @@
         <v>General</v>
       </c>
       <c r="G1044" t="str">
-        <v>110 X 75</v>
+        <v>110 X 90</v>
       </c>
       <c r="H1044" t="str">
         <v>BOX</v>
@@ -36957,13 +36957,13 @@
         <v>1044</v>
       </c>
       <c r="B1045" t="str">
-        <v>-</v>
+        <v>FG-400550</v>
       </c>
       <c r="C1045" t="str">
-        <v>REDUCING BUSH (LW) (110 X 90)</v>
+        <v>AGRI TEE (40MM)</v>
       </c>
       <c r="D1045" t="str">
-        <v>REDUCING BUSH (LW)</v>
+        <v>AGRI TEE</v>
       </c>
       <c r="E1045" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36972,19 +36972,19 @@
         <v>General</v>
       </c>
       <c r="G1045" t="str">
-        <v>110 X 90</v>
+        <v>40MM</v>
       </c>
       <c r="H1045" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1045" t="str">
-        <v>-</v>
+      <c r="I1045">
+        <v>150</v>
       </c>
       <c r="J1045" t="str">
         <v>Active</v>
       </c>
       <c r="K1045" t="str">
-        <v>REDUCING BUSH (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1046">
@@ -36992,10 +36992,10 @@
         <v>1045</v>
       </c>
       <c r="B1046" t="str">
-        <v>FG-400550</v>
+        <v>FG-400551</v>
       </c>
       <c r="C1046" t="str">
-        <v>AGRI TEE (40MM)</v>
+        <v>AGRI TEE (50MM)</v>
       </c>
       <c r="D1046" t="str">
         <v>AGRI TEE</v>
@@ -37007,13 +37007,13 @@
         <v>General</v>
       </c>
       <c r="G1046" t="str">
-        <v>40MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1046" t="str">
         <v>BOX</v>
       </c>
       <c r="I1046">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J1046" t="str">
         <v>Active</v>
@@ -37027,10 +37027,10 @@
         <v>1046</v>
       </c>
       <c r="B1047" t="str">
-        <v>FG-400551</v>
+        <v>FG-400552</v>
       </c>
       <c r="C1047" t="str">
-        <v>AGRI TEE (50MM)</v>
+        <v>AGRI TEE (63MM)</v>
       </c>
       <c r="D1047" t="str">
         <v>AGRI TEE</v>
@@ -37042,13 +37042,13 @@
         <v>General</v>
       </c>
       <c r="G1047" t="str">
-        <v>50MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1047" t="str">
         <v>BOX</v>
       </c>
       <c r="I1047">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J1047" t="str">
         <v>Active</v>
@@ -37062,10 +37062,10 @@
         <v>1047</v>
       </c>
       <c r="B1048" t="str">
-        <v>FG-400552</v>
+        <v>FG-400553</v>
       </c>
       <c r="C1048" t="str">
-        <v>AGRI TEE (63MM)</v>
+        <v>AGRI TEE (75MM)</v>
       </c>
       <c r="D1048" t="str">
         <v>AGRI TEE</v>
@@ -37077,13 +37077,13 @@
         <v>General</v>
       </c>
       <c r="G1048" t="str">
-        <v>63MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1048" t="str">
         <v>BOX</v>
       </c>
       <c r="I1048">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="J1048" t="str">
         <v>Active</v>
@@ -37097,10 +37097,10 @@
         <v>1048</v>
       </c>
       <c r="B1049" t="str">
-        <v>FG-400553</v>
+        <v>FG-400554</v>
       </c>
       <c r="C1049" t="str">
-        <v>AGRI TEE (75MM)</v>
+        <v>AGRI TEE (90MM)</v>
       </c>
       <c r="D1049" t="str">
         <v>AGRI TEE</v>
@@ -37112,13 +37112,13 @@
         <v>General</v>
       </c>
       <c r="G1049" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1049" t="str">
         <v>BOX</v>
       </c>
       <c r="I1049">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J1049" t="str">
         <v>Active</v>
@@ -37132,10 +37132,10 @@
         <v>1049</v>
       </c>
       <c r="B1050" t="str">
-        <v>FG-400554</v>
+        <v>FG-400586</v>
       </c>
       <c r="C1050" t="str">
-        <v>AGRI TEE (90MM)</v>
+        <v>AGRI TEE (110MM)</v>
       </c>
       <c r="D1050" t="str">
         <v>AGRI TEE</v>
@@ -37147,13 +37147,13 @@
         <v>General</v>
       </c>
       <c r="G1050" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1050" t="str">
         <v>BOX</v>
       </c>
       <c r="I1050">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J1050" t="str">
         <v>Active</v>
@@ -37167,10 +37167,10 @@
         <v>1050</v>
       </c>
       <c r="B1051" t="str">
-        <v>FG-400586</v>
+        <v>FG-400607</v>
       </c>
       <c r="C1051" t="str">
-        <v>AGRI TEE (110MM)</v>
+        <v>AGRI TEE (140MM)</v>
       </c>
       <c r="D1051" t="str">
         <v>AGRI TEE</v>
@@ -37182,13 +37182,13 @@
         <v>General</v>
       </c>
       <c r="G1051" t="str">
-        <v>110MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1051" t="str">
         <v>BOX</v>
       </c>
       <c r="I1051">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="J1051" t="str">
         <v>Active</v>
@@ -37202,10 +37202,10 @@
         <v>1051</v>
       </c>
       <c r="B1052" t="str">
-        <v>FG-400607</v>
+        <v>FG-400608</v>
       </c>
       <c r="C1052" t="str">
-        <v>AGRI TEE (140MM)</v>
+        <v>AGRI TEE (160MM)</v>
       </c>
       <c r="D1052" t="str">
         <v>AGRI TEE</v>
@@ -37217,13 +37217,13 @@
         <v>General</v>
       </c>
       <c r="G1052" t="str">
-        <v>140MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1052" t="str">
         <v>BOX</v>
       </c>
       <c r="I1052">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J1052" t="str">
         <v>Active</v>
@@ -37237,13 +37237,13 @@
         <v>1052</v>
       </c>
       <c r="B1053" t="str">
-        <v>FG-400608</v>
+        <v>-</v>
       </c>
       <c r="C1053" t="str">
-        <v>AGRI TEE (160MM)</v>
+        <v>COUPLER (LW) (75MM)</v>
       </c>
       <c r="D1053" t="str">
-        <v>AGRI TEE</v>
+        <v>COUPLER (LW)</v>
       </c>
       <c r="E1053" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37252,19 +37252,19 @@
         <v>General</v>
       </c>
       <c r="G1053" t="str">
-        <v>160MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1053" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1053">
-        <v>9</v>
+      <c r="I1053" t="str">
+        <v>-</v>
       </c>
       <c r="J1053" t="str">
         <v>Active</v>
       </c>
       <c r="K1053" t="str">
-        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
+        <v>COUPLER (LW) for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1054">
@@ -37275,7 +37275,7 @@
         <v>-</v>
       </c>
       <c r="C1054" t="str">
-        <v>COUPLER (LW) (75MM)</v>
+        <v>COUPLER (LW) (90MM)</v>
       </c>
       <c r="D1054" t="str">
         <v>COUPLER (LW)</v>
@@ -37287,7 +37287,7 @@
         <v>General</v>
       </c>
       <c r="G1054" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1054" t="str">
         <v>BOX</v>
@@ -37310,7 +37310,7 @@
         <v>-</v>
       </c>
       <c r="C1055" t="str">
-        <v>COUPLER (LW) (90MM)</v>
+        <v>COUPLER (LW) (110MM)</v>
       </c>
       <c r="D1055" t="str">
         <v>COUPLER (LW)</v>
@@ -37322,7 +37322,7 @@
         <v>General</v>
       </c>
       <c r="G1055" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1055" t="str">
         <v>BOX</v>
@@ -37342,13 +37342,13 @@
         <v>1055</v>
       </c>
       <c r="B1056" t="str">
-        <v>-</v>
+        <v>FG-400561</v>
       </c>
       <c r="C1056" t="str">
-        <v>COUPLER (LW) (110MM)</v>
+        <v>AGRI FABRICATED COUPLER (40MM)</v>
       </c>
       <c r="D1056" t="str">
-        <v>COUPLER (LW)</v>
+        <v>AGRI FABRICATED COUPLER</v>
       </c>
       <c r="E1056" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37357,19 +37357,19 @@
         <v>General</v>
       </c>
       <c r="G1056" t="str">
-        <v>110MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1056" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1056" t="str">
-        <v>-</v>
+      <c r="I1056">
+        <v>300</v>
       </c>
       <c r="J1056" t="str">
         <v>Active</v>
       </c>
       <c r="K1056" t="str">
-        <v>COUPLER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI FABRICATED COUPLER for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1057">
@@ -37377,10 +37377,10 @@
         <v>1056</v>
       </c>
       <c r="B1057" t="str">
-        <v>FG-400561</v>
+        <v>FG-400562</v>
       </c>
       <c r="C1057" t="str">
-        <v>AGRI FABRICATED COUPLER (40MM)</v>
+        <v>AGRI FABRICATED COUPLER (50MM)</v>
       </c>
       <c r="D1057" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37392,13 +37392,13 @@
         <v>General</v>
       </c>
       <c r="G1057" t="str">
-        <v>40MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1057" t="str">
         <v>BOX</v>
       </c>
       <c r="I1057">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J1057" t="str">
         <v>Active</v>
@@ -37412,10 +37412,10 @@
         <v>1057</v>
       </c>
       <c r="B1058" t="str">
-        <v>FG-400562</v>
+        <v>FG-400563</v>
       </c>
       <c r="C1058" t="str">
-        <v>AGRI FABRICATED COUPLER (50MM)</v>
+        <v>AGRI FABRICATED COUPLER (63MM)</v>
       </c>
       <c r="D1058" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37427,7 +37427,7 @@
         <v>General</v>
       </c>
       <c r="G1058" t="str">
-        <v>50MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1058" t="str">
         <v>BOX</v>
@@ -37447,10 +37447,10 @@
         <v>1058</v>
       </c>
       <c r="B1059" t="str">
-        <v>FG-400563</v>
+        <v>FG-400564</v>
       </c>
       <c r="C1059" t="str">
-        <v>AGRI FABRICATED COUPLER (63MM)</v>
+        <v>AGRI FABRICATED COUPLER (75MM)</v>
       </c>
       <c r="D1059" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37462,13 +37462,13 @@
         <v>General</v>
       </c>
       <c r="G1059" t="str">
-        <v>63MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1059" t="str">
         <v>BOX</v>
       </c>
       <c r="I1059">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="J1059" t="str">
         <v>Active</v>
@@ -37482,10 +37482,10 @@
         <v>1059</v>
       </c>
       <c r="B1060" t="str">
-        <v>FG-400564</v>
+        <v>FG-400565</v>
       </c>
       <c r="C1060" t="str">
-        <v>AGRI FABRICATED COUPLER (75MM)</v>
+        <v>AGRI FABRICATED COUPLER (90MM)</v>
       </c>
       <c r="D1060" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37497,13 +37497,13 @@
         <v>General</v>
       </c>
       <c r="G1060" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1060" t="str">
         <v>BOX</v>
       </c>
       <c r="I1060">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="J1060" t="str">
         <v>Active</v>
@@ -37517,10 +37517,10 @@
         <v>1060</v>
       </c>
       <c r="B1061" t="str">
-        <v>FG-400565</v>
+        <v>FG-400566</v>
       </c>
       <c r="C1061" t="str">
-        <v>AGRI FABRICATED COUPLER (90MM)</v>
+        <v>AGRI FABRICATED COUPLER (110MM)</v>
       </c>
       <c r="D1061" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37532,13 +37532,13 @@
         <v>General</v>
       </c>
       <c r="G1061" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1061" t="str">
         <v>BOX</v>
       </c>
       <c r="I1061">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J1061" t="str">
         <v>Active</v>
@@ -37552,10 +37552,10 @@
         <v>1061</v>
       </c>
       <c r="B1062" t="str">
-        <v>FG-400566</v>
+        <v>FG-400587</v>
       </c>
       <c r="C1062" t="str">
-        <v>AGRI FABRICATED COUPLER (110MM)</v>
+        <v>AGRI FABRICATED COUPLER (140MM 4KG)</v>
       </c>
       <c r="D1062" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37567,13 +37567,13 @@
         <v>General</v>
       </c>
       <c r="G1062" t="str">
-        <v>110MM</v>
+        <v>140MM 4KG</v>
       </c>
       <c r="H1062" t="str">
         <v>BOX</v>
       </c>
       <c r="I1062">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J1062" t="str">
         <v>Active</v>
@@ -37587,10 +37587,10 @@
         <v>1062</v>
       </c>
       <c r="B1063" t="str">
-        <v>FG-400587</v>
+        <v>FG-400568</v>
       </c>
       <c r="C1063" t="str">
-        <v>AGRI FABRICATED COUPLER (140MM 4KG)</v>
+        <v>AGRI FABRICATED COUPLER (160MM 4KG)</v>
       </c>
       <c r="D1063" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37602,13 +37602,13 @@
         <v>General</v>
       </c>
       <c r="G1063" t="str">
-        <v>140MM 4KG</v>
+        <v>160MM 4KG</v>
       </c>
       <c r="H1063" t="str">
         <v>BOX</v>
       </c>
       <c r="I1063">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J1063" t="str">
         <v>Active</v>
@@ -37622,13 +37622,13 @@
         <v>1063</v>
       </c>
       <c r="B1064" t="str">
-        <v>FG-400568</v>
+        <v>FG-400567</v>
       </c>
       <c r="C1064" t="str">
-        <v>AGRI FABRICATED COUPLER (160MM 4KG)</v>
+        <v>AGRI FABRICATED COUPLER 6KG (140MM)</v>
       </c>
       <c r="D1064" t="str">
-        <v>AGRI FABRICATED COUPLER</v>
+        <v>AGRI FABRICATED COUPLER 6KG</v>
       </c>
       <c r="E1064" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37637,19 +37637,19 @@
         <v>General</v>
       </c>
       <c r="G1064" t="str">
-        <v>160MM 4KG</v>
+        <v>140MM</v>
       </c>
       <c r="H1064" t="str">
         <v>BOX</v>
       </c>
       <c r="I1064">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J1064" t="str">
         <v>Active</v>
       </c>
       <c r="K1064" t="str">
-        <v>AGRI FABRICATED COUPLER for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
+        <v>AGRI FABRICATED COUPLER 6KG for agriculture irrigation and piping systems. Available sizes: 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1065">
@@ -37657,10 +37657,10 @@
         <v>1064</v>
       </c>
       <c r="B1065" t="str">
-        <v>FG-400567</v>
+        <v>FG-400569</v>
       </c>
       <c r="C1065" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG (140MM)</v>
+        <v>AGRI FABRICATED COUPLER 6KG (160MM)</v>
       </c>
       <c r="D1065" t="str">
         <v>AGRI FABRICATED COUPLER 6KG</v>
@@ -37672,13 +37672,13 @@
         <v>General</v>
       </c>
       <c r="G1065" t="str">
-        <v>140MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1065" t="str">
         <v>BOX</v>
       </c>
       <c r="I1065">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J1065" t="str">
         <v>Active</v>
@@ -37692,13 +37692,13 @@
         <v>1065</v>
       </c>
       <c r="B1066" t="str">
-        <v>FG-400569</v>
+        <v>FG-400544</v>
       </c>
       <c r="C1066" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG (160MM)</v>
+        <v>AGRI ELBOW (40MM)</v>
       </c>
       <c r="D1066" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG</v>
+        <v>AGRI ELBOW</v>
       </c>
       <c r="E1066" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37707,19 +37707,19 @@
         <v>General</v>
       </c>
       <c r="G1066" t="str">
-        <v>160MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1066" t="str">
         <v>BOX</v>
       </c>
       <c r="I1066">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="J1066" t="str">
         <v>Active</v>
       </c>
       <c r="K1066" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG for agriculture irrigation and piping systems. Available sizes: 140MM, 160MM.</v>
+        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1067">
@@ -37727,10 +37727,10 @@
         <v>1066</v>
       </c>
       <c r="B1067" t="str">
-        <v>FG-400544</v>
+        <v>FG-400545</v>
       </c>
       <c r="C1067" t="str">
-        <v>AGRI ELBOW (40MM)</v>
+        <v>AGRI ELBOW (50MM)</v>
       </c>
       <c r="D1067" t="str">
         <v>AGRI ELBOW</v>
@@ -37742,13 +37742,13 @@
         <v>General</v>
       </c>
       <c r="G1067" t="str">
-        <v>40MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1067" t="str">
         <v>BOX</v>
       </c>
       <c r="I1067">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="J1067" t="str">
         <v>Active</v>
@@ -37762,10 +37762,10 @@
         <v>1067</v>
       </c>
       <c r="B1068" t="str">
-        <v>FG-400545</v>
+        <v>FG-400546</v>
       </c>
       <c r="C1068" t="str">
-        <v>AGRI ELBOW (50MM)</v>
+        <v>AGRI ELBOW (63MM)</v>
       </c>
       <c r="D1068" t="str">
         <v>AGRI ELBOW</v>
@@ -37777,13 +37777,13 @@
         <v>General</v>
       </c>
       <c r="G1068" t="str">
-        <v>50MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1068" t="str">
         <v>BOX</v>
       </c>
       <c r="I1068">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J1068" t="str">
         <v>Active</v>
@@ -37797,10 +37797,10 @@
         <v>1068</v>
       </c>
       <c r="B1069" t="str">
-        <v>FG-400546</v>
+        <v>FG-400547</v>
       </c>
       <c r="C1069" t="str">
-        <v>AGRI ELBOW (63MM)</v>
+        <v>AGRI ELBOW (75MM)</v>
       </c>
       <c r="D1069" t="str">
         <v>AGRI ELBOW</v>
@@ -37812,13 +37812,13 @@
         <v>General</v>
       </c>
       <c r="G1069" t="str">
-        <v>63MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1069" t="str">
         <v>BOX</v>
       </c>
       <c r="I1069">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J1069" t="str">
         <v>Active</v>
@@ -37832,10 +37832,10 @@
         <v>1069</v>
       </c>
       <c r="B1070" t="str">
-        <v>FG-400547</v>
+        <v>FG-400548</v>
       </c>
       <c r="C1070" t="str">
-        <v>AGRI ELBOW (75MM)</v>
+        <v>AGRI ELBOW (90MM)</v>
       </c>
       <c r="D1070" t="str">
         <v>AGRI ELBOW</v>
@@ -37847,13 +37847,13 @@
         <v>General</v>
       </c>
       <c r="G1070" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1070" t="str">
         <v>BOX</v>
       </c>
       <c r="I1070">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="J1070" t="str">
         <v>Active</v>
@@ -37867,10 +37867,10 @@
         <v>1070</v>
       </c>
       <c r="B1071" t="str">
-        <v>FG-400548</v>
+        <v>FG-400549</v>
       </c>
       <c r="C1071" t="str">
-        <v>AGRI ELBOW (90MM)</v>
+        <v>AGRI ELBOW (110MM)</v>
       </c>
       <c r="D1071" t="str">
         <v>AGRI ELBOW</v>
@@ -37882,13 +37882,13 @@
         <v>General</v>
       </c>
       <c r="G1071" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1071" t="str">
         <v>BOX</v>
       </c>
       <c r="I1071">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J1071" t="str">
         <v>Active</v>
@@ -37902,10 +37902,10 @@
         <v>1071</v>
       </c>
       <c r="B1072" t="str">
-        <v>FG-400549</v>
+        <v>FG-400595</v>
       </c>
       <c r="C1072" t="str">
-        <v>AGRI ELBOW (110MM)</v>
+        <v>AGRI ELBOW (140MM)</v>
       </c>
       <c r="D1072" t="str">
         <v>AGRI ELBOW</v>
@@ -37917,13 +37917,13 @@
         <v>General</v>
       </c>
       <c r="G1072" t="str">
-        <v>110MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1072" t="str">
         <v>BOX</v>
       </c>
       <c r="I1072">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="J1072" t="str">
         <v>Active</v>
@@ -37937,10 +37937,10 @@
         <v>1072</v>
       </c>
       <c r="B1073" t="str">
-        <v>FG-400595</v>
+        <v>FG-400596</v>
       </c>
       <c r="C1073" t="str">
-        <v>AGRI ELBOW (140MM)</v>
+        <v>AGRI ELBOW (160MM)</v>
       </c>
       <c r="D1073" t="str">
         <v>AGRI ELBOW</v>
@@ -37952,13 +37952,13 @@
         <v>General</v>
       </c>
       <c r="G1073" t="str">
-        <v>140MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1073" t="str">
         <v>BOX</v>
       </c>
       <c r="I1073">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J1073" t="str">
         <v>Active</v>
@@ -37972,13 +37972,13 @@
         <v>1073</v>
       </c>
       <c r="B1074" t="str">
-        <v>FG-400596</v>
+        <v>FG-400555</v>
       </c>
       <c r="C1074" t="str">
-        <v>AGRI ELBOW (160MM)</v>
+        <v>AGRI END CAP (40MM)</v>
       </c>
       <c r="D1074" t="str">
-        <v>AGRI ELBOW</v>
+        <v>AGRI END CAP</v>
       </c>
       <c r="E1074" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37987,19 +37987,19 @@
         <v>General</v>
       </c>
       <c r="G1074" t="str">
-        <v>160MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1074" t="str">
         <v>BOX</v>
       </c>
       <c r="I1074">
-        <v>12</v>
+        <v>800</v>
       </c>
       <c r="J1074" t="str">
         <v>Active</v>
       </c>
       <c r="K1074" t="str">
-        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
+        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1075">
@@ -38007,10 +38007,10 @@
         <v>1074</v>
       </c>
       <c r="B1075" t="str">
-        <v>FG-400555</v>
+        <v>FG-400556</v>
       </c>
       <c r="C1075" t="str">
-        <v>AGRI END CAP (40MM)</v>
+        <v>AGRI END CAP (50MM)</v>
       </c>
       <c r="D1075" t="str">
         <v>AGRI END CAP</v>
@@ -38022,13 +38022,13 @@
         <v>General</v>
       </c>
       <c r="G1075" t="str">
-        <v>40MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1075" t="str">
         <v>BOX</v>
       </c>
       <c r="I1075">
-        <v>800</v>
+        <v>450</v>
       </c>
       <c r="J1075" t="str">
         <v>Active</v>
@@ -38042,10 +38042,10 @@
         <v>1075</v>
       </c>
       <c r="B1076" t="str">
-        <v>FG-400556</v>
+        <v>FG-400557</v>
       </c>
       <c r="C1076" t="str">
-        <v>AGRI END CAP (50MM)</v>
+        <v>AGRI END CAP (63MM)</v>
       </c>
       <c r="D1076" t="str">
         <v>AGRI END CAP</v>
@@ -38057,13 +38057,13 @@
         <v>General</v>
       </c>
       <c r="G1076" t="str">
-        <v>50MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1076" t="str">
         <v>BOX</v>
       </c>
       <c r="I1076">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="J1076" t="str">
         <v>Active</v>
@@ -38077,10 +38077,10 @@
         <v>1076</v>
       </c>
       <c r="B1077" t="str">
-        <v>FG-400557</v>
+        <v>FG-400558</v>
       </c>
       <c r="C1077" t="str">
-        <v>AGRI END CAP (63MM)</v>
+        <v>AGRI END CAP (75MM)</v>
       </c>
       <c r="D1077" t="str">
         <v>AGRI END CAP</v>
@@ -38092,13 +38092,13 @@
         <v>General</v>
       </c>
       <c r="G1077" t="str">
-        <v>63MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1077" t="str">
         <v>BOX</v>
       </c>
       <c r="I1077">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="J1077" t="str">
         <v>Active</v>
@@ -38112,10 +38112,10 @@
         <v>1077</v>
       </c>
       <c r="B1078" t="str">
-        <v>FG-400558</v>
+        <v>FG-400559</v>
       </c>
       <c r="C1078" t="str">
-        <v>AGRI END CAP (75MM)</v>
+        <v>AGRI END CAP (90MM)</v>
       </c>
       <c r="D1078" t="str">
         <v>AGRI END CAP</v>
@@ -38127,13 +38127,13 @@
         <v>General</v>
       </c>
       <c r="G1078" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1078" t="str">
         <v>BOX</v>
       </c>
       <c r="I1078">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J1078" t="str">
         <v>Active</v>
@@ -38147,10 +38147,10 @@
         <v>1078</v>
       </c>
       <c r="B1079" t="str">
-        <v>FG-400559</v>
+        <v>FG-400560</v>
       </c>
       <c r="C1079" t="str">
-        <v>AGRI END CAP (90MM)</v>
+        <v>AGRI END CAP (110MM)</v>
       </c>
       <c r="D1079" t="str">
         <v>AGRI END CAP</v>
@@ -38162,13 +38162,13 @@
         <v>General</v>
       </c>
       <c r="G1079" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1079" t="str">
         <v>BOX</v>
       </c>
       <c r="I1079">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J1079" t="str">
         <v>Active</v>
@@ -38182,10 +38182,10 @@
         <v>1079</v>
       </c>
       <c r="B1080" t="str">
-        <v>FG-400560</v>
+        <v>FG-400639</v>
       </c>
       <c r="C1080" t="str">
-        <v>AGRI END CAP (110MM)</v>
+        <v>AGRI END CAP (140MM 4KG)</v>
       </c>
       <c r="D1080" t="str">
         <v>AGRI END CAP</v>
@@ -38197,13 +38197,13 @@
         <v>General</v>
       </c>
       <c r="G1080" t="str">
-        <v>110MM</v>
+        <v>140MM 4KG</v>
       </c>
       <c r="H1080" t="str">
         <v>BOX</v>
       </c>
       <c r="I1080">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J1080" t="str">
         <v>Active</v>
@@ -38217,10 +38217,10 @@
         <v>1080</v>
       </c>
       <c r="B1081" t="str">
-        <v>FG-400639</v>
+        <v>FG-400640</v>
       </c>
       <c r="C1081" t="str">
-        <v>AGRI END CAP (140MM 4KG)</v>
+        <v>AGRI END CAP (160MM 4KG)</v>
       </c>
       <c r="D1081" t="str">
         <v>AGRI END CAP</v>
@@ -38232,13 +38232,13 @@
         <v>General</v>
       </c>
       <c r="G1081" t="str">
-        <v>140MM 4KG</v>
+        <v>160MM 4KG</v>
       </c>
       <c r="H1081" t="str">
         <v>BOX</v>
       </c>
       <c r="I1081">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J1081" t="str">
         <v>Active</v>
@@ -38252,13 +38252,13 @@
         <v>1081</v>
       </c>
       <c r="B1082" t="str">
-        <v>FG-400640</v>
+        <v>FG-400570</v>
       </c>
       <c r="C1082" t="str">
-        <v>AGRI END CAP (160MM 4KG)</v>
+        <v>AGRI LONG BEND (63MM)</v>
       </c>
       <c r="D1082" t="str">
-        <v>AGRI END CAP</v>
+        <v>AGRI LONG BEND</v>
       </c>
       <c r="E1082" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -38267,19 +38267,19 @@
         <v>General</v>
       </c>
       <c r="G1082" t="str">
-        <v>160MM 4KG</v>
+        <v>63MM</v>
       </c>
       <c r="H1082" t="str">
         <v>BOX</v>
       </c>
       <c r="I1082">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="J1082" t="str">
         <v>Active</v>
       </c>
       <c r="K1082" t="str">
-        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
+        <v>AGRI LONG BEND for agriculture irrigation and piping systems. Available sizes: 63MM, 75MM, 90MM, 110MM.</v>
       </c>
     </row>
     <row r="1083">
@@ -38287,10 +38287,10 @@
         <v>1082</v>
       </c>
       <c r="B1083" t="str">
-        <v>FG-400570</v>
+        <v>FG-400571</v>
       </c>
       <c r="C1083" t="str">
-        <v>AGRI LONG BEND (63MM)</v>
+        <v>AGRI LONG BEND (75MM)</v>
       </c>
       <c r="D1083" t="str">
         <v>AGRI LONG BEND</v>
@@ -38302,13 +38302,13 @@
         <v>General</v>
       </c>
       <c r="G1083" t="str">
-        <v>63MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1083" t="str">
         <v>BOX</v>
       </c>
       <c r="I1083">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J1083" t="str">
         <v>Active</v>
@@ -38322,10 +38322,10 @@
         <v>1083</v>
       </c>
       <c r="B1084" t="str">
-        <v>FG-400571</v>
+        <v>FG-400572</v>
       </c>
       <c r="C1084" t="str">
-        <v>AGRI LONG BEND (75MM)</v>
+        <v>AGRI LONG BEND (90MM)</v>
       </c>
       <c r="D1084" t="str">
         <v>AGRI LONG BEND</v>
@@ -38337,13 +38337,13 @@
         <v>General</v>
       </c>
       <c r="G1084" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1084" t="str">
         <v>BOX</v>
       </c>
       <c r="I1084">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J1084" t="str">
         <v>Active</v>
@@ -38357,10 +38357,10 @@
         <v>1084</v>
       </c>
       <c r="B1085" t="str">
-        <v>FG-400572</v>
+        <v>FG-400573</v>
       </c>
       <c r="C1085" t="str">
-        <v>AGRI LONG BEND (90MM)</v>
+        <v>AGRI LONG BEND (110MM)</v>
       </c>
       <c r="D1085" t="str">
         <v>AGRI LONG BEND</v>
@@ -38372,13 +38372,13 @@
         <v>General</v>
       </c>
       <c r="G1085" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1085" t="str">
         <v>BOX</v>
       </c>
       <c r="I1085">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J1085" t="str">
         <v>Active</v>
@@ -38392,34 +38392,34 @@
         <v>1085</v>
       </c>
       <c r="B1086" t="str">
-        <v>FG-400573</v>
+        <v>FG-401520</v>
       </c>
       <c r="C1086" t="str">
-        <v>AGRI LONG BEND (110MM)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1086" t="str">
-        <v>AGRI LONG BEND</v>
+        <v>SPRINKLER ISI PIPE 6 MTR</v>
       </c>
       <c r="E1086" t="str">
-        <v>Agriculture Pipes &amp; Fittings</v>
+        <v>Sprinkler Pipes &amp; Fittings</v>
       </c>
       <c r="F1086" t="str">
         <v>General</v>
       </c>
       <c r="G1086" t="str">
-        <v>110MM</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1086" t="str">
-        <v>BOX</v>
-      </c>
-      <c r="I1086">
-        <v>10</v>
+        <v>Nos</v>
+      </c>
+      <c r="I1086" t="str">
+        <v>-</v>
       </c>
       <c r="J1086" t="str">
         <v>Active</v>
       </c>
       <c r="K1086" t="str">
-        <v>AGRI LONG BEND for agriculture irrigation and piping systems. Available sizes: 63MM, 75MM, 90MM, 110MM.</v>
+        <v>SPRINKLER ISI PIPE 6 MTR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1087">
@@ -38427,10 +38427,10 @@
         <v>1086</v>
       </c>
       <c r="B1087" t="str">
-        <v>FG-401520</v>
+        <v>FG-401491</v>
       </c>
       <c r="C1087" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (63MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1087" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38442,7 +38442,7 @@
         <v>General</v>
       </c>
       <c r="G1087" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>63MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1087" t="str">
         <v>Nos</v>
@@ -38462,10 +38462,10 @@
         <v>1087</v>
       </c>
       <c r="B1088" t="str">
-        <v>FG-401491</v>
+        <v>FG-401490</v>
       </c>
       <c r="C1088" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (63MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 2.5 KG)</v>
       </c>
       <c r="D1088" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38477,7 +38477,7 @@
         <v>General</v>
       </c>
       <c r="G1088" t="str">
-        <v>63MM L TYPE 3.2 KG</v>
+        <v>75MM C TYPE 2.5 KG</v>
       </c>
       <c r="H1088" t="str">
         <v>Nos</v>
@@ -38497,10 +38497,10 @@
         <v>1088</v>
       </c>
       <c r="B1089" t="str">
-        <v>FG-401490</v>
+        <v>FG-401492</v>
       </c>
       <c r="C1089" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 2.5 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1089" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38512,7 +38512,7 @@
         <v>General</v>
       </c>
       <c r="G1089" t="str">
-        <v>75MM C TYPE 2.5 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1089" t="str">
         <v>Nos</v>
@@ -38532,10 +38532,10 @@
         <v>1089</v>
       </c>
       <c r="B1090" t="str">
-        <v>FG-401492</v>
+        <v>FG-401519</v>
       </c>
       <c r="C1090" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 2.5 KG)</v>
       </c>
       <c r="D1090" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38547,7 +38547,7 @@
         <v>General</v>
       </c>
       <c r="G1090" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>75MM L TYPE 2.5 KG</v>
       </c>
       <c r="H1090" t="str">
         <v>Nos</v>
@@ -38567,10 +38567,10 @@
         <v>1090</v>
       </c>
       <c r="B1091" t="str">
-        <v>FG-401519</v>
+        <v>FG-401521</v>
       </c>
       <c r="C1091" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 2.5 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1091" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38582,7 +38582,7 @@
         <v>General</v>
       </c>
       <c r="G1091" t="str">
-        <v>75MM L TYPE 2.5 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1091" t="str">
         <v>Nos</v>
@@ -38602,13 +38602,13 @@
         <v>1091</v>
       </c>
       <c r="B1092" t="str">
-        <v>FG-401521</v>
+        <v>FG-401522</v>
       </c>
       <c r="C1092" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1092" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR</v>
+        <v>SPRINKLER NISI PIPE 6 MTR</v>
       </c>
       <c r="E1092" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38629,7 +38629,7 @@
         <v>Active</v>
       </c>
       <c r="K1092" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER NISI PIPE 6 MTR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1093">
@@ -38637,10 +38637,10 @@
         <v>1092</v>
       </c>
       <c r="B1093" t="str">
-        <v>FG-401522</v>
+        <v>FG-401523</v>
       </c>
       <c r="C1093" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1093" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38652,7 +38652,7 @@
         <v>General</v>
       </c>
       <c r="G1093" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1093" t="str">
         <v>Nos</v>
@@ -38672,10 +38672,10 @@
         <v>1093</v>
       </c>
       <c r="B1094" t="str">
-        <v>FG-401523</v>
+        <v>FG-401866</v>
       </c>
       <c r="C1094" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (90MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1094" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38687,7 +38687,7 @@
         <v>General</v>
       </c>
       <c r="G1094" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>90MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1094" t="str">
         <v>Nos</v>
@@ -38707,10 +38707,10 @@
         <v>1094</v>
       </c>
       <c r="B1095" t="str">
-        <v>FG-401866</v>
+        <v>FG-401867</v>
       </c>
       <c r="C1095" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (90MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (90MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1095" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38722,7 +38722,7 @@
         <v>General</v>
       </c>
       <c r="G1095" t="str">
-        <v>90MM C TYPE 3.2 KG</v>
+        <v>90MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1095" t="str">
         <v>Nos</v>
@@ -38742,13 +38742,13 @@
         <v>1095</v>
       </c>
       <c r="B1096" t="str">
-        <v>FG-401867</v>
+        <v>FG-401498</v>
       </c>
       <c r="C1096" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (90MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1096" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR</v>
+        <v>SPRINKLER SET 6 MTR ISI</v>
       </c>
       <c r="E1096" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38757,7 +38757,7 @@
         <v>General</v>
       </c>
       <c r="G1096" t="str">
-        <v>90MM L TYPE 3.2 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1096" t="str">
         <v>Nos</v>
@@ -38769,7 +38769,7 @@
         <v>Active</v>
       </c>
       <c r="K1096" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER SET 6 MTR ISI for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1097">
@@ -38777,10 +38777,10 @@
         <v>1096</v>
       </c>
       <c r="B1097" t="str">
-        <v>FG-401498</v>
+        <v>FG-401499</v>
       </c>
       <c r="C1097" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1097" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38792,7 +38792,7 @@
         <v>General</v>
       </c>
       <c r="G1097" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1097" t="str">
         <v>Nos</v>
@@ -38812,10 +38812,10 @@
         <v>1097</v>
       </c>
       <c r="B1098" t="str">
-        <v>FG-401499</v>
+        <v>FG-401500</v>
       </c>
       <c r="C1098" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 2.5 KG)</v>
       </c>
       <c r="D1098" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38827,7 +38827,7 @@
         <v>General</v>
       </c>
       <c r="G1098" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>75MM C TYPE 2.5 KG</v>
       </c>
       <c r="H1098" t="str">
         <v>Nos</v>
@@ -38847,10 +38847,10 @@
         <v>1098</v>
       </c>
       <c r="B1099" t="str">
-        <v>FG-401500</v>
+        <v>FG-401524</v>
       </c>
       <c r="C1099" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 2.5 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 2.5 KG)</v>
       </c>
       <c r="D1099" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38862,7 +38862,7 @@
         <v>General</v>
       </c>
       <c r="G1099" t="str">
-        <v>75MM C TYPE 2.5 KG</v>
+        <v>75MM L TYPE 2.5 KG</v>
       </c>
       <c r="H1099" t="str">
         <v>Nos</v>
@@ -38882,10 +38882,10 @@
         <v>1099</v>
       </c>
       <c r="B1100" t="str">
-        <v>FG-401524</v>
+        <v>FG-401501</v>
       </c>
       <c r="C1100" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 2.5 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1100" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38897,7 +38897,7 @@
         <v>General</v>
       </c>
       <c r="G1100" t="str">
-        <v>75MM L TYPE 2.5 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1100" t="str">
         <v>Nos</v>
@@ -38917,13 +38917,13 @@
         <v>1100</v>
       </c>
       <c r="B1101" t="str">
-        <v>FG-401501</v>
+        <v>FG-401495</v>
       </c>
       <c r="C1101" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1101" t="str">
-        <v>SPRINKLER SET 6 MTR ISI</v>
+        <v>SPRINKLER SET 6 MTR N-ISI</v>
       </c>
       <c r="E1101" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38932,7 +38932,7 @@
         <v>General</v>
       </c>
       <c r="G1101" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1101" t="str">
         <v>Nos</v>
@@ -38944,7 +38944,7 @@
         <v>Active</v>
       </c>
       <c r="K1101" t="str">
-        <v>SPRINKLER SET 6 MTR ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER SET 6 MTR N-ISI for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1102">
@@ -38952,10 +38952,10 @@
         <v>1101</v>
       </c>
       <c r="B1102" t="str">
-        <v>FG-401495</v>
+        <v>FG-401496</v>
       </c>
       <c r="C1102" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1102" t="str">
         <v>SPRINKLER SET 6 MTR N-ISI</v>
@@ -38967,7 +38967,7 @@
         <v>General</v>
       </c>
       <c r="G1102" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1102" t="str">
         <v>Nos</v>
@@ -38987,10 +38987,10 @@
         <v>1102</v>
       </c>
       <c r="B1103" t="str">
-        <v>FG-401496</v>
+        <v>FG-401497</v>
       </c>
       <c r="C1103" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1103" t="str">
         <v>SPRINKLER SET 6 MTR N-ISI</v>
@@ -39002,7 +39002,7 @@
         <v>General</v>
       </c>
       <c r="G1103" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1103" t="str">
         <v>Nos</v>
@@ -39022,13 +39022,13 @@
         <v>1103</v>
       </c>
       <c r="B1104" t="str">
-        <v>FG-401497</v>
+        <v>FG-401503</v>
       </c>
       <c r="C1104" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER FITTINGS TEE (75MM, C TYPE)</v>
       </c>
       <c r="D1104" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI</v>
+        <v>SPRINKLER FITTINGS TEE</v>
       </c>
       <c r="E1104" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39037,7 +39037,7 @@
         <v>General</v>
       </c>
       <c r="G1104" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM, C TYPE</v>
       </c>
       <c r="H1104" t="str">
         <v>Nos</v>
@@ -39049,7 +39049,7 @@
         <v>Active</v>
       </c>
       <c r="K1104" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS TEE for sprinkler irrigation systems. Available sizes: 75MM, C TYPE, 75MM, L TYPE, 63MM, C TYPE.</v>
       </c>
     </row>
     <row r="1105">
@@ -39057,10 +39057,10 @@
         <v>1104</v>
       </c>
       <c r="B1105" t="str">
-        <v>FG-401503</v>
+        <v>FG-401511</v>
       </c>
       <c r="C1105" t="str">
-        <v>SPRINKLER FITTINGS TEE (75MM, C TYPE)</v>
+        <v>SPRINKLER FITTINGS TEE (75MM, L TYPE)</v>
       </c>
       <c r="D1105" t="str">
         <v>SPRINKLER FITTINGS TEE</v>
@@ -39072,7 +39072,7 @@
         <v>General</v>
       </c>
       <c r="G1105" t="str">
-        <v>75MM, C TYPE</v>
+        <v>75MM, L TYPE</v>
       </c>
       <c r="H1105" t="str">
         <v>Nos</v>
@@ -39092,10 +39092,10 @@
         <v>1105</v>
       </c>
       <c r="B1106" t="str">
-        <v>FG-401511</v>
+        <v>FG-401526</v>
       </c>
       <c r="C1106" t="str">
-        <v>SPRINKLER FITTINGS TEE (75MM, L TYPE)</v>
+        <v>SPRINKLER FITTINGS TEE (63MM, C TYPE)</v>
       </c>
       <c r="D1106" t="str">
         <v>SPRINKLER FITTINGS TEE</v>
@@ -39107,7 +39107,7 @@
         <v>General</v>
       </c>
       <c r="G1106" t="str">
-        <v>75MM, L TYPE</v>
+        <v>63MM, C TYPE</v>
       </c>
       <c r="H1106" t="str">
         <v>Nos</v>
@@ -39127,13 +39127,13 @@
         <v>1106</v>
       </c>
       <c r="B1107" t="str">
-        <v>FG-401526</v>
+        <v>FG-401504</v>
       </c>
       <c r="C1107" t="str">
-        <v>SPRINKLER FITTINGS TEE (63MM, C TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (75MM C TYPE)</v>
       </c>
       <c r="D1107" t="str">
-        <v>SPRINKLER FITTINGS TEE</v>
+        <v>SPRINKLER FITTINGS ADAPTOR</v>
       </c>
       <c r="E1107" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39142,7 +39142,7 @@
         <v>General</v>
       </c>
       <c r="G1107" t="str">
-        <v>63MM, C TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1107" t="str">
         <v>Nos</v>
@@ -39154,7 +39154,7 @@
         <v>Active</v>
       </c>
       <c r="K1107" t="str">
-        <v>SPRINKLER FITTINGS TEE for sprinkler irrigation systems. Available sizes: 75MM, C TYPE, 75MM, L TYPE, 63MM, C TYPE.</v>
+        <v>SPRINKLER FITTINGS ADAPTOR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1108">
@@ -39162,10 +39162,10 @@
         <v>1107</v>
       </c>
       <c r="B1108" t="str">
-        <v>FG-401504</v>
+        <v>FG-401512</v>
       </c>
       <c r="C1108" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (75MM P TYPE)</v>
       </c>
       <c r="D1108" t="str">
         <v>SPRINKLER FITTINGS ADAPTOR</v>
@@ -39177,7 +39177,7 @@
         <v>General</v>
       </c>
       <c r="G1108" t="str">
-        <v>75MM C TYPE</v>
+        <v>75MM P TYPE</v>
       </c>
       <c r="H1108" t="str">
         <v>Nos</v>
@@ -39197,10 +39197,10 @@
         <v>1108</v>
       </c>
       <c r="B1109" t="str">
-        <v>FG-401512</v>
+        <v>FG-401527</v>
       </c>
       <c r="C1109" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (75MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (63MM C TYPE)</v>
       </c>
       <c r="D1109" t="str">
         <v>SPRINKLER FITTINGS ADAPTOR</v>
@@ -39212,7 +39212,7 @@
         <v>General</v>
       </c>
       <c r="G1109" t="str">
-        <v>75MM P TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1109" t="str">
         <v>Nos</v>
@@ -39232,13 +39232,13 @@
         <v>1109</v>
       </c>
       <c r="B1110" t="str">
-        <v>FG-401527</v>
+        <v>FG-401502</v>
       </c>
       <c r="C1110" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (75MM C TYPE)</v>
       </c>
       <c r="D1110" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR</v>
+        <v>SPRINKLER FITTINGS BEND</v>
       </c>
       <c r="E1110" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39247,7 +39247,7 @@
         <v>General</v>
       </c>
       <c r="G1110" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1110" t="str">
         <v>Nos</v>
@@ -39259,7 +39259,7 @@
         <v>Active</v>
       </c>
       <c r="K1110" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS BEND for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1111">
@@ -39267,10 +39267,10 @@
         <v>1110</v>
       </c>
       <c r="B1111" t="str">
-        <v>FG-401502</v>
+        <v>FG-401510</v>
       </c>
       <c r="C1111" t="str">
-        <v>SPRINKLER FITTINGS BEND (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (75MM L TYPE)</v>
       </c>
       <c r="D1111" t="str">
         <v>SPRINKLER FITTINGS BEND</v>
@@ -39282,7 +39282,7 @@
         <v>General</v>
       </c>
       <c r="G1111" t="str">
-        <v>75MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1111" t="str">
         <v>Nos</v>
@@ -39302,10 +39302,10 @@
         <v>1111</v>
       </c>
       <c r="B1112" t="str">
-        <v>FG-401510</v>
+        <v>FG-401525</v>
       </c>
       <c r="C1112" t="str">
-        <v>SPRINKLER FITTINGS BEND (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (63MM C TYPE)</v>
       </c>
       <c r="D1112" t="str">
         <v>SPRINKLER FITTINGS BEND</v>
@@ -39317,7 +39317,7 @@
         <v>General</v>
       </c>
       <c r="G1112" t="str">
-        <v>75MM L TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1112" t="str">
         <v>Nos</v>
@@ -39337,13 +39337,13 @@
         <v>1112</v>
       </c>
       <c r="B1113" t="str">
-        <v>FG-401525</v>
+        <v>FG-401514</v>
       </c>
       <c r="C1113" t="str">
-        <v>SPRINKLER FITTINGS BEND (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (75MM L TYPE)</v>
       </c>
       <c r="D1113" t="str">
-        <v>SPRINKLER FITTINGS BEND</v>
+        <v>SPRINKLER FITTINGS END CAP</v>
       </c>
       <c r="E1113" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39352,7 +39352,7 @@
         <v>General</v>
       </c>
       <c r="G1113" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1113" t="str">
         <v>Nos</v>
@@ -39364,7 +39364,7 @@
         <v>Active</v>
       </c>
       <c r="K1113" t="str">
-        <v>SPRINKLER FITTINGS BEND for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS END CAP for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1114">
@@ -39372,10 +39372,10 @@
         <v>1113</v>
       </c>
       <c r="B1114" t="str">
-        <v>FG-401514</v>
+        <v>FG-401506</v>
       </c>
       <c r="C1114" t="str">
-        <v>SPRINKLER FITTINGS END CAP (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (75MM C TYPE)</v>
       </c>
       <c r="D1114" t="str">
         <v>SPRINKLER FITTINGS END CAP</v>
@@ -39387,7 +39387,7 @@
         <v>General</v>
       </c>
       <c r="G1114" t="str">
-        <v>75MM L TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1114" t="str">
         <v>Nos</v>
@@ -39407,10 +39407,10 @@
         <v>1114</v>
       </c>
       <c r="B1115" t="str">
-        <v>FG-401506</v>
+        <v>FG-401529</v>
       </c>
       <c r="C1115" t="str">
-        <v>SPRINKLER FITTINGS END CAP (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (63MM C TYPE)</v>
       </c>
       <c r="D1115" t="str">
         <v>SPRINKLER FITTINGS END CAP</v>
@@ -39422,7 +39422,7 @@
         <v>General</v>
       </c>
       <c r="G1115" t="str">
-        <v>75MM C TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1115" t="str">
         <v>Nos</v>
@@ -39442,13 +39442,13 @@
         <v>1115</v>
       </c>
       <c r="B1116" t="str">
-        <v>FG-401529</v>
+        <v>FG-401517</v>
       </c>
       <c r="C1116" t="str">
-        <v>SPRINKLER FITTINGS END CAP (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (75MM P TYPE)</v>
       </c>
       <c r="D1116" t="str">
-        <v>SPRINKLER FITTINGS END CAP</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
       </c>
       <c r="E1116" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39457,7 +39457,7 @@
         <v>General</v>
       </c>
       <c r="G1116" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM P TYPE</v>
       </c>
       <c r="H1116" t="str">
         <v>Nos</v>
@@ -39469,7 +39469,7 @@
         <v>Active</v>
       </c>
       <c r="K1116" t="str">
-        <v>SPRINKLER FITTINGS END CAP for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1117">
@@ -39477,10 +39477,10 @@
         <v>1116</v>
       </c>
       <c r="B1117" t="str">
-        <v>FG-401517</v>
+        <v>FG-401518</v>
       </c>
       <c r="C1117" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (75MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (63MM P TYPE)</v>
       </c>
       <c r="D1117" t="str">
         <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
@@ -39492,7 +39492,7 @@
         <v>General</v>
       </c>
       <c r="G1117" t="str">
-        <v>75MM P TYPE</v>
+        <v>63MM P TYPE</v>
       </c>
       <c r="H1117" t="str">
         <v>Nos</v>
@@ -39512,13 +39512,13 @@
         <v>1117</v>
       </c>
       <c r="B1118" t="str">
-        <v>FG-401518</v>
+        <v>FG-401505</v>
       </c>
       <c r="C1118" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (63MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (75MM C TYPE)</v>
       </c>
       <c r="D1118" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
+        <v>SPRINKLER FITTINGS PCN</v>
       </c>
       <c r="E1118" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39527,7 +39527,7 @@
         <v>General</v>
       </c>
       <c r="G1118" t="str">
-        <v>63MM P TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1118" t="str">
         <v>Nos</v>
@@ -39539,7 +39539,7 @@
         <v>Active</v>
       </c>
       <c r="K1118" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS PCN for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1119">
@@ -39547,10 +39547,10 @@
         <v>1118</v>
       </c>
       <c r="B1119" t="str">
-        <v>FG-401505</v>
+        <v>FG-401513</v>
       </c>
       <c r="C1119" t="str">
-        <v>SPRINKLER FITTINGS PCN (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (75MM L TYPE)</v>
       </c>
       <c r="D1119" t="str">
         <v>SPRINKLER FITTINGS PCN</v>
@@ -39562,7 +39562,7 @@
         <v>General</v>
       </c>
       <c r="G1119" t="str">
-        <v>75MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1119" t="str">
         <v>Nos</v>
@@ -39582,10 +39582,10 @@
         <v>1119</v>
       </c>
       <c r="B1120" t="str">
-        <v>FG-401513</v>
+        <v>FG-401528</v>
       </c>
       <c r="C1120" t="str">
-        <v>SPRINKLER FITTINGS PCN (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (63MM C TYPE)</v>
       </c>
       <c r="D1120" t="str">
         <v>SPRINKLER FITTINGS PCN</v>
@@ -39597,7 +39597,7 @@
         <v>General</v>
       </c>
       <c r="G1120" t="str">
-        <v>75MM L TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1120" t="str">
         <v>Nos</v>
@@ -39617,13 +39617,13 @@
         <v>1120</v>
       </c>
       <c r="B1121" t="str">
-        <v>FG-401528</v>
+        <v>FG-401507</v>
       </c>
       <c r="C1121" t="str">
-        <v>SPRINKLER FITTINGS PCN (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL (20MM)</v>
       </c>
       <c r="D1121" t="str">
-        <v>SPRINKLER FITTINGS PCN</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL</v>
       </c>
       <c r="E1121" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39632,7 +39632,7 @@
         <v>General</v>
       </c>
       <c r="G1121" t="str">
-        <v>63MM C TYPE</v>
+        <v>20MM</v>
       </c>
       <c r="H1121" t="str">
         <v>Nos</v>
@@ -39644,7 +39644,7 @@
         <v>Active</v>
       </c>
       <c r="K1121" t="str">
-        <v>SPRINKLER FITTINGS PCN for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1122">
@@ -39652,13 +39652,13 @@
         <v>1121</v>
       </c>
       <c r="B1122" t="str">
-        <v>FG-401507</v>
+        <v>FG-401508</v>
       </c>
       <c r="C1122" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL (20MM)</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE (75MM C TYPE)</v>
       </c>
       <c r="D1122" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE</v>
       </c>
       <c r="E1122" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39667,7 +39667,7 @@
         <v>General</v>
       </c>
       <c r="G1122" t="str">
-        <v>20MM</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1122" t="str">
         <v>Nos</v>
@@ -39679,7 +39679,7 @@
         <v>Active</v>
       </c>
       <c r="K1122" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1123">
@@ -39687,10 +39687,10 @@
         <v>1122</v>
       </c>
       <c r="B1123" t="str">
-        <v>FG-401508</v>
+        <v>FG-401515</v>
       </c>
       <c r="C1123" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE (20MM L TYPE)</v>
       </c>
       <c r="D1123" t="str">
         <v>SPRINKLER FITTINGS GI RISER PIPE</v>
@@ -39702,7 +39702,7 @@
         <v>General</v>
       </c>
       <c r="G1123" t="str">
-        <v>75MM C TYPE</v>
+        <v>20MM L TYPE</v>
       </c>
       <c r="H1123" t="str">
         <v>Nos</v>
@@ -39722,25 +39722,25 @@
         <v>1123</v>
       </c>
       <c r="B1124" t="str">
-        <v>FG-401515</v>
+        <v>FG-401742</v>
       </c>
       <c r="C1124" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE (20MM L TYPE)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 1)</v>
       </c>
       <c r="D1124" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE</v>
+        <v>ROUND DRIPLINE 12MM ISI</v>
       </c>
       <c r="E1124" t="str">
-        <v>Sprinkler Pipes &amp; Fittings</v>
+        <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1124" t="str">
-        <v>General</v>
+        <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1124" t="str">
-        <v>20MM L TYPE</v>
+        <v>12-4-30 CLASS 1</v>
       </c>
       <c r="H1124" t="str">
-        <v>Nos</v>
+        <v>ROLL</v>
       </c>
       <c r="I1124" t="str">
         <v>-</v>
@@ -39749,7 +39749,7 @@
         <v>Active</v>
       </c>
       <c r="K1124" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE for sprinkler irrigation systems.</v>
+        <v>ROUND DRIPLINE 12MM ISI certified.</v>
       </c>
     </row>
     <row r="1125">
@@ -39757,10 +39757,10 @@
         <v>1124</v>
       </c>
       <c r="B1125" t="str">
-        <v>FG-401742</v>
+        <v>FG-401743</v>
       </c>
       <c r="C1125" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 1)</v>
       </c>
       <c r="D1125" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39772,7 +39772,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1125" t="str">
-        <v>12-4-30 CLASS 1</v>
+        <v>12-4-40 CLASS 1</v>
       </c>
       <c r="H1125" t="str">
         <v>ROLL</v>
@@ -39792,10 +39792,10 @@
         <v>1125</v>
       </c>
       <c r="B1126" t="str">
-        <v>FG-401743</v>
+        <v>FG-401744</v>
       </c>
       <c r="C1126" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 1)</v>
       </c>
       <c r="D1126" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39807,7 +39807,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1126" t="str">
-        <v>12-4-40 CLASS 1</v>
+        <v>12-4-50 CLASS 1</v>
       </c>
       <c r="H1126" t="str">
         <v>ROLL</v>
@@ -39827,10 +39827,10 @@
         <v>1126</v>
       </c>
       <c r="B1127" t="str">
-        <v>FG-401744</v>
+        <v>FG-401751</v>
       </c>
       <c r="C1127" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1127" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39842,7 +39842,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1127" t="str">
-        <v>12-4-50 CLASS 1</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1127" t="str">
         <v>ROLL</v>
@@ -39862,10 +39862,10 @@
         <v>1127</v>
       </c>
       <c r="B1128" t="str">
-        <v>FG-401751</v>
+        <v>FG-401752</v>
       </c>
       <c r="C1128" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1128" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39877,7 +39877,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1128" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1128" t="str">
         <v>ROLL</v>
@@ -39897,10 +39897,10 @@
         <v>1128</v>
       </c>
       <c r="B1129" t="str">
-        <v>FG-401752</v>
+        <v>FG-401753</v>
       </c>
       <c r="C1129" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1129" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39912,7 +39912,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1129" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1129" t="str">
         <v>ROLL</v>
@@ -39932,10 +39932,10 @@
         <v>1129</v>
       </c>
       <c r="B1130" t="str">
-        <v>FG-401753</v>
+        <v>FG-401754</v>
       </c>
       <c r="C1130" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1130" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39947,7 +39947,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1130" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1130" t="str">
         <v>ROLL</v>
@@ -39967,10 +39967,10 @@
         <v>1130</v>
       </c>
       <c r="B1131" t="str">
-        <v>FG-401754</v>
+        <v>FG-401755</v>
       </c>
       <c r="C1131" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1131" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39982,7 +39982,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1131" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1131" t="str">
         <v>ROLL</v>
@@ -40002,10 +40002,10 @@
         <v>1131</v>
       </c>
       <c r="B1132" t="str">
-        <v>FG-401755</v>
+        <v>FG-401756</v>
       </c>
       <c r="C1132" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1132" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -40017,7 +40017,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1132" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1132" t="str">
         <v>ROLL</v>
@@ -40037,13 +40037,13 @@
         <v>1132</v>
       </c>
       <c r="B1133" t="str">
-        <v>FG-401756</v>
+        <v>FG-401745</v>
       </c>
       <c r="C1133" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1133" t="str">
-        <v>ROUND DRIPLINE 12MM ISI</v>
+        <v>ROUND DRIPLINE 16MM ISI</v>
       </c>
       <c r="E1133" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40052,7 +40052,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1133" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1133" t="str">
         <v>ROLL</v>
@@ -40064,7 +40064,7 @@
         <v>Active</v>
       </c>
       <c r="K1133" t="str">
-        <v>ROUND DRIPLINE 12MM ISI certified.</v>
+        <v>ROUND DRIPLINE 16MM ISI certified.</v>
       </c>
     </row>
     <row r="1134">
@@ -40072,10 +40072,10 @@
         <v>1133</v>
       </c>
       <c r="B1134" t="str">
-        <v>FG-401745</v>
+        <v>FG-401746</v>
       </c>
       <c r="C1134" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1134" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40087,7 +40087,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1134" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1134" t="str">
         <v>ROLL</v>
@@ -40107,10 +40107,10 @@
         <v>1134</v>
       </c>
       <c r="B1135" t="str">
-        <v>FG-401746</v>
+        <v>FG-401747</v>
       </c>
       <c r="C1135" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1135" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40122,7 +40122,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1135" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1135" t="str">
         <v>ROLL</v>
@@ -40142,10 +40142,10 @@
         <v>1135</v>
       </c>
       <c r="B1136" t="str">
-        <v>FG-401747</v>
+        <v>FG-401757</v>
       </c>
       <c r="C1136" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1136" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40157,7 +40157,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1136" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1136" t="str">
         <v>ROLL</v>
@@ -40177,10 +40177,10 @@
         <v>1136</v>
       </c>
       <c r="B1137" t="str">
-        <v>FG-401757</v>
+        <v>FG-401758</v>
       </c>
       <c r="C1137" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1137" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40192,7 +40192,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1137" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1137" t="str">
         <v>ROLL</v>
@@ -40212,10 +40212,10 @@
         <v>1137</v>
       </c>
       <c r="B1138" t="str">
-        <v>FG-401758</v>
+        <v>FG-401759</v>
       </c>
       <c r="C1138" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1138" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40227,7 +40227,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1138" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1138" t="str">
         <v>ROLL</v>
@@ -40247,13 +40247,13 @@
         <v>1138</v>
       </c>
       <c r="B1139" t="str">
-        <v>FG-401759</v>
+        <v>-</v>
       </c>
       <c r="C1139" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-30 CLASS-1)</v>
       </c>
       <c r="D1139" t="str">
-        <v>ROUND DRIPLINE 16MM ISI</v>
+        <v>20MM ROUND INLINE PIPE ISI</v>
       </c>
       <c r="E1139" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40262,10 +40262,10 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1139" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>20-4-30 CLASS-1</v>
       </c>
       <c r="H1139" t="str">
-        <v>ROLL</v>
+        <v>MTR</v>
       </c>
       <c r="I1139" t="str">
         <v>-</v>
@@ -40274,7 +40274,7 @@
         <v>Active</v>
       </c>
       <c r="K1139" t="str">
-        <v>ROUND DRIPLINE 16MM ISI certified.</v>
+        <v>20mm Round Inline Drip Pipe ISI certified.</v>
       </c>
     </row>
     <row r="1140">
@@ -40285,7 +40285,7 @@
         <v>-</v>
       </c>
       <c r="C1140" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-30 CLASS-1)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-40 CLASS-1)</v>
       </c>
       <c r="D1140" t="str">
         <v>20MM ROUND INLINE PIPE ISI</v>
@@ -40297,7 +40297,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1140" t="str">
-        <v>20-4-30 CLASS-1</v>
+        <v>20-4-40 CLASS-1</v>
       </c>
       <c r="H1140" t="str">
         <v>MTR</v>
@@ -40320,7 +40320,7 @@
         <v>-</v>
       </c>
       <c r="C1141" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-40 CLASS-1)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-50 CLASS-1)</v>
       </c>
       <c r="D1141" t="str">
         <v>20MM ROUND INLINE PIPE ISI</v>
@@ -40332,7 +40332,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1141" t="str">
-        <v>20-4-40 CLASS-1</v>
+        <v>20-4-50 CLASS-1</v>
       </c>
       <c r="H1141" t="str">
         <v>MTR</v>
@@ -40352,25 +40352,25 @@
         <v>1141</v>
       </c>
       <c r="B1142" t="str">
-        <v>-</v>
+        <v>FG-401763</v>
       </c>
       <c r="C1142" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-50 CLASS-1)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1142" t="str">
-        <v>20MM ROUND INLINE PIPE ISI</v>
+        <v>FLAT DRIPLINE 12MM ISI</v>
       </c>
       <c r="E1142" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1142" t="str">
-        <v>ROUND DRIP ISI</v>
+        <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1142" t="str">
-        <v>20-4-50 CLASS-1</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1142" t="str">
-        <v>MTR</v>
+        <v>ROLL</v>
       </c>
       <c r="I1142" t="str">
         <v>-</v>
@@ -40379,7 +40379,7 @@
         <v>Active</v>
       </c>
       <c r="K1142" t="str">
-        <v>20mm Round Inline Drip Pipe ISI certified.</v>
+        <v>FLAT DRIPLINE 12MM ISI certified.</v>
       </c>
     </row>
     <row r="1143">
@@ -40387,10 +40387,10 @@
         <v>1142</v>
       </c>
       <c r="B1143" t="str">
-        <v>FG-401763</v>
+        <v>FG-401764</v>
       </c>
       <c r="C1143" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1143" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40402,7 +40402,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1143" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1143" t="str">
         <v>ROLL</v>
@@ -40422,10 +40422,10 @@
         <v>1143</v>
       </c>
       <c r="B1144" t="str">
-        <v>FG-401764</v>
+        <v>FG-401765</v>
       </c>
       <c r="C1144" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1144" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40437,7 +40437,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1144" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1144" t="str">
         <v>ROLL</v>
@@ -40457,10 +40457,10 @@
         <v>1144</v>
       </c>
       <c r="B1145" t="str">
-        <v>FG-401765</v>
+        <v>FG-401766</v>
       </c>
       <c r="C1145" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1145" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40472,7 +40472,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1145" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1145" t="str">
         <v>ROLL</v>
@@ -40492,10 +40492,10 @@
         <v>1145</v>
       </c>
       <c r="B1146" t="str">
-        <v>FG-401766</v>
+        <v>FG-401767</v>
       </c>
       <c r="C1146" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1146" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40507,7 +40507,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1146" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1146" t="str">
         <v>ROLL</v>
@@ -40527,10 +40527,10 @@
         <v>1146</v>
       </c>
       <c r="B1147" t="str">
-        <v>FG-401767</v>
+        <v>FG-401768</v>
       </c>
       <c r="C1147" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1147" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40542,7 +40542,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1147" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1147" t="str">
         <v>ROLL</v>
@@ -40562,13 +40562,13 @@
         <v>1147</v>
       </c>
       <c r="B1148" t="str">
-        <v>FG-401768</v>
+        <v>FG-401760</v>
       </c>
       <c r="C1148" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1148" t="str">
-        <v>FLAT DRIPLINE 12MM ISI</v>
+        <v>FLAT DRIPLINE 16MM ISI</v>
       </c>
       <c r="E1148" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40577,7 +40577,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1148" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1148" t="str">
         <v>ROLL</v>
@@ -40589,7 +40589,7 @@
         <v>Active</v>
       </c>
       <c r="K1148" t="str">
-        <v>FLAT DRIPLINE 12MM ISI certified.</v>
+        <v>FLAT DRIPLINE 16MM ISI certified.</v>
       </c>
     </row>
     <row r="1149">
@@ -40597,10 +40597,10 @@
         <v>1148</v>
       </c>
       <c r="B1149" t="str">
-        <v>FG-401760</v>
+        <v>FG-401761</v>
       </c>
       <c r="C1149" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1149" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40612,7 +40612,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1149" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1149" t="str">
         <v>ROLL</v>
@@ -40632,10 +40632,10 @@
         <v>1149</v>
       </c>
       <c r="B1150" t="str">
-        <v>FG-401761</v>
+        <v>FG-401762</v>
       </c>
       <c r="C1150" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1150" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40647,7 +40647,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1150" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1150" t="str">
         <v>ROLL</v>
@@ -40667,10 +40667,10 @@
         <v>1150</v>
       </c>
       <c r="B1151" t="str">
-        <v>FG-401762</v>
+        <v>FG-401769</v>
       </c>
       <c r="C1151" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1151" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40682,7 +40682,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1151" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1151" t="str">
         <v>ROLL</v>
@@ -40702,10 +40702,10 @@
         <v>1151</v>
       </c>
       <c r="B1152" t="str">
-        <v>FG-401769</v>
+        <v>FG-401770</v>
       </c>
       <c r="C1152" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1152" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40717,7 +40717,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1152" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1152" t="str">
         <v>ROLL</v>
@@ -40737,10 +40737,10 @@
         <v>1152</v>
       </c>
       <c r="B1153" t="str">
-        <v>FG-401770</v>
+        <v>FG-401779</v>
       </c>
       <c r="C1153" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1153" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40752,7 +40752,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1153" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1153" t="str">
         <v>ROLL</v>
@@ -40772,13 +40772,13 @@
         <v>1153</v>
       </c>
       <c r="B1154" t="str">
-        <v>FG-401779</v>
+        <v>FG-401771</v>
       </c>
       <c r="C1154" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-30 CLASS 1)</v>
       </c>
       <c r="D1154" t="str">
-        <v>FLAT DRIPLINE 16MM ISI</v>
+        <v>FLAT DRIPLINE 20MM ISI</v>
       </c>
       <c r="E1154" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40787,7 +40787,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1154" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>20-4-30 CLASS 1</v>
       </c>
       <c r="H1154" t="str">
         <v>ROLL</v>
@@ -40799,7 +40799,7 @@
         <v>Active</v>
       </c>
       <c r="K1154" t="str">
-        <v>FLAT DRIPLINE 16MM ISI certified.</v>
+        <v>FLAT DRIPLINE 20MM ISI certified.</v>
       </c>
     </row>
     <row r="1155">
@@ -40807,10 +40807,10 @@
         <v>1154</v>
       </c>
       <c r="B1155" t="str">
-        <v>FG-401771</v>
+        <v>FG-401772</v>
       </c>
       <c r="C1155" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-40 CLASS 1)</v>
       </c>
       <c r="D1155" t="str">
         <v>FLAT DRIPLINE 20MM ISI</v>
@@ -40822,7 +40822,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1155" t="str">
-        <v>20-4-30 CLASS 1</v>
+        <v>20-4-40 CLASS 1</v>
       </c>
       <c r="H1155" t="str">
         <v>ROLL</v>
@@ -40842,10 +40842,10 @@
         <v>1155</v>
       </c>
       <c r="B1156" t="str">
-        <v>FG-401772</v>
+        <v>FG-401773</v>
       </c>
       <c r="C1156" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-50 CLASS 1)</v>
       </c>
       <c r="D1156" t="str">
         <v>FLAT DRIPLINE 20MM ISI</v>
@@ -40857,7 +40857,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1156" t="str">
-        <v>20-4-40 CLASS 1</v>
+        <v>20-4-50 CLASS 1</v>
       </c>
       <c r="H1156" t="str">
         <v>ROLL</v>
@@ -40877,25 +40877,25 @@
         <v>1156</v>
       </c>
       <c r="B1157" t="str">
-        <v>FG-401773</v>
+        <v>-</v>
       </c>
       <c r="C1157" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-50 CLASS 1)</v>
+        <v>12MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1157" t="str">
-        <v>FLAT DRIPLINE 20MM ISI</v>
+        <v>12MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1157" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1157" t="str">
-        <v>FLAT DRIP ISI</v>
+        <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1157" t="str">
-        <v>20-4-50 CLASS 1</v>
+        <v>CLASS-2</v>
       </c>
       <c r="H1157" t="str">
-        <v>ROLL</v>
+        <v>MTR</v>
       </c>
       <c r="I1157" t="str">
         <v>-</v>
@@ -40904,7 +40904,7 @@
         <v>Active</v>
       </c>
       <c r="K1157" t="str">
-        <v>FLAT DRIPLINE 20MM ISI certified.</v>
+        <v>12mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1158">
@@ -40915,10 +40915,10 @@
         <v>-</v>
       </c>
       <c r="C1158" t="str">
-        <v>12MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>16MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1158" t="str">
-        <v>12MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>16MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1158" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40939,7 +40939,7 @@
         <v>Active</v>
       </c>
       <c r="K1158" t="str">
-        <v>12mm Plain Lateral Online Drip Pipe.</v>
+        <v>16mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1159">
@@ -40950,10 +40950,10 @@
         <v>-</v>
       </c>
       <c r="C1159" t="str">
-        <v>16MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>20MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1159" t="str">
-        <v>16MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>20MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1159" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40974,7 +40974,7 @@
         <v>Active</v>
       </c>
       <c r="K1159" t="str">
-        <v>16mm Plain Lateral Online Drip Pipe.</v>
+        <v>20mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1160">
@@ -40985,10 +40985,10 @@
         <v>-</v>
       </c>
       <c r="C1160" t="str">
-        <v>20MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-1)</v>
       </c>
       <c r="D1160" t="str">
-        <v>20MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1160" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40997,7 +40997,7 @@
         <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1160" t="str">
-        <v>CLASS-2</v>
+        <v>CLASS-1</v>
       </c>
       <c r="H1160" t="str">
         <v>MTR</v>
@@ -41009,7 +41009,7 @@
         <v>Active</v>
       </c>
       <c r="K1160" t="str">
-        <v>20mm Plain Lateral Online Drip Pipe.</v>
+        <v>32mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1161">
@@ -41020,7 +41020,7 @@
         <v>-</v>
       </c>
       <c r="C1161" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-1)</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1161" t="str">
         <v>32MM PLAIN LATERAL ONLINE PIPE</v>
@@ -41032,7 +41032,7 @@
         <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1161" t="str">
-        <v>CLASS-1</v>
+        <v>CLASS-2</v>
       </c>
       <c r="H1161" t="str">
         <v>MTR</v>
@@ -41052,22 +41052,22 @@
         <v>1161</v>
       </c>
       <c r="B1162" t="str">
-        <v>-</v>
+        <v>FG-401763</v>
       </c>
       <c r="C1162" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1162" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12</v>
       </c>
       <c r="E1162" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1162" t="str">
-        <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
+        <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1162" t="str">
-        <v>CLASS-2</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1162" t="str">
         <v>MTR</v>
@@ -41079,7 +41079,7 @@
         <v>Active</v>
       </c>
       <c r="K1162" t="str">
-        <v>32mm Plain Lateral Online Drip Pipe.</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12. Available sizes: 12-4-30 CLASS 2, 12-4-40 CLASS 2, 12-4-50 CLASS 2, 12-4-30 CLASS 3, 12-4-40 CLASS 3, 12-4-50 CLASS 3.</v>
       </c>
     </row>
     <row r="1163">
@@ -41087,10 +41087,10 @@
         <v>1162</v>
       </c>
       <c r="B1163" t="str">
-        <v>FG-401763</v>
+        <v>FG-401764</v>
       </c>
       <c r="C1163" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1163" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41102,7 +41102,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1163" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1163" t="str">
         <v>MTR</v>
@@ -41122,10 +41122,10 @@
         <v>1163</v>
       </c>
       <c r="B1164" t="str">
-        <v>FG-401764</v>
+        <v>FG-401765</v>
       </c>
       <c r="C1164" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1164" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41137,7 +41137,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1164" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1164" t="str">
         <v>MTR</v>
@@ -41157,10 +41157,10 @@
         <v>1164</v>
       </c>
       <c r="B1165" t="str">
-        <v>FG-401765</v>
+        <v>FG-401766</v>
       </c>
       <c r="C1165" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1165" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41172,7 +41172,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1165" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1165" t="str">
         <v>MTR</v>
@@ -41192,10 +41192,10 @@
         <v>1165</v>
       </c>
       <c r="B1166" t="str">
-        <v>FG-401766</v>
+        <v>FG-401767</v>
       </c>
       <c r="C1166" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1166" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41207,7 +41207,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1166" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1166" t="str">
         <v>MTR</v>
@@ -41227,10 +41227,10 @@
         <v>1166</v>
       </c>
       <c r="B1167" t="str">
-        <v>FG-401767</v>
+        <v>FG-401768</v>
       </c>
       <c r="C1167" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1167" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41242,7 +41242,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1167" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1167" t="str">
         <v>MTR</v>
@@ -41262,13 +41262,13 @@
         <v>1167</v>
       </c>
       <c r="B1168" t="str">
-        <v>FG-401768</v>
+        <v>FG-401760</v>
       </c>
       <c r="C1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16</v>
       </c>
       <c r="E1168" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -41277,7 +41277,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1168" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1168" t="str">
         <v>MTR</v>
@@ -41289,7 +41289,7 @@
         <v>Active</v>
       </c>
       <c r="K1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12. Available sizes: 12-4-30 CLASS 2, 12-4-40 CLASS 2, 12-4-50 CLASS 2, 12-4-30 CLASS 3, 12-4-40 CLASS 3, 12-4-50 CLASS 3.</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16. Available sizes: 16-4-30 CLASS 1, 16-4-40 CLASS 1, 16-4-50 CLASS 1, 16-4-30 CLASS 2, 16-4-40 CLASS 2, 16-4-50 CLASS 2.</v>
       </c>
     </row>
     <row r="1169">
@@ -41297,10 +41297,10 @@
         <v>1168</v>
       </c>
       <c r="B1169" t="str">
-        <v>FG-401760</v>
+        <v>FG-401761</v>
       </c>
       <c r="C1169" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1169" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41312,7 +41312,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1169" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1169" t="str">
         <v>MTR</v>
@@ -41332,10 +41332,10 @@
         <v>1169</v>
       </c>
       <c r="B1170" t="str">
-        <v>FG-401761</v>
+        <v>FG-401762</v>
       </c>
       <c r="C1170" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1170" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41347,7 +41347,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1170" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1170" t="str">
         <v>MTR</v>
@@ -41367,10 +41367,10 @@
         <v>1170</v>
       </c>
       <c r="B1171" t="str">
-        <v>FG-401762</v>
+        <v>FG-401769</v>
       </c>
       <c r="C1171" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1171" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41382,7 +41382,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1171" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1171" t="str">
         <v>MTR</v>
@@ -41402,10 +41402,10 @@
         <v>1171</v>
       </c>
       <c r="B1172" t="str">
-        <v>FG-401769</v>
+        <v>FG-401770</v>
       </c>
       <c r="C1172" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1172" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41417,7 +41417,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1172" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1172" t="str">
         <v>MTR</v>
@@ -41437,10 +41437,10 @@
         <v>1172</v>
       </c>
       <c r="B1173" t="str">
-        <v>FG-401770</v>
+        <v>FG-401779</v>
       </c>
       <c r="C1173" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1173" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41452,7 +41452,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1173" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1173" t="str">
         <v>MTR</v>
@@ -41472,13 +41472,13 @@
         <v>1173</v>
       </c>
       <c r="B1174" t="str">
-        <v>FG-401779</v>
+        <v>FG-401771</v>
       </c>
       <c r="C1174" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-30 CLASS 1)</v>
       </c>
       <c r="D1174" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20</v>
       </c>
       <c r="E1174" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -41487,7 +41487,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1174" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>20-4-30 CLASS 1</v>
       </c>
       <c r="H1174" t="str">
         <v>MTR</v>
@@ -41499,7 +41499,7 @@
         <v>Active</v>
       </c>
       <c r="K1174" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16. Available sizes: 16-4-30 CLASS 1, 16-4-40 CLASS 1, 16-4-50 CLASS 1, 16-4-30 CLASS 2, 16-4-40 CLASS 2, 16-4-50 CLASS 2.</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20. Available sizes: 20-4-30 CLASS 1, 20-4-40 CLASS 1, 20-4-50 CLASS 1.</v>
       </c>
     </row>
     <row r="1175">
@@ -41507,10 +41507,10 @@
         <v>1174</v>
       </c>
       <c r="B1175" t="str">
-        <v>FG-401771</v>
+        <v>FG-401772</v>
       </c>
       <c r="C1175" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-40 CLASS 1)</v>
       </c>
       <c r="D1175" t="str">
         <v>FLAT DRIPLINE ISI 400MTR 20</v>
@@ -41522,7 +41522,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1175" t="str">
-        <v>20-4-30 CLASS 1</v>
+        <v>20-4-40 CLASS 1</v>
       </c>
       <c r="H1175" t="str">
         <v>MTR</v>
@@ -41542,10 +41542,10 @@
         <v>1175</v>
       </c>
       <c r="B1176" t="str">
-        <v>FG-401772</v>
+        <v>FG-401773</v>
       </c>
       <c r="C1176" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-50 CLASS 1)</v>
       </c>
       <c r="D1176" t="str">
         <v>FLAT DRIPLINE ISI 400MTR 20</v>
@@ -41557,7 +41557,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1176" t="str">
-        <v>20-4-40 CLASS 1</v>
+        <v>20-4-50 CLASS 1</v>
       </c>
       <c r="H1176" t="str">
         <v>MTR</v>
@@ -41577,22 +41577,22 @@
         <v>1176</v>
       </c>
       <c r="B1177" t="str">
-        <v>FG-401773</v>
+        <v>FG-401066</v>
       </c>
       <c r="C1177" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-50 CLASS 1)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
       </c>
       <c r="D1177" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
       </c>
       <c r="E1177" t="str">
-        <v>DRIP IRRIGATION SYSTEM</v>
+        <v>UPVC CASING PIPES</v>
       </c>
       <c r="F1177" t="str">
-        <v>FLAT DRIP (PEPSI) - INLINE</v>
+        <v>General</v>
       </c>
       <c r="G1177" t="str">
-        <v>20-4-50 CLASS 1</v>
+        <v>35MM 1 1/4 Inch</v>
       </c>
       <c r="H1177" t="str">
         <v>MTR</v>
@@ -41604,7 +41604,7 @@
         <v>Active</v>
       </c>
       <c r="K1177" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20. Available sizes: 20-4-30 CLASS 1, 20-4-40 CLASS 1, 20-4-50 CLASS 1.</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 40MM 1 1/2 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1178">
@@ -41612,10 +41612,10 @@
         <v>1177</v>
       </c>
       <c r="B1178" t="str">
-        <v>FG-401066</v>
+        <v>FG-401067</v>
       </c>
       <c r="C1178" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (40MM 1 1/2 Inch)</v>
       </c>
       <c r="D1178" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41627,7 +41627,7 @@
         <v>General</v>
       </c>
       <c r="G1178" t="str">
-        <v>35MM 1 1/4 Inch</v>
+        <v>40MM 1 1/2 Inch</v>
       </c>
       <c r="H1178" t="str">
         <v>MTR</v>
@@ -41647,10 +41647,10 @@
         <v>1178</v>
       </c>
       <c r="B1179" t="str">
-        <v>FG-401067</v>
+        <v>FG-401068</v>
       </c>
       <c r="C1179" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (40MM 1 1/2 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (50MM 2 Inch)</v>
       </c>
       <c r="D1179" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41662,7 +41662,7 @@
         <v>General</v>
       </c>
       <c r="G1179" t="str">
-        <v>40MM 1 1/2 Inch</v>
+        <v>50MM 2 Inch</v>
       </c>
       <c r="H1179" t="str">
         <v>MTR</v>
@@ -41682,10 +41682,10 @@
         <v>1179</v>
       </c>
       <c r="B1180" t="str">
-        <v>FG-401068</v>
+        <v>FG-401069</v>
       </c>
       <c r="C1180" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (50MM 2 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (100MM 4 Inch)</v>
       </c>
       <c r="D1180" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41697,7 +41697,7 @@
         <v>General</v>
       </c>
       <c r="G1180" t="str">
-        <v>50MM 2 Inch</v>
+        <v>100MM 4 Inch</v>
       </c>
       <c r="H1180" t="str">
         <v>MTR</v>
@@ -41717,10 +41717,10 @@
         <v>1180</v>
       </c>
       <c r="B1181" t="str">
-        <v>FG-401069</v>
+        <v>FG-401070</v>
       </c>
       <c r="C1181" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (100MM 4 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1181" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41732,7 +41732,7 @@
         <v>General</v>
       </c>
       <c r="G1181" t="str">
-        <v>100MM 4 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1181" t="str">
         <v>MTR</v>
@@ -41752,10 +41752,10 @@
         <v>1181</v>
       </c>
       <c r="B1182" t="str">
-        <v>FG-401070</v>
+        <v>FG-401071</v>
       </c>
       <c r="C1182" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1182" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41767,7 +41767,7 @@
         <v>General</v>
       </c>
       <c r="G1182" t="str">
-        <v>125MM 5 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1182" t="str">
         <v>MTR</v>
@@ -41787,10 +41787,10 @@
         <v>1182</v>
       </c>
       <c r="B1183" t="str">
-        <v>FG-401071</v>
+        <v>FG-401072</v>
       </c>
       <c r="C1183" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1183" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41802,7 +41802,7 @@
         <v>General</v>
       </c>
       <c r="G1183" t="str">
-        <v>150MM 6 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1183" t="str">
         <v>MTR</v>
@@ -41822,10 +41822,10 @@
         <v>1183</v>
       </c>
       <c r="B1184" t="str">
-        <v>FG-401072</v>
+        <v>FG-401073</v>
       </c>
       <c r="C1184" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1184" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41837,7 +41837,7 @@
         <v>General</v>
       </c>
       <c r="G1184" t="str">
-        <v>175MM 7 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1184" t="str">
         <v>MTR</v>
@@ -41857,13 +41857,13 @@
         <v>1184</v>
       </c>
       <c r="B1185" t="str">
-        <v>FG-401073</v>
+        <v>FG-401074</v>
       </c>
       <c r="C1185" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1185" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
       </c>
       <c r="E1185" t="str">
         <v>UPVC CASING PIPES</v>
@@ -41872,7 +41872,7 @@
         <v>General</v>
       </c>
       <c r="G1185" t="str">
-        <v>200MM 8 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1185" t="str">
         <v>MTR</v>
@@ -41884,7 +41884,7 @@
         <v>Active</v>
       </c>
       <c r="K1185" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 40MM 1 1/2 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1186">
@@ -41892,10 +41892,10 @@
         <v>1185</v>
       </c>
       <c r="B1186" t="str">
-        <v>FG-401074</v>
+        <v>FG-401075</v>
       </c>
       <c r="C1186" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1186" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41907,7 +41907,7 @@
         <v>General</v>
       </c>
       <c r="G1186" t="str">
-        <v>125MM 5 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1186" t="str">
         <v>MTR</v>
@@ -41927,10 +41927,10 @@
         <v>1186</v>
       </c>
       <c r="B1187" t="str">
-        <v>FG-401075</v>
+        <v>FG-401076</v>
       </c>
       <c r="C1187" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1187" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41942,7 +41942,7 @@
         <v>General</v>
       </c>
       <c r="G1187" t="str">
-        <v>150MM 6 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1187" t="str">
         <v>MTR</v>
@@ -41962,10 +41962,10 @@
         <v>1187</v>
       </c>
       <c r="B1188" t="str">
-        <v>FG-401076</v>
+        <v>FG-401077</v>
       </c>
       <c r="C1188" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1188" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41977,7 +41977,7 @@
         <v>General</v>
       </c>
       <c r="G1188" t="str">
-        <v>175MM 7 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1188" t="str">
         <v>MTR</v>
@@ -41997,13 +41997,13 @@
         <v>1188</v>
       </c>
       <c r="B1189" t="str">
-        <v>FG-401077</v>
+        <v>FG-401149</v>
       </c>
       <c r="C1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M (140MM 5 Inch)</v>
       </c>
       <c r="D1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M</v>
       </c>
       <c r="E1189" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42012,7 +42012,7 @@
         <v>General</v>
       </c>
       <c r="G1189" t="str">
-        <v>200MM 8 Inch</v>
+        <v>140MM 5 Inch</v>
       </c>
       <c r="H1189" t="str">
         <v>MTR</v>
@@ -42024,7 +42024,7 @@
         <v>Active</v>
       </c>
       <c r="K1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M. Available sizes: 140MM 5 Inch.</v>
       </c>
     </row>
     <row r="1190">
@@ -42032,13 +42032,13 @@
         <v>1189</v>
       </c>
       <c r="B1190" t="str">
-        <v>FG-401149</v>
+        <v>FG-401150</v>
       </c>
       <c r="C1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M (140MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M (140MM 5 Inch)</v>
       </c>
       <c r="D1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M</v>
       </c>
       <c r="E1190" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42059,7 +42059,7 @@
         <v>Active</v>
       </c>
       <c r="K1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M. Available sizes: 140MM 5 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M. Available sizes: 140MM 5 Inch.</v>
       </c>
     </row>
     <row r="1191">
@@ -42067,13 +42067,13 @@
         <v>1190</v>
       </c>
       <c r="B1191" t="str">
-        <v>FG-401150</v>
+        <v>FG-401078</v>
       </c>
       <c r="C1191" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M (140MM 5 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1191" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
       </c>
       <c r="E1191" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42082,7 +42082,7 @@
         <v>General</v>
       </c>
       <c r="G1191" t="str">
-        <v>140MM 5 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1191" t="str">
         <v>MTR</v>
@@ -42094,7 +42094,7 @@
         <v>Active</v>
       </c>
       <c r="K1191" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M. Available sizes: 140MM 5 Inch.</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1192">
@@ -42102,10 +42102,10 @@
         <v>1191</v>
       </c>
       <c r="B1192" t="str">
-        <v>FG-401078</v>
+        <v>FG-401079</v>
       </c>
       <c r="C1192" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1192" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42117,7 +42117,7 @@
         <v>General</v>
       </c>
       <c r="G1192" t="str">
-        <v>125MM 5 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1192" t="str">
         <v>MTR</v>
@@ -42137,10 +42137,10 @@
         <v>1192</v>
       </c>
       <c r="B1193" t="str">
-        <v>FG-401079</v>
+        <v>FG-401080</v>
       </c>
       <c r="C1193" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1193" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42152,7 +42152,7 @@
         <v>General</v>
       </c>
       <c r="G1193" t="str">
-        <v>150MM 6 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1193" t="str">
         <v>MTR</v>
@@ -42172,10 +42172,10 @@
         <v>1193</v>
       </c>
       <c r="B1194" t="str">
-        <v>FG-401080</v>
+        <v>FG-401081</v>
       </c>
       <c r="C1194" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1194" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42187,7 +42187,7 @@
         <v>General</v>
       </c>
       <c r="G1194" t="str">
-        <v>175MM 7 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1194" t="str">
         <v>MTR</v>
@@ -42207,13 +42207,13 @@
         <v>1194</v>
       </c>
       <c r="B1195" t="str">
-        <v>FG-401081</v>
+        <v>FG-401119</v>
       </c>
       <c r="C1195" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
       </c>
       <c r="D1195" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
       </c>
       <c r="E1195" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42222,7 +42222,7 @@
         <v>General</v>
       </c>
       <c r="G1195" t="str">
-        <v>200MM 8 Inch</v>
+        <v>35MM 1 1/4 Inch</v>
       </c>
       <c r="H1195" t="str">
         <v>MTR</v>
@@ -42234,7 +42234,7 @@
         <v>Active</v>
       </c>
       <c r="K1195" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1196">
@@ -42242,10 +42242,10 @@
         <v>1195</v>
       </c>
       <c r="B1196" t="str">
-        <v>FG-401119</v>
+        <v>FG-401121</v>
       </c>
       <c r="C1196" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (50MM 2 Inch)</v>
       </c>
       <c r="D1196" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42257,7 +42257,7 @@
         <v>General</v>
       </c>
       <c r="G1196" t="str">
-        <v>35MM 1 1/4 Inch</v>
+        <v>50MM 2 Inch</v>
       </c>
       <c r="H1196" t="str">
         <v>MTR</v>
@@ -42277,10 +42277,10 @@
         <v>1196</v>
       </c>
       <c r="B1197" t="str">
-        <v>FG-401121</v>
+        <v>FG-401122</v>
       </c>
       <c r="C1197" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (50MM 2 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (100MM 4 Inch)</v>
       </c>
       <c r="D1197" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42292,7 +42292,7 @@
         <v>General</v>
       </c>
       <c r="G1197" t="str">
-        <v>50MM 2 Inch</v>
+        <v>100MM 4 Inch</v>
       </c>
       <c r="H1197" t="str">
         <v>MTR</v>
@@ -42312,10 +42312,10 @@
         <v>1197</v>
       </c>
       <c r="B1198" t="str">
-        <v>FG-401122</v>
+        <v>FG-401123</v>
       </c>
       <c r="C1198" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (100MM 4 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1198" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42327,7 +42327,7 @@
         <v>General</v>
       </c>
       <c r="G1198" t="str">
-        <v>100MM 4 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1198" t="str">
         <v>MTR</v>
@@ -42347,10 +42347,10 @@
         <v>1198</v>
       </c>
       <c r="B1199" t="str">
-        <v>FG-401123</v>
+        <v>FG-401124</v>
       </c>
       <c r="C1199" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1199" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42362,7 +42362,7 @@
         <v>General</v>
       </c>
       <c r="G1199" t="str">
-        <v>125MM 5 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1199" t="str">
         <v>MTR</v>
@@ -42382,10 +42382,10 @@
         <v>1199</v>
       </c>
       <c r="B1200" t="str">
-        <v>FG-401124</v>
+        <v>FG-401125</v>
       </c>
       <c r="C1200" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1200" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42397,7 +42397,7 @@
         <v>General</v>
       </c>
       <c r="G1200" t="str">
-        <v>150MM 6 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1200" t="str">
         <v>MTR</v>
@@ -42417,10 +42417,10 @@
         <v>1200</v>
       </c>
       <c r="B1201" t="str">
-        <v>FG-401125</v>
+        <v>FG-401126</v>
       </c>
       <c r="C1201" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1201" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42432,7 +42432,7 @@
         <v>General</v>
       </c>
       <c r="G1201" t="str">
-        <v>175MM 7 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1201" t="str">
         <v>MTR</v>
@@ -42452,22 +42452,22 @@
         <v>1201</v>
       </c>
       <c r="B1202" t="str">
-        <v>FG-401126</v>
+        <v>FG-401166</v>
       </c>
       <c r="C1202" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (200MM 8 Inch)</v>
+        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1202" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
+        <v>COLOUMN PIPE ECO V4</v>
       </c>
       <c r="E1202" t="str">
-        <v>UPVC CASING PIPES</v>
+        <v>UPVC COLUMN PIPES</v>
       </c>
       <c r="F1202" t="str">
         <v>General</v>
       </c>
       <c r="G1202" t="str">
-        <v>200MM 8 Inch</v>
+        <v>33MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1202" t="str">
         <v>MTR</v>
@@ -42479,7 +42479,7 @@
         <v>Active</v>
       </c>
       <c r="K1202" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>COLOUMN PIPE ECO V4 for submersible pump systems.</v>
       </c>
     </row>
     <row r="1203">
@@ -42487,10 +42487,10 @@
         <v>1202</v>
       </c>
       <c r="B1203" t="str">
-        <v>FG-401166</v>
+        <v>FG-401162</v>
       </c>
       <c r="C1203" t="str">
-        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG BELL END TYPE)</v>
       </c>
       <c r="D1203" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42502,7 +42502,7 @@
         <v>General</v>
       </c>
       <c r="G1203" t="str">
-        <v>33MM 12.5KG COUPLER TYPE</v>
+        <v>33MM 12.5KG BELL END TYPE</v>
       </c>
       <c r="H1203" t="str">
         <v>MTR</v>
@@ -42522,10 +42522,10 @@
         <v>1203</v>
       </c>
       <c r="B1204" t="str">
-        <v>FG-401162</v>
+        <v>FG-401165</v>
       </c>
       <c r="C1204" t="str">
-        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG BELL END TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 10KG COUPLER TYPE)</v>
       </c>
       <c r="D1204" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42537,7 +42537,7 @@
         <v>General</v>
       </c>
       <c r="G1204" t="str">
-        <v>33MM 12.5KG BELL END TYPE</v>
+        <v>42MM 10KG COUPLER TYPE</v>
       </c>
       <c r="H1204" t="str">
         <v>MTR</v>
@@ -42557,10 +42557,10 @@
         <v>1204</v>
       </c>
       <c r="B1205" t="str">
-        <v>FG-401165</v>
+        <v>FG-401167</v>
       </c>
       <c r="C1205" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 10KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1205" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42572,7 +42572,7 @@
         <v>General</v>
       </c>
       <c r="G1205" t="str">
-        <v>42MM 10KG COUPLER TYPE</v>
+        <v>42MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1205" t="str">
         <v>MTR</v>
@@ -42592,10 +42592,10 @@
         <v>1205</v>
       </c>
       <c r="B1206" t="str">
-        <v>FG-401167</v>
+        <v>FG-401163</v>
       </c>
       <c r="C1206" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG BELL END TYPE)</v>
       </c>
       <c r="D1206" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42607,7 +42607,7 @@
         <v>General</v>
       </c>
       <c r="G1206" t="str">
-        <v>42MM 12.5KG COUPLER TYPE</v>
+        <v>42MM 12.5KG BELL END TYPE</v>
       </c>
       <c r="H1206" t="str">
         <v>MTR</v>
@@ -42627,10 +42627,10 @@
         <v>1206</v>
       </c>
       <c r="B1207" t="str">
-        <v>FG-401163</v>
+        <v>FG-401164</v>
       </c>
       <c r="C1207" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG BELL END TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (48MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1207" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42642,7 +42642,7 @@
         <v>General</v>
       </c>
       <c r="G1207" t="str">
-        <v>42MM 12.5KG BELL END TYPE</v>
+        <v>48MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1207" t="str">
         <v>MTR</v>
@@ -42662,10 +42662,10 @@
         <v>1207</v>
       </c>
       <c r="B1208" t="str">
-        <v>FG-401164</v>
+        <v>FG-401168</v>
       </c>
       <c r="C1208" t="str">
-        <v>COLOUMN PIPE ECO V4 (48MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (60MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1208" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42677,7 +42677,7 @@
         <v>General</v>
       </c>
       <c r="G1208" t="str">
-        <v>48MM 12.5KG COUPLER TYPE</v>
+        <v>60MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1208" t="str">
         <v>MTR</v>
@@ -42697,13 +42697,13 @@
         <v>1208</v>
       </c>
       <c r="B1209" t="str">
-        <v>FG-401168</v>
+        <v>FG-401175</v>
       </c>
       <c r="C1209" t="str">
-        <v>COLOUMN PIPE ECO V4 (60MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (33MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1209" t="str">
-        <v>COLOUMN PIPE ECO V4</v>
+        <v>COLOUMN PIPE MEDIUM</v>
       </c>
       <c r="E1209" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -42712,7 +42712,7 @@
         <v>General</v>
       </c>
       <c r="G1209" t="str">
-        <v>60MM 12.5KG COUPLER TYPE</v>
+        <v>33MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1209" t="str">
         <v>MTR</v>
@@ -42724,7 +42724,7 @@
         <v>Active</v>
       </c>
       <c r="K1209" t="str">
-        <v>COLOUMN PIPE ECO V4 for submersible pump systems.</v>
+        <v>COLOUMN PIPE MEDIUM for submersible pump systems.</v>
       </c>
     </row>
     <row r="1210">
@@ -42732,10 +42732,10 @@
         <v>1209</v>
       </c>
       <c r="B1210" t="str">
-        <v>FG-401175</v>
+        <v>FG-401177</v>
       </c>
       <c r="C1210" t="str">
-        <v>COLOUMN PIPE MEDIUM (33MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (42MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1210" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42747,7 +42747,7 @@
         <v>General</v>
       </c>
       <c r="G1210" t="str">
-        <v>33MM 18KG COUPLER TYPE</v>
+        <v>42MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1210" t="str">
         <v>MTR</v>
@@ -42767,10 +42767,10 @@
         <v>1210</v>
       </c>
       <c r="B1211" t="str">
-        <v>FG-401177</v>
+        <v>FG-401176</v>
       </c>
       <c r="C1211" t="str">
-        <v>COLOUMN PIPE MEDIUM (42MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (48MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1211" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42782,7 +42782,7 @@
         <v>General</v>
       </c>
       <c r="G1211" t="str">
-        <v>42MM 18KG COUPLER TYPE</v>
+        <v>48MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1211" t="str">
         <v>MTR</v>
@@ -42802,10 +42802,10 @@
         <v>1211</v>
       </c>
       <c r="B1212" t="str">
-        <v>FG-401176</v>
+        <v>FG-401178</v>
       </c>
       <c r="C1212" t="str">
-        <v>COLOUMN PIPE MEDIUM (48MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (60MM 15KG COUPLER TYPE)</v>
       </c>
       <c r="D1212" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42817,7 +42817,7 @@
         <v>General</v>
       </c>
       <c r="G1212" t="str">
-        <v>48MM 18KG COUPLER TYPE</v>
+        <v>60MM 15KG COUPLER TYPE</v>
       </c>
       <c r="H1212" t="str">
         <v>MTR</v>
@@ -42837,10 +42837,10 @@
         <v>1212</v>
       </c>
       <c r="B1213" t="str">
-        <v>FG-401178</v>
+        <v>FG-401180</v>
       </c>
       <c r="C1213" t="str">
-        <v>COLOUMN PIPE MEDIUM (60MM 15KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (75MM 10KG COUPLER TYPE)</v>
       </c>
       <c r="D1213" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42852,7 +42852,7 @@
         <v>General</v>
       </c>
       <c r="G1213" t="str">
-        <v>60MM 15KG COUPLER TYPE</v>
+        <v>75MM 10KG COUPLER TYPE</v>
       </c>
       <c r="H1213" t="str">
         <v>MTR</v>
@@ -42872,13 +42872,13 @@
         <v>1213</v>
       </c>
       <c r="B1214" t="str">
-        <v>FG-401180</v>
+        <v>FG-401169</v>
       </c>
       <c r="C1214" t="str">
-        <v>COLOUMN PIPE MEDIUM (75MM 10KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (33MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1214" t="str">
-        <v>COLOUMN PIPE MEDIUM</v>
+        <v>COLOUMN PIPE STANDARD</v>
       </c>
       <c r="E1214" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -42887,7 +42887,7 @@
         <v>General</v>
       </c>
       <c r="G1214" t="str">
-        <v>75MM 10KG COUPLER TYPE</v>
+        <v>33MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1214" t="str">
         <v>MTR</v>
@@ -42899,7 +42899,7 @@
         <v>Active</v>
       </c>
       <c r="K1214" t="str">
-        <v>COLOUMN PIPE MEDIUM for submersible pump systems.</v>
+        <v>COLOUMN PIPE STANDARD for submersible pump systems.</v>
       </c>
     </row>
     <row r="1215">
@@ -42907,10 +42907,10 @@
         <v>1214</v>
       </c>
       <c r="B1215" t="str">
-        <v>FG-401169</v>
+        <v>FG-401171</v>
       </c>
       <c r="C1215" t="str">
-        <v>COLOUMN PIPE STANDARD (33MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (42MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1215" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42922,7 +42922,7 @@
         <v>General</v>
       </c>
       <c r="G1215" t="str">
-        <v>33MM 25KG COUPLER TYPE</v>
+        <v>42MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1215" t="str">
         <v>MTR</v>
@@ -42942,10 +42942,10 @@
         <v>1215</v>
       </c>
       <c r="B1216" t="str">
-        <v>FG-401171</v>
+        <v>FG-401170</v>
       </c>
       <c r="C1216" t="str">
-        <v>COLOUMN PIPE STANDARD (42MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (48MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1216" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42957,7 +42957,7 @@
         <v>General</v>
       </c>
       <c r="G1216" t="str">
-        <v>42MM 25KG COUPLER TYPE</v>
+        <v>48MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1216" t="str">
         <v>MTR</v>
@@ -42977,10 +42977,10 @@
         <v>1216</v>
       </c>
       <c r="B1217" t="str">
-        <v>FG-401170</v>
+        <v>FG-401172</v>
       </c>
       <c r="C1217" t="str">
-        <v>COLOUMN PIPE STANDARD (48MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (60MM 20KG COUPLER TYPE)</v>
       </c>
       <c r="D1217" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42992,7 +42992,7 @@
         <v>General</v>
       </c>
       <c r="G1217" t="str">
-        <v>48MM 25KG COUPLER TYPE</v>
+        <v>60MM 20KG COUPLER TYPE</v>
       </c>
       <c r="H1217" t="str">
         <v>MTR</v>
@@ -43012,10 +43012,10 @@
         <v>1217</v>
       </c>
       <c r="B1218" t="str">
-        <v>FG-401172</v>
+        <v>FG-401174</v>
       </c>
       <c r="C1218" t="str">
-        <v>COLOUMN PIPE STANDARD (60MM 20KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (75MM 20KG COUPLER TYPE)</v>
       </c>
       <c r="D1218" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -43027,7 +43027,7 @@
         <v>General</v>
       </c>
       <c r="G1218" t="str">
-        <v>60MM 20KG COUPLER TYPE</v>
+        <v>75MM 20KG COUPLER TYPE</v>
       </c>
       <c r="H1218" t="str">
         <v>MTR</v>
@@ -43047,13 +43047,13 @@
         <v>1218</v>
       </c>
       <c r="B1219" t="str">
-        <v>FG-401174</v>
+        <v>-</v>
       </c>
       <c r="C1219" t="str">
-        <v>COLOUMN PIPE STANDARD (75MM 20KG COUPLER TYPE)</v>
+        <v>3M STANDARD PLUS PIPE (60MM 25 COUPLER TYPE)</v>
       </c>
       <c r="D1219" t="str">
-        <v>COLOUMN PIPE STANDARD</v>
+        <v>3M STANDARD PLUS PIPE</v>
       </c>
       <c r="E1219" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43062,7 +43062,7 @@
         <v>General</v>
       </c>
       <c r="G1219" t="str">
-        <v>75MM 20KG COUPLER TYPE</v>
+        <v>60MM 25 COUPLER TYPE</v>
       </c>
       <c r="H1219" t="str">
         <v>MTR</v>
@@ -43074,7 +43074,7 @@
         <v>Active</v>
       </c>
       <c r="K1219" t="str">
-        <v>COLOUMN PIPE STANDARD for submersible pump systems.</v>
+        <v>3M Standard Plus UPVC Column Pipe for submersible pump systems.</v>
       </c>
     </row>
     <row r="1220">
@@ -43082,13 +43082,13 @@
         <v>1219</v>
       </c>
       <c r="B1220" t="str">
-        <v>-</v>
+        <v>FG-401182</v>
       </c>
       <c r="C1220" t="str">
-        <v>3M STANDARD PLUS PIPE (60MM 25 COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (42MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1220" t="str">
-        <v>3M STANDARD PLUS PIPE</v>
+        <v>COLOUMN PIPE HEAVY</v>
       </c>
       <c r="E1220" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43097,7 +43097,7 @@
         <v>General</v>
       </c>
       <c r="G1220" t="str">
-        <v>60MM 25 COUPLER TYPE</v>
+        <v>42MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1220" t="str">
         <v>MTR</v>
@@ -43109,7 +43109,7 @@
         <v>Active</v>
       </c>
       <c r="K1220" t="str">
-        <v>3M Standard Plus UPVC Column Pipe for submersible pump systems.</v>
+        <v>COLOUMN PIPE HEAVY for submersible pump systems.</v>
       </c>
     </row>
     <row r="1221">
@@ -43117,10 +43117,10 @@
         <v>1220</v>
       </c>
       <c r="B1221" t="str">
-        <v>FG-401182</v>
+        <v>FG-401181</v>
       </c>
       <c r="C1221" t="str">
-        <v>COLOUMN PIPE HEAVY (42MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (48MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1221" t="str">
         <v>COLOUMN PIPE HEAVY</v>
@@ -43132,7 +43132,7 @@
         <v>General</v>
       </c>
       <c r="G1221" t="str">
-        <v>42MM 30KG COUPLER TYPE</v>
+        <v>48MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1221" t="str">
         <v>MTR</v>
@@ -43152,10 +43152,10 @@
         <v>1221</v>
       </c>
       <c r="B1222" t="str">
-        <v>FG-401181</v>
+        <v>FG-401183</v>
       </c>
       <c r="C1222" t="str">
-        <v>COLOUMN PIPE HEAVY (48MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (60MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1222" t="str">
         <v>COLOUMN PIPE HEAVY</v>
@@ -43167,7 +43167,7 @@
         <v>General</v>
       </c>
       <c r="G1222" t="str">
-        <v>48MM 30KG COUPLER TYPE</v>
+        <v>60MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1222" t="str">
         <v>MTR</v>
@@ -43187,13 +43187,13 @@
         <v>1222</v>
       </c>
       <c r="B1223" t="str">
-        <v>FG-401183</v>
+        <v>FG-401179</v>
       </c>
       <c r="C1223" t="str">
-        <v>COLOUMN PIPE HEAVY (60MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM PLUS (60MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1223" t="str">
-        <v>COLOUMN PIPE HEAVY</v>
+        <v>COLOUMN PIPE MEDIUM PLUS</v>
       </c>
       <c r="E1223" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43202,7 +43202,7 @@
         <v>General</v>
       </c>
       <c r="G1223" t="str">
-        <v>60MM 30KG COUPLER TYPE</v>
+        <v>60MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1223" t="str">
         <v>MTR</v>
@@ -43214,7 +43214,7 @@
         <v>Active</v>
       </c>
       <c r="K1223" t="str">
-        <v>COLOUMN PIPE HEAVY for submersible pump systems.</v>
+        <v>COLOUMN PIPE MEDIUM PLUS for submersible pump systems.</v>
       </c>
     </row>
     <row r="1224">
@@ -43222,34 +43222,34 @@
         <v>1223</v>
       </c>
       <c r="B1224" t="str">
-        <v>FG-401179</v>
+        <v>FG-401569</v>
       </c>
       <c r="C1224" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS (60MM 18KG COUPLER TYPE)</v>
+        <v>CONSTRUCTION GHAMELA SHIVA (15 Inch)</v>
       </c>
       <c r="D1224" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS</v>
+        <v>CONSTRUCTION GHAMELA SHIVA</v>
       </c>
       <c r="E1224" t="str">
-        <v>UPVC COLUMN PIPES</v>
+        <v>HOUSEHOLD PRODUCTS</v>
       </c>
       <c r="F1224" t="str">
         <v>General</v>
       </c>
       <c r="G1224" t="str">
-        <v>60MM 18KG COUPLER TYPE</v>
+        <v>15 Inch</v>
       </c>
       <c r="H1224" t="str">
-        <v>MTR</v>
+        <v>BAGS</v>
       </c>
       <c r="I1224" t="str">
-        <v>-</v>
+        <v>75</v>
       </c>
       <c r="J1224" t="str">
         <v>Active</v>
       </c>
       <c r="K1224" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS for submersible pump systems.</v>
+        <v>CONSTRUCTION GHAMELA SHIVA high durability ghamela.</v>
       </c>
     </row>
     <row r="1225">
@@ -43257,13 +43257,13 @@
         <v>1224</v>
       </c>
       <c r="B1225" t="str">
-        <v>FG-401569</v>
+        <v>FG-401570</v>
       </c>
       <c r="C1225" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA (15 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA GOURI (15 Inch)</v>
       </c>
       <c r="D1225" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA</v>
+        <v>MULTIPURPOSE GHAMELA GOURI</v>
       </c>
       <c r="E1225" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43284,7 +43284,7 @@
         <v>Active</v>
       </c>
       <c r="K1225" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA GOURI high durability ghamela.</v>
       </c>
     </row>
     <row r="1226">
@@ -43292,13 +43292,13 @@
         <v>1225</v>
       </c>
       <c r="B1226" t="str">
-        <v>FG-401570</v>
+        <v>FG-401571</v>
       </c>
       <c r="C1226" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI (15 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA (16 Inch)</v>
       </c>
       <c r="D1226" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA</v>
       </c>
       <c r="E1226" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43307,19 +43307,19 @@
         <v>General</v>
       </c>
       <c r="G1226" t="str">
-        <v>15 Inch</v>
+        <v>16 Inch</v>
       </c>
       <c r="H1226" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1226" t="str">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="J1226" t="str">
         <v>Active</v>
       </c>
       <c r="K1226" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA high durability ghamela.</v>
       </c>
     </row>
     <row r="1227">
@@ -43327,13 +43327,13 @@
         <v>1226</v>
       </c>
       <c r="B1227" t="str">
-        <v>FG-401571</v>
+        <v>FG-401573</v>
       </c>
       <c r="C1227" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA (16 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV (18 Inch)</v>
       </c>
       <c r="D1227" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV</v>
       </c>
       <c r="E1227" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43342,19 +43342,19 @@
         <v>General</v>
       </c>
       <c r="G1227" t="str">
-        <v>16 Inch</v>
+        <v>18 Inch</v>
       </c>
       <c r="H1227" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1227" t="str">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J1227" t="str">
         <v>Active</v>
       </c>
       <c r="K1227" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV high durability ghamela.</v>
       </c>
     </row>
     <row r="1228">
@@ -43362,13 +43362,13 @@
         <v>1227</v>
       </c>
       <c r="B1228" t="str">
-        <v>FG-401573</v>
+        <v>FG-401574</v>
       </c>
       <c r="C1228" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV (18 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET (20 Inch)</v>
       </c>
       <c r="D1228" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET</v>
       </c>
       <c r="E1228" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43377,19 +43377,19 @@
         <v>General</v>
       </c>
       <c r="G1228" t="str">
-        <v>18 Inch</v>
+        <v>20 Inch</v>
       </c>
       <c r="H1228" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1228" t="str">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J1228" t="str">
         <v>Active</v>
       </c>
       <c r="K1228" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET high durability ghamela.</v>
       </c>
     </row>
     <row r="1229">
@@ -43397,13 +43397,13 @@
         <v>1228</v>
       </c>
       <c r="B1229" t="str">
-        <v>FG-401574</v>
+        <v>FG-401572</v>
       </c>
       <c r="C1229" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET (20 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI (17 Inch)</v>
       </c>
       <c r="D1229" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI</v>
       </c>
       <c r="E1229" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43412,19 +43412,19 @@
         <v>General</v>
       </c>
       <c r="G1229" t="str">
-        <v>20 Inch</v>
+        <v>17 Inch</v>
       </c>
       <c r="H1229" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1229" t="str">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J1229" t="str">
         <v>Active</v>
       </c>
       <c r="K1229" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI high durability ghamela.</v>
       </c>
     </row>
     <row r="1230">
@@ -43432,13 +43432,13 @@
         <v>1229</v>
       </c>
       <c r="B1230" t="str">
-        <v>FG-401572</v>
+        <v>FG-401575</v>
       </c>
       <c r="C1230" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI (17 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ (22 Inch)</v>
       </c>
       <c r="D1230" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ</v>
       </c>
       <c r="E1230" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43447,19 +43447,19 @@
         <v>General</v>
       </c>
       <c r="G1230" t="str">
-        <v>17 Inch</v>
+        <v>22 Inch</v>
       </c>
       <c r="H1230" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1230" t="str">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J1230" t="str">
         <v>Active</v>
       </c>
       <c r="K1230" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ high durability ghamela.</v>
       </c>
     </row>
     <row r="1231">
@@ -43467,13 +43467,13 @@
         <v>1230</v>
       </c>
       <c r="B1231" t="str">
-        <v>FG-401575</v>
+        <v>FG-401578</v>
       </c>
       <c r="C1231" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ (22 Inch)</v>
+        <v>AQUA PLAST GHAMELA 16 (16 Inch)</v>
       </c>
       <c r="D1231" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ</v>
+        <v>AQUA PLAST GHAMELA 16</v>
       </c>
       <c r="E1231" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43482,19 +43482,19 @@
         <v>General</v>
       </c>
       <c r="G1231" t="str">
-        <v>22 Inch</v>
+        <v>16 Inch</v>
       </c>
       <c r="H1231" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1231" t="str">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J1231" t="str">
         <v>Active</v>
       </c>
       <c r="K1231" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ high durability ghamela.</v>
+        <v>AQUA PLAST GHAMELA 16 high durability ghamela.</v>
       </c>
     </row>
     <row r="1232">
@@ -43502,13 +43502,13 @@
         <v>1231</v>
       </c>
       <c r="B1232" t="str">
-        <v>FG-401578</v>
+        <v>FG-401579</v>
       </c>
       <c r="C1232" t="str">
-        <v>AQUA PLAST GHAMELA 16 (16 Inch)</v>
+        <v>AQUA PLAST GHAMELA 17 (17 Inch)</v>
       </c>
       <c r="D1232" t="str">
-        <v>AQUA PLAST GHAMELA 16</v>
+        <v>AQUA PLAST GHAMELA 17</v>
       </c>
       <c r="E1232" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43517,7 +43517,7 @@
         <v>General</v>
       </c>
       <c r="G1232" t="str">
-        <v>16 Inch</v>
+        <v>17 Inch</v>
       </c>
       <c r="H1232" t="str">
         <v>BAGS</v>
@@ -43529,7 +43529,7 @@
         <v>Active</v>
       </c>
       <c r="K1232" t="str">
-        <v>AQUA PLAST GHAMELA 16 high durability ghamela.</v>
+        <v>AQUA PLAST GHAMELA 17 high durability ghamela.</v>
       </c>
     </row>
     <row r="1233">
@@ -43537,34 +43537,34 @@
         <v>1232</v>
       </c>
       <c r="B1233" t="str">
-        <v>FG-401579</v>
+        <v>FG-401364</v>
       </c>
       <c r="C1233" t="str">
-        <v>AQUA PLAST GHAMELA 17 (17 Inch)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1/2 15MM)</v>
       </c>
       <c r="D1233" t="str">
-        <v>AQUA PLAST GHAMELA 17</v>
+        <v>GAP-ORA FLOW GARDEN PIPE</v>
       </c>
       <c r="E1233" t="str">
-        <v>HOUSEHOLD PRODUCTS</v>
+        <v>Garden, Braided &amp; LDPE Pipes</v>
       </c>
       <c r="F1233" t="str">
         <v>General</v>
       </c>
       <c r="G1233" t="str">
-        <v>17 Inch</v>
+        <v>1/2 15MM</v>
       </c>
       <c r="H1233" t="str">
-        <v>BAGS</v>
+        <v>BDL</v>
       </c>
       <c r="I1233" t="str">
-        <v>60</v>
+        <v>-</v>
       </c>
       <c r="J1233" t="str">
         <v>Active</v>
       </c>
       <c r="K1233" t="str">
-        <v>AQUA PLAST GHAMELA 17 high durability ghamela.</v>
+        <v>GAP-ORA FLOW GARDEN PIPE. Available sizes: 1/2 15MM, 3/4 20MM, 1 25MM, 1 1/4 32MM.</v>
       </c>
     </row>
     <row r="1234">
@@ -43572,10 +43572,10 @@
         <v>1233</v>
       </c>
       <c r="B1234" t="str">
-        <v>FG-401364</v>
+        <v>FG-401365</v>
       </c>
       <c r="C1234" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1/2 15MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (3/4 20MM)</v>
       </c>
       <c r="D1234" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43587,7 +43587,7 @@
         <v>General</v>
       </c>
       <c r="G1234" t="str">
-        <v>1/2 15MM</v>
+        <v>3/4 20MM</v>
       </c>
       <c r="H1234" t="str">
         <v>BDL</v>
@@ -43607,10 +43607,10 @@
         <v>1234</v>
       </c>
       <c r="B1235" t="str">
-        <v>FG-401365</v>
+        <v>FG-401366</v>
       </c>
       <c r="C1235" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (3/4 20MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1 25MM)</v>
       </c>
       <c r="D1235" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43622,7 +43622,7 @@
         <v>General</v>
       </c>
       <c r="G1235" t="str">
-        <v>3/4 20MM</v>
+        <v>1 25MM</v>
       </c>
       <c r="H1235" t="str">
         <v>BDL</v>
@@ -43642,10 +43642,10 @@
         <v>1235</v>
       </c>
       <c r="B1236" t="str">
-        <v>FG-401366</v>
+        <v>FG-401367</v>
       </c>
       <c r="C1236" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1 25MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1 1/4 32MM)</v>
       </c>
       <c r="D1236" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43657,7 +43657,7 @@
         <v>General</v>
       </c>
       <c r="G1236" t="str">
-        <v>1 25MM</v>
+        <v>1 1/4 32MM</v>
       </c>
       <c r="H1236" t="str">
         <v>BDL</v>
@@ -43677,13 +43677,13 @@
         <v>1236</v>
       </c>
       <c r="B1237" t="str">
-        <v>FG-401367</v>
+        <v>FG-401370</v>
       </c>
       <c r="C1237" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1 1/4 32MM)</v>
+        <v>GAP-ORA BRAIDED PIPE (15MM 1/2)</v>
       </c>
       <c r="D1237" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE</v>
+        <v>GAP-ORA BRAIDED PIPE</v>
       </c>
       <c r="E1237" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43692,7 +43692,7 @@
         <v>General</v>
       </c>
       <c r="G1237" t="str">
-        <v>1 1/4 32MM</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1237" t="str">
         <v>BDL</v>
@@ -43704,7 +43704,7 @@
         <v>Active</v>
       </c>
       <c r="K1237" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE. Available sizes: 1/2 15MM, 3/4 20MM, 1 25MM, 1 1/4 32MM.</v>
+        <v>GAP-ORA BRAIDED PIPE.</v>
       </c>
     </row>
     <row r="1238">
@@ -43712,10 +43712,10 @@
         <v>1237</v>
       </c>
       <c r="B1238" t="str">
-        <v>FG-401370</v>
+        <v>FG-401371</v>
       </c>
       <c r="C1238" t="str">
-        <v>GAP-ORA BRAIDED PIPE (15MM 1/2)</v>
+        <v>GAP-ORA BRAIDED PIPE (20MM 3/4)</v>
       </c>
       <c r="D1238" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43727,7 +43727,7 @@
         <v>General</v>
       </c>
       <c r="G1238" t="str">
-        <v>15MM 1/2</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1238" t="str">
         <v>BDL</v>
@@ -43747,10 +43747,10 @@
         <v>1238</v>
       </c>
       <c r="B1239" t="str">
-        <v>FG-401371</v>
+        <v>FG-401372</v>
       </c>
       <c r="C1239" t="str">
-        <v>GAP-ORA BRAIDED PIPE (20MM 3/4)</v>
+        <v>GAP-ORA BRAIDED PIPE (25MM 1)</v>
       </c>
       <c r="D1239" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43762,7 +43762,7 @@
         <v>General</v>
       </c>
       <c r="G1239" t="str">
-        <v>20MM 3/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1239" t="str">
         <v>BDL</v>
@@ -43782,10 +43782,10 @@
         <v>1239</v>
       </c>
       <c r="B1240" t="str">
-        <v>FG-401372</v>
+        <v>FG-401373</v>
       </c>
       <c r="C1240" t="str">
-        <v>GAP-ORA BRAIDED PIPE (25MM 1)</v>
+        <v>GAP-ORA BRAIDED PIPE (32MM 1 1/4)</v>
       </c>
       <c r="D1240" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43797,7 +43797,7 @@
         <v>General</v>
       </c>
       <c r="G1240" t="str">
-        <v>25MM 1</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1240" t="str">
         <v>BDL</v>
@@ -43817,13 +43817,13 @@
         <v>1240</v>
       </c>
       <c r="B1241" t="str">
-        <v>FG-401373</v>
+        <v>FG-401355</v>
       </c>
       <c r="C1241" t="str">
-        <v>GAP-ORA BRAIDED PIPE (32MM 1 1/4)</v>
+        <v>GARDEN FOAM PIPES (15MM 1/2)</v>
       </c>
       <c r="D1241" t="str">
-        <v>GAP-ORA BRAIDED PIPE</v>
+        <v>GARDEN FOAM PIPES</v>
       </c>
       <c r="E1241" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43832,7 +43832,7 @@
         <v>General</v>
       </c>
       <c r="G1241" t="str">
-        <v>32MM 1 1/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1241" t="str">
         <v>BDL</v>
@@ -43844,7 +43844,7 @@
         <v>Active</v>
       </c>
       <c r="K1241" t="str">
-        <v>GAP-ORA BRAIDED PIPE.</v>
+        <v>GARDEN FOAM PIPES.</v>
       </c>
     </row>
     <row r="1242">
@@ -43852,10 +43852,10 @@
         <v>1241</v>
       </c>
       <c r="B1242" t="str">
-        <v>FG-401355</v>
+        <v>FG-401356</v>
       </c>
       <c r="C1242" t="str">
-        <v>GARDEN FOAM PIPES (15MM 1/2)</v>
+        <v>GARDEN FOAM PIPES (20MM 3/4)</v>
       </c>
       <c r="D1242" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43867,7 +43867,7 @@
         <v>General</v>
       </c>
       <c r="G1242" t="str">
-        <v>15MM 1/2</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1242" t="str">
         <v>BDL</v>
@@ -43887,10 +43887,10 @@
         <v>1242</v>
       </c>
       <c r="B1243" t="str">
-        <v>FG-401356</v>
+        <v>FG-401369</v>
       </c>
       <c r="C1243" t="str">
-        <v>GARDEN FOAM PIPES (20MM 3/4)</v>
+        <v>GARDEN FOAM PIPES (20MM 3/4 20MTR)</v>
       </c>
       <c r="D1243" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43902,7 +43902,7 @@
         <v>General</v>
       </c>
       <c r="G1243" t="str">
-        <v>20MM 3/4</v>
+        <v>20MM 3/4 20MTR</v>
       </c>
       <c r="H1243" t="str">
         <v>BDL</v>
@@ -43922,10 +43922,10 @@
         <v>1243</v>
       </c>
       <c r="B1244" t="str">
-        <v>FG-401369</v>
+        <v>FG-401357</v>
       </c>
       <c r="C1244" t="str">
-        <v>GARDEN FOAM PIPES (20MM 3/4 20MTR)</v>
+        <v>GARDEN FOAM PIPES (25MM 1)</v>
       </c>
       <c r="D1244" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43937,7 +43937,7 @@
         <v>General</v>
       </c>
       <c r="G1244" t="str">
-        <v>20MM 3/4 20MTR</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1244" t="str">
         <v>BDL</v>
@@ -43957,10 +43957,10 @@
         <v>1244</v>
       </c>
       <c r="B1245" t="str">
-        <v>FG-401357</v>
+        <v>FG-401358</v>
       </c>
       <c r="C1245" t="str">
-        <v>GARDEN FOAM PIPES (25MM 1)</v>
+        <v>GARDEN FOAM PIPES (32MM 1 1/4)</v>
       </c>
       <c r="D1245" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43972,7 +43972,7 @@
         <v>General</v>
       </c>
       <c r="G1245" t="str">
-        <v>25MM 1</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1245" t="str">
         <v>BDL</v>
@@ -43992,13 +43992,13 @@
         <v>1245</v>
       </c>
       <c r="B1246" t="str">
-        <v>FG-401358</v>
+        <v>FG-401344</v>
       </c>
       <c r="C1246" t="str">
-        <v>GARDEN FOAM PIPES (32MM 1 1/4)</v>
+        <v>BRAIDED PIPE (15MM 1/2)</v>
       </c>
       <c r="D1246" t="str">
-        <v>GARDEN FOAM PIPES</v>
+        <v>BRAIDED PIPE</v>
       </c>
       <c r="E1246" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44007,7 +44007,7 @@
         <v>General</v>
       </c>
       <c r="G1246" t="str">
-        <v>32MM 1 1/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1246" t="str">
         <v>BDL</v>
@@ -44019,7 +44019,7 @@
         <v>Active</v>
       </c>
       <c r="K1246" t="str">
-        <v>GARDEN FOAM PIPES.</v>
+        <v>Reinforced Braided Garden Pipe.</v>
       </c>
     </row>
     <row r="1247">
@@ -44027,10 +44027,10 @@
         <v>1246</v>
       </c>
       <c r="B1247" t="str">
-        <v>FG-401344</v>
+        <v>FG-401345</v>
       </c>
       <c r="C1247" t="str">
-        <v>BRAIDED PIPE (15MM 1/2)</v>
+        <v>BRAIDED PIPE (20MM 3/4)</v>
       </c>
       <c r="D1247" t="str">
         <v>BRAIDED PIPE</v>
@@ -44042,7 +44042,7 @@
         <v>General</v>
       </c>
       <c r="G1247" t="str">
-        <v>15MM 1/2</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1247" t="str">
         <v>BDL</v>
@@ -44062,10 +44062,10 @@
         <v>1247</v>
       </c>
       <c r="B1248" t="str">
-        <v>FG-401345</v>
+        <v>FG-401346</v>
       </c>
       <c r="C1248" t="str">
-        <v>BRAIDED PIPE (20MM 3/4)</v>
+        <v>BRAIDED PIPE (25MM 1)</v>
       </c>
       <c r="D1248" t="str">
         <v>BRAIDED PIPE</v>
@@ -44077,7 +44077,7 @@
         <v>General</v>
       </c>
       <c r="G1248" t="str">
-        <v>20MM 3/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1248" t="str">
         <v>BDL</v>
@@ -44097,10 +44097,10 @@
         <v>1248</v>
       </c>
       <c r="B1249" t="str">
-        <v>FG-401346</v>
+        <v>FG-401363</v>
       </c>
       <c r="C1249" t="str">
-        <v>BRAIDED PIPE (25MM 1)</v>
+        <v>BRAIDED PIPE (32MM 1 1/4)</v>
       </c>
       <c r="D1249" t="str">
         <v>BRAIDED PIPE</v>
@@ -44112,7 +44112,7 @@
         <v>General</v>
       </c>
       <c r="G1249" t="str">
-        <v>25MM 1</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1249" t="str">
         <v>BDL</v>
@@ -44132,13 +44132,13 @@
         <v>1249</v>
       </c>
       <c r="B1250" t="str">
-        <v>FG-401363</v>
+        <v>FG-401374</v>
       </c>
       <c r="C1250" t="str">
-        <v>BRAIDED PIPE (32MM 1 1/4)</v>
+        <v>LEVEL PIPE (6MM)</v>
       </c>
       <c r="D1250" t="str">
-        <v>BRAIDED PIPE</v>
+        <v>LEVEL PIPE</v>
       </c>
       <c r="E1250" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44147,7 +44147,7 @@
         <v>General</v>
       </c>
       <c r="G1250" t="str">
-        <v>32MM 1 1/4</v>
+        <v>6MM</v>
       </c>
       <c r="H1250" t="str">
         <v>BDL</v>
@@ -44159,7 +44159,7 @@
         <v>Active</v>
       </c>
       <c r="K1250" t="str">
-        <v>Reinforced Braided Garden Pipe.</v>
+        <v>Transparent Level Pipe for construction &amp; garden work.</v>
       </c>
     </row>
     <row r="1251">
@@ -44167,13 +44167,13 @@
         <v>1250</v>
       </c>
       <c r="B1251" t="str">
-        <v>FG-401374</v>
+        <v>FG-401340</v>
       </c>
       <c r="C1251" t="str">
-        <v>LEVEL PIPE (6MM)</v>
+        <v>GARDEN PIPES SUPER FLOW (15MM 1/2)</v>
       </c>
       <c r="D1251" t="str">
-        <v>LEVEL PIPE</v>
+        <v>GARDEN PIPES SUPER FLOW</v>
       </c>
       <c r="E1251" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44182,7 +44182,7 @@
         <v>General</v>
       </c>
       <c r="G1251" t="str">
-        <v>6MM</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1251" t="str">
         <v>BDL</v>
@@ -44194,7 +44194,7 @@
         <v>Active</v>
       </c>
       <c r="K1251" t="str">
-        <v>Transparent Level Pipe for construction &amp; garden work.</v>
+        <v>GARDEN PIPES SUPER FLOW.</v>
       </c>
     </row>
     <row r="1252">
@@ -44202,10 +44202,10 @@
         <v>1251</v>
       </c>
       <c r="B1252" t="str">
-        <v>FG-401340</v>
+        <v>FG-401341</v>
       </c>
       <c r="C1252" t="str">
-        <v>GARDEN PIPES SUPER FLOW (15MM 1/2)</v>
+        <v>GARDEN PIPES SUPER FLOW (20MM 3/4)</v>
       </c>
       <c r="D1252" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44217,7 +44217,7 @@
         <v>General</v>
       </c>
       <c r="G1252" t="str">
-        <v>15MM 1/2</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1252" t="str">
         <v>BDL</v>
@@ -44237,10 +44237,10 @@
         <v>1252</v>
       </c>
       <c r="B1253" t="str">
-        <v>FG-401341</v>
+        <v>FG-401652</v>
       </c>
       <c r="C1253" t="str">
-        <v>GARDEN PIPES SUPER FLOW (20MM 3/4)</v>
+        <v>GARDEN PIPES SUPER FLOW (20MM 3/4 15MTR)</v>
       </c>
       <c r="D1253" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44252,7 +44252,7 @@
         <v>General</v>
       </c>
       <c r="G1253" t="str">
-        <v>20MM 3/4</v>
+        <v>20MM 3/4 15MTR</v>
       </c>
       <c r="H1253" t="str">
         <v>BDL</v>
@@ -44272,10 +44272,10 @@
         <v>1253</v>
       </c>
       <c r="B1254" t="str">
-        <v>FG-401652</v>
+        <v>FG-401342</v>
       </c>
       <c r="C1254" t="str">
-        <v>GARDEN PIPES SUPER FLOW (20MM 3/4 15MTR)</v>
+        <v>GARDEN PIPES SUPER FLOW (25MM 1)</v>
       </c>
       <c r="D1254" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44287,7 +44287,7 @@
         <v>General</v>
       </c>
       <c r="G1254" t="str">
-        <v>20MM 3/4 15MTR</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1254" t="str">
         <v>BDL</v>
@@ -44307,10 +44307,10 @@
         <v>1254</v>
       </c>
       <c r="B1255" t="str">
-        <v>FG-401342</v>
+        <v>FG-401343</v>
       </c>
       <c r="C1255" t="str">
-        <v>GARDEN PIPES SUPER FLOW (25MM 1)</v>
+        <v>GARDEN PIPES SUPER FLOW (32MM 1 1/4)</v>
       </c>
       <c r="D1255" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44322,7 +44322,7 @@
         <v>General</v>
       </c>
       <c r="G1255" t="str">
-        <v>25MM 1</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1255" t="str">
         <v>BDL</v>
@@ -44342,10 +44342,10 @@
         <v>1255</v>
       </c>
       <c r="B1256" t="str">
-        <v>FG-401343</v>
+        <v>FG-401627</v>
       </c>
       <c r="C1256" t="str">
-        <v>GARDEN PIPES SUPER FLOW (32MM 1 1/4)</v>
+        <v>GARDEN PIPES SUPER FLOW (40MM 1 1/2)</v>
       </c>
       <c r="D1256" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44357,7 +44357,7 @@
         <v>General</v>
       </c>
       <c r="G1256" t="str">
-        <v>32MM 1 1/4</v>
+        <v>40MM 1 1/2</v>
       </c>
       <c r="H1256" t="str">
         <v>BDL</v>
@@ -44377,34 +44377,34 @@
         <v>1256</v>
       </c>
       <c r="B1257" t="str">
-        <v>FG-401627</v>
+        <v>FG-401552</v>
       </c>
       <c r="C1257" t="str">
-        <v>GARDEN PIPES SUPER FLOW (40MM 1 1/2)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2 inch)</v>
       </c>
       <c r="D1257" t="str">
-        <v>GARDEN PIPES SUPER FLOW</v>
+        <v>EDGE SERIES SHORT BODY TAP</v>
       </c>
       <c r="E1257" t="str">
-        <v>Garden, Braided &amp; LDPE Pipes</v>
+        <v>FAUCETS</v>
       </c>
       <c r="F1257" t="str">
         <v>General</v>
       </c>
       <c r="G1257" t="str">
-        <v>40MM 1 1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1257" t="str">
-        <v>BDL</v>
-      </c>
-      <c r="I1257" t="str">
-        <v>-</v>
+        <v>NOS</v>
+      </c>
+      <c r="I1257">
+        <v>20</v>
       </c>
       <c r="J1257" t="str">
         <v>Active</v>
       </c>
       <c r="K1257" t="str">
-        <v>GARDEN PIPES SUPER FLOW.</v>
+        <v>EDGE SERIES SHORT BODY TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1258">
@@ -44415,7 +44415,7 @@
         <v>FG-401552</v>
       </c>
       <c r="C1258" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2 inch)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2)</v>
       </c>
       <c r="D1258" t="str">
         <v>EDGE SERIES SHORT BODY TAP</v>
@@ -44427,7 +44427,7 @@
         <v>General</v>
       </c>
       <c r="G1258" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1258" t="str">
         <v>NOS</v>
@@ -44450,7 +44450,7 @@
         <v>FG-401552</v>
       </c>
       <c r="C1259" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2")</v>
       </c>
       <c r="D1259" t="str">
         <v>EDGE SERIES SHORT BODY TAP</v>
@@ -44462,7 +44462,7 @@
         <v>General</v>
       </c>
       <c r="G1259" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1259" t="str">
         <v>NOS</v>
@@ -44482,13 +44482,13 @@
         <v>1259</v>
       </c>
       <c r="B1260" t="str">
-        <v>FG-401552</v>
+        <v>FG-401551</v>
       </c>
       <c r="C1260" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2")</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2 inch)</v>
       </c>
       <c r="D1260" t="str">
-        <v>EDGE SERIES SHORT BODY TAP</v>
+        <v>EDGE SERIES LONG BODY TAP</v>
       </c>
       <c r="E1260" t="str">
         <v>FAUCETS</v>
@@ -44497,19 +44497,19 @@
         <v>General</v>
       </c>
       <c r="G1260" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1260" t="str">
         <v>NOS</v>
       </c>
       <c r="I1260">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J1260" t="str">
         <v>Active</v>
       </c>
       <c r="K1260" t="str">
-        <v>EDGE SERIES SHORT BODY TAP high quality faucet.</v>
+        <v>EDGE SERIES LONG BODY TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1261">
@@ -44520,7 +44520,7 @@
         <v>FG-401551</v>
       </c>
       <c r="C1261" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2 inch)</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2)</v>
       </c>
       <c r="D1261" t="str">
         <v>EDGE SERIES LONG BODY TAP</v>
@@ -44532,7 +44532,7 @@
         <v>General</v>
       </c>
       <c r="G1261" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1261" t="str">
         <v>NOS</v>
@@ -44555,7 +44555,7 @@
         <v>FG-401551</v>
       </c>
       <c r="C1262" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2)</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2")</v>
       </c>
       <c r="D1262" t="str">
         <v>EDGE SERIES LONG BODY TAP</v>
@@ -44567,7 +44567,7 @@
         <v>General</v>
       </c>
       <c r="G1262" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1262" t="str">
         <v>NOS</v>
@@ -44587,13 +44587,13 @@
         <v>1262</v>
       </c>
       <c r="B1263" t="str">
-        <v>FG-401551</v>
+        <v>FG-401549</v>
       </c>
       <c r="C1263" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2")</v>
+        <v>EDGE SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1263" t="str">
-        <v>EDGE SERIES LONG BODY TAP</v>
+        <v>EDGE SERIES SWAN NECK</v>
       </c>
       <c r="E1263" t="str">
         <v>FAUCETS</v>
@@ -44602,19 +44602,19 @@
         <v>General</v>
       </c>
       <c r="G1263" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1263" t="str">
         <v>NOS</v>
       </c>
       <c r="I1263">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J1263" t="str">
         <v>Active</v>
       </c>
       <c r="K1263" t="str">
-        <v>EDGE SERIES LONG BODY TAP high quality faucet.</v>
+        <v>EDGE SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1264">
@@ -44625,7 +44625,7 @@
         <v>FG-401549</v>
       </c>
       <c r="C1264" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2 inch)</v>
+        <v>EDGE SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1264" t="str">
         <v>EDGE SERIES SWAN NECK</v>
@@ -44637,7 +44637,7 @@
         <v>General</v>
       </c>
       <c r="G1264" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1264" t="str">
         <v>NOS</v>
@@ -44660,7 +44660,7 @@
         <v>FG-401549</v>
       </c>
       <c r="C1265" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2)</v>
+        <v>EDGE SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1265" t="str">
         <v>EDGE SERIES SWAN NECK</v>
@@ -44672,7 +44672,7 @@
         <v>General</v>
       </c>
       <c r="G1265" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1265" t="str">
         <v>NOS</v>
@@ -44692,13 +44692,13 @@
         <v>1265</v>
       </c>
       <c r="B1266" t="str">
-        <v>FG-401549</v>
+        <v>FG-401546</v>
       </c>
       <c r="C1266" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2")</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1266" t="str">
-        <v>EDGE SERIES SWAN NECK</v>
+        <v>EDGE SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1266" t="str">
         <v>FAUCETS</v>
@@ -44707,19 +44707,19 @@
         <v>General</v>
       </c>
       <c r="G1266" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1266" t="str">
         <v>NOS</v>
       </c>
       <c r="I1266">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="J1266" t="str">
         <v>Active</v>
       </c>
       <c r="K1266" t="str">
-        <v>EDGE SERIES SWAN NECK high quality faucet.</v>
+        <v>EDGE SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1267">
@@ -44730,7 +44730,7 @@
         <v>FG-401546</v>
       </c>
       <c r="C1267" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1267" t="str">
         <v>EDGE SERIES ANGULAR VALVE</v>
@@ -44742,7 +44742,7 @@
         <v>General</v>
       </c>
       <c r="G1267" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1267" t="str">
         <v>NOS</v>
@@ -44765,7 +44765,7 @@
         <v>FG-401546</v>
       </c>
       <c r="C1268" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2)</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1268" t="str">
         <v>EDGE SERIES ANGULAR VALVE</v>
@@ -44777,7 +44777,7 @@
         <v>General</v>
       </c>
       <c r="G1268" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1268" t="str">
         <v>NOS</v>
@@ -44797,13 +44797,13 @@
         <v>1268</v>
       </c>
       <c r="B1269" t="str">
-        <v>FG-401546</v>
+        <v>FG-401547</v>
       </c>
       <c r="C1269" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2")</v>
+        <v>EDGE SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1269" t="str">
-        <v>EDGE SERIES ANGULAR VALVE</v>
+        <v>EDGE SERIES PILLAR TAP</v>
       </c>
       <c r="E1269" t="str">
         <v>FAUCETS</v>
@@ -44812,19 +44812,19 @@
         <v>General</v>
       </c>
       <c r="G1269" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1269" t="str">
         <v>NOS</v>
       </c>
       <c r="I1269">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J1269" t="str">
         <v>Active</v>
       </c>
       <c r="K1269" t="str">
-        <v>EDGE SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>EDGE SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1270">
@@ -44835,7 +44835,7 @@
         <v>FG-401547</v>
       </c>
       <c r="C1270" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2 inch)</v>
+        <v>EDGE SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1270" t="str">
         <v>EDGE SERIES PILLAR TAP</v>
@@ -44847,7 +44847,7 @@
         <v>General</v>
       </c>
       <c r="G1270" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1270" t="str">
         <v>NOS</v>
@@ -44870,7 +44870,7 @@
         <v>FG-401547</v>
       </c>
       <c r="C1271" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2)</v>
+        <v>EDGE SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1271" t="str">
         <v>EDGE SERIES PILLAR TAP</v>
@@ -44882,7 +44882,7 @@
         <v>General</v>
       </c>
       <c r="G1271" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1271" t="str">
         <v>NOS</v>
@@ -44902,13 +44902,13 @@
         <v>1271</v>
       </c>
       <c r="B1272" t="str">
-        <v>FG-401547</v>
+        <v>FG-401550</v>
       </c>
       <c r="C1272" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2")</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2 inch)</v>
       </c>
       <c r="D1272" t="str">
-        <v>EDGE SERIES PILLAR TAP</v>
+        <v>EDGE SERIES 2 WAY BIB TAB</v>
       </c>
       <c r="E1272" t="str">
         <v>FAUCETS</v>
@@ -44917,19 +44917,19 @@
         <v>General</v>
       </c>
       <c r="G1272" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1272" t="str">
         <v>NOS</v>
       </c>
       <c r="I1272">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J1272" t="str">
         <v>Active</v>
       </c>
       <c r="K1272" t="str">
-        <v>EDGE SERIES PILLAR TAP high quality faucet.</v>
+        <v>EDGE SERIES 2 WAY BIB TAB high quality faucet.</v>
       </c>
     </row>
     <row r="1273">
@@ -44940,7 +44940,7 @@
         <v>FG-401550</v>
       </c>
       <c r="C1273" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2 inch)</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2)</v>
       </c>
       <c r="D1273" t="str">
         <v>EDGE SERIES 2 WAY BIB TAB</v>
@@ -44952,7 +44952,7 @@
         <v>General</v>
       </c>
       <c r="G1273" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1273" t="str">
         <v>NOS</v>
@@ -44975,7 +44975,7 @@
         <v>FG-401550</v>
       </c>
       <c r="C1274" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2)</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2")</v>
       </c>
       <c r="D1274" t="str">
         <v>EDGE SERIES 2 WAY BIB TAB</v>
@@ -44987,7 +44987,7 @@
         <v>General</v>
       </c>
       <c r="G1274" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1274" t="str">
         <v>NOS</v>
@@ -45007,13 +45007,13 @@
         <v>1274</v>
       </c>
       <c r="B1275" t="str">
-        <v>FG-401550</v>
+        <v>FG-401548</v>
       </c>
       <c r="C1275" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2")</v>
+        <v>EDGE SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1275" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB</v>
+        <v>EDGE SERIES SINK TAP</v>
       </c>
       <c r="E1275" t="str">
         <v>FAUCETS</v>
@@ -45022,19 +45022,19 @@
         <v>General</v>
       </c>
       <c r="G1275" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1275" t="str">
         <v>NOS</v>
       </c>
       <c r="I1275">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1275" t="str">
         <v>Active</v>
       </c>
       <c r="K1275" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB high quality faucet.</v>
+        <v>EDGE SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1276">
@@ -45045,7 +45045,7 @@
         <v>FG-401548</v>
       </c>
       <c r="C1276" t="str">
-        <v>EDGE SERIES SINK TAP (1/2 inch)</v>
+        <v>EDGE SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1276" t="str">
         <v>EDGE SERIES SINK TAP</v>
@@ -45057,7 +45057,7 @@
         <v>General</v>
       </c>
       <c r="G1276" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1276" t="str">
         <v>NOS</v>
@@ -45080,7 +45080,7 @@
         <v>FG-401548</v>
       </c>
       <c r="C1277" t="str">
-        <v>EDGE SERIES SINK TAP (1/2)</v>
+        <v>EDGE SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1277" t="str">
         <v>EDGE SERIES SINK TAP</v>
@@ -45092,7 +45092,7 @@
         <v>General</v>
       </c>
       <c r="G1277" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1277" t="str">
         <v>NOS</v>
@@ -45112,13 +45112,13 @@
         <v>1277</v>
       </c>
       <c r="B1278" t="str">
-        <v>FG-401548</v>
+        <v>FG-401568</v>
       </c>
       <c r="C1278" t="str">
-        <v>EDGE SERIES SINK TAP (1/2")</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1278" t="str">
-        <v>EDGE SERIES SINK TAP</v>
+        <v>SMART SERIES SHORT BODY BIB TAP</v>
       </c>
       <c r="E1278" t="str">
         <v>FAUCETS</v>
@@ -45127,19 +45127,19 @@
         <v>General</v>
       </c>
       <c r="G1278" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1278" t="str">
         <v>NOS</v>
       </c>
       <c r="I1278">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="J1278" t="str">
         <v>Active</v>
       </c>
       <c r="K1278" t="str">
-        <v>EDGE SERIES SINK TAP high quality faucet.</v>
+        <v>SMART SERIES SHORT BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1279">
@@ -45150,7 +45150,7 @@
         <v>FG-401568</v>
       </c>
       <c r="C1279" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1279" t="str">
         <v>SMART SERIES SHORT BODY BIB TAP</v>
@@ -45162,7 +45162,7 @@
         <v>General</v>
       </c>
       <c r="G1279" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1279" t="str">
         <v>NOS</v>
@@ -45185,7 +45185,7 @@
         <v>FG-401568</v>
       </c>
       <c r="C1280" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2)</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1280" t="str">
         <v>SMART SERIES SHORT BODY BIB TAP</v>
@@ -45197,7 +45197,7 @@
         <v>General</v>
       </c>
       <c r="G1280" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1280" t="str">
         <v>NOS</v>
@@ -45217,13 +45217,13 @@
         <v>1280</v>
       </c>
       <c r="B1281" t="str">
-        <v>FG-401568</v>
+        <v>FG-401567</v>
       </c>
       <c r="C1281" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2")</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1281" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP</v>
+        <v>SMART SERIES LONG BODY BIB TAP</v>
       </c>
       <c r="E1281" t="str">
         <v>FAUCETS</v>
@@ -45232,7 +45232,7 @@
         <v>General</v>
       </c>
       <c r="G1281" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1281" t="str">
         <v>NOS</v>
@@ -45244,7 +45244,7 @@
         <v>Active</v>
       </c>
       <c r="K1281" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP high quality faucet.</v>
+        <v>SMART SERIES LONG BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1282">
@@ -45255,7 +45255,7 @@
         <v>FG-401567</v>
       </c>
       <c r="C1282" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1282" t="str">
         <v>SMART SERIES LONG BODY BIB TAP</v>
@@ -45267,7 +45267,7 @@
         <v>General</v>
       </c>
       <c r="G1282" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1282" t="str">
         <v>NOS</v>
@@ -45290,7 +45290,7 @@
         <v>FG-401567</v>
       </c>
       <c r="C1283" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2)</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1283" t="str">
         <v>SMART SERIES LONG BODY BIB TAP</v>
@@ -45302,7 +45302,7 @@
         <v>General</v>
       </c>
       <c r="G1283" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1283" t="str">
         <v>NOS</v>
@@ -45322,13 +45322,13 @@
         <v>1283</v>
       </c>
       <c r="B1284" t="str">
-        <v>FG-401567</v>
+        <v>FG-401562</v>
       </c>
       <c r="C1284" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2")</v>
+        <v>SMART SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1284" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP</v>
+        <v>SMART SERIES PILLAR TAP</v>
       </c>
       <c r="E1284" t="str">
         <v>FAUCETS</v>
@@ -45337,19 +45337,19 @@
         <v>General</v>
       </c>
       <c r="G1284" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1284" t="str">
         <v>NOS</v>
       </c>
       <c r="I1284">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1284" t="str">
         <v>Active</v>
       </c>
       <c r="K1284" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP high quality faucet.</v>
+        <v>SMART SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1285">
@@ -45360,7 +45360,7 @@
         <v>FG-401562</v>
       </c>
       <c r="C1285" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2 inch)</v>
+        <v>SMART SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1285" t="str">
         <v>SMART SERIES PILLAR TAP</v>
@@ -45372,7 +45372,7 @@
         <v>General</v>
       </c>
       <c r="G1285" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1285" t="str">
         <v>NOS</v>
@@ -45395,7 +45395,7 @@
         <v>FG-401562</v>
       </c>
       <c r="C1286" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2)</v>
+        <v>SMART SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1286" t="str">
         <v>SMART SERIES PILLAR TAP</v>
@@ -45407,7 +45407,7 @@
         <v>General</v>
       </c>
       <c r="G1286" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1286" t="str">
         <v>NOS</v>
@@ -45427,13 +45427,13 @@
         <v>1286</v>
       </c>
       <c r="B1287" t="str">
-        <v>FG-401562</v>
+        <v>FG-401563</v>
       </c>
       <c r="C1287" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2")</v>
+        <v>SMART SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1287" t="str">
-        <v>SMART SERIES PILLAR TAP</v>
+        <v>SMART SERIES SINK TAP</v>
       </c>
       <c r="E1287" t="str">
         <v>FAUCETS</v>
@@ -45442,7 +45442,7 @@
         <v>General</v>
       </c>
       <c r="G1287" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1287" t="str">
         <v>NOS</v>
@@ -45454,7 +45454,7 @@
         <v>Active</v>
       </c>
       <c r="K1287" t="str">
-        <v>SMART SERIES PILLAR TAP high quality faucet.</v>
+        <v>SMART SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1288">
@@ -45465,7 +45465,7 @@
         <v>FG-401563</v>
       </c>
       <c r="C1288" t="str">
-        <v>SMART SERIES SINK TAP (1/2 inch)</v>
+        <v>SMART SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1288" t="str">
         <v>SMART SERIES SINK TAP</v>
@@ -45477,7 +45477,7 @@
         <v>General</v>
       </c>
       <c r="G1288" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1288" t="str">
         <v>NOS</v>
@@ -45500,7 +45500,7 @@
         <v>FG-401563</v>
       </c>
       <c r="C1289" t="str">
-        <v>SMART SERIES SINK TAP (1/2)</v>
+        <v>SMART SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1289" t="str">
         <v>SMART SERIES SINK TAP</v>
@@ -45512,7 +45512,7 @@
         <v>General</v>
       </c>
       <c r="G1289" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1289" t="str">
         <v>NOS</v>
@@ -45532,13 +45532,13 @@
         <v>1289</v>
       </c>
       <c r="B1290" t="str">
-        <v>FG-401563</v>
+        <v>FG-401564</v>
       </c>
       <c r="C1290" t="str">
-        <v>SMART SERIES SINK TAP (1/2")</v>
+        <v>SMART SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1290" t="str">
-        <v>SMART SERIES SINK TAP</v>
+        <v>SMART SERIES SWAN NECK</v>
       </c>
       <c r="E1290" t="str">
         <v>FAUCETS</v>
@@ -45547,7 +45547,7 @@
         <v>General</v>
       </c>
       <c r="G1290" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1290" t="str">
         <v>NOS</v>
@@ -45559,7 +45559,7 @@
         <v>Active</v>
       </c>
       <c r="K1290" t="str">
-        <v>SMART SERIES SINK TAP high quality faucet.</v>
+        <v>SMART SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1291">
@@ -45570,7 +45570,7 @@
         <v>FG-401564</v>
       </c>
       <c r="C1291" t="str">
-        <v>SMART SERIES SWAN NECK (1/2 inch)</v>
+        <v>SMART SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1291" t="str">
         <v>SMART SERIES SWAN NECK</v>
@@ -45582,7 +45582,7 @@
         <v>General</v>
       </c>
       <c r="G1291" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1291" t="str">
         <v>NOS</v>
@@ -45605,7 +45605,7 @@
         <v>FG-401564</v>
       </c>
       <c r="C1292" t="str">
-        <v>SMART SERIES SWAN NECK (1/2)</v>
+        <v>SMART SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1292" t="str">
         <v>SMART SERIES SWAN NECK</v>
@@ -45617,7 +45617,7 @@
         <v>General</v>
       </c>
       <c r="G1292" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1292" t="str">
         <v>NOS</v>
@@ -45637,13 +45637,13 @@
         <v>1292</v>
       </c>
       <c r="B1293" t="str">
-        <v>FG-401564</v>
+        <v>FG-401561</v>
       </c>
       <c r="C1293" t="str">
-        <v>SMART SERIES SWAN NECK (1/2")</v>
+        <v>SMART SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1293" t="str">
-        <v>SMART SERIES SWAN NECK</v>
+        <v>SMART SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1293" t="str">
         <v>FAUCETS</v>
@@ -45652,19 +45652,19 @@
         <v>General</v>
       </c>
       <c r="G1293" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1293" t="str">
         <v>NOS</v>
       </c>
       <c r="I1293">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1293" t="str">
         <v>Active</v>
       </c>
       <c r="K1293" t="str">
-        <v>SMART SERIES SWAN NECK high quality faucet.</v>
+        <v>SMART SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1294">
@@ -45672,13 +45672,13 @@
         <v>1293</v>
       </c>
       <c r="B1294" t="str">
-        <v>FG-401561</v>
+        <v>FG-401566</v>
       </c>
       <c r="C1294" t="str">
-        <v>SMART SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1294" t="str">
-        <v>SMART SERIES ANGULAR VALVE</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
       </c>
       <c r="E1294" t="str">
         <v>FAUCETS</v>
@@ -45693,13 +45693,13 @@
         <v>NOS</v>
       </c>
       <c r="I1294">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1294" t="str">
         <v>Active</v>
       </c>
       <c r="K1294" t="str">
-        <v>SMART SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1295">
@@ -45710,7 +45710,7 @@
         <v>FG-401566</v>
       </c>
       <c r="C1295" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1295" t="str">
         <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
@@ -45722,7 +45722,7 @@
         <v>General</v>
       </c>
       <c r="G1295" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1295" t="str">
         <v>NOS</v>
@@ -45745,7 +45745,7 @@
         <v>FG-401566</v>
       </c>
       <c r="C1296" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1296" t="str">
         <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
@@ -45757,7 +45757,7 @@
         <v>General</v>
       </c>
       <c r="G1296" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1296" t="str">
         <v>NOS</v>
@@ -45777,13 +45777,13 @@
         <v>1296</v>
       </c>
       <c r="B1297" t="str">
-        <v>FG-401566</v>
+        <v>FG-401565</v>
       </c>
       <c r="C1297" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2")</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1297" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
+        <v>SMART SERIES 2 WAY BIB TAP</v>
       </c>
       <c r="E1297" t="str">
         <v>FAUCETS</v>
@@ -45792,7 +45792,7 @@
         <v>General</v>
       </c>
       <c r="G1297" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1297" t="str">
         <v>NOS</v>
@@ -45804,7 +45804,7 @@
         <v>Active</v>
       </c>
       <c r="K1297" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
+        <v>SMART SERIES 2 WAY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1298">
@@ -45815,7 +45815,7 @@
         <v>FG-401565</v>
       </c>
       <c r="C1298" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2)</v>
       </c>
       <c r="D1298" t="str">
         <v>SMART SERIES 2 WAY BIB TAP</v>
@@ -45827,7 +45827,7 @@
         <v>General</v>
       </c>
       <c r="G1298" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1298" t="str">
         <v>NOS</v>
@@ -45850,7 +45850,7 @@
         <v>FG-401565</v>
       </c>
       <c r="C1299" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2)</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2")</v>
       </c>
       <c r="D1299" t="str">
         <v>SMART SERIES 2 WAY BIB TAP</v>
@@ -45862,7 +45862,7 @@
         <v>General</v>
       </c>
       <c r="G1299" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1299" t="str">
         <v>NOS</v>
@@ -45882,13 +45882,13 @@
         <v>1299</v>
       </c>
       <c r="B1300" t="str">
-        <v>FG-401565</v>
+        <v>FG-401560</v>
       </c>
       <c r="C1300" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1300" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP</v>
       </c>
       <c r="E1300" t="str">
         <v>FAUCETS</v>
@@ -45897,19 +45897,19 @@
         <v>General</v>
       </c>
       <c r="G1300" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1300" t="str">
         <v>NOS</v>
       </c>
       <c r="I1300">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1300" t="str">
         <v>Active</v>
       </c>
       <c r="K1300" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1301">
@@ -45920,7 +45920,7 @@
         <v>FG-401560</v>
       </c>
       <c r="C1301" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1301" t="str">
         <v>REGULAR SERIES SHORT BODY BIB TAP</v>
@@ -45932,7 +45932,7 @@
         <v>General</v>
       </c>
       <c r="G1301" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1301" t="str">
         <v>NOS</v>
@@ -45955,7 +45955,7 @@
         <v>FG-401560</v>
       </c>
       <c r="C1302" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1302" t="str">
         <v>REGULAR SERIES SHORT BODY BIB TAP</v>
@@ -45967,7 +45967,7 @@
         <v>General</v>
       </c>
       <c r="G1302" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1302" t="str">
         <v>NOS</v>
@@ -45987,13 +45987,13 @@
         <v>1302</v>
       </c>
       <c r="B1303" t="str">
-        <v>FG-401560</v>
+        <v>FG-401559</v>
       </c>
       <c r="C1303" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1303" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP</v>
       </c>
       <c r="E1303" t="str">
         <v>FAUCETS</v>
@@ -46002,7 +46002,7 @@
         <v>General</v>
       </c>
       <c r="G1303" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1303" t="str">
         <v>NOS</v>
@@ -46014,7 +46014,7 @@
         <v>Active</v>
       </c>
       <c r="K1303" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1304">
@@ -46025,7 +46025,7 @@
         <v>FG-401559</v>
       </c>
       <c r="C1304" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1304" t="str">
         <v>REGULAR SERIES LONG BODY BIB TAP</v>
@@ -46037,7 +46037,7 @@
         <v>General</v>
       </c>
       <c r="G1304" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1304" t="str">
         <v>NOS</v>
@@ -46060,7 +46060,7 @@
         <v>FG-401559</v>
       </c>
       <c r="C1305" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1305" t="str">
         <v>REGULAR SERIES LONG BODY BIB TAP</v>
@@ -46072,7 +46072,7 @@
         <v>General</v>
       </c>
       <c r="G1305" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1305" t="str">
         <v>NOS</v>
@@ -46092,13 +46092,13 @@
         <v>1305</v>
       </c>
       <c r="B1306" t="str">
-        <v>FG-401559</v>
+        <v>FG-401554</v>
       </c>
       <c r="C1306" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1306" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP</v>
+        <v>REGULAR SERIES PILLAR TAP</v>
       </c>
       <c r="E1306" t="str">
         <v>FAUCETS</v>
@@ -46107,19 +46107,19 @@
         <v>General</v>
       </c>
       <c r="G1306" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1306" t="str">
         <v>NOS</v>
       </c>
       <c r="I1306">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1306" t="str">
         <v>Active</v>
       </c>
       <c r="K1306" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1307">
@@ -46130,7 +46130,7 @@
         <v>FG-401554</v>
       </c>
       <c r="C1307" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2 inch)</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1307" t="str">
         <v>REGULAR SERIES PILLAR TAP</v>
@@ -46142,7 +46142,7 @@
         <v>General</v>
       </c>
       <c r="G1307" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1307" t="str">
         <v>NOS</v>
@@ -46165,7 +46165,7 @@
         <v>FG-401554</v>
       </c>
       <c r="C1308" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2)</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1308" t="str">
         <v>REGULAR SERIES PILLAR TAP</v>
@@ -46177,7 +46177,7 @@
         <v>General</v>
       </c>
       <c r="G1308" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1308" t="str">
         <v>NOS</v>
@@ -46197,13 +46197,13 @@
         <v>1308</v>
       </c>
       <c r="B1309" t="str">
-        <v>FG-401554</v>
+        <v>FG-401555</v>
       </c>
       <c r="C1309" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2")</v>
+        <v>REGULAR SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1309" t="str">
-        <v>REGULAR SERIES PILLAR TAP</v>
+        <v>REGULAR SERIES SINK TAP</v>
       </c>
       <c r="E1309" t="str">
         <v>FAUCETS</v>
@@ -46212,7 +46212,7 @@
         <v>General</v>
       </c>
       <c r="G1309" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1309" t="str">
         <v>NOS</v>
@@ -46224,7 +46224,7 @@
         <v>Active</v>
       </c>
       <c r="K1309" t="str">
-        <v>REGULAR SERIES PILLAR TAP high quality faucet.</v>
+        <v>REGULAR SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1310">
@@ -46235,7 +46235,7 @@
         <v>FG-401555</v>
       </c>
       <c r="C1310" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2 inch)</v>
+        <v>REGULAR SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1310" t="str">
         <v>REGULAR SERIES SINK TAP</v>
@@ -46247,7 +46247,7 @@
         <v>General</v>
       </c>
       <c r="G1310" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1310" t="str">
         <v>NOS</v>
@@ -46270,7 +46270,7 @@
         <v>FG-401555</v>
       </c>
       <c r="C1311" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2)</v>
+        <v>REGULAR SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1311" t="str">
         <v>REGULAR SERIES SINK TAP</v>
@@ -46282,7 +46282,7 @@
         <v>General</v>
       </c>
       <c r="G1311" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1311" t="str">
         <v>NOS</v>
@@ -46302,13 +46302,13 @@
         <v>1311</v>
       </c>
       <c r="B1312" t="str">
-        <v>FG-401555</v>
+        <v>FG-401556</v>
       </c>
       <c r="C1312" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2")</v>
+        <v>REGULAR SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1312" t="str">
-        <v>REGULAR SERIES SINK TAP</v>
+        <v>REGULAR SERIES SWAN NECK</v>
       </c>
       <c r="E1312" t="str">
         <v>FAUCETS</v>
@@ -46317,7 +46317,7 @@
         <v>General</v>
       </c>
       <c r="G1312" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1312" t="str">
         <v>NOS</v>
@@ -46329,7 +46329,7 @@
         <v>Active</v>
       </c>
       <c r="K1312" t="str">
-        <v>REGULAR SERIES SINK TAP high quality faucet.</v>
+        <v>REGULAR SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1313">
@@ -46340,7 +46340,7 @@
         <v>FG-401556</v>
       </c>
       <c r="C1313" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2 inch)</v>
+        <v>REGULAR SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1313" t="str">
         <v>REGULAR SERIES SWAN NECK</v>
@@ -46352,7 +46352,7 @@
         <v>General</v>
       </c>
       <c r="G1313" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1313" t="str">
         <v>NOS</v>
@@ -46375,7 +46375,7 @@
         <v>FG-401556</v>
       </c>
       <c r="C1314" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2)</v>
+        <v>REGULAR SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1314" t="str">
         <v>REGULAR SERIES SWAN NECK</v>
@@ -46387,7 +46387,7 @@
         <v>General</v>
       </c>
       <c r="G1314" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1314" t="str">
         <v>NOS</v>
@@ -46407,13 +46407,13 @@
         <v>1314</v>
       </c>
       <c r="B1315" t="str">
-        <v>FG-401556</v>
+        <v>FG-401553</v>
       </c>
       <c r="C1315" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2")</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1315" t="str">
-        <v>REGULAR SERIES SWAN NECK</v>
+        <v>REGULAR SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1315" t="str">
         <v>FAUCETS</v>
@@ -46422,19 +46422,19 @@
         <v>General</v>
       </c>
       <c r="G1315" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1315" t="str">
         <v>NOS</v>
       </c>
       <c r="I1315">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1315" t="str">
         <v>Active</v>
       </c>
       <c r="K1315" t="str">
-        <v>REGULAR SERIES SWAN NECK high quality faucet.</v>
+        <v>REGULAR SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1316">
@@ -46445,7 +46445,7 @@
         <v>FG-401553</v>
       </c>
       <c r="C1316" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1316" t="str">
         <v>REGULAR SERIES ANGULAR VALVE</v>
@@ -46457,7 +46457,7 @@
         <v>General</v>
       </c>
       <c r="G1316" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1316" t="str">
         <v>NOS</v>
@@ -46480,7 +46480,7 @@
         <v>FG-401553</v>
       </c>
       <c r="C1317" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2)</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1317" t="str">
         <v>REGULAR SERIES ANGULAR VALVE</v>
@@ -46492,7 +46492,7 @@
         <v>General</v>
       </c>
       <c r="G1317" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1317" t="str">
         <v>NOS</v>
@@ -46512,13 +46512,13 @@
         <v>1317</v>
       </c>
       <c r="B1318" t="str">
-        <v>FG-401553</v>
+        <v>FG-401558</v>
       </c>
       <c r="C1318" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2")</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1318" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
       </c>
       <c r="E1318" t="str">
         <v>FAUCETS</v>
@@ -46527,19 +46527,19 @@
         <v>General</v>
       </c>
       <c r="G1318" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1318" t="str">
         <v>NOS</v>
       </c>
       <c r="I1318">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1318" t="str">
         <v>Active</v>
       </c>
       <c r="K1318" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1319">
@@ -46550,7 +46550,7 @@
         <v>FG-401558</v>
       </c>
       <c r="C1319" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1319" t="str">
         <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
@@ -46562,7 +46562,7 @@
         <v>General</v>
       </c>
       <c r="G1319" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1319" t="str">
         <v>NOS</v>
@@ -46585,7 +46585,7 @@
         <v>FG-401558</v>
       </c>
       <c r="C1320" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2)</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1320" t="str">
         <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
@@ -46597,7 +46597,7 @@
         <v>General</v>
       </c>
       <c r="G1320" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1320" t="str">
         <v>NOS</v>
@@ -46617,13 +46617,13 @@
         <v>1320</v>
       </c>
       <c r="B1321" t="str">
-        <v>FG-401558</v>
+        <v>FG-401557</v>
       </c>
       <c r="C1321" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2")</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1321" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP</v>
       </c>
       <c r="E1321" t="str">
         <v>FAUCETS</v>
@@ -46632,7 +46632,7 @@
         <v>General</v>
       </c>
       <c r="G1321" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1321" t="str">
         <v>NOS</v>
@@ -46644,7 +46644,7 @@
         <v>Active</v>
       </c>
       <c r="K1321" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1322">
@@ -46655,7 +46655,7 @@
         <v>FG-401557</v>
       </c>
       <c r="C1322" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2)</v>
       </c>
       <c r="D1322" t="str">
         <v>REGULAR SERIES 2 WAY BIB TAP</v>
@@ -46667,7 +46667,7 @@
         <v>General</v>
       </c>
       <c r="G1322" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1322" t="str">
         <v>NOS</v>
@@ -46690,7 +46690,7 @@
         <v>FG-401557</v>
       </c>
       <c r="C1323" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2")</v>
       </c>
       <c r="D1323" t="str">
         <v>REGULAR SERIES 2 WAY BIB TAP</v>
@@ -46702,7 +46702,7 @@
         <v>General</v>
       </c>
       <c r="G1323" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1323" t="str">
         <v>NOS</v>
@@ -46722,34 +46722,34 @@
         <v>1323</v>
       </c>
       <c r="B1324" t="str">
-        <v>FG-401557</v>
+        <v>FG-400836</v>
       </c>
       <c r="C1324" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2")</v>
+        <v>SINGLE SIDE HANDLE FLUSH 8L (8L)</v>
       </c>
       <c r="D1324" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP</v>
+        <v>SINGLE SIDE HANDLE FLUSH 8L</v>
       </c>
       <c r="E1324" t="str">
-        <v>FAUCETS</v>
+        <v>Toilet Seat Cover &amp; Flushing Cistern</v>
       </c>
       <c r="F1324" t="str">
         <v>General</v>
       </c>
       <c r="G1324" t="str">
-        <v>1/2"</v>
+        <v>8L</v>
       </c>
       <c r="H1324" t="str">
         <v>NOS</v>
       </c>
       <c r="I1324">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J1324" t="str">
         <v>Active</v>
       </c>
       <c r="K1324" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP high quality faucet.</v>
+        <v>8 Litre Single Side Handle Flushing Cistern.</v>
       </c>
     </row>
     <row r="1325">
@@ -46757,13 +46757,13 @@
         <v>1324</v>
       </c>
       <c r="B1325" t="str">
-        <v>FG-400836</v>
+        <v>FG-400837</v>
       </c>
       <c r="C1325" t="str">
-        <v>SINGLE SIDE HANDLE FLUSH 8L (8L)</v>
+        <v>CENTER SINGLE PUSH FLUSH 8L (8L)</v>
       </c>
       <c r="D1325" t="str">
-        <v>SINGLE SIDE HANDLE FLUSH 8L</v>
+        <v>CENTER SINGLE PUSH FLUSH 8L</v>
       </c>
       <c r="E1325" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46784,7 +46784,7 @@
         <v>Active</v>
       </c>
       <c r="K1325" t="str">
-        <v>8 Litre Single Side Handle Flushing Cistern.</v>
+        <v>8 Litre Center Single Push Flushing Cistern.</v>
       </c>
     </row>
     <row r="1326">
@@ -46792,13 +46792,13 @@
         <v>1325</v>
       </c>
       <c r="B1326" t="str">
-        <v>FG-400837</v>
+        <v>FG-400838</v>
       </c>
       <c r="C1326" t="str">
-        <v>CENTER SINGLE PUSH FLUSH 8L (8L)</v>
+        <v>DUAL FLUSH 10L (10L)</v>
       </c>
       <c r="D1326" t="str">
-        <v>CENTER SINGLE PUSH FLUSH 8L</v>
+        <v>DUAL FLUSH 10L</v>
       </c>
       <c r="E1326" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46807,7 +46807,7 @@
         <v>General</v>
       </c>
       <c r="G1326" t="str">
-        <v>8L</v>
+        <v>10L</v>
       </c>
       <c r="H1326" t="str">
         <v>NOS</v>
@@ -46819,7 +46819,7 @@
         <v>Active</v>
       </c>
       <c r="K1326" t="str">
-        <v>8 Litre Center Single Push Flushing Cistern.</v>
+        <v>10 Litre Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1327">
@@ -46827,13 +46827,13 @@
         <v>1326</v>
       </c>
       <c r="B1327" t="str">
-        <v>FG-400838</v>
+        <v>FG-400835</v>
       </c>
       <c r="C1327" t="str">
-        <v>DUAL FLUSH 10L (10L)</v>
+        <v>EWC SEAT COVER (WITH JET) (Standard)</v>
       </c>
       <c r="D1327" t="str">
-        <v>DUAL FLUSH 10L</v>
+        <v>EWC SEAT COVER (WITH JET)</v>
       </c>
       <c r="E1327" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46842,19 +46842,19 @@
         <v>General</v>
       </c>
       <c r="G1327" t="str">
-        <v>10L</v>
+        <v>Standard</v>
       </c>
       <c r="H1327" t="str">
         <v>NOS</v>
       </c>
       <c r="I1327">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J1327" t="str">
         <v>Active</v>
       </c>
       <c r="K1327" t="str">
-        <v>10 Litre Dual Flush Cistern.</v>
+        <v>EWC Toilet Seat Cover with integrated jet spray.</v>
       </c>
     </row>
     <row r="1328">
@@ -46862,13 +46862,13 @@
         <v>1327</v>
       </c>
       <c r="B1328" t="str">
-        <v>FG-400835</v>
+        <v>FG-400840</v>
       </c>
       <c r="C1328" t="str">
-        <v>EWC SEAT COVER (WITH JET) (Standard)</v>
+        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L) (10L)</v>
       </c>
       <c r="D1328" t="str">
-        <v>EWC SEAT COVER (WITH JET)</v>
+        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L)</v>
       </c>
       <c r="E1328" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46877,19 +46877,19 @@
         <v>General</v>
       </c>
       <c r="G1328" t="str">
-        <v>Standard</v>
+        <v>10L</v>
       </c>
       <c r="H1328" t="str">
         <v>NOS</v>
       </c>
       <c r="I1328">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J1328" t="str">
         <v>Active</v>
       </c>
       <c r="K1328" t="str">
-        <v>EWC Toilet Seat Cover with integrated jet spray.</v>
+        <v>10 Litre Premium Dual Colour Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1329">
@@ -46897,13 +46897,13 @@
         <v>1328</v>
       </c>
       <c r="B1329" t="str">
-        <v>FG-400840</v>
+        <v>FG-400839</v>
       </c>
       <c r="C1329" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L) (10L)</v>
+        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L) (10L)</v>
       </c>
       <c r="D1329" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L)</v>
+        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L)</v>
       </c>
       <c r="E1329" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46924,7 +46924,7 @@
         <v>Active</v>
       </c>
       <c r="K1329" t="str">
-        <v>10 Litre Premium Dual Colour Dual Flush Cistern.</v>
+        <v>10 Litre Economy Dual Colour Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1330">
@@ -46932,13 +46932,13 @@
         <v>1329</v>
       </c>
       <c r="B1330" t="str">
-        <v>FG-400839</v>
+        <v>FG-400834</v>
       </c>
       <c r="C1330" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L) (10L)</v>
+        <v>EWC SEAT COVER (WITHOUT JET) (Standard)</v>
       </c>
       <c r="D1330" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L)</v>
+        <v>EWC SEAT COVER (WITHOUT JET)</v>
       </c>
       <c r="E1330" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46947,59 +46947,24 @@
         <v>General</v>
       </c>
       <c r="G1330" t="str">
-        <v>10L</v>
+        <v>Standard</v>
       </c>
       <c r="H1330" t="str">
         <v>NOS</v>
       </c>
       <c r="I1330">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J1330" t="str">
         <v>Active</v>
       </c>
       <c r="K1330" t="str">
-        <v>10 Litre Economy Dual Colour Dual Flush Cistern.</v>
-      </c>
-    </row>
-    <row r="1331">
-      <c r="A1331">
-        <v>1330</v>
-      </c>
-      <c r="B1331" t="str">
-        <v>FG-400834</v>
-      </c>
-      <c r="C1331" t="str">
-        <v>EWC SEAT COVER (WITHOUT JET) (Standard)</v>
-      </c>
-      <c r="D1331" t="str">
-        <v>EWC SEAT COVER (WITHOUT JET)</v>
-      </c>
-      <c r="E1331" t="str">
-        <v>Toilet Seat Cover &amp; Flushing Cistern</v>
-      </c>
-      <c r="F1331" t="str">
-        <v>General</v>
-      </c>
-      <c r="G1331" t="str">
-        <v>Standard</v>
-      </c>
-      <c r="H1331" t="str">
-        <v>NOS</v>
-      </c>
-      <c r="I1331">
-        <v>20</v>
-      </c>
-      <c r="J1331" t="str">
-        <v>Active</v>
-      </c>
-      <c r="K1331" t="str">
         <v>EWC Toilet Seat Cover without jet spray.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K1331"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K1330"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
+++ b/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1330"/>
+  <dimension ref="A1:K1331"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -35802,10 +35802,10 @@
         <v>1011</v>
       </c>
       <c r="B1012" t="str">
-        <v>-</v>
+        <v>FG-400667</v>
       </c>
       <c r="C1012" t="str">
-        <v>AGRI TEE 10KG</v>
+        <v>AGRI TEE 10KG (25MM)</v>
       </c>
       <c r="D1012" t="str">
         <v>AGRI TEE 10KG</v>
@@ -35817,19 +35817,19 @@
         <v>General</v>
       </c>
       <c r="G1012" t="str">
-        <v>Standard</v>
+        <v>25MM</v>
       </c>
       <c r="H1012" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1012" t="str">
-        <v>-</v>
+      <c r="I1012">
+        <v>180</v>
       </c>
       <c r="J1012" t="str">
         <v>Active</v>
       </c>
       <c r="K1012" t="str">
-        <v>AGRI TEE 10KG.</v>
+        <v>AGRI TEE 10KG. Available sizes: 25MM, 32MM.</v>
       </c>
     </row>
     <row r="1013">
@@ -35837,13 +35837,13 @@
         <v>1012</v>
       </c>
       <c r="B1013" t="str">
-        <v>-</v>
+        <v>FG-400668</v>
       </c>
       <c r="C1013" t="str">
-        <v>PN10 - COUPLER ISI (25MM)</v>
+        <v>AGRI TEE 10KG (32MM)</v>
       </c>
       <c r="D1013" t="str">
-        <v>PN10 - COUPLER ISI</v>
+        <v>AGRI TEE 10KG</v>
       </c>
       <c r="E1013" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35852,19 +35852,19 @@
         <v>General</v>
       </c>
       <c r="G1013" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1013" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1013" t="str">
-        <v>-</v>
+      <c r="I1013">
+        <v>100</v>
       </c>
       <c r="J1013" t="str">
         <v>Active</v>
       </c>
       <c r="K1013" t="str">
-        <v>PN10 - COUPLER ISI for agriculture irrigation and piping systems.</v>
+        <v>AGRI TEE 10KG. Available sizes: 25MM, 32MM.</v>
       </c>
     </row>
     <row r="1014">
@@ -35875,7 +35875,7 @@
         <v>-</v>
       </c>
       <c r="C1014" t="str">
-        <v>PN10 - COUPLER ISI (32MM)</v>
+        <v>PN10 - COUPLER ISI (25MM)</v>
       </c>
       <c r="D1014" t="str">
         <v>PN10 - COUPLER ISI</v>
@@ -35887,7 +35887,7 @@
         <v>General</v>
       </c>
       <c r="G1014" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1014" t="str">
         <v>BOX</v>
@@ -35910,10 +35910,10 @@
         <v>-</v>
       </c>
       <c r="C1015" t="str">
-        <v>PN10 - MTA ISI (25MM)</v>
+        <v>PN10 - COUPLER ISI (32MM)</v>
       </c>
       <c r="D1015" t="str">
-        <v>PN10 - MTA ISI</v>
+        <v>PN10 - COUPLER ISI</v>
       </c>
       <c r="E1015" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35922,7 +35922,7 @@
         <v>General</v>
       </c>
       <c r="G1015" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1015" t="str">
         <v>BOX</v>
@@ -35934,7 +35934,7 @@
         <v>Active</v>
       </c>
       <c r="K1015" t="str">
-        <v>PN10 - MTA ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - COUPLER ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1016">
@@ -35945,7 +35945,7 @@
         <v>-</v>
       </c>
       <c r="C1016" t="str">
-        <v>PN10 - MTA ISI (32MM)</v>
+        <v>PN10 - MTA ISI (25MM)</v>
       </c>
       <c r="D1016" t="str">
         <v>PN10 - MTA ISI</v>
@@ -35957,7 +35957,7 @@
         <v>General</v>
       </c>
       <c r="G1016" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1016" t="str">
         <v>BOX</v>
@@ -35980,10 +35980,10 @@
         <v>-</v>
       </c>
       <c r="C1017" t="str">
-        <v>PN10 - FTA ISI (25MM)</v>
+        <v>PN10 - MTA ISI (32MM)</v>
       </c>
       <c r="D1017" t="str">
-        <v>PN10 - FTA ISI</v>
+        <v>PN10 - MTA ISI</v>
       </c>
       <c r="E1017" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35992,7 +35992,7 @@
         <v>General</v>
       </c>
       <c r="G1017" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1017" t="str">
         <v>BOX</v>
@@ -36004,7 +36004,7 @@
         <v>Active</v>
       </c>
       <c r="K1017" t="str">
-        <v>PN10 - FTA ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - MTA ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1018">
@@ -36015,7 +36015,7 @@
         <v>-</v>
       </c>
       <c r="C1018" t="str">
-        <v>PN10 - FTA ISI (32MM)</v>
+        <v>PN10 - FTA ISI (25MM)</v>
       </c>
       <c r="D1018" t="str">
         <v>PN10 - FTA ISI</v>
@@ -36027,7 +36027,7 @@
         <v>General</v>
       </c>
       <c r="G1018" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1018" t="str">
         <v>BOX</v>
@@ -36050,10 +36050,10 @@
         <v>-</v>
       </c>
       <c r="C1019" t="str">
-        <v>PN10 - END CAP ISI (25MM)</v>
+        <v>PN10 - FTA ISI (32MM)</v>
       </c>
       <c r="D1019" t="str">
-        <v>PN10 - END CAP ISI</v>
+        <v>PN10 - FTA ISI</v>
       </c>
       <c r="E1019" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36062,7 +36062,7 @@
         <v>General</v>
       </c>
       <c r="G1019" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1019" t="str">
         <v>BOX</v>
@@ -36074,7 +36074,7 @@
         <v>Active</v>
       </c>
       <c r="K1019" t="str">
-        <v>PN10 - END CAP ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - FTA ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1020">
@@ -36085,7 +36085,7 @@
         <v>-</v>
       </c>
       <c r="C1020" t="str">
-        <v>PN10 - END CAP ISI (32MM)</v>
+        <v>PN10 - END CAP ISI (25MM)</v>
       </c>
       <c r="D1020" t="str">
         <v>PN10 - END CAP ISI</v>
@@ -36097,7 +36097,7 @@
         <v>General</v>
       </c>
       <c r="G1020" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1020" t="str">
         <v>BOX</v>
@@ -36120,10 +36120,10 @@
         <v>-</v>
       </c>
       <c r="C1021" t="str">
-        <v>PN10 - REDUCING BUSH ISI (32 X 20)</v>
+        <v>PN10 - END CAP ISI (32MM)</v>
       </c>
       <c r="D1021" t="str">
-        <v>PN10 - REDUCING BUSH ISI</v>
+        <v>PN10 - END CAP ISI</v>
       </c>
       <c r="E1021" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36132,7 +36132,7 @@
         <v>General</v>
       </c>
       <c r="G1021" t="str">
-        <v>32 X 20</v>
+        <v>32MM</v>
       </c>
       <c r="H1021" t="str">
         <v>BOX</v>
@@ -36144,7 +36144,7 @@
         <v>Active</v>
       </c>
       <c r="K1021" t="str">
-        <v>PN10 - REDUCING BUSH ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - END CAP ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1022">
@@ -36155,7 +36155,7 @@
         <v>-</v>
       </c>
       <c r="C1022" t="str">
-        <v>PN10 - REDUCING BUSH ISI (32 X 25)</v>
+        <v>PN10 - REDUCING BUSH ISI (32 X 20)</v>
       </c>
       <c r="D1022" t="str">
         <v>PN10 - REDUCING BUSH ISI</v>
@@ -36167,7 +36167,7 @@
         <v>General</v>
       </c>
       <c r="G1022" t="str">
-        <v>32 X 25</v>
+        <v>32 X 20</v>
       </c>
       <c r="H1022" t="str">
         <v>BOX</v>
@@ -36187,13 +36187,13 @@
         <v>1022</v>
       </c>
       <c r="B1023" t="str">
-        <v>FG-400585</v>
+        <v>-</v>
       </c>
       <c r="C1023" t="str">
-        <v>AGRI REDUCER (50X40MM)</v>
+        <v>PN10 - REDUCING BUSH ISI (32 X 25)</v>
       </c>
       <c r="D1023" t="str">
-        <v>AGRI REDUCER</v>
+        <v>PN10 - REDUCING BUSH ISI</v>
       </c>
       <c r="E1023" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36202,19 +36202,19 @@
         <v>General</v>
       </c>
       <c r="G1023" t="str">
-        <v>50X40MM</v>
+        <v>32 X 25</v>
       </c>
       <c r="H1023" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1023">
-        <v>300</v>
+      <c r="I1023" t="str">
+        <v>-</v>
       </c>
       <c r="J1023" t="str">
         <v>Active</v>
       </c>
       <c r="K1023" t="str">
-        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
+        <v>PN10 - REDUCING BUSH ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1024">
@@ -36222,10 +36222,10 @@
         <v>1023</v>
       </c>
       <c r="B1024" t="str">
-        <v>FG-400584</v>
+        <v>FG-400585</v>
       </c>
       <c r="C1024" t="str">
-        <v>AGRI REDUCER (63X40MM)</v>
+        <v>AGRI REDUCER (50X40MM)</v>
       </c>
       <c r="D1024" t="str">
         <v>AGRI REDUCER</v>
@@ -36237,13 +36237,13 @@
         <v>General</v>
       </c>
       <c r="G1024" t="str">
-        <v>63X40MM</v>
+        <v>50X40MM</v>
       </c>
       <c r="H1024" t="str">
         <v>BOX</v>
       </c>
       <c r="I1024">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J1024" t="str">
         <v>Active</v>
@@ -36257,10 +36257,10 @@
         <v>1024</v>
       </c>
       <c r="B1025" t="str">
-        <v>FG-400583</v>
+        <v>FG-400584</v>
       </c>
       <c r="C1025" t="str">
-        <v>AGRI REDUCER (63X50MM)</v>
+        <v>AGRI REDUCER (63X40MM)</v>
       </c>
       <c r="D1025" t="str">
         <v>AGRI REDUCER</v>
@@ -36272,13 +36272,13 @@
         <v>General</v>
       </c>
       <c r="G1025" t="str">
-        <v>63X50MM</v>
+        <v>63X40MM</v>
       </c>
       <c r="H1025" t="str">
         <v>BOX</v>
       </c>
       <c r="I1025">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="J1025" t="str">
         <v>Active</v>
@@ -36292,10 +36292,10 @@
         <v>1025</v>
       </c>
       <c r="B1026" t="str">
-        <v>FG-400582</v>
+        <v>FG-400583</v>
       </c>
       <c r="C1026" t="str">
-        <v>AGRI REDUCER (75X40MM)</v>
+        <v>AGRI REDUCER (63X50MM)</v>
       </c>
       <c r="D1026" t="str">
         <v>AGRI REDUCER</v>
@@ -36307,13 +36307,13 @@
         <v>General</v>
       </c>
       <c r="G1026" t="str">
-        <v>75X40MM</v>
+        <v>63X50MM</v>
       </c>
       <c r="H1026" t="str">
         <v>BOX</v>
       </c>
       <c r="I1026">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J1026" t="str">
         <v>Active</v>
@@ -36327,10 +36327,10 @@
         <v>1026</v>
       </c>
       <c r="B1027" t="str">
-        <v>FG-400581</v>
+        <v>FG-400582</v>
       </c>
       <c r="C1027" t="str">
-        <v>AGRI REDUCER (75X50MM)</v>
+        <v>AGRI REDUCER (75X40MM)</v>
       </c>
       <c r="D1027" t="str">
         <v>AGRI REDUCER</v>
@@ -36342,13 +36342,13 @@
         <v>General</v>
       </c>
       <c r="G1027" t="str">
-        <v>75X50MM</v>
+        <v>75X40MM</v>
       </c>
       <c r="H1027" t="str">
         <v>BOX</v>
       </c>
       <c r="I1027">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J1027" t="str">
         <v>Active</v>
@@ -36362,10 +36362,10 @@
         <v>1027</v>
       </c>
       <c r="B1028" t="str">
-        <v>FG-400580</v>
+        <v>FG-400581</v>
       </c>
       <c r="C1028" t="str">
-        <v>AGRI REDUCER (75X63MM)</v>
+        <v>AGRI REDUCER (75X50MM)</v>
       </c>
       <c r="D1028" t="str">
         <v>AGRI REDUCER</v>
@@ -36377,13 +36377,13 @@
         <v>General</v>
       </c>
       <c r="G1028" t="str">
-        <v>75X63MM</v>
+        <v>75X50MM</v>
       </c>
       <c r="H1028" t="str">
         <v>BOX</v>
       </c>
       <c r="I1028">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J1028" t="str">
         <v>Active</v>
@@ -36397,10 +36397,10 @@
         <v>1028</v>
       </c>
       <c r="B1029" t="str">
-        <v>FG-400579</v>
+        <v>FG-400580</v>
       </c>
       <c r="C1029" t="str">
-        <v>AGRI REDUCER (90X50MM)</v>
+        <v>AGRI REDUCER (75X63MM)</v>
       </c>
       <c r="D1029" t="str">
         <v>AGRI REDUCER</v>
@@ -36412,13 +36412,13 @@
         <v>General</v>
       </c>
       <c r="G1029" t="str">
-        <v>90X50MM</v>
+        <v>75X63MM</v>
       </c>
       <c r="H1029" t="str">
         <v>BOX</v>
       </c>
       <c r="I1029">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J1029" t="str">
         <v>Active</v>
@@ -36432,10 +36432,10 @@
         <v>1029</v>
       </c>
       <c r="B1030" t="str">
-        <v>FG-400578</v>
+        <v>FG-400579</v>
       </c>
       <c r="C1030" t="str">
-        <v>AGRI REDUCER (90X63MM)</v>
+        <v>AGRI REDUCER (90X50MM)</v>
       </c>
       <c r="D1030" t="str">
         <v>AGRI REDUCER</v>
@@ -36447,13 +36447,13 @@
         <v>General</v>
       </c>
       <c r="G1030" t="str">
-        <v>90X63MM</v>
+        <v>90X50MM</v>
       </c>
       <c r="H1030" t="str">
         <v>BOX</v>
       </c>
       <c r="I1030">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J1030" t="str">
         <v>Active</v>
@@ -36467,10 +36467,10 @@
         <v>1030</v>
       </c>
       <c r="B1031" t="str">
-        <v>FG-400577</v>
+        <v>FG-400578</v>
       </c>
       <c r="C1031" t="str">
-        <v>AGRI REDUCER (90X75MM)</v>
+        <v>AGRI REDUCER (90X63MM)</v>
       </c>
       <c r="D1031" t="str">
         <v>AGRI REDUCER</v>
@@ -36482,13 +36482,13 @@
         <v>General</v>
       </c>
       <c r="G1031" t="str">
-        <v>90X75MM</v>
+        <v>90X63MM</v>
       </c>
       <c r="H1031" t="str">
         <v>BOX</v>
       </c>
       <c r="I1031">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J1031" t="str">
         <v>Active</v>
@@ -36502,10 +36502,10 @@
         <v>1031</v>
       </c>
       <c r="B1032" t="str">
-        <v>FG-400576</v>
+        <v>FG-400577</v>
       </c>
       <c r="C1032" t="str">
-        <v>AGRI REDUCER (110X63MM)</v>
+        <v>AGRI REDUCER (90X75MM)</v>
       </c>
       <c r="D1032" t="str">
         <v>AGRI REDUCER</v>
@@ -36517,13 +36517,13 @@
         <v>General</v>
       </c>
       <c r="G1032" t="str">
-        <v>110X63MM</v>
+        <v>90X75MM</v>
       </c>
       <c r="H1032" t="str">
         <v>BOX</v>
       </c>
       <c r="I1032">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J1032" t="str">
         <v>Active</v>
@@ -36537,10 +36537,10 @@
         <v>1032</v>
       </c>
       <c r="B1033" t="str">
-        <v>FG-400575</v>
+        <v>FG-400576</v>
       </c>
       <c r="C1033" t="str">
-        <v>AGRI REDUCER (110X75MM)</v>
+        <v>AGRI REDUCER (110X63MM)</v>
       </c>
       <c r="D1033" t="str">
         <v>AGRI REDUCER</v>
@@ -36552,7 +36552,7 @@
         <v>General</v>
       </c>
       <c r="G1033" t="str">
-        <v>110X75MM</v>
+        <v>110X63MM</v>
       </c>
       <c r="H1033" t="str">
         <v>BOX</v>
@@ -36572,10 +36572,10 @@
         <v>1033</v>
       </c>
       <c r="B1034" t="str">
-        <v>FG-400574</v>
+        <v>FG-400575</v>
       </c>
       <c r="C1034" t="str">
-        <v>AGRI REDUCER (110X90MM)</v>
+        <v>AGRI REDUCER (110X75MM)</v>
       </c>
       <c r="D1034" t="str">
         <v>AGRI REDUCER</v>
@@ -36587,13 +36587,13 @@
         <v>General</v>
       </c>
       <c r="G1034" t="str">
-        <v>110X90MM</v>
+        <v>110X75MM</v>
       </c>
       <c r="H1034" t="str">
         <v>BOX</v>
       </c>
       <c r="I1034">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J1034" t="str">
         <v>Active</v>
@@ -36607,13 +36607,13 @@
         <v>1034</v>
       </c>
       <c r="B1035" t="str">
-        <v>-</v>
+        <v>FG-400574</v>
       </c>
       <c r="C1035" t="str">
-        <v>REDUCING BUSH (LW) (63 X 40)</v>
+        <v>AGRI REDUCER (110X90MM)</v>
       </c>
       <c r="D1035" t="str">
-        <v>REDUCING BUSH (LW)</v>
+        <v>AGRI REDUCER</v>
       </c>
       <c r="E1035" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36622,19 +36622,19 @@
         <v>General</v>
       </c>
       <c r="G1035" t="str">
-        <v>63 X 40</v>
+        <v>110X90MM</v>
       </c>
       <c r="H1035" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1035" t="str">
-        <v>-</v>
+      <c r="I1035">
+        <v>40</v>
       </c>
       <c r="J1035" t="str">
         <v>Active</v>
       </c>
       <c r="K1035" t="str">
-        <v>REDUCING BUSH (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
       </c>
     </row>
     <row r="1036">
@@ -36645,7 +36645,7 @@
         <v>-</v>
       </c>
       <c r="C1036" t="str">
-        <v>REDUCING BUSH (LW) (63 X 50)</v>
+        <v>REDUCING BUSH (LW) (63 X 40)</v>
       </c>
       <c r="D1036" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36657,7 +36657,7 @@
         <v>General</v>
       </c>
       <c r="G1036" t="str">
-        <v>63 X 50</v>
+        <v>63 X 40</v>
       </c>
       <c r="H1036" t="str">
         <v>BOX</v>
@@ -36680,7 +36680,7 @@
         <v>-</v>
       </c>
       <c r="C1037" t="str">
-        <v>REDUCING BUSH (LW) (75 X 40)</v>
+        <v>REDUCING BUSH (LW) (63 X 50)</v>
       </c>
       <c r="D1037" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36692,7 +36692,7 @@
         <v>General</v>
       </c>
       <c r="G1037" t="str">
-        <v>75 X 40</v>
+        <v>63 X 50</v>
       </c>
       <c r="H1037" t="str">
         <v>BOX</v>
@@ -36715,7 +36715,7 @@
         <v>-</v>
       </c>
       <c r="C1038" t="str">
-        <v>REDUCING BUSH (LW) (75 X 63)</v>
+        <v>REDUCING BUSH (LW) (75 X 40)</v>
       </c>
       <c r="D1038" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36727,7 +36727,7 @@
         <v>General</v>
       </c>
       <c r="G1038" t="str">
-        <v>75 X 63</v>
+        <v>75 X 40</v>
       </c>
       <c r="H1038" t="str">
         <v>BOX</v>
@@ -36750,7 +36750,7 @@
         <v>-</v>
       </c>
       <c r="C1039" t="str">
-        <v>REDUCING BUSH (LW) (90 X 50)</v>
+        <v>REDUCING BUSH (LW) (75 X 63)</v>
       </c>
       <c r="D1039" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36762,7 +36762,7 @@
         <v>General</v>
       </c>
       <c r="G1039" t="str">
-        <v>90 X 50</v>
+        <v>75 X 63</v>
       </c>
       <c r="H1039" t="str">
         <v>BOX</v>
@@ -36785,7 +36785,7 @@
         <v>-</v>
       </c>
       <c r="C1040" t="str">
-        <v>REDUCING BUSH (LW) (90 X 63)</v>
+        <v>REDUCING BUSH (LW) (90 X 50)</v>
       </c>
       <c r="D1040" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36797,7 +36797,7 @@
         <v>General</v>
       </c>
       <c r="G1040" t="str">
-        <v>90 X 63</v>
+        <v>90 X 50</v>
       </c>
       <c r="H1040" t="str">
         <v>BOX</v>
@@ -36820,7 +36820,7 @@
         <v>-</v>
       </c>
       <c r="C1041" t="str">
-        <v>REDUCING BUSH (LW) (90 X 75)</v>
+        <v>REDUCING BUSH (LW) (90 X 63)</v>
       </c>
       <c r="D1041" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36832,7 +36832,7 @@
         <v>General</v>
       </c>
       <c r="G1041" t="str">
-        <v>90 X 75</v>
+        <v>90 X 63</v>
       </c>
       <c r="H1041" t="str">
         <v>BOX</v>
@@ -36855,7 +36855,7 @@
         <v>-</v>
       </c>
       <c r="C1042" t="str">
-        <v>REDUCING BUSH (LW) (110 X 63)</v>
+        <v>REDUCING BUSH (LW) (90 X 75)</v>
       </c>
       <c r="D1042" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36867,7 +36867,7 @@
         <v>General</v>
       </c>
       <c r="G1042" t="str">
-        <v>110 X 63</v>
+        <v>90 X 75</v>
       </c>
       <c r="H1042" t="str">
         <v>BOX</v>
@@ -36890,7 +36890,7 @@
         <v>-</v>
       </c>
       <c r="C1043" t="str">
-        <v>REDUCING BUSH (LW) (110 X 75)</v>
+        <v>REDUCING BUSH (LW) (110 X 63)</v>
       </c>
       <c r="D1043" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36902,7 +36902,7 @@
         <v>General</v>
       </c>
       <c r="G1043" t="str">
-        <v>110 X 75</v>
+        <v>110 X 63</v>
       </c>
       <c r="H1043" t="str">
         <v>BOX</v>
@@ -36925,7 +36925,7 @@
         <v>-</v>
       </c>
       <c r="C1044" t="str">
-        <v>REDUCING BUSH (LW) (110 X 90)</v>
+        <v>REDUCING BUSH (LW) (110 X 75)</v>
       </c>
       <c r="D1044" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36937,7 +36937,7 @@
         <v>General</v>
       </c>
       <c r="G1044" t="str">
-        <v>110 X 90</v>
+        <v>110 X 75</v>
       </c>
       <c r="H1044" t="str">
         <v>BOX</v>
@@ -36957,13 +36957,13 @@
         <v>1044</v>
       </c>
       <c r="B1045" t="str">
-        <v>FG-400550</v>
+        <v>-</v>
       </c>
       <c r="C1045" t="str">
-        <v>AGRI TEE (40MM)</v>
+        <v>REDUCING BUSH (LW) (110 X 90)</v>
       </c>
       <c r="D1045" t="str">
-        <v>AGRI TEE</v>
+        <v>REDUCING BUSH (LW)</v>
       </c>
       <c r="E1045" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36972,19 +36972,19 @@
         <v>General</v>
       </c>
       <c r="G1045" t="str">
-        <v>40MM</v>
+        <v>110 X 90</v>
       </c>
       <c r="H1045" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1045">
-        <v>150</v>
+      <c r="I1045" t="str">
+        <v>-</v>
       </c>
       <c r="J1045" t="str">
         <v>Active</v>
       </c>
       <c r="K1045" t="str">
-        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
+        <v>REDUCING BUSH (LW) for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1046">
@@ -36992,10 +36992,10 @@
         <v>1045</v>
       </c>
       <c r="B1046" t="str">
-        <v>FG-400551</v>
+        <v>FG-400550</v>
       </c>
       <c r="C1046" t="str">
-        <v>AGRI TEE (50MM)</v>
+        <v>AGRI TEE (40MM)</v>
       </c>
       <c r="D1046" t="str">
         <v>AGRI TEE</v>
@@ -37007,13 +37007,13 @@
         <v>General</v>
       </c>
       <c r="G1046" t="str">
-        <v>50MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1046" t="str">
         <v>BOX</v>
       </c>
       <c r="I1046">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J1046" t="str">
         <v>Active</v>
@@ -37027,10 +37027,10 @@
         <v>1046</v>
       </c>
       <c r="B1047" t="str">
-        <v>FG-400552</v>
+        <v>FG-400551</v>
       </c>
       <c r="C1047" t="str">
-        <v>AGRI TEE (63MM)</v>
+        <v>AGRI TEE (50MM)</v>
       </c>
       <c r="D1047" t="str">
         <v>AGRI TEE</v>
@@ -37042,13 +37042,13 @@
         <v>General</v>
       </c>
       <c r="G1047" t="str">
-        <v>63MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1047" t="str">
         <v>BOX</v>
       </c>
       <c r="I1047">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="J1047" t="str">
         <v>Active</v>
@@ -37062,10 +37062,10 @@
         <v>1047</v>
       </c>
       <c r="B1048" t="str">
-        <v>FG-400553</v>
+        <v>FG-400552</v>
       </c>
       <c r="C1048" t="str">
-        <v>AGRI TEE (75MM)</v>
+        <v>AGRI TEE (63MM)</v>
       </c>
       <c r="D1048" t="str">
         <v>AGRI TEE</v>
@@ -37077,13 +37077,13 @@
         <v>General</v>
       </c>
       <c r="G1048" t="str">
-        <v>75MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1048" t="str">
         <v>BOX</v>
       </c>
       <c r="I1048">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="J1048" t="str">
         <v>Active</v>
@@ -37097,10 +37097,10 @@
         <v>1048</v>
       </c>
       <c r="B1049" t="str">
-        <v>FG-400554</v>
+        <v>FG-400553</v>
       </c>
       <c r="C1049" t="str">
-        <v>AGRI TEE (90MM)</v>
+        <v>AGRI TEE (75MM)</v>
       </c>
       <c r="D1049" t="str">
         <v>AGRI TEE</v>
@@ -37112,13 +37112,13 @@
         <v>General</v>
       </c>
       <c r="G1049" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1049" t="str">
         <v>BOX</v>
       </c>
       <c r="I1049">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J1049" t="str">
         <v>Active</v>
@@ -37132,10 +37132,10 @@
         <v>1049</v>
       </c>
       <c r="B1050" t="str">
-        <v>FG-400586</v>
+        <v>FG-400554</v>
       </c>
       <c r="C1050" t="str">
-        <v>AGRI TEE (110MM)</v>
+        <v>AGRI TEE (90MM)</v>
       </c>
       <c r="D1050" t="str">
         <v>AGRI TEE</v>
@@ -37147,13 +37147,13 @@
         <v>General</v>
       </c>
       <c r="G1050" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1050" t="str">
         <v>BOX</v>
       </c>
       <c r="I1050">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J1050" t="str">
         <v>Active</v>
@@ -37167,10 +37167,10 @@
         <v>1050</v>
       </c>
       <c r="B1051" t="str">
-        <v>FG-400607</v>
+        <v>FG-400586</v>
       </c>
       <c r="C1051" t="str">
-        <v>AGRI TEE (140MM)</v>
+        <v>AGRI TEE (110MM)</v>
       </c>
       <c r="D1051" t="str">
         <v>AGRI TEE</v>
@@ -37182,13 +37182,13 @@
         <v>General</v>
       </c>
       <c r="G1051" t="str">
-        <v>140MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1051" t="str">
         <v>BOX</v>
       </c>
       <c r="I1051">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="J1051" t="str">
         <v>Active</v>
@@ -37202,10 +37202,10 @@
         <v>1051</v>
       </c>
       <c r="B1052" t="str">
-        <v>FG-400608</v>
+        <v>FG-400607</v>
       </c>
       <c r="C1052" t="str">
-        <v>AGRI TEE (160MM)</v>
+        <v>AGRI TEE (140MM)</v>
       </c>
       <c r="D1052" t="str">
         <v>AGRI TEE</v>
@@ -37217,13 +37217,13 @@
         <v>General</v>
       </c>
       <c r="G1052" t="str">
-        <v>160MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1052" t="str">
         <v>BOX</v>
       </c>
       <c r="I1052">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J1052" t="str">
         <v>Active</v>
@@ -37237,13 +37237,13 @@
         <v>1052</v>
       </c>
       <c r="B1053" t="str">
-        <v>-</v>
+        <v>FG-400608</v>
       </c>
       <c r="C1053" t="str">
-        <v>COUPLER (LW) (75MM)</v>
+        <v>AGRI TEE (160MM)</v>
       </c>
       <c r="D1053" t="str">
-        <v>COUPLER (LW)</v>
+        <v>AGRI TEE</v>
       </c>
       <c r="E1053" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37252,19 +37252,19 @@
         <v>General</v>
       </c>
       <c r="G1053" t="str">
-        <v>75MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1053" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1053" t="str">
-        <v>-</v>
+      <c r="I1053">
+        <v>9</v>
       </c>
       <c r="J1053" t="str">
         <v>Active</v>
       </c>
       <c r="K1053" t="str">
-        <v>COUPLER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1054">
@@ -37275,7 +37275,7 @@
         <v>-</v>
       </c>
       <c r="C1054" t="str">
-        <v>COUPLER (LW) (90MM)</v>
+        <v>COUPLER (LW) (75MM)</v>
       </c>
       <c r="D1054" t="str">
         <v>COUPLER (LW)</v>
@@ -37287,7 +37287,7 @@
         <v>General</v>
       </c>
       <c r="G1054" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1054" t="str">
         <v>BOX</v>
@@ -37310,7 +37310,7 @@
         <v>-</v>
       </c>
       <c r="C1055" t="str">
-        <v>COUPLER (LW) (110MM)</v>
+        <v>COUPLER (LW) (90MM)</v>
       </c>
       <c r="D1055" t="str">
         <v>COUPLER (LW)</v>
@@ -37322,7 +37322,7 @@
         <v>General</v>
       </c>
       <c r="G1055" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1055" t="str">
         <v>BOX</v>
@@ -37342,13 +37342,13 @@
         <v>1055</v>
       </c>
       <c r="B1056" t="str">
-        <v>FG-400561</v>
+        <v>-</v>
       </c>
       <c r="C1056" t="str">
-        <v>AGRI FABRICATED COUPLER (40MM)</v>
+        <v>COUPLER (LW) (110MM)</v>
       </c>
       <c r="D1056" t="str">
-        <v>AGRI FABRICATED COUPLER</v>
+        <v>COUPLER (LW)</v>
       </c>
       <c r="E1056" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37357,19 +37357,19 @@
         <v>General</v>
       </c>
       <c r="G1056" t="str">
-        <v>40MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1056" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1056">
-        <v>300</v>
+      <c r="I1056" t="str">
+        <v>-</v>
       </c>
       <c r="J1056" t="str">
         <v>Active</v>
       </c>
       <c r="K1056" t="str">
-        <v>AGRI FABRICATED COUPLER for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
+        <v>COUPLER (LW) for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1057">
@@ -37377,10 +37377,10 @@
         <v>1056</v>
       </c>
       <c r="B1057" t="str">
-        <v>FG-400562</v>
+        <v>FG-400561</v>
       </c>
       <c r="C1057" t="str">
-        <v>AGRI FABRICATED COUPLER (50MM)</v>
+        <v>AGRI FABRICATED COUPLER (40MM)</v>
       </c>
       <c r="D1057" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37392,13 +37392,13 @@
         <v>General</v>
       </c>
       <c r="G1057" t="str">
-        <v>50MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1057" t="str">
         <v>BOX</v>
       </c>
       <c r="I1057">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J1057" t="str">
         <v>Active</v>
@@ -37412,10 +37412,10 @@
         <v>1057</v>
       </c>
       <c r="B1058" t="str">
-        <v>FG-400563</v>
+        <v>FG-400562</v>
       </c>
       <c r="C1058" t="str">
-        <v>AGRI FABRICATED COUPLER (63MM)</v>
+        <v>AGRI FABRICATED COUPLER (50MM)</v>
       </c>
       <c r="D1058" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37427,7 +37427,7 @@
         <v>General</v>
       </c>
       <c r="G1058" t="str">
-        <v>63MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1058" t="str">
         <v>BOX</v>
@@ -37447,10 +37447,10 @@
         <v>1058</v>
       </c>
       <c r="B1059" t="str">
-        <v>FG-400564</v>
+        <v>FG-400563</v>
       </c>
       <c r="C1059" t="str">
-        <v>AGRI FABRICATED COUPLER (75MM)</v>
+        <v>AGRI FABRICATED COUPLER (63MM)</v>
       </c>
       <c r="D1059" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37462,13 +37462,13 @@
         <v>General</v>
       </c>
       <c r="G1059" t="str">
-        <v>75MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1059" t="str">
         <v>BOX</v>
       </c>
       <c r="I1059">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="J1059" t="str">
         <v>Active</v>
@@ -37482,10 +37482,10 @@
         <v>1059</v>
       </c>
       <c r="B1060" t="str">
-        <v>FG-400565</v>
+        <v>FG-400564</v>
       </c>
       <c r="C1060" t="str">
-        <v>AGRI FABRICATED COUPLER (90MM)</v>
+        <v>AGRI FABRICATED COUPLER (75MM)</v>
       </c>
       <c r="D1060" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37497,13 +37497,13 @@
         <v>General</v>
       </c>
       <c r="G1060" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1060" t="str">
         <v>BOX</v>
       </c>
       <c r="I1060">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="J1060" t="str">
         <v>Active</v>
@@ -37517,10 +37517,10 @@
         <v>1060</v>
       </c>
       <c r="B1061" t="str">
-        <v>FG-400566</v>
+        <v>FG-400565</v>
       </c>
       <c r="C1061" t="str">
-        <v>AGRI FABRICATED COUPLER (110MM)</v>
+        <v>AGRI FABRICATED COUPLER (90MM)</v>
       </c>
       <c r="D1061" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37532,13 +37532,13 @@
         <v>General</v>
       </c>
       <c r="G1061" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1061" t="str">
         <v>BOX</v>
       </c>
       <c r="I1061">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J1061" t="str">
         <v>Active</v>
@@ -37552,10 +37552,10 @@
         <v>1061</v>
       </c>
       <c r="B1062" t="str">
-        <v>FG-400587</v>
+        <v>FG-400566</v>
       </c>
       <c r="C1062" t="str">
-        <v>AGRI FABRICATED COUPLER (140MM 4KG)</v>
+        <v>AGRI FABRICATED COUPLER (110MM)</v>
       </c>
       <c r="D1062" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37567,13 +37567,13 @@
         <v>General</v>
       </c>
       <c r="G1062" t="str">
-        <v>140MM 4KG</v>
+        <v>110MM</v>
       </c>
       <c r="H1062" t="str">
         <v>BOX</v>
       </c>
       <c r="I1062">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J1062" t="str">
         <v>Active</v>
@@ -37587,10 +37587,10 @@
         <v>1062</v>
       </c>
       <c r="B1063" t="str">
-        <v>FG-400568</v>
+        <v>FG-400587</v>
       </c>
       <c r="C1063" t="str">
-        <v>AGRI FABRICATED COUPLER (160MM 4KG)</v>
+        <v>AGRI FABRICATED COUPLER (140MM 4KG)</v>
       </c>
       <c r="D1063" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37602,13 +37602,13 @@
         <v>General</v>
       </c>
       <c r="G1063" t="str">
-        <v>160MM 4KG</v>
+        <v>140MM 4KG</v>
       </c>
       <c r="H1063" t="str">
         <v>BOX</v>
       </c>
       <c r="I1063">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J1063" t="str">
         <v>Active</v>
@@ -37622,13 +37622,13 @@
         <v>1063</v>
       </c>
       <c r="B1064" t="str">
-        <v>FG-400567</v>
+        <v>FG-400568</v>
       </c>
       <c r="C1064" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG (140MM)</v>
+        <v>AGRI FABRICATED COUPLER (160MM 4KG)</v>
       </c>
       <c r="D1064" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG</v>
+        <v>AGRI FABRICATED COUPLER</v>
       </c>
       <c r="E1064" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37637,19 +37637,19 @@
         <v>General</v>
       </c>
       <c r="G1064" t="str">
-        <v>140MM</v>
+        <v>160MM 4KG</v>
       </c>
       <c r="H1064" t="str">
         <v>BOX</v>
       </c>
       <c r="I1064">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J1064" t="str">
         <v>Active</v>
       </c>
       <c r="K1064" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG for agriculture irrigation and piping systems. Available sizes: 140MM, 160MM.</v>
+        <v>AGRI FABRICATED COUPLER for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1065">
@@ -37657,10 +37657,10 @@
         <v>1064</v>
       </c>
       <c r="B1065" t="str">
-        <v>FG-400569</v>
+        <v>FG-400567</v>
       </c>
       <c r="C1065" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG (160MM)</v>
+        <v>AGRI FABRICATED COUPLER 6KG (140MM)</v>
       </c>
       <c r="D1065" t="str">
         <v>AGRI FABRICATED COUPLER 6KG</v>
@@ -37672,13 +37672,13 @@
         <v>General</v>
       </c>
       <c r="G1065" t="str">
-        <v>160MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1065" t="str">
         <v>BOX</v>
       </c>
       <c r="I1065">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J1065" t="str">
         <v>Active</v>
@@ -37692,13 +37692,13 @@
         <v>1065</v>
       </c>
       <c r="B1066" t="str">
-        <v>FG-400544</v>
+        <v>FG-400569</v>
       </c>
       <c r="C1066" t="str">
-        <v>AGRI ELBOW (40MM)</v>
+        <v>AGRI FABRICATED COUPLER 6KG (160MM)</v>
       </c>
       <c r="D1066" t="str">
-        <v>AGRI ELBOW</v>
+        <v>AGRI FABRICATED COUPLER 6KG</v>
       </c>
       <c r="E1066" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37707,19 +37707,19 @@
         <v>General</v>
       </c>
       <c r="G1066" t="str">
-        <v>40MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1066" t="str">
         <v>BOX</v>
       </c>
       <c r="I1066">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="J1066" t="str">
         <v>Active</v>
       </c>
       <c r="K1066" t="str">
-        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
+        <v>AGRI FABRICATED COUPLER 6KG for agriculture irrigation and piping systems. Available sizes: 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1067">
@@ -37727,10 +37727,10 @@
         <v>1066</v>
       </c>
       <c r="B1067" t="str">
-        <v>FG-400545</v>
+        <v>FG-400544</v>
       </c>
       <c r="C1067" t="str">
-        <v>AGRI ELBOW (50MM)</v>
+        <v>AGRI ELBOW (40MM)</v>
       </c>
       <c r="D1067" t="str">
         <v>AGRI ELBOW</v>
@@ -37742,13 +37742,13 @@
         <v>General</v>
       </c>
       <c r="G1067" t="str">
-        <v>50MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1067" t="str">
         <v>BOX</v>
       </c>
       <c r="I1067">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="J1067" t="str">
         <v>Active</v>
@@ -37762,10 +37762,10 @@
         <v>1067</v>
       </c>
       <c r="B1068" t="str">
-        <v>FG-400546</v>
+        <v>FG-400545</v>
       </c>
       <c r="C1068" t="str">
-        <v>AGRI ELBOW (63MM)</v>
+        <v>AGRI ELBOW (50MM)</v>
       </c>
       <c r="D1068" t="str">
         <v>AGRI ELBOW</v>
@@ -37777,13 +37777,13 @@
         <v>General</v>
       </c>
       <c r="G1068" t="str">
-        <v>63MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1068" t="str">
         <v>BOX</v>
       </c>
       <c r="I1068">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J1068" t="str">
         <v>Active</v>
@@ -37797,10 +37797,10 @@
         <v>1068</v>
       </c>
       <c r="B1069" t="str">
-        <v>FG-400547</v>
+        <v>FG-400546</v>
       </c>
       <c r="C1069" t="str">
-        <v>AGRI ELBOW (75MM)</v>
+        <v>AGRI ELBOW (63MM)</v>
       </c>
       <c r="D1069" t="str">
         <v>AGRI ELBOW</v>
@@ -37812,13 +37812,13 @@
         <v>General</v>
       </c>
       <c r="G1069" t="str">
-        <v>75MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1069" t="str">
         <v>BOX</v>
       </c>
       <c r="I1069">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J1069" t="str">
         <v>Active</v>
@@ -37832,10 +37832,10 @@
         <v>1069</v>
       </c>
       <c r="B1070" t="str">
-        <v>FG-400548</v>
+        <v>FG-400547</v>
       </c>
       <c r="C1070" t="str">
-        <v>AGRI ELBOW (90MM)</v>
+        <v>AGRI ELBOW (75MM)</v>
       </c>
       <c r="D1070" t="str">
         <v>AGRI ELBOW</v>
@@ -37847,13 +37847,13 @@
         <v>General</v>
       </c>
       <c r="G1070" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1070" t="str">
         <v>BOX</v>
       </c>
       <c r="I1070">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J1070" t="str">
         <v>Active</v>
@@ -37867,10 +37867,10 @@
         <v>1070</v>
       </c>
       <c r="B1071" t="str">
-        <v>FG-400549</v>
+        <v>FG-400548</v>
       </c>
       <c r="C1071" t="str">
-        <v>AGRI ELBOW (110MM)</v>
+        <v>AGRI ELBOW (90MM)</v>
       </c>
       <c r="D1071" t="str">
         <v>AGRI ELBOW</v>
@@ -37882,13 +37882,13 @@
         <v>General</v>
       </c>
       <c r="G1071" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1071" t="str">
         <v>BOX</v>
       </c>
       <c r="I1071">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="J1071" t="str">
         <v>Active</v>
@@ -37902,10 +37902,10 @@
         <v>1071</v>
       </c>
       <c r="B1072" t="str">
-        <v>FG-400595</v>
+        <v>FG-400549</v>
       </c>
       <c r="C1072" t="str">
-        <v>AGRI ELBOW (140MM)</v>
+        <v>AGRI ELBOW (110MM)</v>
       </c>
       <c r="D1072" t="str">
         <v>AGRI ELBOW</v>
@@ -37917,13 +37917,13 @@
         <v>General</v>
       </c>
       <c r="G1072" t="str">
-        <v>140MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1072" t="str">
         <v>BOX</v>
       </c>
       <c r="I1072">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="J1072" t="str">
         <v>Active</v>
@@ -37937,10 +37937,10 @@
         <v>1072</v>
       </c>
       <c r="B1073" t="str">
-        <v>FG-400596</v>
+        <v>FG-400595</v>
       </c>
       <c r="C1073" t="str">
-        <v>AGRI ELBOW (160MM)</v>
+        <v>AGRI ELBOW (140MM)</v>
       </c>
       <c r="D1073" t="str">
         <v>AGRI ELBOW</v>
@@ -37952,13 +37952,13 @@
         <v>General</v>
       </c>
       <c r="G1073" t="str">
-        <v>160MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1073" t="str">
         <v>BOX</v>
       </c>
       <c r="I1073">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J1073" t="str">
         <v>Active</v>
@@ -37972,13 +37972,13 @@
         <v>1073</v>
       </c>
       <c r="B1074" t="str">
-        <v>FG-400555</v>
+        <v>FG-400596</v>
       </c>
       <c r="C1074" t="str">
-        <v>AGRI END CAP (40MM)</v>
+        <v>AGRI ELBOW (160MM)</v>
       </c>
       <c r="D1074" t="str">
-        <v>AGRI END CAP</v>
+        <v>AGRI ELBOW</v>
       </c>
       <c r="E1074" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37987,19 +37987,19 @@
         <v>General</v>
       </c>
       <c r="G1074" t="str">
-        <v>40MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1074" t="str">
         <v>BOX</v>
       </c>
       <c r="I1074">
-        <v>800</v>
+        <v>12</v>
       </c>
       <c r="J1074" t="str">
         <v>Active</v>
       </c>
       <c r="K1074" t="str">
-        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
+        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1075">
@@ -38007,10 +38007,10 @@
         <v>1074</v>
       </c>
       <c r="B1075" t="str">
-        <v>FG-400556</v>
+        <v>FG-400555</v>
       </c>
       <c r="C1075" t="str">
-        <v>AGRI END CAP (50MM)</v>
+        <v>AGRI END CAP (40MM)</v>
       </c>
       <c r="D1075" t="str">
         <v>AGRI END CAP</v>
@@ -38022,13 +38022,13 @@
         <v>General</v>
       </c>
       <c r="G1075" t="str">
-        <v>50MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1075" t="str">
         <v>BOX</v>
       </c>
       <c r="I1075">
-        <v>450</v>
+        <v>800</v>
       </c>
       <c r="J1075" t="str">
         <v>Active</v>
@@ -38042,10 +38042,10 @@
         <v>1075</v>
       </c>
       <c r="B1076" t="str">
-        <v>FG-400557</v>
+        <v>FG-400556</v>
       </c>
       <c r="C1076" t="str">
-        <v>AGRI END CAP (63MM)</v>
+        <v>AGRI END CAP (50MM)</v>
       </c>
       <c r="D1076" t="str">
         <v>AGRI END CAP</v>
@@ -38057,13 +38057,13 @@
         <v>General</v>
       </c>
       <c r="G1076" t="str">
-        <v>63MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1076" t="str">
         <v>BOX</v>
       </c>
       <c r="I1076">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="J1076" t="str">
         <v>Active</v>
@@ -38077,10 +38077,10 @@
         <v>1076</v>
       </c>
       <c r="B1077" t="str">
-        <v>FG-400558</v>
+        <v>FG-400557</v>
       </c>
       <c r="C1077" t="str">
-        <v>AGRI END CAP (75MM)</v>
+        <v>AGRI END CAP (63MM)</v>
       </c>
       <c r="D1077" t="str">
         <v>AGRI END CAP</v>
@@ -38092,13 +38092,13 @@
         <v>General</v>
       </c>
       <c r="G1077" t="str">
-        <v>75MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1077" t="str">
         <v>BOX</v>
       </c>
       <c r="I1077">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="J1077" t="str">
         <v>Active</v>
@@ -38112,10 +38112,10 @@
         <v>1077</v>
       </c>
       <c r="B1078" t="str">
-        <v>FG-400559</v>
+        <v>FG-400558</v>
       </c>
       <c r="C1078" t="str">
-        <v>AGRI END CAP (90MM)</v>
+        <v>AGRI END CAP (75MM)</v>
       </c>
       <c r="D1078" t="str">
         <v>AGRI END CAP</v>
@@ -38127,13 +38127,13 @@
         <v>General</v>
       </c>
       <c r="G1078" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1078" t="str">
         <v>BOX</v>
       </c>
       <c r="I1078">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J1078" t="str">
         <v>Active</v>
@@ -38147,10 +38147,10 @@
         <v>1078</v>
       </c>
       <c r="B1079" t="str">
-        <v>FG-400560</v>
+        <v>FG-400559</v>
       </c>
       <c r="C1079" t="str">
-        <v>AGRI END CAP (110MM)</v>
+        <v>AGRI END CAP (90MM)</v>
       </c>
       <c r="D1079" t="str">
         <v>AGRI END CAP</v>
@@ -38162,13 +38162,13 @@
         <v>General</v>
       </c>
       <c r="G1079" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1079" t="str">
         <v>BOX</v>
       </c>
       <c r="I1079">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J1079" t="str">
         <v>Active</v>
@@ -38182,10 +38182,10 @@
         <v>1079</v>
       </c>
       <c r="B1080" t="str">
-        <v>FG-400639</v>
+        <v>FG-400560</v>
       </c>
       <c r="C1080" t="str">
-        <v>AGRI END CAP (140MM 4KG)</v>
+        <v>AGRI END CAP (110MM)</v>
       </c>
       <c r="D1080" t="str">
         <v>AGRI END CAP</v>
@@ -38197,13 +38197,13 @@
         <v>General</v>
       </c>
       <c r="G1080" t="str">
-        <v>140MM 4KG</v>
+        <v>110MM</v>
       </c>
       <c r="H1080" t="str">
         <v>BOX</v>
       </c>
       <c r="I1080">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J1080" t="str">
         <v>Active</v>
@@ -38217,10 +38217,10 @@
         <v>1080</v>
       </c>
       <c r="B1081" t="str">
-        <v>FG-400640</v>
+        <v>FG-400639</v>
       </c>
       <c r="C1081" t="str">
-        <v>AGRI END CAP (160MM 4KG)</v>
+        <v>AGRI END CAP (140MM 4KG)</v>
       </c>
       <c r="D1081" t="str">
         <v>AGRI END CAP</v>
@@ -38232,13 +38232,13 @@
         <v>General</v>
       </c>
       <c r="G1081" t="str">
-        <v>160MM 4KG</v>
+        <v>140MM 4KG</v>
       </c>
       <c r="H1081" t="str">
         <v>BOX</v>
       </c>
       <c r="I1081">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J1081" t="str">
         <v>Active</v>
@@ -38252,13 +38252,13 @@
         <v>1081</v>
       </c>
       <c r="B1082" t="str">
-        <v>FG-400570</v>
+        <v>FG-400640</v>
       </c>
       <c r="C1082" t="str">
-        <v>AGRI LONG BEND (63MM)</v>
+        <v>AGRI END CAP (160MM 4KG)</v>
       </c>
       <c r="D1082" t="str">
-        <v>AGRI LONG BEND</v>
+        <v>AGRI END CAP</v>
       </c>
       <c r="E1082" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -38267,19 +38267,19 @@
         <v>General</v>
       </c>
       <c r="G1082" t="str">
-        <v>63MM</v>
+        <v>160MM 4KG</v>
       </c>
       <c r="H1082" t="str">
         <v>BOX</v>
       </c>
       <c r="I1082">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="J1082" t="str">
         <v>Active</v>
       </c>
       <c r="K1082" t="str">
-        <v>AGRI LONG BEND for agriculture irrigation and piping systems. Available sizes: 63MM, 75MM, 90MM, 110MM.</v>
+        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1083">
@@ -38287,10 +38287,10 @@
         <v>1082</v>
       </c>
       <c r="B1083" t="str">
-        <v>FG-400571</v>
+        <v>FG-400570</v>
       </c>
       <c r="C1083" t="str">
-        <v>AGRI LONG BEND (75MM)</v>
+        <v>AGRI LONG BEND (63MM)</v>
       </c>
       <c r="D1083" t="str">
         <v>AGRI LONG BEND</v>
@@ -38302,13 +38302,13 @@
         <v>General</v>
       </c>
       <c r="G1083" t="str">
-        <v>75MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1083" t="str">
         <v>BOX</v>
       </c>
       <c r="I1083">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J1083" t="str">
         <v>Active</v>
@@ -38322,10 +38322,10 @@
         <v>1083</v>
       </c>
       <c r="B1084" t="str">
-        <v>FG-400572</v>
+        <v>FG-400571</v>
       </c>
       <c r="C1084" t="str">
-        <v>AGRI LONG BEND (90MM)</v>
+        <v>AGRI LONG BEND (75MM)</v>
       </c>
       <c r="D1084" t="str">
         <v>AGRI LONG BEND</v>
@@ -38337,13 +38337,13 @@
         <v>General</v>
       </c>
       <c r="G1084" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1084" t="str">
         <v>BOX</v>
       </c>
       <c r="I1084">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J1084" t="str">
         <v>Active</v>
@@ -38357,10 +38357,10 @@
         <v>1084</v>
       </c>
       <c r="B1085" t="str">
-        <v>FG-400573</v>
+        <v>FG-400572</v>
       </c>
       <c r="C1085" t="str">
-        <v>AGRI LONG BEND (110MM)</v>
+        <v>AGRI LONG BEND (90MM)</v>
       </c>
       <c r="D1085" t="str">
         <v>AGRI LONG BEND</v>
@@ -38372,13 +38372,13 @@
         <v>General</v>
       </c>
       <c r="G1085" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1085" t="str">
         <v>BOX</v>
       </c>
       <c r="I1085">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J1085" t="str">
         <v>Active</v>
@@ -38392,34 +38392,34 @@
         <v>1085</v>
       </c>
       <c r="B1086" t="str">
-        <v>FG-401520</v>
+        <v>FG-400573</v>
       </c>
       <c r="C1086" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
+        <v>AGRI LONG BEND (110MM)</v>
       </c>
       <c r="D1086" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR</v>
+        <v>AGRI LONG BEND</v>
       </c>
       <c r="E1086" t="str">
-        <v>Sprinkler Pipes &amp; Fittings</v>
+        <v>Agriculture Pipes &amp; Fittings</v>
       </c>
       <c r="F1086" t="str">
         <v>General</v>
       </c>
       <c r="G1086" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>110MM</v>
       </c>
       <c r="H1086" t="str">
-        <v>Nos</v>
-      </c>
-      <c r="I1086" t="str">
-        <v>-</v>
+        <v>BOX</v>
+      </c>
+      <c r="I1086">
+        <v>10</v>
       </c>
       <c r="J1086" t="str">
         <v>Active</v>
       </c>
       <c r="K1086" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR for sprinkler irrigation systems.</v>
+        <v>AGRI LONG BEND for agriculture irrigation and piping systems. Available sizes: 63MM, 75MM, 90MM, 110MM.</v>
       </c>
     </row>
     <row r="1087">
@@ -38427,10 +38427,10 @@
         <v>1086</v>
       </c>
       <c r="B1087" t="str">
-        <v>FG-401491</v>
+        <v>FG-401520</v>
       </c>
       <c r="C1087" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (63MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1087" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38442,7 +38442,7 @@
         <v>General</v>
       </c>
       <c r="G1087" t="str">
-        <v>63MM L TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1087" t="str">
         <v>Nos</v>
@@ -38462,10 +38462,10 @@
         <v>1087</v>
       </c>
       <c r="B1088" t="str">
-        <v>FG-401490</v>
+        <v>FG-401491</v>
       </c>
       <c r="C1088" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 2.5 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (63MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1088" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38477,7 +38477,7 @@
         <v>General</v>
       </c>
       <c r="G1088" t="str">
-        <v>75MM C TYPE 2.5 KG</v>
+        <v>63MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1088" t="str">
         <v>Nos</v>
@@ -38497,10 +38497,10 @@
         <v>1088</v>
       </c>
       <c r="B1089" t="str">
-        <v>FG-401492</v>
+        <v>FG-401490</v>
       </c>
       <c r="C1089" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 2.5 KG)</v>
       </c>
       <c r="D1089" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38512,7 +38512,7 @@
         <v>General</v>
       </c>
       <c r="G1089" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>75MM C TYPE 2.5 KG</v>
       </c>
       <c r="H1089" t="str">
         <v>Nos</v>
@@ -38532,10 +38532,10 @@
         <v>1089</v>
       </c>
       <c r="B1090" t="str">
-        <v>FG-401519</v>
+        <v>FG-401492</v>
       </c>
       <c r="C1090" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 2.5 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1090" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38547,7 +38547,7 @@
         <v>General</v>
       </c>
       <c r="G1090" t="str">
-        <v>75MM L TYPE 2.5 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1090" t="str">
         <v>Nos</v>
@@ -38567,10 +38567,10 @@
         <v>1090</v>
       </c>
       <c r="B1091" t="str">
-        <v>FG-401521</v>
+        <v>FG-401519</v>
       </c>
       <c r="C1091" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 2.5 KG)</v>
       </c>
       <c r="D1091" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38582,7 +38582,7 @@
         <v>General</v>
       </c>
       <c r="G1091" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 2.5 KG</v>
       </c>
       <c r="H1091" t="str">
         <v>Nos</v>
@@ -38602,13 +38602,13 @@
         <v>1091</v>
       </c>
       <c r="B1092" t="str">
-        <v>FG-401522</v>
+        <v>FG-401521</v>
       </c>
       <c r="C1092" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1092" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR</v>
+        <v>SPRINKLER ISI PIPE 6 MTR</v>
       </c>
       <c r="E1092" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38629,7 +38629,7 @@
         <v>Active</v>
       </c>
       <c r="K1092" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER ISI PIPE 6 MTR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1093">
@@ -38637,10 +38637,10 @@
         <v>1092</v>
       </c>
       <c r="B1093" t="str">
-        <v>FG-401523</v>
+        <v>FG-401522</v>
       </c>
       <c r="C1093" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1093" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38652,7 +38652,7 @@
         <v>General</v>
       </c>
       <c r="G1093" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1093" t="str">
         <v>Nos</v>
@@ -38672,10 +38672,10 @@
         <v>1093</v>
       </c>
       <c r="B1094" t="str">
-        <v>FG-401866</v>
+        <v>FG-401523</v>
       </c>
       <c r="C1094" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (90MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1094" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38687,7 +38687,7 @@
         <v>General</v>
       </c>
       <c r="G1094" t="str">
-        <v>90MM C TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1094" t="str">
         <v>Nos</v>
@@ -38707,10 +38707,10 @@
         <v>1094</v>
       </c>
       <c r="B1095" t="str">
-        <v>FG-401867</v>
+        <v>FG-401866</v>
       </c>
       <c r="C1095" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (90MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (90MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1095" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38722,7 +38722,7 @@
         <v>General</v>
       </c>
       <c r="G1095" t="str">
-        <v>90MM L TYPE 3.2 KG</v>
+        <v>90MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1095" t="str">
         <v>Nos</v>
@@ -38742,13 +38742,13 @@
         <v>1095</v>
       </c>
       <c r="B1096" t="str">
-        <v>FG-401498</v>
+        <v>FG-401867</v>
       </c>
       <c r="C1096" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (90MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1096" t="str">
-        <v>SPRINKLER SET 6 MTR ISI</v>
+        <v>SPRINKLER NISI PIPE 6 MTR</v>
       </c>
       <c r="E1096" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38757,7 +38757,7 @@
         <v>General</v>
       </c>
       <c r="G1096" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>90MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1096" t="str">
         <v>Nos</v>
@@ -38769,7 +38769,7 @@
         <v>Active</v>
       </c>
       <c r="K1096" t="str">
-        <v>SPRINKLER SET 6 MTR ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER NISI PIPE 6 MTR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1097">
@@ -38777,10 +38777,10 @@
         <v>1096</v>
       </c>
       <c r="B1097" t="str">
-        <v>FG-401499</v>
+        <v>FG-401498</v>
       </c>
       <c r="C1097" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1097" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38792,7 +38792,7 @@
         <v>General</v>
       </c>
       <c r="G1097" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1097" t="str">
         <v>Nos</v>
@@ -38812,10 +38812,10 @@
         <v>1097</v>
       </c>
       <c r="B1098" t="str">
-        <v>FG-401500</v>
+        <v>FG-401499</v>
       </c>
       <c r="C1098" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 2.5 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1098" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38827,7 +38827,7 @@
         <v>General</v>
       </c>
       <c r="G1098" t="str">
-        <v>75MM C TYPE 2.5 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1098" t="str">
         <v>Nos</v>
@@ -38847,10 +38847,10 @@
         <v>1098</v>
       </c>
       <c r="B1099" t="str">
-        <v>FG-401524</v>
+        <v>FG-401500</v>
       </c>
       <c r="C1099" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 2.5 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 2.5 KG)</v>
       </c>
       <c r="D1099" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38862,7 +38862,7 @@
         <v>General</v>
       </c>
       <c r="G1099" t="str">
-        <v>75MM L TYPE 2.5 KG</v>
+        <v>75MM C TYPE 2.5 KG</v>
       </c>
       <c r="H1099" t="str">
         <v>Nos</v>
@@ -38882,10 +38882,10 @@
         <v>1099</v>
       </c>
       <c r="B1100" t="str">
-        <v>FG-401501</v>
+        <v>FG-401524</v>
       </c>
       <c r="C1100" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 2.5 KG)</v>
       </c>
       <c r="D1100" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38897,7 +38897,7 @@
         <v>General</v>
       </c>
       <c r="G1100" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 2.5 KG</v>
       </c>
       <c r="H1100" t="str">
         <v>Nos</v>
@@ -38917,13 +38917,13 @@
         <v>1100</v>
       </c>
       <c r="B1101" t="str">
-        <v>FG-401495</v>
+        <v>FG-401501</v>
       </c>
       <c r="C1101" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1101" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI</v>
+        <v>SPRINKLER SET 6 MTR ISI</v>
       </c>
       <c r="E1101" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38932,7 +38932,7 @@
         <v>General</v>
       </c>
       <c r="G1101" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1101" t="str">
         <v>Nos</v>
@@ -38944,7 +38944,7 @@
         <v>Active</v>
       </c>
       <c r="K1101" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER SET 6 MTR ISI for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1102">
@@ -38952,10 +38952,10 @@
         <v>1101</v>
       </c>
       <c r="B1102" t="str">
-        <v>FG-401496</v>
+        <v>FG-401495</v>
       </c>
       <c r="C1102" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1102" t="str">
         <v>SPRINKLER SET 6 MTR N-ISI</v>
@@ -38967,7 +38967,7 @@
         <v>General</v>
       </c>
       <c r="G1102" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1102" t="str">
         <v>Nos</v>
@@ -38987,10 +38987,10 @@
         <v>1102</v>
       </c>
       <c r="B1103" t="str">
-        <v>FG-401497</v>
+        <v>FG-401496</v>
       </c>
       <c r="C1103" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1103" t="str">
         <v>SPRINKLER SET 6 MTR N-ISI</v>
@@ -39002,7 +39002,7 @@
         <v>General</v>
       </c>
       <c r="G1103" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1103" t="str">
         <v>Nos</v>
@@ -39022,13 +39022,13 @@
         <v>1103</v>
       </c>
       <c r="B1104" t="str">
-        <v>FG-401503</v>
+        <v>FG-401497</v>
       </c>
       <c r="C1104" t="str">
-        <v>SPRINKLER FITTINGS TEE (75MM, C TYPE)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1104" t="str">
-        <v>SPRINKLER FITTINGS TEE</v>
+        <v>SPRINKLER SET 6 MTR N-ISI</v>
       </c>
       <c r="E1104" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39037,7 +39037,7 @@
         <v>General</v>
       </c>
       <c r="G1104" t="str">
-        <v>75MM, C TYPE</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1104" t="str">
         <v>Nos</v>
@@ -39049,7 +39049,7 @@
         <v>Active</v>
       </c>
       <c r="K1104" t="str">
-        <v>SPRINKLER FITTINGS TEE for sprinkler irrigation systems. Available sizes: 75MM, C TYPE, 75MM, L TYPE, 63MM, C TYPE.</v>
+        <v>SPRINKLER SET 6 MTR N-ISI for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1105">
@@ -39057,10 +39057,10 @@
         <v>1104</v>
       </c>
       <c r="B1105" t="str">
-        <v>FG-401511</v>
+        <v>FG-401503</v>
       </c>
       <c r="C1105" t="str">
-        <v>SPRINKLER FITTINGS TEE (75MM, L TYPE)</v>
+        <v>SPRINKLER FITTINGS TEE (75MM, C TYPE)</v>
       </c>
       <c r="D1105" t="str">
         <v>SPRINKLER FITTINGS TEE</v>
@@ -39072,7 +39072,7 @@
         <v>General</v>
       </c>
       <c r="G1105" t="str">
-        <v>75MM, L TYPE</v>
+        <v>75MM, C TYPE</v>
       </c>
       <c r="H1105" t="str">
         <v>Nos</v>
@@ -39092,10 +39092,10 @@
         <v>1105</v>
       </c>
       <c r="B1106" t="str">
-        <v>FG-401526</v>
+        <v>FG-401511</v>
       </c>
       <c r="C1106" t="str">
-        <v>SPRINKLER FITTINGS TEE (63MM, C TYPE)</v>
+        <v>SPRINKLER FITTINGS TEE (75MM, L TYPE)</v>
       </c>
       <c r="D1106" t="str">
         <v>SPRINKLER FITTINGS TEE</v>
@@ -39107,7 +39107,7 @@
         <v>General</v>
       </c>
       <c r="G1106" t="str">
-        <v>63MM, C TYPE</v>
+        <v>75MM, L TYPE</v>
       </c>
       <c r="H1106" t="str">
         <v>Nos</v>
@@ -39127,13 +39127,13 @@
         <v>1106</v>
       </c>
       <c r="B1107" t="str">
-        <v>FG-401504</v>
+        <v>FG-401526</v>
       </c>
       <c r="C1107" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS TEE (63MM, C TYPE)</v>
       </c>
       <c r="D1107" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR</v>
+        <v>SPRINKLER FITTINGS TEE</v>
       </c>
       <c r="E1107" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39142,7 +39142,7 @@
         <v>General</v>
       </c>
       <c r="G1107" t="str">
-        <v>75MM C TYPE</v>
+        <v>63MM, C TYPE</v>
       </c>
       <c r="H1107" t="str">
         <v>Nos</v>
@@ -39154,7 +39154,7 @@
         <v>Active</v>
       </c>
       <c r="K1107" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS TEE for sprinkler irrigation systems. Available sizes: 75MM, C TYPE, 75MM, L TYPE, 63MM, C TYPE.</v>
       </c>
     </row>
     <row r="1108">
@@ -39162,10 +39162,10 @@
         <v>1107</v>
       </c>
       <c r="B1108" t="str">
-        <v>FG-401512</v>
+        <v>FG-401504</v>
       </c>
       <c r="C1108" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (75MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (75MM C TYPE)</v>
       </c>
       <c r="D1108" t="str">
         <v>SPRINKLER FITTINGS ADAPTOR</v>
@@ -39177,7 +39177,7 @@
         <v>General</v>
       </c>
       <c r="G1108" t="str">
-        <v>75MM P TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1108" t="str">
         <v>Nos</v>
@@ -39197,10 +39197,10 @@
         <v>1108</v>
       </c>
       <c r="B1109" t="str">
-        <v>FG-401527</v>
+        <v>FG-401512</v>
       </c>
       <c r="C1109" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (75MM P TYPE)</v>
       </c>
       <c r="D1109" t="str">
         <v>SPRINKLER FITTINGS ADAPTOR</v>
@@ -39212,7 +39212,7 @@
         <v>General</v>
       </c>
       <c r="G1109" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM P TYPE</v>
       </c>
       <c r="H1109" t="str">
         <v>Nos</v>
@@ -39232,13 +39232,13 @@
         <v>1109</v>
       </c>
       <c r="B1110" t="str">
-        <v>FG-401502</v>
+        <v>FG-401527</v>
       </c>
       <c r="C1110" t="str">
-        <v>SPRINKLER FITTINGS BEND (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (63MM C TYPE)</v>
       </c>
       <c r="D1110" t="str">
-        <v>SPRINKLER FITTINGS BEND</v>
+        <v>SPRINKLER FITTINGS ADAPTOR</v>
       </c>
       <c r="E1110" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39247,7 +39247,7 @@
         <v>General</v>
       </c>
       <c r="G1110" t="str">
-        <v>75MM C TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1110" t="str">
         <v>Nos</v>
@@ -39259,7 +39259,7 @@
         <v>Active</v>
       </c>
       <c r="K1110" t="str">
-        <v>SPRINKLER FITTINGS BEND for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS ADAPTOR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1111">
@@ -39267,10 +39267,10 @@
         <v>1110</v>
       </c>
       <c r="B1111" t="str">
-        <v>FG-401510</v>
+        <v>FG-401502</v>
       </c>
       <c r="C1111" t="str">
-        <v>SPRINKLER FITTINGS BEND (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (75MM C TYPE)</v>
       </c>
       <c r="D1111" t="str">
         <v>SPRINKLER FITTINGS BEND</v>
@@ -39282,7 +39282,7 @@
         <v>General</v>
       </c>
       <c r="G1111" t="str">
-        <v>75MM L TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1111" t="str">
         <v>Nos</v>
@@ -39302,10 +39302,10 @@
         <v>1111</v>
       </c>
       <c r="B1112" t="str">
-        <v>FG-401525</v>
+        <v>FG-401510</v>
       </c>
       <c r="C1112" t="str">
-        <v>SPRINKLER FITTINGS BEND (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (75MM L TYPE)</v>
       </c>
       <c r="D1112" t="str">
         <v>SPRINKLER FITTINGS BEND</v>
@@ -39317,7 +39317,7 @@
         <v>General</v>
       </c>
       <c r="G1112" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1112" t="str">
         <v>Nos</v>
@@ -39337,13 +39337,13 @@
         <v>1112</v>
       </c>
       <c r="B1113" t="str">
-        <v>FG-401514</v>
+        <v>FG-401525</v>
       </c>
       <c r="C1113" t="str">
-        <v>SPRINKLER FITTINGS END CAP (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (63MM C TYPE)</v>
       </c>
       <c r="D1113" t="str">
-        <v>SPRINKLER FITTINGS END CAP</v>
+        <v>SPRINKLER FITTINGS BEND</v>
       </c>
       <c r="E1113" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39352,7 +39352,7 @@
         <v>General</v>
       </c>
       <c r="G1113" t="str">
-        <v>75MM L TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1113" t="str">
         <v>Nos</v>
@@ -39364,7 +39364,7 @@
         <v>Active</v>
       </c>
       <c r="K1113" t="str">
-        <v>SPRINKLER FITTINGS END CAP for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS BEND for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1114">
@@ -39372,10 +39372,10 @@
         <v>1113</v>
       </c>
       <c r="B1114" t="str">
-        <v>FG-401506</v>
+        <v>FG-401514</v>
       </c>
       <c r="C1114" t="str">
-        <v>SPRINKLER FITTINGS END CAP (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (75MM L TYPE)</v>
       </c>
       <c r="D1114" t="str">
         <v>SPRINKLER FITTINGS END CAP</v>
@@ -39387,7 +39387,7 @@
         <v>General</v>
       </c>
       <c r="G1114" t="str">
-        <v>75MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1114" t="str">
         <v>Nos</v>
@@ -39407,10 +39407,10 @@
         <v>1114</v>
       </c>
       <c r="B1115" t="str">
-        <v>FG-401529</v>
+        <v>FG-401506</v>
       </c>
       <c r="C1115" t="str">
-        <v>SPRINKLER FITTINGS END CAP (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (75MM C TYPE)</v>
       </c>
       <c r="D1115" t="str">
         <v>SPRINKLER FITTINGS END CAP</v>
@@ -39422,7 +39422,7 @@
         <v>General</v>
       </c>
       <c r="G1115" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1115" t="str">
         <v>Nos</v>
@@ -39442,13 +39442,13 @@
         <v>1115</v>
       </c>
       <c r="B1116" t="str">
-        <v>FG-401517</v>
+        <v>FG-401529</v>
       </c>
       <c r="C1116" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (75MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (63MM C TYPE)</v>
       </c>
       <c r="D1116" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
+        <v>SPRINKLER FITTINGS END CAP</v>
       </c>
       <c r="E1116" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39457,7 +39457,7 @@
         <v>General</v>
       </c>
       <c r="G1116" t="str">
-        <v>75MM P TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1116" t="str">
         <v>Nos</v>
@@ -39469,7 +39469,7 @@
         <v>Active</v>
       </c>
       <c r="K1116" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS END CAP for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1117">
@@ -39477,10 +39477,10 @@
         <v>1116</v>
       </c>
       <c r="B1117" t="str">
-        <v>FG-401518</v>
+        <v>FG-401517</v>
       </c>
       <c r="C1117" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (63MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (75MM P TYPE)</v>
       </c>
       <c r="D1117" t="str">
         <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
@@ -39492,7 +39492,7 @@
         <v>General</v>
       </c>
       <c r="G1117" t="str">
-        <v>63MM P TYPE</v>
+        <v>75MM P TYPE</v>
       </c>
       <c r="H1117" t="str">
         <v>Nos</v>
@@ -39512,13 +39512,13 @@
         <v>1117</v>
       </c>
       <c r="B1118" t="str">
-        <v>FG-401505</v>
+        <v>FG-401518</v>
       </c>
       <c r="C1118" t="str">
-        <v>SPRINKLER FITTINGS PCN (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (63MM P TYPE)</v>
       </c>
       <c r="D1118" t="str">
-        <v>SPRINKLER FITTINGS PCN</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
       </c>
       <c r="E1118" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39527,7 +39527,7 @@
         <v>General</v>
       </c>
       <c r="G1118" t="str">
-        <v>75MM C TYPE</v>
+        <v>63MM P TYPE</v>
       </c>
       <c r="H1118" t="str">
         <v>Nos</v>
@@ -39539,7 +39539,7 @@
         <v>Active</v>
       </c>
       <c r="K1118" t="str">
-        <v>SPRINKLER FITTINGS PCN for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1119">
@@ -39547,10 +39547,10 @@
         <v>1118</v>
       </c>
       <c r="B1119" t="str">
-        <v>FG-401513</v>
+        <v>FG-401505</v>
       </c>
       <c r="C1119" t="str">
-        <v>SPRINKLER FITTINGS PCN (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (75MM C TYPE)</v>
       </c>
       <c r="D1119" t="str">
         <v>SPRINKLER FITTINGS PCN</v>
@@ -39562,7 +39562,7 @@
         <v>General</v>
       </c>
       <c r="G1119" t="str">
-        <v>75MM L TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1119" t="str">
         <v>Nos</v>
@@ -39582,10 +39582,10 @@
         <v>1119</v>
       </c>
       <c r="B1120" t="str">
-        <v>FG-401528</v>
+        <v>FG-401513</v>
       </c>
       <c r="C1120" t="str">
-        <v>SPRINKLER FITTINGS PCN (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (75MM L TYPE)</v>
       </c>
       <c r="D1120" t="str">
         <v>SPRINKLER FITTINGS PCN</v>
@@ -39597,7 +39597,7 @@
         <v>General</v>
       </c>
       <c r="G1120" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1120" t="str">
         <v>Nos</v>
@@ -39617,13 +39617,13 @@
         <v>1120</v>
       </c>
       <c r="B1121" t="str">
-        <v>FG-401507</v>
+        <v>FG-401528</v>
       </c>
       <c r="C1121" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL (20MM)</v>
+        <v>SPRINKLER FITTINGS PCN (63MM C TYPE)</v>
       </c>
       <c r="D1121" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL</v>
+        <v>SPRINKLER FITTINGS PCN</v>
       </c>
       <c r="E1121" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39632,7 +39632,7 @@
         <v>General</v>
       </c>
       <c r="G1121" t="str">
-        <v>20MM</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1121" t="str">
         <v>Nos</v>
@@ -39644,7 +39644,7 @@
         <v>Active</v>
       </c>
       <c r="K1121" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS PCN for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1122">
@@ -39652,13 +39652,13 @@
         <v>1121</v>
       </c>
       <c r="B1122" t="str">
-        <v>FG-401508</v>
+        <v>FG-401507</v>
       </c>
       <c r="C1122" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL (20MM)</v>
       </c>
       <c r="D1122" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL</v>
       </c>
       <c r="E1122" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39667,7 +39667,7 @@
         <v>General</v>
       </c>
       <c r="G1122" t="str">
-        <v>75MM C TYPE</v>
+        <v>20MM</v>
       </c>
       <c r="H1122" t="str">
         <v>Nos</v>
@@ -39679,7 +39679,7 @@
         <v>Active</v>
       </c>
       <c r="K1122" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1123">
@@ -39687,10 +39687,10 @@
         <v>1122</v>
       </c>
       <c r="B1123" t="str">
-        <v>FG-401515</v>
+        <v>FG-401508</v>
       </c>
       <c r="C1123" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE (20MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE (75MM C TYPE)</v>
       </c>
       <c r="D1123" t="str">
         <v>SPRINKLER FITTINGS GI RISER PIPE</v>
@@ -39702,7 +39702,7 @@
         <v>General</v>
       </c>
       <c r="G1123" t="str">
-        <v>20MM L TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1123" t="str">
         <v>Nos</v>
@@ -39722,25 +39722,25 @@
         <v>1123</v>
       </c>
       <c r="B1124" t="str">
-        <v>FG-401742</v>
+        <v>FG-401515</v>
       </c>
       <c r="C1124" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 1)</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE (20MM L TYPE)</v>
       </c>
       <c r="D1124" t="str">
-        <v>ROUND DRIPLINE 12MM ISI</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE</v>
       </c>
       <c r="E1124" t="str">
-        <v>DRIP IRRIGATION SYSTEM</v>
+        <v>Sprinkler Pipes &amp; Fittings</v>
       </c>
       <c r="F1124" t="str">
-        <v>ROUND DRIP ISI</v>
+        <v>General</v>
       </c>
       <c r="G1124" t="str">
-        <v>12-4-30 CLASS 1</v>
+        <v>20MM L TYPE</v>
       </c>
       <c r="H1124" t="str">
-        <v>ROLL</v>
+        <v>Nos</v>
       </c>
       <c r="I1124" t="str">
         <v>-</v>
@@ -39749,7 +39749,7 @@
         <v>Active</v>
       </c>
       <c r="K1124" t="str">
-        <v>ROUND DRIPLINE 12MM ISI certified.</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1125">
@@ -39757,10 +39757,10 @@
         <v>1124</v>
       </c>
       <c r="B1125" t="str">
-        <v>FG-401743</v>
+        <v>FG-401742</v>
       </c>
       <c r="C1125" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 1)</v>
       </c>
       <c r="D1125" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39772,7 +39772,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1125" t="str">
-        <v>12-4-40 CLASS 1</v>
+        <v>12-4-30 CLASS 1</v>
       </c>
       <c r="H1125" t="str">
         <v>ROLL</v>
@@ -39792,10 +39792,10 @@
         <v>1125</v>
       </c>
       <c r="B1126" t="str">
-        <v>FG-401744</v>
+        <v>FG-401743</v>
       </c>
       <c r="C1126" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 1)</v>
       </c>
       <c r="D1126" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39807,7 +39807,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1126" t="str">
-        <v>12-4-50 CLASS 1</v>
+        <v>12-4-40 CLASS 1</v>
       </c>
       <c r="H1126" t="str">
         <v>ROLL</v>
@@ -39827,10 +39827,10 @@
         <v>1126</v>
       </c>
       <c r="B1127" t="str">
-        <v>FG-401751</v>
+        <v>FG-401744</v>
       </c>
       <c r="C1127" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 1)</v>
       </c>
       <c r="D1127" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39842,7 +39842,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1127" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-50 CLASS 1</v>
       </c>
       <c r="H1127" t="str">
         <v>ROLL</v>
@@ -39862,10 +39862,10 @@
         <v>1127</v>
       </c>
       <c r="B1128" t="str">
-        <v>FG-401752</v>
+        <v>FG-401751</v>
       </c>
       <c r="C1128" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1128" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39877,7 +39877,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1128" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1128" t="str">
         <v>ROLL</v>
@@ -39897,10 +39897,10 @@
         <v>1128</v>
       </c>
       <c r="B1129" t="str">
-        <v>FG-401753</v>
+        <v>FG-401752</v>
       </c>
       <c r="C1129" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1129" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39912,7 +39912,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1129" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1129" t="str">
         <v>ROLL</v>
@@ -39932,10 +39932,10 @@
         <v>1129</v>
       </c>
       <c r="B1130" t="str">
-        <v>FG-401754</v>
+        <v>FG-401753</v>
       </c>
       <c r="C1130" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1130" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39947,7 +39947,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1130" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1130" t="str">
         <v>ROLL</v>
@@ -39967,10 +39967,10 @@
         <v>1130</v>
       </c>
       <c r="B1131" t="str">
-        <v>FG-401755</v>
+        <v>FG-401754</v>
       </c>
       <c r="C1131" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1131" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39982,7 +39982,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1131" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1131" t="str">
         <v>ROLL</v>
@@ -40002,10 +40002,10 @@
         <v>1131</v>
       </c>
       <c r="B1132" t="str">
-        <v>FG-401756</v>
+        <v>FG-401755</v>
       </c>
       <c r="C1132" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1132" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -40017,7 +40017,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1132" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1132" t="str">
         <v>ROLL</v>
@@ -40037,13 +40037,13 @@
         <v>1132</v>
       </c>
       <c r="B1133" t="str">
-        <v>FG-401745</v>
+        <v>FG-401756</v>
       </c>
       <c r="C1133" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1133" t="str">
-        <v>ROUND DRIPLINE 16MM ISI</v>
+        <v>ROUND DRIPLINE 12MM ISI</v>
       </c>
       <c r="E1133" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40052,7 +40052,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1133" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1133" t="str">
         <v>ROLL</v>
@@ -40064,7 +40064,7 @@
         <v>Active</v>
       </c>
       <c r="K1133" t="str">
-        <v>ROUND DRIPLINE 16MM ISI certified.</v>
+        <v>ROUND DRIPLINE 12MM ISI certified.</v>
       </c>
     </row>
     <row r="1134">
@@ -40072,10 +40072,10 @@
         <v>1133</v>
       </c>
       <c r="B1134" t="str">
-        <v>FG-401746</v>
+        <v>FG-401745</v>
       </c>
       <c r="C1134" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1134" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40087,7 +40087,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1134" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1134" t="str">
         <v>ROLL</v>
@@ -40107,10 +40107,10 @@
         <v>1134</v>
       </c>
       <c r="B1135" t="str">
-        <v>FG-401747</v>
+        <v>FG-401746</v>
       </c>
       <c r="C1135" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1135" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40122,7 +40122,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1135" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1135" t="str">
         <v>ROLL</v>
@@ -40142,10 +40142,10 @@
         <v>1135</v>
       </c>
       <c r="B1136" t="str">
-        <v>FG-401757</v>
+        <v>FG-401747</v>
       </c>
       <c r="C1136" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1136" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40157,7 +40157,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1136" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1136" t="str">
         <v>ROLL</v>
@@ -40177,10 +40177,10 @@
         <v>1136</v>
       </c>
       <c r="B1137" t="str">
-        <v>FG-401758</v>
+        <v>FG-401757</v>
       </c>
       <c r="C1137" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1137" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40192,7 +40192,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1137" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1137" t="str">
         <v>ROLL</v>
@@ -40212,10 +40212,10 @@
         <v>1137</v>
       </c>
       <c r="B1138" t="str">
-        <v>FG-401759</v>
+        <v>FG-401758</v>
       </c>
       <c r="C1138" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1138" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40227,7 +40227,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1138" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1138" t="str">
         <v>ROLL</v>
@@ -40247,13 +40247,13 @@
         <v>1138</v>
       </c>
       <c r="B1139" t="str">
-        <v>-</v>
+        <v>FG-401759</v>
       </c>
       <c r="C1139" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-30 CLASS-1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1139" t="str">
-        <v>20MM ROUND INLINE PIPE ISI</v>
+        <v>ROUND DRIPLINE 16MM ISI</v>
       </c>
       <c r="E1139" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40262,10 +40262,10 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1139" t="str">
-        <v>20-4-30 CLASS-1</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1139" t="str">
-        <v>MTR</v>
+        <v>ROLL</v>
       </c>
       <c r="I1139" t="str">
         <v>-</v>
@@ -40274,7 +40274,7 @@
         <v>Active</v>
       </c>
       <c r="K1139" t="str">
-        <v>20mm Round Inline Drip Pipe ISI certified.</v>
+        <v>ROUND DRIPLINE 16MM ISI certified.</v>
       </c>
     </row>
     <row r="1140">
@@ -40285,7 +40285,7 @@
         <v>-</v>
       </c>
       <c r="C1140" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-40 CLASS-1)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-30 CLASS-1)</v>
       </c>
       <c r="D1140" t="str">
         <v>20MM ROUND INLINE PIPE ISI</v>
@@ -40297,7 +40297,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1140" t="str">
-        <v>20-4-40 CLASS-1</v>
+        <v>20-4-30 CLASS-1</v>
       </c>
       <c r="H1140" t="str">
         <v>MTR</v>
@@ -40320,7 +40320,7 @@
         <v>-</v>
       </c>
       <c r="C1141" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-50 CLASS-1)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-40 CLASS-1)</v>
       </c>
       <c r="D1141" t="str">
         <v>20MM ROUND INLINE PIPE ISI</v>
@@ -40332,7 +40332,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1141" t="str">
-        <v>20-4-50 CLASS-1</v>
+        <v>20-4-40 CLASS-1</v>
       </c>
       <c r="H1141" t="str">
         <v>MTR</v>
@@ -40352,25 +40352,25 @@
         <v>1141</v>
       </c>
       <c r="B1142" t="str">
-        <v>FG-401763</v>
+        <v>-</v>
       </c>
       <c r="C1142" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-50 CLASS-1)</v>
       </c>
       <c r="D1142" t="str">
-        <v>FLAT DRIPLINE 12MM ISI</v>
+        <v>20MM ROUND INLINE PIPE ISI</v>
       </c>
       <c r="E1142" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1142" t="str">
-        <v>FLAT DRIP ISI</v>
+        <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1142" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>20-4-50 CLASS-1</v>
       </c>
       <c r="H1142" t="str">
-        <v>ROLL</v>
+        <v>MTR</v>
       </c>
       <c r="I1142" t="str">
         <v>-</v>
@@ -40379,7 +40379,7 @@
         <v>Active</v>
       </c>
       <c r="K1142" t="str">
-        <v>FLAT DRIPLINE 12MM ISI certified.</v>
+        <v>20mm Round Inline Drip Pipe ISI certified.</v>
       </c>
     </row>
     <row r="1143">
@@ -40387,10 +40387,10 @@
         <v>1142</v>
       </c>
       <c r="B1143" t="str">
-        <v>FG-401764</v>
+        <v>FG-401763</v>
       </c>
       <c r="C1143" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1143" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40402,7 +40402,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1143" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1143" t="str">
         <v>ROLL</v>
@@ -40422,10 +40422,10 @@
         <v>1143</v>
       </c>
       <c r="B1144" t="str">
-        <v>FG-401765</v>
+        <v>FG-401764</v>
       </c>
       <c r="C1144" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1144" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40437,7 +40437,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1144" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1144" t="str">
         <v>ROLL</v>
@@ -40457,10 +40457,10 @@
         <v>1144</v>
       </c>
       <c r="B1145" t="str">
-        <v>FG-401766</v>
+        <v>FG-401765</v>
       </c>
       <c r="C1145" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1145" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40472,7 +40472,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1145" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1145" t="str">
         <v>ROLL</v>
@@ -40492,10 +40492,10 @@
         <v>1145</v>
       </c>
       <c r="B1146" t="str">
-        <v>FG-401767</v>
+        <v>FG-401766</v>
       </c>
       <c r="C1146" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1146" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40507,7 +40507,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1146" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1146" t="str">
         <v>ROLL</v>
@@ -40527,10 +40527,10 @@
         <v>1146</v>
       </c>
       <c r="B1147" t="str">
-        <v>FG-401768</v>
+        <v>FG-401767</v>
       </c>
       <c r="C1147" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1147" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40542,7 +40542,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1147" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1147" t="str">
         <v>ROLL</v>
@@ -40562,13 +40562,13 @@
         <v>1147</v>
       </c>
       <c r="B1148" t="str">
-        <v>FG-401760</v>
+        <v>FG-401768</v>
       </c>
       <c r="C1148" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1148" t="str">
-        <v>FLAT DRIPLINE 16MM ISI</v>
+        <v>FLAT DRIPLINE 12MM ISI</v>
       </c>
       <c r="E1148" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40577,7 +40577,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1148" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1148" t="str">
         <v>ROLL</v>
@@ -40589,7 +40589,7 @@
         <v>Active</v>
       </c>
       <c r="K1148" t="str">
-        <v>FLAT DRIPLINE 16MM ISI certified.</v>
+        <v>FLAT DRIPLINE 12MM ISI certified.</v>
       </c>
     </row>
     <row r="1149">
@@ -40597,10 +40597,10 @@
         <v>1148</v>
       </c>
       <c r="B1149" t="str">
-        <v>FG-401761</v>
+        <v>FG-401760</v>
       </c>
       <c r="C1149" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1149" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40612,7 +40612,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1149" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1149" t="str">
         <v>ROLL</v>
@@ -40632,10 +40632,10 @@
         <v>1149</v>
       </c>
       <c r="B1150" t="str">
-        <v>FG-401762</v>
+        <v>FG-401761</v>
       </c>
       <c r="C1150" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1150" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40647,7 +40647,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1150" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1150" t="str">
         <v>ROLL</v>
@@ -40667,10 +40667,10 @@
         <v>1150</v>
       </c>
       <c r="B1151" t="str">
-        <v>FG-401769</v>
+        <v>FG-401762</v>
       </c>
       <c r="C1151" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1151" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40682,7 +40682,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1151" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1151" t="str">
         <v>ROLL</v>
@@ -40702,10 +40702,10 @@
         <v>1151</v>
       </c>
       <c r="B1152" t="str">
-        <v>FG-401770</v>
+        <v>FG-401769</v>
       </c>
       <c r="C1152" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1152" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40717,7 +40717,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1152" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1152" t="str">
         <v>ROLL</v>
@@ -40737,10 +40737,10 @@
         <v>1152</v>
       </c>
       <c r="B1153" t="str">
-        <v>FG-401779</v>
+        <v>FG-401770</v>
       </c>
       <c r="C1153" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1153" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40752,7 +40752,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1153" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1153" t="str">
         <v>ROLL</v>
@@ -40772,13 +40772,13 @@
         <v>1153</v>
       </c>
       <c r="B1154" t="str">
-        <v>FG-401771</v>
+        <v>FG-401779</v>
       </c>
       <c r="C1154" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1154" t="str">
-        <v>FLAT DRIPLINE 20MM ISI</v>
+        <v>FLAT DRIPLINE 16MM ISI</v>
       </c>
       <c r="E1154" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40787,7 +40787,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1154" t="str">
-        <v>20-4-30 CLASS 1</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1154" t="str">
         <v>ROLL</v>
@@ -40799,7 +40799,7 @@
         <v>Active</v>
       </c>
       <c r="K1154" t="str">
-        <v>FLAT DRIPLINE 20MM ISI certified.</v>
+        <v>FLAT DRIPLINE 16MM ISI certified.</v>
       </c>
     </row>
     <row r="1155">
@@ -40807,10 +40807,10 @@
         <v>1154</v>
       </c>
       <c r="B1155" t="str">
-        <v>FG-401772</v>
+        <v>FG-401771</v>
       </c>
       <c r="C1155" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-30 CLASS 1)</v>
       </c>
       <c r="D1155" t="str">
         <v>FLAT DRIPLINE 20MM ISI</v>
@@ -40822,7 +40822,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1155" t="str">
-        <v>20-4-40 CLASS 1</v>
+        <v>20-4-30 CLASS 1</v>
       </c>
       <c r="H1155" t="str">
         <v>ROLL</v>
@@ -40842,10 +40842,10 @@
         <v>1155</v>
       </c>
       <c r="B1156" t="str">
-        <v>FG-401773</v>
+        <v>FG-401772</v>
       </c>
       <c r="C1156" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-40 CLASS 1)</v>
       </c>
       <c r="D1156" t="str">
         <v>FLAT DRIPLINE 20MM ISI</v>
@@ -40857,7 +40857,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1156" t="str">
-        <v>20-4-50 CLASS 1</v>
+        <v>20-4-40 CLASS 1</v>
       </c>
       <c r="H1156" t="str">
         <v>ROLL</v>
@@ -40877,25 +40877,25 @@
         <v>1156</v>
       </c>
       <c r="B1157" t="str">
-        <v>-</v>
+        <v>FG-401773</v>
       </c>
       <c r="C1157" t="str">
-        <v>12MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-50 CLASS 1)</v>
       </c>
       <c r="D1157" t="str">
-        <v>12MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>FLAT DRIPLINE 20MM ISI</v>
       </c>
       <c r="E1157" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1157" t="str">
-        <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
+        <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1157" t="str">
-        <v>CLASS-2</v>
+        <v>20-4-50 CLASS 1</v>
       </c>
       <c r="H1157" t="str">
-        <v>MTR</v>
+        <v>ROLL</v>
       </c>
       <c r="I1157" t="str">
         <v>-</v>
@@ -40904,7 +40904,7 @@
         <v>Active</v>
       </c>
       <c r="K1157" t="str">
-        <v>12mm Plain Lateral Online Drip Pipe.</v>
+        <v>FLAT DRIPLINE 20MM ISI certified.</v>
       </c>
     </row>
     <row r="1158">
@@ -40915,10 +40915,10 @@
         <v>-</v>
       </c>
       <c r="C1158" t="str">
-        <v>16MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>12MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1158" t="str">
-        <v>16MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>12MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1158" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40939,7 +40939,7 @@
         <v>Active</v>
       </c>
       <c r="K1158" t="str">
-        <v>16mm Plain Lateral Online Drip Pipe.</v>
+        <v>12mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1159">
@@ -40950,10 +40950,10 @@
         <v>-</v>
       </c>
       <c r="C1159" t="str">
-        <v>20MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>16MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1159" t="str">
-        <v>20MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>16MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1159" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40974,7 +40974,7 @@
         <v>Active</v>
       </c>
       <c r="K1159" t="str">
-        <v>20mm Plain Lateral Online Drip Pipe.</v>
+        <v>16mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1160">
@@ -40985,10 +40985,10 @@
         <v>-</v>
       </c>
       <c r="C1160" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-1)</v>
+        <v>20MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1160" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>20MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1160" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40997,7 +40997,7 @@
         <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1160" t="str">
-        <v>CLASS-1</v>
+        <v>CLASS-2</v>
       </c>
       <c r="H1160" t="str">
         <v>MTR</v>
@@ -41009,7 +41009,7 @@
         <v>Active</v>
       </c>
       <c r="K1160" t="str">
-        <v>32mm Plain Lateral Online Drip Pipe.</v>
+        <v>20mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1161">
@@ -41020,7 +41020,7 @@
         <v>-</v>
       </c>
       <c r="C1161" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-1)</v>
       </c>
       <c r="D1161" t="str">
         <v>32MM PLAIN LATERAL ONLINE PIPE</v>
@@ -41032,7 +41032,7 @@
         <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1161" t="str">
-        <v>CLASS-2</v>
+        <v>CLASS-1</v>
       </c>
       <c r="H1161" t="str">
         <v>MTR</v>
@@ -41052,22 +41052,22 @@
         <v>1161</v>
       </c>
       <c r="B1162" t="str">
-        <v>FG-401763</v>
+        <v>-</v>
       </c>
       <c r="C1162" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 2)</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1162" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1162" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1162" t="str">
-        <v>FLAT DRIP (PEPSI) - INLINE</v>
+        <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1162" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>CLASS-2</v>
       </c>
       <c r="H1162" t="str">
         <v>MTR</v>
@@ -41079,7 +41079,7 @@
         <v>Active</v>
       </c>
       <c r="K1162" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12. Available sizes: 12-4-30 CLASS 2, 12-4-40 CLASS 2, 12-4-50 CLASS 2, 12-4-30 CLASS 3, 12-4-40 CLASS 3, 12-4-50 CLASS 3.</v>
+        <v>32mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1163">
@@ -41087,10 +41087,10 @@
         <v>1162</v>
       </c>
       <c r="B1163" t="str">
-        <v>FG-401764</v>
+        <v>FG-401763</v>
       </c>
       <c r="C1163" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1163" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41102,7 +41102,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1163" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1163" t="str">
         <v>MTR</v>
@@ -41122,10 +41122,10 @@
         <v>1163</v>
       </c>
       <c r="B1164" t="str">
-        <v>FG-401765</v>
+        <v>FG-401764</v>
       </c>
       <c r="C1164" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1164" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41137,7 +41137,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1164" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1164" t="str">
         <v>MTR</v>
@@ -41157,10 +41157,10 @@
         <v>1164</v>
       </c>
       <c r="B1165" t="str">
-        <v>FG-401766</v>
+        <v>FG-401765</v>
       </c>
       <c r="C1165" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1165" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41172,7 +41172,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1165" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1165" t="str">
         <v>MTR</v>
@@ -41192,10 +41192,10 @@
         <v>1165</v>
       </c>
       <c r="B1166" t="str">
-        <v>FG-401767</v>
+        <v>FG-401766</v>
       </c>
       <c r="C1166" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1166" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41207,7 +41207,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1166" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1166" t="str">
         <v>MTR</v>
@@ -41227,10 +41227,10 @@
         <v>1166</v>
       </c>
       <c r="B1167" t="str">
-        <v>FG-401768</v>
+        <v>FG-401767</v>
       </c>
       <c r="C1167" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1167" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41242,7 +41242,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1167" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1167" t="str">
         <v>MTR</v>
@@ -41262,13 +41262,13 @@
         <v>1167</v>
       </c>
       <c r="B1168" t="str">
-        <v>FG-401760</v>
+        <v>FG-401768</v>
       </c>
       <c r="C1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12</v>
       </c>
       <c r="E1168" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -41277,7 +41277,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1168" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1168" t="str">
         <v>MTR</v>
@@ -41289,7 +41289,7 @@
         <v>Active</v>
       </c>
       <c r="K1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16. Available sizes: 16-4-30 CLASS 1, 16-4-40 CLASS 1, 16-4-50 CLASS 1, 16-4-30 CLASS 2, 16-4-40 CLASS 2, 16-4-50 CLASS 2.</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12. Available sizes: 12-4-30 CLASS 2, 12-4-40 CLASS 2, 12-4-50 CLASS 2, 12-4-30 CLASS 3, 12-4-40 CLASS 3, 12-4-50 CLASS 3.</v>
       </c>
     </row>
     <row r="1169">
@@ -41297,10 +41297,10 @@
         <v>1168</v>
       </c>
       <c r="B1169" t="str">
-        <v>FG-401761</v>
+        <v>FG-401760</v>
       </c>
       <c r="C1169" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1169" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41312,7 +41312,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1169" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1169" t="str">
         <v>MTR</v>
@@ -41332,10 +41332,10 @@
         <v>1169</v>
       </c>
       <c r="B1170" t="str">
-        <v>FG-401762</v>
+        <v>FG-401761</v>
       </c>
       <c r="C1170" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1170" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41347,7 +41347,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1170" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1170" t="str">
         <v>MTR</v>
@@ -41367,10 +41367,10 @@
         <v>1170</v>
       </c>
       <c r="B1171" t="str">
-        <v>FG-401769</v>
+        <v>FG-401762</v>
       </c>
       <c r="C1171" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1171" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41382,7 +41382,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1171" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1171" t="str">
         <v>MTR</v>
@@ -41402,10 +41402,10 @@
         <v>1171</v>
       </c>
       <c r="B1172" t="str">
-        <v>FG-401770</v>
+        <v>FG-401769</v>
       </c>
       <c r="C1172" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1172" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41417,7 +41417,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1172" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1172" t="str">
         <v>MTR</v>
@@ -41437,10 +41437,10 @@
         <v>1172</v>
       </c>
       <c r="B1173" t="str">
-        <v>FG-401779</v>
+        <v>FG-401770</v>
       </c>
       <c r="C1173" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1173" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41452,7 +41452,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1173" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1173" t="str">
         <v>MTR</v>
@@ -41472,13 +41472,13 @@
         <v>1173</v>
       </c>
       <c r="B1174" t="str">
-        <v>FG-401771</v>
+        <v>FG-401779</v>
       </c>
       <c r="C1174" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1174" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16</v>
       </c>
       <c r="E1174" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -41487,7 +41487,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1174" t="str">
-        <v>20-4-30 CLASS 1</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1174" t="str">
         <v>MTR</v>
@@ -41499,7 +41499,7 @@
         <v>Active</v>
       </c>
       <c r="K1174" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20. Available sizes: 20-4-30 CLASS 1, 20-4-40 CLASS 1, 20-4-50 CLASS 1.</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16. Available sizes: 16-4-30 CLASS 1, 16-4-40 CLASS 1, 16-4-50 CLASS 1, 16-4-30 CLASS 2, 16-4-40 CLASS 2, 16-4-50 CLASS 2.</v>
       </c>
     </row>
     <row r="1175">
@@ -41507,10 +41507,10 @@
         <v>1174</v>
       </c>
       <c r="B1175" t="str">
-        <v>FG-401772</v>
+        <v>FG-401771</v>
       </c>
       <c r="C1175" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-30 CLASS 1)</v>
       </c>
       <c r="D1175" t="str">
         <v>FLAT DRIPLINE ISI 400MTR 20</v>
@@ -41522,7 +41522,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1175" t="str">
-        <v>20-4-40 CLASS 1</v>
+        <v>20-4-30 CLASS 1</v>
       </c>
       <c r="H1175" t="str">
         <v>MTR</v>
@@ -41542,10 +41542,10 @@
         <v>1175</v>
       </c>
       <c r="B1176" t="str">
-        <v>FG-401773</v>
+        <v>FG-401772</v>
       </c>
       <c r="C1176" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-40 CLASS 1)</v>
       </c>
       <c r="D1176" t="str">
         <v>FLAT DRIPLINE ISI 400MTR 20</v>
@@ -41557,7 +41557,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1176" t="str">
-        <v>20-4-50 CLASS 1</v>
+        <v>20-4-40 CLASS 1</v>
       </c>
       <c r="H1176" t="str">
         <v>MTR</v>
@@ -41577,22 +41577,22 @@
         <v>1176</v>
       </c>
       <c r="B1177" t="str">
-        <v>FG-401066</v>
+        <v>FG-401773</v>
       </c>
       <c r="C1177" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-50 CLASS 1)</v>
       </c>
       <c r="D1177" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20</v>
       </c>
       <c r="E1177" t="str">
-        <v>UPVC CASING PIPES</v>
+        <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1177" t="str">
-        <v>General</v>
+        <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1177" t="str">
-        <v>35MM 1 1/4 Inch</v>
+        <v>20-4-50 CLASS 1</v>
       </c>
       <c r="H1177" t="str">
         <v>MTR</v>
@@ -41604,7 +41604,7 @@
         <v>Active</v>
       </c>
       <c r="K1177" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 40MM 1 1/2 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20. Available sizes: 20-4-30 CLASS 1, 20-4-40 CLASS 1, 20-4-50 CLASS 1.</v>
       </c>
     </row>
     <row r="1178">
@@ -41612,10 +41612,10 @@
         <v>1177</v>
       </c>
       <c r="B1178" t="str">
-        <v>FG-401067</v>
+        <v>FG-401066</v>
       </c>
       <c r="C1178" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (40MM 1 1/2 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
       </c>
       <c r="D1178" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41627,7 +41627,7 @@
         <v>General</v>
       </c>
       <c r="G1178" t="str">
-        <v>40MM 1 1/2 Inch</v>
+        <v>35MM 1 1/4 Inch</v>
       </c>
       <c r="H1178" t="str">
         <v>MTR</v>
@@ -41647,10 +41647,10 @@
         <v>1178</v>
       </c>
       <c r="B1179" t="str">
-        <v>FG-401068</v>
+        <v>FG-401067</v>
       </c>
       <c r="C1179" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (50MM 2 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (40MM 1 1/2 Inch)</v>
       </c>
       <c r="D1179" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41662,7 +41662,7 @@
         <v>General</v>
       </c>
       <c r="G1179" t="str">
-        <v>50MM 2 Inch</v>
+        <v>40MM 1 1/2 Inch</v>
       </c>
       <c r="H1179" t="str">
         <v>MTR</v>
@@ -41682,10 +41682,10 @@
         <v>1179</v>
       </c>
       <c r="B1180" t="str">
-        <v>FG-401069</v>
+        <v>FG-401068</v>
       </c>
       <c r="C1180" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (100MM 4 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (50MM 2 Inch)</v>
       </c>
       <c r="D1180" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41697,7 +41697,7 @@
         <v>General</v>
       </c>
       <c r="G1180" t="str">
-        <v>100MM 4 Inch</v>
+        <v>50MM 2 Inch</v>
       </c>
       <c r="H1180" t="str">
         <v>MTR</v>
@@ -41717,10 +41717,10 @@
         <v>1180</v>
       </c>
       <c r="B1181" t="str">
-        <v>FG-401070</v>
+        <v>FG-401069</v>
       </c>
       <c r="C1181" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (100MM 4 Inch)</v>
       </c>
       <c r="D1181" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41732,7 +41732,7 @@
         <v>General</v>
       </c>
       <c r="G1181" t="str">
-        <v>125MM 5 Inch</v>
+        <v>100MM 4 Inch</v>
       </c>
       <c r="H1181" t="str">
         <v>MTR</v>
@@ -41752,10 +41752,10 @@
         <v>1181</v>
       </c>
       <c r="B1182" t="str">
-        <v>FG-401071</v>
+        <v>FG-401070</v>
       </c>
       <c r="C1182" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1182" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41767,7 +41767,7 @@
         <v>General</v>
       </c>
       <c r="G1182" t="str">
-        <v>150MM 6 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1182" t="str">
         <v>MTR</v>
@@ -41787,10 +41787,10 @@
         <v>1182</v>
       </c>
       <c r="B1183" t="str">
-        <v>FG-401072</v>
+        <v>FG-401071</v>
       </c>
       <c r="C1183" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1183" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41802,7 +41802,7 @@
         <v>General</v>
       </c>
       <c r="G1183" t="str">
-        <v>175MM 7 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1183" t="str">
         <v>MTR</v>
@@ -41822,10 +41822,10 @@
         <v>1183</v>
       </c>
       <c r="B1184" t="str">
-        <v>FG-401073</v>
+        <v>FG-401072</v>
       </c>
       <c r="C1184" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1184" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41837,7 +41837,7 @@
         <v>General</v>
       </c>
       <c r="G1184" t="str">
-        <v>200MM 8 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1184" t="str">
         <v>MTR</v>
@@ -41857,13 +41857,13 @@
         <v>1184</v>
       </c>
       <c r="B1185" t="str">
-        <v>FG-401074</v>
+        <v>FG-401073</v>
       </c>
       <c r="C1185" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1185" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
       </c>
       <c r="E1185" t="str">
         <v>UPVC CASING PIPES</v>
@@ -41872,7 +41872,7 @@
         <v>General</v>
       </c>
       <c r="G1185" t="str">
-        <v>125MM 5 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1185" t="str">
         <v>MTR</v>
@@ -41884,7 +41884,7 @@
         <v>Active</v>
       </c>
       <c r="K1185" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 40MM 1 1/2 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1186">
@@ -41892,10 +41892,10 @@
         <v>1185</v>
       </c>
       <c r="B1186" t="str">
-        <v>FG-401075</v>
+        <v>FG-401074</v>
       </c>
       <c r="C1186" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1186" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41907,7 +41907,7 @@
         <v>General</v>
       </c>
       <c r="G1186" t="str">
-        <v>150MM 6 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1186" t="str">
         <v>MTR</v>
@@ -41927,10 +41927,10 @@
         <v>1186</v>
       </c>
       <c r="B1187" t="str">
-        <v>FG-401076</v>
+        <v>FG-401075</v>
       </c>
       <c r="C1187" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1187" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41942,7 +41942,7 @@
         <v>General</v>
       </c>
       <c r="G1187" t="str">
-        <v>175MM 7 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1187" t="str">
         <v>MTR</v>
@@ -41962,10 +41962,10 @@
         <v>1187</v>
       </c>
       <c r="B1188" t="str">
-        <v>FG-401077</v>
+        <v>FG-401076</v>
       </c>
       <c r="C1188" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1188" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41977,7 +41977,7 @@
         <v>General</v>
       </c>
       <c r="G1188" t="str">
-        <v>200MM 8 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1188" t="str">
         <v>MTR</v>
@@ -41997,13 +41997,13 @@
         <v>1188</v>
       </c>
       <c r="B1189" t="str">
-        <v>FG-401149</v>
+        <v>FG-401077</v>
       </c>
       <c r="C1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M (140MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
       </c>
       <c r="E1189" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42012,7 +42012,7 @@
         <v>General</v>
       </c>
       <c r="G1189" t="str">
-        <v>140MM 5 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1189" t="str">
         <v>MTR</v>
@@ -42024,7 +42024,7 @@
         <v>Active</v>
       </c>
       <c r="K1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M. Available sizes: 140MM 5 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1190">
@@ -42032,13 +42032,13 @@
         <v>1189</v>
       </c>
       <c r="B1190" t="str">
-        <v>FG-401150</v>
+        <v>FG-401149</v>
       </c>
       <c r="C1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M (140MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M (140MM 5 Inch)</v>
       </c>
       <c r="D1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M</v>
       </c>
       <c r="E1190" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42059,7 +42059,7 @@
         <v>Active</v>
       </c>
       <c r="K1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M. Available sizes: 140MM 5 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M. Available sizes: 140MM 5 Inch.</v>
       </c>
     </row>
     <row r="1191">
@@ -42067,13 +42067,13 @@
         <v>1190</v>
       </c>
       <c r="B1191" t="str">
-        <v>FG-401078</v>
+        <v>FG-401150</v>
       </c>
       <c r="C1191" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M (140MM 5 Inch)</v>
       </c>
       <c r="D1191" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M</v>
       </c>
       <c r="E1191" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42082,7 +42082,7 @@
         <v>General</v>
       </c>
       <c r="G1191" t="str">
-        <v>125MM 5 Inch</v>
+        <v>140MM 5 Inch</v>
       </c>
       <c r="H1191" t="str">
         <v>MTR</v>
@@ -42094,7 +42094,7 @@
         <v>Active</v>
       </c>
       <c r="K1191" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M. Available sizes: 140MM 5 Inch.</v>
       </c>
     </row>
     <row r="1192">
@@ -42102,10 +42102,10 @@
         <v>1191</v>
       </c>
       <c r="B1192" t="str">
-        <v>FG-401079</v>
+        <v>FG-401078</v>
       </c>
       <c r="C1192" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1192" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42117,7 +42117,7 @@
         <v>General</v>
       </c>
       <c r="G1192" t="str">
-        <v>150MM 6 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1192" t="str">
         <v>MTR</v>
@@ -42137,10 +42137,10 @@
         <v>1192</v>
       </c>
       <c r="B1193" t="str">
-        <v>FG-401080</v>
+        <v>FG-401079</v>
       </c>
       <c r="C1193" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1193" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42152,7 +42152,7 @@
         <v>General</v>
       </c>
       <c r="G1193" t="str">
-        <v>175MM 7 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1193" t="str">
         <v>MTR</v>
@@ -42172,10 +42172,10 @@
         <v>1193</v>
       </c>
       <c r="B1194" t="str">
-        <v>FG-401081</v>
+        <v>FG-401080</v>
       </c>
       <c r="C1194" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1194" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42187,7 +42187,7 @@
         <v>General</v>
       </c>
       <c r="G1194" t="str">
-        <v>200MM 8 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1194" t="str">
         <v>MTR</v>
@@ -42207,13 +42207,13 @@
         <v>1194</v>
       </c>
       <c r="B1195" t="str">
-        <v>FG-401119</v>
+        <v>FG-401081</v>
       </c>
       <c r="C1195" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1195" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
       </c>
       <c r="E1195" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42222,7 +42222,7 @@
         <v>General</v>
       </c>
       <c r="G1195" t="str">
-        <v>35MM 1 1/4 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1195" t="str">
         <v>MTR</v>
@@ -42234,7 +42234,7 @@
         <v>Active</v>
       </c>
       <c r="K1195" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1196">
@@ -42242,10 +42242,10 @@
         <v>1195</v>
       </c>
       <c r="B1196" t="str">
-        <v>FG-401121</v>
+        <v>FG-401119</v>
       </c>
       <c r="C1196" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (50MM 2 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
       </c>
       <c r="D1196" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42257,7 +42257,7 @@
         <v>General</v>
       </c>
       <c r="G1196" t="str">
-        <v>50MM 2 Inch</v>
+        <v>35MM 1 1/4 Inch</v>
       </c>
       <c r="H1196" t="str">
         <v>MTR</v>
@@ -42277,10 +42277,10 @@
         <v>1196</v>
       </c>
       <c r="B1197" t="str">
-        <v>FG-401122</v>
+        <v>FG-401121</v>
       </c>
       <c r="C1197" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (100MM 4 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (50MM 2 Inch)</v>
       </c>
       <c r="D1197" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42292,7 +42292,7 @@
         <v>General</v>
       </c>
       <c r="G1197" t="str">
-        <v>100MM 4 Inch</v>
+        <v>50MM 2 Inch</v>
       </c>
       <c r="H1197" t="str">
         <v>MTR</v>
@@ -42312,10 +42312,10 @@
         <v>1197</v>
       </c>
       <c r="B1198" t="str">
-        <v>FG-401123</v>
+        <v>FG-401122</v>
       </c>
       <c r="C1198" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (100MM 4 Inch)</v>
       </c>
       <c r="D1198" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42327,7 +42327,7 @@
         <v>General</v>
       </c>
       <c r="G1198" t="str">
-        <v>125MM 5 Inch</v>
+        <v>100MM 4 Inch</v>
       </c>
       <c r="H1198" t="str">
         <v>MTR</v>
@@ -42347,10 +42347,10 @@
         <v>1198</v>
       </c>
       <c r="B1199" t="str">
-        <v>FG-401124</v>
+        <v>FG-401123</v>
       </c>
       <c r="C1199" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1199" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42362,7 +42362,7 @@
         <v>General</v>
       </c>
       <c r="G1199" t="str">
-        <v>150MM 6 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1199" t="str">
         <v>MTR</v>
@@ -42382,10 +42382,10 @@
         <v>1199</v>
       </c>
       <c r="B1200" t="str">
-        <v>FG-401125</v>
+        <v>FG-401124</v>
       </c>
       <c r="C1200" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1200" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42397,7 +42397,7 @@
         <v>General</v>
       </c>
       <c r="G1200" t="str">
-        <v>175MM 7 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1200" t="str">
         <v>MTR</v>
@@ -42417,10 +42417,10 @@
         <v>1200</v>
       </c>
       <c r="B1201" t="str">
-        <v>FG-401126</v>
+        <v>FG-401125</v>
       </c>
       <c r="C1201" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1201" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42432,7 +42432,7 @@
         <v>General</v>
       </c>
       <c r="G1201" t="str">
-        <v>200MM 8 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1201" t="str">
         <v>MTR</v>
@@ -42452,22 +42452,22 @@
         <v>1201</v>
       </c>
       <c r="B1202" t="str">
-        <v>FG-401166</v>
+        <v>FG-401126</v>
       </c>
       <c r="C1202" t="str">
-        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG COUPLER TYPE)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1202" t="str">
-        <v>COLOUMN PIPE ECO V4</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
       </c>
       <c r="E1202" t="str">
-        <v>UPVC COLUMN PIPES</v>
+        <v>UPVC CASING PIPES</v>
       </c>
       <c r="F1202" t="str">
         <v>General</v>
       </c>
       <c r="G1202" t="str">
-        <v>33MM 12.5KG COUPLER TYPE</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1202" t="str">
         <v>MTR</v>
@@ -42479,7 +42479,7 @@
         <v>Active</v>
       </c>
       <c r="K1202" t="str">
-        <v>COLOUMN PIPE ECO V4 for submersible pump systems.</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1203">
@@ -42487,10 +42487,10 @@
         <v>1202</v>
       </c>
       <c r="B1203" t="str">
-        <v>FG-401162</v>
+        <v>FG-401166</v>
       </c>
       <c r="C1203" t="str">
-        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG BELL END TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1203" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42502,7 +42502,7 @@
         <v>General</v>
       </c>
       <c r="G1203" t="str">
-        <v>33MM 12.5KG BELL END TYPE</v>
+        <v>33MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1203" t="str">
         <v>MTR</v>
@@ -42522,10 +42522,10 @@
         <v>1203</v>
       </c>
       <c r="B1204" t="str">
-        <v>FG-401165</v>
+        <v>FG-401162</v>
       </c>
       <c r="C1204" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 10KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG BELL END TYPE)</v>
       </c>
       <c r="D1204" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42537,7 +42537,7 @@
         <v>General</v>
       </c>
       <c r="G1204" t="str">
-        <v>42MM 10KG COUPLER TYPE</v>
+        <v>33MM 12.5KG BELL END TYPE</v>
       </c>
       <c r="H1204" t="str">
         <v>MTR</v>
@@ -42557,10 +42557,10 @@
         <v>1204</v>
       </c>
       <c r="B1205" t="str">
-        <v>FG-401167</v>
+        <v>FG-401165</v>
       </c>
       <c r="C1205" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 10KG COUPLER TYPE)</v>
       </c>
       <c r="D1205" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42572,7 +42572,7 @@
         <v>General</v>
       </c>
       <c r="G1205" t="str">
-        <v>42MM 12.5KG COUPLER TYPE</v>
+        <v>42MM 10KG COUPLER TYPE</v>
       </c>
       <c r="H1205" t="str">
         <v>MTR</v>
@@ -42592,10 +42592,10 @@
         <v>1205</v>
       </c>
       <c r="B1206" t="str">
-        <v>FG-401163</v>
+        <v>FG-401167</v>
       </c>
       <c r="C1206" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG BELL END TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1206" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42607,7 +42607,7 @@
         <v>General</v>
       </c>
       <c r="G1206" t="str">
-        <v>42MM 12.5KG BELL END TYPE</v>
+        <v>42MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1206" t="str">
         <v>MTR</v>
@@ -42627,10 +42627,10 @@
         <v>1206</v>
       </c>
       <c r="B1207" t="str">
-        <v>FG-401164</v>
+        <v>FG-401163</v>
       </c>
       <c r="C1207" t="str">
-        <v>COLOUMN PIPE ECO V4 (48MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG BELL END TYPE)</v>
       </c>
       <c r="D1207" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42642,7 +42642,7 @@
         <v>General</v>
       </c>
       <c r="G1207" t="str">
-        <v>48MM 12.5KG COUPLER TYPE</v>
+        <v>42MM 12.5KG BELL END TYPE</v>
       </c>
       <c r="H1207" t="str">
         <v>MTR</v>
@@ -42662,10 +42662,10 @@
         <v>1207</v>
       </c>
       <c r="B1208" t="str">
-        <v>FG-401168</v>
+        <v>FG-401164</v>
       </c>
       <c r="C1208" t="str">
-        <v>COLOUMN PIPE ECO V4 (60MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (48MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1208" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42677,7 +42677,7 @@
         <v>General</v>
       </c>
       <c r="G1208" t="str">
-        <v>60MM 12.5KG COUPLER TYPE</v>
+        <v>48MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1208" t="str">
         <v>MTR</v>
@@ -42697,13 +42697,13 @@
         <v>1208</v>
       </c>
       <c r="B1209" t="str">
-        <v>FG-401175</v>
+        <v>FG-401168</v>
       </c>
       <c r="C1209" t="str">
-        <v>COLOUMN PIPE MEDIUM (33MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (60MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1209" t="str">
-        <v>COLOUMN PIPE MEDIUM</v>
+        <v>COLOUMN PIPE ECO V4</v>
       </c>
       <c r="E1209" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -42712,7 +42712,7 @@
         <v>General</v>
       </c>
       <c r="G1209" t="str">
-        <v>33MM 18KG COUPLER TYPE</v>
+        <v>60MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1209" t="str">
         <v>MTR</v>
@@ -42724,7 +42724,7 @@
         <v>Active</v>
       </c>
       <c r="K1209" t="str">
-        <v>COLOUMN PIPE MEDIUM for submersible pump systems.</v>
+        <v>COLOUMN PIPE ECO V4 for submersible pump systems.</v>
       </c>
     </row>
     <row r="1210">
@@ -42732,10 +42732,10 @@
         <v>1209</v>
       </c>
       <c r="B1210" t="str">
-        <v>FG-401177</v>
+        <v>FG-401175</v>
       </c>
       <c r="C1210" t="str">
-        <v>COLOUMN PIPE MEDIUM (42MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (33MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1210" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42747,7 +42747,7 @@
         <v>General</v>
       </c>
       <c r="G1210" t="str">
-        <v>42MM 18KG COUPLER TYPE</v>
+        <v>33MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1210" t="str">
         <v>MTR</v>
@@ -42767,10 +42767,10 @@
         <v>1210</v>
       </c>
       <c r="B1211" t="str">
-        <v>FG-401176</v>
+        <v>FG-401177</v>
       </c>
       <c r="C1211" t="str">
-        <v>COLOUMN PIPE MEDIUM (48MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (42MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1211" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42782,7 +42782,7 @@
         <v>General</v>
       </c>
       <c r="G1211" t="str">
-        <v>48MM 18KG COUPLER TYPE</v>
+        <v>42MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1211" t="str">
         <v>MTR</v>
@@ -42802,10 +42802,10 @@
         <v>1211</v>
       </c>
       <c r="B1212" t="str">
-        <v>FG-401178</v>
+        <v>FG-401176</v>
       </c>
       <c r="C1212" t="str">
-        <v>COLOUMN PIPE MEDIUM (60MM 15KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (48MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1212" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42817,7 +42817,7 @@
         <v>General</v>
       </c>
       <c r="G1212" t="str">
-        <v>60MM 15KG COUPLER TYPE</v>
+        <v>48MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1212" t="str">
         <v>MTR</v>
@@ -42837,10 +42837,10 @@
         <v>1212</v>
       </c>
       <c r="B1213" t="str">
-        <v>FG-401180</v>
+        <v>FG-401178</v>
       </c>
       <c r="C1213" t="str">
-        <v>COLOUMN PIPE MEDIUM (75MM 10KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (60MM 15KG COUPLER TYPE)</v>
       </c>
       <c r="D1213" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42852,7 +42852,7 @@
         <v>General</v>
       </c>
       <c r="G1213" t="str">
-        <v>75MM 10KG COUPLER TYPE</v>
+        <v>60MM 15KG COUPLER TYPE</v>
       </c>
       <c r="H1213" t="str">
         <v>MTR</v>
@@ -42872,13 +42872,13 @@
         <v>1213</v>
       </c>
       <c r="B1214" t="str">
-        <v>FG-401169</v>
+        <v>FG-401180</v>
       </c>
       <c r="C1214" t="str">
-        <v>COLOUMN PIPE STANDARD (33MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (75MM 10KG COUPLER TYPE)</v>
       </c>
       <c r="D1214" t="str">
-        <v>COLOUMN PIPE STANDARD</v>
+        <v>COLOUMN PIPE MEDIUM</v>
       </c>
       <c r="E1214" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -42887,7 +42887,7 @@
         <v>General</v>
       </c>
       <c r="G1214" t="str">
-        <v>33MM 25KG COUPLER TYPE</v>
+        <v>75MM 10KG COUPLER TYPE</v>
       </c>
       <c r="H1214" t="str">
         <v>MTR</v>
@@ -42899,7 +42899,7 @@
         <v>Active</v>
       </c>
       <c r="K1214" t="str">
-        <v>COLOUMN PIPE STANDARD for submersible pump systems.</v>
+        <v>COLOUMN PIPE MEDIUM for submersible pump systems.</v>
       </c>
     </row>
     <row r="1215">
@@ -42907,10 +42907,10 @@
         <v>1214</v>
       </c>
       <c r="B1215" t="str">
-        <v>FG-401171</v>
+        <v>FG-401169</v>
       </c>
       <c r="C1215" t="str">
-        <v>COLOUMN PIPE STANDARD (42MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (33MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1215" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42922,7 +42922,7 @@
         <v>General</v>
       </c>
       <c r="G1215" t="str">
-        <v>42MM 25KG COUPLER TYPE</v>
+        <v>33MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1215" t="str">
         <v>MTR</v>
@@ -42942,10 +42942,10 @@
         <v>1215</v>
       </c>
       <c r="B1216" t="str">
-        <v>FG-401170</v>
+        <v>FG-401171</v>
       </c>
       <c r="C1216" t="str">
-        <v>COLOUMN PIPE STANDARD (48MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (42MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1216" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42957,7 +42957,7 @@
         <v>General</v>
       </c>
       <c r="G1216" t="str">
-        <v>48MM 25KG COUPLER TYPE</v>
+        <v>42MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1216" t="str">
         <v>MTR</v>
@@ -42977,10 +42977,10 @@
         <v>1216</v>
       </c>
       <c r="B1217" t="str">
-        <v>FG-401172</v>
+        <v>FG-401170</v>
       </c>
       <c r="C1217" t="str">
-        <v>COLOUMN PIPE STANDARD (60MM 20KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (48MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1217" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42992,7 +42992,7 @@
         <v>General</v>
       </c>
       <c r="G1217" t="str">
-        <v>60MM 20KG COUPLER TYPE</v>
+        <v>48MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1217" t="str">
         <v>MTR</v>
@@ -43012,10 +43012,10 @@
         <v>1217</v>
       </c>
       <c r="B1218" t="str">
-        <v>FG-401174</v>
+        <v>FG-401172</v>
       </c>
       <c r="C1218" t="str">
-        <v>COLOUMN PIPE STANDARD (75MM 20KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (60MM 20KG COUPLER TYPE)</v>
       </c>
       <c r="D1218" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -43027,7 +43027,7 @@
         <v>General</v>
       </c>
       <c r="G1218" t="str">
-        <v>75MM 20KG COUPLER TYPE</v>
+        <v>60MM 20KG COUPLER TYPE</v>
       </c>
       <c r="H1218" t="str">
         <v>MTR</v>
@@ -43047,13 +43047,13 @@
         <v>1218</v>
       </c>
       <c r="B1219" t="str">
-        <v>-</v>
+        <v>FG-401174</v>
       </c>
       <c r="C1219" t="str">
-        <v>3M STANDARD PLUS PIPE (60MM 25 COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (75MM 20KG COUPLER TYPE)</v>
       </c>
       <c r="D1219" t="str">
-        <v>3M STANDARD PLUS PIPE</v>
+        <v>COLOUMN PIPE STANDARD</v>
       </c>
       <c r="E1219" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43062,7 +43062,7 @@
         <v>General</v>
       </c>
       <c r="G1219" t="str">
-        <v>60MM 25 COUPLER TYPE</v>
+        <v>75MM 20KG COUPLER TYPE</v>
       </c>
       <c r="H1219" t="str">
         <v>MTR</v>
@@ -43074,7 +43074,7 @@
         <v>Active</v>
       </c>
       <c r="K1219" t="str">
-        <v>3M Standard Plus UPVC Column Pipe for submersible pump systems.</v>
+        <v>COLOUMN PIPE STANDARD for submersible pump systems.</v>
       </c>
     </row>
     <row r="1220">
@@ -43082,13 +43082,13 @@
         <v>1219</v>
       </c>
       <c r="B1220" t="str">
-        <v>FG-401182</v>
+        <v>-</v>
       </c>
       <c r="C1220" t="str">
-        <v>COLOUMN PIPE HEAVY (42MM 30KG COUPLER TYPE)</v>
+        <v>3M STANDARD PLUS PIPE (60MM 25 COUPLER TYPE)</v>
       </c>
       <c r="D1220" t="str">
-        <v>COLOUMN PIPE HEAVY</v>
+        <v>3M STANDARD PLUS PIPE</v>
       </c>
       <c r="E1220" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43097,7 +43097,7 @@
         <v>General</v>
       </c>
       <c r="G1220" t="str">
-        <v>42MM 30KG COUPLER TYPE</v>
+        <v>60MM 25 COUPLER TYPE</v>
       </c>
       <c r="H1220" t="str">
         <v>MTR</v>
@@ -43109,7 +43109,7 @@
         <v>Active</v>
       </c>
       <c r="K1220" t="str">
-        <v>COLOUMN PIPE HEAVY for submersible pump systems.</v>
+        <v>3M Standard Plus UPVC Column Pipe for submersible pump systems.</v>
       </c>
     </row>
     <row r="1221">
@@ -43117,10 +43117,10 @@
         <v>1220</v>
       </c>
       <c r="B1221" t="str">
-        <v>FG-401181</v>
+        <v>FG-401182</v>
       </c>
       <c r="C1221" t="str">
-        <v>COLOUMN PIPE HEAVY (48MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (42MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1221" t="str">
         <v>COLOUMN PIPE HEAVY</v>
@@ -43132,7 +43132,7 @@
         <v>General</v>
       </c>
       <c r="G1221" t="str">
-        <v>48MM 30KG COUPLER TYPE</v>
+        <v>42MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1221" t="str">
         <v>MTR</v>
@@ -43152,10 +43152,10 @@
         <v>1221</v>
       </c>
       <c r="B1222" t="str">
-        <v>FG-401183</v>
+        <v>FG-401181</v>
       </c>
       <c r="C1222" t="str">
-        <v>COLOUMN PIPE HEAVY (60MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (48MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1222" t="str">
         <v>COLOUMN PIPE HEAVY</v>
@@ -43167,7 +43167,7 @@
         <v>General</v>
       </c>
       <c r="G1222" t="str">
-        <v>60MM 30KG COUPLER TYPE</v>
+        <v>48MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1222" t="str">
         <v>MTR</v>
@@ -43187,13 +43187,13 @@
         <v>1222</v>
       </c>
       <c r="B1223" t="str">
-        <v>FG-401179</v>
+        <v>FG-401183</v>
       </c>
       <c r="C1223" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS (60MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (60MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1223" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS</v>
+        <v>COLOUMN PIPE HEAVY</v>
       </c>
       <c r="E1223" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43202,7 +43202,7 @@
         <v>General</v>
       </c>
       <c r="G1223" t="str">
-        <v>60MM 18KG COUPLER TYPE</v>
+        <v>60MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1223" t="str">
         <v>MTR</v>
@@ -43214,7 +43214,7 @@
         <v>Active</v>
       </c>
       <c r="K1223" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS for submersible pump systems.</v>
+        <v>COLOUMN PIPE HEAVY for submersible pump systems.</v>
       </c>
     </row>
     <row r="1224">
@@ -43222,34 +43222,34 @@
         <v>1223</v>
       </c>
       <c r="B1224" t="str">
-        <v>FG-401569</v>
+        <v>FG-401179</v>
       </c>
       <c r="C1224" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA (15 Inch)</v>
+        <v>COLOUMN PIPE MEDIUM PLUS (60MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1224" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA</v>
+        <v>COLOUMN PIPE MEDIUM PLUS</v>
       </c>
       <c r="E1224" t="str">
-        <v>HOUSEHOLD PRODUCTS</v>
+        <v>UPVC COLUMN PIPES</v>
       </c>
       <c r="F1224" t="str">
         <v>General</v>
       </c>
       <c r="G1224" t="str">
-        <v>15 Inch</v>
+        <v>60MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1224" t="str">
-        <v>BAGS</v>
+        <v>MTR</v>
       </c>
       <c r="I1224" t="str">
-        <v>75</v>
+        <v>-</v>
       </c>
       <c r="J1224" t="str">
         <v>Active</v>
       </c>
       <c r="K1224" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA high durability ghamela.</v>
+        <v>COLOUMN PIPE MEDIUM PLUS for submersible pump systems.</v>
       </c>
     </row>
     <row r="1225">
@@ -43257,13 +43257,13 @@
         <v>1224</v>
       </c>
       <c r="B1225" t="str">
-        <v>FG-401570</v>
+        <v>FG-401569</v>
       </c>
       <c r="C1225" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI (15 Inch)</v>
+        <v>CONSTRUCTION GHAMELA SHIVA (15 Inch)</v>
       </c>
       <c r="D1225" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI</v>
+        <v>CONSTRUCTION GHAMELA SHIVA</v>
       </c>
       <c r="E1225" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43284,7 +43284,7 @@
         <v>Active</v>
       </c>
       <c r="K1225" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI high durability ghamela.</v>
+        <v>CONSTRUCTION GHAMELA SHIVA high durability ghamela.</v>
       </c>
     </row>
     <row r="1226">
@@ -43292,13 +43292,13 @@
         <v>1225</v>
       </c>
       <c r="B1226" t="str">
-        <v>FG-401571</v>
+        <v>FG-401570</v>
       </c>
       <c r="C1226" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA (16 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA GOURI (15 Inch)</v>
       </c>
       <c r="D1226" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA</v>
+        <v>MULTIPURPOSE GHAMELA GOURI</v>
       </c>
       <c r="E1226" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43307,19 +43307,19 @@
         <v>General</v>
       </c>
       <c r="G1226" t="str">
-        <v>16 Inch</v>
+        <v>15 Inch</v>
       </c>
       <c r="H1226" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1226" t="str">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="J1226" t="str">
         <v>Active</v>
       </c>
       <c r="K1226" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA GOURI high durability ghamela.</v>
       </c>
     </row>
     <row r="1227">
@@ -43327,13 +43327,13 @@
         <v>1226</v>
       </c>
       <c r="B1227" t="str">
-        <v>FG-401573</v>
+        <v>FG-401571</v>
       </c>
       <c r="C1227" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV (18 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA (16 Inch)</v>
       </c>
       <c r="D1227" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA</v>
       </c>
       <c r="E1227" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43342,19 +43342,19 @@
         <v>General</v>
       </c>
       <c r="G1227" t="str">
-        <v>18 Inch</v>
+        <v>16 Inch</v>
       </c>
       <c r="H1227" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1227" t="str">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J1227" t="str">
         <v>Active</v>
       </c>
       <c r="K1227" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA high durability ghamela.</v>
       </c>
     </row>
     <row r="1228">
@@ -43362,13 +43362,13 @@
         <v>1227</v>
       </c>
       <c r="B1228" t="str">
-        <v>FG-401574</v>
+        <v>FG-401573</v>
       </c>
       <c r="C1228" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET (20 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV (18 Inch)</v>
       </c>
       <c r="D1228" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV</v>
       </c>
       <c r="E1228" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43377,19 +43377,19 @@
         <v>General</v>
       </c>
       <c r="G1228" t="str">
-        <v>20 Inch</v>
+        <v>18 Inch</v>
       </c>
       <c r="H1228" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1228" t="str">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J1228" t="str">
         <v>Active</v>
       </c>
       <c r="K1228" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV high durability ghamela.</v>
       </c>
     </row>
     <row r="1229">
@@ -43397,13 +43397,13 @@
         <v>1228</v>
       </c>
       <c r="B1229" t="str">
-        <v>FG-401572</v>
+        <v>FG-401574</v>
       </c>
       <c r="C1229" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI (17 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET (20 Inch)</v>
       </c>
       <c r="D1229" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET</v>
       </c>
       <c r="E1229" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43412,19 +43412,19 @@
         <v>General</v>
       </c>
       <c r="G1229" t="str">
-        <v>17 Inch</v>
+        <v>20 Inch</v>
       </c>
       <c r="H1229" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1229" t="str">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J1229" t="str">
         <v>Active</v>
       </c>
       <c r="K1229" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET high durability ghamela.</v>
       </c>
     </row>
     <row r="1230">
@@ -43432,13 +43432,13 @@
         <v>1229</v>
       </c>
       <c r="B1230" t="str">
-        <v>FG-401575</v>
+        <v>FG-401572</v>
       </c>
       <c r="C1230" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ (22 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI (17 Inch)</v>
       </c>
       <c r="D1230" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI</v>
       </c>
       <c r="E1230" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43447,19 +43447,19 @@
         <v>General</v>
       </c>
       <c r="G1230" t="str">
-        <v>22 Inch</v>
+        <v>17 Inch</v>
       </c>
       <c r="H1230" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1230" t="str">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J1230" t="str">
         <v>Active</v>
       </c>
       <c r="K1230" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI high durability ghamela.</v>
       </c>
     </row>
     <row r="1231">
@@ -43467,13 +43467,13 @@
         <v>1230</v>
       </c>
       <c r="B1231" t="str">
-        <v>FG-401578</v>
+        <v>FG-401575</v>
       </c>
       <c r="C1231" t="str">
-        <v>AQUA PLAST GHAMELA 16 (16 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ (22 Inch)</v>
       </c>
       <c r="D1231" t="str">
-        <v>AQUA PLAST GHAMELA 16</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ</v>
       </c>
       <c r="E1231" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43482,19 +43482,19 @@
         <v>General</v>
       </c>
       <c r="G1231" t="str">
-        <v>16 Inch</v>
+        <v>22 Inch</v>
       </c>
       <c r="H1231" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1231" t="str">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J1231" t="str">
         <v>Active</v>
       </c>
       <c r="K1231" t="str">
-        <v>AQUA PLAST GHAMELA 16 high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ high durability ghamela.</v>
       </c>
     </row>
     <row r="1232">
@@ -43502,13 +43502,13 @@
         <v>1231</v>
       </c>
       <c r="B1232" t="str">
-        <v>FG-401579</v>
+        <v>FG-401578</v>
       </c>
       <c r="C1232" t="str">
-        <v>AQUA PLAST GHAMELA 17 (17 Inch)</v>
+        <v>AQUA PLAST GHAMELA 16 (16 Inch)</v>
       </c>
       <c r="D1232" t="str">
-        <v>AQUA PLAST GHAMELA 17</v>
+        <v>AQUA PLAST GHAMELA 16</v>
       </c>
       <c r="E1232" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43517,7 +43517,7 @@
         <v>General</v>
       </c>
       <c r="G1232" t="str">
-        <v>17 Inch</v>
+        <v>16 Inch</v>
       </c>
       <c r="H1232" t="str">
         <v>BAGS</v>
@@ -43529,7 +43529,7 @@
         <v>Active</v>
       </c>
       <c r="K1232" t="str">
-        <v>AQUA PLAST GHAMELA 17 high durability ghamela.</v>
+        <v>AQUA PLAST GHAMELA 16 high durability ghamela.</v>
       </c>
     </row>
     <row r="1233">
@@ -43537,34 +43537,34 @@
         <v>1232</v>
       </c>
       <c r="B1233" t="str">
-        <v>FG-401364</v>
+        <v>FG-401579</v>
       </c>
       <c r="C1233" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1/2 15MM)</v>
+        <v>AQUA PLAST GHAMELA 17 (17 Inch)</v>
       </c>
       <c r="D1233" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE</v>
+        <v>AQUA PLAST GHAMELA 17</v>
       </c>
       <c r="E1233" t="str">
-        <v>Garden, Braided &amp; LDPE Pipes</v>
+        <v>HOUSEHOLD PRODUCTS</v>
       </c>
       <c r="F1233" t="str">
         <v>General</v>
       </c>
       <c r="G1233" t="str">
-        <v>1/2 15MM</v>
+        <v>17 Inch</v>
       </c>
       <c r="H1233" t="str">
-        <v>BDL</v>
+        <v>BAGS</v>
       </c>
       <c r="I1233" t="str">
-        <v>-</v>
+        <v>60</v>
       </c>
       <c r="J1233" t="str">
         <v>Active</v>
       </c>
       <c r="K1233" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE. Available sizes: 1/2 15MM, 3/4 20MM, 1 25MM, 1 1/4 32MM.</v>
+        <v>AQUA PLAST GHAMELA 17 high durability ghamela.</v>
       </c>
     </row>
     <row r="1234">
@@ -43572,10 +43572,10 @@
         <v>1233</v>
       </c>
       <c r="B1234" t="str">
-        <v>FG-401365</v>
+        <v>FG-401364</v>
       </c>
       <c r="C1234" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (3/4 20MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1/2 15MM)</v>
       </c>
       <c r="D1234" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43587,7 +43587,7 @@
         <v>General</v>
       </c>
       <c r="G1234" t="str">
-        <v>3/4 20MM</v>
+        <v>1/2 15MM</v>
       </c>
       <c r="H1234" t="str">
         <v>BDL</v>
@@ -43607,10 +43607,10 @@
         <v>1234</v>
       </c>
       <c r="B1235" t="str">
-        <v>FG-401366</v>
+        <v>FG-401365</v>
       </c>
       <c r="C1235" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1 25MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (3/4 20MM)</v>
       </c>
       <c r="D1235" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43622,7 +43622,7 @@
         <v>General</v>
       </c>
       <c r="G1235" t="str">
-        <v>1 25MM</v>
+        <v>3/4 20MM</v>
       </c>
       <c r="H1235" t="str">
         <v>BDL</v>
@@ -43642,10 +43642,10 @@
         <v>1235</v>
       </c>
       <c r="B1236" t="str">
-        <v>FG-401367</v>
+        <v>FG-401366</v>
       </c>
       <c r="C1236" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1 1/4 32MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1 25MM)</v>
       </c>
       <c r="D1236" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43657,7 +43657,7 @@
         <v>General</v>
       </c>
       <c r="G1236" t="str">
-        <v>1 1/4 32MM</v>
+        <v>1 25MM</v>
       </c>
       <c r="H1236" t="str">
         <v>BDL</v>
@@ -43677,13 +43677,13 @@
         <v>1236</v>
       </c>
       <c r="B1237" t="str">
-        <v>FG-401370</v>
+        <v>FG-401367</v>
       </c>
       <c r="C1237" t="str">
-        <v>GAP-ORA BRAIDED PIPE (15MM 1/2)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1 1/4 32MM)</v>
       </c>
       <c r="D1237" t="str">
-        <v>GAP-ORA BRAIDED PIPE</v>
+        <v>GAP-ORA FLOW GARDEN PIPE</v>
       </c>
       <c r="E1237" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43692,7 +43692,7 @@
         <v>General</v>
       </c>
       <c r="G1237" t="str">
-        <v>15MM 1/2</v>
+        <v>1 1/4 32MM</v>
       </c>
       <c r="H1237" t="str">
         <v>BDL</v>
@@ -43704,7 +43704,7 @@
         <v>Active</v>
       </c>
       <c r="K1237" t="str">
-        <v>GAP-ORA BRAIDED PIPE.</v>
+        <v>GAP-ORA FLOW GARDEN PIPE. Available sizes: 1/2 15MM, 3/4 20MM, 1 25MM, 1 1/4 32MM.</v>
       </c>
     </row>
     <row r="1238">
@@ -43712,10 +43712,10 @@
         <v>1237</v>
       </c>
       <c r="B1238" t="str">
-        <v>FG-401371</v>
+        <v>FG-401370</v>
       </c>
       <c r="C1238" t="str">
-        <v>GAP-ORA BRAIDED PIPE (20MM 3/4)</v>
+        <v>GAP-ORA BRAIDED PIPE (15MM 1/2)</v>
       </c>
       <c r="D1238" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43727,7 +43727,7 @@
         <v>General</v>
       </c>
       <c r="G1238" t="str">
-        <v>20MM 3/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1238" t="str">
         <v>BDL</v>
@@ -43747,10 +43747,10 @@
         <v>1238</v>
       </c>
       <c r="B1239" t="str">
-        <v>FG-401372</v>
+        <v>FG-401371</v>
       </c>
       <c r="C1239" t="str">
-        <v>GAP-ORA BRAIDED PIPE (25MM 1)</v>
+        <v>GAP-ORA BRAIDED PIPE (20MM 3/4)</v>
       </c>
       <c r="D1239" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43762,7 +43762,7 @@
         <v>General</v>
       </c>
       <c r="G1239" t="str">
-        <v>25MM 1</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1239" t="str">
         <v>BDL</v>
@@ -43782,10 +43782,10 @@
         <v>1239</v>
       </c>
       <c r="B1240" t="str">
-        <v>FG-401373</v>
+        <v>FG-401372</v>
       </c>
       <c r="C1240" t="str">
-        <v>GAP-ORA BRAIDED PIPE (32MM 1 1/4)</v>
+        <v>GAP-ORA BRAIDED PIPE (25MM 1)</v>
       </c>
       <c r="D1240" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43797,7 +43797,7 @@
         <v>General</v>
       </c>
       <c r="G1240" t="str">
-        <v>32MM 1 1/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1240" t="str">
         <v>BDL</v>
@@ -43817,13 +43817,13 @@
         <v>1240</v>
       </c>
       <c r="B1241" t="str">
-        <v>FG-401355</v>
+        <v>FG-401373</v>
       </c>
       <c r="C1241" t="str">
-        <v>GARDEN FOAM PIPES (15MM 1/2)</v>
+        <v>GAP-ORA BRAIDED PIPE (32MM 1 1/4)</v>
       </c>
       <c r="D1241" t="str">
-        <v>GARDEN FOAM PIPES</v>
+        <v>GAP-ORA BRAIDED PIPE</v>
       </c>
       <c r="E1241" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43832,7 +43832,7 @@
         <v>General</v>
       </c>
       <c r="G1241" t="str">
-        <v>15MM 1/2</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1241" t="str">
         <v>BDL</v>
@@ -43844,7 +43844,7 @@
         <v>Active</v>
       </c>
       <c r="K1241" t="str">
-        <v>GARDEN FOAM PIPES.</v>
+        <v>GAP-ORA BRAIDED PIPE.</v>
       </c>
     </row>
     <row r="1242">
@@ -43852,10 +43852,10 @@
         <v>1241</v>
       </c>
       <c r="B1242" t="str">
-        <v>FG-401356</v>
+        <v>FG-401355</v>
       </c>
       <c r="C1242" t="str">
-        <v>GARDEN FOAM PIPES (20MM 3/4)</v>
+        <v>GARDEN FOAM PIPES (15MM 1/2)</v>
       </c>
       <c r="D1242" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43867,7 +43867,7 @@
         <v>General</v>
       </c>
       <c r="G1242" t="str">
-        <v>20MM 3/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1242" t="str">
         <v>BDL</v>
@@ -43887,10 +43887,10 @@
         <v>1242</v>
       </c>
       <c r="B1243" t="str">
-        <v>FG-401369</v>
+        <v>FG-401356</v>
       </c>
       <c r="C1243" t="str">
-        <v>GARDEN FOAM PIPES (20MM 3/4 20MTR)</v>
+        <v>GARDEN FOAM PIPES (20MM 3/4)</v>
       </c>
       <c r="D1243" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43902,7 +43902,7 @@
         <v>General</v>
       </c>
       <c r="G1243" t="str">
-        <v>20MM 3/4 20MTR</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1243" t="str">
         <v>BDL</v>
@@ -43922,10 +43922,10 @@
         <v>1243</v>
       </c>
       <c r="B1244" t="str">
-        <v>FG-401357</v>
+        <v>FG-401369</v>
       </c>
       <c r="C1244" t="str">
-        <v>GARDEN FOAM PIPES (25MM 1)</v>
+        <v>GARDEN FOAM PIPES (20MM 3/4 20MTR)</v>
       </c>
       <c r="D1244" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43937,7 +43937,7 @@
         <v>General</v>
       </c>
       <c r="G1244" t="str">
-        <v>25MM 1</v>
+        <v>20MM 3/4 20MTR</v>
       </c>
       <c r="H1244" t="str">
         <v>BDL</v>
@@ -43957,10 +43957,10 @@
         <v>1244</v>
       </c>
       <c r="B1245" t="str">
-        <v>FG-401358</v>
+        <v>FG-401357</v>
       </c>
       <c r="C1245" t="str">
-        <v>GARDEN FOAM PIPES (32MM 1 1/4)</v>
+        <v>GARDEN FOAM PIPES (25MM 1)</v>
       </c>
       <c r="D1245" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43972,7 +43972,7 @@
         <v>General</v>
       </c>
       <c r="G1245" t="str">
-        <v>32MM 1 1/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1245" t="str">
         <v>BDL</v>
@@ -43992,13 +43992,13 @@
         <v>1245</v>
       </c>
       <c r="B1246" t="str">
-        <v>FG-401344</v>
+        <v>FG-401358</v>
       </c>
       <c r="C1246" t="str">
-        <v>BRAIDED PIPE (15MM 1/2)</v>
+        <v>GARDEN FOAM PIPES (32MM 1 1/4)</v>
       </c>
       <c r="D1246" t="str">
-        <v>BRAIDED PIPE</v>
+        <v>GARDEN FOAM PIPES</v>
       </c>
       <c r="E1246" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44007,7 +44007,7 @@
         <v>General</v>
       </c>
       <c r="G1246" t="str">
-        <v>15MM 1/2</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1246" t="str">
         <v>BDL</v>
@@ -44019,7 +44019,7 @@
         <v>Active</v>
       </c>
       <c r="K1246" t="str">
-        <v>Reinforced Braided Garden Pipe.</v>
+        <v>GARDEN FOAM PIPES.</v>
       </c>
     </row>
     <row r="1247">
@@ -44027,10 +44027,10 @@
         <v>1246</v>
       </c>
       <c r="B1247" t="str">
-        <v>FG-401345</v>
+        <v>FG-401344</v>
       </c>
       <c r="C1247" t="str">
-        <v>BRAIDED PIPE (20MM 3/4)</v>
+        <v>BRAIDED PIPE (15MM 1/2)</v>
       </c>
       <c r="D1247" t="str">
         <v>BRAIDED PIPE</v>
@@ -44042,7 +44042,7 @@
         <v>General</v>
       </c>
       <c r="G1247" t="str">
-        <v>20MM 3/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1247" t="str">
         <v>BDL</v>
@@ -44062,10 +44062,10 @@
         <v>1247</v>
       </c>
       <c r="B1248" t="str">
-        <v>FG-401346</v>
+        <v>FG-401345</v>
       </c>
       <c r="C1248" t="str">
-        <v>BRAIDED PIPE (25MM 1)</v>
+        <v>BRAIDED PIPE (20MM 3/4)</v>
       </c>
       <c r="D1248" t="str">
         <v>BRAIDED PIPE</v>
@@ -44077,7 +44077,7 @@
         <v>General</v>
       </c>
       <c r="G1248" t="str">
-        <v>25MM 1</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1248" t="str">
         <v>BDL</v>
@@ -44097,10 +44097,10 @@
         <v>1248</v>
       </c>
       <c r="B1249" t="str">
-        <v>FG-401363</v>
+        <v>FG-401346</v>
       </c>
       <c r="C1249" t="str">
-        <v>BRAIDED PIPE (32MM 1 1/4)</v>
+        <v>BRAIDED PIPE (25MM 1)</v>
       </c>
       <c r="D1249" t="str">
         <v>BRAIDED PIPE</v>
@@ -44112,7 +44112,7 @@
         <v>General</v>
       </c>
       <c r="G1249" t="str">
-        <v>32MM 1 1/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1249" t="str">
         <v>BDL</v>
@@ -44132,13 +44132,13 @@
         <v>1249</v>
       </c>
       <c r="B1250" t="str">
-        <v>FG-401374</v>
+        <v>FG-401363</v>
       </c>
       <c r="C1250" t="str">
-        <v>LEVEL PIPE (6MM)</v>
+        <v>BRAIDED PIPE (32MM 1 1/4)</v>
       </c>
       <c r="D1250" t="str">
-        <v>LEVEL PIPE</v>
+        <v>BRAIDED PIPE</v>
       </c>
       <c r="E1250" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44147,7 +44147,7 @@
         <v>General</v>
       </c>
       <c r="G1250" t="str">
-        <v>6MM</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1250" t="str">
         <v>BDL</v>
@@ -44159,7 +44159,7 @@
         <v>Active</v>
       </c>
       <c r="K1250" t="str">
-        <v>Transparent Level Pipe for construction &amp; garden work.</v>
+        <v>Reinforced Braided Garden Pipe.</v>
       </c>
     </row>
     <row r="1251">
@@ -44167,13 +44167,13 @@
         <v>1250</v>
       </c>
       <c r="B1251" t="str">
-        <v>FG-401340</v>
+        <v>FG-401374</v>
       </c>
       <c r="C1251" t="str">
-        <v>GARDEN PIPES SUPER FLOW (15MM 1/2)</v>
+        <v>LEVEL PIPE (6MM)</v>
       </c>
       <c r="D1251" t="str">
-        <v>GARDEN PIPES SUPER FLOW</v>
+        <v>LEVEL PIPE</v>
       </c>
       <c r="E1251" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44182,7 +44182,7 @@
         <v>General</v>
       </c>
       <c r="G1251" t="str">
-        <v>15MM 1/2</v>
+        <v>6MM</v>
       </c>
       <c r="H1251" t="str">
         <v>BDL</v>
@@ -44194,7 +44194,7 @@
         <v>Active</v>
       </c>
       <c r="K1251" t="str">
-        <v>GARDEN PIPES SUPER FLOW.</v>
+        <v>Transparent Level Pipe for construction &amp; garden work.</v>
       </c>
     </row>
     <row r="1252">
@@ -44202,10 +44202,10 @@
         <v>1251</v>
       </c>
       <c r="B1252" t="str">
-        <v>FG-401341</v>
+        <v>FG-401340</v>
       </c>
       <c r="C1252" t="str">
-        <v>GARDEN PIPES SUPER FLOW (20MM 3/4)</v>
+        <v>GARDEN PIPES SUPER FLOW (15MM 1/2)</v>
       </c>
       <c r="D1252" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44217,7 +44217,7 @@
         <v>General</v>
       </c>
       <c r="G1252" t="str">
-        <v>20MM 3/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1252" t="str">
         <v>BDL</v>
@@ -44237,10 +44237,10 @@
         <v>1252</v>
       </c>
       <c r="B1253" t="str">
-        <v>FG-401652</v>
+        <v>FG-401341</v>
       </c>
       <c r="C1253" t="str">
-        <v>GARDEN PIPES SUPER FLOW (20MM 3/4 15MTR)</v>
+        <v>GARDEN PIPES SUPER FLOW (20MM 3/4)</v>
       </c>
       <c r="D1253" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44252,7 +44252,7 @@
         <v>General</v>
       </c>
       <c r="G1253" t="str">
-        <v>20MM 3/4 15MTR</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1253" t="str">
         <v>BDL</v>
@@ -44272,10 +44272,10 @@
         <v>1253</v>
       </c>
       <c r="B1254" t="str">
-        <v>FG-401342</v>
+        <v>FG-401652</v>
       </c>
       <c r="C1254" t="str">
-        <v>GARDEN PIPES SUPER FLOW (25MM 1)</v>
+        <v>GARDEN PIPES SUPER FLOW (20MM 3/4 15MTR)</v>
       </c>
       <c r="D1254" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44287,7 +44287,7 @@
         <v>General</v>
       </c>
       <c r="G1254" t="str">
-        <v>25MM 1</v>
+        <v>20MM 3/4 15MTR</v>
       </c>
       <c r="H1254" t="str">
         <v>BDL</v>
@@ -44307,10 +44307,10 @@
         <v>1254</v>
       </c>
       <c r="B1255" t="str">
-        <v>FG-401343</v>
+        <v>FG-401342</v>
       </c>
       <c r="C1255" t="str">
-        <v>GARDEN PIPES SUPER FLOW (32MM 1 1/4)</v>
+        <v>GARDEN PIPES SUPER FLOW (25MM 1)</v>
       </c>
       <c r="D1255" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44322,7 +44322,7 @@
         <v>General</v>
       </c>
       <c r="G1255" t="str">
-        <v>32MM 1 1/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1255" t="str">
         <v>BDL</v>
@@ -44342,10 +44342,10 @@
         <v>1255</v>
       </c>
       <c r="B1256" t="str">
-        <v>FG-401627</v>
+        <v>FG-401343</v>
       </c>
       <c r="C1256" t="str">
-        <v>GARDEN PIPES SUPER FLOW (40MM 1 1/2)</v>
+        <v>GARDEN PIPES SUPER FLOW (32MM 1 1/4)</v>
       </c>
       <c r="D1256" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44357,7 +44357,7 @@
         <v>General</v>
       </c>
       <c r="G1256" t="str">
-        <v>40MM 1 1/2</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1256" t="str">
         <v>BDL</v>
@@ -44377,34 +44377,34 @@
         <v>1256</v>
       </c>
       <c r="B1257" t="str">
-        <v>FG-401552</v>
+        <v>FG-401627</v>
       </c>
       <c r="C1257" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2 inch)</v>
+        <v>GARDEN PIPES SUPER FLOW (40MM 1 1/2)</v>
       </c>
       <c r="D1257" t="str">
-        <v>EDGE SERIES SHORT BODY TAP</v>
+        <v>GARDEN PIPES SUPER FLOW</v>
       </c>
       <c r="E1257" t="str">
-        <v>FAUCETS</v>
+        <v>Garden, Braided &amp; LDPE Pipes</v>
       </c>
       <c r="F1257" t="str">
         <v>General</v>
       </c>
       <c r="G1257" t="str">
-        <v>1/2 inch</v>
+        <v>40MM 1 1/2</v>
       </c>
       <c r="H1257" t="str">
-        <v>NOS</v>
-      </c>
-      <c r="I1257">
-        <v>20</v>
+        <v>BDL</v>
+      </c>
+      <c r="I1257" t="str">
+        <v>-</v>
       </c>
       <c r="J1257" t="str">
         <v>Active</v>
       </c>
       <c r="K1257" t="str">
-        <v>EDGE SERIES SHORT BODY TAP high quality faucet.</v>
+        <v>GARDEN PIPES SUPER FLOW.</v>
       </c>
     </row>
     <row r="1258">
@@ -44415,7 +44415,7 @@
         <v>FG-401552</v>
       </c>
       <c r="C1258" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2 inch)</v>
       </c>
       <c r="D1258" t="str">
         <v>EDGE SERIES SHORT BODY TAP</v>
@@ -44427,7 +44427,7 @@
         <v>General</v>
       </c>
       <c r="G1258" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1258" t="str">
         <v>NOS</v>
@@ -44450,7 +44450,7 @@
         <v>FG-401552</v>
       </c>
       <c r="C1259" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2")</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2)</v>
       </c>
       <c r="D1259" t="str">
         <v>EDGE SERIES SHORT BODY TAP</v>
@@ -44462,7 +44462,7 @@
         <v>General</v>
       </c>
       <c r="G1259" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1259" t="str">
         <v>NOS</v>
@@ -44482,13 +44482,13 @@
         <v>1259</v>
       </c>
       <c r="B1260" t="str">
-        <v>FG-401551</v>
+        <v>FG-401552</v>
       </c>
       <c r="C1260" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2 inch)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2")</v>
       </c>
       <c r="D1260" t="str">
-        <v>EDGE SERIES LONG BODY TAP</v>
+        <v>EDGE SERIES SHORT BODY TAP</v>
       </c>
       <c r="E1260" t="str">
         <v>FAUCETS</v>
@@ -44497,19 +44497,19 @@
         <v>General</v>
       </c>
       <c r="G1260" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1260" t="str">
         <v>NOS</v>
       </c>
       <c r="I1260">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J1260" t="str">
         <v>Active</v>
       </c>
       <c r="K1260" t="str">
-        <v>EDGE SERIES LONG BODY TAP high quality faucet.</v>
+        <v>EDGE SERIES SHORT BODY TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1261">
@@ -44520,7 +44520,7 @@
         <v>FG-401551</v>
       </c>
       <c r="C1261" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2)</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2 inch)</v>
       </c>
       <c r="D1261" t="str">
         <v>EDGE SERIES LONG BODY TAP</v>
@@ -44532,7 +44532,7 @@
         <v>General</v>
       </c>
       <c r="G1261" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1261" t="str">
         <v>NOS</v>
@@ -44555,7 +44555,7 @@
         <v>FG-401551</v>
       </c>
       <c r="C1262" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2")</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2)</v>
       </c>
       <c r="D1262" t="str">
         <v>EDGE SERIES LONG BODY TAP</v>
@@ -44567,7 +44567,7 @@
         <v>General</v>
       </c>
       <c r="G1262" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1262" t="str">
         <v>NOS</v>
@@ -44587,13 +44587,13 @@
         <v>1262</v>
       </c>
       <c r="B1263" t="str">
-        <v>FG-401549</v>
+        <v>FG-401551</v>
       </c>
       <c r="C1263" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2 inch)</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2")</v>
       </c>
       <c r="D1263" t="str">
-        <v>EDGE SERIES SWAN NECK</v>
+        <v>EDGE SERIES LONG BODY TAP</v>
       </c>
       <c r="E1263" t="str">
         <v>FAUCETS</v>
@@ -44602,19 +44602,19 @@
         <v>General</v>
       </c>
       <c r="G1263" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1263" t="str">
         <v>NOS</v>
       </c>
       <c r="I1263">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J1263" t="str">
         <v>Active</v>
       </c>
       <c r="K1263" t="str">
-        <v>EDGE SERIES SWAN NECK high quality faucet.</v>
+        <v>EDGE SERIES LONG BODY TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1264">
@@ -44625,7 +44625,7 @@
         <v>FG-401549</v>
       </c>
       <c r="C1264" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2)</v>
+        <v>EDGE SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1264" t="str">
         <v>EDGE SERIES SWAN NECK</v>
@@ -44637,7 +44637,7 @@
         <v>General</v>
       </c>
       <c r="G1264" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1264" t="str">
         <v>NOS</v>
@@ -44660,7 +44660,7 @@
         <v>FG-401549</v>
       </c>
       <c r="C1265" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2")</v>
+        <v>EDGE SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1265" t="str">
         <v>EDGE SERIES SWAN NECK</v>
@@ -44672,7 +44672,7 @@
         <v>General</v>
       </c>
       <c r="G1265" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1265" t="str">
         <v>NOS</v>
@@ -44692,13 +44692,13 @@
         <v>1265</v>
       </c>
       <c r="B1266" t="str">
-        <v>FG-401546</v>
+        <v>FG-401549</v>
       </c>
       <c r="C1266" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>EDGE SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1266" t="str">
-        <v>EDGE SERIES ANGULAR VALVE</v>
+        <v>EDGE SERIES SWAN NECK</v>
       </c>
       <c r="E1266" t="str">
         <v>FAUCETS</v>
@@ -44707,19 +44707,19 @@
         <v>General</v>
       </c>
       <c r="G1266" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1266" t="str">
         <v>NOS</v>
       </c>
       <c r="I1266">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J1266" t="str">
         <v>Active</v>
       </c>
       <c r="K1266" t="str">
-        <v>EDGE SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>EDGE SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1267">
@@ -44730,7 +44730,7 @@
         <v>FG-401546</v>
       </c>
       <c r="C1267" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2)</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1267" t="str">
         <v>EDGE SERIES ANGULAR VALVE</v>
@@ -44742,7 +44742,7 @@
         <v>General</v>
       </c>
       <c r="G1267" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1267" t="str">
         <v>NOS</v>
@@ -44765,7 +44765,7 @@
         <v>FG-401546</v>
       </c>
       <c r="C1268" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2")</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1268" t="str">
         <v>EDGE SERIES ANGULAR VALVE</v>
@@ -44777,7 +44777,7 @@
         <v>General</v>
       </c>
       <c r="G1268" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1268" t="str">
         <v>NOS</v>
@@ -44797,13 +44797,13 @@
         <v>1268</v>
       </c>
       <c r="B1269" t="str">
-        <v>FG-401547</v>
+        <v>FG-401546</v>
       </c>
       <c r="C1269" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2 inch)</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1269" t="str">
-        <v>EDGE SERIES PILLAR TAP</v>
+        <v>EDGE SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1269" t="str">
         <v>FAUCETS</v>
@@ -44812,19 +44812,19 @@
         <v>General</v>
       </c>
       <c r="G1269" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1269" t="str">
         <v>NOS</v>
       </c>
       <c r="I1269">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J1269" t="str">
         <v>Active</v>
       </c>
       <c r="K1269" t="str">
-        <v>EDGE SERIES PILLAR TAP high quality faucet.</v>
+        <v>EDGE SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1270">
@@ -44835,7 +44835,7 @@
         <v>FG-401547</v>
       </c>
       <c r="C1270" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2)</v>
+        <v>EDGE SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1270" t="str">
         <v>EDGE SERIES PILLAR TAP</v>
@@ -44847,7 +44847,7 @@
         <v>General</v>
       </c>
       <c r="G1270" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1270" t="str">
         <v>NOS</v>
@@ -44870,7 +44870,7 @@
         <v>FG-401547</v>
       </c>
       <c r="C1271" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2")</v>
+        <v>EDGE SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1271" t="str">
         <v>EDGE SERIES PILLAR TAP</v>
@@ -44882,7 +44882,7 @@
         <v>General</v>
       </c>
       <c r="G1271" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1271" t="str">
         <v>NOS</v>
@@ -44902,13 +44902,13 @@
         <v>1271</v>
       </c>
       <c r="B1272" t="str">
-        <v>FG-401550</v>
+        <v>FG-401547</v>
       </c>
       <c r="C1272" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2 inch)</v>
+        <v>EDGE SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1272" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB</v>
+        <v>EDGE SERIES PILLAR TAP</v>
       </c>
       <c r="E1272" t="str">
         <v>FAUCETS</v>
@@ -44917,19 +44917,19 @@
         <v>General</v>
       </c>
       <c r="G1272" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1272" t="str">
         <v>NOS</v>
       </c>
       <c r="I1272">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J1272" t="str">
         <v>Active</v>
       </c>
       <c r="K1272" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB high quality faucet.</v>
+        <v>EDGE SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1273">
@@ -44940,7 +44940,7 @@
         <v>FG-401550</v>
       </c>
       <c r="C1273" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2)</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2 inch)</v>
       </c>
       <c r="D1273" t="str">
         <v>EDGE SERIES 2 WAY BIB TAB</v>
@@ -44952,7 +44952,7 @@
         <v>General</v>
       </c>
       <c r="G1273" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1273" t="str">
         <v>NOS</v>
@@ -44975,7 +44975,7 @@
         <v>FG-401550</v>
       </c>
       <c r="C1274" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2")</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2)</v>
       </c>
       <c r="D1274" t="str">
         <v>EDGE SERIES 2 WAY BIB TAB</v>
@@ -44987,7 +44987,7 @@
         <v>General</v>
       </c>
       <c r="G1274" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1274" t="str">
         <v>NOS</v>
@@ -45007,13 +45007,13 @@
         <v>1274</v>
       </c>
       <c r="B1275" t="str">
-        <v>FG-401548</v>
+        <v>FG-401550</v>
       </c>
       <c r="C1275" t="str">
-        <v>EDGE SERIES SINK TAP (1/2 inch)</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2")</v>
       </c>
       <c r="D1275" t="str">
-        <v>EDGE SERIES SINK TAP</v>
+        <v>EDGE SERIES 2 WAY BIB TAB</v>
       </c>
       <c r="E1275" t="str">
         <v>FAUCETS</v>
@@ -45022,19 +45022,19 @@
         <v>General</v>
       </c>
       <c r="G1275" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1275" t="str">
         <v>NOS</v>
       </c>
       <c r="I1275">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J1275" t="str">
         <v>Active</v>
       </c>
       <c r="K1275" t="str">
-        <v>EDGE SERIES SINK TAP high quality faucet.</v>
+        <v>EDGE SERIES 2 WAY BIB TAB high quality faucet.</v>
       </c>
     </row>
     <row r="1276">
@@ -45045,7 +45045,7 @@
         <v>FG-401548</v>
       </c>
       <c r="C1276" t="str">
-        <v>EDGE SERIES SINK TAP (1/2)</v>
+        <v>EDGE SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1276" t="str">
         <v>EDGE SERIES SINK TAP</v>
@@ -45057,7 +45057,7 @@
         <v>General</v>
       </c>
       <c r="G1276" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1276" t="str">
         <v>NOS</v>
@@ -45080,7 +45080,7 @@
         <v>FG-401548</v>
       </c>
       <c r="C1277" t="str">
-        <v>EDGE SERIES SINK TAP (1/2")</v>
+        <v>EDGE SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1277" t="str">
         <v>EDGE SERIES SINK TAP</v>
@@ -45092,7 +45092,7 @@
         <v>General</v>
       </c>
       <c r="G1277" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1277" t="str">
         <v>NOS</v>
@@ -45112,13 +45112,13 @@
         <v>1277</v>
       </c>
       <c r="B1278" t="str">
-        <v>FG-401568</v>
+        <v>FG-401548</v>
       </c>
       <c r="C1278" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2 inch)</v>
+        <v>EDGE SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1278" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP</v>
+        <v>EDGE SERIES SINK TAP</v>
       </c>
       <c r="E1278" t="str">
         <v>FAUCETS</v>
@@ -45127,19 +45127,19 @@
         <v>General</v>
       </c>
       <c r="G1278" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1278" t="str">
         <v>NOS</v>
       </c>
       <c r="I1278">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="J1278" t="str">
         <v>Active</v>
       </c>
       <c r="K1278" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP high quality faucet.</v>
+        <v>EDGE SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1279">
@@ -45150,7 +45150,7 @@
         <v>FG-401568</v>
       </c>
       <c r="C1279" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2)</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1279" t="str">
         <v>SMART SERIES SHORT BODY BIB TAP</v>
@@ -45162,7 +45162,7 @@
         <v>General</v>
       </c>
       <c r="G1279" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1279" t="str">
         <v>NOS</v>
@@ -45185,7 +45185,7 @@
         <v>FG-401568</v>
       </c>
       <c r="C1280" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2")</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1280" t="str">
         <v>SMART SERIES SHORT BODY BIB TAP</v>
@@ -45197,7 +45197,7 @@
         <v>General</v>
       </c>
       <c r="G1280" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1280" t="str">
         <v>NOS</v>
@@ -45217,13 +45217,13 @@
         <v>1280</v>
       </c>
       <c r="B1281" t="str">
-        <v>FG-401567</v>
+        <v>FG-401568</v>
       </c>
       <c r="C1281" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1281" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP</v>
+        <v>SMART SERIES SHORT BODY BIB TAP</v>
       </c>
       <c r="E1281" t="str">
         <v>FAUCETS</v>
@@ -45232,7 +45232,7 @@
         <v>General</v>
       </c>
       <c r="G1281" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1281" t="str">
         <v>NOS</v>
@@ -45244,7 +45244,7 @@
         <v>Active</v>
       </c>
       <c r="K1281" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP high quality faucet.</v>
+        <v>SMART SERIES SHORT BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1282">
@@ -45255,7 +45255,7 @@
         <v>FG-401567</v>
       </c>
       <c r="C1282" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2)</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1282" t="str">
         <v>SMART SERIES LONG BODY BIB TAP</v>
@@ -45267,7 +45267,7 @@
         <v>General</v>
       </c>
       <c r="G1282" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1282" t="str">
         <v>NOS</v>
@@ -45290,7 +45290,7 @@
         <v>FG-401567</v>
       </c>
       <c r="C1283" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2")</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1283" t="str">
         <v>SMART SERIES LONG BODY BIB TAP</v>
@@ -45302,7 +45302,7 @@
         <v>General</v>
       </c>
       <c r="G1283" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1283" t="str">
         <v>NOS</v>
@@ -45322,13 +45322,13 @@
         <v>1283</v>
       </c>
       <c r="B1284" t="str">
-        <v>FG-401562</v>
+        <v>FG-401567</v>
       </c>
       <c r="C1284" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2 inch)</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1284" t="str">
-        <v>SMART SERIES PILLAR TAP</v>
+        <v>SMART SERIES LONG BODY BIB TAP</v>
       </c>
       <c r="E1284" t="str">
         <v>FAUCETS</v>
@@ -45337,19 +45337,19 @@
         <v>General</v>
       </c>
       <c r="G1284" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1284" t="str">
         <v>NOS</v>
       </c>
       <c r="I1284">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1284" t="str">
         <v>Active</v>
       </c>
       <c r="K1284" t="str">
-        <v>SMART SERIES PILLAR TAP high quality faucet.</v>
+        <v>SMART SERIES LONG BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1285">
@@ -45360,7 +45360,7 @@
         <v>FG-401562</v>
       </c>
       <c r="C1285" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2)</v>
+        <v>SMART SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1285" t="str">
         <v>SMART SERIES PILLAR TAP</v>
@@ -45372,7 +45372,7 @@
         <v>General</v>
       </c>
       <c r="G1285" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1285" t="str">
         <v>NOS</v>
@@ -45395,7 +45395,7 @@
         <v>FG-401562</v>
       </c>
       <c r="C1286" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2")</v>
+        <v>SMART SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1286" t="str">
         <v>SMART SERIES PILLAR TAP</v>
@@ -45407,7 +45407,7 @@
         <v>General</v>
       </c>
       <c r="G1286" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1286" t="str">
         <v>NOS</v>
@@ -45427,13 +45427,13 @@
         <v>1286</v>
       </c>
       <c r="B1287" t="str">
-        <v>FG-401563</v>
+        <v>FG-401562</v>
       </c>
       <c r="C1287" t="str">
-        <v>SMART SERIES SINK TAP (1/2 inch)</v>
+        <v>SMART SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1287" t="str">
-        <v>SMART SERIES SINK TAP</v>
+        <v>SMART SERIES PILLAR TAP</v>
       </c>
       <c r="E1287" t="str">
         <v>FAUCETS</v>
@@ -45442,7 +45442,7 @@
         <v>General</v>
       </c>
       <c r="G1287" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1287" t="str">
         <v>NOS</v>
@@ -45454,7 +45454,7 @@
         <v>Active</v>
       </c>
       <c r="K1287" t="str">
-        <v>SMART SERIES SINK TAP high quality faucet.</v>
+        <v>SMART SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1288">
@@ -45465,7 +45465,7 @@
         <v>FG-401563</v>
       </c>
       <c r="C1288" t="str">
-        <v>SMART SERIES SINK TAP (1/2)</v>
+        <v>SMART SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1288" t="str">
         <v>SMART SERIES SINK TAP</v>
@@ -45477,7 +45477,7 @@
         <v>General</v>
       </c>
       <c r="G1288" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1288" t="str">
         <v>NOS</v>
@@ -45500,7 +45500,7 @@
         <v>FG-401563</v>
       </c>
       <c r="C1289" t="str">
-        <v>SMART SERIES SINK TAP (1/2")</v>
+        <v>SMART SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1289" t="str">
         <v>SMART SERIES SINK TAP</v>
@@ -45512,7 +45512,7 @@
         <v>General</v>
       </c>
       <c r="G1289" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1289" t="str">
         <v>NOS</v>
@@ -45532,13 +45532,13 @@
         <v>1289</v>
       </c>
       <c r="B1290" t="str">
-        <v>FG-401564</v>
+        <v>FG-401563</v>
       </c>
       <c r="C1290" t="str">
-        <v>SMART SERIES SWAN NECK (1/2 inch)</v>
+        <v>SMART SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1290" t="str">
-        <v>SMART SERIES SWAN NECK</v>
+        <v>SMART SERIES SINK TAP</v>
       </c>
       <c r="E1290" t="str">
         <v>FAUCETS</v>
@@ -45547,7 +45547,7 @@
         <v>General</v>
       </c>
       <c r="G1290" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1290" t="str">
         <v>NOS</v>
@@ -45559,7 +45559,7 @@
         <v>Active</v>
       </c>
       <c r="K1290" t="str">
-        <v>SMART SERIES SWAN NECK high quality faucet.</v>
+        <v>SMART SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1291">
@@ -45570,7 +45570,7 @@
         <v>FG-401564</v>
       </c>
       <c r="C1291" t="str">
-        <v>SMART SERIES SWAN NECK (1/2)</v>
+        <v>SMART SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1291" t="str">
         <v>SMART SERIES SWAN NECK</v>
@@ -45582,7 +45582,7 @@
         <v>General</v>
       </c>
       <c r="G1291" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1291" t="str">
         <v>NOS</v>
@@ -45605,7 +45605,7 @@
         <v>FG-401564</v>
       </c>
       <c r="C1292" t="str">
-        <v>SMART SERIES SWAN NECK (1/2")</v>
+        <v>SMART SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1292" t="str">
         <v>SMART SERIES SWAN NECK</v>
@@ -45617,7 +45617,7 @@
         <v>General</v>
       </c>
       <c r="G1292" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1292" t="str">
         <v>NOS</v>
@@ -45637,13 +45637,13 @@
         <v>1292</v>
       </c>
       <c r="B1293" t="str">
-        <v>FG-401561</v>
+        <v>FG-401564</v>
       </c>
       <c r="C1293" t="str">
-        <v>SMART SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>SMART SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1293" t="str">
-        <v>SMART SERIES ANGULAR VALVE</v>
+        <v>SMART SERIES SWAN NECK</v>
       </c>
       <c r="E1293" t="str">
         <v>FAUCETS</v>
@@ -45652,19 +45652,19 @@
         <v>General</v>
       </c>
       <c r="G1293" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1293" t="str">
         <v>NOS</v>
       </c>
       <c r="I1293">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1293" t="str">
         <v>Active</v>
       </c>
       <c r="K1293" t="str">
-        <v>SMART SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>SMART SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1294">
@@ -45672,13 +45672,13 @@
         <v>1293</v>
       </c>
       <c r="B1294" t="str">
-        <v>FG-401566</v>
+        <v>FG-401561</v>
       </c>
       <c r="C1294" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
+        <v>SMART SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1294" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
+        <v>SMART SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1294" t="str">
         <v>FAUCETS</v>
@@ -45693,13 +45693,13 @@
         <v>NOS</v>
       </c>
       <c r="I1294">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1294" t="str">
         <v>Active</v>
       </c>
       <c r="K1294" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
+        <v>SMART SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1295">
@@ -45710,7 +45710,7 @@
         <v>FG-401566</v>
       </c>
       <c r="C1295" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1295" t="str">
         <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
@@ -45722,7 +45722,7 @@
         <v>General</v>
       </c>
       <c r="G1295" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1295" t="str">
         <v>NOS</v>
@@ -45745,7 +45745,7 @@
         <v>FG-401566</v>
       </c>
       <c r="C1296" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2")</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1296" t="str">
         <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
@@ -45757,7 +45757,7 @@
         <v>General</v>
       </c>
       <c r="G1296" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1296" t="str">
         <v>NOS</v>
@@ -45777,13 +45777,13 @@
         <v>1296</v>
       </c>
       <c r="B1297" t="str">
-        <v>FG-401565</v>
+        <v>FG-401566</v>
       </c>
       <c r="C1297" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1297" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
       </c>
       <c r="E1297" t="str">
         <v>FAUCETS</v>
@@ -45792,7 +45792,7 @@
         <v>General</v>
       </c>
       <c r="G1297" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1297" t="str">
         <v>NOS</v>
@@ -45804,7 +45804,7 @@
         <v>Active</v>
       </c>
       <c r="K1297" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP high quality faucet.</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1298">
@@ -45815,7 +45815,7 @@
         <v>FG-401565</v>
       </c>
       <c r="C1298" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2)</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1298" t="str">
         <v>SMART SERIES 2 WAY BIB TAP</v>
@@ -45827,7 +45827,7 @@
         <v>General</v>
       </c>
       <c r="G1298" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1298" t="str">
         <v>NOS</v>
@@ -45850,7 +45850,7 @@
         <v>FG-401565</v>
       </c>
       <c r="C1299" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2")</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2)</v>
       </c>
       <c r="D1299" t="str">
         <v>SMART SERIES 2 WAY BIB TAP</v>
@@ -45862,7 +45862,7 @@
         <v>General</v>
       </c>
       <c r="G1299" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1299" t="str">
         <v>NOS</v>
@@ -45882,13 +45882,13 @@
         <v>1299</v>
       </c>
       <c r="B1300" t="str">
-        <v>FG-401560</v>
+        <v>FG-401565</v>
       </c>
       <c r="C1300" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2")</v>
       </c>
       <c r="D1300" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP</v>
+        <v>SMART SERIES 2 WAY BIB TAP</v>
       </c>
       <c r="E1300" t="str">
         <v>FAUCETS</v>
@@ -45897,19 +45897,19 @@
         <v>General</v>
       </c>
       <c r="G1300" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1300" t="str">
         <v>NOS</v>
       </c>
       <c r="I1300">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1300" t="str">
         <v>Active</v>
       </c>
       <c r="K1300" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP high quality faucet.</v>
+        <v>SMART SERIES 2 WAY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1301">
@@ -45920,7 +45920,7 @@
         <v>FG-401560</v>
       </c>
       <c r="C1301" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1301" t="str">
         <v>REGULAR SERIES SHORT BODY BIB TAP</v>
@@ -45932,7 +45932,7 @@
         <v>General</v>
       </c>
       <c r="G1301" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1301" t="str">
         <v>NOS</v>
@@ -45955,7 +45955,7 @@
         <v>FG-401560</v>
       </c>
       <c r="C1302" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1302" t="str">
         <v>REGULAR SERIES SHORT BODY BIB TAP</v>
@@ -45967,7 +45967,7 @@
         <v>General</v>
       </c>
       <c r="G1302" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1302" t="str">
         <v>NOS</v>
@@ -45987,13 +45987,13 @@
         <v>1302</v>
       </c>
       <c r="B1303" t="str">
-        <v>FG-401559</v>
+        <v>FG-401560</v>
       </c>
       <c r="C1303" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1303" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP</v>
       </c>
       <c r="E1303" t="str">
         <v>FAUCETS</v>
@@ -46002,7 +46002,7 @@
         <v>General</v>
       </c>
       <c r="G1303" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1303" t="str">
         <v>NOS</v>
@@ -46014,7 +46014,7 @@
         <v>Active</v>
       </c>
       <c r="K1303" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1304">
@@ -46025,7 +46025,7 @@
         <v>FG-401559</v>
       </c>
       <c r="C1304" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1304" t="str">
         <v>REGULAR SERIES LONG BODY BIB TAP</v>
@@ -46037,7 +46037,7 @@
         <v>General</v>
       </c>
       <c r="G1304" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1304" t="str">
         <v>NOS</v>
@@ -46060,7 +46060,7 @@
         <v>FG-401559</v>
       </c>
       <c r="C1305" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1305" t="str">
         <v>REGULAR SERIES LONG BODY BIB TAP</v>
@@ -46072,7 +46072,7 @@
         <v>General</v>
       </c>
       <c r="G1305" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1305" t="str">
         <v>NOS</v>
@@ -46092,13 +46092,13 @@
         <v>1305</v>
       </c>
       <c r="B1306" t="str">
-        <v>FG-401554</v>
+        <v>FG-401559</v>
       </c>
       <c r="C1306" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2 inch)</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1306" t="str">
-        <v>REGULAR SERIES PILLAR TAP</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP</v>
       </c>
       <c r="E1306" t="str">
         <v>FAUCETS</v>
@@ -46107,19 +46107,19 @@
         <v>General</v>
       </c>
       <c r="G1306" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1306" t="str">
         <v>NOS</v>
       </c>
       <c r="I1306">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1306" t="str">
         <v>Active</v>
       </c>
       <c r="K1306" t="str">
-        <v>REGULAR SERIES PILLAR TAP high quality faucet.</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1307">
@@ -46130,7 +46130,7 @@
         <v>FG-401554</v>
       </c>
       <c r="C1307" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2)</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1307" t="str">
         <v>REGULAR SERIES PILLAR TAP</v>
@@ -46142,7 +46142,7 @@
         <v>General</v>
       </c>
       <c r="G1307" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1307" t="str">
         <v>NOS</v>
@@ -46165,7 +46165,7 @@
         <v>FG-401554</v>
       </c>
       <c r="C1308" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2")</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1308" t="str">
         <v>REGULAR SERIES PILLAR TAP</v>
@@ -46177,7 +46177,7 @@
         <v>General</v>
       </c>
       <c r="G1308" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1308" t="str">
         <v>NOS</v>
@@ -46197,13 +46197,13 @@
         <v>1308</v>
       </c>
       <c r="B1309" t="str">
-        <v>FG-401555</v>
+        <v>FG-401554</v>
       </c>
       <c r="C1309" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2 inch)</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1309" t="str">
-        <v>REGULAR SERIES SINK TAP</v>
+        <v>REGULAR SERIES PILLAR TAP</v>
       </c>
       <c r="E1309" t="str">
         <v>FAUCETS</v>
@@ -46212,7 +46212,7 @@
         <v>General</v>
       </c>
       <c r="G1309" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1309" t="str">
         <v>NOS</v>
@@ -46224,7 +46224,7 @@
         <v>Active</v>
       </c>
       <c r="K1309" t="str">
-        <v>REGULAR SERIES SINK TAP high quality faucet.</v>
+        <v>REGULAR SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1310">
@@ -46235,7 +46235,7 @@
         <v>FG-401555</v>
       </c>
       <c r="C1310" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2)</v>
+        <v>REGULAR SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1310" t="str">
         <v>REGULAR SERIES SINK TAP</v>
@@ -46247,7 +46247,7 @@
         <v>General</v>
       </c>
       <c r="G1310" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1310" t="str">
         <v>NOS</v>
@@ -46270,7 +46270,7 @@
         <v>FG-401555</v>
       </c>
       <c r="C1311" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2")</v>
+        <v>REGULAR SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1311" t="str">
         <v>REGULAR SERIES SINK TAP</v>
@@ -46282,7 +46282,7 @@
         <v>General</v>
       </c>
       <c r="G1311" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1311" t="str">
         <v>NOS</v>
@@ -46302,13 +46302,13 @@
         <v>1311</v>
       </c>
       <c r="B1312" t="str">
-        <v>FG-401556</v>
+        <v>FG-401555</v>
       </c>
       <c r="C1312" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2 inch)</v>
+        <v>REGULAR SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1312" t="str">
-        <v>REGULAR SERIES SWAN NECK</v>
+        <v>REGULAR SERIES SINK TAP</v>
       </c>
       <c r="E1312" t="str">
         <v>FAUCETS</v>
@@ -46317,7 +46317,7 @@
         <v>General</v>
       </c>
       <c r="G1312" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1312" t="str">
         <v>NOS</v>
@@ -46329,7 +46329,7 @@
         <v>Active</v>
       </c>
       <c r="K1312" t="str">
-        <v>REGULAR SERIES SWAN NECK high quality faucet.</v>
+        <v>REGULAR SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1313">
@@ -46340,7 +46340,7 @@
         <v>FG-401556</v>
       </c>
       <c r="C1313" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2)</v>
+        <v>REGULAR SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1313" t="str">
         <v>REGULAR SERIES SWAN NECK</v>
@@ -46352,7 +46352,7 @@
         <v>General</v>
       </c>
       <c r="G1313" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1313" t="str">
         <v>NOS</v>
@@ -46375,7 +46375,7 @@
         <v>FG-401556</v>
       </c>
       <c r="C1314" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2")</v>
+        <v>REGULAR SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1314" t="str">
         <v>REGULAR SERIES SWAN NECK</v>
@@ -46387,7 +46387,7 @@
         <v>General</v>
       </c>
       <c r="G1314" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1314" t="str">
         <v>NOS</v>
@@ -46407,13 +46407,13 @@
         <v>1314</v>
       </c>
       <c r="B1315" t="str">
-        <v>FG-401553</v>
+        <v>FG-401556</v>
       </c>
       <c r="C1315" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>REGULAR SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1315" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE</v>
+        <v>REGULAR SERIES SWAN NECK</v>
       </c>
       <c r="E1315" t="str">
         <v>FAUCETS</v>
@@ -46422,19 +46422,19 @@
         <v>General</v>
       </c>
       <c r="G1315" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1315" t="str">
         <v>NOS</v>
       </c>
       <c r="I1315">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1315" t="str">
         <v>Active</v>
       </c>
       <c r="K1315" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>REGULAR SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1316">
@@ -46445,7 +46445,7 @@
         <v>FG-401553</v>
       </c>
       <c r="C1316" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2)</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1316" t="str">
         <v>REGULAR SERIES ANGULAR VALVE</v>
@@ -46457,7 +46457,7 @@
         <v>General</v>
       </c>
       <c r="G1316" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1316" t="str">
         <v>NOS</v>
@@ -46480,7 +46480,7 @@
         <v>FG-401553</v>
       </c>
       <c r="C1317" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2")</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1317" t="str">
         <v>REGULAR SERIES ANGULAR VALVE</v>
@@ -46492,7 +46492,7 @@
         <v>General</v>
       </c>
       <c r="G1317" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1317" t="str">
         <v>NOS</v>
@@ -46512,13 +46512,13 @@
         <v>1317</v>
       </c>
       <c r="B1318" t="str">
-        <v>FG-401558</v>
+        <v>FG-401553</v>
       </c>
       <c r="C1318" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1318" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
+        <v>REGULAR SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1318" t="str">
         <v>FAUCETS</v>
@@ -46527,19 +46527,19 @@
         <v>General</v>
       </c>
       <c r="G1318" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1318" t="str">
         <v>NOS</v>
       </c>
       <c r="I1318">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1318" t="str">
         <v>Active</v>
       </c>
       <c r="K1318" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
+        <v>REGULAR SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1319">
@@ -46550,7 +46550,7 @@
         <v>FG-401558</v>
       </c>
       <c r="C1319" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2)</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1319" t="str">
         <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
@@ -46562,7 +46562,7 @@
         <v>General</v>
       </c>
       <c r="G1319" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1319" t="str">
         <v>NOS</v>
@@ -46585,7 +46585,7 @@
         <v>FG-401558</v>
       </c>
       <c r="C1320" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2")</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1320" t="str">
         <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
@@ -46597,7 +46597,7 @@
         <v>General</v>
       </c>
       <c r="G1320" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1320" t="str">
         <v>NOS</v>
@@ -46617,13 +46617,13 @@
         <v>1320</v>
       </c>
       <c r="B1321" t="str">
-        <v>FG-401557</v>
+        <v>FG-401558</v>
       </c>
       <c r="C1321" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1321" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
       </c>
       <c r="E1321" t="str">
         <v>FAUCETS</v>
@@ -46632,7 +46632,7 @@
         <v>General</v>
       </c>
       <c r="G1321" t="str">
-        <v>1/2 inch</v>
+        <v>1/2"</v>
       </c>
       <c r="H1321" t="str">
         <v>NOS</v>
@@ -46644,7 +46644,7 @@
         <v>Active</v>
       </c>
       <c r="K1321" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1322">
@@ -46655,7 +46655,7 @@
         <v>FG-401557</v>
       </c>
       <c r="C1322" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1322" t="str">
         <v>REGULAR SERIES 2 WAY BIB TAP</v>
@@ -46667,7 +46667,7 @@
         <v>General</v>
       </c>
       <c r="G1322" t="str">
-        <v>1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1322" t="str">
         <v>NOS</v>
@@ -46690,7 +46690,7 @@
         <v>FG-401557</v>
       </c>
       <c r="C1323" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2)</v>
       </c>
       <c r="D1323" t="str">
         <v>REGULAR SERIES 2 WAY BIB TAP</v>
@@ -46702,7 +46702,7 @@
         <v>General</v>
       </c>
       <c r="G1323" t="str">
-        <v>1/2"</v>
+        <v>1/2</v>
       </c>
       <c r="H1323" t="str">
         <v>NOS</v>
@@ -46722,34 +46722,34 @@
         <v>1323</v>
       </c>
       <c r="B1324" t="str">
-        <v>FG-400836</v>
+        <v>FG-401557</v>
       </c>
       <c r="C1324" t="str">
-        <v>SINGLE SIDE HANDLE FLUSH 8L (8L)</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2")</v>
       </c>
       <c r="D1324" t="str">
-        <v>SINGLE SIDE HANDLE FLUSH 8L</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP</v>
       </c>
       <c r="E1324" t="str">
-        <v>Toilet Seat Cover &amp; Flushing Cistern</v>
+        <v>FAUCETS</v>
       </c>
       <c r="F1324" t="str">
         <v>General</v>
       </c>
       <c r="G1324" t="str">
-        <v>8L</v>
+        <v>1/2"</v>
       </c>
       <c r="H1324" t="str">
         <v>NOS</v>
       </c>
       <c r="I1324">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="J1324" t="str">
         <v>Active</v>
       </c>
       <c r="K1324" t="str">
-        <v>8 Litre Single Side Handle Flushing Cistern.</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1325">
@@ -46757,13 +46757,13 @@
         <v>1324</v>
       </c>
       <c r="B1325" t="str">
-        <v>FG-400837</v>
+        <v>FG-400836</v>
       </c>
       <c r="C1325" t="str">
-        <v>CENTER SINGLE PUSH FLUSH 8L (8L)</v>
+        <v>SINGLE SIDE HANDLE FLUSH 8L (8L)</v>
       </c>
       <c r="D1325" t="str">
-        <v>CENTER SINGLE PUSH FLUSH 8L</v>
+        <v>SINGLE SIDE HANDLE FLUSH 8L</v>
       </c>
       <c r="E1325" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46784,7 +46784,7 @@
         <v>Active</v>
       </c>
       <c r="K1325" t="str">
-        <v>8 Litre Center Single Push Flushing Cistern.</v>
+        <v>8 Litre Single Side Handle Flushing Cistern.</v>
       </c>
     </row>
     <row r="1326">
@@ -46792,13 +46792,13 @@
         <v>1325</v>
       </c>
       <c r="B1326" t="str">
-        <v>FG-400838</v>
+        <v>FG-400837</v>
       </c>
       <c r="C1326" t="str">
-        <v>DUAL FLUSH 10L (10L)</v>
+        <v>CENTER SINGLE PUSH FLUSH 8L (8L)</v>
       </c>
       <c r="D1326" t="str">
-        <v>DUAL FLUSH 10L</v>
+        <v>CENTER SINGLE PUSH FLUSH 8L</v>
       </c>
       <c r="E1326" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46807,7 +46807,7 @@
         <v>General</v>
       </c>
       <c r="G1326" t="str">
-        <v>10L</v>
+        <v>8L</v>
       </c>
       <c r="H1326" t="str">
         <v>NOS</v>
@@ -46819,7 +46819,7 @@
         <v>Active</v>
       </c>
       <c r="K1326" t="str">
-        <v>10 Litre Dual Flush Cistern.</v>
+        <v>8 Litre Center Single Push Flushing Cistern.</v>
       </c>
     </row>
     <row r="1327">
@@ -46827,13 +46827,13 @@
         <v>1326</v>
       </c>
       <c r="B1327" t="str">
-        <v>FG-400835</v>
+        <v>FG-400838</v>
       </c>
       <c r="C1327" t="str">
-        <v>EWC SEAT COVER (WITH JET) (Standard)</v>
+        <v>DUAL FLUSH 10L (10L)</v>
       </c>
       <c r="D1327" t="str">
-        <v>EWC SEAT COVER (WITH JET)</v>
+        <v>DUAL FLUSH 10L</v>
       </c>
       <c r="E1327" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46842,19 +46842,19 @@
         <v>General</v>
       </c>
       <c r="G1327" t="str">
-        <v>Standard</v>
+        <v>10L</v>
       </c>
       <c r="H1327" t="str">
         <v>NOS</v>
       </c>
       <c r="I1327">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J1327" t="str">
         <v>Active</v>
       </c>
       <c r="K1327" t="str">
-        <v>EWC Toilet Seat Cover with integrated jet spray.</v>
+        <v>10 Litre Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1328">
@@ -46862,13 +46862,13 @@
         <v>1327</v>
       </c>
       <c r="B1328" t="str">
-        <v>FG-400840</v>
+        <v>FG-400835</v>
       </c>
       <c r="C1328" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L) (10L)</v>
+        <v>EWC SEAT COVER (WITH JET) (Standard)</v>
       </c>
       <c r="D1328" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L)</v>
+        <v>EWC SEAT COVER (WITH JET)</v>
       </c>
       <c r="E1328" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46877,19 +46877,19 @@
         <v>General</v>
       </c>
       <c r="G1328" t="str">
-        <v>10L</v>
+        <v>Standard</v>
       </c>
       <c r="H1328" t="str">
         <v>NOS</v>
       </c>
       <c r="I1328">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J1328" t="str">
         <v>Active</v>
       </c>
       <c r="K1328" t="str">
-        <v>10 Litre Premium Dual Colour Dual Flush Cistern.</v>
+        <v>EWC Toilet Seat Cover with integrated jet spray.</v>
       </c>
     </row>
     <row r="1329">
@@ -46897,13 +46897,13 @@
         <v>1328</v>
       </c>
       <c r="B1329" t="str">
-        <v>FG-400839</v>
+        <v>FG-400840</v>
       </c>
       <c r="C1329" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L) (10L)</v>
+        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L) (10L)</v>
       </c>
       <c r="D1329" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L)</v>
+        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L)</v>
       </c>
       <c r="E1329" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46924,7 +46924,7 @@
         <v>Active</v>
       </c>
       <c r="K1329" t="str">
-        <v>10 Litre Economy Dual Colour Dual Flush Cistern.</v>
+        <v>10 Litre Premium Dual Colour Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1330">
@@ -46932,13 +46932,13 @@
         <v>1329</v>
       </c>
       <c r="B1330" t="str">
-        <v>FG-400834</v>
+        <v>FG-400839</v>
       </c>
       <c r="C1330" t="str">
-        <v>EWC SEAT COVER (WITHOUT JET) (Standard)</v>
+        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L) (10L)</v>
       </c>
       <c r="D1330" t="str">
-        <v>EWC SEAT COVER (WITHOUT JET)</v>
+        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L)</v>
       </c>
       <c r="E1330" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46947,24 +46947,59 @@
         <v>General</v>
       </c>
       <c r="G1330" t="str">
-        <v>Standard</v>
+        <v>10L</v>
       </c>
       <c r="H1330" t="str">
         <v>NOS</v>
       </c>
       <c r="I1330">
+        <v>10</v>
+      </c>
+      <c r="J1330" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K1330" t="str">
+        <v>10 Litre Economy Dual Colour Dual Flush Cistern.</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331">
+        <v>1330</v>
+      </c>
+      <c r="B1331" t="str">
+        <v>FG-400834</v>
+      </c>
+      <c r="C1331" t="str">
+        <v>EWC SEAT COVER (WITHOUT JET) (Standard)</v>
+      </c>
+      <c r="D1331" t="str">
+        <v>EWC SEAT COVER (WITHOUT JET)</v>
+      </c>
+      <c r="E1331" t="str">
+        <v>Toilet Seat Cover &amp; Flushing Cistern</v>
+      </c>
+      <c r="F1331" t="str">
+        <v>General</v>
+      </c>
+      <c r="G1331" t="str">
+        <v>Standard</v>
+      </c>
+      <c r="H1331" t="str">
+        <v>NOS</v>
+      </c>
+      <c r="I1331">
         <v>20</v>
       </c>
-      <c r="J1330" t="str">
-        <v>Active</v>
-      </c>
-      <c r="K1330" t="str">
+      <c r="J1331" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K1331" t="str">
         <v>EWC Toilet Seat Cover without jet spray.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K1330"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K1331"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
+++ b/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1331"/>
+  <dimension ref="A1:K1330"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -35875,10 +35875,10 @@
         <v>-</v>
       </c>
       <c r="C1014" t="str">
-        <v>PN10 - COUPLER ISI (25MM)</v>
+        <v>AGRI COUPLER 10KG</v>
       </c>
       <c r="D1014" t="str">
-        <v>PN10 - COUPLER ISI</v>
+        <v>AGRI COUPLER 10KG</v>
       </c>
       <c r="E1014" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35887,7 +35887,7 @@
         <v>General</v>
       </c>
       <c r="G1014" t="str">
-        <v>25MM</v>
+        <v>Standard</v>
       </c>
       <c r="H1014" t="str">
         <v>BOX</v>
@@ -35899,7 +35899,7 @@
         <v>Active</v>
       </c>
       <c r="K1014" t="str">
-        <v>PN10 - COUPLER ISI for agriculture irrigation and piping systems.</v>
+        <v>AGRI COUPLER 10KG.</v>
       </c>
     </row>
     <row r="1015">
@@ -35910,10 +35910,10 @@
         <v>-</v>
       </c>
       <c r="C1015" t="str">
-        <v>PN10 - COUPLER ISI (32MM)</v>
+        <v>PN10 - MTA ISI (25MM)</v>
       </c>
       <c r="D1015" t="str">
-        <v>PN10 - COUPLER ISI</v>
+        <v>PN10 - MTA ISI</v>
       </c>
       <c r="E1015" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35922,7 +35922,7 @@
         <v>General</v>
       </c>
       <c r="G1015" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1015" t="str">
         <v>BOX</v>
@@ -35934,7 +35934,7 @@
         <v>Active</v>
       </c>
       <c r="K1015" t="str">
-        <v>PN10 - COUPLER ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - MTA ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1016">
@@ -35945,7 +35945,7 @@
         <v>-</v>
       </c>
       <c r="C1016" t="str">
-        <v>PN10 - MTA ISI (25MM)</v>
+        <v>PN10 - MTA ISI (32MM)</v>
       </c>
       <c r="D1016" t="str">
         <v>PN10 - MTA ISI</v>
@@ -35957,7 +35957,7 @@
         <v>General</v>
       </c>
       <c r="G1016" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1016" t="str">
         <v>BOX</v>
@@ -35980,10 +35980,10 @@
         <v>-</v>
       </c>
       <c r="C1017" t="str">
-        <v>PN10 - MTA ISI (32MM)</v>
+        <v>PN10 - FTA ISI (25MM)</v>
       </c>
       <c r="D1017" t="str">
-        <v>PN10 - MTA ISI</v>
+        <v>PN10 - FTA ISI</v>
       </c>
       <c r="E1017" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35992,7 +35992,7 @@
         <v>General</v>
       </c>
       <c r="G1017" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1017" t="str">
         <v>BOX</v>
@@ -36004,7 +36004,7 @@
         <v>Active</v>
       </c>
       <c r="K1017" t="str">
-        <v>PN10 - MTA ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - FTA ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1018">
@@ -36015,7 +36015,7 @@
         <v>-</v>
       </c>
       <c r="C1018" t="str">
-        <v>PN10 - FTA ISI (25MM)</v>
+        <v>PN10 - FTA ISI (32MM)</v>
       </c>
       <c r="D1018" t="str">
         <v>PN10 - FTA ISI</v>
@@ -36027,7 +36027,7 @@
         <v>General</v>
       </c>
       <c r="G1018" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1018" t="str">
         <v>BOX</v>
@@ -36050,10 +36050,10 @@
         <v>-</v>
       </c>
       <c r="C1019" t="str">
-        <v>PN10 - FTA ISI (32MM)</v>
+        <v>PN10 - END CAP ISI (25MM)</v>
       </c>
       <c r="D1019" t="str">
-        <v>PN10 - FTA ISI</v>
+        <v>PN10 - END CAP ISI</v>
       </c>
       <c r="E1019" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36062,7 +36062,7 @@
         <v>General</v>
       </c>
       <c r="G1019" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1019" t="str">
         <v>BOX</v>
@@ -36074,7 +36074,7 @@
         <v>Active</v>
       </c>
       <c r="K1019" t="str">
-        <v>PN10 - FTA ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - END CAP ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1020">
@@ -36085,7 +36085,7 @@
         <v>-</v>
       </c>
       <c r="C1020" t="str">
-        <v>PN10 - END CAP ISI (25MM)</v>
+        <v>PN10 - END CAP ISI (32MM)</v>
       </c>
       <c r="D1020" t="str">
         <v>PN10 - END CAP ISI</v>
@@ -36097,7 +36097,7 @@
         <v>General</v>
       </c>
       <c r="G1020" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1020" t="str">
         <v>BOX</v>
@@ -36120,10 +36120,10 @@
         <v>-</v>
       </c>
       <c r="C1021" t="str">
-        <v>PN10 - END CAP ISI (32MM)</v>
+        <v>PN10 - REDUCING BUSH ISI (32 X 20)</v>
       </c>
       <c r="D1021" t="str">
-        <v>PN10 - END CAP ISI</v>
+        <v>PN10 - REDUCING BUSH ISI</v>
       </c>
       <c r="E1021" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36132,7 +36132,7 @@
         <v>General</v>
       </c>
       <c r="G1021" t="str">
-        <v>32MM</v>
+        <v>32 X 20</v>
       </c>
       <c r="H1021" t="str">
         <v>BOX</v>
@@ -36144,7 +36144,7 @@
         <v>Active</v>
       </c>
       <c r="K1021" t="str">
-        <v>PN10 - END CAP ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - REDUCING BUSH ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1022">
@@ -36155,7 +36155,7 @@
         <v>-</v>
       </c>
       <c r="C1022" t="str">
-        <v>PN10 - REDUCING BUSH ISI (32 X 20)</v>
+        <v>PN10 - REDUCING BUSH ISI (32 X 25)</v>
       </c>
       <c r="D1022" t="str">
         <v>PN10 - REDUCING BUSH ISI</v>
@@ -36167,7 +36167,7 @@
         <v>General</v>
       </c>
       <c r="G1022" t="str">
-        <v>32 X 20</v>
+        <v>32 X 25</v>
       </c>
       <c r="H1022" t="str">
         <v>BOX</v>
@@ -36187,13 +36187,13 @@
         <v>1022</v>
       </c>
       <c r="B1023" t="str">
-        <v>-</v>
+        <v>FG-400585</v>
       </c>
       <c r="C1023" t="str">
-        <v>PN10 - REDUCING BUSH ISI (32 X 25)</v>
+        <v>AGRI REDUCER (50X40MM)</v>
       </c>
       <c r="D1023" t="str">
-        <v>PN10 - REDUCING BUSH ISI</v>
+        <v>AGRI REDUCER</v>
       </c>
       <c r="E1023" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36202,19 +36202,19 @@
         <v>General</v>
       </c>
       <c r="G1023" t="str">
-        <v>32 X 25</v>
+        <v>50X40MM</v>
       </c>
       <c r="H1023" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1023" t="str">
-        <v>-</v>
+      <c r="I1023">
+        <v>300</v>
       </c>
       <c r="J1023" t="str">
         <v>Active</v>
       </c>
       <c r="K1023" t="str">
-        <v>PN10 - REDUCING BUSH ISI for agriculture irrigation and piping systems.</v>
+        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
       </c>
     </row>
     <row r="1024">
@@ -36222,10 +36222,10 @@
         <v>1023</v>
       </c>
       <c r="B1024" t="str">
-        <v>FG-400585</v>
+        <v>FG-400584</v>
       </c>
       <c r="C1024" t="str">
-        <v>AGRI REDUCER (50X40MM)</v>
+        <v>AGRI REDUCER (63X40MM)</v>
       </c>
       <c r="D1024" t="str">
         <v>AGRI REDUCER</v>
@@ -36237,13 +36237,13 @@
         <v>General</v>
       </c>
       <c r="G1024" t="str">
-        <v>50X40MM</v>
+        <v>63X40MM</v>
       </c>
       <c r="H1024" t="str">
         <v>BOX</v>
       </c>
       <c r="I1024">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J1024" t="str">
         <v>Active</v>
@@ -36257,10 +36257,10 @@
         <v>1024</v>
       </c>
       <c r="B1025" t="str">
-        <v>FG-400584</v>
+        <v>FG-400583</v>
       </c>
       <c r="C1025" t="str">
-        <v>AGRI REDUCER (63X40MM)</v>
+        <v>AGRI REDUCER (63X50MM)</v>
       </c>
       <c r="D1025" t="str">
         <v>AGRI REDUCER</v>
@@ -36272,13 +36272,13 @@
         <v>General</v>
       </c>
       <c r="G1025" t="str">
-        <v>63X40MM</v>
+        <v>63X50MM</v>
       </c>
       <c r="H1025" t="str">
         <v>BOX</v>
       </c>
       <c r="I1025">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="J1025" t="str">
         <v>Active</v>
@@ -36292,10 +36292,10 @@
         <v>1025</v>
       </c>
       <c r="B1026" t="str">
-        <v>FG-400583</v>
+        <v>FG-400582</v>
       </c>
       <c r="C1026" t="str">
-        <v>AGRI REDUCER (63X50MM)</v>
+        <v>AGRI REDUCER (75X40MM)</v>
       </c>
       <c r="D1026" t="str">
         <v>AGRI REDUCER</v>
@@ -36307,13 +36307,13 @@
         <v>General</v>
       </c>
       <c r="G1026" t="str">
-        <v>63X50MM</v>
+        <v>75X40MM</v>
       </c>
       <c r="H1026" t="str">
         <v>BOX</v>
       </c>
       <c r="I1026">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J1026" t="str">
         <v>Active</v>
@@ -36327,10 +36327,10 @@
         <v>1026</v>
       </c>
       <c r="B1027" t="str">
-        <v>FG-400582</v>
+        <v>FG-400581</v>
       </c>
       <c r="C1027" t="str">
-        <v>AGRI REDUCER (75X40MM)</v>
+        <v>AGRI REDUCER (75X50MM)</v>
       </c>
       <c r="D1027" t="str">
         <v>AGRI REDUCER</v>
@@ -36342,13 +36342,13 @@
         <v>General</v>
       </c>
       <c r="G1027" t="str">
-        <v>75X40MM</v>
+        <v>75X50MM</v>
       </c>
       <c r="H1027" t="str">
         <v>BOX</v>
       </c>
       <c r="I1027">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J1027" t="str">
         <v>Active</v>
@@ -36362,10 +36362,10 @@
         <v>1027</v>
       </c>
       <c r="B1028" t="str">
-        <v>FG-400581</v>
+        <v>FG-400580</v>
       </c>
       <c r="C1028" t="str">
-        <v>AGRI REDUCER (75X50MM)</v>
+        <v>AGRI REDUCER (75X63MM)</v>
       </c>
       <c r="D1028" t="str">
         <v>AGRI REDUCER</v>
@@ -36377,13 +36377,13 @@
         <v>General</v>
       </c>
       <c r="G1028" t="str">
-        <v>75X50MM</v>
+        <v>75X63MM</v>
       </c>
       <c r="H1028" t="str">
         <v>BOX</v>
       </c>
       <c r="I1028">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J1028" t="str">
         <v>Active</v>
@@ -36397,10 +36397,10 @@
         <v>1028</v>
       </c>
       <c r="B1029" t="str">
-        <v>FG-400580</v>
+        <v>FG-400579</v>
       </c>
       <c r="C1029" t="str">
-        <v>AGRI REDUCER (75X63MM)</v>
+        <v>AGRI REDUCER (90X50MM)</v>
       </c>
       <c r="D1029" t="str">
         <v>AGRI REDUCER</v>
@@ -36412,13 +36412,13 @@
         <v>General</v>
       </c>
       <c r="G1029" t="str">
-        <v>75X63MM</v>
+        <v>90X50MM</v>
       </c>
       <c r="H1029" t="str">
         <v>BOX</v>
       </c>
       <c r="I1029">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J1029" t="str">
         <v>Active</v>
@@ -36432,10 +36432,10 @@
         <v>1029</v>
       </c>
       <c r="B1030" t="str">
-        <v>FG-400579</v>
+        <v>FG-400578</v>
       </c>
       <c r="C1030" t="str">
-        <v>AGRI REDUCER (90X50MM)</v>
+        <v>AGRI REDUCER (90X63MM)</v>
       </c>
       <c r="D1030" t="str">
         <v>AGRI REDUCER</v>
@@ -36447,13 +36447,13 @@
         <v>General</v>
       </c>
       <c r="G1030" t="str">
-        <v>90X50MM</v>
+        <v>90X63MM</v>
       </c>
       <c r="H1030" t="str">
         <v>BOX</v>
       </c>
       <c r="I1030">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J1030" t="str">
         <v>Active</v>
@@ -36467,10 +36467,10 @@
         <v>1030</v>
       </c>
       <c r="B1031" t="str">
-        <v>FG-400578</v>
+        <v>FG-400577</v>
       </c>
       <c r="C1031" t="str">
-        <v>AGRI REDUCER (90X63MM)</v>
+        <v>AGRI REDUCER (90X75MM)</v>
       </c>
       <c r="D1031" t="str">
         <v>AGRI REDUCER</v>
@@ -36482,13 +36482,13 @@
         <v>General</v>
       </c>
       <c r="G1031" t="str">
-        <v>90X63MM</v>
+        <v>90X75MM</v>
       </c>
       <c r="H1031" t="str">
         <v>BOX</v>
       </c>
       <c r="I1031">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="J1031" t="str">
         <v>Active</v>
@@ -36502,10 +36502,10 @@
         <v>1031</v>
       </c>
       <c r="B1032" t="str">
-        <v>FG-400577</v>
+        <v>FG-400576</v>
       </c>
       <c r="C1032" t="str">
-        <v>AGRI REDUCER (90X75MM)</v>
+        <v>AGRI REDUCER (110X63MM)</v>
       </c>
       <c r="D1032" t="str">
         <v>AGRI REDUCER</v>
@@ -36517,13 +36517,13 @@
         <v>General</v>
       </c>
       <c r="G1032" t="str">
-        <v>90X75MM</v>
+        <v>110X63MM</v>
       </c>
       <c r="H1032" t="str">
         <v>BOX</v>
       </c>
       <c r="I1032">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J1032" t="str">
         <v>Active</v>
@@ -36537,10 +36537,10 @@
         <v>1032</v>
       </c>
       <c r="B1033" t="str">
-        <v>FG-400576</v>
+        <v>FG-400575</v>
       </c>
       <c r="C1033" t="str">
-        <v>AGRI REDUCER (110X63MM)</v>
+        <v>AGRI REDUCER (110X75MM)</v>
       </c>
       <c r="D1033" t="str">
         <v>AGRI REDUCER</v>
@@ -36552,7 +36552,7 @@
         <v>General</v>
       </c>
       <c r="G1033" t="str">
-        <v>110X63MM</v>
+        <v>110X75MM</v>
       </c>
       <c r="H1033" t="str">
         <v>BOX</v>
@@ -36572,10 +36572,10 @@
         <v>1033</v>
       </c>
       <c r="B1034" t="str">
-        <v>FG-400575</v>
+        <v>FG-400574</v>
       </c>
       <c r="C1034" t="str">
-        <v>AGRI REDUCER (110X75MM)</v>
+        <v>AGRI REDUCER (110X90MM)</v>
       </c>
       <c r="D1034" t="str">
         <v>AGRI REDUCER</v>
@@ -36587,13 +36587,13 @@
         <v>General</v>
       </c>
       <c r="G1034" t="str">
-        <v>110X75MM</v>
+        <v>110X90MM</v>
       </c>
       <c r="H1034" t="str">
         <v>BOX</v>
       </c>
       <c r="I1034">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J1034" t="str">
         <v>Active</v>
@@ -36607,13 +36607,13 @@
         <v>1034</v>
       </c>
       <c r="B1035" t="str">
-        <v>FG-400574</v>
+        <v>-</v>
       </c>
       <c r="C1035" t="str">
-        <v>AGRI REDUCER (110X90MM)</v>
+        <v>REDUCING BUSH (LW) (63 X 40)</v>
       </c>
       <c r="D1035" t="str">
-        <v>AGRI REDUCER</v>
+        <v>REDUCING BUSH (LW)</v>
       </c>
       <c r="E1035" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36622,19 +36622,19 @@
         <v>General</v>
       </c>
       <c r="G1035" t="str">
-        <v>110X90MM</v>
+        <v>63 X 40</v>
       </c>
       <c r="H1035" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1035">
-        <v>40</v>
+      <c r="I1035" t="str">
+        <v>-</v>
       </c>
       <c r="J1035" t="str">
         <v>Active</v>
       </c>
       <c r="K1035" t="str">
-        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
+        <v>REDUCING BUSH (LW) for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1036">
@@ -36645,7 +36645,7 @@
         <v>-</v>
       </c>
       <c r="C1036" t="str">
-        <v>REDUCING BUSH (LW) (63 X 40)</v>
+        <v>REDUCING BUSH (LW) (63 X 50)</v>
       </c>
       <c r="D1036" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36657,7 +36657,7 @@
         <v>General</v>
       </c>
       <c r="G1036" t="str">
-        <v>63 X 40</v>
+        <v>63 X 50</v>
       </c>
       <c r="H1036" t="str">
         <v>BOX</v>
@@ -36680,7 +36680,7 @@
         <v>-</v>
       </c>
       <c r="C1037" t="str">
-        <v>REDUCING BUSH (LW) (63 X 50)</v>
+        <v>REDUCING BUSH (LW) (75 X 40)</v>
       </c>
       <c r="D1037" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36692,7 +36692,7 @@
         <v>General</v>
       </c>
       <c r="G1037" t="str">
-        <v>63 X 50</v>
+        <v>75 X 40</v>
       </c>
       <c r="H1037" t="str">
         <v>BOX</v>
@@ -36715,7 +36715,7 @@
         <v>-</v>
       </c>
       <c r="C1038" t="str">
-        <v>REDUCING BUSH (LW) (75 X 40)</v>
+        <v>REDUCING BUSH (LW) (75 X 63)</v>
       </c>
       <c r="D1038" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36727,7 +36727,7 @@
         <v>General</v>
       </c>
       <c r="G1038" t="str">
-        <v>75 X 40</v>
+        <v>75 X 63</v>
       </c>
       <c r="H1038" t="str">
         <v>BOX</v>
@@ -36750,7 +36750,7 @@
         <v>-</v>
       </c>
       <c r="C1039" t="str">
-        <v>REDUCING BUSH (LW) (75 X 63)</v>
+        <v>REDUCING BUSH (LW) (90 X 50)</v>
       </c>
       <c r="D1039" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36762,7 +36762,7 @@
         <v>General</v>
       </c>
       <c r="G1039" t="str">
-        <v>75 X 63</v>
+        <v>90 X 50</v>
       </c>
       <c r="H1039" t="str">
         <v>BOX</v>
@@ -36785,7 +36785,7 @@
         <v>-</v>
       </c>
       <c r="C1040" t="str">
-        <v>REDUCING BUSH (LW) (90 X 50)</v>
+        <v>REDUCING BUSH (LW) (90 X 63)</v>
       </c>
       <c r="D1040" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36797,7 +36797,7 @@
         <v>General</v>
       </c>
       <c r="G1040" t="str">
-        <v>90 X 50</v>
+        <v>90 X 63</v>
       </c>
       <c r="H1040" t="str">
         <v>BOX</v>
@@ -36820,7 +36820,7 @@
         <v>-</v>
       </c>
       <c r="C1041" t="str">
-        <v>REDUCING BUSH (LW) (90 X 63)</v>
+        <v>REDUCING BUSH (LW) (90 X 75)</v>
       </c>
       <c r="D1041" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36832,7 +36832,7 @@
         <v>General</v>
       </c>
       <c r="G1041" t="str">
-        <v>90 X 63</v>
+        <v>90 X 75</v>
       </c>
       <c r="H1041" t="str">
         <v>BOX</v>
@@ -36855,7 +36855,7 @@
         <v>-</v>
       </c>
       <c r="C1042" t="str">
-        <v>REDUCING BUSH (LW) (90 X 75)</v>
+        <v>REDUCING BUSH (LW) (110 X 63)</v>
       </c>
       <c r="D1042" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36867,7 +36867,7 @@
         <v>General</v>
       </c>
       <c r="G1042" t="str">
-        <v>90 X 75</v>
+        <v>110 X 63</v>
       </c>
       <c r="H1042" t="str">
         <v>BOX</v>
@@ -36890,7 +36890,7 @@
         <v>-</v>
       </c>
       <c r="C1043" t="str">
-        <v>REDUCING BUSH (LW) (110 X 63)</v>
+        <v>REDUCING BUSH (LW) (110 X 75)</v>
       </c>
       <c r="D1043" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36902,7 +36902,7 @@
         <v>General</v>
       </c>
       <c r="G1043" t="str">
-        <v>110 X 63</v>
+        <v>110 X 75</v>
       </c>
       <c r="H1043" t="str">
         <v>BOX</v>
@@ -36925,7 +36925,7 @@
         <v>-</v>
       </c>
       <c r="C1044" t="str">
-        <v>REDUCING BUSH (LW) (110 X 75)</v>
+        <v>REDUCING BUSH (LW) (110 X 90)</v>
       </c>
       <c r="D1044" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36937,7 +36937,7 @@
         <v>General</v>
       </c>
       <c r="G1044" t="str">
-        <v>110 X 75</v>
+        <v>110 X 90</v>
       </c>
       <c r="H1044" t="str">
         <v>BOX</v>
@@ -36957,13 +36957,13 @@
         <v>1044</v>
       </c>
       <c r="B1045" t="str">
-        <v>-</v>
+        <v>FG-400550</v>
       </c>
       <c r="C1045" t="str">
-        <v>REDUCING BUSH (LW) (110 X 90)</v>
+        <v>AGRI TEE (40MM)</v>
       </c>
       <c r="D1045" t="str">
-        <v>REDUCING BUSH (LW)</v>
+        <v>AGRI TEE</v>
       </c>
       <c r="E1045" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36972,19 +36972,19 @@
         <v>General</v>
       </c>
       <c r="G1045" t="str">
-        <v>110 X 90</v>
+        <v>40MM</v>
       </c>
       <c r="H1045" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1045" t="str">
-        <v>-</v>
+      <c r="I1045">
+        <v>150</v>
       </c>
       <c r="J1045" t="str">
         <v>Active</v>
       </c>
       <c r="K1045" t="str">
-        <v>REDUCING BUSH (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1046">
@@ -36992,10 +36992,10 @@
         <v>1045</v>
       </c>
       <c r="B1046" t="str">
-        <v>FG-400550</v>
+        <v>FG-400551</v>
       </c>
       <c r="C1046" t="str">
-        <v>AGRI TEE (40MM)</v>
+        <v>AGRI TEE (50MM)</v>
       </c>
       <c r="D1046" t="str">
         <v>AGRI TEE</v>
@@ -37007,13 +37007,13 @@
         <v>General</v>
       </c>
       <c r="G1046" t="str">
-        <v>40MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1046" t="str">
         <v>BOX</v>
       </c>
       <c r="I1046">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J1046" t="str">
         <v>Active</v>
@@ -37027,10 +37027,10 @@
         <v>1046</v>
       </c>
       <c r="B1047" t="str">
-        <v>FG-400551</v>
+        <v>FG-400552</v>
       </c>
       <c r="C1047" t="str">
-        <v>AGRI TEE (50MM)</v>
+        <v>AGRI TEE (63MM)</v>
       </c>
       <c r="D1047" t="str">
         <v>AGRI TEE</v>
@@ -37042,13 +37042,13 @@
         <v>General</v>
       </c>
       <c r="G1047" t="str">
-        <v>50MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1047" t="str">
         <v>BOX</v>
       </c>
       <c r="I1047">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J1047" t="str">
         <v>Active</v>
@@ -37062,10 +37062,10 @@
         <v>1047</v>
       </c>
       <c r="B1048" t="str">
-        <v>FG-400552</v>
+        <v>FG-400553</v>
       </c>
       <c r="C1048" t="str">
-        <v>AGRI TEE (63MM)</v>
+        <v>AGRI TEE (75MM)</v>
       </c>
       <c r="D1048" t="str">
         <v>AGRI TEE</v>
@@ -37077,13 +37077,13 @@
         <v>General</v>
       </c>
       <c r="G1048" t="str">
-        <v>63MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1048" t="str">
         <v>BOX</v>
       </c>
       <c r="I1048">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="J1048" t="str">
         <v>Active</v>
@@ -37097,10 +37097,10 @@
         <v>1048</v>
       </c>
       <c r="B1049" t="str">
-        <v>FG-400553</v>
+        <v>FG-400554</v>
       </c>
       <c r="C1049" t="str">
-        <v>AGRI TEE (75MM)</v>
+        <v>AGRI TEE (90MM)</v>
       </c>
       <c r="D1049" t="str">
         <v>AGRI TEE</v>
@@ -37112,13 +37112,13 @@
         <v>General</v>
       </c>
       <c r="G1049" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1049" t="str">
         <v>BOX</v>
       </c>
       <c r="I1049">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J1049" t="str">
         <v>Active</v>
@@ -37132,10 +37132,10 @@
         <v>1049</v>
       </c>
       <c r="B1050" t="str">
-        <v>FG-400554</v>
+        <v>FG-400586</v>
       </c>
       <c r="C1050" t="str">
-        <v>AGRI TEE (90MM)</v>
+        <v>AGRI TEE (110MM)</v>
       </c>
       <c r="D1050" t="str">
         <v>AGRI TEE</v>
@@ -37147,13 +37147,13 @@
         <v>General</v>
       </c>
       <c r="G1050" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1050" t="str">
         <v>BOX</v>
       </c>
       <c r="I1050">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J1050" t="str">
         <v>Active</v>
@@ -37167,10 +37167,10 @@
         <v>1050</v>
       </c>
       <c r="B1051" t="str">
-        <v>FG-400586</v>
+        <v>FG-400607</v>
       </c>
       <c r="C1051" t="str">
-        <v>AGRI TEE (110MM)</v>
+        <v>AGRI TEE (140MM)</v>
       </c>
       <c r="D1051" t="str">
         <v>AGRI TEE</v>
@@ -37182,13 +37182,13 @@
         <v>General</v>
       </c>
       <c r="G1051" t="str">
-        <v>110MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1051" t="str">
         <v>BOX</v>
       </c>
       <c r="I1051">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="J1051" t="str">
         <v>Active</v>
@@ -37202,10 +37202,10 @@
         <v>1051</v>
       </c>
       <c r="B1052" t="str">
-        <v>FG-400607</v>
+        <v>FG-400608</v>
       </c>
       <c r="C1052" t="str">
-        <v>AGRI TEE (140MM)</v>
+        <v>AGRI TEE (160MM)</v>
       </c>
       <c r="D1052" t="str">
         <v>AGRI TEE</v>
@@ -37217,13 +37217,13 @@
         <v>General</v>
       </c>
       <c r="G1052" t="str">
-        <v>140MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1052" t="str">
         <v>BOX</v>
       </c>
       <c r="I1052">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J1052" t="str">
         <v>Active</v>
@@ -37237,13 +37237,13 @@
         <v>1052</v>
       </c>
       <c r="B1053" t="str">
-        <v>FG-400608</v>
+        <v>-</v>
       </c>
       <c r="C1053" t="str">
-        <v>AGRI TEE (160MM)</v>
+        <v>COUPLER (LW) (75MM)</v>
       </c>
       <c r="D1053" t="str">
-        <v>AGRI TEE</v>
+        <v>COUPLER (LW)</v>
       </c>
       <c r="E1053" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37252,19 +37252,19 @@
         <v>General</v>
       </c>
       <c r="G1053" t="str">
-        <v>160MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1053" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1053">
-        <v>9</v>
+      <c r="I1053" t="str">
+        <v>-</v>
       </c>
       <c r="J1053" t="str">
         <v>Active</v>
       </c>
       <c r="K1053" t="str">
-        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
+        <v>COUPLER (LW) for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1054">
@@ -37275,7 +37275,7 @@
         <v>-</v>
       </c>
       <c r="C1054" t="str">
-        <v>COUPLER (LW) (75MM)</v>
+        <v>COUPLER (LW) (90MM)</v>
       </c>
       <c r="D1054" t="str">
         <v>COUPLER (LW)</v>
@@ -37287,7 +37287,7 @@
         <v>General</v>
       </c>
       <c r="G1054" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1054" t="str">
         <v>BOX</v>
@@ -37310,7 +37310,7 @@
         <v>-</v>
       </c>
       <c r="C1055" t="str">
-        <v>COUPLER (LW) (90MM)</v>
+        <v>COUPLER (LW) (110MM)</v>
       </c>
       <c r="D1055" t="str">
         <v>COUPLER (LW)</v>
@@ -37322,7 +37322,7 @@
         <v>General</v>
       </c>
       <c r="G1055" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1055" t="str">
         <v>BOX</v>
@@ -37342,13 +37342,13 @@
         <v>1055</v>
       </c>
       <c r="B1056" t="str">
-        <v>-</v>
+        <v>FG-400561</v>
       </c>
       <c r="C1056" t="str">
-        <v>COUPLER (LW) (110MM)</v>
+        <v>AGRI FABRICATED COUPLER (40MM)</v>
       </c>
       <c r="D1056" t="str">
-        <v>COUPLER (LW)</v>
+        <v>AGRI FABRICATED COUPLER</v>
       </c>
       <c r="E1056" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37357,19 +37357,19 @@
         <v>General</v>
       </c>
       <c r="G1056" t="str">
-        <v>110MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1056" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1056" t="str">
-        <v>-</v>
+      <c r="I1056">
+        <v>300</v>
       </c>
       <c r="J1056" t="str">
         <v>Active</v>
       </c>
       <c r="K1056" t="str">
-        <v>COUPLER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI FABRICATED COUPLER for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1057">
@@ -37377,10 +37377,10 @@
         <v>1056</v>
       </c>
       <c r="B1057" t="str">
-        <v>FG-400561</v>
+        <v>FG-400562</v>
       </c>
       <c r="C1057" t="str">
-        <v>AGRI FABRICATED COUPLER (40MM)</v>
+        <v>AGRI FABRICATED COUPLER (50MM)</v>
       </c>
       <c r="D1057" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37392,13 +37392,13 @@
         <v>General</v>
       </c>
       <c r="G1057" t="str">
-        <v>40MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1057" t="str">
         <v>BOX</v>
       </c>
       <c r="I1057">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J1057" t="str">
         <v>Active</v>
@@ -37412,10 +37412,10 @@
         <v>1057</v>
       </c>
       <c r="B1058" t="str">
-        <v>FG-400562</v>
+        <v>FG-400563</v>
       </c>
       <c r="C1058" t="str">
-        <v>AGRI FABRICATED COUPLER (50MM)</v>
+        <v>AGRI FABRICATED COUPLER (63MM)</v>
       </c>
       <c r="D1058" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37427,7 +37427,7 @@
         <v>General</v>
       </c>
       <c r="G1058" t="str">
-        <v>50MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1058" t="str">
         <v>BOX</v>
@@ -37447,10 +37447,10 @@
         <v>1058</v>
       </c>
       <c r="B1059" t="str">
-        <v>FG-400563</v>
+        <v>FG-400564</v>
       </c>
       <c r="C1059" t="str">
-        <v>AGRI FABRICATED COUPLER (63MM)</v>
+        <v>AGRI FABRICATED COUPLER (75MM)</v>
       </c>
       <c r="D1059" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37462,13 +37462,13 @@
         <v>General</v>
       </c>
       <c r="G1059" t="str">
-        <v>63MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1059" t="str">
         <v>BOX</v>
       </c>
       <c r="I1059">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="J1059" t="str">
         <v>Active</v>
@@ -37482,10 +37482,10 @@
         <v>1059</v>
       </c>
       <c r="B1060" t="str">
-        <v>FG-400564</v>
+        <v>FG-400565</v>
       </c>
       <c r="C1060" t="str">
-        <v>AGRI FABRICATED COUPLER (75MM)</v>
+        <v>AGRI FABRICATED COUPLER (90MM)</v>
       </c>
       <c r="D1060" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37497,13 +37497,13 @@
         <v>General</v>
       </c>
       <c r="G1060" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1060" t="str">
         <v>BOX</v>
       </c>
       <c r="I1060">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="J1060" t="str">
         <v>Active</v>
@@ -37517,10 +37517,10 @@
         <v>1060</v>
       </c>
       <c r="B1061" t="str">
-        <v>FG-400565</v>
+        <v>FG-400566</v>
       </c>
       <c r="C1061" t="str">
-        <v>AGRI FABRICATED COUPLER (90MM)</v>
+        <v>AGRI FABRICATED COUPLER (110MM)</v>
       </c>
       <c r="D1061" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37532,13 +37532,13 @@
         <v>General</v>
       </c>
       <c r="G1061" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1061" t="str">
         <v>BOX</v>
       </c>
       <c r="I1061">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J1061" t="str">
         <v>Active</v>
@@ -37552,10 +37552,10 @@
         <v>1061</v>
       </c>
       <c r="B1062" t="str">
-        <v>FG-400566</v>
+        <v>FG-400587</v>
       </c>
       <c r="C1062" t="str">
-        <v>AGRI FABRICATED COUPLER (110MM)</v>
+        <v>AGRI FABRICATED COUPLER (140MM 4KG)</v>
       </c>
       <c r="D1062" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37567,13 +37567,13 @@
         <v>General</v>
       </c>
       <c r="G1062" t="str">
-        <v>110MM</v>
+        <v>140MM 4KG</v>
       </c>
       <c r="H1062" t="str">
         <v>BOX</v>
       </c>
       <c r="I1062">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J1062" t="str">
         <v>Active</v>
@@ -37587,10 +37587,10 @@
         <v>1062</v>
       </c>
       <c r="B1063" t="str">
-        <v>FG-400587</v>
+        <v>FG-400568</v>
       </c>
       <c r="C1063" t="str">
-        <v>AGRI FABRICATED COUPLER (140MM 4KG)</v>
+        <v>AGRI FABRICATED COUPLER (160MM 4KG)</v>
       </c>
       <c r="D1063" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37602,13 +37602,13 @@
         <v>General</v>
       </c>
       <c r="G1063" t="str">
-        <v>140MM 4KG</v>
+        <v>160MM 4KG</v>
       </c>
       <c r="H1063" t="str">
         <v>BOX</v>
       </c>
       <c r="I1063">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J1063" t="str">
         <v>Active</v>
@@ -37622,13 +37622,13 @@
         <v>1063</v>
       </c>
       <c r="B1064" t="str">
-        <v>FG-400568</v>
+        <v>FG-400567</v>
       </c>
       <c r="C1064" t="str">
-        <v>AGRI FABRICATED COUPLER (160MM 4KG)</v>
+        <v>AGRI FABRICATED COUPLER 6KG (140MM)</v>
       </c>
       <c r="D1064" t="str">
-        <v>AGRI FABRICATED COUPLER</v>
+        <v>AGRI FABRICATED COUPLER 6KG</v>
       </c>
       <c r="E1064" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37637,19 +37637,19 @@
         <v>General</v>
       </c>
       <c r="G1064" t="str">
-        <v>160MM 4KG</v>
+        <v>140MM</v>
       </c>
       <c r="H1064" t="str">
         <v>BOX</v>
       </c>
       <c r="I1064">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J1064" t="str">
         <v>Active</v>
       </c>
       <c r="K1064" t="str">
-        <v>AGRI FABRICATED COUPLER for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
+        <v>AGRI FABRICATED COUPLER 6KG for agriculture irrigation and piping systems. Available sizes: 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1065">
@@ -37657,10 +37657,10 @@
         <v>1064</v>
       </c>
       <c r="B1065" t="str">
-        <v>FG-400567</v>
+        <v>FG-400569</v>
       </c>
       <c r="C1065" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG (140MM)</v>
+        <v>AGRI FABRICATED COUPLER 6KG (160MM)</v>
       </c>
       <c r="D1065" t="str">
         <v>AGRI FABRICATED COUPLER 6KG</v>
@@ -37672,13 +37672,13 @@
         <v>General</v>
       </c>
       <c r="G1065" t="str">
-        <v>140MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1065" t="str">
         <v>BOX</v>
       </c>
       <c r="I1065">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J1065" t="str">
         <v>Active</v>
@@ -37692,13 +37692,13 @@
         <v>1065</v>
       </c>
       <c r="B1066" t="str">
-        <v>FG-400569</v>
+        <v>FG-400544</v>
       </c>
       <c r="C1066" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG (160MM)</v>
+        <v>AGRI ELBOW (40MM)</v>
       </c>
       <c r="D1066" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG</v>
+        <v>AGRI ELBOW</v>
       </c>
       <c r="E1066" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37707,19 +37707,19 @@
         <v>General</v>
       </c>
       <c r="G1066" t="str">
-        <v>160MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1066" t="str">
         <v>BOX</v>
       </c>
       <c r="I1066">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="J1066" t="str">
         <v>Active</v>
       </c>
       <c r="K1066" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG for agriculture irrigation and piping systems. Available sizes: 140MM, 160MM.</v>
+        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1067">
@@ -37727,10 +37727,10 @@
         <v>1066</v>
       </c>
       <c r="B1067" t="str">
-        <v>FG-400544</v>
+        <v>FG-400545</v>
       </c>
       <c r="C1067" t="str">
-        <v>AGRI ELBOW (40MM)</v>
+        <v>AGRI ELBOW (50MM)</v>
       </c>
       <c r="D1067" t="str">
         <v>AGRI ELBOW</v>
@@ -37742,13 +37742,13 @@
         <v>General</v>
       </c>
       <c r="G1067" t="str">
-        <v>40MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1067" t="str">
         <v>BOX</v>
       </c>
       <c r="I1067">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="J1067" t="str">
         <v>Active</v>
@@ -37762,10 +37762,10 @@
         <v>1067</v>
       </c>
       <c r="B1068" t="str">
-        <v>FG-400545</v>
+        <v>FG-400546</v>
       </c>
       <c r="C1068" t="str">
-        <v>AGRI ELBOW (50MM)</v>
+        <v>AGRI ELBOW (63MM)</v>
       </c>
       <c r="D1068" t="str">
         <v>AGRI ELBOW</v>
@@ -37777,13 +37777,13 @@
         <v>General</v>
       </c>
       <c r="G1068" t="str">
-        <v>50MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1068" t="str">
         <v>BOX</v>
       </c>
       <c r="I1068">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J1068" t="str">
         <v>Active</v>
@@ -37797,10 +37797,10 @@
         <v>1068</v>
       </c>
       <c r="B1069" t="str">
-        <v>FG-400546</v>
+        <v>FG-400547</v>
       </c>
       <c r="C1069" t="str">
-        <v>AGRI ELBOW (63MM)</v>
+        <v>AGRI ELBOW (75MM)</v>
       </c>
       <c r="D1069" t="str">
         <v>AGRI ELBOW</v>
@@ -37812,13 +37812,13 @@
         <v>General</v>
       </c>
       <c r="G1069" t="str">
-        <v>63MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1069" t="str">
         <v>BOX</v>
       </c>
       <c r="I1069">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J1069" t="str">
         <v>Active</v>
@@ -37832,10 +37832,10 @@
         <v>1069</v>
       </c>
       <c r="B1070" t="str">
-        <v>FG-400547</v>
+        <v>FG-400548</v>
       </c>
       <c r="C1070" t="str">
-        <v>AGRI ELBOW (75MM)</v>
+        <v>AGRI ELBOW (90MM)</v>
       </c>
       <c r="D1070" t="str">
         <v>AGRI ELBOW</v>
@@ -37847,13 +37847,13 @@
         <v>General</v>
       </c>
       <c r="G1070" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1070" t="str">
         <v>BOX</v>
       </c>
       <c r="I1070">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="J1070" t="str">
         <v>Active</v>
@@ -37867,10 +37867,10 @@
         <v>1070</v>
       </c>
       <c r="B1071" t="str">
-        <v>FG-400548</v>
+        <v>FG-400549</v>
       </c>
       <c r="C1071" t="str">
-        <v>AGRI ELBOW (90MM)</v>
+        <v>AGRI ELBOW (110MM)</v>
       </c>
       <c r="D1071" t="str">
         <v>AGRI ELBOW</v>
@@ -37882,13 +37882,13 @@
         <v>General</v>
       </c>
       <c r="G1071" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1071" t="str">
         <v>BOX</v>
       </c>
       <c r="I1071">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J1071" t="str">
         <v>Active</v>
@@ -37902,10 +37902,10 @@
         <v>1071</v>
       </c>
       <c r="B1072" t="str">
-        <v>FG-400549</v>
+        <v>FG-400595</v>
       </c>
       <c r="C1072" t="str">
-        <v>AGRI ELBOW (110MM)</v>
+        <v>AGRI ELBOW (140MM)</v>
       </c>
       <c r="D1072" t="str">
         <v>AGRI ELBOW</v>
@@ -37917,13 +37917,13 @@
         <v>General</v>
       </c>
       <c r="G1072" t="str">
-        <v>110MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1072" t="str">
         <v>BOX</v>
       </c>
       <c r="I1072">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="J1072" t="str">
         <v>Active</v>
@@ -37937,10 +37937,10 @@
         <v>1072</v>
       </c>
       <c r="B1073" t="str">
-        <v>FG-400595</v>
+        <v>FG-400596</v>
       </c>
       <c r="C1073" t="str">
-        <v>AGRI ELBOW (140MM)</v>
+        <v>AGRI ELBOW (160MM)</v>
       </c>
       <c r="D1073" t="str">
         <v>AGRI ELBOW</v>
@@ -37952,13 +37952,13 @@
         <v>General</v>
       </c>
       <c r="G1073" t="str">
-        <v>140MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1073" t="str">
         <v>BOX</v>
       </c>
       <c r="I1073">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J1073" t="str">
         <v>Active</v>
@@ -37972,13 +37972,13 @@
         <v>1073</v>
       </c>
       <c r="B1074" t="str">
-        <v>FG-400596</v>
+        <v>FG-400555</v>
       </c>
       <c r="C1074" t="str">
-        <v>AGRI ELBOW (160MM)</v>
+        <v>AGRI END CAP (40MM)</v>
       </c>
       <c r="D1074" t="str">
-        <v>AGRI ELBOW</v>
+        <v>AGRI END CAP</v>
       </c>
       <c r="E1074" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37987,19 +37987,19 @@
         <v>General</v>
       </c>
       <c r="G1074" t="str">
-        <v>160MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1074" t="str">
         <v>BOX</v>
       </c>
       <c r="I1074">
-        <v>12</v>
+        <v>800</v>
       </c>
       <c r="J1074" t="str">
         <v>Active</v>
       </c>
       <c r="K1074" t="str">
-        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
+        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1075">
@@ -38007,10 +38007,10 @@
         <v>1074</v>
       </c>
       <c r="B1075" t="str">
-        <v>FG-400555</v>
+        <v>FG-400556</v>
       </c>
       <c r="C1075" t="str">
-        <v>AGRI END CAP (40MM)</v>
+        <v>AGRI END CAP (50MM)</v>
       </c>
       <c r="D1075" t="str">
         <v>AGRI END CAP</v>
@@ -38022,13 +38022,13 @@
         <v>General</v>
       </c>
       <c r="G1075" t="str">
-        <v>40MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1075" t="str">
         <v>BOX</v>
       </c>
       <c r="I1075">
-        <v>800</v>
+        <v>450</v>
       </c>
       <c r="J1075" t="str">
         <v>Active</v>
@@ -38042,10 +38042,10 @@
         <v>1075</v>
       </c>
       <c r="B1076" t="str">
-        <v>FG-400556</v>
+        <v>FG-400557</v>
       </c>
       <c r="C1076" t="str">
-        <v>AGRI END CAP (50MM)</v>
+        <v>AGRI END CAP (63MM)</v>
       </c>
       <c r="D1076" t="str">
         <v>AGRI END CAP</v>
@@ -38057,13 +38057,13 @@
         <v>General</v>
       </c>
       <c r="G1076" t="str">
-        <v>50MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1076" t="str">
         <v>BOX</v>
       </c>
       <c r="I1076">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="J1076" t="str">
         <v>Active</v>
@@ -38077,10 +38077,10 @@
         <v>1076</v>
       </c>
       <c r="B1077" t="str">
-        <v>FG-400557</v>
+        <v>FG-400558</v>
       </c>
       <c r="C1077" t="str">
-        <v>AGRI END CAP (63MM)</v>
+        <v>AGRI END CAP (75MM)</v>
       </c>
       <c r="D1077" t="str">
         <v>AGRI END CAP</v>
@@ -38092,13 +38092,13 @@
         <v>General</v>
       </c>
       <c r="G1077" t="str">
-        <v>63MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1077" t="str">
         <v>BOX</v>
       </c>
       <c r="I1077">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="J1077" t="str">
         <v>Active</v>
@@ -38112,10 +38112,10 @@
         <v>1077</v>
       </c>
       <c r="B1078" t="str">
-        <v>FG-400558</v>
+        <v>FG-400559</v>
       </c>
       <c r="C1078" t="str">
-        <v>AGRI END CAP (75MM)</v>
+        <v>AGRI END CAP (90MM)</v>
       </c>
       <c r="D1078" t="str">
         <v>AGRI END CAP</v>
@@ -38127,13 +38127,13 @@
         <v>General</v>
       </c>
       <c r="G1078" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1078" t="str">
         <v>BOX</v>
       </c>
       <c r="I1078">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J1078" t="str">
         <v>Active</v>
@@ -38147,10 +38147,10 @@
         <v>1078</v>
       </c>
       <c r="B1079" t="str">
-        <v>FG-400559</v>
+        <v>FG-400560</v>
       </c>
       <c r="C1079" t="str">
-        <v>AGRI END CAP (90MM)</v>
+        <v>AGRI END CAP (110MM)</v>
       </c>
       <c r="D1079" t="str">
         <v>AGRI END CAP</v>
@@ -38162,13 +38162,13 @@
         <v>General</v>
       </c>
       <c r="G1079" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1079" t="str">
         <v>BOX</v>
       </c>
       <c r="I1079">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J1079" t="str">
         <v>Active</v>
@@ -38182,10 +38182,10 @@
         <v>1079</v>
       </c>
       <c r="B1080" t="str">
-        <v>FG-400560</v>
+        <v>FG-400639</v>
       </c>
       <c r="C1080" t="str">
-        <v>AGRI END CAP (110MM)</v>
+        <v>AGRI END CAP (140MM 4KG)</v>
       </c>
       <c r="D1080" t="str">
         <v>AGRI END CAP</v>
@@ -38197,13 +38197,13 @@
         <v>General</v>
       </c>
       <c r="G1080" t="str">
-        <v>110MM</v>
+        <v>140MM 4KG</v>
       </c>
       <c r="H1080" t="str">
         <v>BOX</v>
       </c>
       <c r="I1080">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J1080" t="str">
         <v>Active</v>
@@ -38217,10 +38217,10 @@
         <v>1080</v>
       </c>
       <c r="B1081" t="str">
-        <v>FG-400639</v>
+        <v>FG-400640</v>
       </c>
       <c r="C1081" t="str">
-        <v>AGRI END CAP (140MM 4KG)</v>
+        <v>AGRI END CAP (160MM 4KG)</v>
       </c>
       <c r="D1081" t="str">
         <v>AGRI END CAP</v>
@@ -38232,13 +38232,13 @@
         <v>General</v>
       </c>
       <c r="G1081" t="str">
-        <v>140MM 4KG</v>
+        <v>160MM 4KG</v>
       </c>
       <c r="H1081" t="str">
         <v>BOX</v>
       </c>
       <c r="I1081">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J1081" t="str">
         <v>Active</v>
@@ -38252,13 +38252,13 @@
         <v>1081</v>
       </c>
       <c r="B1082" t="str">
-        <v>FG-400640</v>
+        <v>FG-400570</v>
       </c>
       <c r="C1082" t="str">
-        <v>AGRI END CAP (160MM 4KG)</v>
+        <v>AGRI LONG BEND (63MM)</v>
       </c>
       <c r="D1082" t="str">
-        <v>AGRI END CAP</v>
+        <v>AGRI LONG BEND</v>
       </c>
       <c r="E1082" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -38267,19 +38267,19 @@
         <v>General</v>
       </c>
       <c r="G1082" t="str">
-        <v>160MM 4KG</v>
+        <v>63MM</v>
       </c>
       <c r="H1082" t="str">
         <v>BOX</v>
       </c>
       <c r="I1082">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="J1082" t="str">
         <v>Active</v>
       </c>
       <c r="K1082" t="str">
-        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
+        <v>AGRI LONG BEND for agriculture irrigation and piping systems. Available sizes: 63MM, 75MM, 90MM, 110MM.</v>
       </c>
     </row>
     <row r="1083">
@@ -38287,10 +38287,10 @@
         <v>1082</v>
       </c>
       <c r="B1083" t="str">
-        <v>FG-400570</v>
+        <v>FG-400571</v>
       </c>
       <c r="C1083" t="str">
-        <v>AGRI LONG BEND (63MM)</v>
+        <v>AGRI LONG BEND (75MM)</v>
       </c>
       <c r="D1083" t="str">
         <v>AGRI LONG BEND</v>
@@ -38302,13 +38302,13 @@
         <v>General</v>
       </c>
       <c r="G1083" t="str">
-        <v>63MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1083" t="str">
         <v>BOX</v>
       </c>
       <c r="I1083">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J1083" t="str">
         <v>Active</v>
@@ -38322,10 +38322,10 @@
         <v>1083</v>
       </c>
       <c r="B1084" t="str">
-        <v>FG-400571</v>
+        <v>FG-400572</v>
       </c>
       <c r="C1084" t="str">
-        <v>AGRI LONG BEND (75MM)</v>
+        <v>AGRI LONG BEND (90MM)</v>
       </c>
       <c r="D1084" t="str">
         <v>AGRI LONG BEND</v>
@@ -38337,13 +38337,13 @@
         <v>General</v>
       </c>
       <c r="G1084" t="str">
-        <v>75MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1084" t="str">
         <v>BOX</v>
       </c>
       <c r="I1084">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J1084" t="str">
         <v>Active</v>
@@ -38357,10 +38357,10 @@
         <v>1084</v>
       </c>
       <c r="B1085" t="str">
-        <v>FG-400572</v>
+        <v>FG-400573</v>
       </c>
       <c r="C1085" t="str">
-        <v>AGRI LONG BEND (90MM)</v>
+        <v>AGRI LONG BEND (110MM)</v>
       </c>
       <c r="D1085" t="str">
         <v>AGRI LONG BEND</v>
@@ -38372,13 +38372,13 @@
         <v>General</v>
       </c>
       <c r="G1085" t="str">
-        <v>90MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1085" t="str">
         <v>BOX</v>
       </c>
       <c r="I1085">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J1085" t="str">
         <v>Active</v>
@@ -38392,34 +38392,34 @@
         <v>1085</v>
       </c>
       <c r="B1086" t="str">
-        <v>FG-400573</v>
+        <v>FG-401520</v>
       </c>
       <c r="C1086" t="str">
-        <v>AGRI LONG BEND (110MM)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1086" t="str">
-        <v>AGRI LONG BEND</v>
+        <v>SPRINKLER ISI PIPE 6 MTR</v>
       </c>
       <c r="E1086" t="str">
-        <v>Agriculture Pipes &amp; Fittings</v>
+        <v>Sprinkler Pipes &amp; Fittings</v>
       </c>
       <c r="F1086" t="str">
         <v>General</v>
       </c>
       <c r="G1086" t="str">
-        <v>110MM</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1086" t="str">
-        <v>BOX</v>
-      </c>
-      <c r="I1086">
-        <v>10</v>
+        <v>Nos</v>
+      </c>
+      <c r="I1086" t="str">
+        <v>-</v>
       </c>
       <c r="J1086" t="str">
         <v>Active</v>
       </c>
       <c r="K1086" t="str">
-        <v>AGRI LONG BEND for agriculture irrigation and piping systems. Available sizes: 63MM, 75MM, 90MM, 110MM.</v>
+        <v>SPRINKLER ISI PIPE 6 MTR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1087">
@@ -38427,10 +38427,10 @@
         <v>1086</v>
       </c>
       <c r="B1087" t="str">
-        <v>FG-401520</v>
+        <v>FG-401491</v>
       </c>
       <c r="C1087" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (63MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1087" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38442,7 +38442,7 @@
         <v>General</v>
       </c>
       <c r="G1087" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>63MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1087" t="str">
         <v>Nos</v>
@@ -38462,10 +38462,10 @@
         <v>1087</v>
       </c>
       <c r="B1088" t="str">
-        <v>FG-401491</v>
+        <v>FG-401490</v>
       </c>
       <c r="C1088" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (63MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 2.5 KG)</v>
       </c>
       <c r="D1088" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38477,7 +38477,7 @@
         <v>General</v>
       </c>
       <c r="G1088" t="str">
-        <v>63MM L TYPE 3.2 KG</v>
+        <v>75MM C TYPE 2.5 KG</v>
       </c>
       <c r="H1088" t="str">
         <v>Nos</v>
@@ -38497,10 +38497,10 @@
         <v>1088</v>
       </c>
       <c r="B1089" t="str">
-        <v>FG-401490</v>
+        <v>FG-401492</v>
       </c>
       <c r="C1089" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 2.5 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1089" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38512,7 +38512,7 @@
         <v>General</v>
       </c>
       <c r="G1089" t="str">
-        <v>75MM C TYPE 2.5 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1089" t="str">
         <v>Nos</v>
@@ -38532,10 +38532,10 @@
         <v>1089</v>
       </c>
       <c r="B1090" t="str">
-        <v>FG-401492</v>
+        <v>FG-401519</v>
       </c>
       <c r="C1090" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 2.5 KG)</v>
       </c>
       <c r="D1090" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38547,7 +38547,7 @@
         <v>General</v>
       </c>
       <c r="G1090" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>75MM L TYPE 2.5 KG</v>
       </c>
       <c r="H1090" t="str">
         <v>Nos</v>
@@ -38567,10 +38567,10 @@
         <v>1090</v>
       </c>
       <c r="B1091" t="str">
-        <v>FG-401519</v>
+        <v>FG-401521</v>
       </c>
       <c r="C1091" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 2.5 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1091" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38582,7 +38582,7 @@
         <v>General</v>
       </c>
       <c r="G1091" t="str">
-        <v>75MM L TYPE 2.5 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1091" t="str">
         <v>Nos</v>
@@ -38602,13 +38602,13 @@
         <v>1091</v>
       </c>
       <c r="B1092" t="str">
-        <v>FG-401521</v>
+        <v>FG-401522</v>
       </c>
       <c r="C1092" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1092" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR</v>
+        <v>SPRINKLER NISI PIPE 6 MTR</v>
       </c>
       <c r="E1092" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38629,7 +38629,7 @@
         <v>Active</v>
       </c>
       <c r="K1092" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER NISI PIPE 6 MTR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1093">
@@ -38637,10 +38637,10 @@
         <v>1092</v>
       </c>
       <c r="B1093" t="str">
-        <v>FG-401522</v>
+        <v>FG-401523</v>
       </c>
       <c r="C1093" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1093" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38652,7 +38652,7 @@
         <v>General</v>
       </c>
       <c r="G1093" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1093" t="str">
         <v>Nos</v>
@@ -38672,10 +38672,10 @@
         <v>1093</v>
       </c>
       <c r="B1094" t="str">
-        <v>FG-401523</v>
+        <v>FG-401866</v>
       </c>
       <c r="C1094" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (90MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1094" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38687,7 +38687,7 @@
         <v>General</v>
       </c>
       <c r="G1094" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>90MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1094" t="str">
         <v>Nos</v>
@@ -38707,10 +38707,10 @@
         <v>1094</v>
       </c>
       <c r="B1095" t="str">
-        <v>FG-401866</v>
+        <v>FG-401867</v>
       </c>
       <c r="C1095" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (90MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (90MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1095" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38722,7 +38722,7 @@
         <v>General</v>
       </c>
       <c r="G1095" t="str">
-        <v>90MM C TYPE 3.2 KG</v>
+        <v>90MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1095" t="str">
         <v>Nos</v>
@@ -38742,13 +38742,13 @@
         <v>1095</v>
       </c>
       <c r="B1096" t="str">
-        <v>FG-401867</v>
+        <v>FG-401498</v>
       </c>
       <c r="C1096" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (90MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1096" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR</v>
+        <v>SPRINKLER SET 6 MTR ISI</v>
       </c>
       <c r="E1096" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38757,7 +38757,7 @@
         <v>General</v>
       </c>
       <c r="G1096" t="str">
-        <v>90MM L TYPE 3.2 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1096" t="str">
         <v>Nos</v>
@@ -38769,7 +38769,7 @@
         <v>Active</v>
       </c>
       <c r="K1096" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER SET 6 MTR ISI for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1097">
@@ -38777,10 +38777,10 @@
         <v>1096</v>
       </c>
       <c r="B1097" t="str">
-        <v>FG-401498</v>
+        <v>FG-401499</v>
       </c>
       <c r="C1097" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1097" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38792,7 +38792,7 @@
         <v>General</v>
       </c>
       <c r="G1097" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1097" t="str">
         <v>Nos</v>
@@ -38812,10 +38812,10 @@
         <v>1097</v>
       </c>
       <c r="B1098" t="str">
-        <v>FG-401499</v>
+        <v>FG-401500</v>
       </c>
       <c r="C1098" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 2.5 KG)</v>
       </c>
       <c r="D1098" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38827,7 +38827,7 @@
         <v>General</v>
       </c>
       <c r="G1098" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>75MM C TYPE 2.5 KG</v>
       </c>
       <c r="H1098" t="str">
         <v>Nos</v>
@@ -38847,10 +38847,10 @@
         <v>1098</v>
       </c>
       <c r="B1099" t="str">
-        <v>FG-401500</v>
+        <v>FG-401524</v>
       </c>
       <c r="C1099" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 2.5 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 2.5 KG)</v>
       </c>
       <c r="D1099" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38862,7 +38862,7 @@
         <v>General</v>
       </c>
       <c r="G1099" t="str">
-        <v>75MM C TYPE 2.5 KG</v>
+        <v>75MM L TYPE 2.5 KG</v>
       </c>
       <c r="H1099" t="str">
         <v>Nos</v>
@@ -38882,10 +38882,10 @@
         <v>1099</v>
       </c>
       <c r="B1100" t="str">
-        <v>FG-401524</v>
+        <v>FG-401501</v>
       </c>
       <c r="C1100" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 2.5 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1100" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38897,7 +38897,7 @@
         <v>General</v>
       </c>
       <c r="G1100" t="str">
-        <v>75MM L TYPE 2.5 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1100" t="str">
         <v>Nos</v>
@@ -38917,13 +38917,13 @@
         <v>1100</v>
       </c>
       <c r="B1101" t="str">
-        <v>FG-401501</v>
+        <v>FG-401495</v>
       </c>
       <c r="C1101" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1101" t="str">
-        <v>SPRINKLER SET 6 MTR ISI</v>
+        <v>SPRINKLER SET 6 MTR N-ISI</v>
       </c>
       <c r="E1101" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38932,7 +38932,7 @@
         <v>General</v>
       </c>
       <c r="G1101" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1101" t="str">
         <v>Nos</v>
@@ -38944,7 +38944,7 @@
         <v>Active</v>
       </c>
       <c r="K1101" t="str">
-        <v>SPRINKLER SET 6 MTR ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER SET 6 MTR N-ISI for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1102">
@@ -38952,10 +38952,10 @@
         <v>1101</v>
       </c>
       <c r="B1102" t="str">
-        <v>FG-401495</v>
+        <v>FG-401496</v>
       </c>
       <c r="C1102" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1102" t="str">
         <v>SPRINKLER SET 6 MTR N-ISI</v>
@@ -38967,7 +38967,7 @@
         <v>General</v>
       </c>
       <c r="G1102" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1102" t="str">
         <v>Nos</v>
@@ -38987,10 +38987,10 @@
         <v>1102</v>
       </c>
       <c r="B1103" t="str">
-        <v>FG-401496</v>
+        <v>FG-401497</v>
       </c>
       <c r="C1103" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1103" t="str">
         <v>SPRINKLER SET 6 MTR N-ISI</v>
@@ -39002,7 +39002,7 @@
         <v>General</v>
       </c>
       <c r="G1103" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1103" t="str">
         <v>Nos</v>
@@ -39022,13 +39022,13 @@
         <v>1103</v>
       </c>
       <c r="B1104" t="str">
-        <v>FG-401497</v>
+        <v>FG-401503</v>
       </c>
       <c r="C1104" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER FITTINGS TEE (75MM, C TYPE)</v>
       </c>
       <c r="D1104" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI</v>
+        <v>SPRINKLER FITTINGS TEE</v>
       </c>
       <c r="E1104" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39037,7 +39037,7 @@
         <v>General</v>
       </c>
       <c r="G1104" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM, C TYPE</v>
       </c>
       <c r="H1104" t="str">
         <v>Nos</v>
@@ -39049,7 +39049,7 @@
         <v>Active</v>
       </c>
       <c r="K1104" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS TEE for sprinkler irrigation systems. Available sizes: 75MM, C TYPE, 75MM, L TYPE, 63MM, C TYPE.</v>
       </c>
     </row>
     <row r="1105">
@@ -39057,10 +39057,10 @@
         <v>1104</v>
       </c>
       <c r="B1105" t="str">
-        <v>FG-401503</v>
+        <v>FG-401511</v>
       </c>
       <c r="C1105" t="str">
-        <v>SPRINKLER FITTINGS TEE (75MM, C TYPE)</v>
+        <v>SPRINKLER FITTINGS TEE (75MM, L TYPE)</v>
       </c>
       <c r="D1105" t="str">
         <v>SPRINKLER FITTINGS TEE</v>
@@ -39072,7 +39072,7 @@
         <v>General</v>
       </c>
       <c r="G1105" t="str">
-        <v>75MM, C TYPE</v>
+        <v>75MM, L TYPE</v>
       </c>
       <c r="H1105" t="str">
         <v>Nos</v>
@@ -39092,10 +39092,10 @@
         <v>1105</v>
       </c>
       <c r="B1106" t="str">
-        <v>FG-401511</v>
+        <v>FG-401526</v>
       </c>
       <c r="C1106" t="str">
-        <v>SPRINKLER FITTINGS TEE (75MM, L TYPE)</v>
+        <v>SPRINKLER FITTINGS TEE (63MM, C TYPE)</v>
       </c>
       <c r="D1106" t="str">
         <v>SPRINKLER FITTINGS TEE</v>
@@ -39107,7 +39107,7 @@
         <v>General</v>
       </c>
       <c r="G1106" t="str">
-        <v>75MM, L TYPE</v>
+        <v>63MM, C TYPE</v>
       </c>
       <c r="H1106" t="str">
         <v>Nos</v>
@@ -39127,13 +39127,13 @@
         <v>1106</v>
       </c>
       <c r="B1107" t="str">
-        <v>FG-401526</v>
+        <v>FG-401504</v>
       </c>
       <c r="C1107" t="str">
-        <v>SPRINKLER FITTINGS TEE (63MM, C TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (75MM C TYPE)</v>
       </c>
       <c r="D1107" t="str">
-        <v>SPRINKLER FITTINGS TEE</v>
+        <v>SPRINKLER FITTINGS ADAPTOR</v>
       </c>
       <c r="E1107" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39142,7 +39142,7 @@
         <v>General</v>
       </c>
       <c r="G1107" t="str">
-        <v>63MM, C TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1107" t="str">
         <v>Nos</v>
@@ -39154,7 +39154,7 @@
         <v>Active</v>
       </c>
       <c r="K1107" t="str">
-        <v>SPRINKLER FITTINGS TEE for sprinkler irrigation systems. Available sizes: 75MM, C TYPE, 75MM, L TYPE, 63MM, C TYPE.</v>
+        <v>SPRINKLER FITTINGS ADAPTOR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1108">
@@ -39162,10 +39162,10 @@
         <v>1107</v>
       </c>
       <c r="B1108" t="str">
-        <v>FG-401504</v>
+        <v>FG-401512</v>
       </c>
       <c r="C1108" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (75MM P TYPE)</v>
       </c>
       <c r="D1108" t="str">
         <v>SPRINKLER FITTINGS ADAPTOR</v>
@@ -39177,7 +39177,7 @@
         <v>General</v>
       </c>
       <c r="G1108" t="str">
-        <v>75MM C TYPE</v>
+        <v>75MM P TYPE</v>
       </c>
       <c r="H1108" t="str">
         <v>Nos</v>
@@ -39197,10 +39197,10 @@
         <v>1108</v>
       </c>
       <c r="B1109" t="str">
-        <v>FG-401512</v>
+        <v>FG-401527</v>
       </c>
       <c r="C1109" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (75MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (63MM C TYPE)</v>
       </c>
       <c r="D1109" t="str">
         <v>SPRINKLER FITTINGS ADAPTOR</v>
@@ -39212,7 +39212,7 @@
         <v>General</v>
       </c>
       <c r="G1109" t="str">
-        <v>75MM P TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1109" t="str">
         <v>Nos</v>
@@ -39232,13 +39232,13 @@
         <v>1109</v>
       </c>
       <c r="B1110" t="str">
-        <v>FG-401527</v>
+        <v>FG-401502</v>
       </c>
       <c r="C1110" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (75MM C TYPE)</v>
       </c>
       <c r="D1110" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR</v>
+        <v>SPRINKLER FITTINGS BEND</v>
       </c>
       <c r="E1110" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39247,7 +39247,7 @@
         <v>General</v>
       </c>
       <c r="G1110" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1110" t="str">
         <v>Nos</v>
@@ -39259,7 +39259,7 @@
         <v>Active</v>
       </c>
       <c r="K1110" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS BEND for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1111">
@@ -39267,10 +39267,10 @@
         <v>1110</v>
       </c>
       <c r="B1111" t="str">
-        <v>FG-401502</v>
+        <v>FG-401510</v>
       </c>
       <c r="C1111" t="str">
-        <v>SPRINKLER FITTINGS BEND (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (75MM L TYPE)</v>
       </c>
       <c r="D1111" t="str">
         <v>SPRINKLER FITTINGS BEND</v>
@@ -39282,7 +39282,7 @@
         <v>General</v>
       </c>
       <c r="G1111" t="str">
-        <v>75MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1111" t="str">
         <v>Nos</v>
@@ -39302,10 +39302,10 @@
         <v>1111</v>
       </c>
       <c r="B1112" t="str">
-        <v>FG-401510</v>
+        <v>FG-401525</v>
       </c>
       <c r="C1112" t="str">
-        <v>SPRINKLER FITTINGS BEND (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (63MM C TYPE)</v>
       </c>
       <c r="D1112" t="str">
         <v>SPRINKLER FITTINGS BEND</v>
@@ -39317,7 +39317,7 @@
         <v>General</v>
       </c>
       <c r="G1112" t="str">
-        <v>75MM L TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1112" t="str">
         <v>Nos</v>
@@ -39337,13 +39337,13 @@
         <v>1112</v>
       </c>
       <c r="B1113" t="str">
-        <v>FG-401525</v>
+        <v>FG-401514</v>
       </c>
       <c r="C1113" t="str">
-        <v>SPRINKLER FITTINGS BEND (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (75MM L TYPE)</v>
       </c>
       <c r="D1113" t="str">
-        <v>SPRINKLER FITTINGS BEND</v>
+        <v>SPRINKLER FITTINGS END CAP</v>
       </c>
       <c r="E1113" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39352,7 +39352,7 @@
         <v>General</v>
       </c>
       <c r="G1113" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1113" t="str">
         <v>Nos</v>
@@ -39364,7 +39364,7 @@
         <v>Active</v>
       </c>
       <c r="K1113" t="str">
-        <v>SPRINKLER FITTINGS BEND for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS END CAP for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1114">
@@ -39372,10 +39372,10 @@
         <v>1113</v>
       </c>
       <c r="B1114" t="str">
-        <v>FG-401514</v>
+        <v>FG-401506</v>
       </c>
       <c r="C1114" t="str">
-        <v>SPRINKLER FITTINGS END CAP (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (75MM C TYPE)</v>
       </c>
       <c r="D1114" t="str">
         <v>SPRINKLER FITTINGS END CAP</v>
@@ -39387,7 +39387,7 @@
         <v>General</v>
       </c>
       <c r="G1114" t="str">
-        <v>75MM L TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1114" t="str">
         <v>Nos</v>
@@ -39407,10 +39407,10 @@
         <v>1114</v>
       </c>
       <c r="B1115" t="str">
-        <v>FG-401506</v>
+        <v>FG-401529</v>
       </c>
       <c r="C1115" t="str">
-        <v>SPRINKLER FITTINGS END CAP (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (63MM C TYPE)</v>
       </c>
       <c r="D1115" t="str">
         <v>SPRINKLER FITTINGS END CAP</v>
@@ -39422,7 +39422,7 @@
         <v>General</v>
       </c>
       <c r="G1115" t="str">
-        <v>75MM C TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1115" t="str">
         <v>Nos</v>
@@ -39442,13 +39442,13 @@
         <v>1115</v>
       </c>
       <c r="B1116" t="str">
-        <v>FG-401529</v>
+        <v>FG-401517</v>
       </c>
       <c r="C1116" t="str">
-        <v>SPRINKLER FITTINGS END CAP (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (75MM P TYPE)</v>
       </c>
       <c r="D1116" t="str">
-        <v>SPRINKLER FITTINGS END CAP</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
       </c>
       <c r="E1116" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39457,7 +39457,7 @@
         <v>General</v>
       </c>
       <c r="G1116" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM P TYPE</v>
       </c>
       <c r="H1116" t="str">
         <v>Nos</v>
@@ -39469,7 +39469,7 @@
         <v>Active</v>
       </c>
       <c r="K1116" t="str">
-        <v>SPRINKLER FITTINGS END CAP for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1117">
@@ -39477,10 +39477,10 @@
         <v>1116</v>
       </c>
       <c r="B1117" t="str">
-        <v>FG-401517</v>
+        <v>FG-401518</v>
       </c>
       <c r="C1117" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (75MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (63MM P TYPE)</v>
       </c>
       <c r="D1117" t="str">
         <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
@@ -39492,7 +39492,7 @@
         <v>General</v>
       </c>
       <c r="G1117" t="str">
-        <v>75MM P TYPE</v>
+        <v>63MM P TYPE</v>
       </c>
       <c r="H1117" t="str">
         <v>Nos</v>
@@ -39512,13 +39512,13 @@
         <v>1117</v>
       </c>
       <c r="B1118" t="str">
-        <v>FG-401518</v>
+        <v>FG-401505</v>
       </c>
       <c r="C1118" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (63MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (75MM C TYPE)</v>
       </c>
       <c r="D1118" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
+        <v>SPRINKLER FITTINGS PCN</v>
       </c>
       <c r="E1118" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39527,7 +39527,7 @@
         <v>General</v>
       </c>
       <c r="G1118" t="str">
-        <v>63MM P TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1118" t="str">
         <v>Nos</v>
@@ -39539,7 +39539,7 @@
         <v>Active</v>
       </c>
       <c r="K1118" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS PCN for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1119">
@@ -39547,10 +39547,10 @@
         <v>1118</v>
       </c>
       <c r="B1119" t="str">
-        <v>FG-401505</v>
+        <v>FG-401513</v>
       </c>
       <c r="C1119" t="str">
-        <v>SPRINKLER FITTINGS PCN (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (75MM L TYPE)</v>
       </c>
       <c r="D1119" t="str">
         <v>SPRINKLER FITTINGS PCN</v>
@@ -39562,7 +39562,7 @@
         <v>General</v>
       </c>
       <c r="G1119" t="str">
-        <v>75MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1119" t="str">
         <v>Nos</v>
@@ -39582,10 +39582,10 @@
         <v>1119</v>
       </c>
       <c r="B1120" t="str">
-        <v>FG-401513</v>
+        <v>FG-401528</v>
       </c>
       <c r="C1120" t="str">
-        <v>SPRINKLER FITTINGS PCN (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (63MM C TYPE)</v>
       </c>
       <c r="D1120" t="str">
         <v>SPRINKLER FITTINGS PCN</v>
@@ -39597,7 +39597,7 @@
         <v>General</v>
       </c>
       <c r="G1120" t="str">
-        <v>75MM L TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1120" t="str">
         <v>Nos</v>
@@ -39617,13 +39617,13 @@
         <v>1120</v>
       </c>
       <c r="B1121" t="str">
-        <v>FG-401528</v>
+        <v>FG-401507</v>
       </c>
       <c r="C1121" t="str">
-        <v>SPRINKLER FITTINGS PCN (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL (20MM)</v>
       </c>
       <c r="D1121" t="str">
-        <v>SPRINKLER FITTINGS PCN</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL</v>
       </c>
       <c r="E1121" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39632,7 +39632,7 @@
         <v>General</v>
       </c>
       <c r="G1121" t="str">
-        <v>63MM C TYPE</v>
+        <v>20MM</v>
       </c>
       <c r="H1121" t="str">
         <v>Nos</v>
@@ -39644,7 +39644,7 @@
         <v>Active</v>
       </c>
       <c r="K1121" t="str">
-        <v>SPRINKLER FITTINGS PCN for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1122">
@@ -39652,13 +39652,13 @@
         <v>1121</v>
       </c>
       <c r="B1122" t="str">
-        <v>FG-401507</v>
+        <v>FG-401508</v>
       </c>
       <c r="C1122" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL (20MM)</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE (75MM C TYPE)</v>
       </c>
       <c r="D1122" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE</v>
       </c>
       <c r="E1122" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39667,7 +39667,7 @@
         <v>General</v>
       </c>
       <c r="G1122" t="str">
-        <v>20MM</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1122" t="str">
         <v>Nos</v>
@@ -39679,7 +39679,7 @@
         <v>Active</v>
       </c>
       <c r="K1122" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1123">
@@ -39687,10 +39687,10 @@
         <v>1122</v>
       </c>
       <c r="B1123" t="str">
-        <v>FG-401508</v>
+        <v>FG-401515</v>
       </c>
       <c r="C1123" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE (20MM L TYPE)</v>
       </c>
       <c r="D1123" t="str">
         <v>SPRINKLER FITTINGS GI RISER PIPE</v>
@@ -39702,7 +39702,7 @@
         <v>General</v>
       </c>
       <c r="G1123" t="str">
-        <v>75MM C TYPE</v>
+        <v>20MM L TYPE</v>
       </c>
       <c r="H1123" t="str">
         <v>Nos</v>
@@ -39722,25 +39722,25 @@
         <v>1123</v>
       </c>
       <c r="B1124" t="str">
-        <v>FG-401515</v>
+        <v>FG-401742</v>
       </c>
       <c r="C1124" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE (20MM L TYPE)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 1)</v>
       </c>
       <c r="D1124" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE</v>
+        <v>ROUND DRIPLINE 12MM ISI</v>
       </c>
       <c r="E1124" t="str">
-        <v>Sprinkler Pipes &amp; Fittings</v>
+        <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1124" t="str">
-        <v>General</v>
+        <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1124" t="str">
-        <v>20MM L TYPE</v>
+        <v>12-4-30 CLASS 1</v>
       </c>
       <c r="H1124" t="str">
-        <v>Nos</v>
+        <v>ROLL</v>
       </c>
       <c r="I1124" t="str">
         <v>-</v>
@@ -39749,7 +39749,7 @@
         <v>Active</v>
       </c>
       <c r="K1124" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE for sprinkler irrigation systems.</v>
+        <v>ROUND DRIPLINE 12MM ISI certified.</v>
       </c>
     </row>
     <row r="1125">
@@ -39757,10 +39757,10 @@
         <v>1124</v>
       </c>
       <c r="B1125" t="str">
-        <v>FG-401742</v>
+        <v>FG-401743</v>
       </c>
       <c r="C1125" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 1)</v>
       </c>
       <c r="D1125" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39772,7 +39772,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1125" t="str">
-        <v>12-4-30 CLASS 1</v>
+        <v>12-4-40 CLASS 1</v>
       </c>
       <c r="H1125" t="str">
         <v>ROLL</v>
@@ -39792,10 +39792,10 @@
         <v>1125</v>
       </c>
       <c r="B1126" t="str">
-        <v>FG-401743</v>
+        <v>FG-401744</v>
       </c>
       <c r="C1126" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 1)</v>
       </c>
       <c r="D1126" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39807,7 +39807,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1126" t="str">
-        <v>12-4-40 CLASS 1</v>
+        <v>12-4-50 CLASS 1</v>
       </c>
       <c r="H1126" t="str">
         <v>ROLL</v>
@@ -39827,10 +39827,10 @@
         <v>1126</v>
       </c>
       <c r="B1127" t="str">
-        <v>FG-401744</v>
+        <v>FG-401751</v>
       </c>
       <c r="C1127" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1127" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39842,7 +39842,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1127" t="str">
-        <v>12-4-50 CLASS 1</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1127" t="str">
         <v>ROLL</v>
@@ -39862,10 +39862,10 @@
         <v>1127</v>
       </c>
       <c r="B1128" t="str">
-        <v>FG-401751</v>
+        <v>FG-401752</v>
       </c>
       <c r="C1128" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1128" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39877,7 +39877,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1128" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1128" t="str">
         <v>ROLL</v>
@@ -39897,10 +39897,10 @@
         <v>1128</v>
       </c>
       <c r="B1129" t="str">
-        <v>FG-401752</v>
+        <v>FG-401753</v>
       </c>
       <c r="C1129" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1129" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39912,7 +39912,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1129" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1129" t="str">
         <v>ROLL</v>
@@ -39932,10 +39932,10 @@
         <v>1129</v>
       </c>
       <c r="B1130" t="str">
-        <v>FG-401753</v>
+        <v>FG-401754</v>
       </c>
       <c r="C1130" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1130" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39947,7 +39947,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1130" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1130" t="str">
         <v>ROLL</v>
@@ -39967,10 +39967,10 @@
         <v>1130</v>
       </c>
       <c r="B1131" t="str">
-        <v>FG-401754</v>
+        <v>FG-401755</v>
       </c>
       <c r="C1131" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1131" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39982,7 +39982,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1131" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1131" t="str">
         <v>ROLL</v>
@@ -40002,10 +40002,10 @@
         <v>1131</v>
       </c>
       <c r="B1132" t="str">
-        <v>FG-401755</v>
+        <v>FG-401756</v>
       </c>
       <c r="C1132" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1132" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -40017,7 +40017,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1132" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1132" t="str">
         <v>ROLL</v>
@@ -40037,13 +40037,13 @@
         <v>1132</v>
       </c>
       <c r="B1133" t="str">
-        <v>FG-401756</v>
+        <v>FG-401745</v>
       </c>
       <c r="C1133" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1133" t="str">
-        <v>ROUND DRIPLINE 12MM ISI</v>
+        <v>ROUND DRIPLINE 16MM ISI</v>
       </c>
       <c r="E1133" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40052,7 +40052,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1133" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1133" t="str">
         <v>ROLL</v>
@@ -40064,7 +40064,7 @@
         <v>Active</v>
       </c>
       <c r="K1133" t="str">
-        <v>ROUND DRIPLINE 12MM ISI certified.</v>
+        <v>ROUND DRIPLINE 16MM ISI certified.</v>
       </c>
     </row>
     <row r="1134">
@@ -40072,10 +40072,10 @@
         <v>1133</v>
       </c>
       <c r="B1134" t="str">
-        <v>FG-401745</v>
+        <v>FG-401746</v>
       </c>
       <c r="C1134" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1134" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40087,7 +40087,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1134" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1134" t="str">
         <v>ROLL</v>
@@ -40107,10 +40107,10 @@
         <v>1134</v>
       </c>
       <c r="B1135" t="str">
-        <v>FG-401746</v>
+        <v>FG-401747</v>
       </c>
       <c r="C1135" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1135" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40122,7 +40122,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1135" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1135" t="str">
         <v>ROLL</v>
@@ -40142,10 +40142,10 @@
         <v>1135</v>
       </c>
       <c r="B1136" t="str">
-        <v>FG-401747</v>
+        <v>FG-401757</v>
       </c>
       <c r="C1136" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1136" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40157,7 +40157,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1136" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1136" t="str">
         <v>ROLL</v>
@@ -40177,10 +40177,10 @@
         <v>1136</v>
       </c>
       <c r="B1137" t="str">
-        <v>FG-401757</v>
+        <v>FG-401758</v>
       </c>
       <c r="C1137" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1137" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40192,7 +40192,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1137" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1137" t="str">
         <v>ROLL</v>
@@ -40212,10 +40212,10 @@
         <v>1137</v>
       </c>
       <c r="B1138" t="str">
-        <v>FG-401758</v>
+        <v>FG-401759</v>
       </c>
       <c r="C1138" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1138" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40227,7 +40227,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1138" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1138" t="str">
         <v>ROLL</v>
@@ -40247,13 +40247,13 @@
         <v>1138</v>
       </c>
       <c r="B1139" t="str">
-        <v>FG-401759</v>
+        <v>-</v>
       </c>
       <c r="C1139" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-30 CLASS-1)</v>
       </c>
       <c r="D1139" t="str">
-        <v>ROUND DRIPLINE 16MM ISI</v>
+        <v>20MM ROUND INLINE PIPE ISI</v>
       </c>
       <c r="E1139" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40262,10 +40262,10 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1139" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>20-4-30 CLASS-1</v>
       </c>
       <c r="H1139" t="str">
-        <v>ROLL</v>
+        <v>MTR</v>
       </c>
       <c r="I1139" t="str">
         <v>-</v>
@@ -40274,7 +40274,7 @@
         <v>Active</v>
       </c>
       <c r="K1139" t="str">
-        <v>ROUND DRIPLINE 16MM ISI certified.</v>
+        <v>20mm Round Inline Drip Pipe ISI certified.</v>
       </c>
     </row>
     <row r="1140">
@@ -40285,7 +40285,7 @@
         <v>-</v>
       </c>
       <c r="C1140" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-30 CLASS-1)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-40 CLASS-1)</v>
       </c>
       <c r="D1140" t="str">
         <v>20MM ROUND INLINE PIPE ISI</v>
@@ -40297,7 +40297,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1140" t="str">
-        <v>20-4-30 CLASS-1</v>
+        <v>20-4-40 CLASS-1</v>
       </c>
       <c r="H1140" t="str">
         <v>MTR</v>
@@ -40320,7 +40320,7 @@
         <v>-</v>
       </c>
       <c r="C1141" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-40 CLASS-1)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-50 CLASS-1)</v>
       </c>
       <c r="D1141" t="str">
         <v>20MM ROUND INLINE PIPE ISI</v>
@@ -40332,7 +40332,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1141" t="str">
-        <v>20-4-40 CLASS-1</v>
+        <v>20-4-50 CLASS-1</v>
       </c>
       <c r="H1141" t="str">
         <v>MTR</v>
@@ -40352,25 +40352,25 @@
         <v>1141</v>
       </c>
       <c r="B1142" t="str">
-        <v>-</v>
+        <v>FG-401763</v>
       </c>
       <c r="C1142" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-50 CLASS-1)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1142" t="str">
-        <v>20MM ROUND INLINE PIPE ISI</v>
+        <v>FLAT DRIPLINE 12MM ISI</v>
       </c>
       <c r="E1142" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1142" t="str">
-        <v>ROUND DRIP ISI</v>
+        <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1142" t="str">
-        <v>20-4-50 CLASS-1</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1142" t="str">
-        <v>MTR</v>
+        <v>ROLL</v>
       </c>
       <c r="I1142" t="str">
         <v>-</v>
@@ -40379,7 +40379,7 @@
         <v>Active</v>
       </c>
       <c r="K1142" t="str">
-        <v>20mm Round Inline Drip Pipe ISI certified.</v>
+        <v>FLAT DRIPLINE 12MM ISI certified.</v>
       </c>
     </row>
     <row r="1143">
@@ -40387,10 +40387,10 @@
         <v>1142</v>
       </c>
       <c r="B1143" t="str">
-        <v>FG-401763</v>
+        <v>FG-401764</v>
       </c>
       <c r="C1143" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1143" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40402,7 +40402,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1143" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1143" t="str">
         <v>ROLL</v>
@@ -40422,10 +40422,10 @@
         <v>1143</v>
       </c>
       <c r="B1144" t="str">
-        <v>FG-401764</v>
+        <v>FG-401765</v>
       </c>
       <c r="C1144" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1144" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40437,7 +40437,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1144" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1144" t="str">
         <v>ROLL</v>
@@ -40457,10 +40457,10 @@
         <v>1144</v>
       </c>
       <c r="B1145" t="str">
-        <v>FG-401765</v>
+        <v>FG-401766</v>
       </c>
       <c r="C1145" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1145" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40472,7 +40472,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1145" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1145" t="str">
         <v>ROLL</v>
@@ -40492,10 +40492,10 @@
         <v>1145</v>
       </c>
       <c r="B1146" t="str">
-        <v>FG-401766</v>
+        <v>FG-401767</v>
       </c>
       <c r="C1146" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1146" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40507,7 +40507,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1146" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1146" t="str">
         <v>ROLL</v>
@@ -40527,10 +40527,10 @@
         <v>1146</v>
       </c>
       <c r="B1147" t="str">
-        <v>FG-401767</v>
+        <v>FG-401768</v>
       </c>
       <c r="C1147" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1147" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40542,7 +40542,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1147" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1147" t="str">
         <v>ROLL</v>
@@ -40562,13 +40562,13 @@
         <v>1147</v>
       </c>
       <c r="B1148" t="str">
-        <v>FG-401768</v>
+        <v>FG-401760</v>
       </c>
       <c r="C1148" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1148" t="str">
-        <v>FLAT DRIPLINE 12MM ISI</v>
+        <v>FLAT DRIPLINE 16MM ISI</v>
       </c>
       <c r="E1148" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40577,7 +40577,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1148" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1148" t="str">
         <v>ROLL</v>
@@ -40589,7 +40589,7 @@
         <v>Active</v>
       </c>
       <c r="K1148" t="str">
-        <v>FLAT DRIPLINE 12MM ISI certified.</v>
+        <v>FLAT DRIPLINE 16MM ISI certified.</v>
       </c>
     </row>
     <row r="1149">
@@ -40597,10 +40597,10 @@
         <v>1148</v>
       </c>
       <c r="B1149" t="str">
-        <v>FG-401760</v>
+        <v>FG-401761</v>
       </c>
       <c r="C1149" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1149" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40612,7 +40612,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1149" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1149" t="str">
         <v>ROLL</v>
@@ -40632,10 +40632,10 @@
         <v>1149</v>
       </c>
       <c r="B1150" t="str">
-        <v>FG-401761</v>
+        <v>FG-401762</v>
       </c>
       <c r="C1150" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1150" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40647,7 +40647,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1150" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1150" t="str">
         <v>ROLL</v>
@@ -40667,10 +40667,10 @@
         <v>1150</v>
       </c>
       <c r="B1151" t="str">
-        <v>FG-401762</v>
+        <v>FG-401769</v>
       </c>
       <c r="C1151" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1151" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40682,7 +40682,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1151" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1151" t="str">
         <v>ROLL</v>
@@ -40702,10 +40702,10 @@
         <v>1151</v>
       </c>
       <c r="B1152" t="str">
-        <v>FG-401769</v>
+        <v>FG-401770</v>
       </c>
       <c r="C1152" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1152" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40717,7 +40717,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1152" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1152" t="str">
         <v>ROLL</v>
@@ -40737,10 +40737,10 @@
         <v>1152</v>
       </c>
       <c r="B1153" t="str">
-        <v>FG-401770</v>
+        <v>FG-401779</v>
       </c>
       <c r="C1153" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1153" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40752,7 +40752,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1153" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1153" t="str">
         <v>ROLL</v>
@@ -40772,13 +40772,13 @@
         <v>1153</v>
       </c>
       <c r="B1154" t="str">
-        <v>FG-401779</v>
+        <v>FG-401771</v>
       </c>
       <c r="C1154" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-30 CLASS 1)</v>
       </c>
       <c r="D1154" t="str">
-        <v>FLAT DRIPLINE 16MM ISI</v>
+        <v>FLAT DRIPLINE 20MM ISI</v>
       </c>
       <c r="E1154" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40787,7 +40787,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1154" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>20-4-30 CLASS 1</v>
       </c>
       <c r="H1154" t="str">
         <v>ROLL</v>
@@ -40799,7 +40799,7 @@
         <v>Active</v>
       </c>
       <c r="K1154" t="str">
-        <v>FLAT DRIPLINE 16MM ISI certified.</v>
+        <v>FLAT DRIPLINE 20MM ISI certified.</v>
       </c>
     </row>
     <row r="1155">
@@ -40807,10 +40807,10 @@
         <v>1154</v>
       </c>
       <c r="B1155" t="str">
-        <v>FG-401771</v>
+        <v>FG-401772</v>
       </c>
       <c r="C1155" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-40 CLASS 1)</v>
       </c>
       <c r="D1155" t="str">
         <v>FLAT DRIPLINE 20MM ISI</v>
@@ -40822,7 +40822,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1155" t="str">
-        <v>20-4-30 CLASS 1</v>
+        <v>20-4-40 CLASS 1</v>
       </c>
       <c r="H1155" t="str">
         <v>ROLL</v>
@@ -40842,10 +40842,10 @@
         <v>1155</v>
       </c>
       <c r="B1156" t="str">
-        <v>FG-401772</v>
+        <v>FG-401773</v>
       </c>
       <c r="C1156" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-50 CLASS 1)</v>
       </c>
       <c r="D1156" t="str">
         <v>FLAT DRIPLINE 20MM ISI</v>
@@ -40857,7 +40857,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1156" t="str">
-        <v>20-4-40 CLASS 1</v>
+        <v>20-4-50 CLASS 1</v>
       </c>
       <c r="H1156" t="str">
         <v>ROLL</v>
@@ -40877,25 +40877,25 @@
         <v>1156</v>
       </c>
       <c r="B1157" t="str">
-        <v>FG-401773</v>
+        <v>-</v>
       </c>
       <c r="C1157" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-50 CLASS 1)</v>
+        <v>12MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1157" t="str">
-        <v>FLAT DRIPLINE 20MM ISI</v>
+        <v>12MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1157" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1157" t="str">
-        <v>FLAT DRIP ISI</v>
+        <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1157" t="str">
-        <v>20-4-50 CLASS 1</v>
+        <v>CLASS-2</v>
       </c>
       <c r="H1157" t="str">
-        <v>ROLL</v>
+        <v>MTR</v>
       </c>
       <c r="I1157" t="str">
         <v>-</v>
@@ -40904,7 +40904,7 @@
         <v>Active</v>
       </c>
       <c r="K1157" t="str">
-        <v>FLAT DRIPLINE 20MM ISI certified.</v>
+        <v>12mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1158">
@@ -40915,10 +40915,10 @@
         <v>-</v>
       </c>
       <c r="C1158" t="str">
-        <v>12MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>16MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1158" t="str">
-        <v>12MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>16MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1158" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40939,7 +40939,7 @@
         <v>Active</v>
       </c>
       <c r="K1158" t="str">
-        <v>12mm Plain Lateral Online Drip Pipe.</v>
+        <v>16mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1159">
@@ -40950,10 +40950,10 @@
         <v>-</v>
       </c>
       <c r="C1159" t="str">
-        <v>16MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>20MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1159" t="str">
-        <v>16MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>20MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1159" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40974,7 +40974,7 @@
         <v>Active</v>
       </c>
       <c r="K1159" t="str">
-        <v>16mm Plain Lateral Online Drip Pipe.</v>
+        <v>20mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1160">
@@ -40985,10 +40985,10 @@
         <v>-</v>
       </c>
       <c r="C1160" t="str">
-        <v>20MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-1)</v>
       </c>
       <c r="D1160" t="str">
-        <v>20MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1160" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40997,7 +40997,7 @@
         <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1160" t="str">
-        <v>CLASS-2</v>
+        <v>CLASS-1</v>
       </c>
       <c r="H1160" t="str">
         <v>MTR</v>
@@ -41009,7 +41009,7 @@
         <v>Active</v>
       </c>
       <c r="K1160" t="str">
-        <v>20mm Plain Lateral Online Drip Pipe.</v>
+        <v>32mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1161">
@@ -41020,7 +41020,7 @@
         <v>-</v>
       </c>
       <c r="C1161" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-1)</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1161" t="str">
         <v>32MM PLAIN LATERAL ONLINE PIPE</v>
@@ -41032,7 +41032,7 @@
         <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1161" t="str">
-        <v>CLASS-1</v>
+        <v>CLASS-2</v>
       </c>
       <c r="H1161" t="str">
         <v>MTR</v>
@@ -41052,22 +41052,22 @@
         <v>1161</v>
       </c>
       <c r="B1162" t="str">
-        <v>-</v>
+        <v>FG-401763</v>
       </c>
       <c r="C1162" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1162" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12</v>
       </c>
       <c r="E1162" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1162" t="str">
-        <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
+        <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1162" t="str">
-        <v>CLASS-2</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1162" t="str">
         <v>MTR</v>
@@ -41079,7 +41079,7 @@
         <v>Active</v>
       </c>
       <c r="K1162" t="str">
-        <v>32mm Plain Lateral Online Drip Pipe.</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12. Available sizes: 12-4-30 CLASS 2, 12-4-40 CLASS 2, 12-4-50 CLASS 2, 12-4-30 CLASS 3, 12-4-40 CLASS 3, 12-4-50 CLASS 3.</v>
       </c>
     </row>
     <row r="1163">
@@ -41087,10 +41087,10 @@
         <v>1162</v>
       </c>
       <c r="B1163" t="str">
-        <v>FG-401763</v>
+        <v>FG-401764</v>
       </c>
       <c r="C1163" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1163" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41102,7 +41102,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1163" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1163" t="str">
         <v>MTR</v>
@@ -41122,10 +41122,10 @@
         <v>1163</v>
       </c>
       <c r="B1164" t="str">
-        <v>FG-401764</v>
+        <v>FG-401765</v>
       </c>
       <c r="C1164" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1164" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41137,7 +41137,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1164" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1164" t="str">
         <v>MTR</v>
@@ -41157,10 +41157,10 @@
         <v>1164</v>
       </c>
       <c r="B1165" t="str">
-        <v>FG-401765</v>
+        <v>FG-401766</v>
       </c>
       <c r="C1165" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1165" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41172,7 +41172,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1165" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1165" t="str">
         <v>MTR</v>
@@ -41192,10 +41192,10 @@
         <v>1165</v>
       </c>
       <c r="B1166" t="str">
-        <v>FG-401766</v>
+        <v>FG-401767</v>
       </c>
       <c r="C1166" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1166" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41207,7 +41207,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1166" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1166" t="str">
         <v>MTR</v>
@@ -41227,10 +41227,10 @@
         <v>1166</v>
       </c>
       <c r="B1167" t="str">
-        <v>FG-401767</v>
+        <v>FG-401768</v>
       </c>
       <c r="C1167" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1167" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41242,7 +41242,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1167" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1167" t="str">
         <v>MTR</v>
@@ -41262,13 +41262,13 @@
         <v>1167</v>
       </c>
       <c r="B1168" t="str">
-        <v>FG-401768</v>
+        <v>FG-401760</v>
       </c>
       <c r="C1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16</v>
       </c>
       <c r="E1168" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -41277,7 +41277,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1168" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1168" t="str">
         <v>MTR</v>
@@ -41289,7 +41289,7 @@
         <v>Active</v>
       </c>
       <c r="K1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12. Available sizes: 12-4-30 CLASS 2, 12-4-40 CLASS 2, 12-4-50 CLASS 2, 12-4-30 CLASS 3, 12-4-40 CLASS 3, 12-4-50 CLASS 3.</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16. Available sizes: 16-4-30 CLASS 1, 16-4-40 CLASS 1, 16-4-50 CLASS 1, 16-4-30 CLASS 2, 16-4-40 CLASS 2, 16-4-50 CLASS 2.</v>
       </c>
     </row>
     <row r="1169">
@@ -41297,10 +41297,10 @@
         <v>1168</v>
       </c>
       <c r="B1169" t="str">
-        <v>FG-401760</v>
+        <v>FG-401761</v>
       </c>
       <c r="C1169" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1169" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41312,7 +41312,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1169" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1169" t="str">
         <v>MTR</v>
@@ -41332,10 +41332,10 @@
         <v>1169</v>
       </c>
       <c r="B1170" t="str">
-        <v>FG-401761</v>
+        <v>FG-401762</v>
       </c>
       <c r="C1170" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1170" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41347,7 +41347,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1170" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1170" t="str">
         <v>MTR</v>
@@ -41367,10 +41367,10 @@
         <v>1170</v>
       </c>
       <c r="B1171" t="str">
-        <v>FG-401762</v>
+        <v>FG-401769</v>
       </c>
       <c r="C1171" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1171" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41382,7 +41382,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1171" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1171" t="str">
         <v>MTR</v>
@@ -41402,10 +41402,10 @@
         <v>1171</v>
       </c>
       <c r="B1172" t="str">
-        <v>FG-401769</v>
+        <v>FG-401770</v>
       </c>
       <c r="C1172" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1172" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41417,7 +41417,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1172" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1172" t="str">
         <v>MTR</v>
@@ -41437,10 +41437,10 @@
         <v>1172</v>
       </c>
       <c r="B1173" t="str">
-        <v>FG-401770</v>
+        <v>FG-401779</v>
       </c>
       <c r="C1173" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1173" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41452,7 +41452,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1173" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1173" t="str">
         <v>MTR</v>
@@ -41472,13 +41472,13 @@
         <v>1173</v>
       </c>
       <c r="B1174" t="str">
-        <v>FG-401779</v>
+        <v>FG-401771</v>
       </c>
       <c r="C1174" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-30 CLASS 1)</v>
       </c>
       <c r="D1174" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20</v>
       </c>
       <c r="E1174" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -41487,7 +41487,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1174" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>20-4-30 CLASS 1</v>
       </c>
       <c r="H1174" t="str">
         <v>MTR</v>
@@ -41499,7 +41499,7 @@
         <v>Active</v>
       </c>
       <c r="K1174" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16. Available sizes: 16-4-30 CLASS 1, 16-4-40 CLASS 1, 16-4-50 CLASS 1, 16-4-30 CLASS 2, 16-4-40 CLASS 2, 16-4-50 CLASS 2.</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20. Available sizes: 20-4-30 CLASS 1, 20-4-40 CLASS 1, 20-4-50 CLASS 1.</v>
       </c>
     </row>
     <row r="1175">
@@ -41507,10 +41507,10 @@
         <v>1174</v>
       </c>
       <c r="B1175" t="str">
-        <v>FG-401771</v>
+        <v>FG-401772</v>
       </c>
       <c r="C1175" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-40 CLASS 1)</v>
       </c>
       <c r="D1175" t="str">
         <v>FLAT DRIPLINE ISI 400MTR 20</v>
@@ -41522,7 +41522,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1175" t="str">
-        <v>20-4-30 CLASS 1</v>
+        <v>20-4-40 CLASS 1</v>
       </c>
       <c r="H1175" t="str">
         <v>MTR</v>
@@ -41542,10 +41542,10 @@
         <v>1175</v>
       </c>
       <c r="B1176" t="str">
-        <v>FG-401772</v>
+        <v>FG-401773</v>
       </c>
       <c r="C1176" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-50 CLASS 1)</v>
       </c>
       <c r="D1176" t="str">
         <v>FLAT DRIPLINE ISI 400MTR 20</v>
@@ -41557,7 +41557,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1176" t="str">
-        <v>20-4-40 CLASS 1</v>
+        <v>20-4-50 CLASS 1</v>
       </c>
       <c r="H1176" t="str">
         <v>MTR</v>
@@ -41577,22 +41577,22 @@
         <v>1176</v>
       </c>
       <c r="B1177" t="str">
-        <v>FG-401773</v>
+        <v>FG-401066</v>
       </c>
       <c r="C1177" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-50 CLASS 1)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
       </c>
       <c r="D1177" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
       </c>
       <c r="E1177" t="str">
-        <v>DRIP IRRIGATION SYSTEM</v>
+        <v>UPVC CASING PIPES</v>
       </c>
       <c r="F1177" t="str">
-        <v>FLAT DRIP (PEPSI) - INLINE</v>
+        <v>General</v>
       </c>
       <c r="G1177" t="str">
-        <v>20-4-50 CLASS 1</v>
+        <v>35MM 1 1/4 Inch</v>
       </c>
       <c r="H1177" t="str">
         <v>MTR</v>
@@ -41604,7 +41604,7 @@
         <v>Active</v>
       </c>
       <c r="K1177" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20. Available sizes: 20-4-30 CLASS 1, 20-4-40 CLASS 1, 20-4-50 CLASS 1.</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 40MM 1 1/2 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1178">
@@ -41612,10 +41612,10 @@
         <v>1177</v>
       </c>
       <c r="B1178" t="str">
-        <v>FG-401066</v>
+        <v>FG-401067</v>
       </c>
       <c r="C1178" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (40MM 1 1/2 Inch)</v>
       </c>
       <c r="D1178" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41627,7 +41627,7 @@
         <v>General</v>
       </c>
       <c r="G1178" t="str">
-        <v>35MM 1 1/4 Inch</v>
+        <v>40MM 1 1/2 Inch</v>
       </c>
       <c r="H1178" t="str">
         <v>MTR</v>
@@ -41647,10 +41647,10 @@
         <v>1178</v>
       </c>
       <c r="B1179" t="str">
-        <v>FG-401067</v>
+        <v>FG-401068</v>
       </c>
       <c r="C1179" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (40MM 1 1/2 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (50MM 2 Inch)</v>
       </c>
       <c r="D1179" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41662,7 +41662,7 @@
         <v>General</v>
       </c>
       <c r="G1179" t="str">
-        <v>40MM 1 1/2 Inch</v>
+        <v>50MM 2 Inch</v>
       </c>
       <c r="H1179" t="str">
         <v>MTR</v>
@@ -41682,10 +41682,10 @@
         <v>1179</v>
       </c>
       <c r="B1180" t="str">
-        <v>FG-401068</v>
+        <v>FG-401069</v>
       </c>
       <c r="C1180" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (50MM 2 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (100MM 4 Inch)</v>
       </c>
       <c r="D1180" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41697,7 +41697,7 @@
         <v>General</v>
       </c>
       <c r="G1180" t="str">
-        <v>50MM 2 Inch</v>
+        <v>100MM 4 Inch</v>
       </c>
       <c r="H1180" t="str">
         <v>MTR</v>
@@ -41717,10 +41717,10 @@
         <v>1180</v>
       </c>
       <c r="B1181" t="str">
-        <v>FG-401069</v>
+        <v>FG-401070</v>
       </c>
       <c r="C1181" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (100MM 4 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1181" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41732,7 +41732,7 @@
         <v>General</v>
       </c>
       <c r="G1181" t="str">
-        <v>100MM 4 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1181" t="str">
         <v>MTR</v>
@@ -41752,10 +41752,10 @@
         <v>1181</v>
       </c>
       <c r="B1182" t="str">
-        <v>FG-401070</v>
+        <v>FG-401071</v>
       </c>
       <c r="C1182" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1182" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41767,7 +41767,7 @@
         <v>General</v>
       </c>
       <c r="G1182" t="str">
-        <v>125MM 5 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1182" t="str">
         <v>MTR</v>
@@ -41787,10 +41787,10 @@
         <v>1182</v>
       </c>
       <c r="B1183" t="str">
-        <v>FG-401071</v>
+        <v>FG-401072</v>
       </c>
       <c r="C1183" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1183" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41802,7 +41802,7 @@
         <v>General</v>
       </c>
       <c r="G1183" t="str">
-        <v>150MM 6 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1183" t="str">
         <v>MTR</v>
@@ -41822,10 +41822,10 @@
         <v>1183</v>
       </c>
       <c r="B1184" t="str">
-        <v>FG-401072</v>
+        <v>FG-401073</v>
       </c>
       <c r="C1184" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1184" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41837,7 +41837,7 @@
         <v>General</v>
       </c>
       <c r="G1184" t="str">
-        <v>175MM 7 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1184" t="str">
         <v>MTR</v>
@@ -41857,13 +41857,13 @@
         <v>1184</v>
       </c>
       <c r="B1185" t="str">
-        <v>FG-401073</v>
+        <v>FG-401074</v>
       </c>
       <c r="C1185" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1185" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
       </c>
       <c r="E1185" t="str">
         <v>UPVC CASING PIPES</v>
@@ -41872,7 +41872,7 @@
         <v>General</v>
       </c>
       <c r="G1185" t="str">
-        <v>200MM 8 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1185" t="str">
         <v>MTR</v>
@@ -41884,7 +41884,7 @@
         <v>Active</v>
       </c>
       <c r="K1185" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 40MM 1 1/2 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1186">
@@ -41892,10 +41892,10 @@
         <v>1185</v>
       </c>
       <c r="B1186" t="str">
-        <v>FG-401074</v>
+        <v>FG-401075</v>
       </c>
       <c r="C1186" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1186" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41907,7 +41907,7 @@
         <v>General</v>
       </c>
       <c r="G1186" t="str">
-        <v>125MM 5 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1186" t="str">
         <v>MTR</v>
@@ -41927,10 +41927,10 @@
         <v>1186</v>
       </c>
       <c r="B1187" t="str">
-        <v>FG-401075</v>
+        <v>FG-401076</v>
       </c>
       <c r="C1187" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1187" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41942,7 +41942,7 @@
         <v>General</v>
       </c>
       <c r="G1187" t="str">
-        <v>150MM 6 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1187" t="str">
         <v>MTR</v>
@@ -41962,10 +41962,10 @@
         <v>1187</v>
       </c>
       <c r="B1188" t="str">
-        <v>FG-401076</v>
+        <v>FG-401077</v>
       </c>
       <c r="C1188" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1188" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41977,7 +41977,7 @@
         <v>General</v>
       </c>
       <c r="G1188" t="str">
-        <v>175MM 7 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1188" t="str">
         <v>MTR</v>
@@ -41997,13 +41997,13 @@
         <v>1188</v>
       </c>
       <c r="B1189" t="str">
-        <v>FG-401077</v>
+        <v>FG-401149</v>
       </c>
       <c r="C1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M (140MM 5 Inch)</v>
       </c>
       <c r="D1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M</v>
       </c>
       <c r="E1189" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42012,7 +42012,7 @@
         <v>General</v>
       </c>
       <c r="G1189" t="str">
-        <v>200MM 8 Inch</v>
+        <v>140MM 5 Inch</v>
       </c>
       <c r="H1189" t="str">
         <v>MTR</v>
@@ -42024,7 +42024,7 @@
         <v>Active</v>
       </c>
       <c r="K1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M. Available sizes: 140MM 5 Inch.</v>
       </c>
     </row>
     <row r="1190">
@@ -42032,13 +42032,13 @@
         <v>1189</v>
       </c>
       <c r="B1190" t="str">
-        <v>FG-401149</v>
+        <v>FG-401150</v>
       </c>
       <c r="C1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M (140MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M (140MM 5 Inch)</v>
       </c>
       <c r="D1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M</v>
       </c>
       <c r="E1190" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42059,7 +42059,7 @@
         <v>Active</v>
       </c>
       <c r="K1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M. Available sizes: 140MM 5 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M. Available sizes: 140MM 5 Inch.</v>
       </c>
     </row>
     <row r="1191">
@@ -42067,13 +42067,13 @@
         <v>1190</v>
       </c>
       <c r="B1191" t="str">
-        <v>FG-401150</v>
+        <v>FG-401078</v>
       </c>
       <c r="C1191" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M (140MM 5 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1191" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
       </c>
       <c r="E1191" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42082,7 +42082,7 @@
         <v>General</v>
       </c>
       <c r="G1191" t="str">
-        <v>140MM 5 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1191" t="str">
         <v>MTR</v>
@@ -42094,7 +42094,7 @@
         <v>Active</v>
       </c>
       <c r="K1191" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M. Available sizes: 140MM 5 Inch.</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1192">
@@ -42102,10 +42102,10 @@
         <v>1191</v>
       </c>
       <c r="B1192" t="str">
-        <v>FG-401078</v>
+        <v>FG-401079</v>
       </c>
       <c r="C1192" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1192" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42117,7 +42117,7 @@
         <v>General</v>
       </c>
       <c r="G1192" t="str">
-        <v>125MM 5 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1192" t="str">
         <v>MTR</v>
@@ -42137,10 +42137,10 @@
         <v>1192</v>
       </c>
       <c r="B1193" t="str">
-        <v>FG-401079</v>
+        <v>FG-401080</v>
       </c>
       <c r="C1193" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1193" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42152,7 +42152,7 @@
         <v>General</v>
       </c>
       <c r="G1193" t="str">
-        <v>150MM 6 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1193" t="str">
         <v>MTR</v>
@@ -42172,10 +42172,10 @@
         <v>1193</v>
       </c>
       <c r="B1194" t="str">
-        <v>FG-401080</v>
+        <v>FG-401081</v>
       </c>
       <c r="C1194" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1194" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42187,7 +42187,7 @@
         <v>General</v>
       </c>
       <c r="G1194" t="str">
-        <v>175MM 7 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1194" t="str">
         <v>MTR</v>
@@ -42207,13 +42207,13 @@
         <v>1194</v>
       </c>
       <c r="B1195" t="str">
-        <v>FG-401081</v>
+        <v>FG-401119</v>
       </c>
       <c r="C1195" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
       </c>
       <c r="D1195" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
       </c>
       <c r="E1195" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42222,7 +42222,7 @@
         <v>General</v>
       </c>
       <c r="G1195" t="str">
-        <v>200MM 8 Inch</v>
+        <v>35MM 1 1/4 Inch</v>
       </c>
       <c r="H1195" t="str">
         <v>MTR</v>
@@ -42234,7 +42234,7 @@
         <v>Active</v>
       </c>
       <c r="K1195" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1196">
@@ -42242,10 +42242,10 @@
         <v>1195</v>
       </c>
       <c r="B1196" t="str">
-        <v>FG-401119</v>
+        <v>FG-401121</v>
       </c>
       <c r="C1196" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (50MM 2 Inch)</v>
       </c>
       <c r="D1196" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42257,7 +42257,7 @@
         <v>General</v>
       </c>
       <c r="G1196" t="str">
-        <v>35MM 1 1/4 Inch</v>
+        <v>50MM 2 Inch</v>
       </c>
       <c r="H1196" t="str">
         <v>MTR</v>
@@ -42277,10 +42277,10 @@
         <v>1196</v>
       </c>
       <c r="B1197" t="str">
-        <v>FG-401121</v>
+        <v>FG-401122</v>
       </c>
       <c r="C1197" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (50MM 2 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (100MM 4 Inch)</v>
       </c>
       <c r="D1197" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42292,7 +42292,7 @@
         <v>General</v>
       </c>
       <c r="G1197" t="str">
-        <v>50MM 2 Inch</v>
+        <v>100MM 4 Inch</v>
       </c>
       <c r="H1197" t="str">
         <v>MTR</v>
@@ -42312,10 +42312,10 @@
         <v>1197</v>
       </c>
       <c r="B1198" t="str">
-        <v>FG-401122</v>
+        <v>FG-401123</v>
       </c>
       <c r="C1198" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (100MM 4 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1198" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42327,7 +42327,7 @@
         <v>General</v>
       </c>
       <c r="G1198" t="str">
-        <v>100MM 4 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1198" t="str">
         <v>MTR</v>
@@ -42347,10 +42347,10 @@
         <v>1198</v>
       </c>
       <c r="B1199" t="str">
-        <v>FG-401123</v>
+        <v>FG-401124</v>
       </c>
       <c r="C1199" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1199" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42362,7 +42362,7 @@
         <v>General</v>
       </c>
       <c r="G1199" t="str">
-        <v>125MM 5 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1199" t="str">
         <v>MTR</v>
@@ -42382,10 +42382,10 @@
         <v>1199</v>
       </c>
       <c r="B1200" t="str">
-        <v>FG-401124</v>
+        <v>FG-401125</v>
       </c>
       <c r="C1200" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1200" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42397,7 +42397,7 @@
         <v>General</v>
       </c>
       <c r="G1200" t="str">
-        <v>150MM 6 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1200" t="str">
         <v>MTR</v>
@@ -42417,10 +42417,10 @@
         <v>1200</v>
       </c>
       <c r="B1201" t="str">
-        <v>FG-401125</v>
+        <v>FG-401126</v>
       </c>
       <c r="C1201" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1201" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42432,7 +42432,7 @@
         <v>General</v>
       </c>
       <c r="G1201" t="str">
-        <v>175MM 7 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1201" t="str">
         <v>MTR</v>
@@ -42452,22 +42452,22 @@
         <v>1201</v>
       </c>
       <c r="B1202" t="str">
-        <v>FG-401126</v>
+        <v>FG-401166</v>
       </c>
       <c r="C1202" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (200MM 8 Inch)</v>
+        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1202" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
+        <v>COLOUMN PIPE ECO V4</v>
       </c>
       <c r="E1202" t="str">
-        <v>UPVC CASING PIPES</v>
+        <v>UPVC COLUMN PIPES</v>
       </c>
       <c r="F1202" t="str">
         <v>General</v>
       </c>
       <c r="G1202" t="str">
-        <v>200MM 8 Inch</v>
+        <v>33MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1202" t="str">
         <v>MTR</v>
@@ -42479,7 +42479,7 @@
         <v>Active</v>
       </c>
       <c r="K1202" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>COLOUMN PIPE ECO V4 for submersible pump systems.</v>
       </c>
     </row>
     <row r="1203">
@@ -42487,10 +42487,10 @@
         <v>1202</v>
       </c>
       <c r="B1203" t="str">
-        <v>FG-401166</v>
+        <v>FG-401162</v>
       </c>
       <c r="C1203" t="str">
-        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG BELL END TYPE)</v>
       </c>
       <c r="D1203" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42502,7 +42502,7 @@
         <v>General</v>
       </c>
       <c r="G1203" t="str">
-        <v>33MM 12.5KG COUPLER TYPE</v>
+        <v>33MM 12.5KG BELL END TYPE</v>
       </c>
       <c r="H1203" t="str">
         <v>MTR</v>
@@ -42522,10 +42522,10 @@
         <v>1203</v>
       </c>
       <c r="B1204" t="str">
-        <v>FG-401162</v>
+        <v>FG-401165</v>
       </c>
       <c r="C1204" t="str">
-        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG BELL END TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 10KG COUPLER TYPE)</v>
       </c>
       <c r="D1204" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42537,7 +42537,7 @@
         <v>General</v>
       </c>
       <c r="G1204" t="str">
-        <v>33MM 12.5KG BELL END TYPE</v>
+        <v>42MM 10KG COUPLER TYPE</v>
       </c>
       <c r="H1204" t="str">
         <v>MTR</v>
@@ -42557,10 +42557,10 @@
         <v>1204</v>
       </c>
       <c r="B1205" t="str">
-        <v>FG-401165</v>
+        <v>FG-401167</v>
       </c>
       <c r="C1205" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 10KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1205" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42572,7 +42572,7 @@
         <v>General</v>
       </c>
       <c r="G1205" t="str">
-        <v>42MM 10KG COUPLER TYPE</v>
+        <v>42MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1205" t="str">
         <v>MTR</v>
@@ -42592,10 +42592,10 @@
         <v>1205</v>
       </c>
       <c r="B1206" t="str">
-        <v>FG-401167</v>
+        <v>FG-401163</v>
       </c>
       <c r="C1206" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG BELL END TYPE)</v>
       </c>
       <c r="D1206" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42607,7 +42607,7 @@
         <v>General</v>
       </c>
       <c r="G1206" t="str">
-        <v>42MM 12.5KG COUPLER TYPE</v>
+        <v>42MM 12.5KG BELL END TYPE</v>
       </c>
       <c r="H1206" t="str">
         <v>MTR</v>
@@ -42627,10 +42627,10 @@
         <v>1206</v>
       </c>
       <c r="B1207" t="str">
-        <v>FG-401163</v>
+        <v>FG-401164</v>
       </c>
       <c r="C1207" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG BELL END TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (48MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1207" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42642,7 +42642,7 @@
         <v>General</v>
       </c>
       <c r="G1207" t="str">
-        <v>42MM 12.5KG BELL END TYPE</v>
+        <v>48MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1207" t="str">
         <v>MTR</v>
@@ -42662,10 +42662,10 @@
         <v>1207</v>
       </c>
       <c r="B1208" t="str">
-        <v>FG-401164</v>
+        <v>FG-401168</v>
       </c>
       <c r="C1208" t="str">
-        <v>COLOUMN PIPE ECO V4 (48MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (60MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1208" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42677,7 +42677,7 @@
         <v>General</v>
       </c>
       <c r="G1208" t="str">
-        <v>48MM 12.5KG COUPLER TYPE</v>
+        <v>60MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1208" t="str">
         <v>MTR</v>
@@ -42697,13 +42697,13 @@
         <v>1208</v>
       </c>
       <c r="B1209" t="str">
-        <v>FG-401168</v>
+        <v>FG-401175</v>
       </c>
       <c r="C1209" t="str">
-        <v>COLOUMN PIPE ECO V4 (60MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (33MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1209" t="str">
-        <v>COLOUMN PIPE ECO V4</v>
+        <v>COLOUMN PIPE MEDIUM</v>
       </c>
       <c r="E1209" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -42712,7 +42712,7 @@
         <v>General</v>
       </c>
       <c r="G1209" t="str">
-        <v>60MM 12.5KG COUPLER TYPE</v>
+        <v>33MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1209" t="str">
         <v>MTR</v>
@@ -42724,7 +42724,7 @@
         <v>Active</v>
       </c>
       <c r="K1209" t="str">
-        <v>COLOUMN PIPE ECO V4 for submersible pump systems.</v>
+        <v>COLOUMN PIPE MEDIUM for submersible pump systems.</v>
       </c>
     </row>
     <row r="1210">
@@ -42732,10 +42732,10 @@
         <v>1209</v>
       </c>
       <c r="B1210" t="str">
-        <v>FG-401175</v>
+        <v>FG-401177</v>
       </c>
       <c r="C1210" t="str">
-        <v>COLOUMN PIPE MEDIUM (33MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (42MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1210" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42747,7 +42747,7 @@
         <v>General</v>
       </c>
       <c r="G1210" t="str">
-        <v>33MM 18KG COUPLER TYPE</v>
+        <v>42MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1210" t="str">
         <v>MTR</v>
@@ -42767,10 +42767,10 @@
         <v>1210</v>
       </c>
       <c r="B1211" t="str">
-        <v>FG-401177</v>
+        <v>FG-401176</v>
       </c>
       <c r="C1211" t="str">
-        <v>COLOUMN PIPE MEDIUM (42MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (48MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1211" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42782,7 +42782,7 @@
         <v>General</v>
       </c>
       <c r="G1211" t="str">
-        <v>42MM 18KG COUPLER TYPE</v>
+        <v>48MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1211" t="str">
         <v>MTR</v>
@@ -42802,10 +42802,10 @@
         <v>1211</v>
       </c>
       <c r="B1212" t="str">
-        <v>FG-401176</v>
+        <v>FG-401178</v>
       </c>
       <c r="C1212" t="str">
-        <v>COLOUMN PIPE MEDIUM (48MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (60MM 15KG COUPLER TYPE)</v>
       </c>
       <c r="D1212" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42817,7 +42817,7 @@
         <v>General</v>
       </c>
       <c r="G1212" t="str">
-        <v>48MM 18KG COUPLER TYPE</v>
+        <v>60MM 15KG COUPLER TYPE</v>
       </c>
       <c r="H1212" t="str">
         <v>MTR</v>
@@ -42837,10 +42837,10 @@
         <v>1212</v>
       </c>
       <c r="B1213" t="str">
-        <v>FG-401178</v>
+        <v>FG-401180</v>
       </c>
       <c r="C1213" t="str">
-        <v>COLOUMN PIPE MEDIUM (60MM 15KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (75MM 10KG COUPLER TYPE)</v>
       </c>
       <c r="D1213" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42852,7 +42852,7 @@
         <v>General</v>
       </c>
       <c r="G1213" t="str">
-        <v>60MM 15KG COUPLER TYPE</v>
+        <v>75MM 10KG COUPLER TYPE</v>
       </c>
       <c r="H1213" t="str">
         <v>MTR</v>
@@ -42872,13 +42872,13 @@
         <v>1213</v>
       </c>
       <c r="B1214" t="str">
-        <v>FG-401180</v>
+        <v>FG-401169</v>
       </c>
       <c r="C1214" t="str">
-        <v>COLOUMN PIPE MEDIUM (75MM 10KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (33MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1214" t="str">
-        <v>COLOUMN PIPE MEDIUM</v>
+        <v>COLOUMN PIPE STANDARD</v>
       </c>
       <c r="E1214" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -42887,7 +42887,7 @@
         <v>General</v>
       </c>
       <c r="G1214" t="str">
-        <v>75MM 10KG COUPLER TYPE</v>
+        <v>33MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1214" t="str">
         <v>MTR</v>
@@ -42899,7 +42899,7 @@
         <v>Active</v>
       </c>
       <c r="K1214" t="str">
-        <v>COLOUMN PIPE MEDIUM for submersible pump systems.</v>
+        <v>COLOUMN PIPE STANDARD for submersible pump systems.</v>
       </c>
     </row>
     <row r="1215">
@@ -42907,10 +42907,10 @@
         <v>1214</v>
       </c>
       <c r="B1215" t="str">
-        <v>FG-401169</v>
+        <v>FG-401171</v>
       </c>
       <c r="C1215" t="str">
-        <v>COLOUMN PIPE STANDARD (33MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (42MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1215" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42922,7 +42922,7 @@
         <v>General</v>
       </c>
       <c r="G1215" t="str">
-        <v>33MM 25KG COUPLER TYPE</v>
+        <v>42MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1215" t="str">
         <v>MTR</v>
@@ -42942,10 +42942,10 @@
         <v>1215</v>
       </c>
       <c r="B1216" t="str">
-        <v>FG-401171</v>
+        <v>FG-401170</v>
       </c>
       <c r="C1216" t="str">
-        <v>COLOUMN PIPE STANDARD (42MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (48MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1216" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42957,7 +42957,7 @@
         <v>General</v>
       </c>
       <c r="G1216" t="str">
-        <v>42MM 25KG COUPLER TYPE</v>
+        <v>48MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1216" t="str">
         <v>MTR</v>
@@ -42977,10 +42977,10 @@
         <v>1216</v>
       </c>
       <c r="B1217" t="str">
-        <v>FG-401170</v>
+        <v>FG-401172</v>
       </c>
       <c r="C1217" t="str">
-        <v>COLOUMN PIPE STANDARD (48MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (60MM 20KG COUPLER TYPE)</v>
       </c>
       <c r="D1217" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42992,7 +42992,7 @@
         <v>General</v>
       </c>
       <c r="G1217" t="str">
-        <v>48MM 25KG COUPLER TYPE</v>
+        <v>60MM 20KG COUPLER TYPE</v>
       </c>
       <c r="H1217" t="str">
         <v>MTR</v>
@@ -43012,10 +43012,10 @@
         <v>1217</v>
       </c>
       <c r="B1218" t="str">
-        <v>FG-401172</v>
+        <v>FG-401174</v>
       </c>
       <c r="C1218" t="str">
-        <v>COLOUMN PIPE STANDARD (60MM 20KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (75MM 20KG COUPLER TYPE)</v>
       </c>
       <c r="D1218" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -43027,7 +43027,7 @@
         <v>General</v>
       </c>
       <c r="G1218" t="str">
-        <v>60MM 20KG COUPLER TYPE</v>
+        <v>75MM 20KG COUPLER TYPE</v>
       </c>
       <c r="H1218" t="str">
         <v>MTR</v>
@@ -43047,13 +43047,13 @@
         <v>1218</v>
       </c>
       <c r="B1219" t="str">
-        <v>FG-401174</v>
+        <v>-</v>
       </c>
       <c r="C1219" t="str">
-        <v>COLOUMN PIPE STANDARD (75MM 20KG COUPLER TYPE)</v>
+        <v>3M STANDARD PLUS PIPE (60MM 25 COUPLER TYPE)</v>
       </c>
       <c r="D1219" t="str">
-        <v>COLOUMN PIPE STANDARD</v>
+        <v>3M STANDARD PLUS PIPE</v>
       </c>
       <c r="E1219" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43062,7 +43062,7 @@
         <v>General</v>
       </c>
       <c r="G1219" t="str">
-        <v>75MM 20KG COUPLER TYPE</v>
+        <v>60MM 25 COUPLER TYPE</v>
       </c>
       <c r="H1219" t="str">
         <v>MTR</v>
@@ -43074,7 +43074,7 @@
         <v>Active</v>
       </c>
       <c r="K1219" t="str">
-        <v>COLOUMN PIPE STANDARD for submersible pump systems.</v>
+        <v>3M Standard Plus UPVC Column Pipe for submersible pump systems.</v>
       </c>
     </row>
     <row r="1220">
@@ -43082,13 +43082,13 @@
         <v>1219</v>
       </c>
       <c r="B1220" t="str">
-        <v>-</v>
+        <v>FG-401182</v>
       </c>
       <c r="C1220" t="str">
-        <v>3M STANDARD PLUS PIPE (60MM 25 COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (42MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1220" t="str">
-        <v>3M STANDARD PLUS PIPE</v>
+        <v>COLOUMN PIPE HEAVY</v>
       </c>
       <c r="E1220" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43097,7 +43097,7 @@
         <v>General</v>
       </c>
       <c r="G1220" t="str">
-        <v>60MM 25 COUPLER TYPE</v>
+        <v>42MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1220" t="str">
         <v>MTR</v>
@@ -43109,7 +43109,7 @@
         <v>Active</v>
       </c>
       <c r="K1220" t="str">
-        <v>3M Standard Plus UPVC Column Pipe for submersible pump systems.</v>
+        <v>COLOUMN PIPE HEAVY for submersible pump systems.</v>
       </c>
     </row>
     <row r="1221">
@@ -43117,10 +43117,10 @@
         <v>1220</v>
       </c>
       <c r="B1221" t="str">
-        <v>FG-401182</v>
+        <v>FG-401181</v>
       </c>
       <c r="C1221" t="str">
-        <v>COLOUMN PIPE HEAVY (42MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (48MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1221" t="str">
         <v>COLOUMN PIPE HEAVY</v>
@@ -43132,7 +43132,7 @@
         <v>General</v>
       </c>
       <c r="G1221" t="str">
-        <v>42MM 30KG COUPLER TYPE</v>
+        <v>48MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1221" t="str">
         <v>MTR</v>
@@ -43152,10 +43152,10 @@
         <v>1221</v>
       </c>
       <c r="B1222" t="str">
-        <v>FG-401181</v>
+        <v>FG-401183</v>
       </c>
       <c r="C1222" t="str">
-        <v>COLOUMN PIPE HEAVY (48MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (60MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1222" t="str">
         <v>COLOUMN PIPE HEAVY</v>
@@ -43167,7 +43167,7 @@
         <v>General</v>
       </c>
       <c r="G1222" t="str">
-        <v>48MM 30KG COUPLER TYPE</v>
+        <v>60MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1222" t="str">
         <v>MTR</v>
@@ -43187,13 +43187,13 @@
         <v>1222</v>
       </c>
       <c r="B1223" t="str">
-        <v>FG-401183</v>
+        <v>FG-401179</v>
       </c>
       <c r="C1223" t="str">
-        <v>COLOUMN PIPE HEAVY (60MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM PLUS (60MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1223" t="str">
-        <v>COLOUMN PIPE HEAVY</v>
+        <v>COLOUMN PIPE MEDIUM PLUS</v>
       </c>
       <c r="E1223" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43202,7 +43202,7 @@
         <v>General</v>
       </c>
       <c r="G1223" t="str">
-        <v>60MM 30KG COUPLER TYPE</v>
+        <v>60MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1223" t="str">
         <v>MTR</v>
@@ -43214,7 +43214,7 @@
         <v>Active</v>
       </c>
       <c r="K1223" t="str">
-        <v>COLOUMN PIPE HEAVY for submersible pump systems.</v>
+        <v>COLOUMN PIPE MEDIUM PLUS for submersible pump systems.</v>
       </c>
     </row>
     <row r="1224">
@@ -43222,34 +43222,34 @@
         <v>1223</v>
       </c>
       <c r="B1224" t="str">
-        <v>FG-401179</v>
+        <v>FG-401569</v>
       </c>
       <c r="C1224" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS (60MM 18KG COUPLER TYPE)</v>
+        <v>CONSTRUCTION GHAMELA SHIVA (15 Inch)</v>
       </c>
       <c r="D1224" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS</v>
+        <v>CONSTRUCTION GHAMELA SHIVA</v>
       </c>
       <c r="E1224" t="str">
-        <v>UPVC COLUMN PIPES</v>
+        <v>HOUSEHOLD PRODUCTS</v>
       </c>
       <c r="F1224" t="str">
         <v>General</v>
       </c>
       <c r="G1224" t="str">
-        <v>60MM 18KG COUPLER TYPE</v>
+        <v>15 Inch</v>
       </c>
       <c r="H1224" t="str">
-        <v>MTR</v>
+        <v>BAGS</v>
       </c>
       <c r="I1224" t="str">
-        <v>-</v>
+        <v>75</v>
       </c>
       <c r="J1224" t="str">
         <v>Active</v>
       </c>
       <c r="K1224" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS for submersible pump systems.</v>
+        <v>CONSTRUCTION GHAMELA SHIVA high durability ghamela.</v>
       </c>
     </row>
     <row r="1225">
@@ -43257,13 +43257,13 @@
         <v>1224</v>
       </c>
       <c r="B1225" t="str">
-        <v>FG-401569</v>
+        <v>FG-401570</v>
       </c>
       <c r="C1225" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA (15 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA GOURI (15 Inch)</v>
       </c>
       <c r="D1225" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA</v>
+        <v>MULTIPURPOSE GHAMELA GOURI</v>
       </c>
       <c r="E1225" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43284,7 +43284,7 @@
         <v>Active</v>
       </c>
       <c r="K1225" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA GOURI high durability ghamela.</v>
       </c>
     </row>
     <row r="1226">
@@ -43292,13 +43292,13 @@
         <v>1225</v>
       </c>
       <c r="B1226" t="str">
-        <v>FG-401570</v>
+        <v>FG-401571</v>
       </c>
       <c r="C1226" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI (15 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA (16 Inch)</v>
       </c>
       <c r="D1226" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA</v>
       </c>
       <c r="E1226" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43307,19 +43307,19 @@
         <v>General</v>
       </c>
       <c r="G1226" t="str">
-        <v>15 Inch</v>
+        <v>16 Inch</v>
       </c>
       <c r="H1226" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1226" t="str">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="J1226" t="str">
         <v>Active</v>
       </c>
       <c r="K1226" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA high durability ghamela.</v>
       </c>
     </row>
     <row r="1227">
@@ -43327,13 +43327,13 @@
         <v>1226</v>
       </c>
       <c r="B1227" t="str">
-        <v>FG-401571</v>
+        <v>FG-401573</v>
       </c>
       <c r="C1227" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA (16 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV (18 Inch)</v>
       </c>
       <c r="D1227" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV</v>
       </c>
       <c r="E1227" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43342,19 +43342,19 @@
         <v>General</v>
       </c>
       <c r="G1227" t="str">
-        <v>16 Inch</v>
+        <v>18 Inch</v>
       </c>
       <c r="H1227" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1227" t="str">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J1227" t="str">
         <v>Active</v>
       </c>
       <c r="K1227" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV high durability ghamela.</v>
       </c>
     </row>
     <row r="1228">
@@ -43362,13 +43362,13 @@
         <v>1227</v>
       </c>
       <c r="B1228" t="str">
-        <v>FG-401573</v>
+        <v>FG-401574</v>
       </c>
       <c r="C1228" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV (18 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET (20 Inch)</v>
       </c>
       <c r="D1228" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET</v>
       </c>
       <c r="E1228" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43377,19 +43377,19 @@
         <v>General</v>
       </c>
       <c r="G1228" t="str">
-        <v>18 Inch</v>
+        <v>20 Inch</v>
       </c>
       <c r="H1228" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1228" t="str">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J1228" t="str">
         <v>Active</v>
       </c>
       <c r="K1228" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET high durability ghamela.</v>
       </c>
     </row>
     <row r="1229">
@@ -43397,13 +43397,13 @@
         <v>1228</v>
       </c>
       <c r="B1229" t="str">
-        <v>FG-401574</v>
+        <v>FG-401572</v>
       </c>
       <c r="C1229" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET (20 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI (17 Inch)</v>
       </c>
       <c r="D1229" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI</v>
       </c>
       <c r="E1229" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43412,19 +43412,19 @@
         <v>General</v>
       </c>
       <c r="G1229" t="str">
-        <v>20 Inch</v>
+        <v>17 Inch</v>
       </c>
       <c r="H1229" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1229" t="str">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J1229" t="str">
         <v>Active</v>
       </c>
       <c r="K1229" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI high durability ghamela.</v>
       </c>
     </row>
     <row r="1230">
@@ -43432,13 +43432,13 @@
         <v>1229</v>
       </c>
       <c r="B1230" t="str">
-        <v>FG-401572</v>
+        <v>FG-401575</v>
       </c>
       <c r="C1230" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI (17 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ (22 Inch)</v>
       </c>
       <c r="D1230" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ</v>
       </c>
       <c r="E1230" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43447,19 +43447,19 @@
         <v>General</v>
       </c>
       <c r="G1230" t="str">
-        <v>17 Inch</v>
+        <v>22 Inch</v>
       </c>
       <c r="H1230" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1230" t="str">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J1230" t="str">
         <v>Active</v>
       </c>
       <c r="K1230" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ high durability ghamela.</v>
       </c>
     </row>
     <row r="1231">
@@ -43467,13 +43467,13 @@
         <v>1230</v>
       </c>
       <c r="B1231" t="str">
-        <v>FG-401575</v>
+        <v>FG-401578</v>
       </c>
       <c r="C1231" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ (22 Inch)</v>
+        <v>AQUA PLAST GHAMELA 16 (16 Inch)</v>
       </c>
       <c r="D1231" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ</v>
+        <v>AQUA PLAST GHAMELA 16</v>
       </c>
       <c r="E1231" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43482,19 +43482,19 @@
         <v>General</v>
       </c>
       <c r="G1231" t="str">
-        <v>22 Inch</v>
+        <v>16 Inch</v>
       </c>
       <c r="H1231" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1231" t="str">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J1231" t="str">
         <v>Active</v>
       </c>
       <c r="K1231" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ high durability ghamela.</v>
+        <v>AQUA PLAST GHAMELA 16 high durability ghamela.</v>
       </c>
     </row>
     <row r="1232">
@@ -43502,13 +43502,13 @@
         <v>1231</v>
       </c>
       <c r="B1232" t="str">
-        <v>FG-401578</v>
+        <v>FG-401579</v>
       </c>
       <c r="C1232" t="str">
-        <v>AQUA PLAST GHAMELA 16 (16 Inch)</v>
+        <v>AQUA PLAST GHAMELA 17 (17 Inch)</v>
       </c>
       <c r="D1232" t="str">
-        <v>AQUA PLAST GHAMELA 16</v>
+        <v>AQUA PLAST GHAMELA 17</v>
       </c>
       <c r="E1232" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43517,7 +43517,7 @@
         <v>General</v>
       </c>
       <c r="G1232" t="str">
-        <v>16 Inch</v>
+        <v>17 Inch</v>
       </c>
       <c r="H1232" t="str">
         <v>BAGS</v>
@@ -43529,7 +43529,7 @@
         <v>Active</v>
       </c>
       <c r="K1232" t="str">
-        <v>AQUA PLAST GHAMELA 16 high durability ghamela.</v>
+        <v>AQUA PLAST GHAMELA 17 high durability ghamela.</v>
       </c>
     </row>
     <row r="1233">
@@ -43537,34 +43537,34 @@
         <v>1232</v>
       </c>
       <c r="B1233" t="str">
-        <v>FG-401579</v>
+        <v>FG-401364</v>
       </c>
       <c r="C1233" t="str">
-        <v>AQUA PLAST GHAMELA 17 (17 Inch)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1/2 15MM)</v>
       </c>
       <c r="D1233" t="str">
-        <v>AQUA PLAST GHAMELA 17</v>
+        <v>GAP-ORA FLOW GARDEN PIPE</v>
       </c>
       <c r="E1233" t="str">
-        <v>HOUSEHOLD PRODUCTS</v>
+        <v>Garden, Braided &amp; LDPE Pipes</v>
       </c>
       <c r="F1233" t="str">
         <v>General</v>
       </c>
       <c r="G1233" t="str">
-        <v>17 Inch</v>
+        <v>1/2 15MM</v>
       </c>
       <c r="H1233" t="str">
-        <v>BAGS</v>
+        <v>BDL</v>
       </c>
       <c r="I1233" t="str">
-        <v>60</v>
+        <v>-</v>
       </c>
       <c r="J1233" t="str">
         <v>Active</v>
       </c>
       <c r="K1233" t="str">
-        <v>AQUA PLAST GHAMELA 17 high durability ghamela.</v>
+        <v>GAP-ORA FLOW GARDEN PIPE. Available sizes: 1/2 15MM, 3/4 20MM, 1 25MM, 1 1/4 32MM.</v>
       </c>
     </row>
     <row r="1234">
@@ -43572,10 +43572,10 @@
         <v>1233</v>
       </c>
       <c r="B1234" t="str">
-        <v>FG-401364</v>
+        <v>FG-401365</v>
       </c>
       <c r="C1234" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1/2 15MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (3/4 20MM)</v>
       </c>
       <c r="D1234" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43587,7 +43587,7 @@
         <v>General</v>
       </c>
       <c r="G1234" t="str">
-        <v>1/2 15MM</v>
+        <v>3/4 20MM</v>
       </c>
       <c r="H1234" t="str">
         <v>BDL</v>
@@ -43607,10 +43607,10 @@
         <v>1234</v>
       </c>
       <c r="B1235" t="str">
-        <v>FG-401365</v>
+        <v>FG-401366</v>
       </c>
       <c r="C1235" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (3/4 20MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1 25MM)</v>
       </c>
       <c r="D1235" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43622,7 +43622,7 @@
         <v>General</v>
       </c>
       <c r="G1235" t="str">
-        <v>3/4 20MM</v>
+        <v>1 25MM</v>
       </c>
       <c r="H1235" t="str">
         <v>BDL</v>
@@ -43642,10 +43642,10 @@
         <v>1235</v>
       </c>
       <c r="B1236" t="str">
-        <v>FG-401366</v>
+        <v>FG-401367</v>
       </c>
       <c r="C1236" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1 25MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1 1/4 32MM)</v>
       </c>
       <c r="D1236" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43657,7 +43657,7 @@
         <v>General</v>
       </c>
       <c r="G1236" t="str">
-        <v>1 25MM</v>
+        <v>1 1/4 32MM</v>
       </c>
       <c r="H1236" t="str">
         <v>BDL</v>
@@ -43677,13 +43677,13 @@
         <v>1236</v>
       </c>
       <c r="B1237" t="str">
-        <v>FG-401367</v>
+        <v>FG-401370</v>
       </c>
       <c r="C1237" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1 1/4 32MM)</v>
+        <v>GAP-ORA BRAIDED PIPE (15MM 1/2)</v>
       </c>
       <c r="D1237" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE</v>
+        <v>GAP-ORA BRAIDED PIPE</v>
       </c>
       <c r="E1237" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43692,7 +43692,7 @@
         <v>General</v>
       </c>
       <c r="G1237" t="str">
-        <v>1 1/4 32MM</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1237" t="str">
         <v>BDL</v>
@@ -43704,7 +43704,7 @@
         <v>Active</v>
       </c>
       <c r="K1237" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE. Available sizes: 1/2 15MM, 3/4 20MM, 1 25MM, 1 1/4 32MM.</v>
+        <v>GAP-ORA BRAIDED PIPE.</v>
       </c>
     </row>
     <row r="1238">
@@ -43712,10 +43712,10 @@
         <v>1237</v>
       </c>
       <c r="B1238" t="str">
-        <v>FG-401370</v>
+        <v>FG-401371</v>
       </c>
       <c r="C1238" t="str">
-        <v>GAP-ORA BRAIDED PIPE (15MM 1/2)</v>
+        <v>GAP-ORA BRAIDED PIPE (20MM 3/4)</v>
       </c>
       <c r="D1238" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43727,7 +43727,7 @@
         <v>General</v>
       </c>
       <c r="G1238" t="str">
-        <v>15MM 1/2</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1238" t="str">
         <v>BDL</v>
@@ -43747,10 +43747,10 @@
         <v>1238</v>
       </c>
       <c r="B1239" t="str">
-        <v>FG-401371</v>
+        <v>FG-401372</v>
       </c>
       <c r="C1239" t="str">
-        <v>GAP-ORA BRAIDED PIPE (20MM 3/4)</v>
+        <v>GAP-ORA BRAIDED PIPE (25MM 1)</v>
       </c>
       <c r="D1239" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43762,7 +43762,7 @@
         <v>General</v>
       </c>
       <c r="G1239" t="str">
-        <v>20MM 3/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1239" t="str">
         <v>BDL</v>
@@ -43782,10 +43782,10 @@
         <v>1239</v>
       </c>
       <c r="B1240" t="str">
-        <v>FG-401372</v>
+        <v>FG-401373</v>
       </c>
       <c r="C1240" t="str">
-        <v>GAP-ORA BRAIDED PIPE (25MM 1)</v>
+        <v>GAP-ORA BRAIDED PIPE (32MM 1 1/4)</v>
       </c>
       <c r="D1240" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43797,7 +43797,7 @@
         <v>General</v>
       </c>
       <c r="G1240" t="str">
-        <v>25MM 1</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1240" t="str">
         <v>BDL</v>
@@ -43817,13 +43817,13 @@
         <v>1240</v>
       </c>
       <c r="B1241" t="str">
-        <v>FG-401373</v>
+        <v>FG-401355</v>
       </c>
       <c r="C1241" t="str">
-        <v>GAP-ORA BRAIDED PIPE (32MM 1 1/4)</v>
+        <v>GARDEN FOAM PIPES (15MM 1/2)</v>
       </c>
       <c r="D1241" t="str">
-        <v>GAP-ORA BRAIDED PIPE</v>
+        <v>GARDEN FOAM PIPES</v>
       </c>
       <c r="E1241" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43832,7 +43832,7 @@
         <v>General</v>
       </c>
       <c r="G1241" t="str">
-        <v>32MM 1 1/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1241" t="str">
         <v>BDL</v>
@@ -43844,7 +43844,7 @@
         <v>Active</v>
       </c>
       <c r="K1241" t="str">
-        <v>GAP-ORA BRAIDED PIPE.</v>
+        <v>GARDEN FOAM PIPES.</v>
       </c>
     </row>
     <row r="1242">
@@ -43852,10 +43852,10 @@
         <v>1241</v>
       </c>
       <c r="B1242" t="str">
-        <v>FG-401355</v>
+        <v>FG-401356</v>
       </c>
       <c r="C1242" t="str">
-        <v>GARDEN FOAM PIPES (15MM 1/2)</v>
+        <v>GARDEN FOAM PIPES (20MM 3/4)</v>
       </c>
       <c r="D1242" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43867,7 +43867,7 @@
         <v>General</v>
       </c>
       <c r="G1242" t="str">
-        <v>15MM 1/2</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1242" t="str">
         <v>BDL</v>
@@ -43887,10 +43887,10 @@
         <v>1242</v>
       </c>
       <c r="B1243" t="str">
-        <v>FG-401356</v>
+        <v>FG-401369</v>
       </c>
       <c r="C1243" t="str">
-        <v>GARDEN FOAM PIPES (20MM 3/4)</v>
+        <v>GARDEN FOAM PIPES (20MM 3/4 20MTR)</v>
       </c>
       <c r="D1243" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43902,7 +43902,7 @@
         <v>General</v>
       </c>
       <c r="G1243" t="str">
-        <v>20MM 3/4</v>
+        <v>20MM 3/4 20MTR</v>
       </c>
       <c r="H1243" t="str">
         <v>BDL</v>
@@ -43922,10 +43922,10 @@
         <v>1243</v>
       </c>
       <c r="B1244" t="str">
-        <v>FG-401369</v>
+        <v>FG-401357</v>
       </c>
       <c r="C1244" t="str">
-        <v>GARDEN FOAM PIPES (20MM 3/4 20MTR)</v>
+        <v>GARDEN FOAM PIPES (25MM 1)</v>
       </c>
       <c r="D1244" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43937,7 +43937,7 @@
         <v>General</v>
       </c>
       <c r="G1244" t="str">
-        <v>20MM 3/4 20MTR</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1244" t="str">
         <v>BDL</v>
@@ -43957,10 +43957,10 @@
         <v>1244</v>
       </c>
       <c r="B1245" t="str">
-        <v>FG-401357</v>
+        <v>FG-401358</v>
       </c>
       <c r="C1245" t="str">
-        <v>GARDEN FOAM PIPES (25MM 1)</v>
+        <v>GARDEN FOAM PIPES (32MM 1 1/4)</v>
       </c>
       <c r="D1245" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43972,7 +43972,7 @@
         <v>General</v>
       </c>
       <c r="G1245" t="str">
-        <v>25MM 1</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1245" t="str">
         <v>BDL</v>
@@ -43992,13 +43992,13 @@
         <v>1245</v>
       </c>
       <c r="B1246" t="str">
-        <v>FG-401358</v>
+        <v>FG-401344</v>
       </c>
       <c r="C1246" t="str">
-        <v>GARDEN FOAM PIPES (32MM 1 1/4)</v>
+        <v>BRAIDED PIPE (15MM 1/2)</v>
       </c>
       <c r="D1246" t="str">
-        <v>GARDEN FOAM PIPES</v>
+        <v>BRAIDED PIPE</v>
       </c>
       <c r="E1246" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44007,7 +44007,7 @@
         <v>General</v>
       </c>
       <c r="G1246" t="str">
-        <v>32MM 1 1/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1246" t="str">
         <v>BDL</v>
@@ -44019,7 +44019,7 @@
         <v>Active</v>
       </c>
       <c r="K1246" t="str">
-        <v>GARDEN FOAM PIPES.</v>
+        <v>Reinforced Braided Garden Pipe.</v>
       </c>
     </row>
     <row r="1247">
@@ -44027,10 +44027,10 @@
         <v>1246</v>
       </c>
       <c r="B1247" t="str">
-        <v>FG-401344</v>
+        <v>FG-401345</v>
       </c>
       <c r="C1247" t="str">
-        <v>BRAIDED PIPE (15MM 1/2)</v>
+        <v>BRAIDED PIPE (20MM 3/4)</v>
       </c>
       <c r="D1247" t="str">
         <v>BRAIDED PIPE</v>
@@ -44042,7 +44042,7 @@
         <v>General</v>
       </c>
       <c r="G1247" t="str">
-        <v>15MM 1/2</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1247" t="str">
         <v>BDL</v>
@@ -44062,10 +44062,10 @@
         <v>1247</v>
       </c>
       <c r="B1248" t="str">
-        <v>FG-401345</v>
+        <v>FG-401346</v>
       </c>
       <c r="C1248" t="str">
-        <v>BRAIDED PIPE (20MM 3/4)</v>
+        <v>BRAIDED PIPE (25MM 1)</v>
       </c>
       <c r="D1248" t="str">
         <v>BRAIDED PIPE</v>
@@ -44077,7 +44077,7 @@
         <v>General</v>
       </c>
       <c r="G1248" t="str">
-        <v>20MM 3/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1248" t="str">
         <v>BDL</v>
@@ -44097,10 +44097,10 @@
         <v>1248</v>
       </c>
       <c r="B1249" t="str">
-        <v>FG-401346</v>
+        <v>FG-401363</v>
       </c>
       <c r="C1249" t="str">
-        <v>BRAIDED PIPE (25MM 1)</v>
+        <v>BRAIDED PIPE (32MM 1 1/4)</v>
       </c>
       <c r="D1249" t="str">
         <v>BRAIDED PIPE</v>
@@ -44112,7 +44112,7 @@
         <v>General</v>
       </c>
       <c r="G1249" t="str">
-        <v>25MM 1</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1249" t="str">
         <v>BDL</v>
@@ -44132,13 +44132,13 @@
         <v>1249</v>
       </c>
       <c r="B1250" t="str">
-        <v>FG-401363</v>
+        <v>FG-401374</v>
       </c>
       <c r="C1250" t="str">
-        <v>BRAIDED PIPE (32MM 1 1/4)</v>
+        <v>LEVEL PIPE (6MM)</v>
       </c>
       <c r="D1250" t="str">
-        <v>BRAIDED PIPE</v>
+        <v>LEVEL PIPE</v>
       </c>
       <c r="E1250" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44147,7 +44147,7 @@
         <v>General</v>
       </c>
       <c r="G1250" t="str">
-        <v>32MM 1 1/4</v>
+        <v>6MM</v>
       </c>
       <c r="H1250" t="str">
         <v>BDL</v>
@@ -44159,7 +44159,7 @@
         <v>Active</v>
       </c>
       <c r="K1250" t="str">
-        <v>Reinforced Braided Garden Pipe.</v>
+        <v>Transparent Level Pipe for construction &amp; garden work.</v>
       </c>
     </row>
     <row r="1251">
@@ -44167,13 +44167,13 @@
         <v>1250</v>
       </c>
       <c r="B1251" t="str">
-        <v>FG-401374</v>
+        <v>FG-401340</v>
       </c>
       <c r="C1251" t="str">
-        <v>LEVEL PIPE (6MM)</v>
+        <v>GARDEN PIPES SUPER FLOW (15MM 1/2)</v>
       </c>
       <c r="D1251" t="str">
-        <v>LEVEL PIPE</v>
+        <v>GARDEN PIPES SUPER FLOW</v>
       </c>
       <c r="E1251" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -44182,7 +44182,7 @@
         <v>General</v>
       </c>
       <c r="G1251" t="str">
-        <v>6MM</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1251" t="str">
         <v>BDL</v>
@@ -44194,7 +44194,7 @@
         <v>Active</v>
       </c>
       <c r="K1251" t="str">
-        <v>Transparent Level Pipe for construction &amp; garden work.</v>
+        <v>GARDEN PIPES SUPER FLOW.</v>
       </c>
     </row>
     <row r="1252">
@@ -44202,10 +44202,10 @@
         <v>1251</v>
       </c>
       <c r="B1252" t="str">
-        <v>FG-401340</v>
+        <v>FG-401341</v>
       </c>
       <c r="C1252" t="str">
-        <v>GARDEN PIPES SUPER FLOW (15MM 1/2)</v>
+        <v>GARDEN PIPES SUPER FLOW (20MM 3/4)</v>
       </c>
       <c r="D1252" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44217,7 +44217,7 @@
         <v>General</v>
       </c>
       <c r="G1252" t="str">
-        <v>15MM 1/2</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1252" t="str">
         <v>BDL</v>
@@ -44237,10 +44237,10 @@
         <v>1252</v>
       </c>
       <c r="B1253" t="str">
-        <v>FG-401341</v>
+        <v>FG-401652</v>
       </c>
       <c r="C1253" t="str">
-        <v>GARDEN PIPES SUPER FLOW (20MM 3/4)</v>
+        <v>GARDEN PIPES SUPER FLOW (20MM 3/4 15MTR)</v>
       </c>
       <c r="D1253" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44252,7 +44252,7 @@
         <v>General</v>
       </c>
       <c r="G1253" t="str">
-        <v>20MM 3/4</v>
+        <v>20MM 3/4 15MTR</v>
       </c>
       <c r="H1253" t="str">
         <v>BDL</v>
@@ -44272,10 +44272,10 @@
         <v>1253</v>
       </c>
       <c r="B1254" t="str">
-        <v>FG-401652</v>
+        <v>FG-401342</v>
       </c>
       <c r="C1254" t="str">
-        <v>GARDEN PIPES SUPER FLOW (20MM 3/4 15MTR)</v>
+        <v>GARDEN PIPES SUPER FLOW (25MM 1)</v>
       </c>
       <c r="D1254" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44287,7 +44287,7 @@
         <v>General</v>
       </c>
       <c r="G1254" t="str">
-        <v>20MM 3/4 15MTR</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1254" t="str">
         <v>BDL</v>
@@ -44307,10 +44307,10 @@
         <v>1254</v>
       </c>
       <c r="B1255" t="str">
-        <v>FG-401342</v>
+        <v>FG-401343</v>
       </c>
       <c r="C1255" t="str">
-        <v>GARDEN PIPES SUPER FLOW (25MM 1)</v>
+        <v>GARDEN PIPES SUPER FLOW (32MM 1 1/4)</v>
       </c>
       <c r="D1255" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44322,7 +44322,7 @@
         <v>General</v>
       </c>
       <c r="G1255" t="str">
-        <v>25MM 1</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1255" t="str">
         <v>BDL</v>
@@ -44342,10 +44342,10 @@
         <v>1255</v>
       </c>
       <c r="B1256" t="str">
-        <v>FG-401343</v>
+        <v>FG-401627</v>
       </c>
       <c r="C1256" t="str">
-        <v>GARDEN PIPES SUPER FLOW (32MM 1 1/4)</v>
+        <v>GARDEN PIPES SUPER FLOW (40MM 1 1/2)</v>
       </c>
       <c r="D1256" t="str">
         <v>GARDEN PIPES SUPER FLOW</v>
@@ -44357,7 +44357,7 @@
         <v>General</v>
       </c>
       <c r="G1256" t="str">
-        <v>32MM 1 1/4</v>
+        <v>40MM 1 1/2</v>
       </c>
       <c r="H1256" t="str">
         <v>BDL</v>
@@ -44377,34 +44377,34 @@
         <v>1256</v>
       </c>
       <c r="B1257" t="str">
-        <v>FG-401627</v>
+        <v>FG-401552</v>
       </c>
       <c r="C1257" t="str">
-        <v>GARDEN PIPES SUPER FLOW (40MM 1 1/2)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2 inch)</v>
       </c>
       <c r="D1257" t="str">
-        <v>GARDEN PIPES SUPER FLOW</v>
+        <v>EDGE SERIES SHORT BODY TAP</v>
       </c>
       <c r="E1257" t="str">
-        <v>Garden, Braided &amp; LDPE Pipes</v>
+        <v>FAUCETS</v>
       </c>
       <c r="F1257" t="str">
         <v>General</v>
       </c>
       <c r="G1257" t="str">
-        <v>40MM 1 1/2</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1257" t="str">
-        <v>BDL</v>
-      </c>
-      <c r="I1257" t="str">
-        <v>-</v>
+        <v>NOS</v>
+      </c>
+      <c r="I1257">
+        <v>20</v>
       </c>
       <c r="J1257" t="str">
         <v>Active</v>
       </c>
       <c r="K1257" t="str">
-        <v>GARDEN PIPES SUPER FLOW.</v>
+        <v>EDGE SERIES SHORT BODY TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1258">
@@ -44415,7 +44415,7 @@
         <v>FG-401552</v>
       </c>
       <c r="C1258" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2 inch)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2)</v>
       </c>
       <c r="D1258" t="str">
         <v>EDGE SERIES SHORT BODY TAP</v>
@@ -44427,7 +44427,7 @@
         <v>General</v>
       </c>
       <c r="G1258" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1258" t="str">
         <v>NOS</v>
@@ -44450,7 +44450,7 @@
         <v>FG-401552</v>
       </c>
       <c r="C1259" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2)</v>
+        <v>EDGE SERIES SHORT BODY TAP (1/2")</v>
       </c>
       <c r="D1259" t="str">
         <v>EDGE SERIES SHORT BODY TAP</v>
@@ -44462,7 +44462,7 @@
         <v>General</v>
       </c>
       <c r="G1259" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1259" t="str">
         <v>NOS</v>
@@ -44482,13 +44482,13 @@
         <v>1259</v>
       </c>
       <c r="B1260" t="str">
-        <v>FG-401552</v>
+        <v>FG-401551</v>
       </c>
       <c r="C1260" t="str">
-        <v>EDGE SERIES SHORT BODY TAP (1/2")</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2 inch)</v>
       </c>
       <c r="D1260" t="str">
-        <v>EDGE SERIES SHORT BODY TAP</v>
+        <v>EDGE SERIES LONG BODY TAP</v>
       </c>
       <c r="E1260" t="str">
         <v>FAUCETS</v>
@@ -44497,19 +44497,19 @@
         <v>General</v>
       </c>
       <c r="G1260" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1260" t="str">
         <v>NOS</v>
       </c>
       <c r="I1260">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J1260" t="str">
         <v>Active</v>
       </c>
       <c r="K1260" t="str">
-        <v>EDGE SERIES SHORT BODY TAP high quality faucet.</v>
+        <v>EDGE SERIES LONG BODY TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1261">
@@ -44520,7 +44520,7 @@
         <v>FG-401551</v>
       </c>
       <c r="C1261" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2 inch)</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2)</v>
       </c>
       <c r="D1261" t="str">
         <v>EDGE SERIES LONG BODY TAP</v>
@@ -44532,7 +44532,7 @@
         <v>General</v>
       </c>
       <c r="G1261" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1261" t="str">
         <v>NOS</v>
@@ -44555,7 +44555,7 @@
         <v>FG-401551</v>
       </c>
       <c r="C1262" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2)</v>
+        <v>EDGE SERIES LONG BODY TAP (1/2")</v>
       </c>
       <c r="D1262" t="str">
         <v>EDGE SERIES LONG BODY TAP</v>
@@ -44567,7 +44567,7 @@
         <v>General</v>
       </c>
       <c r="G1262" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1262" t="str">
         <v>NOS</v>
@@ -44587,13 +44587,13 @@
         <v>1262</v>
       </c>
       <c r="B1263" t="str">
-        <v>FG-401551</v>
+        <v>FG-401549</v>
       </c>
       <c r="C1263" t="str">
-        <v>EDGE SERIES LONG BODY TAP (1/2")</v>
+        <v>EDGE SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1263" t="str">
-        <v>EDGE SERIES LONG BODY TAP</v>
+        <v>EDGE SERIES SWAN NECK</v>
       </c>
       <c r="E1263" t="str">
         <v>FAUCETS</v>
@@ -44602,19 +44602,19 @@
         <v>General</v>
       </c>
       <c r="G1263" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1263" t="str">
         <v>NOS</v>
       </c>
       <c r="I1263">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J1263" t="str">
         <v>Active</v>
       </c>
       <c r="K1263" t="str">
-        <v>EDGE SERIES LONG BODY TAP high quality faucet.</v>
+        <v>EDGE SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1264">
@@ -44625,7 +44625,7 @@
         <v>FG-401549</v>
       </c>
       <c r="C1264" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2 inch)</v>
+        <v>EDGE SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1264" t="str">
         <v>EDGE SERIES SWAN NECK</v>
@@ -44637,7 +44637,7 @@
         <v>General</v>
       </c>
       <c r="G1264" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1264" t="str">
         <v>NOS</v>
@@ -44660,7 +44660,7 @@
         <v>FG-401549</v>
       </c>
       <c r="C1265" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2)</v>
+        <v>EDGE SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1265" t="str">
         <v>EDGE SERIES SWAN NECK</v>
@@ -44672,7 +44672,7 @@
         <v>General</v>
       </c>
       <c r="G1265" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1265" t="str">
         <v>NOS</v>
@@ -44692,13 +44692,13 @@
         <v>1265</v>
       </c>
       <c r="B1266" t="str">
-        <v>FG-401549</v>
+        <v>FG-401546</v>
       </c>
       <c r="C1266" t="str">
-        <v>EDGE SERIES SWAN NECK (1/2")</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1266" t="str">
-        <v>EDGE SERIES SWAN NECK</v>
+        <v>EDGE SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1266" t="str">
         <v>FAUCETS</v>
@@ -44707,19 +44707,19 @@
         <v>General</v>
       </c>
       <c r="G1266" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1266" t="str">
         <v>NOS</v>
       </c>
       <c r="I1266">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="J1266" t="str">
         <v>Active</v>
       </c>
       <c r="K1266" t="str">
-        <v>EDGE SERIES SWAN NECK high quality faucet.</v>
+        <v>EDGE SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1267">
@@ -44730,7 +44730,7 @@
         <v>FG-401546</v>
       </c>
       <c r="C1267" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1267" t="str">
         <v>EDGE SERIES ANGULAR VALVE</v>
@@ -44742,7 +44742,7 @@
         <v>General</v>
       </c>
       <c r="G1267" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1267" t="str">
         <v>NOS</v>
@@ -44765,7 +44765,7 @@
         <v>FG-401546</v>
       </c>
       <c r="C1268" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2)</v>
+        <v>EDGE SERIES ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1268" t="str">
         <v>EDGE SERIES ANGULAR VALVE</v>
@@ -44777,7 +44777,7 @@
         <v>General</v>
       </c>
       <c r="G1268" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1268" t="str">
         <v>NOS</v>
@@ -44797,13 +44797,13 @@
         <v>1268</v>
       </c>
       <c r="B1269" t="str">
-        <v>FG-401546</v>
+        <v>FG-401547</v>
       </c>
       <c r="C1269" t="str">
-        <v>EDGE SERIES ANGULAR VALVE (1/2")</v>
+        <v>EDGE SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1269" t="str">
-        <v>EDGE SERIES ANGULAR VALVE</v>
+        <v>EDGE SERIES PILLAR TAP</v>
       </c>
       <c r="E1269" t="str">
         <v>FAUCETS</v>
@@ -44812,19 +44812,19 @@
         <v>General</v>
       </c>
       <c r="G1269" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1269" t="str">
         <v>NOS</v>
       </c>
       <c r="I1269">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J1269" t="str">
         <v>Active</v>
       </c>
       <c r="K1269" t="str">
-        <v>EDGE SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>EDGE SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1270">
@@ -44835,7 +44835,7 @@
         <v>FG-401547</v>
       </c>
       <c r="C1270" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2 inch)</v>
+        <v>EDGE SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1270" t="str">
         <v>EDGE SERIES PILLAR TAP</v>
@@ -44847,7 +44847,7 @@
         <v>General</v>
       </c>
       <c r="G1270" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1270" t="str">
         <v>NOS</v>
@@ -44870,7 +44870,7 @@
         <v>FG-401547</v>
       </c>
       <c r="C1271" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2)</v>
+        <v>EDGE SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1271" t="str">
         <v>EDGE SERIES PILLAR TAP</v>
@@ -44882,7 +44882,7 @@
         <v>General</v>
       </c>
       <c r="G1271" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1271" t="str">
         <v>NOS</v>
@@ -44902,13 +44902,13 @@
         <v>1271</v>
       </c>
       <c r="B1272" t="str">
-        <v>FG-401547</v>
+        <v>FG-401550</v>
       </c>
       <c r="C1272" t="str">
-        <v>EDGE SERIES PILLAR TAP (1/2")</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2 inch)</v>
       </c>
       <c r="D1272" t="str">
-        <v>EDGE SERIES PILLAR TAP</v>
+        <v>EDGE SERIES 2 WAY BIB TAB</v>
       </c>
       <c r="E1272" t="str">
         <v>FAUCETS</v>
@@ -44917,19 +44917,19 @@
         <v>General</v>
       </c>
       <c r="G1272" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1272" t="str">
         <v>NOS</v>
       </c>
       <c r="I1272">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J1272" t="str">
         <v>Active</v>
       </c>
       <c r="K1272" t="str">
-        <v>EDGE SERIES PILLAR TAP high quality faucet.</v>
+        <v>EDGE SERIES 2 WAY BIB TAB high quality faucet.</v>
       </c>
     </row>
     <row r="1273">
@@ -44940,7 +44940,7 @@
         <v>FG-401550</v>
       </c>
       <c r="C1273" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2 inch)</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2)</v>
       </c>
       <c r="D1273" t="str">
         <v>EDGE SERIES 2 WAY BIB TAB</v>
@@ -44952,7 +44952,7 @@
         <v>General</v>
       </c>
       <c r="G1273" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1273" t="str">
         <v>NOS</v>
@@ -44975,7 +44975,7 @@
         <v>FG-401550</v>
       </c>
       <c r="C1274" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2)</v>
+        <v>EDGE SERIES 2 WAY BIB TAB (1/2")</v>
       </c>
       <c r="D1274" t="str">
         <v>EDGE SERIES 2 WAY BIB TAB</v>
@@ -44987,7 +44987,7 @@
         <v>General</v>
       </c>
       <c r="G1274" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1274" t="str">
         <v>NOS</v>
@@ -45007,13 +45007,13 @@
         <v>1274</v>
       </c>
       <c r="B1275" t="str">
-        <v>FG-401550</v>
+        <v>FG-401548</v>
       </c>
       <c r="C1275" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB (1/2")</v>
+        <v>EDGE SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1275" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB</v>
+        <v>EDGE SERIES SINK TAP</v>
       </c>
       <c r="E1275" t="str">
         <v>FAUCETS</v>
@@ -45022,19 +45022,19 @@
         <v>General</v>
       </c>
       <c r="G1275" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1275" t="str">
         <v>NOS</v>
       </c>
       <c r="I1275">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1275" t="str">
         <v>Active</v>
       </c>
       <c r="K1275" t="str">
-        <v>EDGE SERIES 2 WAY BIB TAB high quality faucet.</v>
+        <v>EDGE SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1276">
@@ -45045,7 +45045,7 @@
         <v>FG-401548</v>
       </c>
       <c r="C1276" t="str">
-        <v>EDGE SERIES SINK TAP (1/2 inch)</v>
+        <v>EDGE SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1276" t="str">
         <v>EDGE SERIES SINK TAP</v>
@@ -45057,7 +45057,7 @@
         <v>General</v>
       </c>
       <c r="G1276" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1276" t="str">
         <v>NOS</v>
@@ -45080,7 +45080,7 @@
         <v>FG-401548</v>
       </c>
       <c r="C1277" t="str">
-        <v>EDGE SERIES SINK TAP (1/2)</v>
+        <v>EDGE SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1277" t="str">
         <v>EDGE SERIES SINK TAP</v>
@@ -45092,7 +45092,7 @@
         <v>General</v>
       </c>
       <c r="G1277" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1277" t="str">
         <v>NOS</v>
@@ -45112,13 +45112,13 @@
         <v>1277</v>
       </c>
       <c r="B1278" t="str">
-        <v>FG-401548</v>
+        <v>FG-401568</v>
       </c>
       <c r="C1278" t="str">
-        <v>EDGE SERIES SINK TAP (1/2")</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1278" t="str">
-        <v>EDGE SERIES SINK TAP</v>
+        <v>SMART SERIES SHORT BODY BIB TAP</v>
       </c>
       <c r="E1278" t="str">
         <v>FAUCETS</v>
@@ -45127,19 +45127,19 @@
         <v>General</v>
       </c>
       <c r="G1278" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1278" t="str">
         <v>NOS</v>
       </c>
       <c r="I1278">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="J1278" t="str">
         <v>Active</v>
       </c>
       <c r="K1278" t="str">
-        <v>EDGE SERIES SINK TAP high quality faucet.</v>
+        <v>SMART SERIES SHORT BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1279">
@@ -45150,7 +45150,7 @@
         <v>FG-401568</v>
       </c>
       <c r="C1279" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1279" t="str">
         <v>SMART SERIES SHORT BODY BIB TAP</v>
@@ -45162,7 +45162,7 @@
         <v>General</v>
       </c>
       <c r="G1279" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1279" t="str">
         <v>NOS</v>
@@ -45185,7 +45185,7 @@
         <v>FG-401568</v>
       </c>
       <c r="C1280" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2)</v>
+        <v>SMART SERIES SHORT BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1280" t="str">
         <v>SMART SERIES SHORT BODY BIB TAP</v>
@@ -45197,7 +45197,7 @@
         <v>General</v>
       </c>
       <c r="G1280" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1280" t="str">
         <v>NOS</v>
@@ -45217,13 +45217,13 @@
         <v>1280</v>
       </c>
       <c r="B1281" t="str">
-        <v>FG-401568</v>
+        <v>FG-401567</v>
       </c>
       <c r="C1281" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP (1/2")</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1281" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP</v>
+        <v>SMART SERIES LONG BODY BIB TAP</v>
       </c>
       <c r="E1281" t="str">
         <v>FAUCETS</v>
@@ -45232,7 +45232,7 @@
         <v>General</v>
       </c>
       <c r="G1281" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1281" t="str">
         <v>NOS</v>
@@ -45244,7 +45244,7 @@
         <v>Active</v>
       </c>
       <c r="K1281" t="str">
-        <v>SMART SERIES SHORT BODY BIB TAP high quality faucet.</v>
+        <v>SMART SERIES LONG BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1282">
@@ -45255,7 +45255,7 @@
         <v>FG-401567</v>
       </c>
       <c r="C1282" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1282" t="str">
         <v>SMART SERIES LONG BODY BIB TAP</v>
@@ -45267,7 +45267,7 @@
         <v>General</v>
       </c>
       <c r="G1282" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1282" t="str">
         <v>NOS</v>
@@ -45290,7 +45290,7 @@
         <v>FG-401567</v>
       </c>
       <c r="C1283" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2)</v>
+        <v>SMART SERIES LONG BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1283" t="str">
         <v>SMART SERIES LONG BODY BIB TAP</v>
@@ -45302,7 +45302,7 @@
         <v>General</v>
       </c>
       <c r="G1283" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1283" t="str">
         <v>NOS</v>
@@ -45322,13 +45322,13 @@
         <v>1283</v>
       </c>
       <c r="B1284" t="str">
-        <v>FG-401567</v>
+        <v>FG-401562</v>
       </c>
       <c r="C1284" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP (1/2")</v>
+        <v>SMART SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1284" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP</v>
+        <v>SMART SERIES PILLAR TAP</v>
       </c>
       <c r="E1284" t="str">
         <v>FAUCETS</v>
@@ -45337,19 +45337,19 @@
         <v>General</v>
       </c>
       <c r="G1284" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1284" t="str">
         <v>NOS</v>
       </c>
       <c r="I1284">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1284" t="str">
         <v>Active</v>
       </c>
       <c r="K1284" t="str">
-        <v>SMART SERIES LONG BODY BIB TAP high quality faucet.</v>
+        <v>SMART SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1285">
@@ -45360,7 +45360,7 @@
         <v>FG-401562</v>
       </c>
       <c r="C1285" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2 inch)</v>
+        <v>SMART SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1285" t="str">
         <v>SMART SERIES PILLAR TAP</v>
@@ -45372,7 +45372,7 @@
         <v>General</v>
       </c>
       <c r="G1285" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1285" t="str">
         <v>NOS</v>
@@ -45395,7 +45395,7 @@
         <v>FG-401562</v>
       </c>
       <c r="C1286" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2)</v>
+        <v>SMART SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1286" t="str">
         <v>SMART SERIES PILLAR TAP</v>
@@ -45407,7 +45407,7 @@
         <v>General</v>
       </c>
       <c r="G1286" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1286" t="str">
         <v>NOS</v>
@@ -45427,13 +45427,13 @@
         <v>1286</v>
       </c>
       <c r="B1287" t="str">
-        <v>FG-401562</v>
+        <v>FG-401563</v>
       </c>
       <c r="C1287" t="str">
-        <v>SMART SERIES PILLAR TAP (1/2")</v>
+        <v>SMART SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1287" t="str">
-        <v>SMART SERIES PILLAR TAP</v>
+        <v>SMART SERIES SINK TAP</v>
       </c>
       <c r="E1287" t="str">
         <v>FAUCETS</v>
@@ -45442,7 +45442,7 @@
         <v>General</v>
       </c>
       <c r="G1287" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1287" t="str">
         <v>NOS</v>
@@ -45454,7 +45454,7 @@
         <v>Active</v>
       </c>
       <c r="K1287" t="str">
-        <v>SMART SERIES PILLAR TAP high quality faucet.</v>
+        <v>SMART SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1288">
@@ -45465,7 +45465,7 @@
         <v>FG-401563</v>
       </c>
       <c r="C1288" t="str">
-        <v>SMART SERIES SINK TAP (1/2 inch)</v>
+        <v>SMART SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1288" t="str">
         <v>SMART SERIES SINK TAP</v>
@@ -45477,7 +45477,7 @@
         <v>General</v>
       </c>
       <c r="G1288" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1288" t="str">
         <v>NOS</v>
@@ -45500,7 +45500,7 @@
         <v>FG-401563</v>
       </c>
       <c r="C1289" t="str">
-        <v>SMART SERIES SINK TAP (1/2)</v>
+        <v>SMART SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1289" t="str">
         <v>SMART SERIES SINK TAP</v>
@@ -45512,7 +45512,7 @@
         <v>General</v>
       </c>
       <c r="G1289" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1289" t="str">
         <v>NOS</v>
@@ -45532,13 +45532,13 @@
         <v>1289</v>
       </c>
       <c r="B1290" t="str">
-        <v>FG-401563</v>
+        <v>FG-401564</v>
       </c>
       <c r="C1290" t="str">
-        <v>SMART SERIES SINK TAP (1/2")</v>
+        <v>SMART SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1290" t="str">
-        <v>SMART SERIES SINK TAP</v>
+        <v>SMART SERIES SWAN NECK</v>
       </c>
       <c r="E1290" t="str">
         <v>FAUCETS</v>
@@ -45547,7 +45547,7 @@
         <v>General</v>
       </c>
       <c r="G1290" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1290" t="str">
         <v>NOS</v>
@@ -45559,7 +45559,7 @@
         <v>Active</v>
       </c>
       <c r="K1290" t="str">
-        <v>SMART SERIES SINK TAP high quality faucet.</v>
+        <v>SMART SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1291">
@@ -45570,7 +45570,7 @@
         <v>FG-401564</v>
       </c>
       <c r="C1291" t="str">
-        <v>SMART SERIES SWAN NECK (1/2 inch)</v>
+        <v>SMART SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1291" t="str">
         <v>SMART SERIES SWAN NECK</v>
@@ -45582,7 +45582,7 @@
         <v>General</v>
       </c>
       <c r="G1291" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1291" t="str">
         <v>NOS</v>
@@ -45605,7 +45605,7 @@
         <v>FG-401564</v>
       </c>
       <c r="C1292" t="str">
-        <v>SMART SERIES SWAN NECK (1/2)</v>
+        <v>SMART SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1292" t="str">
         <v>SMART SERIES SWAN NECK</v>
@@ -45617,7 +45617,7 @@
         <v>General</v>
       </c>
       <c r="G1292" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1292" t="str">
         <v>NOS</v>
@@ -45637,13 +45637,13 @@
         <v>1292</v>
       </c>
       <c r="B1293" t="str">
-        <v>FG-401564</v>
+        <v>FG-401561</v>
       </c>
       <c r="C1293" t="str">
-        <v>SMART SERIES SWAN NECK (1/2")</v>
+        <v>SMART SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1293" t="str">
-        <v>SMART SERIES SWAN NECK</v>
+        <v>SMART SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1293" t="str">
         <v>FAUCETS</v>
@@ -45652,19 +45652,19 @@
         <v>General</v>
       </c>
       <c r="G1293" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1293" t="str">
         <v>NOS</v>
       </c>
       <c r="I1293">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1293" t="str">
         <v>Active</v>
       </c>
       <c r="K1293" t="str">
-        <v>SMART SERIES SWAN NECK high quality faucet.</v>
+        <v>SMART SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1294">
@@ -45672,13 +45672,13 @@
         <v>1293</v>
       </c>
       <c r="B1294" t="str">
-        <v>FG-401561</v>
+        <v>FG-401566</v>
       </c>
       <c r="C1294" t="str">
-        <v>SMART SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1294" t="str">
-        <v>SMART SERIES ANGULAR VALVE</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
       </c>
       <c r="E1294" t="str">
         <v>FAUCETS</v>
@@ -45693,13 +45693,13 @@
         <v>NOS</v>
       </c>
       <c r="I1294">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1294" t="str">
         <v>Active</v>
       </c>
       <c r="K1294" t="str">
-        <v>SMART SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1295">
@@ -45710,7 +45710,7 @@
         <v>FG-401566</v>
       </c>
       <c r="C1295" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1295" t="str">
         <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
@@ -45722,7 +45722,7 @@
         <v>General</v>
       </c>
       <c r="G1295" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1295" t="str">
         <v>NOS</v>
@@ -45745,7 +45745,7 @@
         <v>FG-401566</v>
       </c>
       <c r="C1296" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2)</v>
+        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1296" t="str">
         <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
@@ -45757,7 +45757,7 @@
         <v>General</v>
       </c>
       <c r="G1296" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1296" t="str">
         <v>NOS</v>
@@ -45777,13 +45777,13 @@
         <v>1296</v>
       </c>
       <c r="B1297" t="str">
-        <v>FG-401566</v>
+        <v>FG-401565</v>
       </c>
       <c r="C1297" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE (1/2")</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1297" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE</v>
+        <v>SMART SERIES 2 WAY BIB TAP</v>
       </c>
       <c r="E1297" t="str">
         <v>FAUCETS</v>
@@ -45792,7 +45792,7 @@
         <v>General</v>
       </c>
       <c r="G1297" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1297" t="str">
         <v>NOS</v>
@@ -45804,7 +45804,7 @@
         <v>Active</v>
       </c>
       <c r="K1297" t="str">
-        <v>SMART SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
+        <v>SMART SERIES 2 WAY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1298">
@@ -45815,7 +45815,7 @@
         <v>FG-401565</v>
       </c>
       <c r="C1298" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2 inch)</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2)</v>
       </c>
       <c r="D1298" t="str">
         <v>SMART SERIES 2 WAY BIB TAP</v>
@@ -45827,7 +45827,7 @@
         <v>General</v>
       </c>
       <c r="G1298" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1298" t="str">
         <v>NOS</v>
@@ -45850,7 +45850,7 @@
         <v>FG-401565</v>
       </c>
       <c r="C1299" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2)</v>
+        <v>SMART SERIES 2 WAY BIB TAP (1/2")</v>
       </c>
       <c r="D1299" t="str">
         <v>SMART SERIES 2 WAY BIB TAP</v>
@@ -45862,7 +45862,7 @@
         <v>General</v>
       </c>
       <c r="G1299" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1299" t="str">
         <v>NOS</v>
@@ -45882,13 +45882,13 @@
         <v>1299</v>
       </c>
       <c r="B1300" t="str">
-        <v>FG-401565</v>
+        <v>FG-401560</v>
       </c>
       <c r="C1300" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1300" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP</v>
       </c>
       <c r="E1300" t="str">
         <v>FAUCETS</v>
@@ -45897,19 +45897,19 @@
         <v>General</v>
       </c>
       <c r="G1300" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1300" t="str">
         <v>NOS</v>
       </c>
       <c r="I1300">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1300" t="str">
         <v>Active</v>
       </c>
       <c r="K1300" t="str">
-        <v>SMART SERIES 2 WAY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1301">
@@ -45920,7 +45920,7 @@
         <v>FG-401560</v>
       </c>
       <c r="C1301" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1301" t="str">
         <v>REGULAR SERIES SHORT BODY BIB TAP</v>
@@ -45932,7 +45932,7 @@
         <v>General</v>
       </c>
       <c r="G1301" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1301" t="str">
         <v>NOS</v>
@@ -45955,7 +45955,7 @@
         <v>FG-401560</v>
       </c>
       <c r="C1302" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1302" t="str">
         <v>REGULAR SERIES SHORT BODY BIB TAP</v>
@@ -45967,7 +45967,7 @@
         <v>General</v>
       </c>
       <c r="G1302" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1302" t="str">
         <v>NOS</v>
@@ -45987,13 +45987,13 @@
         <v>1302</v>
       </c>
       <c r="B1303" t="str">
-        <v>FG-401560</v>
+        <v>FG-401559</v>
       </c>
       <c r="C1303" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1303" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP</v>
       </c>
       <c r="E1303" t="str">
         <v>FAUCETS</v>
@@ -46002,7 +46002,7 @@
         <v>General</v>
       </c>
       <c r="G1303" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1303" t="str">
         <v>NOS</v>
@@ -46014,7 +46014,7 @@
         <v>Active</v>
       </c>
       <c r="K1303" t="str">
-        <v>REGULAR SERIES SHORT BODY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1304">
@@ -46025,7 +46025,7 @@
         <v>FG-401559</v>
       </c>
       <c r="C1304" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2)</v>
       </c>
       <c r="D1304" t="str">
         <v>REGULAR SERIES LONG BODY BIB TAP</v>
@@ -46037,7 +46037,7 @@
         <v>General</v>
       </c>
       <c r="G1304" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1304" t="str">
         <v>NOS</v>
@@ -46060,7 +46060,7 @@
         <v>FG-401559</v>
       </c>
       <c r="C1305" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES LONG BODY BIB TAP (1/2")</v>
       </c>
       <c r="D1305" t="str">
         <v>REGULAR SERIES LONG BODY BIB TAP</v>
@@ -46072,7 +46072,7 @@
         <v>General</v>
       </c>
       <c r="G1305" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1305" t="str">
         <v>NOS</v>
@@ -46092,13 +46092,13 @@
         <v>1305</v>
       </c>
       <c r="B1306" t="str">
-        <v>FG-401559</v>
+        <v>FG-401554</v>
       </c>
       <c r="C1306" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP (1/2")</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2 inch)</v>
       </c>
       <c r="D1306" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP</v>
+        <v>REGULAR SERIES PILLAR TAP</v>
       </c>
       <c r="E1306" t="str">
         <v>FAUCETS</v>
@@ -46107,19 +46107,19 @@
         <v>General</v>
       </c>
       <c r="G1306" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1306" t="str">
         <v>NOS</v>
       </c>
       <c r="I1306">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1306" t="str">
         <v>Active</v>
       </c>
       <c r="K1306" t="str">
-        <v>REGULAR SERIES LONG BODY BIB TAP high quality faucet.</v>
+        <v>REGULAR SERIES PILLAR TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1307">
@@ -46130,7 +46130,7 @@
         <v>FG-401554</v>
       </c>
       <c r="C1307" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2 inch)</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2)</v>
       </c>
       <c r="D1307" t="str">
         <v>REGULAR SERIES PILLAR TAP</v>
@@ -46142,7 +46142,7 @@
         <v>General</v>
       </c>
       <c r="G1307" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1307" t="str">
         <v>NOS</v>
@@ -46165,7 +46165,7 @@
         <v>FG-401554</v>
       </c>
       <c r="C1308" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2)</v>
+        <v>REGULAR SERIES PILLAR TAP (1/2")</v>
       </c>
       <c r="D1308" t="str">
         <v>REGULAR SERIES PILLAR TAP</v>
@@ -46177,7 +46177,7 @@
         <v>General</v>
       </c>
       <c r="G1308" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1308" t="str">
         <v>NOS</v>
@@ -46197,13 +46197,13 @@
         <v>1308</v>
       </c>
       <c r="B1309" t="str">
-        <v>FG-401554</v>
+        <v>FG-401555</v>
       </c>
       <c r="C1309" t="str">
-        <v>REGULAR SERIES PILLAR TAP (1/2")</v>
+        <v>REGULAR SERIES SINK TAP (1/2 inch)</v>
       </c>
       <c r="D1309" t="str">
-        <v>REGULAR SERIES PILLAR TAP</v>
+        <v>REGULAR SERIES SINK TAP</v>
       </c>
       <c r="E1309" t="str">
         <v>FAUCETS</v>
@@ -46212,7 +46212,7 @@
         <v>General</v>
       </c>
       <c r="G1309" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1309" t="str">
         <v>NOS</v>
@@ -46224,7 +46224,7 @@
         <v>Active</v>
       </c>
       <c r="K1309" t="str">
-        <v>REGULAR SERIES PILLAR TAP high quality faucet.</v>
+        <v>REGULAR SERIES SINK TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1310">
@@ -46235,7 +46235,7 @@
         <v>FG-401555</v>
       </c>
       <c r="C1310" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2 inch)</v>
+        <v>REGULAR SERIES SINK TAP (1/2)</v>
       </c>
       <c r="D1310" t="str">
         <v>REGULAR SERIES SINK TAP</v>
@@ -46247,7 +46247,7 @@
         <v>General</v>
       </c>
       <c r="G1310" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1310" t="str">
         <v>NOS</v>
@@ -46270,7 +46270,7 @@
         <v>FG-401555</v>
       </c>
       <c r="C1311" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2)</v>
+        <v>REGULAR SERIES SINK TAP (1/2")</v>
       </c>
       <c r="D1311" t="str">
         <v>REGULAR SERIES SINK TAP</v>
@@ -46282,7 +46282,7 @@
         <v>General</v>
       </c>
       <c r="G1311" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1311" t="str">
         <v>NOS</v>
@@ -46302,13 +46302,13 @@
         <v>1311</v>
       </c>
       <c r="B1312" t="str">
-        <v>FG-401555</v>
+        <v>FG-401556</v>
       </c>
       <c r="C1312" t="str">
-        <v>REGULAR SERIES SINK TAP (1/2")</v>
+        <v>REGULAR SERIES SWAN NECK (1/2 inch)</v>
       </c>
       <c r="D1312" t="str">
-        <v>REGULAR SERIES SINK TAP</v>
+        <v>REGULAR SERIES SWAN NECK</v>
       </c>
       <c r="E1312" t="str">
         <v>FAUCETS</v>
@@ -46317,7 +46317,7 @@
         <v>General</v>
       </c>
       <c r="G1312" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1312" t="str">
         <v>NOS</v>
@@ -46329,7 +46329,7 @@
         <v>Active</v>
       </c>
       <c r="K1312" t="str">
-        <v>REGULAR SERIES SINK TAP high quality faucet.</v>
+        <v>REGULAR SERIES SWAN NECK high quality faucet.</v>
       </c>
     </row>
     <row r="1313">
@@ -46340,7 +46340,7 @@
         <v>FG-401556</v>
       </c>
       <c r="C1313" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2 inch)</v>
+        <v>REGULAR SERIES SWAN NECK (1/2)</v>
       </c>
       <c r="D1313" t="str">
         <v>REGULAR SERIES SWAN NECK</v>
@@ -46352,7 +46352,7 @@
         <v>General</v>
       </c>
       <c r="G1313" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1313" t="str">
         <v>NOS</v>
@@ -46375,7 +46375,7 @@
         <v>FG-401556</v>
       </c>
       <c r="C1314" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2)</v>
+        <v>REGULAR SERIES SWAN NECK (1/2")</v>
       </c>
       <c r="D1314" t="str">
         <v>REGULAR SERIES SWAN NECK</v>
@@ -46387,7 +46387,7 @@
         <v>General</v>
       </c>
       <c r="G1314" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1314" t="str">
         <v>NOS</v>
@@ -46407,13 +46407,13 @@
         <v>1314</v>
       </c>
       <c r="B1315" t="str">
-        <v>FG-401556</v>
+        <v>FG-401553</v>
       </c>
       <c r="C1315" t="str">
-        <v>REGULAR SERIES SWAN NECK (1/2")</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1315" t="str">
-        <v>REGULAR SERIES SWAN NECK</v>
+        <v>REGULAR SERIES ANGULAR VALVE</v>
       </c>
       <c r="E1315" t="str">
         <v>FAUCETS</v>
@@ -46422,19 +46422,19 @@
         <v>General</v>
       </c>
       <c r="G1315" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1315" t="str">
         <v>NOS</v>
       </c>
       <c r="I1315">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J1315" t="str">
         <v>Active</v>
       </c>
       <c r="K1315" t="str">
-        <v>REGULAR SERIES SWAN NECK high quality faucet.</v>
+        <v>REGULAR SERIES ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1316">
@@ -46445,7 +46445,7 @@
         <v>FG-401553</v>
       </c>
       <c r="C1316" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2 inch)</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1316" t="str">
         <v>REGULAR SERIES ANGULAR VALVE</v>
@@ -46457,7 +46457,7 @@
         <v>General</v>
       </c>
       <c r="G1316" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1316" t="str">
         <v>NOS</v>
@@ -46480,7 +46480,7 @@
         <v>FG-401553</v>
       </c>
       <c r="C1317" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2)</v>
+        <v>REGULAR SERIES ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1317" t="str">
         <v>REGULAR SERIES ANGULAR VALVE</v>
@@ -46492,7 +46492,7 @@
         <v>General</v>
       </c>
       <c r="G1317" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1317" t="str">
         <v>NOS</v>
@@ -46512,13 +46512,13 @@
         <v>1317</v>
       </c>
       <c r="B1318" t="str">
-        <v>FG-401553</v>
+        <v>FG-401558</v>
       </c>
       <c r="C1318" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE (1/2")</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
       </c>
       <c r="D1318" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
       </c>
       <c r="E1318" t="str">
         <v>FAUCETS</v>
@@ -46527,19 +46527,19 @@
         <v>General</v>
       </c>
       <c r="G1318" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1318" t="str">
         <v>NOS</v>
       </c>
       <c r="I1318">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J1318" t="str">
         <v>Active</v>
       </c>
       <c r="K1318" t="str">
-        <v>REGULAR SERIES ANGULAR VALVE high quality faucet.</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
       </c>
     </row>
     <row r="1319">
@@ -46550,7 +46550,7 @@
         <v>FG-401558</v>
       </c>
       <c r="C1319" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2 inch)</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2)</v>
       </c>
       <c r="D1319" t="str">
         <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
@@ -46562,7 +46562,7 @@
         <v>General</v>
       </c>
       <c r="G1319" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1319" t="str">
         <v>NOS</v>
@@ -46585,7 +46585,7 @@
         <v>FG-401558</v>
       </c>
       <c r="C1320" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2)</v>
+        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2")</v>
       </c>
       <c r="D1320" t="str">
         <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
@@ -46597,7 +46597,7 @@
         <v>General</v>
       </c>
       <c r="G1320" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1320" t="str">
         <v>NOS</v>
@@ -46617,13 +46617,13 @@
         <v>1320</v>
       </c>
       <c r="B1321" t="str">
-        <v>FG-401558</v>
+        <v>FG-401557</v>
       </c>
       <c r="C1321" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE (1/2")</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2 inch)</v>
       </c>
       <c r="D1321" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP</v>
       </c>
       <c r="E1321" t="str">
         <v>FAUCETS</v>
@@ -46632,7 +46632,7 @@
         <v>General</v>
       </c>
       <c r="G1321" t="str">
-        <v>1/2"</v>
+        <v>1/2 inch</v>
       </c>
       <c r="H1321" t="str">
         <v>NOS</v>
@@ -46644,7 +46644,7 @@
         <v>Active</v>
       </c>
       <c r="K1321" t="str">
-        <v>REGULAR SERIES 2 WAY ANGULAR VALVE high quality faucet.</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP high quality faucet.</v>
       </c>
     </row>
     <row r="1322">
@@ -46655,7 +46655,7 @@
         <v>FG-401557</v>
       </c>
       <c r="C1322" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2 inch)</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2)</v>
       </c>
       <c r="D1322" t="str">
         <v>REGULAR SERIES 2 WAY BIB TAP</v>
@@ -46667,7 +46667,7 @@
         <v>General</v>
       </c>
       <c r="G1322" t="str">
-        <v>1/2 inch</v>
+        <v>1/2</v>
       </c>
       <c r="H1322" t="str">
         <v>NOS</v>
@@ -46690,7 +46690,7 @@
         <v>FG-401557</v>
       </c>
       <c r="C1323" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2)</v>
+        <v>REGULAR SERIES 2 WAY BIB TAP (1/2")</v>
       </c>
       <c r="D1323" t="str">
         <v>REGULAR SERIES 2 WAY BIB TAP</v>
@@ -46702,7 +46702,7 @@
         <v>General</v>
       </c>
       <c r="G1323" t="str">
-        <v>1/2</v>
+        <v>1/2"</v>
       </c>
       <c r="H1323" t="str">
         <v>NOS</v>
@@ -46722,34 +46722,34 @@
         <v>1323</v>
       </c>
       <c r="B1324" t="str">
-        <v>FG-401557</v>
+        <v>FG-400836</v>
       </c>
       <c r="C1324" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP (1/2")</v>
+        <v>SINGLE SIDE HANDLE FLUSH 8L (8L)</v>
       </c>
       <c r="D1324" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP</v>
+        <v>SINGLE SIDE HANDLE FLUSH 8L</v>
       </c>
       <c r="E1324" t="str">
-        <v>FAUCETS</v>
+        <v>Toilet Seat Cover &amp; Flushing Cistern</v>
       </c>
       <c r="F1324" t="str">
         <v>General</v>
       </c>
       <c r="G1324" t="str">
-        <v>1/2"</v>
+        <v>8L</v>
       </c>
       <c r="H1324" t="str">
         <v>NOS</v>
       </c>
       <c r="I1324">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J1324" t="str">
         <v>Active</v>
       </c>
       <c r="K1324" t="str">
-        <v>REGULAR SERIES 2 WAY BIB TAP high quality faucet.</v>
+        <v>8 Litre Single Side Handle Flushing Cistern.</v>
       </c>
     </row>
     <row r="1325">
@@ -46757,13 +46757,13 @@
         <v>1324</v>
       </c>
       <c r="B1325" t="str">
-        <v>FG-400836</v>
+        <v>FG-400837</v>
       </c>
       <c r="C1325" t="str">
-        <v>SINGLE SIDE HANDLE FLUSH 8L (8L)</v>
+        <v>CENTER SINGLE PUSH FLUSH 8L (8L)</v>
       </c>
       <c r="D1325" t="str">
-        <v>SINGLE SIDE HANDLE FLUSH 8L</v>
+        <v>CENTER SINGLE PUSH FLUSH 8L</v>
       </c>
       <c r="E1325" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46784,7 +46784,7 @@
         <v>Active</v>
       </c>
       <c r="K1325" t="str">
-        <v>8 Litre Single Side Handle Flushing Cistern.</v>
+        <v>8 Litre Center Single Push Flushing Cistern.</v>
       </c>
     </row>
     <row r="1326">
@@ -46792,13 +46792,13 @@
         <v>1325</v>
       </c>
       <c r="B1326" t="str">
-        <v>FG-400837</v>
+        <v>FG-400838</v>
       </c>
       <c r="C1326" t="str">
-        <v>CENTER SINGLE PUSH FLUSH 8L (8L)</v>
+        <v>DUAL FLUSH 10L (10L)</v>
       </c>
       <c r="D1326" t="str">
-        <v>CENTER SINGLE PUSH FLUSH 8L</v>
+        <v>DUAL FLUSH 10L</v>
       </c>
       <c r="E1326" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46807,7 +46807,7 @@
         <v>General</v>
       </c>
       <c r="G1326" t="str">
-        <v>8L</v>
+        <v>10L</v>
       </c>
       <c r="H1326" t="str">
         <v>NOS</v>
@@ -46819,7 +46819,7 @@
         <v>Active</v>
       </c>
       <c r="K1326" t="str">
-        <v>8 Litre Center Single Push Flushing Cistern.</v>
+        <v>10 Litre Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1327">
@@ -46827,13 +46827,13 @@
         <v>1326</v>
       </c>
       <c r="B1327" t="str">
-        <v>FG-400838</v>
+        <v>FG-400835</v>
       </c>
       <c r="C1327" t="str">
-        <v>DUAL FLUSH 10L (10L)</v>
+        <v>EWC SEAT COVER (WITH JET) (Standard)</v>
       </c>
       <c r="D1327" t="str">
-        <v>DUAL FLUSH 10L</v>
+        <v>EWC SEAT COVER (WITH JET)</v>
       </c>
       <c r="E1327" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46842,19 +46842,19 @@
         <v>General</v>
       </c>
       <c r="G1327" t="str">
-        <v>10L</v>
+        <v>Standard</v>
       </c>
       <c r="H1327" t="str">
         <v>NOS</v>
       </c>
       <c r="I1327">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J1327" t="str">
         <v>Active</v>
       </c>
       <c r="K1327" t="str">
-        <v>10 Litre Dual Flush Cistern.</v>
+        <v>EWC Toilet Seat Cover with integrated jet spray.</v>
       </c>
     </row>
     <row r="1328">
@@ -46862,13 +46862,13 @@
         <v>1327</v>
       </c>
       <c r="B1328" t="str">
-        <v>FG-400835</v>
+        <v>FG-400840</v>
       </c>
       <c r="C1328" t="str">
-        <v>EWC SEAT COVER (WITH JET) (Standard)</v>
+        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L) (10L)</v>
       </c>
       <c r="D1328" t="str">
-        <v>EWC SEAT COVER (WITH JET)</v>
+        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L)</v>
       </c>
       <c r="E1328" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46877,19 +46877,19 @@
         <v>General</v>
       </c>
       <c r="G1328" t="str">
-        <v>Standard</v>
+        <v>10L</v>
       </c>
       <c r="H1328" t="str">
         <v>NOS</v>
       </c>
       <c r="I1328">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J1328" t="str">
         <v>Active</v>
       </c>
       <c r="K1328" t="str">
-        <v>EWC Toilet Seat Cover with integrated jet spray.</v>
+        <v>10 Litre Premium Dual Colour Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1329">
@@ -46897,13 +46897,13 @@
         <v>1328</v>
       </c>
       <c r="B1329" t="str">
-        <v>FG-400840</v>
+        <v>FG-400839</v>
       </c>
       <c r="C1329" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L) (10L)</v>
+        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L) (10L)</v>
       </c>
       <c r="D1329" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (PREMIUM 10L)</v>
+        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L)</v>
       </c>
       <c r="E1329" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46924,7 +46924,7 @@
         <v>Active</v>
       </c>
       <c r="K1329" t="str">
-        <v>10 Litre Premium Dual Colour Dual Flush Cistern.</v>
+        <v>10 Litre Economy Dual Colour Dual Flush Cistern.</v>
       </c>
     </row>
     <row r="1330">
@@ -46932,13 +46932,13 @@
         <v>1329</v>
       </c>
       <c r="B1330" t="str">
-        <v>FG-400839</v>
+        <v>FG-400834</v>
       </c>
       <c r="C1330" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L) (10L)</v>
+        <v>EWC SEAT COVER (WITHOUT JET) (Standard)</v>
       </c>
       <c r="D1330" t="str">
-        <v>DUAL FLUSH DUAL COLOUR (ECONOMY 10L)</v>
+        <v>EWC SEAT COVER (WITHOUT JET)</v>
       </c>
       <c r="E1330" t="str">
         <v>Toilet Seat Cover &amp; Flushing Cistern</v>
@@ -46947,59 +46947,24 @@
         <v>General</v>
       </c>
       <c r="G1330" t="str">
-        <v>10L</v>
+        <v>Standard</v>
       </c>
       <c r="H1330" t="str">
         <v>NOS</v>
       </c>
       <c r="I1330">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J1330" t="str">
         <v>Active</v>
       </c>
       <c r="K1330" t="str">
-        <v>10 Litre Economy Dual Colour Dual Flush Cistern.</v>
-      </c>
-    </row>
-    <row r="1331">
-      <c r="A1331">
-        <v>1330</v>
-      </c>
-      <c r="B1331" t="str">
-        <v>FG-400834</v>
-      </c>
-      <c r="C1331" t="str">
-        <v>EWC SEAT COVER (WITHOUT JET) (Standard)</v>
-      </c>
-      <c r="D1331" t="str">
-        <v>EWC SEAT COVER (WITHOUT JET)</v>
-      </c>
-      <c r="E1331" t="str">
-        <v>Toilet Seat Cover &amp; Flushing Cistern</v>
-      </c>
-      <c r="F1331" t="str">
-        <v>General</v>
-      </c>
-      <c r="G1331" t="str">
-        <v>Standard</v>
-      </c>
-      <c r="H1331" t="str">
-        <v>NOS</v>
-      </c>
-      <c r="I1331">
-        <v>20</v>
-      </c>
-      <c r="J1331" t="str">
-        <v>Active</v>
-      </c>
-      <c r="K1331" t="str">
         <v>EWC Toilet Seat Cover without jet spray.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K1331"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K1330"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
+++ b/public/Gouri_Aqua_Plast_Products_Catalog.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1330"/>
+  <dimension ref="A1:K1331"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -35872,10 +35872,10 @@
         <v>1013</v>
       </c>
       <c r="B1014" t="str">
-        <v>-</v>
+        <v>FG-400669</v>
       </c>
       <c r="C1014" t="str">
-        <v>AGRI COUPLER 10KG</v>
+        <v>AGRI COUPLER 10KG (25MM)</v>
       </c>
       <c r="D1014" t="str">
         <v>AGRI COUPLER 10KG</v>
@@ -35887,19 +35887,19 @@
         <v>General</v>
       </c>
       <c r="G1014" t="str">
-        <v>Standard</v>
+        <v>25MM</v>
       </c>
       <c r="H1014" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1014" t="str">
-        <v>-</v>
+      <c r="I1014">
+        <v>450</v>
       </c>
       <c r="J1014" t="str">
         <v>Active</v>
       </c>
       <c r="K1014" t="str">
-        <v>AGRI COUPLER 10KG.</v>
+        <v>AGRI COUPLER 10KG. Available sizes: 25MM, 32MM.</v>
       </c>
     </row>
     <row r="1015">
@@ -35907,13 +35907,13 @@
         <v>1014</v>
       </c>
       <c r="B1015" t="str">
-        <v>-</v>
+        <v>FG-400670</v>
       </c>
       <c r="C1015" t="str">
-        <v>PN10 - MTA ISI (25MM)</v>
+        <v>AGRI COUPLER 10KG (32MM)</v>
       </c>
       <c r="D1015" t="str">
-        <v>PN10 - MTA ISI</v>
+        <v>AGRI COUPLER 10KG</v>
       </c>
       <c r="E1015" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35922,19 +35922,19 @@
         <v>General</v>
       </c>
       <c r="G1015" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1015" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1015" t="str">
-        <v>-</v>
+      <c r="I1015">
+        <v>250</v>
       </c>
       <c r="J1015" t="str">
         <v>Active</v>
       </c>
       <c r="K1015" t="str">
-        <v>PN10 - MTA ISI for agriculture irrigation and piping systems.</v>
+        <v>AGRI COUPLER 10KG. Available sizes: 25MM, 32MM.</v>
       </c>
     </row>
     <row r="1016">
@@ -35945,7 +35945,7 @@
         <v>-</v>
       </c>
       <c r="C1016" t="str">
-        <v>PN10 - MTA ISI (32MM)</v>
+        <v>PN10 - MTA ISI (25MM)</v>
       </c>
       <c r="D1016" t="str">
         <v>PN10 - MTA ISI</v>
@@ -35957,7 +35957,7 @@
         <v>General</v>
       </c>
       <c r="G1016" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1016" t="str">
         <v>BOX</v>
@@ -35980,10 +35980,10 @@
         <v>-</v>
       </c>
       <c r="C1017" t="str">
-        <v>PN10 - FTA ISI (25MM)</v>
+        <v>PN10 - MTA ISI (32MM)</v>
       </c>
       <c r="D1017" t="str">
-        <v>PN10 - FTA ISI</v>
+        <v>PN10 - MTA ISI</v>
       </c>
       <c r="E1017" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -35992,7 +35992,7 @@
         <v>General</v>
       </c>
       <c r="G1017" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1017" t="str">
         <v>BOX</v>
@@ -36004,7 +36004,7 @@
         <v>Active</v>
       </c>
       <c r="K1017" t="str">
-        <v>PN10 - FTA ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - MTA ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1018">
@@ -36015,7 +36015,7 @@
         <v>-</v>
       </c>
       <c r="C1018" t="str">
-        <v>PN10 - FTA ISI (32MM)</v>
+        <v>PN10 - FTA ISI (25MM)</v>
       </c>
       <c r="D1018" t="str">
         <v>PN10 - FTA ISI</v>
@@ -36027,7 +36027,7 @@
         <v>General</v>
       </c>
       <c r="G1018" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1018" t="str">
         <v>BOX</v>
@@ -36050,10 +36050,10 @@
         <v>-</v>
       </c>
       <c r="C1019" t="str">
-        <v>PN10 - END CAP ISI (25MM)</v>
+        <v>PN10 - FTA ISI (32MM)</v>
       </c>
       <c r="D1019" t="str">
-        <v>PN10 - END CAP ISI</v>
+        <v>PN10 - FTA ISI</v>
       </c>
       <c r="E1019" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36062,7 +36062,7 @@
         <v>General</v>
       </c>
       <c r="G1019" t="str">
-        <v>25MM</v>
+        <v>32MM</v>
       </c>
       <c r="H1019" t="str">
         <v>BOX</v>
@@ -36074,7 +36074,7 @@
         <v>Active</v>
       </c>
       <c r="K1019" t="str">
-        <v>PN10 - END CAP ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - FTA ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1020">
@@ -36085,7 +36085,7 @@
         <v>-</v>
       </c>
       <c r="C1020" t="str">
-        <v>PN10 - END CAP ISI (32MM)</v>
+        <v>PN10 - END CAP ISI (25MM)</v>
       </c>
       <c r="D1020" t="str">
         <v>PN10 - END CAP ISI</v>
@@ -36097,7 +36097,7 @@
         <v>General</v>
       </c>
       <c r="G1020" t="str">
-        <v>32MM</v>
+        <v>25MM</v>
       </c>
       <c r="H1020" t="str">
         <v>BOX</v>
@@ -36120,10 +36120,10 @@
         <v>-</v>
       </c>
       <c r="C1021" t="str">
-        <v>PN10 - REDUCING BUSH ISI (32 X 20)</v>
+        <v>PN10 - END CAP ISI (32MM)</v>
       </c>
       <c r="D1021" t="str">
-        <v>PN10 - REDUCING BUSH ISI</v>
+        <v>PN10 - END CAP ISI</v>
       </c>
       <c r="E1021" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36132,7 +36132,7 @@
         <v>General</v>
       </c>
       <c r="G1021" t="str">
-        <v>32 X 20</v>
+        <v>32MM</v>
       </c>
       <c r="H1021" t="str">
         <v>BOX</v>
@@ -36144,7 +36144,7 @@
         <v>Active</v>
       </c>
       <c r="K1021" t="str">
-        <v>PN10 - REDUCING BUSH ISI for agriculture irrigation and piping systems.</v>
+        <v>PN10 - END CAP ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1022">
@@ -36155,7 +36155,7 @@
         <v>-</v>
       </c>
       <c r="C1022" t="str">
-        <v>PN10 - REDUCING BUSH ISI (32 X 25)</v>
+        <v>PN10 - REDUCING BUSH ISI (32 X 20)</v>
       </c>
       <c r="D1022" t="str">
         <v>PN10 - REDUCING BUSH ISI</v>
@@ -36167,7 +36167,7 @@
         <v>General</v>
       </c>
       <c r="G1022" t="str">
-        <v>32 X 25</v>
+        <v>32 X 20</v>
       </c>
       <c r="H1022" t="str">
         <v>BOX</v>
@@ -36187,13 +36187,13 @@
         <v>1022</v>
       </c>
       <c r="B1023" t="str">
-        <v>FG-400585</v>
+        <v>-</v>
       </c>
       <c r="C1023" t="str">
-        <v>AGRI REDUCER (50X40MM)</v>
+        <v>PN10 - REDUCING BUSH ISI (32 X 25)</v>
       </c>
       <c r="D1023" t="str">
-        <v>AGRI REDUCER</v>
+        <v>PN10 - REDUCING BUSH ISI</v>
       </c>
       <c r="E1023" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36202,19 +36202,19 @@
         <v>General</v>
       </c>
       <c r="G1023" t="str">
-        <v>50X40MM</v>
+        <v>32 X 25</v>
       </c>
       <c r="H1023" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1023">
-        <v>300</v>
+      <c r="I1023" t="str">
+        <v>-</v>
       </c>
       <c r="J1023" t="str">
         <v>Active</v>
       </c>
       <c r="K1023" t="str">
-        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
+        <v>PN10 - REDUCING BUSH ISI for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1024">
@@ -36222,10 +36222,10 @@
         <v>1023</v>
       </c>
       <c r="B1024" t="str">
-        <v>FG-400584</v>
+        <v>FG-400585</v>
       </c>
       <c r="C1024" t="str">
-        <v>AGRI REDUCER (63X40MM)</v>
+        <v>AGRI REDUCER (50X40MM)</v>
       </c>
       <c r="D1024" t="str">
         <v>AGRI REDUCER</v>
@@ -36237,13 +36237,13 @@
         <v>General</v>
       </c>
       <c r="G1024" t="str">
-        <v>63X40MM</v>
+        <v>50X40MM</v>
       </c>
       <c r="H1024" t="str">
         <v>BOX</v>
       </c>
       <c r="I1024">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J1024" t="str">
         <v>Active</v>
@@ -36257,10 +36257,10 @@
         <v>1024</v>
       </c>
       <c r="B1025" t="str">
-        <v>FG-400583</v>
+        <v>FG-400584</v>
       </c>
       <c r="C1025" t="str">
-        <v>AGRI REDUCER (63X50MM)</v>
+        <v>AGRI REDUCER (63X40MM)</v>
       </c>
       <c r="D1025" t="str">
         <v>AGRI REDUCER</v>
@@ -36272,13 +36272,13 @@
         <v>General</v>
       </c>
       <c r="G1025" t="str">
-        <v>63X50MM</v>
+        <v>63X40MM</v>
       </c>
       <c r="H1025" t="str">
         <v>BOX</v>
       </c>
       <c r="I1025">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="J1025" t="str">
         <v>Active</v>
@@ -36292,10 +36292,10 @@
         <v>1025</v>
       </c>
       <c r="B1026" t="str">
-        <v>FG-400582</v>
+        <v>FG-400583</v>
       </c>
       <c r="C1026" t="str">
-        <v>AGRI REDUCER (75X40MM)</v>
+        <v>AGRI REDUCER (63X50MM)</v>
       </c>
       <c r="D1026" t="str">
         <v>AGRI REDUCER</v>
@@ -36307,13 +36307,13 @@
         <v>General</v>
       </c>
       <c r="G1026" t="str">
-        <v>75X40MM</v>
+        <v>63X50MM</v>
       </c>
       <c r="H1026" t="str">
         <v>BOX</v>
       </c>
       <c r="I1026">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J1026" t="str">
         <v>Active</v>
@@ -36327,10 +36327,10 @@
         <v>1026</v>
       </c>
       <c r="B1027" t="str">
-        <v>FG-400581</v>
+        <v>FG-400582</v>
       </c>
       <c r="C1027" t="str">
-        <v>AGRI REDUCER (75X50MM)</v>
+        <v>AGRI REDUCER (75X40MM)</v>
       </c>
       <c r="D1027" t="str">
         <v>AGRI REDUCER</v>
@@ -36342,13 +36342,13 @@
         <v>General</v>
       </c>
       <c r="G1027" t="str">
-        <v>75X50MM</v>
+        <v>75X40MM</v>
       </c>
       <c r="H1027" t="str">
         <v>BOX</v>
       </c>
       <c r="I1027">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J1027" t="str">
         <v>Active</v>
@@ -36362,10 +36362,10 @@
         <v>1027</v>
       </c>
       <c r="B1028" t="str">
-        <v>FG-400580</v>
+        <v>FG-400581</v>
       </c>
       <c r="C1028" t="str">
-        <v>AGRI REDUCER (75X63MM)</v>
+        <v>AGRI REDUCER (75X50MM)</v>
       </c>
       <c r="D1028" t="str">
         <v>AGRI REDUCER</v>
@@ -36377,13 +36377,13 @@
         <v>General</v>
       </c>
       <c r="G1028" t="str">
-        <v>75X63MM</v>
+        <v>75X50MM</v>
       </c>
       <c r="H1028" t="str">
         <v>BOX</v>
       </c>
       <c r="I1028">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J1028" t="str">
         <v>Active</v>
@@ -36397,10 +36397,10 @@
         <v>1028</v>
       </c>
       <c r="B1029" t="str">
-        <v>FG-400579</v>
+        <v>FG-400580</v>
       </c>
       <c r="C1029" t="str">
-        <v>AGRI REDUCER (90X50MM)</v>
+        <v>AGRI REDUCER (75X63MM)</v>
       </c>
       <c r="D1029" t="str">
         <v>AGRI REDUCER</v>
@@ -36412,13 +36412,13 @@
         <v>General</v>
       </c>
       <c r="G1029" t="str">
-        <v>90X50MM</v>
+        <v>75X63MM</v>
       </c>
       <c r="H1029" t="str">
         <v>BOX</v>
       </c>
       <c r="I1029">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J1029" t="str">
         <v>Active</v>
@@ -36432,10 +36432,10 @@
         <v>1029</v>
       </c>
       <c r="B1030" t="str">
-        <v>FG-400578</v>
+        <v>FG-400579</v>
       </c>
       <c r="C1030" t="str">
-        <v>AGRI REDUCER (90X63MM)</v>
+        <v>AGRI REDUCER (90X50MM)</v>
       </c>
       <c r="D1030" t="str">
         <v>AGRI REDUCER</v>
@@ -36447,13 +36447,13 @@
         <v>General</v>
       </c>
       <c r="G1030" t="str">
-        <v>90X63MM</v>
+        <v>90X50MM</v>
       </c>
       <c r="H1030" t="str">
         <v>BOX</v>
       </c>
       <c r="I1030">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J1030" t="str">
         <v>Active</v>
@@ -36467,10 +36467,10 @@
         <v>1030</v>
       </c>
       <c r="B1031" t="str">
-        <v>FG-400577</v>
+        <v>FG-400578</v>
       </c>
       <c r="C1031" t="str">
-        <v>AGRI REDUCER (90X75MM)</v>
+        <v>AGRI REDUCER (90X63MM)</v>
       </c>
       <c r="D1031" t="str">
         <v>AGRI REDUCER</v>
@@ -36482,13 +36482,13 @@
         <v>General</v>
       </c>
       <c r="G1031" t="str">
-        <v>90X75MM</v>
+        <v>90X63MM</v>
       </c>
       <c r="H1031" t="str">
         <v>BOX</v>
       </c>
       <c r="I1031">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J1031" t="str">
         <v>Active</v>
@@ -36502,10 +36502,10 @@
         <v>1031</v>
       </c>
       <c r="B1032" t="str">
-        <v>FG-400576</v>
+        <v>FG-400577</v>
       </c>
       <c r="C1032" t="str">
-        <v>AGRI REDUCER (110X63MM)</v>
+        <v>AGRI REDUCER (90X75MM)</v>
       </c>
       <c r="D1032" t="str">
         <v>AGRI REDUCER</v>
@@ -36517,13 +36517,13 @@
         <v>General</v>
       </c>
       <c r="G1032" t="str">
-        <v>110X63MM</v>
+        <v>90X75MM</v>
       </c>
       <c r="H1032" t="str">
         <v>BOX</v>
       </c>
       <c r="I1032">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J1032" t="str">
         <v>Active</v>
@@ -36537,10 +36537,10 @@
         <v>1032</v>
       </c>
       <c r="B1033" t="str">
-        <v>FG-400575</v>
+        <v>FG-400576</v>
       </c>
       <c r="C1033" t="str">
-        <v>AGRI REDUCER (110X75MM)</v>
+        <v>AGRI REDUCER (110X63MM)</v>
       </c>
       <c r="D1033" t="str">
         <v>AGRI REDUCER</v>
@@ -36552,7 +36552,7 @@
         <v>General</v>
       </c>
       <c r="G1033" t="str">
-        <v>110X75MM</v>
+        <v>110X63MM</v>
       </c>
       <c r="H1033" t="str">
         <v>BOX</v>
@@ -36572,10 +36572,10 @@
         <v>1033</v>
       </c>
       <c r="B1034" t="str">
-        <v>FG-400574</v>
+        <v>FG-400575</v>
       </c>
       <c r="C1034" t="str">
-        <v>AGRI REDUCER (110X90MM)</v>
+        <v>AGRI REDUCER (110X75MM)</v>
       </c>
       <c r="D1034" t="str">
         <v>AGRI REDUCER</v>
@@ -36587,13 +36587,13 @@
         <v>General</v>
       </c>
       <c r="G1034" t="str">
-        <v>110X90MM</v>
+        <v>110X75MM</v>
       </c>
       <c r="H1034" t="str">
         <v>BOX</v>
       </c>
       <c r="I1034">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J1034" t="str">
         <v>Active</v>
@@ -36607,13 +36607,13 @@
         <v>1034</v>
       </c>
       <c r="B1035" t="str">
-        <v>-</v>
+        <v>FG-400574</v>
       </c>
       <c r="C1035" t="str">
-        <v>REDUCING BUSH (LW) (63 X 40)</v>
+        <v>AGRI REDUCER (110X90MM)</v>
       </c>
       <c r="D1035" t="str">
-        <v>REDUCING BUSH (LW)</v>
+        <v>AGRI REDUCER</v>
       </c>
       <c r="E1035" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36622,19 +36622,19 @@
         <v>General</v>
       </c>
       <c r="G1035" t="str">
-        <v>63 X 40</v>
+        <v>110X90MM</v>
       </c>
       <c r="H1035" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1035" t="str">
-        <v>-</v>
+      <c r="I1035">
+        <v>40</v>
       </c>
       <c r="J1035" t="str">
         <v>Active</v>
       </c>
       <c r="K1035" t="str">
-        <v>REDUCING BUSH (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI REDUCER for agriculture irrigation and piping systems. Available sizes: 50X40MM, 63X40MM, 63X50MM, 75X40MM, 75X50MM, 75X63MM, 90X50MM, 90X63MM, 90X75MM, 110X63MM, 110X75MM, 110X90MM.</v>
       </c>
     </row>
     <row r="1036">
@@ -36645,7 +36645,7 @@
         <v>-</v>
       </c>
       <c r="C1036" t="str">
-        <v>REDUCING BUSH (LW) (63 X 50)</v>
+        <v>REDUCING BUSH (LW) (63 X 40)</v>
       </c>
       <c r="D1036" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36657,7 +36657,7 @@
         <v>General</v>
       </c>
       <c r="G1036" t="str">
-        <v>63 X 50</v>
+        <v>63 X 40</v>
       </c>
       <c r="H1036" t="str">
         <v>BOX</v>
@@ -36680,7 +36680,7 @@
         <v>-</v>
       </c>
       <c r="C1037" t="str">
-        <v>REDUCING BUSH (LW) (75 X 40)</v>
+        <v>REDUCING BUSH (LW) (63 X 50)</v>
       </c>
       <c r="D1037" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36692,7 +36692,7 @@
         <v>General</v>
       </c>
       <c r="G1037" t="str">
-        <v>75 X 40</v>
+        <v>63 X 50</v>
       </c>
       <c r="H1037" t="str">
         <v>BOX</v>
@@ -36715,7 +36715,7 @@
         <v>-</v>
       </c>
       <c r="C1038" t="str">
-        <v>REDUCING BUSH (LW) (75 X 63)</v>
+        <v>REDUCING BUSH (LW) (75 X 40)</v>
       </c>
       <c r="D1038" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36727,7 +36727,7 @@
         <v>General</v>
       </c>
       <c r="G1038" t="str">
-        <v>75 X 63</v>
+        <v>75 X 40</v>
       </c>
       <c r="H1038" t="str">
         <v>BOX</v>
@@ -36750,7 +36750,7 @@
         <v>-</v>
       </c>
       <c r="C1039" t="str">
-        <v>REDUCING BUSH (LW) (90 X 50)</v>
+        <v>REDUCING BUSH (LW) (75 X 63)</v>
       </c>
       <c r="D1039" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36762,7 +36762,7 @@
         <v>General</v>
       </c>
       <c r="G1039" t="str">
-        <v>90 X 50</v>
+        <v>75 X 63</v>
       </c>
       <c r="H1039" t="str">
         <v>BOX</v>
@@ -36785,7 +36785,7 @@
         <v>-</v>
       </c>
       <c r="C1040" t="str">
-        <v>REDUCING BUSH (LW) (90 X 63)</v>
+        <v>REDUCING BUSH (LW) (90 X 50)</v>
       </c>
       <c r="D1040" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36797,7 +36797,7 @@
         <v>General</v>
       </c>
       <c r="G1040" t="str">
-        <v>90 X 63</v>
+        <v>90 X 50</v>
       </c>
       <c r="H1040" t="str">
         <v>BOX</v>
@@ -36820,7 +36820,7 @@
         <v>-</v>
       </c>
       <c r="C1041" t="str">
-        <v>REDUCING BUSH (LW) (90 X 75)</v>
+        <v>REDUCING BUSH (LW) (90 X 63)</v>
       </c>
       <c r="D1041" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36832,7 +36832,7 @@
         <v>General</v>
       </c>
       <c r="G1041" t="str">
-        <v>90 X 75</v>
+        <v>90 X 63</v>
       </c>
       <c r="H1041" t="str">
         <v>BOX</v>
@@ -36855,7 +36855,7 @@
         <v>-</v>
       </c>
       <c r="C1042" t="str">
-        <v>REDUCING BUSH (LW) (110 X 63)</v>
+        <v>REDUCING BUSH (LW) (90 X 75)</v>
       </c>
       <c r="D1042" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36867,7 +36867,7 @@
         <v>General</v>
       </c>
       <c r="G1042" t="str">
-        <v>110 X 63</v>
+        <v>90 X 75</v>
       </c>
       <c r="H1042" t="str">
         <v>BOX</v>
@@ -36890,7 +36890,7 @@
         <v>-</v>
       </c>
       <c r="C1043" t="str">
-        <v>REDUCING BUSH (LW) (110 X 75)</v>
+        <v>REDUCING BUSH (LW) (110 X 63)</v>
       </c>
       <c r="D1043" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36902,7 +36902,7 @@
         <v>General</v>
       </c>
       <c r="G1043" t="str">
-        <v>110 X 75</v>
+        <v>110 X 63</v>
       </c>
       <c r="H1043" t="str">
         <v>BOX</v>
@@ -36925,7 +36925,7 @@
         <v>-</v>
       </c>
       <c r="C1044" t="str">
-        <v>REDUCING BUSH (LW) (110 X 90)</v>
+        <v>REDUCING BUSH (LW) (110 X 75)</v>
       </c>
       <c r="D1044" t="str">
         <v>REDUCING BUSH (LW)</v>
@@ -36937,7 +36937,7 @@
         <v>General</v>
       </c>
       <c r="G1044" t="str">
-        <v>110 X 90</v>
+        <v>110 X 75</v>
       </c>
       <c r="H1044" t="str">
         <v>BOX</v>
@@ -36957,13 +36957,13 @@
         <v>1044</v>
       </c>
       <c r="B1045" t="str">
-        <v>FG-400550</v>
+        <v>-</v>
       </c>
       <c r="C1045" t="str">
-        <v>AGRI TEE (40MM)</v>
+        <v>REDUCING BUSH (LW) (110 X 90)</v>
       </c>
       <c r="D1045" t="str">
-        <v>AGRI TEE</v>
+        <v>REDUCING BUSH (LW)</v>
       </c>
       <c r="E1045" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -36972,19 +36972,19 @@
         <v>General</v>
       </c>
       <c r="G1045" t="str">
-        <v>40MM</v>
+        <v>110 X 90</v>
       </c>
       <c r="H1045" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1045">
-        <v>150</v>
+      <c r="I1045" t="str">
+        <v>-</v>
       </c>
       <c r="J1045" t="str">
         <v>Active</v>
       </c>
       <c r="K1045" t="str">
-        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
+        <v>REDUCING BUSH (LW) for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1046">
@@ -36992,10 +36992,10 @@
         <v>1045</v>
       </c>
       <c r="B1046" t="str">
-        <v>FG-400551</v>
+        <v>FG-400550</v>
       </c>
       <c r="C1046" t="str">
-        <v>AGRI TEE (50MM)</v>
+        <v>AGRI TEE (40MM)</v>
       </c>
       <c r="D1046" t="str">
         <v>AGRI TEE</v>
@@ -37007,13 +37007,13 @@
         <v>General</v>
       </c>
       <c r="G1046" t="str">
-        <v>50MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1046" t="str">
         <v>BOX</v>
       </c>
       <c r="I1046">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J1046" t="str">
         <v>Active</v>
@@ -37027,10 +37027,10 @@
         <v>1046</v>
       </c>
       <c r="B1047" t="str">
-        <v>FG-400552</v>
+        <v>FG-400551</v>
       </c>
       <c r="C1047" t="str">
-        <v>AGRI TEE (63MM)</v>
+        <v>AGRI TEE (50MM)</v>
       </c>
       <c r="D1047" t="str">
         <v>AGRI TEE</v>
@@ -37042,13 +37042,13 @@
         <v>General</v>
       </c>
       <c r="G1047" t="str">
-        <v>63MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1047" t="str">
         <v>BOX</v>
       </c>
       <c r="I1047">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="J1047" t="str">
         <v>Active</v>
@@ -37062,10 +37062,10 @@
         <v>1047</v>
       </c>
       <c r="B1048" t="str">
-        <v>FG-400553</v>
+        <v>FG-400552</v>
       </c>
       <c r="C1048" t="str">
-        <v>AGRI TEE (75MM)</v>
+        <v>AGRI TEE (63MM)</v>
       </c>
       <c r="D1048" t="str">
         <v>AGRI TEE</v>
@@ -37077,13 +37077,13 @@
         <v>General</v>
       </c>
       <c r="G1048" t="str">
-        <v>75MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1048" t="str">
         <v>BOX</v>
       </c>
       <c r="I1048">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="J1048" t="str">
         <v>Active</v>
@@ -37097,10 +37097,10 @@
         <v>1048</v>
       </c>
       <c r="B1049" t="str">
-        <v>FG-400554</v>
+        <v>FG-400553</v>
       </c>
       <c r="C1049" t="str">
-        <v>AGRI TEE (90MM)</v>
+        <v>AGRI TEE (75MM)</v>
       </c>
       <c r="D1049" t="str">
         <v>AGRI TEE</v>
@@ -37112,13 +37112,13 @@
         <v>General</v>
       </c>
       <c r="G1049" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1049" t="str">
         <v>BOX</v>
       </c>
       <c r="I1049">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J1049" t="str">
         <v>Active</v>
@@ -37132,10 +37132,10 @@
         <v>1049</v>
       </c>
       <c r="B1050" t="str">
-        <v>FG-400586</v>
+        <v>FG-400554</v>
       </c>
       <c r="C1050" t="str">
-        <v>AGRI TEE (110MM)</v>
+        <v>AGRI TEE (90MM)</v>
       </c>
       <c r="D1050" t="str">
         <v>AGRI TEE</v>
@@ -37147,13 +37147,13 @@
         <v>General</v>
       </c>
       <c r="G1050" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1050" t="str">
         <v>BOX</v>
       </c>
       <c r="I1050">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J1050" t="str">
         <v>Active</v>
@@ -37167,10 +37167,10 @@
         <v>1050</v>
       </c>
       <c r="B1051" t="str">
-        <v>FG-400607</v>
+        <v>FG-400586</v>
       </c>
       <c r="C1051" t="str">
-        <v>AGRI TEE (140MM)</v>
+        <v>AGRI TEE (110MM)</v>
       </c>
       <c r="D1051" t="str">
         <v>AGRI TEE</v>
@@ -37182,13 +37182,13 @@
         <v>General</v>
       </c>
       <c r="G1051" t="str">
-        <v>140MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1051" t="str">
         <v>BOX</v>
       </c>
       <c r="I1051">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="J1051" t="str">
         <v>Active</v>
@@ -37202,10 +37202,10 @@
         <v>1051</v>
       </c>
       <c r="B1052" t="str">
-        <v>FG-400608</v>
+        <v>FG-400607</v>
       </c>
       <c r="C1052" t="str">
-        <v>AGRI TEE (160MM)</v>
+        <v>AGRI TEE (140MM)</v>
       </c>
       <c r="D1052" t="str">
         <v>AGRI TEE</v>
@@ -37217,13 +37217,13 @@
         <v>General</v>
       </c>
       <c r="G1052" t="str">
-        <v>160MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1052" t="str">
         <v>BOX</v>
       </c>
       <c r="I1052">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J1052" t="str">
         <v>Active</v>
@@ -37237,13 +37237,13 @@
         <v>1052</v>
       </c>
       <c r="B1053" t="str">
-        <v>-</v>
+        <v>FG-400608</v>
       </c>
       <c r="C1053" t="str">
-        <v>COUPLER (LW) (75MM)</v>
+        <v>AGRI TEE (160MM)</v>
       </c>
       <c r="D1053" t="str">
-        <v>COUPLER (LW)</v>
+        <v>AGRI TEE</v>
       </c>
       <c r="E1053" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37252,19 +37252,19 @@
         <v>General</v>
       </c>
       <c r="G1053" t="str">
-        <v>75MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1053" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1053" t="str">
-        <v>-</v>
+      <c r="I1053">
+        <v>9</v>
       </c>
       <c r="J1053" t="str">
         <v>Active</v>
       </c>
       <c r="K1053" t="str">
-        <v>COUPLER (LW) for agriculture irrigation and piping systems.</v>
+        <v>AGRI TEE for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1054">
@@ -37275,7 +37275,7 @@
         <v>-</v>
       </c>
       <c r="C1054" t="str">
-        <v>COUPLER (LW) (90MM)</v>
+        <v>COUPLER (LW) (75MM)</v>
       </c>
       <c r="D1054" t="str">
         <v>COUPLER (LW)</v>
@@ -37287,7 +37287,7 @@
         <v>General</v>
       </c>
       <c r="G1054" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1054" t="str">
         <v>BOX</v>
@@ -37310,7 +37310,7 @@
         <v>-</v>
       </c>
       <c r="C1055" t="str">
-        <v>COUPLER (LW) (110MM)</v>
+        <v>COUPLER (LW) (90MM)</v>
       </c>
       <c r="D1055" t="str">
         <v>COUPLER (LW)</v>
@@ -37322,7 +37322,7 @@
         <v>General</v>
       </c>
       <c r="G1055" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1055" t="str">
         <v>BOX</v>
@@ -37342,13 +37342,13 @@
         <v>1055</v>
       </c>
       <c r="B1056" t="str">
-        <v>FG-400561</v>
+        <v>-</v>
       </c>
       <c r="C1056" t="str">
-        <v>AGRI FABRICATED COUPLER (40MM)</v>
+        <v>COUPLER (LW) (110MM)</v>
       </c>
       <c r="D1056" t="str">
-        <v>AGRI FABRICATED COUPLER</v>
+        <v>COUPLER (LW)</v>
       </c>
       <c r="E1056" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37357,19 +37357,19 @@
         <v>General</v>
       </c>
       <c r="G1056" t="str">
-        <v>40MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1056" t="str">
         <v>BOX</v>
       </c>
-      <c r="I1056">
-        <v>300</v>
+      <c r="I1056" t="str">
+        <v>-</v>
       </c>
       <c r="J1056" t="str">
         <v>Active</v>
       </c>
       <c r="K1056" t="str">
-        <v>AGRI FABRICATED COUPLER for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
+        <v>COUPLER (LW) for agriculture irrigation and piping systems.</v>
       </c>
     </row>
     <row r="1057">
@@ -37377,10 +37377,10 @@
         <v>1056</v>
       </c>
       <c r="B1057" t="str">
-        <v>FG-400562</v>
+        <v>FG-400561</v>
       </c>
       <c r="C1057" t="str">
-        <v>AGRI FABRICATED COUPLER (50MM)</v>
+        <v>AGRI FABRICATED COUPLER (40MM)</v>
       </c>
       <c r="D1057" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37392,13 +37392,13 @@
         <v>General</v>
       </c>
       <c r="G1057" t="str">
-        <v>50MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1057" t="str">
         <v>BOX</v>
       </c>
       <c r="I1057">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J1057" t="str">
         <v>Active</v>
@@ -37412,10 +37412,10 @@
         <v>1057</v>
       </c>
       <c r="B1058" t="str">
-        <v>FG-400563</v>
+        <v>FG-400562</v>
       </c>
       <c r="C1058" t="str">
-        <v>AGRI FABRICATED COUPLER (63MM)</v>
+        <v>AGRI FABRICATED COUPLER (50MM)</v>
       </c>
       <c r="D1058" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37427,7 +37427,7 @@
         <v>General</v>
       </c>
       <c r="G1058" t="str">
-        <v>63MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1058" t="str">
         <v>BOX</v>
@@ -37447,10 +37447,10 @@
         <v>1058</v>
       </c>
       <c r="B1059" t="str">
-        <v>FG-400564</v>
+        <v>FG-400563</v>
       </c>
       <c r="C1059" t="str">
-        <v>AGRI FABRICATED COUPLER (75MM)</v>
+        <v>AGRI FABRICATED COUPLER (63MM)</v>
       </c>
       <c r="D1059" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37462,13 +37462,13 @@
         <v>General</v>
       </c>
       <c r="G1059" t="str">
-        <v>75MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1059" t="str">
         <v>BOX</v>
       </c>
       <c r="I1059">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="J1059" t="str">
         <v>Active</v>
@@ -37482,10 +37482,10 @@
         <v>1059</v>
       </c>
       <c r="B1060" t="str">
-        <v>FG-400565</v>
+        <v>FG-400564</v>
       </c>
       <c r="C1060" t="str">
-        <v>AGRI FABRICATED COUPLER (90MM)</v>
+        <v>AGRI FABRICATED COUPLER (75MM)</v>
       </c>
       <c r="D1060" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37497,13 +37497,13 @@
         <v>General</v>
       </c>
       <c r="G1060" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1060" t="str">
         <v>BOX</v>
       </c>
       <c r="I1060">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="J1060" t="str">
         <v>Active</v>
@@ -37517,10 +37517,10 @@
         <v>1060</v>
       </c>
       <c r="B1061" t="str">
-        <v>FG-400566</v>
+        <v>FG-400565</v>
       </c>
       <c r="C1061" t="str">
-        <v>AGRI FABRICATED COUPLER (110MM)</v>
+        <v>AGRI FABRICATED COUPLER (90MM)</v>
       </c>
       <c r="D1061" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37532,13 +37532,13 @@
         <v>General</v>
       </c>
       <c r="G1061" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1061" t="str">
         <v>BOX</v>
       </c>
       <c r="I1061">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J1061" t="str">
         <v>Active</v>
@@ -37552,10 +37552,10 @@
         <v>1061</v>
       </c>
       <c r="B1062" t="str">
-        <v>FG-400587</v>
+        <v>FG-400566</v>
       </c>
       <c r="C1062" t="str">
-        <v>AGRI FABRICATED COUPLER (140MM 4KG)</v>
+        <v>AGRI FABRICATED COUPLER (110MM)</v>
       </c>
       <c r="D1062" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37567,13 +37567,13 @@
         <v>General</v>
       </c>
       <c r="G1062" t="str">
-        <v>140MM 4KG</v>
+        <v>110MM</v>
       </c>
       <c r="H1062" t="str">
         <v>BOX</v>
       </c>
       <c r="I1062">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J1062" t="str">
         <v>Active</v>
@@ -37587,10 +37587,10 @@
         <v>1062</v>
       </c>
       <c r="B1063" t="str">
-        <v>FG-400568</v>
+        <v>FG-400587</v>
       </c>
       <c r="C1063" t="str">
-        <v>AGRI FABRICATED COUPLER (160MM 4KG)</v>
+        <v>AGRI FABRICATED COUPLER (140MM 4KG)</v>
       </c>
       <c r="D1063" t="str">
         <v>AGRI FABRICATED COUPLER</v>
@@ -37602,13 +37602,13 @@
         <v>General</v>
       </c>
       <c r="G1063" t="str">
-        <v>160MM 4KG</v>
+        <v>140MM 4KG</v>
       </c>
       <c r="H1063" t="str">
         <v>BOX</v>
       </c>
       <c r="I1063">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J1063" t="str">
         <v>Active</v>
@@ -37622,13 +37622,13 @@
         <v>1063</v>
       </c>
       <c r="B1064" t="str">
-        <v>FG-400567</v>
+        <v>FG-400568</v>
       </c>
       <c r="C1064" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG (140MM)</v>
+        <v>AGRI FABRICATED COUPLER (160MM 4KG)</v>
       </c>
       <c r="D1064" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG</v>
+        <v>AGRI FABRICATED COUPLER</v>
       </c>
       <c r="E1064" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37637,19 +37637,19 @@
         <v>General</v>
       </c>
       <c r="G1064" t="str">
-        <v>140MM</v>
+        <v>160MM 4KG</v>
       </c>
       <c r="H1064" t="str">
         <v>BOX</v>
       </c>
       <c r="I1064">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J1064" t="str">
         <v>Active</v>
       </c>
       <c r="K1064" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG for agriculture irrigation and piping systems. Available sizes: 140MM, 160MM.</v>
+        <v>AGRI FABRICATED COUPLER for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1065">
@@ -37657,10 +37657,10 @@
         <v>1064</v>
       </c>
       <c r="B1065" t="str">
-        <v>FG-400569</v>
+        <v>FG-400567</v>
       </c>
       <c r="C1065" t="str">
-        <v>AGRI FABRICATED COUPLER 6KG (160MM)</v>
+        <v>AGRI FABRICATED COUPLER 6KG (140MM)</v>
       </c>
       <c r="D1065" t="str">
         <v>AGRI FABRICATED COUPLER 6KG</v>
@@ -37672,13 +37672,13 @@
         <v>General</v>
       </c>
       <c r="G1065" t="str">
-        <v>160MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1065" t="str">
         <v>BOX</v>
       </c>
       <c r="I1065">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J1065" t="str">
         <v>Active</v>
@@ -37692,13 +37692,13 @@
         <v>1065</v>
       </c>
       <c r="B1066" t="str">
-        <v>FG-400544</v>
+        <v>FG-400569</v>
       </c>
       <c r="C1066" t="str">
-        <v>AGRI ELBOW (40MM)</v>
+        <v>AGRI FABRICATED COUPLER 6KG (160MM)</v>
       </c>
       <c r="D1066" t="str">
-        <v>AGRI ELBOW</v>
+        <v>AGRI FABRICATED COUPLER 6KG</v>
       </c>
       <c r="E1066" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37707,19 +37707,19 @@
         <v>General</v>
       </c>
       <c r="G1066" t="str">
-        <v>40MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1066" t="str">
         <v>BOX</v>
       </c>
       <c r="I1066">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="J1066" t="str">
         <v>Active</v>
       </c>
       <c r="K1066" t="str">
-        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
+        <v>AGRI FABRICATED COUPLER 6KG for agriculture irrigation and piping systems. Available sizes: 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1067">
@@ -37727,10 +37727,10 @@
         <v>1066</v>
       </c>
       <c r="B1067" t="str">
-        <v>FG-400545</v>
+        <v>FG-400544</v>
       </c>
       <c r="C1067" t="str">
-        <v>AGRI ELBOW (50MM)</v>
+        <v>AGRI ELBOW (40MM)</v>
       </c>
       <c r="D1067" t="str">
         <v>AGRI ELBOW</v>
@@ -37742,13 +37742,13 @@
         <v>General</v>
       </c>
       <c r="G1067" t="str">
-        <v>50MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1067" t="str">
         <v>BOX</v>
       </c>
       <c r="I1067">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="J1067" t="str">
         <v>Active</v>
@@ -37762,10 +37762,10 @@
         <v>1067</v>
       </c>
       <c r="B1068" t="str">
-        <v>FG-400546</v>
+        <v>FG-400545</v>
       </c>
       <c r="C1068" t="str">
-        <v>AGRI ELBOW (63MM)</v>
+        <v>AGRI ELBOW (50MM)</v>
       </c>
       <c r="D1068" t="str">
         <v>AGRI ELBOW</v>
@@ -37777,13 +37777,13 @@
         <v>General</v>
       </c>
       <c r="G1068" t="str">
-        <v>63MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1068" t="str">
         <v>BOX</v>
       </c>
       <c r="I1068">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J1068" t="str">
         <v>Active</v>
@@ -37797,10 +37797,10 @@
         <v>1068</v>
       </c>
       <c r="B1069" t="str">
-        <v>FG-400547</v>
+        <v>FG-400546</v>
       </c>
       <c r="C1069" t="str">
-        <v>AGRI ELBOW (75MM)</v>
+        <v>AGRI ELBOW (63MM)</v>
       </c>
       <c r="D1069" t="str">
         <v>AGRI ELBOW</v>
@@ -37812,13 +37812,13 @@
         <v>General</v>
       </c>
       <c r="G1069" t="str">
-        <v>75MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1069" t="str">
         <v>BOX</v>
       </c>
       <c r="I1069">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J1069" t="str">
         <v>Active</v>
@@ -37832,10 +37832,10 @@
         <v>1069</v>
       </c>
       <c r="B1070" t="str">
-        <v>FG-400548</v>
+        <v>FG-400547</v>
       </c>
       <c r="C1070" t="str">
-        <v>AGRI ELBOW (90MM)</v>
+        <v>AGRI ELBOW (75MM)</v>
       </c>
       <c r="D1070" t="str">
         <v>AGRI ELBOW</v>
@@ -37847,13 +37847,13 @@
         <v>General</v>
       </c>
       <c r="G1070" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1070" t="str">
         <v>BOX</v>
       </c>
       <c r="I1070">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J1070" t="str">
         <v>Active</v>
@@ -37867,10 +37867,10 @@
         <v>1070</v>
       </c>
       <c r="B1071" t="str">
-        <v>FG-400549</v>
+        <v>FG-400548</v>
       </c>
       <c r="C1071" t="str">
-        <v>AGRI ELBOW (110MM)</v>
+        <v>AGRI ELBOW (90MM)</v>
       </c>
       <c r="D1071" t="str">
         <v>AGRI ELBOW</v>
@@ -37882,13 +37882,13 @@
         <v>General</v>
       </c>
       <c r="G1071" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1071" t="str">
         <v>BOX</v>
       </c>
       <c r="I1071">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="J1071" t="str">
         <v>Active</v>
@@ -37902,10 +37902,10 @@
         <v>1071</v>
       </c>
       <c r="B1072" t="str">
-        <v>FG-400595</v>
+        <v>FG-400549</v>
       </c>
       <c r="C1072" t="str">
-        <v>AGRI ELBOW (140MM)</v>
+        <v>AGRI ELBOW (110MM)</v>
       </c>
       <c r="D1072" t="str">
         <v>AGRI ELBOW</v>
@@ -37917,13 +37917,13 @@
         <v>General</v>
       </c>
       <c r="G1072" t="str">
-        <v>140MM</v>
+        <v>110MM</v>
       </c>
       <c r="H1072" t="str">
         <v>BOX</v>
       </c>
       <c r="I1072">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="J1072" t="str">
         <v>Active</v>
@@ -37937,10 +37937,10 @@
         <v>1072</v>
       </c>
       <c r="B1073" t="str">
-        <v>FG-400596</v>
+        <v>FG-400595</v>
       </c>
       <c r="C1073" t="str">
-        <v>AGRI ELBOW (160MM)</v>
+        <v>AGRI ELBOW (140MM)</v>
       </c>
       <c r="D1073" t="str">
         <v>AGRI ELBOW</v>
@@ -37952,13 +37952,13 @@
         <v>General</v>
       </c>
       <c r="G1073" t="str">
-        <v>160MM</v>
+        <v>140MM</v>
       </c>
       <c r="H1073" t="str">
         <v>BOX</v>
       </c>
       <c r="I1073">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J1073" t="str">
         <v>Active</v>
@@ -37972,13 +37972,13 @@
         <v>1073</v>
       </c>
       <c r="B1074" t="str">
-        <v>FG-400555</v>
+        <v>FG-400596</v>
       </c>
       <c r="C1074" t="str">
-        <v>AGRI END CAP (40MM)</v>
+        <v>AGRI ELBOW (160MM)</v>
       </c>
       <c r="D1074" t="str">
-        <v>AGRI END CAP</v>
+        <v>AGRI ELBOW</v>
       </c>
       <c r="E1074" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -37987,19 +37987,19 @@
         <v>General</v>
       </c>
       <c r="G1074" t="str">
-        <v>40MM</v>
+        <v>160MM</v>
       </c>
       <c r="H1074" t="str">
         <v>BOX</v>
       </c>
       <c r="I1074">
-        <v>800</v>
+        <v>12</v>
       </c>
       <c r="J1074" t="str">
         <v>Active</v>
       </c>
       <c r="K1074" t="str">
-        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
+        <v>AGRI ELBOW for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM, 160MM.</v>
       </c>
     </row>
     <row r="1075">
@@ -38007,10 +38007,10 @@
         <v>1074</v>
       </c>
       <c r="B1075" t="str">
-        <v>FG-400556</v>
+        <v>FG-400555</v>
       </c>
       <c r="C1075" t="str">
-        <v>AGRI END CAP (50MM)</v>
+        <v>AGRI END CAP (40MM)</v>
       </c>
       <c r="D1075" t="str">
         <v>AGRI END CAP</v>
@@ -38022,13 +38022,13 @@
         <v>General</v>
       </c>
       <c r="G1075" t="str">
-        <v>50MM</v>
+        <v>40MM</v>
       </c>
       <c r="H1075" t="str">
         <v>BOX</v>
       </c>
       <c r="I1075">
-        <v>450</v>
+        <v>800</v>
       </c>
       <c r="J1075" t="str">
         <v>Active</v>
@@ -38042,10 +38042,10 @@
         <v>1075</v>
       </c>
       <c r="B1076" t="str">
-        <v>FG-400557</v>
+        <v>FG-400556</v>
       </c>
       <c r="C1076" t="str">
-        <v>AGRI END CAP (63MM)</v>
+        <v>AGRI END CAP (50MM)</v>
       </c>
       <c r="D1076" t="str">
         <v>AGRI END CAP</v>
@@ -38057,13 +38057,13 @@
         <v>General</v>
       </c>
       <c r="G1076" t="str">
-        <v>63MM</v>
+        <v>50MM</v>
       </c>
       <c r="H1076" t="str">
         <v>BOX</v>
       </c>
       <c r="I1076">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="J1076" t="str">
         <v>Active</v>
@@ -38077,10 +38077,10 @@
         <v>1076</v>
       </c>
       <c r="B1077" t="str">
-        <v>FG-400558</v>
+        <v>FG-400557</v>
       </c>
       <c r="C1077" t="str">
-        <v>AGRI END CAP (75MM)</v>
+        <v>AGRI END CAP (63MM)</v>
       </c>
       <c r="D1077" t="str">
         <v>AGRI END CAP</v>
@@ -38092,13 +38092,13 @@
         <v>General</v>
       </c>
       <c r="G1077" t="str">
-        <v>75MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1077" t="str">
         <v>BOX</v>
       </c>
       <c r="I1077">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="J1077" t="str">
         <v>Active</v>
@@ -38112,10 +38112,10 @@
         <v>1077</v>
       </c>
       <c r="B1078" t="str">
-        <v>FG-400559</v>
+        <v>FG-400558</v>
       </c>
       <c r="C1078" t="str">
-        <v>AGRI END CAP (90MM)</v>
+        <v>AGRI END CAP (75MM)</v>
       </c>
       <c r="D1078" t="str">
         <v>AGRI END CAP</v>
@@ -38127,13 +38127,13 @@
         <v>General</v>
       </c>
       <c r="G1078" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1078" t="str">
         <v>BOX</v>
       </c>
       <c r="I1078">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J1078" t="str">
         <v>Active</v>
@@ -38147,10 +38147,10 @@
         <v>1078</v>
       </c>
       <c r="B1079" t="str">
-        <v>FG-400560</v>
+        <v>FG-400559</v>
       </c>
       <c r="C1079" t="str">
-        <v>AGRI END CAP (110MM)</v>
+        <v>AGRI END CAP (90MM)</v>
       </c>
       <c r="D1079" t="str">
         <v>AGRI END CAP</v>
@@ -38162,13 +38162,13 @@
         <v>General</v>
       </c>
       <c r="G1079" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1079" t="str">
         <v>BOX</v>
       </c>
       <c r="I1079">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J1079" t="str">
         <v>Active</v>
@@ -38182,10 +38182,10 @@
         <v>1079</v>
       </c>
       <c r="B1080" t="str">
-        <v>FG-400639</v>
+        <v>FG-400560</v>
       </c>
       <c r="C1080" t="str">
-        <v>AGRI END CAP (140MM 4KG)</v>
+        <v>AGRI END CAP (110MM)</v>
       </c>
       <c r="D1080" t="str">
         <v>AGRI END CAP</v>
@@ -38197,13 +38197,13 @@
         <v>General</v>
       </c>
       <c r="G1080" t="str">
-        <v>140MM 4KG</v>
+        <v>110MM</v>
       </c>
       <c r="H1080" t="str">
         <v>BOX</v>
       </c>
       <c r="I1080">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J1080" t="str">
         <v>Active</v>
@@ -38217,10 +38217,10 @@
         <v>1080</v>
       </c>
       <c r="B1081" t="str">
-        <v>FG-400640</v>
+        <v>FG-400639</v>
       </c>
       <c r="C1081" t="str">
-        <v>AGRI END CAP (160MM 4KG)</v>
+        <v>AGRI END CAP (140MM 4KG)</v>
       </c>
       <c r="D1081" t="str">
         <v>AGRI END CAP</v>
@@ -38232,13 +38232,13 @@
         <v>General</v>
       </c>
       <c r="G1081" t="str">
-        <v>160MM 4KG</v>
+        <v>140MM 4KG</v>
       </c>
       <c r="H1081" t="str">
         <v>BOX</v>
       </c>
       <c r="I1081">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J1081" t="str">
         <v>Active</v>
@@ -38252,13 +38252,13 @@
         <v>1081</v>
       </c>
       <c r="B1082" t="str">
-        <v>FG-400570</v>
+        <v>FG-400640</v>
       </c>
       <c r="C1082" t="str">
-        <v>AGRI LONG BEND (63MM)</v>
+        <v>AGRI END CAP (160MM 4KG)</v>
       </c>
       <c r="D1082" t="str">
-        <v>AGRI LONG BEND</v>
+        <v>AGRI END CAP</v>
       </c>
       <c r="E1082" t="str">
         <v>Agriculture Pipes &amp; Fittings</v>
@@ -38267,19 +38267,19 @@
         <v>General</v>
       </c>
       <c r="G1082" t="str">
-        <v>63MM</v>
+        <v>160MM 4KG</v>
       </c>
       <c r="H1082" t="str">
         <v>BOX</v>
       </c>
       <c r="I1082">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="J1082" t="str">
         <v>Active</v>
       </c>
       <c r="K1082" t="str">
-        <v>AGRI LONG BEND for agriculture irrigation and piping systems. Available sizes: 63MM, 75MM, 90MM, 110MM.</v>
+        <v>AGRI END CAP for agriculture irrigation and piping systems. Available sizes: 40MM, 50MM, 63MM, 75MM, 90MM, 110MM, 140MM 4KG, 160MM 4KG.</v>
       </c>
     </row>
     <row r="1083">
@@ -38287,10 +38287,10 @@
         <v>1082</v>
       </c>
       <c r="B1083" t="str">
-        <v>FG-400571</v>
+        <v>FG-400570</v>
       </c>
       <c r="C1083" t="str">
-        <v>AGRI LONG BEND (75MM)</v>
+        <v>AGRI LONG BEND (63MM)</v>
       </c>
       <c r="D1083" t="str">
         <v>AGRI LONG BEND</v>
@@ -38302,13 +38302,13 @@
         <v>General</v>
       </c>
       <c r="G1083" t="str">
-        <v>75MM</v>
+        <v>63MM</v>
       </c>
       <c r="H1083" t="str">
         <v>BOX</v>
       </c>
       <c r="I1083">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J1083" t="str">
         <v>Active</v>
@@ -38322,10 +38322,10 @@
         <v>1083</v>
       </c>
       <c r="B1084" t="str">
-        <v>FG-400572</v>
+        <v>FG-400571</v>
       </c>
       <c r="C1084" t="str">
-        <v>AGRI LONG BEND (90MM)</v>
+        <v>AGRI LONG BEND (75MM)</v>
       </c>
       <c r="D1084" t="str">
         <v>AGRI LONG BEND</v>
@@ -38337,13 +38337,13 @@
         <v>General</v>
       </c>
       <c r="G1084" t="str">
-        <v>90MM</v>
+        <v>75MM</v>
       </c>
       <c r="H1084" t="str">
         <v>BOX</v>
       </c>
       <c r="I1084">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J1084" t="str">
         <v>Active</v>
@@ -38357,10 +38357,10 @@
         <v>1084</v>
       </c>
       <c r="B1085" t="str">
-        <v>FG-400573</v>
+        <v>FG-400572</v>
       </c>
       <c r="C1085" t="str">
-        <v>AGRI LONG BEND (110MM)</v>
+        <v>AGRI LONG BEND (90MM)</v>
       </c>
       <c r="D1085" t="str">
         <v>AGRI LONG BEND</v>
@@ -38372,13 +38372,13 @@
         <v>General</v>
       </c>
       <c r="G1085" t="str">
-        <v>110MM</v>
+        <v>90MM</v>
       </c>
       <c r="H1085" t="str">
         <v>BOX</v>
       </c>
       <c r="I1085">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J1085" t="str">
         <v>Active</v>
@@ -38392,34 +38392,34 @@
         <v>1085</v>
       </c>
       <c r="B1086" t="str">
-        <v>FG-401520</v>
+        <v>FG-400573</v>
       </c>
       <c r="C1086" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
+        <v>AGRI LONG BEND (110MM)</v>
       </c>
       <c r="D1086" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR</v>
+        <v>AGRI LONG BEND</v>
       </c>
       <c r="E1086" t="str">
-        <v>Sprinkler Pipes &amp; Fittings</v>
+        <v>Agriculture Pipes &amp; Fittings</v>
       </c>
       <c r="F1086" t="str">
         <v>General</v>
       </c>
       <c r="G1086" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>110MM</v>
       </c>
       <c r="H1086" t="str">
-        <v>Nos</v>
-      </c>
-      <c r="I1086" t="str">
-        <v>-</v>
+        <v>BOX</v>
+      </c>
+      <c r="I1086">
+        <v>10</v>
       </c>
       <c r="J1086" t="str">
         <v>Active</v>
       </c>
       <c r="K1086" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR for sprinkler irrigation systems.</v>
+        <v>AGRI LONG BEND for agriculture irrigation and piping systems. Available sizes: 63MM, 75MM, 90MM, 110MM.</v>
       </c>
     </row>
     <row r="1087">
@@ -38427,10 +38427,10 @@
         <v>1086</v>
       </c>
       <c r="B1087" t="str">
-        <v>FG-401491</v>
+        <v>FG-401520</v>
       </c>
       <c r="C1087" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (63MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1087" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38442,7 +38442,7 @@
         <v>General</v>
       </c>
       <c r="G1087" t="str">
-        <v>63MM L TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1087" t="str">
         <v>Nos</v>
@@ -38462,10 +38462,10 @@
         <v>1087</v>
       </c>
       <c r="B1088" t="str">
-        <v>FG-401490</v>
+        <v>FG-401491</v>
       </c>
       <c r="C1088" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 2.5 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (63MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1088" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38477,7 +38477,7 @@
         <v>General</v>
       </c>
       <c r="G1088" t="str">
-        <v>75MM C TYPE 2.5 KG</v>
+        <v>63MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1088" t="str">
         <v>Nos</v>
@@ -38497,10 +38497,10 @@
         <v>1088</v>
       </c>
       <c r="B1089" t="str">
-        <v>FG-401492</v>
+        <v>FG-401490</v>
       </c>
       <c r="C1089" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 2.5 KG)</v>
       </c>
       <c r="D1089" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38512,7 +38512,7 @@
         <v>General</v>
       </c>
       <c r="G1089" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>75MM C TYPE 2.5 KG</v>
       </c>
       <c r="H1089" t="str">
         <v>Nos</v>
@@ -38532,10 +38532,10 @@
         <v>1089</v>
       </c>
       <c r="B1090" t="str">
-        <v>FG-401519</v>
+        <v>FG-401492</v>
       </c>
       <c r="C1090" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 2.5 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1090" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38547,7 +38547,7 @@
         <v>General</v>
       </c>
       <c r="G1090" t="str">
-        <v>75MM L TYPE 2.5 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1090" t="str">
         <v>Nos</v>
@@ -38567,10 +38567,10 @@
         <v>1090</v>
       </c>
       <c r="B1091" t="str">
-        <v>FG-401521</v>
+        <v>FG-401519</v>
       </c>
       <c r="C1091" t="str">
-        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM L TYPE 2.5 KG)</v>
       </c>
       <c r="D1091" t="str">
         <v>SPRINKLER ISI PIPE 6 MTR</v>
@@ -38582,7 +38582,7 @@
         <v>General</v>
       </c>
       <c r="G1091" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 2.5 KG</v>
       </c>
       <c r="H1091" t="str">
         <v>Nos</v>
@@ -38602,13 +38602,13 @@
         <v>1091</v>
       </c>
       <c r="B1092" t="str">
-        <v>FG-401522</v>
+        <v>FG-401521</v>
       </c>
       <c r="C1092" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER ISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1092" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR</v>
+        <v>SPRINKLER ISI PIPE 6 MTR</v>
       </c>
       <c r="E1092" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38629,7 +38629,7 @@
         <v>Active</v>
       </c>
       <c r="K1092" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER ISI PIPE 6 MTR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1093">
@@ -38637,10 +38637,10 @@
         <v>1092</v>
       </c>
       <c r="B1093" t="str">
-        <v>FG-401523</v>
+        <v>FG-401522</v>
       </c>
       <c r="C1093" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1093" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38652,7 +38652,7 @@
         <v>General</v>
       </c>
       <c r="G1093" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1093" t="str">
         <v>Nos</v>
@@ -38672,10 +38672,10 @@
         <v>1093</v>
       </c>
       <c r="B1094" t="str">
-        <v>FG-401866</v>
+        <v>FG-401523</v>
       </c>
       <c r="C1094" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (90MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1094" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38687,7 +38687,7 @@
         <v>General</v>
       </c>
       <c r="G1094" t="str">
-        <v>90MM C TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1094" t="str">
         <v>Nos</v>
@@ -38707,10 +38707,10 @@
         <v>1094</v>
       </c>
       <c r="B1095" t="str">
-        <v>FG-401867</v>
+        <v>FG-401866</v>
       </c>
       <c r="C1095" t="str">
-        <v>SPRINKLER NISI PIPE 6 MTR (90MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (90MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1095" t="str">
         <v>SPRINKLER NISI PIPE 6 MTR</v>
@@ -38722,7 +38722,7 @@
         <v>General</v>
       </c>
       <c r="G1095" t="str">
-        <v>90MM L TYPE 3.2 KG</v>
+        <v>90MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1095" t="str">
         <v>Nos</v>
@@ -38742,13 +38742,13 @@
         <v>1095</v>
       </c>
       <c r="B1096" t="str">
-        <v>FG-401498</v>
+        <v>FG-401867</v>
       </c>
       <c r="C1096" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER NISI PIPE 6 MTR (90MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1096" t="str">
-        <v>SPRINKLER SET 6 MTR ISI</v>
+        <v>SPRINKLER NISI PIPE 6 MTR</v>
       </c>
       <c r="E1096" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38757,7 +38757,7 @@
         <v>General</v>
       </c>
       <c r="G1096" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>90MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1096" t="str">
         <v>Nos</v>
@@ -38769,7 +38769,7 @@
         <v>Active</v>
       </c>
       <c r="K1096" t="str">
-        <v>SPRINKLER SET 6 MTR ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER NISI PIPE 6 MTR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1097">
@@ -38777,10 +38777,10 @@
         <v>1096</v>
       </c>
       <c r="B1097" t="str">
-        <v>FG-401499</v>
+        <v>FG-401498</v>
       </c>
       <c r="C1097" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1097" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38792,7 +38792,7 @@
         <v>General</v>
       </c>
       <c r="G1097" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1097" t="str">
         <v>Nos</v>
@@ -38812,10 +38812,10 @@
         <v>1097</v>
       </c>
       <c r="B1098" t="str">
-        <v>FG-401500</v>
+        <v>FG-401499</v>
       </c>
       <c r="C1098" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 2.5 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1098" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38827,7 +38827,7 @@
         <v>General</v>
       </c>
       <c r="G1098" t="str">
-        <v>75MM C TYPE 2.5 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1098" t="str">
         <v>Nos</v>
@@ -38847,10 +38847,10 @@
         <v>1098</v>
       </c>
       <c r="B1099" t="str">
-        <v>FG-401524</v>
+        <v>FG-401500</v>
       </c>
       <c r="C1099" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 2.5 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM C TYPE 2.5 KG)</v>
       </c>
       <c r="D1099" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38862,7 +38862,7 @@
         <v>General</v>
       </c>
       <c r="G1099" t="str">
-        <v>75MM L TYPE 2.5 KG</v>
+        <v>75MM C TYPE 2.5 KG</v>
       </c>
       <c r="H1099" t="str">
         <v>Nos</v>
@@ -38882,10 +38882,10 @@
         <v>1099</v>
       </c>
       <c r="B1100" t="str">
-        <v>FG-401501</v>
+        <v>FG-401524</v>
       </c>
       <c r="C1100" t="str">
-        <v>SPRINKLER SET 6 MTR ISI (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (75MM L TYPE 2.5 KG)</v>
       </c>
       <c r="D1100" t="str">
         <v>SPRINKLER SET 6 MTR ISI</v>
@@ -38897,7 +38897,7 @@
         <v>General</v>
       </c>
       <c r="G1100" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 2.5 KG</v>
       </c>
       <c r="H1100" t="str">
         <v>Nos</v>
@@ -38917,13 +38917,13 @@
         <v>1100</v>
       </c>
       <c r="B1101" t="str">
-        <v>FG-401495</v>
+        <v>FG-401501</v>
       </c>
       <c r="C1101" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (75MM L TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR ISI (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1101" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI</v>
+        <v>SPRINKLER SET 6 MTR ISI</v>
       </c>
       <c r="E1101" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -38932,7 +38932,7 @@
         <v>General</v>
       </c>
       <c r="G1101" t="str">
-        <v>75MM L TYPE 3.2 KG</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1101" t="str">
         <v>Nos</v>
@@ -38944,7 +38944,7 @@
         <v>Active</v>
       </c>
       <c r="K1101" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI for sprinkler irrigation systems.</v>
+        <v>SPRINKLER SET 6 MTR ISI for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1102">
@@ -38952,10 +38952,10 @@
         <v>1101</v>
       </c>
       <c r="B1102" t="str">
-        <v>FG-401496</v>
+        <v>FG-401495</v>
       </c>
       <c r="C1102" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (75MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (75MM L TYPE 3.2 KG)</v>
       </c>
       <c r="D1102" t="str">
         <v>SPRINKLER SET 6 MTR N-ISI</v>
@@ -38967,7 +38967,7 @@
         <v>General</v>
       </c>
       <c r="G1102" t="str">
-        <v>75MM C TYPE 3.2 KG</v>
+        <v>75MM L TYPE 3.2 KG</v>
       </c>
       <c r="H1102" t="str">
         <v>Nos</v>
@@ -38987,10 +38987,10 @@
         <v>1102</v>
       </c>
       <c r="B1103" t="str">
-        <v>FG-401497</v>
+        <v>FG-401496</v>
       </c>
       <c r="C1103" t="str">
-        <v>SPRINKLER SET 6 MTR N-ISI (63MM C TYPE 3.2 KG)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (75MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1103" t="str">
         <v>SPRINKLER SET 6 MTR N-ISI</v>
@@ -39002,7 +39002,7 @@
         <v>General</v>
       </c>
       <c r="G1103" t="str">
-        <v>63MM C TYPE 3.2 KG</v>
+        <v>75MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1103" t="str">
         <v>Nos</v>
@@ -39022,13 +39022,13 @@
         <v>1103</v>
       </c>
       <c r="B1104" t="str">
-        <v>FG-401503</v>
+        <v>FG-401497</v>
       </c>
       <c r="C1104" t="str">
-        <v>SPRINKLER FITTINGS TEE (75MM, C TYPE)</v>
+        <v>SPRINKLER SET 6 MTR N-ISI (63MM C TYPE 3.2 KG)</v>
       </c>
       <c r="D1104" t="str">
-        <v>SPRINKLER FITTINGS TEE</v>
+        <v>SPRINKLER SET 6 MTR N-ISI</v>
       </c>
       <c r="E1104" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39037,7 +39037,7 @@
         <v>General</v>
       </c>
       <c r="G1104" t="str">
-        <v>75MM, C TYPE</v>
+        <v>63MM C TYPE 3.2 KG</v>
       </c>
       <c r="H1104" t="str">
         <v>Nos</v>
@@ -39049,7 +39049,7 @@
         <v>Active</v>
       </c>
       <c r="K1104" t="str">
-        <v>SPRINKLER FITTINGS TEE for sprinkler irrigation systems. Available sizes: 75MM, C TYPE, 75MM, L TYPE, 63MM, C TYPE.</v>
+        <v>SPRINKLER SET 6 MTR N-ISI for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1105">
@@ -39057,10 +39057,10 @@
         <v>1104</v>
       </c>
       <c r="B1105" t="str">
-        <v>FG-401511</v>
+        <v>FG-401503</v>
       </c>
       <c r="C1105" t="str">
-        <v>SPRINKLER FITTINGS TEE (75MM, L TYPE)</v>
+        <v>SPRINKLER FITTINGS TEE (75MM, C TYPE)</v>
       </c>
       <c r="D1105" t="str">
         <v>SPRINKLER FITTINGS TEE</v>
@@ -39072,7 +39072,7 @@
         <v>General</v>
       </c>
       <c r="G1105" t="str">
-        <v>75MM, L TYPE</v>
+        <v>75MM, C TYPE</v>
       </c>
       <c r="H1105" t="str">
         <v>Nos</v>
@@ -39092,10 +39092,10 @@
         <v>1105</v>
       </c>
       <c r="B1106" t="str">
-        <v>FG-401526</v>
+        <v>FG-401511</v>
       </c>
       <c r="C1106" t="str">
-        <v>SPRINKLER FITTINGS TEE (63MM, C TYPE)</v>
+        <v>SPRINKLER FITTINGS TEE (75MM, L TYPE)</v>
       </c>
       <c r="D1106" t="str">
         <v>SPRINKLER FITTINGS TEE</v>
@@ -39107,7 +39107,7 @@
         <v>General</v>
       </c>
       <c r="G1106" t="str">
-        <v>63MM, C TYPE</v>
+        <v>75MM, L TYPE</v>
       </c>
       <c r="H1106" t="str">
         <v>Nos</v>
@@ -39127,13 +39127,13 @@
         <v>1106</v>
       </c>
       <c r="B1107" t="str">
-        <v>FG-401504</v>
+        <v>FG-401526</v>
       </c>
       <c r="C1107" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS TEE (63MM, C TYPE)</v>
       </c>
       <c r="D1107" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR</v>
+        <v>SPRINKLER FITTINGS TEE</v>
       </c>
       <c r="E1107" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39142,7 +39142,7 @@
         <v>General</v>
       </c>
       <c r="G1107" t="str">
-        <v>75MM C TYPE</v>
+        <v>63MM, C TYPE</v>
       </c>
       <c r="H1107" t="str">
         <v>Nos</v>
@@ -39154,7 +39154,7 @@
         <v>Active</v>
       </c>
       <c r="K1107" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS TEE for sprinkler irrigation systems. Available sizes: 75MM, C TYPE, 75MM, L TYPE, 63MM, C TYPE.</v>
       </c>
     </row>
     <row r="1108">
@@ -39162,10 +39162,10 @@
         <v>1107</v>
       </c>
       <c r="B1108" t="str">
-        <v>FG-401512</v>
+        <v>FG-401504</v>
       </c>
       <c r="C1108" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (75MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (75MM C TYPE)</v>
       </c>
       <c r="D1108" t="str">
         <v>SPRINKLER FITTINGS ADAPTOR</v>
@@ -39177,7 +39177,7 @@
         <v>General</v>
       </c>
       <c r="G1108" t="str">
-        <v>75MM P TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1108" t="str">
         <v>Nos</v>
@@ -39197,10 +39197,10 @@
         <v>1108</v>
       </c>
       <c r="B1109" t="str">
-        <v>FG-401527</v>
+        <v>FG-401512</v>
       </c>
       <c r="C1109" t="str">
-        <v>SPRINKLER FITTINGS ADAPTOR (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (75MM P TYPE)</v>
       </c>
       <c r="D1109" t="str">
         <v>SPRINKLER FITTINGS ADAPTOR</v>
@@ -39212,7 +39212,7 @@
         <v>General</v>
       </c>
       <c r="G1109" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM P TYPE</v>
       </c>
       <c r="H1109" t="str">
         <v>Nos</v>
@@ -39232,13 +39232,13 @@
         <v>1109</v>
       </c>
       <c r="B1110" t="str">
-        <v>FG-401502</v>
+        <v>FG-401527</v>
       </c>
       <c r="C1110" t="str">
-        <v>SPRINKLER FITTINGS BEND (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS ADAPTOR (63MM C TYPE)</v>
       </c>
       <c r="D1110" t="str">
-        <v>SPRINKLER FITTINGS BEND</v>
+        <v>SPRINKLER FITTINGS ADAPTOR</v>
       </c>
       <c r="E1110" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39247,7 +39247,7 @@
         <v>General</v>
       </c>
       <c r="G1110" t="str">
-        <v>75MM C TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1110" t="str">
         <v>Nos</v>
@@ -39259,7 +39259,7 @@
         <v>Active</v>
       </c>
       <c r="K1110" t="str">
-        <v>SPRINKLER FITTINGS BEND for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS ADAPTOR for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1111">
@@ -39267,10 +39267,10 @@
         <v>1110</v>
       </c>
       <c r="B1111" t="str">
-        <v>FG-401510</v>
+        <v>FG-401502</v>
       </c>
       <c r="C1111" t="str">
-        <v>SPRINKLER FITTINGS BEND (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (75MM C TYPE)</v>
       </c>
       <c r="D1111" t="str">
         <v>SPRINKLER FITTINGS BEND</v>
@@ -39282,7 +39282,7 @@
         <v>General</v>
       </c>
       <c r="G1111" t="str">
-        <v>75MM L TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1111" t="str">
         <v>Nos</v>
@@ -39302,10 +39302,10 @@
         <v>1111</v>
       </c>
       <c r="B1112" t="str">
-        <v>FG-401525</v>
+        <v>FG-401510</v>
       </c>
       <c r="C1112" t="str">
-        <v>SPRINKLER FITTINGS BEND (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (75MM L TYPE)</v>
       </c>
       <c r="D1112" t="str">
         <v>SPRINKLER FITTINGS BEND</v>
@@ -39317,7 +39317,7 @@
         <v>General</v>
       </c>
       <c r="G1112" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1112" t="str">
         <v>Nos</v>
@@ -39337,13 +39337,13 @@
         <v>1112</v>
       </c>
       <c r="B1113" t="str">
-        <v>FG-401514</v>
+        <v>FG-401525</v>
       </c>
       <c r="C1113" t="str">
-        <v>SPRINKLER FITTINGS END CAP (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS BEND (63MM C TYPE)</v>
       </c>
       <c r="D1113" t="str">
-        <v>SPRINKLER FITTINGS END CAP</v>
+        <v>SPRINKLER FITTINGS BEND</v>
       </c>
       <c r="E1113" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39352,7 +39352,7 @@
         <v>General</v>
       </c>
       <c r="G1113" t="str">
-        <v>75MM L TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1113" t="str">
         <v>Nos</v>
@@ -39364,7 +39364,7 @@
         <v>Active</v>
       </c>
       <c r="K1113" t="str">
-        <v>SPRINKLER FITTINGS END CAP for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS BEND for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1114">
@@ -39372,10 +39372,10 @@
         <v>1113</v>
       </c>
       <c r="B1114" t="str">
-        <v>FG-401506</v>
+        <v>FG-401514</v>
       </c>
       <c r="C1114" t="str">
-        <v>SPRINKLER FITTINGS END CAP (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (75MM L TYPE)</v>
       </c>
       <c r="D1114" t="str">
         <v>SPRINKLER FITTINGS END CAP</v>
@@ -39387,7 +39387,7 @@
         <v>General</v>
       </c>
       <c r="G1114" t="str">
-        <v>75MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1114" t="str">
         <v>Nos</v>
@@ -39407,10 +39407,10 @@
         <v>1114</v>
       </c>
       <c r="B1115" t="str">
-        <v>FG-401529</v>
+        <v>FG-401506</v>
       </c>
       <c r="C1115" t="str">
-        <v>SPRINKLER FITTINGS END CAP (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (75MM C TYPE)</v>
       </c>
       <c r="D1115" t="str">
         <v>SPRINKLER FITTINGS END CAP</v>
@@ -39422,7 +39422,7 @@
         <v>General</v>
       </c>
       <c r="G1115" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1115" t="str">
         <v>Nos</v>
@@ -39442,13 +39442,13 @@
         <v>1115</v>
       </c>
       <c r="B1116" t="str">
-        <v>FG-401517</v>
+        <v>FG-401529</v>
       </c>
       <c r="C1116" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (75MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS END CAP (63MM C TYPE)</v>
       </c>
       <c r="D1116" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
+        <v>SPRINKLER FITTINGS END CAP</v>
       </c>
       <c r="E1116" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39457,7 +39457,7 @@
         <v>General</v>
       </c>
       <c r="G1116" t="str">
-        <v>75MM P TYPE</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1116" t="str">
         <v>Nos</v>
@@ -39469,7 +39469,7 @@
         <v>Active</v>
       </c>
       <c r="K1116" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS END CAP for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1117">
@@ -39477,10 +39477,10 @@
         <v>1116</v>
       </c>
       <c r="B1117" t="str">
-        <v>FG-401518</v>
+        <v>FG-401517</v>
       </c>
       <c r="C1117" t="str">
-        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (63MM P TYPE)</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (75MM P TYPE)</v>
       </c>
       <c r="D1117" t="str">
         <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
@@ -39492,7 +39492,7 @@
         <v>General</v>
       </c>
       <c r="G1117" t="str">
-        <v>63MM P TYPE</v>
+        <v>75MM P TYPE</v>
       </c>
       <c r="H1117" t="str">
         <v>Nos</v>
@@ -39512,13 +39512,13 @@
         <v>1117</v>
       </c>
       <c r="B1118" t="str">
-        <v>FG-401505</v>
+        <v>FG-401518</v>
       </c>
       <c r="C1118" t="str">
-        <v>SPRINKLER FITTINGS PCN (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP (63MM P TYPE)</v>
       </c>
       <c r="D1118" t="str">
-        <v>SPRINKLER FITTINGS PCN</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP</v>
       </c>
       <c r="E1118" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39527,7 +39527,7 @@
         <v>General</v>
       </c>
       <c r="G1118" t="str">
-        <v>75MM C TYPE</v>
+        <v>63MM P TYPE</v>
       </c>
       <c r="H1118" t="str">
         <v>Nos</v>
@@ -39539,7 +39539,7 @@
         <v>Active</v>
       </c>
       <c r="K1118" t="str">
-        <v>SPRINKLER FITTINGS PCN for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS LATCH &amp; CLAMP for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1119">
@@ -39547,10 +39547,10 @@
         <v>1118</v>
       </c>
       <c r="B1119" t="str">
-        <v>FG-401513</v>
+        <v>FG-401505</v>
       </c>
       <c r="C1119" t="str">
-        <v>SPRINKLER FITTINGS PCN (75MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (75MM C TYPE)</v>
       </c>
       <c r="D1119" t="str">
         <v>SPRINKLER FITTINGS PCN</v>
@@ -39562,7 +39562,7 @@
         <v>General</v>
       </c>
       <c r="G1119" t="str">
-        <v>75MM L TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1119" t="str">
         <v>Nos</v>
@@ -39582,10 +39582,10 @@
         <v>1119</v>
       </c>
       <c r="B1120" t="str">
-        <v>FG-401528</v>
+        <v>FG-401513</v>
       </c>
       <c r="C1120" t="str">
-        <v>SPRINKLER FITTINGS PCN (63MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS PCN (75MM L TYPE)</v>
       </c>
       <c r="D1120" t="str">
         <v>SPRINKLER FITTINGS PCN</v>
@@ -39597,7 +39597,7 @@
         <v>General</v>
       </c>
       <c r="G1120" t="str">
-        <v>63MM C TYPE</v>
+        <v>75MM L TYPE</v>
       </c>
       <c r="H1120" t="str">
         <v>Nos</v>
@@ -39617,13 +39617,13 @@
         <v>1120</v>
       </c>
       <c r="B1121" t="str">
-        <v>FG-401507</v>
+        <v>FG-401528</v>
       </c>
       <c r="C1121" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL (20MM)</v>
+        <v>SPRINKLER FITTINGS PCN (63MM C TYPE)</v>
       </c>
       <c r="D1121" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL</v>
+        <v>SPRINKLER FITTINGS PCN</v>
       </c>
       <c r="E1121" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39632,7 +39632,7 @@
         <v>General</v>
       </c>
       <c r="G1121" t="str">
-        <v>20MM</v>
+        <v>63MM C TYPE</v>
       </c>
       <c r="H1121" t="str">
         <v>Nos</v>
@@ -39644,7 +39644,7 @@
         <v>Active</v>
       </c>
       <c r="K1121" t="str">
-        <v>SPRINKLER FITTINGS NOZZELGUN METAL for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS PCN for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1122">
@@ -39652,13 +39652,13 @@
         <v>1121</v>
       </c>
       <c r="B1122" t="str">
-        <v>FG-401508</v>
+        <v>FG-401507</v>
       </c>
       <c r="C1122" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE (75MM C TYPE)</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL (20MM)</v>
       </c>
       <c r="D1122" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL</v>
       </c>
       <c r="E1122" t="str">
         <v>Sprinkler Pipes &amp; Fittings</v>
@@ -39667,7 +39667,7 @@
         <v>General</v>
       </c>
       <c r="G1122" t="str">
-        <v>75MM C TYPE</v>
+        <v>20MM</v>
       </c>
       <c r="H1122" t="str">
         <v>Nos</v>
@@ -39679,7 +39679,7 @@
         <v>Active</v>
       </c>
       <c r="K1122" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE for sprinkler irrigation systems.</v>
+        <v>SPRINKLER FITTINGS NOZZELGUN METAL for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1123">
@@ -39687,10 +39687,10 @@
         <v>1122</v>
       </c>
       <c r="B1123" t="str">
-        <v>FG-401515</v>
+        <v>FG-401508</v>
       </c>
       <c r="C1123" t="str">
-        <v>SPRINKLER FITTINGS GI RISER PIPE (20MM L TYPE)</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE (75MM C TYPE)</v>
       </c>
       <c r="D1123" t="str">
         <v>SPRINKLER FITTINGS GI RISER PIPE</v>
@@ -39702,7 +39702,7 @@
         <v>General</v>
       </c>
       <c r="G1123" t="str">
-        <v>20MM L TYPE</v>
+        <v>75MM C TYPE</v>
       </c>
       <c r="H1123" t="str">
         <v>Nos</v>
@@ -39722,25 +39722,25 @@
         <v>1123</v>
       </c>
       <c r="B1124" t="str">
-        <v>FG-401742</v>
+        <v>FG-401515</v>
       </c>
       <c r="C1124" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 1)</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE (20MM L TYPE)</v>
       </c>
       <c r="D1124" t="str">
-        <v>ROUND DRIPLINE 12MM ISI</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE</v>
       </c>
       <c r="E1124" t="str">
-        <v>DRIP IRRIGATION SYSTEM</v>
+        <v>Sprinkler Pipes &amp; Fittings</v>
       </c>
       <c r="F1124" t="str">
-        <v>ROUND DRIP ISI</v>
+        <v>General</v>
       </c>
       <c r="G1124" t="str">
-        <v>12-4-30 CLASS 1</v>
+        <v>20MM L TYPE</v>
       </c>
       <c r="H1124" t="str">
-        <v>ROLL</v>
+        <v>Nos</v>
       </c>
       <c r="I1124" t="str">
         <v>-</v>
@@ -39749,7 +39749,7 @@
         <v>Active</v>
       </c>
       <c r="K1124" t="str">
-        <v>ROUND DRIPLINE 12MM ISI certified.</v>
+        <v>SPRINKLER FITTINGS GI RISER PIPE for sprinkler irrigation systems.</v>
       </c>
     </row>
     <row r="1125">
@@ -39757,10 +39757,10 @@
         <v>1124</v>
       </c>
       <c r="B1125" t="str">
-        <v>FG-401743</v>
+        <v>FG-401742</v>
       </c>
       <c r="C1125" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 1)</v>
       </c>
       <c r="D1125" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39772,7 +39772,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1125" t="str">
-        <v>12-4-40 CLASS 1</v>
+        <v>12-4-30 CLASS 1</v>
       </c>
       <c r="H1125" t="str">
         <v>ROLL</v>
@@ -39792,10 +39792,10 @@
         <v>1125</v>
       </c>
       <c r="B1126" t="str">
-        <v>FG-401744</v>
+        <v>FG-401743</v>
       </c>
       <c r="C1126" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 1)</v>
       </c>
       <c r="D1126" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39807,7 +39807,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1126" t="str">
-        <v>12-4-50 CLASS 1</v>
+        <v>12-4-40 CLASS 1</v>
       </c>
       <c r="H1126" t="str">
         <v>ROLL</v>
@@ -39827,10 +39827,10 @@
         <v>1126</v>
       </c>
       <c r="B1127" t="str">
-        <v>FG-401751</v>
+        <v>FG-401744</v>
       </c>
       <c r="C1127" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 1)</v>
       </c>
       <c r="D1127" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39842,7 +39842,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1127" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-50 CLASS 1</v>
       </c>
       <c r="H1127" t="str">
         <v>ROLL</v>
@@ -39862,10 +39862,10 @@
         <v>1127</v>
       </c>
       <c r="B1128" t="str">
-        <v>FG-401752</v>
+        <v>FG-401751</v>
       </c>
       <c r="C1128" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1128" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39877,7 +39877,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1128" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1128" t="str">
         <v>ROLL</v>
@@ -39897,10 +39897,10 @@
         <v>1128</v>
       </c>
       <c r="B1129" t="str">
-        <v>FG-401753</v>
+        <v>FG-401752</v>
       </c>
       <c r="C1129" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1129" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39912,7 +39912,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1129" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1129" t="str">
         <v>ROLL</v>
@@ -39932,10 +39932,10 @@
         <v>1129</v>
       </c>
       <c r="B1130" t="str">
-        <v>FG-401754</v>
+        <v>FG-401753</v>
       </c>
       <c r="C1130" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1130" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39947,7 +39947,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1130" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1130" t="str">
         <v>ROLL</v>
@@ -39967,10 +39967,10 @@
         <v>1130</v>
       </c>
       <c r="B1131" t="str">
-        <v>FG-401755</v>
+        <v>FG-401754</v>
       </c>
       <c r="C1131" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1131" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -39982,7 +39982,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1131" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1131" t="str">
         <v>ROLL</v>
@@ -40002,10 +40002,10 @@
         <v>1131</v>
       </c>
       <c r="B1132" t="str">
-        <v>FG-401756</v>
+        <v>FG-401755</v>
       </c>
       <c r="C1132" t="str">
-        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1132" t="str">
         <v>ROUND DRIPLINE 12MM ISI</v>
@@ -40017,7 +40017,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1132" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1132" t="str">
         <v>ROLL</v>
@@ -40037,13 +40037,13 @@
         <v>1132</v>
       </c>
       <c r="B1133" t="str">
-        <v>FG-401745</v>
+        <v>FG-401756</v>
       </c>
       <c r="C1133" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
+        <v>ROUND DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1133" t="str">
-        <v>ROUND DRIPLINE 16MM ISI</v>
+        <v>ROUND DRIPLINE 12MM ISI</v>
       </c>
       <c r="E1133" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40052,7 +40052,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1133" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1133" t="str">
         <v>ROLL</v>
@@ -40064,7 +40064,7 @@
         <v>Active</v>
       </c>
       <c r="K1133" t="str">
-        <v>ROUND DRIPLINE 16MM ISI certified.</v>
+        <v>ROUND DRIPLINE 12MM ISI certified.</v>
       </c>
     </row>
     <row r="1134">
@@ -40072,10 +40072,10 @@
         <v>1133</v>
       </c>
       <c r="B1134" t="str">
-        <v>FG-401746</v>
+        <v>FG-401745</v>
       </c>
       <c r="C1134" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1134" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40087,7 +40087,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1134" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1134" t="str">
         <v>ROLL</v>
@@ -40107,10 +40107,10 @@
         <v>1134</v>
       </c>
       <c r="B1135" t="str">
-        <v>FG-401747</v>
+        <v>FG-401746</v>
       </c>
       <c r="C1135" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1135" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40122,7 +40122,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1135" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1135" t="str">
         <v>ROLL</v>
@@ -40142,10 +40142,10 @@
         <v>1135</v>
       </c>
       <c r="B1136" t="str">
-        <v>FG-401757</v>
+        <v>FG-401747</v>
       </c>
       <c r="C1136" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1136" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40157,7 +40157,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1136" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1136" t="str">
         <v>ROLL</v>
@@ -40177,10 +40177,10 @@
         <v>1136</v>
       </c>
       <c r="B1137" t="str">
-        <v>FG-401758</v>
+        <v>FG-401757</v>
       </c>
       <c r="C1137" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1137" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40192,7 +40192,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1137" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1137" t="str">
         <v>ROLL</v>
@@ -40212,10 +40212,10 @@
         <v>1137</v>
       </c>
       <c r="B1138" t="str">
-        <v>FG-401759</v>
+        <v>FG-401758</v>
       </c>
       <c r="C1138" t="str">
-        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1138" t="str">
         <v>ROUND DRIPLINE 16MM ISI</v>
@@ -40227,7 +40227,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1138" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1138" t="str">
         <v>ROLL</v>
@@ -40247,13 +40247,13 @@
         <v>1138</v>
       </c>
       <c r="B1139" t="str">
-        <v>-</v>
+        <v>FG-401759</v>
       </c>
       <c r="C1139" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-30 CLASS-1)</v>
+        <v>ROUND DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1139" t="str">
-        <v>20MM ROUND INLINE PIPE ISI</v>
+        <v>ROUND DRIPLINE 16MM ISI</v>
       </c>
       <c r="E1139" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40262,10 +40262,10 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1139" t="str">
-        <v>20-4-30 CLASS-1</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1139" t="str">
-        <v>MTR</v>
+        <v>ROLL</v>
       </c>
       <c r="I1139" t="str">
         <v>-</v>
@@ -40274,7 +40274,7 @@
         <v>Active</v>
       </c>
       <c r="K1139" t="str">
-        <v>20mm Round Inline Drip Pipe ISI certified.</v>
+        <v>ROUND DRIPLINE 16MM ISI certified.</v>
       </c>
     </row>
     <row r="1140">
@@ -40285,7 +40285,7 @@
         <v>-</v>
       </c>
       <c r="C1140" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-40 CLASS-1)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-30 CLASS-1)</v>
       </c>
       <c r="D1140" t="str">
         <v>20MM ROUND INLINE PIPE ISI</v>
@@ -40297,7 +40297,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1140" t="str">
-        <v>20-4-40 CLASS-1</v>
+        <v>20-4-30 CLASS-1</v>
       </c>
       <c r="H1140" t="str">
         <v>MTR</v>
@@ -40320,7 +40320,7 @@
         <v>-</v>
       </c>
       <c r="C1141" t="str">
-        <v>20MM ROUND INLINE PIPE ISI (20-4-50 CLASS-1)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-40 CLASS-1)</v>
       </c>
       <c r="D1141" t="str">
         <v>20MM ROUND INLINE PIPE ISI</v>
@@ -40332,7 +40332,7 @@
         <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1141" t="str">
-        <v>20-4-50 CLASS-1</v>
+        <v>20-4-40 CLASS-1</v>
       </c>
       <c r="H1141" t="str">
         <v>MTR</v>
@@ -40352,25 +40352,25 @@
         <v>1141</v>
       </c>
       <c r="B1142" t="str">
-        <v>FG-401763</v>
+        <v>-</v>
       </c>
       <c r="C1142" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
+        <v>20MM ROUND INLINE PIPE ISI (20-4-50 CLASS-1)</v>
       </c>
       <c r="D1142" t="str">
-        <v>FLAT DRIPLINE 12MM ISI</v>
+        <v>20MM ROUND INLINE PIPE ISI</v>
       </c>
       <c r="E1142" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1142" t="str">
-        <v>FLAT DRIP ISI</v>
+        <v>ROUND DRIP ISI</v>
       </c>
       <c r="G1142" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>20-4-50 CLASS-1</v>
       </c>
       <c r="H1142" t="str">
-        <v>ROLL</v>
+        <v>MTR</v>
       </c>
       <c r="I1142" t="str">
         <v>-</v>
@@ -40379,7 +40379,7 @@
         <v>Active</v>
       </c>
       <c r="K1142" t="str">
-        <v>FLAT DRIPLINE 12MM ISI certified.</v>
+        <v>20mm Round Inline Drip Pipe ISI certified.</v>
       </c>
     </row>
     <row r="1143">
@@ -40387,10 +40387,10 @@
         <v>1142</v>
       </c>
       <c r="B1143" t="str">
-        <v>FG-401764</v>
+        <v>FG-401763</v>
       </c>
       <c r="C1143" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1143" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40402,7 +40402,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1143" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1143" t="str">
         <v>ROLL</v>
@@ -40422,10 +40422,10 @@
         <v>1143</v>
       </c>
       <c r="B1144" t="str">
-        <v>FG-401765</v>
+        <v>FG-401764</v>
       </c>
       <c r="C1144" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1144" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40437,7 +40437,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1144" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1144" t="str">
         <v>ROLL</v>
@@ -40457,10 +40457,10 @@
         <v>1144</v>
       </c>
       <c r="B1145" t="str">
-        <v>FG-401766</v>
+        <v>FG-401765</v>
       </c>
       <c r="C1145" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1145" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40472,7 +40472,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1145" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1145" t="str">
         <v>ROLL</v>
@@ -40492,10 +40492,10 @@
         <v>1145</v>
       </c>
       <c r="B1146" t="str">
-        <v>FG-401767</v>
+        <v>FG-401766</v>
       </c>
       <c r="C1146" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1146" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40507,7 +40507,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1146" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1146" t="str">
         <v>ROLL</v>
@@ -40527,10 +40527,10 @@
         <v>1146</v>
       </c>
       <c r="B1147" t="str">
-        <v>FG-401768</v>
+        <v>FG-401767</v>
       </c>
       <c r="C1147" t="str">
-        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1147" t="str">
         <v>FLAT DRIPLINE 12MM ISI</v>
@@ -40542,7 +40542,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1147" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1147" t="str">
         <v>ROLL</v>
@@ -40562,13 +40562,13 @@
         <v>1147</v>
       </c>
       <c r="B1148" t="str">
-        <v>FG-401760</v>
+        <v>FG-401768</v>
       </c>
       <c r="C1148" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE 12MM ISI (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1148" t="str">
-        <v>FLAT DRIPLINE 16MM ISI</v>
+        <v>FLAT DRIPLINE 12MM ISI</v>
       </c>
       <c r="E1148" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40577,7 +40577,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1148" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1148" t="str">
         <v>ROLL</v>
@@ -40589,7 +40589,7 @@
         <v>Active</v>
       </c>
       <c r="K1148" t="str">
-        <v>FLAT DRIPLINE 16MM ISI certified.</v>
+        <v>FLAT DRIPLINE 12MM ISI certified.</v>
       </c>
     </row>
     <row r="1149">
@@ -40597,10 +40597,10 @@
         <v>1148</v>
       </c>
       <c r="B1149" t="str">
-        <v>FG-401761</v>
+        <v>FG-401760</v>
       </c>
       <c r="C1149" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1149" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40612,7 +40612,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1149" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1149" t="str">
         <v>ROLL</v>
@@ -40632,10 +40632,10 @@
         <v>1149</v>
       </c>
       <c r="B1150" t="str">
-        <v>FG-401762</v>
+        <v>FG-401761</v>
       </c>
       <c r="C1150" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1150" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40647,7 +40647,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1150" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1150" t="str">
         <v>ROLL</v>
@@ -40667,10 +40667,10 @@
         <v>1150</v>
       </c>
       <c r="B1151" t="str">
-        <v>FG-401769</v>
+        <v>FG-401762</v>
       </c>
       <c r="C1151" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1151" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40682,7 +40682,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1151" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1151" t="str">
         <v>ROLL</v>
@@ -40702,10 +40702,10 @@
         <v>1151</v>
       </c>
       <c r="B1152" t="str">
-        <v>FG-401770</v>
+        <v>FG-401769</v>
       </c>
       <c r="C1152" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1152" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40717,7 +40717,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1152" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1152" t="str">
         <v>ROLL</v>
@@ -40737,10 +40737,10 @@
         <v>1152</v>
       </c>
       <c r="B1153" t="str">
-        <v>FG-401779</v>
+        <v>FG-401770</v>
       </c>
       <c r="C1153" t="str">
-        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1153" t="str">
         <v>FLAT DRIPLINE 16MM ISI</v>
@@ -40752,7 +40752,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1153" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1153" t="str">
         <v>ROLL</v>
@@ -40772,13 +40772,13 @@
         <v>1153</v>
       </c>
       <c r="B1154" t="str">
-        <v>FG-401771</v>
+        <v>FG-401779</v>
       </c>
       <c r="C1154" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE 16MM ISI (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1154" t="str">
-        <v>FLAT DRIPLINE 20MM ISI</v>
+        <v>FLAT DRIPLINE 16MM ISI</v>
       </c>
       <c r="E1154" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40787,7 +40787,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1154" t="str">
-        <v>20-4-30 CLASS 1</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1154" t="str">
         <v>ROLL</v>
@@ -40799,7 +40799,7 @@
         <v>Active</v>
       </c>
       <c r="K1154" t="str">
-        <v>FLAT DRIPLINE 20MM ISI certified.</v>
+        <v>FLAT DRIPLINE 16MM ISI certified.</v>
       </c>
     </row>
     <row r="1155">
@@ -40807,10 +40807,10 @@
         <v>1154</v>
       </c>
       <c r="B1155" t="str">
-        <v>FG-401772</v>
+        <v>FG-401771</v>
       </c>
       <c r="C1155" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-30 CLASS 1)</v>
       </c>
       <c r="D1155" t="str">
         <v>FLAT DRIPLINE 20MM ISI</v>
@@ -40822,7 +40822,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1155" t="str">
-        <v>20-4-40 CLASS 1</v>
+        <v>20-4-30 CLASS 1</v>
       </c>
       <c r="H1155" t="str">
         <v>ROLL</v>
@@ -40842,10 +40842,10 @@
         <v>1155</v>
       </c>
       <c r="B1156" t="str">
-        <v>FG-401773</v>
+        <v>FG-401772</v>
       </c>
       <c r="C1156" t="str">
-        <v>FLAT DRIPLINE 20MM ISI (20-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-40 CLASS 1)</v>
       </c>
       <c r="D1156" t="str">
         <v>FLAT DRIPLINE 20MM ISI</v>
@@ -40857,7 +40857,7 @@
         <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1156" t="str">
-        <v>20-4-50 CLASS 1</v>
+        <v>20-4-40 CLASS 1</v>
       </c>
       <c r="H1156" t="str">
         <v>ROLL</v>
@@ -40877,25 +40877,25 @@
         <v>1156</v>
       </c>
       <c r="B1157" t="str">
-        <v>-</v>
+        <v>FG-401773</v>
       </c>
       <c r="C1157" t="str">
-        <v>12MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>FLAT DRIPLINE 20MM ISI (20-4-50 CLASS 1)</v>
       </c>
       <c r="D1157" t="str">
-        <v>12MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>FLAT DRIPLINE 20MM ISI</v>
       </c>
       <c r="E1157" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1157" t="str">
-        <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
+        <v>FLAT DRIP ISI</v>
       </c>
       <c r="G1157" t="str">
-        <v>CLASS-2</v>
+        <v>20-4-50 CLASS 1</v>
       </c>
       <c r="H1157" t="str">
-        <v>MTR</v>
+        <v>ROLL</v>
       </c>
       <c r="I1157" t="str">
         <v>-</v>
@@ -40904,7 +40904,7 @@
         <v>Active</v>
       </c>
       <c r="K1157" t="str">
-        <v>12mm Plain Lateral Online Drip Pipe.</v>
+        <v>FLAT DRIPLINE 20MM ISI certified.</v>
       </c>
     </row>
     <row r="1158">
@@ -40915,10 +40915,10 @@
         <v>-</v>
       </c>
       <c r="C1158" t="str">
-        <v>16MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>12MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1158" t="str">
-        <v>16MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>12MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1158" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40939,7 +40939,7 @@
         <v>Active</v>
       </c>
       <c r="K1158" t="str">
-        <v>16mm Plain Lateral Online Drip Pipe.</v>
+        <v>12mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1159">
@@ -40950,10 +40950,10 @@
         <v>-</v>
       </c>
       <c r="C1159" t="str">
-        <v>20MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>16MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1159" t="str">
-        <v>20MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>16MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1159" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40974,7 +40974,7 @@
         <v>Active</v>
       </c>
       <c r="K1159" t="str">
-        <v>20mm Plain Lateral Online Drip Pipe.</v>
+        <v>16mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1160">
@@ -40985,10 +40985,10 @@
         <v>-</v>
       </c>
       <c r="C1160" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-1)</v>
+        <v>20MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1160" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE</v>
+        <v>20MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1160" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -40997,7 +40997,7 @@
         <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1160" t="str">
-        <v>CLASS-1</v>
+        <v>CLASS-2</v>
       </c>
       <c r="H1160" t="str">
         <v>MTR</v>
@@ -41009,7 +41009,7 @@
         <v>Active</v>
       </c>
       <c r="K1160" t="str">
-        <v>32mm Plain Lateral Online Drip Pipe.</v>
+        <v>20mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1161">
@@ -41020,7 +41020,7 @@
         <v>-</v>
       </c>
       <c r="C1161" t="str">
-        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-1)</v>
       </c>
       <c r="D1161" t="str">
         <v>32MM PLAIN LATERAL ONLINE PIPE</v>
@@ -41032,7 +41032,7 @@
         <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1161" t="str">
-        <v>CLASS-2</v>
+        <v>CLASS-1</v>
       </c>
       <c r="H1161" t="str">
         <v>MTR</v>
@@ -41052,22 +41052,22 @@
         <v>1161</v>
       </c>
       <c r="B1162" t="str">
-        <v>FG-401763</v>
+        <v>-</v>
       </c>
       <c r="C1162" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 2)</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE (CLASS-2)</v>
       </c>
       <c r="D1162" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12</v>
+        <v>32MM PLAIN LATERAL ONLINE PIPE</v>
       </c>
       <c r="E1162" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1162" t="str">
-        <v>FLAT DRIP (PEPSI) - INLINE</v>
+        <v>ROUND DRIP ONLINE / HYDROCOL (LATERAL)</v>
       </c>
       <c r="G1162" t="str">
-        <v>12-4-30 CLASS 2</v>
+        <v>CLASS-2</v>
       </c>
       <c r="H1162" t="str">
         <v>MTR</v>
@@ -41079,7 +41079,7 @@
         <v>Active</v>
       </c>
       <c r="K1162" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12. Available sizes: 12-4-30 CLASS 2, 12-4-40 CLASS 2, 12-4-50 CLASS 2, 12-4-30 CLASS 3, 12-4-40 CLASS 3, 12-4-50 CLASS 3.</v>
+        <v>32mm Plain Lateral Online Drip Pipe.</v>
       </c>
     </row>
     <row r="1163">
@@ -41087,10 +41087,10 @@
         <v>1162</v>
       </c>
       <c r="B1163" t="str">
-        <v>FG-401764</v>
+        <v>FG-401763</v>
       </c>
       <c r="C1163" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 2)</v>
       </c>
       <c r="D1163" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41102,7 +41102,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1163" t="str">
-        <v>12-4-40 CLASS 2</v>
+        <v>12-4-30 CLASS 2</v>
       </c>
       <c r="H1163" t="str">
         <v>MTR</v>
@@ -41122,10 +41122,10 @@
         <v>1163</v>
       </c>
       <c r="B1164" t="str">
-        <v>FG-401765</v>
+        <v>FG-401764</v>
       </c>
       <c r="C1164" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 2)</v>
       </c>
       <c r="D1164" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41137,7 +41137,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1164" t="str">
-        <v>12-4-50 CLASS 2</v>
+        <v>12-4-40 CLASS 2</v>
       </c>
       <c r="H1164" t="str">
         <v>MTR</v>
@@ -41157,10 +41157,10 @@
         <v>1164</v>
       </c>
       <c r="B1165" t="str">
-        <v>FG-401766</v>
+        <v>FG-401765</v>
       </c>
       <c r="C1165" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 2)</v>
       </c>
       <c r="D1165" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41172,7 +41172,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1165" t="str">
-        <v>12-4-30 CLASS 3</v>
+        <v>12-4-50 CLASS 2</v>
       </c>
       <c r="H1165" t="str">
         <v>MTR</v>
@@ -41192,10 +41192,10 @@
         <v>1165</v>
       </c>
       <c r="B1166" t="str">
-        <v>FG-401767</v>
+        <v>FG-401766</v>
       </c>
       <c r="C1166" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-30 CLASS 3)</v>
       </c>
       <c r="D1166" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41207,7 +41207,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1166" t="str">
-        <v>12-4-40 CLASS 3</v>
+        <v>12-4-30 CLASS 3</v>
       </c>
       <c r="H1166" t="str">
         <v>MTR</v>
@@ -41227,10 +41227,10 @@
         <v>1166</v>
       </c>
       <c r="B1167" t="str">
-        <v>FG-401768</v>
+        <v>FG-401767</v>
       </c>
       <c r="C1167" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 3)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-40 CLASS 3)</v>
       </c>
       <c r="D1167" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 12</v>
@@ -41242,7 +41242,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1167" t="str">
-        <v>12-4-50 CLASS 3</v>
+        <v>12-4-40 CLASS 3</v>
       </c>
       <c r="H1167" t="str">
         <v>MTR</v>
@@ -41262,13 +41262,13 @@
         <v>1167</v>
       </c>
       <c r="B1168" t="str">
-        <v>FG-401760</v>
+        <v>FG-401768</v>
       </c>
       <c r="C1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12 (12-4-50 CLASS 3)</v>
       </c>
       <c r="D1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12</v>
       </c>
       <c r="E1168" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -41277,7 +41277,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1168" t="str">
-        <v>16-4-30 CLASS 1</v>
+        <v>12-4-50 CLASS 3</v>
       </c>
       <c r="H1168" t="str">
         <v>MTR</v>
@@ -41289,7 +41289,7 @@
         <v>Active</v>
       </c>
       <c r="K1168" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16. Available sizes: 16-4-30 CLASS 1, 16-4-40 CLASS 1, 16-4-50 CLASS 1, 16-4-30 CLASS 2, 16-4-40 CLASS 2, 16-4-50 CLASS 2.</v>
+        <v>FLAT DRIPLINE ISI 500MTR 12. Available sizes: 12-4-30 CLASS 2, 12-4-40 CLASS 2, 12-4-50 CLASS 2, 12-4-30 CLASS 3, 12-4-40 CLASS 3, 12-4-50 CLASS 3.</v>
       </c>
     </row>
     <row r="1169">
@@ -41297,10 +41297,10 @@
         <v>1168</v>
       </c>
       <c r="B1169" t="str">
-        <v>FG-401761</v>
+        <v>FG-401760</v>
       </c>
       <c r="C1169" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 1)</v>
       </c>
       <c r="D1169" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41312,7 +41312,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1169" t="str">
-        <v>16-4-40 CLASS 1</v>
+        <v>16-4-30 CLASS 1</v>
       </c>
       <c r="H1169" t="str">
         <v>MTR</v>
@@ -41332,10 +41332,10 @@
         <v>1169</v>
       </c>
       <c r="B1170" t="str">
-        <v>FG-401762</v>
+        <v>FG-401761</v>
       </c>
       <c r="C1170" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 1)</v>
       </c>
       <c r="D1170" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41347,7 +41347,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1170" t="str">
-        <v>16-4-50 CLASS 1</v>
+        <v>16-4-40 CLASS 1</v>
       </c>
       <c r="H1170" t="str">
         <v>MTR</v>
@@ -41367,10 +41367,10 @@
         <v>1170</v>
       </c>
       <c r="B1171" t="str">
-        <v>FG-401769</v>
+        <v>FG-401762</v>
       </c>
       <c r="C1171" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 1)</v>
       </c>
       <c r="D1171" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41382,7 +41382,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1171" t="str">
-        <v>16-4-30 CLASS 2</v>
+        <v>16-4-50 CLASS 1</v>
       </c>
       <c r="H1171" t="str">
         <v>MTR</v>
@@ -41402,10 +41402,10 @@
         <v>1171</v>
       </c>
       <c r="B1172" t="str">
-        <v>FG-401770</v>
+        <v>FG-401769</v>
       </c>
       <c r="C1172" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-30 CLASS 2)</v>
       </c>
       <c r="D1172" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41417,7 +41417,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1172" t="str">
-        <v>16-4-40 CLASS 2</v>
+        <v>16-4-30 CLASS 2</v>
       </c>
       <c r="H1172" t="str">
         <v>MTR</v>
@@ -41437,10 +41437,10 @@
         <v>1172</v>
       </c>
       <c r="B1173" t="str">
-        <v>FG-401779</v>
+        <v>FG-401770</v>
       </c>
       <c r="C1173" t="str">
-        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 2)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-40 CLASS 2)</v>
       </c>
       <c r="D1173" t="str">
         <v>FLAT DRIPLINE ISI 500MTR 16</v>
@@ -41452,7 +41452,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1173" t="str">
-        <v>16-4-50 CLASS 2</v>
+        <v>16-4-40 CLASS 2</v>
       </c>
       <c r="H1173" t="str">
         <v>MTR</v>
@@ -41472,13 +41472,13 @@
         <v>1173</v>
       </c>
       <c r="B1174" t="str">
-        <v>FG-401771</v>
+        <v>FG-401779</v>
       </c>
       <c r="C1174" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-30 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16 (16-4-50 CLASS 2)</v>
       </c>
       <c r="D1174" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16</v>
       </c>
       <c r="E1174" t="str">
         <v>DRIP IRRIGATION SYSTEM</v>
@@ -41487,7 +41487,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1174" t="str">
-        <v>20-4-30 CLASS 1</v>
+        <v>16-4-50 CLASS 2</v>
       </c>
       <c r="H1174" t="str">
         <v>MTR</v>
@@ -41499,7 +41499,7 @@
         <v>Active</v>
       </c>
       <c r="K1174" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20. Available sizes: 20-4-30 CLASS 1, 20-4-40 CLASS 1, 20-4-50 CLASS 1.</v>
+        <v>FLAT DRIPLINE ISI 500MTR 16. Available sizes: 16-4-30 CLASS 1, 16-4-40 CLASS 1, 16-4-50 CLASS 1, 16-4-30 CLASS 2, 16-4-40 CLASS 2, 16-4-50 CLASS 2.</v>
       </c>
     </row>
     <row r="1175">
@@ -41507,10 +41507,10 @@
         <v>1174</v>
       </c>
       <c r="B1175" t="str">
-        <v>FG-401772</v>
+        <v>FG-401771</v>
       </c>
       <c r="C1175" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-40 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-30 CLASS 1)</v>
       </c>
       <c r="D1175" t="str">
         <v>FLAT DRIPLINE ISI 400MTR 20</v>
@@ -41522,7 +41522,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1175" t="str">
-        <v>20-4-40 CLASS 1</v>
+        <v>20-4-30 CLASS 1</v>
       </c>
       <c r="H1175" t="str">
         <v>MTR</v>
@@ -41542,10 +41542,10 @@
         <v>1175</v>
       </c>
       <c r="B1176" t="str">
-        <v>FG-401773</v>
+        <v>FG-401772</v>
       </c>
       <c r="C1176" t="str">
-        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-50 CLASS 1)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-40 CLASS 1)</v>
       </c>
       <c r="D1176" t="str">
         <v>FLAT DRIPLINE ISI 400MTR 20</v>
@@ -41557,7 +41557,7 @@
         <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1176" t="str">
-        <v>20-4-50 CLASS 1</v>
+        <v>20-4-40 CLASS 1</v>
       </c>
       <c r="H1176" t="str">
         <v>MTR</v>
@@ -41577,22 +41577,22 @@
         <v>1176</v>
       </c>
       <c r="B1177" t="str">
-        <v>FG-401066</v>
+        <v>FG-401773</v>
       </c>
       <c r="C1177" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20 (20-4-50 CLASS 1)</v>
       </c>
       <c r="D1177" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20</v>
       </c>
       <c r="E1177" t="str">
-        <v>UPVC CASING PIPES</v>
+        <v>DRIP IRRIGATION SYSTEM</v>
       </c>
       <c r="F1177" t="str">
-        <v>General</v>
+        <v>FLAT DRIP (PEPSI) - INLINE</v>
       </c>
       <c r="G1177" t="str">
-        <v>35MM 1 1/4 Inch</v>
+        <v>20-4-50 CLASS 1</v>
       </c>
       <c r="H1177" t="str">
         <v>MTR</v>
@@ -41604,7 +41604,7 @@
         <v>Active</v>
       </c>
       <c r="K1177" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 40MM 1 1/2 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>FLAT DRIPLINE ISI 400MTR 20. Available sizes: 20-4-30 CLASS 1, 20-4-40 CLASS 1, 20-4-50 CLASS 1.</v>
       </c>
     </row>
     <row r="1178">
@@ -41612,10 +41612,10 @@
         <v>1177</v>
       </c>
       <c r="B1178" t="str">
-        <v>FG-401067</v>
+        <v>FG-401066</v>
       </c>
       <c r="C1178" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (40MM 1 1/2 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
       </c>
       <c r="D1178" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41627,7 +41627,7 @@
         <v>General</v>
       </c>
       <c r="G1178" t="str">
-        <v>40MM 1 1/2 Inch</v>
+        <v>35MM 1 1/4 Inch</v>
       </c>
       <c r="H1178" t="str">
         <v>MTR</v>
@@ -41647,10 +41647,10 @@
         <v>1178</v>
       </c>
       <c r="B1179" t="str">
-        <v>FG-401068</v>
+        <v>FG-401067</v>
       </c>
       <c r="C1179" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (50MM 2 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (40MM 1 1/2 Inch)</v>
       </c>
       <c r="D1179" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41662,7 +41662,7 @@
         <v>General</v>
       </c>
       <c r="G1179" t="str">
-        <v>50MM 2 Inch</v>
+        <v>40MM 1 1/2 Inch</v>
       </c>
       <c r="H1179" t="str">
         <v>MTR</v>
@@ -41682,10 +41682,10 @@
         <v>1179</v>
       </c>
       <c r="B1180" t="str">
-        <v>FG-401069</v>
+        <v>FG-401068</v>
       </c>
       <c r="C1180" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (100MM 4 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (50MM 2 Inch)</v>
       </c>
       <c r="D1180" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41697,7 +41697,7 @@
         <v>General</v>
       </c>
       <c r="G1180" t="str">
-        <v>100MM 4 Inch</v>
+        <v>50MM 2 Inch</v>
       </c>
       <c r="H1180" t="str">
         <v>MTR</v>
@@ -41717,10 +41717,10 @@
         <v>1180</v>
       </c>
       <c r="B1181" t="str">
-        <v>FG-401070</v>
+        <v>FG-401069</v>
       </c>
       <c r="C1181" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (100MM 4 Inch)</v>
       </c>
       <c r="D1181" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41732,7 +41732,7 @@
         <v>General</v>
       </c>
       <c r="G1181" t="str">
-        <v>125MM 5 Inch</v>
+        <v>100MM 4 Inch</v>
       </c>
       <c r="H1181" t="str">
         <v>MTR</v>
@@ -41752,10 +41752,10 @@
         <v>1181</v>
       </c>
       <c r="B1182" t="str">
-        <v>FG-401071</v>
+        <v>FG-401070</v>
       </c>
       <c r="C1182" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1182" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41767,7 +41767,7 @@
         <v>General</v>
       </c>
       <c r="G1182" t="str">
-        <v>150MM 6 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1182" t="str">
         <v>MTR</v>
@@ -41787,10 +41787,10 @@
         <v>1182</v>
       </c>
       <c r="B1183" t="str">
-        <v>FG-401072</v>
+        <v>FG-401071</v>
       </c>
       <c r="C1183" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1183" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41802,7 +41802,7 @@
         <v>General</v>
       </c>
       <c r="G1183" t="str">
-        <v>175MM 7 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1183" t="str">
         <v>MTR</v>
@@ -41822,10 +41822,10 @@
         <v>1183</v>
       </c>
       <c r="B1184" t="str">
-        <v>FG-401073</v>
+        <v>FG-401072</v>
       </c>
       <c r="C1184" t="str">
-        <v>CASING PIPE BLUE THD CM-SCH-80-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1184" t="str">
         <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
@@ -41837,7 +41837,7 @@
         <v>General</v>
       </c>
       <c r="G1184" t="str">
-        <v>200MM 8 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1184" t="str">
         <v>MTR</v>
@@ -41857,13 +41857,13 @@
         <v>1184</v>
       </c>
       <c r="B1185" t="str">
-        <v>FG-401074</v>
+        <v>FG-401073</v>
       </c>
       <c r="C1185" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1185" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M</v>
       </c>
       <c r="E1185" t="str">
         <v>UPVC CASING PIPES</v>
@@ -41872,7 +41872,7 @@
         <v>General</v>
       </c>
       <c r="G1185" t="str">
-        <v>125MM 5 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1185" t="str">
         <v>MTR</v>
@@ -41884,7 +41884,7 @@
         <v>Active</v>
       </c>
       <c r="K1185" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE THD CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 40MM 1 1/2 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1186">
@@ -41892,10 +41892,10 @@
         <v>1185</v>
       </c>
       <c r="B1186" t="str">
-        <v>FG-401075</v>
+        <v>FG-401074</v>
       </c>
       <c r="C1186" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1186" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41907,7 +41907,7 @@
         <v>General</v>
       </c>
       <c r="G1186" t="str">
-        <v>150MM 6 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1186" t="str">
         <v>MTR</v>
@@ -41927,10 +41927,10 @@
         <v>1186</v>
       </c>
       <c r="B1187" t="str">
-        <v>FG-401076</v>
+        <v>FG-401075</v>
       </c>
       <c r="C1187" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1187" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41942,7 +41942,7 @@
         <v>General</v>
       </c>
       <c r="G1187" t="str">
-        <v>175MM 7 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1187" t="str">
         <v>MTR</v>
@@ -41962,10 +41962,10 @@
         <v>1187</v>
       </c>
       <c r="B1188" t="str">
-        <v>FG-401077</v>
+        <v>FG-401076</v>
       </c>
       <c r="C1188" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1188" t="str">
         <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
@@ -41977,7 +41977,7 @@
         <v>General</v>
       </c>
       <c r="G1188" t="str">
-        <v>200MM 8 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1188" t="str">
         <v>MTR</v>
@@ -41997,13 +41997,13 @@
         <v>1188</v>
       </c>
       <c r="B1189" t="str">
-        <v>FG-401149</v>
+        <v>FG-401077</v>
       </c>
       <c r="C1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M (140MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M</v>
       </c>
       <c r="E1189" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42012,7 +42012,7 @@
         <v>General</v>
       </c>
       <c r="G1189" t="str">
-        <v>140MM 5 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1189" t="str">
         <v>MTR</v>
@@ -42024,7 +42024,7 @@
         <v>Active</v>
       </c>
       <c r="K1189" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-40-5M. Available sizes: 140MM 5 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1190">
@@ -42032,13 +42032,13 @@
         <v>1189</v>
       </c>
       <c r="B1190" t="str">
-        <v>FG-401150</v>
+        <v>FG-401149</v>
       </c>
       <c r="C1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M (140MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M (140MM 5 Inch)</v>
       </c>
       <c r="D1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M</v>
       </c>
       <c r="E1190" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42059,7 +42059,7 @@
         <v>Active</v>
       </c>
       <c r="K1190" t="str">
-        <v>CASING PIPE BLUE THD CS-SCH-80-5M. Available sizes: 140MM 5 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-40-5M. Available sizes: 140MM 5 Inch.</v>
       </c>
     </row>
     <row r="1191">
@@ -42067,13 +42067,13 @@
         <v>1190</v>
       </c>
       <c r="B1191" t="str">
-        <v>FG-401078</v>
+        <v>FG-401150</v>
       </c>
       <c r="C1191" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M (140MM 5 Inch)</v>
       </c>
       <c r="D1191" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M</v>
       </c>
       <c r="E1191" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42082,7 +42082,7 @@
         <v>General</v>
       </c>
       <c r="G1191" t="str">
-        <v>125MM 5 Inch</v>
+        <v>140MM 5 Inch</v>
       </c>
       <c r="H1191" t="str">
         <v>MTR</v>
@@ -42094,7 +42094,7 @@
         <v>Active</v>
       </c>
       <c r="K1191" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE THD CS-SCH-80-5M. Available sizes: 140MM 5 Inch.</v>
       </c>
     </row>
     <row r="1192">
@@ -42102,10 +42102,10 @@
         <v>1191</v>
       </c>
       <c r="B1192" t="str">
-        <v>FG-401079</v>
+        <v>FG-401078</v>
       </c>
       <c r="C1192" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1192" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42117,7 +42117,7 @@
         <v>General</v>
       </c>
       <c r="G1192" t="str">
-        <v>150MM 6 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1192" t="str">
         <v>MTR</v>
@@ -42137,10 +42137,10 @@
         <v>1192</v>
       </c>
       <c r="B1193" t="str">
-        <v>FG-401080</v>
+        <v>FG-401079</v>
       </c>
       <c r="C1193" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1193" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42152,7 +42152,7 @@
         <v>General</v>
       </c>
       <c r="G1193" t="str">
-        <v>175MM 7 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1193" t="str">
         <v>MTR</v>
@@ -42172,10 +42172,10 @@
         <v>1193</v>
       </c>
       <c r="B1194" t="str">
-        <v>FG-401081</v>
+        <v>FG-401080</v>
       </c>
       <c r="C1194" t="str">
-        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1194" t="str">
         <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
@@ -42187,7 +42187,7 @@
         <v>General</v>
       </c>
       <c r="G1194" t="str">
-        <v>200MM 8 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1194" t="str">
         <v>MTR</v>
@@ -42207,13 +42207,13 @@
         <v>1194</v>
       </c>
       <c r="B1195" t="str">
-        <v>FG-401119</v>
+        <v>FG-401081</v>
       </c>
       <c r="C1195" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1195" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M</v>
       </c>
       <c r="E1195" t="str">
         <v>UPVC CASING PIPES</v>
@@ -42222,7 +42222,7 @@
         <v>General</v>
       </c>
       <c r="G1195" t="str">
-        <v>35MM 1 1/4 Inch</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1195" t="str">
         <v>MTR</v>
@@ -42234,7 +42234,7 @@
         <v>Active</v>
       </c>
       <c r="K1195" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
+        <v>CASING PIPE BLUE PLN CS-SCH-40-3M. Available sizes: 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1196">
@@ -42242,10 +42242,10 @@
         <v>1195</v>
       </c>
       <c r="B1196" t="str">
-        <v>FG-401121</v>
+        <v>FG-401119</v>
       </c>
       <c r="C1196" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (50MM 2 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (35MM 1 1/4 Inch)</v>
       </c>
       <c r="D1196" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42257,7 +42257,7 @@
         <v>General</v>
       </c>
       <c r="G1196" t="str">
-        <v>50MM 2 Inch</v>
+        <v>35MM 1 1/4 Inch</v>
       </c>
       <c r="H1196" t="str">
         <v>MTR</v>
@@ -42277,10 +42277,10 @@
         <v>1196</v>
       </c>
       <c r="B1197" t="str">
-        <v>FG-401122</v>
+        <v>FG-401121</v>
       </c>
       <c r="C1197" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (100MM 4 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (50MM 2 Inch)</v>
       </c>
       <c r="D1197" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42292,7 +42292,7 @@
         <v>General</v>
       </c>
       <c r="G1197" t="str">
-        <v>100MM 4 Inch</v>
+        <v>50MM 2 Inch</v>
       </c>
       <c r="H1197" t="str">
         <v>MTR</v>
@@ -42312,10 +42312,10 @@
         <v>1197</v>
       </c>
       <c r="B1198" t="str">
-        <v>FG-401123</v>
+        <v>FG-401122</v>
       </c>
       <c r="C1198" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (125MM 5 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (100MM 4 Inch)</v>
       </c>
       <c r="D1198" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42327,7 +42327,7 @@
         <v>General</v>
       </c>
       <c r="G1198" t="str">
-        <v>125MM 5 Inch</v>
+        <v>100MM 4 Inch</v>
       </c>
       <c r="H1198" t="str">
         <v>MTR</v>
@@ -42347,10 +42347,10 @@
         <v>1198</v>
       </c>
       <c r="B1199" t="str">
-        <v>FG-401124</v>
+        <v>FG-401123</v>
       </c>
       <c r="C1199" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (150MM 6 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (125MM 5 Inch)</v>
       </c>
       <c r="D1199" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42362,7 +42362,7 @@
         <v>General</v>
       </c>
       <c r="G1199" t="str">
-        <v>150MM 6 Inch</v>
+        <v>125MM 5 Inch</v>
       </c>
       <c r="H1199" t="str">
         <v>MTR</v>
@@ -42382,10 +42382,10 @@
         <v>1199</v>
       </c>
       <c r="B1200" t="str">
-        <v>FG-401125</v>
+        <v>FG-401124</v>
       </c>
       <c r="C1200" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (175MM 7 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (150MM 6 Inch)</v>
       </c>
       <c r="D1200" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42397,7 +42397,7 @@
         <v>General</v>
       </c>
       <c r="G1200" t="str">
-        <v>175MM 7 Inch</v>
+        <v>150MM 6 Inch</v>
       </c>
       <c r="H1200" t="str">
         <v>MTR</v>
@@ -42417,10 +42417,10 @@
         <v>1200</v>
       </c>
       <c r="B1201" t="str">
-        <v>FG-401126</v>
+        <v>FG-401125</v>
       </c>
       <c r="C1201" t="str">
-        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (200MM 8 Inch)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (175MM 7 Inch)</v>
       </c>
       <c r="D1201" t="str">
         <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
@@ -42432,7 +42432,7 @@
         <v>General</v>
       </c>
       <c r="G1201" t="str">
-        <v>200MM 8 Inch</v>
+        <v>175MM 7 Inch</v>
       </c>
       <c r="H1201" t="str">
         <v>MTR</v>
@@ -42452,22 +42452,22 @@
         <v>1201</v>
       </c>
       <c r="B1202" t="str">
-        <v>FG-401166</v>
+        <v>FG-401126</v>
       </c>
       <c r="C1202" t="str">
-        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG COUPLER TYPE)</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M (200MM 8 Inch)</v>
       </c>
       <c r="D1202" t="str">
-        <v>COLOUMN PIPE ECO V4</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M</v>
       </c>
       <c r="E1202" t="str">
-        <v>UPVC COLUMN PIPES</v>
+        <v>UPVC CASING PIPES</v>
       </c>
       <c r="F1202" t="str">
         <v>General</v>
       </c>
       <c r="G1202" t="str">
-        <v>33MM 12.5KG COUPLER TYPE</v>
+        <v>200MM 8 Inch</v>
       </c>
       <c r="H1202" t="str">
         <v>MTR</v>
@@ -42479,7 +42479,7 @@
         <v>Active</v>
       </c>
       <c r="K1202" t="str">
-        <v>COLOUMN PIPE ECO V4 for submersible pump systems.</v>
+        <v>CASING PIPE BLUE PLN CM-SCH-80-3M. Available sizes: 35MM 1 1/4 Inch, 50MM 2 Inch, 100MM 4 Inch, 125MM 5 Inch, 150MM 6 Inch, 175MM 7 Inch, 200MM 8 Inch.</v>
       </c>
     </row>
     <row r="1203">
@@ -42487,10 +42487,10 @@
         <v>1202</v>
       </c>
       <c r="B1203" t="str">
-        <v>FG-401162</v>
+        <v>FG-401166</v>
       </c>
       <c r="C1203" t="str">
-        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG BELL END TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1203" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42502,7 +42502,7 @@
         <v>General</v>
       </c>
       <c r="G1203" t="str">
-        <v>33MM 12.5KG BELL END TYPE</v>
+        <v>33MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1203" t="str">
         <v>MTR</v>
@@ -42522,10 +42522,10 @@
         <v>1203</v>
       </c>
       <c r="B1204" t="str">
-        <v>FG-401165</v>
+        <v>FG-401162</v>
       </c>
       <c r="C1204" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 10KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (33MM 12.5KG BELL END TYPE)</v>
       </c>
       <c r="D1204" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42537,7 +42537,7 @@
         <v>General</v>
       </c>
       <c r="G1204" t="str">
-        <v>42MM 10KG COUPLER TYPE</v>
+        <v>33MM 12.5KG BELL END TYPE</v>
       </c>
       <c r="H1204" t="str">
         <v>MTR</v>
@@ -42557,10 +42557,10 @@
         <v>1204</v>
       </c>
       <c r="B1205" t="str">
-        <v>FG-401167</v>
+        <v>FG-401165</v>
       </c>
       <c r="C1205" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 10KG COUPLER TYPE)</v>
       </c>
       <c r="D1205" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42572,7 +42572,7 @@
         <v>General</v>
       </c>
       <c r="G1205" t="str">
-        <v>42MM 12.5KG COUPLER TYPE</v>
+        <v>42MM 10KG COUPLER TYPE</v>
       </c>
       <c r="H1205" t="str">
         <v>MTR</v>
@@ -42592,10 +42592,10 @@
         <v>1205</v>
       </c>
       <c r="B1206" t="str">
-        <v>FG-401163</v>
+        <v>FG-401167</v>
       </c>
       <c r="C1206" t="str">
-        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG BELL END TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1206" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42607,7 +42607,7 @@
         <v>General</v>
       </c>
       <c r="G1206" t="str">
-        <v>42MM 12.5KG BELL END TYPE</v>
+        <v>42MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1206" t="str">
         <v>MTR</v>
@@ -42627,10 +42627,10 @@
         <v>1206</v>
       </c>
       <c r="B1207" t="str">
-        <v>FG-401164</v>
+        <v>FG-401163</v>
       </c>
       <c r="C1207" t="str">
-        <v>COLOUMN PIPE ECO V4 (48MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (42MM 12.5KG BELL END TYPE)</v>
       </c>
       <c r="D1207" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42642,7 +42642,7 @@
         <v>General</v>
       </c>
       <c r="G1207" t="str">
-        <v>48MM 12.5KG COUPLER TYPE</v>
+        <v>42MM 12.5KG BELL END TYPE</v>
       </c>
       <c r="H1207" t="str">
         <v>MTR</v>
@@ -42662,10 +42662,10 @@
         <v>1207</v>
       </c>
       <c r="B1208" t="str">
-        <v>FG-401168</v>
+        <v>FG-401164</v>
       </c>
       <c r="C1208" t="str">
-        <v>COLOUMN PIPE ECO V4 (60MM 12.5KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (48MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1208" t="str">
         <v>COLOUMN PIPE ECO V4</v>
@@ -42677,7 +42677,7 @@
         <v>General</v>
       </c>
       <c r="G1208" t="str">
-        <v>60MM 12.5KG COUPLER TYPE</v>
+        <v>48MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1208" t="str">
         <v>MTR</v>
@@ -42697,13 +42697,13 @@
         <v>1208</v>
       </c>
       <c r="B1209" t="str">
-        <v>FG-401175</v>
+        <v>FG-401168</v>
       </c>
       <c r="C1209" t="str">
-        <v>COLOUMN PIPE MEDIUM (33MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE ECO V4 (60MM 12.5KG COUPLER TYPE)</v>
       </c>
       <c r="D1209" t="str">
-        <v>COLOUMN PIPE MEDIUM</v>
+        <v>COLOUMN PIPE ECO V4</v>
       </c>
       <c r="E1209" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -42712,7 +42712,7 @@
         <v>General</v>
       </c>
       <c r="G1209" t="str">
-        <v>33MM 18KG COUPLER TYPE</v>
+        <v>60MM 12.5KG COUPLER TYPE</v>
       </c>
       <c r="H1209" t="str">
         <v>MTR</v>
@@ -42724,7 +42724,7 @@
         <v>Active</v>
       </c>
       <c r="K1209" t="str">
-        <v>COLOUMN PIPE MEDIUM for submersible pump systems.</v>
+        <v>COLOUMN PIPE ECO V4 for submersible pump systems.</v>
       </c>
     </row>
     <row r="1210">
@@ -42732,10 +42732,10 @@
         <v>1209</v>
       </c>
       <c r="B1210" t="str">
-        <v>FG-401177</v>
+        <v>FG-401175</v>
       </c>
       <c r="C1210" t="str">
-        <v>COLOUMN PIPE MEDIUM (42MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (33MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1210" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42747,7 +42747,7 @@
         <v>General</v>
       </c>
       <c r="G1210" t="str">
-        <v>42MM 18KG COUPLER TYPE</v>
+        <v>33MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1210" t="str">
         <v>MTR</v>
@@ -42767,10 +42767,10 @@
         <v>1210</v>
       </c>
       <c r="B1211" t="str">
-        <v>FG-401176</v>
+        <v>FG-401177</v>
       </c>
       <c r="C1211" t="str">
-        <v>COLOUMN PIPE MEDIUM (48MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (42MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1211" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42782,7 +42782,7 @@
         <v>General</v>
       </c>
       <c r="G1211" t="str">
-        <v>48MM 18KG COUPLER TYPE</v>
+        <v>42MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1211" t="str">
         <v>MTR</v>
@@ -42802,10 +42802,10 @@
         <v>1211</v>
       </c>
       <c r="B1212" t="str">
-        <v>FG-401178</v>
+        <v>FG-401176</v>
       </c>
       <c r="C1212" t="str">
-        <v>COLOUMN PIPE MEDIUM (60MM 15KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (48MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1212" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42817,7 +42817,7 @@
         <v>General</v>
       </c>
       <c r="G1212" t="str">
-        <v>60MM 15KG COUPLER TYPE</v>
+        <v>48MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1212" t="str">
         <v>MTR</v>
@@ -42837,10 +42837,10 @@
         <v>1212</v>
       </c>
       <c r="B1213" t="str">
-        <v>FG-401180</v>
+        <v>FG-401178</v>
       </c>
       <c r="C1213" t="str">
-        <v>COLOUMN PIPE MEDIUM (75MM 10KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (60MM 15KG COUPLER TYPE)</v>
       </c>
       <c r="D1213" t="str">
         <v>COLOUMN PIPE MEDIUM</v>
@@ -42852,7 +42852,7 @@
         <v>General</v>
       </c>
       <c r="G1213" t="str">
-        <v>75MM 10KG COUPLER TYPE</v>
+        <v>60MM 15KG COUPLER TYPE</v>
       </c>
       <c r="H1213" t="str">
         <v>MTR</v>
@@ -42872,13 +42872,13 @@
         <v>1213</v>
       </c>
       <c r="B1214" t="str">
-        <v>FG-401169</v>
+        <v>FG-401180</v>
       </c>
       <c r="C1214" t="str">
-        <v>COLOUMN PIPE STANDARD (33MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE MEDIUM (75MM 10KG COUPLER TYPE)</v>
       </c>
       <c r="D1214" t="str">
-        <v>COLOUMN PIPE STANDARD</v>
+        <v>COLOUMN PIPE MEDIUM</v>
       </c>
       <c r="E1214" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -42887,7 +42887,7 @@
         <v>General</v>
       </c>
       <c r="G1214" t="str">
-        <v>33MM 25KG COUPLER TYPE</v>
+        <v>75MM 10KG COUPLER TYPE</v>
       </c>
       <c r="H1214" t="str">
         <v>MTR</v>
@@ -42899,7 +42899,7 @@
         <v>Active</v>
       </c>
       <c r="K1214" t="str">
-        <v>COLOUMN PIPE STANDARD for submersible pump systems.</v>
+        <v>COLOUMN PIPE MEDIUM for submersible pump systems.</v>
       </c>
     </row>
     <row r="1215">
@@ -42907,10 +42907,10 @@
         <v>1214</v>
       </c>
       <c r="B1215" t="str">
-        <v>FG-401171</v>
+        <v>FG-401169</v>
       </c>
       <c r="C1215" t="str">
-        <v>COLOUMN PIPE STANDARD (42MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (33MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1215" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42922,7 +42922,7 @@
         <v>General</v>
       </c>
       <c r="G1215" t="str">
-        <v>42MM 25KG COUPLER TYPE</v>
+        <v>33MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1215" t="str">
         <v>MTR</v>
@@ -42942,10 +42942,10 @@
         <v>1215</v>
       </c>
       <c r="B1216" t="str">
-        <v>FG-401170</v>
+        <v>FG-401171</v>
       </c>
       <c r="C1216" t="str">
-        <v>COLOUMN PIPE STANDARD (48MM 25KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (42MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1216" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42957,7 +42957,7 @@
         <v>General</v>
       </c>
       <c r="G1216" t="str">
-        <v>48MM 25KG COUPLER TYPE</v>
+        <v>42MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1216" t="str">
         <v>MTR</v>
@@ -42977,10 +42977,10 @@
         <v>1216</v>
       </c>
       <c r="B1217" t="str">
-        <v>FG-401172</v>
+        <v>FG-401170</v>
       </c>
       <c r="C1217" t="str">
-        <v>COLOUMN PIPE STANDARD (60MM 20KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (48MM 25KG COUPLER TYPE)</v>
       </c>
       <c r="D1217" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -42992,7 +42992,7 @@
         <v>General</v>
       </c>
       <c r="G1217" t="str">
-        <v>60MM 20KG COUPLER TYPE</v>
+        <v>48MM 25KG COUPLER TYPE</v>
       </c>
       <c r="H1217" t="str">
         <v>MTR</v>
@@ -43012,10 +43012,10 @@
         <v>1217</v>
       </c>
       <c r="B1218" t="str">
-        <v>FG-401174</v>
+        <v>FG-401172</v>
       </c>
       <c r="C1218" t="str">
-        <v>COLOUMN PIPE STANDARD (75MM 20KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (60MM 20KG COUPLER TYPE)</v>
       </c>
       <c r="D1218" t="str">
         <v>COLOUMN PIPE STANDARD</v>
@@ -43027,7 +43027,7 @@
         <v>General</v>
       </c>
       <c r="G1218" t="str">
-        <v>75MM 20KG COUPLER TYPE</v>
+        <v>60MM 20KG COUPLER TYPE</v>
       </c>
       <c r="H1218" t="str">
         <v>MTR</v>
@@ -43047,13 +43047,13 @@
         <v>1218</v>
       </c>
       <c r="B1219" t="str">
-        <v>-</v>
+        <v>FG-401174</v>
       </c>
       <c r="C1219" t="str">
-        <v>3M STANDARD PLUS PIPE (60MM 25 COUPLER TYPE)</v>
+        <v>COLOUMN PIPE STANDARD (75MM 20KG COUPLER TYPE)</v>
       </c>
       <c r="D1219" t="str">
-        <v>3M STANDARD PLUS PIPE</v>
+        <v>COLOUMN PIPE STANDARD</v>
       </c>
       <c r="E1219" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43062,7 +43062,7 @@
         <v>General</v>
       </c>
       <c r="G1219" t="str">
-        <v>60MM 25 COUPLER TYPE</v>
+        <v>75MM 20KG COUPLER TYPE</v>
       </c>
       <c r="H1219" t="str">
         <v>MTR</v>
@@ -43074,7 +43074,7 @@
         <v>Active</v>
       </c>
       <c r="K1219" t="str">
-        <v>3M Standard Plus UPVC Column Pipe for submersible pump systems.</v>
+        <v>COLOUMN PIPE STANDARD for submersible pump systems.</v>
       </c>
     </row>
     <row r="1220">
@@ -43082,13 +43082,13 @@
         <v>1219</v>
       </c>
       <c r="B1220" t="str">
-        <v>FG-401182</v>
+        <v>-</v>
       </c>
       <c r="C1220" t="str">
-        <v>COLOUMN PIPE HEAVY (42MM 30KG COUPLER TYPE)</v>
+        <v>3M STANDARD PLUS PIPE (60MM 25 COUPLER TYPE)</v>
       </c>
       <c r="D1220" t="str">
-        <v>COLOUMN PIPE HEAVY</v>
+        <v>3M STANDARD PLUS PIPE</v>
       </c>
       <c r="E1220" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43097,7 +43097,7 @@
         <v>General</v>
       </c>
       <c r="G1220" t="str">
-        <v>42MM 30KG COUPLER TYPE</v>
+        <v>60MM 25 COUPLER TYPE</v>
       </c>
       <c r="H1220" t="str">
         <v>MTR</v>
@@ -43109,7 +43109,7 @@
         <v>Active</v>
       </c>
       <c r="K1220" t="str">
-        <v>COLOUMN PIPE HEAVY for submersible pump systems.</v>
+        <v>3M Standard Plus UPVC Column Pipe for submersible pump systems.</v>
       </c>
     </row>
     <row r="1221">
@@ -43117,10 +43117,10 @@
         <v>1220</v>
       </c>
       <c r="B1221" t="str">
-        <v>FG-401181</v>
+        <v>FG-401182</v>
       </c>
       <c r="C1221" t="str">
-        <v>COLOUMN PIPE HEAVY (48MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (42MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1221" t="str">
         <v>COLOUMN PIPE HEAVY</v>
@@ -43132,7 +43132,7 @@
         <v>General</v>
       </c>
       <c r="G1221" t="str">
-        <v>48MM 30KG COUPLER TYPE</v>
+        <v>42MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1221" t="str">
         <v>MTR</v>
@@ -43152,10 +43152,10 @@
         <v>1221</v>
       </c>
       <c r="B1222" t="str">
-        <v>FG-401183</v>
+        <v>FG-401181</v>
       </c>
       <c r="C1222" t="str">
-        <v>COLOUMN PIPE HEAVY (60MM 30KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (48MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1222" t="str">
         <v>COLOUMN PIPE HEAVY</v>
@@ -43167,7 +43167,7 @@
         <v>General</v>
       </c>
       <c r="G1222" t="str">
-        <v>60MM 30KG COUPLER TYPE</v>
+        <v>48MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1222" t="str">
         <v>MTR</v>
@@ -43187,13 +43187,13 @@
         <v>1222</v>
       </c>
       <c r="B1223" t="str">
-        <v>FG-401179</v>
+        <v>FG-401183</v>
       </c>
       <c r="C1223" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS (60MM 18KG COUPLER TYPE)</v>
+        <v>COLOUMN PIPE HEAVY (60MM 30KG COUPLER TYPE)</v>
       </c>
       <c r="D1223" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS</v>
+        <v>COLOUMN PIPE HEAVY</v>
       </c>
       <c r="E1223" t="str">
         <v>UPVC COLUMN PIPES</v>
@@ -43202,7 +43202,7 @@
         <v>General</v>
       </c>
       <c r="G1223" t="str">
-        <v>60MM 18KG COUPLER TYPE</v>
+        <v>60MM 30KG COUPLER TYPE</v>
       </c>
       <c r="H1223" t="str">
         <v>MTR</v>
@@ -43214,7 +43214,7 @@
         <v>Active</v>
       </c>
       <c r="K1223" t="str">
-        <v>COLOUMN PIPE MEDIUM PLUS for submersible pump systems.</v>
+        <v>COLOUMN PIPE HEAVY for submersible pump systems.</v>
       </c>
     </row>
     <row r="1224">
@@ -43222,34 +43222,34 @@
         <v>1223</v>
       </c>
       <c r="B1224" t="str">
-        <v>FG-401569</v>
+        <v>FG-401179</v>
       </c>
       <c r="C1224" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA (15 Inch)</v>
+        <v>COLOUMN PIPE MEDIUM PLUS (60MM 18KG COUPLER TYPE)</v>
       </c>
       <c r="D1224" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA</v>
+        <v>COLOUMN PIPE MEDIUM PLUS</v>
       </c>
       <c r="E1224" t="str">
-        <v>HOUSEHOLD PRODUCTS</v>
+        <v>UPVC COLUMN PIPES</v>
       </c>
       <c r="F1224" t="str">
         <v>General</v>
       </c>
       <c r="G1224" t="str">
-        <v>15 Inch</v>
+        <v>60MM 18KG COUPLER TYPE</v>
       </c>
       <c r="H1224" t="str">
-        <v>BAGS</v>
+        <v>MTR</v>
       </c>
       <c r="I1224" t="str">
-        <v>75</v>
+        <v>-</v>
       </c>
       <c r="J1224" t="str">
         <v>Active</v>
       </c>
       <c r="K1224" t="str">
-        <v>CONSTRUCTION GHAMELA SHIVA high durability ghamela.</v>
+        <v>COLOUMN PIPE MEDIUM PLUS for submersible pump systems.</v>
       </c>
     </row>
     <row r="1225">
@@ -43257,13 +43257,13 @@
         <v>1224</v>
       </c>
       <c r="B1225" t="str">
-        <v>FG-401570</v>
+        <v>FG-401569</v>
       </c>
       <c r="C1225" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI (15 Inch)</v>
+        <v>CONSTRUCTION GHAMELA SHIVA (15 Inch)</v>
       </c>
       <c r="D1225" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI</v>
+        <v>CONSTRUCTION GHAMELA SHIVA</v>
       </c>
       <c r="E1225" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43284,7 +43284,7 @@
         <v>Active</v>
       </c>
       <c r="K1225" t="str">
-        <v>MULTIPURPOSE GHAMELA GOURI high durability ghamela.</v>
+        <v>CONSTRUCTION GHAMELA SHIVA high durability ghamela.</v>
       </c>
     </row>
     <row r="1226">
@@ -43292,13 +43292,13 @@
         <v>1225</v>
       </c>
       <c r="B1226" t="str">
-        <v>FG-401571</v>
+        <v>FG-401570</v>
       </c>
       <c r="C1226" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA (16 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA GOURI (15 Inch)</v>
       </c>
       <c r="D1226" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA</v>
+        <v>MULTIPURPOSE GHAMELA GOURI</v>
       </c>
       <c r="E1226" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43307,19 +43307,19 @@
         <v>General</v>
       </c>
       <c r="G1226" t="str">
-        <v>16 Inch</v>
+        <v>15 Inch</v>
       </c>
       <c r="H1226" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1226" t="str">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="J1226" t="str">
         <v>Active</v>
       </c>
       <c r="K1226" t="str">
-        <v>MULTIPURPOSE GHAMELA KRISHNA high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA GOURI high durability ghamela.</v>
       </c>
     </row>
     <row r="1227">
@@ -43327,13 +43327,13 @@
         <v>1226</v>
       </c>
       <c r="B1227" t="str">
-        <v>FG-401573</v>
+        <v>FG-401571</v>
       </c>
       <c r="C1227" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV (18 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA (16 Inch)</v>
       </c>
       <c r="D1227" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA</v>
       </c>
       <c r="E1227" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43342,19 +43342,19 @@
         <v>General</v>
       </c>
       <c r="G1227" t="str">
-        <v>18 Inch</v>
+        <v>16 Inch</v>
       </c>
       <c r="H1227" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1227" t="str">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J1227" t="str">
         <v>Active</v>
       </c>
       <c r="K1227" t="str">
-        <v>MULTIPURPOSE GHAMELA RAGHAV high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA KRISHNA high durability ghamela.</v>
       </c>
     </row>
     <row r="1228">
@@ -43362,13 +43362,13 @@
         <v>1227</v>
       </c>
       <c r="B1228" t="str">
-        <v>FG-401574</v>
+        <v>FG-401573</v>
       </c>
       <c r="C1228" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET (20 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV (18 Inch)</v>
       </c>
       <c r="D1228" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV</v>
       </c>
       <c r="E1228" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43377,19 +43377,19 @@
         <v>General</v>
       </c>
       <c r="G1228" t="str">
-        <v>20 Inch</v>
+        <v>18 Inch</v>
       </c>
       <c r="H1228" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1228" t="str">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J1228" t="str">
         <v>Active</v>
       </c>
       <c r="K1228" t="str">
-        <v>MULTIPURPOSE GHAMELA ANIKET high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA RAGHAV high durability ghamela.</v>
       </c>
     </row>
     <row r="1229">
@@ -43397,13 +43397,13 @@
         <v>1228</v>
       </c>
       <c r="B1229" t="str">
-        <v>FG-401572</v>
+        <v>FG-401574</v>
       </c>
       <c r="C1229" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI (17 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET (20 Inch)</v>
       </c>
       <c r="D1229" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET</v>
       </c>
       <c r="E1229" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43412,19 +43412,19 @@
         <v>General</v>
       </c>
       <c r="G1229" t="str">
-        <v>17 Inch</v>
+        <v>20 Inch</v>
       </c>
       <c r="H1229" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1229" t="str">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J1229" t="str">
         <v>Active</v>
       </c>
       <c r="K1229" t="str">
-        <v>MULTIPURPOSE GHAMELA TEJASWI high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA ANIKET high durability ghamela.</v>
       </c>
     </row>
     <row r="1230">
@@ -43432,13 +43432,13 @@
         <v>1229</v>
       </c>
       <c r="B1230" t="str">
-        <v>FG-401575</v>
+        <v>FG-401572</v>
       </c>
       <c r="C1230" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ (22 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI (17 Inch)</v>
       </c>
       <c r="D1230" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI</v>
       </c>
       <c r="E1230" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43447,19 +43447,19 @@
         <v>General</v>
       </c>
       <c r="G1230" t="str">
-        <v>22 Inch</v>
+        <v>17 Inch</v>
       </c>
       <c r="H1230" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1230" t="str">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J1230" t="str">
         <v>Active</v>
       </c>
       <c r="K1230" t="str">
-        <v>MULTIPURPOSE GHAMELA GAJRAJ high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA TEJASWI high durability ghamela.</v>
       </c>
     </row>
     <row r="1231">
@@ -43467,13 +43467,13 @@
         <v>1230</v>
       </c>
       <c r="B1231" t="str">
-        <v>FG-401578</v>
+        <v>FG-401575</v>
       </c>
       <c r="C1231" t="str">
-        <v>AQUA PLAST GHAMELA 16 (16 Inch)</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ (22 Inch)</v>
       </c>
       <c r="D1231" t="str">
-        <v>AQUA PLAST GHAMELA 16</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ</v>
       </c>
       <c r="E1231" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43482,19 +43482,19 @@
         <v>General</v>
       </c>
       <c r="G1231" t="str">
-        <v>16 Inch</v>
+        <v>22 Inch</v>
       </c>
       <c r="H1231" t="str">
         <v>BAGS</v>
       </c>
       <c r="I1231" t="str">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J1231" t="str">
         <v>Active</v>
       </c>
       <c r="K1231" t="str">
-        <v>AQUA PLAST GHAMELA 16 high durability ghamela.</v>
+        <v>MULTIPURPOSE GHAMELA GAJRAJ high durability ghamela.</v>
       </c>
     </row>
     <row r="1232">
@@ -43502,13 +43502,13 @@
         <v>1231</v>
       </c>
       <c r="B1232" t="str">
-        <v>FG-401579</v>
+        <v>FG-401578</v>
       </c>
       <c r="C1232" t="str">
-        <v>AQUA PLAST GHAMELA 17 (17 Inch)</v>
+        <v>AQUA PLAST GHAMELA 16 (16 Inch)</v>
       </c>
       <c r="D1232" t="str">
-        <v>AQUA PLAST GHAMELA 17</v>
+        <v>AQUA PLAST GHAMELA 16</v>
       </c>
       <c r="E1232" t="str">
         <v>HOUSEHOLD PRODUCTS</v>
@@ -43517,7 +43517,7 @@
         <v>General</v>
       </c>
       <c r="G1232" t="str">
-        <v>17 Inch</v>
+        <v>16 Inch</v>
       </c>
       <c r="H1232" t="str">
         <v>BAGS</v>
@@ -43529,7 +43529,7 @@
         <v>Active</v>
       </c>
       <c r="K1232" t="str">
-        <v>AQUA PLAST GHAMELA 17 high durability ghamela.</v>
+        <v>AQUA PLAST GHAMELA 16 high durability ghamela.</v>
       </c>
     </row>
     <row r="1233">
@@ -43537,34 +43537,34 @@
         <v>1232</v>
       </c>
       <c r="B1233" t="str">
-        <v>FG-401364</v>
+        <v>FG-401579</v>
       </c>
       <c r="C1233" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1/2 15MM)</v>
+        <v>AQUA PLAST GHAMELA 17 (17 Inch)</v>
       </c>
       <c r="D1233" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE</v>
+        <v>AQUA PLAST GHAMELA 17</v>
       </c>
       <c r="E1233" t="str">
-        <v>Garden, Braided &amp; LDPE Pipes</v>
+        <v>HOUSEHOLD PRODUCTS</v>
       </c>
       <c r="F1233" t="str">
         <v>General</v>
       </c>
       <c r="G1233" t="str">
-        <v>1/2 15MM</v>
+        <v>17 Inch</v>
       </c>
       <c r="H1233" t="str">
-        <v>BDL</v>
+        <v>BAGS</v>
       </c>
       <c r="I1233" t="str">
-        <v>-</v>
+        <v>60</v>
       </c>
       <c r="J1233" t="str">
         <v>Active</v>
       </c>
       <c r="K1233" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE. Available sizes: 1/2 15MM, 3/4 20MM, 1 25MM, 1 1/4 32MM.</v>
+        <v>AQUA PLAST GHAMELA 17 high durability ghamela.</v>
       </c>
     </row>
     <row r="1234">
@@ -43572,10 +43572,10 @@
         <v>1233</v>
       </c>
       <c r="B1234" t="str">
-        <v>FG-401365</v>
+        <v>FG-401364</v>
       </c>
       <c r="C1234" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (3/4 20MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1/2 15MM)</v>
       </c>
       <c r="D1234" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43587,7 +43587,7 @@
         <v>General</v>
       </c>
       <c r="G1234" t="str">
-        <v>3/4 20MM</v>
+        <v>1/2 15MM</v>
       </c>
       <c r="H1234" t="str">
         <v>BDL</v>
@@ -43607,10 +43607,10 @@
         <v>1234</v>
       </c>
       <c r="B1235" t="str">
-        <v>FG-401366</v>
+        <v>FG-401365</v>
       </c>
       <c r="C1235" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1 25MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (3/4 20MM)</v>
       </c>
       <c r="D1235" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43622,7 +43622,7 @@
         <v>General</v>
       </c>
       <c r="G1235" t="str">
-        <v>1 25MM</v>
+        <v>3/4 20MM</v>
       </c>
       <c r="H1235" t="str">
         <v>BDL</v>
@@ -43642,10 +43642,10 @@
         <v>1235</v>
       </c>
       <c r="B1236" t="str">
-        <v>FG-401367</v>
+        <v>FG-401366</v>
       </c>
       <c r="C1236" t="str">
-        <v>GAP-ORA FLOW GARDEN PIPE (1 1/4 32MM)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1 25MM)</v>
       </c>
       <c r="D1236" t="str">
         <v>GAP-ORA FLOW GARDEN PIPE</v>
@@ -43657,7 +43657,7 @@
         <v>General</v>
       </c>
       <c r="G1236" t="str">
-        <v>1 1/4 32MM</v>
+        <v>1 25MM</v>
       </c>
       <c r="H1236" t="str">
         <v>BDL</v>
@@ -43677,13 +43677,13 @@
         <v>1236</v>
       </c>
       <c r="B1237" t="str">
-        <v>FG-401370</v>
+        <v>FG-401367</v>
       </c>
       <c r="C1237" t="str">
-        <v>GAP-ORA BRAIDED PIPE (15MM 1/2)</v>
+        <v>GAP-ORA FLOW GARDEN PIPE (1 1/4 32MM)</v>
       </c>
       <c r="D1237" t="str">
-        <v>GAP-ORA BRAIDED PIPE</v>
+        <v>GAP-ORA FLOW GARDEN PIPE</v>
       </c>
       <c r="E1237" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43692,7 +43692,7 @@
         <v>General</v>
       </c>
       <c r="G1237" t="str">
-        <v>15MM 1/2</v>
+        <v>1 1/4 32MM</v>
       </c>
       <c r="H1237" t="str">
         <v>BDL</v>
@@ -43704,7 +43704,7 @@
         <v>Active</v>
       </c>
       <c r="K1237" t="str">
-        <v>GAP-ORA BRAIDED PIPE.</v>
+        <v>GAP-ORA FLOW GARDEN PIPE. Available sizes: 1/2 15MM, 3/4 20MM, 1 25MM, 1 1/4 32MM.</v>
       </c>
     </row>
     <row r="1238">
@@ -43712,10 +43712,10 @@
         <v>1237</v>
       </c>
       <c r="B1238" t="str">
-        <v>FG-401371</v>
+        <v>FG-401370</v>
       </c>
       <c r="C1238" t="str">
-        <v>GAP-ORA BRAIDED PIPE (20MM 3/4)</v>
+        <v>GAP-ORA BRAIDED PIPE (15MM 1/2)</v>
       </c>
       <c r="D1238" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43727,7 +43727,7 @@
         <v>General</v>
       </c>
       <c r="G1238" t="str">
-        <v>20MM 3/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1238" t="str">
         <v>BDL</v>
@@ -43747,10 +43747,10 @@
         <v>1238</v>
       </c>
       <c r="B1239" t="str">
-        <v>FG-401372</v>
+        <v>FG-401371</v>
       </c>
       <c r="C1239" t="str">
-        <v>GAP-ORA BRAIDED PIPE (25MM 1)</v>
+        <v>GAP-ORA BRAIDED PIPE (20MM 3/4)</v>
       </c>
       <c r="D1239" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43762,7 +43762,7 @@
         <v>General</v>
       </c>
       <c r="G1239" t="str">
-        <v>25MM 1</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1239" t="str">
         <v>BDL</v>
@@ -43782,10 +43782,10 @@
         <v>1239</v>
       </c>
       <c r="B1240" t="str">
-        <v>FG-401373</v>
+        <v>FG-401372</v>
       </c>
       <c r="C1240" t="str">
-        <v>GAP-ORA BRAIDED PIPE (32MM 1 1/4)</v>
+        <v>GAP-ORA BRAIDED PIPE (25MM 1)</v>
       </c>
       <c r="D1240" t="str">
         <v>GAP-ORA BRAIDED PIPE</v>
@@ -43797,7 +43797,7 @@
         <v>General</v>
       </c>
       <c r="G1240" t="str">
-        <v>32MM 1 1/4</v>
+        <v>25MM 1</v>
       </c>
       <c r="H1240" t="str">
         <v>BDL</v>
@@ -43817,13 +43817,13 @@
         <v>1240</v>
       </c>
       <c r="B1241" t="str">
-        <v>FG-401355</v>
+        <v>FG-401373</v>
       </c>
       <c r="C1241" t="str">
-        <v>GARDEN FOAM PIPES (15MM 1/2)</v>
+        <v>GAP-ORA BRAIDED PIPE (32MM 1 1/4)</v>
       </c>
       <c r="D1241" t="str">
-        <v>GARDEN FOAM PIPES</v>
+        <v>GAP-ORA BRAIDED PIPE</v>
       </c>
       <c r="E1241" t="str">
         <v>Garden, Braided &amp; LDPE Pipes</v>
@@ -43832,7 +43832,7 @@
         <v>General</v>
       </c>
       <c r="G1241" t="str">
-        <v>15MM 1/2</v>
+        <v>32MM 1 1/4</v>
       </c>
       <c r="H1241" t="str">
         <v>BDL</v>
@@ -43844,7 +43844,7 @@
         <v>Active</v>
       </c>
       <c r="K1241" t="str">
-        <v>GARDEN FOAM PIPES.</v>
+        <v>GAP-ORA BRAIDED PIPE.</v>
       </c>
     </row>
     <row r="1242">
@@ -43852,10 +43852,10 @@
         <v>1241</v>
       </c>
       <c r="B1242" t="str">
-        <v>FG-401356</v>
+        <v>FG-401355</v>
       </c>
       <c r="C1242" t="str">
-        <v>GARDEN FOAM PIPES (20MM 3/4)</v>
+        <v>GARDEN FOAM PIPES (15MM 1/2)</v>
       </c>
       <c r="D1242" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43867,7 +43867,7 @@
         <v>General</v>
       </c>
       <c r="G1242" t="str">
-        <v>20MM 3/4</v>
+        <v>15MM 1/2</v>
       </c>
       <c r="H1242" t="str">
         <v>BDL</v>
@@ -43887,10 +43887,10 @@
         <v>1242</v>
       </c>
       <c r="B1243" t="str">
-        <v>FG-401369</v>
+        <v>FG-401356</v>
       </c>
       <c r="C1243" t="str">
-        <v>GARDEN FOAM PIPES (20MM 3/4 20MTR)</v>
+        <v>GARDEN FOAM PIPES (20MM 3/4)</v>
       </c>
       <c r="D1243" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43902,7 +43902,7 @@
         <v>General</v>
       </c>
       <c r="G1243" t="str">
-        <v>20MM 3/4 20MTR</v>
+        <v>20MM 3/4</v>
       </c>
       <c r="H1243" t="str">
         <v>BDL</v>
@@ -43922,10 +43922,10 @@
         <v>1243</v>
       </c>
       <c r="B1244" t="str">
-        <v>FG-401357</v>
+        <v>FG-401369</v>
       </c>
       <c r="C1244" t="str">
-        <v>GARDEN FOAM PIPES (25MM 1)</v>
+        <v>GARDEN FOAM PIPES (20MM 3/4 20MTR)</v>
       </c>
       <c r="D1244" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43937,7 +43937,7 @@
         <v>General</v>
       </c>
       <c r="G1244" t="str">
-        <v>25MM 1</v>
+        <v>20MM 3/4 20MTR</v>
       </c>
       <c r="H1244" t="str">
         <v>BDL</v>
@@ -43957,10 +43957,10 @@
         <v>1244</v>
       </c>
       <c r="B1245" t="str">
-        <v>FG-401358</v>
+        <v>FG-401357</v>
       </c>
       <c r="C1245" t="str">
-        <v>GARDEN FOAM PIPES (32MM 1 1/4)</v>
+        <v>GARDEN FOAM PIPES (25MM 1)</v>
       </c>
       <c r="D1245" t="str">
         <v>GARDEN FOAM PIPES</v>
@@ -43972,7 +4